--- a/Documentation/HoferL-JournalPlanif-M5.xlsx
+++ b/Documentation/HoferL-JournalPlanif-M5.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Journal" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SommeParJours" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Plannification" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PlanificationExemple" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="Journal" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="SommeParJours" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Plannification" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="PlanificationExemple" sheetId="4" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$B$2:$H$30</definedName>
@@ -21,8 +21,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
   <si>
     <t>date</t>
   </si>
@@ -169,6 +191,12 @@
   </si>
   <si>
     <t xml:space="preserve">Finalisation de la maquette + test</t>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programmation des classes + test SQLite</t>
   </si>
   <si>
     <t>Phases</t>
@@ -194,9 +222,6 @@
   </si>
   <si>
     <t>02.03.2026</t>
-  </si>
-  <si>
-    <t>03.03.2026</t>
   </si>
   <si>
     <t>16.03.2026</t>
@@ -2301,7 +2326,7 @@
             <c:strRef>
               <c:f>SommeParJours!$A$2:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>20.01.2026</c:v>
                 </c:pt>
@@ -2331,6 +2356,15 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>12.02.2026</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>13.02.2026</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>24.02.2026</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>03.03.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2370,6 +2404,15 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0.08333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.0625</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2692,8 +2735,8 @@
   </c:chart>
   <c:spPr bwMode="auto">
     <a:xfrm rot="0">
-      <a:off x="0" y="0"/>
-      <a:ext cx="0" cy="0"/>
+      <a:off x="1973108" y="70845"/>
+      <a:ext cx="5882350" cy="3850639"/>
     </a:xfrm>
     <a:prstGeom prst="rect">
       <a:avLst/>
@@ -3391,15 +3434,15 @@
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>512609</xdr:colOff>
+      <xdr:colOff>68108</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>70846</xdr:rowOff>
+      <xdr:rowOff>70845</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>383626</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>701125</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>9886</xdr:rowOff>
+      <xdr:rowOff>9885</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3409,8 +3452,8 @@
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm rot="0">
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off x="1973108" y="70845"/>
+        <a:ext cx="5882350" cy="3850639"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3424,8 +3467,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E25">
-  <autoFilter ref="B2:E25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E26">
+  <autoFilter ref="B2:E26"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -3986,7 +4029,7 @@
       </c>
       <c r="I3" s="9">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.065217391304347824</v>
+        <v>0.056074766355140186</v>
       </c>
       <c r="J3" s="10"/>
     </row>
@@ -4012,7 +4055,7 @@
       </c>
       <c r="I4" s="9">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.065217391304347824</v>
+        <v>0.056074766355140186</v>
       </c>
     </row>
     <row r="5" ht="28.5">
@@ -4037,7 +4080,7 @@
       </c>
       <c r="I5" s="9">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.13043478260869565</v>
+        <v>0.11214953271028037</v>
       </c>
     </row>
     <row r="6">
@@ -4058,11 +4101,11 @@
       </c>
       <c r="H6" s="8">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>11</v>
+        <v>15.499999999999998</v>
       </c>
       <c r="I6" s="9">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.2391304347826087</v>
+        <v>0.28971962616822428</v>
       </c>
     </row>
     <row r="7">
@@ -4087,7 +4130,7 @@
       </c>
       <c r="I7" s="9">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.4565217391304347</v>
+        <v>0.39252336448598124</v>
       </c>
     </row>
     <row r="8" ht="28.5">
@@ -4108,11 +4151,11 @@
       </c>
       <c r="H8" s="8">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I8" s="9">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.043478260869565216</v>
+        <v>0.093457943925233641</v>
       </c>
     </row>
     <row r="9">
@@ -4183,7 +4226,7 @@
       </c>
       <c r="H11" s="8">
         <f>SUM(H3:H10)</f>
-        <v>46</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="12">
@@ -4371,24 +4414,32 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C25" s="4">
         <v>0.125</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="6" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="6"/>
+      <c r="B26" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="4">
+        <v>0.125</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="27">
       <c r="B27" s="3"/>
@@ -4718,7 +4769,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00770051-00AC-442C-B38D-008B00050008}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00D900E8-00A9-48EE-A1ED-003400B10084}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -4732,7 +4783,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" customWidth="1" min="3" max="3" style="17" width="5.6640625"/>
     <col bestFit="1" customWidth="1" min="4" max="4" width="12.21875"/>
@@ -4750,8 +4801,8 @@
       <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="str">
-        <f t="array" ref="A2:A13">_xlfn.UNIQUE(Journal[date])</f>
+      <c r="A2" s="18" t="str" cm="1">
+        <f t="array" ref="A2:A14">_xlfn.UNIQUE(Journal[date])</f>
         <v>20.01.2026</v>
       </c>
       <c r="B2" s="19">
@@ -4882,7 +4933,14 @@
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="18"/>
+      <c r="A14" s="18" t="str">
+        <f/>
+        <v>03.03.2026</v>
+      </c>
+      <c r="B14" s="19">
+        <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
+        <v>0.125</v>
+      </c>
       <c r="C14"/>
     </row>
     <row r="15">
@@ -6391,7 +6449,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="2" max="2" width="4.33203125"/>
     <col bestFit="1" min="3" max="3" width="35.77734375"/>
@@ -6408,16 +6466,16 @@
   <sheetData>
     <row r="1" s="24" customFormat="1" ht="66.599999999999994" customHeight="1">
       <c r="B1" s="25" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D1" s="27" t="s">
         <v>5</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F1" s="28" t="s">
         <v>11</v>
@@ -6426,7 +6484,7 @@
         <v>17</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I1" s="27" t="s">
         <v>22</v>
@@ -6435,85 +6493,85 @@
         <v>37</v>
       </c>
       <c r="K1" s="27" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L1" s="31" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M1" s="27" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N1" s="29" t="s">
         <v>47</v>
       </c>
       <c r="O1" s="30" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P1" s="27" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="Q1" s="27" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R1" s="27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S1" s="27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T1" s="27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U1" s="27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="V1" s="29" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="W1" s="32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="X1" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Y1" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Z1" s="29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AA1" s="33" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AB1" s="34" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AC1" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AD1" s="31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AE1" s="35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF1" s="36" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AG1" s="37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH1" s="37" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI1" s="37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AJ1" s="37" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AK1" s="34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL1" s="38"/>
       <c r="AM1" s="38"/>
@@ -6609,7 +6667,7 @@
     <row r="4" ht="12" customHeight="1">
       <c r="B4" s="39"/>
       <c r="C4" s="40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D4" s="41"/>
       <c r="E4" s="41"/>
@@ -6765,7 +6823,7 @@
     <row r="8" ht="12" customHeight="1">
       <c r="B8" s="39"/>
       <c r="C8" s="40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8" s="55"/>
       <c r="E8" s="55"/>
@@ -6843,7 +6901,7 @@
     <row r="10" ht="12" customHeight="1">
       <c r="B10" s="39"/>
       <c r="C10" s="40" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D10" s="41"/>
       <c r="E10" s="41"/>
@@ -6921,7 +6979,7 @@
     <row r="12" ht="12" customHeight="1">
       <c r="B12" s="39"/>
       <c r="C12" s="40" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D12" s="41"/>
       <c r="E12" s="41"/>
@@ -6998,10 +7056,10 @@
     </row>
     <row r="14" ht="12" customHeight="1">
       <c r="B14" s="56" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" s="55"/>
       <c r="E14" s="55"/>
@@ -7079,7 +7137,7 @@
     <row r="16" ht="12" customHeight="1">
       <c r="B16" s="56"/>
       <c r="C16" s="57" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D16" s="55"/>
       <c r="E16" s="55"/>
@@ -7154,13 +7212,13 @@
       <c r="AJ17" s="59"/>
       <c r="AK17" s="59"/>
       <c r="AN17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
       <c r="B18" s="56"/>
       <c r="C18" s="57" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D18" s="55"/>
       <c r="E18" s="55"/>
@@ -7238,7 +7296,7 @@
     <row r="20" ht="12" customHeight="1">
       <c r="B20" s="56"/>
       <c r="C20" s="57" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D20" s="59"/>
       <c r="E20" s="59"/>
@@ -7316,7 +7374,7 @@
     <row r="22" ht="12" customHeight="1">
       <c r="B22" s="56"/>
       <c r="C22" s="57" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D22" s="59"/>
       <c r="E22" s="59"/>
@@ -7394,7 +7452,7 @@
     <row r="24" ht="12" customHeight="1">
       <c r="B24" s="56"/>
       <c r="C24" s="57" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D24" s="59"/>
       <c r="E24" s="59"/>
@@ -7471,10 +7529,10 @@
     </row>
     <row r="26" ht="12" customHeight="1">
       <c r="B26" s="39" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C26" s="40" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D26" s="41"/>
       <c r="E26" s="41"/>
@@ -7552,7 +7610,7 @@
     <row r="28" ht="12" customHeight="1">
       <c r="B28" s="39"/>
       <c r="C28" s="40" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D28" s="41"/>
       <c r="E28" s="41"/>
@@ -7630,7 +7688,7 @@
     <row r="30" ht="12" customHeight="1">
       <c r="B30" s="39"/>
       <c r="C30" s="40" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D30" s="41"/>
       <c r="E30" s="41"/>
@@ -7708,7 +7766,7 @@
     <row r="32" ht="12" customHeight="1">
       <c r="B32" s="39"/>
       <c r="C32" s="40" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D32" s="41"/>
       <c r="E32" s="41"/>
@@ -7785,10 +7843,10 @@
     </row>
     <row r="34" ht="12" customHeight="1">
       <c r="B34" s="56" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C34" s="66" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="59"/>
@@ -7866,7 +7924,7 @@
     <row r="36" ht="12" customHeight="1">
       <c r="B36" s="56"/>
       <c r="C36" s="66" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D36" s="59"/>
       <c r="E36" s="59"/>
@@ -7944,7 +8002,7 @@
     <row r="38" ht="12" customHeight="1">
       <c r="B38" s="56"/>
       <c r="C38" s="66" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D38" s="59"/>
       <c r="E38" s="59"/>
@@ -8022,7 +8080,7 @@
     <row r="40" ht="12" customHeight="1">
       <c r="B40" s="56"/>
       <c r="C40" s="66" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
@@ -8102,7 +8160,7 @@
         <v>21</v>
       </c>
       <c r="C42" s="68" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D42" s="41"/>
       <c r="E42" s="41"/>
@@ -8180,7 +8238,7 @@
     <row r="44" ht="12" customHeight="1">
       <c r="B44" s="39"/>
       <c r="C44" s="68" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D44" s="41"/>
       <c r="E44" s="41"/>
@@ -8257,7 +8315,7 @@
     </row>
     <row r="46" ht="12" customHeight="1">
       <c r="B46" s="56" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C46" s="57" t="s">
         <v>24</v>
@@ -8335,14 +8393,14 @@
       <c r="AJ47" s="59"/>
       <c r="AK47" s="59"/>
       <c r="AN47" s="69" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO47" s="55"/>
     </row>
     <row r="48" ht="12" customHeight="1">
       <c r="B48" s="56"/>
       <c r="C48" s="57" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D48" s="59"/>
       <c r="E48" s="59"/>
@@ -8379,7 +8437,7 @@
       <c r="AJ48" s="59"/>
       <c r="AK48" s="70"/>
       <c r="AN48" s="69" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AO48" s="54"/>
     </row>
@@ -8421,28 +8479,19 @@
       <c r="AJ49" s="59"/>
       <c r="AK49" s="59"/>
       <c r="AN49" s="69" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AO49" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="B34:B41"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="B26:B33"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B2:B13"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C12:C13"/>
     <mergeCell ref="B14:B25"/>
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="C16:C17"/>
@@ -8450,13 +8499,22 @@
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B2:B13"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="B26:B33"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B34:B41"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="C48:C49"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -8490,37 +8548,37 @@
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
       <c r="B2" s="72" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C2" s="73" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D2" s="74" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E2" s="75" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F2" s="76" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G2" s="76"/>
       <c r="H2" s="76"/>
       <c r="I2" s="75"/>
       <c r="J2" s="76" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K2" s="76"/>
       <c r="L2" s="76"/>
       <c r="M2" s="75"/>
       <c r="N2" s="76" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O2" s="76"/>
       <c r="P2" s="76"/>
       <c r="Q2" s="75"/>
       <c r="R2" s="76" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="S2" s="77"/>
       <c r="AD2" s="21"/>
@@ -8529,7 +8587,7 @@
       <c r="B3" s="78"/>
       <c r="C3" s="79"/>
       <c r="D3" s="80" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E3" s="81">
         <v>4</v>
@@ -8577,15 +8635,15 @@
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
       <c r="B4" s="85" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C4" s="73" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D4" s="86"/>
       <c r="E4" s="87"/>
@@ -8604,7 +8662,7 @@
       <c r="R4" s="90"/>
       <c r="S4" s="91"/>
       <c r="U4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
@@ -8630,7 +8688,7 @@
     <row r="6" ht="12" customHeight="1">
       <c r="B6" s="85"/>
       <c r="C6" s="100" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D6" s="101"/>
       <c r="E6" s="102"/>
@@ -8649,7 +8707,7 @@
       <c r="R6" s="106"/>
       <c r="S6" s="107"/>
       <c r="U6" s="108" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="V6" s="108"/>
     </row>
@@ -8673,13 +8731,13 @@
       <c r="R7" s="98"/>
       <c r="S7" s="99"/>
       <c r="U7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
       <c r="B8" s="85"/>
       <c r="C8" s="100" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D8" s="101"/>
       <c r="E8" s="102"/>
@@ -8698,7 +8756,7 @@
       <c r="R8" s="106"/>
       <c r="S8" s="107"/>
       <c r="U8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
@@ -8724,7 +8782,7 @@
     <row r="10" ht="12" customHeight="1">
       <c r="B10" s="85"/>
       <c r="C10" s="100" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D10" s="101"/>
       <c r="E10" s="102"/>
@@ -8765,10 +8823,10 @@
     </row>
     <row r="12" ht="12" customHeight="1">
       <c r="B12" s="72" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C12" s="73" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D12" s="86"/>
       <c r="E12" s="87"/>
@@ -8810,7 +8868,7 @@
     <row r="14" ht="12" customHeight="1">
       <c r="B14" s="85"/>
       <c r="C14" s="100" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D14" s="119"/>
       <c r="E14" s="102"/>
@@ -8852,7 +8910,7 @@
     <row r="16" ht="12" customHeight="1">
       <c r="B16" s="85"/>
       <c r="C16" s="100" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D16" s="101"/>
       <c r="E16" s="102"/>
@@ -8893,10 +8951,10 @@
     </row>
     <row r="18" ht="12" customHeight="1">
       <c r="B18" s="74" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C18" s="73" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D18" s="86"/>
       <c r="E18" s="87"/>
@@ -8938,7 +8996,7 @@
     <row r="20" ht="12" customHeight="1">
       <c r="B20" s="85"/>
       <c r="C20" s="100" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D20" s="101"/>
       <c r="E20" s="102"/>
@@ -8980,7 +9038,7 @@
     <row r="22" ht="12" customHeight="1">
       <c r="B22" s="85"/>
       <c r="C22" s="100" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D22" s="101"/>
       <c r="E22" s="102"/>
@@ -9021,10 +9079,10 @@
     </row>
     <row r="24" ht="12" customHeight="1">
       <c r="B24" s="74" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C24" s="73" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D24" s="86"/>
       <c r="E24" s="87"/>
@@ -9066,7 +9124,7 @@
     <row r="26" ht="12" customHeight="1">
       <c r="B26" s="85"/>
       <c r="C26" s="100" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D26" s="101"/>
       <c r="E26" s="102"/>
@@ -9108,7 +9166,7 @@
     <row r="28" ht="12" customHeight="1">
       <c r="B28" s="85"/>
       <c r="C28" s="100" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D28" s="101"/>
       <c r="E28" s="102"/>
@@ -9152,7 +9210,7 @@
         <v>12</v>
       </c>
       <c r="C30" s="132" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D30" s="86"/>
       <c r="E30" s="133"/>
@@ -9236,7 +9294,7 @@
     <row r="34" ht="12" customHeight="1">
       <c r="B34" s="138"/>
       <c r="C34" s="92" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D34" s="124"/>
       <c r="E34" s="152"/>
@@ -9256,7 +9314,7 @@
       <c r="S34" s="156"/>
       <c r="U34" s="157"/>
       <c r="V34" s="158" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
@@ -9280,7 +9338,7 @@
       <c r="S35" s="116"/>
       <c r="U35" s="165"/>
       <c r="V35" s="166" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/HoferL-JournalPlanif-M5.xlsx
+++ b/Documentation/HoferL-JournalPlanif-M5.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="1" state="visible" r:id="rId2"/>
@@ -2039,66 +2039,11 @@
           <c:cat>
             <c:strRef>
               <c:f>Journal!$G$3:$G$10</c:f>
-              <c:strCache>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>Cours</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Plannification</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Recherche</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Maquettage</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Documentation</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Programmation</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Tests</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Présentation</c:v>
-                </c:pt>
-              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Journal!$I$3:$I$10</c:f>
-              <c:numCache>
-                <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>0.06521739130434782</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.06521739130434782</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.13043478260869565</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.2391304347826087</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.4565217391304347</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.043478260869565216</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:f>Journal!$H$3:$H$10</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4769,7 +4714,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00D900E8-00A9-48EE-A1ED-003400B10084}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00CC0040-003C-41BA-B267-00AB00D30038}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -6796,7 +6741,7 @@
       <c r="L7" s="45"/>
       <c r="M7" s="41"/>
       <c r="N7" s="46"/>
-      <c r="O7" s="47"/>
+      <c r="O7" s="53"/>
       <c r="P7" s="41"/>
       <c r="Q7" s="41"/>
       <c r="R7" s="41"/>
@@ -6864,17 +6809,17 @@
       <c r="B9" s="39"/>
       <c r="C9" s="40"/>
       <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="49"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="51"/>
       <c r="G9" s="46"/>
       <c r="H9" s="47"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="54"/>
       <c r="K9" s="41"/>
       <c r="L9" s="45"/>
-      <c r="M9" s="41"/>
+      <c r="M9" s="54"/>
       <c r="N9" s="46"/>
-      <c r="O9" s="47"/>
+      <c r="O9" s="53"/>
       <c r="P9" s="41"/>
       <c r="Q9" s="41"/>
       <c r="R9" s="41"/>
@@ -7896,9 +7841,9 @@
       <c r="K35" s="67"/>
       <c r="L35" s="45"/>
       <c r="M35" s="59"/>
-      <c r="N35" s="60"/>
+      <c r="N35" s="52"/>
       <c r="O35" s="58"/>
-      <c r="P35" s="59"/>
+      <c r="P35" s="54"/>
       <c r="Q35" s="59"/>
       <c r="R35" s="59"/>
       <c r="S35" s="59"/>
@@ -7976,7 +7921,7 @@
       <c r="M37" s="59"/>
       <c r="N37" s="60"/>
       <c r="O37" s="58"/>
-      <c r="P37" s="59"/>
+      <c r="P37" s="54"/>
       <c r="Q37" s="59"/>
       <c r="R37" s="59"/>
       <c r="S37" s="59"/>

--- a/Documentation/HoferL-JournalPlanif-M5.xlsx
+++ b/Documentation/HoferL-JournalPlanif-M5.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
   <si>
     <t>date</t>
   </si>
@@ -209,6 +209,9 @@
   </si>
   <si>
     <t xml:space="preserve">Documentation de la maquette</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implémentation des police, couleur, themes et propriété d'affichage. Reflexion sur la possibilité d'avoir un thème sombre ET claire.</t>
   </si>
   <si>
     <t>Phases</t>
@@ -1435,7 +1438,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="169">
+  <cellXfs count="168">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1470,9 +1473,6 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4209,7 +4209,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>14816</xdr:colOff>
+      <xdr:colOff>14815</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>131232</xdr:rowOff>
     </xdr:to>
@@ -4273,8 +4273,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E29">
-  <autoFilter ref="B2:E29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E30">
+  <autoFilter ref="B2:E30"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="I3" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.050000000000000003</v>
+        <v>4.6875e-002</v>
       </c>
       <c r="J3" s="11" t="str" cm="1">
         <f t="array" ref="J3:J8">_xlfn._xlws.FILTER(G3:G10,H3:H10&gt;0)</f>
@@ -4853,7 +4853,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="5">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>8</v>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="I4" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.050000000000000003</v>
+        <v>4.6875e-002</v>
       </c>
       <c r="J4" s="3" t="str">
         <f/>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="I5" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.10000000000000001</v>
+        <v>9.375e-002</v>
       </c>
       <c r="J5" s="3" t="str">
         <f/>
@@ -4919,7 +4919,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="5">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>8</v>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="I6" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.28333333333333333</v>
+        <v>0.265625</v>
       </c>
       <c r="J6" s="3" t="str">
         <f/>
@@ -4952,7 +4952,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="5">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>8</v>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="I7" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.43333333333333335</v>
+        <v>0.40625</v>
       </c>
       <c r="J7" s="3" t="str">
         <f/>
@@ -4998,11 +4998,11 @@
       </c>
       <c r="H8" s="9">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I8" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.083333333333333329</v>
+        <v>0.140625</v>
       </c>
       <c r="J8" s="3" t="str">
         <f/>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="K8" s="12">
         <f/>
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -5045,7 +5045,7 @@
         <v>22</v>
       </c>
       <c r="C10" s="5">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>12</v>
@@ -5072,7 +5072,7 @@
         <v>22</v>
       </c>
       <c r="C11" s="5">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>12</v>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="H11" s="9">
         <f>SUM(H3:H10)</f>
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -5095,7 +5095,7 @@
         <v>22</v>
       </c>
       <c r="C12" s="5">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>10</v>
@@ -5110,7 +5110,7 @@
         <v>22</v>
       </c>
       <c r="C13" s="5">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>12</v>
@@ -5125,7 +5125,7 @@
         <v>29</v>
       </c>
       <c r="C14" s="5">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>12</v>
@@ -5181,7 +5181,7 @@
         <v>35</v>
       </c>
       <c r="C18" s="5">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>10</v>
@@ -5195,7 +5195,7 @@
         <v>37</v>
       </c>
       <c r="C19" s="5">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>12</v>
@@ -5209,7 +5209,7 @@
         <v>39</v>
       </c>
       <c r="C20" s="5">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>19</v>
@@ -5223,7 +5223,7 @@
         <v>39</v>
       </c>
       <c r="C21" s="5">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>15</v>
@@ -5251,7 +5251,7 @@
         <v>43</v>
       </c>
       <c r="C23" s="5">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>15</v>
@@ -5265,7 +5265,7 @@
         <v>45</v>
       </c>
       <c r="C24" s="5">
-        <v>0.0625</v>
+        <v>6.25e-002</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>15</v>
@@ -5303,52 +5303,60 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="4" t="s">
         <v>49</v>
       </c>
       <c r="C27" s="5">
-        <v>0.083333333333333329</v>
-      </c>
-      <c r="D27" s="16" t="s">
+        <v>8.3333333333333329e-002</v>
+      </c>
+      <c r="D27" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" s="7" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="15" t="s">
+    <row r="28" ht="28.5">
+      <c r="B28" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C28" s="5">
-        <v>0.0625</v>
-      </c>
-      <c r="D28" s="16" t="s">
+        <v>6.25e-002</v>
+      </c>
+      <c r="D28" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E28" s="17" t="s">
+      <c r="E28" s="7" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C29" s="5">
         <v>0.125</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D29" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E29" s="17" t="s">
+      <c r="E29" s="7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="4"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="7"/>
+    <row r="30" ht="42.75">
+      <c r="B30" s="4">
+        <v>46087</v>
+      </c>
+      <c r="C30" s="5">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="31">
       <c r="B31" s="4"/>
@@ -5453,163 +5461,163 @@
       <c r="E47" s="7"/>
     </row>
     <row r="48">
-      <c r="B48" s="18"/>
+      <c r="B48" s="17"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
     </row>
     <row r="49">
-      <c r="B49" s="18"/>
+      <c r="B49" s="17"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
     </row>
     <row r="50">
-      <c r="B50" s="18"/>
+      <c r="B50" s="17"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
     </row>
     <row r="51">
-      <c r="B51" s="18"/>
+      <c r="B51" s="17"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
     </row>
     <row r="52">
-      <c r="B52" s="18"/>
+      <c r="B52" s="17"/>
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
     </row>
     <row r="53">
-      <c r="B53" s="18"/>
+      <c r="B53" s="17"/>
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
     </row>
     <row r="54">
-      <c r="B54" s="18"/>
+      <c r="B54" s="17"/>
       <c r="C54" s="6"/>
       <c r="D54" s="6"/>
       <c r="E54" s="6"/>
     </row>
     <row r="55">
-      <c r="B55" s="18"/>
+      <c r="B55" s="17"/>
       <c r="C55" s="6"/>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
     </row>
     <row r="56">
-      <c r="B56" s="18"/>
+      <c r="B56" s="17"/>
       <c r="C56" s="6"/>
       <c r="D56" s="6"/>
       <c r="E56" s="6"/>
     </row>
     <row r="57">
-      <c r="B57" s="18"/>
+      <c r="B57" s="17"/>
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
       <c r="E57" s="6"/>
     </row>
     <row r="58">
-      <c r="B58" s="18"/>
+      <c r="B58" s="17"/>
       <c r="C58" s="6"/>
       <c r="D58" s="6"/>
       <c r="E58" s="6"/>
     </row>
     <row r="59">
-      <c r="B59" s="18"/>
+      <c r="B59" s="17"/>
       <c r="C59" s="6"/>
       <c r="D59" s="6"/>
       <c r="E59" s="6"/>
     </row>
     <row r="60">
-      <c r="B60" s="18"/>
+      <c r="B60" s="17"/>
       <c r="C60" s="6"/>
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
     </row>
     <row r="61">
-      <c r="B61" s="18"/>
+      <c r="B61" s="17"/>
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
     </row>
     <row r="62">
-      <c r="B62" s="18"/>
+      <c r="B62" s="17"/>
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
     </row>
     <row r="63">
-      <c r="B63" s="18"/>
+      <c r="B63" s="17"/>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
     </row>
     <row r="64">
-      <c r="B64" s="18"/>
+      <c r="B64" s="17"/>
       <c r="C64" s="6"/>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
     </row>
     <row r="65">
-      <c r="B65" s="18"/>
+      <c r="B65" s="17"/>
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
     </row>
     <row r="66">
-      <c r="B66" s="18"/>
+      <c r="B66" s="17"/>
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
     </row>
     <row r="67">
-      <c r="B67" s="18"/>
+      <c r="B67" s="17"/>
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
     </row>
     <row r="68">
-      <c r="B68" s="18"/>
+      <c r="B68" s="17"/>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
     </row>
     <row r="69">
-      <c r="B69" s="18"/>
+      <c r="B69" s="17"/>
       <c r="C69" s="6"/>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
     </row>
     <row r="70">
-      <c r="B70" s="18"/>
+      <c r="B70" s="17"/>
       <c r="C70" s="6"/>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
     </row>
     <row r="71">
-      <c r="B71" s="18"/>
+      <c r="B71" s="17"/>
       <c r="C71" s="6"/>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
     </row>
     <row r="72">
-      <c r="B72" s="18"/>
+      <c r="B72" s="17"/>
       <c r="C72" s="6"/>
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
     </row>
     <row r="73">
-      <c r="B73" s="18"/>
+      <c r="B73" s="17"/>
       <c r="C73" s="6"/>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
     </row>
     <row r="74">
-      <c r="B74" s="18"/>
+      <c r="B74" s="17"/>
       <c r="C74" s="6"/>
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
@@ -5666,7 +5674,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00C400A3-007D-4F76-915F-000C0016009F}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00F90069-000C-4FB8-B761-00BB00FB0041}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -5682,7 +5690,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="3" max="3" style="19" width="5.6640625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" style="18" width="5.6640625"/>
     <col bestFit="1" customWidth="1" min="4" max="4" width="12.21875"/>
     <col bestFit="1" customWidth="1" min="5" max="5" width="9.5546875"/>
     <col bestFit="1" customWidth="1" min="6" max="6" width="11.109375"/>
@@ -5698,1645 +5706,1648 @@
       <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="str" cm="1">
-        <f t="array" ref="A2:A15">_xlfn.UNIQUE(Journal[date])</f>
+      <c r="A2" s="19" t="str" cm="1">
+        <f t="array" ref="A2:A16">_xlfn.UNIQUE(Journal[date])</f>
         <v>20.01.2026</v>
       </c>
-      <c r="B2" s="21">
+      <c r="B2" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A2,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C2" s="21"/>
+      <c r="C2" s="20"/>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="str">
+      <c r="A3" s="19" t="str">
         <f/>
         <v>27.01.2026</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="str">
+      <c r="A4" s="19" t="str">
         <f/>
         <v>30.01.2026</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C4"/>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="str">
+      <c r="A5" s="19" t="str">
         <f/>
         <v>03.02.2026</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0.25</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="str">
+      <c r="A6" s="19" t="str">
         <f/>
         <v>04.02.2026</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="str">
+      <c r="A7" s="19" t="str">
         <f/>
         <v>06.02.2026</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C7"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="str">
+      <c r="A8" s="19" t="str">
         <f/>
         <v>08.02.2026</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="str">
+      <c r="A9" s="19" t="str">
         <f/>
         <v>09.02.2026</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="str">
+      <c r="A10" s="19" t="str">
         <f/>
         <v>10.02.2026</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="str">
+      <c r="A11" s="19" t="str">
         <f/>
         <v>12.02.2026</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="str">
+      <c r="A12" s="19" t="str">
         <f/>
         <v>13.02.2026</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
-        <v>0.0625</v>
+        <v>6.25e-002</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="str">
+      <c r="A13" s="19" t="str">
         <f/>
         <v>24.02.2026</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0.125</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="str">
+      <c r="A14" s="19" t="str">
         <f/>
         <v>03.03.2026</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="str">
+      <c r="A15" s="19" t="str">
         <f/>
         <v>05.03.2026</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="20"/>
+      <c r="A16" s="19">
+        <f/>
+        <v>46087</v>
+      </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="20"/>
+      <c r="A17" s="19"/>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="20"/>
+      <c r="A18" s="19"/>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="20"/>
+      <c r="A19" s="19"/>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="20"/>
+      <c r="A20" s="19"/>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="20"/>
+      <c r="A21" s="19"/>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="20"/>
+      <c r="A22" s="19"/>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="20"/>
+      <c r="A23" s="19"/>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="20"/>
+      <c r="A24" s="19"/>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="20"/>
+      <c r="A25" s="19"/>
       <c r="C25"/>
     </row>
     <row r="26">
-      <c r="A26" s="20"/>
-      <c r="C26" s="22">
+      <c r="A26" s="19"/>
+      <c r="C26" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20"/>
-      <c r="C27" s="22">
+      <c r="A27" s="19"/>
+      <c r="C27" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20"/>
-      <c r="C28" s="22">
+      <c r="A28" s="19"/>
+      <c r="C28" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="20"/>
-      <c r="C29" s="22">
+      <c r="A29" s="19"/>
+      <c r="C29" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="20"/>
-      <c r="C30" s="22">
+      <c r="A30" s="19"/>
+      <c r="C30" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20"/>
-      <c r="C31" s="22">
+      <c r="A31" s="19"/>
+      <c r="C31" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="20"/>
-      <c r="C32" s="22">
+      <c r="A32" s="19"/>
+      <c r="C32" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="20"/>
-      <c r="C33" s="22">
+      <c r="A33" s="19"/>
+      <c r="C33" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20"/>
-      <c r="C34" s="22">
+      <c r="A34" s="19"/>
+      <c r="C34" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20"/>
-      <c r="C35" s="22">
+      <c r="A35" s="19"/>
+      <c r="C35" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="20"/>
-      <c r="C36" s="22">
+      <c r="A36" s="19"/>
+      <c r="C36" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="20"/>
-      <c r="C37" s="22">
+      <c r="A37" s="19"/>
+      <c r="C37" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="20"/>
-      <c r="C38" s="22">
+      <c r="A38" s="19"/>
+      <c r="C38" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="20"/>
-      <c r="C39" s="22">
+      <c r="A39" s="19"/>
+      <c r="C39" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="20"/>
-      <c r="B40" s="21" t="str">
+      <c r="A40" s="19"/>
+      <c r="B40" s="20" t="str">
         <f t="shared" ref="B40:B103" si="0">IF(C40&gt;0,C40,"")</f>
         <v/>
       </c>
-      <c r="C40" s="22">
+      <c r="C40" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="20"/>
-      <c r="B41" s="21" t="str">
+      <c r="A41" s="19"/>
+      <c r="B41" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="22">
+      <c r="C41" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="23"/>
-      <c r="B42" s="21" t="str">
+      <c r="A42" s="22"/>
+      <c r="B42" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="22">
+      <c r="C42" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="23"/>
-      <c r="B43" s="21" t="str">
+      <c r="A43" s="22"/>
+      <c r="B43" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="22">
+      <c r="C43" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="23"/>
-      <c r="B44" s="21" t="str">
+      <c r="A44" s="22"/>
+      <c r="B44" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="22">
+      <c r="C44" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="23"/>
-      <c r="B45" s="21" t="str">
+      <c r="A45" s="22"/>
+      <c r="B45" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="22">
+      <c r="C45" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="23"/>
-      <c r="B46" s="21" t="str">
+      <c r="A46" s="22"/>
+      <c r="B46" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="22">
+      <c r="C46" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="24"/>
-      <c r="B47" s="21" t="str">
+      <c r="A47" s="23"/>
+      <c r="B47" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="22">
+      <c r="C47" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="24"/>
-      <c r="B48" s="21" t="str">
+      <c r="A48" s="23"/>
+      <c r="B48" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="22">
+      <c r="C48" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="24"/>
-      <c r="B49" s="21" t="str">
+      <c r="A49" s="23"/>
+      <c r="B49" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C49" s="22">
+      <c r="C49" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="24"/>
-      <c r="B50" s="21" t="str">
+      <c r="A50" s="23"/>
+      <c r="B50" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C50" s="22">
+      <c r="C50" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="24"/>
-      <c r="B51" s="21" t="str">
+      <c r="A51" s="23"/>
+      <c r="B51" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C51" s="22">
+      <c r="C51" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="24"/>
-      <c r="B52" s="21" t="str">
+      <c r="A52" s="23"/>
+      <c r="B52" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C52" s="22">
+      <c r="C52" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="24"/>
-      <c r="B53" s="21" t="str">
+      <c r="A53" s="23"/>
+      <c r="B53" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C53" s="22">
+      <c r="C53" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="24"/>
-      <c r="B54" s="21" t="str">
+      <c r="A54" s="23"/>
+      <c r="B54" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C54" s="22">
+      <c r="C54" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="24"/>
-      <c r="B55" s="21" t="str">
+      <c r="A55" s="23"/>
+      <c r="B55" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C55" s="22">
+      <c r="C55" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="24"/>
-      <c r="B56" s="21" t="str">
+      <c r="A56" s="23"/>
+      <c r="B56" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C56" s="22">
+      <c r="C56" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="24"/>
-      <c r="B57" s="21" t="str">
+      <c r="A57" s="23"/>
+      <c r="B57" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C57" s="22">
+      <c r="C57" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="24"/>
-      <c r="B58" s="21" t="str">
+      <c r="A58" s="23"/>
+      <c r="B58" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C58" s="22">
+      <c r="C58" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="24"/>
-      <c r="B59" s="21" t="str">
+      <c r="A59" s="23"/>
+      <c r="B59" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C59" s="22">
+      <c r="C59" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="24"/>
-      <c r="B60" s="21" t="str">
+      <c r="A60" s="23"/>
+      <c r="B60" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C60" s="22">
+      <c r="C60" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="24"/>
-      <c r="B61" s="21" t="str">
+      <c r="A61" s="23"/>
+      <c r="B61" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C61" s="22">
+      <c r="C61" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="24"/>
-      <c r="B62" s="21" t="str">
+      <c r="A62" s="23"/>
+      <c r="B62" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C62" s="22">
+      <c r="C62" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="24"/>
-      <c r="B63" s="21" t="str">
+      <c r="A63" s="23"/>
+      <c r="B63" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C63" s="22">
+      <c r="C63" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="24"/>
-      <c r="B64" s="21" t="str">
+      <c r="A64" s="23"/>
+      <c r="B64" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C64" s="22">
+      <c r="C64" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="24"/>
-      <c r="B65" s="21" t="str">
+      <c r="A65" s="23"/>
+      <c r="B65" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C65" s="22">
+      <c r="C65" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="24"/>
-      <c r="B66" s="21" t="str">
+      <c r="A66" s="23"/>
+      <c r="B66" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C66" s="22">
+      <c r="C66" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="24"/>
-      <c r="B67" s="21" t="str">
+      <c r="A67" s="23"/>
+      <c r="B67" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C67" s="22">
+      <c r="C67" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="24"/>
-      <c r="B68" s="21" t="str">
+      <c r="A68" s="23"/>
+      <c r="B68" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C68" s="22">
+      <c r="C68" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="24"/>
-      <c r="B69" s="21" t="str">
+      <c r="A69" s="23"/>
+      <c r="B69" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C69" s="22">
+      <c r="C69" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="24"/>
-      <c r="B70" s="21" t="str">
+      <c r="A70" s="23"/>
+      <c r="B70" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C70" s="22">
+      <c r="C70" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="24"/>
-      <c r="B71" s="21" t="str">
+      <c r="A71" s="23"/>
+      <c r="B71" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C71" s="22">
+      <c r="C71" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="24"/>
-      <c r="B72" s="21" t="str">
+      <c r="A72" s="23"/>
+      <c r="B72" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C72" s="22">
+      <c r="C72" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="24"/>
-      <c r="B73" s="21" t="str">
+      <c r="A73" s="23"/>
+      <c r="B73" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C73" s="22">
+      <c r="C73" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="24"/>
-      <c r="B74" s="21" t="str">
+      <c r="A74" s="23"/>
+      <c r="B74" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C74" s="22">
+      <c r="C74" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="24"/>
-      <c r="B75" s="21" t="str">
+      <c r="A75" s="23"/>
+      <c r="B75" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C75" s="22">
+      <c r="C75" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="24"/>
-      <c r="B76" s="21" t="str">
+      <c r="A76" s="23"/>
+      <c r="B76" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C76" s="22">
+      <c r="C76" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="24"/>
-      <c r="B77" s="21" t="str">
+      <c r="A77" s="23"/>
+      <c r="B77" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C77" s="22">
+      <c r="C77" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="24"/>
-      <c r="B78" s="21" t="str">
+      <c r="A78" s="23"/>
+      <c r="B78" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C78" s="22">
+      <c r="C78" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="24"/>
-      <c r="B79" s="21" t="str">
+      <c r="A79" s="23"/>
+      <c r="B79" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C79" s="22">
+      <c r="C79" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="24"/>
-      <c r="B80" s="21" t="str">
+      <c r="A80" s="23"/>
+      <c r="B80" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C80" s="22">
+      <c r="C80" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="24"/>
-      <c r="B81" s="21" t="str">
+      <c r="A81" s="23"/>
+      <c r="B81" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C81" s="22">
+      <c r="C81" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="24"/>
-      <c r="B82" s="21" t="str">
+      <c r="A82" s="23"/>
+      <c r="B82" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C82" s="22">
+      <c r="C82" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="24"/>
-      <c r="B83" s="21" t="str">
+      <c r="A83" s="23"/>
+      <c r="B83" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C83" s="22">
+      <c r="C83" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="24"/>
-      <c r="B84" s="21" t="str">
+      <c r="A84" s="23"/>
+      <c r="B84" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C84" s="22">
+      <c r="C84" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="24"/>
-      <c r="B85" s="21" t="str">
+      <c r="A85" s="23"/>
+      <c r="B85" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C85" s="22">
+      <c r="C85" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="24"/>
-      <c r="B86" s="21" t="str">
+      <c r="A86" s="23"/>
+      <c r="B86" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C86" s="22">
+      <c r="C86" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="24"/>
-      <c r="B87" s="21" t="str">
+      <c r="A87" s="23"/>
+      <c r="B87" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C87" s="22">
+      <c r="C87" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="24"/>
-      <c r="B88" s="21" t="str">
+      <c r="A88" s="23"/>
+      <c r="B88" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C88" s="22">
+      <c r="C88" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="24"/>
-      <c r="B89" s="21" t="str">
+      <c r="A89" s="23"/>
+      <c r="B89" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C89" s="22">
+      <c r="C89" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="24"/>
-      <c r="B90" s="21" t="str">
+      <c r="A90" s="23"/>
+      <c r="B90" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C90" s="22">
+      <c r="C90" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="24"/>
-      <c r="B91" s="21" t="str">
+      <c r="A91" s="23"/>
+      <c r="B91" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C91" s="22">
+      <c r="C91" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="24"/>
-      <c r="B92" s="21" t="str">
+      <c r="A92" s="23"/>
+      <c r="B92" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C92" s="22">
+      <c r="C92" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="24"/>
-      <c r="B93" s="21" t="str">
+      <c r="A93" s="23"/>
+      <c r="B93" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C93" s="22">
+      <c r="C93" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="24"/>
-      <c r="B94" s="21" t="str">
+      <c r="A94" s="23"/>
+      <c r="B94" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C94" s="22">
+      <c r="C94" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="24"/>
-      <c r="B95" s="21" t="str">
+      <c r="A95" s="23"/>
+      <c r="B95" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C95" s="22">
+      <c r="C95" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="24"/>
-      <c r="B96" s="21" t="str">
+      <c r="A96" s="23"/>
+      <c r="B96" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C96" s="22">
+      <c r="C96" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="24"/>
-      <c r="B97" s="21" t="str">
+      <c r="A97" s="23"/>
+      <c r="B97" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C97" s="22">
+      <c r="C97" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="24"/>
-      <c r="B98" s="21" t="str">
+      <c r="A98" s="23"/>
+      <c r="B98" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C98" s="22">
+      <c r="C98" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="24"/>
-      <c r="B99" s="21" t="str">
+      <c r="A99" s="23"/>
+      <c r="B99" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C99" s="22">
+      <c r="C99" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="24"/>
-      <c r="B100" s="21" t="str">
+      <c r="A100" s="23"/>
+      <c r="B100" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C100" s="22">
+      <c r="C100" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="24"/>
-      <c r="B101" s="21" t="str">
+      <c r="A101" s="23"/>
+      <c r="B101" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C101" s="22">
+      <c r="C101" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="24"/>
-      <c r="B102" s="21" t="str">
+      <c r="A102" s="23"/>
+      <c r="B102" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C102" s="22">
+      <c r="C102" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="24"/>
-      <c r="B103" s="21" t="str">
+      <c r="A103" s="23"/>
+      <c r="B103" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C103" s="22">
+      <c r="C103" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="24"/>
-      <c r="B104" s="21" t="str">
+      <c r="A104" s="23"/>
+      <c r="B104" s="20" t="str">
         <f t="shared" ref="B104:B114" si="1">IF(C104&gt;0,C104,"")</f>
         <v/>
       </c>
-      <c r="C104" s="22">
+      <c r="C104" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="24"/>
-      <c r="B105" s="21" t="str">
+      <c r="A105" s="23"/>
+      <c r="B105" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C105" s="22">
+      <c r="C105" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="24"/>
-      <c r="B106" s="21" t="str">
+      <c r="A106" s="23"/>
+      <c r="B106" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C106" s="22">
+      <c r="C106" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="24"/>
-      <c r="B107" s="21" t="str">
+      <c r="A107" s="23"/>
+      <c r="B107" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C107" s="22">
+      <c r="C107" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="24"/>
-      <c r="B108" s="21" t="str">
+      <c r="A108" s="23"/>
+      <c r="B108" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C108" s="22">
+      <c r="C108" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="24"/>
-      <c r="B109" s="21" t="str">
+      <c r="A109" s="23"/>
+      <c r="B109" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C109" s="22">
+      <c r="C109" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="24"/>
-      <c r="B110" s="21" t="str">
+      <c r="A110" s="23"/>
+      <c r="B110" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C110" s="22">
+      <c r="C110" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="24"/>
-      <c r="B111" s="21" t="str">
+      <c r="A111" s="23"/>
+      <c r="B111" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C111" s="22">
+      <c r="C111" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="24"/>
-      <c r="B112" s="21" t="str">
+      <c r="A112" s="23"/>
+      <c r="B112" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C112" s="22">
+      <c r="C112" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="24"/>
-      <c r="B113" s="21" t="str">
+      <c r="A113" s="23"/>
+      <c r="B113" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C113" s="22">
+      <c r="C113" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="24"/>
-      <c r="B114" s="21" t="str">
+      <c r="A114" s="23"/>
+      <c r="B114" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C114" s="22">
+      <c r="C114" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="24"/>
-      <c r="B115" s="24"/>
-      <c r="C115" s="22"/>
+      <c r="A115" s="23"/>
+      <c r="B115" s="23"/>
+      <c r="C115" s="21"/>
     </row>
     <row r="116">
-      <c r="A116" s="24"/>
-      <c r="B116" s="24"/>
-      <c r="C116" s="22"/>
+      <c r="A116" s="23"/>
+      <c r="B116" s="23"/>
+      <c r="C116" s="21"/>
     </row>
     <row r="117">
-      <c r="A117" s="24"/>
-      <c r="B117" s="24"/>
-      <c r="C117" s="22"/>
+      <c r="A117" s="23"/>
+      <c r="B117" s="23"/>
+      <c r="C117" s="21"/>
     </row>
     <row r="118">
-      <c r="A118" s="24"/>
-      <c r="B118" s="24"/>
-      <c r="C118" s="22"/>
+      <c r="A118" s="23"/>
+      <c r="B118" s="23"/>
+      <c r="C118" s="21"/>
     </row>
     <row r="119">
-      <c r="A119" s="24"/>
-      <c r="B119" s="24"/>
-      <c r="C119" s="22"/>
+      <c r="A119" s="23"/>
+      <c r="B119" s="23"/>
+      <c r="C119" s="21"/>
     </row>
     <row r="120">
-      <c r="A120" s="24"/>
-      <c r="B120" s="24"/>
-      <c r="C120" s="22"/>
+      <c r="A120" s="23"/>
+      <c r="B120" s="23"/>
+      <c r="C120" s="21"/>
     </row>
     <row r="121">
-      <c r="A121" s="24"/>
-      <c r="B121" s="24"/>
-      <c r="C121" s="22"/>
+      <c r="A121" s="23"/>
+      <c r="B121" s="23"/>
+      <c r="C121" s="21"/>
     </row>
     <row r="122">
-      <c r="A122" s="24"/>
-      <c r="B122" s="24"/>
-      <c r="C122" s="22"/>
+      <c r="A122" s="23"/>
+      <c r="B122" s="23"/>
+      <c r="C122" s="21"/>
     </row>
     <row r="123">
-      <c r="A123" s="24"/>
-      <c r="B123" s="24"/>
-      <c r="C123" s="22"/>
+      <c r="A123" s="23"/>
+      <c r="B123" s="23"/>
+      <c r="C123" s="21"/>
     </row>
     <row r="124">
-      <c r="A124" s="24"/>
-      <c r="B124" s="24"/>
-      <c r="C124" s="22"/>
+      <c r="A124" s="23"/>
+      <c r="B124" s="23"/>
+      <c r="C124" s="21"/>
     </row>
     <row r="125">
-      <c r="A125" s="24"/>
-      <c r="B125" s="24"/>
-      <c r="C125" s="22"/>
+      <c r="A125" s="23"/>
+      <c r="B125" s="23"/>
+      <c r="C125" s="21"/>
     </row>
     <row r="126">
-      <c r="A126" s="24"/>
-      <c r="B126" s="24"/>
-      <c r="C126" s="22"/>
+      <c r="A126" s="23"/>
+      <c r="B126" s="23"/>
+      <c r="C126" s="21"/>
     </row>
     <row r="127">
-      <c r="A127" s="24"/>
-      <c r="B127" s="24"/>
-      <c r="C127" s="22"/>
+      <c r="A127" s="23"/>
+      <c r="B127" s="23"/>
+      <c r="C127" s="21"/>
     </row>
     <row r="128">
-      <c r="A128" s="24"/>
-      <c r="B128" s="24"/>
-      <c r="C128" s="22"/>
+      <c r="A128" s="23"/>
+      <c r="B128" s="23"/>
+      <c r="C128" s="21"/>
     </row>
     <row r="129">
-      <c r="A129" s="24"/>
-      <c r="B129" s="24"/>
-      <c r="C129" s="22"/>
+      <c r="A129" s="23"/>
+      <c r="B129" s="23"/>
+      <c r="C129" s="21"/>
     </row>
     <row r="130">
-      <c r="A130" s="24"/>
-      <c r="B130" s="24"/>
-      <c r="C130" s="22"/>
+      <c r="A130" s="23"/>
+      <c r="B130" s="23"/>
+      <c r="C130" s="21"/>
     </row>
     <row r="131">
-      <c r="A131" s="24"/>
-      <c r="B131" s="24"/>
-      <c r="C131" s="22"/>
+      <c r="A131" s="23"/>
+      <c r="B131" s="23"/>
+      <c r="C131" s="21"/>
     </row>
     <row r="132">
-      <c r="A132" s="24"/>
-      <c r="B132" s="24"/>
-      <c r="C132" s="22"/>
+      <c r="A132" s="23"/>
+      <c r="B132" s="23"/>
+      <c r="C132" s="21"/>
     </row>
     <row r="133">
-      <c r="A133" s="24"/>
-      <c r="B133" s="24"/>
-      <c r="C133" s="22"/>
+      <c r="A133" s="23"/>
+      <c r="B133" s="23"/>
+      <c r="C133" s="21"/>
     </row>
     <row r="134">
-      <c r="A134" s="24"/>
-      <c r="B134" s="24"/>
-      <c r="C134" s="22"/>
+      <c r="A134" s="23"/>
+      <c r="B134" s="23"/>
+      <c r="C134" s="21"/>
     </row>
     <row r="135">
-      <c r="A135" s="24"/>
-      <c r="B135" s="24"/>
-      <c r="C135" s="22"/>
+      <c r="A135" s="23"/>
+      <c r="B135" s="23"/>
+      <c r="C135" s="21"/>
     </row>
     <row r="136">
-      <c r="A136" s="24"/>
-      <c r="B136" s="24"/>
-      <c r="C136" s="22"/>
+      <c r="A136" s="23"/>
+      <c r="B136" s="23"/>
+      <c r="C136" s="21"/>
     </row>
     <row r="137">
-      <c r="A137" s="24"/>
-      <c r="B137" s="24"/>
-      <c r="C137" s="22"/>
+      <c r="A137" s="23"/>
+      <c r="B137" s="23"/>
+      <c r="C137" s="21"/>
     </row>
     <row r="138">
-      <c r="A138" s="24"/>
-      <c r="B138" s="24"/>
-      <c r="C138" s="22"/>
+      <c r="A138" s="23"/>
+      <c r="B138" s="23"/>
+      <c r="C138" s="21"/>
     </row>
     <row r="139">
-      <c r="A139" s="24"/>
-      <c r="B139" s="24"/>
-      <c r="C139" s="22"/>
+      <c r="A139" s="23"/>
+      <c r="B139" s="23"/>
+      <c r="C139" s="21"/>
     </row>
     <row r="140">
-      <c r="A140" s="24"/>
-      <c r="B140" s="24"/>
-      <c r="C140" s="22"/>
+      <c r="A140" s="23"/>
+      <c r="B140" s="23"/>
+      <c r="C140" s="21"/>
     </row>
     <row r="141">
-      <c r="A141" s="24"/>
-      <c r="B141" s="24"/>
-      <c r="C141" s="22"/>
+      <c r="A141" s="23"/>
+      <c r="B141" s="23"/>
+      <c r="C141" s="21"/>
     </row>
     <row r="142">
-      <c r="A142" s="24"/>
-      <c r="B142" s="24"/>
-      <c r="C142" s="22"/>
+      <c r="A142" s="23"/>
+      <c r="B142" s="23"/>
+      <c r="C142" s="21"/>
     </row>
     <row r="143">
-      <c r="A143" s="24"/>
-      <c r="B143" s="24"/>
-      <c r="C143" s="22"/>
+      <c r="A143" s="23"/>
+      <c r="B143" s="23"/>
+      <c r="C143" s="21"/>
     </row>
     <row r="144">
-      <c r="A144" s="24"/>
-      <c r="B144" s="24"/>
-      <c r="C144" s="22"/>
+      <c r="A144" s="23"/>
+      <c r="B144" s="23"/>
+      <c r="C144" s="21"/>
     </row>
     <row r="145">
-      <c r="A145" s="24"/>
-      <c r="B145" s="24"/>
-      <c r="C145" s="22"/>
+      <c r="A145" s="23"/>
+      <c r="B145" s="23"/>
+      <c r="C145" s="21"/>
     </row>
     <row r="146">
-      <c r="A146" s="24"/>
-      <c r="B146" s="24"/>
-      <c r="C146" s="22"/>
+      <c r="A146" s="23"/>
+      <c r="B146" s="23"/>
+      <c r="C146" s="21"/>
     </row>
     <row r="147">
-      <c r="A147" s="24"/>
-      <c r="B147" s="24"/>
-      <c r="C147" s="22"/>
+      <c r="A147" s="23"/>
+      <c r="B147" s="23"/>
+      <c r="C147" s="21"/>
     </row>
     <row r="148">
-      <c r="A148" s="24"/>
-      <c r="B148" s="24"/>
-      <c r="C148" s="22"/>
+      <c r="A148" s="23"/>
+      <c r="B148" s="23"/>
+      <c r="C148" s="21"/>
     </row>
     <row r="149">
-      <c r="A149" s="24"/>
-      <c r="B149" s="24"/>
-      <c r="C149" s="22"/>
+      <c r="A149" s="23"/>
+      <c r="B149" s="23"/>
+      <c r="C149" s="21"/>
     </row>
     <row r="150">
-      <c r="A150" s="24"/>
-      <c r="B150" s="24"/>
-      <c r="C150" s="22"/>
+      <c r="A150" s="23"/>
+      <c r="B150" s="23"/>
+      <c r="C150" s="21"/>
     </row>
     <row r="151">
-      <c r="A151" s="24"/>
-      <c r="B151" s="24"/>
-      <c r="C151" s="22"/>
+      <c r="A151" s="23"/>
+      <c r="B151" s="23"/>
+      <c r="C151" s="21"/>
     </row>
     <row r="152">
-      <c r="A152" s="24"/>
-      <c r="B152" s="24"/>
-      <c r="C152" s="22"/>
+      <c r="A152" s="23"/>
+      <c r="B152" s="23"/>
+      <c r="C152" s="21"/>
     </row>
     <row r="153">
-      <c r="A153" s="24"/>
-      <c r="B153" s="24"/>
-      <c r="C153" s="22"/>
+      <c r="A153" s="23"/>
+      <c r="B153" s="23"/>
+      <c r="C153" s="21"/>
     </row>
     <row r="154">
-      <c r="A154" s="24"/>
-      <c r="B154" s="24"/>
-      <c r="C154" s="22"/>
+      <c r="A154" s="23"/>
+      <c r="B154" s="23"/>
+      <c r="C154" s="21"/>
     </row>
     <row r="155">
-      <c r="A155" s="24"/>
-      <c r="B155" s="24"/>
-      <c r="C155" s="22"/>
+      <c r="A155" s="23"/>
+      <c r="B155" s="23"/>
+      <c r="C155" s="21"/>
     </row>
     <row r="156">
-      <c r="A156" s="24"/>
-      <c r="B156" s="24"/>
-      <c r="C156" s="22"/>
+      <c r="A156" s="23"/>
+      <c r="B156" s="23"/>
+      <c r="C156" s="21"/>
     </row>
     <row r="157">
-      <c r="A157" s="24"/>
-      <c r="B157" s="24"/>
-      <c r="C157" s="22"/>
+      <c r="A157" s="23"/>
+      <c r="B157" s="23"/>
+      <c r="C157" s="21"/>
     </row>
     <row r="158">
-      <c r="A158" s="24"/>
-      <c r="B158" s="24"/>
-      <c r="C158" s="22"/>
+      <c r="A158" s="23"/>
+      <c r="B158" s="23"/>
+      <c r="C158" s="21"/>
     </row>
     <row r="159">
-      <c r="A159" s="24"/>
-      <c r="B159" s="24"/>
+      <c r="A159" s="23"/>
+      <c r="B159" s="23"/>
     </row>
     <row r="160">
-      <c r="A160" s="24"/>
-      <c r="B160" s="24"/>
+      <c r="A160" s="23"/>
+      <c r="B160" s="23"/>
     </row>
     <row r="161">
-      <c r="A161" s="24"/>
-      <c r="B161" s="24"/>
+      <c r="A161" s="23"/>
+      <c r="B161" s="23"/>
     </row>
     <row r="162">
-      <c r="A162" s="24"/>
-      <c r="B162" s="24"/>
+      <c r="A162" s="23"/>
+      <c r="B162" s="23"/>
     </row>
     <row r="163">
-      <c r="A163" s="24"/>
-      <c r="B163" s="24"/>
+      <c r="A163" s="23"/>
+      <c r="B163" s="23"/>
     </row>
     <row r="164">
-      <c r="A164" s="24"/>
-      <c r="B164" s="24"/>
+      <c r="A164" s="23"/>
+      <c r="B164" s="23"/>
     </row>
     <row r="165">
-      <c r="A165" s="24"/>
-      <c r="B165" s="24"/>
+      <c r="A165" s="23"/>
+      <c r="B165" s="23"/>
     </row>
     <row r="166">
-      <c r="A166" s="24"/>
-      <c r="B166" s="24"/>
+      <c r="A166" s="23"/>
+      <c r="B166" s="23"/>
     </row>
     <row r="167">
-      <c r="A167" s="24"/>
-      <c r="B167" s="24"/>
+      <c r="A167" s="23"/>
+      <c r="B167" s="23"/>
     </row>
     <row r="168">
-      <c r="A168" s="24"/>
-      <c r="B168" s="24"/>
+      <c r="A168" s="23"/>
+      <c r="B168" s="23"/>
     </row>
     <row r="169">
-      <c r="A169" s="24"/>
-      <c r="B169" s="24"/>
+      <c r="A169" s="23"/>
+      <c r="B169" s="23"/>
     </row>
     <row r="170">
-      <c r="A170" s="24"/>
-      <c r="B170" s="24"/>
+      <c r="A170" s="23"/>
+      <c r="B170" s="23"/>
     </row>
     <row r="171">
-      <c r="A171" s="24"/>
-      <c r="B171" s="24"/>
+      <c r="A171" s="23"/>
+      <c r="B171" s="23"/>
     </row>
     <row r="172">
-      <c r="A172" s="24"/>
-      <c r="B172" s="24"/>
+      <c r="A172" s="23"/>
+      <c r="B172" s="23"/>
     </row>
     <row r="173">
-      <c r="A173" s="24"/>
-      <c r="B173" s="24"/>
+      <c r="A173" s="23"/>
+      <c r="B173" s="23"/>
     </row>
     <row r="174">
-      <c r="A174" s="24"/>
-      <c r="B174" s="24"/>
+      <c r="A174" s="23"/>
+      <c r="B174" s="23"/>
     </row>
     <row r="175">
-      <c r="A175" s="24"/>
-      <c r="B175" s="24"/>
+      <c r="A175" s="23"/>
+      <c r="B175" s="23"/>
     </row>
     <row r="176">
-      <c r="A176" s="24"/>
-      <c r="B176" s="24"/>
+      <c r="A176" s="23"/>
+      <c r="B176" s="23"/>
     </row>
     <row r="177">
-      <c r="A177" s="24"/>
-      <c r="B177" s="24"/>
+      <c r="A177" s="23"/>
+      <c r="B177" s="23"/>
     </row>
     <row r="178">
-      <c r="A178" s="24"/>
-      <c r="B178" s="24"/>
+      <c r="A178" s="23"/>
+      <c r="B178" s="23"/>
     </row>
     <row r="179">
-      <c r="A179" s="24"/>
-      <c r="B179" s="24"/>
+      <c r="A179" s="23"/>
+      <c r="B179" s="23"/>
     </row>
     <row r="180">
-      <c r="A180" s="24"/>
-      <c r="B180" s="24"/>
+      <c r="A180" s="23"/>
+      <c r="B180" s="23"/>
     </row>
     <row r="181">
-      <c r="A181" s="24"/>
-      <c r="B181" s="24"/>
+      <c r="A181" s="23"/>
+      <c r="B181" s="23"/>
     </row>
     <row r="182">
-      <c r="A182" s="24"/>
-      <c r="B182" s="24"/>
+      <c r="A182" s="23"/>
+      <c r="B182" s="23"/>
     </row>
     <row r="183">
-      <c r="A183" s="24"/>
-      <c r="B183" s="24"/>
+      <c r="A183" s="23"/>
+      <c r="B183" s="23"/>
     </row>
     <row r="184">
-      <c r="A184" s="24"/>
-      <c r="B184" s="24"/>
+      <c r="A184" s="23"/>
+      <c r="B184" s="23"/>
     </row>
     <row r="185">
-      <c r="A185" s="24"/>
-      <c r="B185" s="24"/>
+      <c r="A185" s="23"/>
+      <c r="B185" s="23"/>
     </row>
     <row r="186">
-      <c r="A186" s="24"/>
-      <c r="B186" s="24"/>
+      <c r="A186" s="23"/>
+      <c r="B186" s="23"/>
     </row>
     <row r="187">
-      <c r="A187" s="24"/>
-      <c r="B187" s="24"/>
+      <c r="A187" s="23"/>
+      <c r="B187" s="23"/>
     </row>
     <row r="188">
-      <c r="A188" s="24"/>
-      <c r="B188" s="24"/>
+      <c r="A188" s="23"/>
+      <c r="B188" s="23"/>
     </row>
     <row r="189">
-      <c r="A189" s="24"/>
-      <c r="B189" s="24"/>
+      <c r="A189" s="23"/>
+      <c r="B189" s="23"/>
     </row>
     <row r="190">
-      <c r="A190" s="24"/>
-      <c r="B190" s="24"/>
+      <c r="A190" s="23"/>
+      <c r="B190" s="23"/>
     </row>
     <row r="191">
-      <c r="A191" s="24"/>
-      <c r="B191" s="24"/>
+      <c r="A191" s="23"/>
+      <c r="B191" s="23"/>
     </row>
     <row r="192">
-      <c r="A192" s="24"/>
-      <c r="B192" s="24"/>
+      <c r="A192" s="23"/>
+      <c r="B192" s="23"/>
     </row>
     <row r="193">
-      <c r="A193" s="24"/>
-      <c r="B193" s="24"/>
+      <c r="A193" s="23"/>
+      <c r="B193" s="23"/>
     </row>
     <row r="194">
-      <c r="A194" s="24"/>
-      <c r="B194" s="24"/>
+      <c r="A194" s="23"/>
+      <c r="B194" s="23"/>
     </row>
     <row r="195">
-      <c r="A195" s="24"/>
-      <c r="B195" s="24"/>
+      <c r="A195" s="23"/>
+      <c r="B195" s="23"/>
     </row>
     <row r="196">
-      <c r="A196" s="24"/>
-      <c r="B196" s="24"/>
+      <c r="A196" s="23"/>
+      <c r="B196" s="23"/>
     </row>
     <row r="197">
-      <c r="A197" s="24"/>
-      <c r="B197" s="24"/>
+      <c r="A197" s="23"/>
+      <c r="B197" s="23"/>
     </row>
     <row r="198">
-      <c r="A198" s="24"/>
-      <c r="B198" s="24"/>
+      <c r="A198" s="23"/>
+      <c r="B198" s="23"/>
     </row>
     <row r="199">
-      <c r="A199" s="24"/>
-      <c r="B199" s="24"/>
+      <c r="A199" s="23"/>
+      <c r="B199" s="23"/>
     </row>
     <row r="200">
-      <c r="A200" s="24"/>
-      <c r="B200" s="24"/>
+      <c r="A200" s="23"/>
+      <c r="B200" s="23"/>
     </row>
     <row r="201">
-      <c r="A201" s="24"/>
-      <c r="B201" s="24"/>
+      <c r="A201" s="23"/>
+      <c r="B201" s="23"/>
     </row>
     <row r="202">
-      <c r="A202" s="24"/>
-      <c r="B202" s="24"/>
+      <c r="A202" s="23"/>
+      <c r="B202" s="23"/>
     </row>
     <row r="203">
-      <c r="A203" s="24"/>
-      <c r="B203" s="24"/>
+      <c r="A203" s="23"/>
+      <c r="B203" s="23"/>
     </row>
     <row r="204">
-      <c r="A204" s="24"/>
-      <c r="B204" s="24"/>
+      <c r="A204" s="23"/>
+      <c r="B204" s="23"/>
     </row>
     <row r="205">
-      <c r="A205" s="24"/>
-      <c r="B205" s="24"/>
+      <c r="A205" s="23"/>
+      <c r="B205" s="23"/>
     </row>
     <row r="206">
-      <c r="A206" s="24"/>
-      <c r="B206" s="24"/>
+      <c r="A206" s="23"/>
+      <c r="B206" s="23"/>
     </row>
     <row r="207">
-      <c r="A207" s="24"/>
-      <c r="B207" s="24"/>
+      <c r="A207" s="23"/>
+      <c r="B207" s="23"/>
     </row>
     <row r="208">
-      <c r="A208" s="24"/>
-      <c r="B208" s="24"/>
+      <c r="A208" s="23"/>
+      <c r="B208" s="23"/>
     </row>
     <row r="209">
-      <c r="A209" s="24"/>
-      <c r="B209" s="24"/>
+      <c r="A209" s="23"/>
+      <c r="B209" s="23"/>
     </row>
     <row r="210">
-      <c r="A210" s="24"/>
-      <c r="B210" s="24"/>
+      <c r="A210" s="23"/>
+      <c r="B210" s="23"/>
     </row>
     <row r="211">
-      <c r="A211" s="24"/>
-      <c r="B211" s="24"/>
+      <c r="A211" s="23"/>
+      <c r="B211" s="23"/>
     </row>
     <row r="212">
-      <c r="A212" s="24"/>
-      <c r="B212" s="24"/>
+      <c r="A212" s="23"/>
+      <c r="B212" s="23"/>
     </row>
     <row r="213">
-      <c r="A213" s="24"/>
-      <c r="B213" s="24"/>
+      <c r="A213" s="23"/>
+      <c r="B213" s="23"/>
     </row>
     <row r="214">
-      <c r="A214" s="24"/>
-      <c r="B214" s="24"/>
+      <c r="A214" s="23"/>
+      <c r="B214" s="23"/>
     </row>
     <row r="215">
-      <c r="A215" s="24"/>
-      <c r="B215" s="24"/>
+      <c r="A215" s="23"/>
+      <c r="B215" s="23"/>
     </row>
     <row r="216">
-      <c r="A216" s="24"/>
-      <c r="B216" s="24"/>
+      <c r="A216" s="23"/>
+      <c r="B216" s="23"/>
     </row>
     <row r="217">
-      <c r="A217" s="24"/>
-      <c r="B217" s="24"/>
+      <c r="A217" s="23"/>
+      <c r="B217" s="23"/>
     </row>
     <row r="218">
-      <c r="A218" s="24"/>
-      <c r="B218" s="24"/>
+      <c r="A218" s="23"/>
+      <c r="B218" s="23"/>
     </row>
     <row r="219">
-      <c r="A219" s="24"/>
-      <c r="B219" s="24"/>
+      <c r="A219" s="23"/>
+      <c r="B219" s="23"/>
     </row>
     <row r="220">
-      <c r="A220" s="24"/>
-      <c r="B220" s="24"/>
+      <c r="A220" s="23"/>
+      <c r="B220" s="23"/>
     </row>
     <row r="221">
-      <c r="A221" s="24"/>
-      <c r="B221" s="24"/>
+      <c r="A221" s="23"/>
+      <c r="B221" s="23"/>
     </row>
     <row r="222">
-      <c r="A222" s="24"/>
-      <c r="B222" s="24"/>
+      <c r="A222" s="23"/>
+      <c r="B222" s="23"/>
     </row>
     <row r="223">
-      <c r="A223" s="24"/>
-      <c r="B223" s="24"/>
+      <c r="A223" s="23"/>
+      <c r="B223" s="23"/>
     </row>
     <row r="224">
-      <c r="A224" s="24"/>
-      <c r="B224" s="24"/>
+      <c r="A224" s="23"/>
+      <c r="B224" s="23"/>
     </row>
     <row r="225">
-      <c r="A225" s="24"/>
-      <c r="B225" s="24"/>
+      <c r="A225" s="23"/>
+      <c r="B225" s="23"/>
     </row>
     <row r="226">
-      <c r="A226" s="24"/>
-      <c r="B226" s="24"/>
+      <c r="A226" s="23"/>
+      <c r="B226" s="23"/>
     </row>
     <row r="227">
-      <c r="A227" s="24"/>
-      <c r="B227" s="24"/>
+      <c r="A227" s="23"/>
+      <c r="B227" s="23"/>
     </row>
     <row r="228">
-      <c r="A228" s="24"/>
-      <c r="B228" s="24"/>
+      <c r="A228" s="23"/>
+      <c r="B228" s="23"/>
     </row>
     <row r="229">
-      <c r="A229" s="24"/>
-      <c r="B229" s="24"/>
+      <c r="A229" s="23"/>
+      <c r="B229" s="23"/>
     </row>
     <row r="230">
-      <c r="A230" s="24"/>
-      <c r="B230" s="24"/>
+      <c r="A230" s="23"/>
+      <c r="B230" s="23"/>
     </row>
     <row r="231">
-      <c r="A231" s="24"/>
-      <c r="B231" s="24"/>
+      <c r="A231" s="23"/>
+      <c r="B231" s="23"/>
     </row>
     <row r="232">
-      <c r="A232" s="24"/>
-      <c r="B232" s="24"/>
+      <c r="A232" s="23"/>
+      <c r="B232" s="23"/>
     </row>
     <row r="233">
-      <c r="A233" s="24"/>
-      <c r="B233" s="24"/>
+      <c r="A233" s="23"/>
+      <c r="B233" s="23"/>
     </row>
     <row r="234">
-      <c r="A234" s="24"/>
-      <c r="B234" s="24"/>
+      <c r="A234" s="23"/>
+      <c r="B234" s="23"/>
     </row>
     <row r="235">
-      <c r="A235" s="24"/>
-      <c r="B235" s="24"/>
+      <c r="A235" s="23"/>
+      <c r="B235" s="23"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -7354,2034 +7365,2034 @@
     <col customWidth="1" min="2" max="2" width="4.33203125"/>
     <col bestFit="1" min="3" max="3" width="35.77734375"/>
     <col customWidth="1" min="4" max="11" width="3.44140625"/>
-    <col customWidth="1" min="12" max="12" style="25" width="6"/>
+    <col customWidth="1" min="12" max="12" style="24" width="6"/>
     <col customWidth="1" min="13" max="22" width="3.44140625"/>
-    <col customWidth="1" min="23" max="23" style="25" width="6"/>
+    <col customWidth="1" min="23" max="23" style="24" width="6"/>
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
-    <col customWidth="1" min="30" max="30" style="25" width="6"/>
+    <col customWidth="1" min="30" max="30" style="24" width="6"/>
     <col customWidth="1" min="31" max="39" width="3.44140625"/>
     <col bestFit="1" customWidth="1" min="40" max="40" width="13.88671875"/>
     <col customWidth="1" min="41" max="47" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="26" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="B1" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="28" t="s">
+    <row r="1" s="25" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="B1" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="C1" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="30" t="s">
+      <c r="E1" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="29" t="s">
+      <c r="H1" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="29" t="s">
+      <c r="J1" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="L1" s="33" t="s">
+      <c r="K1" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="M1" s="29" t="s">
+      <c r="L1" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="N1" s="31" t="s">
+      <c r="M1" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="N1" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="P1" s="29" t="s">
+      <c r="O1" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="P1" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="R1" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="S1" s="29" t="s">
+      <c r="Q1" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="R1" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="T1" s="29" t="s">
+      <c r="S1" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="U1" s="29" t="s">
+      <c r="T1" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="V1" s="31" t="s">
+      <c r="U1" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="W1" s="34" t="s">
+      <c r="V1" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="X1" s="29" t="s">
+      <c r="W1" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="Y1" s="29" t="s">
+      <c r="X1" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="Z1" s="31" t="s">
+      <c r="Y1" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="AA1" s="35" t="s">
+      <c r="Z1" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="AB1" s="36" t="s">
+      <c r="AA1" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="AC1" s="36" t="s">
+      <c r="AB1" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="AD1" s="33" t="s">
+      <c r="AC1" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="AE1" s="37" t="s">
+      <c r="AD1" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="AF1" s="38" t="s">
+      <c r="AE1" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="AG1" s="39" t="s">
+      <c r="AF1" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="AH1" s="39" t="s">
+      <c r="AG1" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="AI1" s="39" t="s">
+      <c r="AH1" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="AJ1" s="39" t="s">
+      <c r="AI1" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="AK1" s="36" t="s">
+      <c r="AJ1" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="AL1" s="40"/>
-      <c r="AM1" s="40"/>
-      <c r="AN1" s="40"/>
-      <c r="AO1" s="40"/>
-      <c r="AP1" s="40"/>
-      <c r="AQ1" s="40"/>
-      <c r="AR1" s="40"/>
-      <c r="AS1" s="40"/>
-      <c r="AT1" s="40"/>
-      <c r="AU1" s="40"/>
+      <c r="AK1" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL1" s="39"/>
+      <c r="AM1" s="39"/>
+      <c r="AN1" s="39"/>
+      <c r="AO1" s="39"/>
+      <c r="AP1" s="39"/>
+      <c r="AQ1" s="39"/>
+      <c r="AR1" s="39"/>
+      <c r="AS1" s="39"/>
+      <c r="AT1" s="39"/>
+      <c r="AU1" s="39"/>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="49"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="43"/>
-      <c r="S2" s="43"/>
-      <c r="T2" s="43"/>
-      <c r="U2" s="43"/>
-      <c r="V2" s="48"/>
-      <c r="W2" s="50"/>
-      <c r="X2" s="43"/>
-      <c r="Y2" s="43"/>
-      <c r="Z2" s="48"/>
-      <c r="AA2" s="49"/>
-      <c r="AB2" s="43"/>
-      <c r="AC2" s="43"/>
-      <c r="AD2" s="47"/>
-      <c r="AE2" s="48"/>
-      <c r="AF2" s="49"/>
-      <c r="AG2" s="43"/>
-      <c r="AH2" s="43"/>
-      <c r="AI2" s="43"/>
-      <c r="AJ2" s="43"/>
-      <c r="AK2" s="43"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="42"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="42"/>
+      <c r="S2" s="42"/>
+      <c r="T2" s="42"/>
+      <c r="U2" s="42"/>
+      <c r="V2" s="47"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="42"/>
+      <c r="Y2" s="42"/>
+      <c r="Z2" s="47"/>
+      <c r="AA2" s="48"/>
+      <c r="AB2" s="42"/>
+      <c r="AC2" s="42"/>
+      <c r="AD2" s="46"/>
+      <c r="AE2" s="47"/>
+      <c r="AF2" s="48"/>
+      <c r="AG2" s="42"/>
+      <c r="AH2" s="42"/>
+      <c r="AI2" s="42"/>
+      <c r="AJ2" s="42"/>
+      <c r="AK2" s="42"/>
     </row>
     <row r="3" ht="12" customHeight="1">
-      <c r="B3" s="41"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="49"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="43"/>
-      <c r="U3" s="43"/>
-      <c r="V3" s="48"/>
-      <c r="W3" s="50"/>
-      <c r="X3" s="43"/>
-      <c r="Y3" s="43"/>
-      <c r="Z3" s="48"/>
-      <c r="AA3" s="49"/>
-      <c r="AB3" s="43"/>
-      <c r="AC3" s="43"/>
-      <c r="AD3" s="47"/>
-      <c r="AE3" s="48"/>
-      <c r="AF3" s="49"/>
-      <c r="AG3" s="43"/>
-      <c r="AH3" s="43"/>
-      <c r="AI3" s="43"/>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="42"/>
+      <c r="R3" s="42"/>
+      <c r="S3" s="42"/>
+      <c r="T3" s="42"/>
+      <c r="U3" s="42"/>
+      <c r="V3" s="47"/>
+      <c r="W3" s="49"/>
+      <c r="X3" s="42"/>
+      <c r="Y3" s="42"/>
+      <c r="Z3" s="47"/>
+      <c r="AA3" s="48"/>
+      <c r="AB3" s="42"/>
+      <c r="AC3" s="42"/>
+      <c r="AD3" s="46"/>
+      <c r="AE3" s="47"/>
+      <c r="AF3" s="48"/>
+      <c r="AG3" s="42"/>
+      <c r="AH3" s="42"/>
+      <c r="AI3" s="42"/>
+      <c r="AJ3" s="42"/>
+      <c r="AK3" s="42"/>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="41"/>
-      <c r="C4" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="49"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="43"/>
-      <c r="T4" s="43"/>
-      <c r="U4" s="43"/>
-      <c r="V4" s="48"/>
-      <c r="W4" s="50"/>
-      <c r="X4" s="43"/>
-      <c r="Y4" s="43"/>
-      <c r="Z4" s="48"/>
-      <c r="AA4" s="49"/>
-      <c r="AB4" s="43"/>
-      <c r="AC4" s="43"/>
-      <c r="AD4" s="47"/>
-      <c r="AE4" s="48"/>
-      <c r="AF4" s="49"/>
-      <c r="AG4" s="43"/>
-      <c r="AH4" s="43"/>
-      <c r="AI4" s="43"/>
-      <c r="AJ4" s="43"/>
-      <c r="AK4" s="43"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="42"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="42"/>
+      <c r="Q4" s="42"/>
+      <c r="R4" s="42"/>
+      <c r="S4" s="42"/>
+      <c r="T4" s="42"/>
+      <c r="U4" s="42"/>
+      <c r="V4" s="47"/>
+      <c r="W4" s="49"/>
+      <c r="X4" s="42"/>
+      <c r="Y4" s="42"/>
+      <c r="Z4" s="47"/>
+      <c r="AA4" s="48"/>
+      <c r="AB4" s="42"/>
+      <c r="AC4" s="42"/>
+      <c r="AD4" s="46"/>
+      <c r="AE4" s="47"/>
+      <c r="AF4" s="48"/>
+      <c r="AG4" s="42"/>
+      <c r="AH4" s="42"/>
+      <c r="AI4" s="42"/>
+      <c r="AJ4" s="42"/>
+      <c r="AK4" s="42"/>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="41"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="47"/>
-      <c r="M5" s="43"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="43"/>
-      <c r="Q5" s="43"/>
-      <c r="R5" s="43"/>
-      <c r="S5" s="43"/>
-      <c r="T5" s="43"/>
-      <c r="U5" s="43"/>
-      <c r="V5" s="48"/>
-      <c r="W5" s="50"/>
-      <c r="X5" s="43"/>
-      <c r="Y5" s="43"/>
-      <c r="Z5" s="48"/>
-      <c r="AA5" s="49"/>
-      <c r="AB5" s="43"/>
-      <c r="AC5" s="43"/>
-      <c r="AD5" s="47"/>
-      <c r="AE5" s="48"/>
-      <c r="AF5" s="49"/>
-      <c r="AG5" s="43"/>
-      <c r="AH5" s="43"/>
-      <c r="AI5" s="43"/>
-      <c r="AJ5" s="43"/>
-      <c r="AK5" s="43"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="42"/>
+      <c r="N5" s="47"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="42"/>
+      <c r="Q5" s="42"/>
+      <c r="R5" s="42"/>
+      <c r="S5" s="42"/>
+      <c r="T5" s="42"/>
+      <c r="U5" s="42"/>
+      <c r="V5" s="47"/>
+      <c r="W5" s="49"/>
+      <c r="X5" s="42"/>
+      <c r="Y5" s="42"/>
+      <c r="Z5" s="47"/>
+      <c r="AA5" s="48"/>
+      <c r="AB5" s="42"/>
+      <c r="AC5" s="42"/>
+      <c r="AD5" s="46"/>
+      <c r="AE5" s="47"/>
+      <c r="AF5" s="48"/>
+      <c r="AG5" s="42"/>
+      <c r="AH5" s="42"/>
+      <c r="AI5" s="42"/>
+      <c r="AJ5" s="42"/>
+      <c r="AK5" s="42"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="41"/>
-      <c r="C6" s="42" t="s">
+      <c r="B6" s="40"/>
+      <c r="C6" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43"/>
-      <c r="L6" s="47"/>
-      <c r="M6" s="43"/>
-      <c r="N6" s="48"/>
-      <c r="O6" s="49"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="43"/>
-      <c r="R6" s="43"/>
-      <c r="S6" s="43"/>
-      <c r="T6" s="43"/>
-      <c r="U6" s="43"/>
-      <c r="V6" s="48"/>
-      <c r="W6" s="50"/>
-      <c r="X6" s="43"/>
-      <c r="Y6" s="43"/>
-      <c r="Z6" s="48"/>
-      <c r="AA6" s="49"/>
-      <c r="AB6" s="43"/>
-      <c r="AC6" s="43"/>
-      <c r="AD6" s="47"/>
-      <c r="AE6" s="45"/>
-      <c r="AF6" s="46"/>
-      <c r="AG6" s="57"/>
-      <c r="AH6" s="57"/>
-      <c r="AI6" s="57"/>
-      <c r="AJ6" s="57"/>
-      <c r="AK6" s="57"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="46"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="48"/>
+      <c r="P6" s="42"/>
+      <c r="Q6" s="42"/>
+      <c r="R6" s="42"/>
+      <c r="S6" s="42"/>
+      <c r="T6" s="42"/>
+      <c r="U6" s="42"/>
+      <c r="V6" s="47"/>
+      <c r="W6" s="49"/>
+      <c r="X6" s="42"/>
+      <c r="Y6" s="42"/>
+      <c r="Z6" s="47"/>
+      <c r="AA6" s="48"/>
+      <c r="AB6" s="42"/>
+      <c r="AC6" s="42"/>
+      <c r="AD6" s="46"/>
+      <c r="AE6" s="44"/>
+      <c r="AF6" s="45"/>
+      <c r="AG6" s="56"/>
+      <c r="AH6" s="56"/>
+      <c r="AI6" s="56"/>
+      <c r="AJ6" s="56"/>
+      <c r="AK6" s="56"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="41"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="43"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="43"/>
-      <c r="N7" s="48"/>
-      <c r="O7" s="55"/>
-      <c r="P7" s="43"/>
-      <c r="Q7" s="43"/>
-      <c r="R7" s="43"/>
-      <c r="S7" s="43"/>
-      <c r="T7" s="43"/>
-      <c r="U7" s="43"/>
-      <c r="V7" s="48"/>
-      <c r="W7" s="50"/>
-      <c r="X7" s="43"/>
-      <c r="Y7" s="43"/>
-      <c r="Z7" s="48"/>
-      <c r="AA7" s="49"/>
-      <c r="AB7" s="43"/>
-      <c r="AC7" s="43"/>
-      <c r="AD7" s="47"/>
-      <c r="AE7" s="48"/>
-      <c r="AF7" s="49"/>
-      <c r="AG7" s="43"/>
-      <c r="AH7" s="43"/>
-      <c r="AI7" s="43"/>
-      <c r="AJ7" s="43"/>
-      <c r="AK7" s="43"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="47"/>
+      <c r="O7" s="54"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="42"/>
+      <c r="R7" s="42"/>
+      <c r="S7" s="42"/>
+      <c r="T7" s="42"/>
+      <c r="U7" s="42"/>
+      <c r="V7" s="47"/>
+      <c r="W7" s="49"/>
+      <c r="X7" s="42"/>
+      <c r="Y7" s="42"/>
+      <c r="Z7" s="47"/>
+      <c r="AA7" s="48"/>
+      <c r="AB7" s="42"/>
+      <c r="AC7" s="42"/>
+      <c r="AD7" s="46"/>
+      <c r="AE7" s="47"/>
+      <c r="AF7" s="48"/>
+      <c r="AG7" s="42"/>
+      <c r="AH7" s="42"/>
+      <c r="AI7" s="42"/>
+      <c r="AJ7" s="42"/>
+      <c r="AK7" s="42"/>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="41"/>
-      <c r="C8" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
-      <c r="K8" s="57"/>
-      <c r="L8" s="47"/>
-      <c r="M8" s="57"/>
-      <c r="N8" s="45"/>
-      <c r="O8" s="46"/>
-      <c r="P8" s="57"/>
-      <c r="Q8" s="57"/>
-      <c r="R8" s="57"/>
-      <c r="S8" s="57"/>
-      <c r="T8" s="57"/>
-      <c r="U8" s="57"/>
-      <c r="V8" s="45"/>
-      <c r="W8" s="50"/>
-      <c r="X8" s="57"/>
-      <c r="Y8" s="57"/>
-      <c r="Z8" s="45"/>
-      <c r="AA8" s="46"/>
-      <c r="AB8" s="57"/>
-      <c r="AC8" s="57"/>
-      <c r="AD8" s="47"/>
-      <c r="AE8" s="45"/>
-      <c r="AF8" s="46"/>
-      <c r="AG8" s="57"/>
-      <c r="AH8" s="57"/>
-      <c r="AI8" s="57"/>
-      <c r="AJ8" s="57"/>
-      <c r="AK8" s="57"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="41" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="56"/>
+      <c r="K8" s="56"/>
+      <c r="L8" s="46"/>
+      <c r="M8" s="56"/>
+      <c r="N8" s="44"/>
+      <c r="O8" s="45"/>
+      <c r="P8" s="56"/>
+      <c r="Q8" s="56"/>
+      <c r="R8" s="56"/>
+      <c r="S8" s="56"/>
+      <c r="T8" s="56"/>
+      <c r="U8" s="56"/>
+      <c r="V8" s="44"/>
+      <c r="W8" s="49"/>
+      <c r="X8" s="56"/>
+      <c r="Y8" s="56"/>
+      <c r="Z8" s="44"/>
+      <c r="AA8" s="45"/>
+      <c r="AB8" s="56"/>
+      <c r="AC8" s="56"/>
+      <c r="AD8" s="46"/>
+      <c r="AE8" s="44"/>
+      <c r="AF8" s="45"/>
+      <c r="AG8" s="56"/>
+      <c r="AH8" s="56"/>
+      <c r="AI8" s="56"/>
+      <c r="AJ8" s="56"/>
+      <c r="AK8" s="56"/>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="41"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="56"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="56"/>
-      <c r="K9" s="43"/>
-      <c r="L9" s="47"/>
-      <c r="M9" s="56"/>
-      <c r="N9" s="48"/>
-      <c r="O9" s="55"/>
-      <c r="P9" s="43"/>
-      <c r="Q9" s="43"/>
-      <c r="R9" s="43"/>
-      <c r="S9" s="43"/>
-      <c r="T9" s="43"/>
-      <c r="U9" s="43"/>
-      <c r="V9" s="48"/>
-      <c r="W9" s="50"/>
-      <c r="X9" s="43"/>
-      <c r="Y9" s="43"/>
-      <c r="Z9" s="48"/>
-      <c r="AA9" s="49"/>
-      <c r="AB9" s="43"/>
-      <c r="AC9" s="43"/>
-      <c r="AD9" s="47"/>
-      <c r="AE9" s="48"/>
-      <c r="AF9" s="49"/>
-      <c r="AG9" s="43"/>
-      <c r="AH9" s="43"/>
-      <c r="AI9" s="43"/>
-      <c r="AJ9" s="43"/>
-      <c r="AK9" s="43"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="55"/>
+      <c r="J9" s="55"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="46"/>
+      <c r="M9" s="55"/>
+      <c r="N9" s="47"/>
+      <c r="O9" s="54"/>
+      <c r="P9" s="42"/>
+      <c r="Q9" s="42"/>
+      <c r="R9" s="42"/>
+      <c r="S9" s="42"/>
+      <c r="T9" s="42"/>
+      <c r="U9" s="42"/>
+      <c r="V9" s="47"/>
+      <c r="W9" s="49"/>
+      <c r="X9" s="42"/>
+      <c r="Y9" s="42"/>
+      <c r="Z9" s="47"/>
+      <c r="AA9" s="48"/>
+      <c r="AB9" s="42"/>
+      <c r="AC9" s="42"/>
+      <c r="AD9" s="46"/>
+      <c r="AE9" s="47"/>
+      <c r="AF9" s="48"/>
+      <c r="AG9" s="42"/>
+      <c r="AH9" s="42"/>
+      <c r="AI9" s="42"/>
+      <c r="AJ9" s="42"/>
+      <c r="AK9" s="42"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="41"/>
-      <c r="C10" s="42" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="43"/>
-      <c r="K10" s="43"/>
-      <c r="L10" s="47"/>
-      <c r="M10" s="43"/>
-      <c r="N10" s="48"/>
-      <c r="O10" s="49"/>
-      <c r="P10" s="43"/>
-      <c r="Q10" s="43"/>
-      <c r="R10" s="43"/>
-      <c r="S10" s="43"/>
-      <c r="T10" s="43"/>
-      <c r="U10" s="43"/>
-      <c r="V10" s="45"/>
-      <c r="W10" s="50"/>
-      <c r="X10" s="57"/>
-      <c r="Y10" s="57"/>
-      <c r="Z10" s="45"/>
-      <c r="AA10" s="49"/>
-      <c r="AB10" s="43"/>
-      <c r="AC10" s="43"/>
-      <c r="AD10" s="47"/>
-      <c r="AE10" s="48"/>
-      <c r="AF10" s="49"/>
-      <c r="AG10" s="43"/>
-      <c r="AH10" s="43"/>
-      <c r="AI10" s="43"/>
-      <c r="AJ10" s="43"/>
-      <c r="AK10" s="43"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="46"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="47"/>
+      <c r="O10" s="48"/>
+      <c r="P10" s="42"/>
+      <c r="Q10" s="42"/>
+      <c r="R10" s="42"/>
+      <c r="S10" s="42"/>
+      <c r="T10" s="42"/>
+      <c r="U10" s="42"/>
+      <c r="V10" s="44"/>
+      <c r="W10" s="49"/>
+      <c r="X10" s="56"/>
+      <c r="Y10" s="56"/>
+      <c r="Z10" s="44"/>
+      <c r="AA10" s="48"/>
+      <c r="AB10" s="42"/>
+      <c r="AC10" s="42"/>
+      <c r="AD10" s="46"/>
+      <c r="AE10" s="47"/>
+      <c r="AF10" s="48"/>
+      <c r="AG10" s="42"/>
+      <c r="AH10" s="42"/>
+      <c r="AI10" s="42"/>
+      <c r="AJ10" s="42"/>
+      <c r="AK10" s="42"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="41"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="43"/>
-      <c r="K11" s="43"/>
-      <c r="L11" s="47"/>
-      <c r="M11" s="43"/>
-      <c r="N11" s="48"/>
-      <c r="O11" s="49"/>
-      <c r="P11" s="43"/>
-      <c r="Q11" s="43"/>
-      <c r="R11" s="43"/>
-      <c r="S11" s="43"/>
-      <c r="T11" s="43"/>
-      <c r="U11" s="43"/>
-      <c r="V11" s="48"/>
-      <c r="W11" s="50"/>
-      <c r="X11" s="43"/>
-      <c r="Y11" s="43"/>
-      <c r="Z11" s="48"/>
-      <c r="AA11" s="49"/>
-      <c r="AB11" s="43"/>
-      <c r="AC11" s="43"/>
-      <c r="AD11" s="47"/>
-      <c r="AE11" s="48"/>
-      <c r="AF11" s="49"/>
-      <c r="AG11" s="43"/>
-      <c r="AH11" s="43"/>
-      <c r="AI11" s="43"/>
-      <c r="AJ11" s="43"/>
-      <c r="AK11" s="43"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="46"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="47"/>
+      <c r="O11" s="48"/>
+      <c r="P11" s="42"/>
+      <c r="Q11" s="42"/>
+      <c r="R11" s="42"/>
+      <c r="S11" s="42"/>
+      <c r="T11" s="42"/>
+      <c r="U11" s="42"/>
+      <c r="V11" s="47"/>
+      <c r="W11" s="49"/>
+      <c r="X11" s="42"/>
+      <c r="Y11" s="42"/>
+      <c r="Z11" s="47"/>
+      <c r="AA11" s="48"/>
+      <c r="AB11" s="42"/>
+      <c r="AC11" s="42"/>
+      <c r="AD11" s="46"/>
+      <c r="AE11" s="47"/>
+      <c r="AF11" s="48"/>
+      <c r="AG11" s="42"/>
+      <c r="AH11" s="42"/>
+      <c r="AI11" s="42"/>
+      <c r="AJ11" s="42"/>
+      <c r="AK11" s="42"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="41"/>
-      <c r="C12" s="42" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="43"/>
-      <c r="N12" s="48"/>
-      <c r="O12" s="49"/>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="43"/>
-      <c r="S12" s="43"/>
-      <c r="T12" s="43"/>
-      <c r="U12" s="43"/>
-      <c r="V12" s="48"/>
-      <c r="W12" s="50"/>
-      <c r="X12" s="43"/>
-      <c r="Y12" s="43"/>
-      <c r="Z12" s="48"/>
-      <c r="AA12" s="49"/>
-      <c r="AB12" s="43"/>
-      <c r="AC12" s="43"/>
-      <c r="AD12" s="47"/>
-      <c r="AE12" s="48"/>
-      <c r="AF12" s="46"/>
-      <c r="AG12" s="57"/>
-      <c r="AH12" s="57"/>
-      <c r="AI12" s="57"/>
-      <c r="AJ12" s="57"/>
-      <c r="AK12" s="57"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="47"/>
+      <c r="O12" s="48"/>
+      <c r="P12" s="42"/>
+      <c r="Q12" s="42"/>
+      <c r="R12" s="42"/>
+      <c r="S12" s="42"/>
+      <c r="T12" s="42"/>
+      <c r="U12" s="42"/>
+      <c r="V12" s="47"/>
+      <c r="W12" s="49"/>
+      <c r="X12" s="42"/>
+      <c r="Y12" s="42"/>
+      <c r="Z12" s="47"/>
+      <c r="AA12" s="48"/>
+      <c r="AB12" s="42"/>
+      <c r="AC12" s="42"/>
+      <c r="AD12" s="46"/>
+      <c r="AE12" s="47"/>
+      <c r="AF12" s="45"/>
+      <c r="AG12" s="56"/>
+      <c r="AH12" s="56"/>
+      <c r="AI12" s="56"/>
+      <c r="AJ12" s="56"/>
+      <c r="AK12" s="56"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="41"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="47"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="48"/>
-      <c r="O13" s="49"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="43"/>
-      <c r="T13" s="43"/>
-      <c r="U13" s="43"/>
-      <c r="V13" s="48"/>
-      <c r="W13" s="50"/>
-      <c r="X13" s="43"/>
-      <c r="Y13" s="43"/>
-      <c r="Z13" s="48"/>
-      <c r="AA13" s="49"/>
-      <c r="AB13" s="43"/>
-      <c r="AC13" s="43"/>
-      <c r="AD13" s="47"/>
-      <c r="AE13" s="48"/>
-      <c r="AF13" s="49"/>
-      <c r="AG13" s="43"/>
-      <c r="AH13" s="43"/>
-      <c r="AI13" s="43"/>
-      <c r="AJ13" s="43"/>
-      <c r="AK13" s="43"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="46"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="47"/>
+      <c r="O13" s="48"/>
+      <c r="P13" s="42"/>
+      <c r="Q13" s="42"/>
+      <c r="R13" s="42"/>
+      <c r="S13" s="42"/>
+      <c r="T13" s="42"/>
+      <c r="U13" s="42"/>
+      <c r="V13" s="47"/>
+      <c r="W13" s="49"/>
+      <c r="X13" s="42"/>
+      <c r="Y13" s="42"/>
+      <c r="Z13" s="47"/>
+      <c r="AA13" s="48"/>
+      <c r="AB13" s="42"/>
+      <c r="AC13" s="42"/>
+      <c r="AD13" s="46"/>
+      <c r="AE13" s="47"/>
+      <c r="AF13" s="48"/>
+      <c r="AG13" s="42"/>
+      <c r="AH13" s="42"/>
+      <c r="AI13" s="42"/>
+      <c r="AJ13" s="42"/>
+      <c r="AK13" s="42"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="58" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" s="59" t="s">
+      <c r="B14" s="57" t="s">
         <v>88</v>
       </c>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="61"/>
-      <c r="K14" s="61"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="61"/>
-      <c r="N14" s="62"/>
-      <c r="O14" s="60"/>
-      <c r="P14" s="61"/>
-      <c r="Q14" s="61"/>
-      <c r="R14" s="61"/>
-      <c r="S14" s="61"/>
-      <c r="T14" s="61"/>
-      <c r="U14" s="61"/>
-      <c r="V14" s="62"/>
-      <c r="W14" s="50"/>
-      <c r="X14" s="61"/>
-      <c r="Y14" s="61"/>
-      <c r="Z14" s="62"/>
-      <c r="AA14" s="60"/>
-      <c r="AB14" s="61"/>
-      <c r="AC14" s="61"/>
-      <c r="AD14" s="47"/>
-      <c r="AE14" s="62"/>
-      <c r="AF14" s="60"/>
-      <c r="AG14" s="61"/>
-      <c r="AH14" s="61"/>
-      <c r="AI14" s="61"/>
-      <c r="AJ14" s="61"/>
-      <c r="AK14" s="61"/>
+      <c r="C14" s="58" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="60"/>
+      <c r="K14" s="60"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="60"/>
+      <c r="N14" s="61"/>
+      <c r="O14" s="59"/>
+      <c r="P14" s="60"/>
+      <c r="Q14" s="60"/>
+      <c r="R14" s="60"/>
+      <c r="S14" s="60"/>
+      <c r="T14" s="60"/>
+      <c r="U14" s="60"/>
+      <c r="V14" s="61"/>
+      <c r="W14" s="49"/>
+      <c r="X14" s="60"/>
+      <c r="Y14" s="60"/>
+      <c r="Z14" s="61"/>
+      <c r="AA14" s="59"/>
+      <c r="AB14" s="60"/>
+      <c r="AC14" s="60"/>
+      <c r="AD14" s="46"/>
+      <c r="AE14" s="61"/>
+      <c r="AF14" s="59"/>
+      <c r="AG14" s="60"/>
+      <c r="AH14" s="60"/>
+      <c r="AI14" s="60"/>
+      <c r="AJ14" s="60"/>
+      <c r="AK14" s="60"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="58"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="56"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="61"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="61"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="61"/>
-      <c r="N15" s="62"/>
-      <c r="O15" s="60"/>
-      <c r="P15" s="61"/>
-      <c r="Q15" s="61"/>
-      <c r="R15" s="61"/>
-      <c r="S15" s="61"/>
-      <c r="T15" s="61"/>
-      <c r="U15" s="61"/>
-      <c r="V15" s="62"/>
-      <c r="W15" s="50"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="61"/>
-      <c r="Z15" s="62"/>
-      <c r="AA15" s="60"/>
-      <c r="AB15" s="61"/>
-      <c r="AC15" s="61"/>
-      <c r="AD15" s="47"/>
-      <c r="AE15" s="62"/>
-      <c r="AF15" s="60"/>
-      <c r="AG15" s="61"/>
-      <c r="AH15" s="61"/>
-      <c r="AI15" s="61"/>
-      <c r="AJ15" s="61"/>
-      <c r="AK15" s="61"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="59"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="60"/>
+      <c r="L15" s="46"/>
+      <c r="M15" s="60"/>
+      <c r="N15" s="61"/>
+      <c r="O15" s="59"/>
+      <c r="P15" s="60"/>
+      <c r="Q15" s="60"/>
+      <c r="R15" s="60"/>
+      <c r="S15" s="60"/>
+      <c r="T15" s="60"/>
+      <c r="U15" s="60"/>
+      <c r="V15" s="61"/>
+      <c r="W15" s="49"/>
+      <c r="X15" s="60"/>
+      <c r="Y15" s="60"/>
+      <c r="Z15" s="61"/>
+      <c r="AA15" s="59"/>
+      <c r="AB15" s="60"/>
+      <c r="AC15" s="60"/>
+      <c r="AD15" s="46"/>
+      <c r="AE15" s="61"/>
+      <c r="AF15" s="59"/>
+      <c r="AG15" s="60"/>
+      <c r="AH15" s="60"/>
+      <c r="AI15" s="60"/>
+      <c r="AJ15" s="60"/>
+      <c r="AK15" s="60"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="58"/>
-      <c r="C16" s="59" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="62"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="61"/>
-      <c r="J16" s="61"/>
-      <c r="K16" s="61"/>
-      <c r="L16" s="47"/>
-      <c r="M16" s="61"/>
-      <c r="N16" s="62"/>
-      <c r="O16" s="60"/>
-      <c r="P16" s="61"/>
-      <c r="Q16" s="61"/>
-      <c r="R16" s="61"/>
-      <c r="S16" s="61"/>
-      <c r="T16" s="61"/>
-      <c r="U16" s="61"/>
-      <c r="V16" s="62"/>
-      <c r="W16" s="50"/>
-      <c r="X16" s="61"/>
-      <c r="Y16" s="61"/>
-      <c r="Z16" s="62"/>
-      <c r="AA16" s="60"/>
-      <c r="AB16" s="61"/>
-      <c r="AC16" s="61"/>
-      <c r="AD16" s="47"/>
-      <c r="AE16" s="62"/>
-      <c r="AF16" s="60"/>
-      <c r="AG16" s="61"/>
-      <c r="AH16" s="61"/>
-      <c r="AI16" s="61"/>
-      <c r="AJ16" s="61"/>
-      <c r="AK16" s="61"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="58" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="59"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="60"/>
+      <c r="L16" s="46"/>
+      <c r="M16" s="60"/>
+      <c r="N16" s="61"/>
+      <c r="O16" s="59"/>
+      <c r="P16" s="60"/>
+      <c r="Q16" s="60"/>
+      <c r="R16" s="60"/>
+      <c r="S16" s="60"/>
+      <c r="T16" s="60"/>
+      <c r="U16" s="60"/>
+      <c r="V16" s="61"/>
+      <c r="W16" s="49"/>
+      <c r="X16" s="60"/>
+      <c r="Y16" s="60"/>
+      <c r="Z16" s="61"/>
+      <c r="AA16" s="59"/>
+      <c r="AB16" s="60"/>
+      <c r="AC16" s="60"/>
+      <c r="AD16" s="46"/>
+      <c r="AE16" s="61"/>
+      <c r="AF16" s="59"/>
+      <c r="AG16" s="60"/>
+      <c r="AH16" s="60"/>
+      <c r="AI16" s="60"/>
+      <c r="AJ16" s="60"/>
+      <c r="AK16" s="60"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="58"/>
-      <c r="C17" s="59"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="64"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="60"/>
-      <c r="I17" s="61"/>
-      <c r="J17" s="61"/>
-      <c r="K17" s="61"/>
-      <c r="L17" s="47"/>
-      <c r="M17" s="61"/>
-      <c r="N17" s="62"/>
-      <c r="O17" s="60"/>
-      <c r="P17" s="61"/>
-      <c r="Q17" s="61"/>
-      <c r="R17" s="61"/>
-      <c r="S17" s="61"/>
-      <c r="T17" s="61"/>
-      <c r="U17" s="61"/>
-      <c r="V17" s="62"/>
-      <c r="W17" s="50"/>
-      <c r="X17" s="61"/>
-      <c r="Y17" s="61"/>
-      <c r="Z17" s="62"/>
-      <c r="AA17" s="60"/>
-      <c r="AB17" s="61"/>
-      <c r="AC17" s="61"/>
-      <c r="AD17" s="47"/>
-      <c r="AE17" s="62"/>
-      <c r="AF17" s="60"/>
-      <c r="AG17" s="61"/>
-      <c r="AH17" s="61"/>
-      <c r="AI17" s="61"/>
-      <c r="AJ17" s="61"/>
-      <c r="AK17" s="61"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="60"/>
+      <c r="K17" s="60"/>
+      <c r="L17" s="46"/>
+      <c r="M17" s="60"/>
+      <c r="N17" s="61"/>
+      <c r="O17" s="59"/>
+      <c r="P17" s="60"/>
+      <c r="Q17" s="60"/>
+      <c r="R17" s="60"/>
+      <c r="S17" s="60"/>
+      <c r="T17" s="60"/>
+      <c r="U17" s="60"/>
+      <c r="V17" s="61"/>
+      <c r="W17" s="49"/>
+      <c r="X17" s="60"/>
+      <c r="Y17" s="60"/>
+      <c r="Z17" s="61"/>
+      <c r="AA17" s="59"/>
+      <c r="AB17" s="60"/>
+      <c r="AC17" s="60"/>
+      <c r="AD17" s="46"/>
+      <c r="AE17" s="61"/>
+      <c r="AF17" s="59"/>
+      <c r="AG17" s="60"/>
+      <c r="AH17" s="60"/>
+      <c r="AI17" s="60"/>
+      <c r="AJ17" s="60"/>
+      <c r="AK17" s="60"/>
       <c r="AN17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="58"/>
-      <c r="C18" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="64"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="60"/>
-      <c r="I18" s="61"/>
-      <c r="J18" s="61"/>
-      <c r="K18" s="61"/>
-      <c r="L18" s="47"/>
-      <c r="M18" s="61"/>
-      <c r="N18" s="62"/>
-      <c r="O18" s="60"/>
-      <c r="P18" s="61"/>
-      <c r="Q18" s="61"/>
-      <c r="R18" s="61"/>
-      <c r="S18" s="61"/>
-      <c r="T18" s="61"/>
-      <c r="U18" s="61"/>
-      <c r="V18" s="62"/>
-      <c r="W18" s="50"/>
-      <c r="X18" s="61"/>
-      <c r="Y18" s="61"/>
-      <c r="Z18" s="62"/>
-      <c r="AA18" s="60"/>
-      <c r="AB18" s="61"/>
-      <c r="AC18" s="61"/>
-      <c r="AD18" s="47"/>
-      <c r="AE18" s="62"/>
-      <c r="AF18" s="60"/>
-      <c r="AG18" s="61"/>
-      <c r="AH18" s="61"/>
-      <c r="AI18" s="61"/>
-      <c r="AJ18" s="61"/>
-      <c r="AK18" s="61"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="58" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="60"/>
+      <c r="K18" s="60"/>
+      <c r="L18" s="46"/>
+      <c r="M18" s="60"/>
+      <c r="N18" s="61"/>
+      <c r="O18" s="59"/>
+      <c r="P18" s="60"/>
+      <c r="Q18" s="60"/>
+      <c r="R18" s="60"/>
+      <c r="S18" s="60"/>
+      <c r="T18" s="60"/>
+      <c r="U18" s="60"/>
+      <c r="V18" s="61"/>
+      <c r="W18" s="49"/>
+      <c r="X18" s="60"/>
+      <c r="Y18" s="60"/>
+      <c r="Z18" s="61"/>
+      <c r="AA18" s="59"/>
+      <c r="AB18" s="60"/>
+      <c r="AC18" s="60"/>
+      <c r="AD18" s="46"/>
+      <c r="AE18" s="61"/>
+      <c r="AF18" s="59"/>
+      <c r="AG18" s="60"/>
+      <c r="AH18" s="60"/>
+      <c r="AI18" s="60"/>
+      <c r="AJ18" s="60"/>
+      <c r="AK18" s="60"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="58"/>
-      <c r="C19" s="59"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="61"/>
-      <c r="J19" s="61"/>
-      <c r="K19" s="61"/>
-      <c r="L19" s="47"/>
-      <c r="M19" s="61"/>
-      <c r="N19" s="62"/>
-      <c r="O19" s="60"/>
-      <c r="P19" s="61"/>
-      <c r="Q19" s="61"/>
-      <c r="R19" s="61"/>
-      <c r="S19" s="61"/>
-      <c r="T19" s="61"/>
-      <c r="U19" s="61"/>
-      <c r="V19" s="62"/>
-      <c r="W19" s="50"/>
-      <c r="X19" s="61"/>
-      <c r="Y19" s="61"/>
-      <c r="Z19" s="62"/>
-      <c r="AA19" s="60"/>
-      <c r="AB19" s="61"/>
-      <c r="AC19" s="61"/>
-      <c r="AD19" s="47"/>
-      <c r="AE19" s="62"/>
-      <c r="AF19" s="60"/>
-      <c r="AG19" s="61"/>
-      <c r="AH19" s="61"/>
-      <c r="AI19" s="61"/>
-      <c r="AJ19" s="61"/>
-      <c r="AK19" s="61"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="64"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="60"/>
+      <c r="L19" s="46"/>
+      <c r="M19" s="60"/>
+      <c r="N19" s="61"/>
+      <c r="O19" s="59"/>
+      <c r="P19" s="60"/>
+      <c r="Q19" s="60"/>
+      <c r="R19" s="60"/>
+      <c r="S19" s="60"/>
+      <c r="T19" s="60"/>
+      <c r="U19" s="60"/>
+      <c r="V19" s="61"/>
+      <c r="W19" s="49"/>
+      <c r="X19" s="60"/>
+      <c r="Y19" s="60"/>
+      <c r="Z19" s="61"/>
+      <c r="AA19" s="59"/>
+      <c r="AB19" s="60"/>
+      <c r="AC19" s="60"/>
+      <c r="AD19" s="46"/>
+      <c r="AE19" s="61"/>
+      <c r="AF19" s="59"/>
+      <c r="AG19" s="60"/>
+      <c r="AH19" s="60"/>
+      <c r="AI19" s="60"/>
+      <c r="AJ19" s="60"/>
+      <c r="AK19" s="60"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="58"/>
-      <c r="C20" s="59" t="s">
-        <v>92</v>
-      </c>
-      <c r="D20" s="61"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="64"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="61"/>
-      <c r="K20" s="61"/>
-      <c r="L20" s="47"/>
-      <c r="M20" s="61"/>
-      <c r="N20" s="62"/>
-      <c r="O20" s="60"/>
-      <c r="P20" s="61"/>
-      <c r="Q20" s="61"/>
-      <c r="R20" s="61"/>
-      <c r="S20" s="61"/>
-      <c r="T20" s="61"/>
-      <c r="U20" s="61"/>
-      <c r="V20" s="62"/>
-      <c r="W20" s="50"/>
-      <c r="X20" s="61"/>
-      <c r="Y20" s="61"/>
-      <c r="Z20" s="62"/>
-      <c r="AA20" s="60"/>
-      <c r="AB20" s="61"/>
-      <c r="AC20" s="61"/>
-      <c r="AD20" s="47"/>
-      <c r="AE20" s="62"/>
-      <c r="AF20" s="60"/>
-      <c r="AG20" s="61"/>
-      <c r="AH20" s="61"/>
-      <c r="AI20" s="61"/>
-      <c r="AJ20" s="61"/>
-      <c r="AK20" s="61"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="58" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="60"/>
+      <c r="L20" s="46"/>
+      <c r="M20" s="60"/>
+      <c r="N20" s="61"/>
+      <c r="O20" s="59"/>
+      <c r="P20" s="60"/>
+      <c r="Q20" s="60"/>
+      <c r="R20" s="60"/>
+      <c r="S20" s="60"/>
+      <c r="T20" s="60"/>
+      <c r="U20" s="60"/>
+      <c r="V20" s="61"/>
+      <c r="W20" s="49"/>
+      <c r="X20" s="60"/>
+      <c r="Y20" s="60"/>
+      <c r="Z20" s="61"/>
+      <c r="AA20" s="59"/>
+      <c r="AB20" s="60"/>
+      <c r="AC20" s="60"/>
+      <c r="AD20" s="46"/>
+      <c r="AE20" s="61"/>
+      <c r="AF20" s="59"/>
+      <c r="AG20" s="60"/>
+      <c r="AH20" s="60"/>
+      <c r="AI20" s="60"/>
+      <c r="AJ20" s="60"/>
+      <c r="AK20" s="60"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="58"/>
-      <c r="C21" s="59"/>
-      <c r="D21" s="61"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="60"/>
-      <c r="I21" s="56"/>
-      <c r="J21" s="61"/>
-      <c r="K21" s="61"/>
-      <c r="L21" s="47"/>
-      <c r="M21" s="61"/>
-      <c r="N21" s="62"/>
-      <c r="O21" s="60"/>
-      <c r="P21" s="61"/>
-      <c r="Q21" s="61"/>
-      <c r="R21" s="61"/>
-      <c r="S21" s="61"/>
-      <c r="T21" s="61"/>
-      <c r="U21" s="61"/>
-      <c r="V21" s="62"/>
-      <c r="W21" s="50"/>
-      <c r="X21" s="61"/>
-      <c r="Y21" s="61"/>
-      <c r="Z21" s="62"/>
-      <c r="AA21" s="60"/>
-      <c r="AB21" s="61"/>
-      <c r="AC21" s="61"/>
-      <c r="AD21" s="47"/>
-      <c r="AE21" s="62"/>
-      <c r="AF21" s="60"/>
-      <c r="AG21" s="61"/>
-      <c r="AH21" s="61"/>
-      <c r="AI21" s="61"/>
-      <c r="AJ21" s="61"/>
-      <c r="AK21" s="61"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="63"/>
+      <c r="G21" s="61"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="55"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="60"/>
+      <c r="L21" s="46"/>
+      <c r="M21" s="60"/>
+      <c r="N21" s="61"/>
+      <c r="O21" s="59"/>
+      <c r="P21" s="60"/>
+      <c r="Q21" s="60"/>
+      <c r="R21" s="60"/>
+      <c r="S21" s="60"/>
+      <c r="T21" s="60"/>
+      <c r="U21" s="60"/>
+      <c r="V21" s="61"/>
+      <c r="W21" s="49"/>
+      <c r="X21" s="60"/>
+      <c r="Y21" s="60"/>
+      <c r="Z21" s="61"/>
+      <c r="AA21" s="59"/>
+      <c r="AB21" s="60"/>
+      <c r="AC21" s="60"/>
+      <c r="AD21" s="46"/>
+      <c r="AE21" s="61"/>
+      <c r="AF21" s="59"/>
+      <c r="AG21" s="60"/>
+      <c r="AH21" s="60"/>
+      <c r="AI21" s="60"/>
+      <c r="AJ21" s="60"/>
+      <c r="AK21" s="60"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="58"/>
-      <c r="C22" s="59" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61"/>
-      <c r="F22" s="64"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="61"/>
-      <c r="K22" s="61"/>
-      <c r="L22" s="47"/>
-      <c r="M22" s="61"/>
-      <c r="N22" s="62"/>
-      <c r="O22" s="60"/>
-      <c r="P22" s="61"/>
-      <c r="Q22" s="61"/>
-      <c r="R22" s="61"/>
-      <c r="S22" s="61"/>
-      <c r="T22" s="61"/>
-      <c r="U22" s="61"/>
-      <c r="V22" s="62"/>
-      <c r="W22" s="50"/>
-      <c r="X22" s="61"/>
-      <c r="Y22" s="61"/>
-      <c r="Z22" s="62"/>
-      <c r="AA22" s="60"/>
-      <c r="AB22" s="61"/>
-      <c r="AC22" s="61"/>
-      <c r="AD22" s="47"/>
-      <c r="AE22" s="62"/>
-      <c r="AF22" s="60"/>
-      <c r="AG22" s="61"/>
-      <c r="AH22" s="61"/>
-      <c r="AI22" s="61"/>
-      <c r="AJ22" s="61"/>
-      <c r="AK22" s="61"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="60"/>
+      <c r="L22" s="46"/>
+      <c r="M22" s="60"/>
+      <c r="N22" s="61"/>
+      <c r="O22" s="59"/>
+      <c r="P22" s="60"/>
+      <c r="Q22" s="60"/>
+      <c r="R22" s="60"/>
+      <c r="S22" s="60"/>
+      <c r="T22" s="60"/>
+      <c r="U22" s="60"/>
+      <c r="V22" s="61"/>
+      <c r="W22" s="49"/>
+      <c r="X22" s="60"/>
+      <c r="Y22" s="60"/>
+      <c r="Z22" s="61"/>
+      <c r="AA22" s="59"/>
+      <c r="AB22" s="60"/>
+      <c r="AC22" s="60"/>
+      <c r="AD22" s="46"/>
+      <c r="AE22" s="61"/>
+      <c r="AF22" s="59"/>
+      <c r="AG22" s="60"/>
+      <c r="AH22" s="60"/>
+      <c r="AI22" s="60"/>
+      <c r="AJ22" s="60"/>
+      <c r="AK22" s="60"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="58"/>
-      <c r="C23" s="59"/>
-      <c r="D23" s="61"/>
-      <c r="E23" s="61"/>
-      <c r="F23" s="64"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="60"/>
-      <c r="I23" s="56"/>
-      <c r="J23" s="52"/>
-      <c r="K23" s="61"/>
-      <c r="L23" s="47"/>
-      <c r="M23" s="61"/>
-      <c r="N23" s="62"/>
-      <c r="O23" s="60"/>
-      <c r="P23" s="61"/>
-      <c r="Q23" s="61"/>
-      <c r="R23" s="61"/>
-      <c r="S23" s="61"/>
-      <c r="T23" s="61"/>
-      <c r="U23" s="61"/>
-      <c r="V23" s="62"/>
-      <c r="W23" s="50"/>
-      <c r="X23" s="61"/>
-      <c r="Y23" s="61"/>
-      <c r="Z23" s="62"/>
-      <c r="AA23" s="60"/>
-      <c r="AB23" s="61"/>
-      <c r="AC23" s="61"/>
-      <c r="AD23" s="47"/>
-      <c r="AE23" s="62"/>
-      <c r="AF23" s="60"/>
-      <c r="AG23" s="61"/>
-      <c r="AH23" s="61"/>
-      <c r="AI23" s="61"/>
-      <c r="AJ23" s="61"/>
-      <c r="AK23" s="61"/>
+      <c r="B23" s="57"/>
+      <c r="C23" s="58"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="63"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="55"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="46"/>
+      <c r="M23" s="60"/>
+      <c r="N23" s="61"/>
+      <c r="O23" s="59"/>
+      <c r="P23" s="60"/>
+      <c r="Q23" s="60"/>
+      <c r="R23" s="60"/>
+      <c r="S23" s="60"/>
+      <c r="T23" s="60"/>
+      <c r="U23" s="60"/>
+      <c r="V23" s="61"/>
+      <c r="W23" s="49"/>
+      <c r="X23" s="60"/>
+      <c r="Y23" s="60"/>
+      <c r="Z23" s="61"/>
+      <c r="AA23" s="59"/>
+      <c r="AB23" s="60"/>
+      <c r="AC23" s="60"/>
+      <c r="AD23" s="46"/>
+      <c r="AE23" s="61"/>
+      <c r="AF23" s="59"/>
+      <c r="AG23" s="60"/>
+      <c r="AH23" s="60"/>
+      <c r="AI23" s="60"/>
+      <c r="AJ23" s="60"/>
+      <c r="AK23" s="60"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="58"/>
-      <c r="C24" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="D24" s="61"/>
-      <c r="E24" s="61"/>
-      <c r="F24" s="64"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="60"/>
-      <c r="I24" s="57"/>
-      <c r="J24" s="61"/>
-      <c r="K24" s="61"/>
-      <c r="L24" s="47"/>
-      <c r="M24" s="61"/>
-      <c r="N24" s="62"/>
-      <c r="O24" s="60"/>
-      <c r="P24" s="61"/>
-      <c r="Q24" s="61"/>
-      <c r="R24" s="61"/>
-      <c r="S24" s="61"/>
-      <c r="T24" s="61"/>
-      <c r="U24" s="61"/>
-      <c r="V24" s="62"/>
-      <c r="W24" s="50"/>
-      <c r="X24" s="61"/>
-      <c r="Y24" s="61"/>
-      <c r="Z24" s="62"/>
-      <c r="AA24" s="60"/>
-      <c r="AB24" s="61"/>
-      <c r="AC24" s="61"/>
-      <c r="AD24" s="47"/>
-      <c r="AE24" s="62"/>
-      <c r="AF24" s="60"/>
-      <c r="AG24" s="61"/>
-      <c r="AH24" s="61"/>
-      <c r="AI24" s="61"/>
-      <c r="AJ24" s="61"/>
-      <c r="AK24" s="61"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="58" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24" s="60"/>
+      <c r="E24" s="60"/>
+      <c r="F24" s="63"/>
+      <c r="G24" s="61"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="56"/>
+      <c r="J24" s="60"/>
+      <c r="K24" s="60"/>
+      <c r="L24" s="46"/>
+      <c r="M24" s="60"/>
+      <c r="N24" s="61"/>
+      <c r="O24" s="59"/>
+      <c r="P24" s="60"/>
+      <c r="Q24" s="60"/>
+      <c r="R24" s="60"/>
+      <c r="S24" s="60"/>
+      <c r="T24" s="60"/>
+      <c r="U24" s="60"/>
+      <c r="V24" s="61"/>
+      <c r="W24" s="49"/>
+      <c r="X24" s="60"/>
+      <c r="Y24" s="60"/>
+      <c r="Z24" s="61"/>
+      <c r="AA24" s="59"/>
+      <c r="AB24" s="60"/>
+      <c r="AC24" s="60"/>
+      <c r="AD24" s="46"/>
+      <c r="AE24" s="61"/>
+      <c r="AF24" s="59"/>
+      <c r="AG24" s="60"/>
+      <c r="AH24" s="60"/>
+      <c r="AI24" s="60"/>
+      <c r="AJ24" s="60"/>
+      <c r="AK24" s="60"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="58"/>
-      <c r="C25" s="59"/>
-      <c r="D25" s="61"/>
-      <c r="E25" s="61"/>
-      <c r="F25" s="64"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="60"/>
-      <c r="I25" s="61"/>
-      <c r="J25" s="52"/>
-      <c r="K25" s="61"/>
-      <c r="L25" s="47"/>
-      <c r="M25" s="61"/>
-      <c r="N25" s="62"/>
-      <c r="O25" s="60"/>
-      <c r="P25" s="61"/>
-      <c r="Q25" s="61"/>
-      <c r="R25" s="61"/>
-      <c r="S25" s="61"/>
-      <c r="T25" s="61"/>
-      <c r="U25" s="61"/>
-      <c r="V25" s="62"/>
-      <c r="W25" s="50"/>
-      <c r="X25" s="61"/>
-      <c r="Y25" s="61"/>
-      <c r="Z25" s="62"/>
-      <c r="AA25" s="60"/>
-      <c r="AB25" s="61"/>
-      <c r="AC25" s="61"/>
-      <c r="AD25" s="47"/>
-      <c r="AE25" s="62"/>
-      <c r="AF25" s="60"/>
-      <c r="AG25" s="61"/>
-      <c r="AH25" s="61"/>
-      <c r="AI25" s="61"/>
-      <c r="AJ25" s="61"/>
-      <c r="AK25" s="61"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="60"/>
+      <c r="E25" s="60"/>
+      <c r="F25" s="63"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="60"/>
+      <c r="J25" s="51"/>
+      <c r="K25" s="60"/>
+      <c r="L25" s="46"/>
+      <c r="M25" s="60"/>
+      <c r="N25" s="61"/>
+      <c r="O25" s="59"/>
+      <c r="P25" s="60"/>
+      <c r="Q25" s="60"/>
+      <c r="R25" s="60"/>
+      <c r="S25" s="60"/>
+      <c r="T25" s="60"/>
+      <c r="U25" s="60"/>
+      <c r="V25" s="61"/>
+      <c r="W25" s="49"/>
+      <c r="X25" s="60"/>
+      <c r="Y25" s="60"/>
+      <c r="Z25" s="61"/>
+      <c r="AA25" s="59"/>
+      <c r="AB25" s="60"/>
+      <c r="AC25" s="60"/>
+      <c r="AD25" s="46"/>
+      <c r="AE25" s="61"/>
+      <c r="AF25" s="59"/>
+      <c r="AG25" s="60"/>
+      <c r="AH25" s="60"/>
+      <c r="AI25" s="60"/>
+      <c r="AJ25" s="60"/>
+      <c r="AK25" s="60"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="C26" s="42" t="s">
+      <c r="B26" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="51"/>
-      <c r="G26" s="48"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="43"/>
-      <c r="K26" s="43"/>
-      <c r="L26" s="47"/>
-      <c r="M26" s="43"/>
-      <c r="N26" s="48"/>
-      <c r="O26" s="49"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="43"/>
-      <c r="V26" s="48"/>
-      <c r="W26" s="50"/>
-      <c r="X26" s="43"/>
-      <c r="Y26" s="43"/>
-      <c r="Z26" s="48"/>
-      <c r="AA26" s="49"/>
-      <c r="AB26" s="43"/>
-      <c r="AC26" s="43"/>
-      <c r="AD26" s="47"/>
-      <c r="AE26" s="48"/>
-      <c r="AF26" s="49"/>
-      <c r="AG26" s="43"/>
-      <c r="AH26" s="43"/>
-      <c r="AI26" s="43"/>
-      <c r="AJ26" s="43"/>
-      <c r="AK26" s="43"/>
+      <c r="C26" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="42"/>
+      <c r="L26" s="46"/>
+      <c r="M26" s="42"/>
+      <c r="N26" s="47"/>
+      <c r="O26" s="48"/>
+      <c r="P26" s="42"/>
+      <c r="Q26" s="42"/>
+      <c r="R26" s="42"/>
+      <c r="S26" s="42"/>
+      <c r="T26" s="42"/>
+      <c r="U26" s="42"/>
+      <c r="V26" s="47"/>
+      <c r="W26" s="49"/>
+      <c r="X26" s="42"/>
+      <c r="Y26" s="42"/>
+      <c r="Z26" s="47"/>
+      <c r="AA26" s="48"/>
+      <c r="AB26" s="42"/>
+      <c r="AC26" s="42"/>
+      <c r="AD26" s="46"/>
+      <c r="AE26" s="47"/>
+      <c r="AF26" s="48"/>
+      <c r="AG26" s="42"/>
+      <c r="AH26" s="42"/>
+      <c r="AI26" s="42"/>
+      <c r="AJ26" s="42"/>
+      <c r="AK26" s="42"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="41"/>
-      <c r="C27" s="42"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="51"/>
-      <c r="G27" s="54"/>
-      <c r="H27" s="55"/>
-      <c r="I27" s="43"/>
-      <c r="J27" s="43"/>
-      <c r="K27" s="43"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="43"/>
-      <c r="N27" s="48"/>
-      <c r="O27" s="49"/>
-      <c r="P27" s="43"/>
-      <c r="Q27" s="43"/>
-      <c r="R27" s="43"/>
-      <c r="S27" s="43"/>
-      <c r="T27" s="43"/>
-      <c r="U27" s="43"/>
-      <c r="V27" s="48"/>
-      <c r="W27" s="50"/>
-      <c r="X27" s="43"/>
-      <c r="Y27" s="43"/>
-      <c r="Z27" s="48"/>
-      <c r="AA27" s="49"/>
-      <c r="AB27" s="43"/>
-      <c r="AC27" s="43"/>
-      <c r="AD27" s="47"/>
-      <c r="AE27" s="48"/>
-      <c r="AF27" s="49"/>
-      <c r="AG27" s="43"/>
-      <c r="AH27" s="43"/>
-      <c r="AI27" s="43"/>
-      <c r="AJ27" s="43"/>
-      <c r="AK27" s="43"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="42"/>
+      <c r="L27" s="46"/>
+      <c r="M27" s="42"/>
+      <c r="N27" s="47"/>
+      <c r="O27" s="48"/>
+      <c r="P27" s="42"/>
+      <c r="Q27" s="42"/>
+      <c r="R27" s="42"/>
+      <c r="S27" s="42"/>
+      <c r="T27" s="42"/>
+      <c r="U27" s="42"/>
+      <c r="V27" s="47"/>
+      <c r="W27" s="49"/>
+      <c r="X27" s="42"/>
+      <c r="Y27" s="42"/>
+      <c r="Z27" s="47"/>
+      <c r="AA27" s="48"/>
+      <c r="AB27" s="42"/>
+      <c r="AC27" s="42"/>
+      <c r="AD27" s="46"/>
+      <c r="AE27" s="47"/>
+      <c r="AF27" s="48"/>
+      <c r="AG27" s="42"/>
+      <c r="AH27" s="42"/>
+      <c r="AI27" s="42"/>
+      <c r="AJ27" s="42"/>
+      <c r="AK27" s="42"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="41"/>
-      <c r="C28" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="48"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="57"/>
-      <c r="K28" s="57"/>
-      <c r="L28" s="47"/>
-      <c r="M28" s="43"/>
-      <c r="N28" s="48"/>
-      <c r="O28" s="49"/>
-      <c r="P28" s="43"/>
-      <c r="Q28" s="43"/>
-      <c r="R28" s="43"/>
-      <c r="S28" s="43"/>
-      <c r="T28" s="43"/>
-      <c r="U28" s="43"/>
-      <c r="V28" s="48"/>
-      <c r="W28" s="50"/>
-      <c r="X28" s="43"/>
-      <c r="Y28" s="43"/>
-      <c r="Z28" s="48"/>
-      <c r="AA28" s="49"/>
-      <c r="AB28" s="43"/>
-      <c r="AC28" s="43"/>
-      <c r="AD28" s="47"/>
-      <c r="AE28" s="48"/>
-      <c r="AF28" s="49"/>
-      <c r="AG28" s="43"/>
-      <c r="AH28" s="43"/>
-      <c r="AI28" s="43"/>
-      <c r="AJ28" s="43"/>
-      <c r="AK28" s="43"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" s="42"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="56"/>
+      <c r="K28" s="56"/>
+      <c r="L28" s="46"/>
+      <c r="M28" s="42"/>
+      <c r="N28" s="47"/>
+      <c r="O28" s="48"/>
+      <c r="P28" s="42"/>
+      <c r="Q28" s="42"/>
+      <c r="R28" s="42"/>
+      <c r="S28" s="42"/>
+      <c r="T28" s="42"/>
+      <c r="U28" s="42"/>
+      <c r="V28" s="47"/>
+      <c r="W28" s="49"/>
+      <c r="X28" s="42"/>
+      <c r="Y28" s="42"/>
+      <c r="Z28" s="47"/>
+      <c r="AA28" s="48"/>
+      <c r="AB28" s="42"/>
+      <c r="AC28" s="42"/>
+      <c r="AD28" s="46"/>
+      <c r="AE28" s="47"/>
+      <c r="AF28" s="48"/>
+      <c r="AG28" s="42"/>
+      <c r="AH28" s="42"/>
+      <c r="AI28" s="42"/>
+      <c r="AJ28" s="42"/>
+      <c r="AK28" s="42"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="41"/>
-      <c r="C29" s="42"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="55"/>
-      <c r="I29" s="43"/>
-      <c r="J29" s="66"/>
-      <c r="K29" s="43"/>
-      <c r="L29" s="47"/>
-      <c r="M29" s="43"/>
-      <c r="N29" s="48"/>
-      <c r="O29" s="49"/>
-      <c r="P29" s="43"/>
-      <c r="Q29" s="43"/>
-      <c r="R29" s="43"/>
-      <c r="S29" s="43"/>
-      <c r="T29" s="43"/>
-      <c r="U29" s="43"/>
-      <c r="V29" s="48"/>
-      <c r="W29" s="50"/>
-      <c r="X29" s="43"/>
-      <c r="Y29" s="43"/>
-      <c r="Z29" s="48"/>
-      <c r="AA29" s="49"/>
-      <c r="AB29" s="43"/>
-      <c r="AC29" s="43"/>
-      <c r="AD29" s="47"/>
-      <c r="AE29" s="48"/>
-      <c r="AF29" s="49"/>
-      <c r="AG29" s="43"/>
-      <c r="AH29" s="43"/>
-      <c r="AI29" s="43"/>
-      <c r="AJ29" s="43"/>
-      <c r="AK29" s="43"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="65"/>
+      <c r="K29" s="42"/>
+      <c r="L29" s="46"/>
+      <c r="M29" s="42"/>
+      <c r="N29" s="47"/>
+      <c r="O29" s="48"/>
+      <c r="P29" s="42"/>
+      <c r="Q29" s="42"/>
+      <c r="R29" s="42"/>
+      <c r="S29" s="42"/>
+      <c r="T29" s="42"/>
+      <c r="U29" s="42"/>
+      <c r="V29" s="47"/>
+      <c r="W29" s="49"/>
+      <c r="X29" s="42"/>
+      <c r="Y29" s="42"/>
+      <c r="Z29" s="47"/>
+      <c r="AA29" s="48"/>
+      <c r="AB29" s="42"/>
+      <c r="AC29" s="42"/>
+      <c r="AD29" s="46"/>
+      <c r="AE29" s="47"/>
+      <c r="AF29" s="48"/>
+      <c r="AG29" s="42"/>
+      <c r="AH29" s="42"/>
+      <c r="AI29" s="42"/>
+      <c r="AJ29" s="42"/>
+      <c r="AK29" s="42"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="41"/>
-      <c r="C30" s="42" t="s">
-        <v>98</v>
-      </c>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="51"/>
-      <c r="G30" s="48"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="57"/>
-      <c r="K30" s="57"/>
-      <c r="L30" s="47"/>
-      <c r="M30" s="57"/>
-      <c r="N30" s="48"/>
-      <c r="O30" s="49"/>
-      <c r="P30" s="43"/>
-      <c r="Q30" s="43"/>
-      <c r="R30" s="43"/>
-      <c r="S30" s="43"/>
-      <c r="T30" s="43"/>
-      <c r="U30" s="43"/>
-      <c r="V30" s="48"/>
-      <c r="W30" s="50"/>
-      <c r="X30" s="43"/>
-      <c r="Y30" s="43"/>
-      <c r="Z30" s="48"/>
-      <c r="AA30" s="49"/>
-      <c r="AB30" s="43"/>
-      <c r="AC30" s="43"/>
-      <c r="AD30" s="47"/>
-      <c r="AE30" s="48"/>
-      <c r="AF30" s="49"/>
-      <c r="AG30" s="43"/>
-      <c r="AH30" s="43"/>
-      <c r="AI30" s="43"/>
-      <c r="AJ30" s="43"/>
-      <c r="AK30" s="43"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" s="42"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="50"/>
+      <c r="G30" s="47"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="56"/>
+      <c r="J30" s="56"/>
+      <c r="K30" s="56"/>
+      <c r="L30" s="46"/>
+      <c r="M30" s="56"/>
+      <c r="N30" s="47"/>
+      <c r="O30" s="48"/>
+      <c r="P30" s="42"/>
+      <c r="Q30" s="42"/>
+      <c r="R30" s="42"/>
+      <c r="S30" s="42"/>
+      <c r="T30" s="42"/>
+      <c r="U30" s="42"/>
+      <c r="V30" s="47"/>
+      <c r="W30" s="49"/>
+      <c r="X30" s="42"/>
+      <c r="Y30" s="42"/>
+      <c r="Z30" s="47"/>
+      <c r="AA30" s="48"/>
+      <c r="AB30" s="42"/>
+      <c r="AC30" s="42"/>
+      <c r="AD30" s="46"/>
+      <c r="AE30" s="47"/>
+      <c r="AF30" s="48"/>
+      <c r="AG30" s="42"/>
+      <c r="AH30" s="42"/>
+      <c r="AI30" s="42"/>
+      <c r="AJ30" s="42"/>
+      <c r="AK30" s="42"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="41"/>
-      <c r="C31" s="42"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="53"/>
-      <c r="G31" s="54"/>
-      <c r="H31" s="55"/>
-      <c r="I31" s="43"/>
-      <c r="J31" s="66"/>
-      <c r="K31" s="66"/>
-      <c r="L31" s="67"/>
-      <c r="M31" s="43"/>
-      <c r="N31" s="54"/>
-      <c r="O31" s="49"/>
-      <c r="P31" s="43"/>
-      <c r="Q31" s="43"/>
-      <c r="R31" s="43"/>
-      <c r="S31" s="43"/>
-      <c r="T31" s="43"/>
-      <c r="U31" s="43"/>
-      <c r="V31" s="48"/>
-      <c r="W31" s="50"/>
-      <c r="X31" s="43"/>
-      <c r="Y31" s="43"/>
-      <c r="Z31" s="48"/>
-      <c r="AA31" s="49"/>
-      <c r="AB31" s="43"/>
-      <c r="AC31" s="43"/>
-      <c r="AD31" s="47"/>
-      <c r="AE31" s="48"/>
-      <c r="AF31" s="49"/>
-      <c r="AG31" s="43"/>
-      <c r="AH31" s="43"/>
-      <c r="AI31" s="43"/>
-      <c r="AJ31" s="43"/>
-      <c r="AK31" s="43"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="53"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="65"/>
+      <c r="K31" s="65"/>
+      <c r="L31" s="66"/>
+      <c r="M31" s="42"/>
+      <c r="N31" s="53"/>
+      <c r="O31" s="48"/>
+      <c r="P31" s="42"/>
+      <c r="Q31" s="42"/>
+      <c r="R31" s="42"/>
+      <c r="S31" s="42"/>
+      <c r="T31" s="42"/>
+      <c r="U31" s="42"/>
+      <c r="V31" s="47"/>
+      <c r="W31" s="49"/>
+      <c r="X31" s="42"/>
+      <c r="Y31" s="42"/>
+      <c r="Z31" s="47"/>
+      <c r="AA31" s="48"/>
+      <c r="AB31" s="42"/>
+      <c r="AC31" s="42"/>
+      <c r="AD31" s="46"/>
+      <c r="AE31" s="47"/>
+      <c r="AF31" s="48"/>
+      <c r="AG31" s="42"/>
+      <c r="AH31" s="42"/>
+      <c r="AI31" s="42"/>
+      <c r="AJ31" s="42"/>
+      <c r="AK31" s="42"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="41"/>
-      <c r="C32" s="42" t="s">
-        <v>99</v>
-      </c>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="51"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="43"/>
-      <c r="J32" s="43"/>
-      <c r="K32" s="43"/>
-      <c r="L32" s="47"/>
-      <c r="M32" s="57"/>
-      <c r="N32" s="45"/>
-      <c r="O32" s="49"/>
-      <c r="P32" s="43"/>
-      <c r="Q32" s="43"/>
-      <c r="R32" s="43"/>
-      <c r="S32" s="43"/>
-      <c r="T32" s="43"/>
-      <c r="U32" s="43"/>
-      <c r="V32" s="48"/>
-      <c r="W32" s="50"/>
-      <c r="X32" s="43"/>
-      <c r="Y32" s="43"/>
-      <c r="Z32" s="48"/>
-      <c r="AA32" s="49"/>
-      <c r="AB32" s="43"/>
-      <c r="AC32" s="43"/>
-      <c r="AD32" s="47"/>
-      <c r="AE32" s="48"/>
-      <c r="AF32" s="49"/>
-      <c r="AG32" s="43"/>
-      <c r="AH32" s="43"/>
-      <c r="AI32" s="43"/>
-      <c r="AJ32" s="43"/>
-      <c r="AK32" s="43"/>
+      <c r="B32" s="40"/>
+      <c r="C32" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="48"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="42"/>
+      <c r="K32" s="42"/>
+      <c r="L32" s="46"/>
+      <c r="M32" s="56"/>
+      <c r="N32" s="44"/>
+      <c r="O32" s="48"/>
+      <c r="P32" s="42"/>
+      <c r="Q32" s="42"/>
+      <c r="R32" s="42"/>
+      <c r="S32" s="42"/>
+      <c r="T32" s="42"/>
+      <c r="U32" s="42"/>
+      <c r="V32" s="47"/>
+      <c r="W32" s="49"/>
+      <c r="X32" s="42"/>
+      <c r="Y32" s="42"/>
+      <c r="Z32" s="47"/>
+      <c r="AA32" s="48"/>
+      <c r="AB32" s="42"/>
+      <c r="AC32" s="42"/>
+      <c r="AD32" s="46"/>
+      <c r="AE32" s="47"/>
+      <c r="AF32" s="48"/>
+      <c r="AG32" s="42"/>
+      <c r="AH32" s="42"/>
+      <c r="AI32" s="42"/>
+      <c r="AJ32" s="42"/>
+      <c r="AK32" s="42"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="41"/>
-      <c r="C33" s="42"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="51"/>
-      <c r="G33" s="48"/>
-      <c r="H33" s="49"/>
-      <c r="I33" s="43"/>
-      <c r="J33" s="43"/>
-      <c r="K33" s="43"/>
-      <c r="L33" s="47"/>
-      <c r="M33" s="43"/>
-      <c r="N33" s="54"/>
-      <c r="O33" s="49"/>
-      <c r="P33" s="43"/>
-      <c r="Q33" s="43"/>
-      <c r="R33" s="43"/>
-      <c r="S33" s="43"/>
-      <c r="T33" s="43"/>
-      <c r="U33" s="43"/>
-      <c r="V33" s="48"/>
-      <c r="W33" s="50"/>
-      <c r="X33" s="43"/>
-      <c r="Y33" s="43"/>
-      <c r="Z33" s="48"/>
-      <c r="AA33" s="49"/>
-      <c r="AB33" s="43"/>
-      <c r="AC33" s="43"/>
-      <c r="AD33" s="47"/>
-      <c r="AE33" s="48"/>
-      <c r="AF33" s="49"/>
-      <c r="AG33" s="43"/>
-      <c r="AH33" s="43"/>
-      <c r="AI33" s="43"/>
-      <c r="AJ33" s="43"/>
-      <c r="AK33" s="43"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="48"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="42"/>
+      <c r="K33" s="42"/>
+      <c r="L33" s="46"/>
+      <c r="M33" s="42"/>
+      <c r="N33" s="53"/>
+      <c r="O33" s="48"/>
+      <c r="P33" s="42"/>
+      <c r="Q33" s="42"/>
+      <c r="R33" s="42"/>
+      <c r="S33" s="42"/>
+      <c r="T33" s="42"/>
+      <c r="U33" s="42"/>
+      <c r="V33" s="47"/>
+      <c r="W33" s="49"/>
+      <c r="X33" s="42"/>
+      <c r="Y33" s="42"/>
+      <c r="Z33" s="47"/>
+      <c r="AA33" s="48"/>
+      <c r="AB33" s="42"/>
+      <c r="AC33" s="42"/>
+      <c r="AD33" s="46"/>
+      <c r="AE33" s="47"/>
+      <c r="AF33" s="48"/>
+      <c r="AG33" s="42"/>
+      <c r="AH33" s="42"/>
+      <c r="AI33" s="42"/>
+      <c r="AJ33" s="42"/>
+      <c r="AK33" s="42"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="58" t="s">
-        <v>100</v>
-      </c>
-      <c r="C34" s="68" t="s">
+      <c r="B34" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="D34" s="61"/>
-      <c r="E34" s="61"/>
-      <c r="F34" s="64"/>
-      <c r="G34" s="62"/>
-      <c r="H34" s="60"/>
-      <c r="I34" s="61"/>
-      <c r="J34" s="61"/>
-      <c r="K34" s="61"/>
-      <c r="L34" s="47"/>
-      <c r="M34" s="57"/>
-      <c r="N34" s="45"/>
-      <c r="O34" s="46"/>
-      <c r="P34" s="57"/>
-      <c r="Q34" s="57"/>
-      <c r="R34" s="57"/>
-      <c r="S34" s="61"/>
-      <c r="T34" s="61"/>
-      <c r="U34" s="61"/>
-      <c r="V34" s="62"/>
-      <c r="W34" s="50"/>
-      <c r="X34" s="61"/>
-      <c r="Y34" s="61"/>
-      <c r="Z34" s="62"/>
-      <c r="AA34" s="60"/>
-      <c r="AB34" s="61"/>
-      <c r="AC34" s="61"/>
-      <c r="AD34" s="47"/>
-      <c r="AE34" s="62"/>
-      <c r="AF34" s="60"/>
-      <c r="AG34" s="61"/>
-      <c r="AH34" s="61"/>
-      <c r="AI34" s="61"/>
-      <c r="AJ34" s="61"/>
-      <c r="AK34" s="61"/>
+      <c r="C34" s="67" t="s">
+        <v>102</v>
+      </c>
+      <c r="D34" s="60"/>
+      <c r="E34" s="60"/>
+      <c r="F34" s="63"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="59"/>
+      <c r="I34" s="60"/>
+      <c r="J34" s="60"/>
+      <c r="K34" s="60"/>
+      <c r="L34" s="46"/>
+      <c r="M34" s="56"/>
+      <c r="N34" s="44"/>
+      <c r="O34" s="45"/>
+      <c r="P34" s="56"/>
+      <c r="Q34" s="56"/>
+      <c r="R34" s="56"/>
+      <c r="S34" s="60"/>
+      <c r="T34" s="60"/>
+      <c r="U34" s="60"/>
+      <c r="V34" s="61"/>
+      <c r="W34" s="49"/>
+      <c r="X34" s="60"/>
+      <c r="Y34" s="60"/>
+      <c r="Z34" s="61"/>
+      <c r="AA34" s="59"/>
+      <c r="AB34" s="60"/>
+      <c r="AC34" s="60"/>
+      <c r="AD34" s="46"/>
+      <c r="AE34" s="61"/>
+      <c r="AF34" s="59"/>
+      <c r="AG34" s="60"/>
+      <c r="AH34" s="60"/>
+      <c r="AI34" s="60"/>
+      <c r="AJ34" s="60"/>
+      <c r="AK34" s="60"/>
     </row>
     <row r="35" ht="12" customHeight="1">
-      <c r="B35" s="58"/>
-      <c r="C35" s="68"/>
-      <c r="D35" s="61"/>
-      <c r="E35" s="61"/>
-      <c r="F35" s="64"/>
-      <c r="G35" s="62"/>
-      <c r="H35" s="60"/>
-      <c r="I35" s="61"/>
-      <c r="J35" s="61"/>
-      <c r="K35" s="69"/>
-      <c r="L35" s="47"/>
-      <c r="M35" s="61"/>
-      <c r="N35" s="54"/>
-      <c r="O35" s="60"/>
-      <c r="P35" s="56"/>
-      <c r="Q35" s="61"/>
-      <c r="R35" s="61"/>
-      <c r="S35" s="61"/>
-      <c r="T35" s="61"/>
-      <c r="U35" s="61"/>
-      <c r="V35" s="62"/>
-      <c r="W35" s="50"/>
-      <c r="X35" s="61"/>
-      <c r="Y35" s="61"/>
-      <c r="Z35" s="62"/>
-      <c r="AA35" s="60"/>
-      <c r="AB35" s="61"/>
-      <c r="AC35" s="61"/>
-      <c r="AD35" s="47"/>
-      <c r="AE35" s="62"/>
-      <c r="AF35" s="60"/>
-      <c r="AG35" s="61"/>
-      <c r="AH35" s="61"/>
-      <c r="AI35" s="61"/>
-      <c r="AJ35" s="61"/>
-      <c r="AK35" s="61"/>
+      <c r="B35" s="57"/>
+      <c r="C35" s="67"/>
+      <c r="D35" s="60"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="61"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="60"/>
+      <c r="J35" s="60"/>
+      <c r="K35" s="68"/>
+      <c r="L35" s="46"/>
+      <c r="M35" s="60"/>
+      <c r="N35" s="53"/>
+      <c r="O35" s="59"/>
+      <c r="P35" s="55"/>
+      <c r="Q35" s="60"/>
+      <c r="R35" s="60"/>
+      <c r="S35" s="60"/>
+      <c r="T35" s="60"/>
+      <c r="U35" s="60"/>
+      <c r="V35" s="61"/>
+      <c r="W35" s="49"/>
+      <c r="X35" s="60"/>
+      <c r="Y35" s="60"/>
+      <c r="Z35" s="61"/>
+      <c r="AA35" s="59"/>
+      <c r="AB35" s="60"/>
+      <c r="AC35" s="60"/>
+      <c r="AD35" s="46"/>
+      <c r="AE35" s="61"/>
+      <c r="AF35" s="59"/>
+      <c r="AG35" s="60"/>
+      <c r="AH35" s="60"/>
+      <c r="AI35" s="60"/>
+      <c r="AJ35" s="60"/>
+      <c r="AK35" s="60"/>
     </row>
     <row r="36" ht="12" customHeight="1">
-      <c r="B36" s="58"/>
-      <c r="C36" s="68" t="s">
-        <v>102</v>
-      </c>
-      <c r="D36" s="61"/>
-      <c r="E36" s="61"/>
-      <c r="F36" s="64"/>
-      <c r="G36" s="62"/>
-      <c r="H36" s="60"/>
-      <c r="I36" s="61"/>
-      <c r="J36" s="61"/>
-      <c r="K36" s="61"/>
-      <c r="L36" s="47"/>
-      <c r="M36" s="57"/>
-      <c r="N36" s="45"/>
-      <c r="O36" s="46"/>
-      <c r="P36" s="57"/>
-      <c r="Q36" s="61"/>
-      <c r="R36" s="61"/>
-      <c r="S36" s="61"/>
-      <c r="T36" s="61"/>
-      <c r="U36" s="61"/>
-      <c r="V36" s="62"/>
-      <c r="W36" s="50"/>
-      <c r="X36" s="61"/>
-      <c r="Y36" s="61"/>
-      <c r="Z36" s="62"/>
-      <c r="AA36" s="60"/>
-      <c r="AB36" s="61"/>
-      <c r="AC36" s="61"/>
-      <c r="AD36" s="47"/>
-      <c r="AE36" s="62"/>
-      <c r="AF36" s="60"/>
-      <c r="AG36" s="61"/>
-      <c r="AH36" s="61"/>
-      <c r="AI36" s="61"/>
-      <c r="AJ36" s="61"/>
-      <c r="AK36" s="61"/>
+      <c r="B36" s="57"/>
+      <c r="C36" s="67" t="s">
+        <v>103</v>
+      </c>
+      <c r="D36" s="60"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="63"/>
+      <c r="G36" s="61"/>
+      <c r="H36" s="59"/>
+      <c r="I36" s="60"/>
+      <c r="J36" s="60"/>
+      <c r="K36" s="60"/>
+      <c r="L36" s="46"/>
+      <c r="M36" s="56"/>
+      <c r="N36" s="44"/>
+      <c r="O36" s="45"/>
+      <c r="P36" s="56"/>
+      <c r="Q36" s="60"/>
+      <c r="R36" s="60"/>
+      <c r="S36" s="60"/>
+      <c r="T36" s="60"/>
+      <c r="U36" s="60"/>
+      <c r="V36" s="61"/>
+      <c r="W36" s="49"/>
+      <c r="X36" s="60"/>
+      <c r="Y36" s="60"/>
+      <c r="Z36" s="61"/>
+      <c r="AA36" s="59"/>
+      <c r="AB36" s="60"/>
+      <c r="AC36" s="60"/>
+      <c r="AD36" s="46"/>
+      <c r="AE36" s="61"/>
+      <c r="AF36" s="59"/>
+      <c r="AG36" s="60"/>
+      <c r="AH36" s="60"/>
+      <c r="AI36" s="60"/>
+      <c r="AJ36" s="60"/>
+      <c r="AK36" s="60"/>
     </row>
     <row r="37" ht="12" customHeight="1">
-      <c r="B37" s="58"/>
-      <c r="C37" s="68"/>
-      <c r="D37" s="61"/>
-      <c r="E37" s="61"/>
-      <c r="F37" s="64"/>
-      <c r="G37" s="62"/>
-      <c r="H37" s="60"/>
-      <c r="I37" s="61"/>
-      <c r="J37" s="61"/>
-      <c r="K37" s="69"/>
-      <c r="L37" s="47"/>
-      <c r="M37" s="61"/>
-      <c r="N37" s="62"/>
-      <c r="O37" s="60"/>
-      <c r="P37" s="56"/>
-      <c r="Q37" s="61"/>
-      <c r="R37" s="61"/>
-      <c r="S37" s="61"/>
-      <c r="T37" s="61"/>
-      <c r="U37" s="61"/>
-      <c r="V37" s="62"/>
-      <c r="W37" s="50"/>
-      <c r="X37" s="61"/>
-      <c r="Y37" s="61"/>
-      <c r="Z37" s="62"/>
-      <c r="AA37" s="60"/>
-      <c r="AB37" s="61"/>
-      <c r="AC37" s="61"/>
-      <c r="AD37" s="47"/>
-      <c r="AE37" s="62"/>
-      <c r="AF37" s="60"/>
-      <c r="AG37" s="61"/>
-      <c r="AH37" s="61"/>
-      <c r="AI37" s="61"/>
-      <c r="AJ37" s="61"/>
-      <c r="AK37" s="61"/>
+      <c r="B37" s="57"/>
+      <c r="C37" s="67"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="63"/>
+      <c r="G37" s="61"/>
+      <c r="H37" s="59"/>
+      <c r="I37" s="60"/>
+      <c r="J37" s="60"/>
+      <c r="K37" s="68"/>
+      <c r="L37" s="46"/>
+      <c r="M37" s="60"/>
+      <c r="N37" s="61"/>
+      <c r="O37" s="59"/>
+      <c r="P37" s="55"/>
+      <c r="Q37" s="60"/>
+      <c r="R37" s="60"/>
+      <c r="S37" s="60"/>
+      <c r="T37" s="60"/>
+      <c r="U37" s="60"/>
+      <c r="V37" s="61"/>
+      <c r="W37" s="49"/>
+      <c r="X37" s="60"/>
+      <c r="Y37" s="60"/>
+      <c r="Z37" s="61"/>
+      <c r="AA37" s="59"/>
+      <c r="AB37" s="60"/>
+      <c r="AC37" s="60"/>
+      <c r="AD37" s="46"/>
+      <c r="AE37" s="61"/>
+      <c r="AF37" s="59"/>
+      <c r="AG37" s="60"/>
+      <c r="AH37" s="60"/>
+      <c r="AI37" s="60"/>
+      <c r="AJ37" s="60"/>
+      <c r="AK37" s="60"/>
     </row>
     <row r="38" ht="12" customHeight="1">
-      <c r="B38" s="58"/>
-      <c r="C38" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="D38" s="61"/>
-      <c r="E38" s="61"/>
-      <c r="F38" s="64"/>
-      <c r="G38" s="62"/>
-      <c r="H38" s="60"/>
-      <c r="I38" s="61"/>
-      <c r="J38" s="61"/>
-      <c r="K38" s="61"/>
-      <c r="L38" s="47"/>
-      <c r="M38" s="61"/>
-      <c r="N38" s="62"/>
-      <c r="O38" s="46"/>
-      <c r="P38" s="57"/>
-      <c r="Q38" s="57"/>
-      <c r="R38" s="57"/>
-      <c r="S38" s="57"/>
-      <c r="T38" s="57"/>
-      <c r="U38" s="57"/>
-      <c r="V38" s="45"/>
-      <c r="W38" s="50"/>
-      <c r="X38" s="57"/>
-      <c r="Y38" s="57"/>
-      <c r="Z38" s="62"/>
-      <c r="AA38" s="60"/>
-      <c r="AB38" s="61"/>
-      <c r="AC38" s="61"/>
-      <c r="AD38" s="47"/>
-      <c r="AE38" s="62"/>
-      <c r="AF38" s="60"/>
-      <c r="AG38" s="61"/>
-      <c r="AH38" s="61"/>
-      <c r="AI38" s="61"/>
-      <c r="AJ38" s="61"/>
-      <c r="AK38" s="61"/>
+      <c r="B38" s="57"/>
+      <c r="C38" s="67" t="s">
+        <v>104</v>
+      </c>
+      <c r="D38" s="60"/>
+      <c r="E38" s="60"/>
+      <c r="F38" s="63"/>
+      <c r="G38" s="61"/>
+      <c r="H38" s="59"/>
+      <c r="I38" s="60"/>
+      <c r="J38" s="60"/>
+      <c r="K38" s="60"/>
+      <c r="L38" s="46"/>
+      <c r="M38" s="60"/>
+      <c r="N38" s="61"/>
+      <c r="O38" s="45"/>
+      <c r="P38" s="56"/>
+      <c r="Q38" s="56"/>
+      <c r="R38" s="56"/>
+      <c r="S38" s="56"/>
+      <c r="T38" s="56"/>
+      <c r="U38" s="56"/>
+      <c r="V38" s="44"/>
+      <c r="W38" s="49"/>
+      <c r="X38" s="56"/>
+      <c r="Y38" s="56"/>
+      <c r="Z38" s="61"/>
+      <c r="AA38" s="59"/>
+      <c r="AB38" s="60"/>
+      <c r="AC38" s="60"/>
+      <c r="AD38" s="46"/>
+      <c r="AE38" s="61"/>
+      <c r="AF38" s="59"/>
+      <c r="AG38" s="60"/>
+      <c r="AH38" s="60"/>
+      <c r="AI38" s="60"/>
+      <c r="AJ38" s="60"/>
+      <c r="AK38" s="60"/>
     </row>
     <row r="39" ht="12" customHeight="1">
-      <c r="B39" s="58"/>
-      <c r="C39" s="68"/>
-      <c r="D39" s="61"/>
-      <c r="E39" s="61"/>
-      <c r="F39" s="64"/>
-      <c r="G39" s="62"/>
-      <c r="H39" s="60"/>
-      <c r="I39" s="61"/>
-      <c r="J39" s="61"/>
-      <c r="K39" s="61"/>
-      <c r="L39" s="47"/>
-      <c r="M39" s="61"/>
-      <c r="N39" s="62"/>
-      <c r="O39" s="60"/>
-      <c r="P39" s="61"/>
-      <c r="Q39" s="61"/>
-      <c r="R39" s="61"/>
-      <c r="S39" s="61"/>
-      <c r="T39" s="61"/>
-      <c r="U39" s="61"/>
-      <c r="V39" s="62"/>
-      <c r="W39" s="50"/>
-      <c r="X39" s="61"/>
-      <c r="Y39" s="61"/>
-      <c r="Z39" s="62"/>
-      <c r="AA39" s="60"/>
-      <c r="AB39" s="61"/>
-      <c r="AC39" s="61"/>
-      <c r="AD39" s="47"/>
-      <c r="AE39" s="62"/>
-      <c r="AF39" s="60"/>
-      <c r="AG39" s="61"/>
-      <c r="AH39" s="61"/>
-      <c r="AI39" s="61"/>
-      <c r="AJ39" s="61"/>
-      <c r="AK39" s="61"/>
+      <c r="B39" s="57"/>
+      <c r="C39" s="67"/>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="63"/>
+      <c r="G39" s="61"/>
+      <c r="H39" s="59"/>
+      <c r="I39" s="60"/>
+      <c r="J39" s="60"/>
+      <c r="K39" s="60"/>
+      <c r="L39" s="46"/>
+      <c r="M39" s="60"/>
+      <c r="N39" s="61"/>
+      <c r="O39" s="59"/>
+      <c r="P39" s="60"/>
+      <c r="Q39" s="60"/>
+      <c r="R39" s="60"/>
+      <c r="S39" s="60"/>
+      <c r="T39" s="60"/>
+      <c r="U39" s="60"/>
+      <c r="V39" s="61"/>
+      <c r="W39" s="49"/>
+      <c r="X39" s="60"/>
+      <c r="Y39" s="60"/>
+      <c r="Z39" s="61"/>
+      <c r="AA39" s="59"/>
+      <c r="AB39" s="60"/>
+      <c r="AC39" s="60"/>
+      <c r="AD39" s="46"/>
+      <c r="AE39" s="61"/>
+      <c r="AF39" s="59"/>
+      <c r="AG39" s="60"/>
+      <c r="AH39" s="60"/>
+      <c r="AI39" s="60"/>
+      <c r="AJ39" s="60"/>
+      <c r="AK39" s="60"/>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="B40" s="58"/>
-      <c r="C40" s="68" t="s">
-        <v>104</v>
-      </c>
-      <c r="D40" s="61"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="64"/>
-      <c r="G40" s="62"/>
-      <c r="H40" s="60"/>
-      <c r="I40" s="61"/>
-      <c r="J40" s="61"/>
-      <c r="K40" s="61"/>
-      <c r="L40" s="47"/>
-      <c r="M40" s="61"/>
-      <c r="N40" s="62"/>
-      <c r="O40" s="60"/>
-      <c r="P40" s="61"/>
-      <c r="Q40" s="61"/>
-      <c r="R40" s="57"/>
-      <c r="S40" s="57"/>
-      <c r="T40" s="57"/>
-      <c r="U40" s="57"/>
-      <c r="V40" s="45"/>
-      <c r="W40" s="50"/>
-      <c r="X40" s="57"/>
-      <c r="Y40" s="57"/>
-      <c r="Z40" s="45"/>
-      <c r="AA40" s="46"/>
-      <c r="AB40" s="57"/>
-      <c r="AC40" s="57"/>
-      <c r="AD40" s="47"/>
-      <c r="AE40" s="62"/>
-      <c r="AF40" s="60"/>
-      <c r="AG40" s="61"/>
-      <c r="AH40" s="61"/>
-      <c r="AI40" s="61"/>
-      <c r="AJ40" s="61"/>
-      <c r="AK40" s="61"/>
+      <c r="B40" s="57"/>
+      <c r="C40" s="67" t="s">
+        <v>105</v>
+      </c>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="63"/>
+      <c r="G40" s="61"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="60"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="60"/>
+      <c r="L40" s="46"/>
+      <c r="M40" s="60"/>
+      <c r="N40" s="61"/>
+      <c r="O40" s="59"/>
+      <c r="P40" s="60"/>
+      <c r="Q40" s="60"/>
+      <c r="R40" s="56"/>
+      <c r="S40" s="56"/>
+      <c r="T40" s="56"/>
+      <c r="U40" s="56"/>
+      <c r="V40" s="44"/>
+      <c r="W40" s="49"/>
+      <c r="X40" s="56"/>
+      <c r="Y40" s="56"/>
+      <c r="Z40" s="44"/>
+      <c r="AA40" s="45"/>
+      <c r="AB40" s="56"/>
+      <c r="AC40" s="56"/>
+      <c r="AD40" s="46"/>
+      <c r="AE40" s="61"/>
+      <c r="AF40" s="59"/>
+      <c r="AG40" s="60"/>
+      <c r="AH40" s="60"/>
+      <c r="AI40" s="60"/>
+      <c r="AJ40" s="60"/>
+      <c r="AK40" s="60"/>
     </row>
     <row r="41" ht="12" customHeight="1">
-      <c r="B41" s="58"/>
-      <c r="C41" s="68"/>
-      <c r="D41" s="61"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="64"/>
-      <c r="G41" s="62"/>
-      <c r="H41" s="60"/>
-      <c r="I41" s="61"/>
-      <c r="J41" s="61"/>
-      <c r="K41" s="61"/>
-      <c r="L41" s="47"/>
-      <c r="M41" s="61"/>
-      <c r="N41" s="62"/>
-      <c r="O41" s="60"/>
-      <c r="P41" s="61"/>
-      <c r="Q41" s="61"/>
-      <c r="R41" s="61"/>
-      <c r="S41" s="61"/>
-      <c r="T41" s="61"/>
-      <c r="U41" s="61"/>
-      <c r="V41" s="62"/>
-      <c r="W41" s="50"/>
-      <c r="X41" s="61"/>
-      <c r="Y41" s="61"/>
-      <c r="Z41" s="62"/>
-      <c r="AA41" s="60"/>
-      <c r="AB41" s="61"/>
-      <c r="AC41" s="61"/>
-      <c r="AD41" s="47"/>
-      <c r="AE41" s="62"/>
-      <c r="AF41" s="60"/>
-      <c r="AG41" s="61"/>
-      <c r="AH41" s="61"/>
-      <c r="AI41" s="61"/>
-      <c r="AJ41" s="61"/>
-      <c r="AK41" s="61"/>
+      <c r="B41" s="57"/>
+      <c r="C41" s="67"/>
+      <c r="D41" s="60"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="63"/>
+      <c r="G41" s="61"/>
+      <c r="H41" s="59"/>
+      <c r="I41" s="60"/>
+      <c r="J41" s="60"/>
+      <c r="K41" s="60"/>
+      <c r="L41" s="46"/>
+      <c r="M41" s="60"/>
+      <c r="N41" s="61"/>
+      <c r="O41" s="59"/>
+      <c r="P41" s="60"/>
+      <c r="Q41" s="60"/>
+      <c r="R41" s="60"/>
+      <c r="S41" s="60"/>
+      <c r="T41" s="60"/>
+      <c r="U41" s="60"/>
+      <c r="V41" s="61"/>
+      <c r="W41" s="49"/>
+      <c r="X41" s="60"/>
+      <c r="Y41" s="60"/>
+      <c r="Z41" s="61"/>
+      <c r="AA41" s="59"/>
+      <c r="AB41" s="60"/>
+      <c r="AC41" s="60"/>
+      <c r="AD41" s="46"/>
+      <c r="AE41" s="61"/>
+      <c r="AF41" s="59"/>
+      <c r="AG41" s="60"/>
+      <c r="AH41" s="60"/>
+      <c r="AI41" s="60"/>
+      <c r="AJ41" s="60"/>
+      <c r="AK41" s="60"/>
     </row>
     <row r="42" ht="12" customHeight="1">
-      <c r="B42" s="41" t="s">
+      <c r="B42" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="70" t="s">
-        <v>105</v>
-      </c>
-      <c r="D42" s="43"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="51"/>
-      <c r="G42" s="48"/>
-      <c r="H42" s="49"/>
-      <c r="I42" s="43"/>
-      <c r="J42" s="43"/>
-      <c r="K42" s="43"/>
-      <c r="L42" s="47"/>
-      <c r="M42" s="43"/>
-      <c r="N42" s="48"/>
-      <c r="O42" s="49"/>
-      <c r="P42" s="57"/>
-      <c r="Q42" s="57"/>
-      <c r="R42" s="43"/>
-      <c r="S42" s="43"/>
-      <c r="T42" s="43"/>
-      <c r="U42" s="43"/>
-      <c r="V42" s="45"/>
-      <c r="W42" s="50"/>
-      <c r="X42" s="57"/>
-      <c r="Y42" s="57"/>
-      <c r="Z42" s="45"/>
-      <c r="AA42" s="46"/>
-      <c r="AB42" s="57"/>
-      <c r="AC42" s="57"/>
-      <c r="AD42" s="47"/>
-      <c r="AE42" s="48"/>
-      <c r="AF42" s="49"/>
-      <c r="AG42" s="43"/>
-      <c r="AH42" s="43"/>
-      <c r="AI42" s="43"/>
-      <c r="AJ42" s="43"/>
-      <c r="AK42" s="43"/>
+      <c r="C42" s="69" t="s">
+        <v>106</v>
+      </c>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="50"/>
+      <c r="G42" s="47"/>
+      <c r="H42" s="48"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="42"/>
+      <c r="L42" s="46"/>
+      <c r="M42" s="42"/>
+      <c r="N42" s="47"/>
+      <c r="O42" s="48"/>
+      <c r="P42" s="56"/>
+      <c r="Q42" s="56"/>
+      <c r="R42" s="42"/>
+      <c r="S42" s="42"/>
+      <c r="T42" s="42"/>
+      <c r="U42" s="42"/>
+      <c r="V42" s="44"/>
+      <c r="W42" s="49"/>
+      <c r="X42" s="56"/>
+      <c r="Y42" s="56"/>
+      <c r="Z42" s="44"/>
+      <c r="AA42" s="45"/>
+      <c r="AB42" s="56"/>
+      <c r="AC42" s="56"/>
+      <c r="AD42" s="46"/>
+      <c r="AE42" s="47"/>
+      <c r="AF42" s="48"/>
+      <c r="AG42" s="42"/>
+      <c r="AH42" s="42"/>
+      <c r="AI42" s="42"/>
+      <c r="AJ42" s="42"/>
+      <c r="AK42" s="42"/>
     </row>
     <row r="43" ht="12" customHeight="1">
-      <c r="B43" s="41"/>
-      <c r="C43" s="70"/>
-      <c r="D43" s="43"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="51"/>
-      <c r="G43" s="48"/>
-      <c r="H43" s="49"/>
-      <c r="I43" s="43"/>
-      <c r="J43" s="43"/>
-      <c r="K43" s="43"/>
-      <c r="L43" s="47"/>
-      <c r="M43" s="43"/>
-      <c r="N43" s="48"/>
-      <c r="O43" s="49"/>
-      <c r="P43" s="43"/>
-      <c r="Q43" s="43"/>
-      <c r="R43" s="43"/>
-      <c r="S43" s="43"/>
-      <c r="T43" s="43"/>
-      <c r="U43" s="43"/>
-      <c r="V43" s="48"/>
-      <c r="W43" s="50"/>
-      <c r="X43" s="43"/>
-      <c r="Y43" s="43"/>
-      <c r="Z43" s="48"/>
-      <c r="AA43" s="49"/>
-      <c r="AB43" s="43"/>
-      <c r="AC43" s="43"/>
-      <c r="AD43" s="47"/>
-      <c r="AE43" s="48"/>
-      <c r="AF43" s="49"/>
-      <c r="AG43" s="43"/>
-      <c r="AH43" s="43"/>
-      <c r="AI43" s="43"/>
-      <c r="AJ43" s="43"/>
-      <c r="AK43" s="43"/>
+      <c r="B43" s="40"/>
+      <c r="C43" s="69"/>
+      <c r="D43" s="42"/>
+      <c r="E43" s="42"/>
+      <c r="F43" s="50"/>
+      <c r="G43" s="47"/>
+      <c r="H43" s="48"/>
+      <c r="I43" s="42"/>
+      <c r="J43" s="42"/>
+      <c r="K43" s="42"/>
+      <c r="L43" s="46"/>
+      <c r="M43" s="42"/>
+      <c r="N43" s="47"/>
+      <c r="O43" s="48"/>
+      <c r="P43" s="42"/>
+      <c r="Q43" s="42"/>
+      <c r="R43" s="42"/>
+      <c r="S43" s="42"/>
+      <c r="T43" s="42"/>
+      <c r="U43" s="42"/>
+      <c r="V43" s="47"/>
+      <c r="W43" s="49"/>
+      <c r="X43" s="42"/>
+      <c r="Y43" s="42"/>
+      <c r="Z43" s="47"/>
+      <c r="AA43" s="48"/>
+      <c r="AB43" s="42"/>
+      <c r="AC43" s="42"/>
+      <c r="AD43" s="46"/>
+      <c r="AE43" s="47"/>
+      <c r="AF43" s="48"/>
+      <c r="AG43" s="42"/>
+      <c r="AH43" s="42"/>
+      <c r="AI43" s="42"/>
+      <c r="AJ43" s="42"/>
+      <c r="AK43" s="42"/>
     </row>
     <row r="44" ht="12" customHeight="1">
-      <c r="B44" s="41"/>
-      <c r="C44" s="70" t="s">
-        <v>106</v>
-      </c>
-      <c r="D44" s="43"/>
-      <c r="E44" s="43"/>
-      <c r="F44" s="51"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="49"/>
-      <c r="I44" s="43"/>
-      <c r="J44" s="43"/>
-      <c r="K44" s="43"/>
-      <c r="L44" s="47"/>
-      <c r="M44" s="43"/>
-      <c r="N44" s="48"/>
-      <c r="O44" s="49"/>
-      <c r="P44" s="57"/>
-      <c r="Q44" s="57"/>
-      <c r="R44" s="43"/>
-      <c r="S44" s="43"/>
-      <c r="T44" s="43"/>
-      <c r="U44" s="43"/>
-      <c r="V44" s="48"/>
-      <c r="W44" s="50"/>
-      <c r="X44" s="57"/>
-      <c r="Y44" s="57"/>
-      <c r="Z44" s="48"/>
-      <c r="AA44" s="49"/>
-      <c r="AB44" s="43"/>
-      <c r="AC44" s="57"/>
-      <c r="AD44" s="47"/>
-      <c r="AE44" s="45"/>
-      <c r="AF44" s="46"/>
-      <c r="AG44" s="43"/>
-      <c r="AH44" s="43"/>
-      <c r="AI44" s="57"/>
-      <c r="AJ44" s="43"/>
-      <c r="AK44" s="43"/>
+      <c r="B44" s="40"/>
+      <c r="C44" s="69" t="s">
+        <v>107</v>
+      </c>
+      <c r="D44" s="42"/>
+      <c r="E44" s="42"/>
+      <c r="F44" s="50"/>
+      <c r="G44" s="47"/>
+      <c r="H44" s="48"/>
+      <c r="I44" s="42"/>
+      <c r="J44" s="42"/>
+      <c r="K44" s="42"/>
+      <c r="L44" s="46"/>
+      <c r="M44" s="42"/>
+      <c r="N44" s="47"/>
+      <c r="O44" s="48"/>
+      <c r="P44" s="56"/>
+      <c r="Q44" s="56"/>
+      <c r="R44" s="42"/>
+      <c r="S44" s="42"/>
+      <c r="T44" s="42"/>
+      <c r="U44" s="42"/>
+      <c r="V44" s="47"/>
+      <c r="W44" s="49"/>
+      <c r="X44" s="56"/>
+      <c r="Y44" s="56"/>
+      <c r="Z44" s="47"/>
+      <c r="AA44" s="48"/>
+      <c r="AB44" s="42"/>
+      <c r="AC44" s="56"/>
+      <c r="AD44" s="46"/>
+      <c r="AE44" s="44"/>
+      <c r="AF44" s="45"/>
+      <c r="AG44" s="42"/>
+      <c r="AH44" s="42"/>
+      <c r="AI44" s="56"/>
+      <c r="AJ44" s="42"/>
+      <c r="AK44" s="42"/>
     </row>
     <row r="45" ht="12" customHeight="1">
-      <c r="B45" s="41"/>
-      <c r="C45" s="70"/>
-      <c r="D45" s="43"/>
-      <c r="E45" s="43"/>
-      <c r="F45" s="51"/>
-      <c r="G45" s="48"/>
-      <c r="H45" s="49"/>
-      <c r="I45" s="43"/>
-      <c r="J45" s="43"/>
-      <c r="K45" s="43"/>
-      <c r="L45" s="47"/>
-      <c r="M45" s="43"/>
-      <c r="N45" s="48"/>
-      <c r="O45" s="49"/>
-      <c r="P45" s="43"/>
-      <c r="Q45" s="43"/>
-      <c r="R45" s="43"/>
-      <c r="S45" s="43"/>
-      <c r="T45" s="43"/>
-      <c r="U45" s="43"/>
-      <c r="V45" s="48"/>
-      <c r="W45" s="50"/>
-      <c r="X45" s="43"/>
-      <c r="Y45" s="43"/>
-      <c r="Z45" s="48"/>
-      <c r="AA45" s="49"/>
-      <c r="AB45" s="43"/>
-      <c r="AC45" s="43"/>
-      <c r="AD45" s="47"/>
-      <c r="AE45" s="48"/>
-      <c r="AF45" s="49"/>
-      <c r="AG45" s="43"/>
-      <c r="AH45" s="43"/>
-      <c r="AI45" s="43"/>
-      <c r="AJ45" s="43"/>
-      <c r="AK45" s="43"/>
+      <c r="B45" s="40"/>
+      <c r="C45" s="69"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="50"/>
+      <c r="G45" s="47"/>
+      <c r="H45" s="48"/>
+      <c r="I45" s="42"/>
+      <c r="J45" s="42"/>
+      <c r="K45" s="42"/>
+      <c r="L45" s="46"/>
+      <c r="M45" s="42"/>
+      <c r="N45" s="47"/>
+      <c r="O45" s="48"/>
+      <c r="P45" s="42"/>
+      <c r="Q45" s="42"/>
+      <c r="R45" s="42"/>
+      <c r="S45" s="42"/>
+      <c r="T45" s="42"/>
+      <c r="U45" s="42"/>
+      <c r="V45" s="47"/>
+      <c r="W45" s="49"/>
+      <c r="X45" s="42"/>
+      <c r="Y45" s="42"/>
+      <c r="Z45" s="47"/>
+      <c r="AA45" s="48"/>
+      <c r="AB45" s="42"/>
+      <c r="AC45" s="42"/>
+      <c r="AD45" s="46"/>
+      <c r="AE45" s="47"/>
+      <c r="AF45" s="48"/>
+      <c r="AG45" s="42"/>
+      <c r="AH45" s="42"/>
+      <c r="AI45" s="42"/>
+      <c r="AJ45" s="42"/>
+      <c r="AK45" s="42"/>
     </row>
     <row r="46" ht="12" customHeight="1">
-      <c r="B46" s="58" t="s">
-        <v>107</v>
-      </c>
-      <c r="C46" s="59" t="s">
+      <c r="B46" s="57" t="s">
+        <v>108</v>
+      </c>
+      <c r="C46" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="D46" s="61"/>
-      <c r="E46" s="61"/>
-      <c r="F46" s="64"/>
-      <c r="G46" s="62"/>
-      <c r="H46" s="60"/>
-      <c r="I46" s="61"/>
-      <c r="J46" s="61"/>
-      <c r="K46" s="61"/>
-      <c r="L46" s="47"/>
-      <c r="M46" s="61"/>
-      <c r="N46" s="62"/>
-      <c r="O46" s="60"/>
-      <c r="P46" s="61"/>
-      <c r="Q46" s="61"/>
-      <c r="R46" s="61"/>
-      <c r="S46" s="61"/>
-      <c r="T46" s="61"/>
-      <c r="U46" s="61"/>
-      <c r="V46" s="62"/>
-      <c r="W46" s="50"/>
-      <c r="X46" s="61"/>
-      <c r="Y46" s="61"/>
-      <c r="Z46" s="62"/>
-      <c r="AA46" s="60"/>
-      <c r="AB46" s="61"/>
-      <c r="AC46" s="61"/>
-      <c r="AD46" s="47"/>
-      <c r="AE46" s="62"/>
-      <c r="AF46" s="60"/>
-      <c r="AG46" s="61"/>
-      <c r="AH46" s="61"/>
-      <c r="AI46" s="61"/>
-      <c r="AJ46" s="57"/>
-      <c r="AK46" s="61"/>
+      <c r="D46" s="60"/>
+      <c r="E46" s="60"/>
+      <c r="F46" s="63"/>
+      <c r="G46" s="61"/>
+      <c r="H46" s="59"/>
+      <c r="I46" s="60"/>
+      <c r="J46" s="60"/>
+      <c r="K46" s="60"/>
+      <c r="L46" s="46"/>
+      <c r="M46" s="60"/>
+      <c r="N46" s="61"/>
+      <c r="O46" s="59"/>
+      <c r="P46" s="60"/>
+      <c r="Q46" s="60"/>
+      <c r="R46" s="60"/>
+      <c r="S46" s="60"/>
+      <c r="T46" s="60"/>
+      <c r="U46" s="60"/>
+      <c r="V46" s="61"/>
+      <c r="W46" s="49"/>
+      <c r="X46" s="60"/>
+      <c r="Y46" s="60"/>
+      <c r="Z46" s="61"/>
+      <c r="AA46" s="59"/>
+      <c r="AB46" s="60"/>
+      <c r="AC46" s="60"/>
+      <c r="AD46" s="46"/>
+      <c r="AE46" s="61"/>
+      <c r="AF46" s="59"/>
+      <c r="AG46" s="60"/>
+      <c r="AH46" s="60"/>
+      <c r="AI46" s="60"/>
+      <c r="AJ46" s="56"/>
+      <c r="AK46" s="60"/>
     </row>
     <row r="47" ht="12" customHeight="1">
-      <c r="B47" s="58"/>
-      <c r="C47" s="59"/>
-      <c r="D47" s="61"/>
-      <c r="E47" s="61"/>
-      <c r="F47" s="64"/>
-      <c r="G47" s="62"/>
-      <c r="H47" s="60"/>
-      <c r="I47" s="61"/>
-      <c r="J47" s="61"/>
-      <c r="K47" s="61"/>
-      <c r="L47" s="47"/>
-      <c r="M47" s="61"/>
-      <c r="N47" s="62"/>
-      <c r="O47" s="60"/>
-      <c r="P47" s="61"/>
-      <c r="Q47" s="61"/>
-      <c r="R47" s="61"/>
-      <c r="S47" s="61"/>
-      <c r="T47" s="61"/>
-      <c r="U47" s="61"/>
-      <c r="V47" s="62"/>
-      <c r="W47" s="50"/>
-      <c r="X47" s="61"/>
-      <c r="Y47" s="61"/>
-      <c r="Z47" s="62"/>
-      <c r="AA47" s="60"/>
-      <c r="AB47" s="61"/>
-      <c r="AC47" s="61"/>
-      <c r="AD47" s="47"/>
-      <c r="AE47" s="62"/>
-      <c r="AF47" s="60"/>
-      <c r="AG47" s="61"/>
-      <c r="AH47" s="61"/>
-      <c r="AI47" s="61"/>
-      <c r="AJ47" s="61"/>
-      <c r="AK47" s="61"/>
-      <c r="AN47" s="71" t="s">
-        <v>108</v>
-      </c>
-      <c r="AO47" s="57"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="58"/>
+      <c r="D47" s="60"/>
+      <c r="E47" s="60"/>
+      <c r="F47" s="63"/>
+      <c r="G47" s="61"/>
+      <c r="H47" s="59"/>
+      <c r="I47" s="60"/>
+      <c r="J47" s="60"/>
+      <c r="K47" s="60"/>
+      <c r="L47" s="46"/>
+      <c r="M47" s="60"/>
+      <c r="N47" s="61"/>
+      <c r="O47" s="59"/>
+      <c r="P47" s="60"/>
+      <c r="Q47" s="60"/>
+      <c r="R47" s="60"/>
+      <c r="S47" s="60"/>
+      <c r="T47" s="60"/>
+      <c r="U47" s="60"/>
+      <c r="V47" s="61"/>
+      <c r="W47" s="49"/>
+      <c r="X47" s="60"/>
+      <c r="Y47" s="60"/>
+      <c r="Z47" s="61"/>
+      <c r="AA47" s="59"/>
+      <c r="AB47" s="60"/>
+      <c r="AC47" s="60"/>
+      <c r="AD47" s="46"/>
+      <c r="AE47" s="61"/>
+      <c r="AF47" s="59"/>
+      <c r="AG47" s="60"/>
+      <c r="AH47" s="60"/>
+      <c r="AI47" s="60"/>
+      <c r="AJ47" s="60"/>
+      <c r="AK47" s="60"/>
+      <c r="AN47" s="70" t="s">
+        <v>109</v>
+      </c>
+      <c r="AO47" s="56"/>
     </row>
     <row r="48" ht="12" customHeight="1">
-      <c r="B48" s="58"/>
-      <c r="C48" s="59" t="s">
-        <v>109</v>
-      </c>
-      <c r="D48" s="61"/>
-      <c r="E48" s="61"/>
-      <c r="F48" s="64"/>
-      <c r="G48" s="62"/>
-      <c r="H48" s="60"/>
-      <c r="I48" s="61"/>
-      <c r="J48" s="61"/>
-      <c r="K48" s="61"/>
-      <c r="L48" s="47"/>
-      <c r="M48" s="61"/>
-      <c r="N48" s="62"/>
-      <c r="O48" s="60"/>
-      <c r="P48" s="61"/>
-      <c r="Q48" s="61"/>
-      <c r="R48" s="61"/>
-      <c r="S48" s="61"/>
-      <c r="T48" s="61"/>
-      <c r="U48" s="61"/>
-      <c r="V48" s="62"/>
-      <c r="W48" s="50"/>
-      <c r="X48" s="61"/>
-      <c r="Y48" s="61"/>
-      <c r="Z48" s="62"/>
-      <c r="AA48" s="60"/>
-      <c r="AB48" s="61"/>
-      <c r="AC48" s="61"/>
-      <c r="AD48" s="47"/>
-      <c r="AE48" s="62"/>
-      <c r="AF48" s="60"/>
-      <c r="AG48" s="61"/>
-      <c r="AH48" s="61"/>
-      <c r="AI48" s="61"/>
-      <c r="AJ48" s="61"/>
-      <c r="AK48" s="72"/>
-      <c r="AN48" s="71" t="s">
+      <c r="B48" s="57"/>
+      <c r="C48" s="58" t="s">
         <v>110</v>
       </c>
-      <c r="AO48" s="56"/>
+      <c r="D48" s="60"/>
+      <c r="E48" s="60"/>
+      <c r="F48" s="63"/>
+      <c r="G48" s="61"/>
+      <c r="H48" s="59"/>
+      <c r="I48" s="60"/>
+      <c r="J48" s="60"/>
+      <c r="K48" s="60"/>
+      <c r="L48" s="46"/>
+      <c r="M48" s="60"/>
+      <c r="N48" s="61"/>
+      <c r="O48" s="59"/>
+      <c r="P48" s="60"/>
+      <c r="Q48" s="60"/>
+      <c r="R48" s="60"/>
+      <c r="S48" s="60"/>
+      <c r="T48" s="60"/>
+      <c r="U48" s="60"/>
+      <c r="V48" s="61"/>
+      <c r="W48" s="49"/>
+      <c r="X48" s="60"/>
+      <c r="Y48" s="60"/>
+      <c r="Z48" s="61"/>
+      <c r="AA48" s="59"/>
+      <c r="AB48" s="60"/>
+      <c r="AC48" s="60"/>
+      <c r="AD48" s="46"/>
+      <c r="AE48" s="61"/>
+      <c r="AF48" s="59"/>
+      <c r="AG48" s="60"/>
+      <c r="AH48" s="60"/>
+      <c r="AI48" s="60"/>
+      <c r="AJ48" s="60"/>
+      <c r="AK48" s="71"/>
+      <c r="AN48" s="70" t="s">
+        <v>111</v>
+      </c>
+      <c r="AO48" s="55"/>
     </row>
     <row r="49" ht="12" customHeight="1">
-      <c r="B49" s="58"/>
-      <c r="C49" s="59"/>
-      <c r="D49" s="61"/>
-      <c r="E49" s="61"/>
-      <c r="F49" s="64"/>
-      <c r="G49" s="62"/>
-      <c r="H49" s="60"/>
-      <c r="I49" s="61"/>
-      <c r="J49" s="61"/>
-      <c r="K49" s="61"/>
-      <c r="L49" s="47"/>
-      <c r="M49" s="61"/>
-      <c r="N49" s="62"/>
-      <c r="O49" s="60"/>
-      <c r="P49" s="61"/>
-      <c r="Q49" s="61"/>
-      <c r="R49" s="61"/>
-      <c r="S49" s="61"/>
-      <c r="T49" s="61"/>
-      <c r="U49" s="61"/>
-      <c r="V49" s="62"/>
-      <c r="W49" s="50"/>
-      <c r="X49" s="61"/>
-      <c r="Y49" s="61"/>
-      <c r="Z49" s="62"/>
-      <c r="AA49" s="60"/>
-      <c r="AB49" s="61"/>
-      <c r="AC49" s="61"/>
-      <c r="AD49" s="47"/>
-      <c r="AE49" s="62"/>
-      <c r="AF49" s="60"/>
-      <c r="AG49" s="61"/>
-      <c r="AH49" s="61"/>
-      <c r="AI49" s="61"/>
-      <c r="AJ49" s="61"/>
-      <c r="AK49" s="61"/>
-      <c r="AN49" s="71" t="s">
-        <v>111</v>
-      </c>
-      <c r="AO49" s="52"/>
+      <c r="B49" s="57"/>
+      <c r="C49" s="58"/>
+      <c r="D49" s="60"/>
+      <c r="E49" s="60"/>
+      <c r="F49" s="63"/>
+      <c r="G49" s="61"/>
+      <c r="H49" s="59"/>
+      <c r="I49" s="60"/>
+      <c r="J49" s="60"/>
+      <c r="K49" s="60"/>
+      <c r="L49" s="46"/>
+      <c r="M49" s="60"/>
+      <c r="N49" s="61"/>
+      <c r="O49" s="59"/>
+      <c r="P49" s="60"/>
+      <c r="Q49" s="60"/>
+      <c r="R49" s="60"/>
+      <c r="S49" s="60"/>
+      <c r="T49" s="60"/>
+      <c r="U49" s="60"/>
+      <c r="V49" s="61"/>
+      <c r="W49" s="49"/>
+      <c r="X49" s="60"/>
+      <c r="Y49" s="60"/>
+      <c r="Z49" s="61"/>
+      <c r="AA49" s="59"/>
+      <c r="AB49" s="60"/>
+      <c r="AC49" s="60"/>
+      <c r="AD49" s="46"/>
+      <c r="AE49" s="61"/>
+      <c r="AF49" s="59"/>
+      <c r="AG49" s="60"/>
+      <c r="AH49" s="60"/>
+      <c r="AI49" s="60"/>
+      <c r="AJ49" s="60"/>
+      <c r="AK49" s="60"/>
+      <c r="AN49" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="AO49" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -9444,801 +9455,801 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="73"/>
+      <c r="B1" s="72"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="74" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="75" t="s">
+      <c r="B2" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="76" t="s">
-        <v>112</v>
-      </c>
-      <c r="E2" s="77" t="s">
+      <c r="C2" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="75" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="78" t="s">
+      <c r="E2" s="76" t="s">
         <v>114</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="78" t="s">
+      <c r="F2" s="77" t="s">
         <v>115</v>
       </c>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="78" t="s">
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="77" t="s">
         <v>116</v>
       </c>
-      <c r="O2" s="78"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="78" t="s">
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="76"/>
+      <c r="N2" s="77" t="s">
         <v>117</v>
       </c>
-      <c r="S2" s="79"/>
-      <c r="AD2" s="23"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="77" t="s">
+        <v>118</v>
+      </c>
+      <c r="S2" s="78"/>
+      <c r="AD2" s="22"/>
     </row>
     <row r="3">
-      <c r="B3" s="80"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="82" t="s">
-        <v>118</v>
-      </c>
-      <c r="E3" s="83">
+      <c r="B3" s="79"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="81" t="s">
+        <v>119</v>
+      </c>
+      <c r="E3" s="82">
         <v>4</v>
       </c>
-      <c r="F3" s="84">
+      <c r="F3" s="83">
         <v>1</v>
       </c>
-      <c r="G3" s="85">
+      <c r="G3" s="84">
         <v>2</v>
       </c>
-      <c r="H3" s="85">
+      <c r="H3" s="84">
         <v>3</v>
       </c>
-      <c r="I3" s="83">
+      <c r="I3" s="82">
         <v>4</v>
       </c>
-      <c r="J3" s="84">
+      <c r="J3" s="83">
         <v>1</v>
       </c>
-      <c r="K3" s="85">
+      <c r="K3" s="84">
         <v>2</v>
       </c>
-      <c r="L3" s="85">
+      <c r="L3" s="84">
         <v>3</v>
       </c>
-      <c r="M3" s="83">
+      <c r="M3" s="82">
         <v>4</v>
       </c>
-      <c r="N3" s="84">
+      <c r="N3" s="83">
         <v>1</v>
       </c>
-      <c r="O3" s="85">
+      <c r="O3" s="84">
         <v>2</v>
       </c>
-      <c r="P3" s="85">
+      <c r="P3" s="84">
         <v>3</v>
       </c>
-      <c r="Q3" s="83">
+      <c r="Q3" s="82">
         <v>4</v>
       </c>
-      <c r="R3" s="84">
+      <c r="R3" s="83">
         <v>1</v>
       </c>
-      <c r="S3" s="86">
+      <c r="S3" s="85">
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="87" t="s">
-        <v>120</v>
-      </c>
-      <c r="C4" s="75" t="s">
+      <c r="B4" s="86" t="s">
         <v>121</v>
       </c>
-      <c r="D4" s="88"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="92"/>
-      <c r="K4" s="91"/>
-      <c r="L4" s="91"/>
-      <c r="M4" s="89"/>
-      <c r="N4" s="92"/>
-      <c r="O4" s="91"/>
-      <c r="P4" s="91"/>
-      <c r="Q4" s="89"/>
-      <c r="R4" s="92"/>
-      <c r="S4" s="93"/>
+      <c r="C4" s="74" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" s="87"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="91"/>
+      <c r="K4" s="90"/>
+      <c r="L4" s="90"/>
+      <c r="M4" s="88"/>
+      <c r="N4" s="91"/>
+      <c r="O4" s="90"/>
+      <c r="P4" s="90"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="91"/>
+      <c r="S4" s="92"/>
       <c r="U4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="87"/>
-      <c r="C5" s="94"/>
-      <c r="D5" s="95"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="99"/>
-      <c r="I5" s="96"/>
-      <c r="J5" s="100"/>
-      <c r="K5" s="99"/>
-      <c r="L5" s="99"/>
-      <c r="M5" s="96"/>
-      <c r="N5" s="100"/>
-      <c r="O5" s="99"/>
-      <c r="P5" s="99"/>
-      <c r="Q5" s="96"/>
-      <c r="R5" s="100"/>
-      <c r="S5" s="101"/>
+      <c r="B5" s="86"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="95"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="97"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="95"/>
+      <c r="J5" s="99"/>
+      <c r="K5" s="98"/>
+      <c r="L5" s="98"/>
+      <c r="M5" s="95"/>
+      <c r="N5" s="99"/>
+      <c r="O5" s="98"/>
+      <c r="P5" s="98"/>
+      <c r="Q5" s="95"/>
+      <c r="R5" s="99"/>
+      <c r="S5" s="100"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="87"/>
-      <c r="C6" s="102" t="s">
-        <v>123</v>
-      </c>
-      <c r="D6" s="103"/>
-      <c r="E6" s="104"/>
-      <c r="F6" s="105"/>
-      <c r="G6" s="106"/>
-      <c r="H6" s="107"/>
-      <c r="I6" s="104"/>
-      <c r="J6" s="108"/>
-      <c r="K6" s="107"/>
-      <c r="L6" s="107"/>
-      <c r="M6" s="104"/>
-      <c r="N6" s="108"/>
-      <c r="O6" s="107"/>
-      <c r="P6" s="107"/>
-      <c r="Q6" s="104"/>
-      <c r="R6" s="108"/>
-      <c r="S6" s="109"/>
-      <c r="U6" s="110" t="s">
+      <c r="B6" s="86"/>
+      <c r="C6" s="101" t="s">
         <v>124</v>
       </c>
-      <c r="V6" s="110"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="104"/>
+      <c r="G6" s="105"/>
+      <c r="H6" s="106"/>
+      <c r="I6" s="103"/>
+      <c r="J6" s="107"/>
+      <c r="K6" s="106"/>
+      <c r="L6" s="106"/>
+      <c r="M6" s="103"/>
+      <c r="N6" s="107"/>
+      <c r="O6" s="106"/>
+      <c r="P6" s="106"/>
+      <c r="Q6" s="103"/>
+      <c r="R6" s="107"/>
+      <c r="S6" s="108"/>
+      <c r="U6" s="109" t="s">
+        <v>125</v>
+      </c>
+      <c r="V6" s="109"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="87"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="96"/>
-      <c r="F7" s="100"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="100"/>
-      <c r="K7" s="99"/>
-      <c r="L7" s="99"/>
-      <c r="M7" s="96"/>
-      <c r="N7" s="100"/>
-      <c r="O7" s="99"/>
-      <c r="P7" s="99"/>
-      <c r="Q7" s="96"/>
-      <c r="R7" s="100"/>
-      <c r="S7" s="101"/>
+      <c r="B7" s="86"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="95"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="97"/>
+      <c r="H7" s="97"/>
+      <c r="I7" s="95"/>
+      <c r="J7" s="99"/>
+      <c r="K7" s="98"/>
+      <c r="L7" s="98"/>
+      <c r="M7" s="95"/>
+      <c r="N7" s="99"/>
+      <c r="O7" s="98"/>
+      <c r="P7" s="98"/>
+      <c r="Q7" s="95"/>
+      <c r="R7" s="99"/>
+      <c r="S7" s="100"/>
       <c r="U7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="87"/>
-      <c r="C8" s="102" t="s">
-        <v>126</v>
-      </c>
-      <c r="D8" s="103"/>
-      <c r="E8" s="104"/>
-      <c r="F8" s="105"/>
-      <c r="G8" s="107"/>
-      <c r="H8" s="107"/>
-      <c r="I8" s="104"/>
-      <c r="J8" s="108"/>
-      <c r="K8" s="107"/>
-      <c r="L8" s="107"/>
-      <c r="M8" s="104"/>
-      <c r="N8" s="108"/>
-      <c r="O8" s="107"/>
-      <c r="P8" s="107"/>
-      <c r="Q8" s="104"/>
-      <c r="R8" s="108"/>
-      <c r="S8" s="109"/>
+      <c r="B8" s="86"/>
+      <c r="C8" s="101" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="102"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="104"/>
+      <c r="G8" s="106"/>
+      <c r="H8" s="106"/>
+      <c r="I8" s="103"/>
+      <c r="J8" s="107"/>
+      <c r="K8" s="106"/>
+      <c r="L8" s="106"/>
+      <c r="M8" s="103"/>
+      <c r="N8" s="107"/>
+      <c r="O8" s="106"/>
+      <c r="P8" s="106"/>
+      <c r="Q8" s="103"/>
+      <c r="R8" s="107"/>
+      <c r="S8" s="108"/>
       <c r="U8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="87"/>
-      <c r="C9" s="94"/>
-      <c r="D9" s="95"/>
-      <c r="E9" s="96"/>
-      <c r="F9" s="100"/>
-      <c r="G9" s="98"/>
-      <c r="H9" s="99"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="100"/>
-      <c r="K9" s="99"/>
-      <c r="L9" s="99"/>
-      <c r="M9" s="96"/>
-      <c r="N9" s="100"/>
-      <c r="O9" s="99"/>
-      <c r="P9" s="99"/>
-      <c r="Q9" s="96"/>
-      <c r="R9" s="100"/>
-      <c r="S9" s="101"/>
+      <c r="B9" s="86"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="94"/>
+      <c r="E9" s="95"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="97"/>
+      <c r="H9" s="98"/>
+      <c r="I9" s="95"/>
+      <c r="J9" s="99"/>
+      <c r="K9" s="98"/>
+      <c r="L9" s="98"/>
+      <c r="M9" s="95"/>
+      <c r="N9" s="99"/>
+      <c r="O9" s="98"/>
+      <c r="P9" s="98"/>
+      <c r="Q9" s="95"/>
+      <c r="R9" s="99"/>
+      <c r="S9" s="100"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="87"/>
-      <c r="C10" s="102" t="s">
-        <v>128</v>
-      </c>
-      <c r="D10" s="103"/>
-      <c r="E10" s="104"/>
-      <c r="F10" s="108"/>
-      <c r="G10" s="106"/>
-      <c r="H10" s="106"/>
-      <c r="I10" s="104"/>
-      <c r="J10" s="108"/>
-      <c r="K10" s="107"/>
-      <c r="L10" s="107"/>
-      <c r="M10" s="104"/>
-      <c r="N10" s="108"/>
-      <c r="O10" s="107"/>
-      <c r="P10" s="107"/>
-      <c r="Q10" s="104"/>
-      <c r="R10" s="108"/>
-      <c r="S10" s="109"/>
+      <c r="B10" s="86"/>
+      <c r="C10" s="101" t="s">
+        <v>129</v>
+      </c>
+      <c r="D10" s="102"/>
+      <c r="E10" s="103"/>
+      <c r="F10" s="107"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="103"/>
+      <c r="J10" s="107"/>
+      <c r="K10" s="106"/>
+      <c r="L10" s="106"/>
+      <c r="M10" s="103"/>
+      <c r="N10" s="107"/>
+      <c r="O10" s="106"/>
+      <c r="P10" s="106"/>
+      <c r="Q10" s="103"/>
+      <c r="R10" s="107"/>
+      <c r="S10" s="108"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="111"/>
-      <c r="C11" s="112"/>
-      <c r="D11" s="113"/>
-      <c r="E11" s="114"/>
-      <c r="F11" s="115"/>
-      <c r="G11" s="116"/>
-      <c r="H11" s="116"/>
-      <c r="I11" s="114"/>
-      <c r="J11" s="115"/>
-      <c r="K11" s="117"/>
-      <c r="L11" s="117"/>
-      <c r="M11" s="114"/>
-      <c r="N11" s="115"/>
-      <c r="O11" s="117"/>
-      <c r="P11" s="117"/>
-      <c r="Q11" s="114"/>
-      <c r="R11" s="115"/>
-      <c r="S11" s="118"/>
+      <c r="B11" s="110"/>
+      <c r="C11" s="111"/>
+      <c r="D11" s="112"/>
+      <c r="E11" s="113"/>
+      <c r="F11" s="114"/>
+      <c r="G11" s="115"/>
+      <c r="H11" s="115"/>
+      <c r="I11" s="113"/>
+      <c r="J11" s="114"/>
+      <c r="K11" s="116"/>
+      <c r="L11" s="116"/>
+      <c r="M11" s="113"/>
+      <c r="N11" s="114"/>
+      <c r="O11" s="116"/>
+      <c r="P11" s="116"/>
+      <c r="Q11" s="113"/>
+      <c r="R11" s="114"/>
+      <c r="S11" s="117"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="74" t="s">
-        <v>129</v>
-      </c>
-      <c r="C12" s="75" t="s">
+      <c r="B12" s="73" t="s">
         <v>130</v>
       </c>
-      <c r="D12" s="88"/>
-      <c r="E12" s="89"/>
-      <c r="F12" s="92"/>
-      <c r="G12" s="91"/>
-      <c r="H12" s="119"/>
-      <c r="I12" s="120"/>
-      <c r="J12" s="92"/>
-      <c r="K12" s="91"/>
-      <c r="L12" s="91"/>
-      <c r="M12" s="89"/>
-      <c r="N12" s="92"/>
-      <c r="O12" s="91"/>
-      <c r="P12" s="91"/>
-      <c r="Q12" s="89"/>
-      <c r="R12" s="92"/>
-      <c r="S12" s="93"/>
+      <c r="C12" s="74" t="s">
+        <v>131</v>
+      </c>
+      <c r="D12" s="87"/>
+      <c r="E12" s="88"/>
+      <c r="F12" s="91"/>
+      <c r="G12" s="90"/>
+      <c r="H12" s="118"/>
+      <c r="I12" s="119"/>
+      <c r="J12" s="91"/>
+      <c r="K12" s="90"/>
+      <c r="L12" s="90"/>
+      <c r="M12" s="88"/>
+      <c r="N12" s="91"/>
+      <c r="O12" s="90"/>
+      <c r="P12" s="90"/>
+      <c r="Q12" s="88"/>
+      <c r="R12" s="91"/>
+      <c r="S12" s="92"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="87"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="96"/>
-      <c r="F13" s="100"/>
-      <c r="G13" s="99"/>
-      <c r="H13" s="99"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="97"/>
-      <c r="K13" s="99"/>
-      <c r="L13" s="99"/>
-      <c r="M13" s="96"/>
-      <c r="N13" s="100"/>
-      <c r="O13" s="99"/>
-      <c r="P13" s="99"/>
-      <c r="Q13" s="96"/>
-      <c r="R13" s="100"/>
-      <c r="S13" s="101"/>
+      <c r="B13" s="86"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="94"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="98"/>
+      <c r="H13" s="98"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="96"/>
+      <c r="K13" s="98"/>
+      <c r="L13" s="98"/>
+      <c r="M13" s="95"/>
+      <c r="N13" s="99"/>
+      <c r="O13" s="98"/>
+      <c r="P13" s="98"/>
+      <c r="Q13" s="95"/>
+      <c r="R13" s="99"/>
+      <c r="S13" s="100"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="87"/>
-      <c r="C14" s="102" t="s">
-        <v>131</v>
-      </c>
-      <c r="D14" s="121"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="108"/>
-      <c r="G14" s="107"/>
-      <c r="H14" s="106"/>
-      <c r="I14" s="104"/>
-      <c r="J14" s="108"/>
-      <c r="K14" s="107"/>
-      <c r="L14" s="107"/>
-      <c r="M14" s="104"/>
-      <c r="N14" s="108"/>
-      <c r="O14" s="107"/>
-      <c r="P14" s="107"/>
-      <c r="Q14" s="104"/>
-      <c r="R14" s="108"/>
-      <c r="S14" s="109"/>
+      <c r="B14" s="86"/>
+      <c r="C14" s="101" t="s">
+        <v>132</v>
+      </c>
+      <c r="D14" s="120"/>
+      <c r="E14" s="103"/>
+      <c r="F14" s="107"/>
+      <c r="G14" s="106"/>
+      <c r="H14" s="105"/>
+      <c r="I14" s="103"/>
+      <c r="J14" s="107"/>
+      <c r="K14" s="106"/>
+      <c r="L14" s="106"/>
+      <c r="M14" s="103"/>
+      <c r="N14" s="107"/>
+      <c r="O14" s="106"/>
+      <c r="P14" s="106"/>
+      <c r="Q14" s="103"/>
+      <c r="R14" s="107"/>
+      <c r="S14" s="108"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="87"/>
-      <c r="C15" s="94"/>
-      <c r="D15" s="95"/>
-      <c r="E15" s="96"/>
-      <c r="F15" s="100"/>
-      <c r="G15" s="99"/>
-      <c r="H15" s="99"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="97"/>
-      <c r="K15" s="99"/>
-      <c r="L15" s="99"/>
-      <c r="M15" s="96"/>
-      <c r="N15" s="100"/>
-      <c r="O15" s="99"/>
-      <c r="P15" s="99"/>
-      <c r="Q15" s="96"/>
-      <c r="R15" s="100"/>
-      <c r="S15" s="101"/>
+      <c r="B15" s="86"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="94"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="98"/>
+      <c r="H15" s="98"/>
+      <c r="I15" s="121"/>
+      <c r="J15" s="96"/>
+      <c r="K15" s="98"/>
+      <c r="L15" s="98"/>
+      <c r="M15" s="95"/>
+      <c r="N15" s="99"/>
+      <c r="O15" s="98"/>
+      <c r="P15" s="98"/>
+      <c r="Q15" s="95"/>
+      <c r="R15" s="99"/>
+      <c r="S15" s="100"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="87"/>
-      <c r="C16" s="102" t="s">
-        <v>132</v>
-      </c>
-      <c r="D16" s="103"/>
-      <c r="E16" s="104"/>
-      <c r="F16" s="108"/>
-      <c r="G16" s="107"/>
-      <c r="H16" s="106"/>
-      <c r="I16" s="123"/>
-      <c r="J16" s="108"/>
-      <c r="K16" s="107"/>
-      <c r="L16" s="107"/>
-      <c r="M16" s="104"/>
-      <c r="N16" s="108"/>
-      <c r="O16" s="107"/>
-      <c r="P16" s="107"/>
-      <c r="Q16" s="104"/>
-      <c r="R16" s="108"/>
-      <c r="S16" s="109"/>
+      <c r="B16" s="86"/>
+      <c r="C16" s="101" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="102"/>
+      <c r="E16" s="103"/>
+      <c r="F16" s="107"/>
+      <c r="G16" s="106"/>
+      <c r="H16" s="105"/>
+      <c r="I16" s="122"/>
+      <c r="J16" s="107"/>
+      <c r="K16" s="106"/>
+      <c r="L16" s="106"/>
+      <c r="M16" s="103"/>
+      <c r="N16" s="107"/>
+      <c r="O16" s="106"/>
+      <c r="P16" s="106"/>
+      <c r="Q16" s="103"/>
+      <c r="R16" s="107"/>
+      <c r="S16" s="108"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="111"/>
-      <c r="C17" s="112"/>
-      <c r="D17" s="113"/>
-      <c r="E17" s="114"/>
-      <c r="F17" s="115"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="117"/>
-      <c r="I17" s="114"/>
-      <c r="J17" s="124"/>
-      <c r="K17" s="116"/>
-      <c r="L17" s="117"/>
-      <c r="M17" s="114"/>
-      <c r="N17" s="115"/>
-      <c r="O17" s="117"/>
-      <c r="P17" s="117"/>
-      <c r="Q17" s="114"/>
-      <c r="R17" s="115"/>
-      <c r="S17" s="118"/>
+      <c r="B17" s="110"/>
+      <c r="C17" s="111"/>
+      <c r="D17" s="112"/>
+      <c r="E17" s="113"/>
+      <c r="F17" s="114"/>
+      <c r="G17" s="116"/>
+      <c r="H17" s="116"/>
+      <c r="I17" s="113"/>
+      <c r="J17" s="123"/>
+      <c r="K17" s="115"/>
+      <c r="L17" s="116"/>
+      <c r="M17" s="113"/>
+      <c r="N17" s="114"/>
+      <c r="O17" s="116"/>
+      <c r="P17" s="116"/>
+      <c r="Q17" s="113"/>
+      <c r="R17" s="114"/>
+      <c r="S17" s="117"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="76" t="s">
-        <v>133</v>
-      </c>
-      <c r="C18" s="75" t="s">
+      <c r="B18" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="D18" s="88"/>
-      <c r="E18" s="89"/>
-      <c r="F18" s="92"/>
-      <c r="G18" s="91"/>
-      <c r="H18" s="91"/>
-      <c r="I18" s="120"/>
-      <c r="J18" s="92"/>
-      <c r="K18" s="91"/>
-      <c r="L18" s="91"/>
-      <c r="M18" s="89"/>
-      <c r="N18" s="92"/>
-      <c r="O18" s="91"/>
-      <c r="P18" s="91"/>
-      <c r="Q18" s="89"/>
-      <c r="R18" s="92"/>
-      <c r="S18" s="93"/>
+      <c r="C18" s="74" t="s">
+        <v>135</v>
+      </c>
+      <c r="D18" s="87"/>
+      <c r="E18" s="88"/>
+      <c r="F18" s="91"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="119"/>
+      <c r="J18" s="91"/>
+      <c r="K18" s="90"/>
+      <c r="L18" s="90"/>
+      <c r="M18" s="88"/>
+      <c r="N18" s="91"/>
+      <c r="O18" s="90"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="88"/>
+      <c r="R18" s="91"/>
+      <c r="S18" s="92"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="87"/>
-      <c r="C19" s="94"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="96"/>
-      <c r="F19" s="100"/>
-      <c r="G19" s="98"/>
-      <c r="H19" s="99"/>
-      <c r="I19" s="96"/>
-      <c r="J19" s="100"/>
-      <c r="K19" s="99"/>
-      <c r="L19" s="99"/>
-      <c r="M19" s="96"/>
-      <c r="N19" s="100"/>
-      <c r="O19" s="99"/>
-      <c r="P19" s="99"/>
-      <c r="Q19" s="96"/>
-      <c r="R19" s="100"/>
-      <c r="S19" s="101"/>
+      <c r="B19" s="86"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="94"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="99"/>
+      <c r="G19" s="97"/>
+      <c r="H19" s="98"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="99"/>
+      <c r="K19" s="98"/>
+      <c r="L19" s="98"/>
+      <c r="M19" s="95"/>
+      <c r="N19" s="99"/>
+      <c r="O19" s="98"/>
+      <c r="P19" s="98"/>
+      <c r="Q19" s="95"/>
+      <c r="R19" s="99"/>
+      <c r="S19" s="100"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="87"/>
-      <c r="C20" s="102" t="s">
-        <v>135</v>
-      </c>
-      <c r="D20" s="103"/>
-      <c r="E20" s="104"/>
-      <c r="F20" s="108"/>
-      <c r="G20" s="107"/>
-      <c r="H20" s="107"/>
-      <c r="I20" s="123"/>
-      <c r="J20" s="105"/>
-      <c r="K20" s="106"/>
-      <c r="L20" s="106"/>
-      <c r="M20" s="104"/>
-      <c r="N20" s="108"/>
-      <c r="O20" s="107"/>
-      <c r="P20" s="107"/>
-      <c r="Q20" s="104"/>
-      <c r="R20" s="108"/>
-      <c r="S20" s="109"/>
+      <c r="B20" s="86"/>
+      <c r="C20" s="101" t="s">
+        <v>136</v>
+      </c>
+      <c r="D20" s="102"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="107"/>
+      <c r="G20" s="106"/>
+      <c r="H20" s="106"/>
+      <c r="I20" s="122"/>
+      <c r="J20" s="104"/>
+      <c r="K20" s="105"/>
+      <c r="L20" s="105"/>
+      <c r="M20" s="103"/>
+      <c r="N20" s="107"/>
+      <c r="O20" s="106"/>
+      <c r="P20" s="106"/>
+      <c r="Q20" s="103"/>
+      <c r="R20" s="107"/>
+      <c r="S20" s="108"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="87"/>
-      <c r="C21" s="94"/>
-      <c r="D21" s="95"/>
-      <c r="E21" s="96"/>
-      <c r="F21" s="100"/>
-      <c r="G21" s="99"/>
-      <c r="H21" s="99"/>
-      <c r="I21" s="96"/>
-      <c r="J21" s="100"/>
-      <c r="K21" s="99"/>
-      <c r="L21" s="99"/>
-      <c r="M21" s="96"/>
-      <c r="N21" s="125"/>
-      <c r="O21" s="99"/>
-      <c r="P21" s="99"/>
-      <c r="Q21" s="96"/>
-      <c r="R21" s="100"/>
-      <c r="S21" s="101"/>
+      <c r="B21" s="86"/>
+      <c r="C21" s="93"/>
+      <c r="D21" s="94"/>
+      <c r="E21" s="95"/>
+      <c r="F21" s="99"/>
+      <c r="G21" s="98"/>
+      <c r="H21" s="98"/>
+      <c r="I21" s="95"/>
+      <c r="J21" s="99"/>
+      <c r="K21" s="98"/>
+      <c r="L21" s="98"/>
+      <c r="M21" s="95"/>
+      <c r="N21" s="124"/>
+      <c r="O21" s="98"/>
+      <c r="P21" s="98"/>
+      <c r="Q21" s="95"/>
+      <c r="R21" s="99"/>
+      <c r="S21" s="100"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="87"/>
-      <c r="C22" s="102" t="s">
-        <v>136</v>
-      </c>
-      <c r="D22" s="103"/>
-      <c r="E22" s="104"/>
-      <c r="F22" s="108"/>
-      <c r="G22" s="107"/>
-      <c r="H22" s="107"/>
-      <c r="I22" s="104"/>
-      <c r="J22" s="108"/>
-      <c r="K22" s="106"/>
-      <c r="L22" s="106"/>
-      <c r="M22" s="104"/>
-      <c r="N22" s="108"/>
-      <c r="O22" s="107"/>
-      <c r="P22" s="107"/>
-      <c r="Q22" s="104"/>
-      <c r="R22" s="108"/>
-      <c r="S22" s="109"/>
+      <c r="B22" s="86"/>
+      <c r="C22" s="101" t="s">
+        <v>137</v>
+      </c>
+      <c r="D22" s="102"/>
+      <c r="E22" s="103"/>
+      <c r="F22" s="107"/>
+      <c r="G22" s="106"/>
+      <c r="H22" s="106"/>
+      <c r="I22" s="103"/>
+      <c r="J22" s="107"/>
+      <c r="K22" s="105"/>
+      <c r="L22" s="105"/>
+      <c r="M22" s="103"/>
+      <c r="N22" s="107"/>
+      <c r="O22" s="106"/>
+      <c r="P22" s="106"/>
+      <c r="Q22" s="103"/>
+      <c r="R22" s="107"/>
+      <c r="S22" s="108"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="111"/>
-      <c r="C23" s="112"/>
-      <c r="D23" s="113"/>
-      <c r="E23" s="114"/>
-      <c r="F23" s="115"/>
-      <c r="G23" s="117"/>
-      <c r="H23" s="117"/>
-      <c r="I23" s="114"/>
-      <c r="J23" s="115"/>
-      <c r="K23" s="117"/>
-      <c r="L23" s="117"/>
-      <c r="M23" s="114"/>
-      <c r="N23" s="115"/>
-      <c r="O23" s="117"/>
-      <c r="P23" s="117"/>
-      <c r="Q23" s="114"/>
-      <c r="R23" s="115"/>
-      <c r="S23" s="118"/>
+      <c r="B23" s="110"/>
+      <c r="C23" s="111"/>
+      <c r="D23" s="112"/>
+      <c r="E23" s="113"/>
+      <c r="F23" s="114"/>
+      <c r="G23" s="116"/>
+      <c r="H23" s="116"/>
+      <c r="I23" s="113"/>
+      <c r="J23" s="114"/>
+      <c r="K23" s="116"/>
+      <c r="L23" s="116"/>
+      <c r="M23" s="113"/>
+      <c r="N23" s="114"/>
+      <c r="O23" s="116"/>
+      <c r="P23" s="116"/>
+      <c r="Q23" s="113"/>
+      <c r="R23" s="114"/>
+      <c r="S23" s="117"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="76" t="s">
-        <v>137</v>
-      </c>
-      <c r="C24" s="75" t="s">
+      <c r="B24" s="75" t="s">
         <v>138</v>
       </c>
-      <c r="D24" s="88"/>
-      <c r="E24" s="89"/>
-      <c r="F24" s="92"/>
-      <c r="G24" s="91"/>
-      <c r="H24" s="91"/>
-      <c r="I24" s="89"/>
-      <c r="J24" s="92"/>
-      <c r="K24" s="91"/>
-      <c r="L24" s="91"/>
-      <c r="M24" s="120"/>
-      <c r="N24" s="90"/>
-      <c r="O24" s="119"/>
-      <c r="P24" s="119"/>
-      <c r="Q24" s="89"/>
-      <c r="R24" s="92"/>
-      <c r="S24" s="93"/>
+      <c r="C24" s="74" t="s">
+        <v>139</v>
+      </c>
+      <c r="D24" s="87"/>
+      <c r="E24" s="88"/>
+      <c r="F24" s="91"/>
+      <c r="G24" s="90"/>
+      <c r="H24" s="90"/>
+      <c r="I24" s="88"/>
+      <c r="J24" s="91"/>
+      <c r="K24" s="90"/>
+      <c r="L24" s="90"/>
+      <c r="M24" s="119"/>
+      <c r="N24" s="89"/>
+      <c r="O24" s="118"/>
+      <c r="P24" s="118"/>
+      <c r="Q24" s="88"/>
+      <c r="R24" s="91"/>
+      <c r="S24" s="92"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="87"/>
-      <c r="C25" s="94"/>
-      <c r="D25" s="95"/>
-      <c r="E25" s="96"/>
-      <c r="F25" s="100"/>
-      <c r="G25" s="99"/>
-      <c r="H25" s="99"/>
-      <c r="I25" s="96"/>
-      <c r="J25" s="100"/>
-      <c r="K25" s="99"/>
-      <c r="L25" s="99"/>
-      <c r="M25" s="96"/>
-      <c r="N25" s="100"/>
-      <c r="O25" s="99"/>
-      <c r="P25" s="99"/>
-      <c r="Q25" s="96"/>
-      <c r="R25" s="100"/>
-      <c r="S25" s="101"/>
+      <c r="B25" s="86"/>
+      <c r="C25" s="93"/>
+      <c r="D25" s="94"/>
+      <c r="E25" s="95"/>
+      <c r="F25" s="99"/>
+      <c r="G25" s="98"/>
+      <c r="H25" s="98"/>
+      <c r="I25" s="95"/>
+      <c r="J25" s="99"/>
+      <c r="K25" s="98"/>
+      <c r="L25" s="98"/>
+      <c r="M25" s="95"/>
+      <c r="N25" s="99"/>
+      <c r="O25" s="98"/>
+      <c r="P25" s="98"/>
+      <c r="Q25" s="95"/>
+      <c r="R25" s="99"/>
+      <c r="S25" s="100"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="87"/>
-      <c r="C26" s="102" t="s">
-        <v>139</v>
-      </c>
-      <c r="D26" s="103"/>
-      <c r="E26" s="104"/>
-      <c r="F26" s="108"/>
-      <c r="G26" s="107"/>
-      <c r="H26" s="107"/>
-      <c r="I26" s="104"/>
-      <c r="J26" s="108"/>
-      <c r="K26" s="107"/>
-      <c r="L26" s="107"/>
-      <c r="M26" s="104"/>
-      <c r="N26" s="108"/>
-      <c r="O26" s="106"/>
-      <c r="P26" s="106"/>
-      <c r="Q26" s="104"/>
-      <c r="R26" s="108"/>
-      <c r="S26" s="109"/>
+      <c r="B26" s="86"/>
+      <c r="C26" s="101" t="s">
+        <v>140</v>
+      </c>
+      <c r="D26" s="102"/>
+      <c r="E26" s="103"/>
+      <c r="F26" s="107"/>
+      <c r="G26" s="106"/>
+      <c r="H26" s="106"/>
+      <c r="I26" s="103"/>
+      <c r="J26" s="107"/>
+      <c r="K26" s="106"/>
+      <c r="L26" s="106"/>
+      <c r="M26" s="103"/>
+      <c r="N26" s="107"/>
+      <c r="O26" s="105"/>
+      <c r="P26" s="105"/>
+      <c r="Q26" s="103"/>
+      <c r="R26" s="107"/>
+      <c r="S26" s="108"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="87"/>
-      <c r="C27" s="94"/>
-      <c r="D27" s="95"/>
-      <c r="E27" s="96"/>
-      <c r="F27" s="100"/>
-      <c r="G27" s="99"/>
-      <c r="H27" s="99"/>
-      <c r="I27" s="96"/>
-      <c r="J27" s="100"/>
-      <c r="K27" s="99"/>
-      <c r="L27" s="99"/>
-      <c r="M27" s="96"/>
-      <c r="N27" s="100"/>
-      <c r="O27" s="99"/>
-      <c r="P27" s="99"/>
-      <c r="Q27" s="96"/>
-      <c r="R27" s="100"/>
-      <c r="S27" s="101"/>
+      <c r="B27" s="86"/>
+      <c r="C27" s="93"/>
+      <c r="D27" s="94"/>
+      <c r="E27" s="95"/>
+      <c r="F27" s="99"/>
+      <c r="G27" s="98"/>
+      <c r="H27" s="98"/>
+      <c r="I27" s="95"/>
+      <c r="J27" s="99"/>
+      <c r="K27" s="98"/>
+      <c r="L27" s="98"/>
+      <c r="M27" s="95"/>
+      <c r="N27" s="99"/>
+      <c r="O27" s="98"/>
+      <c r="P27" s="98"/>
+      <c r="Q27" s="95"/>
+      <c r="R27" s="99"/>
+      <c r="S27" s="100"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="87"/>
-      <c r="C28" s="102" t="s">
-        <v>140</v>
-      </c>
-      <c r="D28" s="103"/>
-      <c r="E28" s="104"/>
-      <c r="F28" s="108"/>
-      <c r="G28" s="107"/>
-      <c r="H28" s="107"/>
-      <c r="I28" s="104"/>
-      <c r="J28" s="108"/>
-      <c r="K28" s="107"/>
-      <c r="L28" s="107"/>
-      <c r="M28" s="104"/>
-      <c r="N28" s="108"/>
-      <c r="O28" s="107"/>
-      <c r="P28" s="106"/>
-      <c r="Q28" s="123"/>
-      <c r="R28" s="108"/>
-      <c r="S28" s="109"/>
+      <c r="B28" s="86"/>
+      <c r="C28" s="101" t="s">
+        <v>141</v>
+      </c>
+      <c r="D28" s="102"/>
+      <c r="E28" s="103"/>
+      <c r="F28" s="107"/>
+      <c r="G28" s="106"/>
+      <c r="H28" s="106"/>
+      <c r="I28" s="103"/>
+      <c r="J28" s="107"/>
+      <c r="K28" s="106"/>
+      <c r="L28" s="106"/>
+      <c r="M28" s="103"/>
+      <c r="N28" s="107"/>
+      <c r="O28" s="106"/>
+      <c r="P28" s="105"/>
+      <c r="Q28" s="122"/>
+      <c r="R28" s="107"/>
+      <c r="S28" s="108"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="87"/>
-      <c r="C29" s="81"/>
-      <c r="D29" s="126"/>
-      <c r="E29" s="127"/>
-      <c r="F29" s="128"/>
-      <c r="G29" s="129"/>
-      <c r="H29" s="130"/>
-      <c r="I29" s="127"/>
-      <c r="J29" s="128"/>
-      <c r="K29" s="129"/>
-      <c r="L29" s="130"/>
-      <c r="M29" s="127"/>
-      <c r="N29" s="131"/>
-      <c r="O29" s="130"/>
-      <c r="P29" s="129"/>
-      <c r="Q29" s="127"/>
-      <c r="R29" s="128"/>
-      <c r="S29" s="132"/>
+      <c r="B29" s="86"/>
+      <c r="C29" s="80"/>
+      <c r="D29" s="125"/>
+      <c r="E29" s="126"/>
+      <c r="F29" s="127"/>
+      <c r="G29" s="128"/>
+      <c r="H29" s="129"/>
+      <c r="I29" s="126"/>
+      <c r="J29" s="127"/>
+      <c r="K29" s="128"/>
+      <c r="L29" s="129"/>
+      <c r="M29" s="126"/>
+      <c r="N29" s="130"/>
+      <c r="O29" s="129"/>
+      <c r="P29" s="128"/>
+      <c r="Q29" s="126"/>
+      <c r="R29" s="127"/>
+      <c r="S29" s="131"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="133" t="s">
+      <c r="B30" s="132" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="134" t="s">
-        <v>84</v>
-      </c>
-      <c r="D30" s="88"/>
-      <c r="E30" s="135"/>
-      <c r="F30" s="136"/>
-      <c r="G30" s="136"/>
-      <c r="H30" s="137"/>
-      <c r="I30" s="138"/>
-      <c r="J30" s="136"/>
-      <c r="K30" s="136"/>
-      <c r="L30" s="137"/>
-      <c r="M30" s="138"/>
-      <c r="N30" s="136"/>
-      <c r="O30" s="137"/>
-      <c r="P30" s="136"/>
-      <c r="Q30" s="138"/>
-      <c r="R30" s="136"/>
-      <c r="S30" s="139"/>
+      <c r="C30" s="133" t="s">
+        <v>85</v>
+      </c>
+      <c r="D30" s="87"/>
+      <c r="E30" s="134"/>
+      <c r="F30" s="135"/>
+      <c r="G30" s="135"/>
+      <c r="H30" s="136"/>
+      <c r="I30" s="137"/>
+      <c r="J30" s="135"/>
+      <c r="K30" s="135"/>
+      <c r="L30" s="136"/>
+      <c r="M30" s="137"/>
+      <c r="N30" s="135"/>
+      <c r="O30" s="136"/>
+      <c r="P30" s="135"/>
+      <c r="Q30" s="137"/>
+      <c r="R30" s="135"/>
+      <c r="S30" s="138"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="140"/>
-      <c r="C31" s="141"/>
-      <c r="D31" s="95"/>
-      <c r="E31" s="142"/>
-      <c r="F31" s="143"/>
-      <c r="G31" s="143"/>
-      <c r="H31" s="144"/>
-      <c r="I31" s="145"/>
-      <c r="J31" s="143"/>
-      <c r="K31" s="146"/>
-      <c r="L31" s="144"/>
-      <c r="M31" s="145"/>
-      <c r="N31" s="143"/>
-      <c r="O31" s="144"/>
-      <c r="P31" s="143"/>
-      <c r="Q31" s="145"/>
-      <c r="R31" s="143"/>
-      <c r="S31" s="101"/>
+      <c r="B31" s="139"/>
+      <c r="C31" s="140"/>
+      <c r="D31" s="94"/>
+      <c r="E31" s="141"/>
+      <c r="F31" s="142"/>
+      <c r="G31" s="142"/>
+      <c r="H31" s="143"/>
+      <c r="I31" s="144"/>
+      <c r="J31" s="142"/>
+      <c r="K31" s="145"/>
+      <c r="L31" s="143"/>
+      <c r="M31" s="144"/>
+      <c r="N31" s="142"/>
+      <c r="O31" s="143"/>
+      <c r="P31" s="142"/>
+      <c r="Q31" s="144"/>
+      <c r="R31" s="142"/>
+      <c r="S31" s="100"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="140"/>
-      <c r="C32" s="141" t="s">
+      <c r="B32" s="139"/>
+      <c r="C32" s="140" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="103"/>
-      <c r="E32" s="147"/>
-      <c r="F32" s="148"/>
-      <c r="G32" s="148"/>
-      <c r="H32" s="149"/>
-      <c r="I32" s="150"/>
-      <c r="J32" s="148"/>
-      <c r="K32" s="148"/>
-      <c r="L32" s="149"/>
-      <c r="M32" s="150"/>
-      <c r="N32" s="148"/>
-      <c r="O32" s="149"/>
-      <c r="P32" s="148"/>
-      <c r="Q32" s="150"/>
-      <c r="R32" s="148"/>
-      <c r="S32" s="151"/>
+      <c r="D32" s="102"/>
+      <c r="E32" s="146"/>
+      <c r="F32" s="147"/>
+      <c r="G32" s="147"/>
+      <c r="H32" s="148"/>
+      <c r="I32" s="149"/>
+      <c r="J32" s="147"/>
+      <c r="K32" s="147"/>
+      <c r="L32" s="148"/>
+      <c r="M32" s="149"/>
+      <c r="N32" s="147"/>
+      <c r="O32" s="148"/>
+      <c r="P32" s="147"/>
+      <c r="Q32" s="149"/>
+      <c r="R32" s="147"/>
+      <c r="S32" s="150"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="140"/>
-      <c r="C33" s="141"/>
-      <c r="D33" s="95"/>
-      <c r="E33" s="142"/>
-      <c r="F33" s="146"/>
-      <c r="G33" s="143"/>
-      <c r="H33" s="152"/>
-      <c r="I33" s="153"/>
-      <c r="J33" s="143"/>
-      <c r="K33" s="146"/>
-      <c r="L33" s="144"/>
-      <c r="M33" s="145"/>
-      <c r="N33" s="143"/>
-      <c r="O33" s="144"/>
-      <c r="P33" s="143"/>
-      <c r="Q33" s="145"/>
-      <c r="R33" s="143"/>
-      <c r="S33" s="101"/>
+      <c r="B33" s="139"/>
+      <c r="C33" s="140"/>
+      <c r="D33" s="94"/>
+      <c r="E33" s="141"/>
+      <c r="F33" s="145"/>
+      <c r="G33" s="142"/>
+      <c r="H33" s="151"/>
+      <c r="I33" s="152"/>
+      <c r="J33" s="142"/>
+      <c r="K33" s="145"/>
+      <c r="L33" s="143"/>
+      <c r="M33" s="144"/>
+      <c r="N33" s="142"/>
+      <c r="O33" s="143"/>
+      <c r="P33" s="142"/>
+      <c r="Q33" s="144"/>
+      <c r="R33" s="142"/>
+      <c r="S33" s="100"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="140"/>
-      <c r="C34" s="94" t="s">
-        <v>141</v>
-      </c>
-      <c r="D34" s="126"/>
-      <c r="E34" s="154"/>
-      <c r="F34" s="155"/>
-      <c r="G34" s="155"/>
-      <c r="H34" s="156"/>
-      <c r="I34" s="157"/>
-      <c r="J34" s="155"/>
-      <c r="K34" s="155"/>
-      <c r="L34" s="156"/>
-      <c r="M34" s="157"/>
-      <c r="N34" s="155"/>
-      <c r="O34" s="156"/>
-      <c r="P34" s="155"/>
-      <c r="Q34" s="157"/>
-      <c r="R34" s="155"/>
-      <c r="S34" s="158"/>
-      <c r="U34" s="159"/>
-      <c r="V34" s="160" t="s">
+      <c r="B34" s="139"/>
+      <c r="C34" s="93" t="s">
         <v>142</v>
       </c>
+      <c r="D34" s="125"/>
+      <c r="E34" s="153"/>
+      <c r="F34" s="154"/>
+      <c r="G34" s="154"/>
+      <c r="H34" s="155"/>
+      <c r="I34" s="156"/>
+      <c r="J34" s="154"/>
+      <c r="K34" s="154"/>
+      <c r="L34" s="155"/>
+      <c r="M34" s="156"/>
+      <c r="N34" s="154"/>
+      <c r="O34" s="155"/>
+      <c r="P34" s="154"/>
+      <c r="Q34" s="156"/>
+      <c r="R34" s="154"/>
+      <c r="S34" s="157"/>
+      <c r="U34" s="158"/>
+      <c r="V34" s="159" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="161"/>
-      <c r="C35" s="162"/>
-      <c r="D35" s="113"/>
-      <c r="E35" s="163"/>
-      <c r="F35" s="164"/>
-      <c r="G35" s="164"/>
-      <c r="H35" s="165"/>
-      <c r="I35" s="166"/>
-      <c r="J35" s="164"/>
-      <c r="K35" s="164"/>
-      <c r="L35" s="165"/>
-      <c r="M35" s="166"/>
-      <c r="N35" s="164"/>
-      <c r="O35" s="165"/>
-      <c r="P35" s="164"/>
-      <c r="Q35" s="166"/>
-      <c r="R35" s="164"/>
-      <c r="S35" s="118"/>
-      <c r="U35" s="167"/>
-      <c r="V35" s="168" t="s">
-        <v>143</v>
+      <c r="B35" s="160"/>
+      <c r="C35" s="161"/>
+      <c r="D35" s="112"/>
+      <c r="E35" s="162"/>
+      <c r="F35" s="163"/>
+      <c r="G35" s="163"/>
+      <c r="H35" s="164"/>
+      <c r="I35" s="165"/>
+      <c r="J35" s="163"/>
+      <c r="K35" s="163"/>
+      <c r="L35" s="164"/>
+      <c r="M35" s="165"/>
+      <c r="N35" s="163"/>
+      <c r="O35" s="164"/>
+      <c r="P35" s="163"/>
+      <c r="Q35" s="165"/>
+      <c r="R35" s="163"/>
+      <c r="S35" s="117"/>
+      <c r="U35" s="166"/>
+      <c r="V35" s="167" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/HoferL-JournalPlanif-M5.xlsx
+++ b/Documentation/HoferL-JournalPlanif-M5.xlsx
@@ -12,7 +12,7 @@
     <sheet name="PlanificationExemple" sheetId="4" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$B$2:$H$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$B$2:$H$33</definedName>
   </definedNames>
   <calcPr concurrentCalc="0"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
   <si>
     <t>date</t>
   </si>
@@ -212,6 +212,18 @@
   </si>
   <si>
     <t xml:space="preserve">Implémentation des police, couleur, themes et propriété d'affichage. Reflexion sur la possibilité d'avoir un thème sombre ET claire.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test de fonctionnement sur Windows, Linux et MacOS. Fonctionnel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajout des boutons de navigation entre les pages. Ajout de la page paramète. Implémentation du changement de thème et de la séléction du fichier BDD.db. Ajout d'une démonstration de la page d'accueil avec les notes (moyenne et tendances).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentation des différents fichiers (code) du projet. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentation des ressources globale et de la page paramètres.</t>
   </si>
   <si>
     <t>Phases</t>
@@ -1438,7 +1450,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="170">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1468,6 +1480,7 @@
     <xf fontId="2" fillId="0" borderId="0" numFmtId="9" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1475,10 +1488,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1488,6 +1501,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1"/>
@@ -2276,10 +2290,10 @@
                   <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>26</c:v>
+                  <c:v>27.999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2516,12 +2530,6 @@
           <c:tx>
             <c:strRef>
               <c:f>SommeParJours!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>somme</c:v>
-                </c:pt>
-              </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr bwMode="auto">
@@ -2539,9 +2547,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>SommeParJours!$A$2:$A$14</c:f>
+              <c:f>SommeParJours!$A$2:$A$18</c:f>
               <c:strCache>
-                <c:ptCount val="13"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>20.01.2026</c:v>
                 </c:pt>
@@ -2581,15 +2589,27 @@
                 <c:pt idx="12">
                   <c:v>03.03.2026</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>05.03.2026</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3/6/2026</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3/7/2026</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3/10/2026</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SommeParJours!$B$2:$B$14</c:f>
+              <c:f>SommeParJours!$B$2:$B$18</c:f>
               <c:numCache>
                 <c:formatCode>h:mm;@</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>0.16666666666666666</c:v>
                 </c:pt>
@@ -2627,7 +2647,19 @@
                   <c:v>0.125</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.125</c:v>
+                  <c:v>0.20833333333333331</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.1875</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.1875</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.08333333333333333</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4273,8 +4305,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E30">
-  <autoFilter ref="B2:E30"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E34">
+  <autoFilter ref="B2:E34"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -4837,14 +4869,14 @@
       </c>
       <c r="I3" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>4.6875e-002</v>
+        <v>0.040000000000000001</v>
       </c>
       <c r="J3" s="11" t="str" cm="1">
-        <f t="array" ref="J3:J8">_xlfn._xlws.FILTER(G3:G10,H3:H10&gt;0)</f>
+        <f t="array" ref="J3:J9">_xlfn._xlws.FILTER(G3:G10,H3:H10&gt;0)</f>
         <v>Cours</v>
       </c>
       <c r="K3" s="12" cm="1">
-        <f t="array" ref="K3:K8">_xlfn._xlws.FILTER(H3:H10,H3:H10&gt;0)</f>
+        <f t="array" ref="K3:K9">_xlfn._xlws.FILTER(H3:H10,H3:H10&gt;0)</f>
         <v>3</v>
       </c>
     </row>
@@ -4853,7 +4885,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="5">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>8</v>
@@ -4870,7 +4902,7 @@
       </c>
       <c r="I4" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>4.6875e-002</v>
+        <v>0.040000000000000001</v>
       </c>
       <c r="J4" s="3" t="str">
         <f/>
@@ -4903,7 +4935,7 @@
       </c>
       <c r="I5" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>9.375e-002</v>
+        <v>0.080000000000000002</v>
       </c>
       <c r="J5" s="3" t="str">
         <f/>
@@ -4919,7 +4951,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="5">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>8</v>
@@ -4936,7 +4968,7 @@
       </c>
       <c r="I6" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.265625</v>
+        <v>0.22666666666666666</v>
       </c>
       <c r="J6" s="3" t="str">
         <f/>
@@ -4952,7 +4984,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="5">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>8</v>
@@ -4965,11 +4997,11 @@
       </c>
       <c r="H7" s="9">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>26</v>
+        <v>30.5</v>
       </c>
       <c r="I7" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.40625</v>
+        <v>0.40666666666666668</v>
       </c>
       <c r="J7" s="3" t="str">
         <f/>
@@ -4977,7 +5009,7 @@
       </c>
       <c r="K7" s="12">
         <f/>
-        <v>26</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="8" ht="28.5">
@@ -4998,11 +5030,11 @@
       </c>
       <c r="H8" s="9">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I8" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.140625</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="J8" s="3" t="str">
         <f/>
@@ -5010,7 +5042,7 @@
       </c>
       <c r="K8" s="12">
         <f/>
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -5031,21 +5063,27 @@
       </c>
       <c r="H9" s="9">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I9" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+        <v>0.0066666666666666671</v>
+      </c>
+      <c r="J9" s="3" t="str">
+        <f/>
+        <v>Tests</v>
+      </c>
+      <c r="K9" s="13">
+        <f/>
+        <v>0.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="5">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>12</v>
@@ -5053,10 +5091,10 @@
       <c r="E10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="15">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
         <v>0</v>
       </c>
@@ -5072,7 +5110,7 @@
         <v>22</v>
       </c>
       <c r="C11" s="5">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>12</v>
@@ -5085,7 +5123,7 @@
       </c>
       <c r="H11" s="9">
         <f>SUM(H3:H10)</f>
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -5095,7 +5133,7 @@
         <v>22</v>
       </c>
       <c r="C12" s="5">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>10</v>
@@ -5110,7 +5148,7 @@
         <v>22</v>
       </c>
       <c r="C13" s="5">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>12</v>
@@ -5125,7 +5163,7 @@
         <v>29</v>
       </c>
       <c r="C14" s="5">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>12</v>
@@ -5181,7 +5219,7 @@
         <v>35</v>
       </c>
       <c r="C18" s="5">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>10</v>
@@ -5195,7 +5233,7 @@
         <v>37</v>
       </c>
       <c r="C19" s="5">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>12</v>
@@ -5209,7 +5247,7 @@
         <v>39</v>
       </c>
       <c r="C20" s="5">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>19</v>
@@ -5223,7 +5261,7 @@
         <v>39</v>
       </c>
       <c r="C21" s="5">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>15</v>
@@ -5251,7 +5289,7 @@
         <v>43</v>
       </c>
       <c r="C23" s="5">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>15</v>
@@ -5265,7 +5303,7 @@
         <v>45</v>
       </c>
       <c r="C24" s="5">
-        <v>6.25e-002</v>
+        <v>0.0625</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>15</v>
@@ -5307,7 +5345,7 @@
         <v>49</v>
       </c>
       <c r="C27" s="5">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>12</v>
@@ -5321,7 +5359,7 @@
         <v>52</v>
       </c>
       <c r="C28" s="5">
-        <v>6.25e-002</v>
+        <v>0.0625</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>15</v>
@@ -5351,36 +5389,68 @@
       <c r="C30" s="5">
         <v>0.16666666666666666</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E30" s="16" t="s">
+      <c r="E30" s="7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="4"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="7"/>
-    </row>
-    <row r="32">
-      <c r="B32" s="4"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="7"/>
+    <row r="31" ht="42.75">
+      <c r="B31" s="4">
+        <v>46087</v>
+      </c>
+      <c r="C31" s="5">
+        <v>0.020833333333333332</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" ht="57">
+      <c r="B32" s="4">
+        <v>46088</v>
+      </c>
+      <c r="C32" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="33">
-      <c r="B33" s="4"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="7"/>
+      <c r="B33" s="4">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="5">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="34">
-      <c r="B34" s="4"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="7"/>
+      <c r="B34" s="4">
+        <v>46091</v>
+      </c>
+      <c r="C34" s="5">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="35">
       <c r="B35" s="4"/>
@@ -5397,13 +5467,13 @@
     <row r="37">
       <c r="B37" s="4"/>
       <c r="C37" s="5"/>
-      <c r="D37" s="7"/>
+      <c r="D37" s="6"/>
       <c r="E37" s="7"/>
     </row>
     <row r="38">
       <c r="B38" s="4"/>
       <c r="C38" s="5"/>
-      <c r="D38" s="6"/>
+      <c r="D38" s="7"/>
       <c r="E38" s="7"/>
     </row>
     <row r="39">
@@ -5461,169 +5531,169 @@
       <c r="E47" s="7"/>
     </row>
     <row r="48">
-      <c r="B48" s="17"/>
-      <c r="C48" s="6"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="5"/>
       <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
+      <c r="E48" s="7"/>
     </row>
     <row r="49">
-      <c r="B49" s="17"/>
+      <c r="B49" s="18"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
     </row>
     <row r="50">
-      <c r="B50" s="17"/>
+      <c r="B50" s="18"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
     </row>
     <row r="51">
-      <c r="B51" s="17"/>
+      <c r="B51" s="18"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
     </row>
     <row r="52">
-      <c r="B52" s="17"/>
+      <c r="B52" s="18"/>
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
     </row>
     <row r="53">
-      <c r="B53" s="17"/>
+      <c r="B53" s="18"/>
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
     </row>
     <row r="54">
-      <c r="B54" s="17"/>
+      <c r="B54" s="18"/>
       <c r="C54" s="6"/>
       <c r="D54" s="6"/>
       <c r="E54" s="6"/>
     </row>
     <row r="55">
-      <c r="B55" s="17"/>
+      <c r="B55" s="18"/>
       <c r="C55" s="6"/>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
     </row>
     <row r="56">
-      <c r="B56" s="17"/>
+      <c r="B56" s="18"/>
       <c r="C56" s="6"/>
       <c r="D56" s="6"/>
       <c r="E56" s="6"/>
     </row>
     <row r="57">
-      <c r="B57" s="17"/>
+      <c r="B57" s="18"/>
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
       <c r="E57" s="6"/>
     </row>
     <row r="58">
-      <c r="B58" s="17"/>
+      <c r="B58" s="18"/>
       <c r="C58" s="6"/>
       <c r="D58" s="6"/>
       <c r="E58" s="6"/>
     </row>
     <row r="59">
-      <c r="B59" s="17"/>
+      <c r="B59" s="18"/>
       <c r="C59" s="6"/>
       <c r="D59" s="6"/>
       <c r="E59" s="6"/>
     </row>
     <row r="60">
-      <c r="B60" s="17"/>
+      <c r="B60" s="18"/>
       <c r="C60" s="6"/>
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
     </row>
     <row r="61">
-      <c r="B61" s="17"/>
+      <c r="B61" s="18"/>
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
     </row>
     <row r="62">
-      <c r="B62" s="17"/>
+      <c r="B62" s="18"/>
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
     </row>
     <row r="63">
-      <c r="B63" s="17"/>
+      <c r="B63" s="18"/>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
     </row>
     <row r="64">
-      <c r="B64" s="17"/>
+      <c r="B64" s="18"/>
       <c r="C64" s="6"/>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
     </row>
     <row r="65">
-      <c r="B65" s="17"/>
+      <c r="B65" s="18"/>
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
     </row>
     <row r="66">
-      <c r="B66" s="17"/>
+      <c r="B66" s="18"/>
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
     </row>
     <row r="67">
-      <c r="B67" s="17"/>
+      <c r="B67" s="18"/>
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
     </row>
     <row r="68">
-      <c r="B68" s="17"/>
+      <c r="B68" s="18"/>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
     </row>
     <row r="69">
-      <c r="B69" s="17"/>
+      <c r="B69" s="18"/>
       <c r="C69" s="6"/>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
     </row>
     <row r="70">
-      <c r="B70" s="17"/>
+      <c r="B70" s="18"/>
       <c r="C70" s="6"/>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
     </row>
     <row r="71">
-      <c r="B71" s="17"/>
+      <c r="B71" s="18"/>
       <c r="C71" s="6"/>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
     </row>
     <row r="72">
-      <c r="B72" s="17"/>
+      <c r="B72" s="18"/>
       <c r="C72" s="6"/>
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
     </row>
     <row r="73">
-      <c r="B73" s="17"/>
+      <c r="B73" s="18"/>
       <c r="C73" s="6"/>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
     </row>
     <row r="74">
-      <c r="B74" s="17"/>
+      <c r="B74" s="18"/>
       <c r="C74" s="6"/>
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
     </row>
     <row r="75">
-      <c r="B75" s="6"/>
+      <c r="B75" s="18"/>
       <c r="C75" s="6"/>
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
@@ -5657,6 +5727,12 @@
       <c r="C80" s="6"/>
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
+    </row>
+    <row r="81">
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -5674,11 +5750,11 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00F90069-000C-4FB8-B761-00BB00FB0041}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00460070-00E0-41C0-BBEB-00B20011005C}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D55</xm:sqref>
+          <xm:sqref>D3:D56</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5690,7 +5766,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="3" max="3" style="18" width="5.6640625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" style="19" width="5.6640625"/>
     <col bestFit="1" customWidth="1" min="4" max="4" width="12.21875"/>
     <col bestFit="1" customWidth="1" min="5" max="5" width="9.5546875"/>
     <col bestFit="1" customWidth="1" min="6" max="6" width="11.109375"/>
@@ -5706,1648 +5782,1671 @@
       <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" s="19" t="str" cm="1">
-        <f t="array" ref="A2:A16">_xlfn.UNIQUE(Journal[date])</f>
+      <c r="A2" s="20" t="str" cm="1">
+        <f t="array" ref="A2:A18">_xlfn.UNIQUE(Journal[date])</f>
         <v>20.01.2026</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A2,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C2" s="20"/>
+      <c r="C2" s="21"/>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="str">
+      <c r="A3" s="20" t="str">
         <f/>
         <v>27.01.2026</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="str">
+      <c r="A4" s="20" t="str">
         <f/>
         <v>30.01.2026</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C4"/>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="str">
+      <c r="A5" s="20" t="str">
         <f/>
         <v>03.02.2026</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0.25</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="str">
+      <c r="A6" s="20" t="str">
         <f/>
         <v>04.02.2026</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="str">
+      <c r="A7" s="20" t="str">
         <f/>
         <v>06.02.2026</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C7"/>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="str">
+      <c r="A8" s="20" t="str">
         <f/>
         <v>08.02.2026</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="str">
+      <c r="A9" s="20" t="str">
         <f/>
         <v>09.02.2026</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="str">
+      <c r="A10" s="20" t="str">
         <f/>
         <v>10.02.2026</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="str">
+      <c r="A11" s="20" t="str">
         <f/>
         <v>12.02.2026</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="str">
+      <c r="A12" s="20" t="str">
         <f/>
         <v>13.02.2026</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
-        <v>6.25e-002</v>
+        <v>0.0625</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="str">
+      <c r="A13" s="20" t="str">
         <f/>
         <v>24.02.2026</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B13" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0.125</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="str">
+      <c r="A14" s="20" t="str">
         <f/>
         <v>03.03.2026</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="21">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="str">
+      <c r="A15" s="20" t="str">
         <f/>
         <v>05.03.2026</v>
       </c>
+      <c r="B15" s="21">
+        <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
+        <v>0.1875</v>
+      </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="19">
+      <c r="A16" s="20">
         <f/>
         <v>46087</v>
       </c>
+      <c r="B16" s="21">
+        <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
+        <v>0.1875</v>
+      </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="19"/>
+      <c r="A17" s="20">
+        <f/>
+        <v>46088</v>
+      </c>
+      <c r="B17" s="21">
+        <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
+        <v>0.25</v>
+      </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="19"/>
+      <c r="A18" s="20">
+        <f/>
+        <v>46091</v>
+      </c>
+      <c r="B18" s="21">
+        <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
+        <v>0.1875</v>
+      </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="19"/>
+      <c r="A19" s="20"/>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="19"/>
+      <c r="A20" s="20"/>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="19"/>
+      <c r="A21" s="20"/>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="19"/>
+      <c r="A22" s="20"/>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="19"/>
+      <c r="A23" s="20"/>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="19"/>
+      <c r="A24" s="20"/>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="19"/>
+      <c r="A25" s="20"/>
       <c r="C25"/>
+      <c r="F25" s="22"/>
     </row>
     <row r="26">
-      <c r="A26" s="19"/>
-      <c r="C26" s="21">
+      <c r="A26" s="20"/>
+      <c r="C26" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="19"/>
-      <c r="C27" s="21">
+      <c r="A27" s="20"/>
+      <c r="C27" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="19"/>
-      <c r="C28" s="21">
+      <c r="A28" s="20"/>
+      <c r="C28" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="19"/>
-      <c r="C29" s="21">
+      <c r="A29" s="20"/>
+      <c r="C29" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="19"/>
-      <c r="C30" s="21">
+      <c r="A30" s="20"/>
+      <c r="C30" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="19"/>
-      <c r="C31" s="21">
+      <c r="A31" s="20"/>
+      <c r="C31" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="19"/>
-      <c r="C32" s="21">
+      <c r="A32" s="20"/>
+      <c r="C32" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="19"/>
-      <c r="C33" s="21">
+      <c r="A33" s="20"/>
+      <c r="C33" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="19"/>
-      <c r="C34" s="21">
+      <c r="A34" s="20"/>
+      <c r="C34" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="19"/>
-      <c r="C35" s="21">
+      <c r="A35" s="20"/>
+      <c r="C35" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="19"/>
-      <c r="C36" s="21">
+      <c r="A36" s="20"/>
+      <c r="C36" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="19"/>
-      <c r="C37" s="21">
+      <c r="A37" s="20"/>
+      <c r="C37" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="19"/>
-      <c r="C38" s="21">
+      <c r="A38" s="20"/>
+      <c r="C38" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="19"/>
-      <c r="C39" s="21">
+      <c r="A39" s="20"/>
+      <c r="C39" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="19"/>
-      <c r="B40" s="20" t="str">
+      <c r="A40" s="20"/>
+      <c r="B40" s="21" t="str">
         <f t="shared" ref="B40:B103" si="0">IF(C40&gt;0,C40,"")</f>
         <v/>
       </c>
-      <c r="C40" s="21">
+      <c r="C40" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="19"/>
-      <c r="B41" s="20" t="str">
+      <c r="A41" s="20"/>
+      <c r="B41" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="21">
+      <c r="C41" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="22"/>
-      <c r="B42" s="20" t="str">
+      <c r="A42" s="24"/>
+      <c r="B42" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="21">
+      <c r="C42" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="22"/>
-      <c r="B43" s="20" t="str">
+      <c r="A43" s="24"/>
+      <c r="B43" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="21">
+      <c r="C43" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="22"/>
-      <c r="B44" s="20" t="str">
+      <c r="A44" s="24"/>
+      <c r="B44" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="21">
+      <c r="C44" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="22"/>
-      <c r="B45" s="20" t="str">
+      <c r="A45" s="24"/>
+      <c r="B45" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="21">
+      <c r="C45" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="22"/>
-      <c r="B46" s="20" t="str">
+      <c r="A46" s="24"/>
+      <c r="B46" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="21">
+      <c r="C46" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="23"/>
-      <c r="B47" s="20" t="str">
+      <c r="A47" s="25"/>
+      <c r="B47" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="21">
+      <c r="C47" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="23"/>
-      <c r="B48" s="20" t="str">
+      <c r="A48" s="25"/>
+      <c r="B48" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="21">
+      <c r="C48" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="23"/>
-      <c r="B49" s="20" t="str">
+      <c r="A49" s="25"/>
+      <c r="B49" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C49" s="21">
+      <c r="C49" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="23"/>
-      <c r="B50" s="20" t="str">
+      <c r="A50" s="25"/>
+      <c r="B50" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C50" s="21">
+      <c r="C50" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="23"/>
-      <c r="B51" s="20" t="str">
+      <c r="A51" s="25"/>
+      <c r="B51" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C51" s="21">
+      <c r="C51" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="23"/>
-      <c r="B52" s="20" t="str">
+      <c r="A52" s="25"/>
+      <c r="B52" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C52" s="21">
+      <c r="C52" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="23"/>
-      <c r="B53" s="20" t="str">
+      <c r="A53" s="25"/>
+      <c r="B53" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C53" s="21">
+      <c r="C53" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="23"/>
-      <c r="B54" s="20" t="str">
+      <c r="A54" s="25"/>
+      <c r="B54" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C54" s="21">
+      <c r="C54" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="23"/>
-      <c r="B55" s="20" t="str">
+      <c r="A55" s="25"/>
+      <c r="B55" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C55" s="21">
+      <c r="C55" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="23"/>
-      <c r="B56" s="20" t="str">
+      <c r="A56" s="25"/>
+      <c r="B56" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C56" s="21">
+      <c r="C56" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="23"/>
-      <c r="B57" s="20" t="str">
+      <c r="A57" s="25"/>
+      <c r="B57" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C57" s="21">
+      <c r="C57" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="23"/>
-      <c r="B58" s="20" t="str">
+      <c r="A58" s="25"/>
+      <c r="B58" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C58" s="21">
+      <c r="C58" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="23"/>
-      <c r="B59" s="20" t="str">
+      <c r="A59" s="25"/>
+      <c r="B59" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C59" s="21">
+      <c r="C59" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="23"/>
-      <c r="B60" s="20" t="str">
+      <c r="A60" s="25"/>
+      <c r="B60" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C60" s="21">
+      <c r="C60" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="23"/>
-      <c r="B61" s="20" t="str">
+      <c r="A61" s="25"/>
+      <c r="B61" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C61" s="21">
+      <c r="C61" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="23"/>
-      <c r="B62" s="20" t="str">
+      <c r="A62" s="25"/>
+      <c r="B62" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C62" s="21">
+      <c r="C62" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="23"/>
-      <c r="B63" s="20" t="str">
+      <c r="A63" s="25"/>
+      <c r="B63" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C63" s="21">
+      <c r="C63" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="23"/>
-      <c r="B64" s="20" t="str">
+      <c r="A64" s="25"/>
+      <c r="B64" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C64" s="21">
+      <c r="C64" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="23"/>
-      <c r="B65" s="20" t="str">
+      <c r="A65" s="25"/>
+      <c r="B65" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C65" s="21">
+      <c r="C65" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="23"/>
-      <c r="B66" s="20" t="str">
+      <c r="A66" s="25"/>
+      <c r="B66" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C66" s="21">
+      <c r="C66" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="23"/>
-      <c r="B67" s="20" t="str">
+      <c r="A67" s="25"/>
+      <c r="B67" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C67" s="21">
+      <c r="C67" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="23"/>
-      <c r="B68" s="20" t="str">
+      <c r="A68" s="25"/>
+      <c r="B68" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C68" s="21">
+      <c r="C68" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="23"/>
-      <c r="B69" s="20" t="str">
+      <c r="A69" s="25"/>
+      <c r="B69" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C69" s="21">
+      <c r="C69" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="23"/>
-      <c r="B70" s="20" t="str">
+      <c r="A70" s="25"/>
+      <c r="B70" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C70" s="21">
+      <c r="C70" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="23"/>
-      <c r="B71" s="20" t="str">
+      <c r="A71" s="25"/>
+      <c r="B71" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C71" s="21">
+      <c r="C71" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="23"/>
-      <c r="B72" s="20" t="str">
+      <c r="A72" s="25"/>
+      <c r="B72" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C72" s="21">
+      <c r="C72" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="23"/>
-      <c r="B73" s="20" t="str">
+      <c r="A73" s="25"/>
+      <c r="B73" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C73" s="21">
+      <c r="C73" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="23"/>
-      <c r="B74" s="20" t="str">
+      <c r="A74" s="25"/>
+      <c r="B74" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C74" s="21">
+      <c r="C74" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="23"/>
-      <c r="B75" s="20" t="str">
+      <c r="A75" s="25"/>
+      <c r="B75" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C75" s="21">
+      <c r="C75" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="23"/>
-      <c r="B76" s="20" t="str">
+      <c r="A76" s="25"/>
+      <c r="B76" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C76" s="21">
+      <c r="C76" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="23"/>
-      <c r="B77" s="20" t="str">
+      <c r="A77" s="25"/>
+      <c r="B77" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C77" s="21">
+      <c r="C77" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="23"/>
-      <c r="B78" s="20" t="str">
+      <c r="A78" s="25"/>
+      <c r="B78" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C78" s="21">
+      <c r="C78" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="23"/>
-      <c r="B79" s="20" t="str">
+      <c r="A79" s="25"/>
+      <c r="B79" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C79" s="21">
+      <c r="C79" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="23"/>
-      <c r="B80" s="20" t="str">
+      <c r="A80" s="25"/>
+      <c r="B80" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C80" s="21">
+      <c r="C80" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="23"/>
-      <c r="B81" s="20" t="str">
+      <c r="A81" s="25"/>
+      <c r="B81" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C81" s="21">
+      <c r="C81" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="23"/>
-      <c r="B82" s="20" t="str">
+      <c r="A82" s="25"/>
+      <c r="B82" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C82" s="21">
+      <c r="C82" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="23"/>
-      <c r="B83" s="20" t="str">
+      <c r="A83" s="25"/>
+      <c r="B83" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C83" s="21">
+      <c r="C83" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="23"/>
-      <c r="B84" s="20" t="str">
+      <c r="A84" s="25"/>
+      <c r="B84" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C84" s="21">
+      <c r="C84" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="23"/>
-      <c r="B85" s="20" t="str">
+      <c r="A85" s="25"/>
+      <c r="B85" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C85" s="21">
+      <c r="C85" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="23"/>
-      <c r="B86" s="20" t="str">
+      <c r="A86" s="25"/>
+      <c r="B86" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C86" s="21">
+      <c r="C86" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="23"/>
-      <c r="B87" s="20" t="str">
+      <c r="A87" s="25"/>
+      <c r="B87" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C87" s="21">
+      <c r="C87" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="23"/>
-      <c r="B88" s="20" t="str">
+      <c r="A88" s="25"/>
+      <c r="B88" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C88" s="21">
+      <c r="C88" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="23"/>
-      <c r="B89" s="20" t="str">
+      <c r="A89" s="25"/>
+      <c r="B89" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C89" s="21">
+      <c r="C89" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="23"/>
-      <c r="B90" s="20" t="str">
+      <c r="A90" s="25"/>
+      <c r="B90" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C90" s="21">
+      <c r="C90" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="23"/>
-      <c r="B91" s="20" t="str">
+      <c r="A91" s="25"/>
+      <c r="B91" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C91" s="21">
+      <c r="C91" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="23"/>
-      <c r="B92" s="20" t="str">
+      <c r="A92" s="25"/>
+      <c r="B92" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C92" s="21">
+      <c r="C92" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="23"/>
-      <c r="B93" s="20" t="str">
+      <c r="A93" s="25"/>
+      <c r="B93" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C93" s="21">
+      <c r="C93" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="23"/>
-      <c r="B94" s="20" t="str">
+      <c r="A94" s="25"/>
+      <c r="B94" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C94" s="21">
+      <c r="C94" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="23"/>
-      <c r="B95" s="20" t="str">
+      <c r="A95" s="25"/>
+      <c r="B95" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C95" s="21">
+      <c r="C95" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="23"/>
-      <c r="B96" s="20" t="str">
+      <c r="A96" s="25"/>
+      <c r="B96" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C96" s="21">
+      <c r="C96" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="23"/>
-      <c r="B97" s="20" t="str">
+      <c r="A97" s="25"/>
+      <c r="B97" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C97" s="21">
+      <c r="C97" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="23"/>
-      <c r="B98" s="20" t="str">
+      <c r="A98" s="25"/>
+      <c r="B98" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C98" s="21">
+      <c r="C98" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="23"/>
-      <c r="B99" s="20" t="str">
+      <c r="A99" s="25"/>
+      <c r="B99" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C99" s="21">
+      <c r="C99" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="23"/>
-      <c r="B100" s="20" t="str">
+      <c r="A100" s="25"/>
+      <c r="B100" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C100" s="21">
+      <c r="C100" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="23"/>
-      <c r="B101" s="20" t="str">
+      <c r="A101" s="25"/>
+      <c r="B101" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C101" s="21">
+      <c r="C101" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="23"/>
-      <c r="B102" s="20" t="str">
+      <c r="A102" s="25"/>
+      <c r="B102" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C102" s="21">
+      <c r="C102" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="23"/>
-      <c r="B103" s="20" t="str">
+      <c r="A103" s="25"/>
+      <c r="B103" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C103" s="21">
+      <c r="C103" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="23"/>
-      <c r="B104" s="20" t="str">
+      <c r="A104" s="25"/>
+      <c r="B104" s="21" t="str">
         <f t="shared" ref="B104:B114" si="1">IF(C104&gt;0,C104,"")</f>
         <v/>
       </c>
-      <c r="C104" s="21">
+      <c r="C104" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="23"/>
-      <c r="B105" s="20" t="str">
+      <c r="A105" s="25"/>
+      <c r="B105" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C105" s="21">
+      <c r="C105" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="23"/>
-      <c r="B106" s="20" t="str">
+      <c r="A106" s="25"/>
+      <c r="B106" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C106" s="21">
+      <c r="C106" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="23"/>
-      <c r="B107" s="20" t="str">
+      <c r="A107" s="25"/>
+      <c r="B107" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C107" s="21">
+      <c r="C107" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="23"/>
-      <c r="B108" s="20" t="str">
+      <c r="A108" s="25"/>
+      <c r="B108" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C108" s="21">
+      <c r="C108" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="23"/>
-      <c r="B109" s="20" t="str">
+      <c r="A109" s="25"/>
+      <c r="B109" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C109" s="21">
+      <c r="C109" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="23"/>
-      <c r="B110" s="20" t="str">
+      <c r="A110" s="25"/>
+      <c r="B110" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C110" s="21">
+      <c r="C110" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="23"/>
-      <c r="B111" s="20" t="str">
+      <c r="A111" s="25"/>
+      <c r="B111" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C111" s="21">
+      <c r="C111" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="23"/>
-      <c r="B112" s="20" t="str">
+      <c r="A112" s="25"/>
+      <c r="B112" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C112" s="21">
+      <c r="C112" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="23"/>
-      <c r="B113" s="20" t="str">
+      <c r="A113" s="25"/>
+      <c r="B113" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C113" s="21">
+      <c r="C113" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="23"/>
-      <c r="B114" s="20" t="str">
+      <c r="A114" s="25"/>
+      <c r="B114" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C114" s="21">
+      <c r="C114" s="23">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="23"/>
-      <c r="B115" s="23"/>
-      <c r="C115" s="21"/>
+      <c r="A115" s="25"/>
+      <c r="B115" s="25"/>
+      <c r="C115" s="23"/>
     </row>
     <row r="116">
-      <c r="A116" s="23"/>
-      <c r="B116" s="23"/>
-      <c r="C116" s="21"/>
+      <c r="A116" s="25"/>
+      <c r="B116" s="25"/>
+      <c r="C116" s="23"/>
     </row>
     <row r="117">
-      <c r="A117" s="23"/>
-      <c r="B117" s="23"/>
-      <c r="C117" s="21"/>
+      <c r="A117" s="25"/>
+      <c r="B117" s="25"/>
+      <c r="C117" s="23"/>
     </row>
     <row r="118">
-      <c r="A118" s="23"/>
-      <c r="B118" s="23"/>
-      <c r="C118" s="21"/>
+      <c r="A118" s="25"/>
+      <c r="B118" s="25"/>
+      <c r="C118" s="23"/>
     </row>
     <row r="119">
-      <c r="A119" s="23"/>
-      <c r="B119" s="23"/>
-      <c r="C119" s="21"/>
+      <c r="A119" s="25"/>
+      <c r="B119" s="25"/>
+      <c r="C119" s="23"/>
     </row>
     <row r="120">
-      <c r="A120" s="23"/>
-      <c r="B120" s="23"/>
-      <c r="C120" s="21"/>
+      <c r="A120" s="25"/>
+      <c r="B120" s="25"/>
+      <c r="C120" s="23"/>
     </row>
     <row r="121">
-      <c r="A121" s="23"/>
-      <c r="B121" s="23"/>
-      <c r="C121" s="21"/>
+      <c r="A121" s="25"/>
+      <c r="B121" s="25"/>
+      <c r="C121" s="23"/>
     </row>
     <row r="122">
-      <c r="A122" s="23"/>
-      <c r="B122" s="23"/>
-      <c r="C122" s="21"/>
+      <c r="A122" s="25"/>
+      <c r="B122" s="25"/>
+      <c r="C122" s="23"/>
     </row>
     <row r="123">
-      <c r="A123" s="23"/>
-      <c r="B123" s="23"/>
-      <c r="C123" s="21"/>
+      <c r="A123" s="25"/>
+      <c r="B123" s="25"/>
+      <c r="C123" s="23"/>
     </row>
     <row r="124">
-      <c r="A124" s="23"/>
-      <c r="B124" s="23"/>
-      <c r="C124" s="21"/>
+      <c r="A124" s="25"/>
+      <c r="B124" s="25"/>
+      <c r="C124" s="23"/>
     </row>
     <row r="125">
-      <c r="A125" s="23"/>
-      <c r="B125" s="23"/>
-      <c r="C125" s="21"/>
+      <c r="A125" s="25"/>
+      <c r="B125" s="25"/>
+      <c r="C125" s="23"/>
     </row>
     <row r="126">
-      <c r="A126" s="23"/>
-      <c r="B126" s="23"/>
-      <c r="C126" s="21"/>
+      <c r="A126" s="25"/>
+      <c r="B126" s="25"/>
+      <c r="C126" s="23"/>
     </row>
     <row r="127">
-      <c r="A127" s="23"/>
-      <c r="B127" s="23"/>
-      <c r="C127" s="21"/>
+      <c r="A127" s="25"/>
+      <c r="B127" s="25"/>
+      <c r="C127" s="23"/>
     </row>
     <row r="128">
-      <c r="A128" s="23"/>
-      <c r="B128" s="23"/>
-      <c r="C128" s="21"/>
+      <c r="A128" s="25"/>
+      <c r="B128" s="25"/>
+      <c r="C128" s="23"/>
     </row>
     <row r="129">
-      <c r="A129" s="23"/>
-      <c r="B129" s="23"/>
-      <c r="C129" s="21"/>
+      <c r="A129" s="25"/>
+      <c r="B129" s="25"/>
+      <c r="C129" s="23"/>
     </row>
     <row r="130">
-      <c r="A130" s="23"/>
-      <c r="B130" s="23"/>
-      <c r="C130" s="21"/>
+      <c r="A130" s="25"/>
+      <c r="B130" s="25"/>
+      <c r="C130" s="23"/>
     </row>
     <row r="131">
-      <c r="A131" s="23"/>
-      <c r="B131" s="23"/>
-      <c r="C131" s="21"/>
+      <c r="A131" s="25"/>
+      <c r="B131" s="25"/>
+      <c r="C131" s="23"/>
     </row>
     <row r="132">
-      <c r="A132" s="23"/>
-      <c r="B132" s="23"/>
-      <c r="C132" s="21"/>
+      <c r="A132" s="25"/>
+      <c r="B132" s="25"/>
+      <c r="C132" s="23"/>
     </row>
     <row r="133">
-      <c r="A133" s="23"/>
-      <c r="B133" s="23"/>
-      <c r="C133" s="21"/>
+      <c r="A133" s="25"/>
+      <c r="B133" s="25"/>
+      <c r="C133" s="23"/>
     </row>
     <row r="134">
-      <c r="A134" s="23"/>
-      <c r="B134" s="23"/>
-      <c r="C134" s="21"/>
+      <c r="A134" s="25"/>
+      <c r="B134" s="25"/>
+      <c r="C134" s="23"/>
     </row>
     <row r="135">
-      <c r="A135" s="23"/>
-      <c r="B135" s="23"/>
-      <c r="C135" s="21"/>
+      <c r="A135" s="25"/>
+      <c r="B135" s="25"/>
+      <c r="C135" s="23"/>
     </row>
     <row r="136">
-      <c r="A136" s="23"/>
-      <c r="B136" s="23"/>
-      <c r="C136" s="21"/>
+      <c r="A136" s="25"/>
+      <c r="B136" s="25"/>
+      <c r="C136" s="23"/>
     </row>
     <row r="137">
-      <c r="A137" s="23"/>
-      <c r="B137" s="23"/>
-      <c r="C137" s="21"/>
+      <c r="A137" s="25"/>
+      <c r="B137" s="25"/>
+      <c r="C137" s="23"/>
     </row>
     <row r="138">
-      <c r="A138" s="23"/>
-      <c r="B138" s="23"/>
-      <c r="C138" s="21"/>
+      <c r="A138" s="25"/>
+      <c r="B138" s="25"/>
+      <c r="C138" s="23"/>
     </row>
     <row r="139">
-      <c r="A139" s="23"/>
-      <c r="B139" s="23"/>
-      <c r="C139" s="21"/>
+      <c r="A139" s="25"/>
+      <c r="B139" s="25"/>
+      <c r="C139" s="23"/>
     </row>
     <row r="140">
-      <c r="A140" s="23"/>
-      <c r="B140" s="23"/>
-      <c r="C140" s="21"/>
+      <c r="A140" s="25"/>
+      <c r="B140" s="25"/>
+      <c r="C140" s="23"/>
     </row>
     <row r="141">
-      <c r="A141" s="23"/>
-      <c r="B141" s="23"/>
-      <c r="C141" s="21"/>
+      <c r="A141" s="25"/>
+      <c r="B141" s="25"/>
+      <c r="C141" s="23"/>
     </row>
     <row r="142">
-      <c r="A142" s="23"/>
-      <c r="B142" s="23"/>
-      <c r="C142" s="21"/>
+      <c r="A142" s="25"/>
+      <c r="B142" s="25"/>
+      <c r="C142" s="23"/>
     </row>
     <row r="143">
-      <c r="A143" s="23"/>
-      <c r="B143" s="23"/>
-      <c r="C143" s="21"/>
+      <c r="A143" s="25"/>
+      <c r="B143" s="25"/>
+      <c r="C143" s="23"/>
     </row>
     <row r="144">
-      <c r="A144" s="23"/>
-      <c r="B144" s="23"/>
-      <c r="C144" s="21"/>
+      <c r="A144" s="25"/>
+      <c r="B144" s="25"/>
+      <c r="C144" s="23"/>
     </row>
     <row r="145">
-      <c r="A145" s="23"/>
-      <c r="B145" s="23"/>
-      <c r="C145" s="21"/>
+      <c r="A145" s="25"/>
+      <c r="B145" s="25"/>
+      <c r="C145" s="23"/>
     </row>
     <row r="146">
-      <c r="A146" s="23"/>
-      <c r="B146" s="23"/>
-      <c r="C146" s="21"/>
+      <c r="A146" s="25"/>
+      <c r="B146" s="25"/>
+      <c r="C146" s="23"/>
     </row>
     <row r="147">
-      <c r="A147" s="23"/>
-      <c r="B147" s="23"/>
-      <c r="C147" s="21"/>
+      <c r="A147" s="25"/>
+      <c r="B147" s="25"/>
+      <c r="C147" s="23"/>
     </row>
     <row r="148">
-      <c r="A148" s="23"/>
-      <c r="B148" s="23"/>
-      <c r="C148" s="21"/>
+      <c r="A148" s="25"/>
+      <c r="B148" s="25"/>
+      <c r="C148" s="23"/>
     </row>
     <row r="149">
-      <c r="A149" s="23"/>
-      <c r="B149" s="23"/>
-      <c r="C149" s="21"/>
+      <c r="A149" s="25"/>
+      <c r="B149" s="25"/>
+      <c r="C149" s="23"/>
     </row>
     <row r="150">
-      <c r="A150" s="23"/>
-      <c r="B150" s="23"/>
-      <c r="C150" s="21"/>
+      <c r="A150" s="25"/>
+      <c r="B150" s="25"/>
+      <c r="C150" s="23"/>
     </row>
     <row r="151">
-      <c r="A151" s="23"/>
-      <c r="B151" s="23"/>
-      <c r="C151" s="21"/>
+      <c r="A151" s="25"/>
+      <c r="B151" s="25"/>
+      <c r="C151" s="23"/>
     </row>
     <row r="152">
-      <c r="A152" s="23"/>
-      <c r="B152" s="23"/>
-      <c r="C152" s="21"/>
+      <c r="A152" s="25"/>
+      <c r="B152" s="25"/>
+      <c r="C152" s="23"/>
     </row>
     <row r="153">
-      <c r="A153" s="23"/>
-      <c r="B153" s="23"/>
-      <c r="C153" s="21"/>
+      <c r="A153" s="25"/>
+      <c r="B153" s="25"/>
+      <c r="C153" s="23"/>
     </row>
     <row r="154">
-      <c r="A154" s="23"/>
-      <c r="B154" s="23"/>
-      <c r="C154" s="21"/>
+      <c r="A154" s="25"/>
+      <c r="B154" s="25"/>
+      <c r="C154" s="23"/>
     </row>
     <row r="155">
-      <c r="A155" s="23"/>
-      <c r="B155" s="23"/>
-      <c r="C155" s="21"/>
+      <c r="A155" s="25"/>
+      <c r="B155" s="25"/>
+      <c r="C155" s="23"/>
     </row>
     <row r="156">
-      <c r="A156" s="23"/>
-      <c r="B156" s="23"/>
-      <c r="C156" s="21"/>
+      <c r="A156" s="25"/>
+      <c r="B156" s="25"/>
+      <c r="C156" s="23"/>
     </row>
     <row r="157">
-      <c r="A157" s="23"/>
-      <c r="B157" s="23"/>
-      <c r="C157" s="21"/>
+      <c r="A157" s="25"/>
+      <c r="B157" s="25"/>
+      <c r="C157" s="23"/>
     </row>
     <row r="158">
-      <c r="A158" s="23"/>
-      <c r="B158" s="23"/>
-      <c r="C158" s="21"/>
+      <c r="A158" s="25"/>
+      <c r="B158" s="25"/>
+      <c r="C158" s="23"/>
     </row>
     <row r="159">
-      <c r="A159" s="23"/>
-      <c r="B159" s="23"/>
+      <c r="A159" s="25"/>
+      <c r="B159" s="25"/>
     </row>
     <row r="160">
-      <c r="A160" s="23"/>
-      <c r="B160" s="23"/>
+      <c r="A160" s="25"/>
+      <c r="B160" s="25"/>
     </row>
     <row r="161">
-      <c r="A161" s="23"/>
-      <c r="B161" s="23"/>
+      <c r="A161" s="25"/>
+      <c r="B161" s="25"/>
     </row>
     <row r="162">
-      <c r="A162" s="23"/>
-      <c r="B162" s="23"/>
+      <c r="A162" s="25"/>
+      <c r="B162" s="25"/>
     </row>
     <row r="163">
-      <c r="A163" s="23"/>
-      <c r="B163" s="23"/>
+      <c r="A163" s="25"/>
+      <c r="B163" s="25"/>
     </row>
     <row r="164">
-      <c r="A164" s="23"/>
-      <c r="B164" s="23"/>
+      <c r="A164" s="25"/>
+      <c r="B164" s="25"/>
     </row>
     <row r="165">
-      <c r="A165" s="23"/>
-      <c r="B165" s="23"/>
+      <c r="A165" s="25"/>
+      <c r="B165" s="25"/>
     </row>
     <row r="166">
-      <c r="A166" s="23"/>
-      <c r="B166" s="23"/>
+      <c r="A166" s="25"/>
+      <c r="B166" s="25"/>
     </row>
     <row r="167">
-      <c r="A167" s="23"/>
-      <c r="B167" s="23"/>
+      <c r="A167" s="25"/>
+      <c r="B167" s="25"/>
     </row>
     <row r="168">
-      <c r="A168" s="23"/>
-      <c r="B168" s="23"/>
+      <c r="A168" s="25"/>
+      <c r="B168" s="25"/>
     </row>
     <row r="169">
-      <c r="A169" s="23"/>
-      <c r="B169" s="23"/>
+      <c r="A169" s="25"/>
+      <c r="B169" s="25"/>
     </row>
     <row r="170">
-      <c r="A170" s="23"/>
-      <c r="B170" s="23"/>
+      <c r="A170" s="25"/>
+      <c r="B170" s="25"/>
     </row>
     <row r="171">
-      <c r="A171" s="23"/>
-      <c r="B171" s="23"/>
+      <c r="A171" s="25"/>
+      <c r="B171" s="25"/>
     </row>
     <row r="172">
-      <c r="A172" s="23"/>
-      <c r="B172" s="23"/>
+      <c r="A172" s="25"/>
+      <c r="B172" s="25"/>
     </row>
     <row r="173">
-      <c r="A173" s="23"/>
-      <c r="B173" s="23"/>
+      <c r="A173" s="25"/>
+      <c r="B173" s="25"/>
     </row>
     <row r="174">
-      <c r="A174" s="23"/>
-      <c r="B174" s="23"/>
+      <c r="A174" s="25"/>
+      <c r="B174" s="25"/>
     </row>
     <row r="175">
-      <c r="A175" s="23"/>
-      <c r="B175" s="23"/>
+      <c r="A175" s="25"/>
+      <c r="B175" s="25"/>
     </row>
     <row r="176">
-      <c r="A176" s="23"/>
-      <c r="B176" s="23"/>
+      <c r="A176" s="25"/>
+      <c r="B176" s="25"/>
     </row>
     <row r="177">
-      <c r="A177" s="23"/>
-      <c r="B177" s="23"/>
+      <c r="A177" s="25"/>
+      <c r="B177" s="25"/>
     </row>
     <row r="178">
-      <c r="A178" s="23"/>
-      <c r="B178" s="23"/>
+      <c r="A178" s="25"/>
+      <c r="B178" s="25"/>
     </row>
     <row r="179">
-      <c r="A179" s="23"/>
-      <c r="B179" s="23"/>
+      <c r="A179" s="25"/>
+      <c r="B179" s="25"/>
     </row>
     <row r="180">
-      <c r="A180" s="23"/>
-      <c r="B180" s="23"/>
+      <c r="A180" s="25"/>
+      <c r="B180" s="25"/>
     </row>
     <row r="181">
-      <c r="A181" s="23"/>
-      <c r="B181" s="23"/>
+      <c r="A181" s="25"/>
+      <c r="B181" s="25"/>
     </row>
     <row r="182">
-      <c r="A182" s="23"/>
-      <c r="B182" s="23"/>
+      <c r="A182" s="25"/>
+      <c r="B182" s="25"/>
     </row>
     <row r="183">
-      <c r="A183" s="23"/>
-      <c r="B183" s="23"/>
+      <c r="A183" s="25"/>
+      <c r="B183" s="25"/>
     </row>
     <row r="184">
-      <c r="A184" s="23"/>
-      <c r="B184" s="23"/>
+      <c r="A184" s="25"/>
+      <c r="B184" s="25"/>
     </row>
     <row r="185">
-      <c r="A185" s="23"/>
-      <c r="B185" s="23"/>
+      <c r="A185" s="25"/>
+      <c r="B185" s="25"/>
     </row>
     <row r="186">
-      <c r="A186" s="23"/>
-      <c r="B186" s="23"/>
+      <c r="A186" s="25"/>
+      <c r="B186" s="25"/>
     </row>
     <row r="187">
-      <c r="A187" s="23"/>
-      <c r="B187" s="23"/>
+      <c r="A187" s="25"/>
+      <c r="B187" s="25"/>
     </row>
     <row r="188">
-      <c r="A188" s="23"/>
-      <c r="B188" s="23"/>
+      <c r="A188" s="25"/>
+      <c r="B188" s="25"/>
     </row>
     <row r="189">
-      <c r="A189" s="23"/>
-      <c r="B189" s="23"/>
+      <c r="A189" s="25"/>
+      <c r="B189" s="25"/>
     </row>
     <row r="190">
-      <c r="A190" s="23"/>
-      <c r="B190" s="23"/>
+      <c r="A190" s="25"/>
+      <c r="B190" s="25"/>
     </row>
     <row r="191">
-      <c r="A191" s="23"/>
-      <c r="B191" s="23"/>
+      <c r="A191" s="25"/>
+      <c r="B191" s="25"/>
     </row>
     <row r="192">
-      <c r="A192" s="23"/>
-      <c r="B192" s="23"/>
+      <c r="A192" s="25"/>
+      <c r="B192" s="25"/>
     </row>
     <row r="193">
-      <c r="A193" s="23"/>
-      <c r="B193" s="23"/>
+      <c r="A193" s="25"/>
+      <c r="B193" s="25"/>
     </row>
     <row r="194">
-      <c r="A194" s="23"/>
-      <c r="B194" s="23"/>
+      <c r="A194" s="25"/>
+      <c r="B194" s="25"/>
     </row>
     <row r="195">
-      <c r="A195" s="23"/>
-      <c r="B195" s="23"/>
+      <c r="A195" s="25"/>
+      <c r="B195" s="25"/>
     </row>
     <row r="196">
-      <c r="A196" s="23"/>
-      <c r="B196" s="23"/>
+      <c r="A196" s="25"/>
+      <c r="B196" s="25"/>
     </row>
     <row r="197">
-      <c r="A197" s="23"/>
-      <c r="B197" s="23"/>
+      <c r="A197" s="25"/>
+      <c r="B197" s="25"/>
     </row>
     <row r="198">
-      <c r="A198" s="23"/>
-      <c r="B198" s="23"/>
+      <c r="A198" s="25"/>
+      <c r="B198" s="25"/>
     </row>
     <row r="199">
-      <c r="A199" s="23"/>
-      <c r="B199" s="23"/>
+      <c r="A199" s="25"/>
+      <c r="B199" s="25"/>
     </row>
     <row r="200">
-      <c r="A200" s="23"/>
-      <c r="B200" s="23"/>
+      <c r="A200" s="25"/>
+      <c r="B200" s="25"/>
     </row>
     <row r="201">
-      <c r="A201" s="23"/>
-      <c r="B201" s="23"/>
+      <c r="A201" s="25"/>
+      <c r="B201" s="25"/>
     </row>
     <row r="202">
-      <c r="A202" s="23"/>
-      <c r="B202" s="23"/>
+      <c r="A202" s="25"/>
+      <c r="B202" s="25"/>
     </row>
     <row r="203">
-      <c r="A203" s="23"/>
-      <c r="B203" s="23"/>
+      <c r="A203" s="25"/>
+      <c r="B203" s="25"/>
     </row>
     <row r="204">
-      <c r="A204" s="23"/>
-      <c r="B204" s="23"/>
+      <c r="A204" s="25"/>
+      <c r="B204" s="25"/>
     </row>
     <row r="205">
-      <c r="A205" s="23"/>
-      <c r="B205" s="23"/>
+      <c r="A205" s="25"/>
+      <c r="B205" s="25"/>
     </row>
     <row r="206">
-      <c r="A206" s="23"/>
-      <c r="B206" s="23"/>
+      <c r="A206" s="25"/>
+      <c r="B206" s="25"/>
     </row>
     <row r="207">
-      <c r="A207" s="23"/>
-      <c r="B207" s="23"/>
+      <c r="A207" s="25"/>
+      <c r="B207" s="25"/>
     </row>
     <row r="208">
-      <c r="A208" s="23"/>
-      <c r="B208" s="23"/>
+      <c r="A208" s="25"/>
+      <c r="B208" s="25"/>
     </row>
     <row r="209">
-      <c r="A209" s="23"/>
-      <c r="B209" s="23"/>
+      <c r="A209" s="25"/>
+      <c r="B209" s="25"/>
     </row>
     <row r="210">
-      <c r="A210" s="23"/>
-      <c r="B210" s="23"/>
+      <c r="A210" s="25"/>
+      <c r="B210" s="25"/>
     </row>
     <row r="211">
-      <c r="A211" s="23"/>
-      <c r="B211" s="23"/>
+      <c r="A211" s="25"/>
+      <c r="B211" s="25"/>
     </row>
     <row r="212">
-      <c r="A212" s="23"/>
-      <c r="B212" s="23"/>
+      <c r="A212" s="25"/>
+      <c r="B212" s="25"/>
     </row>
     <row r="213">
-      <c r="A213" s="23"/>
-      <c r="B213" s="23"/>
+      <c r="A213" s="25"/>
+      <c r="B213" s="25"/>
     </row>
     <row r="214">
-      <c r="A214" s="23"/>
-      <c r="B214" s="23"/>
+      <c r="A214" s="25"/>
+      <c r="B214" s="25"/>
     </row>
     <row r="215">
-      <c r="A215" s="23"/>
-      <c r="B215" s="23"/>
+      <c r="A215" s="25"/>
+      <c r="B215" s="25"/>
     </row>
     <row r="216">
-      <c r="A216" s="23"/>
-      <c r="B216" s="23"/>
+      <c r="A216" s="25"/>
+      <c r="B216" s="25"/>
     </row>
     <row r="217">
-      <c r="A217" s="23"/>
-      <c r="B217" s="23"/>
+      <c r="A217" s="25"/>
+      <c r="B217" s="25"/>
     </row>
     <row r="218">
-      <c r="A218" s="23"/>
-      <c r="B218" s="23"/>
+      <c r="A218" s="25"/>
+      <c r="B218" s="25"/>
     </row>
     <row r="219">
-      <c r="A219" s="23"/>
-      <c r="B219" s="23"/>
+      <c r="A219" s="25"/>
+      <c r="B219" s="25"/>
     </row>
     <row r="220">
-      <c r="A220" s="23"/>
-      <c r="B220" s="23"/>
+      <c r="A220" s="25"/>
+      <c r="B220" s="25"/>
     </row>
     <row r="221">
-      <c r="A221" s="23"/>
-      <c r="B221" s="23"/>
+      <c r="A221" s="25"/>
+      <c r="B221" s="25"/>
     </row>
     <row r="222">
-      <c r="A222" s="23"/>
-      <c r="B222" s="23"/>
+      <c r="A222" s="25"/>
+      <c r="B222" s="25"/>
     </row>
     <row r="223">
-      <c r="A223" s="23"/>
-      <c r="B223" s="23"/>
+      <c r="A223" s="25"/>
+      <c r="B223" s="25"/>
     </row>
     <row r="224">
-      <c r="A224" s="23"/>
-      <c r="B224" s="23"/>
+      <c r="A224" s="25"/>
+      <c r="B224" s="25"/>
     </row>
     <row r="225">
-      <c r="A225" s="23"/>
-      <c r="B225" s="23"/>
+      <c r="A225" s="25"/>
+      <c r="B225" s="25"/>
     </row>
     <row r="226">
-      <c r="A226" s="23"/>
-      <c r="B226" s="23"/>
+      <c r="A226" s="25"/>
+      <c r="B226" s="25"/>
     </row>
     <row r="227">
-      <c r="A227" s="23"/>
-      <c r="B227" s="23"/>
+      <c r="A227" s="25"/>
+      <c r="B227" s="25"/>
     </row>
     <row r="228">
-      <c r="A228" s="23"/>
-      <c r="B228" s="23"/>
+      <c r="A228" s="25"/>
+      <c r="B228" s="25"/>
     </row>
     <row r="229">
-      <c r="A229" s="23"/>
-      <c r="B229" s="23"/>
+      <c r="A229" s="25"/>
+      <c r="B229" s="25"/>
     </row>
     <row r="230">
-      <c r="A230" s="23"/>
-      <c r="B230" s="23"/>
+      <c r="A230" s="25"/>
+      <c r="B230" s="25"/>
     </row>
     <row r="231">
-      <c r="A231" s="23"/>
-      <c r="B231" s="23"/>
+      <c r="A231" s="25"/>
+      <c r="B231" s="25"/>
     </row>
     <row r="232">
-      <c r="A232" s="23"/>
-      <c r="B232" s="23"/>
+      <c r="A232" s="25"/>
+      <c r="B232" s="25"/>
     </row>
     <row r="233">
-      <c r="A233" s="23"/>
-      <c r="B233" s="23"/>
+      <c r="A233" s="25"/>
+      <c r="B233" s="25"/>
     </row>
     <row r="234">
-      <c r="A234" s="23"/>
-      <c r="B234" s="23"/>
+      <c r="A234" s="25"/>
+      <c r="B234" s="25"/>
     </row>
     <row r="235">
-      <c r="A235" s="23"/>
-      <c r="B235" s="23"/>
+      <c r="A235" s="25"/>
+      <c r="B235" s="25"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -7365,2034 +7464,2034 @@
     <col customWidth="1" min="2" max="2" width="4.33203125"/>
     <col bestFit="1" min="3" max="3" width="35.77734375"/>
     <col customWidth="1" min="4" max="11" width="3.44140625"/>
-    <col customWidth="1" min="12" max="12" style="24" width="6"/>
+    <col customWidth="1" min="12" max="12" style="26" width="6"/>
     <col customWidth="1" min="13" max="22" width="3.44140625"/>
-    <col customWidth="1" min="23" max="23" style="24" width="6"/>
+    <col customWidth="1" min="23" max="23" style="26" width="6"/>
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
-    <col customWidth="1" min="30" max="30" style="24" width="6"/>
+    <col customWidth="1" min="30" max="30" style="26" width="6"/>
     <col customWidth="1" min="31" max="39" width="3.44140625"/>
     <col bestFit="1" customWidth="1" min="40" max="40" width="13.88671875"/>
     <col customWidth="1" min="41" max="47" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="25" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="B1" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="D1" s="28" t="s">
+    <row r="1" s="27" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="B1" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="29" t="s">
+      <c r="E1" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="G1" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="28" t="s">
+      <c r="H1" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="J1" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="L1" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>62</v>
-      </c>
-      <c r="N1" s="30" t="s">
+      <c r="K1" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="L1" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="N1" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="P1" s="28" t="s">
+      <c r="O1" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="P1" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="R1" s="28" t="s">
+      <c r="Q1" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="S1" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="T1" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="U1" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="V1" s="30" t="s">
+      <c r="R1" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="W1" s="33" t="s">
+      <c r="S1" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="X1" s="28" t="s">
+      <c r="T1" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="Y1" s="28" t="s">
+      <c r="U1" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="Z1" s="30" t="s">
+      <c r="V1" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="AA1" s="34" t="s">
+      <c r="W1" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="AB1" s="35" t="s">
+      <c r="X1" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="AC1" s="35" t="s">
+      <c r="Y1" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="AD1" s="32" t="s">
+      <c r="Z1" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="AE1" s="36" t="s">
+      <c r="AA1" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="AF1" s="37" t="s">
+      <c r="AB1" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="AG1" s="38" t="s">
+      <c r="AC1" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="AH1" s="38" t="s">
+      <c r="AD1" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="AI1" s="38" t="s">
+      <c r="AE1" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="AJ1" s="38" t="s">
+      <c r="AF1" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="AK1" s="35" t="s">
+      <c r="AG1" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="AL1" s="39"/>
-      <c r="AM1" s="39"/>
-      <c r="AN1" s="39"/>
-      <c r="AO1" s="39"/>
-      <c r="AP1" s="39"/>
-      <c r="AQ1" s="39"/>
-      <c r="AR1" s="39"/>
-      <c r="AS1" s="39"/>
-      <c r="AT1" s="39"/>
-      <c r="AU1" s="39"/>
+      <c r="AH1" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI1" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="AJ1" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK1" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="AL1" s="41"/>
+      <c r="AM1" s="41"/>
+      <c r="AN1" s="41"/>
+      <c r="AO1" s="41"/>
+      <c r="AP1" s="41"/>
+      <c r="AQ1" s="41"/>
+      <c r="AR1" s="41"/>
+      <c r="AS1" s="41"/>
+      <c r="AT1" s="41"/>
+      <c r="AU1" s="41"/>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="C2" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
-      <c r="T2" s="42"/>
-      <c r="U2" s="42"/>
-      <c r="V2" s="47"/>
-      <c r="W2" s="49"/>
-      <c r="X2" s="42"/>
-      <c r="Y2" s="42"/>
-      <c r="Z2" s="47"/>
-      <c r="AA2" s="48"/>
-      <c r="AB2" s="42"/>
-      <c r="AC2" s="42"/>
-      <c r="AD2" s="46"/>
-      <c r="AE2" s="47"/>
-      <c r="AF2" s="48"/>
-      <c r="AG2" s="42"/>
-      <c r="AH2" s="42"/>
-      <c r="AI2" s="42"/>
-      <c r="AJ2" s="42"/>
-      <c r="AK2" s="42"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="50"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="44"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="44"/>
+      <c r="V2" s="49"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="44"/>
+      <c r="Y2" s="44"/>
+      <c r="Z2" s="49"/>
+      <c r="AA2" s="50"/>
+      <c r="AB2" s="44"/>
+      <c r="AC2" s="44"/>
+      <c r="AD2" s="48"/>
+      <c r="AE2" s="49"/>
+      <c r="AF2" s="50"/>
+      <c r="AG2" s="44"/>
+      <c r="AH2" s="44"/>
+      <c r="AI2" s="44"/>
+      <c r="AJ2" s="44"/>
+      <c r="AK2" s="44"/>
     </row>
     <row r="3" ht="12" customHeight="1">
-      <c r="B3" s="40"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="42"/>
-      <c r="R3" s="42"/>
-      <c r="S3" s="42"/>
-      <c r="T3" s="42"/>
-      <c r="U3" s="42"/>
-      <c r="V3" s="47"/>
-      <c r="W3" s="49"/>
-      <c r="X3" s="42"/>
-      <c r="Y3" s="42"/>
-      <c r="Z3" s="47"/>
-      <c r="AA3" s="48"/>
-      <c r="AB3" s="42"/>
-      <c r="AC3" s="42"/>
-      <c r="AD3" s="46"/>
-      <c r="AE3" s="47"/>
-      <c r="AF3" s="48"/>
-      <c r="AG3" s="42"/>
-      <c r="AH3" s="42"/>
-      <c r="AI3" s="42"/>
-      <c r="AJ3" s="42"/>
-      <c r="AK3" s="42"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="44"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="50"/>
+      <c r="P3" s="44"/>
+      <c r="Q3" s="44"/>
+      <c r="R3" s="44"/>
+      <c r="S3" s="44"/>
+      <c r="T3" s="44"/>
+      <c r="U3" s="44"/>
+      <c r="V3" s="49"/>
+      <c r="W3" s="51"/>
+      <c r="X3" s="44"/>
+      <c r="Y3" s="44"/>
+      <c r="Z3" s="49"/>
+      <c r="AA3" s="50"/>
+      <c r="AB3" s="44"/>
+      <c r="AC3" s="44"/>
+      <c r="AD3" s="48"/>
+      <c r="AE3" s="49"/>
+      <c r="AF3" s="50"/>
+      <c r="AG3" s="44"/>
+      <c r="AH3" s="44"/>
+      <c r="AI3" s="44"/>
+      <c r="AJ3" s="44"/>
+      <c r="AK3" s="44"/>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="40"/>
-      <c r="C4" s="41" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="42"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="46"/>
-      <c r="M4" s="42"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="42"/>
-      <c r="Q4" s="42"/>
-      <c r="R4" s="42"/>
-      <c r="S4" s="42"/>
-      <c r="T4" s="42"/>
-      <c r="U4" s="42"/>
-      <c r="V4" s="47"/>
-      <c r="W4" s="49"/>
-      <c r="X4" s="42"/>
-      <c r="Y4" s="42"/>
-      <c r="Z4" s="47"/>
-      <c r="AA4" s="48"/>
-      <c r="AB4" s="42"/>
-      <c r="AC4" s="42"/>
-      <c r="AD4" s="46"/>
-      <c r="AE4" s="47"/>
-      <c r="AF4" s="48"/>
-      <c r="AG4" s="42"/>
-      <c r="AH4" s="42"/>
-      <c r="AI4" s="42"/>
-      <c r="AJ4" s="42"/>
-      <c r="AK4" s="42"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="43" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="49"/>
+      <c r="O4" s="50"/>
+      <c r="P4" s="44"/>
+      <c r="Q4" s="44"/>
+      <c r="R4" s="44"/>
+      <c r="S4" s="44"/>
+      <c r="T4" s="44"/>
+      <c r="U4" s="44"/>
+      <c r="V4" s="49"/>
+      <c r="W4" s="51"/>
+      <c r="X4" s="44"/>
+      <c r="Y4" s="44"/>
+      <c r="Z4" s="49"/>
+      <c r="AA4" s="50"/>
+      <c r="AB4" s="44"/>
+      <c r="AC4" s="44"/>
+      <c r="AD4" s="48"/>
+      <c r="AE4" s="49"/>
+      <c r="AF4" s="50"/>
+      <c r="AG4" s="44"/>
+      <c r="AH4" s="44"/>
+      <c r="AI4" s="44"/>
+      <c r="AJ4" s="44"/>
+      <c r="AK4" s="44"/>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="42"/>
-      <c r="N5" s="47"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="42"/>
-      <c r="Q5" s="42"/>
-      <c r="R5" s="42"/>
-      <c r="S5" s="42"/>
-      <c r="T5" s="42"/>
-      <c r="U5" s="42"/>
-      <c r="V5" s="47"/>
-      <c r="W5" s="49"/>
-      <c r="X5" s="42"/>
-      <c r="Y5" s="42"/>
-      <c r="Z5" s="47"/>
-      <c r="AA5" s="48"/>
-      <c r="AB5" s="42"/>
-      <c r="AC5" s="42"/>
-      <c r="AD5" s="46"/>
-      <c r="AE5" s="47"/>
-      <c r="AF5" s="48"/>
-      <c r="AG5" s="42"/>
-      <c r="AH5" s="42"/>
-      <c r="AI5" s="42"/>
-      <c r="AJ5" s="42"/>
-      <c r="AK5" s="42"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="44"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="50"/>
+      <c r="P5" s="44"/>
+      <c r="Q5" s="44"/>
+      <c r="R5" s="44"/>
+      <c r="S5" s="44"/>
+      <c r="T5" s="44"/>
+      <c r="U5" s="44"/>
+      <c r="V5" s="49"/>
+      <c r="W5" s="51"/>
+      <c r="X5" s="44"/>
+      <c r="Y5" s="44"/>
+      <c r="Z5" s="49"/>
+      <c r="AA5" s="50"/>
+      <c r="AB5" s="44"/>
+      <c r="AC5" s="44"/>
+      <c r="AD5" s="48"/>
+      <c r="AE5" s="49"/>
+      <c r="AF5" s="50"/>
+      <c r="AG5" s="44"/>
+      <c r="AH5" s="44"/>
+      <c r="AI5" s="44"/>
+      <c r="AJ5" s="44"/>
+      <c r="AK5" s="44"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="40"/>
-      <c r="C6" s="41" t="s">
+      <c r="B6" s="42"/>
+      <c r="C6" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="46"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="47"/>
-      <c r="O6" s="48"/>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="42"/>
-      <c r="R6" s="42"/>
-      <c r="S6" s="42"/>
-      <c r="T6" s="42"/>
-      <c r="U6" s="42"/>
-      <c r="V6" s="47"/>
-      <c r="W6" s="49"/>
-      <c r="X6" s="42"/>
-      <c r="Y6" s="42"/>
-      <c r="Z6" s="47"/>
-      <c r="AA6" s="48"/>
-      <c r="AB6" s="42"/>
-      <c r="AC6" s="42"/>
-      <c r="AD6" s="46"/>
-      <c r="AE6" s="44"/>
-      <c r="AF6" s="45"/>
-      <c r="AG6" s="56"/>
-      <c r="AH6" s="56"/>
-      <c r="AI6" s="56"/>
-      <c r="AJ6" s="56"/>
-      <c r="AK6" s="56"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="50"/>
+      <c r="P6" s="44"/>
+      <c r="Q6" s="44"/>
+      <c r="R6" s="44"/>
+      <c r="S6" s="44"/>
+      <c r="T6" s="44"/>
+      <c r="U6" s="44"/>
+      <c r="V6" s="49"/>
+      <c r="W6" s="51"/>
+      <c r="X6" s="44"/>
+      <c r="Y6" s="44"/>
+      <c r="Z6" s="49"/>
+      <c r="AA6" s="50"/>
+      <c r="AB6" s="44"/>
+      <c r="AC6" s="44"/>
+      <c r="AD6" s="48"/>
+      <c r="AE6" s="46"/>
+      <c r="AF6" s="47"/>
+      <c r="AG6" s="58"/>
+      <c r="AH6" s="58"/>
+      <c r="AI6" s="58"/>
+      <c r="AJ6" s="58"/>
+      <c r="AK6" s="58"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="40"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="42"/>
-      <c r="N7" s="47"/>
-      <c r="O7" s="54"/>
-      <c r="P7" s="42"/>
-      <c r="Q7" s="42"/>
-      <c r="R7" s="42"/>
-      <c r="S7" s="42"/>
-      <c r="T7" s="42"/>
-      <c r="U7" s="42"/>
-      <c r="V7" s="47"/>
-      <c r="W7" s="49"/>
-      <c r="X7" s="42"/>
-      <c r="Y7" s="42"/>
-      <c r="Z7" s="47"/>
-      <c r="AA7" s="48"/>
-      <c r="AB7" s="42"/>
-      <c r="AC7" s="42"/>
-      <c r="AD7" s="46"/>
-      <c r="AE7" s="47"/>
-      <c r="AF7" s="48"/>
-      <c r="AG7" s="42"/>
-      <c r="AH7" s="42"/>
-      <c r="AI7" s="42"/>
-      <c r="AJ7" s="42"/>
-      <c r="AK7" s="42"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="44"/>
+      <c r="N7" s="49"/>
+      <c r="O7" s="56"/>
+      <c r="P7" s="44"/>
+      <c r="Q7" s="57"/>
+      <c r="R7" s="44"/>
+      <c r="S7" s="44"/>
+      <c r="T7" s="44"/>
+      <c r="U7" s="44"/>
+      <c r="V7" s="49"/>
+      <c r="W7" s="51"/>
+      <c r="X7" s="44"/>
+      <c r="Y7" s="44"/>
+      <c r="Z7" s="49"/>
+      <c r="AA7" s="50"/>
+      <c r="AB7" s="44"/>
+      <c r="AC7" s="44"/>
+      <c r="AD7" s="48"/>
+      <c r="AE7" s="49"/>
+      <c r="AF7" s="50"/>
+      <c r="AG7" s="44"/>
+      <c r="AH7" s="44"/>
+      <c r="AI7" s="44"/>
+      <c r="AJ7" s="44"/>
+      <c r="AK7" s="44"/>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="40"/>
-      <c r="C8" s="41" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="46"/>
-      <c r="M8" s="56"/>
-      <c r="N8" s="44"/>
-      <c r="O8" s="45"/>
-      <c r="P8" s="56"/>
-      <c r="Q8" s="56"/>
-      <c r="R8" s="56"/>
-      <c r="S8" s="56"/>
-      <c r="T8" s="56"/>
-      <c r="U8" s="56"/>
-      <c r="V8" s="44"/>
-      <c r="W8" s="49"/>
-      <c r="X8" s="56"/>
-      <c r="Y8" s="56"/>
-      <c r="Z8" s="44"/>
-      <c r="AA8" s="45"/>
-      <c r="AB8" s="56"/>
-      <c r="AC8" s="56"/>
-      <c r="AD8" s="46"/>
-      <c r="AE8" s="44"/>
-      <c r="AF8" s="45"/>
-      <c r="AG8" s="56"/>
-      <c r="AH8" s="56"/>
-      <c r="AI8" s="56"/>
-      <c r="AJ8" s="56"/>
-      <c r="AK8" s="56"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="47"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="58"/>
+      <c r="K8" s="58"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="58"/>
+      <c r="N8" s="46"/>
+      <c r="O8" s="47"/>
+      <c r="P8" s="58"/>
+      <c r="Q8" s="58"/>
+      <c r="R8" s="58"/>
+      <c r="S8" s="58"/>
+      <c r="T8" s="58"/>
+      <c r="U8" s="58"/>
+      <c r="V8" s="46"/>
+      <c r="W8" s="51"/>
+      <c r="X8" s="58"/>
+      <c r="Y8" s="58"/>
+      <c r="Z8" s="46"/>
+      <c r="AA8" s="47"/>
+      <c r="AB8" s="58"/>
+      <c r="AC8" s="58"/>
+      <c r="AD8" s="48"/>
+      <c r="AE8" s="46"/>
+      <c r="AF8" s="47"/>
+      <c r="AG8" s="58"/>
+      <c r="AH8" s="58"/>
+      <c r="AI8" s="58"/>
+      <c r="AJ8" s="58"/>
+      <c r="AK8" s="58"/>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="40"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="55"/>
-      <c r="J9" s="55"/>
-      <c r="K9" s="42"/>
-      <c r="L9" s="46"/>
-      <c r="M9" s="55"/>
-      <c r="N9" s="47"/>
-      <c r="O9" s="54"/>
-      <c r="P9" s="42"/>
-      <c r="Q9" s="42"/>
-      <c r="R9" s="42"/>
-      <c r="S9" s="42"/>
-      <c r="T9" s="42"/>
-      <c r="U9" s="42"/>
-      <c r="V9" s="47"/>
-      <c r="W9" s="49"/>
-      <c r="X9" s="42"/>
-      <c r="Y9" s="42"/>
-      <c r="Z9" s="47"/>
-      <c r="AA9" s="48"/>
-      <c r="AB9" s="42"/>
-      <c r="AC9" s="42"/>
-      <c r="AD9" s="46"/>
-      <c r="AE9" s="47"/>
-      <c r="AF9" s="48"/>
-      <c r="AG9" s="42"/>
-      <c r="AH9" s="42"/>
-      <c r="AI9" s="42"/>
-      <c r="AJ9" s="42"/>
-      <c r="AK9" s="42"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="50"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="57"/>
+      <c r="K9" s="44"/>
+      <c r="L9" s="48"/>
+      <c r="M9" s="57"/>
+      <c r="N9" s="49"/>
+      <c r="O9" s="56"/>
+      <c r="P9" s="44"/>
+      <c r="Q9" s="57"/>
+      <c r="R9" s="44"/>
+      <c r="S9" s="44"/>
+      <c r="T9" s="44"/>
+      <c r="U9" s="44"/>
+      <c r="V9" s="49"/>
+      <c r="W9" s="51"/>
+      <c r="X9" s="44"/>
+      <c r="Y9" s="44"/>
+      <c r="Z9" s="49"/>
+      <c r="AA9" s="50"/>
+      <c r="AB9" s="44"/>
+      <c r="AC9" s="44"/>
+      <c r="AD9" s="48"/>
+      <c r="AE9" s="49"/>
+      <c r="AF9" s="50"/>
+      <c r="AG9" s="44"/>
+      <c r="AH9" s="44"/>
+      <c r="AI9" s="44"/>
+      <c r="AJ9" s="44"/>
+      <c r="AK9" s="44"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="40"/>
-      <c r="C10" s="41" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="47"/>
-      <c r="O10" s="48"/>
-      <c r="P10" s="42"/>
-      <c r="Q10" s="42"/>
-      <c r="R10" s="42"/>
-      <c r="S10" s="42"/>
-      <c r="T10" s="42"/>
-      <c r="U10" s="42"/>
-      <c r="V10" s="44"/>
-      <c r="W10" s="49"/>
-      <c r="X10" s="56"/>
-      <c r="Y10" s="56"/>
-      <c r="Z10" s="44"/>
-      <c r="AA10" s="48"/>
-      <c r="AB10" s="42"/>
-      <c r="AC10" s="42"/>
-      <c r="AD10" s="46"/>
-      <c r="AE10" s="47"/>
-      <c r="AF10" s="48"/>
-      <c r="AG10" s="42"/>
-      <c r="AH10" s="42"/>
-      <c r="AI10" s="42"/>
-      <c r="AJ10" s="42"/>
-      <c r="AK10" s="42"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="50"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="48"/>
+      <c r="M10" s="44"/>
+      <c r="N10" s="49"/>
+      <c r="O10" s="50"/>
+      <c r="P10" s="44"/>
+      <c r="Q10" s="44"/>
+      <c r="R10" s="44"/>
+      <c r="S10" s="44"/>
+      <c r="T10" s="44"/>
+      <c r="U10" s="44"/>
+      <c r="V10" s="46"/>
+      <c r="W10" s="51"/>
+      <c r="X10" s="58"/>
+      <c r="Y10" s="58"/>
+      <c r="Z10" s="46"/>
+      <c r="AA10" s="50"/>
+      <c r="AB10" s="44"/>
+      <c r="AC10" s="44"/>
+      <c r="AD10" s="48"/>
+      <c r="AE10" s="49"/>
+      <c r="AF10" s="50"/>
+      <c r="AG10" s="44"/>
+      <c r="AH10" s="44"/>
+      <c r="AI10" s="44"/>
+      <c r="AJ10" s="44"/>
+      <c r="AK10" s="44"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="40"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="42"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="46"/>
-      <c r="M11" s="42"/>
-      <c r="N11" s="47"/>
-      <c r="O11" s="48"/>
-      <c r="P11" s="42"/>
-      <c r="Q11" s="42"/>
-      <c r="R11" s="42"/>
-      <c r="S11" s="42"/>
-      <c r="T11" s="42"/>
-      <c r="U11" s="42"/>
-      <c r="V11" s="47"/>
-      <c r="W11" s="49"/>
-      <c r="X11" s="42"/>
-      <c r="Y11" s="42"/>
-      <c r="Z11" s="47"/>
-      <c r="AA11" s="48"/>
-      <c r="AB11" s="42"/>
-      <c r="AC11" s="42"/>
-      <c r="AD11" s="46"/>
-      <c r="AE11" s="47"/>
-      <c r="AF11" s="48"/>
-      <c r="AG11" s="42"/>
-      <c r="AH11" s="42"/>
-      <c r="AI11" s="42"/>
-      <c r="AJ11" s="42"/>
-      <c r="AK11" s="42"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="49"/>
+      <c r="O11" s="50"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="44"/>
+      <c r="T11" s="44"/>
+      <c r="U11" s="44"/>
+      <c r="V11" s="49"/>
+      <c r="W11" s="51"/>
+      <c r="X11" s="44"/>
+      <c r="Y11" s="44"/>
+      <c r="Z11" s="49"/>
+      <c r="AA11" s="50"/>
+      <c r="AB11" s="44"/>
+      <c r="AC11" s="44"/>
+      <c r="AD11" s="48"/>
+      <c r="AE11" s="49"/>
+      <c r="AF11" s="50"/>
+      <c r="AG11" s="44"/>
+      <c r="AH11" s="44"/>
+      <c r="AI11" s="44"/>
+      <c r="AJ11" s="44"/>
+      <c r="AK11" s="44"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="40"/>
-      <c r="C12" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
-      <c r="K12" s="42"/>
-      <c r="L12" s="46"/>
-      <c r="M12" s="42"/>
-      <c r="N12" s="47"/>
-      <c r="O12" s="48"/>
-      <c r="P12" s="42"/>
-      <c r="Q12" s="42"/>
-      <c r="R12" s="42"/>
-      <c r="S12" s="42"/>
-      <c r="T12" s="42"/>
-      <c r="U12" s="42"/>
-      <c r="V12" s="47"/>
-      <c r="W12" s="49"/>
-      <c r="X12" s="42"/>
-      <c r="Y12" s="42"/>
-      <c r="Z12" s="47"/>
-      <c r="AA12" s="48"/>
-      <c r="AB12" s="42"/>
-      <c r="AC12" s="42"/>
-      <c r="AD12" s="46"/>
-      <c r="AE12" s="47"/>
-      <c r="AF12" s="45"/>
-      <c r="AG12" s="56"/>
-      <c r="AH12" s="56"/>
-      <c r="AI12" s="56"/>
-      <c r="AJ12" s="56"/>
-      <c r="AK12" s="56"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="48"/>
+      <c r="M12" s="44"/>
+      <c r="N12" s="49"/>
+      <c r="O12" s="50"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="44"/>
+      <c r="R12" s="44"/>
+      <c r="S12" s="44"/>
+      <c r="T12" s="44"/>
+      <c r="U12" s="44"/>
+      <c r="V12" s="49"/>
+      <c r="W12" s="51"/>
+      <c r="X12" s="44"/>
+      <c r="Y12" s="44"/>
+      <c r="Z12" s="49"/>
+      <c r="AA12" s="50"/>
+      <c r="AB12" s="44"/>
+      <c r="AC12" s="44"/>
+      <c r="AD12" s="48"/>
+      <c r="AE12" s="49"/>
+      <c r="AF12" s="47"/>
+      <c r="AG12" s="58"/>
+      <c r="AH12" s="58"/>
+      <c r="AI12" s="58"/>
+      <c r="AJ12" s="58"/>
+      <c r="AK12" s="58"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="40"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="42"/>
-      <c r="K13" s="42"/>
-      <c r="L13" s="46"/>
-      <c r="M13" s="42"/>
-      <c r="N13" s="47"/>
-      <c r="O13" s="48"/>
-      <c r="P13" s="42"/>
-      <c r="Q13" s="42"/>
-      <c r="R13" s="42"/>
-      <c r="S13" s="42"/>
-      <c r="T13" s="42"/>
-      <c r="U13" s="42"/>
-      <c r="V13" s="47"/>
-      <c r="W13" s="49"/>
-      <c r="X13" s="42"/>
-      <c r="Y13" s="42"/>
-      <c r="Z13" s="47"/>
-      <c r="AA13" s="48"/>
-      <c r="AB13" s="42"/>
-      <c r="AC13" s="42"/>
-      <c r="AD13" s="46"/>
-      <c r="AE13" s="47"/>
-      <c r="AF13" s="48"/>
-      <c r="AG13" s="42"/>
-      <c r="AH13" s="42"/>
-      <c r="AI13" s="42"/>
-      <c r="AJ13" s="42"/>
-      <c r="AK13" s="42"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44"/>
+      <c r="L13" s="48"/>
+      <c r="M13" s="44"/>
+      <c r="N13" s="49"/>
+      <c r="O13" s="50"/>
+      <c r="P13" s="44"/>
+      <c r="Q13" s="44"/>
+      <c r="R13" s="44"/>
+      <c r="S13" s="44"/>
+      <c r="T13" s="44"/>
+      <c r="U13" s="44"/>
+      <c r="V13" s="49"/>
+      <c r="W13" s="51"/>
+      <c r="X13" s="44"/>
+      <c r="Y13" s="44"/>
+      <c r="Z13" s="49"/>
+      <c r="AA13" s="50"/>
+      <c r="AB13" s="44"/>
+      <c r="AC13" s="44"/>
+      <c r="AD13" s="48"/>
+      <c r="AE13" s="49"/>
+      <c r="AF13" s="50"/>
+      <c r="AG13" s="44"/>
+      <c r="AH13" s="44"/>
+      <c r="AI13" s="44"/>
+      <c r="AJ13" s="44"/>
+      <c r="AK13" s="44"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="57" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" s="58" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="60"/>
-      <c r="K14" s="60"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="60"/>
-      <c r="N14" s="61"/>
-      <c r="O14" s="59"/>
-      <c r="P14" s="60"/>
-      <c r="Q14" s="60"/>
-      <c r="R14" s="60"/>
-      <c r="S14" s="60"/>
-      <c r="T14" s="60"/>
-      <c r="U14" s="60"/>
-      <c r="V14" s="61"/>
-      <c r="W14" s="49"/>
-      <c r="X14" s="60"/>
-      <c r="Y14" s="60"/>
-      <c r="Z14" s="61"/>
-      <c r="AA14" s="59"/>
-      <c r="AB14" s="60"/>
-      <c r="AC14" s="60"/>
-      <c r="AD14" s="46"/>
-      <c r="AE14" s="61"/>
-      <c r="AF14" s="59"/>
-      <c r="AG14" s="60"/>
-      <c r="AH14" s="60"/>
-      <c r="AI14" s="60"/>
-      <c r="AJ14" s="60"/>
-      <c r="AK14" s="60"/>
+      <c r="B14" s="59" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="48"/>
+      <c r="M14" s="62"/>
+      <c r="N14" s="63"/>
+      <c r="O14" s="61"/>
+      <c r="P14" s="62"/>
+      <c r="Q14" s="62"/>
+      <c r="R14" s="62"/>
+      <c r="S14" s="62"/>
+      <c r="T14" s="62"/>
+      <c r="U14" s="62"/>
+      <c r="V14" s="63"/>
+      <c r="W14" s="51"/>
+      <c r="X14" s="62"/>
+      <c r="Y14" s="62"/>
+      <c r="Z14" s="63"/>
+      <c r="AA14" s="61"/>
+      <c r="AB14" s="62"/>
+      <c r="AC14" s="62"/>
+      <c r="AD14" s="48"/>
+      <c r="AE14" s="63"/>
+      <c r="AF14" s="61"/>
+      <c r="AG14" s="62"/>
+      <c r="AH14" s="62"/>
+      <c r="AI14" s="62"/>
+      <c r="AJ14" s="62"/>
+      <c r="AK14" s="62"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="57"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="59"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="60"/>
-      <c r="K15" s="60"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="60"/>
-      <c r="N15" s="61"/>
-      <c r="O15" s="59"/>
-      <c r="P15" s="60"/>
-      <c r="Q15" s="60"/>
-      <c r="R15" s="60"/>
-      <c r="S15" s="60"/>
-      <c r="T15" s="60"/>
-      <c r="U15" s="60"/>
-      <c r="V15" s="61"/>
-      <c r="W15" s="49"/>
-      <c r="X15" s="60"/>
-      <c r="Y15" s="60"/>
-      <c r="Z15" s="61"/>
-      <c r="AA15" s="59"/>
-      <c r="AB15" s="60"/>
-      <c r="AC15" s="60"/>
-      <c r="AD15" s="46"/>
-      <c r="AE15" s="61"/>
-      <c r="AF15" s="59"/>
-      <c r="AG15" s="60"/>
-      <c r="AH15" s="60"/>
-      <c r="AI15" s="60"/>
-      <c r="AJ15" s="60"/>
-      <c r="AK15" s="60"/>
+      <c r="B15" s="59"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="62"/>
+      <c r="K15" s="62"/>
+      <c r="L15" s="48"/>
+      <c r="M15" s="62"/>
+      <c r="N15" s="63"/>
+      <c r="O15" s="61"/>
+      <c r="P15" s="62"/>
+      <c r="Q15" s="62"/>
+      <c r="R15" s="62"/>
+      <c r="S15" s="62"/>
+      <c r="T15" s="62"/>
+      <c r="U15" s="62"/>
+      <c r="V15" s="63"/>
+      <c r="W15" s="51"/>
+      <c r="X15" s="62"/>
+      <c r="Y15" s="62"/>
+      <c r="Z15" s="63"/>
+      <c r="AA15" s="61"/>
+      <c r="AB15" s="62"/>
+      <c r="AC15" s="62"/>
+      <c r="AD15" s="48"/>
+      <c r="AE15" s="63"/>
+      <c r="AF15" s="61"/>
+      <c r="AG15" s="62"/>
+      <c r="AH15" s="62"/>
+      <c r="AI15" s="62"/>
+      <c r="AJ15" s="62"/>
+      <c r="AK15" s="62"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="57"/>
-      <c r="C16" s="58" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="59"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="60"/>
-      <c r="K16" s="60"/>
-      <c r="L16" s="46"/>
-      <c r="M16" s="60"/>
-      <c r="N16" s="61"/>
-      <c r="O16" s="59"/>
-      <c r="P16" s="60"/>
-      <c r="Q16" s="60"/>
-      <c r="R16" s="60"/>
-      <c r="S16" s="60"/>
-      <c r="T16" s="60"/>
-      <c r="U16" s="60"/>
-      <c r="V16" s="61"/>
-      <c r="W16" s="49"/>
-      <c r="X16" s="60"/>
-      <c r="Y16" s="60"/>
-      <c r="Z16" s="61"/>
-      <c r="AA16" s="59"/>
-      <c r="AB16" s="60"/>
-      <c r="AC16" s="60"/>
-      <c r="AD16" s="46"/>
-      <c r="AE16" s="61"/>
-      <c r="AF16" s="59"/>
-      <c r="AG16" s="60"/>
-      <c r="AH16" s="60"/>
-      <c r="AI16" s="60"/>
-      <c r="AJ16" s="60"/>
-      <c r="AK16" s="60"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="60" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="58"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="63"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="62"/>
+      <c r="K16" s="62"/>
+      <c r="L16" s="48"/>
+      <c r="M16" s="62"/>
+      <c r="N16" s="63"/>
+      <c r="O16" s="61"/>
+      <c r="P16" s="62"/>
+      <c r="Q16" s="62"/>
+      <c r="R16" s="62"/>
+      <c r="S16" s="62"/>
+      <c r="T16" s="62"/>
+      <c r="U16" s="62"/>
+      <c r="V16" s="63"/>
+      <c r="W16" s="51"/>
+      <c r="X16" s="62"/>
+      <c r="Y16" s="62"/>
+      <c r="Z16" s="63"/>
+      <c r="AA16" s="61"/>
+      <c r="AB16" s="62"/>
+      <c r="AC16" s="62"/>
+      <c r="AD16" s="48"/>
+      <c r="AE16" s="63"/>
+      <c r="AF16" s="61"/>
+      <c r="AG16" s="62"/>
+      <c r="AH16" s="62"/>
+      <c r="AI16" s="62"/>
+      <c r="AJ16" s="62"/>
+      <c r="AK16" s="62"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="57"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="63"/>
-      <c r="G17" s="61"/>
-      <c r="H17" s="59"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="60"/>
-      <c r="K17" s="60"/>
-      <c r="L17" s="46"/>
-      <c r="M17" s="60"/>
-      <c r="N17" s="61"/>
-      <c r="O17" s="59"/>
-      <c r="P17" s="60"/>
-      <c r="Q17" s="60"/>
-      <c r="R17" s="60"/>
-      <c r="S17" s="60"/>
-      <c r="T17" s="60"/>
-      <c r="U17" s="60"/>
-      <c r="V17" s="61"/>
-      <c r="W17" s="49"/>
-      <c r="X17" s="60"/>
-      <c r="Y17" s="60"/>
-      <c r="Z17" s="61"/>
-      <c r="AA17" s="59"/>
-      <c r="AB17" s="60"/>
-      <c r="AC17" s="60"/>
-      <c r="AD17" s="46"/>
-      <c r="AE17" s="61"/>
-      <c r="AF17" s="59"/>
-      <c r="AG17" s="60"/>
-      <c r="AH17" s="60"/>
-      <c r="AI17" s="60"/>
-      <c r="AJ17" s="60"/>
-      <c r="AK17" s="60"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="62"/>
+      <c r="K17" s="62"/>
+      <c r="L17" s="48"/>
+      <c r="M17" s="62"/>
+      <c r="N17" s="63"/>
+      <c r="O17" s="61"/>
+      <c r="P17" s="62"/>
+      <c r="Q17" s="62"/>
+      <c r="R17" s="62"/>
+      <c r="S17" s="62"/>
+      <c r="T17" s="62"/>
+      <c r="U17" s="62"/>
+      <c r="V17" s="63"/>
+      <c r="W17" s="51"/>
+      <c r="X17" s="62"/>
+      <c r="Y17" s="62"/>
+      <c r="Z17" s="63"/>
+      <c r="AA17" s="61"/>
+      <c r="AB17" s="62"/>
+      <c r="AC17" s="62"/>
+      <c r="AD17" s="48"/>
+      <c r="AE17" s="63"/>
+      <c r="AF17" s="61"/>
+      <c r="AG17" s="62"/>
+      <c r="AH17" s="62"/>
+      <c r="AI17" s="62"/>
+      <c r="AJ17" s="62"/>
+      <c r="AK17" s="62"/>
       <c r="AN17" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="57"/>
-      <c r="C18" s="58" t="s">
-        <v>92</v>
-      </c>
-      <c r="D18" s="56"/>
-      <c r="E18" s="56"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="59"/>
-      <c r="I18" s="60"/>
-      <c r="J18" s="60"/>
-      <c r="K18" s="60"/>
-      <c r="L18" s="46"/>
-      <c r="M18" s="60"/>
-      <c r="N18" s="61"/>
-      <c r="O18" s="59"/>
-      <c r="P18" s="60"/>
-      <c r="Q18" s="60"/>
-      <c r="R18" s="60"/>
-      <c r="S18" s="60"/>
-      <c r="T18" s="60"/>
-      <c r="U18" s="60"/>
-      <c r="V18" s="61"/>
-      <c r="W18" s="49"/>
-      <c r="X18" s="60"/>
-      <c r="Y18" s="60"/>
-      <c r="Z18" s="61"/>
-      <c r="AA18" s="59"/>
-      <c r="AB18" s="60"/>
-      <c r="AC18" s="60"/>
-      <c r="AD18" s="46"/>
-      <c r="AE18" s="61"/>
-      <c r="AF18" s="59"/>
-      <c r="AG18" s="60"/>
-      <c r="AH18" s="60"/>
-      <c r="AI18" s="60"/>
-      <c r="AJ18" s="60"/>
-      <c r="AK18" s="60"/>
+      <c r="B18" s="59"/>
+      <c r="C18" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="63"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="62"/>
+      <c r="K18" s="62"/>
+      <c r="L18" s="48"/>
+      <c r="M18" s="62"/>
+      <c r="N18" s="63"/>
+      <c r="O18" s="61"/>
+      <c r="P18" s="62"/>
+      <c r="Q18" s="62"/>
+      <c r="R18" s="62"/>
+      <c r="S18" s="62"/>
+      <c r="T18" s="62"/>
+      <c r="U18" s="62"/>
+      <c r="V18" s="63"/>
+      <c r="W18" s="51"/>
+      <c r="X18" s="62"/>
+      <c r="Y18" s="62"/>
+      <c r="Z18" s="63"/>
+      <c r="AA18" s="61"/>
+      <c r="AB18" s="62"/>
+      <c r="AC18" s="62"/>
+      <c r="AD18" s="48"/>
+      <c r="AE18" s="63"/>
+      <c r="AF18" s="61"/>
+      <c r="AG18" s="62"/>
+      <c r="AH18" s="62"/>
+      <c r="AI18" s="62"/>
+      <c r="AJ18" s="62"/>
+      <c r="AK18" s="62"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="57"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="64"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="60"/>
-      <c r="K19" s="60"/>
-      <c r="L19" s="46"/>
-      <c r="M19" s="60"/>
-      <c r="N19" s="61"/>
-      <c r="O19" s="59"/>
-      <c r="P19" s="60"/>
-      <c r="Q19" s="60"/>
-      <c r="R19" s="60"/>
-      <c r="S19" s="60"/>
-      <c r="T19" s="60"/>
-      <c r="U19" s="60"/>
-      <c r="V19" s="61"/>
-      <c r="W19" s="49"/>
-      <c r="X19" s="60"/>
-      <c r="Y19" s="60"/>
-      <c r="Z19" s="61"/>
-      <c r="AA19" s="59"/>
-      <c r="AB19" s="60"/>
-      <c r="AC19" s="60"/>
-      <c r="AD19" s="46"/>
-      <c r="AE19" s="61"/>
-      <c r="AF19" s="59"/>
-      <c r="AG19" s="60"/>
-      <c r="AH19" s="60"/>
-      <c r="AI19" s="60"/>
-      <c r="AJ19" s="60"/>
-      <c r="AK19" s="60"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="62"/>
+      <c r="K19" s="62"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="62"/>
+      <c r="N19" s="63"/>
+      <c r="O19" s="61"/>
+      <c r="P19" s="62"/>
+      <c r="Q19" s="62"/>
+      <c r="R19" s="62"/>
+      <c r="S19" s="62"/>
+      <c r="T19" s="62"/>
+      <c r="U19" s="62"/>
+      <c r="V19" s="63"/>
+      <c r="W19" s="51"/>
+      <c r="X19" s="62"/>
+      <c r="Y19" s="62"/>
+      <c r="Z19" s="63"/>
+      <c r="AA19" s="61"/>
+      <c r="AB19" s="62"/>
+      <c r="AC19" s="62"/>
+      <c r="AD19" s="48"/>
+      <c r="AE19" s="63"/>
+      <c r="AF19" s="61"/>
+      <c r="AG19" s="62"/>
+      <c r="AH19" s="62"/>
+      <c r="AI19" s="62"/>
+      <c r="AJ19" s="62"/>
+      <c r="AK19" s="62"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="57"/>
-      <c r="C20" s="58" t="s">
-        <v>93</v>
-      </c>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="56"/>
-      <c r="J20" s="60"/>
-      <c r="K20" s="60"/>
-      <c r="L20" s="46"/>
-      <c r="M20" s="60"/>
-      <c r="N20" s="61"/>
-      <c r="O20" s="59"/>
-      <c r="P20" s="60"/>
-      <c r="Q20" s="60"/>
-      <c r="R20" s="60"/>
-      <c r="S20" s="60"/>
-      <c r="T20" s="60"/>
-      <c r="U20" s="60"/>
-      <c r="V20" s="61"/>
-      <c r="W20" s="49"/>
-      <c r="X20" s="60"/>
-      <c r="Y20" s="60"/>
-      <c r="Z20" s="61"/>
-      <c r="AA20" s="59"/>
-      <c r="AB20" s="60"/>
-      <c r="AC20" s="60"/>
-      <c r="AD20" s="46"/>
-      <c r="AE20" s="61"/>
-      <c r="AF20" s="59"/>
-      <c r="AG20" s="60"/>
-      <c r="AH20" s="60"/>
-      <c r="AI20" s="60"/>
-      <c r="AJ20" s="60"/>
-      <c r="AK20" s="60"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="60" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" s="62"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="62"/>
+      <c r="K20" s="62"/>
+      <c r="L20" s="48"/>
+      <c r="M20" s="62"/>
+      <c r="N20" s="63"/>
+      <c r="O20" s="61"/>
+      <c r="P20" s="62"/>
+      <c r="Q20" s="62"/>
+      <c r="R20" s="62"/>
+      <c r="S20" s="62"/>
+      <c r="T20" s="62"/>
+      <c r="U20" s="62"/>
+      <c r="V20" s="63"/>
+      <c r="W20" s="51"/>
+      <c r="X20" s="62"/>
+      <c r="Y20" s="62"/>
+      <c r="Z20" s="63"/>
+      <c r="AA20" s="61"/>
+      <c r="AB20" s="62"/>
+      <c r="AC20" s="62"/>
+      <c r="AD20" s="48"/>
+      <c r="AE20" s="63"/>
+      <c r="AF20" s="61"/>
+      <c r="AG20" s="62"/>
+      <c r="AH20" s="62"/>
+      <c r="AI20" s="62"/>
+      <c r="AJ20" s="62"/>
+      <c r="AK20" s="62"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="57"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="63"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="55"/>
-      <c r="J21" s="60"/>
-      <c r="K21" s="60"/>
-      <c r="L21" s="46"/>
-      <c r="M21" s="60"/>
-      <c r="N21" s="61"/>
-      <c r="O21" s="59"/>
-      <c r="P21" s="60"/>
-      <c r="Q21" s="60"/>
-      <c r="R21" s="60"/>
-      <c r="S21" s="60"/>
-      <c r="T21" s="60"/>
-      <c r="U21" s="60"/>
-      <c r="V21" s="61"/>
-      <c r="W21" s="49"/>
-      <c r="X21" s="60"/>
-      <c r="Y21" s="60"/>
-      <c r="Z21" s="61"/>
-      <c r="AA21" s="59"/>
-      <c r="AB21" s="60"/>
-      <c r="AC21" s="60"/>
-      <c r="AD21" s="46"/>
-      <c r="AE21" s="61"/>
-      <c r="AF21" s="59"/>
-      <c r="AG21" s="60"/>
-      <c r="AH21" s="60"/>
-      <c r="AI21" s="60"/>
-      <c r="AJ21" s="60"/>
-      <c r="AK21" s="60"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="62"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="48"/>
+      <c r="M21" s="62"/>
+      <c r="N21" s="63"/>
+      <c r="O21" s="61"/>
+      <c r="P21" s="62"/>
+      <c r="Q21" s="62"/>
+      <c r="R21" s="62"/>
+      <c r="S21" s="62"/>
+      <c r="T21" s="62"/>
+      <c r="U21" s="62"/>
+      <c r="V21" s="63"/>
+      <c r="W21" s="51"/>
+      <c r="X21" s="62"/>
+      <c r="Y21" s="62"/>
+      <c r="Z21" s="63"/>
+      <c r="AA21" s="61"/>
+      <c r="AB21" s="62"/>
+      <c r="AC21" s="62"/>
+      <c r="AD21" s="48"/>
+      <c r="AE21" s="63"/>
+      <c r="AF21" s="61"/>
+      <c r="AG21" s="62"/>
+      <c r="AH21" s="62"/>
+      <c r="AI21" s="62"/>
+      <c r="AJ21" s="62"/>
+      <c r="AK21" s="62"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="57"/>
-      <c r="C22" s="58" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="63"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="56"/>
-      <c r="J22" s="60"/>
-      <c r="K22" s="60"/>
-      <c r="L22" s="46"/>
-      <c r="M22" s="60"/>
-      <c r="N22" s="61"/>
-      <c r="O22" s="59"/>
-      <c r="P22" s="60"/>
-      <c r="Q22" s="60"/>
-      <c r="R22" s="60"/>
-      <c r="S22" s="60"/>
-      <c r="T22" s="60"/>
-      <c r="U22" s="60"/>
-      <c r="V22" s="61"/>
-      <c r="W22" s="49"/>
-      <c r="X22" s="60"/>
-      <c r="Y22" s="60"/>
-      <c r="Z22" s="61"/>
-      <c r="AA22" s="59"/>
-      <c r="AB22" s="60"/>
-      <c r="AC22" s="60"/>
-      <c r="AD22" s="46"/>
-      <c r="AE22" s="61"/>
-      <c r="AF22" s="59"/>
-      <c r="AG22" s="60"/>
-      <c r="AH22" s="60"/>
-      <c r="AI22" s="60"/>
-      <c r="AJ22" s="60"/>
-      <c r="AK22" s="60"/>
+      <c r="B22" s="59"/>
+      <c r="C22" s="60" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="48"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="63"/>
+      <c r="O22" s="61"/>
+      <c r="P22" s="62"/>
+      <c r="Q22" s="62"/>
+      <c r="R22" s="62"/>
+      <c r="S22" s="62"/>
+      <c r="T22" s="62"/>
+      <c r="U22" s="62"/>
+      <c r="V22" s="63"/>
+      <c r="W22" s="51"/>
+      <c r="X22" s="62"/>
+      <c r="Y22" s="62"/>
+      <c r="Z22" s="63"/>
+      <c r="AA22" s="61"/>
+      <c r="AB22" s="62"/>
+      <c r="AC22" s="62"/>
+      <c r="AD22" s="48"/>
+      <c r="AE22" s="63"/>
+      <c r="AF22" s="61"/>
+      <c r="AG22" s="62"/>
+      <c r="AH22" s="62"/>
+      <c r="AI22" s="62"/>
+      <c r="AJ22" s="62"/>
+      <c r="AK22" s="62"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="57"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="61"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="55"/>
-      <c r="J23" s="51"/>
-      <c r="K23" s="60"/>
-      <c r="L23" s="46"/>
-      <c r="M23" s="60"/>
-      <c r="N23" s="61"/>
-      <c r="O23" s="59"/>
-      <c r="P23" s="60"/>
-      <c r="Q23" s="60"/>
-      <c r="R23" s="60"/>
-      <c r="S23" s="60"/>
-      <c r="T23" s="60"/>
-      <c r="U23" s="60"/>
-      <c r="V23" s="61"/>
-      <c r="W23" s="49"/>
-      <c r="X23" s="60"/>
-      <c r="Y23" s="60"/>
-      <c r="Z23" s="61"/>
-      <c r="AA23" s="59"/>
-      <c r="AB23" s="60"/>
-      <c r="AC23" s="60"/>
-      <c r="AD23" s="46"/>
-      <c r="AE23" s="61"/>
-      <c r="AF23" s="59"/>
-      <c r="AG23" s="60"/>
-      <c r="AH23" s="60"/>
-      <c r="AI23" s="60"/>
-      <c r="AJ23" s="60"/>
-      <c r="AK23" s="60"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="63"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="62"/>
+      <c r="L23" s="48"/>
+      <c r="M23" s="62"/>
+      <c r="N23" s="63"/>
+      <c r="O23" s="61"/>
+      <c r="P23" s="62"/>
+      <c r="Q23" s="62"/>
+      <c r="R23" s="62"/>
+      <c r="S23" s="62"/>
+      <c r="T23" s="62"/>
+      <c r="U23" s="62"/>
+      <c r="V23" s="63"/>
+      <c r="W23" s="51"/>
+      <c r="X23" s="62"/>
+      <c r="Y23" s="62"/>
+      <c r="Z23" s="63"/>
+      <c r="AA23" s="61"/>
+      <c r="AB23" s="62"/>
+      <c r="AC23" s="62"/>
+      <c r="AD23" s="48"/>
+      <c r="AE23" s="63"/>
+      <c r="AF23" s="61"/>
+      <c r="AG23" s="62"/>
+      <c r="AH23" s="62"/>
+      <c r="AI23" s="62"/>
+      <c r="AJ23" s="62"/>
+      <c r="AK23" s="62"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="57"/>
-      <c r="C24" s="58" t="s">
-        <v>95</v>
-      </c>
-      <c r="D24" s="60"/>
-      <c r="E24" s="60"/>
-      <c r="F24" s="63"/>
-      <c r="G24" s="61"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="56"/>
-      <c r="J24" s="60"/>
-      <c r="K24" s="60"/>
-      <c r="L24" s="46"/>
-      <c r="M24" s="60"/>
-      <c r="N24" s="61"/>
-      <c r="O24" s="59"/>
-      <c r="P24" s="60"/>
-      <c r="Q24" s="60"/>
-      <c r="R24" s="60"/>
-      <c r="S24" s="60"/>
-      <c r="T24" s="60"/>
-      <c r="U24" s="60"/>
-      <c r="V24" s="61"/>
-      <c r="W24" s="49"/>
-      <c r="X24" s="60"/>
-      <c r="Y24" s="60"/>
-      <c r="Z24" s="61"/>
-      <c r="AA24" s="59"/>
-      <c r="AB24" s="60"/>
-      <c r="AC24" s="60"/>
-      <c r="AD24" s="46"/>
-      <c r="AE24" s="61"/>
-      <c r="AF24" s="59"/>
-      <c r="AG24" s="60"/>
-      <c r="AH24" s="60"/>
-      <c r="AI24" s="60"/>
-      <c r="AJ24" s="60"/>
-      <c r="AK24" s="60"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="60" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="62"/>
+      <c r="E24" s="62"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="62"/>
+      <c r="K24" s="62"/>
+      <c r="L24" s="48"/>
+      <c r="M24" s="62"/>
+      <c r="N24" s="63"/>
+      <c r="O24" s="61"/>
+      <c r="P24" s="62"/>
+      <c r="Q24" s="62"/>
+      <c r="R24" s="62"/>
+      <c r="S24" s="62"/>
+      <c r="T24" s="62"/>
+      <c r="U24" s="62"/>
+      <c r="V24" s="63"/>
+      <c r="W24" s="51"/>
+      <c r="X24" s="62"/>
+      <c r="Y24" s="62"/>
+      <c r="Z24" s="63"/>
+      <c r="AA24" s="61"/>
+      <c r="AB24" s="62"/>
+      <c r="AC24" s="62"/>
+      <c r="AD24" s="48"/>
+      <c r="AE24" s="63"/>
+      <c r="AF24" s="61"/>
+      <c r="AG24" s="62"/>
+      <c r="AH24" s="62"/>
+      <c r="AI24" s="62"/>
+      <c r="AJ24" s="62"/>
+      <c r="AK24" s="62"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="57"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="60"/>
-      <c r="E25" s="60"/>
-      <c r="F25" s="63"/>
-      <c r="G25" s="61"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="60"/>
-      <c r="J25" s="51"/>
-      <c r="K25" s="60"/>
-      <c r="L25" s="46"/>
-      <c r="M25" s="60"/>
-      <c r="N25" s="61"/>
-      <c r="O25" s="59"/>
-      <c r="P25" s="60"/>
-      <c r="Q25" s="60"/>
-      <c r="R25" s="60"/>
-      <c r="S25" s="60"/>
-      <c r="T25" s="60"/>
-      <c r="U25" s="60"/>
-      <c r="V25" s="61"/>
-      <c r="W25" s="49"/>
-      <c r="X25" s="60"/>
-      <c r="Y25" s="60"/>
-      <c r="Z25" s="61"/>
-      <c r="AA25" s="59"/>
-      <c r="AB25" s="60"/>
-      <c r="AC25" s="60"/>
-      <c r="AD25" s="46"/>
-      <c r="AE25" s="61"/>
-      <c r="AF25" s="59"/>
-      <c r="AG25" s="60"/>
-      <c r="AH25" s="60"/>
-      <c r="AI25" s="60"/>
-      <c r="AJ25" s="60"/>
-      <c r="AK25" s="60"/>
+      <c r="B25" s="59"/>
+      <c r="C25" s="60"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="63"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="62"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="62"/>
+      <c r="L25" s="48"/>
+      <c r="M25" s="62"/>
+      <c r="N25" s="63"/>
+      <c r="O25" s="61"/>
+      <c r="P25" s="62"/>
+      <c r="Q25" s="62"/>
+      <c r="R25" s="62"/>
+      <c r="S25" s="62"/>
+      <c r="T25" s="62"/>
+      <c r="U25" s="62"/>
+      <c r="V25" s="63"/>
+      <c r="W25" s="51"/>
+      <c r="X25" s="62"/>
+      <c r="Y25" s="62"/>
+      <c r="Z25" s="63"/>
+      <c r="AA25" s="61"/>
+      <c r="AB25" s="62"/>
+      <c r="AC25" s="62"/>
+      <c r="AD25" s="48"/>
+      <c r="AE25" s="63"/>
+      <c r="AF25" s="61"/>
+      <c r="AG25" s="62"/>
+      <c r="AH25" s="62"/>
+      <c r="AI25" s="62"/>
+      <c r="AJ25" s="62"/>
+      <c r="AK25" s="62"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="C26" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="42"/>
-      <c r="K26" s="42"/>
-      <c r="L26" s="46"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="47"/>
-      <c r="O26" s="48"/>
-      <c r="P26" s="42"/>
-      <c r="Q26" s="42"/>
-      <c r="R26" s="42"/>
-      <c r="S26" s="42"/>
-      <c r="T26" s="42"/>
-      <c r="U26" s="42"/>
-      <c r="V26" s="47"/>
-      <c r="W26" s="49"/>
-      <c r="X26" s="42"/>
-      <c r="Y26" s="42"/>
-      <c r="Z26" s="47"/>
-      <c r="AA26" s="48"/>
-      <c r="AB26" s="42"/>
-      <c r="AC26" s="42"/>
-      <c r="AD26" s="46"/>
-      <c r="AE26" s="47"/>
-      <c r="AF26" s="48"/>
-      <c r="AG26" s="42"/>
-      <c r="AH26" s="42"/>
-      <c r="AI26" s="42"/>
-      <c r="AJ26" s="42"/>
-      <c r="AK26" s="42"/>
+      <c r="B26" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="58"/>
+      <c r="J26" s="44"/>
+      <c r="K26" s="44"/>
+      <c r="L26" s="48"/>
+      <c r="M26" s="44"/>
+      <c r="N26" s="49"/>
+      <c r="O26" s="50"/>
+      <c r="P26" s="44"/>
+      <c r="Q26" s="44"/>
+      <c r="R26" s="44"/>
+      <c r="S26" s="44"/>
+      <c r="T26" s="44"/>
+      <c r="U26" s="44"/>
+      <c r="V26" s="49"/>
+      <c r="W26" s="51"/>
+      <c r="X26" s="44"/>
+      <c r="Y26" s="44"/>
+      <c r="Z26" s="49"/>
+      <c r="AA26" s="50"/>
+      <c r="AB26" s="44"/>
+      <c r="AC26" s="44"/>
+      <c r="AD26" s="48"/>
+      <c r="AE26" s="49"/>
+      <c r="AF26" s="50"/>
+      <c r="AG26" s="44"/>
+      <c r="AH26" s="44"/>
+      <c r="AI26" s="44"/>
+      <c r="AJ26" s="44"/>
+      <c r="AK26" s="44"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="40"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="42"/>
-      <c r="K27" s="42"/>
-      <c r="L27" s="46"/>
-      <c r="M27" s="42"/>
-      <c r="N27" s="47"/>
-      <c r="O27" s="48"/>
-      <c r="P27" s="42"/>
-      <c r="Q27" s="42"/>
-      <c r="R27" s="42"/>
-      <c r="S27" s="42"/>
-      <c r="T27" s="42"/>
-      <c r="U27" s="42"/>
-      <c r="V27" s="47"/>
-      <c r="W27" s="49"/>
-      <c r="X27" s="42"/>
-      <c r="Y27" s="42"/>
-      <c r="Z27" s="47"/>
-      <c r="AA27" s="48"/>
-      <c r="AB27" s="42"/>
-      <c r="AC27" s="42"/>
-      <c r="AD27" s="46"/>
-      <c r="AE27" s="47"/>
-      <c r="AF27" s="48"/>
-      <c r="AG27" s="42"/>
-      <c r="AH27" s="42"/>
-      <c r="AI27" s="42"/>
-      <c r="AJ27" s="42"/>
-      <c r="AK27" s="42"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="55"/>
+      <c r="H27" s="56"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="44"/>
+      <c r="L27" s="48"/>
+      <c r="M27" s="44"/>
+      <c r="N27" s="49"/>
+      <c r="O27" s="50"/>
+      <c r="P27" s="44"/>
+      <c r="Q27" s="44"/>
+      <c r="R27" s="44"/>
+      <c r="S27" s="44"/>
+      <c r="T27" s="44"/>
+      <c r="U27" s="44"/>
+      <c r="V27" s="49"/>
+      <c r="W27" s="51"/>
+      <c r="X27" s="44"/>
+      <c r="Y27" s="44"/>
+      <c r="Z27" s="49"/>
+      <c r="AA27" s="50"/>
+      <c r="AB27" s="44"/>
+      <c r="AC27" s="44"/>
+      <c r="AD27" s="48"/>
+      <c r="AE27" s="49"/>
+      <c r="AF27" s="50"/>
+      <c r="AG27" s="44"/>
+      <c r="AH27" s="44"/>
+      <c r="AI27" s="44"/>
+      <c r="AJ27" s="44"/>
+      <c r="AK27" s="44"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="40"/>
-      <c r="C28" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="D28" s="42"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="56"/>
-      <c r="K28" s="56"/>
-      <c r="L28" s="46"/>
-      <c r="M28" s="42"/>
-      <c r="N28" s="47"/>
-      <c r="O28" s="48"/>
-      <c r="P28" s="42"/>
-      <c r="Q28" s="42"/>
-      <c r="R28" s="42"/>
-      <c r="S28" s="42"/>
-      <c r="T28" s="42"/>
-      <c r="U28" s="42"/>
-      <c r="V28" s="47"/>
-      <c r="W28" s="49"/>
-      <c r="X28" s="42"/>
-      <c r="Y28" s="42"/>
-      <c r="Z28" s="47"/>
-      <c r="AA28" s="48"/>
-      <c r="AB28" s="42"/>
-      <c r="AC28" s="42"/>
-      <c r="AD28" s="46"/>
-      <c r="AE28" s="47"/>
-      <c r="AF28" s="48"/>
-      <c r="AG28" s="42"/>
-      <c r="AH28" s="42"/>
-      <c r="AI28" s="42"/>
-      <c r="AJ28" s="42"/>
-      <c r="AK28" s="42"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="47"/>
+      <c r="I28" s="58"/>
+      <c r="J28" s="58"/>
+      <c r="K28" s="58"/>
+      <c r="L28" s="48"/>
+      <c r="M28" s="44"/>
+      <c r="N28" s="49"/>
+      <c r="O28" s="50"/>
+      <c r="P28" s="44"/>
+      <c r="Q28" s="44"/>
+      <c r="R28" s="44"/>
+      <c r="S28" s="44"/>
+      <c r="T28" s="44"/>
+      <c r="U28" s="44"/>
+      <c r="V28" s="49"/>
+      <c r="W28" s="51"/>
+      <c r="X28" s="44"/>
+      <c r="Y28" s="44"/>
+      <c r="Z28" s="49"/>
+      <c r="AA28" s="50"/>
+      <c r="AB28" s="44"/>
+      <c r="AC28" s="44"/>
+      <c r="AD28" s="48"/>
+      <c r="AE28" s="49"/>
+      <c r="AF28" s="50"/>
+      <c r="AG28" s="44"/>
+      <c r="AH28" s="44"/>
+      <c r="AI28" s="44"/>
+      <c r="AJ28" s="44"/>
+      <c r="AK28" s="44"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="40"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="53"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="42"/>
-      <c r="L29" s="46"/>
-      <c r="M29" s="42"/>
-      <c r="N29" s="47"/>
-      <c r="O29" s="48"/>
-      <c r="P29" s="42"/>
-      <c r="Q29" s="42"/>
-      <c r="R29" s="42"/>
-      <c r="S29" s="42"/>
-      <c r="T29" s="42"/>
-      <c r="U29" s="42"/>
-      <c r="V29" s="47"/>
-      <c r="W29" s="49"/>
-      <c r="X29" s="42"/>
-      <c r="Y29" s="42"/>
-      <c r="Z29" s="47"/>
-      <c r="AA29" s="48"/>
-      <c r="AB29" s="42"/>
-      <c r="AC29" s="42"/>
-      <c r="AD29" s="46"/>
-      <c r="AE29" s="47"/>
-      <c r="AF29" s="48"/>
-      <c r="AG29" s="42"/>
-      <c r="AH29" s="42"/>
-      <c r="AI29" s="42"/>
-      <c r="AJ29" s="42"/>
-      <c r="AK29" s="42"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="55"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="67"/>
+      <c r="K29" s="44"/>
+      <c r="L29" s="48"/>
+      <c r="M29" s="44"/>
+      <c r="N29" s="49"/>
+      <c r="O29" s="50"/>
+      <c r="P29" s="44"/>
+      <c r="Q29" s="44"/>
+      <c r="R29" s="44"/>
+      <c r="S29" s="44"/>
+      <c r="T29" s="44"/>
+      <c r="U29" s="44"/>
+      <c r="V29" s="49"/>
+      <c r="W29" s="51"/>
+      <c r="X29" s="44"/>
+      <c r="Y29" s="44"/>
+      <c r="Z29" s="49"/>
+      <c r="AA29" s="50"/>
+      <c r="AB29" s="44"/>
+      <c r="AC29" s="44"/>
+      <c r="AD29" s="48"/>
+      <c r="AE29" s="49"/>
+      <c r="AF29" s="50"/>
+      <c r="AG29" s="44"/>
+      <c r="AH29" s="44"/>
+      <c r="AI29" s="44"/>
+      <c r="AJ29" s="44"/>
+      <c r="AK29" s="44"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="40"/>
-      <c r="C30" s="41" t="s">
-        <v>99</v>
-      </c>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="47"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="56"/>
-      <c r="J30" s="56"/>
-      <c r="K30" s="56"/>
-      <c r="L30" s="46"/>
-      <c r="M30" s="56"/>
-      <c r="N30" s="47"/>
-      <c r="O30" s="48"/>
-      <c r="P30" s="42"/>
-      <c r="Q30" s="42"/>
-      <c r="R30" s="42"/>
-      <c r="S30" s="42"/>
-      <c r="T30" s="42"/>
-      <c r="U30" s="42"/>
-      <c r="V30" s="47"/>
-      <c r="W30" s="49"/>
-      <c r="X30" s="42"/>
-      <c r="Y30" s="42"/>
-      <c r="Z30" s="47"/>
-      <c r="AA30" s="48"/>
-      <c r="AB30" s="42"/>
-      <c r="AC30" s="42"/>
-      <c r="AD30" s="46"/>
-      <c r="AE30" s="47"/>
-      <c r="AF30" s="48"/>
-      <c r="AG30" s="42"/>
-      <c r="AH30" s="42"/>
-      <c r="AI30" s="42"/>
-      <c r="AJ30" s="42"/>
-      <c r="AK30" s="42"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="49"/>
+      <c r="H30" s="47"/>
+      <c r="I30" s="58"/>
+      <c r="J30" s="58"/>
+      <c r="K30" s="58"/>
+      <c r="L30" s="48"/>
+      <c r="M30" s="58"/>
+      <c r="N30" s="49"/>
+      <c r="O30" s="50"/>
+      <c r="P30" s="44"/>
+      <c r="Q30" s="44"/>
+      <c r="R30" s="44"/>
+      <c r="S30" s="44"/>
+      <c r="T30" s="44"/>
+      <c r="U30" s="44"/>
+      <c r="V30" s="49"/>
+      <c r="W30" s="51"/>
+      <c r="X30" s="44"/>
+      <c r="Y30" s="44"/>
+      <c r="Z30" s="49"/>
+      <c r="AA30" s="50"/>
+      <c r="AB30" s="44"/>
+      <c r="AC30" s="44"/>
+      <c r="AD30" s="48"/>
+      <c r="AE30" s="49"/>
+      <c r="AF30" s="50"/>
+      <c r="AG30" s="44"/>
+      <c r="AH30" s="44"/>
+      <c r="AI30" s="44"/>
+      <c r="AJ30" s="44"/>
+      <c r="AK30" s="44"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="40"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="53"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="42"/>
-      <c r="J31" s="65"/>
-      <c r="K31" s="65"/>
-      <c r="L31" s="66"/>
-      <c r="M31" s="42"/>
-      <c r="N31" s="53"/>
-      <c r="O31" s="48"/>
-      <c r="P31" s="42"/>
-      <c r="Q31" s="42"/>
-      <c r="R31" s="42"/>
-      <c r="S31" s="42"/>
-      <c r="T31" s="42"/>
-      <c r="U31" s="42"/>
-      <c r="V31" s="47"/>
-      <c r="W31" s="49"/>
-      <c r="X31" s="42"/>
-      <c r="Y31" s="42"/>
-      <c r="Z31" s="47"/>
-      <c r="AA31" s="48"/>
-      <c r="AB31" s="42"/>
-      <c r="AC31" s="42"/>
-      <c r="AD31" s="46"/>
-      <c r="AE31" s="47"/>
-      <c r="AF31" s="48"/>
-      <c r="AG31" s="42"/>
-      <c r="AH31" s="42"/>
-      <c r="AI31" s="42"/>
-      <c r="AJ31" s="42"/>
-      <c r="AK31" s="42"/>
+      <c r="B31" s="42"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="56"/>
+      <c r="I31" s="44"/>
+      <c r="J31" s="67"/>
+      <c r="K31" s="67"/>
+      <c r="L31" s="68"/>
+      <c r="M31" s="44"/>
+      <c r="N31" s="55"/>
+      <c r="O31" s="50"/>
+      <c r="P31" s="44"/>
+      <c r="Q31" s="44"/>
+      <c r="R31" s="44"/>
+      <c r="S31" s="44"/>
+      <c r="T31" s="44"/>
+      <c r="U31" s="44"/>
+      <c r="V31" s="49"/>
+      <c r="W31" s="51"/>
+      <c r="X31" s="44"/>
+      <c r="Y31" s="44"/>
+      <c r="Z31" s="49"/>
+      <c r="AA31" s="50"/>
+      <c r="AB31" s="44"/>
+      <c r="AC31" s="44"/>
+      <c r="AD31" s="48"/>
+      <c r="AE31" s="49"/>
+      <c r="AF31" s="50"/>
+      <c r="AG31" s="44"/>
+      <c r="AH31" s="44"/>
+      <c r="AI31" s="44"/>
+      <c r="AJ31" s="44"/>
+      <c r="AK31" s="44"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="40"/>
-      <c r="C32" s="41" t="s">
-        <v>100</v>
-      </c>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="47"/>
-      <c r="H32" s="48"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="42"/>
-      <c r="K32" s="42"/>
-      <c r="L32" s="46"/>
-      <c r="M32" s="56"/>
-      <c r="N32" s="44"/>
-      <c r="O32" s="48"/>
-      <c r="P32" s="42"/>
-      <c r="Q32" s="42"/>
-      <c r="R32" s="42"/>
-      <c r="S32" s="42"/>
-      <c r="T32" s="42"/>
-      <c r="U32" s="42"/>
-      <c r="V32" s="47"/>
-      <c r="W32" s="49"/>
-      <c r="X32" s="42"/>
-      <c r="Y32" s="42"/>
-      <c r="Z32" s="47"/>
-      <c r="AA32" s="48"/>
-      <c r="AB32" s="42"/>
-      <c r="AC32" s="42"/>
-      <c r="AD32" s="46"/>
-      <c r="AE32" s="47"/>
-      <c r="AF32" s="48"/>
-      <c r="AG32" s="42"/>
-      <c r="AH32" s="42"/>
-      <c r="AI32" s="42"/>
-      <c r="AJ32" s="42"/>
-      <c r="AK32" s="42"/>
+      <c r="B32" s="42"/>
+      <c r="C32" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="49"/>
+      <c r="H32" s="50"/>
+      <c r="I32" s="44"/>
+      <c r="J32" s="44"/>
+      <c r="K32" s="44"/>
+      <c r="L32" s="48"/>
+      <c r="M32" s="58"/>
+      <c r="N32" s="46"/>
+      <c r="O32" s="50"/>
+      <c r="P32" s="44"/>
+      <c r="Q32" s="44"/>
+      <c r="R32" s="44"/>
+      <c r="S32" s="44"/>
+      <c r="T32" s="44"/>
+      <c r="U32" s="44"/>
+      <c r="V32" s="49"/>
+      <c r="W32" s="51"/>
+      <c r="X32" s="44"/>
+      <c r="Y32" s="44"/>
+      <c r="Z32" s="49"/>
+      <c r="AA32" s="50"/>
+      <c r="AB32" s="44"/>
+      <c r="AC32" s="44"/>
+      <c r="AD32" s="48"/>
+      <c r="AE32" s="49"/>
+      <c r="AF32" s="50"/>
+      <c r="AG32" s="44"/>
+      <c r="AH32" s="44"/>
+      <c r="AI32" s="44"/>
+      <c r="AJ32" s="44"/>
+      <c r="AK32" s="44"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="40"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="42"/>
-      <c r="J33" s="42"/>
-      <c r="K33" s="42"/>
-      <c r="L33" s="46"/>
-      <c r="M33" s="42"/>
-      <c r="N33" s="53"/>
-      <c r="O33" s="48"/>
-      <c r="P33" s="42"/>
-      <c r="Q33" s="42"/>
-      <c r="R33" s="42"/>
-      <c r="S33" s="42"/>
-      <c r="T33" s="42"/>
-      <c r="U33" s="42"/>
-      <c r="V33" s="47"/>
-      <c r="W33" s="49"/>
-      <c r="X33" s="42"/>
-      <c r="Y33" s="42"/>
-      <c r="Z33" s="47"/>
-      <c r="AA33" s="48"/>
-      <c r="AB33" s="42"/>
-      <c r="AC33" s="42"/>
-      <c r="AD33" s="46"/>
-      <c r="AE33" s="47"/>
-      <c r="AF33" s="48"/>
-      <c r="AG33" s="42"/>
-      <c r="AH33" s="42"/>
-      <c r="AI33" s="42"/>
-      <c r="AJ33" s="42"/>
-      <c r="AK33" s="42"/>
+      <c r="B33" s="42"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="49"/>
+      <c r="H33" s="50"/>
+      <c r="I33" s="44"/>
+      <c r="J33" s="44"/>
+      <c r="K33" s="44"/>
+      <c r="L33" s="48"/>
+      <c r="M33" s="44"/>
+      <c r="N33" s="55"/>
+      <c r="O33" s="50"/>
+      <c r="P33" s="44"/>
+      <c r="Q33" s="44"/>
+      <c r="R33" s="44"/>
+      <c r="S33" s="44"/>
+      <c r="T33" s="44"/>
+      <c r="U33" s="44"/>
+      <c r="V33" s="49"/>
+      <c r="W33" s="51"/>
+      <c r="X33" s="44"/>
+      <c r="Y33" s="44"/>
+      <c r="Z33" s="49"/>
+      <c r="AA33" s="50"/>
+      <c r="AB33" s="44"/>
+      <c r="AC33" s="44"/>
+      <c r="AD33" s="48"/>
+      <c r="AE33" s="49"/>
+      <c r="AF33" s="50"/>
+      <c r="AG33" s="44"/>
+      <c r="AH33" s="44"/>
+      <c r="AI33" s="44"/>
+      <c r="AJ33" s="44"/>
+      <c r="AK33" s="44"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="57" t="s">
-        <v>101</v>
-      </c>
-      <c r="C34" s="67" t="s">
-        <v>102</v>
-      </c>
-      <c r="D34" s="60"/>
-      <c r="E34" s="60"/>
-      <c r="F34" s="63"/>
-      <c r="G34" s="61"/>
-      <c r="H34" s="59"/>
-      <c r="I34" s="60"/>
-      <c r="J34" s="60"/>
-      <c r="K34" s="60"/>
-      <c r="L34" s="46"/>
-      <c r="M34" s="56"/>
-      <c r="N34" s="44"/>
-      <c r="O34" s="45"/>
-      <c r="P34" s="56"/>
-      <c r="Q34" s="56"/>
-      <c r="R34" s="56"/>
-      <c r="S34" s="60"/>
-      <c r="T34" s="60"/>
-      <c r="U34" s="60"/>
-      <c r="V34" s="61"/>
-      <c r="W34" s="49"/>
-      <c r="X34" s="60"/>
-      <c r="Y34" s="60"/>
-      <c r="Z34" s="61"/>
-      <c r="AA34" s="59"/>
-      <c r="AB34" s="60"/>
-      <c r="AC34" s="60"/>
-      <c r="AD34" s="46"/>
-      <c r="AE34" s="61"/>
-      <c r="AF34" s="59"/>
-      <c r="AG34" s="60"/>
-      <c r="AH34" s="60"/>
-      <c r="AI34" s="60"/>
-      <c r="AJ34" s="60"/>
-      <c r="AK34" s="60"/>
+      <c r="B34" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" s="69" t="s">
+        <v>106</v>
+      </c>
+      <c r="D34" s="62"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="65"/>
+      <c r="G34" s="63"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="62"/>
+      <c r="J34" s="62"/>
+      <c r="K34" s="62"/>
+      <c r="L34" s="48"/>
+      <c r="M34" s="58"/>
+      <c r="N34" s="46"/>
+      <c r="O34" s="47"/>
+      <c r="P34" s="58"/>
+      <c r="Q34" s="58"/>
+      <c r="R34" s="58"/>
+      <c r="S34" s="62"/>
+      <c r="T34" s="62"/>
+      <c r="U34" s="62"/>
+      <c r="V34" s="63"/>
+      <c r="W34" s="51"/>
+      <c r="X34" s="62"/>
+      <c r="Y34" s="62"/>
+      <c r="Z34" s="63"/>
+      <c r="AA34" s="61"/>
+      <c r="AB34" s="62"/>
+      <c r="AC34" s="62"/>
+      <c r="AD34" s="48"/>
+      <c r="AE34" s="63"/>
+      <c r="AF34" s="61"/>
+      <c r="AG34" s="62"/>
+      <c r="AH34" s="62"/>
+      <c r="AI34" s="62"/>
+      <c r="AJ34" s="62"/>
+      <c r="AK34" s="62"/>
     </row>
     <row r="35" ht="12" customHeight="1">
-      <c r="B35" s="57"/>
-      <c r="C35" s="67"/>
-      <c r="D35" s="60"/>
-      <c r="E35" s="60"/>
-      <c r="F35" s="63"/>
-      <c r="G35" s="61"/>
-      <c r="H35" s="59"/>
-      <c r="I35" s="60"/>
-      <c r="J35" s="60"/>
-      <c r="K35" s="68"/>
-      <c r="L35" s="46"/>
-      <c r="M35" s="60"/>
-      <c r="N35" s="53"/>
-      <c r="O35" s="59"/>
-      <c r="P35" s="55"/>
-      <c r="Q35" s="60"/>
-      <c r="R35" s="60"/>
-      <c r="S35" s="60"/>
-      <c r="T35" s="60"/>
-      <c r="U35" s="60"/>
-      <c r="V35" s="61"/>
-      <c r="W35" s="49"/>
-      <c r="X35" s="60"/>
-      <c r="Y35" s="60"/>
-      <c r="Z35" s="61"/>
-      <c r="AA35" s="59"/>
-      <c r="AB35" s="60"/>
-      <c r="AC35" s="60"/>
-      <c r="AD35" s="46"/>
-      <c r="AE35" s="61"/>
-      <c r="AF35" s="59"/>
-      <c r="AG35" s="60"/>
-      <c r="AH35" s="60"/>
-      <c r="AI35" s="60"/>
-      <c r="AJ35" s="60"/>
-      <c r="AK35" s="60"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="69"/>
+      <c r="D35" s="62"/>
+      <c r="E35" s="62"/>
+      <c r="F35" s="65"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="61"/>
+      <c r="I35" s="62"/>
+      <c r="J35" s="62"/>
+      <c r="K35" s="70"/>
+      <c r="L35" s="48"/>
+      <c r="M35" s="62"/>
+      <c r="N35" s="55"/>
+      <c r="O35" s="61"/>
+      <c r="P35" s="57"/>
+      <c r="Q35" s="62"/>
+      <c r="R35" s="62"/>
+      <c r="S35" s="62"/>
+      <c r="T35" s="62"/>
+      <c r="U35" s="62"/>
+      <c r="V35" s="63"/>
+      <c r="W35" s="51"/>
+      <c r="X35" s="62"/>
+      <c r="Y35" s="62"/>
+      <c r="Z35" s="63"/>
+      <c r="AA35" s="61"/>
+      <c r="AB35" s="62"/>
+      <c r="AC35" s="62"/>
+      <c r="AD35" s="48"/>
+      <c r="AE35" s="63"/>
+      <c r="AF35" s="61"/>
+      <c r="AG35" s="62"/>
+      <c r="AH35" s="62"/>
+      <c r="AI35" s="62"/>
+      <c r="AJ35" s="62"/>
+      <c r="AK35" s="62"/>
     </row>
     <row r="36" ht="12" customHeight="1">
-      <c r="B36" s="57"/>
-      <c r="C36" s="67" t="s">
-        <v>103</v>
-      </c>
-      <c r="D36" s="60"/>
-      <c r="E36" s="60"/>
-      <c r="F36" s="63"/>
-      <c r="G36" s="61"/>
-      <c r="H36" s="59"/>
-      <c r="I36" s="60"/>
-      <c r="J36" s="60"/>
-      <c r="K36" s="60"/>
-      <c r="L36" s="46"/>
-      <c r="M36" s="56"/>
-      <c r="N36" s="44"/>
-      <c r="O36" s="45"/>
-      <c r="P36" s="56"/>
-      <c r="Q36" s="60"/>
-      <c r="R36" s="60"/>
-      <c r="S36" s="60"/>
-      <c r="T36" s="60"/>
-      <c r="U36" s="60"/>
-      <c r="V36" s="61"/>
-      <c r="W36" s="49"/>
-      <c r="X36" s="60"/>
-      <c r="Y36" s="60"/>
-      <c r="Z36" s="61"/>
-      <c r="AA36" s="59"/>
-      <c r="AB36" s="60"/>
-      <c r="AC36" s="60"/>
-      <c r="AD36" s="46"/>
-      <c r="AE36" s="61"/>
-      <c r="AF36" s="59"/>
-      <c r="AG36" s="60"/>
-      <c r="AH36" s="60"/>
-      <c r="AI36" s="60"/>
-      <c r="AJ36" s="60"/>
-      <c r="AK36" s="60"/>
+      <c r="B36" s="59"/>
+      <c r="C36" s="69" t="s">
+        <v>107</v>
+      </c>
+      <c r="D36" s="62"/>
+      <c r="E36" s="62"/>
+      <c r="F36" s="65"/>
+      <c r="G36" s="63"/>
+      <c r="H36" s="61"/>
+      <c r="I36" s="62"/>
+      <c r="J36" s="62"/>
+      <c r="K36" s="62"/>
+      <c r="L36" s="48"/>
+      <c r="M36" s="58"/>
+      <c r="N36" s="46"/>
+      <c r="O36" s="47"/>
+      <c r="P36" s="58"/>
+      <c r="Q36" s="62"/>
+      <c r="R36" s="62"/>
+      <c r="S36" s="62"/>
+      <c r="T36" s="62"/>
+      <c r="U36" s="62"/>
+      <c r="V36" s="63"/>
+      <c r="W36" s="51"/>
+      <c r="X36" s="62"/>
+      <c r="Y36" s="62"/>
+      <c r="Z36" s="63"/>
+      <c r="AA36" s="61"/>
+      <c r="AB36" s="62"/>
+      <c r="AC36" s="62"/>
+      <c r="AD36" s="48"/>
+      <c r="AE36" s="63"/>
+      <c r="AF36" s="61"/>
+      <c r="AG36" s="62"/>
+      <c r="AH36" s="62"/>
+      <c r="AI36" s="62"/>
+      <c r="AJ36" s="62"/>
+      <c r="AK36" s="62"/>
     </row>
     <row r="37" ht="12" customHeight="1">
-      <c r="B37" s="57"/>
-      <c r="C37" s="67"/>
-      <c r="D37" s="60"/>
-      <c r="E37" s="60"/>
-      <c r="F37" s="63"/>
-      <c r="G37" s="61"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="60"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="68"/>
-      <c r="L37" s="46"/>
-      <c r="M37" s="60"/>
-      <c r="N37" s="61"/>
-      <c r="O37" s="59"/>
-      <c r="P37" s="55"/>
-      <c r="Q37" s="60"/>
-      <c r="R37" s="60"/>
-      <c r="S37" s="60"/>
-      <c r="T37" s="60"/>
-      <c r="U37" s="60"/>
-      <c r="V37" s="61"/>
-      <c r="W37" s="49"/>
-      <c r="X37" s="60"/>
-      <c r="Y37" s="60"/>
-      <c r="Z37" s="61"/>
-      <c r="AA37" s="59"/>
-      <c r="AB37" s="60"/>
-      <c r="AC37" s="60"/>
-      <c r="AD37" s="46"/>
-      <c r="AE37" s="61"/>
-      <c r="AF37" s="59"/>
-      <c r="AG37" s="60"/>
-      <c r="AH37" s="60"/>
-      <c r="AI37" s="60"/>
-      <c r="AJ37" s="60"/>
-      <c r="AK37" s="60"/>
+      <c r="B37" s="59"/>
+      <c r="C37" s="69"/>
+      <c r="D37" s="62"/>
+      <c r="E37" s="62"/>
+      <c r="F37" s="65"/>
+      <c r="G37" s="63"/>
+      <c r="H37" s="61"/>
+      <c r="I37" s="62"/>
+      <c r="J37" s="62"/>
+      <c r="K37" s="70"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="62"/>
+      <c r="N37" s="63"/>
+      <c r="O37" s="61"/>
+      <c r="P37" s="57"/>
+      <c r="Q37" s="62"/>
+      <c r="R37" s="62"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="62"/>
+      <c r="U37" s="62"/>
+      <c r="V37" s="63"/>
+      <c r="W37" s="51"/>
+      <c r="X37" s="62"/>
+      <c r="Y37" s="62"/>
+      <c r="Z37" s="63"/>
+      <c r="AA37" s="61"/>
+      <c r="AB37" s="62"/>
+      <c r="AC37" s="62"/>
+      <c r="AD37" s="48"/>
+      <c r="AE37" s="63"/>
+      <c r="AF37" s="61"/>
+      <c r="AG37" s="62"/>
+      <c r="AH37" s="62"/>
+      <c r="AI37" s="62"/>
+      <c r="AJ37" s="62"/>
+      <c r="AK37" s="62"/>
     </row>
     <row r="38" ht="12" customHeight="1">
-      <c r="B38" s="57"/>
-      <c r="C38" s="67" t="s">
-        <v>104</v>
-      </c>
-      <c r="D38" s="60"/>
-      <c r="E38" s="60"/>
-      <c r="F38" s="63"/>
-      <c r="G38" s="61"/>
-      <c r="H38" s="59"/>
-      <c r="I38" s="60"/>
-      <c r="J38" s="60"/>
-      <c r="K38" s="60"/>
-      <c r="L38" s="46"/>
-      <c r="M38" s="60"/>
-      <c r="N38" s="61"/>
-      <c r="O38" s="45"/>
-      <c r="P38" s="56"/>
-      <c r="Q38" s="56"/>
-      <c r="R38" s="56"/>
-      <c r="S38" s="56"/>
-      <c r="T38" s="56"/>
-      <c r="U38" s="56"/>
-      <c r="V38" s="44"/>
-      <c r="W38" s="49"/>
-      <c r="X38" s="56"/>
-      <c r="Y38" s="56"/>
-      <c r="Z38" s="61"/>
-      <c r="AA38" s="59"/>
-      <c r="AB38" s="60"/>
-      <c r="AC38" s="60"/>
-      <c r="AD38" s="46"/>
-      <c r="AE38" s="61"/>
-      <c r="AF38" s="59"/>
-      <c r="AG38" s="60"/>
-      <c r="AH38" s="60"/>
-      <c r="AI38" s="60"/>
-      <c r="AJ38" s="60"/>
-      <c r="AK38" s="60"/>
+      <c r="B38" s="59"/>
+      <c r="C38" s="69" t="s">
+        <v>108</v>
+      </c>
+      <c r="D38" s="62"/>
+      <c r="E38" s="62"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="63"/>
+      <c r="H38" s="61"/>
+      <c r="I38" s="62"/>
+      <c r="J38" s="62"/>
+      <c r="K38" s="62"/>
+      <c r="L38" s="48"/>
+      <c r="M38" s="62"/>
+      <c r="N38" s="63"/>
+      <c r="O38" s="47"/>
+      <c r="P38" s="58"/>
+      <c r="Q38" s="58"/>
+      <c r="R38" s="58"/>
+      <c r="S38" s="58"/>
+      <c r="T38" s="58"/>
+      <c r="U38" s="58"/>
+      <c r="V38" s="46"/>
+      <c r="W38" s="51"/>
+      <c r="X38" s="58"/>
+      <c r="Y38" s="58"/>
+      <c r="Z38" s="63"/>
+      <c r="AA38" s="61"/>
+      <c r="AB38" s="62"/>
+      <c r="AC38" s="62"/>
+      <c r="AD38" s="48"/>
+      <c r="AE38" s="63"/>
+      <c r="AF38" s="61"/>
+      <c r="AG38" s="62"/>
+      <c r="AH38" s="62"/>
+      <c r="AI38" s="62"/>
+      <c r="AJ38" s="62"/>
+      <c r="AK38" s="62"/>
     </row>
     <row r="39" ht="12" customHeight="1">
-      <c r="B39" s="57"/>
-      <c r="C39" s="67"/>
-      <c r="D39" s="60"/>
-      <c r="E39" s="60"/>
-      <c r="F39" s="63"/>
-      <c r="G39" s="61"/>
-      <c r="H39" s="59"/>
-      <c r="I39" s="60"/>
-      <c r="J39" s="60"/>
-      <c r="K39" s="60"/>
-      <c r="L39" s="46"/>
-      <c r="M39" s="60"/>
-      <c r="N39" s="61"/>
-      <c r="O39" s="59"/>
-      <c r="P39" s="60"/>
-      <c r="Q39" s="60"/>
-      <c r="R39" s="60"/>
-      <c r="S39" s="60"/>
-      <c r="T39" s="60"/>
-      <c r="U39" s="60"/>
-      <c r="V39" s="61"/>
-      <c r="W39" s="49"/>
-      <c r="X39" s="60"/>
-      <c r="Y39" s="60"/>
-      <c r="Z39" s="61"/>
-      <c r="AA39" s="59"/>
-      <c r="AB39" s="60"/>
-      <c r="AC39" s="60"/>
-      <c r="AD39" s="46"/>
-      <c r="AE39" s="61"/>
-      <c r="AF39" s="59"/>
-      <c r="AG39" s="60"/>
-      <c r="AH39" s="60"/>
-      <c r="AI39" s="60"/>
-      <c r="AJ39" s="60"/>
-      <c r="AK39" s="60"/>
+      <c r="B39" s="59"/>
+      <c r="C39" s="69"/>
+      <c r="D39" s="62"/>
+      <c r="E39" s="62"/>
+      <c r="F39" s="65"/>
+      <c r="G39" s="63"/>
+      <c r="H39" s="61"/>
+      <c r="I39" s="62"/>
+      <c r="J39" s="62"/>
+      <c r="K39" s="62"/>
+      <c r="L39" s="48"/>
+      <c r="M39" s="62"/>
+      <c r="N39" s="63"/>
+      <c r="O39" s="61"/>
+      <c r="P39" s="57"/>
+      <c r="Q39" s="57"/>
+      <c r="R39" s="62"/>
+      <c r="S39" s="62"/>
+      <c r="T39" s="62"/>
+      <c r="U39" s="62"/>
+      <c r="V39" s="63"/>
+      <c r="W39" s="51"/>
+      <c r="X39" s="62"/>
+      <c r="Y39" s="62"/>
+      <c r="Z39" s="63"/>
+      <c r="AA39" s="61"/>
+      <c r="AB39" s="62"/>
+      <c r="AC39" s="62"/>
+      <c r="AD39" s="48"/>
+      <c r="AE39" s="63"/>
+      <c r="AF39" s="61"/>
+      <c r="AG39" s="62"/>
+      <c r="AH39" s="62"/>
+      <c r="AI39" s="62"/>
+      <c r="AJ39" s="62"/>
+      <c r="AK39" s="62"/>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="B40" s="57"/>
-      <c r="C40" s="67" t="s">
-        <v>105</v>
-      </c>
-      <c r="D40" s="60"/>
-      <c r="E40" s="60"/>
-      <c r="F40" s="63"/>
-      <c r="G40" s="61"/>
-      <c r="H40" s="59"/>
-      <c r="I40" s="60"/>
-      <c r="J40" s="60"/>
-      <c r="K40" s="60"/>
-      <c r="L40" s="46"/>
-      <c r="M40" s="60"/>
-      <c r="N40" s="61"/>
-      <c r="O40" s="59"/>
-      <c r="P40" s="60"/>
-      <c r="Q40" s="60"/>
-      <c r="R40" s="56"/>
-      <c r="S40" s="56"/>
-      <c r="T40" s="56"/>
-      <c r="U40" s="56"/>
-      <c r="V40" s="44"/>
-      <c r="W40" s="49"/>
-      <c r="X40" s="56"/>
-      <c r="Y40" s="56"/>
-      <c r="Z40" s="44"/>
-      <c r="AA40" s="45"/>
-      <c r="AB40" s="56"/>
-      <c r="AC40" s="56"/>
-      <c r="AD40" s="46"/>
-      <c r="AE40" s="61"/>
-      <c r="AF40" s="59"/>
-      <c r="AG40" s="60"/>
-      <c r="AH40" s="60"/>
-      <c r="AI40" s="60"/>
-      <c r="AJ40" s="60"/>
-      <c r="AK40" s="60"/>
+      <c r="B40" s="59"/>
+      <c r="C40" s="69" t="s">
+        <v>109</v>
+      </c>
+      <c r="D40" s="62"/>
+      <c r="E40" s="62"/>
+      <c r="F40" s="65"/>
+      <c r="G40" s="63"/>
+      <c r="H40" s="61"/>
+      <c r="I40" s="62"/>
+      <c r="J40" s="62"/>
+      <c r="K40" s="62"/>
+      <c r="L40" s="48"/>
+      <c r="M40" s="62"/>
+      <c r="N40" s="63"/>
+      <c r="O40" s="61"/>
+      <c r="P40" s="62"/>
+      <c r="Q40" s="62"/>
+      <c r="R40" s="58"/>
+      <c r="S40" s="58"/>
+      <c r="T40" s="58"/>
+      <c r="U40" s="58"/>
+      <c r="V40" s="46"/>
+      <c r="W40" s="51"/>
+      <c r="X40" s="58"/>
+      <c r="Y40" s="58"/>
+      <c r="Z40" s="46"/>
+      <c r="AA40" s="47"/>
+      <c r="AB40" s="58"/>
+      <c r="AC40" s="58"/>
+      <c r="AD40" s="48"/>
+      <c r="AE40" s="63"/>
+      <c r="AF40" s="61"/>
+      <c r="AG40" s="62"/>
+      <c r="AH40" s="62"/>
+      <c r="AI40" s="62"/>
+      <c r="AJ40" s="62"/>
+      <c r="AK40" s="62"/>
     </row>
     <row r="41" ht="12" customHeight="1">
-      <c r="B41" s="57"/>
-      <c r="C41" s="67"/>
-      <c r="D41" s="60"/>
-      <c r="E41" s="60"/>
-      <c r="F41" s="63"/>
-      <c r="G41" s="61"/>
-      <c r="H41" s="59"/>
-      <c r="I41" s="60"/>
-      <c r="J41" s="60"/>
-      <c r="K41" s="60"/>
-      <c r="L41" s="46"/>
-      <c r="M41" s="60"/>
-      <c r="N41" s="61"/>
-      <c r="O41" s="59"/>
-      <c r="P41" s="60"/>
-      <c r="Q41" s="60"/>
-      <c r="R41" s="60"/>
-      <c r="S41" s="60"/>
-      <c r="T41" s="60"/>
-      <c r="U41" s="60"/>
-      <c r="V41" s="61"/>
-      <c r="W41" s="49"/>
-      <c r="X41" s="60"/>
-      <c r="Y41" s="60"/>
-      <c r="Z41" s="61"/>
-      <c r="AA41" s="59"/>
-      <c r="AB41" s="60"/>
-      <c r="AC41" s="60"/>
-      <c r="AD41" s="46"/>
-      <c r="AE41" s="61"/>
-      <c r="AF41" s="59"/>
-      <c r="AG41" s="60"/>
-      <c r="AH41" s="60"/>
-      <c r="AI41" s="60"/>
-      <c r="AJ41" s="60"/>
-      <c r="AK41" s="60"/>
+      <c r="B41" s="59"/>
+      <c r="C41" s="69"/>
+      <c r="D41" s="62"/>
+      <c r="E41" s="62"/>
+      <c r="F41" s="65"/>
+      <c r="G41" s="63"/>
+      <c r="H41" s="61"/>
+      <c r="I41" s="62"/>
+      <c r="J41" s="62"/>
+      <c r="K41" s="62"/>
+      <c r="L41" s="48"/>
+      <c r="M41" s="62"/>
+      <c r="N41" s="63"/>
+      <c r="O41" s="61"/>
+      <c r="P41" s="62"/>
+      <c r="Q41" s="57"/>
+      <c r="R41" s="62"/>
+      <c r="S41" s="62"/>
+      <c r="T41" s="62"/>
+      <c r="U41" s="62"/>
+      <c r="V41" s="63"/>
+      <c r="W41" s="51"/>
+      <c r="X41" s="62"/>
+      <c r="Y41" s="62"/>
+      <c r="Z41" s="63"/>
+      <c r="AA41" s="61"/>
+      <c r="AB41" s="62"/>
+      <c r="AC41" s="62"/>
+      <c r="AD41" s="48"/>
+      <c r="AE41" s="63"/>
+      <c r="AF41" s="61"/>
+      <c r="AG41" s="62"/>
+      <c r="AH41" s="62"/>
+      <c r="AI41" s="62"/>
+      <c r="AJ41" s="62"/>
+      <c r="AK41" s="62"/>
     </row>
     <row r="42" ht="12" customHeight="1">
-      <c r="B42" s="40" t="s">
+      <c r="B42" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="69" t="s">
-        <v>106</v>
-      </c>
-      <c r="D42" s="42"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="50"/>
-      <c r="G42" s="47"/>
-      <c r="H42" s="48"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="46"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="47"/>
-      <c r="O42" s="48"/>
-      <c r="P42" s="56"/>
-      <c r="Q42" s="56"/>
-      <c r="R42" s="42"/>
-      <c r="S42" s="42"/>
-      <c r="T42" s="42"/>
-      <c r="U42" s="42"/>
-      <c r="V42" s="44"/>
-      <c r="W42" s="49"/>
-      <c r="X42" s="56"/>
-      <c r="Y42" s="56"/>
-      <c r="Z42" s="44"/>
-      <c r="AA42" s="45"/>
-      <c r="AB42" s="56"/>
-      <c r="AC42" s="56"/>
-      <c r="AD42" s="46"/>
-      <c r="AE42" s="47"/>
-      <c r="AF42" s="48"/>
-      <c r="AG42" s="42"/>
-      <c r="AH42" s="42"/>
-      <c r="AI42" s="42"/>
-      <c r="AJ42" s="42"/>
-      <c r="AK42" s="42"/>
+      <c r="C42" s="71" t="s">
+        <v>110</v>
+      </c>
+      <c r="D42" s="44"/>
+      <c r="E42" s="44"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="49"/>
+      <c r="H42" s="50"/>
+      <c r="I42" s="44"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="44"/>
+      <c r="L42" s="48"/>
+      <c r="M42" s="44"/>
+      <c r="N42" s="49"/>
+      <c r="O42" s="50"/>
+      <c r="P42" s="58"/>
+      <c r="Q42" s="58"/>
+      <c r="R42" s="44"/>
+      <c r="S42" s="44"/>
+      <c r="T42" s="44"/>
+      <c r="U42" s="44"/>
+      <c r="V42" s="46"/>
+      <c r="W42" s="51"/>
+      <c r="X42" s="58"/>
+      <c r="Y42" s="58"/>
+      <c r="Z42" s="46"/>
+      <c r="AA42" s="47"/>
+      <c r="AB42" s="58"/>
+      <c r="AC42" s="58"/>
+      <c r="AD42" s="48"/>
+      <c r="AE42" s="49"/>
+      <c r="AF42" s="50"/>
+      <c r="AG42" s="44"/>
+      <c r="AH42" s="44"/>
+      <c r="AI42" s="44"/>
+      <c r="AJ42" s="44"/>
+      <c r="AK42" s="44"/>
     </row>
     <row r="43" ht="12" customHeight="1">
-      <c r="B43" s="40"/>
-      <c r="C43" s="69"/>
-      <c r="D43" s="42"/>
-      <c r="E43" s="42"/>
-      <c r="F43" s="50"/>
-      <c r="G43" s="47"/>
-      <c r="H43" s="48"/>
-      <c r="I43" s="42"/>
-      <c r="J43" s="42"/>
-      <c r="K43" s="42"/>
-      <c r="L43" s="46"/>
-      <c r="M43" s="42"/>
-      <c r="N43" s="47"/>
-      <c r="O43" s="48"/>
-      <c r="P43" s="42"/>
-      <c r="Q43" s="42"/>
-      <c r="R43" s="42"/>
-      <c r="S43" s="42"/>
-      <c r="T43" s="42"/>
-      <c r="U43" s="42"/>
-      <c r="V43" s="47"/>
-      <c r="W43" s="49"/>
-      <c r="X43" s="42"/>
-      <c r="Y43" s="42"/>
-      <c r="Z43" s="47"/>
-      <c r="AA43" s="48"/>
-      <c r="AB43" s="42"/>
-      <c r="AC43" s="42"/>
-      <c r="AD43" s="46"/>
-      <c r="AE43" s="47"/>
-      <c r="AF43" s="48"/>
-      <c r="AG43" s="42"/>
-      <c r="AH43" s="42"/>
-      <c r="AI43" s="42"/>
-      <c r="AJ43" s="42"/>
-      <c r="AK43" s="42"/>
+      <c r="B43" s="42"/>
+      <c r="C43" s="71"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="49"/>
+      <c r="H43" s="50"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="48"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="49"/>
+      <c r="O43" s="50"/>
+      <c r="P43" s="44"/>
+      <c r="Q43" s="57"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="44"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="44"/>
+      <c r="V43" s="49"/>
+      <c r="W43" s="51"/>
+      <c r="X43" s="44"/>
+      <c r="Y43" s="44"/>
+      <c r="Z43" s="49"/>
+      <c r="AA43" s="50"/>
+      <c r="AB43" s="44"/>
+      <c r="AC43" s="44"/>
+      <c r="AD43" s="48"/>
+      <c r="AE43" s="49"/>
+      <c r="AF43" s="50"/>
+      <c r="AG43" s="44"/>
+      <c r="AH43" s="44"/>
+      <c r="AI43" s="44"/>
+      <c r="AJ43" s="44"/>
+      <c r="AK43" s="44"/>
     </row>
     <row r="44" ht="12" customHeight="1">
-      <c r="B44" s="40"/>
-      <c r="C44" s="69" t="s">
-        <v>107</v>
-      </c>
-      <c r="D44" s="42"/>
-      <c r="E44" s="42"/>
-      <c r="F44" s="50"/>
-      <c r="G44" s="47"/>
-      <c r="H44" s="48"/>
-      <c r="I44" s="42"/>
-      <c r="J44" s="42"/>
-      <c r="K44" s="42"/>
-      <c r="L44" s="46"/>
-      <c r="M44" s="42"/>
-      <c r="N44" s="47"/>
-      <c r="O44" s="48"/>
-      <c r="P44" s="56"/>
-      <c r="Q44" s="56"/>
-      <c r="R44" s="42"/>
-      <c r="S44" s="42"/>
-      <c r="T44" s="42"/>
-      <c r="U44" s="42"/>
-      <c r="V44" s="47"/>
-      <c r="W44" s="49"/>
-      <c r="X44" s="56"/>
-      <c r="Y44" s="56"/>
-      <c r="Z44" s="47"/>
-      <c r="AA44" s="48"/>
-      <c r="AB44" s="42"/>
-      <c r="AC44" s="56"/>
-      <c r="AD44" s="46"/>
-      <c r="AE44" s="44"/>
-      <c r="AF44" s="45"/>
-      <c r="AG44" s="42"/>
-      <c r="AH44" s="42"/>
-      <c r="AI44" s="56"/>
-      <c r="AJ44" s="42"/>
-      <c r="AK44" s="42"/>
+      <c r="B44" s="42"/>
+      <c r="C44" s="71" t="s">
+        <v>111</v>
+      </c>
+      <c r="D44" s="44"/>
+      <c r="E44" s="44"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="49"/>
+      <c r="H44" s="50"/>
+      <c r="I44" s="44"/>
+      <c r="J44" s="44"/>
+      <c r="K44" s="44"/>
+      <c r="L44" s="48"/>
+      <c r="M44" s="44"/>
+      <c r="N44" s="49"/>
+      <c r="O44" s="50"/>
+      <c r="P44" s="58"/>
+      <c r="Q44" s="58"/>
+      <c r="R44" s="44"/>
+      <c r="S44" s="44"/>
+      <c r="T44" s="44"/>
+      <c r="U44" s="44"/>
+      <c r="V44" s="49"/>
+      <c r="W44" s="51"/>
+      <c r="X44" s="58"/>
+      <c r="Y44" s="58"/>
+      <c r="Z44" s="49"/>
+      <c r="AA44" s="50"/>
+      <c r="AB44" s="44"/>
+      <c r="AC44" s="58"/>
+      <c r="AD44" s="48"/>
+      <c r="AE44" s="46"/>
+      <c r="AF44" s="47"/>
+      <c r="AG44" s="44"/>
+      <c r="AH44" s="44"/>
+      <c r="AI44" s="58"/>
+      <c r="AJ44" s="44"/>
+      <c r="AK44" s="44"/>
     </row>
     <row r="45" ht="12" customHeight="1">
-      <c r="B45" s="40"/>
-      <c r="C45" s="69"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="50"/>
-      <c r="G45" s="47"/>
-      <c r="H45" s="48"/>
-      <c r="I45" s="42"/>
-      <c r="J45" s="42"/>
-      <c r="K45" s="42"/>
-      <c r="L45" s="46"/>
-      <c r="M45" s="42"/>
-      <c r="N45" s="47"/>
-      <c r="O45" s="48"/>
-      <c r="P45" s="42"/>
-      <c r="Q45" s="42"/>
-      <c r="R45" s="42"/>
-      <c r="S45" s="42"/>
-      <c r="T45" s="42"/>
-      <c r="U45" s="42"/>
-      <c r="V45" s="47"/>
-      <c r="W45" s="49"/>
-      <c r="X45" s="42"/>
-      <c r="Y45" s="42"/>
-      <c r="Z45" s="47"/>
-      <c r="AA45" s="48"/>
-      <c r="AB45" s="42"/>
-      <c r="AC45" s="42"/>
-      <c r="AD45" s="46"/>
-      <c r="AE45" s="47"/>
-      <c r="AF45" s="48"/>
-      <c r="AG45" s="42"/>
-      <c r="AH45" s="42"/>
-      <c r="AI45" s="42"/>
-      <c r="AJ45" s="42"/>
-      <c r="AK45" s="42"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="71"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="44"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="49"/>
+      <c r="H45" s="50"/>
+      <c r="I45" s="44"/>
+      <c r="J45" s="44"/>
+      <c r="K45" s="44"/>
+      <c r="L45" s="48"/>
+      <c r="M45" s="44"/>
+      <c r="N45" s="49"/>
+      <c r="O45" s="50"/>
+      <c r="P45" s="44"/>
+      <c r="Q45" s="44"/>
+      <c r="R45" s="44"/>
+      <c r="S45" s="44"/>
+      <c r="T45" s="44"/>
+      <c r="U45" s="44"/>
+      <c r="V45" s="49"/>
+      <c r="W45" s="51"/>
+      <c r="X45" s="44"/>
+      <c r="Y45" s="44"/>
+      <c r="Z45" s="49"/>
+      <c r="AA45" s="50"/>
+      <c r="AB45" s="44"/>
+      <c r="AC45" s="44"/>
+      <c r="AD45" s="48"/>
+      <c r="AE45" s="49"/>
+      <c r="AF45" s="50"/>
+      <c r="AG45" s="44"/>
+      <c r="AH45" s="44"/>
+      <c r="AI45" s="44"/>
+      <c r="AJ45" s="44"/>
+      <c r="AK45" s="44"/>
     </row>
     <row r="46" ht="12" customHeight="1">
-      <c r="B46" s="57" t="s">
-        <v>108</v>
-      </c>
-      <c r="C46" s="58" t="s">
+      <c r="B46" s="59" t="s">
+        <v>112</v>
+      </c>
+      <c r="C46" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="D46" s="60"/>
-      <c r="E46" s="60"/>
-      <c r="F46" s="63"/>
-      <c r="G46" s="61"/>
-      <c r="H46" s="59"/>
-      <c r="I46" s="60"/>
-      <c r="J46" s="60"/>
-      <c r="K46" s="60"/>
-      <c r="L46" s="46"/>
-      <c r="M46" s="60"/>
-      <c r="N46" s="61"/>
-      <c r="O46" s="59"/>
-      <c r="P46" s="60"/>
-      <c r="Q46" s="60"/>
-      <c r="R46" s="60"/>
-      <c r="S46" s="60"/>
-      <c r="T46" s="60"/>
-      <c r="U46" s="60"/>
-      <c r="V46" s="61"/>
-      <c r="W46" s="49"/>
-      <c r="X46" s="60"/>
-      <c r="Y46" s="60"/>
-      <c r="Z46" s="61"/>
-      <c r="AA46" s="59"/>
-      <c r="AB46" s="60"/>
-      <c r="AC46" s="60"/>
-      <c r="AD46" s="46"/>
-      <c r="AE46" s="61"/>
-      <c r="AF46" s="59"/>
-      <c r="AG46" s="60"/>
-      <c r="AH46" s="60"/>
-      <c r="AI46" s="60"/>
-      <c r="AJ46" s="56"/>
-      <c r="AK46" s="60"/>
+      <c r="D46" s="62"/>
+      <c r="E46" s="62"/>
+      <c r="F46" s="65"/>
+      <c r="G46" s="63"/>
+      <c r="H46" s="61"/>
+      <c r="I46" s="62"/>
+      <c r="J46" s="62"/>
+      <c r="K46" s="62"/>
+      <c r="L46" s="48"/>
+      <c r="M46" s="62"/>
+      <c r="N46" s="63"/>
+      <c r="O46" s="61"/>
+      <c r="P46" s="62"/>
+      <c r="Q46" s="62"/>
+      <c r="R46" s="62"/>
+      <c r="S46" s="62"/>
+      <c r="T46" s="62"/>
+      <c r="U46" s="62"/>
+      <c r="V46" s="63"/>
+      <c r="W46" s="51"/>
+      <c r="X46" s="62"/>
+      <c r="Y46" s="62"/>
+      <c r="Z46" s="63"/>
+      <c r="AA46" s="61"/>
+      <c r="AB46" s="62"/>
+      <c r="AC46" s="62"/>
+      <c r="AD46" s="48"/>
+      <c r="AE46" s="63"/>
+      <c r="AF46" s="61"/>
+      <c r="AG46" s="62"/>
+      <c r="AH46" s="62"/>
+      <c r="AI46" s="62"/>
+      <c r="AJ46" s="58"/>
+      <c r="AK46" s="62"/>
     </row>
     <row r="47" ht="12" customHeight="1">
-      <c r="B47" s="57"/>
-      <c r="C47" s="58"/>
-      <c r="D47" s="60"/>
-      <c r="E47" s="60"/>
-      <c r="F47" s="63"/>
-      <c r="G47" s="61"/>
-      <c r="H47" s="59"/>
-      <c r="I47" s="60"/>
-      <c r="J47" s="60"/>
-      <c r="K47" s="60"/>
-      <c r="L47" s="46"/>
-      <c r="M47" s="60"/>
-      <c r="N47" s="61"/>
-      <c r="O47" s="59"/>
-      <c r="P47" s="60"/>
-      <c r="Q47" s="60"/>
-      <c r="R47" s="60"/>
-      <c r="S47" s="60"/>
-      <c r="T47" s="60"/>
-      <c r="U47" s="60"/>
-      <c r="V47" s="61"/>
-      <c r="W47" s="49"/>
-      <c r="X47" s="60"/>
-      <c r="Y47" s="60"/>
-      <c r="Z47" s="61"/>
-      <c r="AA47" s="59"/>
-      <c r="AB47" s="60"/>
-      <c r="AC47" s="60"/>
-      <c r="AD47" s="46"/>
-      <c r="AE47" s="61"/>
-      <c r="AF47" s="59"/>
-      <c r="AG47" s="60"/>
-      <c r="AH47" s="60"/>
-      <c r="AI47" s="60"/>
-      <c r="AJ47" s="60"/>
-      <c r="AK47" s="60"/>
-      <c r="AN47" s="70" t="s">
-        <v>109</v>
-      </c>
-      <c r="AO47" s="56"/>
+      <c r="B47" s="59"/>
+      <c r="C47" s="60"/>
+      <c r="D47" s="62"/>
+      <c r="E47" s="62"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="63"/>
+      <c r="H47" s="61"/>
+      <c r="I47" s="62"/>
+      <c r="J47" s="62"/>
+      <c r="K47" s="62"/>
+      <c r="L47" s="48"/>
+      <c r="M47" s="62"/>
+      <c r="N47" s="63"/>
+      <c r="O47" s="61"/>
+      <c r="P47" s="62"/>
+      <c r="Q47" s="62"/>
+      <c r="R47" s="62"/>
+      <c r="S47" s="62"/>
+      <c r="T47" s="62"/>
+      <c r="U47" s="62"/>
+      <c r="V47" s="63"/>
+      <c r="W47" s="51"/>
+      <c r="X47" s="62"/>
+      <c r="Y47" s="62"/>
+      <c r="Z47" s="63"/>
+      <c r="AA47" s="61"/>
+      <c r="AB47" s="62"/>
+      <c r="AC47" s="62"/>
+      <c r="AD47" s="48"/>
+      <c r="AE47" s="63"/>
+      <c r="AF47" s="61"/>
+      <c r="AG47" s="62"/>
+      <c r="AH47" s="62"/>
+      <c r="AI47" s="62"/>
+      <c r="AJ47" s="62"/>
+      <c r="AK47" s="62"/>
+      <c r="AN47" s="72" t="s">
+        <v>113</v>
+      </c>
+      <c r="AO47" s="58"/>
     </row>
     <row r="48" ht="12" customHeight="1">
-      <c r="B48" s="57"/>
-      <c r="C48" s="58" t="s">
-        <v>110</v>
-      </c>
-      <c r="D48" s="60"/>
-      <c r="E48" s="60"/>
-      <c r="F48" s="63"/>
-      <c r="G48" s="61"/>
-      <c r="H48" s="59"/>
-      <c r="I48" s="60"/>
-      <c r="J48" s="60"/>
-      <c r="K48" s="60"/>
-      <c r="L48" s="46"/>
-      <c r="M48" s="60"/>
-      <c r="N48" s="61"/>
-      <c r="O48" s="59"/>
-      <c r="P48" s="60"/>
-      <c r="Q48" s="60"/>
-      <c r="R48" s="60"/>
-      <c r="S48" s="60"/>
-      <c r="T48" s="60"/>
-      <c r="U48" s="60"/>
-      <c r="V48" s="61"/>
-      <c r="W48" s="49"/>
-      <c r="X48" s="60"/>
-      <c r="Y48" s="60"/>
-      <c r="Z48" s="61"/>
-      <c r="AA48" s="59"/>
-      <c r="AB48" s="60"/>
-      <c r="AC48" s="60"/>
-      <c r="AD48" s="46"/>
-      <c r="AE48" s="61"/>
-      <c r="AF48" s="59"/>
-      <c r="AG48" s="60"/>
-      <c r="AH48" s="60"/>
-      <c r="AI48" s="60"/>
-      <c r="AJ48" s="60"/>
-      <c r="AK48" s="71"/>
-      <c r="AN48" s="70" t="s">
-        <v>111</v>
-      </c>
-      <c r="AO48" s="55"/>
+      <c r="B48" s="59"/>
+      <c r="C48" s="60" t="s">
+        <v>114</v>
+      </c>
+      <c r="D48" s="62"/>
+      <c r="E48" s="62"/>
+      <c r="F48" s="65"/>
+      <c r="G48" s="63"/>
+      <c r="H48" s="61"/>
+      <c r="I48" s="62"/>
+      <c r="J48" s="62"/>
+      <c r="K48" s="62"/>
+      <c r="L48" s="48"/>
+      <c r="M48" s="62"/>
+      <c r="N48" s="63"/>
+      <c r="O48" s="61"/>
+      <c r="P48" s="62"/>
+      <c r="Q48" s="62"/>
+      <c r="R48" s="62"/>
+      <c r="S48" s="62"/>
+      <c r="T48" s="62"/>
+      <c r="U48" s="62"/>
+      <c r="V48" s="63"/>
+      <c r="W48" s="51"/>
+      <c r="X48" s="62"/>
+      <c r="Y48" s="62"/>
+      <c r="Z48" s="63"/>
+      <c r="AA48" s="61"/>
+      <c r="AB48" s="62"/>
+      <c r="AC48" s="62"/>
+      <c r="AD48" s="48"/>
+      <c r="AE48" s="63"/>
+      <c r="AF48" s="61"/>
+      <c r="AG48" s="62"/>
+      <c r="AH48" s="62"/>
+      <c r="AI48" s="62"/>
+      <c r="AJ48" s="62"/>
+      <c r="AK48" s="73"/>
+      <c r="AN48" s="72" t="s">
+        <v>115</v>
+      </c>
+      <c r="AO48" s="57"/>
     </row>
     <row r="49" ht="12" customHeight="1">
-      <c r="B49" s="57"/>
-      <c r="C49" s="58"/>
-      <c r="D49" s="60"/>
-      <c r="E49" s="60"/>
-      <c r="F49" s="63"/>
-      <c r="G49" s="61"/>
-      <c r="H49" s="59"/>
-      <c r="I49" s="60"/>
-      <c r="J49" s="60"/>
-      <c r="K49" s="60"/>
-      <c r="L49" s="46"/>
-      <c r="M49" s="60"/>
-      <c r="N49" s="61"/>
-      <c r="O49" s="59"/>
-      <c r="P49" s="60"/>
-      <c r="Q49" s="60"/>
-      <c r="R49" s="60"/>
-      <c r="S49" s="60"/>
-      <c r="T49" s="60"/>
-      <c r="U49" s="60"/>
-      <c r="V49" s="61"/>
-      <c r="W49" s="49"/>
-      <c r="X49" s="60"/>
-      <c r="Y49" s="60"/>
-      <c r="Z49" s="61"/>
-      <c r="AA49" s="59"/>
-      <c r="AB49" s="60"/>
-      <c r="AC49" s="60"/>
-      <c r="AD49" s="46"/>
-      <c r="AE49" s="61"/>
-      <c r="AF49" s="59"/>
-      <c r="AG49" s="60"/>
-      <c r="AH49" s="60"/>
-      <c r="AI49" s="60"/>
-      <c r="AJ49" s="60"/>
-      <c r="AK49" s="60"/>
-      <c r="AN49" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="AO49" s="51"/>
+      <c r="B49" s="59"/>
+      <c r="C49" s="60"/>
+      <c r="D49" s="62"/>
+      <c r="E49" s="62"/>
+      <c r="F49" s="65"/>
+      <c r="G49" s="63"/>
+      <c r="H49" s="61"/>
+      <c r="I49" s="62"/>
+      <c r="J49" s="62"/>
+      <c r="K49" s="62"/>
+      <c r="L49" s="48"/>
+      <c r="M49" s="62"/>
+      <c r="N49" s="63"/>
+      <c r="O49" s="61"/>
+      <c r="P49" s="62"/>
+      <c r="Q49" s="62"/>
+      <c r="R49" s="62"/>
+      <c r="S49" s="62"/>
+      <c r="T49" s="62"/>
+      <c r="U49" s="62"/>
+      <c r="V49" s="63"/>
+      <c r="W49" s="51"/>
+      <c r="X49" s="62"/>
+      <c r="Y49" s="62"/>
+      <c r="Z49" s="63"/>
+      <c r="AA49" s="61"/>
+      <c r="AB49" s="62"/>
+      <c r="AC49" s="62"/>
+      <c r="AD49" s="48"/>
+      <c r="AE49" s="63"/>
+      <c r="AF49" s="61"/>
+      <c r="AG49" s="62"/>
+      <c r="AH49" s="62"/>
+      <c r="AI49" s="62"/>
+      <c r="AJ49" s="62"/>
+      <c r="AK49" s="62"/>
+      <c r="AN49" s="72" t="s">
+        <v>116</v>
+      </c>
+      <c r="AO49" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -9455,801 +9554,801 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="72"/>
+      <c r="B1" s="74"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="75" t="s">
-        <v>113</v>
-      </c>
-      <c r="E2" s="76" t="s">
-        <v>114</v>
-      </c>
-      <c r="F2" s="77" t="s">
-        <v>115</v>
-      </c>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="77" t="s">
-        <v>116</v>
-      </c>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="77" t="s">
+      <c r="B2" s="75" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="76" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="77" t="s">
         <v>117</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="77" t="s">
+      <c r="E2" s="78" t="s">
         <v>118</v>
       </c>
-      <c r="S2" s="78"/>
-      <c r="AD2" s="22"/>
+      <c r="F2" s="79" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="79" t="s">
+        <v>120</v>
+      </c>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="79" t="s">
+        <v>121</v>
+      </c>
+      <c r="O2" s="79"/>
+      <c r="P2" s="79"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="79" t="s">
+        <v>122</v>
+      </c>
+      <c r="S2" s="80"/>
+      <c r="AD2" s="24"/>
     </row>
     <row r="3">
-      <c r="B3" s="79"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="81" t="s">
-        <v>119</v>
-      </c>
-      <c r="E3" s="82">
+      <c r="B3" s="81"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="83" t="s">
+        <v>123</v>
+      </c>
+      <c r="E3" s="84">
         <v>4</v>
       </c>
-      <c r="F3" s="83">
+      <c r="F3" s="85">
         <v>1</v>
       </c>
-      <c r="G3" s="84">
+      <c r="G3" s="86">
         <v>2</v>
       </c>
-      <c r="H3" s="84">
+      <c r="H3" s="86">
         <v>3</v>
       </c>
-      <c r="I3" s="82">
+      <c r="I3" s="84">
         <v>4</v>
       </c>
-      <c r="J3" s="83">
+      <c r="J3" s="85">
         <v>1</v>
       </c>
-      <c r="K3" s="84">
+      <c r="K3" s="86">
         <v>2</v>
       </c>
-      <c r="L3" s="84">
+      <c r="L3" s="86">
         <v>3</v>
       </c>
-      <c r="M3" s="82">
+      <c r="M3" s="84">
         <v>4</v>
       </c>
-      <c r="N3" s="83">
+      <c r="N3" s="85">
         <v>1</v>
       </c>
-      <c r="O3" s="84">
+      <c r="O3" s="86">
         <v>2</v>
       </c>
-      <c r="P3" s="84">
+      <c r="P3" s="86">
         <v>3</v>
       </c>
-      <c r="Q3" s="82">
+      <c r="Q3" s="84">
         <v>4</v>
       </c>
-      <c r="R3" s="83">
+      <c r="R3" s="85">
         <v>1</v>
       </c>
-      <c r="S3" s="85">
+      <c r="S3" s="87">
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="86" t="s">
-        <v>121</v>
-      </c>
-      <c r="C4" s="74" t="s">
-        <v>122</v>
-      </c>
-      <c r="D4" s="87"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="90"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="91"/>
-      <c r="K4" s="90"/>
-      <c r="L4" s="90"/>
-      <c r="M4" s="88"/>
-      <c r="N4" s="91"/>
-      <c r="O4" s="90"/>
-      <c r="P4" s="90"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="91"/>
-      <c r="S4" s="92"/>
+      <c r="B4" s="88" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" s="76" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="89"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="92"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="92"/>
+      <c r="L4" s="92"/>
+      <c r="M4" s="90"/>
+      <c r="N4" s="93"/>
+      <c r="O4" s="92"/>
+      <c r="P4" s="92"/>
+      <c r="Q4" s="90"/>
+      <c r="R4" s="93"/>
+      <c r="S4" s="94"/>
       <c r="U4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="86"/>
-      <c r="C5" s="93"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="95"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="95"/>
-      <c r="J5" s="99"/>
-      <c r="K5" s="98"/>
-      <c r="L5" s="98"/>
-      <c r="M5" s="95"/>
-      <c r="N5" s="99"/>
-      <c r="O5" s="98"/>
-      <c r="P5" s="98"/>
-      <c r="Q5" s="95"/>
-      <c r="R5" s="99"/>
-      <c r="S5" s="100"/>
+      <c r="B5" s="88"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="96"/>
+      <c r="E5" s="97"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="97"/>
+      <c r="J5" s="101"/>
+      <c r="K5" s="100"/>
+      <c r="L5" s="100"/>
+      <c r="M5" s="97"/>
+      <c r="N5" s="101"/>
+      <c r="O5" s="100"/>
+      <c r="P5" s="100"/>
+      <c r="Q5" s="97"/>
+      <c r="R5" s="101"/>
+      <c r="S5" s="102"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="86"/>
-      <c r="C6" s="101" t="s">
-        <v>124</v>
-      </c>
-      <c r="D6" s="102"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="104"/>
-      <c r="G6" s="105"/>
-      <c r="H6" s="106"/>
-      <c r="I6" s="103"/>
-      <c r="J6" s="107"/>
-      <c r="K6" s="106"/>
-      <c r="L6" s="106"/>
-      <c r="M6" s="103"/>
-      <c r="N6" s="107"/>
-      <c r="O6" s="106"/>
-      <c r="P6" s="106"/>
-      <c r="Q6" s="103"/>
-      <c r="R6" s="107"/>
-      <c r="S6" s="108"/>
-      <c r="U6" s="109" t="s">
-        <v>125</v>
-      </c>
-      <c r="V6" s="109"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="104"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="106"/>
+      <c r="G6" s="107"/>
+      <c r="H6" s="108"/>
+      <c r="I6" s="105"/>
+      <c r="J6" s="109"/>
+      <c r="K6" s="108"/>
+      <c r="L6" s="108"/>
+      <c r="M6" s="105"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="108"/>
+      <c r="P6" s="108"/>
+      <c r="Q6" s="105"/>
+      <c r="R6" s="109"/>
+      <c r="S6" s="110"/>
+      <c r="U6" s="111" t="s">
+        <v>129</v>
+      </c>
+      <c r="V6" s="111"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="86"/>
-      <c r="C7" s="93"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="95"/>
-      <c r="F7" s="99"/>
-      <c r="G7" s="97"/>
-      <c r="H7" s="97"/>
-      <c r="I7" s="95"/>
-      <c r="J7" s="99"/>
-      <c r="K7" s="98"/>
-      <c r="L7" s="98"/>
-      <c r="M7" s="95"/>
-      <c r="N7" s="99"/>
-      <c r="O7" s="98"/>
-      <c r="P7" s="98"/>
-      <c r="Q7" s="95"/>
-      <c r="R7" s="99"/>
-      <c r="S7" s="100"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="96"/>
+      <c r="E7" s="97"/>
+      <c r="F7" s="101"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="99"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="101"/>
+      <c r="K7" s="100"/>
+      <c r="L7" s="100"/>
+      <c r="M7" s="97"/>
+      <c r="N7" s="101"/>
+      <c r="O7" s="100"/>
+      <c r="P7" s="100"/>
+      <c r="Q7" s="97"/>
+      <c r="R7" s="101"/>
+      <c r="S7" s="102"/>
       <c r="U7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="86"/>
-      <c r="C8" s="101" t="s">
-        <v>127</v>
-      </c>
-      <c r="D8" s="102"/>
-      <c r="E8" s="103"/>
-      <c r="F8" s="104"/>
-      <c r="G8" s="106"/>
-      <c r="H8" s="106"/>
-      <c r="I8" s="103"/>
-      <c r="J8" s="107"/>
-      <c r="K8" s="106"/>
-      <c r="L8" s="106"/>
-      <c r="M8" s="103"/>
-      <c r="N8" s="107"/>
-      <c r="O8" s="106"/>
-      <c r="P8" s="106"/>
-      <c r="Q8" s="103"/>
-      <c r="R8" s="107"/>
-      <c r="S8" s="108"/>
+      <c r="B8" s="88"/>
+      <c r="C8" s="103" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" s="104"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="106"/>
+      <c r="G8" s="108"/>
+      <c r="H8" s="108"/>
+      <c r="I8" s="105"/>
+      <c r="J8" s="109"/>
+      <c r="K8" s="108"/>
+      <c r="L8" s="108"/>
+      <c r="M8" s="105"/>
+      <c r="N8" s="109"/>
+      <c r="O8" s="108"/>
+      <c r="P8" s="108"/>
+      <c r="Q8" s="105"/>
+      <c r="R8" s="109"/>
+      <c r="S8" s="110"/>
       <c r="U8" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="86"/>
-      <c r="C9" s="93"/>
-      <c r="D9" s="94"/>
-      <c r="E9" s="95"/>
-      <c r="F9" s="99"/>
-      <c r="G9" s="97"/>
-      <c r="H9" s="98"/>
-      <c r="I9" s="95"/>
-      <c r="J9" s="99"/>
-      <c r="K9" s="98"/>
-      <c r="L9" s="98"/>
-      <c r="M9" s="95"/>
-      <c r="N9" s="99"/>
-      <c r="O9" s="98"/>
-      <c r="P9" s="98"/>
-      <c r="Q9" s="95"/>
-      <c r="R9" s="99"/>
-      <c r="S9" s="100"/>
+      <c r="B9" s="88"/>
+      <c r="C9" s="95"/>
+      <c r="D9" s="96"/>
+      <c r="E9" s="97"/>
+      <c r="F9" s="101"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="100"/>
+      <c r="I9" s="97"/>
+      <c r="J9" s="101"/>
+      <c r="K9" s="100"/>
+      <c r="L9" s="100"/>
+      <c r="M9" s="97"/>
+      <c r="N9" s="101"/>
+      <c r="O9" s="100"/>
+      <c r="P9" s="100"/>
+      <c r="Q9" s="97"/>
+      <c r="R9" s="101"/>
+      <c r="S9" s="102"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="86"/>
-      <c r="C10" s="101" t="s">
-        <v>129</v>
-      </c>
-      <c r="D10" s="102"/>
-      <c r="E10" s="103"/>
-      <c r="F10" s="107"/>
-      <c r="G10" s="105"/>
-      <c r="H10" s="105"/>
-      <c r="I10" s="103"/>
-      <c r="J10" s="107"/>
-      <c r="K10" s="106"/>
-      <c r="L10" s="106"/>
-      <c r="M10" s="103"/>
-      <c r="N10" s="107"/>
-      <c r="O10" s="106"/>
-      <c r="P10" s="106"/>
-      <c r="Q10" s="103"/>
-      <c r="R10" s="107"/>
-      <c r="S10" s="108"/>
+      <c r="B10" s="88"/>
+      <c r="C10" s="103" t="s">
+        <v>133</v>
+      </c>
+      <c r="D10" s="104"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="109"/>
+      <c r="G10" s="107"/>
+      <c r="H10" s="107"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="109"/>
+      <c r="K10" s="108"/>
+      <c r="L10" s="108"/>
+      <c r="M10" s="105"/>
+      <c r="N10" s="109"/>
+      <c r="O10" s="108"/>
+      <c r="P10" s="108"/>
+      <c r="Q10" s="105"/>
+      <c r="R10" s="109"/>
+      <c r="S10" s="110"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="110"/>
-      <c r="C11" s="111"/>
-      <c r="D11" s="112"/>
-      <c r="E11" s="113"/>
-      <c r="F11" s="114"/>
-      <c r="G11" s="115"/>
-      <c r="H11" s="115"/>
-      <c r="I11" s="113"/>
-      <c r="J11" s="114"/>
-      <c r="K11" s="116"/>
-      <c r="L11" s="116"/>
-      <c r="M11" s="113"/>
-      <c r="N11" s="114"/>
-      <c r="O11" s="116"/>
-      <c r="P11" s="116"/>
-      <c r="Q11" s="113"/>
-      <c r="R11" s="114"/>
-      <c r="S11" s="117"/>
+      <c r="B11" s="112"/>
+      <c r="C11" s="113"/>
+      <c r="D11" s="114"/>
+      <c r="E11" s="115"/>
+      <c r="F11" s="116"/>
+      <c r="G11" s="117"/>
+      <c r="H11" s="117"/>
+      <c r="I11" s="115"/>
+      <c r="J11" s="116"/>
+      <c r="K11" s="118"/>
+      <c r="L11" s="118"/>
+      <c r="M11" s="115"/>
+      <c r="N11" s="116"/>
+      <c r="O11" s="118"/>
+      <c r="P11" s="118"/>
+      <c r="Q11" s="115"/>
+      <c r="R11" s="116"/>
+      <c r="S11" s="119"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="73" t="s">
-        <v>130</v>
-      </c>
-      <c r="C12" s="74" t="s">
-        <v>131</v>
-      </c>
-      <c r="D12" s="87"/>
-      <c r="E12" s="88"/>
-      <c r="F12" s="91"/>
-      <c r="G12" s="90"/>
-      <c r="H12" s="118"/>
-      <c r="I12" s="119"/>
-      <c r="J12" s="91"/>
-      <c r="K12" s="90"/>
-      <c r="L12" s="90"/>
-      <c r="M12" s="88"/>
-      <c r="N12" s="91"/>
-      <c r="O12" s="90"/>
-      <c r="P12" s="90"/>
-      <c r="Q12" s="88"/>
-      <c r="R12" s="91"/>
-      <c r="S12" s="92"/>
+      <c r="B12" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="C12" s="76" t="s">
+        <v>135</v>
+      </c>
+      <c r="D12" s="89"/>
+      <c r="E12" s="90"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="92"/>
+      <c r="H12" s="120"/>
+      <c r="I12" s="121"/>
+      <c r="J12" s="93"/>
+      <c r="K12" s="92"/>
+      <c r="L12" s="92"/>
+      <c r="M12" s="90"/>
+      <c r="N12" s="93"/>
+      <c r="O12" s="92"/>
+      <c r="P12" s="92"/>
+      <c r="Q12" s="90"/>
+      <c r="R12" s="93"/>
+      <c r="S12" s="94"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="86"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="94"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="99"/>
-      <c r="G13" s="98"/>
-      <c r="H13" s="98"/>
-      <c r="I13" s="95"/>
-      <c r="J13" s="96"/>
-      <c r="K13" s="98"/>
-      <c r="L13" s="98"/>
-      <c r="M13" s="95"/>
-      <c r="N13" s="99"/>
-      <c r="O13" s="98"/>
-      <c r="P13" s="98"/>
-      <c r="Q13" s="95"/>
-      <c r="R13" s="99"/>
-      <c r="S13" s="100"/>
+      <c r="B13" s="88"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="96"/>
+      <c r="E13" s="97"/>
+      <c r="F13" s="101"/>
+      <c r="G13" s="100"/>
+      <c r="H13" s="100"/>
+      <c r="I13" s="97"/>
+      <c r="J13" s="98"/>
+      <c r="K13" s="100"/>
+      <c r="L13" s="100"/>
+      <c r="M13" s="97"/>
+      <c r="N13" s="101"/>
+      <c r="O13" s="100"/>
+      <c r="P13" s="100"/>
+      <c r="Q13" s="97"/>
+      <c r="R13" s="101"/>
+      <c r="S13" s="102"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="86"/>
-      <c r="C14" s="101" t="s">
-        <v>132</v>
-      </c>
-      <c r="D14" s="120"/>
-      <c r="E14" s="103"/>
-      <c r="F14" s="107"/>
-      <c r="G14" s="106"/>
-      <c r="H14" s="105"/>
-      <c r="I14" s="103"/>
-      <c r="J14" s="107"/>
-      <c r="K14" s="106"/>
-      <c r="L14" s="106"/>
-      <c r="M14" s="103"/>
-      <c r="N14" s="107"/>
-      <c r="O14" s="106"/>
-      <c r="P14" s="106"/>
-      <c r="Q14" s="103"/>
-      <c r="R14" s="107"/>
-      <c r="S14" s="108"/>
+      <c r="B14" s="88"/>
+      <c r="C14" s="103" t="s">
+        <v>136</v>
+      </c>
+      <c r="D14" s="122"/>
+      <c r="E14" s="105"/>
+      <c r="F14" s="109"/>
+      <c r="G14" s="108"/>
+      <c r="H14" s="107"/>
+      <c r="I14" s="105"/>
+      <c r="J14" s="109"/>
+      <c r="K14" s="108"/>
+      <c r="L14" s="108"/>
+      <c r="M14" s="105"/>
+      <c r="N14" s="109"/>
+      <c r="O14" s="108"/>
+      <c r="P14" s="108"/>
+      <c r="Q14" s="105"/>
+      <c r="R14" s="109"/>
+      <c r="S14" s="110"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="86"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="94"/>
-      <c r="E15" s="95"/>
-      <c r="F15" s="99"/>
-      <c r="G15" s="98"/>
-      <c r="H15" s="98"/>
-      <c r="I15" s="121"/>
-      <c r="J15" s="96"/>
-      <c r="K15" s="98"/>
-      <c r="L15" s="98"/>
-      <c r="M15" s="95"/>
-      <c r="N15" s="99"/>
-      <c r="O15" s="98"/>
-      <c r="P15" s="98"/>
-      <c r="Q15" s="95"/>
-      <c r="R15" s="99"/>
-      <c r="S15" s="100"/>
+      <c r="B15" s="88"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="96"/>
+      <c r="E15" s="97"/>
+      <c r="F15" s="101"/>
+      <c r="G15" s="100"/>
+      <c r="H15" s="100"/>
+      <c r="I15" s="123"/>
+      <c r="J15" s="98"/>
+      <c r="K15" s="100"/>
+      <c r="L15" s="100"/>
+      <c r="M15" s="97"/>
+      <c r="N15" s="101"/>
+      <c r="O15" s="100"/>
+      <c r="P15" s="100"/>
+      <c r="Q15" s="97"/>
+      <c r="R15" s="101"/>
+      <c r="S15" s="102"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="86"/>
-      <c r="C16" s="101" t="s">
-        <v>133</v>
-      </c>
-      <c r="D16" s="102"/>
-      <c r="E16" s="103"/>
-      <c r="F16" s="107"/>
-      <c r="G16" s="106"/>
-      <c r="H16" s="105"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="107"/>
-      <c r="K16" s="106"/>
-      <c r="L16" s="106"/>
-      <c r="M16" s="103"/>
-      <c r="N16" s="107"/>
-      <c r="O16" s="106"/>
-      <c r="P16" s="106"/>
-      <c r="Q16" s="103"/>
-      <c r="R16" s="107"/>
-      <c r="S16" s="108"/>
+      <c r="B16" s="88"/>
+      <c r="C16" s="103" t="s">
+        <v>137</v>
+      </c>
+      <c r="D16" s="104"/>
+      <c r="E16" s="105"/>
+      <c r="F16" s="109"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="107"/>
+      <c r="I16" s="124"/>
+      <c r="J16" s="109"/>
+      <c r="K16" s="108"/>
+      <c r="L16" s="108"/>
+      <c r="M16" s="105"/>
+      <c r="N16" s="109"/>
+      <c r="O16" s="108"/>
+      <c r="P16" s="108"/>
+      <c r="Q16" s="105"/>
+      <c r="R16" s="109"/>
+      <c r="S16" s="110"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="110"/>
-      <c r="C17" s="111"/>
-      <c r="D17" s="112"/>
-      <c r="E17" s="113"/>
-      <c r="F17" s="114"/>
-      <c r="G17" s="116"/>
-      <c r="H17" s="116"/>
-      <c r="I17" s="113"/>
-      <c r="J17" s="123"/>
-      <c r="K17" s="115"/>
-      <c r="L17" s="116"/>
-      <c r="M17" s="113"/>
-      <c r="N17" s="114"/>
-      <c r="O17" s="116"/>
-      <c r="P17" s="116"/>
-      <c r="Q17" s="113"/>
-      <c r="R17" s="114"/>
-      <c r="S17" s="117"/>
+      <c r="B17" s="112"/>
+      <c r="C17" s="113"/>
+      <c r="D17" s="114"/>
+      <c r="E17" s="115"/>
+      <c r="F17" s="116"/>
+      <c r="G17" s="118"/>
+      <c r="H17" s="118"/>
+      <c r="I17" s="115"/>
+      <c r="J17" s="125"/>
+      <c r="K17" s="117"/>
+      <c r="L17" s="118"/>
+      <c r="M17" s="115"/>
+      <c r="N17" s="116"/>
+      <c r="O17" s="118"/>
+      <c r="P17" s="118"/>
+      <c r="Q17" s="115"/>
+      <c r="R17" s="116"/>
+      <c r="S17" s="119"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="75" t="s">
-        <v>134</v>
-      </c>
-      <c r="C18" s="74" t="s">
-        <v>135</v>
-      </c>
-      <c r="D18" s="87"/>
-      <c r="E18" s="88"/>
-      <c r="F18" s="91"/>
-      <c r="G18" s="90"/>
-      <c r="H18" s="90"/>
-      <c r="I18" s="119"/>
-      <c r="J18" s="91"/>
-      <c r="K18" s="90"/>
-      <c r="L18" s="90"/>
-      <c r="M18" s="88"/>
-      <c r="N18" s="91"/>
-      <c r="O18" s="90"/>
-      <c r="P18" s="90"/>
-      <c r="Q18" s="88"/>
-      <c r="R18" s="91"/>
-      <c r="S18" s="92"/>
+      <c r="B18" s="77" t="s">
+        <v>138</v>
+      </c>
+      <c r="C18" s="76" t="s">
+        <v>139</v>
+      </c>
+      <c r="D18" s="89"/>
+      <c r="E18" s="90"/>
+      <c r="F18" s="93"/>
+      <c r="G18" s="92"/>
+      <c r="H18" s="92"/>
+      <c r="I18" s="121"/>
+      <c r="J18" s="93"/>
+      <c r="K18" s="92"/>
+      <c r="L18" s="92"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="93"/>
+      <c r="O18" s="92"/>
+      <c r="P18" s="92"/>
+      <c r="Q18" s="90"/>
+      <c r="R18" s="93"/>
+      <c r="S18" s="94"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="86"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="94"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="99"/>
-      <c r="G19" s="97"/>
-      <c r="H19" s="98"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="99"/>
-      <c r="K19" s="98"/>
-      <c r="L19" s="98"/>
-      <c r="M19" s="95"/>
-      <c r="N19" s="99"/>
-      <c r="O19" s="98"/>
-      <c r="P19" s="98"/>
-      <c r="Q19" s="95"/>
-      <c r="R19" s="99"/>
-      <c r="S19" s="100"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="96"/>
+      <c r="E19" s="97"/>
+      <c r="F19" s="101"/>
+      <c r="G19" s="99"/>
+      <c r="H19" s="100"/>
+      <c r="I19" s="97"/>
+      <c r="J19" s="101"/>
+      <c r="K19" s="100"/>
+      <c r="L19" s="100"/>
+      <c r="M19" s="97"/>
+      <c r="N19" s="101"/>
+      <c r="O19" s="100"/>
+      <c r="P19" s="100"/>
+      <c r="Q19" s="97"/>
+      <c r="R19" s="101"/>
+      <c r="S19" s="102"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="86"/>
-      <c r="C20" s="101" t="s">
-        <v>136</v>
-      </c>
-      <c r="D20" s="102"/>
-      <c r="E20" s="103"/>
-      <c r="F20" s="107"/>
-      <c r="G20" s="106"/>
-      <c r="H20" s="106"/>
-      <c r="I20" s="122"/>
-      <c r="J20" s="104"/>
-      <c r="K20" s="105"/>
-      <c r="L20" s="105"/>
-      <c r="M20" s="103"/>
-      <c r="N20" s="107"/>
-      <c r="O20" s="106"/>
-      <c r="P20" s="106"/>
-      <c r="Q20" s="103"/>
-      <c r="R20" s="107"/>
-      <c r="S20" s="108"/>
+      <c r="B20" s="88"/>
+      <c r="C20" s="103" t="s">
+        <v>140</v>
+      </c>
+      <c r="D20" s="104"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="109"/>
+      <c r="G20" s="108"/>
+      <c r="H20" s="108"/>
+      <c r="I20" s="124"/>
+      <c r="J20" s="106"/>
+      <c r="K20" s="107"/>
+      <c r="L20" s="107"/>
+      <c r="M20" s="105"/>
+      <c r="N20" s="109"/>
+      <c r="O20" s="108"/>
+      <c r="P20" s="108"/>
+      <c r="Q20" s="105"/>
+      <c r="R20" s="109"/>
+      <c r="S20" s="110"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="86"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="94"/>
-      <c r="E21" s="95"/>
-      <c r="F21" s="99"/>
-      <c r="G21" s="98"/>
-      <c r="H21" s="98"/>
-      <c r="I21" s="95"/>
-      <c r="J21" s="99"/>
-      <c r="K21" s="98"/>
-      <c r="L21" s="98"/>
-      <c r="M21" s="95"/>
-      <c r="N21" s="124"/>
-      <c r="O21" s="98"/>
-      <c r="P21" s="98"/>
-      <c r="Q21" s="95"/>
-      <c r="R21" s="99"/>
-      <c r="S21" s="100"/>
+      <c r="B21" s="88"/>
+      <c r="C21" s="95"/>
+      <c r="D21" s="96"/>
+      <c r="E21" s="97"/>
+      <c r="F21" s="101"/>
+      <c r="G21" s="100"/>
+      <c r="H21" s="100"/>
+      <c r="I21" s="97"/>
+      <c r="J21" s="101"/>
+      <c r="K21" s="100"/>
+      <c r="L21" s="100"/>
+      <c r="M21" s="97"/>
+      <c r="N21" s="126"/>
+      <c r="O21" s="100"/>
+      <c r="P21" s="100"/>
+      <c r="Q21" s="97"/>
+      <c r="R21" s="101"/>
+      <c r="S21" s="102"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="86"/>
-      <c r="C22" s="101" t="s">
-        <v>137</v>
-      </c>
-      <c r="D22" s="102"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="107"/>
-      <c r="G22" s="106"/>
-      <c r="H22" s="106"/>
-      <c r="I22" s="103"/>
-      <c r="J22" s="107"/>
-      <c r="K22" s="105"/>
-      <c r="L22" s="105"/>
-      <c r="M22" s="103"/>
-      <c r="N22" s="107"/>
-      <c r="O22" s="106"/>
-      <c r="P22" s="106"/>
-      <c r="Q22" s="103"/>
-      <c r="R22" s="107"/>
-      <c r="S22" s="108"/>
+      <c r="B22" s="88"/>
+      <c r="C22" s="103" t="s">
+        <v>141</v>
+      </c>
+      <c r="D22" s="104"/>
+      <c r="E22" s="105"/>
+      <c r="F22" s="109"/>
+      <c r="G22" s="108"/>
+      <c r="H22" s="108"/>
+      <c r="I22" s="105"/>
+      <c r="J22" s="109"/>
+      <c r="K22" s="107"/>
+      <c r="L22" s="107"/>
+      <c r="M22" s="105"/>
+      <c r="N22" s="109"/>
+      <c r="O22" s="108"/>
+      <c r="P22" s="108"/>
+      <c r="Q22" s="105"/>
+      <c r="R22" s="109"/>
+      <c r="S22" s="110"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="110"/>
-      <c r="C23" s="111"/>
-      <c r="D23" s="112"/>
-      <c r="E23" s="113"/>
-      <c r="F23" s="114"/>
-      <c r="G23" s="116"/>
-      <c r="H23" s="116"/>
-      <c r="I23" s="113"/>
-      <c r="J23" s="114"/>
-      <c r="K23" s="116"/>
-      <c r="L23" s="116"/>
-      <c r="M23" s="113"/>
-      <c r="N23" s="114"/>
-      <c r="O23" s="116"/>
-      <c r="P23" s="116"/>
-      <c r="Q23" s="113"/>
-      <c r="R23" s="114"/>
-      <c r="S23" s="117"/>
+      <c r="B23" s="112"/>
+      <c r="C23" s="113"/>
+      <c r="D23" s="114"/>
+      <c r="E23" s="115"/>
+      <c r="F23" s="116"/>
+      <c r="G23" s="118"/>
+      <c r="H23" s="118"/>
+      <c r="I23" s="115"/>
+      <c r="J23" s="116"/>
+      <c r="K23" s="118"/>
+      <c r="L23" s="118"/>
+      <c r="M23" s="115"/>
+      <c r="N23" s="116"/>
+      <c r="O23" s="118"/>
+      <c r="P23" s="118"/>
+      <c r="Q23" s="115"/>
+      <c r="R23" s="116"/>
+      <c r="S23" s="119"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="75" t="s">
-        <v>138</v>
-      </c>
-      <c r="C24" s="74" t="s">
-        <v>139</v>
-      </c>
-      <c r="D24" s="87"/>
-      <c r="E24" s="88"/>
-      <c r="F24" s="91"/>
-      <c r="G24" s="90"/>
-      <c r="H24" s="90"/>
-      <c r="I24" s="88"/>
-      <c r="J24" s="91"/>
-      <c r="K24" s="90"/>
-      <c r="L24" s="90"/>
-      <c r="M24" s="119"/>
-      <c r="N24" s="89"/>
-      <c r="O24" s="118"/>
-      <c r="P24" s="118"/>
-      <c r="Q24" s="88"/>
-      <c r="R24" s="91"/>
-      <c r="S24" s="92"/>
+      <c r="B24" s="77" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="76" t="s">
+        <v>143</v>
+      </c>
+      <c r="D24" s="89"/>
+      <c r="E24" s="90"/>
+      <c r="F24" s="93"/>
+      <c r="G24" s="92"/>
+      <c r="H24" s="92"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="93"/>
+      <c r="K24" s="92"/>
+      <c r="L24" s="92"/>
+      <c r="M24" s="121"/>
+      <c r="N24" s="91"/>
+      <c r="O24" s="120"/>
+      <c r="P24" s="120"/>
+      <c r="Q24" s="90"/>
+      <c r="R24" s="93"/>
+      <c r="S24" s="94"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="86"/>
-      <c r="C25" s="93"/>
-      <c r="D25" s="94"/>
-      <c r="E25" s="95"/>
-      <c r="F25" s="99"/>
-      <c r="G25" s="98"/>
-      <c r="H25" s="98"/>
-      <c r="I25" s="95"/>
-      <c r="J25" s="99"/>
-      <c r="K25" s="98"/>
-      <c r="L25" s="98"/>
-      <c r="M25" s="95"/>
-      <c r="N25" s="99"/>
-      <c r="O25" s="98"/>
-      <c r="P25" s="98"/>
-      <c r="Q25" s="95"/>
-      <c r="R25" s="99"/>
-      <c r="S25" s="100"/>
+      <c r="B25" s="88"/>
+      <c r="C25" s="95"/>
+      <c r="D25" s="96"/>
+      <c r="E25" s="97"/>
+      <c r="F25" s="101"/>
+      <c r="G25" s="100"/>
+      <c r="H25" s="100"/>
+      <c r="I25" s="97"/>
+      <c r="J25" s="101"/>
+      <c r="K25" s="100"/>
+      <c r="L25" s="100"/>
+      <c r="M25" s="97"/>
+      <c r="N25" s="101"/>
+      <c r="O25" s="100"/>
+      <c r="P25" s="100"/>
+      <c r="Q25" s="97"/>
+      <c r="R25" s="101"/>
+      <c r="S25" s="102"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="86"/>
-      <c r="C26" s="101" t="s">
-        <v>140</v>
-      </c>
-      <c r="D26" s="102"/>
-      <c r="E26" s="103"/>
-      <c r="F26" s="107"/>
-      <c r="G26" s="106"/>
-      <c r="H26" s="106"/>
-      <c r="I26" s="103"/>
-      <c r="J26" s="107"/>
-      <c r="K26" s="106"/>
-      <c r="L26" s="106"/>
-      <c r="M26" s="103"/>
-      <c r="N26" s="107"/>
-      <c r="O26" s="105"/>
-      <c r="P26" s="105"/>
-      <c r="Q26" s="103"/>
-      <c r="R26" s="107"/>
-      <c r="S26" s="108"/>
+      <c r="B26" s="88"/>
+      <c r="C26" s="103" t="s">
+        <v>144</v>
+      </c>
+      <c r="D26" s="104"/>
+      <c r="E26" s="105"/>
+      <c r="F26" s="109"/>
+      <c r="G26" s="108"/>
+      <c r="H26" s="108"/>
+      <c r="I26" s="105"/>
+      <c r="J26" s="109"/>
+      <c r="K26" s="108"/>
+      <c r="L26" s="108"/>
+      <c r="M26" s="105"/>
+      <c r="N26" s="109"/>
+      <c r="O26" s="107"/>
+      <c r="P26" s="107"/>
+      <c r="Q26" s="105"/>
+      <c r="R26" s="109"/>
+      <c r="S26" s="110"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="86"/>
-      <c r="C27" s="93"/>
-      <c r="D27" s="94"/>
-      <c r="E27" s="95"/>
-      <c r="F27" s="99"/>
-      <c r="G27" s="98"/>
-      <c r="H27" s="98"/>
-      <c r="I27" s="95"/>
-      <c r="J27" s="99"/>
-      <c r="K27" s="98"/>
-      <c r="L27" s="98"/>
-      <c r="M27" s="95"/>
-      <c r="N27" s="99"/>
-      <c r="O27" s="98"/>
-      <c r="P27" s="98"/>
-      <c r="Q27" s="95"/>
-      <c r="R27" s="99"/>
-      <c r="S27" s="100"/>
+      <c r="B27" s="88"/>
+      <c r="C27" s="95"/>
+      <c r="D27" s="96"/>
+      <c r="E27" s="97"/>
+      <c r="F27" s="101"/>
+      <c r="G27" s="100"/>
+      <c r="H27" s="100"/>
+      <c r="I27" s="97"/>
+      <c r="J27" s="101"/>
+      <c r="K27" s="100"/>
+      <c r="L27" s="100"/>
+      <c r="M27" s="97"/>
+      <c r="N27" s="101"/>
+      <c r="O27" s="100"/>
+      <c r="P27" s="100"/>
+      <c r="Q27" s="97"/>
+      <c r="R27" s="101"/>
+      <c r="S27" s="102"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="86"/>
-      <c r="C28" s="101" t="s">
-        <v>141</v>
-      </c>
-      <c r="D28" s="102"/>
-      <c r="E28" s="103"/>
-      <c r="F28" s="107"/>
-      <c r="G28" s="106"/>
-      <c r="H28" s="106"/>
-      <c r="I28" s="103"/>
-      <c r="J28" s="107"/>
-      <c r="K28" s="106"/>
-      <c r="L28" s="106"/>
-      <c r="M28" s="103"/>
-      <c r="N28" s="107"/>
-      <c r="O28" s="106"/>
-      <c r="P28" s="105"/>
-      <c r="Q28" s="122"/>
-      <c r="R28" s="107"/>
-      <c r="S28" s="108"/>
+      <c r="B28" s="88"/>
+      <c r="C28" s="103" t="s">
+        <v>145</v>
+      </c>
+      <c r="D28" s="104"/>
+      <c r="E28" s="105"/>
+      <c r="F28" s="109"/>
+      <c r="G28" s="108"/>
+      <c r="H28" s="108"/>
+      <c r="I28" s="105"/>
+      <c r="J28" s="109"/>
+      <c r="K28" s="108"/>
+      <c r="L28" s="108"/>
+      <c r="M28" s="105"/>
+      <c r="N28" s="109"/>
+      <c r="O28" s="108"/>
+      <c r="P28" s="107"/>
+      <c r="Q28" s="124"/>
+      <c r="R28" s="109"/>
+      <c r="S28" s="110"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="86"/>
-      <c r="C29" s="80"/>
-      <c r="D29" s="125"/>
-      <c r="E29" s="126"/>
-      <c r="F29" s="127"/>
-      <c r="G29" s="128"/>
-      <c r="H29" s="129"/>
-      <c r="I29" s="126"/>
-      <c r="J29" s="127"/>
-      <c r="K29" s="128"/>
-      <c r="L29" s="129"/>
-      <c r="M29" s="126"/>
-      <c r="N29" s="130"/>
-      <c r="O29" s="129"/>
-      <c r="P29" s="128"/>
-      <c r="Q29" s="126"/>
-      <c r="R29" s="127"/>
-      <c r="S29" s="131"/>
+      <c r="B29" s="88"/>
+      <c r="C29" s="82"/>
+      <c r="D29" s="127"/>
+      <c r="E29" s="128"/>
+      <c r="F29" s="129"/>
+      <c r="G29" s="130"/>
+      <c r="H29" s="131"/>
+      <c r="I29" s="128"/>
+      <c r="J29" s="129"/>
+      <c r="K29" s="130"/>
+      <c r="L29" s="131"/>
+      <c r="M29" s="128"/>
+      <c r="N29" s="132"/>
+      <c r="O29" s="131"/>
+      <c r="P29" s="130"/>
+      <c r="Q29" s="128"/>
+      <c r="R29" s="129"/>
+      <c r="S29" s="133"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="132" t="s">
+      <c r="B30" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="133" t="s">
-        <v>85</v>
-      </c>
-      <c r="D30" s="87"/>
-      <c r="E30" s="134"/>
-      <c r="F30" s="135"/>
-      <c r="G30" s="135"/>
-      <c r="H30" s="136"/>
-      <c r="I30" s="137"/>
-      <c r="J30" s="135"/>
-      <c r="K30" s="135"/>
-      <c r="L30" s="136"/>
-      <c r="M30" s="137"/>
-      <c r="N30" s="135"/>
-      <c r="O30" s="136"/>
-      <c r="P30" s="135"/>
-      <c r="Q30" s="137"/>
-      <c r="R30" s="135"/>
-      <c r="S30" s="138"/>
+      <c r="C30" s="135" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" s="89"/>
+      <c r="E30" s="136"/>
+      <c r="F30" s="137"/>
+      <c r="G30" s="137"/>
+      <c r="H30" s="138"/>
+      <c r="I30" s="139"/>
+      <c r="J30" s="137"/>
+      <c r="K30" s="137"/>
+      <c r="L30" s="138"/>
+      <c r="M30" s="139"/>
+      <c r="N30" s="137"/>
+      <c r="O30" s="138"/>
+      <c r="P30" s="137"/>
+      <c r="Q30" s="139"/>
+      <c r="R30" s="137"/>
+      <c r="S30" s="140"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="139"/>
-      <c r="C31" s="140"/>
-      <c r="D31" s="94"/>
-      <c r="E31" s="141"/>
-      <c r="F31" s="142"/>
-      <c r="G31" s="142"/>
-      <c r="H31" s="143"/>
-      <c r="I31" s="144"/>
-      <c r="J31" s="142"/>
-      <c r="K31" s="145"/>
-      <c r="L31" s="143"/>
-      <c r="M31" s="144"/>
-      <c r="N31" s="142"/>
-      <c r="O31" s="143"/>
-      <c r="P31" s="142"/>
-      <c r="Q31" s="144"/>
-      <c r="R31" s="142"/>
-      <c r="S31" s="100"/>
+      <c r="B31" s="141"/>
+      <c r="C31" s="142"/>
+      <c r="D31" s="96"/>
+      <c r="E31" s="143"/>
+      <c r="F31" s="144"/>
+      <c r="G31" s="144"/>
+      <c r="H31" s="145"/>
+      <c r="I31" s="146"/>
+      <c r="J31" s="144"/>
+      <c r="K31" s="147"/>
+      <c r="L31" s="145"/>
+      <c r="M31" s="146"/>
+      <c r="N31" s="144"/>
+      <c r="O31" s="145"/>
+      <c r="P31" s="144"/>
+      <c r="Q31" s="146"/>
+      <c r="R31" s="144"/>
+      <c r="S31" s="102"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="139"/>
-      <c r="C32" s="140" t="s">
+      <c r="B32" s="141"/>
+      <c r="C32" s="142" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="102"/>
-      <c r="E32" s="146"/>
-      <c r="F32" s="147"/>
-      <c r="G32" s="147"/>
-      <c r="H32" s="148"/>
-      <c r="I32" s="149"/>
-      <c r="J32" s="147"/>
-      <c r="K32" s="147"/>
-      <c r="L32" s="148"/>
-      <c r="M32" s="149"/>
-      <c r="N32" s="147"/>
-      <c r="O32" s="148"/>
-      <c r="P32" s="147"/>
-      <c r="Q32" s="149"/>
-      <c r="R32" s="147"/>
-      <c r="S32" s="150"/>
+      <c r="D32" s="104"/>
+      <c r="E32" s="148"/>
+      <c r="F32" s="149"/>
+      <c r="G32" s="149"/>
+      <c r="H32" s="150"/>
+      <c r="I32" s="151"/>
+      <c r="J32" s="149"/>
+      <c r="K32" s="149"/>
+      <c r="L32" s="150"/>
+      <c r="M32" s="151"/>
+      <c r="N32" s="149"/>
+      <c r="O32" s="150"/>
+      <c r="P32" s="149"/>
+      <c r="Q32" s="151"/>
+      <c r="R32" s="149"/>
+      <c r="S32" s="152"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="139"/>
-      <c r="C33" s="140"/>
-      <c r="D33" s="94"/>
-      <c r="E33" s="141"/>
-      <c r="F33" s="145"/>
-      <c r="G33" s="142"/>
-      <c r="H33" s="151"/>
-      <c r="I33" s="152"/>
-      <c r="J33" s="142"/>
-      <c r="K33" s="145"/>
-      <c r="L33" s="143"/>
-      <c r="M33" s="144"/>
-      <c r="N33" s="142"/>
-      <c r="O33" s="143"/>
-      <c r="P33" s="142"/>
-      <c r="Q33" s="144"/>
-      <c r="R33" s="142"/>
-      <c r="S33" s="100"/>
+      <c r="B33" s="141"/>
+      <c r="C33" s="142"/>
+      <c r="D33" s="96"/>
+      <c r="E33" s="143"/>
+      <c r="F33" s="147"/>
+      <c r="G33" s="144"/>
+      <c r="H33" s="153"/>
+      <c r="I33" s="154"/>
+      <c r="J33" s="144"/>
+      <c r="K33" s="147"/>
+      <c r="L33" s="145"/>
+      <c r="M33" s="146"/>
+      <c r="N33" s="144"/>
+      <c r="O33" s="145"/>
+      <c r="P33" s="144"/>
+      <c r="Q33" s="146"/>
+      <c r="R33" s="144"/>
+      <c r="S33" s="102"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="139"/>
-      <c r="C34" s="93" t="s">
-        <v>142</v>
-      </c>
-      <c r="D34" s="125"/>
-      <c r="E34" s="153"/>
-      <c r="F34" s="154"/>
-      <c r="G34" s="154"/>
-      <c r="H34" s="155"/>
-      <c r="I34" s="156"/>
-      <c r="J34" s="154"/>
-      <c r="K34" s="154"/>
-      <c r="L34" s="155"/>
-      <c r="M34" s="156"/>
-      <c r="N34" s="154"/>
-      <c r="O34" s="155"/>
-      <c r="P34" s="154"/>
-      <c r="Q34" s="156"/>
-      <c r="R34" s="154"/>
-      <c r="S34" s="157"/>
-      <c r="U34" s="158"/>
-      <c r="V34" s="159" t="s">
-        <v>143</v>
+      <c r="B34" s="141"/>
+      <c r="C34" s="95" t="s">
+        <v>146</v>
+      </c>
+      <c r="D34" s="127"/>
+      <c r="E34" s="155"/>
+      <c r="F34" s="156"/>
+      <c r="G34" s="156"/>
+      <c r="H34" s="157"/>
+      <c r="I34" s="158"/>
+      <c r="J34" s="156"/>
+      <c r="K34" s="156"/>
+      <c r="L34" s="157"/>
+      <c r="M34" s="158"/>
+      <c r="N34" s="156"/>
+      <c r="O34" s="157"/>
+      <c r="P34" s="156"/>
+      <c r="Q34" s="158"/>
+      <c r="R34" s="156"/>
+      <c r="S34" s="159"/>
+      <c r="U34" s="160"/>
+      <c r="V34" s="161" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="160"/>
-      <c r="C35" s="161"/>
-      <c r="D35" s="112"/>
-      <c r="E35" s="162"/>
-      <c r="F35" s="163"/>
-      <c r="G35" s="163"/>
-      <c r="H35" s="164"/>
-      <c r="I35" s="165"/>
-      <c r="J35" s="163"/>
-      <c r="K35" s="163"/>
-      <c r="L35" s="164"/>
-      <c r="M35" s="165"/>
-      <c r="N35" s="163"/>
-      <c r="O35" s="164"/>
-      <c r="P35" s="163"/>
-      <c r="Q35" s="165"/>
-      <c r="R35" s="163"/>
-      <c r="S35" s="117"/>
-      <c r="U35" s="166"/>
-      <c r="V35" s="167" t="s">
-        <v>144</v>
+      <c r="B35" s="162"/>
+      <c r="C35" s="163"/>
+      <c r="D35" s="114"/>
+      <c r="E35" s="164"/>
+      <c r="F35" s="165"/>
+      <c r="G35" s="165"/>
+      <c r="H35" s="166"/>
+      <c r="I35" s="167"/>
+      <c r="J35" s="165"/>
+      <c r="K35" s="165"/>
+      <c r="L35" s="166"/>
+      <c r="M35" s="167"/>
+      <c r="N35" s="165"/>
+      <c r="O35" s="166"/>
+      <c r="P35" s="165"/>
+      <c r="Q35" s="167"/>
+      <c r="R35" s="165"/>
+      <c r="S35" s="119"/>
+      <c r="U35" s="168"/>
+      <c r="V35" s="169" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/HoferL-JournalPlanif-M5.xlsx
+++ b/Documentation/HoferL-JournalPlanif-M5.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="150">
   <si>
     <t>date</t>
   </si>
@@ -223,7 +223,10 @@
     <t xml:space="preserve">Documentation des différents fichiers (code) du projet. </t>
   </si>
   <si>
-    <t xml:space="preserve">Documentation des ressources globale et de la page paramètres.</t>
+    <t xml:space="preserve">Documentation des ressources globale et de la page paramètres. Relecture et correction du document.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modification de l'aboressance du projet</t>
   </si>
   <si>
     <t>Phases</t>
@@ -1450,7 +1453,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="169">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1489,9 +1492,6 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4305,8 +4305,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E34">
-  <autoFilter ref="B2:E34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E35">
+  <autoFilter ref="B2:E35"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="I3" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.040000000000000001</v>
+        <v>3.9735099337748346e-002</v>
       </c>
       <c r="J3" s="11" t="str" cm="1">
         <f t="array" ref="J3:J9">_xlfn._xlws.FILTER(G3:G10,H3:H10&gt;0)</f>
@@ -4885,7 +4885,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="5">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>8</v>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="I4" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.040000000000000001</v>
+        <v>3.9735099337748346e-002</v>
       </c>
       <c r="J4" s="3" t="str">
         <f/>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="I5" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.080000000000000002</v>
+        <v>7.9470198675496692e-002</v>
       </c>
       <c r="J5" s="3" t="str">
         <f/>
@@ -4951,7 +4951,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="5">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>8</v>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="I6" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.22666666666666666</v>
+        <v>0.2251655629139073</v>
       </c>
       <c r="J6" s="3" t="str">
         <f/>
@@ -4984,7 +4984,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="5">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>8</v>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="I7" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.40666666666666668</v>
+        <v>0.40397350993377484</v>
       </c>
       <c r="J7" s="3" t="str">
         <f/>
@@ -5030,11 +5030,11 @@
       </c>
       <c r="H8" s="9">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="I8" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.20000000000000001</v>
+        <v>0.20529801324503311</v>
       </c>
       <c r="J8" s="3" t="str">
         <f/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="K8" s="12">
         <f/>
-        <v>15</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="9">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="I9" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.0066666666666666671</v>
+        <v>6.6225165562913907e-003</v>
       </c>
       <c r="J9" s="3" t="str">
         <f/>
@@ -5083,7 +5083,7 @@
         <v>22</v>
       </c>
       <c r="C10" s="5">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>12</v>
@@ -5110,7 +5110,7 @@
         <v>22</v>
       </c>
       <c r="C11" s="5">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>12</v>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="H11" s="9">
         <f>SUM(H3:H10)</f>
-        <v>75</v>
+        <v>75.5</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -5133,7 +5133,7 @@
         <v>22</v>
       </c>
       <c r="C12" s="5">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>10</v>
@@ -5148,7 +5148,7 @@
         <v>22</v>
       </c>
       <c r="C13" s="5">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>12</v>
@@ -5163,7 +5163,7 @@
         <v>29</v>
       </c>
       <c r="C14" s="5">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>12</v>
@@ -5219,7 +5219,7 @@
         <v>35</v>
       </c>
       <c r="C18" s="5">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>10</v>
@@ -5233,7 +5233,7 @@
         <v>37</v>
       </c>
       <c r="C19" s="5">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>12</v>
@@ -5247,7 +5247,7 @@
         <v>39</v>
       </c>
       <c r="C20" s="5">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>19</v>
@@ -5261,7 +5261,7 @@
         <v>39</v>
       </c>
       <c r="C21" s="5">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>15</v>
@@ -5289,7 +5289,7 @@
         <v>43</v>
       </c>
       <c r="C23" s="5">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>15</v>
@@ -5303,7 +5303,7 @@
         <v>45</v>
       </c>
       <c r="C24" s="5">
-        <v>0.0625</v>
+        <v>6.25e-002</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>15</v>
@@ -5345,7 +5345,7 @@
         <v>49</v>
       </c>
       <c r="C27" s="5">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>12</v>
@@ -5359,7 +5359,7 @@
         <v>52</v>
       </c>
       <c r="C28" s="5">
-        <v>0.0625</v>
+        <v>6.25e-002</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>15</v>
@@ -5396,12 +5396,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" ht="42.75">
+    <row r="31" ht="28.5">
       <c r="B31" s="4">
         <v>46087</v>
       </c>
       <c r="C31" s="5">
-        <v>0.020833333333333332</v>
+        <v>2.0833333333333332e-002</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>21</v>
@@ -5429,34 +5429,42 @@
         <v>46091</v>
       </c>
       <c r="C33" s="5">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E33" s="16" t="s">
+      <c r="E33" s="7" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="28.5">
       <c r="B34" s="4">
         <v>46091</v>
       </c>
       <c r="C34" s="5">
         <v>0.10416666666666667</v>
       </c>
-      <c r="D34" s="17" t="s">
+      <c r="D34" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="16" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="4"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="7"/>
+      <c r="B35" s="4">
+        <v>46091</v>
+      </c>
+      <c r="C35" s="5">
+        <v>2.0833333333333332e-002</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="36">
       <c r="B36" s="4"/>
@@ -5537,163 +5545,163 @@
       <c r="E48" s="7"/>
     </row>
     <row r="49">
-      <c r="B49" s="18"/>
+      <c r="B49" s="17"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
     </row>
     <row r="50">
-      <c r="B50" s="18"/>
+      <c r="B50" s="17"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
     </row>
     <row r="51">
-      <c r="B51" s="18"/>
+      <c r="B51" s="17"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
     </row>
     <row r="52">
-      <c r="B52" s="18"/>
+      <c r="B52" s="17"/>
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
     </row>
     <row r="53">
-      <c r="B53" s="18"/>
+      <c r="B53" s="17"/>
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
     </row>
     <row r="54">
-      <c r="B54" s="18"/>
+      <c r="B54" s="17"/>
       <c r="C54" s="6"/>
       <c r="D54" s="6"/>
       <c r="E54" s="6"/>
     </row>
     <row r="55">
-      <c r="B55" s="18"/>
+      <c r="B55" s="17"/>
       <c r="C55" s="6"/>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
     </row>
     <row r="56">
-      <c r="B56" s="18"/>
+      <c r="B56" s="17"/>
       <c r="C56" s="6"/>
       <c r="D56" s="6"/>
       <c r="E56" s="6"/>
     </row>
     <row r="57">
-      <c r="B57" s="18"/>
+      <c r="B57" s="17"/>
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
       <c r="E57" s="6"/>
     </row>
     <row r="58">
-      <c r="B58" s="18"/>
+      <c r="B58" s="17"/>
       <c r="C58" s="6"/>
       <c r="D58" s="6"/>
       <c r="E58" s="6"/>
     </row>
     <row r="59">
-      <c r="B59" s="18"/>
+      <c r="B59" s="17"/>
       <c r="C59" s="6"/>
       <c r="D59" s="6"/>
       <c r="E59" s="6"/>
     </row>
     <row r="60">
-      <c r="B60" s="18"/>
+      <c r="B60" s="17"/>
       <c r="C60" s="6"/>
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
     </row>
     <row r="61">
-      <c r="B61" s="18"/>
+      <c r="B61" s="17"/>
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
     </row>
     <row r="62">
-      <c r="B62" s="18"/>
+      <c r="B62" s="17"/>
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
     </row>
     <row r="63">
-      <c r="B63" s="18"/>
+      <c r="B63" s="17"/>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
     </row>
     <row r="64">
-      <c r="B64" s="18"/>
+      <c r="B64" s="17"/>
       <c r="C64" s="6"/>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
     </row>
     <row r="65">
-      <c r="B65" s="18"/>
+      <c r="B65" s="17"/>
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
     </row>
     <row r="66">
-      <c r="B66" s="18"/>
+      <c r="B66" s="17"/>
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
     </row>
     <row r="67">
-      <c r="B67" s="18"/>
+      <c r="B67" s="17"/>
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
     </row>
     <row r="68">
-      <c r="B68" s="18"/>
+      <c r="B68" s="17"/>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
     </row>
     <row r="69">
-      <c r="B69" s="18"/>
+      <c r="B69" s="17"/>
       <c r="C69" s="6"/>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
     </row>
     <row r="70">
-      <c r="B70" s="18"/>
+      <c r="B70" s="17"/>
       <c r="C70" s="6"/>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
     </row>
     <row r="71">
-      <c r="B71" s="18"/>
+      <c r="B71" s="17"/>
       <c r="C71" s="6"/>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
     </row>
     <row r="72">
-      <c r="B72" s="18"/>
+      <c r="B72" s="17"/>
       <c r="C72" s="6"/>
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
     </row>
     <row r="73">
-      <c r="B73" s="18"/>
+      <c r="B73" s="17"/>
       <c r="C73" s="6"/>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
     </row>
     <row r="74">
-      <c r="B74" s="18"/>
+      <c r="B74" s="17"/>
       <c r="C74" s="6"/>
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
     </row>
     <row r="75">
-      <c r="B75" s="18"/>
+      <c r="B75" s="17"/>
       <c r="C75" s="6"/>
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
@@ -5750,7 +5758,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00460070-00E0-41C0-BBEB-00B20011005C}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00FB0068-0060-4094-95D0-00EB00B100D6}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -5766,7 +5774,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="3" max="3" style="19" width="5.6640625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" style="18" width="5.6640625"/>
     <col bestFit="1" customWidth="1" min="4" max="4" width="12.21875"/>
     <col bestFit="1" customWidth="1" min="5" max="5" width="9.5546875"/>
     <col bestFit="1" customWidth="1" min="6" max="6" width="11.109375"/>
@@ -5782,1671 +5790,1671 @@
       <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="str" cm="1">
+      <c r="A2" s="19" t="str" cm="1">
         <f t="array" ref="A2:A18">_xlfn.UNIQUE(Journal[date])</f>
         <v>20.01.2026</v>
       </c>
-      <c r="B2" s="21">
+      <c r="B2" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A2,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C2" s="21"/>
+      <c r="C2" s="20"/>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="str">
+      <c r="A3" s="19" t="str">
         <f/>
         <v>27.01.2026</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="str">
+      <c r="A4" s="19" t="str">
         <f/>
         <v>30.01.2026</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C4"/>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="str">
+      <c r="A5" s="19" t="str">
         <f/>
         <v>03.02.2026</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0.25</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="str">
+      <c r="A6" s="19" t="str">
         <f/>
         <v>04.02.2026</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="str">
+      <c r="A7" s="19" t="str">
         <f/>
         <v>06.02.2026</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C7"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="str">
+      <c r="A8" s="19" t="str">
         <f/>
         <v>08.02.2026</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="str">
+      <c r="A9" s="19" t="str">
         <f/>
         <v>09.02.2026</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="str">
+      <c r="A10" s="19" t="str">
         <f/>
         <v>10.02.2026</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="str">
+      <c r="A11" s="19" t="str">
         <f/>
         <v>12.02.2026</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="str">
+      <c r="A12" s="19" t="str">
         <f/>
         <v>13.02.2026</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
-        <v>0.0625</v>
+        <v>6.25e-002</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="str">
+      <c r="A13" s="19" t="str">
         <f/>
         <v>24.02.2026</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0.125</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="str">
+      <c r="A14" s="19" t="str">
         <f/>
         <v>03.03.2026</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="str">
+      <c r="A15" s="19" t="str">
         <f/>
         <v>05.03.2026</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="20">
+      <c r="A16" s="19">
         <f/>
         <v>46087</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="20">
+      <c r="A17" s="19">
         <f/>
         <v>46088</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0.25</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="20">
+      <c r="A18" s="19">
         <f/>
         <v>46091</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="20">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
-        <v>0.1875</v>
+        <v>0.20833333333333334</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="20"/>
+      <c r="A19" s="19"/>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="20"/>
+      <c r="A20" s="19"/>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="20"/>
+      <c r="A21" s="19"/>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="20"/>
+      <c r="A22" s="19"/>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="20"/>
+      <c r="A23" s="19"/>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="20"/>
+      <c r="A24" s="19"/>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="20"/>
+      <c r="A25" s="19"/>
       <c r="C25"/>
-      <c r="F25" s="22"/>
+      <c r="F25" s="21"/>
     </row>
     <row r="26">
-      <c r="A26" s="20"/>
-      <c r="C26" s="23">
+      <c r="A26" s="19"/>
+      <c r="C26" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20"/>
-      <c r="C27" s="23">
+      <c r="A27" s="19"/>
+      <c r="C27" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20"/>
-      <c r="C28" s="23">
+      <c r="A28" s="19"/>
+      <c r="C28" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="20"/>
-      <c r="C29" s="23">
+      <c r="A29" s="19"/>
+      <c r="C29" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="20"/>
-      <c r="C30" s="23">
+      <c r="A30" s="19"/>
+      <c r="C30" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20"/>
-      <c r="C31" s="23">
+      <c r="A31" s="19"/>
+      <c r="C31" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="20"/>
-      <c r="C32" s="23">
+      <c r="A32" s="19"/>
+      <c r="C32" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="20"/>
-      <c r="C33" s="23">
+      <c r="A33" s="19"/>
+      <c r="C33" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20"/>
-      <c r="C34" s="23">
+      <c r="A34" s="19"/>
+      <c r="C34" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20"/>
-      <c r="C35" s="23">
+      <c r="A35" s="19"/>
+      <c r="C35" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="20"/>
-      <c r="C36" s="23">
+      <c r="A36" s="19"/>
+      <c r="C36" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="20"/>
-      <c r="C37" s="23">
+      <c r="A37" s="19"/>
+      <c r="C37" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="20"/>
-      <c r="C38" s="23">
+      <c r="A38" s="19"/>
+      <c r="C38" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="20"/>
-      <c r="C39" s="23">
+      <c r="A39" s="19"/>
+      <c r="C39" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="20"/>
-      <c r="B40" s="21" t="str">
+      <c r="A40" s="19"/>
+      <c r="B40" s="20" t="str">
         <f t="shared" ref="B40:B103" si="0">IF(C40&gt;0,C40,"")</f>
         <v/>
       </c>
-      <c r="C40" s="23">
+      <c r="C40" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="20"/>
-      <c r="B41" s="21" t="str">
+      <c r="A41" s="19"/>
+      <c r="B41" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="23">
+      <c r="C41" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="24"/>
-      <c r="B42" s="21" t="str">
+      <c r="A42" s="23"/>
+      <c r="B42" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="23">
+      <c r="C42" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="24"/>
-      <c r="B43" s="21" t="str">
+      <c r="A43" s="23"/>
+      <c r="B43" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="23">
+      <c r="C43" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="24"/>
-      <c r="B44" s="21" t="str">
+      <c r="A44" s="23"/>
+      <c r="B44" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="23">
+      <c r="C44" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="24"/>
-      <c r="B45" s="21" t="str">
+      <c r="A45" s="23"/>
+      <c r="B45" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="23">
+      <c r="C45" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="24"/>
-      <c r="B46" s="21" t="str">
+      <c r="A46" s="23"/>
+      <c r="B46" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="23">
+      <c r="C46" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="25"/>
-      <c r="B47" s="21" t="str">
+      <c r="A47" s="24"/>
+      <c r="B47" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="23">
+      <c r="C47" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="25"/>
-      <c r="B48" s="21" t="str">
+      <c r="A48" s="24"/>
+      <c r="B48" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="23">
+      <c r="C48" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="25"/>
-      <c r="B49" s="21" t="str">
+      <c r="A49" s="24"/>
+      <c r="B49" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C49" s="23">
+      <c r="C49" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="25"/>
-      <c r="B50" s="21" t="str">
+      <c r="A50" s="24"/>
+      <c r="B50" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C50" s="23">
+      <c r="C50" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="25"/>
-      <c r="B51" s="21" t="str">
+      <c r="A51" s="24"/>
+      <c r="B51" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C51" s="23">
+      <c r="C51" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="25"/>
-      <c r="B52" s="21" t="str">
+      <c r="A52" s="24"/>
+      <c r="B52" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C52" s="23">
+      <c r="C52" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="25"/>
-      <c r="B53" s="21" t="str">
+      <c r="A53" s="24"/>
+      <c r="B53" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C53" s="23">
+      <c r="C53" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="25"/>
-      <c r="B54" s="21" t="str">
+      <c r="A54" s="24"/>
+      <c r="B54" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C54" s="23">
+      <c r="C54" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="25"/>
-      <c r="B55" s="21" t="str">
+      <c r="A55" s="24"/>
+      <c r="B55" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C55" s="23">
+      <c r="C55" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="25"/>
-      <c r="B56" s="21" t="str">
+      <c r="A56" s="24"/>
+      <c r="B56" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C56" s="23">
+      <c r="C56" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="25"/>
-      <c r="B57" s="21" t="str">
+      <c r="A57" s="24"/>
+      <c r="B57" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C57" s="23">
+      <c r="C57" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="25"/>
-      <c r="B58" s="21" t="str">
+      <c r="A58" s="24"/>
+      <c r="B58" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C58" s="23">
+      <c r="C58" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="25"/>
-      <c r="B59" s="21" t="str">
+      <c r="A59" s="24"/>
+      <c r="B59" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C59" s="23">
+      <c r="C59" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="25"/>
-      <c r="B60" s="21" t="str">
+      <c r="A60" s="24"/>
+      <c r="B60" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C60" s="23">
+      <c r="C60" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="25"/>
-      <c r="B61" s="21" t="str">
+      <c r="A61" s="24"/>
+      <c r="B61" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C61" s="23">
+      <c r="C61" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="25"/>
-      <c r="B62" s="21" t="str">
+      <c r="A62" s="24"/>
+      <c r="B62" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C62" s="23">
+      <c r="C62" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="25"/>
-      <c r="B63" s="21" t="str">
+      <c r="A63" s="24"/>
+      <c r="B63" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C63" s="23">
+      <c r="C63" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="25"/>
-      <c r="B64" s="21" t="str">
+      <c r="A64" s="24"/>
+      <c r="B64" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C64" s="23">
+      <c r="C64" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="25"/>
-      <c r="B65" s="21" t="str">
+      <c r="A65" s="24"/>
+      <c r="B65" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C65" s="23">
+      <c r="C65" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="25"/>
-      <c r="B66" s="21" t="str">
+      <c r="A66" s="24"/>
+      <c r="B66" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C66" s="23">
+      <c r="C66" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="25"/>
-      <c r="B67" s="21" t="str">
+      <c r="A67" s="24"/>
+      <c r="B67" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C67" s="23">
+      <c r="C67" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="25"/>
-      <c r="B68" s="21" t="str">
+      <c r="A68" s="24"/>
+      <c r="B68" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C68" s="23">
+      <c r="C68" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="25"/>
-      <c r="B69" s="21" t="str">
+      <c r="A69" s="24"/>
+      <c r="B69" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C69" s="23">
+      <c r="C69" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="25"/>
-      <c r="B70" s="21" t="str">
+      <c r="A70" s="24"/>
+      <c r="B70" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C70" s="23">
+      <c r="C70" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="25"/>
-      <c r="B71" s="21" t="str">
+      <c r="A71" s="24"/>
+      <c r="B71" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C71" s="23">
+      <c r="C71" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="25"/>
-      <c r="B72" s="21" t="str">
+      <c r="A72" s="24"/>
+      <c r="B72" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C72" s="23">
+      <c r="C72" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="25"/>
-      <c r="B73" s="21" t="str">
+      <c r="A73" s="24"/>
+      <c r="B73" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C73" s="23">
+      <c r="C73" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="25"/>
-      <c r="B74" s="21" t="str">
+      <c r="A74" s="24"/>
+      <c r="B74" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C74" s="23">
+      <c r="C74" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="25"/>
-      <c r="B75" s="21" t="str">
+      <c r="A75" s="24"/>
+      <c r="B75" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C75" s="23">
+      <c r="C75" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="25"/>
-      <c r="B76" s="21" t="str">
+      <c r="A76" s="24"/>
+      <c r="B76" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C76" s="23">
+      <c r="C76" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="25"/>
-      <c r="B77" s="21" t="str">
+      <c r="A77" s="24"/>
+      <c r="B77" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C77" s="23">
+      <c r="C77" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="25"/>
-      <c r="B78" s="21" t="str">
+      <c r="A78" s="24"/>
+      <c r="B78" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C78" s="23">
+      <c r="C78" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="25"/>
-      <c r="B79" s="21" t="str">
+      <c r="A79" s="24"/>
+      <c r="B79" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C79" s="23">
+      <c r="C79" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="25"/>
-      <c r="B80" s="21" t="str">
+      <c r="A80" s="24"/>
+      <c r="B80" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C80" s="23">
+      <c r="C80" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="25"/>
-      <c r="B81" s="21" t="str">
+      <c r="A81" s="24"/>
+      <c r="B81" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C81" s="23">
+      <c r="C81" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="25"/>
-      <c r="B82" s="21" t="str">
+      <c r="A82" s="24"/>
+      <c r="B82" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C82" s="23">
+      <c r="C82" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="25"/>
-      <c r="B83" s="21" t="str">
+      <c r="A83" s="24"/>
+      <c r="B83" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C83" s="23">
+      <c r="C83" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="25"/>
-      <c r="B84" s="21" t="str">
+      <c r="A84" s="24"/>
+      <c r="B84" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C84" s="23">
+      <c r="C84" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="25"/>
-      <c r="B85" s="21" t="str">
+      <c r="A85" s="24"/>
+      <c r="B85" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C85" s="23">
+      <c r="C85" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="25"/>
-      <c r="B86" s="21" t="str">
+      <c r="A86" s="24"/>
+      <c r="B86" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C86" s="23">
+      <c r="C86" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="25"/>
-      <c r="B87" s="21" t="str">
+      <c r="A87" s="24"/>
+      <c r="B87" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C87" s="23">
+      <c r="C87" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="25"/>
-      <c r="B88" s="21" t="str">
+      <c r="A88" s="24"/>
+      <c r="B88" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C88" s="23">
+      <c r="C88" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="25"/>
-      <c r="B89" s="21" t="str">
+      <c r="A89" s="24"/>
+      <c r="B89" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C89" s="23">
+      <c r="C89" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="25"/>
-      <c r="B90" s="21" t="str">
+      <c r="A90" s="24"/>
+      <c r="B90" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C90" s="23">
+      <c r="C90" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="25"/>
-      <c r="B91" s="21" t="str">
+      <c r="A91" s="24"/>
+      <c r="B91" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C91" s="23">
+      <c r="C91" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="25"/>
-      <c r="B92" s="21" t="str">
+      <c r="A92" s="24"/>
+      <c r="B92" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C92" s="23">
+      <c r="C92" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="25"/>
-      <c r="B93" s="21" t="str">
+      <c r="A93" s="24"/>
+      <c r="B93" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C93" s="23">
+      <c r="C93" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="25"/>
-      <c r="B94" s="21" t="str">
+      <c r="A94" s="24"/>
+      <c r="B94" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C94" s="23">
+      <c r="C94" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="25"/>
-      <c r="B95" s="21" t="str">
+      <c r="A95" s="24"/>
+      <c r="B95" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C95" s="23">
+      <c r="C95" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="25"/>
-      <c r="B96" s="21" t="str">
+      <c r="A96" s="24"/>
+      <c r="B96" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C96" s="23">
+      <c r="C96" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="25"/>
-      <c r="B97" s="21" t="str">
+      <c r="A97" s="24"/>
+      <c r="B97" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C97" s="23">
+      <c r="C97" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="25"/>
-      <c r="B98" s="21" t="str">
+      <c r="A98" s="24"/>
+      <c r="B98" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C98" s="23">
+      <c r="C98" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="25"/>
-      <c r="B99" s="21" t="str">
+      <c r="A99" s="24"/>
+      <c r="B99" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C99" s="23">
+      <c r="C99" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="25"/>
-      <c r="B100" s="21" t="str">
+      <c r="A100" s="24"/>
+      <c r="B100" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C100" s="23">
+      <c r="C100" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="25"/>
-      <c r="B101" s="21" t="str">
+      <c r="A101" s="24"/>
+      <c r="B101" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C101" s="23">
+      <c r="C101" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="25"/>
-      <c r="B102" s="21" t="str">
+      <c r="A102" s="24"/>
+      <c r="B102" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C102" s="23">
+      <c r="C102" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="25"/>
-      <c r="B103" s="21" t="str">
+      <c r="A103" s="24"/>
+      <c r="B103" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C103" s="23">
+      <c r="C103" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="25"/>
-      <c r="B104" s="21" t="str">
+      <c r="A104" s="24"/>
+      <c r="B104" s="20" t="str">
         <f t="shared" ref="B104:B114" si="1">IF(C104&gt;0,C104,"")</f>
         <v/>
       </c>
-      <c r="C104" s="23">
+      <c r="C104" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="25"/>
-      <c r="B105" s="21" t="str">
+      <c r="A105" s="24"/>
+      <c r="B105" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C105" s="23">
+      <c r="C105" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="25"/>
-      <c r="B106" s="21" t="str">
+      <c r="A106" s="24"/>
+      <c r="B106" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C106" s="23">
+      <c r="C106" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="25"/>
-      <c r="B107" s="21" t="str">
+      <c r="A107" s="24"/>
+      <c r="B107" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C107" s="23">
+      <c r="C107" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="25"/>
-      <c r="B108" s="21" t="str">
+      <c r="A108" s="24"/>
+      <c r="B108" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C108" s="23">
+      <c r="C108" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="25"/>
-      <c r="B109" s="21" t="str">
+      <c r="A109" s="24"/>
+      <c r="B109" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C109" s="23">
+      <c r="C109" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="25"/>
-      <c r="B110" s="21" t="str">
+      <c r="A110" s="24"/>
+      <c r="B110" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C110" s="23">
+      <c r="C110" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="25"/>
-      <c r="B111" s="21" t="str">
+      <c r="A111" s="24"/>
+      <c r="B111" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C111" s="23">
+      <c r="C111" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="25"/>
-      <c r="B112" s="21" t="str">
+      <c r="A112" s="24"/>
+      <c r="B112" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C112" s="23">
+      <c r="C112" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="25"/>
-      <c r="B113" s="21" t="str">
+      <c r="A113" s="24"/>
+      <c r="B113" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C113" s="23">
+      <c r="C113" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="25"/>
-      <c r="B114" s="21" t="str">
+      <c r="A114" s="24"/>
+      <c r="B114" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C114" s="23">
+      <c r="C114" s="22">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="25"/>
-      <c r="B115" s="25"/>
-      <c r="C115" s="23"/>
+      <c r="A115" s="24"/>
+      <c r="B115" s="24"/>
+      <c r="C115" s="22"/>
     </row>
     <row r="116">
-      <c r="A116" s="25"/>
-      <c r="B116" s="25"/>
-      <c r="C116" s="23"/>
+      <c r="A116" s="24"/>
+      <c r="B116" s="24"/>
+      <c r="C116" s="22"/>
     </row>
     <row r="117">
-      <c r="A117" s="25"/>
-      <c r="B117" s="25"/>
-      <c r="C117" s="23"/>
+      <c r="A117" s="24"/>
+      <c r="B117" s="24"/>
+      <c r="C117" s="22"/>
     </row>
     <row r="118">
-      <c r="A118" s="25"/>
-      <c r="B118" s="25"/>
-      <c r="C118" s="23"/>
+      <c r="A118" s="24"/>
+      <c r="B118" s="24"/>
+      <c r="C118" s="22"/>
     </row>
     <row r="119">
-      <c r="A119" s="25"/>
-      <c r="B119" s="25"/>
-      <c r="C119" s="23"/>
+      <c r="A119" s="24"/>
+      <c r="B119" s="24"/>
+      <c r="C119" s="22"/>
     </row>
     <row r="120">
-      <c r="A120" s="25"/>
-      <c r="B120" s="25"/>
-      <c r="C120" s="23"/>
+      <c r="A120" s="24"/>
+      <c r="B120" s="24"/>
+      <c r="C120" s="22"/>
     </row>
     <row r="121">
-      <c r="A121" s="25"/>
-      <c r="B121" s="25"/>
-      <c r="C121" s="23"/>
+      <c r="A121" s="24"/>
+      <c r="B121" s="24"/>
+      <c r="C121" s="22"/>
     </row>
     <row r="122">
-      <c r="A122" s="25"/>
-      <c r="B122" s="25"/>
-      <c r="C122" s="23"/>
+      <c r="A122" s="24"/>
+      <c r="B122" s="24"/>
+      <c r="C122" s="22"/>
     </row>
     <row r="123">
-      <c r="A123" s="25"/>
-      <c r="B123" s="25"/>
-      <c r="C123" s="23"/>
+      <c r="A123" s="24"/>
+      <c r="B123" s="24"/>
+      <c r="C123" s="22"/>
     </row>
     <row r="124">
-      <c r="A124" s="25"/>
-      <c r="B124" s="25"/>
-      <c r="C124" s="23"/>
+      <c r="A124" s="24"/>
+      <c r="B124" s="24"/>
+      <c r="C124" s="22"/>
     </row>
     <row r="125">
-      <c r="A125" s="25"/>
-      <c r="B125" s="25"/>
-      <c r="C125" s="23"/>
+      <c r="A125" s="24"/>
+      <c r="B125" s="24"/>
+      <c r="C125" s="22"/>
     </row>
     <row r="126">
-      <c r="A126" s="25"/>
-      <c r="B126" s="25"/>
-      <c r="C126" s="23"/>
+      <c r="A126" s="24"/>
+      <c r="B126" s="24"/>
+      <c r="C126" s="22"/>
     </row>
     <row r="127">
-      <c r="A127" s="25"/>
-      <c r="B127" s="25"/>
-      <c r="C127" s="23"/>
+      <c r="A127" s="24"/>
+      <c r="B127" s="24"/>
+      <c r="C127" s="22"/>
     </row>
     <row r="128">
-      <c r="A128" s="25"/>
-      <c r="B128" s="25"/>
-      <c r="C128" s="23"/>
+      <c r="A128" s="24"/>
+      <c r="B128" s="24"/>
+      <c r="C128" s="22"/>
     </row>
     <row r="129">
-      <c r="A129" s="25"/>
-      <c r="B129" s="25"/>
-      <c r="C129" s="23"/>
+      <c r="A129" s="24"/>
+      <c r="B129" s="24"/>
+      <c r="C129" s="22"/>
     </row>
     <row r="130">
-      <c r="A130" s="25"/>
-      <c r="B130" s="25"/>
-      <c r="C130" s="23"/>
+      <c r="A130" s="24"/>
+      <c r="B130" s="24"/>
+      <c r="C130" s="22"/>
     </row>
     <row r="131">
-      <c r="A131" s="25"/>
-      <c r="B131" s="25"/>
-      <c r="C131" s="23"/>
+      <c r="A131" s="24"/>
+      <c r="B131" s="24"/>
+      <c r="C131" s="22"/>
     </row>
     <row r="132">
-      <c r="A132" s="25"/>
-      <c r="B132" s="25"/>
-      <c r="C132" s="23"/>
+      <c r="A132" s="24"/>
+      <c r="B132" s="24"/>
+      <c r="C132" s="22"/>
     </row>
     <row r="133">
-      <c r="A133" s="25"/>
-      <c r="B133" s="25"/>
-      <c r="C133" s="23"/>
+      <c r="A133" s="24"/>
+      <c r="B133" s="24"/>
+      <c r="C133" s="22"/>
     </row>
     <row r="134">
-      <c r="A134" s="25"/>
-      <c r="B134" s="25"/>
-      <c r="C134" s="23"/>
+      <c r="A134" s="24"/>
+      <c r="B134" s="24"/>
+      <c r="C134" s="22"/>
     </row>
     <row r="135">
-      <c r="A135" s="25"/>
-      <c r="B135" s="25"/>
-      <c r="C135" s="23"/>
+      <c r="A135" s="24"/>
+      <c r="B135" s="24"/>
+      <c r="C135" s="22"/>
     </row>
     <row r="136">
-      <c r="A136" s="25"/>
-      <c r="B136" s="25"/>
-      <c r="C136" s="23"/>
+      <c r="A136" s="24"/>
+      <c r="B136" s="24"/>
+      <c r="C136" s="22"/>
     </row>
     <row r="137">
-      <c r="A137" s="25"/>
-      <c r="B137" s="25"/>
-      <c r="C137" s="23"/>
+      <c r="A137" s="24"/>
+      <c r="B137" s="24"/>
+      <c r="C137" s="22"/>
     </row>
     <row r="138">
-      <c r="A138" s="25"/>
-      <c r="B138" s="25"/>
-      <c r="C138" s="23"/>
+      <c r="A138" s="24"/>
+      <c r="B138" s="24"/>
+      <c r="C138" s="22"/>
     </row>
     <row r="139">
-      <c r="A139" s="25"/>
-      <c r="B139" s="25"/>
-      <c r="C139" s="23"/>
+      <c r="A139" s="24"/>
+      <c r="B139" s="24"/>
+      <c r="C139" s="22"/>
     </row>
     <row r="140">
-      <c r="A140" s="25"/>
-      <c r="B140" s="25"/>
-      <c r="C140" s="23"/>
+      <c r="A140" s="24"/>
+      <c r="B140" s="24"/>
+      <c r="C140" s="22"/>
     </row>
     <row r="141">
-      <c r="A141" s="25"/>
-      <c r="B141" s="25"/>
-      <c r="C141" s="23"/>
+      <c r="A141" s="24"/>
+      <c r="B141" s="24"/>
+      <c r="C141" s="22"/>
     </row>
     <row r="142">
-      <c r="A142" s="25"/>
-      <c r="B142" s="25"/>
-      <c r="C142" s="23"/>
+      <c r="A142" s="24"/>
+      <c r="B142" s="24"/>
+      <c r="C142" s="22"/>
     </row>
     <row r="143">
-      <c r="A143" s="25"/>
-      <c r="B143" s="25"/>
-      <c r="C143" s="23"/>
+      <c r="A143" s="24"/>
+      <c r="B143" s="24"/>
+      <c r="C143" s="22"/>
     </row>
     <row r="144">
-      <c r="A144" s="25"/>
-      <c r="B144" s="25"/>
-      <c r="C144" s="23"/>
+      <c r="A144" s="24"/>
+      <c r="B144" s="24"/>
+      <c r="C144" s="22"/>
     </row>
     <row r="145">
-      <c r="A145" s="25"/>
-      <c r="B145" s="25"/>
-      <c r="C145" s="23"/>
+      <c r="A145" s="24"/>
+      <c r="B145" s="24"/>
+      <c r="C145" s="22"/>
     </row>
     <row r="146">
-      <c r="A146" s="25"/>
-      <c r="B146" s="25"/>
-      <c r="C146" s="23"/>
+      <c r="A146" s="24"/>
+      <c r="B146" s="24"/>
+      <c r="C146" s="22"/>
     </row>
     <row r="147">
-      <c r="A147" s="25"/>
-      <c r="B147" s="25"/>
-      <c r="C147" s="23"/>
+      <c r="A147" s="24"/>
+      <c r="B147" s="24"/>
+      <c r="C147" s="22"/>
     </row>
     <row r="148">
-      <c r="A148" s="25"/>
-      <c r="B148" s="25"/>
-      <c r="C148" s="23"/>
+      <c r="A148" s="24"/>
+      <c r="B148" s="24"/>
+      <c r="C148" s="22"/>
     </row>
     <row r="149">
-      <c r="A149" s="25"/>
-      <c r="B149" s="25"/>
-      <c r="C149" s="23"/>
+      <c r="A149" s="24"/>
+      <c r="B149" s="24"/>
+      <c r="C149" s="22"/>
     </row>
     <row r="150">
-      <c r="A150" s="25"/>
-      <c r="B150" s="25"/>
-      <c r="C150" s="23"/>
+      <c r="A150" s="24"/>
+      <c r="B150" s="24"/>
+      <c r="C150" s="22"/>
     </row>
     <row r="151">
-      <c r="A151" s="25"/>
-      <c r="B151" s="25"/>
-      <c r="C151" s="23"/>
+      <c r="A151" s="24"/>
+      <c r="B151" s="24"/>
+      <c r="C151" s="22"/>
     </row>
     <row r="152">
-      <c r="A152" s="25"/>
-      <c r="B152" s="25"/>
-      <c r="C152" s="23"/>
+      <c r="A152" s="24"/>
+      <c r="B152" s="24"/>
+      <c r="C152" s="22"/>
     </row>
     <row r="153">
-      <c r="A153" s="25"/>
-      <c r="B153" s="25"/>
-      <c r="C153" s="23"/>
+      <c r="A153" s="24"/>
+      <c r="B153" s="24"/>
+      <c r="C153" s="22"/>
     </row>
     <row r="154">
-      <c r="A154" s="25"/>
-      <c r="B154" s="25"/>
-      <c r="C154" s="23"/>
+      <c r="A154" s="24"/>
+      <c r="B154" s="24"/>
+      <c r="C154" s="22"/>
     </row>
     <row r="155">
-      <c r="A155" s="25"/>
-      <c r="B155" s="25"/>
-      <c r="C155" s="23"/>
+      <c r="A155" s="24"/>
+      <c r="B155" s="24"/>
+      <c r="C155" s="22"/>
     </row>
     <row r="156">
-      <c r="A156" s="25"/>
-      <c r="B156" s="25"/>
-      <c r="C156" s="23"/>
+      <c r="A156" s="24"/>
+      <c r="B156" s="24"/>
+      <c r="C156" s="22"/>
     </row>
     <row r="157">
-      <c r="A157" s="25"/>
-      <c r="B157" s="25"/>
-      <c r="C157" s="23"/>
+      <c r="A157" s="24"/>
+      <c r="B157" s="24"/>
+      <c r="C157" s="22"/>
     </row>
     <row r="158">
-      <c r="A158" s="25"/>
-      <c r="B158" s="25"/>
-      <c r="C158" s="23"/>
+      <c r="A158" s="24"/>
+      <c r="B158" s="24"/>
+      <c r="C158" s="22"/>
     </row>
     <row r="159">
-      <c r="A159" s="25"/>
-      <c r="B159" s="25"/>
+      <c r="A159" s="24"/>
+      <c r="B159" s="24"/>
     </row>
     <row r="160">
-      <c r="A160" s="25"/>
-      <c r="B160" s="25"/>
+      <c r="A160" s="24"/>
+      <c r="B160" s="24"/>
     </row>
     <row r="161">
-      <c r="A161" s="25"/>
-      <c r="B161" s="25"/>
+      <c r="A161" s="24"/>
+      <c r="B161" s="24"/>
     </row>
     <row r="162">
-      <c r="A162" s="25"/>
-      <c r="B162" s="25"/>
+      <c r="A162" s="24"/>
+      <c r="B162" s="24"/>
     </row>
     <row r="163">
-      <c r="A163" s="25"/>
-      <c r="B163" s="25"/>
+      <c r="A163" s="24"/>
+      <c r="B163" s="24"/>
     </row>
     <row r="164">
-      <c r="A164" s="25"/>
-      <c r="B164" s="25"/>
+      <c r="A164" s="24"/>
+      <c r="B164" s="24"/>
     </row>
     <row r="165">
-      <c r="A165" s="25"/>
-      <c r="B165" s="25"/>
+      <c r="A165" s="24"/>
+      <c r="B165" s="24"/>
     </row>
     <row r="166">
-      <c r="A166" s="25"/>
-      <c r="B166" s="25"/>
+      <c r="A166" s="24"/>
+      <c r="B166" s="24"/>
     </row>
     <row r="167">
-      <c r="A167" s="25"/>
-      <c r="B167" s="25"/>
+      <c r="A167" s="24"/>
+      <c r="B167" s="24"/>
     </row>
     <row r="168">
-      <c r="A168" s="25"/>
-      <c r="B168" s="25"/>
+      <c r="A168" s="24"/>
+      <c r="B168" s="24"/>
     </row>
     <row r="169">
-      <c r="A169" s="25"/>
-      <c r="B169" s="25"/>
+      <c r="A169" s="24"/>
+      <c r="B169" s="24"/>
     </row>
     <row r="170">
-      <c r="A170" s="25"/>
-      <c r="B170" s="25"/>
+      <c r="A170" s="24"/>
+      <c r="B170" s="24"/>
     </row>
     <row r="171">
-      <c r="A171" s="25"/>
-      <c r="B171" s="25"/>
+      <c r="A171" s="24"/>
+      <c r="B171" s="24"/>
     </row>
     <row r="172">
-      <c r="A172" s="25"/>
-      <c r="B172" s="25"/>
+      <c r="A172" s="24"/>
+      <c r="B172" s="24"/>
     </row>
     <row r="173">
-      <c r="A173" s="25"/>
-      <c r="B173" s="25"/>
+      <c r="A173" s="24"/>
+      <c r="B173" s="24"/>
     </row>
     <row r="174">
-      <c r="A174" s="25"/>
-      <c r="B174" s="25"/>
+      <c r="A174" s="24"/>
+      <c r="B174" s="24"/>
     </row>
     <row r="175">
-      <c r="A175" s="25"/>
-      <c r="B175" s="25"/>
+      <c r="A175" s="24"/>
+      <c r="B175" s="24"/>
     </row>
     <row r="176">
-      <c r="A176" s="25"/>
-      <c r="B176" s="25"/>
+      <c r="A176" s="24"/>
+      <c r="B176" s="24"/>
     </row>
     <row r="177">
-      <c r="A177" s="25"/>
-      <c r="B177" s="25"/>
+      <c r="A177" s="24"/>
+      <c r="B177" s="24"/>
     </row>
     <row r="178">
-      <c r="A178" s="25"/>
-      <c r="B178" s="25"/>
+      <c r="A178" s="24"/>
+      <c r="B178" s="24"/>
     </row>
     <row r="179">
-      <c r="A179" s="25"/>
-      <c r="B179" s="25"/>
+      <c r="A179" s="24"/>
+      <c r="B179" s="24"/>
     </row>
     <row r="180">
-      <c r="A180" s="25"/>
-      <c r="B180" s="25"/>
+      <c r="A180" s="24"/>
+      <c r="B180" s="24"/>
     </row>
     <row r="181">
-      <c r="A181" s="25"/>
-      <c r="B181" s="25"/>
+      <c r="A181" s="24"/>
+      <c r="B181" s="24"/>
     </row>
     <row r="182">
-      <c r="A182" s="25"/>
-      <c r="B182" s="25"/>
+      <c r="A182" s="24"/>
+      <c r="B182" s="24"/>
     </row>
     <row r="183">
-      <c r="A183" s="25"/>
-      <c r="B183" s="25"/>
+      <c r="A183" s="24"/>
+      <c r="B183" s="24"/>
     </row>
     <row r="184">
-      <c r="A184" s="25"/>
-      <c r="B184" s="25"/>
+      <c r="A184" s="24"/>
+      <c r="B184" s="24"/>
     </row>
     <row r="185">
-      <c r="A185" s="25"/>
-      <c r="B185" s="25"/>
+      <c r="A185" s="24"/>
+      <c r="B185" s="24"/>
     </row>
     <row r="186">
-      <c r="A186" s="25"/>
-      <c r="B186" s="25"/>
+      <c r="A186" s="24"/>
+      <c r="B186" s="24"/>
     </row>
     <row r="187">
-      <c r="A187" s="25"/>
-      <c r="B187" s="25"/>
+      <c r="A187" s="24"/>
+      <c r="B187" s="24"/>
     </row>
     <row r="188">
-      <c r="A188" s="25"/>
-      <c r="B188" s="25"/>
+      <c r="A188" s="24"/>
+      <c r="B188" s="24"/>
     </row>
     <row r="189">
-      <c r="A189" s="25"/>
-      <c r="B189" s="25"/>
+      <c r="A189" s="24"/>
+      <c r="B189" s="24"/>
     </row>
     <row r="190">
-      <c r="A190" s="25"/>
-      <c r="B190" s="25"/>
+      <c r="A190" s="24"/>
+      <c r="B190" s="24"/>
     </row>
     <row r="191">
-      <c r="A191" s="25"/>
-      <c r="B191" s="25"/>
+      <c r="A191" s="24"/>
+      <c r="B191" s="24"/>
     </row>
     <row r="192">
-      <c r="A192" s="25"/>
-      <c r="B192" s="25"/>
+      <c r="A192" s="24"/>
+      <c r="B192" s="24"/>
     </row>
     <row r="193">
-      <c r="A193" s="25"/>
-      <c r="B193" s="25"/>
+      <c r="A193" s="24"/>
+      <c r="B193" s="24"/>
     </row>
     <row r="194">
-      <c r="A194" s="25"/>
-      <c r="B194" s="25"/>
+      <c r="A194" s="24"/>
+      <c r="B194" s="24"/>
     </row>
     <row r="195">
-      <c r="A195" s="25"/>
-      <c r="B195" s="25"/>
+      <c r="A195" s="24"/>
+      <c r="B195" s="24"/>
     </row>
     <row r="196">
-      <c r="A196" s="25"/>
-      <c r="B196" s="25"/>
+      <c r="A196" s="24"/>
+      <c r="B196" s="24"/>
     </row>
     <row r="197">
-      <c r="A197" s="25"/>
-      <c r="B197" s="25"/>
+      <c r="A197" s="24"/>
+      <c r="B197" s="24"/>
     </row>
     <row r="198">
-      <c r="A198" s="25"/>
-      <c r="B198" s="25"/>
+      <c r="A198" s="24"/>
+      <c r="B198" s="24"/>
     </row>
     <row r="199">
-      <c r="A199" s="25"/>
-      <c r="B199" s="25"/>
+      <c r="A199" s="24"/>
+      <c r="B199" s="24"/>
     </row>
     <row r="200">
-      <c r="A200" s="25"/>
-      <c r="B200" s="25"/>
+      <c r="A200" s="24"/>
+      <c r="B200" s="24"/>
     </row>
     <row r="201">
-      <c r="A201" s="25"/>
-      <c r="B201" s="25"/>
+      <c r="A201" s="24"/>
+      <c r="B201" s="24"/>
     </row>
     <row r="202">
-      <c r="A202" s="25"/>
-      <c r="B202" s="25"/>
+      <c r="A202" s="24"/>
+      <c r="B202" s="24"/>
     </row>
     <row r="203">
-      <c r="A203" s="25"/>
-      <c r="B203" s="25"/>
+      <c r="A203" s="24"/>
+      <c r="B203" s="24"/>
     </row>
     <row r="204">
-      <c r="A204" s="25"/>
-      <c r="B204" s="25"/>
+      <c r="A204" s="24"/>
+      <c r="B204" s="24"/>
     </row>
     <row r="205">
-      <c r="A205" s="25"/>
-      <c r="B205" s="25"/>
+      <c r="A205" s="24"/>
+      <c r="B205" s="24"/>
     </row>
     <row r="206">
-      <c r="A206" s="25"/>
-      <c r="B206" s="25"/>
+      <c r="A206" s="24"/>
+      <c r="B206" s="24"/>
     </row>
     <row r="207">
-      <c r="A207" s="25"/>
-      <c r="B207" s="25"/>
+      <c r="A207" s="24"/>
+      <c r="B207" s="24"/>
     </row>
     <row r="208">
-      <c r="A208" s="25"/>
-      <c r="B208" s="25"/>
+      <c r="A208" s="24"/>
+      <c r="B208" s="24"/>
     </row>
     <row r="209">
-      <c r="A209" s="25"/>
-      <c r="B209" s="25"/>
+      <c r="A209" s="24"/>
+      <c r="B209" s="24"/>
     </row>
     <row r="210">
-      <c r="A210" s="25"/>
-      <c r="B210" s="25"/>
+      <c r="A210" s="24"/>
+      <c r="B210" s="24"/>
     </row>
     <row r="211">
-      <c r="A211" s="25"/>
-      <c r="B211" s="25"/>
+      <c r="A211" s="24"/>
+      <c r="B211" s="24"/>
     </row>
     <row r="212">
-      <c r="A212" s="25"/>
-      <c r="B212" s="25"/>
+      <c r="A212" s="24"/>
+      <c r="B212" s="24"/>
     </row>
     <row r="213">
-      <c r="A213" s="25"/>
-      <c r="B213" s="25"/>
+      <c r="A213" s="24"/>
+      <c r="B213" s="24"/>
     </row>
     <row r="214">
-      <c r="A214" s="25"/>
-      <c r="B214" s="25"/>
+      <c r="A214" s="24"/>
+      <c r="B214" s="24"/>
     </row>
     <row r="215">
-      <c r="A215" s="25"/>
-      <c r="B215" s="25"/>
+      <c r="A215" s="24"/>
+      <c r="B215" s="24"/>
     </row>
     <row r="216">
-      <c r="A216" s="25"/>
-      <c r="B216" s="25"/>
+      <c r="A216" s="24"/>
+      <c r="B216" s="24"/>
     </row>
     <row r="217">
-      <c r="A217" s="25"/>
-      <c r="B217" s="25"/>
+      <c r="A217" s="24"/>
+      <c r="B217" s="24"/>
     </row>
     <row r="218">
-      <c r="A218" s="25"/>
-      <c r="B218" s="25"/>
+      <c r="A218" s="24"/>
+      <c r="B218" s="24"/>
     </row>
     <row r="219">
-      <c r="A219" s="25"/>
-      <c r="B219" s="25"/>
+      <c r="A219" s="24"/>
+      <c r="B219" s="24"/>
     </row>
     <row r="220">
-      <c r="A220" s="25"/>
-      <c r="B220" s="25"/>
+      <c r="A220" s="24"/>
+      <c r="B220" s="24"/>
     </row>
     <row r="221">
-      <c r="A221" s="25"/>
-      <c r="B221" s="25"/>
+      <c r="A221" s="24"/>
+      <c r="B221" s="24"/>
     </row>
     <row r="222">
-      <c r="A222" s="25"/>
-      <c r="B222" s="25"/>
+      <c r="A222" s="24"/>
+      <c r="B222" s="24"/>
     </row>
     <row r="223">
-      <c r="A223" s="25"/>
-      <c r="B223" s="25"/>
+      <c r="A223" s="24"/>
+      <c r="B223" s="24"/>
     </row>
     <row r="224">
-      <c r="A224" s="25"/>
-      <c r="B224" s="25"/>
+      <c r="A224" s="24"/>
+      <c r="B224" s="24"/>
     </row>
     <row r="225">
-      <c r="A225" s="25"/>
-      <c r="B225" s="25"/>
+      <c r="A225" s="24"/>
+      <c r="B225" s="24"/>
     </row>
     <row r="226">
-      <c r="A226" s="25"/>
-      <c r="B226" s="25"/>
+      <c r="A226" s="24"/>
+      <c r="B226" s="24"/>
     </row>
     <row r="227">
-      <c r="A227" s="25"/>
-      <c r="B227" s="25"/>
+      <c r="A227" s="24"/>
+      <c r="B227" s="24"/>
     </row>
     <row r="228">
-      <c r="A228" s="25"/>
-      <c r="B228" s="25"/>
+      <c r="A228" s="24"/>
+      <c r="B228" s="24"/>
     </row>
     <row r="229">
-      <c r="A229" s="25"/>
-      <c r="B229" s="25"/>
+      <c r="A229" s="24"/>
+      <c r="B229" s="24"/>
     </row>
     <row r="230">
-      <c r="A230" s="25"/>
-      <c r="B230" s="25"/>
+      <c r="A230" s="24"/>
+      <c r="B230" s="24"/>
     </row>
     <row r="231">
-      <c r="A231" s="25"/>
-      <c r="B231" s="25"/>
+      <c r="A231" s="24"/>
+      <c r="B231" s="24"/>
     </row>
     <row r="232">
-      <c r="A232" s="25"/>
-      <c r="B232" s="25"/>
+      <c r="A232" s="24"/>
+      <c r="B232" s="24"/>
     </row>
     <row r="233">
-      <c r="A233" s="25"/>
-      <c r="B233" s="25"/>
+      <c r="A233" s="24"/>
+      <c r="B233" s="24"/>
     </row>
     <row r="234">
-      <c r="A234" s="25"/>
-      <c r="B234" s="25"/>
+      <c r="A234" s="24"/>
+      <c r="B234" s="24"/>
     </row>
     <row r="235">
-      <c r="A235" s="25"/>
-      <c r="B235" s="25"/>
+      <c r="A235" s="24"/>
+      <c r="B235" s="24"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -7464,2034 +7472,2034 @@
     <col customWidth="1" min="2" max="2" width="4.33203125"/>
     <col bestFit="1" min="3" max="3" width="35.77734375"/>
     <col customWidth="1" min="4" max="11" width="3.44140625"/>
-    <col customWidth="1" min="12" max="12" style="26" width="6"/>
+    <col customWidth="1" min="12" max="12" style="25" width="6"/>
     <col customWidth="1" min="13" max="22" width="3.44140625"/>
-    <col customWidth="1" min="23" max="23" style="26" width="6"/>
+    <col customWidth="1" min="23" max="23" style="25" width="6"/>
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
-    <col customWidth="1" min="30" max="30" style="26" width="6"/>
+    <col customWidth="1" min="30" max="30" style="25" width="6"/>
     <col customWidth="1" min="31" max="39" width="3.44140625"/>
     <col bestFit="1" customWidth="1" min="40" max="40" width="13.88671875"/>
     <col customWidth="1" min="41" max="47" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="27" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="B1" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="29" t="s">
+    <row r="1" s="26" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="B1" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="C1" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="F1" s="31" t="s">
+      <c r="E1" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="32" t="s">
+      <c r="G1" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="30" t="s">
+      <c r="H1" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="J1" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="L1" s="34" t="s">
+      <c r="K1" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="M1" s="30" t="s">
+      <c r="L1" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="N1" s="32" t="s">
+      <c r="M1" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="N1" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="P1" s="30" t="s">
+      <c r="O1" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="P1" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="R1" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="S1" s="30" t="s">
+      <c r="Q1" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="R1" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="T1" s="30" t="s">
+      <c r="S1" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="U1" s="30" t="s">
+      <c r="T1" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="V1" s="32" t="s">
+      <c r="U1" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="W1" s="35" t="s">
+      <c r="V1" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="X1" s="30" t="s">
+      <c r="W1" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="Y1" s="30" t="s">
+      <c r="X1" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="Z1" s="32" t="s">
+      <c r="Y1" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AA1" s="36" t="s">
+      <c r="Z1" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="AB1" s="37" t="s">
+      <c r="AA1" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="AC1" s="37" t="s">
+      <c r="AB1" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="AD1" s="34" t="s">
+      <c r="AC1" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="AE1" s="38" t="s">
+      <c r="AD1" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="AF1" s="39" t="s">
+      <c r="AE1" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="AG1" s="40" t="s">
+      <c r="AF1" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="AH1" s="40" t="s">
+      <c r="AG1" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="AI1" s="40" t="s">
+      <c r="AH1" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="AJ1" s="40" t="s">
+      <c r="AI1" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="AK1" s="37" t="s">
+      <c r="AJ1" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="AL1" s="41"/>
-      <c r="AM1" s="41"/>
-      <c r="AN1" s="41"/>
-      <c r="AO1" s="41"/>
-      <c r="AP1" s="41"/>
-      <c r="AQ1" s="41"/>
-      <c r="AR1" s="41"/>
-      <c r="AS1" s="41"/>
-      <c r="AT1" s="41"/>
-      <c r="AU1" s="41"/>
+      <c r="AK1" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL1" s="40"/>
+      <c r="AM1" s="40"/>
+      <c r="AN1" s="40"/>
+      <c r="AO1" s="40"/>
+      <c r="AP1" s="40"/>
+      <c r="AQ1" s="40"/>
+      <c r="AR1" s="40"/>
+      <c r="AS1" s="40"/>
+      <c r="AT1" s="40"/>
+      <c r="AU1" s="40"/>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="44"/>
-      <c r="S2" s="44"/>
-      <c r="T2" s="44"/>
-      <c r="U2" s="44"/>
-      <c r="V2" s="49"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="44"/>
-      <c r="Y2" s="44"/>
-      <c r="Z2" s="49"/>
-      <c r="AA2" s="50"/>
-      <c r="AB2" s="44"/>
-      <c r="AC2" s="44"/>
-      <c r="AD2" s="48"/>
-      <c r="AE2" s="49"/>
-      <c r="AF2" s="50"/>
-      <c r="AG2" s="44"/>
-      <c r="AH2" s="44"/>
-      <c r="AI2" s="44"/>
-      <c r="AJ2" s="44"/>
-      <c r="AK2" s="44"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+      <c r="V2" s="48"/>
+      <c r="W2" s="50"/>
+      <c r="X2" s="43"/>
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="48"/>
+      <c r="AA2" s="49"/>
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="43"/>
+      <c r="AD2" s="47"/>
+      <c r="AE2" s="48"/>
+      <c r="AF2" s="49"/>
+      <c r="AG2" s="43"/>
+      <c r="AH2" s="43"/>
+      <c r="AI2" s="43"/>
+      <c r="AJ2" s="43"/>
+      <c r="AK2" s="43"/>
     </row>
     <row r="3" ht="12" customHeight="1">
-      <c r="B3" s="42"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="49"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="44"/>
-      <c r="Q3" s="44"/>
-      <c r="R3" s="44"/>
-      <c r="S3" s="44"/>
-      <c r="T3" s="44"/>
-      <c r="U3" s="44"/>
-      <c r="V3" s="49"/>
-      <c r="W3" s="51"/>
-      <c r="X3" s="44"/>
-      <c r="Y3" s="44"/>
-      <c r="Z3" s="49"/>
-      <c r="AA3" s="50"/>
-      <c r="AB3" s="44"/>
-      <c r="AC3" s="44"/>
-      <c r="AD3" s="48"/>
-      <c r="AE3" s="49"/>
-      <c r="AF3" s="50"/>
-      <c r="AG3" s="44"/>
-      <c r="AH3" s="44"/>
-      <c r="AI3" s="44"/>
-      <c r="AJ3" s="44"/>
-      <c r="AK3" s="44"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="48"/>
+      <c r="W3" s="50"/>
+      <c r="X3" s="43"/>
+      <c r="Y3" s="43"/>
+      <c r="Z3" s="48"/>
+      <c r="AA3" s="49"/>
+      <c r="AB3" s="43"/>
+      <c r="AC3" s="43"/>
+      <c r="AD3" s="47"/>
+      <c r="AE3" s="48"/>
+      <c r="AF3" s="49"/>
+      <c r="AG3" s="43"/>
+      <c r="AH3" s="43"/>
+      <c r="AI3" s="43"/>
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="42"/>
-      <c r="C4" s="43" t="s">
-        <v>88</v>
-      </c>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="48"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="49"/>
-      <c r="O4" s="50"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44"/>
-      <c r="S4" s="44"/>
-      <c r="T4" s="44"/>
-      <c r="U4" s="44"/>
-      <c r="V4" s="49"/>
-      <c r="W4" s="51"/>
-      <c r="X4" s="44"/>
-      <c r="Y4" s="44"/>
-      <c r="Z4" s="49"/>
-      <c r="AA4" s="50"/>
-      <c r="AB4" s="44"/>
-      <c r="AC4" s="44"/>
-      <c r="AD4" s="48"/>
-      <c r="AE4" s="49"/>
-      <c r="AF4" s="50"/>
-      <c r="AG4" s="44"/>
-      <c r="AH4" s="44"/>
-      <c r="AI4" s="44"/>
-      <c r="AJ4" s="44"/>
-      <c r="AK4" s="44"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="49"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="43"/>
+      <c r="T4" s="43"/>
+      <c r="U4" s="43"/>
+      <c r="V4" s="48"/>
+      <c r="W4" s="50"/>
+      <c r="X4" s="43"/>
+      <c r="Y4" s="43"/>
+      <c r="Z4" s="48"/>
+      <c r="AA4" s="49"/>
+      <c r="AB4" s="43"/>
+      <c r="AC4" s="43"/>
+      <c r="AD4" s="47"/>
+      <c r="AE4" s="48"/>
+      <c r="AF4" s="49"/>
+      <c r="AG4" s="43"/>
+      <c r="AH4" s="43"/>
+      <c r="AI4" s="43"/>
+      <c r="AJ4" s="43"/>
+      <c r="AK4" s="43"/>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="42"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="48"/>
-      <c r="M5" s="44"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="50"/>
-      <c r="P5" s="44"/>
-      <c r="Q5" s="44"/>
-      <c r="R5" s="44"/>
-      <c r="S5" s="44"/>
-      <c r="T5" s="44"/>
-      <c r="U5" s="44"/>
-      <c r="V5" s="49"/>
-      <c r="W5" s="51"/>
-      <c r="X5" s="44"/>
-      <c r="Y5" s="44"/>
-      <c r="Z5" s="49"/>
-      <c r="AA5" s="50"/>
-      <c r="AB5" s="44"/>
-      <c r="AC5" s="44"/>
-      <c r="AD5" s="48"/>
-      <c r="AE5" s="49"/>
-      <c r="AF5" s="50"/>
-      <c r="AG5" s="44"/>
-      <c r="AH5" s="44"/>
-      <c r="AI5" s="44"/>
-      <c r="AJ5" s="44"/>
-      <c r="AK5" s="44"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="43"/>
+      <c r="Q5" s="43"/>
+      <c r="R5" s="43"/>
+      <c r="S5" s="43"/>
+      <c r="T5" s="43"/>
+      <c r="U5" s="43"/>
+      <c r="V5" s="48"/>
+      <c r="W5" s="50"/>
+      <c r="X5" s="43"/>
+      <c r="Y5" s="43"/>
+      <c r="Z5" s="48"/>
+      <c r="AA5" s="49"/>
+      <c r="AB5" s="43"/>
+      <c r="AC5" s="43"/>
+      <c r="AD5" s="47"/>
+      <c r="AE5" s="48"/>
+      <c r="AF5" s="49"/>
+      <c r="AG5" s="43"/>
+      <c r="AH5" s="43"/>
+      <c r="AI5" s="43"/>
+      <c r="AJ5" s="43"/>
+      <c r="AK5" s="43"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="42"/>
-      <c r="C6" s="43" t="s">
+      <c r="B6" s="41"/>
+      <c r="C6" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="48"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="49"/>
-      <c r="O6" s="50"/>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="44"/>
-      <c r="R6" s="44"/>
-      <c r="S6" s="44"/>
-      <c r="T6" s="44"/>
-      <c r="U6" s="44"/>
-      <c r="V6" s="49"/>
-      <c r="W6" s="51"/>
-      <c r="X6" s="44"/>
-      <c r="Y6" s="44"/>
-      <c r="Z6" s="49"/>
-      <c r="AA6" s="50"/>
-      <c r="AB6" s="44"/>
-      <c r="AC6" s="44"/>
-      <c r="AD6" s="48"/>
-      <c r="AE6" s="46"/>
-      <c r="AF6" s="47"/>
-      <c r="AG6" s="58"/>
-      <c r="AH6" s="58"/>
-      <c r="AI6" s="58"/>
-      <c r="AJ6" s="58"/>
-      <c r="AK6" s="58"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="48"/>
+      <c r="O6" s="49"/>
+      <c r="P6" s="43"/>
+      <c r="Q6" s="43"/>
+      <c r="R6" s="43"/>
+      <c r="S6" s="43"/>
+      <c r="T6" s="43"/>
+      <c r="U6" s="43"/>
+      <c r="V6" s="48"/>
+      <c r="W6" s="50"/>
+      <c r="X6" s="43"/>
+      <c r="Y6" s="43"/>
+      <c r="Z6" s="48"/>
+      <c r="AA6" s="49"/>
+      <c r="AB6" s="43"/>
+      <c r="AC6" s="43"/>
+      <c r="AD6" s="47"/>
+      <c r="AE6" s="45"/>
+      <c r="AF6" s="46"/>
+      <c r="AG6" s="57"/>
+      <c r="AH6" s="57"/>
+      <c r="AI6" s="57"/>
+      <c r="AJ6" s="57"/>
+      <c r="AK6" s="57"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="42"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="48"/>
-      <c r="M7" s="44"/>
-      <c r="N7" s="49"/>
-      <c r="O7" s="56"/>
-      <c r="P7" s="44"/>
-      <c r="Q7" s="57"/>
-      <c r="R7" s="44"/>
-      <c r="S7" s="44"/>
-      <c r="T7" s="44"/>
-      <c r="U7" s="44"/>
-      <c r="V7" s="49"/>
-      <c r="W7" s="51"/>
-      <c r="X7" s="44"/>
-      <c r="Y7" s="44"/>
-      <c r="Z7" s="49"/>
-      <c r="AA7" s="50"/>
-      <c r="AB7" s="44"/>
-      <c r="AC7" s="44"/>
-      <c r="AD7" s="48"/>
-      <c r="AE7" s="49"/>
-      <c r="AF7" s="50"/>
-      <c r="AG7" s="44"/>
-      <c r="AH7" s="44"/>
-      <c r="AI7" s="44"/>
-      <c r="AJ7" s="44"/>
-      <c r="AK7" s="44"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="43"/>
+      <c r="L7" s="47"/>
+      <c r="M7" s="43"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="55"/>
+      <c r="P7" s="43"/>
+      <c r="Q7" s="56"/>
+      <c r="R7" s="43"/>
+      <c r="S7" s="43"/>
+      <c r="T7" s="43"/>
+      <c r="U7" s="43"/>
+      <c r="V7" s="48"/>
+      <c r="W7" s="50"/>
+      <c r="X7" s="43"/>
+      <c r="Y7" s="43"/>
+      <c r="Z7" s="48"/>
+      <c r="AA7" s="49"/>
+      <c r="AB7" s="43"/>
+      <c r="AC7" s="43"/>
+      <c r="AD7" s="47"/>
+      <c r="AE7" s="48"/>
+      <c r="AF7" s="49"/>
+      <c r="AG7" s="43"/>
+      <c r="AH7" s="43"/>
+      <c r="AI7" s="43"/>
+      <c r="AJ7" s="43"/>
+      <c r="AK7" s="43"/>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="42"/>
-      <c r="C8" s="43" t="s">
-        <v>89</v>
-      </c>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="58"/>
-      <c r="K8" s="58"/>
-      <c r="L8" s="48"/>
-      <c r="M8" s="58"/>
-      <c r="N8" s="46"/>
-      <c r="O8" s="47"/>
-      <c r="P8" s="58"/>
-      <c r="Q8" s="58"/>
-      <c r="R8" s="58"/>
-      <c r="S8" s="58"/>
-      <c r="T8" s="58"/>
-      <c r="U8" s="58"/>
-      <c r="V8" s="46"/>
-      <c r="W8" s="51"/>
-      <c r="X8" s="58"/>
-      <c r="Y8" s="58"/>
-      <c r="Z8" s="46"/>
-      <c r="AA8" s="47"/>
-      <c r="AB8" s="58"/>
-      <c r="AC8" s="58"/>
-      <c r="AD8" s="48"/>
-      <c r="AE8" s="46"/>
-      <c r="AF8" s="47"/>
-      <c r="AG8" s="58"/>
-      <c r="AH8" s="58"/>
-      <c r="AI8" s="58"/>
-      <c r="AJ8" s="58"/>
-      <c r="AK8" s="58"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="47"/>
+      <c r="M8" s="57"/>
+      <c r="N8" s="45"/>
+      <c r="O8" s="46"/>
+      <c r="P8" s="57"/>
+      <c r="Q8" s="57"/>
+      <c r="R8" s="57"/>
+      <c r="S8" s="57"/>
+      <c r="T8" s="57"/>
+      <c r="U8" s="57"/>
+      <c r="V8" s="45"/>
+      <c r="W8" s="50"/>
+      <c r="X8" s="57"/>
+      <c r="Y8" s="57"/>
+      <c r="Z8" s="45"/>
+      <c r="AA8" s="46"/>
+      <c r="AB8" s="57"/>
+      <c r="AC8" s="57"/>
+      <c r="AD8" s="47"/>
+      <c r="AE8" s="45"/>
+      <c r="AF8" s="46"/>
+      <c r="AG8" s="57"/>
+      <c r="AH8" s="57"/>
+      <c r="AI8" s="57"/>
+      <c r="AJ8" s="57"/>
+      <c r="AK8" s="57"/>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="42"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="57"/>
-      <c r="K9" s="44"/>
-      <c r="L9" s="48"/>
-      <c r="M9" s="57"/>
-      <c r="N9" s="49"/>
-      <c r="O9" s="56"/>
-      <c r="P9" s="44"/>
-      <c r="Q9" s="57"/>
-      <c r="R9" s="44"/>
-      <c r="S9" s="44"/>
-      <c r="T9" s="44"/>
-      <c r="U9" s="44"/>
-      <c r="V9" s="49"/>
-      <c r="W9" s="51"/>
-      <c r="X9" s="44"/>
-      <c r="Y9" s="44"/>
-      <c r="Z9" s="49"/>
-      <c r="AA9" s="50"/>
-      <c r="AB9" s="44"/>
-      <c r="AC9" s="44"/>
-      <c r="AD9" s="48"/>
-      <c r="AE9" s="49"/>
-      <c r="AF9" s="50"/>
-      <c r="AG9" s="44"/>
-      <c r="AH9" s="44"/>
-      <c r="AI9" s="44"/>
-      <c r="AJ9" s="44"/>
-      <c r="AK9" s="44"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="56"/>
+      <c r="K9" s="43"/>
+      <c r="L9" s="47"/>
+      <c r="M9" s="56"/>
+      <c r="N9" s="48"/>
+      <c r="O9" s="55"/>
+      <c r="P9" s="43"/>
+      <c r="Q9" s="56"/>
+      <c r="R9" s="43"/>
+      <c r="S9" s="43"/>
+      <c r="T9" s="43"/>
+      <c r="U9" s="43"/>
+      <c r="V9" s="48"/>
+      <c r="W9" s="50"/>
+      <c r="X9" s="43"/>
+      <c r="Y9" s="43"/>
+      <c r="Z9" s="48"/>
+      <c r="AA9" s="49"/>
+      <c r="AB9" s="43"/>
+      <c r="AC9" s="43"/>
+      <c r="AD9" s="47"/>
+      <c r="AE9" s="48"/>
+      <c r="AF9" s="49"/>
+      <c r="AG9" s="43"/>
+      <c r="AH9" s="43"/>
+      <c r="AI9" s="43"/>
+      <c r="AJ9" s="43"/>
+      <c r="AK9" s="43"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="42"/>
-      <c r="C10" s="43" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="48"/>
-      <c r="M10" s="44"/>
-      <c r="N10" s="49"/>
-      <c r="O10" s="50"/>
-      <c r="P10" s="44"/>
-      <c r="Q10" s="44"/>
-      <c r="R10" s="44"/>
-      <c r="S10" s="44"/>
-      <c r="T10" s="44"/>
-      <c r="U10" s="44"/>
-      <c r="V10" s="46"/>
-      <c r="W10" s="51"/>
-      <c r="X10" s="58"/>
-      <c r="Y10" s="58"/>
-      <c r="Z10" s="46"/>
-      <c r="AA10" s="50"/>
-      <c r="AB10" s="44"/>
-      <c r="AC10" s="44"/>
-      <c r="AD10" s="48"/>
-      <c r="AE10" s="49"/>
-      <c r="AF10" s="50"/>
-      <c r="AG10" s="44"/>
-      <c r="AH10" s="44"/>
-      <c r="AI10" s="44"/>
-      <c r="AJ10" s="44"/>
-      <c r="AK10" s="44"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="47"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="49"/>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="43"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="43"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="43"/>
+      <c r="V10" s="45"/>
+      <c r="W10" s="50"/>
+      <c r="X10" s="57"/>
+      <c r="Y10" s="57"/>
+      <c r="Z10" s="45"/>
+      <c r="AA10" s="49"/>
+      <c r="AB10" s="43"/>
+      <c r="AC10" s="43"/>
+      <c r="AD10" s="47"/>
+      <c r="AE10" s="48"/>
+      <c r="AF10" s="49"/>
+      <c r="AG10" s="43"/>
+      <c r="AH10" s="43"/>
+      <c r="AI10" s="43"/>
+      <c r="AJ10" s="43"/>
+      <c r="AK10" s="43"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="42"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="44"/>
-      <c r="K11" s="44"/>
-      <c r="L11" s="48"/>
-      <c r="M11" s="44"/>
-      <c r="N11" s="49"/>
-      <c r="O11" s="50"/>
-      <c r="P11" s="44"/>
-      <c r="Q11" s="44"/>
-      <c r="R11" s="44"/>
-      <c r="S11" s="44"/>
-      <c r="T11" s="44"/>
-      <c r="U11" s="44"/>
-      <c r="V11" s="49"/>
-      <c r="W11" s="51"/>
-      <c r="X11" s="44"/>
-      <c r="Y11" s="44"/>
-      <c r="Z11" s="49"/>
-      <c r="AA11" s="50"/>
-      <c r="AB11" s="44"/>
-      <c r="AC11" s="44"/>
-      <c r="AD11" s="48"/>
-      <c r="AE11" s="49"/>
-      <c r="AF11" s="50"/>
-      <c r="AG11" s="44"/>
-      <c r="AH11" s="44"/>
-      <c r="AI11" s="44"/>
-      <c r="AJ11" s="44"/>
-      <c r="AK11" s="44"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="43"/>
+      <c r="L11" s="47"/>
+      <c r="M11" s="43"/>
+      <c r="N11" s="48"/>
+      <c r="O11" s="49"/>
+      <c r="P11" s="43"/>
+      <c r="Q11" s="43"/>
+      <c r="R11" s="43"/>
+      <c r="S11" s="43"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="43"/>
+      <c r="V11" s="48"/>
+      <c r="W11" s="50"/>
+      <c r="X11" s="43"/>
+      <c r="Y11" s="43"/>
+      <c r="Z11" s="48"/>
+      <c r="AA11" s="49"/>
+      <c r="AB11" s="43"/>
+      <c r="AC11" s="43"/>
+      <c r="AD11" s="47"/>
+      <c r="AE11" s="48"/>
+      <c r="AF11" s="49"/>
+      <c r="AG11" s="43"/>
+      <c r="AH11" s="43"/>
+      <c r="AI11" s="43"/>
+      <c r="AJ11" s="43"/>
+      <c r="AK11" s="43"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="42"/>
-      <c r="C12" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="48"/>
-      <c r="M12" s="44"/>
-      <c r="N12" s="49"/>
-      <c r="O12" s="50"/>
-      <c r="P12" s="44"/>
-      <c r="Q12" s="44"/>
-      <c r="R12" s="44"/>
-      <c r="S12" s="44"/>
-      <c r="T12" s="44"/>
-      <c r="U12" s="44"/>
-      <c r="V12" s="49"/>
-      <c r="W12" s="51"/>
-      <c r="X12" s="44"/>
-      <c r="Y12" s="44"/>
-      <c r="Z12" s="49"/>
-      <c r="AA12" s="50"/>
-      <c r="AB12" s="44"/>
-      <c r="AC12" s="44"/>
-      <c r="AD12" s="48"/>
-      <c r="AE12" s="49"/>
-      <c r="AF12" s="47"/>
-      <c r="AG12" s="58"/>
-      <c r="AH12" s="58"/>
-      <c r="AI12" s="58"/>
-      <c r="AJ12" s="58"/>
-      <c r="AK12" s="58"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="48"/>
+      <c r="O12" s="49"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
+      <c r="V12" s="48"/>
+      <c r="W12" s="50"/>
+      <c r="X12" s="43"/>
+      <c r="Y12" s="43"/>
+      <c r="Z12" s="48"/>
+      <c r="AA12" s="49"/>
+      <c r="AB12" s="43"/>
+      <c r="AC12" s="43"/>
+      <c r="AD12" s="47"/>
+      <c r="AE12" s="48"/>
+      <c r="AF12" s="46"/>
+      <c r="AG12" s="57"/>
+      <c r="AH12" s="57"/>
+      <c r="AI12" s="57"/>
+      <c r="AJ12" s="57"/>
+      <c r="AK12" s="57"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="42"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="44"/>
-      <c r="K13" s="44"/>
-      <c r="L13" s="48"/>
-      <c r="M13" s="44"/>
-      <c r="N13" s="49"/>
-      <c r="O13" s="50"/>
-      <c r="P13" s="44"/>
-      <c r="Q13" s="44"/>
-      <c r="R13" s="44"/>
-      <c r="S13" s="44"/>
-      <c r="T13" s="44"/>
-      <c r="U13" s="44"/>
-      <c r="V13" s="49"/>
-      <c r="W13" s="51"/>
-      <c r="X13" s="44"/>
-      <c r="Y13" s="44"/>
-      <c r="Z13" s="49"/>
-      <c r="AA13" s="50"/>
-      <c r="AB13" s="44"/>
-      <c r="AC13" s="44"/>
-      <c r="AD13" s="48"/>
-      <c r="AE13" s="49"/>
-      <c r="AF13" s="50"/>
-      <c r="AG13" s="44"/>
-      <c r="AH13" s="44"/>
-      <c r="AI13" s="44"/>
-      <c r="AJ13" s="44"/>
-      <c r="AK13" s="44"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="47"/>
+      <c r="M13" s="43"/>
+      <c r="N13" s="48"/>
+      <c r="O13" s="49"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="43"/>
+      <c r="T13" s="43"/>
+      <c r="U13" s="43"/>
+      <c r="V13" s="48"/>
+      <c r="W13" s="50"/>
+      <c r="X13" s="43"/>
+      <c r="Y13" s="43"/>
+      <c r="Z13" s="48"/>
+      <c r="AA13" s="49"/>
+      <c r="AB13" s="43"/>
+      <c r="AC13" s="43"/>
+      <c r="AD13" s="47"/>
+      <c r="AE13" s="48"/>
+      <c r="AF13" s="49"/>
+      <c r="AG13" s="43"/>
+      <c r="AH13" s="43"/>
+      <c r="AI13" s="43"/>
+      <c r="AJ13" s="43"/>
+      <c r="AK13" s="43"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="59" t="s">
-        <v>92</v>
-      </c>
-      <c r="C14" s="60" t="s">
+      <c r="B14" s="58" t="s">
         <v>93</v>
       </c>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="48"/>
-      <c r="M14" s="62"/>
-      <c r="N14" s="63"/>
-      <c r="O14" s="61"/>
-      <c r="P14" s="62"/>
-      <c r="Q14" s="62"/>
-      <c r="R14" s="62"/>
-      <c r="S14" s="62"/>
-      <c r="T14" s="62"/>
-      <c r="U14" s="62"/>
-      <c r="V14" s="63"/>
-      <c r="W14" s="51"/>
-      <c r="X14" s="62"/>
-      <c r="Y14" s="62"/>
-      <c r="Z14" s="63"/>
-      <c r="AA14" s="61"/>
-      <c r="AB14" s="62"/>
-      <c r="AC14" s="62"/>
-      <c r="AD14" s="48"/>
-      <c r="AE14" s="63"/>
-      <c r="AF14" s="61"/>
-      <c r="AG14" s="62"/>
-      <c r="AH14" s="62"/>
-      <c r="AI14" s="62"/>
-      <c r="AJ14" s="62"/>
-      <c r="AK14" s="62"/>
+      <c r="C14" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="61"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="61"/>
+      <c r="N14" s="62"/>
+      <c r="O14" s="60"/>
+      <c r="P14" s="61"/>
+      <c r="Q14" s="61"/>
+      <c r="R14" s="61"/>
+      <c r="S14" s="61"/>
+      <c r="T14" s="61"/>
+      <c r="U14" s="61"/>
+      <c r="V14" s="62"/>
+      <c r="W14" s="50"/>
+      <c r="X14" s="61"/>
+      <c r="Y14" s="61"/>
+      <c r="Z14" s="62"/>
+      <c r="AA14" s="60"/>
+      <c r="AB14" s="61"/>
+      <c r="AC14" s="61"/>
+      <c r="AD14" s="47"/>
+      <c r="AE14" s="62"/>
+      <c r="AF14" s="60"/>
+      <c r="AG14" s="61"/>
+      <c r="AH14" s="61"/>
+      <c r="AI14" s="61"/>
+      <c r="AJ14" s="61"/>
+      <c r="AK14" s="61"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="59"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="61"/>
-      <c r="I15" s="62"/>
-      <c r="J15" s="62"/>
-      <c r="K15" s="62"/>
-      <c r="L15" s="48"/>
-      <c r="M15" s="62"/>
-      <c r="N15" s="63"/>
-      <c r="O15" s="61"/>
-      <c r="P15" s="62"/>
-      <c r="Q15" s="62"/>
-      <c r="R15" s="62"/>
-      <c r="S15" s="62"/>
-      <c r="T15" s="62"/>
-      <c r="U15" s="62"/>
-      <c r="V15" s="63"/>
-      <c r="W15" s="51"/>
-      <c r="X15" s="62"/>
-      <c r="Y15" s="62"/>
-      <c r="Z15" s="63"/>
-      <c r="AA15" s="61"/>
-      <c r="AB15" s="62"/>
-      <c r="AC15" s="62"/>
-      <c r="AD15" s="48"/>
-      <c r="AE15" s="63"/>
-      <c r="AF15" s="61"/>
-      <c r="AG15" s="62"/>
-      <c r="AH15" s="62"/>
-      <c r="AI15" s="62"/>
-      <c r="AJ15" s="62"/>
-      <c r="AK15" s="62"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="61"/>
+      <c r="L15" s="47"/>
+      <c r="M15" s="61"/>
+      <c r="N15" s="62"/>
+      <c r="O15" s="60"/>
+      <c r="P15" s="61"/>
+      <c r="Q15" s="61"/>
+      <c r="R15" s="61"/>
+      <c r="S15" s="61"/>
+      <c r="T15" s="61"/>
+      <c r="U15" s="61"/>
+      <c r="V15" s="62"/>
+      <c r="W15" s="50"/>
+      <c r="X15" s="61"/>
+      <c r="Y15" s="61"/>
+      <c r="Z15" s="62"/>
+      <c r="AA15" s="60"/>
+      <c r="AB15" s="61"/>
+      <c r="AC15" s="61"/>
+      <c r="AD15" s="47"/>
+      <c r="AE15" s="62"/>
+      <c r="AF15" s="60"/>
+      <c r="AG15" s="61"/>
+      <c r="AH15" s="61"/>
+      <c r="AI15" s="61"/>
+      <c r="AJ15" s="61"/>
+      <c r="AK15" s="61"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="59"/>
-      <c r="C16" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="63"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="62"/>
-      <c r="J16" s="62"/>
-      <c r="K16" s="62"/>
-      <c r="L16" s="48"/>
-      <c r="M16" s="62"/>
-      <c r="N16" s="63"/>
-      <c r="O16" s="61"/>
-      <c r="P16" s="62"/>
-      <c r="Q16" s="62"/>
-      <c r="R16" s="62"/>
-      <c r="S16" s="62"/>
-      <c r="T16" s="62"/>
-      <c r="U16" s="62"/>
-      <c r="V16" s="63"/>
-      <c r="W16" s="51"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="62"/>
-      <c r="Z16" s="63"/>
-      <c r="AA16" s="61"/>
-      <c r="AB16" s="62"/>
-      <c r="AC16" s="62"/>
-      <c r="AD16" s="48"/>
-      <c r="AE16" s="63"/>
-      <c r="AF16" s="61"/>
-      <c r="AG16" s="62"/>
-      <c r="AH16" s="62"/>
-      <c r="AI16" s="62"/>
-      <c r="AJ16" s="62"/>
-      <c r="AK16" s="62"/>
+      <c r="B16" s="58"/>
+      <c r="C16" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" s="57"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="62"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="61"/>
+      <c r="K16" s="61"/>
+      <c r="L16" s="47"/>
+      <c r="M16" s="61"/>
+      <c r="N16" s="62"/>
+      <c r="O16" s="60"/>
+      <c r="P16" s="61"/>
+      <c r="Q16" s="61"/>
+      <c r="R16" s="61"/>
+      <c r="S16" s="61"/>
+      <c r="T16" s="61"/>
+      <c r="U16" s="61"/>
+      <c r="V16" s="62"/>
+      <c r="W16" s="50"/>
+      <c r="X16" s="61"/>
+      <c r="Y16" s="61"/>
+      <c r="Z16" s="62"/>
+      <c r="AA16" s="60"/>
+      <c r="AB16" s="61"/>
+      <c r="AC16" s="61"/>
+      <c r="AD16" s="47"/>
+      <c r="AE16" s="62"/>
+      <c r="AF16" s="60"/>
+      <c r="AG16" s="61"/>
+      <c r="AH16" s="61"/>
+      <c r="AI16" s="61"/>
+      <c r="AJ16" s="61"/>
+      <c r="AK16" s="61"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="59"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="65"/>
-      <c r="G17" s="63"/>
-      <c r="H17" s="61"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="62"/>
-      <c r="L17" s="48"/>
-      <c r="M17" s="62"/>
-      <c r="N17" s="63"/>
-      <c r="O17" s="61"/>
-      <c r="P17" s="62"/>
-      <c r="Q17" s="62"/>
-      <c r="R17" s="62"/>
-      <c r="S17" s="62"/>
-      <c r="T17" s="62"/>
-      <c r="U17" s="62"/>
-      <c r="V17" s="63"/>
-      <c r="W17" s="51"/>
-      <c r="X17" s="62"/>
-      <c r="Y17" s="62"/>
-      <c r="Z17" s="63"/>
-      <c r="AA17" s="61"/>
-      <c r="AB17" s="62"/>
-      <c r="AC17" s="62"/>
-      <c r="AD17" s="48"/>
-      <c r="AE17" s="63"/>
-      <c r="AF17" s="61"/>
-      <c r="AG17" s="62"/>
-      <c r="AH17" s="62"/>
-      <c r="AI17" s="62"/>
-      <c r="AJ17" s="62"/>
-      <c r="AK17" s="62"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="64"/>
+      <c r="G17" s="62"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="61"/>
+      <c r="L17" s="47"/>
+      <c r="M17" s="61"/>
+      <c r="N17" s="62"/>
+      <c r="O17" s="60"/>
+      <c r="P17" s="61"/>
+      <c r="Q17" s="61"/>
+      <c r="R17" s="61"/>
+      <c r="S17" s="61"/>
+      <c r="T17" s="61"/>
+      <c r="U17" s="61"/>
+      <c r="V17" s="62"/>
+      <c r="W17" s="50"/>
+      <c r="X17" s="61"/>
+      <c r="Y17" s="61"/>
+      <c r="Z17" s="62"/>
+      <c r="AA17" s="60"/>
+      <c r="AB17" s="61"/>
+      <c r="AC17" s="61"/>
+      <c r="AD17" s="47"/>
+      <c r="AE17" s="62"/>
+      <c r="AF17" s="60"/>
+      <c r="AG17" s="61"/>
+      <c r="AH17" s="61"/>
+      <c r="AI17" s="61"/>
+      <c r="AJ17" s="61"/>
+      <c r="AK17" s="61"/>
       <c r="AN17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="59"/>
-      <c r="C18" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="63"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
-      <c r="L18" s="48"/>
-      <c r="M18" s="62"/>
-      <c r="N18" s="63"/>
-      <c r="O18" s="61"/>
-      <c r="P18" s="62"/>
-      <c r="Q18" s="62"/>
-      <c r="R18" s="62"/>
-      <c r="S18" s="62"/>
-      <c r="T18" s="62"/>
-      <c r="U18" s="62"/>
-      <c r="V18" s="63"/>
-      <c r="W18" s="51"/>
-      <c r="X18" s="62"/>
-      <c r="Y18" s="62"/>
-      <c r="Z18" s="63"/>
-      <c r="AA18" s="61"/>
-      <c r="AB18" s="62"/>
-      <c r="AC18" s="62"/>
-      <c r="AD18" s="48"/>
-      <c r="AE18" s="63"/>
-      <c r="AF18" s="61"/>
-      <c r="AG18" s="62"/>
-      <c r="AH18" s="62"/>
-      <c r="AI18" s="62"/>
-      <c r="AJ18" s="62"/>
-      <c r="AK18" s="62"/>
+      <c r="B18" s="58"/>
+      <c r="C18" s="59" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="64"/>
+      <c r="G18" s="62"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="61"/>
+      <c r="K18" s="61"/>
+      <c r="L18" s="47"/>
+      <c r="M18" s="61"/>
+      <c r="N18" s="62"/>
+      <c r="O18" s="60"/>
+      <c r="P18" s="61"/>
+      <c r="Q18" s="61"/>
+      <c r="R18" s="61"/>
+      <c r="S18" s="61"/>
+      <c r="T18" s="61"/>
+      <c r="U18" s="61"/>
+      <c r="V18" s="62"/>
+      <c r="W18" s="50"/>
+      <c r="X18" s="61"/>
+      <c r="Y18" s="61"/>
+      <c r="Z18" s="62"/>
+      <c r="AA18" s="60"/>
+      <c r="AB18" s="61"/>
+      <c r="AC18" s="61"/>
+      <c r="AD18" s="47"/>
+      <c r="AE18" s="62"/>
+      <c r="AF18" s="60"/>
+      <c r="AG18" s="61"/>
+      <c r="AH18" s="61"/>
+      <c r="AI18" s="61"/>
+      <c r="AJ18" s="61"/>
+      <c r="AK18" s="61"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="59"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="66"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="62"/>
-      <c r="N19" s="63"/>
-      <c r="O19" s="61"/>
-      <c r="P19" s="62"/>
-      <c r="Q19" s="62"/>
-      <c r="R19" s="62"/>
-      <c r="S19" s="62"/>
-      <c r="T19" s="62"/>
-      <c r="U19" s="62"/>
-      <c r="V19" s="63"/>
-      <c r="W19" s="51"/>
-      <c r="X19" s="62"/>
-      <c r="Y19" s="62"/>
-      <c r="Z19" s="63"/>
-      <c r="AA19" s="61"/>
-      <c r="AB19" s="62"/>
-      <c r="AC19" s="62"/>
-      <c r="AD19" s="48"/>
-      <c r="AE19" s="63"/>
-      <c r="AF19" s="61"/>
-      <c r="AG19" s="62"/>
-      <c r="AH19" s="62"/>
-      <c r="AI19" s="62"/>
-      <c r="AJ19" s="62"/>
-      <c r="AK19" s="62"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="62"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="61"/>
+      <c r="K19" s="61"/>
+      <c r="L19" s="47"/>
+      <c r="M19" s="61"/>
+      <c r="N19" s="62"/>
+      <c r="O19" s="60"/>
+      <c r="P19" s="61"/>
+      <c r="Q19" s="61"/>
+      <c r="R19" s="61"/>
+      <c r="S19" s="61"/>
+      <c r="T19" s="61"/>
+      <c r="U19" s="61"/>
+      <c r="V19" s="62"/>
+      <c r="W19" s="50"/>
+      <c r="X19" s="61"/>
+      <c r="Y19" s="61"/>
+      <c r="Z19" s="62"/>
+      <c r="AA19" s="60"/>
+      <c r="AB19" s="61"/>
+      <c r="AC19" s="61"/>
+      <c r="AD19" s="47"/>
+      <c r="AE19" s="62"/>
+      <c r="AF19" s="60"/>
+      <c r="AG19" s="61"/>
+      <c r="AH19" s="61"/>
+      <c r="AI19" s="61"/>
+      <c r="AJ19" s="61"/>
+      <c r="AK19" s="61"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="59"/>
-      <c r="C20" s="60" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" s="62"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62"/>
-      <c r="L20" s="48"/>
-      <c r="M20" s="62"/>
-      <c r="N20" s="63"/>
-      <c r="O20" s="61"/>
-      <c r="P20" s="62"/>
-      <c r="Q20" s="62"/>
-      <c r="R20" s="62"/>
-      <c r="S20" s="62"/>
-      <c r="T20" s="62"/>
-      <c r="U20" s="62"/>
-      <c r="V20" s="63"/>
-      <c r="W20" s="51"/>
-      <c r="X20" s="62"/>
-      <c r="Y20" s="62"/>
-      <c r="Z20" s="63"/>
-      <c r="AA20" s="61"/>
-      <c r="AB20" s="62"/>
-      <c r="AC20" s="62"/>
-      <c r="AD20" s="48"/>
-      <c r="AE20" s="63"/>
-      <c r="AF20" s="61"/>
-      <c r="AG20" s="62"/>
-      <c r="AH20" s="62"/>
-      <c r="AI20" s="62"/>
-      <c r="AJ20" s="62"/>
-      <c r="AK20" s="62"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="59" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="61"/>
+      <c r="L20" s="47"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="62"/>
+      <c r="O20" s="60"/>
+      <c r="P20" s="61"/>
+      <c r="Q20" s="61"/>
+      <c r="R20" s="61"/>
+      <c r="S20" s="61"/>
+      <c r="T20" s="61"/>
+      <c r="U20" s="61"/>
+      <c r="V20" s="62"/>
+      <c r="W20" s="50"/>
+      <c r="X20" s="61"/>
+      <c r="Y20" s="61"/>
+      <c r="Z20" s="62"/>
+      <c r="AA20" s="60"/>
+      <c r="AB20" s="61"/>
+      <c r="AC20" s="61"/>
+      <c r="AD20" s="47"/>
+      <c r="AE20" s="62"/>
+      <c r="AF20" s="60"/>
+      <c r="AG20" s="61"/>
+      <c r="AH20" s="61"/>
+      <c r="AI20" s="61"/>
+      <c r="AJ20" s="61"/>
+      <c r="AK20" s="61"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="59"/>
-      <c r="C21" s="60"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="63"/>
-      <c r="H21" s="61"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="62"/>
-      <c r="L21" s="48"/>
-      <c r="M21" s="62"/>
-      <c r="N21" s="63"/>
-      <c r="O21" s="61"/>
-      <c r="P21" s="62"/>
-      <c r="Q21" s="62"/>
-      <c r="R21" s="62"/>
-      <c r="S21" s="62"/>
-      <c r="T21" s="62"/>
-      <c r="U21" s="62"/>
-      <c r="V21" s="63"/>
-      <c r="W21" s="51"/>
-      <c r="X21" s="62"/>
-      <c r="Y21" s="62"/>
-      <c r="Z21" s="63"/>
-      <c r="AA21" s="61"/>
-      <c r="AB21" s="62"/>
-      <c r="AC21" s="62"/>
-      <c r="AD21" s="48"/>
-      <c r="AE21" s="63"/>
-      <c r="AF21" s="61"/>
-      <c r="AG21" s="62"/>
-      <c r="AH21" s="62"/>
-      <c r="AI21" s="62"/>
-      <c r="AJ21" s="62"/>
-      <c r="AK21" s="62"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="61"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="61"/>
+      <c r="K21" s="61"/>
+      <c r="L21" s="47"/>
+      <c r="M21" s="61"/>
+      <c r="N21" s="62"/>
+      <c r="O21" s="60"/>
+      <c r="P21" s="61"/>
+      <c r="Q21" s="61"/>
+      <c r="R21" s="61"/>
+      <c r="S21" s="61"/>
+      <c r="T21" s="61"/>
+      <c r="U21" s="61"/>
+      <c r="V21" s="62"/>
+      <c r="W21" s="50"/>
+      <c r="X21" s="61"/>
+      <c r="Y21" s="61"/>
+      <c r="Z21" s="62"/>
+      <c r="AA21" s="60"/>
+      <c r="AB21" s="61"/>
+      <c r="AC21" s="61"/>
+      <c r="AD21" s="47"/>
+      <c r="AE21" s="62"/>
+      <c r="AF21" s="60"/>
+      <c r="AG21" s="61"/>
+      <c r="AH21" s="61"/>
+      <c r="AI21" s="61"/>
+      <c r="AJ21" s="61"/>
+      <c r="AK21" s="61"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="59"/>
-      <c r="C22" s="60" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="62"/>
-      <c r="K22" s="62"/>
-      <c r="L22" s="48"/>
-      <c r="M22" s="62"/>
-      <c r="N22" s="63"/>
-      <c r="O22" s="61"/>
-      <c r="P22" s="62"/>
-      <c r="Q22" s="62"/>
-      <c r="R22" s="62"/>
-      <c r="S22" s="62"/>
-      <c r="T22" s="62"/>
-      <c r="U22" s="62"/>
-      <c r="V22" s="63"/>
-      <c r="W22" s="51"/>
-      <c r="X22" s="62"/>
-      <c r="Y22" s="62"/>
-      <c r="Z22" s="63"/>
-      <c r="AA22" s="61"/>
-      <c r="AB22" s="62"/>
-      <c r="AC22" s="62"/>
-      <c r="AD22" s="48"/>
-      <c r="AE22" s="63"/>
-      <c r="AF22" s="61"/>
-      <c r="AG22" s="62"/>
-      <c r="AH22" s="62"/>
-      <c r="AI22" s="62"/>
-      <c r="AJ22" s="62"/>
-      <c r="AK22" s="62"/>
+      <c r="B22" s="58"/>
+      <c r="C22" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="64"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="61"/>
+      <c r="K22" s="61"/>
+      <c r="L22" s="47"/>
+      <c r="M22" s="61"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="60"/>
+      <c r="P22" s="61"/>
+      <c r="Q22" s="61"/>
+      <c r="R22" s="61"/>
+      <c r="S22" s="61"/>
+      <c r="T22" s="61"/>
+      <c r="U22" s="61"/>
+      <c r="V22" s="62"/>
+      <c r="W22" s="50"/>
+      <c r="X22" s="61"/>
+      <c r="Y22" s="61"/>
+      <c r="Z22" s="62"/>
+      <c r="AA22" s="60"/>
+      <c r="AB22" s="61"/>
+      <c r="AC22" s="61"/>
+      <c r="AD22" s="47"/>
+      <c r="AE22" s="62"/>
+      <c r="AF22" s="60"/>
+      <c r="AG22" s="61"/>
+      <c r="AH22" s="61"/>
+      <c r="AI22" s="61"/>
+      <c r="AJ22" s="61"/>
+      <c r="AK22" s="61"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="59"/>
-      <c r="C23" s="60"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="61"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="53"/>
-      <c r="K23" s="62"/>
-      <c r="L23" s="48"/>
-      <c r="M23" s="62"/>
-      <c r="N23" s="63"/>
-      <c r="O23" s="61"/>
-      <c r="P23" s="62"/>
-      <c r="Q23" s="62"/>
-      <c r="R23" s="62"/>
-      <c r="S23" s="62"/>
-      <c r="T23" s="62"/>
-      <c r="U23" s="62"/>
-      <c r="V23" s="63"/>
-      <c r="W23" s="51"/>
-      <c r="X23" s="62"/>
-      <c r="Y23" s="62"/>
-      <c r="Z23" s="63"/>
-      <c r="AA23" s="61"/>
-      <c r="AB23" s="62"/>
-      <c r="AC23" s="62"/>
-      <c r="AD23" s="48"/>
-      <c r="AE23" s="63"/>
-      <c r="AF23" s="61"/>
-      <c r="AG23" s="62"/>
-      <c r="AH23" s="62"/>
-      <c r="AI23" s="62"/>
-      <c r="AJ23" s="62"/>
-      <c r="AK23" s="62"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="64"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="52"/>
+      <c r="K23" s="61"/>
+      <c r="L23" s="47"/>
+      <c r="M23" s="61"/>
+      <c r="N23" s="62"/>
+      <c r="O23" s="60"/>
+      <c r="P23" s="61"/>
+      <c r="Q23" s="61"/>
+      <c r="R23" s="61"/>
+      <c r="S23" s="61"/>
+      <c r="T23" s="61"/>
+      <c r="U23" s="61"/>
+      <c r="V23" s="62"/>
+      <c r="W23" s="50"/>
+      <c r="X23" s="61"/>
+      <c r="Y23" s="61"/>
+      <c r="Z23" s="62"/>
+      <c r="AA23" s="60"/>
+      <c r="AB23" s="61"/>
+      <c r="AC23" s="61"/>
+      <c r="AD23" s="47"/>
+      <c r="AE23" s="62"/>
+      <c r="AF23" s="60"/>
+      <c r="AG23" s="61"/>
+      <c r="AH23" s="61"/>
+      <c r="AI23" s="61"/>
+      <c r="AJ23" s="61"/>
+      <c r="AK23" s="61"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="59"/>
-      <c r="C24" s="60" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" s="62"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="63"/>
-      <c r="H24" s="61"/>
-      <c r="I24" s="58"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="62"/>
-      <c r="L24" s="48"/>
-      <c r="M24" s="62"/>
-      <c r="N24" s="63"/>
-      <c r="O24" s="61"/>
-      <c r="P24" s="62"/>
-      <c r="Q24" s="62"/>
-      <c r="R24" s="62"/>
-      <c r="S24" s="62"/>
-      <c r="T24" s="62"/>
-      <c r="U24" s="62"/>
-      <c r="V24" s="63"/>
-      <c r="W24" s="51"/>
-      <c r="X24" s="62"/>
-      <c r="Y24" s="62"/>
-      <c r="Z24" s="63"/>
-      <c r="AA24" s="61"/>
-      <c r="AB24" s="62"/>
-      <c r="AC24" s="62"/>
-      <c r="AD24" s="48"/>
-      <c r="AE24" s="63"/>
-      <c r="AF24" s="61"/>
-      <c r="AG24" s="62"/>
-      <c r="AH24" s="62"/>
-      <c r="AI24" s="62"/>
-      <c r="AJ24" s="62"/>
-      <c r="AK24" s="62"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="59" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="61"/>
+      <c r="E24" s="61"/>
+      <c r="F24" s="64"/>
+      <c r="G24" s="62"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="61"/>
+      <c r="K24" s="61"/>
+      <c r="L24" s="47"/>
+      <c r="M24" s="61"/>
+      <c r="N24" s="62"/>
+      <c r="O24" s="60"/>
+      <c r="P24" s="61"/>
+      <c r="Q24" s="61"/>
+      <c r="R24" s="61"/>
+      <c r="S24" s="61"/>
+      <c r="T24" s="61"/>
+      <c r="U24" s="61"/>
+      <c r="V24" s="62"/>
+      <c r="W24" s="50"/>
+      <c r="X24" s="61"/>
+      <c r="Y24" s="61"/>
+      <c r="Z24" s="62"/>
+      <c r="AA24" s="60"/>
+      <c r="AB24" s="61"/>
+      <c r="AC24" s="61"/>
+      <c r="AD24" s="47"/>
+      <c r="AE24" s="62"/>
+      <c r="AF24" s="60"/>
+      <c r="AG24" s="61"/>
+      <c r="AH24" s="61"/>
+      <c r="AI24" s="61"/>
+      <c r="AJ24" s="61"/>
+      <c r="AK24" s="61"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="59"/>
-      <c r="C25" s="60"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="63"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="53"/>
-      <c r="K25" s="62"/>
-      <c r="L25" s="48"/>
-      <c r="M25" s="62"/>
-      <c r="N25" s="63"/>
-      <c r="O25" s="61"/>
-      <c r="P25" s="62"/>
-      <c r="Q25" s="62"/>
-      <c r="R25" s="62"/>
-      <c r="S25" s="62"/>
-      <c r="T25" s="62"/>
-      <c r="U25" s="62"/>
-      <c r="V25" s="63"/>
-      <c r="W25" s="51"/>
-      <c r="X25" s="62"/>
-      <c r="Y25" s="62"/>
-      <c r="Z25" s="63"/>
-      <c r="AA25" s="61"/>
-      <c r="AB25" s="62"/>
-      <c r="AC25" s="62"/>
-      <c r="AD25" s="48"/>
-      <c r="AE25" s="63"/>
-      <c r="AF25" s="61"/>
-      <c r="AG25" s="62"/>
-      <c r="AH25" s="62"/>
-      <c r="AI25" s="62"/>
-      <c r="AJ25" s="62"/>
-      <c r="AK25" s="62"/>
+      <c r="B25" s="58"/>
+      <c r="C25" s="59"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="64"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="52"/>
+      <c r="K25" s="61"/>
+      <c r="L25" s="47"/>
+      <c r="M25" s="61"/>
+      <c r="N25" s="62"/>
+      <c r="O25" s="60"/>
+      <c r="P25" s="61"/>
+      <c r="Q25" s="61"/>
+      <c r="R25" s="61"/>
+      <c r="S25" s="61"/>
+      <c r="T25" s="61"/>
+      <c r="U25" s="61"/>
+      <c r="V25" s="62"/>
+      <c r="W25" s="50"/>
+      <c r="X25" s="61"/>
+      <c r="Y25" s="61"/>
+      <c r="Z25" s="62"/>
+      <c r="AA25" s="60"/>
+      <c r="AB25" s="61"/>
+      <c r="AC25" s="61"/>
+      <c r="AD25" s="47"/>
+      <c r="AE25" s="62"/>
+      <c r="AF25" s="60"/>
+      <c r="AG25" s="61"/>
+      <c r="AH25" s="61"/>
+      <c r="AI25" s="61"/>
+      <c r="AJ25" s="61"/>
+      <c r="AK25" s="61"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="C26" s="43" t="s">
+      <c r="B26" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="52"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="44"/>
-      <c r="K26" s="44"/>
-      <c r="L26" s="48"/>
-      <c r="M26" s="44"/>
-      <c r="N26" s="49"/>
-      <c r="O26" s="50"/>
-      <c r="P26" s="44"/>
-      <c r="Q26" s="44"/>
-      <c r="R26" s="44"/>
-      <c r="S26" s="44"/>
-      <c r="T26" s="44"/>
-      <c r="U26" s="44"/>
-      <c r="V26" s="49"/>
-      <c r="W26" s="51"/>
-      <c r="X26" s="44"/>
-      <c r="Y26" s="44"/>
-      <c r="Z26" s="49"/>
-      <c r="AA26" s="50"/>
-      <c r="AB26" s="44"/>
-      <c r="AC26" s="44"/>
-      <c r="AD26" s="48"/>
-      <c r="AE26" s="49"/>
-      <c r="AF26" s="50"/>
-      <c r="AG26" s="44"/>
-      <c r="AH26" s="44"/>
-      <c r="AI26" s="44"/>
-      <c r="AJ26" s="44"/>
-      <c r="AK26" s="44"/>
+      <c r="C26" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="51"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="47"/>
+      <c r="M26" s="43"/>
+      <c r="N26" s="48"/>
+      <c r="O26" s="49"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="48"/>
+      <c r="W26" s="50"/>
+      <c r="X26" s="43"/>
+      <c r="Y26" s="43"/>
+      <c r="Z26" s="48"/>
+      <c r="AA26" s="49"/>
+      <c r="AB26" s="43"/>
+      <c r="AC26" s="43"/>
+      <c r="AD26" s="47"/>
+      <c r="AE26" s="48"/>
+      <c r="AF26" s="49"/>
+      <c r="AG26" s="43"/>
+      <c r="AH26" s="43"/>
+      <c r="AI26" s="43"/>
+      <c r="AJ26" s="43"/>
+      <c r="AK26" s="43"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="42"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="52"/>
-      <c r="G27" s="55"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="44"/>
-      <c r="J27" s="44"/>
-      <c r="K27" s="44"/>
-      <c r="L27" s="48"/>
-      <c r="M27" s="44"/>
-      <c r="N27" s="49"/>
-      <c r="O27" s="50"/>
-      <c r="P27" s="44"/>
-      <c r="Q27" s="44"/>
-      <c r="R27" s="44"/>
-      <c r="S27" s="44"/>
-      <c r="T27" s="44"/>
-      <c r="U27" s="44"/>
-      <c r="V27" s="49"/>
-      <c r="W27" s="51"/>
-      <c r="X27" s="44"/>
-      <c r="Y27" s="44"/>
-      <c r="Z27" s="49"/>
-      <c r="AA27" s="50"/>
-      <c r="AB27" s="44"/>
-      <c r="AC27" s="44"/>
-      <c r="AD27" s="48"/>
-      <c r="AE27" s="49"/>
-      <c r="AF27" s="50"/>
-      <c r="AG27" s="44"/>
-      <c r="AH27" s="44"/>
-      <c r="AI27" s="44"/>
-      <c r="AJ27" s="44"/>
-      <c r="AK27" s="44"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="54"/>
+      <c r="H27" s="55"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="47"/>
+      <c r="M27" s="43"/>
+      <c r="N27" s="48"/>
+      <c r="O27" s="49"/>
+      <c r="P27" s="43"/>
+      <c r="Q27" s="43"/>
+      <c r="R27" s="43"/>
+      <c r="S27" s="43"/>
+      <c r="T27" s="43"/>
+      <c r="U27" s="43"/>
+      <c r="V27" s="48"/>
+      <c r="W27" s="50"/>
+      <c r="X27" s="43"/>
+      <c r="Y27" s="43"/>
+      <c r="Z27" s="48"/>
+      <c r="AA27" s="49"/>
+      <c r="AB27" s="43"/>
+      <c r="AC27" s="43"/>
+      <c r="AD27" s="47"/>
+      <c r="AE27" s="48"/>
+      <c r="AF27" s="49"/>
+      <c r="AG27" s="43"/>
+      <c r="AH27" s="43"/>
+      <c r="AI27" s="43"/>
+      <c r="AJ27" s="43"/>
+      <c r="AK27" s="43"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="42"/>
-      <c r="C28" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="52"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="47"/>
-      <c r="I28" s="58"/>
-      <c r="J28" s="58"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="48"/>
-      <c r="M28" s="44"/>
-      <c r="N28" s="49"/>
-      <c r="O28" s="50"/>
-      <c r="P28" s="44"/>
-      <c r="Q28" s="44"/>
-      <c r="R28" s="44"/>
-      <c r="S28" s="44"/>
-      <c r="T28" s="44"/>
-      <c r="U28" s="44"/>
-      <c r="V28" s="49"/>
-      <c r="W28" s="51"/>
-      <c r="X28" s="44"/>
-      <c r="Y28" s="44"/>
-      <c r="Z28" s="49"/>
-      <c r="AA28" s="50"/>
-      <c r="AB28" s="44"/>
-      <c r="AC28" s="44"/>
-      <c r="AD28" s="48"/>
-      <c r="AE28" s="49"/>
-      <c r="AF28" s="50"/>
-      <c r="AG28" s="44"/>
-      <c r="AH28" s="44"/>
-      <c r="AI28" s="44"/>
-      <c r="AJ28" s="44"/>
-      <c r="AK28" s="44"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="57"/>
+      <c r="K28" s="57"/>
+      <c r="L28" s="47"/>
+      <c r="M28" s="43"/>
+      <c r="N28" s="48"/>
+      <c r="O28" s="49"/>
+      <c r="P28" s="43"/>
+      <c r="Q28" s="43"/>
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="43"/>
+      <c r="U28" s="43"/>
+      <c r="V28" s="48"/>
+      <c r="W28" s="50"/>
+      <c r="X28" s="43"/>
+      <c r="Y28" s="43"/>
+      <c r="Z28" s="48"/>
+      <c r="AA28" s="49"/>
+      <c r="AB28" s="43"/>
+      <c r="AC28" s="43"/>
+      <c r="AD28" s="47"/>
+      <c r="AE28" s="48"/>
+      <c r="AF28" s="49"/>
+      <c r="AG28" s="43"/>
+      <c r="AH28" s="43"/>
+      <c r="AI28" s="43"/>
+      <c r="AJ28" s="43"/>
+      <c r="AK28" s="43"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="42"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="52"/>
-      <c r="G29" s="55"/>
-      <c r="H29" s="56"/>
-      <c r="I29" s="44"/>
-      <c r="J29" s="67"/>
-      <c r="K29" s="44"/>
-      <c r="L29" s="48"/>
-      <c r="M29" s="44"/>
-      <c r="N29" s="49"/>
-      <c r="O29" s="50"/>
-      <c r="P29" s="44"/>
-      <c r="Q29" s="44"/>
-      <c r="R29" s="44"/>
-      <c r="S29" s="44"/>
-      <c r="T29" s="44"/>
-      <c r="U29" s="44"/>
-      <c r="V29" s="49"/>
-      <c r="W29" s="51"/>
-      <c r="X29" s="44"/>
-      <c r="Y29" s="44"/>
-      <c r="Z29" s="49"/>
-      <c r="AA29" s="50"/>
-      <c r="AB29" s="44"/>
-      <c r="AC29" s="44"/>
-      <c r="AD29" s="48"/>
-      <c r="AE29" s="49"/>
-      <c r="AF29" s="50"/>
-      <c r="AG29" s="44"/>
-      <c r="AH29" s="44"/>
-      <c r="AI29" s="44"/>
-      <c r="AJ29" s="44"/>
-      <c r="AK29" s="44"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="51"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="66"/>
+      <c r="K29" s="43"/>
+      <c r="L29" s="47"/>
+      <c r="M29" s="43"/>
+      <c r="N29" s="48"/>
+      <c r="O29" s="49"/>
+      <c r="P29" s="43"/>
+      <c r="Q29" s="43"/>
+      <c r="R29" s="43"/>
+      <c r="S29" s="43"/>
+      <c r="T29" s="43"/>
+      <c r="U29" s="43"/>
+      <c r="V29" s="48"/>
+      <c r="W29" s="50"/>
+      <c r="X29" s="43"/>
+      <c r="Y29" s="43"/>
+      <c r="Z29" s="48"/>
+      <c r="AA29" s="49"/>
+      <c r="AB29" s="43"/>
+      <c r="AC29" s="43"/>
+      <c r="AD29" s="47"/>
+      <c r="AE29" s="48"/>
+      <c r="AF29" s="49"/>
+      <c r="AG29" s="43"/>
+      <c r="AH29" s="43"/>
+      <c r="AI29" s="43"/>
+      <c r="AJ29" s="43"/>
+      <c r="AK29" s="43"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="42"/>
-      <c r="C30" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="47"/>
-      <c r="I30" s="58"/>
-      <c r="J30" s="58"/>
-      <c r="K30" s="58"/>
-      <c r="L30" s="48"/>
-      <c r="M30" s="58"/>
-      <c r="N30" s="49"/>
-      <c r="O30" s="50"/>
-      <c r="P30" s="44"/>
-      <c r="Q30" s="44"/>
-      <c r="R30" s="44"/>
-      <c r="S30" s="44"/>
-      <c r="T30" s="44"/>
-      <c r="U30" s="44"/>
-      <c r="V30" s="49"/>
-      <c r="W30" s="51"/>
-      <c r="X30" s="44"/>
-      <c r="Y30" s="44"/>
-      <c r="Z30" s="49"/>
-      <c r="AA30" s="50"/>
-      <c r="AB30" s="44"/>
-      <c r="AC30" s="44"/>
-      <c r="AD30" s="48"/>
-      <c r="AE30" s="49"/>
-      <c r="AF30" s="50"/>
-      <c r="AG30" s="44"/>
-      <c r="AH30" s="44"/>
-      <c r="AI30" s="44"/>
-      <c r="AJ30" s="44"/>
-      <c r="AK30" s="44"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="42" t="s">
+        <v>104</v>
+      </c>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="47"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="48"/>
+      <c r="O30" s="49"/>
+      <c r="P30" s="43"/>
+      <c r="Q30" s="43"/>
+      <c r="R30" s="43"/>
+      <c r="S30" s="43"/>
+      <c r="T30" s="43"/>
+      <c r="U30" s="43"/>
+      <c r="V30" s="48"/>
+      <c r="W30" s="50"/>
+      <c r="X30" s="43"/>
+      <c r="Y30" s="43"/>
+      <c r="Z30" s="48"/>
+      <c r="AA30" s="49"/>
+      <c r="AB30" s="43"/>
+      <c r="AC30" s="43"/>
+      <c r="AD30" s="47"/>
+      <c r="AE30" s="48"/>
+      <c r="AF30" s="49"/>
+      <c r="AG30" s="43"/>
+      <c r="AH30" s="43"/>
+      <c r="AI30" s="43"/>
+      <c r="AJ30" s="43"/>
+      <c r="AK30" s="43"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="42"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="44"/>
-      <c r="E31" s="44"/>
-      <c r="F31" s="54"/>
-      <c r="G31" s="55"/>
-      <c r="H31" s="56"/>
-      <c r="I31" s="44"/>
-      <c r="J31" s="67"/>
-      <c r="K31" s="67"/>
-      <c r="L31" s="68"/>
-      <c r="M31" s="44"/>
-      <c r="N31" s="55"/>
-      <c r="O31" s="50"/>
-      <c r="P31" s="44"/>
-      <c r="Q31" s="44"/>
-      <c r="R31" s="44"/>
-      <c r="S31" s="44"/>
-      <c r="T31" s="44"/>
-      <c r="U31" s="44"/>
-      <c r="V31" s="49"/>
-      <c r="W31" s="51"/>
-      <c r="X31" s="44"/>
-      <c r="Y31" s="44"/>
-      <c r="Z31" s="49"/>
-      <c r="AA31" s="50"/>
-      <c r="AB31" s="44"/>
-      <c r="AC31" s="44"/>
-      <c r="AD31" s="48"/>
-      <c r="AE31" s="49"/>
-      <c r="AF31" s="50"/>
-      <c r="AG31" s="44"/>
-      <c r="AH31" s="44"/>
-      <c r="AI31" s="44"/>
-      <c r="AJ31" s="44"/>
-      <c r="AK31" s="44"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="66"/>
+      <c r="K31" s="66"/>
+      <c r="L31" s="67"/>
+      <c r="M31" s="43"/>
+      <c r="N31" s="54"/>
+      <c r="O31" s="49"/>
+      <c r="P31" s="43"/>
+      <c r="Q31" s="43"/>
+      <c r="R31" s="43"/>
+      <c r="S31" s="43"/>
+      <c r="T31" s="43"/>
+      <c r="U31" s="43"/>
+      <c r="V31" s="48"/>
+      <c r="W31" s="50"/>
+      <c r="X31" s="43"/>
+      <c r="Y31" s="43"/>
+      <c r="Z31" s="48"/>
+      <c r="AA31" s="49"/>
+      <c r="AB31" s="43"/>
+      <c r="AC31" s="43"/>
+      <c r="AD31" s="47"/>
+      <c r="AE31" s="48"/>
+      <c r="AF31" s="49"/>
+      <c r="AG31" s="43"/>
+      <c r="AH31" s="43"/>
+      <c r="AI31" s="43"/>
+      <c r="AJ31" s="43"/>
+      <c r="AK31" s="43"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="42"/>
-      <c r="C32" s="43" t="s">
-        <v>104</v>
-      </c>
-      <c r="D32" s="44"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="50"/>
-      <c r="I32" s="44"/>
-      <c r="J32" s="44"/>
-      <c r="K32" s="44"/>
-      <c r="L32" s="48"/>
-      <c r="M32" s="58"/>
-      <c r="N32" s="46"/>
-      <c r="O32" s="50"/>
-      <c r="P32" s="44"/>
-      <c r="Q32" s="44"/>
-      <c r="R32" s="44"/>
-      <c r="S32" s="44"/>
-      <c r="T32" s="44"/>
-      <c r="U32" s="44"/>
-      <c r="V32" s="49"/>
-      <c r="W32" s="51"/>
-      <c r="X32" s="44"/>
-      <c r="Y32" s="44"/>
-      <c r="Z32" s="49"/>
-      <c r="AA32" s="50"/>
-      <c r="AB32" s="44"/>
-      <c r="AC32" s="44"/>
-      <c r="AD32" s="48"/>
-      <c r="AE32" s="49"/>
-      <c r="AF32" s="50"/>
-      <c r="AG32" s="44"/>
-      <c r="AH32" s="44"/>
-      <c r="AI32" s="44"/>
-      <c r="AJ32" s="44"/>
-      <c r="AK32" s="44"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="48"/>
+      <c r="H32" s="49"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="43"/>
+      <c r="L32" s="47"/>
+      <c r="M32" s="57"/>
+      <c r="N32" s="45"/>
+      <c r="O32" s="49"/>
+      <c r="P32" s="43"/>
+      <c r="Q32" s="43"/>
+      <c r="R32" s="43"/>
+      <c r="S32" s="43"/>
+      <c r="T32" s="43"/>
+      <c r="U32" s="43"/>
+      <c r="V32" s="48"/>
+      <c r="W32" s="50"/>
+      <c r="X32" s="43"/>
+      <c r="Y32" s="43"/>
+      <c r="Z32" s="48"/>
+      <c r="AA32" s="49"/>
+      <c r="AB32" s="43"/>
+      <c r="AC32" s="43"/>
+      <c r="AD32" s="47"/>
+      <c r="AE32" s="48"/>
+      <c r="AF32" s="49"/>
+      <c r="AG32" s="43"/>
+      <c r="AH32" s="43"/>
+      <c r="AI32" s="43"/>
+      <c r="AJ32" s="43"/>
+      <c r="AK32" s="43"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="42"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="44"/>
-      <c r="E33" s="44"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="49"/>
-      <c r="H33" s="50"/>
-      <c r="I33" s="44"/>
-      <c r="J33" s="44"/>
-      <c r="K33" s="44"/>
-      <c r="L33" s="48"/>
-      <c r="M33" s="44"/>
-      <c r="N33" s="55"/>
-      <c r="O33" s="50"/>
-      <c r="P33" s="44"/>
-      <c r="Q33" s="44"/>
-      <c r="R33" s="44"/>
-      <c r="S33" s="44"/>
-      <c r="T33" s="44"/>
-      <c r="U33" s="44"/>
-      <c r="V33" s="49"/>
-      <c r="W33" s="51"/>
-      <c r="X33" s="44"/>
-      <c r="Y33" s="44"/>
-      <c r="Z33" s="49"/>
-      <c r="AA33" s="50"/>
-      <c r="AB33" s="44"/>
-      <c r="AC33" s="44"/>
-      <c r="AD33" s="48"/>
-      <c r="AE33" s="49"/>
-      <c r="AF33" s="50"/>
-      <c r="AG33" s="44"/>
-      <c r="AH33" s="44"/>
-      <c r="AI33" s="44"/>
-      <c r="AJ33" s="44"/>
-      <c r="AK33" s="44"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="42"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="43"/>
+      <c r="L33" s="47"/>
+      <c r="M33" s="43"/>
+      <c r="N33" s="54"/>
+      <c r="O33" s="49"/>
+      <c r="P33" s="43"/>
+      <c r="Q33" s="43"/>
+      <c r="R33" s="43"/>
+      <c r="S33" s="43"/>
+      <c r="T33" s="43"/>
+      <c r="U33" s="43"/>
+      <c r="V33" s="48"/>
+      <c r="W33" s="50"/>
+      <c r="X33" s="43"/>
+      <c r="Y33" s="43"/>
+      <c r="Z33" s="48"/>
+      <c r="AA33" s="49"/>
+      <c r="AB33" s="43"/>
+      <c r="AC33" s="43"/>
+      <c r="AD33" s="47"/>
+      <c r="AE33" s="48"/>
+      <c r="AF33" s="49"/>
+      <c r="AG33" s="43"/>
+      <c r="AH33" s="43"/>
+      <c r="AI33" s="43"/>
+      <c r="AJ33" s="43"/>
+      <c r="AK33" s="43"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="59" t="s">
-        <v>105</v>
-      </c>
-      <c r="C34" s="69" t="s">
+      <c r="B34" s="58" t="s">
         <v>106</v>
       </c>
-      <c r="D34" s="62"/>
-      <c r="E34" s="62"/>
-      <c r="F34" s="65"/>
-      <c r="G34" s="63"/>
-      <c r="H34" s="61"/>
-      <c r="I34" s="62"/>
-      <c r="J34" s="62"/>
-      <c r="K34" s="62"/>
-      <c r="L34" s="48"/>
-      <c r="M34" s="58"/>
-      <c r="N34" s="46"/>
-      <c r="O34" s="47"/>
-      <c r="P34" s="58"/>
-      <c r="Q34" s="58"/>
-      <c r="R34" s="58"/>
-      <c r="S34" s="62"/>
-      <c r="T34" s="62"/>
-      <c r="U34" s="62"/>
-      <c r="V34" s="63"/>
-      <c r="W34" s="51"/>
-      <c r="X34" s="62"/>
-      <c r="Y34" s="62"/>
-      <c r="Z34" s="63"/>
-      <c r="AA34" s="61"/>
-      <c r="AB34" s="62"/>
-      <c r="AC34" s="62"/>
-      <c r="AD34" s="48"/>
-      <c r="AE34" s="63"/>
-      <c r="AF34" s="61"/>
-      <c r="AG34" s="62"/>
-      <c r="AH34" s="62"/>
-      <c r="AI34" s="62"/>
-      <c r="AJ34" s="62"/>
-      <c r="AK34" s="62"/>
+      <c r="C34" s="68" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" s="61"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="64"/>
+      <c r="G34" s="62"/>
+      <c r="H34" s="60"/>
+      <c r="I34" s="61"/>
+      <c r="J34" s="61"/>
+      <c r="K34" s="61"/>
+      <c r="L34" s="47"/>
+      <c r="M34" s="57"/>
+      <c r="N34" s="45"/>
+      <c r="O34" s="46"/>
+      <c r="P34" s="57"/>
+      <c r="Q34" s="57"/>
+      <c r="R34" s="57"/>
+      <c r="S34" s="61"/>
+      <c r="T34" s="61"/>
+      <c r="U34" s="61"/>
+      <c r="V34" s="62"/>
+      <c r="W34" s="50"/>
+      <c r="X34" s="61"/>
+      <c r="Y34" s="61"/>
+      <c r="Z34" s="62"/>
+      <c r="AA34" s="60"/>
+      <c r="AB34" s="61"/>
+      <c r="AC34" s="61"/>
+      <c r="AD34" s="47"/>
+      <c r="AE34" s="62"/>
+      <c r="AF34" s="60"/>
+      <c r="AG34" s="61"/>
+      <c r="AH34" s="61"/>
+      <c r="AI34" s="61"/>
+      <c r="AJ34" s="61"/>
+      <c r="AK34" s="61"/>
     </row>
     <row r="35" ht="12" customHeight="1">
-      <c r="B35" s="59"/>
-      <c r="C35" s="69"/>
-      <c r="D35" s="62"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="63"/>
-      <c r="H35" s="61"/>
-      <c r="I35" s="62"/>
-      <c r="J35" s="62"/>
-      <c r="K35" s="70"/>
-      <c r="L35" s="48"/>
-      <c r="M35" s="62"/>
-      <c r="N35" s="55"/>
-      <c r="O35" s="61"/>
-      <c r="P35" s="57"/>
-      <c r="Q35" s="62"/>
-      <c r="R35" s="62"/>
-      <c r="S35" s="62"/>
-      <c r="T35" s="62"/>
-      <c r="U35" s="62"/>
-      <c r="V35" s="63"/>
-      <c r="W35" s="51"/>
-      <c r="X35" s="62"/>
-      <c r="Y35" s="62"/>
-      <c r="Z35" s="63"/>
-      <c r="AA35" s="61"/>
-      <c r="AB35" s="62"/>
-      <c r="AC35" s="62"/>
-      <c r="AD35" s="48"/>
-      <c r="AE35" s="63"/>
-      <c r="AF35" s="61"/>
-      <c r="AG35" s="62"/>
-      <c r="AH35" s="62"/>
-      <c r="AI35" s="62"/>
-      <c r="AJ35" s="62"/>
-      <c r="AK35" s="62"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="68"/>
+      <c r="D35" s="61"/>
+      <c r="E35" s="61"/>
+      <c r="F35" s="64"/>
+      <c r="G35" s="62"/>
+      <c r="H35" s="60"/>
+      <c r="I35" s="61"/>
+      <c r="J35" s="61"/>
+      <c r="K35" s="69"/>
+      <c r="L35" s="47"/>
+      <c r="M35" s="61"/>
+      <c r="N35" s="54"/>
+      <c r="O35" s="60"/>
+      <c r="P35" s="56"/>
+      <c r="Q35" s="61"/>
+      <c r="R35" s="61"/>
+      <c r="S35" s="61"/>
+      <c r="T35" s="61"/>
+      <c r="U35" s="61"/>
+      <c r="V35" s="62"/>
+      <c r="W35" s="50"/>
+      <c r="X35" s="61"/>
+      <c r="Y35" s="61"/>
+      <c r="Z35" s="62"/>
+      <c r="AA35" s="60"/>
+      <c r="AB35" s="61"/>
+      <c r="AC35" s="61"/>
+      <c r="AD35" s="47"/>
+      <c r="AE35" s="62"/>
+      <c r="AF35" s="60"/>
+      <c r="AG35" s="61"/>
+      <c r="AH35" s="61"/>
+      <c r="AI35" s="61"/>
+      <c r="AJ35" s="61"/>
+      <c r="AK35" s="61"/>
     </row>
     <row r="36" ht="12" customHeight="1">
-      <c r="B36" s="59"/>
-      <c r="C36" s="69" t="s">
-        <v>107</v>
-      </c>
-      <c r="D36" s="62"/>
-      <c r="E36" s="62"/>
-      <c r="F36" s="65"/>
-      <c r="G36" s="63"/>
-      <c r="H36" s="61"/>
-      <c r="I36" s="62"/>
-      <c r="J36" s="62"/>
-      <c r="K36" s="62"/>
-      <c r="L36" s="48"/>
-      <c r="M36" s="58"/>
-      <c r="N36" s="46"/>
-      <c r="O36" s="47"/>
-      <c r="P36" s="58"/>
-      <c r="Q36" s="62"/>
-      <c r="R36" s="62"/>
-      <c r="S36" s="62"/>
-      <c r="T36" s="62"/>
-      <c r="U36" s="62"/>
-      <c r="V36" s="63"/>
-      <c r="W36" s="51"/>
-      <c r="X36" s="62"/>
-      <c r="Y36" s="62"/>
-      <c r="Z36" s="63"/>
-      <c r="AA36" s="61"/>
-      <c r="AB36" s="62"/>
-      <c r="AC36" s="62"/>
-      <c r="AD36" s="48"/>
-      <c r="AE36" s="63"/>
-      <c r="AF36" s="61"/>
-      <c r="AG36" s="62"/>
-      <c r="AH36" s="62"/>
-      <c r="AI36" s="62"/>
-      <c r="AJ36" s="62"/>
-      <c r="AK36" s="62"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="68" t="s">
+        <v>108</v>
+      </c>
+      <c r="D36" s="61"/>
+      <c r="E36" s="61"/>
+      <c r="F36" s="64"/>
+      <c r="G36" s="62"/>
+      <c r="H36" s="60"/>
+      <c r="I36" s="61"/>
+      <c r="J36" s="61"/>
+      <c r="K36" s="61"/>
+      <c r="L36" s="47"/>
+      <c r="M36" s="57"/>
+      <c r="N36" s="45"/>
+      <c r="O36" s="46"/>
+      <c r="P36" s="57"/>
+      <c r="Q36" s="61"/>
+      <c r="R36" s="61"/>
+      <c r="S36" s="61"/>
+      <c r="T36" s="61"/>
+      <c r="U36" s="61"/>
+      <c r="V36" s="62"/>
+      <c r="W36" s="50"/>
+      <c r="X36" s="61"/>
+      <c r="Y36" s="61"/>
+      <c r="Z36" s="62"/>
+      <c r="AA36" s="60"/>
+      <c r="AB36" s="61"/>
+      <c r="AC36" s="61"/>
+      <c r="AD36" s="47"/>
+      <c r="AE36" s="62"/>
+      <c r="AF36" s="60"/>
+      <c r="AG36" s="61"/>
+      <c r="AH36" s="61"/>
+      <c r="AI36" s="61"/>
+      <c r="AJ36" s="61"/>
+      <c r="AK36" s="61"/>
     </row>
     <row r="37" ht="12" customHeight="1">
-      <c r="B37" s="59"/>
-      <c r="C37" s="69"/>
-      <c r="D37" s="62"/>
-      <c r="E37" s="62"/>
-      <c r="F37" s="65"/>
-      <c r="G37" s="63"/>
-      <c r="H37" s="61"/>
-      <c r="I37" s="62"/>
-      <c r="J37" s="62"/>
-      <c r="K37" s="70"/>
-      <c r="L37" s="48"/>
-      <c r="M37" s="62"/>
-      <c r="N37" s="63"/>
-      <c r="O37" s="61"/>
-      <c r="P37" s="57"/>
-      <c r="Q37" s="62"/>
-      <c r="R37" s="62"/>
-      <c r="S37" s="62"/>
-      <c r="T37" s="62"/>
-      <c r="U37" s="62"/>
-      <c r="V37" s="63"/>
-      <c r="W37" s="51"/>
-      <c r="X37" s="62"/>
-      <c r="Y37" s="62"/>
-      <c r="Z37" s="63"/>
-      <c r="AA37" s="61"/>
-      <c r="AB37" s="62"/>
-      <c r="AC37" s="62"/>
-      <c r="AD37" s="48"/>
-      <c r="AE37" s="63"/>
-      <c r="AF37" s="61"/>
-      <c r="AG37" s="62"/>
-      <c r="AH37" s="62"/>
-      <c r="AI37" s="62"/>
-      <c r="AJ37" s="62"/>
-      <c r="AK37" s="62"/>
+      <c r="B37" s="58"/>
+      <c r="C37" s="68"/>
+      <c r="D37" s="61"/>
+      <c r="E37" s="61"/>
+      <c r="F37" s="64"/>
+      <c r="G37" s="62"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="61"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="69"/>
+      <c r="L37" s="47"/>
+      <c r="M37" s="61"/>
+      <c r="N37" s="62"/>
+      <c r="O37" s="60"/>
+      <c r="P37" s="56"/>
+      <c r="Q37" s="61"/>
+      <c r="R37" s="61"/>
+      <c r="S37" s="61"/>
+      <c r="T37" s="61"/>
+      <c r="U37" s="61"/>
+      <c r="V37" s="62"/>
+      <c r="W37" s="50"/>
+      <c r="X37" s="61"/>
+      <c r="Y37" s="61"/>
+      <c r="Z37" s="62"/>
+      <c r="AA37" s="60"/>
+      <c r="AB37" s="61"/>
+      <c r="AC37" s="61"/>
+      <c r="AD37" s="47"/>
+      <c r="AE37" s="62"/>
+      <c r="AF37" s="60"/>
+      <c r="AG37" s="61"/>
+      <c r="AH37" s="61"/>
+      <c r="AI37" s="61"/>
+      <c r="AJ37" s="61"/>
+      <c r="AK37" s="61"/>
     </row>
     <row r="38" ht="12" customHeight="1">
-      <c r="B38" s="59"/>
-      <c r="C38" s="69" t="s">
-        <v>108</v>
-      </c>
-      <c r="D38" s="62"/>
-      <c r="E38" s="62"/>
-      <c r="F38" s="65"/>
-      <c r="G38" s="63"/>
-      <c r="H38" s="61"/>
-      <c r="I38" s="62"/>
-      <c r="J38" s="62"/>
-      <c r="K38" s="62"/>
-      <c r="L38" s="48"/>
-      <c r="M38" s="62"/>
-      <c r="N38" s="63"/>
-      <c r="O38" s="47"/>
-      <c r="P38" s="58"/>
-      <c r="Q38" s="58"/>
-      <c r="R38" s="58"/>
-      <c r="S38" s="58"/>
-      <c r="T38" s="58"/>
-      <c r="U38" s="58"/>
-      <c r="V38" s="46"/>
-      <c r="W38" s="51"/>
-      <c r="X38" s="58"/>
-      <c r="Y38" s="58"/>
-      <c r="Z38" s="63"/>
-      <c r="AA38" s="61"/>
-      <c r="AB38" s="62"/>
-      <c r="AC38" s="62"/>
-      <c r="AD38" s="48"/>
-      <c r="AE38" s="63"/>
-      <c r="AF38" s="61"/>
-      <c r="AG38" s="62"/>
-      <c r="AH38" s="62"/>
-      <c r="AI38" s="62"/>
-      <c r="AJ38" s="62"/>
-      <c r="AK38" s="62"/>
+      <c r="B38" s="58"/>
+      <c r="C38" s="68" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" s="61"/>
+      <c r="E38" s="61"/>
+      <c r="F38" s="64"/>
+      <c r="G38" s="62"/>
+      <c r="H38" s="60"/>
+      <c r="I38" s="61"/>
+      <c r="J38" s="61"/>
+      <c r="K38" s="61"/>
+      <c r="L38" s="47"/>
+      <c r="M38" s="61"/>
+      <c r="N38" s="62"/>
+      <c r="O38" s="46"/>
+      <c r="P38" s="57"/>
+      <c r="Q38" s="57"/>
+      <c r="R38" s="57"/>
+      <c r="S38" s="57"/>
+      <c r="T38" s="57"/>
+      <c r="U38" s="57"/>
+      <c r="V38" s="45"/>
+      <c r="W38" s="50"/>
+      <c r="X38" s="57"/>
+      <c r="Y38" s="57"/>
+      <c r="Z38" s="62"/>
+      <c r="AA38" s="60"/>
+      <c r="AB38" s="61"/>
+      <c r="AC38" s="61"/>
+      <c r="AD38" s="47"/>
+      <c r="AE38" s="62"/>
+      <c r="AF38" s="60"/>
+      <c r="AG38" s="61"/>
+      <c r="AH38" s="61"/>
+      <c r="AI38" s="61"/>
+      <c r="AJ38" s="61"/>
+      <c r="AK38" s="61"/>
     </row>
     <row r="39" ht="12" customHeight="1">
-      <c r="B39" s="59"/>
-      <c r="C39" s="69"/>
-      <c r="D39" s="62"/>
-      <c r="E39" s="62"/>
-      <c r="F39" s="65"/>
-      <c r="G39" s="63"/>
-      <c r="H39" s="61"/>
-      <c r="I39" s="62"/>
-      <c r="J39" s="62"/>
-      <c r="K39" s="62"/>
-      <c r="L39" s="48"/>
-      <c r="M39" s="62"/>
-      <c r="N39" s="63"/>
-      <c r="O39" s="61"/>
-      <c r="P39" s="57"/>
-      <c r="Q39" s="57"/>
-      <c r="R39" s="62"/>
-      <c r="S39" s="62"/>
-      <c r="T39" s="62"/>
-      <c r="U39" s="62"/>
-      <c r="V39" s="63"/>
-      <c r="W39" s="51"/>
-      <c r="X39" s="62"/>
-      <c r="Y39" s="62"/>
-      <c r="Z39" s="63"/>
-      <c r="AA39" s="61"/>
-      <c r="AB39" s="62"/>
-      <c r="AC39" s="62"/>
-      <c r="AD39" s="48"/>
-      <c r="AE39" s="63"/>
-      <c r="AF39" s="61"/>
-      <c r="AG39" s="62"/>
-      <c r="AH39" s="62"/>
-      <c r="AI39" s="62"/>
-      <c r="AJ39" s="62"/>
-      <c r="AK39" s="62"/>
+      <c r="B39" s="58"/>
+      <c r="C39" s="68"/>
+      <c r="D39" s="61"/>
+      <c r="E39" s="61"/>
+      <c r="F39" s="64"/>
+      <c r="G39" s="62"/>
+      <c r="H39" s="60"/>
+      <c r="I39" s="61"/>
+      <c r="J39" s="61"/>
+      <c r="K39" s="61"/>
+      <c r="L39" s="47"/>
+      <c r="M39" s="61"/>
+      <c r="N39" s="62"/>
+      <c r="O39" s="60"/>
+      <c r="P39" s="56"/>
+      <c r="Q39" s="56"/>
+      <c r="R39" s="61"/>
+      <c r="S39" s="61"/>
+      <c r="T39" s="61"/>
+      <c r="U39" s="61"/>
+      <c r="V39" s="62"/>
+      <c r="W39" s="50"/>
+      <c r="X39" s="61"/>
+      <c r="Y39" s="61"/>
+      <c r="Z39" s="62"/>
+      <c r="AA39" s="60"/>
+      <c r="AB39" s="61"/>
+      <c r="AC39" s="61"/>
+      <c r="AD39" s="47"/>
+      <c r="AE39" s="62"/>
+      <c r="AF39" s="60"/>
+      <c r="AG39" s="61"/>
+      <c r="AH39" s="61"/>
+      <c r="AI39" s="61"/>
+      <c r="AJ39" s="61"/>
+      <c r="AK39" s="61"/>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="B40" s="59"/>
-      <c r="C40" s="69" t="s">
-        <v>109</v>
-      </c>
-      <c r="D40" s="62"/>
-      <c r="E40" s="62"/>
-      <c r="F40" s="65"/>
-      <c r="G40" s="63"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="62"/>
-      <c r="J40" s="62"/>
-      <c r="K40" s="62"/>
-      <c r="L40" s="48"/>
-      <c r="M40" s="62"/>
-      <c r="N40" s="63"/>
-      <c r="O40" s="61"/>
-      <c r="P40" s="62"/>
-      <c r="Q40" s="62"/>
-      <c r="R40" s="58"/>
-      <c r="S40" s="58"/>
-      <c r="T40" s="58"/>
-      <c r="U40" s="58"/>
-      <c r="V40" s="46"/>
-      <c r="W40" s="51"/>
-      <c r="X40" s="58"/>
-      <c r="Y40" s="58"/>
-      <c r="Z40" s="46"/>
-      <c r="AA40" s="47"/>
-      <c r="AB40" s="58"/>
-      <c r="AC40" s="58"/>
-      <c r="AD40" s="48"/>
-      <c r="AE40" s="63"/>
-      <c r="AF40" s="61"/>
-      <c r="AG40" s="62"/>
-      <c r="AH40" s="62"/>
-      <c r="AI40" s="62"/>
-      <c r="AJ40" s="62"/>
-      <c r="AK40" s="62"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="68" t="s">
+        <v>110</v>
+      </c>
+      <c r="D40" s="61"/>
+      <c r="E40" s="61"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="62"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="61"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="61"/>
+      <c r="L40" s="47"/>
+      <c r="M40" s="61"/>
+      <c r="N40" s="62"/>
+      <c r="O40" s="60"/>
+      <c r="P40" s="61"/>
+      <c r="Q40" s="61"/>
+      <c r="R40" s="57"/>
+      <c r="S40" s="57"/>
+      <c r="T40" s="57"/>
+      <c r="U40" s="57"/>
+      <c r="V40" s="45"/>
+      <c r="W40" s="50"/>
+      <c r="X40" s="57"/>
+      <c r="Y40" s="57"/>
+      <c r="Z40" s="45"/>
+      <c r="AA40" s="46"/>
+      <c r="AB40" s="57"/>
+      <c r="AC40" s="57"/>
+      <c r="AD40" s="47"/>
+      <c r="AE40" s="62"/>
+      <c r="AF40" s="60"/>
+      <c r="AG40" s="61"/>
+      <c r="AH40" s="61"/>
+      <c r="AI40" s="61"/>
+      <c r="AJ40" s="61"/>
+      <c r="AK40" s="61"/>
     </row>
     <row r="41" ht="12" customHeight="1">
-      <c r="B41" s="59"/>
-      <c r="C41" s="69"/>
-      <c r="D41" s="62"/>
-      <c r="E41" s="62"/>
-      <c r="F41" s="65"/>
-      <c r="G41" s="63"/>
-      <c r="H41" s="61"/>
-      <c r="I41" s="62"/>
-      <c r="J41" s="62"/>
-      <c r="K41" s="62"/>
-      <c r="L41" s="48"/>
-      <c r="M41" s="62"/>
-      <c r="N41" s="63"/>
-      <c r="O41" s="61"/>
-      <c r="P41" s="62"/>
-      <c r="Q41" s="57"/>
-      <c r="R41" s="62"/>
-      <c r="S41" s="62"/>
-      <c r="T41" s="62"/>
-      <c r="U41" s="62"/>
-      <c r="V41" s="63"/>
-      <c r="W41" s="51"/>
-      <c r="X41" s="62"/>
-      <c r="Y41" s="62"/>
-      <c r="Z41" s="63"/>
-      <c r="AA41" s="61"/>
-      <c r="AB41" s="62"/>
-      <c r="AC41" s="62"/>
-      <c r="AD41" s="48"/>
-      <c r="AE41" s="63"/>
-      <c r="AF41" s="61"/>
-      <c r="AG41" s="62"/>
-      <c r="AH41" s="62"/>
-      <c r="AI41" s="62"/>
-      <c r="AJ41" s="62"/>
-      <c r="AK41" s="62"/>
+      <c r="B41" s="58"/>
+      <c r="C41" s="68"/>
+      <c r="D41" s="61"/>
+      <c r="E41" s="61"/>
+      <c r="F41" s="64"/>
+      <c r="G41" s="62"/>
+      <c r="H41" s="60"/>
+      <c r="I41" s="61"/>
+      <c r="J41" s="61"/>
+      <c r="K41" s="61"/>
+      <c r="L41" s="47"/>
+      <c r="M41" s="61"/>
+      <c r="N41" s="62"/>
+      <c r="O41" s="60"/>
+      <c r="P41" s="61"/>
+      <c r="Q41" s="56"/>
+      <c r="R41" s="61"/>
+      <c r="S41" s="61"/>
+      <c r="T41" s="61"/>
+      <c r="U41" s="61"/>
+      <c r="V41" s="62"/>
+      <c r="W41" s="50"/>
+      <c r="X41" s="61"/>
+      <c r="Y41" s="61"/>
+      <c r="Z41" s="62"/>
+      <c r="AA41" s="60"/>
+      <c r="AB41" s="61"/>
+      <c r="AC41" s="61"/>
+      <c r="AD41" s="47"/>
+      <c r="AE41" s="62"/>
+      <c r="AF41" s="60"/>
+      <c r="AG41" s="61"/>
+      <c r="AH41" s="61"/>
+      <c r="AI41" s="61"/>
+      <c r="AJ41" s="61"/>
+      <c r="AK41" s="61"/>
     </row>
     <row r="42" ht="12" customHeight="1">
-      <c r="B42" s="42" t="s">
+      <c r="B42" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="71" t="s">
-        <v>110</v>
-      </c>
-      <c r="D42" s="44"/>
-      <c r="E42" s="44"/>
-      <c r="F42" s="52"/>
-      <c r="G42" s="49"/>
-      <c r="H42" s="50"/>
-      <c r="I42" s="44"/>
-      <c r="J42" s="44"/>
-      <c r="K42" s="44"/>
-      <c r="L42" s="48"/>
-      <c r="M42" s="44"/>
-      <c r="N42" s="49"/>
-      <c r="O42" s="50"/>
-      <c r="P42" s="58"/>
-      <c r="Q42" s="58"/>
-      <c r="R42" s="44"/>
-      <c r="S42" s="44"/>
-      <c r="T42" s="44"/>
-      <c r="U42" s="44"/>
-      <c r="V42" s="46"/>
-      <c r="W42" s="51"/>
-      <c r="X42" s="58"/>
-      <c r="Y42" s="58"/>
-      <c r="Z42" s="46"/>
-      <c r="AA42" s="47"/>
-      <c r="AB42" s="58"/>
-      <c r="AC42" s="58"/>
-      <c r="AD42" s="48"/>
-      <c r="AE42" s="49"/>
-      <c r="AF42" s="50"/>
-      <c r="AG42" s="44"/>
-      <c r="AH42" s="44"/>
-      <c r="AI42" s="44"/>
-      <c r="AJ42" s="44"/>
-      <c r="AK42" s="44"/>
+      <c r="C42" s="70" t="s">
+        <v>111</v>
+      </c>
+      <c r="D42" s="43"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="51"/>
+      <c r="G42" s="48"/>
+      <c r="H42" s="49"/>
+      <c r="I42" s="43"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="43"/>
+      <c r="L42" s="47"/>
+      <c r="M42" s="43"/>
+      <c r="N42" s="48"/>
+      <c r="O42" s="49"/>
+      <c r="P42" s="57"/>
+      <c r="Q42" s="57"/>
+      <c r="R42" s="43"/>
+      <c r="S42" s="43"/>
+      <c r="T42" s="43"/>
+      <c r="U42" s="43"/>
+      <c r="V42" s="45"/>
+      <c r="W42" s="50"/>
+      <c r="X42" s="57"/>
+      <c r="Y42" s="57"/>
+      <c r="Z42" s="45"/>
+      <c r="AA42" s="46"/>
+      <c r="AB42" s="57"/>
+      <c r="AC42" s="57"/>
+      <c r="AD42" s="47"/>
+      <c r="AE42" s="48"/>
+      <c r="AF42" s="49"/>
+      <c r="AG42" s="43"/>
+      <c r="AH42" s="43"/>
+      <c r="AI42" s="43"/>
+      <c r="AJ42" s="43"/>
+      <c r="AK42" s="43"/>
     </row>
     <row r="43" ht="12" customHeight="1">
-      <c r="B43" s="42"/>
-      <c r="C43" s="71"/>
-      <c r="D43" s="44"/>
-      <c r="E43" s="44"/>
-      <c r="F43" s="52"/>
-      <c r="G43" s="49"/>
-      <c r="H43" s="50"/>
-      <c r="I43" s="44"/>
-      <c r="J43" s="44"/>
-      <c r="K43" s="44"/>
-      <c r="L43" s="48"/>
-      <c r="M43" s="44"/>
-      <c r="N43" s="49"/>
-      <c r="O43" s="50"/>
-      <c r="P43" s="44"/>
-      <c r="Q43" s="57"/>
-      <c r="R43" s="44"/>
-      <c r="S43" s="44"/>
-      <c r="T43" s="44"/>
-      <c r="U43" s="44"/>
-      <c r="V43" s="49"/>
-      <c r="W43" s="51"/>
-      <c r="X43" s="44"/>
-      <c r="Y43" s="44"/>
-      <c r="Z43" s="49"/>
-      <c r="AA43" s="50"/>
-      <c r="AB43" s="44"/>
-      <c r="AC43" s="44"/>
-      <c r="AD43" s="48"/>
-      <c r="AE43" s="49"/>
-      <c r="AF43" s="50"/>
-      <c r="AG43" s="44"/>
-      <c r="AH43" s="44"/>
-      <c r="AI43" s="44"/>
-      <c r="AJ43" s="44"/>
-      <c r="AK43" s="44"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="70"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="51"/>
+      <c r="G43" s="48"/>
+      <c r="H43" s="49"/>
+      <c r="I43" s="43"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="43"/>
+      <c r="L43" s="47"/>
+      <c r="M43" s="43"/>
+      <c r="N43" s="48"/>
+      <c r="O43" s="49"/>
+      <c r="P43" s="43"/>
+      <c r="Q43" s="56"/>
+      <c r="R43" s="43"/>
+      <c r="S43" s="43"/>
+      <c r="T43" s="43"/>
+      <c r="U43" s="43"/>
+      <c r="V43" s="48"/>
+      <c r="W43" s="50"/>
+      <c r="X43" s="43"/>
+      <c r="Y43" s="43"/>
+      <c r="Z43" s="48"/>
+      <c r="AA43" s="49"/>
+      <c r="AB43" s="43"/>
+      <c r="AC43" s="43"/>
+      <c r="AD43" s="47"/>
+      <c r="AE43" s="48"/>
+      <c r="AF43" s="49"/>
+      <c r="AG43" s="43"/>
+      <c r="AH43" s="43"/>
+      <c r="AI43" s="43"/>
+      <c r="AJ43" s="43"/>
+      <c r="AK43" s="43"/>
     </row>
     <row r="44" ht="12" customHeight="1">
-      <c r="B44" s="42"/>
-      <c r="C44" s="71" t="s">
-        <v>111</v>
-      </c>
-      <c r="D44" s="44"/>
-      <c r="E44" s="44"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="49"/>
-      <c r="H44" s="50"/>
-      <c r="I44" s="44"/>
-      <c r="J44" s="44"/>
-      <c r="K44" s="44"/>
-      <c r="L44" s="48"/>
-      <c r="M44" s="44"/>
-      <c r="N44" s="49"/>
-      <c r="O44" s="50"/>
-      <c r="P44" s="58"/>
-      <c r="Q44" s="58"/>
-      <c r="R44" s="44"/>
-      <c r="S44" s="44"/>
-      <c r="T44" s="44"/>
-      <c r="U44" s="44"/>
-      <c r="V44" s="49"/>
-      <c r="W44" s="51"/>
-      <c r="X44" s="58"/>
-      <c r="Y44" s="58"/>
-      <c r="Z44" s="49"/>
-      <c r="AA44" s="50"/>
-      <c r="AB44" s="44"/>
-      <c r="AC44" s="58"/>
-      <c r="AD44" s="48"/>
-      <c r="AE44" s="46"/>
-      <c r="AF44" s="47"/>
-      <c r="AG44" s="44"/>
-      <c r="AH44" s="44"/>
-      <c r="AI44" s="58"/>
-      <c r="AJ44" s="44"/>
-      <c r="AK44" s="44"/>
+      <c r="B44" s="41"/>
+      <c r="C44" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="51"/>
+      <c r="G44" s="48"/>
+      <c r="H44" s="49"/>
+      <c r="I44" s="43"/>
+      <c r="J44" s="43"/>
+      <c r="K44" s="43"/>
+      <c r="L44" s="47"/>
+      <c r="M44" s="43"/>
+      <c r="N44" s="48"/>
+      <c r="O44" s="49"/>
+      <c r="P44" s="57"/>
+      <c r="Q44" s="57"/>
+      <c r="R44" s="43"/>
+      <c r="S44" s="43"/>
+      <c r="T44" s="43"/>
+      <c r="U44" s="43"/>
+      <c r="V44" s="48"/>
+      <c r="W44" s="50"/>
+      <c r="X44" s="57"/>
+      <c r="Y44" s="57"/>
+      <c r="Z44" s="48"/>
+      <c r="AA44" s="49"/>
+      <c r="AB44" s="43"/>
+      <c r="AC44" s="57"/>
+      <c r="AD44" s="47"/>
+      <c r="AE44" s="45"/>
+      <c r="AF44" s="46"/>
+      <c r="AG44" s="43"/>
+      <c r="AH44" s="43"/>
+      <c r="AI44" s="57"/>
+      <c r="AJ44" s="43"/>
+      <c r="AK44" s="43"/>
     </row>
     <row r="45" ht="12" customHeight="1">
-      <c r="B45" s="42"/>
-      <c r="C45" s="71"/>
-      <c r="D45" s="44"/>
-      <c r="E45" s="44"/>
-      <c r="F45" s="52"/>
-      <c r="G45" s="49"/>
-      <c r="H45" s="50"/>
-      <c r="I45" s="44"/>
-      <c r="J45" s="44"/>
-      <c r="K45" s="44"/>
-      <c r="L45" s="48"/>
-      <c r="M45" s="44"/>
-      <c r="N45" s="49"/>
-      <c r="O45" s="50"/>
-      <c r="P45" s="44"/>
-      <c r="Q45" s="44"/>
-      <c r="R45" s="44"/>
-      <c r="S45" s="44"/>
-      <c r="T45" s="44"/>
-      <c r="U45" s="44"/>
-      <c r="V45" s="49"/>
-      <c r="W45" s="51"/>
-      <c r="X45" s="44"/>
-      <c r="Y45" s="44"/>
-      <c r="Z45" s="49"/>
-      <c r="AA45" s="50"/>
-      <c r="AB45" s="44"/>
-      <c r="AC45" s="44"/>
-      <c r="AD45" s="48"/>
-      <c r="AE45" s="49"/>
-      <c r="AF45" s="50"/>
-      <c r="AG45" s="44"/>
-      <c r="AH45" s="44"/>
-      <c r="AI45" s="44"/>
-      <c r="AJ45" s="44"/>
-      <c r="AK45" s="44"/>
+      <c r="B45" s="41"/>
+      <c r="C45" s="70"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="48"/>
+      <c r="H45" s="49"/>
+      <c r="I45" s="43"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="43"/>
+      <c r="L45" s="47"/>
+      <c r="M45" s="43"/>
+      <c r="N45" s="48"/>
+      <c r="O45" s="49"/>
+      <c r="P45" s="43"/>
+      <c r="Q45" s="43"/>
+      <c r="R45" s="43"/>
+      <c r="S45" s="43"/>
+      <c r="T45" s="43"/>
+      <c r="U45" s="43"/>
+      <c r="V45" s="48"/>
+      <c r="W45" s="50"/>
+      <c r="X45" s="43"/>
+      <c r="Y45" s="43"/>
+      <c r="Z45" s="48"/>
+      <c r="AA45" s="49"/>
+      <c r="AB45" s="43"/>
+      <c r="AC45" s="43"/>
+      <c r="AD45" s="47"/>
+      <c r="AE45" s="48"/>
+      <c r="AF45" s="49"/>
+      <c r="AG45" s="43"/>
+      <c r="AH45" s="43"/>
+      <c r="AI45" s="43"/>
+      <c r="AJ45" s="43"/>
+      <c r="AK45" s="43"/>
     </row>
     <row r="46" ht="12" customHeight="1">
-      <c r="B46" s="59" t="s">
-        <v>112</v>
-      </c>
-      <c r="C46" s="60" t="s">
+      <c r="B46" s="58" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="D46" s="62"/>
-      <c r="E46" s="62"/>
-      <c r="F46" s="65"/>
-      <c r="G46" s="63"/>
-      <c r="H46" s="61"/>
-      <c r="I46" s="62"/>
-      <c r="J46" s="62"/>
-      <c r="K46" s="62"/>
-      <c r="L46" s="48"/>
-      <c r="M46" s="62"/>
-      <c r="N46" s="63"/>
-      <c r="O46" s="61"/>
-      <c r="P46" s="62"/>
-      <c r="Q46" s="62"/>
-      <c r="R46" s="62"/>
-      <c r="S46" s="62"/>
-      <c r="T46" s="62"/>
-      <c r="U46" s="62"/>
-      <c r="V46" s="63"/>
-      <c r="W46" s="51"/>
-      <c r="X46" s="62"/>
-      <c r="Y46" s="62"/>
-      <c r="Z46" s="63"/>
-      <c r="AA46" s="61"/>
-      <c r="AB46" s="62"/>
-      <c r="AC46" s="62"/>
-      <c r="AD46" s="48"/>
-      <c r="AE46" s="63"/>
-      <c r="AF46" s="61"/>
-      <c r="AG46" s="62"/>
-      <c r="AH46" s="62"/>
-      <c r="AI46" s="62"/>
-      <c r="AJ46" s="58"/>
-      <c r="AK46" s="62"/>
+      <c r="D46" s="61"/>
+      <c r="E46" s="61"/>
+      <c r="F46" s="64"/>
+      <c r="G46" s="62"/>
+      <c r="H46" s="60"/>
+      <c r="I46" s="61"/>
+      <c r="J46" s="61"/>
+      <c r="K46" s="61"/>
+      <c r="L46" s="47"/>
+      <c r="M46" s="61"/>
+      <c r="N46" s="62"/>
+      <c r="O46" s="60"/>
+      <c r="P46" s="61"/>
+      <c r="Q46" s="61"/>
+      <c r="R46" s="61"/>
+      <c r="S46" s="61"/>
+      <c r="T46" s="61"/>
+      <c r="U46" s="61"/>
+      <c r="V46" s="62"/>
+      <c r="W46" s="50"/>
+      <c r="X46" s="61"/>
+      <c r="Y46" s="61"/>
+      <c r="Z46" s="62"/>
+      <c r="AA46" s="60"/>
+      <c r="AB46" s="61"/>
+      <c r="AC46" s="61"/>
+      <c r="AD46" s="47"/>
+      <c r="AE46" s="62"/>
+      <c r="AF46" s="60"/>
+      <c r="AG46" s="61"/>
+      <c r="AH46" s="61"/>
+      <c r="AI46" s="61"/>
+      <c r="AJ46" s="57"/>
+      <c r="AK46" s="61"/>
     </row>
     <row r="47" ht="12" customHeight="1">
-      <c r="B47" s="59"/>
-      <c r="C47" s="60"/>
-      <c r="D47" s="62"/>
-      <c r="E47" s="62"/>
-      <c r="F47" s="65"/>
-      <c r="G47" s="63"/>
-      <c r="H47" s="61"/>
-      <c r="I47" s="62"/>
-      <c r="J47" s="62"/>
-      <c r="K47" s="62"/>
-      <c r="L47" s="48"/>
-      <c r="M47" s="62"/>
-      <c r="N47" s="63"/>
-      <c r="O47" s="61"/>
-      <c r="P47" s="62"/>
-      <c r="Q47" s="62"/>
-      <c r="R47" s="62"/>
-      <c r="S47" s="62"/>
-      <c r="T47" s="62"/>
-      <c r="U47" s="62"/>
-      <c r="V47" s="63"/>
-      <c r="W47" s="51"/>
-      <c r="X47" s="62"/>
-      <c r="Y47" s="62"/>
-      <c r="Z47" s="63"/>
-      <c r="AA47" s="61"/>
-      <c r="AB47" s="62"/>
-      <c r="AC47" s="62"/>
-      <c r="AD47" s="48"/>
-      <c r="AE47" s="63"/>
-      <c r="AF47" s="61"/>
-      <c r="AG47" s="62"/>
-      <c r="AH47" s="62"/>
-      <c r="AI47" s="62"/>
-      <c r="AJ47" s="62"/>
-      <c r="AK47" s="62"/>
-      <c r="AN47" s="72" t="s">
-        <v>113</v>
-      </c>
-      <c r="AO47" s="58"/>
+      <c r="B47" s="58"/>
+      <c r="C47" s="59"/>
+      <c r="D47" s="61"/>
+      <c r="E47" s="61"/>
+      <c r="F47" s="64"/>
+      <c r="G47" s="62"/>
+      <c r="H47" s="60"/>
+      <c r="I47" s="61"/>
+      <c r="J47" s="61"/>
+      <c r="K47" s="61"/>
+      <c r="L47" s="47"/>
+      <c r="M47" s="61"/>
+      <c r="N47" s="62"/>
+      <c r="O47" s="60"/>
+      <c r="P47" s="61"/>
+      <c r="Q47" s="61"/>
+      <c r="R47" s="61"/>
+      <c r="S47" s="61"/>
+      <c r="T47" s="61"/>
+      <c r="U47" s="61"/>
+      <c r="V47" s="62"/>
+      <c r="W47" s="50"/>
+      <c r="X47" s="61"/>
+      <c r="Y47" s="61"/>
+      <c r="Z47" s="62"/>
+      <c r="AA47" s="60"/>
+      <c r="AB47" s="61"/>
+      <c r="AC47" s="61"/>
+      <c r="AD47" s="47"/>
+      <c r="AE47" s="62"/>
+      <c r="AF47" s="60"/>
+      <c r="AG47" s="61"/>
+      <c r="AH47" s="61"/>
+      <c r="AI47" s="61"/>
+      <c r="AJ47" s="61"/>
+      <c r="AK47" s="61"/>
+      <c r="AN47" s="71" t="s">
+        <v>114</v>
+      </c>
+      <c r="AO47" s="57"/>
     </row>
     <row r="48" ht="12" customHeight="1">
-      <c r="B48" s="59"/>
-      <c r="C48" s="60" t="s">
-        <v>114</v>
-      </c>
-      <c r="D48" s="62"/>
-      <c r="E48" s="62"/>
-      <c r="F48" s="65"/>
-      <c r="G48" s="63"/>
-      <c r="H48" s="61"/>
-      <c r="I48" s="62"/>
-      <c r="J48" s="62"/>
-      <c r="K48" s="62"/>
-      <c r="L48" s="48"/>
-      <c r="M48" s="62"/>
-      <c r="N48" s="63"/>
-      <c r="O48" s="61"/>
-      <c r="P48" s="62"/>
-      <c r="Q48" s="62"/>
-      <c r="R48" s="62"/>
-      <c r="S48" s="62"/>
-      <c r="T48" s="62"/>
-      <c r="U48" s="62"/>
-      <c r="V48" s="63"/>
-      <c r="W48" s="51"/>
-      <c r="X48" s="62"/>
-      <c r="Y48" s="62"/>
-      <c r="Z48" s="63"/>
-      <c r="AA48" s="61"/>
-      <c r="AB48" s="62"/>
-      <c r="AC48" s="62"/>
-      <c r="AD48" s="48"/>
-      <c r="AE48" s="63"/>
-      <c r="AF48" s="61"/>
-      <c r="AG48" s="62"/>
-      <c r="AH48" s="62"/>
-      <c r="AI48" s="62"/>
-      <c r="AJ48" s="62"/>
-      <c r="AK48" s="73"/>
-      <c r="AN48" s="72" t="s">
+      <c r="B48" s="58"/>
+      <c r="C48" s="59" t="s">
         <v>115</v>
       </c>
-      <c r="AO48" s="57"/>
+      <c r="D48" s="61"/>
+      <c r="E48" s="61"/>
+      <c r="F48" s="64"/>
+      <c r="G48" s="62"/>
+      <c r="H48" s="60"/>
+      <c r="I48" s="61"/>
+      <c r="J48" s="61"/>
+      <c r="K48" s="61"/>
+      <c r="L48" s="47"/>
+      <c r="M48" s="61"/>
+      <c r="N48" s="62"/>
+      <c r="O48" s="60"/>
+      <c r="P48" s="61"/>
+      <c r="Q48" s="61"/>
+      <c r="R48" s="61"/>
+      <c r="S48" s="61"/>
+      <c r="T48" s="61"/>
+      <c r="U48" s="61"/>
+      <c r="V48" s="62"/>
+      <c r="W48" s="50"/>
+      <c r="X48" s="61"/>
+      <c r="Y48" s="61"/>
+      <c r="Z48" s="62"/>
+      <c r="AA48" s="60"/>
+      <c r="AB48" s="61"/>
+      <c r="AC48" s="61"/>
+      <c r="AD48" s="47"/>
+      <c r="AE48" s="62"/>
+      <c r="AF48" s="60"/>
+      <c r="AG48" s="61"/>
+      <c r="AH48" s="61"/>
+      <c r="AI48" s="61"/>
+      <c r="AJ48" s="61"/>
+      <c r="AK48" s="72"/>
+      <c r="AN48" s="71" t="s">
+        <v>116</v>
+      </c>
+      <c r="AO48" s="56"/>
     </row>
     <row r="49" ht="12" customHeight="1">
-      <c r="B49" s="59"/>
-      <c r="C49" s="60"/>
-      <c r="D49" s="62"/>
-      <c r="E49" s="62"/>
-      <c r="F49" s="65"/>
-      <c r="G49" s="63"/>
-      <c r="H49" s="61"/>
-      <c r="I49" s="62"/>
-      <c r="J49" s="62"/>
-      <c r="K49" s="62"/>
-      <c r="L49" s="48"/>
-      <c r="M49" s="62"/>
-      <c r="N49" s="63"/>
-      <c r="O49" s="61"/>
-      <c r="P49" s="62"/>
-      <c r="Q49" s="62"/>
-      <c r="R49" s="62"/>
-      <c r="S49" s="62"/>
-      <c r="T49" s="62"/>
-      <c r="U49" s="62"/>
-      <c r="V49" s="63"/>
-      <c r="W49" s="51"/>
-      <c r="X49" s="62"/>
-      <c r="Y49" s="62"/>
-      <c r="Z49" s="63"/>
-      <c r="AA49" s="61"/>
-      <c r="AB49" s="62"/>
-      <c r="AC49" s="62"/>
-      <c r="AD49" s="48"/>
-      <c r="AE49" s="63"/>
-      <c r="AF49" s="61"/>
-      <c r="AG49" s="62"/>
-      <c r="AH49" s="62"/>
-      <c r="AI49" s="62"/>
-      <c r="AJ49" s="62"/>
-      <c r="AK49" s="62"/>
-      <c r="AN49" s="72" t="s">
-        <v>116</v>
-      </c>
-      <c r="AO49" s="53"/>
+      <c r="B49" s="58"/>
+      <c r="C49" s="59"/>
+      <c r="D49" s="61"/>
+      <c r="E49" s="61"/>
+      <c r="F49" s="64"/>
+      <c r="G49" s="62"/>
+      <c r="H49" s="60"/>
+      <c r="I49" s="61"/>
+      <c r="J49" s="61"/>
+      <c r="K49" s="61"/>
+      <c r="L49" s="47"/>
+      <c r="M49" s="61"/>
+      <c r="N49" s="62"/>
+      <c r="O49" s="60"/>
+      <c r="P49" s="61"/>
+      <c r="Q49" s="61"/>
+      <c r="R49" s="61"/>
+      <c r="S49" s="61"/>
+      <c r="T49" s="61"/>
+      <c r="U49" s="61"/>
+      <c r="V49" s="62"/>
+      <c r="W49" s="50"/>
+      <c r="X49" s="61"/>
+      <c r="Y49" s="61"/>
+      <c r="Z49" s="62"/>
+      <c r="AA49" s="60"/>
+      <c r="AB49" s="61"/>
+      <c r="AC49" s="61"/>
+      <c r="AD49" s="47"/>
+      <c r="AE49" s="62"/>
+      <c r="AF49" s="60"/>
+      <c r="AG49" s="61"/>
+      <c r="AH49" s="61"/>
+      <c r="AI49" s="61"/>
+      <c r="AJ49" s="61"/>
+      <c r="AK49" s="61"/>
+      <c r="AN49" s="71" t="s">
+        <v>117</v>
+      </c>
+      <c r="AO49" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -9554,801 +9562,801 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="74"/>
+      <c r="B1" s="73"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="75" t="s">
-        <v>60</v>
-      </c>
-      <c r="C2" s="76" t="s">
+      <c r="B2" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="D2" s="77" t="s">
-        <v>117</v>
-      </c>
-      <c r="E2" s="78" t="s">
+      <c r="C2" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="76" t="s">
         <v>118</v>
       </c>
-      <c r="F2" s="79" t="s">
+      <c r="E2" s="77" t="s">
         <v>119</v>
       </c>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="79" t="s">
+      <c r="F2" s="78" t="s">
         <v>120</v>
       </c>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="79" t="s">
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="78" t="s">
         <v>121</v>
       </c>
-      <c r="O2" s="79"/>
-      <c r="P2" s="79"/>
-      <c r="Q2" s="78"/>
-      <c r="R2" s="79" t="s">
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="78" t="s">
         <v>122</v>
       </c>
-      <c r="S2" s="80"/>
-      <c r="AD2" s="24"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="78" t="s">
+        <v>123</v>
+      </c>
+      <c r="S2" s="79"/>
+      <c r="AD2" s="23"/>
     </row>
     <row r="3">
-      <c r="B3" s="81"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="83" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="84">
+      <c r="B3" s="80"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="82" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" s="83">
         <v>4</v>
       </c>
-      <c r="F3" s="85">
+      <c r="F3" s="84">
         <v>1</v>
       </c>
-      <c r="G3" s="86">
+      <c r="G3" s="85">
         <v>2</v>
       </c>
-      <c r="H3" s="86">
+      <c r="H3" s="85">
         <v>3</v>
       </c>
-      <c r="I3" s="84">
+      <c r="I3" s="83">
         <v>4</v>
       </c>
-      <c r="J3" s="85">
+      <c r="J3" s="84">
         <v>1</v>
       </c>
-      <c r="K3" s="86">
+      <c r="K3" s="85">
         <v>2</v>
       </c>
-      <c r="L3" s="86">
+      <c r="L3" s="85">
         <v>3</v>
       </c>
-      <c r="M3" s="84">
+      <c r="M3" s="83">
         <v>4</v>
       </c>
-      <c r="N3" s="85">
+      <c r="N3" s="84">
         <v>1</v>
       </c>
-      <c r="O3" s="86">
+      <c r="O3" s="85">
         <v>2</v>
       </c>
-      <c r="P3" s="86">
+      <c r="P3" s="85">
         <v>3</v>
       </c>
-      <c r="Q3" s="84">
+      <c r="Q3" s="83">
         <v>4</v>
       </c>
-      <c r="R3" s="85">
+      <c r="R3" s="84">
         <v>1</v>
       </c>
-      <c r="S3" s="87">
+      <c r="S3" s="86">
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="88" t="s">
-        <v>125</v>
-      </c>
-      <c r="C4" s="76" t="s">
+      <c r="B4" s="87" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="89"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="92"/>
-      <c r="I4" s="90"/>
-      <c r="J4" s="93"/>
-      <c r="K4" s="92"/>
-      <c r="L4" s="92"/>
-      <c r="M4" s="90"/>
-      <c r="N4" s="93"/>
-      <c r="O4" s="92"/>
-      <c r="P4" s="92"/>
-      <c r="Q4" s="90"/>
-      <c r="R4" s="93"/>
-      <c r="S4" s="94"/>
+      <c r="C4" s="75" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" s="88"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="92"/>
+      <c r="K4" s="91"/>
+      <c r="L4" s="91"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="92"/>
+      <c r="O4" s="91"/>
+      <c r="P4" s="91"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="92"/>
+      <c r="S4" s="93"/>
       <c r="U4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="88"/>
-      <c r="C5" s="95"/>
-      <c r="D5" s="96"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="99"/>
-      <c r="H5" s="100"/>
-      <c r="I5" s="97"/>
-      <c r="J5" s="101"/>
-      <c r="K5" s="100"/>
-      <c r="L5" s="100"/>
-      <c r="M5" s="97"/>
-      <c r="N5" s="101"/>
-      <c r="O5" s="100"/>
-      <c r="P5" s="100"/>
-      <c r="Q5" s="97"/>
-      <c r="R5" s="101"/>
-      <c r="S5" s="102"/>
+      <c r="B5" s="87"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="95"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="97"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="96"/>
+      <c r="J5" s="100"/>
+      <c r="K5" s="99"/>
+      <c r="L5" s="99"/>
+      <c r="M5" s="96"/>
+      <c r="N5" s="100"/>
+      <c r="O5" s="99"/>
+      <c r="P5" s="99"/>
+      <c r="Q5" s="96"/>
+      <c r="R5" s="100"/>
+      <c r="S5" s="101"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="88"/>
-      <c r="C6" s="103" t="s">
-        <v>128</v>
-      </c>
-      <c r="D6" s="104"/>
-      <c r="E6" s="105"/>
-      <c r="F6" s="106"/>
-      <c r="G6" s="107"/>
-      <c r="H6" s="108"/>
-      <c r="I6" s="105"/>
-      <c r="J6" s="109"/>
-      <c r="K6" s="108"/>
-      <c r="L6" s="108"/>
-      <c r="M6" s="105"/>
-      <c r="N6" s="109"/>
-      <c r="O6" s="108"/>
-      <c r="P6" s="108"/>
-      <c r="Q6" s="105"/>
-      <c r="R6" s="109"/>
-      <c r="S6" s="110"/>
-      <c r="U6" s="111" t="s">
+      <c r="B6" s="87"/>
+      <c r="C6" s="102" t="s">
         <v>129</v>
       </c>
-      <c r="V6" s="111"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="104"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="106"/>
+      <c r="H6" s="107"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="108"/>
+      <c r="K6" s="107"/>
+      <c r="L6" s="107"/>
+      <c r="M6" s="104"/>
+      <c r="N6" s="108"/>
+      <c r="O6" s="107"/>
+      <c r="P6" s="107"/>
+      <c r="Q6" s="104"/>
+      <c r="R6" s="108"/>
+      <c r="S6" s="109"/>
+      <c r="U6" s="110" t="s">
+        <v>130</v>
+      </c>
+      <c r="V6" s="110"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="88"/>
-      <c r="C7" s="95"/>
-      <c r="D7" s="96"/>
-      <c r="E7" s="97"/>
-      <c r="F7" s="101"/>
-      <c r="G7" s="99"/>
-      <c r="H7" s="99"/>
-      <c r="I7" s="97"/>
-      <c r="J7" s="101"/>
-      <c r="K7" s="100"/>
-      <c r="L7" s="100"/>
-      <c r="M7" s="97"/>
-      <c r="N7" s="101"/>
-      <c r="O7" s="100"/>
-      <c r="P7" s="100"/>
-      <c r="Q7" s="97"/>
-      <c r="R7" s="101"/>
-      <c r="S7" s="102"/>
+      <c r="B7" s="87"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="96"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="98"/>
+      <c r="H7" s="98"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="100"/>
+      <c r="K7" s="99"/>
+      <c r="L7" s="99"/>
+      <c r="M7" s="96"/>
+      <c r="N7" s="100"/>
+      <c r="O7" s="99"/>
+      <c r="P7" s="99"/>
+      <c r="Q7" s="96"/>
+      <c r="R7" s="100"/>
+      <c r="S7" s="101"/>
       <c r="U7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="88"/>
-      <c r="C8" s="103" t="s">
-        <v>131</v>
-      </c>
-      <c r="D8" s="104"/>
-      <c r="E8" s="105"/>
-      <c r="F8" s="106"/>
-      <c r="G8" s="108"/>
-      <c r="H8" s="108"/>
-      <c r="I8" s="105"/>
-      <c r="J8" s="109"/>
-      <c r="K8" s="108"/>
-      <c r="L8" s="108"/>
-      <c r="M8" s="105"/>
-      <c r="N8" s="109"/>
-      <c r="O8" s="108"/>
-      <c r="P8" s="108"/>
-      <c r="Q8" s="105"/>
-      <c r="R8" s="109"/>
-      <c r="S8" s="110"/>
+      <c r="B8" s="87"/>
+      <c r="C8" s="102" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="103"/>
+      <c r="E8" s="104"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="107"/>
+      <c r="H8" s="107"/>
+      <c r="I8" s="104"/>
+      <c r="J8" s="108"/>
+      <c r="K8" s="107"/>
+      <c r="L8" s="107"/>
+      <c r="M8" s="104"/>
+      <c r="N8" s="108"/>
+      <c r="O8" s="107"/>
+      <c r="P8" s="107"/>
+      <c r="Q8" s="104"/>
+      <c r="R8" s="108"/>
+      <c r="S8" s="109"/>
       <c r="U8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="88"/>
-      <c r="C9" s="95"/>
-      <c r="D9" s="96"/>
-      <c r="E9" s="97"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="99"/>
-      <c r="H9" s="100"/>
-      <c r="I9" s="97"/>
-      <c r="J9" s="101"/>
-      <c r="K9" s="100"/>
-      <c r="L9" s="100"/>
-      <c r="M9" s="97"/>
-      <c r="N9" s="101"/>
-      <c r="O9" s="100"/>
-      <c r="P9" s="100"/>
-      <c r="Q9" s="97"/>
-      <c r="R9" s="101"/>
-      <c r="S9" s="102"/>
+      <c r="B9" s="87"/>
+      <c r="C9" s="94"/>
+      <c r="D9" s="95"/>
+      <c r="E9" s="96"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="98"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="96"/>
+      <c r="J9" s="100"/>
+      <c r="K9" s="99"/>
+      <c r="L9" s="99"/>
+      <c r="M9" s="96"/>
+      <c r="N9" s="100"/>
+      <c r="O9" s="99"/>
+      <c r="P9" s="99"/>
+      <c r="Q9" s="96"/>
+      <c r="R9" s="100"/>
+      <c r="S9" s="101"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="88"/>
-      <c r="C10" s="103" t="s">
-        <v>133</v>
-      </c>
-      <c r="D10" s="104"/>
-      <c r="E10" s="105"/>
-      <c r="F10" s="109"/>
-      <c r="G10" s="107"/>
-      <c r="H10" s="107"/>
-      <c r="I10" s="105"/>
-      <c r="J10" s="109"/>
-      <c r="K10" s="108"/>
-      <c r="L10" s="108"/>
-      <c r="M10" s="105"/>
-      <c r="N10" s="109"/>
-      <c r="O10" s="108"/>
-      <c r="P10" s="108"/>
-      <c r="Q10" s="105"/>
-      <c r="R10" s="109"/>
-      <c r="S10" s="110"/>
+      <c r="B10" s="87"/>
+      <c r="C10" s="102" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" s="103"/>
+      <c r="E10" s="104"/>
+      <c r="F10" s="108"/>
+      <c r="G10" s="106"/>
+      <c r="H10" s="106"/>
+      <c r="I10" s="104"/>
+      <c r="J10" s="108"/>
+      <c r="K10" s="107"/>
+      <c r="L10" s="107"/>
+      <c r="M10" s="104"/>
+      <c r="N10" s="108"/>
+      <c r="O10" s="107"/>
+      <c r="P10" s="107"/>
+      <c r="Q10" s="104"/>
+      <c r="R10" s="108"/>
+      <c r="S10" s="109"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="112"/>
-      <c r="C11" s="113"/>
-      <c r="D11" s="114"/>
-      <c r="E11" s="115"/>
-      <c r="F11" s="116"/>
-      <c r="G11" s="117"/>
-      <c r="H11" s="117"/>
-      <c r="I11" s="115"/>
-      <c r="J11" s="116"/>
-      <c r="K11" s="118"/>
-      <c r="L11" s="118"/>
-      <c r="M11" s="115"/>
-      <c r="N11" s="116"/>
-      <c r="O11" s="118"/>
-      <c r="P11" s="118"/>
-      <c r="Q11" s="115"/>
-      <c r="R11" s="116"/>
-      <c r="S11" s="119"/>
+      <c r="B11" s="111"/>
+      <c r="C11" s="112"/>
+      <c r="D11" s="113"/>
+      <c r="E11" s="114"/>
+      <c r="F11" s="115"/>
+      <c r="G11" s="116"/>
+      <c r="H11" s="116"/>
+      <c r="I11" s="114"/>
+      <c r="J11" s="115"/>
+      <c r="K11" s="117"/>
+      <c r="L11" s="117"/>
+      <c r="M11" s="114"/>
+      <c r="N11" s="115"/>
+      <c r="O11" s="117"/>
+      <c r="P11" s="117"/>
+      <c r="Q11" s="114"/>
+      <c r="R11" s="115"/>
+      <c r="S11" s="118"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="75" t="s">
-        <v>134</v>
-      </c>
-      <c r="C12" s="76" t="s">
+      <c r="B12" s="74" t="s">
         <v>135</v>
       </c>
-      <c r="D12" s="89"/>
-      <c r="E12" s="90"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="92"/>
-      <c r="H12" s="120"/>
-      <c r="I12" s="121"/>
-      <c r="J12" s="93"/>
-      <c r="K12" s="92"/>
-      <c r="L12" s="92"/>
-      <c r="M12" s="90"/>
-      <c r="N12" s="93"/>
-      <c r="O12" s="92"/>
-      <c r="P12" s="92"/>
-      <c r="Q12" s="90"/>
-      <c r="R12" s="93"/>
-      <c r="S12" s="94"/>
+      <c r="C12" s="75" t="s">
+        <v>136</v>
+      </c>
+      <c r="D12" s="88"/>
+      <c r="E12" s="89"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="91"/>
+      <c r="H12" s="119"/>
+      <c r="I12" s="120"/>
+      <c r="J12" s="92"/>
+      <c r="K12" s="91"/>
+      <c r="L12" s="91"/>
+      <c r="M12" s="89"/>
+      <c r="N12" s="92"/>
+      <c r="O12" s="91"/>
+      <c r="P12" s="91"/>
+      <c r="Q12" s="89"/>
+      <c r="R12" s="92"/>
+      <c r="S12" s="93"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="88"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="96"/>
-      <c r="E13" s="97"/>
-      <c r="F13" s="101"/>
-      <c r="G13" s="100"/>
-      <c r="H13" s="100"/>
-      <c r="I13" s="97"/>
-      <c r="J13" s="98"/>
-      <c r="K13" s="100"/>
-      <c r="L13" s="100"/>
-      <c r="M13" s="97"/>
-      <c r="N13" s="101"/>
-      <c r="O13" s="100"/>
-      <c r="P13" s="100"/>
-      <c r="Q13" s="97"/>
-      <c r="R13" s="101"/>
-      <c r="S13" s="102"/>
+      <c r="B13" s="87"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="96"/>
+      <c r="F13" s="100"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="99"/>
+      <c r="I13" s="96"/>
+      <c r="J13" s="97"/>
+      <c r="K13" s="99"/>
+      <c r="L13" s="99"/>
+      <c r="M13" s="96"/>
+      <c r="N13" s="100"/>
+      <c r="O13" s="99"/>
+      <c r="P13" s="99"/>
+      <c r="Q13" s="96"/>
+      <c r="R13" s="100"/>
+      <c r="S13" s="101"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="88"/>
-      <c r="C14" s="103" t="s">
-        <v>136</v>
-      </c>
-      <c r="D14" s="122"/>
-      <c r="E14" s="105"/>
-      <c r="F14" s="109"/>
-      <c r="G14" s="108"/>
-      <c r="H14" s="107"/>
-      <c r="I14" s="105"/>
-      <c r="J14" s="109"/>
-      <c r="K14" s="108"/>
-      <c r="L14" s="108"/>
-      <c r="M14" s="105"/>
-      <c r="N14" s="109"/>
-      <c r="O14" s="108"/>
-      <c r="P14" s="108"/>
-      <c r="Q14" s="105"/>
-      <c r="R14" s="109"/>
-      <c r="S14" s="110"/>
+      <c r="B14" s="87"/>
+      <c r="C14" s="102" t="s">
+        <v>137</v>
+      </c>
+      <c r="D14" s="121"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="108"/>
+      <c r="G14" s="107"/>
+      <c r="H14" s="106"/>
+      <c r="I14" s="104"/>
+      <c r="J14" s="108"/>
+      <c r="K14" s="107"/>
+      <c r="L14" s="107"/>
+      <c r="M14" s="104"/>
+      <c r="N14" s="108"/>
+      <c r="O14" s="107"/>
+      <c r="P14" s="107"/>
+      <c r="Q14" s="104"/>
+      <c r="R14" s="108"/>
+      <c r="S14" s="109"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="88"/>
-      <c r="C15" s="95"/>
-      <c r="D15" s="96"/>
-      <c r="E15" s="97"/>
-      <c r="F15" s="101"/>
-      <c r="G15" s="100"/>
-      <c r="H15" s="100"/>
-      <c r="I15" s="123"/>
-      <c r="J15" s="98"/>
-      <c r="K15" s="100"/>
-      <c r="L15" s="100"/>
-      <c r="M15" s="97"/>
-      <c r="N15" s="101"/>
-      <c r="O15" s="100"/>
-      <c r="P15" s="100"/>
-      <c r="Q15" s="97"/>
-      <c r="R15" s="101"/>
-      <c r="S15" s="102"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="94"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="96"/>
+      <c r="F15" s="100"/>
+      <c r="G15" s="99"/>
+      <c r="H15" s="99"/>
+      <c r="I15" s="122"/>
+      <c r="J15" s="97"/>
+      <c r="K15" s="99"/>
+      <c r="L15" s="99"/>
+      <c r="M15" s="96"/>
+      <c r="N15" s="100"/>
+      <c r="O15" s="99"/>
+      <c r="P15" s="99"/>
+      <c r="Q15" s="96"/>
+      <c r="R15" s="100"/>
+      <c r="S15" s="101"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="88"/>
-      <c r="C16" s="103" t="s">
-        <v>137</v>
-      </c>
-      <c r="D16" s="104"/>
-      <c r="E16" s="105"/>
-      <c r="F16" s="109"/>
-      <c r="G16" s="108"/>
-      <c r="H16" s="107"/>
-      <c r="I16" s="124"/>
-      <c r="J16" s="109"/>
-      <c r="K16" s="108"/>
-      <c r="L16" s="108"/>
-      <c r="M16" s="105"/>
-      <c r="N16" s="109"/>
-      <c r="O16" s="108"/>
-      <c r="P16" s="108"/>
-      <c r="Q16" s="105"/>
-      <c r="R16" s="109"/>
-      <c r="S16" s="110"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="102" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16" s="103"/>
+      <c r="E16" s="104"/>
+      <c r="F16" s="108"/>
+      <c r="G16" s="107"/>
+      <c r="H16" s="106"/>
+      <c r="I16" s="123"/>
+      <c r="J16" s="108"/>
+      <c r="K16" s="107"/>
+      <c r="L16" s="107"/>
+      <c r="M16" s="104"/>
+      <c r="N16" s="108"/>
+      <c r="O16" s="107"/>
+      <c r="P16" s="107"/>
+      <c r="Q16" s="104"/>
+      <c r="R16" s="108"/>
+      <c r="S16" s="109"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="112"/>
-      <c r="C17" s="113"/>
-      <c r="D17" s="114"/>
-      <c r="E17" s="115"/>
-      <c r="F17" s="116"/>
-      <c r="G17" s="118"/>
-      <c r="H17" s="118"/>
-      <c r="I17" s="115"/>
-      <c r="J17" s="125"/>
-      <c r="K17" s="117"/>
-      <c r="L17" s="118"/>
-      <c r="M17" s="115"/>
-      <c r="N17" s="116"/>
-      <c r="O17" s="118"/>
-      <c r="P17" s="118"/>
-      <c r="Q17" s="115"/>
-      <c r="R17" s="116"/>
-      <c r="S17" s="119"/>
+      <c r="B17" s="111"/>
+      <c r="C17" s="112"/>
+      <c r="D17" s="113"/>
+      <c r="E17" s="114"/>
+      <c r="F17" s="115"/>
+      <c r="G17" s="117"/>
+      <c r="H17" s="117"/>
+      <c r="I17" s="114"/>
+      <c r="J17" s="124"/>
+      <c r="K17" s="116"/>
+      <c r="L17" s="117"/>
+      <c r="M17" s="114"/>
+      <c r="N17" s="115"/>
+      <c r="O17" s="117"/>
+      <c r="P17" s="117"/>
+      <c r="Q17" s="114"/>
+      <c r="R17" s="115"/>
+      <c r="S17" s="118"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="77" t="s">
-        <v>138</v>
-      </c>
-      <c r="C18" s="76" t="s">
+      <c r="B18" s="76" t="s">
         <v>139</v>
       </c>
-      <c r="D18" s="89"/>
-      <c r="E18" s="90"/>
-      <c r="F18" s="93"/>
-      <c r="G18" s="92"/>
-      <c r="H18" s="92"/>
-      <c r="I18" s="121"/>
-      <c r="J18" s="93"/>
-      <c r="K18" s="92"/>
-      <c r="L18" s="92"/>
-      <c r="M18" s="90"/>
-      <c r="N18" s="93"/>
-      <c r="O18" s="92"/>
-      <c r="P18" s="92"/>
-      <c r="Q18" s="90"/>
-      <c r="R18" s="93"/>
-      <c r="S18" s="94"/>
+      <c r="C18" s="75" t="s">
+        <v>140</v>
+      </c>
+      <c r="D18" s="88"/>
+      <c r="E18" s="89"/>
+      <c r="F18" s="92"/>
+      <c r="G18" s="91"/>
+      <c r="H18" s="91"/>
+      <c r="I18" s="120"/>
+      <c r="J18" s="92"/>
+      <c r="K18" s="91"/>
+      <c r="L18" s="91"/>
+      <c r="M18" s="89"/>
+      <c r="N18" s="92"/>
+      <c r="O18" s="91"/>
+      <c r="P18" s="91"/>
+      <c r="Q18" s="89"/>
+      <c r="R18" s="92"/>
+      <c r="S18" s="93"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="88"/>
-      <c r="C19" s="95"/>
-      <c r="D19" s="96"/>
-      <c r="E19" s="97"/>
-      <c r="F19" s="101"/>
-      <c r="G19" s="99"/>
-      <c r="H19" s="100"/>
-      <c r="I19" s="97"/>
-      <c r="J19" s="101"/>
-      <c r="K19" s="100"/>
-      <c r="L19" s="100"/>
-      <c r="M19" s="97"/>
-      <c r="N19" s="101"/>
-      <c r="O19" s="100"/>
-      <c r="P19" s="100"/>
-      <c r="Q19" s="97"/>
-      <c r="R19" s="101"/>
-      <c r="S19" s="102"/>
+      <c r="B19" s="87"/>
+      <c r="C19" s="94"/>
+      <c r="D19" s="95"/>
+      <c r="E19" s="96"/>
+      <c r="F19" s="100"/>
+      <c r="G19" s="98"/>
+      <c r="H19" s="99"/>
+      <c r="I19" s="96"/>
+      <c r="J19" s="100"/>
+      <c r="K19" s="99"/>
+      <c r="L19" s="99"/>
+      <c r="M19" s="96"/>
+      <c r="N19" s="100"/>
+      <c r="O19" s="99"/>
+      <c r="P19" s="99"/>
+      <c r="Q19" s="96"/>
+      <c r="R19" s="100"/>
+      <c r="S19" s="101"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="88"/>
-      <c r="C20" s="103" t="s">
-        <v>140</v>
-      </c>
-      <c r="D20" s="104"/>
-      <c r="E20" s="105"/>
-      <c r="F20" s="109"/>
-      <c r="G20" s="108"/>
-      <c r="H20" s="108"/>
-      <c r="I20" s="124"/>
-      <c r="J20" s="106"/>
-      <c r="K20" s="107"/>
-      <c r="L20" s="107"/>
-      <c r="M20" s="105"/>
-      <c r="N20" s="109"/>
-      <c r="O20" s="108"/>
-      <c r="P20" s="108"/>
-      <c r="Q20" s="105"/>
-      <c r="R20" s="109"/>
-      <c r="S20" s="110"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="102" t="s">
+        <v>141</v>
+      </c>
+      <c r="D20" s="103"/>
+      <c r="E20" s="104"/>
+      <c r="F20" s="108"/>
+      <c r="G20" s="107"/>
+      <c r="H20" s="107"/>
+      <c r="I20" s="123"/>
+      <c r="J20" s="105"/>
+      <c r="K20" s="106"/>
+      <c r="L20" s="106"/>
+      <c r="M20" s="104"/>
+      <c r="N20" s="108"/>
+      <c r="O20" s="107"/>
+      <c r="P20" s="107"/>
+      <c r="Q20" s="104"/>
+      <c r="R20" s="108"/>
+      <c r="S20" s="109"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="88"/>
-      <c r="C21" s="95"/>
-      <c r="D21" s="96"/>
-      <c r="E21" s="97"/>
-      <c r="F21" s="101"/>
-      <c r="G21" s="100"/>
-      <c r="H21" s="100"/>
-      <c r="I21" s="97"/>
-      <c r="J21" s="101"/>
-      <c r="K21" s="100"/>
-      <c r="L21" s="100"/>
-      <c r="M21" s="97"/>
-      <c r="N21" s="126"/>
-      <c r="O21" s="100"/>
-      <c r="P21" s="100"/>
-      <c r="Q21" s="97"/>
-      <c r="R21" s="101"/>
-      <c r="S21" s="102"/>
+      <c r="B21" s="87"/>
+      <c r="C21" s="94"/>
+      <c r="D21" s="95"/>
+      <c r="E21" s="96"/>
+      <c r="F21" s="100"/>
+      <c r="G21" s="99"/>
+      <c r="H21" s="99"/>
+      <c r="I21" s="96"/>
+      <c r="J21" s="100"/>
+      <c r="K21" s="99"/>
+      <c r="L21" s="99"/>
+      <c r="M21" s="96"/>
+      <c r="N21" s="125"/>
+      <c r="O21" s="99"/>
+      <c r="P21" s="99"/>
+      <c r="Q21" s="96"/>
+      <c r="R21" s="100"/>
+      <c r="S21" s="101"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="88"/>
-      <c r="C22" s="103" t="s">
-        <v>141</v>
-      </c>
-      <c r="D22" s="104"/>
-      <c r="E22" s="105"/>
-      <c r="F22" s="109"/>
-      <c r="G22" s="108"/>
-      <c r="H22" s="108"/>
-      <c r="I22" s="105"/>
-      <c r="J22" s="109"/>
-      <c r="K22" s="107"/>
-      <c r="L22" s="107"/>
-      <c r="M22" s="105"/>
-      <c r="N22" s="109"/>
-      <c r="O22" s="108"/>
-      <c r="P22" s="108"/>
-      <c r="Q22" s="105"/>
-      <c r="R22" s="109"/>
-      <c r="S22" s="110"/>
+      <c r="B22" s="87"/>
+      <c r="C22" s="102" t="s">
+        <v>142</v>
+      </c>
+      <c r="D22" s="103"/>
+      <c r="E22" s="104"/>
+      <c r="F22" s="108"/>
+      <c r="G22" s="107"/>
+      <c r="H22" s="107"/>
+      <c r="I22" s="104"/>
+      <c r="J22" s="108"/>
+      <c r="K22" s="106"/>
+      <c r="L22" s="106"/>
+      <c r="M22" s="104"/>
+      <c r="N22" s="108"/>
+      <c r="O22" s="107"/>
+      <c r="P22" s="107"/>
+      <c r="Q22" s="104"/>
+      <c r="R22" s="108"/>
+      <c r="S22" s="109"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="112"/>
-      <c r="C23" s="113"/>
-      <c r="D23" s="114"/>
-      <c r="E23" s="115"/>
-      <c r="F23" s="116"/>
-      <c r="G23" s="118"/>
-      <c r="H23" s="118"/>
-      <c r="I23" s="115"/>
-      <c r="J23" s="116"/>
-      <c r="K23" s="118"/>
-      <c r="L23" s="118"/>
-      <c r="M23" s="115"/>
-      <c r="N23" s="116"/>
-      <c r="O23" s="118"/>
-      <c r="P23" s="118"/>
-      <c r="Q23" s="115"/>
-      <c r="R23" s="116"/>
-      <c r="S23" s="119"/>
+      <c r="B23" s="111"/>
+      <c r="C23" s="112"/>
+      <c r="D23" s="113"/>
+      <c r="E23" s="114"/>
+      <c r="F23" s="115"/>
+      <c r="G23" s="117"/>
+      <c r="H23" s="117"/>
+      <c r="I23" s="114"/>
+      <c r="J23" s="115"/>
+      <c r="K23" s="117"/>
+      <c r="L23" s="117"/>
+      <c r="M23" s="114"/>
+      <c r="N23" s="115"/>
+      <c r="O23" s="117"/>
+      <c r="P23" s="117"/>
+      <c r="Q23" s="114"/>
+      <c r="R23" s="115"/>
+      <c r="S23" s="118"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="77" t="s">
-        <v>142</v>
-      </c>
-      <c r="C24" s="76" t="s">
+      <c r="B24" s="76" t="s">
         <v>143</v>
       </c>
-      <c r="D24" s="89"/>
-      <c r="E24" s="90"/>
-      <c r="F24" s="93"/>
-      <c r="G24" s="92"/>
-      <c r="H24" s="92"/>
-      <c r="I24" s="90"/>
-      <c r="J24" s="93"/>
-      <c r="K24" s="92"/>
-      <c r="L24" s="92"/>
-      <c r="M24" s="121"/>
-      <c r="N24" s="91"/>
-      <c r="O24" s="120"/>
-      <c r="P24" s="120"/>
-      <c r="Q24" s="90"/>
-      <c r="R24" s="93"/>
-      <c r="S24" s="94"/>
+      <c r="C24" s="75" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" s="88"/>
+      <c r="E24" s="89"/>
+      <c r="F24" s="92"/>
+      <c r="G24" s="91"/>
+      <c r="H24" s="91"/>
+      <c r="I24" s="89"/>
+      <c r="J24" s="92"/>
+      <c r="K24" s="91"/>
+      <c r="L24" s="91"/>
+      <c r="M24" s="120"/>
+      <c r="N24" s="90"/>
+      <c r="O24" s="119"/>
+      <c r="P24" s="119"/>
+      <c r="Q24" s="89"/>
+      <c r="R24" s="92"/>
+      <c r="S24" s="93"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="88"/>
-      <c r="C25" s="95"/>
-      <c r="D25" s="96"/>
-      <c r="E25" s="97"/>
-      <c r="F25" s="101"/>
-      <c r="G25" s="100"/>
-      <c r="H25" s="100"/>
-      <c r="I25" s="97"/>
-      <c r="J25" s="101"/>
-      <c r="K25" s="100"/>
-      <c r="L25" s="100"/>
-      <c r="M25" s="97"/>
-      <c r="N25" s="101"/>
-      <c r="O25" s="100"/>
-      <c r="P25" s="100"/>
-      <c r="Q25" s="97"/>
-      <c r="R25" s="101"/>
-      <c r="S25" s="102"/>
+      <c r="B25" s="87"/>
+      <c r="C25" s="94"/>
+      <c r="D25" s="95"/>
+      <c r="E25" s="96"/>
+      <c r="F25" s="100"/>
+      <c r="G25" s="99"/>
+      <c r="H25" s="99"/>
+      <c r="I25" s="96"/>
+      <c r="J25" s="100"/>
+      <c r="K25" s="99"/>
+      <c r="L25" s="99"/>
+      <c r="M25" s="96"/>
+      <c r="N25" s="100"/>
+      <c r="O25" s="99"/>
+      <c r="P25" s="99"/>
+      <c r="Q25" s="96"/>
+      <c r="R25" s="100"/>
+      <c r="S25" s="101"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="88"/>
-      <c r="C26" s="103" t="s">
-        <v>144</v>
-      </c>
-      <c r="D26" s="104"/>
-      <c r="E26" s="105"/>
-      <c r="F26" s="109"/>
-      <c r="G26" s="108"/>
-      <c r="H26" s="108"/>
-      <c r="I26" s="105"/>
-      <c r="J26" s="109"/>
-      <c r="K26" s="108"/>
-      <c r="L26" s="108"/>
-      <c r="M26" s="105"/>
-      <c r="N26" s="109"/>
-      <c r="O26" s="107"/>
-      <c r="P26" s="107"/>
-      <c r="Q26" s="105"/>
-      <c r="R26" s="109"/>
-      <c r="S26" s="110"/>
+      <c r="B26" s="87"/>
+      <c r="C26" s="102" t="s">
+        <v>145</v>
+      </c>
+      <c r="D26" s="103"/>
+      <c r="E26" s="104"/>
+      <c r="F26" s="108"/>
+      <c r="G26" s="107"/>
+      <c r="H26" s="107"/>
+      <c r="I26" s="104"/>
+      <c r="J26" s="108"/>
+      <c r="K26" s="107"/>
+      <c r="L26" s="107"/>
+      <c r="M26" s="104"/>
+      <c r="N26" s="108"/>
+      <c r="O26" s="106"/>
+      <c r="P26" s="106"/>
+      <c r="Q26" s="104"/>
+      <c r="R26" s="108"/>
+      <c r="S26" s="109"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="88"/>
-      <c r="C27" s="95"/>
-      <c r="D27" s="96"/>
-      <c r="E27" s="97"/>
-      <c r="F27" s="101"/>
-      <c r="G27" s="100"/>
-      <c r="H27" s="100"/>
-      <c r="I27" s="97"/>
-      <c r="J27" s="101"/>
-      <c r="K27" s="100"/>
-      <c r="L27" s="100"/>
-      <c r="M27" s="97"/>
-      <c r="N27" s="101"/>
-      <c r="O27" s="100"/>
-      <c r="P27" s="100"/>
-      <c r="Q27" s="97"/>
-      <c r="R27" s="101"/>
-      <c r="S27" s="102"/>
+      <c r="B27" s="87"/>
+      <c r="C27" s="94"/>
+      <c r="D27" s="95"/>
+      <c r="E27" s="96"/>
+      <c r="F27" s="100"/>
+      <c r="G27" s="99"/>
+      <c r="H27" s="99"/>
+      <c r="I27" s="96"/>
+      <c r="J27" s="100"/>
+      <c r="K27" s="99"/>
+      <c r="L27" s="99"/>
+      <c r="M27" s="96"/>
+      <c r="N27" s="100"/>
+      <c r="O27" s="99"/>
+      <c r="P27" s="99"/>
+      <c r="Q27" s="96"/>
+      <c r="R27" s="100"/>
+      <c r="S27" s="101"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="88"/>
-      <c r="C28" s="103" t="s">
-        <v>145</v>
-      </c>
-      <c r="D28" s="104"/>
-      <c r="E28" s="105"/>
-      <c r="F28" s="109"/>
-      <c r="G28" s="108"/>
-      <c r="H28" s="108"/>
-      <c r="I28" s="105"/>
-      <c r="J28" s="109"/>
-      <c r="K28" s="108"/>
-      <c r="L28" s="108"/>
-      <c r="M28" s="105"/>
-      <c r="N28" s="109"/>
-      <c r="O28" s="108"/>
-      <c r="P28" s="107"/>
-      <c r="Q28" s="124"/>
-      <c r="R28" s="109"/>
-      <c r="S28" s="110"/>
+      <c r="B28" s="87"/>
+      <c r="C28" s="102" t="s">
+        <v>146</v>
+      </c>
+      <c r="D28" s="103"/>
+      <c r="E28" s="104"/>
+      <c r="F28" s="108"/>
+      <c r="G28" s="107"/>
+      <c r="H28" s="107"/>
+      <c r="I28" s="104"/>
+      <c r="J28" s="108"/>
+      <c r="K28" s="107"/>
+      <c r="L28" s="107"/>
+      <c r="M28" s="104"/>
+      <c r="N28" s="108"/>
+      <c r="O28" s="107"/>
+      <c r="P28" s="106"/>
+      <c r="Q28" s="123"/>
+      <c r="R28" s="108"/>
+      <c r="S28" s="109"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="88"/>
-      <c r="C29" s="82"/>
-      <c r="D29" s="127"/>
-      <c r="E29" s="128"/>
-      <c r="F29" s="129"/>
-      <c r="G29" s="130"/>
-      <c r="H29" s="131"/>
-      <c r="I29" s="128"/>
-      <c r="J29" s="129"/>
-      <c r="K29" s="130"/>
-      <c r="L29" s="131"/>
-      <c r="M29" s="128"/>
-      <c r="N29" s="132"/>
-      <c r="O29" s="131"/>
-      <c r="P29" s="130"/>
-      <c r="Q29" s="128"/>
-      <c r="R29" s="129"/>
-      <c r="S29" s="133"/>
+      <c r="B29" s="87"/>
+      <c r="C29" s="81"/>
+      <c r="D29" s="126"/>
+      <c r="E29" s="127"/>
+      <c r="F29" s="128"/>
+      <c r="G29" s="129"/>
+      <c r="H29" s="130"/>
+      <c r="I29" s="127"/>
+      <c r="J29" s="128"/>
+      <c r="K29" s="129"/>
+      <c r="L29" s="130"/>
+      <c r="M29" s="127"/>
+      <c r="N29" s="131"/>
+      <c r="O29" s="130"/>
+      <c r="P29" s="129"/>
+      <c r="Q29" s="127"/>
+      <c r="R29" s="128"/>
+      <c r="S29" s="132"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="134" t="s">
+      <c r="B30" s="133" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="135" t="s">
-        <v>89</v>
-      </c>
-      <c r="D30" s="89"/>
-      <c r="E30" s="136"/>
-      <c r="F30" s="137"/>
-      <c r="G30" s="137"/>
-      <c r="H30" s="138"/>
-      <c r="I30" s="139"/>
-      <c r="J30" s="137"/>
-      <c r="K30" s="137"/>
-      <c r="L30" s="138"/>
-      <c r="M30" s="139"/>
-      <c r="N30" s="137"/>
-      <c r="O30" s="138"/>
-      <c r="P30" s="137"/>
-      <c r="Q30" s="139"/>
-      <c r="R30" s="137"/>
-      <c r="S30" s="140"/>
+      <c r="C30" s="134" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" s="88"/>
+      <c r="E30" s="135"/>
+      <c r="F30" s="136"/>
+      <c r="G30" s="136"/>
+      <c r="H30" s="137"/>
+      <c r="I30" s="138"/>
+      <c r="J30" s="136"/>
+      <c r="K30" s="136"/>
+      <c r="L30" s="137"/>
+      <c r="M30" s="138"/>
+      <c r="N30" s="136"/>
+      <c r="O30" s="137"/>
+      <c r="P30" s="136"/>
+      <c r="Q30" s="138"/>
+      <c r="R30" s="136"/>
+      <c r="S30" s="139"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="141"/>
-      <c r="C31" s="142"/>
-      <c r="D31" s="96"/>
-      <c r="E31" s="143"/>
-      <c r="F31" s="144"/>
-      <c r="G31" s="144"/>
-      <c r="H31" s="145"/>
-      <c r="I31" s="146"/>
-      <c r="J31" s="144"/>
-      <c r="K31" s="147"/>
-      <c r="L31" s="145"/>
-      <c r="M31" s="146"/>
-      <c r="N31" s="144"/>
-      <c r="O31" s="145"/>
-      <c r="P31" s="144"/>
-      <c r="Q31" s="146"/>
-      <c r="R31" s="144"/>
-      <c r="S31" s="102"/>
+      <c r="B31" s="140"/>
+      <c r="C31" s="141"/>
+      <c r="D31" s="95"/>
+      <c r="E31" s="142"/>
+      <c r="F31" s="143"/>
+      <c r="G31" s="143"/>
+      <c r="H31" s="144"/>
+      <c r="I31" s="145"/>
+      <c r="J31" s="143"/>
+      <c r="K31" s="146"/>
+      <c r="L31" s="144"/>
+      <c r="M31" s="145"/>
+      <c r="N31" s="143"/>
+      <c r="O31" s="144"/>
+      <c r="P31" s="143"/>
+      <c r="Q31" s="145"/>
+      <c r="R31" s="143"/>
+      <c r="S31" s="101"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="141"/>
-      <c r="C32" s="142" t="s">
+      <c r="B32" s="140"/>
+      <c r="C32" s="141" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="104"/>
-      <c r="E32" s="148"/>
-      <c r="F32" s="149"/>
-      <c r="G32" s="149"/>
-      <c r="H32" s="150"/>
-      <c r="I32" s="151"/>
-      <c r="J32" s="149"/>
-      <c r="K32" s="149"/>
-      <c r="L32" s="150"/>
-      <c r="M32" s="151"/>
-      <c r="N32" s="149"/>
-      <c r="O32" s="150"/>
-      <c r="P32" s="149"/>
-      <c r="Q32" s="151"/>
-      <c r="R32" s="149"/>
-      <c r="S32" s="152"/>
+      <c r="D32" s="103"/>
+      <c r="E32" s="147"/>
+      <c r="F32" s="148"/>
+      <c r="G32" s="148"/>
+      <c r="H32" s="149"/>
+      <c r="I32" s="150"/>
+      <c r="J32" s="148"/>
+      <c r="K32" s="148"/>
+      <c r="L32" s="149"/>
+      <c r="M32" s="150"/>
+      <c r="N32" s="148"/>
+      <c r="O32" s="149"/>
+      <c r="P32" s="148"/>
+      <c r="Q32" s="150"/>
+      <c r="R32" s="148"/>
+      <c r="S32" s="151"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="141"/>
-      <c r="C33" s="142"/>
-      <c r="D33" s="96"/>
-      <c r="E33" s="143"/>
-      <c r="F33" s="147"/>
-      <c r="G33" s="144"/>
-      <c r="H33" s="153"/>
-      <c r="I33" s="154"/>
-      <c r="J33" s="144"/>
-      <c r="K33" s="147"/>
-      <c r="L33" s="145"/>
-      <c r="M33" s="146"/>
-      <c r="N33" s="144"/>
-      <c r="O33" s="145"/>
-      <c r="P33" s="144"/>
-      <c r="Q33" s="146"/>
-      <c r="R33" s="144"/>
-      <c r="S33" s="102"/>
+      <c r="B33" s="140"/>
+      <c r="C33" s="141"/>
+      <c r="D33" s="95"/>
+      <c r="E33" s="142"/>
+      <c r="F33" s="146"/>
+      <c r="G33" s="143"/>
+      <c r="H33" s="152"/>
+      <c r="I33" s="153"/>
+      <c r="J33" s="143"/>
+      <c r="K33" s="146"/>
+      <c r="L33" s="144"/>
+      <c r="M33" s="145"/>
+      <c r="N33" s="143"/>
+      <c r="O33" s="144"/>
+      <c r="P33" s="143"/>
+      <c r="Q33" s="145"/>
+      <c r="R33" s="143"/>
+      <c r="S33" s="101"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="141"/>
-      <c r="C34" s="95" t="s">
-        <v>146</v>
-      </c>
-      <c r="D34" s="127"/>
-      <c r="E34" s="155"/>
-      <c r="F34" s="156"/>
-      <c r="G34" s="156"/>
-      <c r="H34" s="157"/>
-      <c r="I34" s="158"/>
-      <c r="J34" s="156"/>
-      <c r="K34" s="156"/>
-      <c r="L34" s="157"/>
-      <c r="M34" s="158"/>
-      <c r="N34" s="156"/>
-      <c r="O34" s="157"/>
-      <c r="P34" s="156"/>
-      <c r="Q34" s="158"/>
-      <c r="R34" s="156"/>
-      <c r="S34" s="159"/>
-      <c r="U34" s="160"/>
-      <c r="V34" s="161" t="s">
+      <c r="B34" s="140"/>
+      <c r="C34" s="94" t="s">
         <v>147</v>
       </c>
+      <c r="D34" s="126"/>
+      <c r="E34" s="154"/>
+      <c r="F34" s="155"/>
+      <c r="G34" s="155"/>
+      <c r="H34" s="156"/>
+      <c r="I34" s="157"/>
+      <c r="J34" s="155"/>
+      <c r="K34" s="155"/>
+      <c r="L34" s="156"/>
+      <c r="M34" s="157"/>
+      <c r="N34" s="155"/>
+      <c r="O34" s="156"/>
+      <c r="P34" s="155"/>
+      <c r="Q34" s="157"/>
+      <c r="R34" s="155"/>
+      <c r="S34" s="158"/>
+      <c r="U34" s="159"/>
+      <c r="V34" s="160" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="162"/>
-      <c r="C35" s="163"/>
-      <c r="D35" s="114"/>
-      <c r="E35" s="164"/>
-      <c r="F35" s="165"/>
-      <c r="G35" s="165"/>
-      <c r="H35" s="166"/>
-      <c r="I35" s="167"/>
-      <c r="J35" s="165"/>
-      <c r="K35" s="165"/>
-      <c r="L35" s="166"/>
-      <c r="M35" s="167"/>
-      <c r="N35" s="165"/>
-      <c r="O35" s="166"/>
-      <c r="P35" s="165"/>
-      <c r="Q35" s="167"/>
-      <c r="R35" s="165"/>
-      <c r="S35" s="119"/>
-      <c r="U35" s="168"/>
-      <c r="V35" s="169" t="s">
-        <v>148</v>
+      <c r="B35" s="161"/>
+      <c r="C35" s="162"/>
+      <c r="D35" s="113"/>
+      <c r="E35" s="163"/>
+      <c r="F35" s="164"/>
+      <c r="G35" s="164"/>
+      <c r="H35" s="165"/>
+      <c r="I35" s="166"/>
+      <c r="J35" s="164"/>
+      <c r="K35" s="164"/>
+      <c r="L35" s="165"/>
+      <c r="M35" s="166"/>
+      <c r="N35" s="164"/>
+      <c r="O35" s="165"/>
+      <c r="P35" s="164"/>
+      <c r="Q35" s="166"/>
+      <c r="R35" s="164"/>
+      <c r="S35" s="118"/>
+      <c r="U35" s="167"/>
+      <c r="V35" s="168" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/HoferL-JournalPlanif-M5.xlsx
+++ b/Documentation/HoferL-JournalPlanif-M5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lukas\Desktop\ScholarLog\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC831C6-9A90-44DB-AD49-EAEEEAF2F259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{459BF26C-B436-48F0-99EA-6CF5AC0F8218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="162">
   <si>
     <t>date</t>
   </si>
@@ -553,6 +553,15 @@
   </si>
   <si>
     <t>&lt;-- A jour avec la BDD</t>
+  </si>
+  <si>
+    <t>Documentation des fichiers MVVM + Documentation du repertoire intérrction avec la BDD.</t>
+  </si>
+  <si>
+    <t>Implémentation correction de la séparation en MVVM.</t>
+  </si>
+  <si>
+    <t>Recherche de pratique de programmation sur les MVVM.</t>
   </si>
 </sst>
 </file>
@@ -565,7 +574,7 @@
     <numFmt numFmtId="166" formatCode="0.0&quot; H&quot;;@"/>
     <numFmt numFmtId="167" formatCode="0&quot;H&quot;"/>
     <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="170" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="169" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -1768,6 +1777,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
@@ -1846,10 +1859,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="63" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2252,16 +2261,16 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>31.5</c:v>
+                  <c:v>33.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>40.5</c:v>
+                  <c:v>41.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3677,8 +3686,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Journal" displayName="Journal" ref="B2:E44">
-  <autoFilter ref="B2:E44" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Journal" displayName="Journal" ref="B2:E47">
+  <autoFilter ref="B2:E47" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="date" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Temps" dataDxfId="3"/>
@@ -3959,7 +3968,7 @@
       </c>
       <c r="I3" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>2.9411764705882353E-2</v>
+        <v>2.8301886792452831E-2</v>
       </c>
       <c r="J3" s="11" t="str" cm="1">
         <f t="array" ref="J3:J9">_xlfn._xlws.FILTER(G3:G10,H3:H10&gt;0)</f>
@@ -3992,7 +4001,7 @@
       </c>
       <c r="I4" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>2.9411764705882353E-2</v>
+        <v>2.8301886792452831E-2</v>
       </c>
       <c r="J4" s="3" t="str">
         <v>Plannification</v>
@@ -4019,17 +4028,17 @@
       </c>
       <c r="H5" s="9">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>5.8823529411764705E-2</v>
+        <v>6.6037735849056603E-2</v>
       </c>
       <c r="J5" s="3" t="str">
         <v>Recherche</v>
       </c>
       <c r="K5" s="12">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
@@ -4054,7 +4063,7 @@
       </c>
       <c r="I6" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.16666666666666666</v>
+        <v>0.16037735849056603</v>
       </c>
       <c r="J6" s="3" t="str">
         <v>Maquettage</v>
@@ -4081,17 +4090,17 @@
       </c>
       <c r="H7" s="9">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>31.5</v>
+        <v>33.5</v>
       </c>
       <c r="I7" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.30882352941176472</v>
+        <v>0.31603773584905659</v>
       </c>
       <c r="J7" s="3" t="str">
         <v>Documentation</v>
       </c>
       <c r="K7" s="12">
-        <v>31.5</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="8" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -4112,17 +4121,17 @@
       </c>
       <c r="H8" s="9">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>40.5</v>
+        <v>41.5</v>
       </c>
       <c r="I8" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.39705882352941174</v>
+        <v>0.39150943396226418</v>
       </c>
       <c r="J8" s="3" t="str">
         <v>Programmation</v>
       </c>
       <c r="K8" s="12">
-        <v>40.5</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
@@ -4147,7 +4156,7 @@
       </c>
       <c r="I9" s="10">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>9.8039215686274508E-3</v>
+        <v>9.433962264150943E-3</v>
       </c>
       <c r="J9" s="3" t="str">
         <v>Tests</v>
@@ -4201,7 +4210,7 @@
       </c>
       <c r="H11" s="9">
         <f>SUM(H3:H10)</f>
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -4599,9 +4608,9 @@
       <c r="E39" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H39" s="171"/>
-      <c r="I39" s="170"/>
-      <c r="J39" s="172"/>
+      <c r="H39" s="145"/>
+      <c r="I39" s="144"/>
+      <c r="J39" s="146"/>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B40" s="4">
@@ -4677,22 +4686,46 @@
       </c>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B45" s="4"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="7"/>
+      <c r="B45" s="4">
+        <v>46100</v>
+      </c>
+      <c r="C45" s="5">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B46" s="4"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="7"/>
-    </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B47" s="4"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="7"/>
+      <c r="B46" s="4">
+        <v>46100</v>
+      </c>
+      <c r="C46" s="5">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B47" s="4">
+        <v>46100</v>
+      </c>
+      <c r="C47" s="5">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" s="16"/>
@@ -4934,7 +4967,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="str" cm="1">
-        <f t="array" ref="A2:A24">_xlfn.UNIQUE(Journal[date])</f>
+        <f t="array" ref="A2:A25">_xlfn.UNIQUE(Journal[date])</f>
         <v>20.01.2026</v>
       </c>
       <c r="B2" s="19">
@@ -5140,7 +5173,9 @@
       <c r="C24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="18"/>
+      <c r="A25" s="18">
+        <v>46100</v>
+      </c>
       <c r="C25"/>
       <c r="F25" s="20"/>
     </row>
@@ -6741,10 +6776,10 @@
       <c r="AU1" s="39"/>
     </row>
     <row r="2" spans="2:47" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="144" t="s">
+      <c r="B2" s="148" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="149" t="s">
+      <c r="C2" s="153" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="40"/>
@@ -6783,8 +6818,8 @@
       <c r="AK2" s="40"/>
     </row>
     <row r="3" spans="2:47" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="144"/>
-      <c r="C3" s="149"/>
+      <c r="B3" s="148"/>
+      <c r="C3" s="153"/>
       <c r="D3" s="40"/>
       <c r="E3" s="40"/>
       <c r="F3" s="48"/>
@@ -6821,8 +6856,8 @@
       <c r="AK3" s="40"/>
     </row>
     <row r="4" spans="2:47" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="144"/>
-      <c r="C4" s="149" t="s">
+      <c r="B4" s="148"/>
+      <c r="C4" s="153" t="s">
         <v>89</v>
       </c>
       <c r="D4" s="40"/>
@@ -6861,8 +6896,8 @@
       <c r="AK4" s="40"/>
     </row>
     <row r="5" spans="2:47" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="144"/>
-      <c r="C5" s="149"/>
+      <c r="B5" s="148"/>
+      <c r="C5" s="153"/>
       <c r="D5" s="40"/>
       <c r="E5" s="40"/>
       <c r="F5" s="50"/>
@@ -6899,8 +6934,8 @@
       <c r="AK5" s="40"/>
     </row>
     <row r="6" spans="2:47" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="144"/>
-      <c r="C6" s="149" t="s">
+      <c r="B6" s="148"/>
+      <c r="C6" s="153" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="40"/>
@@ -6939,8 +6974,8 @@
       <c r="AK6" s="54"/>
     </row>
     <row r="7" spans="2:47" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="144"/>
-      <c r="C7" s="149"/>
+      <c r="B7" s="148"/>
+      <c r="C7" s="153"/>
       <c r="D7" s="40"/>
       <c r="E7" s="40"/>
       <c r="F7" s="50"/>
@@ -6977,8 +7012,8 @@
       <c r="AK7" s="40"/>
     </row>
     <row r="8" spans="2:47" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="144"/>
-      <c r="C8" s="149" t="s">
+      <c r="B8" s="148"/>
+      <c r="C8" s="153" t="s">
         <v>90</v>
       </c>
       <c r="D8" s="54"/>
@@ -7017,8 +7052,8 @@
       <c r="AK8" s="54"/>
     </row>
     <row r="9" spans="2:47" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="144"/>
-      <c r="C9" s="149"/>
+      <c r="B9" s="148"/>
+      <c r="C9" s="153"/>
       <c r="D9" s="40"/>
       <c r="E9" s="53"/>
       <c r="F9" s="50"/>
@@ -7055,8 +7090,8 @@
       <c r="AK9" s="40"/>
     </row>
     <row r="10" spans="2:47" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="144"/>
-      <c r="C10" s="149" t="s">
+      <c r="B10" s="148"/>
+      <c r="C10" s="153" t="s">
         <v>91</v>
       </c>
       <c r="D10" s="40"/>
@@ -7095,8 +7130,8 @@
       <c r="AK10" s="40"/>
     </row>
     <row r="11" spans="2:47" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="144"/>
-      <c r="C11" s="149"/>
+      <c r="B11" s="148"/>
+      <c r="C11" s="153"/>
       <c r="D11" s="40"/>
       <c r="E11" s="40"/>
       <c r="F11" s="48"/>
@@ -7133,8 +7168,8 @@
       <c r="AK11" s="40"/>
     </row>
     <row r="12" spans="2:47" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="144"/>
-      <c r="C12" s="149" t="s">
+      <c r="B12" s="148"/>
+      <c r="C12" s="153" t="s">
         <v>92</v>
       </c>
       <c r="D12" s="40"/>
@@ -7173,8 +7208,8 @@
       <c r="AK12" s="54"/>
     </row>
     <row r="13" spans="2:47" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="144"/>
-      <c r="C13" s="149"/>
+      <c r="B13" s="148"/>
+      <c r="C13" s="153"/>
       <c r="D13" s="40"/>
       <c r="E13" s="40"/>
       <c r="F13" s="48"/>
@@ -7211,10 +7246,10 @@
       <c r="AK13" s="40"/>
     </row>
     <row r="14" spans="2:47" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="146" t="s">
+      <c r="B14" s="150" t="s">
         <v>93</v>
       </c>
-      <c r="C14" s="147" t="s">
+      <c r="C14" s="151" t="s">
         <v>94</v>
       </c>
       <c r="D14" s="54"/>
@@ -7253,8 +7288,8 @@
       <c r="AK14" s="56"/>
     </row>
     <row r="15" spans="2:47" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="146"/>
-      <c r="C15" s="147"/>
+      <c r="B15" s="150"/>
+      <c r="C15" s="151"/>
       <c r="D15" s="56"/>
       <c r="E15" s="53"/>
       <c r="F15" s="50"/>
@@ -7291,8 +7326,8 @@
       <c r="AK15" s="56"/>
     </row>
     <row r="16" spans="2:47" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="146"/>
-      <c r="C16" s="147" t="s">
+      <c r="B16" s="150"/>
+      <c r="C16" s="151" t="s">
         <v>95</v>
       </c>
       <c r="D16" s="54"/>
@@ -7331,8 +7366,8 @@
       <c r="AK16" s="56"/>
     </row>
     <row r="17" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="146"/>
-      <c r="C17" s="147"/>
+      <c r="B17" s="150"/>
+      <c r="C17" s="151"/>
       <c r="D17" s="58"/>
       <c r="E17" s="53"/>
       <c r="F17" s="59"/>
@@ -7372,8 +7407,8 @@
       </c>
     </row>
     <row r="18" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="146"/>
-      <c r="C18" s="147" t="s">
+      <c r="B18" s="150"/>
+      <c r="C18" s="151" t="s">
         <v>97</v>
       </c>
       <c r="D18" s="54"/>
@@ -7412,8 +7447,8 @@
       <c r="AK18" s="56"/>
     </row>
     <row r="19" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="146"/>
-      <c r="C19" s="147"/>
+      <c r="B19" s="150"/>
+      <c r="C19" s="151"/>
       <c r="D19" s="56"/>
       <c r="E19" s="53"/>
       <c r="F19" s="60"/>
@@ -7450,8 +7485,8 @@
       <c r="AK19" s="56"/>
     </row>
     <row r="20" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="146"/>
-      <c r="C20" s="147" t="s">
+      <c r="B20" s="150"/>
+      <c r="C20" s="151" t="s">
         <v>98</v>
       </c>
       <c r="D20" s="56"/>
@@ -7490,8 +7525,8 @@
       <c r="AK20" s="56"/>
     </row>
     <row r="21" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="146"/>
-      <c r="C21" s="147"/>
+      <c r="B21" s="150"/>
+      <c r="C21" s="151"/>
       <c r="D21" s="56"/>
       <c r="E21" s="56"/>
       <c r="F21" s="59"/>
@@ -7528,8 +7563,8 @@
       <c r="AK21" s="56"/>
     </row>
     <row r="22" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="146"/>
-      <c r="C22" s="147" t="s">
+      <c r="B22" s="150"/>
+      <c r="C22" s="151" t="s">
         <v>99</v>
       </c>
       <c r="D22" s="56"/>
@@ -7568,8 +7603,8 @@
       <c r="AK22" s="56"/>
     </row>
     <row r="23" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="146"/>
-      <c r="C23" s="147"/>
+      <c r="B23" s="150"/>
+      <c r="C23" s="151"/>
       <c r="D23" s="56"/>
       <c r="E23" s="56"/>
       <c r="F23" s="59"/>
@@ -7606,8 +7641,8 @@
       <c r="AK23" s="56"/>
     </row>
     <row r="24" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="146"/>
-      <c r="C24" s="147" t="s">
+      <c r="B24" s="150"/>
+      <c r="C24" s="151" t="s">
         <v>100</v>
       </c>
       <c r="D24" s="56"/>
@@ -7646,8 +7681,8 @@
       <c r="AK24" s="56"/>
     </row>
     <row r="25" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="146"/>
-      <c r="C25" s="147"/>
+      <c r="B25" s="150"/>
+      <c r="C25" s="151"/>
       <c r="D25" s="56"/>
       <c r="E25" s="56"/>
       <c r="F25" s="59"/>
@@ -7684,10 +7719,10 @@
       <c r="AK25" s="56"/>
     </row>
     <row r="26" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="144" t="s">
+      <c r="B26" s="148" t="s">
         <v>101</v>
       </c>
-      <c r="C26" s="149" t="s">
+      <c r="C26" s="153" t="s">
         <v>102</v>
       </c>
       <c r="D26" s="40"/>
@@ -7726,8 +7761,8 @@
       <c r="AK26" s="40"/>
     </row>
     <row r="27" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="144"/>
-      <c r="C27" s="149"/>
+      <c r="B27" s="148"/>
+      <c r="C27" s="153"/>
       <c r="D27" s="40"/>
       <c r="E27" s="40"/>
       <c r="F27" s="48"/>
@@ -7764,8 +7799,8 @@
       <c r="AK27" s="40"/>
     </row>
     <row r="28" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="144"/>
-      <c r="C28" s="149" t="s">
+      <c r="B28" s="148"/>
+      <c r="C28" s="153" t="s">
         <v>103</v>
       </c>
       <c r="D28" s="40"/>
@@ -7804,8 +7839,8 @@
       <c r="AK28" s="40"/>
     </row>
     <row r="29" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="144"/>
-      <c r="C29" s="149"/>
+      <c r="B29" s="148"/>
+      <c r="C29" s="153"/>
       <c r="D29" s="40"/>
       <c r="E29" s="40"/>
       <c r="F29" s="48"/>
@@ -7842,8 +7877,8 @@
       <c r="AK29" s="40"/>
     </row>
     <row r="30" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="144"/>
-      <c r="C30" s="149" t="s">
+      <c r="B30" s="148"/>
+      <c r="C30" s="153" t="s">
         <v>104</v>
       </c>
       <c r="D30" s="40"/>
@@ -7882,8 +7917,8 @@
       <c r="AK30" s="40"/>
     </row>
     <row r="31" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="144"/>
-      <c r="C31" s="149"/>
+      <c r="B31" s="148"/>
+      <c r="C31" s="153"/>
       <c r="D31" s="40"/>
       <c r="E31" s="40"/>
       <c r="F31" s="50"/>
@@ -7920,8 +7955,8 @@
       <c r="AK31" s="40"/>
     </row>
     <row r="32" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="144"/>
-      <c r="C32" s="149" t="s">
+      <c r="B32" s="148"/>
+      <c r="C32" s="153" t="s">
         <v>105</v>
       </c>
       <c r="D32" s="40"/>
@@ -7960,8 +7995,8 @@
       <c r="AK32" s="40"/>
     </row>
     <row r="33" spans="2:41" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="144"/>
-      <c r="C33" s="149"/>
+      <c r="B33" s="148"/>
+      <c r="C33" s="153"/>
       <c r="D33" s="40"/>
       <c r="E33" s="40"/>
       <c r="F33" s="48"/>
@@ -7998,10 +8033,10 @@
       <c r="AK33" s="40"/>
     </row>
     <row r="34" spans="2:41" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="146" t="s">
+      <c r="B34" s="150" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="148" t="s">
+      <c r="C34" s="152" t="s">
         <v>107</v>
       </c>
       <c r="D34" s="56"/>
@@ -8040,8 +8075,8 @@
       <c r="AK34" s="56"/>
     </row>
     <row r="35" spans="2:41" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="146"/>
-      <c r="C35" s="148"/>
+      <c r="B35" s="150"/>
+      <c r="C35" s="152"/>
       <c r="D35" s="56"/>
       <c r="E35" s="56"/>
       <c r="F35" s="59"/>
@@ -8056,8 +8091,8 @@
       <c r="O35" s="55"/>
       <c r="P35" s="53"/>
       <c r="Q35" s="56"/>
-      <c r="R35" s="173"/>
-      <c r="S35" s="173"/>
+      <c r="R35" s="147"/>
+      <c r="S35" s="147"/>
       <c r="T35" s="56"/>
       <c r="U35" s="56"/>
       <c r="V35" s="57"/>
@@ -8078,8 +8113,8 @@
       <c r="AK35" s="56"/>
     </row>
     <row r="36" spans="2:41" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="146"/>
-      <c r="C36" s="148" t="s">
+      <c r="B36" s="150"/>
+      <c r="C36" s="152" t="s">
         <v>108</v>
       </c>
       <c r="D36" s="56"/>
@@ -8118,8 +8153,8 @@
       <c r="AK36" s="56"/>
     </row>
     <row r="37" spans="2:41" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="146"/>
-      <c r="C37" s="148"/>
+      <c r="B37" s="150"/>
+      <c r="C37" s="152"/>
       <c r="D37" s="56"/>
       <c r="E37" s="56"/>
       <c r="F37" s="59"/>
@@ -8134,8 +8169,8 @@
       <c r="O37" s="55"/>
       <c r="P37" s="53"/>
       <c r="Q37" s="56"/>
-      <c r="R37" s="173"/>
-      <c r="S37" s="173"/>
+      <c r="R37" s="147"/>
+      <c r="S37" s="147"/>
       <c r="T37" s="56"/>
       <c r="U37" s="56"/>
       <c r="V37" s="57"/>
@@ -8156,8 +8191,8 @@
       <c r="AK37" s="56"/>
     </row>
     <row r="38" spans="2:41" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="146"/>
-      <c r="C38" s="148" t="s">
+      <c r="B38" s="150"/>
+      <c r="C38" s="152" t="s">
         <v>109</v>
       </c>
       <c r="D38" s="56"/>
@@ -8196,8 +8231,8 @@
       <c r="AK38" s="56"/>
     </row>
     <row r="39" spans="2:41" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="146"/>
-      <c r="C39" s="148"/>
+      <c r="B39" s="150"/>
+      <c r="C39" s="152"/>
       <c r="D39" s="56"/>
       <c r="E39" s="56"/>
       <c r="F39" s="59"/>
@@ -8234,8 +8269,8 @@
       <c r="AK39" s="56"/>
     </row>
     <row r="40" spans="2:41" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="146"/>
-      <c r="C40" s="148" t="s">
+      <c r="B40" s="150"/>
+      <c r="C40" s="152" t="s">
         <v>110</v>
       </c>
       <c r="D40" s="56"/>
@@ -8274,8 +8309,8 @@
       <c r="AK40" s="56"/>
     </row>
     <row r="41" spans="2:41" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="146"/>
-      <c r="C41" s="148"/>
+      <c r="B41" s="150"/>
+      <c r="C41" s="152"/>
       <c r="D41" s="56"/>
       <c r="E41" s="56"/>
       <c r="F41" s="59"/>
@@ -8312,10 +8347,10 @@
       <c r="AK41" s="56"/>
     </row>
     <row r="42" spans="2:41" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="144" t="s">
+      <c r="B42" s="148" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="145" t="s">
+      <c r="C42" s="149" t="s">
         <v>111</v>
       </c>
       <c r="D42" s="40"/>
@@ -8354,8 +8389,8 @@
       <c r="AK42" s="40"/>
     </row>
     <row r="43" spans="2:41" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="144"/>
-      <c r="C43" s="145"/>
+      <c r="B43" s="148"/>
+      <c r="C43" s="149"/>
       <c r="D43" s="40"/>
       <c r="E43" s="40"/>
       <c r="F43" s="48"/>
@@ -8392,8 +8427,8 @@
       <c r="AK43" s="40"/>
     </row>
     <row r="44" spans="2:41" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="144"/>
-      <c r="C44" s="145" t="s">
+      <c r="B44" s="148"/>
+      <c r="C44" s="149" t="s">
         <v>112</v>
       </c>
       <c r="D44" s="40"/>
@@ -8432,8 +8467,8 @@
       <c r="AK44" s="40"/>
     </row>
     <row r="45" spans="2:41" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="144"/>
-      <c r="C45" s="145"/>
+      <c r="B45" s="148"/>
+      <c r="C45" s="149"/>
       <c r="D45" s="40"/>
       <c r="E45" s="40"/>
       <c r="F45" s="48"/>
@@ -8470,10 +8505,10 @@
       <c r="AK45" s="40"/>
     </row>
     <row r="46" spans="2:41" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="146" t="s">
+      <c r="B46" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="C46" s="147" t="s">
+      <c r="C46" s="151" t="s">
         <v>24</v>
       </c>
       <c r="D46" s="56"/>
@@ -8512,8 +8547,8 @@
       <c r="AK46" s="56"/>
     </row>
     <row r="47" spans="2:41" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="146"/>
-      <c r="C47" s="147"/>
+      <c r="B47" s="150"/>
+      <c r="C47" s="151"/>
       <c r="D47" s="56"/>
       <c r="E47" s="56"/>
       <c r="F47" s="59"/>
@@ -8554,8 +8589,8 @@
       <c r="AO47" s="54"/>
     </row>
     <row r="48" spans="2:41" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="146"/>
-      <c r="C48" s="147" t="s">
+      <c r="B48" s="150"/>
+      <c r="C48" s="151" t="s">
         <v>115</v>
       </c>
       <c r="D48" s="56"/>
@@ -8598,8 +8633,8 @@
       <c r="AO48" s="53"/>
     </row>
     <row r="49" spans="2:41" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="146"/>
-      <c r="C49" s="147"/>
+      <c r="B49" s="150"/>
+      <c r="C49" s="151"/>
       <c r="D49" s="56"/>
       <c r="E49" s="56"/>
       <c r="F49" s="59"/>
@@ -8700,10 +8735,10 @@
       <c r="B1" s="66"/>
     </row>
     <row r="2" spans="2:30" ht="56.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="159" t="s">
+      <c r="B2" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="154" t="s">
+      <c r="C2" s="158" t="s">
         <v>62</v>
       </c>
       <c r="D2" s="67" t="s">
@@ -8712,33 +8747,33 @@
       <c r="E2" s="68" t="s">
         <v>119</v>
       </c>
-      <c r="F2" s="150" t="s">
+      <c r="F2" s="154" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="150"/>
-      <c r="H2" s="150"/>
-      <c r="I2" s="162"/>
-      <c r="J2" s="150" t="s">
+      <c r="G2" s="154"/>
+      <c r="H2" s="154"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="154" t="s">
         <v>121</v>
       </c>
-      <c r="K2" s="150"/>
-      <c r="L2" s="150"/>
-      <c r="M2" s="162"/>
-      <c r="N2" s="150" t="s">
+      <c r="K2" s="154"/>
+      <c r="L2" s="154"/>
+      <c r="M2" s="166"/>
+      <c r="N2" s="154" t="s">
         <v>122</v>
       </c>
-      <c r="O2" s="150"/>
-      <c r="P2" s="150"/>
-      <c r="Q2" s="162"/>
-      <c r="R2" s="150" t="s">
+      <c r="O2" s="154"/>
+      <c r="P2" s="154"/>
+      <c r="Q2" s="166"/>
+      <c r="R2" s="154" t="s">
         <v>123</v>
       </c>
-      <c r="S2" s="151"/>
+      <c r="S2" s="155"/>
       <c r="AD2" s="22"/>
     </row>
     <row r="3" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B3" s="160"/>
-      <c r="C3" s="161"/>
+      <c r="B3" s="164"/>
+      <c r="C3" s="165"/>
       <c r="D3" s="69" t="s">
         <v>124</v>
       </c>
@@ -8792,10 +8827,10 @@
       </c>
     </row>
     <row r="4" spans="2:30" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="152" t="s">
+      <c r="B4" s="156" t="s">
         <v>126</v>
       </c>
-      <c r="C4" s="154" t="s">
+      <c r="C4" s="158" t="s">
         <v>127</v>
       </c>
       <c r="D4" s="74"/>
@@ -8819,8 +8854,8 @@
       </c>
     </row>
     <row r="5" spans="2:30" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="152"/>
-      <c r="C5" s="155"/>
+      <c r="B5" s="156"/>
+      <c r="C5" s="159"/>
       <c r="D5" s="80"/>
       <c r="E5" s="81"/>
       <c r="F5" s="82"/>
@@ -8839,8 +8874,8 @@
       <c r="S5" s="86"/>
     </row>
     <row r="6" spans="2:30" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="152"/>
-      <c r="C6" s="156" t="s">
+      <c r="B6" s="156"/>
+      <c r="C6" s="160" t="s">
         <v>129</v>
       </c>
       <c r="D6" s="87"/>
@@ -8859,14 +8894,14 @@
       <c r="Q6" s="88"/>
       <c r="R6" s="92"/>
       <c r="S6" s="93"/>
-      <c r="U6" s="157" t="s">
+      <c r="U6" s="161" t="s">
         <v>130</v>
       </c>
-      <c r="V6" s="157"/>
+      <c r="V6" s="161"/>
     </row>
     <row r="7" spans="2:30" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="152"/>
-      <c r="C7" s="155"/>
+      <c r="B7" s="156"/>
+      <c r="C7" s="159"/>
       <c r="D7" s="80"/>
       <c r="E7" s="81"/>
       <c r="F7" s="85"/>
@@ -8888,8 +8923,8 @@
       </c>
     </row>
     <row r="8" spans="2:30" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="152"/>
-      <c r="C8" s="156" t="s">
+      <c r="B8" s="156"/>
+      <c r="C8" s="160" t="s">
         <v>132</v>
       </c>
       <c r="D8" s="87"/>
@@ -8913,8 +8948,8 @@
       </c>
     </row>
     <row r="9" spans="2:30" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="152"/>
-      <c r="C9" s="155"/>
+      <c r="B9" s="156"/>
+      <c r="C9" s="159"/>
       <c r="D9" s="80"/>
       <c r="E9" s="81"/>
       <c r="F9" s="85"/>
@@ -8933,8 +8968,8 @@
       <c r="S9" s="86"/>
     </row>
     <row r="10" spans="2:30" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="152"/>
-      <c r="C10" s="156" t="s">
+      <c r="B10" s="156"/>
+      <c r="C10" s="160" t="s">
         <v>134</v>
       </c>
       <c r="D10" s="87"/>
@@ -8955,8 +8990,8 @@
       <c r="S10" s="93"/>
     </row>
     <row r="11" spans="2:30" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="153"/>
-      <c r="C11" s="158"/>
+      <c r="B11" s="157"/>
+      <c r="C11" s="162"/>
       <c r="D11" s="94"/>
       <c r="E11" s="95"/>
       <c r="F11" s="96"/>
@@ -8975,10 +9010,10 @@
       <c r="S11" s="99"/>
     </row>
     <row r="12" spans="2:30" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="159" t="s">
+      <c r="B12" s="163" t="s">
         <v>135</v>
       </c>
-      <c r="C12" s="154" t="s">
+      <c r="C12" s="158" t="s">
         <v>136</v>
       </c>
       <c r="D12" s="74"/>
@@ -8999,8 +9034,8 @@
       <c r="S12" s="79"/>
     </row>
     <row r="13" spans="2:30" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="152"/>
-      <c r="C13" s="155"/>
+      <c r="B13" s="156"/>
+      <c r="C13" s="159"/>
       <c r="D13" s="80"/>
       <c r="E13" s="81"/>
       <c r="F13" s="85"/>
@@ -9019,8 +9054,8 @@
       <c r="S13" s="86"/>
     </row>
     <row r="14" spans="2:30" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="152"/>
-      <c r="C14" s="156" t="s">
+      <c r="B14" s="156"/>
+      <c r="C14" s="160" t="s">
         <v>137</v>
       </c>
       <c r="D14" s="102"/>
@@ -9041,8 +9076,8 @@
       <c r="S14" s="93"/>
     </row>
     <row r="15" spans="2:30" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="152"/>
-      <c r="C15" s="155"/>
+      <c r="B15" s="156"/>
+      <c r="C15" s="159"/>
       <c r="D15" s="80"/>
       <c r="E15" s="81"/>
       <c r="F15" s="85"/>
@@ -9061,8 +9096,8 @@
       <c r="S15" s="86"/>
     </row>
     <row r="16" spans="2:30" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="152"/>
-      <c r="C16" s="156" t="s">
+      <c r="B16" s="156"/>
+      <c r="C16" s="160" t="s">
         <v>138</v>
       </c>
       <c r="D16" s="87"/>
@@ -9083,8 +9118,8 @@
       <c r="S16" s="93"/>
     </row>
     <row r="17" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="153"/>
-      <c r="C17" s="158"/>
+      <c r="B17" s="157"/>
+      <c r="C17" s="162"/>
       <c r="D17" s="94"/>
       <c r="E17" s="95"/>
       <c r="F17" s="96"/>
@@ -9103,10 +9138,10 @@
       <c r="S17" s="99"/>
     </row>
     <row r="18" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="163" t="s">
+      <c r="B18" s="167" t="s">
         <v>139</v>
       </c>
-      <c r="C18" s="154" t="s">
+      <c r="C18" s="158" t="s">
         <v>140</v>
       </c>
       <c r="D18" s="74"/>
@@ -9127,8 +9162,8 @@
       <c r="S18" s="79"/>
     </row>
     <row r="19" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="152"/>
-      <c r="C19" s="155"/>
+      <c r="B19" s="156"/>
+      <c r="C19" s="159"/>
       <c r="D19" s="80"/>
       <c r="E19" s="81"/>
       <c r="F19" s="85"/>
@@ -9147,8 +9182,8 @@
       <c r="S19" s="86"/>
     </row>
     <row r="20" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="152"/>
-      <c r="C20" s="156" t="s">
+      <c r="B20" s="156"/>
+      <c r="C20" s="160" t="s">
         <v>141</v>
       </c>
       <c r="D20" s="87"/>
@@ -9169,8 +9204,8 @@
       <c r="S20" s="93"/>
     </row>
     <row r="21" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="152"/>
-      <c r="C21" s="155"/>
+      <c r="B21" s="156"/>
+      <c r="C21" s="159"/>
       <c r="D21" s="80"/>
       <c r="E21" s="81"/>
       <c r="F21" s="85"/>
@@ -9189,8 +9224,8 @@
       <c r="S21" s="86"/>
     </row>
     <row r="22" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="152"/>
-      <c r="C22" s="156" t="s">
+      <c r="B22" s="156"/>
+      <c r="C22" s="160" t="s">
         <v>142</v>
       </c>
       <c r="D22" s="87"/>
@@ -9211,8 +9246,8 @@
       <c r="S22" s="93"/>
     </row>
     <row r="23" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="153"/>
-      <c r="C23" s="158"/>
+      <c r="B23" s="157"/>
+      <c r="C23" s="162"/>
       <c r="D23" s="94"/>
       <c r="E23" s="95"/>
       <c r="F23" s="96"/>
@@ -9231,10 +9266,10 @@
       <c r="S23" s="99"/>
     </row>
     <row r="24" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="163" t="s">
+      <c r="B24" s="167" t="s">
         <v>143</v>
       </c>
-      <c r="C24" s="154" t="s">
+      <c r="C24" s="158" t="s">
         <v>144</v>
       </c>
       <c r="D24" s="74"/>
@@ -9255,8 +9290,8 @@
       <c r="S24" s="79"/>
     </row>
     <row r="25" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="152"/>
-      <c r="C25" s="155"/>
+      <c r="B25" s="156"/>
+      <c r="C25" s="159"/>
       <c r="D25" s="80"/>
       <c r="E25" s="81"/>
       <c r="F25" s="85"/>
@@ -9275,8 +9310,8 @@
       <c r="S25" s="86"/>
     </row>
     <row r="26" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="152"/>
-      <c r="C26" s="156" t="s">
+      <c r="B26" s="156"/>
+      <c r="C26" s="160" t="s">
         <v>145</v>
       </c>
       <c r="D26" s="87"/>
@@ -9297,8 +9332,8 @@
       <c r="S26" s="93"/>
     </row>
     <row r="27" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="152"/>
-      <c r="C27" s="155"/>
+      <c r="B27" s="156"/>
+      <c r="C27" s="159"/>
       <c r="D27" s="80"/>
       <c r="E27" s="81"/>
       <c r="F27" s="85"/>
@@ -9317,8 +9352,8 @@
       <c r="S27" s="86"/>
     </row>
     <row r="28" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="152"/>
-      <c r="C28" s="156" t="s">
+      <c r="B28" s="156"/>
+      <c r="C28" s="160" t="s">
         <v>146</v>
       </c>
       <c r="D28" s="87"/>
@@ -9339,8 +9374,8 @@
       <c r="S28" s="93"/>
     </row>
     <row r="29" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="152"/>
-      <c r="C29" s="161"/>
+      <c r="B29" s="156"/>
+      <c r="C29" s="165"/>
       <c r="D29" s="107"/>
       <c r="E29" s="108"/>
       <c r="F29" s="109"/>
@@ -9359,10 +9394,10 @@
       <c r="S29" s="113"/>
     </row>
     <row r="30" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="164" t="s">
+      <c r="B30" s="168" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="167" t="s">
+      <c r="C30" s="171" t="s">
         <v>90</v>
       </c>
       <c r="D30" s="74"/>
@@ -9383,8 +9418,8 @@
       <c r="S30" s="118"/>
     </row>
     <row r="31" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="165"/>
-      <c r="C31" s="168"/>
+      <c r="B31" s="169"/>
+      <c r="C31" s="172"/>
       <c r="D31" s="80"/>
       <c r="E31" s="119"/>
       <c r="F31" s="120"/>
@@ -9403,8 +9438,8 @@
       <c r="S31" s="86"/>
     </row>
     <row r="32" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="165"/>
-      <c r="C32" s="168" t="s">
+      <c r="B32" s="169"/>
+      <c r="C32" s="172" t="s">
         <v>12</v>
       </c>
       <c r="D32" s="87"/>
@@ -9425,8 +9460,8 @@
       <c r="S32" s="128"/>
     </row>
     <row r="33" spans="2:22" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="165"/>
-      <c r="C33" s="168"/>
+      <c r="B33" s="169"/>
+      <c r="C33" s="172"/>
       <c r="D33" s="80"/>
       <c r="E33" s="119"/>
       <c r="F33" s="123"/>
@@ -9445,8 +9480,8 @@
       <c r="S33" s="86"/>
     </row>
     <row r="34" spans="2:22" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="165"/>
-      <c r="C34" s="155" t="s">
+      <c r="B34" s="169"/>
+      <c r="C34" s="159" t="s">
         <v>147</v>
       </c>
       <c r="D34" s="107"/>
@@ -9471,8 +9506,8 @@
       </c>
     </row>
     <row r="35" spans="2:22" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="166"/>
-      <c r="C35" s="169"/>
+      <c r="B35" s="170"/>
+      <c r="C35" s="173"/>
       <c r="D35" s="94"/>
       <c r="E35" s="138"/>
       <c r="F35" s="139"/>

--- a/Documentation/HoferL-JournalPlanif-M5.xlsx
+++ b/Documentation/HoferL-JournalPlanif-M5.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
   <si>
     <t>date</t>
   </si>
@@ -274,6 +274,15 @@
   </si>
   <si>
     <t xml:space="preserve">Documentation des fichiers MVVM + Documentation du repertoire intérraction avec la BDD et de l'rchitecture globale et modélisation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recherche d'une solution optimal pour stocker des scan d'évaluation dans l'application</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Création d'un PoC du concept. Test de fonctionnement du WorkFlow : PDF -&gt; Compression images -&gt; Archive -&gt; PDF. Fonctionnel 6,8Mo -&gt; 400Ko.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implémentation et séparation des responsabilités dans des classes séparés. WorkFlow en mémoire et Blob pour la souvegarde dans SQLite fonctionnel. (sans test d'injection du blob)</t>
   </si>
   <si>
     <t>Phases</t>
@@ -1512,10 +1521,13 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="176">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1552,11 +1564,20 @@
     <xf fontId="0" fillId="0" borderId="2" numFmtId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="20" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2453,13 +2474,13 @@
                   <c:v>05.03.2026</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>06.03.2026</c:v>
+                  <c:v>3/6/2026</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>07.03.2026</c:v>
+                  <c:v>3/7/2026</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>10.03.2026</c:v>
+                  <c:v>3/10/2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3574,8 +3595,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E47">
-  <autoFilter ref="B2:E47"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E50">
+  <autoFilter ref="B2:E50"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -4086,9 +4107,9 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="2"/>
     <col customWidth="1" min="2" max="2" width="11.33203125"/>
-    <col customWidth="1" min="3" max="3" width="7.6640625"/>
+    <col customWidth="1" min="3" max="3" style="1" width="7.6640625"/>
     <col bestFit="1" customWidth="1" min="4" max="4" width="15.21875"/>
-    <col customWidth="1" min="5" max="5" width="56.109375"/>
+    <col customWidth="1" min="5" max="5" style="2" width="56.109375"/>
     <col customWidth="1" min="6" max="6" width="2.88671875"/>
     <col customWidth="1" min="7" max="7" width="27.44140625"/>
     <col customWidth="1" min="8" max="8" width="10.21875"/>
@@ -4105,763 +4126,763 @@
       <c r="D2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G2" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
     </row>
     <row r="3">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="6">
         <v>0.125</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
         <v>3</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.027272727272727271</v>
-      </c>
-      <c r="J3" s="11" t="str" cm="1">
+        <v>2.5210084033613446e-002</v>
+      </c>
+      <c r="J3" s="12" t="str" cm="1">
         <f t="array" ref="J3:J9">_xlfn._xlws.FILTER(G3:G10,H3:H10&gt;0)</f>
         <v>Cours</v>
       </c>
-      <c r="K3" s="12" cm="1">
+      <c r="K3" s="13" cm="1">
         <f t="array" ref="K3:K9">_xlfn._xlws.FILTER(H3:H10,H3:H10&gt;0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="5">
-        <v>0.041666666666666664</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="C4" s="6">
+        <v>4.1666666666666664e-002</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
         <v>3</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.027272727272727271</v>
-      </c>
-      <c r="J4" s="3" t="str">
+        <v>2.5210084033613446e-002</v>
+      </c>
+      <c r="J4" s="4" t="str">
         <f/>
         <v>Plannification</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="13">
         <f/>
         <v>3</v>
       </c>
     </row>
     <row r="5" ht="28.5">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="6">
         <v>0.125</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>7</v>
-      </c>
-      <c r="I5" s="10">
+        <v>9</v>
+      </c>
+      <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.06363636363636363</v>
-      </c>
-      <c r="J5" s="3" t="str">
+        <v>7.5630252100840331e-002</v>
+      </c>
+      <c r="J5" s="4" t="str">
         <f/>
         <v>Recherche</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="13">
         <f/>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="5">
-        <v>0.041666666666666664</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="C6" s="6">
+        <v>4.1666666666666664e-002</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
         <v>17</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.15454545454545454</v>
-      </c>
-      <c r="J6" s="3" t="str">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="J6" s="4" t="str">
         <f/>
         <v>Maquettage</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="13">
         <f/>
         <v>17</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="5">
-        <v>0.041666666666666664</v>
-      </c>
-      <c r="D7" s="6" t="s">
+      <c r="C7" s="6">
+        <v>4.1666666666666664e-002</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
         <v>37.5</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.34090909090909088</v>
-      </c>
-      <c r="J7" s="3" t="str">
+        <v>0.31512605042016806</v>
+      </c>
+      <c r="J7" s="4" t="str">
         <f/>
         <v>Documentation</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="13">
         <f/>
         <v>37.5</v>
       </c>
     </row>
     <row r="8" ht="28.5">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="6">
         <v>0.125</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>41.5</v>
-      </c>
-      <c r="I8" s="10">
+        <v>48.5</v>
+      </c>
+      <c r="I8" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.37727272727272726</v>
-      </c>
-      <c r="J8" s="3" t="str">
+        <v>0.40756302521008403</v>
+      </c>
+      <c r="J8" s="4" t="str">
         <f/>
         <v>Programmation</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="13">
         <f/>
-        <v>41.5</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="6">
         <v>0.16666666666666666</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
         <v>1</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.0090909090909090905</v>
-      </c>
-      <c r="J9" s="3" t="str">
+        <v>8.4033613445378148e-003</v>
+      </c>
+      <c r="J9" s="4" t="str">
         <f/>
         <v>Tests</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="14">
         <f/>
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="5">
-        <v>0.083333333333333329</v>
-      </c>
-      <c r="D10" s="6" t="s">
+      <c r="C10" s="6">
+        <v>8.3333333333333329e-002</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="16">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
         <v>0</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
         <v>0</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
     </row>
     <row r="11" ht="28.5">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="5">
-        <v>0.041666666666666664</v>
-      </c>
-      <c r="D11" s="6" t="s">
+      <c r="C11" s="6">
+        <v>4.1666666666666664e-002</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="10">
         <f>SUM(H3:H10)</f>
-        <v>110</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
     </row>
     <row r="12">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="5">
-        <v>0.041666666666666664</v>
-      </c>
-      <c r="D12" s="6" t="s">
+      <c r="C12" s="6">
+        <v>4.1666666666666664e-002</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H12" s="9"/>
+      <c r="H12" s="10"/>
     </row>
     <row r="13" ht="42.75">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="5">
-        <v>0.083333333333333329</v>
-      </c>
-      <c r="D13" s="6" t="s">
+      <c r="C13" s="6">
+        <v>8.3333333333333329e-002</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="9"/>
+      <c r="H13" s="10"/>
     </row>
     <row r="14" ht="28.5">
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="5">
-        <v>0.083333333333333329</v>
-      </c>
-      <c r="D14" s="6" t="s">
+      <c r="C14" s="6">
+        <v>8.3333333333333329e-002</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" ht="28.5">
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="6">
         <v>0.125</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="6">
         <v>0.125</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="8" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" ht="28.5">
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="6">
         <v>0.16666666666666666</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="8" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="5">
-        <v>0.083333333333333329</v>
-      </c>
-      <c r="D18" s="6" t="s">
+      <c r="C18" s="6">
+        <v>8.3333333333333329e-002</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="8" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="5">
-        <v>0.041666666666666664</v>
-      </c>
-      <c r="D19" s="6" t="s">
+      <c r="C19" s="6">
+        <v>4.1666666666666664e-002</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="5">
-        <v>0.083333333333333329</v>
-      </c>
-      <c r="D20" s="6" t="s">
+      <c r="C20" s="6">
+        <v>8.3333333333333329e-002</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="5">
-        <v>0.083333333333333329</v>
-      </c>
-      <c r="D21" s="6" t="s">
+      <c r="C21" s="6">
+        <v>8.3333333333333329e-002</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="8" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="6">
         <v>0.125</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="8" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="5">
-        <v>0.083333333333333329</v>
-      </c>
-      <c r="D23" s="6" t="s">
+      <c r="C23" s="6">
+        <v>8.3333333333333329e-002</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="5">
-        <v>0.0625</v>
-      </c>
-      <c r="D24" s="6" t="s">
+      <c r="C24" s="6">
+        <v>6.25e-002</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="8" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="6">
         <v>0.125</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="8" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="6">
         <v>0.125</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="8" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C27" s="5">
-        <v>0.083333333333333329</v>
-      </c>
-      <c r="D27" s="6" t="s">
+      <c r="C27" s="6">
+        <v>8.3333333333333329e-002</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="8" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="28" ht="28.5">
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="5">
-        <v>0.0625</v>
-      </c>
-      <c r="D28" s="6" t="s">
+      <c r="C28" s="6">
+        <v>6.25e-002</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="8" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="6">
         <v>0.125</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="8" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="30" ht="42.75">
-      <c r="B30" s="4">
+      <c r="B30" s="5">
         <v>46087</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="6">
         <v>0.16666666666666666</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="8" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="31" ht="28.5">
-      <c r="B31" s="4">
+      <c r="B31" s="5">
         <v>46087</v>
       </c>
-      <c r="C31" s="5">
-        <v>0.020833333333333332</v>
-      </c>
-      <c r="D31" s="6" t="s">
+      <c r="C31" s="6">
+        <v>2.0833333333333332e-002</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="8" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="32" ht="57">
-      <c r="B32" s="4">
+      <c r="B32" s="5">
         <v>46088</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32" s="6">
         <v>0.25</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="8" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="4">
+      <c r="B33" s="5">
         <v>46091</v>
       </c>
-      <c r="C33" s="5">
-        <v>0.020833333333333332</v>
-      </c>
-      <c r="D33" s="6" t="s">
+      <c r="C33" s="6">
+        <v>2.0833333333333332e-002</v>
+      </c>
+      <c r="D33" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="8" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="34" ht="28.5">
-      <c r="B34" s="4">
+      <c r="B34" s="5">
         <v>46091</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34" s="6">
         <v>0.10416666666666667</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="8" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="4">
+      <c r="B35" s="5">
         <v>46091</v>
       </c>
-      <c r="C35" s="5">
-        <v>0.020833333333333332</v>
-      </c>
-      <c r="D35" s="6" t="s">
+      <c r="C35" s="6">
+        <v>2.0833333333333332e-002</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="8" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="4">
+      <c r="B36" s="5">
         <v>46091</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C36" s="6">
         <v>0.14583333333333334</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D36" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="8" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="37" ht="28.5">
-      <c r="B37" s="4">
+      <c r="B37" s="5">
         <v>46093</v>
       </c>
-      <c r="C37" s="5">
-        <v>0.083333333333333329</v>
-      </c>
-      <c r="D37" s="6" t="s">
+      <c r="C37" s="6">
+        <v>8.3333333333333329e-002</v>
+      </c>
+      <c r="D37" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="8" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="38" ht="57">
-      <c r="B38" s="4">
+      <c r="B38" s="5">
         <v>46095</v>
       </c>
-      <c r="C38" s="5">
+      <c r="C38" s="6">
         <v>0.1875</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D38" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="E38" s="8" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="39" ht="28.5">
-      <c r="B39" s="4">
+      <c r="B39" s="5">
         <v>46087</v>
       </c>
-      <c r="C39" s="5">
-        <v>0.020833333333333332</v>
-      </c>
-      <c r="D39" s="6" t="s">
+      <c r="C39" s="6">
+        <v>2.0833333333333332e-002</v>
+      </c>
+      <c r="D39" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="E39" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="H39" s="16"/>
-      <c r="I39" s="17"/>
-      <c r="J39" s="18"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="19"/>
     </row>
     <row r="40">
-      <c r="B40" s="4">
+      <c r="B40" s="5">
         <v>46096</v>
       </c>
-      <c r="C40" s="5">
+      <c r="C40" s="6">
         <v>0.10416666666666667</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="E40" s="8" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="41" ht="42.75">
-      <c r="B41" s="4">
+      <c r="B41" s="5">
         <v>46096</v>
       </c>
-      <c r="C41" s="5">
+      <c r="C41" s="6">
         <v>0.10416666666666667</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E41" s="8" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="42" ht="42.75">
-      <c r="B42" s="4">
+      <c r="B42" s="5">
         <v>46097</v>
       </c>
-      <c r="C42" s="5">
+      <c r="C42" s="6">
         <v>0.14583333333333334</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="8" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="43" ht="28.5">
-      <c r="B43" s="4">
+      <c r="B43" s="5">
         <v>46098</v>
       </c>
-      <c r="C43" s="5">
+      <c r="C43" s="6">
         <v>0.16666666666666666</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="E43" s="8" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="44" ht="57">
-      <c r="B44" s="4">
+      <c r="B44" s="5">
         <v>46099</v>
       </c>
-      <c r="C44" s="5">
+      <c r="C44" s="6">
         <v>0.20833333333333334</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D44" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="E44" s="8" t="s">
         <v>68</v>
       </c>
       <c r="G44" t="s">
@@ -4869,244 +4890,268 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="4">
+      <c r="B45" s="5">
         <v>46100</v>
       </c>
-      <c r="C45" s="5">
-        <v>0.041666666666666664</v>
-      </c>
-      <c r="D45" s="6" t="s">
+      <c r="C45" s="6">
+        <v>4.1666666666666664e-002</v>
+      </c>
+      <c r="D45" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="7" t="s">
+      <c r="E45" s="8" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="4">
+      <c r="B46" s="5">
         <v>46100</v>
       </c>
-      <c r="C46" s="5">
-        <v>0.041666666666666664</v>
-      </c>
-      <c r="D46" s="6" t="s">
+      <c r="C46" s="6">
+        <v>4.1666666666666664e-002</v>
+      </c>
+      <c r="D46" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E46" s="7" t="s">
+      <c r="E46" s="8" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="47" ht="42.75">
-      <c r="B47" s="4">
+      <c r="B47" s="5">
         <v>46100</v>
       </c>
-      <c r="C47" s="5">
+      <c r="C47" s="6">
         <v>0.25</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D47" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E47" s="19" t="s">
+      <c r="E47" s="8" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="20"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="20"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-    </row>
-    <row r="50">
-      <c r="B50" s="20"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
+    <row r="48" ht="28.5">
+      <c r="B48" s="20">
+        <v>46102</v>
+      </c>
+      <c r="C48" s="21">
+        <v>8.3333333333333329e-002</v>
+      </c>
+      <c r="D48" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="23" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="49" ht="42.75">
+      <c r="B49" s="20">
+        <v>46102</v>
+      </c>
+      <c r="C49" s="21">
+        <v>0.125</v>
+      </c>
+      <c r="D49" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" s="23" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50" ht="57">
+      <c r="B50" s="20">
+        <v>46103</v>
+      </c>
+      <c r="C50" s="21">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D50" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50" s="23" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="51">
       <c r="B51" s="20"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="8"/>
     </row>
     <row r="52">
       <c r="B52" s="20"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="8"/>
     </row>
     <row r="53">
       <c r="B53" s="20"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="8"/>
     </row>
     <row r="54">
       <c r="B54" s="20"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="8"/>
     </row>
     <row r="55">
       <c r="B55" s="20"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="8"/>
     </row>
     <row r="56">
       <c r="B56" s="20"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="8"/>
     </row>
     <row r="57">
       <c r="B57" s="20"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="8"/>
     </row>
     <row r="58">
       <c r="B58" s="20"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="8"/>
     </row>
     <row r="59">
       <c r="B59" s="20"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="8"/>
     </row>
     <row r="60">
       <c r="B60" s="20"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6"/>
+      <c r="C60" s="24"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="8"/>
     </row>
     <row r="61">
       <c r="B61" s="20"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="8"/>
     </row>
     <row r="62">
       <c r="B62" s="20"/>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6"/>
+      <c r="C62" s="24"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="8"/>
     </row>
     <row r="63">
       <c r="B63" s="20"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
+      <c r="C63" s="24"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="8"/>
     </row>
     <row r="64">
       <c r="B64" s="20"/>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6"/>
+      <c r="C64" s="24"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="8"/>
     </row>
     <row r="65">
       <c r="B65" s="20"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
+      <c r="C65" s="24"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="8"/>
     </row>
     <row r="66">
       <c r="B66" s="20"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6"/>
+      <c r="C66" s="24"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="8"/>
     </row>
     <row r="67">
       <c r="B67" s="20"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="6"/>
+      <c r="C67" s="24"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="8"/>
     </row>
     <row r="68">
       <c r="B68" s="20"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="6"/>
+      <c r="C68" s="24"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="8"/>
     </row>
     <row r="69">
       <c r="B69" s="20"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6"/>
+      <c r="C69" s="24"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="8"/>
     </row>
     <row r="70">
       <c r="B70" s="20"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="6"/>
+      <c r="C70" s="24"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="8"/>
     </row>
     <row r="71">
       <c r="B71" s="20"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
+      <c r="C71" s="24"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="8"/>
     </row>
     <row r="72">
       <c r="B72" s="20"/>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="6"/>
+      <c r="C72" s="24"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="8"/>
     </row>
     <row r="73">
       <c r="B73" s="20"/>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
-      <c r="E73" s="6"/>
+      <c r="C73" s="24"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="8"/>
     </row>
     <row r="74">
       <c r="B74" s="20"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6"/>
+      <c r="C74" s="24"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="8"/>
     </row>
     <row r="75">
-      <c r="B75" s="6"/>
-      <c r="C75" s="6"/>
-      <c r="D75" s="6"/>
-      <c r="E75" s="6"/>
+      <c r="B75" s="7"/>
+      <c r="C75" s="24"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="8"/>
     </row>
     <row r="76">
-      <c r="B76" s="6"/>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
-      <c r="E76" s="6"/>
+      <c r="B76" s="7"/>
+      <c r="C76" s="24"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="8"/>
     </row>
     <row r="77">
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="6"/>
-      <c r="E77" s="6"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="24"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="8"/>
     </row>
     <row r="78">
-      <c r="B78" s="6"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
-      <c r="E78" s="6"/>
+      <c r="B78" s="7"/>
+      <c r="C78" s="24"/>
+      <c r="D78" s="7"/>
+      <c r="E78" s="8"/>
     </row>
     <row r="79">
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="6"/>
+      <c r="B79" s="7"/>
+      <c r="C79" s="24"/>
+      <c r="D79" s="7"/>
+      <c r="E79" s="8"/>
     </row>
     <row r="80">
-      <c r="B80" s="6"/>
-      <c r="C80" s="6"/>
-      <c r="D80" s="6"/>
-      <c r="E80" s="6"/>
+      <c r="B80" s="7"/>
+      <c r="C80" s="24"/>
+      <c r="D80" s="7"/>
+      <c r="E80" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -5124,7 +5169,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00CA006F-00E1-49E0-976F-004F00A40023}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00FC00F8-008A-4DC7-AF34-001F00B8000F}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -5140,7 +5185,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="3" max="3" style="3" width="5.6640625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" style="4" width="5.6640625"/>
     <col bestFit="1" customWidth="1" min="4" max="4" width="12.21875"/>
     <col bestFit="1" customWidth="1" min="5" max="5" width="9.5546875"/>
     <col bestFit="1" customWidth="1" min="6" max="6" width="11.109375"/>
@@ -5156,1692 +5201,1698 @@
       <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="str" cm="1">
-        <f t="array" ref="A2:A25">_xlfn.UNIQUE(Journal[date])</f>
+      <c r="A2" s="25" t="str" cm="1">
+        <f t="array" ref="A2:A27">_xlfn.UNIQUE(Journal[date])</f>
         <v>20.01.2026</v>
       </c>
-      <c r="B2" s="22">
+      <c r="B2" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A2,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C2" s="22"/>
+      <c r="C2" s="26"/>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="str">
+      <c r="A3" s="25" t="str">
         <f/>
         <v>27.01.2026</v>
       </c>
-      <c r="B3" s="22">
+      <c r="B3" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="str">
+      <c r="A4" s="25" t="str">
         <f/>
         <v>30.01.2026</v>
       </c>
-      <c r="B4" s="22">
+      <c r="B4" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C4"/>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="str">
+      <c r="A5" s="25" t="str">
         <f/>
         <v>03.02.2026</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0.25</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="str">
+      <c r="A6" s="25" t="str">
         <f/>
         <v>04.02.2026</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="str">
+      <c r="A7" s="25" t="str">
         <f/>
         <v>06.02.2026</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C7"/>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="str">
+      <c r="A8" s="25" t="str">
         <f/>
         <v>08.02.2026</v>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="str">
+      <c r="A9" s="25" t="str">
         <f/>
         <v>09.02.2026</v>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="str">
+      <c r="A10" s="25" t="str">
         <f/>
         <v>10.02.2026</v>
       </c>
-      <c r="B10" s="22">
+      <c r="B10" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="str">
+      <c r="A11" s="25" t="str">
         <f/>
         <v>12.02.2026</v>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="str">
+      <c r="A12" s="25" t="str">
         <f/>
         <v>13.02.2026</v>
       </c>
-      <c r="B12" s="22">
+      <c r="B12" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
-        <v>0.0625</v>
+        <v>6.25e-002</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="str">
+      <c r="A13" s="25" t="str">
         <f/>
         <v>24.02.2026</v>
       </c>
-      <c r="B13" s="22">
+      <c r="B13" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0.125</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="str">
+      <c r="A14" s="25" t="str">
         <f/>
         <v>03.03.2026</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="str">
+      <c r="A15" s="25" t="str">
         <f/>
         <v>05.03.2026</v>
       </c>
-      <c r="B15" s="22">
+      <c r="B15" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="21">
+      <c r="A16" s="25">
         <f/>
         <v>46087</v>
       </c>
-      <c r="B16" s="22">
+      <c r="B16" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="21">
+      <c r="A17" s="25">
         <f/>
         <v>46088</v>
       </c>
-      <c r="B17" s="22">
+      <c r="B17" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0.25</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="21">
+      <c r="A18" s="25">
         <f/>
         <v>46091</v>
       </c>
-      <c r="B18" s="22">
+      <c r="B18" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="21">
+      <c r="A19" s="25">
         <f/>
         <v>46093</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="21">
+      <c r="A20" s="25">
         <f/>
         <v>46095</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="21">
+      <c r="A21" s="25">
         <f/>
         <v>46096</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="21">
+      <c r="A22" s="25">
         <f/>
         <v>46097</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="21">
+      <c r="A23" s="25">
         <f/>
         <v>46098</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="21">
+      <c r="A24" s="25">
         <f/>
         <v>46099</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="21">
+      <c r="A25" s="25">
         <f/>
         <v>46100</v>
       </c>
       <c r="C25"/>
-      <c r="F25" s="23"/>
+      <c r="F25" s="27"/>
     </row>
     <row r="26">
-      <c r="A26" s="21"/>
-      <c r="C26" s="24">
+      <c r="A26" s="25">
+        <f/>
+        <v>46102</v>
+      </c>
+      <c r="C26" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="21"/>
-      <c r="C27" s="24">
+      <c r="A27" s="25">
+        <f/>
+        <v>46103</v>
+      </c>
+      <c r="C27" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
-        <v>0</v>
+        <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="21"/>
-      <c r="C28" s="24">
+      <c r="A28" s="25"/>
+      <c r="C28" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="21"/>
-      <c r="C29" s="24">
+      <c r="A29" s="25"/>
+      <c r="C29" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="21"/>
-      <c r="C30" s="24">
+      <c r="A30" s="25"/>
+      <c r="C30" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="21"/>
-      <c r="C31" s="24">
+      <c r="A31" s="25"/>
+      <c r="C31" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="21"/>
-      <c r="C32" s="24">
+      <c r="A32" s="25"/>
+      <c r="C32" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="21"/>
-      <c r="C33" s="24">
+      <c r="A33" s="25"/>
+      <c r="C33" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="21"/>
-      <c r="C34" s="24">
+      <c r="A34" s="25"/>
+      <c r="C34" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="21"/>
-      <c r="C35" s="24">
+      <c r="A35" s="25"/>
+      <c r="C35" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="21"/>
-      <c r="C36" s="24">
+      <c r="A36" s="25"/>
+      <c r="C36" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="21"/>
-      <c r="C37" s="24">
+      <c r="A37" s="25"/>
+      <c r="C37" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="21"/>
-      <c r="C38" s="24">
+      <c r="A38" s="25"/>
+      <c r="C38" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="21"/>
-      <c r="C39" s="24">
+      <c r="A39" s="25"/>
+      <c r="C39" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="21"/>
-      <c r="B40" s="22" t="str">
+      <c r="A40" s="25"/>
+      <c r="B40" s="26" t="str">
         <f t="shared" ref="B40:B103" si="0">IF(C40&gt;0,C40,"")</f>
         <v/>
       </c>
-      <c r="C40" s="24">
+      <c r="C40" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="21"/>
-      <c r="B41" s="22" t="str">
+      <c r="A41" s="25"/>
+      <c r="B41" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="24">
+      <c r="C41" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="25"/>
-      <c r="B42" s="22" t="str">
+      <c r="A42" s="29"/>
+      <c r="B42" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="24">
+      <c r="C42" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="25"/>
-      <c r="B43" s="22" t="str">
+      <c r="A43" s="29"/>
+      <c r="B43" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="24">
+      <c r="C43" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="25"/>
-      <c r="B44" s="22" t="str">
+      <c r="A44" s="29"/>
+      <c r="B44" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="24">
+      <c r="C44" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="25"/>
-      <c r="B45" s="22" t="str">
+      <c r="A45" s="29"/>
+      <c r="B45" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="24">
+      <c r="C45" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="25"/>
-      <c r="B46" s="22" t="str">
+      <c r="A46" s="29"/>
+      <c r="B46" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="24">
+      <c r="C46" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="26"/>
-      <c r="B47" s="22" t="str">
+      <c r="A47" s="30"/>
+      <c r="B47" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="24">
+      <c r="C47" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="26"/>
-      <c r="B48" s="22" t="str">
+      <c r="A48" s="30"/>
+      <c r="B48" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="24">
+      <c r="C48" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="26"/>
-      <c r="B49" s="22" t="str">
+      <c r="A49" s="30"/>
+      <c r="B49" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C49" s="24">
+      <c r="C49" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="26"/>
-      <c r="B50" s="22" t="str">
+      <c r="A50" s="30"/>
+      <c r="B50" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C50" s="24">
+      <c r="C50" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="26"/>
-      <c r="B51" s="22" t="str">
+      <c r="A51" s="30"/>
+      <c r="B51" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C51" s="24">
+      <c r="C51" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="26"/>
-      <c r="B52" s="22" t="str">
+      <c r="A52" s="30"/>
+      <c r="B52" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C52" s="24">
+      <c r="C52" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="26"/>
-      <c r="B53" s="22" t="str">
+      <c r="A53" s="30"/>
+      <c r="B53" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C53" s="24">
+      <c r="C53" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="26"/>
-      <c r="B54" s="22" t="str">
+      <c r="A54" s="30"/>
+      <c r="B54" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C54" s="24">
+      <c r="C54" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="26"/>
-      <c r="B55" s="22" t="str">
+      <c r="A55" s="30"/>
+      <c r="B55" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C55" s="24">
+      <c r="C55" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="26"/>
-      <c r="B56" s="22" t="str">
+      <c r="A56" s="30"/>
+      <c r="B56" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C56" s="24">
+      <c r="C56" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="26"/>
-      <c r="B57" s="22" t="str">
+      <c r="A57" s="30"/>
+      <c r="B57" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C57" s="24">
+      <c r="C57" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="26"/>
-      <c r="B58" s="22" t="str">
+      <c r="A58" s="30"/>
+      <c r="B58" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C58" s="24">
+      <c r="C58" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="26"/>
-      <c r="B59" s="22" t="str">
+      <c r="A59" s="30"/>
+      <c r="B59" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C59" s="24">
+      <c r="C59" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="26"/>
-      <c r="B60" s="22" t="str">
+      <c r="A60" s="30"/>
+      <c r="B60" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C60" s="24">
+      <c r="C60" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="26"/>
-      <c r="B61" s="22" t="str">
+      <c r="A61" s="30"/>
+      <c r="B61" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C61" s="24">
+      <c r="C61" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="26"/>
-      <c r="B62" s="22" t="str">
+      <c r="A62" s="30"/>
+      <c r="B62" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C62" s="24">
+      <c r="C62" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="26"/>
-      <c r="B63" s="22" t="str">
+      <c r="A63" s="30"/>
+      <c r="B63" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C63" s="24">
+      <c r="C63" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="26"/>
-      <c r="B64" s="22" t="str">
+      <c r="A64" s="30"/>
+      <c r="B64" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C64" s="24">
+      <c r="C64" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="26"/>
-      <c r="B65" s="22" t="str">
+      <c r="A65" s="30"/>
+      <c r="B65" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C65" s="24">
+      <c r="C65" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="26"/>
-      <c r="B66" s="22" t="str">
+      <c r="A66" s="30"/>
+      <c r="B66" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C66" s="24">
+      <c r="C66" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="26"/>
-      <c r="B67" s="22" t="str">
+      <c r="A67" s="30"/>
+      <c r="B67" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C67" s="24">
+      <c r="C67" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="26"/>
-      <c r="B68" s="22" t="str">
+      <c r="A68" s="30"/>
+      <c r="B68" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C68" s="24">
+      <c r="C68" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="26"/>
-      <c r="B69" s="22" t="str">
+      <c r="A69" s="30"/>
+      <c r="B69" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C69" s="24">
+      <c r="C69" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="26"/>
-      <c r="B70" s="22" t="str">
+      <c r="A70" s="30"/>
+      <c r="B70" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C70" s="24">
+      <c r="C70" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="26"/>
-      <c r="B71" s="22" t="str">
+      <c r="A71" s="30"/>
+      <c r="B71" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C71" s="24">
+      <c r="C71" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="26"/>
-      <c r="B72" s="22" t="str">
+      <c r="A72" s="30"/>
+      <c r="B72" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C72" s="24">
+      <c r="C72" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="26"/>
-      <c r="B73" s="22" t="str">
+      <c r="A73" s="30"/>
+      <c r="B73" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C73" s="24">
+      <c r="C73" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="26"/>
-      <c r="B74" s="22" t="str">
+      <c r="A74" s="30"/>
+      <c r="B74" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C74" s="24">
+      <c r="C74" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="26"/>
-      <c r="B75" s="22" t="str">
+      <c r="A75" s="30"/>
+      <c r="B75" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C75" s="24">
+      <c r="C75" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="26"/>
-      <c r="B76" s="22" t="str">
+      <c r="A76" s="30"/>
+      <c r="B76" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C76" s="24">
+      <c r="C76" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="26"/>
-      <c r="B77" s="22" t="str">
+      <c r="A77" s="30"/>
+      <c r="B77" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C77" s="24">
+      <c r="C77" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="26"/>
-      <c r="B78" s="22" t="str">
+      <c r="A78" s="30"/>
+      <c r="B78" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C78" s="24">
+      <c r="C78" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="26"/>
-      <c r="B79" s="22" t="str">
+      <c r="A79" s="30"/>
+      <c r="B79" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C79" s="24">
+      <c r="C79" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="26"/>
-      <c r="B80" s="22" t="str">
+      <c r="A80" s="30"/>
+      <c r="B80" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C80" s="24">
+      <c r="C80" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="26"/>
-      <c r="B81" s="22" t="str">
+      <c r="A81" s="30"/>
+      <c r="B81" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C81" s="24">
+      <c r="C81" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="26"/>
-      <c r="B82" s="22" t="str">
+      <c r="A82" s="30"/>
+      <c r="B82" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C82" s="24">
+      <c r="C82" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="26"/>
-      <c r="B83" s="22" t="str">
+      <c r="A83" s="30"/>
+      <c r="B83" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C83" s="24">
+      <c r="C83" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="26"/>
-      <c r="B84" s="22" t="str">
+      <c r="A84" s="30"/>
+      <c r="B84" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C84" s="24">
+      <c r="C84" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="26"/>
-      <c r="B85" s="22" t="str">
+      <c r="A85" s="30"/>
+      <c r="B85" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C85" s="24">
+      <c r="C85" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="26"/>
-      <c r="B86" s="22" t="str">
+      <c r="A86" s="30"/>
+      <c r="B86" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C86" s="24">
+      <c r="C86" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="26"/>
-      <c r="B87" s="22" t="str">
+      <c r="A87" s="30"/>
+      <c r="B87" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C87" s="24">
+      <c r="C87" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="26"/>
-      <c r="B88" s="22" t="str">
+      <c r="A88" s="30"/>
+      <c r="B88" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C88" s="24">
+      <c r="C88" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="26"/>
-      <c r="B89" s="22" t="str">
+      <c r="A89" s="30"/>
+      <c r="B89" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C89" s="24">
+      <c r="C89" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="26"/>
-      <c r="B90" s="22" t="str">
+      <c r="A90" s="30"/>
+      <c r="B90" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C90" s="24">
+      <c r="C90" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="26"/>
-      <c r="B91" s="22" t="str">
+      <c r="A91" s="30"/>
+      <c r="B91" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C91" s="24">
+      <c r="C91" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="26"/>
-      <c r="B92" s="22" t="str">
+      <c r="A92" s="30"/>
+      <c r="B92" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C92" s="24">
+      <c r="C92" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="26"/>
-      <c r="B93" s="22" t="str">
+      <c r="A93" s="30"/>
+      <c r="B93" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C93" s="24">
+      <c r="C93" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="26"/>
-      <c r="B94" s="22" t="str">
+      <c r="A94" s="30"/>
+      <c r="B94" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C94" s="24">
+      <c r="C94" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="26"/>
-      <c r="B95" s="22" t="str">
+      <c r="A95" s="30"/>
+      <c r="B95" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C95" s="24">
+      <c r="C95" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="26"/>
-      <c r="B96" s="22" t="str">
+      <c r="A96" s="30"/>
+      <c r="B96" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C96" s="24">
+      <c r="C96" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="26"/>
-      <c r="B97" s="22" t="str">
+      <c r="A97" s="30"/>
+      <c r="B97" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C97" s="24">
+      <c r="C97" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="26"/>
-      <c r="B98" s="22" t="str">
+      <c r="A98" s="30"/>
+      <c r="B98" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C98" s="24">
+      <c r="C98" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="26"/>
-      <c r="B99" s="22" t="str">
+      <c r="A99" s="30"/>
+      <c r="B99" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C99" s="24">
+      <c r="C99" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="26"/>
-      <c r="B100" s="22" t="str">
+      <c r="A100" s="30"/>
+      <c r="B100" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C100" s="24">
+      <c r="C100" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="26"/>
-      <c r="B101" s="22" t="str">
+      <c r="A101" s="30"/>
+      <c r="B101" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C101" s="24">
+      <c r="C101" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="26"/>
-      <c r="B102" s="22" t="str">
+      <c r="A102" s="30"/>
+      <c r="B102" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C102" s="24">
+      <c r="C102" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="26"/>
-      <c r="B103" s="22" t="str">
+      <c r="A103" s="30"/>
+      <c r="B103" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C103" s="24">
+      <c r="C103" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="26"/>
-      <c r="B104" s="22" t="str">
+      <c r="A104" s="30"/>
+      <c r="B104" s="26" t="str">
         <f t="shared" ref="B104:B114" si="1">IF(C104&gt;0,C104,"")</f>
         <v/>
       </c>
-      <c r="C104" s="24">
+      <c r="C104" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="26"/>
-      <c r="B105" s="22" t="str">
+      <c r="A105" s="30"/>
+      <c r="B105" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C105" s="24">
+      <c r="C105" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="26"/>
-      <c r="B106" s="22" t="str">
+      <c r="A106" s="30"/>
+      <c r="B106" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C106" s="24">
+      <c r="C106" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="26"/>
-      <c r="B107" s="22" t="str">
+      <c r="A107" s="30"/>
+      <c r="B107" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C107" s="24">
+      <c r="C107" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="26"/>
-      <c r="B108" s="22" t="str">
+      <c r="A108" s="30"/>
+      <c r="B108" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C108" s="24">
+      <c r="C108" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="26"/>
-      <c r="B109" s="22" t="str">
+      <c r="A109" s="30"/>
+      <c r="B109" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C109" s="24">
+      <c r="C109" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="26"/>
-      <c r="B110" s="22" t="str">
+      <c r="A110" s="30"/>
+      <c r="B110" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C110" s="24">
+      <c r="C110" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="26"/>
-      <c r="B111" s="22" t="str">
+      <c r="A111" s="30"/>
+      <c r="B111" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C111" s="24">
+      <c r="C111" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="26"/>
-      <c r="B112" s="22" t="str">
+      <c r="A112" s="30"/>
+      <c r="B112" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C112" s="24">
+      <c r="C112" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="26"/>
-      <c r="B113" s="22" t="str">
+      <c r="A113" s="30"/>
+      <c r="B113" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C113" s="24">
+      <c r="C113" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="26"/>
-      <c r="B114" s="22" t="str">
+      <c r="A114" s="30"/>
+      <c r="B114" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C114" s="24">
+      <c r="C114" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="26"/>
-      <c r="B115" s="26"/>
-      <c r="C115" s="24"/>
+      <c r="A115" s="30"/>
+      <c r="B115" s="30"/>
+      <c r="C115" s="28"/>
     </row>
     <row r="116">
-      <c r="A116" s="26"/>
-      <c r="B116" s="26"/>
-      <c r="C116" s="24"/>
+      <c r="A116" s="30"/>
+      <c r="B116" s="30"/>
+      <c r="C116" s="28"/>
     </row>
     <row r="117">
-      <c r="A117" s="26"/>
-      <c r="B117" s="26"/>
-      <c r="C117" s="24"/>
+      <c r="A117" s="30"/>
+      <c r="B117" s="30"/>
+      <c r="C117" s="28"/>
     </row>
     <row r="118">
-      <c r="A118" s="26"/>
-      <c r="B118" s="26"/>
-      <c r="C118" s="24"/>
+      <c r="A118" s="30"/>
+      <c r="B118" s="30"/>
+      <c r="C118" s="28"/>
     </row>
     <row r="119">
-      <c r="A119" s="26"/>
-      <c r="B119" s="26"/>
-      <c r="C119" s="24"/>
+      <c r="A119" s="30"/>
+      <c r="B119" s="30"/>
+      <c r="C119" s="28"/>
     </row>
     <row r="120">
-      <c r="A120" s="26"/>
-      <c r="B120" s="26"/>
-      <c r="C120" s="24"/>
+      <c r="A120" s="30"/>
+      <c r="B120" s="30"/>
+      <c r="C120" s="28"/>
     </row>
     <row r="121">
-      <c r="A121" s="26"/>
-      <c r="B121" s="26"/>
-      <c r="C121" s="24"/>
+      <c r="A121" s="30"/>
+      <c r="B121" s="30"/>
+      <c r="C121" s="28"/>
     </row>
     <row r="122">
-      <c r="A122" s="26"/>
-      <c r="B122" s="26"/>
-      <c r="C122" s="24"/>
+      <c r="A122" s="30"/>
+      <c r="B122" s="30"/>
+      <c r="C122" s="28"/>
     </row>
     <row r="123">
-      <c r="A123" s="26"/>
-      <c r="B123" s="26"/>
-      <c r="C123" s="24"/>
+      <c r="A123" s="30"/>
+      <c r="B123" s="30"/>
+      <c r="C123" s="28"/>
     </row>
     <row r="124">
-      <c r="A124" s="26"/>
-      <c r="B124" s="26"/>
-      <c r="C124" s="24"/>
+      <c r="A124" s="30"/>
+      <c r="B124" s="30"/>
+      <c r="C124" s="28"/>
     </row>
     <row r="125">
-      <c r="A125" s="26"/>
-      <c r="B125" s="26"/>
-      <c r="C125" s="24"/>
+      <c r="A125" s="30"/>
+      <c r="B125" s="30"/>
+      <c r="C125" s="28"/>
     </row>
     <row r="126">
-      <c r="A126" s="26"/>
-      <c r="B126" s="26"/>
-      <c r="C126" s="24"/>
+      <c r="A126" s="30"/>
+      <c r="B126" s="30"/>
+      <c r="C126" s="28"/>
     </row>
     <row r="127">
-      <c r="A127" s="26"/>
-      <c r="B127" s="26"/>
-      <c r="C127" s="24"/>
+      <c r="A127" s="30"/>
+      <c r="B127" s="30"/>
+      <c r="C127" s="28"/>
     </row>
     <row r="128">
-      <c r="A128" s="26"/>
-      <c r="B128" s="26"/>
-      <c r="C128" s="24"/>
+      <c r="A128" s="30"/>
+      <c r="B128" s="30"/>
+      <c r="C128" s="28"/>
     </row>
     <row r="129">
-      <c r="A129" s="26"/>
-      <c r="B129" s="26"/>
-      <c r="C129" s="24"/>
+      <c r="A129" s="30"/>
+      <c r="B129" s="30"/>
+      <c r="C129" s="28"/>
     </row>
     <row r="130">
-      <c r="A130" s="26"/>
-      <c r="B130" s="26"/>
-      <c r="C130" s="24"/>
+      <c r="A130" s="30"/>
+      <c r="B130" s="30"/>
+      <c r="C130" s="28"/>
     </row>
     <row r="131">
-      <c r="A131" s="26"/>
-      <c r="B131" s="26"/>
-      <c r="C131" s="24"/>
+      <c r="A131" s="30"/>
+      <c r="B131" s="30"/>
+      <c r="C131" s="28"/>
     </row>
     <row r="132">
-      <c r="A132" s="26"/>
-      <c r="B132" s="26"/>
-      <c r="C132" s="24"/>
+      <c r="A132" s="30"/>
+      <c r="B132" s="30"/>
+      <c r="C132" s="28"/>
     </row>
     <row r="133">
-      <c r="A133" s="26"/>
-      <c r="B133" s="26"/>
-      <c r="C133" s="24"/>
+      <c r="A133" s="30"/>
+      <c r="B133" s="30"/>
+      <c r="C133" s="28"/>
     </row>
     <row r="134">
-      <c r="A134" s="26"/>
-      <c r="B134" s="26"/>
-      <c r="C134" s="24"/>
+      <c r="A134" s="30"/>
+      <c r="B134" s="30"/>
+      <c r="C134" s="28"/>
     </row>
     <row r="135">
-      <c r="A135" s="26"/>
-      <c r="B135" s="26"/>
-      <c r="C135" s="24"/>
+      <c r="A135" s="30"/>
+      <c r="B135" s="30"/>
+      <c r="C135" s="28"/>
     </row>
     <row r="136">
-      <c r="A136" s="26"/>
-      <c r="B136" s="26"/>
-      <c r="C136" s="24"/>
+      <c r="A136" s="30"/>
+      <c r="B136" s="30"/>
+      <c r="C136" s="28"/>
     </row>
     <row r="137">
-      <c r="A137" s="26"/>
-      <c r="B137" s="26"/>
-      <c r="C137" s="24"/>
+      <c r="A137" s="30"/>
+      <c r="B137" s="30"/>
+      <c r="C137" s="28"/>
     </row>
     <row r="138">
-      <c r="A138" s="26"/>
-      <c r="B138" s="26"/>
-      <c r="C138" s="24"/>
+      <c r="A138" s="30"/>
+      <c r="B138" s="30"/>
+      <c r="C138" s="28"/>
     </row>
     <row r="139">
-      <c r="A139" s="26"/>
-      <c r="B139" s="26"/>
-      <c r="C139" s="24"/>
+      <c r="A139" s="30"/>
+      <c r="B139" s="30"/>
+      <c r="C139" s="28"/>
     </row>
     <row r="140">
-      <c r="A140" s="26"/>
-      <c r="B140" s="26"/>
-      <c r="C140" s="24"/>
+      <c r="A140" s="30"/>
+      <c r="B140" s="30"/>
+      <c r="C140" s="28"/>
     </row>
     <row r="141">
-      <c r="A141" s="26"/>
-      <c r="B141" s="26"/>
-      <c r="C141" s="24"/>
+      <c r="A141" s="30"/>
+      <c r="B141" s="30"/>
+      <c r="C141" s="28"/>
     </row>
     <row r="142">
-      <c r="A142" s="26"/>
-      <c r="B142" s="26"/>
-      <c r="C142" s="24"/>
+      <c r="A142" s="30"/>
+      <c r="B142" s="30"/>
+      <c r="C142" s="28"/>
     </row>
     <row r="143">
-      <c r="A143" s="26"/>
-      <c r="B143" s="26"/>
-      <c r="C143" s="24"/>
+      <c r="A143" s="30"/>
+      <c r="B143" s="30"/>
+      <c r="C143" s="28"/>
     </row>
     <row r="144">
-      <c r="A144" s="26"/>
-      <c r="B144" s="26"/>
-      <c r="C144" s="24"/>
+      <c r="A144" s="30"/>
+      <c r="B144" s="30"/>
+      <c r="C144" s="28"/>
     </row>
     <row r="145">
-      <c r="A145" s="26"/>
-      <c r="B145" s="26"/>
-      <c r="C145" s="24"/>
+      <c r="A145" s="30"/>
+      <c r="B145" s="30"/>
+      <c r="C145" s="28"/>
     </row>
     <row r="146">
-      <c r="A146" s="26"/>
-      <c r="B146" s="26"/>
-      <c r="C146" s="24"/>
+      <c r="A146" s="30"/>
+      <c r="B146" s="30"/>
+      <c r="C146" s="28"/>
     </row>
     <row r="147">
-      <c r="A147" s="26"/>
-      <c r="B147" s="26"/>
-      <c r="C147" s="24"/>
+      <c r="A147" s="30"/>
+      <c r="B147" s="30"/>
+      <c r="C147" s="28"/>
     </row>
     <row r="148">
-      <c r="A148" s="26"/>
-      <c r="B148" s="26"/>
-      <c r="C148" s="24"/>
+      <c r="A148" s="30"/>
+      <c r="B148" s="30"/>
+      <c r="C148" s="28"/>
     </row>
     <row r="149">
-      <c r="A149" s="26"/>
-      <c r="B149" s="26"/>
-      <c r="C149" s="24"/>
+      <c r="A149" s="30"/>
+      <c r="B149" s="30"/>
+      <c r="C149" s="28"/>
     </row>
     <row r="150">
-      <c r="A150" s="26"/>
-      <c r="B150" s="26"/>
-      <c r="C150" s="24"/>
+      <c r="A150" s="30"/>
+      <c r="B150" s="30"/>
+      <c r="C150" s="28"/>
     </row>
     <row r="151">
-      <c r="A151" s="26"/>
-      <c r="B151" s="26"/>
-      <c r="C151" s="24"/>
+      <c r="A151" s="30"/>
+      <c r="B151" s="30"/>
+      <c r="C151" s="28"/>
     </row>
     <row r="152">
-      <c r="A152" s="26"/>
-      <c r="B152" s="26"/>
-      <c r="C152" s="24"/>
+      <c r="A152" s="30"/>
+      <c r="B152" s="30"/>
+      <c r="C152" s="28"/>
     </row>
     <row r="153">
-      <c r="A153" s="26"/>
-      <c r="B153" s="26"/>
-      <c r="C153" s="24"/>
+      <c r="A153" s="30"/>
+      <c r="B153" s="30"/>
+      <c r="C153" s="28"/>
     </row>
     <row r="154">
-      <c r="A154" s="26"/>
-      <c r="B154" s="26"/>
-      <c r="C154" s="24"/>
+      <c r="A154" s="30"/>
+      <c r="B154" s="30"/>
+      <c r="C154" s="28"/>
     </row>
     <row r="155">
-      <c r="A155" s="26"/>
-      <c r="B155" s="26"/>
-      <c r="C155" s="24"/>
+      <c r="A155" s="30"/>
+      <c r="B155" s="30"/>
+      <c r="C155" s="28"/>
     </row>
     <row r="156">
-      <c r="A156" s="26"/>
-      <c r="B156" s="26"/>
-      <c r="C156" s="24"/>
+      <c r="A156" s="30"/>
+      <c r="B156" s="30"/>
+      <c r="C156" s="28"/>
     </row>
     <row r="157">
-      <c r="A157" s="26"/>
-      <c r="B157" s="26"/>
-      <c r="C157" s="24"/>
+      <c r="A157" s="30"/>
+      <c r="B157" s="30"/>
+      <c r="C157" s="28"/>
     </row>
     <row r="158">
-      <c r="A158" s="26"/>
-      <c r="B158" s="26"/>
-      <c r="C158" s="24"/>
+      <c r="A158" s="30"/>
+      <c r="B158" s="30"/>
+      <c r="C158" s="28"/>
     </row>
     <row r="159">
-      <c r="A159" s="26"/>
-      <c r="B159" s="26"/>
+      <c r="A159" s="30"/>
+      <c r="B159" s="30"/>
     </row>
     <row r="160">
-      <c r="A160" s="26"/>
-      <c r="B160" s="26"/>
+      <c r="A160" s="30"/>
+      <c r="B160" s="30"/>
     </row>
     <row r="161">
-      <c r="A161" s="26"/>
-      <c r="B161" s="26"/>
+      <c r="A161" s="30"/>
+      <c r="B161" s="30"/>
     </row>
     <row r="162">
-      <c r="A162" s="26"/>
-      <c r="B162" s="26"/>
+      <c r="A162" s="30"/>
+      <c r="B162" s="30"/>
     </row>
     <row r="163">
-      <c r="A163" s="26"/>
-      <c r="B163" s="26"/>
+      <c r="A163" s="30"/>
+      <c r="B163" s="30"/>
     </row>
     <row r="164">
-      <c r="A164" s="26"/>
-      <c r="B164" s="26"/>
+      <c r="A164" s="30"/>
+      <c r="B164" s="30"/>
     </row>
     <row r="165">
-      <c r="A165" s="26"/>
-      <c r="B165" s="26"/>
+      <c r="A165" s="30"/>
+      <c r="B165" s="30"/>
     </row>
     <row r="166">
-      <c r="A166" s="26"/>
-      <c r="B166" s="26"/>
+      <c r="A166" s="30"/>
+      <c r="B166" s="30"/>
     </row>
     <row r="167">
-      <c r="A167" s="26"/>
-      <c r="B167" s="26"/>
+      <c r="A167" s="30"/>
+      <c r="B167" s="30"/>
     </row>
     <row r="168">
-      <c r="A168" s="26"/>
-      <c r="B168" s="26"/>
+      <c r="A168" s="30"/>
+      <c r="B168" s="30"/>
     </row>
     <row r="169">
-      <c r="A169" s="26"/>
-      <c r="B169" s="26"/>
+      <c r="A169" s="30"/>
+      <c r="B169" s="30"/>
     </row>
     <row r="170">
-      <c r="A170" s="26"/>
-      <c r="B170" s="26"/>
+      <c r="A170" s="30"/>
+      <c r="B170" s="30"/>
     </row>
     <row r="171">
-      <c r="A171" s="26"/>
-      <c r="B171" s="26"/>
+      <c r="A171" s="30"/>
+      <c r="B171" s="30"/>
     </row>
     <row r="172">
-      <c r="A172" s="26"/>
-      <c r="B172" s="26"/>
+      <c r="A172" s="30"/>
+      <c r="B172" s="30"/>
     </row>
     <row r="173">
-      <c r="A173" s="26"/>
-      <c r="B173" s="26"/>
+      <c r="A173" s="30"/>
+      <c r="B173" s="30"/>
     </row>
     <row r="174">
-      <c r="A174" s="26"/>
-      <c r="B174" s="26"/>
+      <c r="A174" s="30"/>
+      <c r="B174" s="30"/>
     </row>
     <row r="175">
-      <c r="A175" s="26"/>
-      <c r="B175" s="26"/>
+      <c r="A175" s="30"/>
+      <c r="B175" s="30"/>
     </row>
     <row r="176">
-      <c r="A176" s="26"/>
-      <c r="B176" s="26"/>
+      <c r="A176" s="30"/>
+      <c r="B176" s="30"/>
     </row>
     <row r="177">
-      <c r="A177" s="26"/>
-      <c r="B177" s="26"/>
+      <c r="A177" s="30"/>
+      <c r="B177" s="30"/>
     </row>
     <row r="178">
-      <c r="A178" s="26"/>
-      <c r="B178" s="26"/>
+      <c r="A178" s="30"/>
+      <c r="B178" s="30"/>
     </row>
     <row r="179">
-      <c r="A179" s="26"/>
-      <c r="B179" s="26"/>
+      <c r="A179" s="30"/>
+      <c r="B179" s="30"/>
     </row>
     <row r="180">
-      <c r="A180" s="26"/>
-      <c r="B180" s="26"/>
+      <c r="A180" s="30"/>
+      <c r="B180" s="30"/>
     </row>
     <row r="181">
-      <c r="A181" s="26"/>
-      <c r="B181" s="26"/>
+      <c r="A181" s="30"/>
+      <c r="B181" s="30"/>
     </row>
     <row r="182">
-      <c r="A182" s="26"/>
-      <c r="B182" s="26"/>
+      <c r="A182" s="30"/>
+      <c r="B182" s="30"/>
     </row>
     <row r="183">
-      <c r="A183" s="26"/>
-      <c r="B183" s="26"/>
+      <c r="A183" s="30"/>
+      <c r="B183" s="30"/>
     </row>
     <row r="184">
-      <c r="A184" s="26"/>
-      <c r="B184" s="26"/>
+      <c r="A184" s="30"/>
+      <c r="B184" s="30"/>
     </row>
     <row r="185">
-      <c r="A185" s="26"/>
-      <c r="B185" s="26"/>
+      <c r="A185" s="30"/>
+      <c r="B185" s="30"/>
     </row>
     <row r="186">
-      <c r="A186" s="26"/>
-      <c r="B186" s="26"/>
+      <c r="A186" s="30"/>
+      <c r="B186" s="30"/>
     </row>
     <row r="187">
-      <c r="A187" s="26"/>
-      <c r="B187" s="26"/>
+      <c r="A187" s="30"/>
+      <c r="B187" s="30"/>
     </row>
     <row r="188">
-      <c r="A188" s="26"/>
-      <c r="B188" s="26"/>
+      <c r="A188" s="30"/>
+      <c r="B188" s="30"/>
     </row>
     <row r="189">
-      <c r="A189" s="26"/>
-      <c r="B189" s="26"/>
+      <c r="A189" s="30"/>
+      <c r="B189" s="30"/>
     </row>
     <row r="190">
-      <c r="A190" s="26"/>
-      <c r="B190" s="26"/>
+      <c r="A190" s="30"/>
+      <c r="B190" s="30"/>
     </row>
     <row r="191">
-      <c r="A191" s="26"/>
-      <c r="B191" s="26"/>
+      <c r="A191" s="30"/>
+      <c r="B191" s="30"/>
     </row>
     <row r="192">
-      <c r="A192" s="26"/>
-      <c r="B192" s="26"/>
+      <c r="A192" s="30"/>
+      <c r="B192" s="30"/>
     </row>
     <row r="193">
-      <c r="A193" s="26"/>
-      <c r="B193" s="26"/>
+      <c r="A193" s="30"/>
+      <c r="B193" s="30"/>
     </row>
     <row r="194">
-      <c r="A194" s="26"/>
-      <c r="B194" s="26"/>
+      <c r="A194" s="30"/>
+      <c r="B194" s="30"/>
     </row>
     <row r="195">
-      <c r="A195" s="26"/>
-      <c r="B195" s="26"/>
+      <c r="A195" s="30"/>
+      <c r="B195" s="30"/>
     </row>
     <row r="196">
-      <c r="A196" s="26"/>
-      <c r="B196" s="26"/>
+      <c r="A196" s="30"/>
+      <c r="B196" s="30"/>
     </row>
     <row r="197">
-      <c r="A197" s="26"/>
-      <c r="B197" s="26"/>
+      <c r="A197" s="30"/>
+      <c r="B197" s="30"/>
     </row>
     <row r="198">
-      <c r="A198" s="26"/>
-      <c r="B198" s="26"/>
+      <c r="A198" s="30"/>
+      <c r="B198" s="30"/>
     </row>
     <row r="199">
-      <c r="A199" s="26"/>
-      <c r="B199" s="26"/>
+      <c r="A199" s="30"/>
+      <c r="B199" s="30"/>
     </row>
     <row r="200">
-      <c r="A200" s="26"/>
-      <c r="B200" s="26"/>
+      <c r="A200" s="30"/>
+      <c r="B200" s="30"/>
     </row>
     <row r="201">
-      <c r="A201" s="26"/>
-      <c r="B201" s="26"/>
+      <c r="A201" s="30"/>
+      <c r="B201" s="30"/>
     </row>
     <row r="202">
-      <c r="A202" s="26"/>
-      <c r="B202" s="26"/>
+      <c r="A202" s="30"/>
+      <c r="B202" s="30"/>
     </row>
     <row r="203">
-      <c r="A203" s="26"/>
-      <c r="B203" s="26"/>
+      <c r="A203" s="30"/>
+      <c r="B203" s="30"/>
     </row>
     <row r="204">
-      <c r="A204" s="26"/>
-      <c r="B204" s="26"/>
+      <c r="A204" s="30"/>
+      <c r="B204" s="30"/>
     </row>
     <row r="205">
-      <c r="A205" s="26"/>
-      <c r="B205" s="26"/>
+      <c r="A205" s="30"/>
+      <c r="B205" s="30"/>
     </row>
     <row r="206">
-      <c r="A206" s="26"/>
-      <c r="B206" s="26"/>
+      <c r="A206" s="30"/>
+      <c r="B206" s="30"/>
     </row>
     <row r="207">
-      <c r="A207" s="26"/>
-      <c r="B207" s="26"/>
+      <c r="A207" s="30"/>
+      <c r="B207" s="30"/>
     </row>
     <row r="208">
-      <c r="A208" s="26"/>
-      <c r="B208" s="26"/>
+      <c r="A208" s="30"/>
+      <c r="B208" s="30"/>
     </row>
     <row r="209">
-      <c r="A209" s="26"/>
-      <c r="B209" s="26"/>
+      <c r="A209" s="30"/>
+      <c r="B209" s="30"/>
     </row>
     <row r="210">
-      <c r="A210" s="26"/>
-      <c r="B210" s="26"/>
+      <c r="A210" s="30"/>
+      <c r="B210" s="30"/>
     </row>
     <row r="211">
-      <c r="A211" s="26"/>
-      <c r="B211" s="26"/>
+      <c r="A211" s="30"/>
+      <c r="B211" s="30"/>
     </row>
     <row r="212">
-      <c r="A212" s="26"/>
-      <c r="B212" s="26"/>
+      <c r="A212" s="30"/>
+      <c r="B212" s="30"/>
     </row>
     <row r="213">
-      <c r="A213" s="26"/>
-      <c r="B213" s="26"/>
+      <c r="A213" s="30"/>
+      <c r="B213" s="30"/>
     </row>
     <row r="214">
-      <c r="A214" s="26"/>
-      <c r="B214" s="26"/>
+      <c r="A214" s="30"/>
+      <c r="B214" s="30"/>
     </row>
     <row r="215">
-      <c r="A215" s="26"/>
-      <c r="B215" s="26"/>
+      <c r="A215" s="30"/>
+      <c r="B215" s="30"/>
     </row>
     <row r="216">
-      <c r="A216" s="26"/>
-      <c r="B216" s="26"/>
+      <c r="A216" s="30"/>
+      <c r="B216" s="30"/>
     </row>
     <row r="217">
-      <c r="A217" s="26"/>
-      <c r="B217" s="26"/>
+      <c r="A217" s="30"/>
+      <c r="B217" s="30"/>
     </row>
     <row r="218">
-      <c r="A218" s="26"/>
-      <c r="B218" s="26"/>
+      <c r="A218" s="30"/>
+      <c r="B218" s="30"/>
     </row>
     <row r="219">
-      <c r="A219" s="26"/>
-      <c r="B219" s="26"/>
+      <c r="A219" s="30"/>
+      <c r="B219" s="30"/>
     </row>
     <row r="220">
-      <c r="A220" s="26"/>
-      <c r="B220" s="26"/>
+      <c r="A220" s="30"/>
+      <c r="B220" s="30"/>
     </row>
     <row r="221">
-      <c r="A221" s="26"/>
-      <c r="B221" s="26"/>
+      <c r="A221" s="30"/>
+      <c r="B221" s="30"/>
     </row>
     <row r="222">
-      <c r="A222" s="26"/>
-      <c r="B222" s="26"/>
+      <c r="A222" s="30"/>
+      <c r="B222" s="30"/>
     </row>
     <row r="223">
-      <c r="A223" s="26"/>
-      <c r="B223" s="26"/>
+      <c r="A223" s="30"/>
+      <c r="B223" s="30"/>
     </row>
     <row r="224">
-      <c r="A224" s="26"/>
-      <c r="B224" s="26"/>
+      <c r="A224" s="30"/>
+      <c r="B224" s="30"/>
     </row>
     <row r="225">
-      <c r="A225" s="26"/>
-      <c r="B225" s="26"/>
+      <c r="A225" s="30"/>
+      <c r="B225" s="30"/>
     </row>
     <row r="226">
-      <c r="A226" s="26"/>
-      <c r="B226" s="26"/>
+      <c r="A226" s="30"/>
+      <c r="B226" s="30"/>
     </row>
     <row r="227">
-      <c r="A227" s="26"/>
-      <c r="B227" s="26"/>
+      <c r="A227" s="30"/>
+      <c r="B227" s="30"/>
     </row>
     <row r="228">
-      <c r="A228" s="26"/>
-      <c r="B228" s="26"/>
+      <c r="A228" s="30"/>
+      <c r="B228" s="30"/>
     </row>
     <row r="229">
-      <c r="A229" s="26"/>
-      <c r="B229" s="26"/>
+      <c r="A229" s="30"/>
+      <c r="B229" s="30"/>
     </row>
     <row r="230">
-      <c r="A230" s="26"/>
-      <c r="B230" s="26"/>
+      <c r="A230" s="30"/>
+      <c r="B230" s="30"/>
     </row>
     <row r="231">
-      <c r="A231" s="26"/>
-      <c r="B231" s="26"/>
+      <c r="A231" s="30"/>
+      <c r="B231" s="30"/>
     </row>
     <row r="232">
-      <c r="A232" s="26"/>
-      <c r="B232" s="26"/>
+      <c r="A232" s="30"/>
+      <c r="B232" s="30"/>
     </row>
     <row r="233">
-      <c r="A233" s="26"/>
-      <c r="B233" s="26"/>
+      <c r="A233" s="30"/>
+      <c r="B233" s="30"/>
     </row>
     <row r="234">
-      <c r="A234" s="26"/>
-      <c r="B234" s="26"/>
+      <c r="A234" s="30"/>
+      <c r="B234" s="30"/>
     </row>
     <row r="235">
-      <c r="A235" s="26"/>
-      <c r="B235" s="26"/>
+      <c r="A235" s="30"/>
+      <c r="B235" s="30"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -6859,2034 +6910,2034 @@
     <col customWidth="1" min="2" max="2" width="4.33203125"/>
     <col bestFit="1" min="3" max="3" width="35.77734375"/>
     <col customWidth="1" min="4" max="11" width="3.44140625"/>
-    <col customWidth="1" min="12" max="12" style="27" width="6"/>
+    <col customWidth="1" min="12" max="12" style="31" width="6"/>
     <col customWidth="1" min="13" max="22" width="3.44140625"/>
-    <col customWidth="1" min="23" max="23" style="27" width="6"/>
+    <col customWidth="1" min="23" max="23" style="31" width="6"/>
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
-    <col customWidth="1" min="30" max="30" style="27" width="6"/>
+    <col customWidth="1" min="30" max="30" style="31" width="6"/>
     <col customWidth="1" min="31" max="39" width="3.44140625"/>
     <col bestFit="1" customWidth="1" min="40" max="40" width="13.88671875"/>
     <col customWidth="1" min="41" max="47" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="28" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="B1" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="31" t="s">
+    <row r="1" s="32" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="B1" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="F1" s="32" t="s">
+      <c r="E1" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="31" t="s">
+      <c r="H1" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="L1" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="M1" s="31" t="s">
-        <v>79</v>
-      </c>
-      <c r="N1" s="33" t="s">
+      <c r="K1" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1" s="39" t="s">
+        <v>81</v>
+      </c>
+      <c r="M1" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="N1" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="34" t="s">
+      <c r="O1" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="P1" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q1" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="P1" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q1" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="R1" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="S1" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="T1" s="31" t="s">
-        <v>83</v>
-      </c>
-      <c r="U1" s="31" t="s">
+      <c r="R1" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="V1" s="33" t="s">
+      <c r="S1" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="W1" s="36" t="s">
+      <c r="T1" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="X1" s="31" t="s">
+      <c r="U1" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="Y1" s="31" t="s">
+      <c r="V1" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="Z1" s="33" t="s">
+      <c r="W1" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="AA1" s="37" t="s">
+      <c r="X1" s="35" t="s">
         <v>90</v>
       </c>
-      <c r="AB1" s="38" t="s">
+      <c r="Y1" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="AC1" s="38" t="s">
+      <c r="Z1" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="AD1" s="35" t="s">
+      <c r="AA1" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="AE1" s="39" t="s">
+      <c r="AB1" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="AF1" s="40" t="s">
+      <c r="AC1" s="42" t="s">
         <v>95</v>
       </c>
-      <c r="AG1" s="41" t="s">
+      <c r="AD1" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="AH1" s="41" t="s">
+      <c r="AE1" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="AI1" s="41" t="s">
+      <c r="AF1" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="AJ1" s="41" t="s">
+      <c r="AG1" s="45" t="s">
         <v>99</v>
       </c>
-      <c r="AK1" s="38" t="s">
+      <c r="AH1" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="AL1" s="42"/>
-      <c r="AM1" s="42"/>
-      <c r="AN1" s="42"/>
-      <c r="AO1" s="42"/>
-      <c r="AP1" s="42"/>
-      <c r="AQ1" s="42"/>
-      <c r="AR1" s="42"/>
-      <c r="AS1" s="42"/>
-      <c r="AT1" s="42"/>
-      <c r="AU1" s="42"/>
+      <c r="AI1" s="45" t="s">
+        <v>101</v>
+      </c>
+      <c r="AJ1" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="AK1" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL1" s="46"/>
+      <c r="AM1" s="46"/>
+      <c r="AN1" s="46"/>
+      <c r="AO1" s="46"/>
+      <c r="AP1" s="46"/>
+      <c r="AQ1" s="46"/>
+      <c r="AR1" s="46"/>
+      <c r="AS1" s="46"/>
+      <c r="AT1" s="46"/>
+      <c r="AU1" s="46"/>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45"/>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
-      <c r="V2" s="50"/>
-      <c r="W2" s="52"/>
-      <c r="X2" s="45"/>
-      <c r="Y2" s="45"/>
-      <c r="Z2" s="50"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="45"/>
-      <c r="AC2" s="45"/>
-      <c r="AD2" s="49"/>
-      <c r="AE2" s="50"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="45"/>
-      <c r="AH2" s="45"/>
-      <c r="AI2" s="45"/>
-      <c r="AJ2" s="45"/>
-      <c r="AK2" s="45"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
+      <c r="V2" s="54"/>
+      <c r="W2" s="56"/>
+      <c r="X2" s="49"/>
+      <c r="Y2" s="49"/>
+      <c r="Z2" s="54"/>
+      <c r="AA2" s="55"/>
+      <c r="AB2" s="49"/>
+      <c r="AC2" s="49"/>
+      <c r="AD2" s="53"/>
+      <c r="AE2" s="54"/>
+      <c r="AF2" s="55"/>
+      <c r="AG2" s="49"/>
+      <c r="AH2" s="49"/>
+      <c r="AI2" s="49"/>
+      <c r="AJ2" s="49"/>
+      <c r="AK2" s="49"/>
     </row>
     <row r="3" ht="12" customHeight="1">
-      <c r="B3" s="43"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="49"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="51"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45"/>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
-      <c r="V3" s="50"/>
-      <c r="W3" s="52"/>
-      <c r="X3" s="45"/>
-      <c r="Y3" s="45"/>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="51"/>
-      <c r="AB3" s="45"/>
-      <c r="AC3" s="45"/>
-      <c r="AD3" s="49"/>
-      <c r="AE3" s="50"/>
-      <c r="AF3" s="51"/>
-      <c r="AG3" s="45"/>
-      <c r="AH3" s="45"/>
-      <c r="AI3" s="45"/>
-      <c r="AJ3" s="45"/>
-      <c r="AK3" s="45"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="55"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="49"/>
+      <c r="T3" s="49"/>
+      <c r="U3" s="49"/>
+      <c r="V3" s="54"/>
+      <c r="W3" s="56"/>
+      <c r="X3" s="49"/>
+      <c r="Y3" s="49"/>
+      <c r="Z3" s="54"/>
+      <c r="AA3" s="55"/>
+      <c r="AB3" s="49"/>
+      <c r="AC3" s="49"/>
+      <c r="AD3" s="53"/>
+      <c r="AE3" s="54"/>
+      <c r="AF3" s="55"/>
+      <c r="AG3" s="49"/>
+      <c r="AH3" s="49"/>
+      <c r="AI3" s="49"/>
+      <c r="AJ3" s="49"/>
+      <c r="AK3" s="49"/>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="43"/>
-      <c r="C4" s="44" t="s">
-        <v>101</v>
-      </c>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="49"/>
-      <c r="M4" s="45"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="51"/>
-      <c r="P4" s="45"/>
-      <c r="Q4" s="45"/>
-      <c r="R4" s="45"/>
-      <c r="S4" s="45"/>
-      <c r="T4" s="45"/>
-      <c r="U4" s="45"/>
-      <c r="V4" s="50"/>
-      <c r="W4" s="52"/>
-      <c r="X4" s="45"/>
-      <c r="Y4" s="45"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="51"/>
-      <c r="AB4" s="45"/>
-      <c r="AC4" s="45"/>
-      <c r="AD4" s="49"/>
-      <c r="AE4" s="50"/>
-      <c r="AF4" s="51"/>
-      <c r="AG4" s="45"/>
-      <c r="AH4" s="45"/>
-      <c r="AI4" s="45"/>
-      <c r="AJ4" s="45"/>
-      <c r="AK4" s="45"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="49"/>
+      <c r="Q4" s="49"/>
+      <c r="R4" s="49"/>
+      <c r="S4" s="49"/>
+      <c r="T4" s="49"/>
+      <c r="U4" s="49"/>
+      <c r="V4" s="54"/>
+      <c r="W4" s="56"/>
+      <c r="X4" s="49"/>
+      <c r="Y4" s="49"/>
+      <c r="Z4" s="54"/>
+      <c r="AA4" s="55"/>
+      <c r="AB4" s="49"/>
+      <c r="AC4" s="49"/>
+      <c r="AD4" s="53"/>
+      <c r="AE4" s="54"/>
+      <c r="AF4" s="55"/>
+      <c r="AG4" s="49"/>
+      <c r="AH4" s="49"/>
+      <c r="AI4" s="49"/>
+      <c r="AJ4" s="49"/>
+      <c r="AK4" s="49"/>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="43"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="51"/>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="45"/>
-      <c r="R5" s="45"/>
-      <c r="S5" s="45"/>
-      <c r="T5" s="45"/>
-      <c r="U5" s="45"/>
-      <c r="V5" s="50"/>
-      <c r="W5" s="52"/>
-      <c r="X5" s="45"/>
-      <c r="Y5" s="45"/>
-      <c r="Z5" s="50"/>
-      <c r="AA5" s="51"/>
-      <c r="AB5" s="45"/>
-      <c r="AC5" s="45"/>
-      <c r="AD5" s="49"/>
-      <c r="AE5" s="50"/>
-      <c r="AF5" s="51"/>
-      <c r="AG5" s="45"/>
-      <c r="AH5" s="45"/>
-      <c r="AI5" s="45"/>
-      <c r="AJ5" s="45"/>
-      <c r="AK5" s="45"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="54"/>
+      <c r="W5" s="56"/>
+      <c r="X5" s="49"/>
+      <c r="Y5" s="49"/>
+      <c r="Z5" s="54"/>
+      <c r="AA5" s="55"/>
+      <c r="AB5" s="49"/>
+      <c r="AC5" s="49"/>
+      <c r="AD5" s="53"/>
+      <c r="AE5" s="54"/>
+      <c r="AF5" s="55"/>
+      <c r="AG5" s="49"/>
+      <c r="AH5" s="49"/>
+      <c r="AI5" s="49"/>
+      <c r="AJ5" s="49"/>
+      <c r="AK5" s="49"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="43"/>
-      <c r="C6" s="44" t="s">
+      <c r="B6" s="47"/>
+      <c r="C6" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="45"/>
-      <c r="N6" s="50"/>
-      <c r="O6" s="51"/>
-      <c r="P6" s="45"/>
-      <c r="Q6" s="45"/>
-      <c r="R6" s="45"/>
-      <c r="S6" s="45"/>
-      <c r="T6" s="45"/>
-      <c r="U6" s="45"/>
-      <c r="V6" s="50"/>
-      <c r="W6" s="52"/>
-      <c r="X6" s="45"/>
-      <c r="Y6" s="45"/>
-      <c r="Z6" s="50"/>
-      <c r="AA6" s="51"/>
-      <c r="AB6" s="45"/>
-      <c r="AC6" s="45"/>
-      <c r="AD6" s="49"/>
-      <c r="AE6" s="47"/>
-      <c r="AF6" s="48"/>
-      <c r="AG6" s="59"/>
-      <c r="AH6" s="59"/>
-      <c r="AI6" s="59"/>
-      <c r="AJ6" s="59"/>
-      <c r="AK6" s="59"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="49"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="54"/>
+      <c r="O6" s="55"/>
+      <c r="P6" s="49"/>
+      <c r="Q6" s="49"/>
+      <c r="R6" s="49"/>
+      <c r="S6" s="49"/>
+      <c r="T6" s="49"/>
+      <c r="U6" s="49"/>
+      <c r="V6" s="54"/>
+      <c r="W6" s="56"/>
+      <c r="X6" s="49"/>
+      <c r="Y6" s="49"/>
+      <c r="Z6" s="54"/>
+      <c r="AA6" s="55"/>
+      <c r="AB6" s="49"/>
+      <c r="AC6" s="49"/>
+      <c r="AD6" s="53"/>
+      <c r="AE6" s="51"/>
+      <c r="AF6" s="52"/>
+      <c r="AG6" s="63"/>
+      <c r="AH6" s="63"/>
+      <c r="AI6" s="63"/>
+      <c r="AJ6" s="63"/>
+      <c r="AK6" s="63"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="43"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="49"/>
-      <c r="M7" s="45"/>
-      <c r="N7" s="50"/>
-      <c r="O7" s="57"/>
-      <c r="P7" s="45"/>
-      <c r="Q7" s="58"/>
-      <c r="R7" s="45"/>
-      <c r="S7" s="45"/>
-      <c r="T7" s="45"/>
-      <c r="U7" s="45"/>
-      <c r="V7" s="50"/>
-      <c r="W7" s="52"/>
-      <c r="X7" s="45"/>
-      <c r="Y7" s="45"/>
-      <c r="Z7" s="50"/>
-      <c r="AA7" s="51"/>
-      <c r="AB7" s="45"/>
-      <c r="AC7" s="45"/>
-      <c r="AD7" s="49"/>
-      <c r="AE7" s="50"/>
-      <c r="AF7" s="51"/>
-      <c r="AG7" s="45"/>
-      <c r="AH7" s="45"/>
-      <c r="AI7" s="45"/>
-      <c r="AJ7" s="45"/>
-      <c r="AK7" s="45"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="53"/>
+      <c r="M7" s="49"/>
+      <c r="N7" s="54"/>
+      <c r="O7" s="61"/>
+      <c r="P7" s="49"/>
+      <c r="Q7" s="62"/>
+      <c r="R7" s="49"/>
+      <c r="S7" s="49"/>
+      <c r="T7" s="49"/>
+      <c r="U7" s="49"/>
+      <c r="V7" s="54"/>
+      <c r="W7" s="56"/>
+      <c r="X7" s="49"/>
+      <c r="Y7" s="49"/>
+      <c r="Z7" s="54"/>
+      <c r="AA7" s="55"/>
+      <c r="AB7" s="49"/>
+      <c r="AC7" s="49"/>
+      <c r="AD7" s="53"/>
+      <c r="AE7" s="54"/>
+      <c r="AF7" s="55"/>
+      <c r="AG7" s="49"/>
+      <c r="AH7" s="49"/>
+      <c r="AI7" s="49"/>
+      <c r="AJ7" s="49"/>
+      <c r="AK7" s="49"/>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="43"/>
-      <c r="C8" s="44" t="s">
-        <v>102</v>
-      </c>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="59"/>
-      <c r="K8" s="59"/>
-      <c r="L8" s="49"/>
-      <c r="M8" s="59"/>
-      <c r="N8" s="47"/>
-      <c r="O8" s="48"/>
-      <c r="P8" s="59"/>
-      <c r="Q8" s="59"/>
-      <c r="R8" s="59"/>
-      <c r="S8" s="59"/>
-      <c r="T8" s="59"/>
-      <c r="U8" s="59"/>
-      <c r="V8" s="47"/>
-      <c r="W8" s="52"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="59"/>
-      <c r="Z8" s="47"/>
-      <c r="AA8" s="48"/>
-      <c r="AB8" s="59"/>
-      <c r="AC8" s="59"/>
-      <c r="AD8" s="49"/>
-      <c r="AE8" s="47"/>
-      <c r="AF8" s="48"/>
-      <c r="AG8" s="59"/>
-      <c r="AH8" s="59"/>
-      <c r="AI8" s="59"/>
-      <c r="AJ8" s="59"/>
-      <c r="AK8" s="59"/>
+      <c r="B8" s="47"/>
+      <c r="C8" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="63"/>
+      <c r="K8" s="63"/>
+      <c r="L8" s="53"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="51"/>
+      <c r="O8" s="52"/>
+      <c r="P8" s="63"/>
+      <c r="Q8" s="63"/>
+      <c r="R8" s="63"/>
+      <c r="S8" s="63"/>
+      <c r="T8" s="63"/>
+      <c r="U8" s="63"/>
+      <c r="V8" s="51"/>
+      <c r="W8" s="56"/>
+      <c r="X8" s="63"/>
+      <c r="Y8" s="63"/>
+      <c r="Z8" s="51"/>
+      <c r="AA8" s="52"/>
+      <c r="AB8" s="63"/>
+      <c r="AC8" s="63"/>
+      <c r="AD8" s="53"/>
+      <c r="AE8" s="51"/>
+      <c r="AF8" s="52"/>
+      <c r="AG8" s="63"/>
+      <c r="AH8" s="63"/>
+      <c r="AI8" s="63"/>
+      <c r="AJ8" s="63"/>
+      <c r="AK8" s="63"/>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="43"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="58"/>
-      <c r="K9" s="45"/>
-      <c r="L9" s="49"/>
-      <c r="M9" s="58"/>
-      <c r="N9" s="50"/>
-      <c r="O9" s="57"/>
-      <c r="P9" s="45"/>
-      <c r="Q9" s="58"/>
-      <c r="R9" s="45"/>
-      <c r="S9" s="60"/>
-      <c r="T9" s="45"/>
-      <c r="U9" s="45"/>
-      <c r="V9" s="50"/>
-      <c r="W9" s="52"/>
-      <c r="X9" s="45"/>
-      <c r="Y9" s="45"/>
-      <c r="Z9" s="50"/>
-      <c r="AA9" s="51"/>
-      <c r="AB9" s="45"/>
-      <c r="AC9" s="45"/>
-      <c r="AD9" s="49"/>
-      <c r="AE9" s="50"/>
-      <c r="AF9" s="51"/>
-      <c r="AG9" s="45"/>
-      <c r="AH9" s="45"/>
-      <c r="AI9" s="45"/>
-      <c r="AJ9" s="45"/>
-      <c r="AK9" s="45"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="62"/>
+      <c r="J9" s="62"/>
+      <c r="K9" s="49"/>
+      <c r="L9" s="53"/>
+      <c r="M9" s="62"/>
+      <c r="N9" s="54"/>
+      <c r="O9" s="61"/>
+      <c r="P9" s="49"/>
+      <c r="Q9" s="62"/>
+      <c r="R9" s="49"/>
+      <c r="S9" s="64"/>
+      <c r="T9" s="49"/>
+      <c r="U9" s="49"/>
+      <c r="V9" s="54"/>
+      <c r="W9" s="56"/>
+      <c r="X9" s="49"/>
+      <c r="Y9" s="49"/>
+      <c r="Z9" s="54"/>
+      <c r="AA9" s="55"/>
+      <c r="AB9" s="49"/>
+      <c r="AC9" s="49"/>
+      <c r="AD9" s="53"/>
+      <c r="AE9" s="54"/>
+      <c r="AF9" s="55"/>
+      <c r="AG9" s="49"/>
+      <c r="AH9" s="49"/>
+      <c r="AI9" s="49"/>
+      <c r="AJ9" s="49"/>
+      <c r="AK9" s="49"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="43"/>
-      <c r="C10" s="44" t="s">
-        <v>103</v>
-      </c>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="45"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="45"/>
-      <c r="N10" s="50"/>
-      <c r="O10" s="51"/>
-      <c r="P10" s="45"/>
-      <c r="Q10" s="45"/>
-      <c r="R10" s="45"/>
-      <c r="S10" s="45"/>
-      <c r="T10" s="45"/>
-      <c r="U10" s="45"/>
-      <c r="V10" s="47"/>
-      <c r="W10" s="52"/>
-      <c r="X10" s="59"/>
-      <c r="Y10" s="59"/>
-      <c r="Z10" s="47"/>
-      <c r="AA10" s="51"/>
-      <c r="AB10" s="45"/>
-      <c r="AC10" s="45"/>
-      <c r="AD10" s="49"/>
-      <c r="AE10" s="50"/>
-      <c r="AF10" s="51"/>
-      <c r="AG10" s="45"/>
-      <c r="AH10" s="45"/>
-      <c r="AI10" s="45"/>
-      <c r="AJ10" s="45"/>
-      <c r="AK10" s="45"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="49"/>
+      <c r="N10" s="54"/>
+      <c r="O10" s="55"/>
+      <c r="P10" s="49"/>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="49"/>
+      <c r="S10" s="49"/>
+      <c r="T10" s="49"/>
+      <c r="U10" s="49"/>
+      <c r="V10" s="51"/>
+      <c r="W10" s="56"/>
+      <c r="X10" s="63"/>
+      <c r="Y10" s="63"/>
+      <c r="Z10" s="51"/>
+      <c r="AA10" s="55"/>
+      <c r="AB10" s="49"/>
+      <c r="AC10" s="49"/>
+      <c r="AD10" s="53"/>
+      <c r="AE10" s="54"/>
+      <c r="AF10" s="55"/>
+      <c r="AG10" s="49"/>
+      <c r="AH10" s="49"/>
+      <c r="AI10" s="49"/>
+      <c r="AJ10" s="49"/>
+      <c r="AK10" s="49"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="43"/>
-      <c r="C11" s="44"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="49"/>
-      <c r="M11" s="45"/>
-      <c r="N11" s="50"/>
-      <c r="O11" s="51"/>
-      <c r="P11" s="45"/>
-      <c r="Q11" s="45"/>
-      <c r="R11" s="45"/>
-      <c r="S11" s="45"/>
-      <c r="T11" s="45"/>
-      <c r="U11" s="45"/>
-      <c r="V11" s="50"/>
-      <c r="W11" s="52"/>
-      <c r="X11" s="45"/>
-      <c r="Y11" s="45"/>
-      <c r="Z11" s="50"/>
-      <c r="AA11" s="51"/>
-      <c r="AB11" s="45"/>
-      <c r="AC11" s="45"/>
-      <c r="AD11" s="49"/>
-      <c r="AE11" s="50"/>
-      <c r="AF11" s="51"/>
-      <c r="AG11" s="45"/>
-      <c r="AH11" s="45"/>
-      <c r="AI11" s="45"/>
-      <c r="AJ11" s="45"/>
-      <c r="AK11" s="45"/>
+      <c r="B11" s="47"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="49"/>
+      <c r="K11" s="49"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="49"/>
+      <c r="N11" s="54"/>
+      <c r="O11" s="55"/>
+      <c r="P11" s="49"/>
+      <c r="Q11" s="49"/>
+      <c r="R11" s="49"/>
+      <c r="S11" s="49"/>
+      <c r="T11" s="49"/>
+      <c r="U11" s="49"/>
+      <c r="V11" s="54"/>
+      <c r="W11" s="56"/>
+      <c r="X11" s="49"/>
+      <c r="Y11" s="49"/>
+      <c r="Z11" s="54"/>
+      <c r="AA11" s="55"/>
+      <c r="AB11" s="49"/>
+      <c r="AC11" s="49"/>
+      <c r="AD11" s="53"/>
+      <c r="AE11" s="54"/>
+      <c r="AF11" s="55"/>
+      <c r="AG11" s="49"/>
+      <c r="AH11" s="49"/>
+      <c r="AI11" s="49"/>
+      <c r="AJ11" s="49"/>
+      <c r="AK11" s="49"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="43"/>
-      <c r="C12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="49"/>
-      <c r="M12" s="45"/>
-      <c r="N12" s="50"/>
-      <c r="O12" s="51"/>
-      <c r="P12" s="45"/>
-      <c r="Q12" s="45"/>
-      <c r="R12" s="45"/>
-      <c r="S12" s="45"/>
-      <c r="T12" s="45"/>
-      <c r="U12" s="45"/>
-      <c r="V12" s="50"/>
-      <c r="W12" s="52"/>
-      <c r="X12" s="45"/>
-      <c r="Y12" s="45"/>
-      <c r="Z12" s="50"/>
-      <c r="AA12" s="51"/>
-      <c r="AB12" s="45"/>
-      <c r="AC12" s="45"/>
-      <c r="AD12" s="49"/>
-      <c r="AE12" s="50"/>
-      <c r="AF12" s="48"/>
-      <c r="AG12" s="59"/>
-      <c r="AH12" s="59"/>
-      <c r="AI12" s="59"/>
-      <c r="AJ12" s="59"/>
-      <c r="AK12" s="59"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="49"/>
+      <c r="L12" s="53"/>
+      <c r="M12" s="49"/>
+      <c r="N12" s="54"/>
+      <c r="O12" s="55"/>
+      <c r="P12" s="49"/>
+      <c r="Q12" s="49"/>
+      <c r="R12" s="49"/>
+      <c r="S12" s="49"/>
+      <c r="T12" s="49"/>
+      <c r="U12" s="49"/>
+      <c r="V12" s="54"/>
+      <c r="W12" s="56"/>
+      <c r="X12" s="49"/>
+      <c r="Y12" s="49"/>
+      <c r="Z12" s="54"/>
+      <c r="AA12" s="55"/>
+      <c r="AB12" s="49"/>
+      <c r="AC12" s="49"/>
+      <c r="AD12" s="53"/>
+      <c r="AE12" s="54"/>
+      <c r="AF12" s="52"/>
+      <c r="AG12" s="63"/>
+      <c r="AH12" s="63"/>
+      <c r="AI12" s="63"/>
+      <c r="AJ12" s="63"/>
+      <c r="AK12" s="63"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="43"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
-      <c r="K13" s="45"/>
-      <c r="L13" s="49"/>
-      <c r="M13" s="45"/>
-      <c r="N13" s="50"/>
-      <c r="O13" s="51"/>
-      <c r="P13" s="45"/>
-      <c r="Q13" s="45"/>
-      <c r="R13" s="45"/>
-      <c r="S13" s="45"/>
-      <c r="T13" s="45"/>
-      <c r="U13" s="45"/>
-      <c r="V13" s="50"/>
-      <c r="W13" s="52"/>
-      <c r="X13" s="45"/>
-      <c r="Y13" s="45"/>
-      <c r="Z13" s="50"/>
-      <c r="AA13" s="51"/>
-      <c r="AB13" s="45"/>
-      <c r="AC13" s="45"/>
-      <c r="AD13" s="49"/>
-      <c r="AE13" s="50"/>
-      <c r="AF13" s="51"/>
-      <c r="AG13" s="45"/>
-      <c r="AH13" s="45"/>
-      <c r="AI13" s="45"/>
-      <c r="AJ13" s="45"/>
-      <c r="AK13" s="45"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="49"/>
+      <c r="K13" s="49"/>
+      <c r="L13" s="53"/>
+      <c r="M13" s="49"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="55"/>
+      <c r="P13" s="49"/>
+      <c r="Q13" s="49"/>
+      <c r="R13" s="49"/>
+      <c r="S13" s="49"/>
+      <c r="T13" s="49"/>
+      <c r="U13" s="49"/>
+      <c r="V13" s="54"/>
+      <c r="W13" s="56"/>
+      <c r="X13" s="49"/>
+      <c r="Y13" s="49"/>
+      <c r="Z13" s="54"/>
+      <c r="AA13" s="55"/>
+      <c r="AB13" s="49"/>
+      <c r="AC13" s="49"/>
+      <c r="AD13" s="53"/>
+      <c r="AE13" s="54"/>
+      <c r="AF13" s="55"/>
+      <c r="AG13" s="49"/>
+      <c r="AH13" s="49"/>
+      <c r="AI13" s="49"/>
+      <c r="AJ13" s="49"/>
+      <c r="AK13" s="49"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="61" t="s">
-        <v>105</v>
-      </c>
-      <c r="C14" s="62" t="s">
-        <v>106</v>
-      </c>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="64"/>
-      <c r="K14" s="64"/>
-      <c r="L14" s="49"/>
-      <c r="M14" s="64"/>
-      <c r="N14" s="65"/>
-      <c r="O14" s="63"/>
-      <c r="P14" s="64"/>
-      <c r="Q14" s="64"/>
-      <c r="R14" s="64"/>
-      <c r="S14" s="64"/>
-      <c r="T14" s="64"/>
-      <c r="U14" s="64"/>
-      <c r="V14" s="65"/>
-      <c r="W14" s="52"/>
-      <c r="X14" s="64"/>
-      <c r="Y14" s="64"/>
-      <c r="Z14" s="65"/>
-      <c r="AA14" s="63"/>
-      <c r="AB14" s="64"/>
-      <c r="AC14" s="64"/>
-      <c r="AD14" s="49"/>
-      <c r="AE14" s="65"/>
-      <c r="AF14" s="63"/>
-      <c r="AG14" s="64"/>
-      <c r="AH14" s="64"/>
-      <c r="AI14" s="64"/>
-      <c r="AJ14" s="64"/>
-      <c r="AK14" s="64"/>
+      <c r="B14" s="65" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="66" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="68"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="53"/>
+      <c r="M14" s="68"/>
+      <c r="N14" s="69"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="68"/>
+      <c r="Q14" s="68"/>
+      <c r="R14" s="68"/>
+      <c r="S14" s="68"/>
+      <c r="T14" s="68"/>
+      <c r="U14" s="68"/>
+      <c r="V14" s="69"/>
+      <c r="W14" s="56"/>
+      <c r="X14" s="68"/>
+      <c r="Y14" s="68"/>
+      <c r="Z14" s="69"/>
+      <c r="AA14" s="67"/>
+      <c r="AB14" s="68"/>
+      <c r="AC14" s="68"/>
+      <c r="AD14" s="53"/>
+      <c r="AE14" s="69"/>
+      <c r="AF14" s="67"/>
+      <c r="AG14" s="68"/>
+      <c r="AH14" s="68"/>
+      <c r="AI14" s="68"/>
+      <c r="AJ14" s="68"/>
+      <c r="AK14" s="68"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="61"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="64"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="56"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="64"/>
-      <c r="J15" s="64"/>
-      <c r="K15" s="64"/>
-      <c r="L15" s="49"/>
-      <c r="M15" s="64"/>
-      <c r="N15" s="65"/>
-      <c r="O15" s="63"/>
-      <c r="P15" s="64"/>
-      <c r="Q15" s="64"/>
-      <c r="R15" s="64"/>
-      <c r="S15" s="64"/>
-      <c r="T15" s="64"/>
-      <c r="U15" s="64"/>
-      <c r="V15" s="65"/>
-      <c r="W15" s="52"/>
-      <c r="X15" s="64"/>
-      <c r="Y15" s="64"/>
-      <c r="Z15" s="65"/>
-      <c r="AA15" s="63"/>
-      <c r="AB15" s="64"/>
-      <c r="AC15" s="64"/>
-      <c r="AD15" s="49"/>
-      <c r="AE15" s="65"/>
-      <c r="AF15" s="63"/>
-      <c r="AG15" s="64"/>
-      <c r="AH15" s="64"/>
-      <c r="AI15" s="64"/>
-      <c r="AJ15" s="64"/>
-      <c r="AK15" s="64"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="68"/>
+      <c r="L15" s="53"/>
+      <c r="M15" s="68"/>
+      <c r="N15" s="69"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="68"/>
+      <c r="Q15" s="68"/>
+      <c r="R15" s="68"/>
+      <c r="S15" s="68"/>
+      <c r="T15" s="68"/>
+      <c r="U15" s="68"/>
+      <c r="V15" s="69"/>
+      <c r="W15" s="56"/>
+      <c r="X15" s="68"/>
+      <c r="Y15" s="68"/>
+      <c r="Z15" s="69"/>
+      <c r="AA15" s="67"/>
+      <c r="AB15" s="68"/>
+      <c r="AC15" s="68"/>
+      <c r="AD15" s="53"/>
+      <c r="AE15" s="69"/>
+      <c r="AF15" s="67"/>
+      <c r="AG15" s="68"/>
+      <c r="AH15" s="68"/>
+      <c r="AI15" s="68"/>
+      <c r="AJ15" s="68"/>
+      <c r="AK15" s="68"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="61"/>
-      <c r="C16" s="62" t="s">
-        <v>107</v>
-      </c>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="65"/>
-      <c r="H16" s="63"/>
-      <c r="I16" s="64"/>
-      <c r="J16" s="64"/>
-      <c r="K16" s="64"/>
-      <c r="L16" s="49"/>
-      <c r="M16" s="64"/>
-      <c r="N16" s="65"/>
-      <c r="O16" s="63"/>
-      <c r="P16" s="64"/>
-      <c r="Q16" s="64"/>
-      <c r="R16" s="64"/>
-      <c r="S16" s="64"/>
-      <c r="T16" s="64"/>
-      <c r="U16" s="64"/>
-      <c r="V16" s="65"/>
-      <c r="W16" s="52"/>
-      <c r="X16" s="64"/>
-      <c r="Y16" s="64"/>
-      <c r="Z16" s="65"/>
-      <c r="AA16" s="63"/>
-      <c r="AB16" s="64"/>
-      <c r="AC16" s="64"/>
-      <c r="AD16" s="49"/>
-      <c r="AE16" s="65"/>
-      <c r="AF16" s="63"/>
-      <c r="AG16" s="64"/>
-      <c r="AH16" s="64"/>
-      <c r="AI16" s="64"/>
-      <c r="AJ16" s="64"/>
-      <c r="AK16" s="64"/>
+      <c r="B16" s="65"/>
+      <c r="C16" s="66" t="s">
+        <v>110</v>
+      </c>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="67"/>
+      <c r="I16" s="68"/>
+      <c r="J16" s="68"/>
+      <c r="K16" s="68"/>
+      <c r="L16" s="53"/>
+      <c r="M16" s="68"/>
+      <c r="N16" s="69"/>
+      <c r="O16" s="67"/>
+      <c r="P16" s="68"/>
+      <c r="Q16" s="68"/>
+      <c r="R16" s="68"/>
+      <c r="S16" s="68"/>
+      <c r="T16" s="68"/>
+      <c r="U16" s="68"/>
+      <c r="V16" s="69"/>
+      <c r="W16" s="56"/>
+      <c r="X16" s="68"/>
+      <c r="Y16" s="68"/>
+      <c r="Z16" s="69"/>
+      <c r="AA16" s="67"/>
+      <c r="AB16" s="68"/>
+      <c r="AC16" s="68"/>
+      <c r="AD16" s="53"/>
+      <c r="AE16" s="69"/>
+      <c r="AF16" s="67"/>
+      <c r="AG16" s="68"/>
+      <c r="AH16" s="68"/>
+      <c r="AI16" s="68"/>
+      <c r="AJ16" s="68"/>
+      <c r="AK16" s="68"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="61"/>
-      <c r="C17" s="62"/>
-      <c r="D17" s="66"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="67"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="63"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="64"/>
-      <c r="K17" s="64"/>
-      <c r="L17" s="49"/>
-      <c r="M17" s="64"/>
-      <c r="N17" s="65"/>
-      <c r="O17" s="63"/>
-      <c r="P17" s="64"/>
-      <c r="Q17" s="64"/>
-      <c r="R17" s="64"/>
-      <c r="S17" s="64"/>
-      <c r="T17" s="64"/>
-      <c r="U17" s="64"/>
-      <c r="V17" s="65"/>
-      <c r="W17" s="52"/>
-      <c r="X17" s="64"/>
-      <c r="Y17" s="64"/>
-      <c r="Z17" s="65"/>
-      <c r="AA17" s="63"/>
-      <c r="AB17" s="64"/>
-      <c r="AC17" s="64"/>
-      <c r="AD17" s="49"/>
-      <c r="AE17" s="65"/>
-      <c r="AF17" s="63"/>
-      <c r="AG17" s="64"/>
-      <c r="AH17" s="64"/>
-      <c r="AI17" s="64"/>
-      <c r="AJ17" s="64"/>
-      <c r="AK17" s="64"/>
+      <c r="B17" s="65"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="67"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
+      <c r="L17" s="53"/>
+      <c r="M17" s="68"/>
+      <c r="N17" s="69"/>
+      <c r="O17" s="67"/>
+      <c r="P17" s="68"/>
+      <c r="Q17" s="68"/>
+      <c r="R17" s="68"/>
+      <c r="S17" s="68"/>
+      <c r="T17" s="68"/>
+      <c r="U17" s="68"/>
+      <c r="V17" s="69"/>
+      <c r="W17" s="56"/>
+      <c r="X17" s="68"/>
+      <c r="Y17" s="68"/>
+      <c r="Z17" s="69"/>
+      <c r="AA17" s="67"/>
+      <c r="AB17" s="68"/>
+      <c r="AC17" s="68"/>
+      <c r="AD17" s="53"/>
+      <c r="AE17" s="69"/>
+      <c r="AF17" s="67"/>
+      <c r="AG17" s="68"/>
+      <c r="AH17" s="68"/>
+      <c r="AI17" s="68"/>
+      <c r="AJ17" s="68"/>
+      <c r="AK17" s="68"/>
       <c r="AN17" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="61"/>
-      <c r="C18" s="62" t="s">
-        <v>109</v>
-      </c>
-      <c r="D18" s="59"/>
-      <c r="E18" s="59"/>
-      <c r="F18" s="67"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="63"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="64"/>
-      <c r="K18" s="64"/>
-      <c r="L18" s="49"/>
-      <c r="M18" s="64"/>
-      <c r="N18" s="65"/>
-      <c r="O18" s="63"/>
-      <c r="P18" s="64"/>
-      <c r="Q18" s="64"/>
-      <c r="R18" s="64"/>
-      <c r="S18" s="64"/>
-      <c r="T18" s="64"/>
-      <c r="U18" s="64"/>
-      <c r="V18" s="65"/>
-      <c r="W18" s="52"/>
-      <c r="X18" s="64"/>
-      <c r="Y18" s="64"/>
-      <c r="Z18" s="65"/>
-      <c r="AA18" s="63"/>
-      <c r="AB18" s="64"/>
-      <c r="AC18" s="64"/>
-      <c r="AD18" s="49"/>
-      <c r="AE18" s="65"/>
-      <c r="AF18" s="63"/>
-      <c r="AG18" s="64"/>
-      <c r="AH18" s="64"/>
-      <c r="AI18" s="64"/>
-      <c r="AJ18" s="64"/>
-      <c r="AK18" s="64"/>
+      <c r="B18" s="65"/>
+      <c r="C18" s="66" t="s">
+        <v>112</v>
+      </c>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="67"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="68"/>
+      <c r="K18" s="68"/>
+      <c r="L18" s="53"/>
+      <c r="M18" s="68"/>
+      <c r="N18" s="69"/>
+      <c r="O18" s="67"/>
+      <c r="P18" s="68"/>
+      <c r="Q18" s="68"/>
+      <c r="R18" s="68"/>
+      <c r="S18" s="68"/>
+      <c r="T18" s="68"/>
+      <c r="U18" s="68"/>
+      <c r="V18" s="69"/>
+      <c r="W18" s="56"/>
+      <c r="X18" s="68"/>
+      <c r="Y18" s="68"/>
+      <c r="Z18" s="69"/>
+      <c r="AA18" s="67"/>
+      <c r="AB18" s="68"/>
+      <c r="AC18" s="68"/>
+      <c r="AD18" s="53"/>
+      <c r="AE18" s="69"/>
+      <c r="AF18" s="67"/>
+      <c r="AG18" s="68"/>
+      <c r="AH18" s="68"/>
+      <c r="AI18" s="68"/>
+      <c r="AJ18" s="68"/>
+      <c r="AK18" s="68"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="61"/>
-      <c r="C19" s="62"/>
-      <c r="D19" s="64"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="65"/>
-      <c r="H19" s="63"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="64"/>
-      <c r="K19" s="64"/>
-      <c r="L19" s="49"/>
-      <c r="M19" s="64"/>
-      <c r="N19" s="65"/>
-      <c r="O19" s="63"/>
-      <c r="P19" s="64"/>
-      <c r="Q19" s="64"/>
-      <c r="R19" s="64"/>
-      <c r="S19" s="64"/>
-      <c r="T19" s="64"/>
-      <c r="U19" s="64"/>
-      <c r="V19" s="65"/>
-      <c r="W19" s="52"/>
-      <c r="X19" s="64"/>
-      <c r="Y19" s="64"/>
-      <c r="Z19" s="65"/>
-      <c r="AA19" s="63"/>
-      <c r="AB19" s="64"/>
-      <c r="AC19" s="64"/>
-      <c r="AD19" s="49"/>
-      <c r="AE19" s="65"/>
-      <c r="AF19" s="63"/>
-      <c r="AG19" s="64"/>
-      <c r="AH19" s="64"/>
-      <c r="AI19" s="64"/>
-      <c r="AJ19" s="64"/>
-      <c r="AK19" s="64"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="72"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="67"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
+      <c r="L19" s="53"/>
+      <c r="M19" s="68"/>
+      <c r="N19" s="69"/>
+      <c r="O19" s="67"/>
+      <c r="P19" s="68"/>
+      <c r="Q19" s="68"/>
+      <c r="R19" s="68"/>
+      <c r="S19" s="68"/>
+      <c r="T19" s="68"/>
+      <c r="U19" s="68"/>
+      <c r="V19" s="69"/>
+      <c r="W19" s="56"/>
+      <c r="X19" s="68"/>
+      <c r="Y19" s="68"/>
+      <c r="Z19" s="69"/>
+      <c r="AA19" s="67"/>
+      <c r="AB19" s="68"/>
+      <c r="AC19" s="68"/>
+      <c r="AD19" s="53"/>
+      <c r="AE19" s="69"/>
+      <c r="AF19" s="67"/>
+      <c r="AG19" s="68"/>
+      <c r="AH19" s="68"/>
+      <c r="AI19" s="68"/>
+      <c r="AJ19" s="68"/>
+      <c r="AK19" s="68"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="61"/>
-      <c r="C20" s="62" t="s">
-        <v>110</v>
-      </c>
-      <c r="D20" s="64"/>
-      <c r="E20" s="64"/>
-      <c r="F20" s="67"/>
-      <c r="G20" s="47"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="59"/>
-      <c r="J20" s="64"/>
-      <c r="K20" s="64"/>
-      <c r="L20" s="49"/>
-      <c r="M20" s="64"/>
-      <c r="N20" s="65"/>
-      <c r="O20" s="63"/>
-      <c r="P20" s="64"/>
-      <c r="Q20" s="64"/>
-      <c r="R20" s="64"/>
-      <c r="S20" s="64"/>
-      <c r="T20" s="64"/>
-      <c r="U20" s="64"/>
-      <c r="V20" s="65"/>
-      <c r="W20" s="52"/>
-      <c r="X20" s="64"/>
-      <c r="Y20" s="64"/>
-      <c r="Z20" s="65"/>
-      <c r="AA20" s="63"/>
-      <c r="AB20" s="64"/>
-      <c r="AC20" s="64"/>
-      <c r="AD20" s="49"/>
-      <c r="AE20" s="65"/>
-      <c r="AF20" s="63"/>
-      <c r="AG20" s="64"/>
-      <c r="AH20" s="64"/>
-      <c r="AI20" s="64"/>
-      <c r="AJ20" s="64"/>
-      <c r="AK20" s="64"/>
+      <c r="B20" s="65"/>
+      <c r="C20" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68"/>
+      <c r="L20" s="53"/>
+      <c r="M20" s="68"/>
+      <c r="N20" s="69"/>
+      <c r="O20" s="67"/>
+      <c r="P20" s="68"/>
+      <c r="Q20" s="68"/>
+      <c r="R20" s="68"/>
+      <c r="S20" s="68"/>
+      <c r="T20" s="68"/>
+      <c r="U20" s="68"/>
+      <c r="V20" s="69"/>
+      <c r="W20" s="56"/>
+      <c r="X20" s="68"/>
+      <c r="Y20" s="68"/>
+      <c r="Z20" s="69"/>
+      <c r="AA20" s="67"/>
+      <c r="AB20" s="68"/>
+      <c r="AC20" s="68"/>
+      <c r="AD20" s="53"/>
+      <c r="AE20" s="69"/>
+      <c r="AF20" s="67"/>
+      <c r="AG20" s="68"/>
+      <c r="AH20" s="68"/>
+      <c r="AI20" s="68"/>
+      <c r="AJ20" s="68"/>
+      <c r="AK20" s="68"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="61"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="64"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="63"/>
-      <c r="I21" s="58"/>
-      <c r="J21" s="64"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="49"/>
-      <c r="M21" s="64"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="63"/>
-      <c r="P21" s="64"/>
-      <c r="Q21" s="64"/>
-      <c r="R21" s="64"/>
-      <c r="S21" s="64"/>
-      <c r="T21" s="64"/>
-      <c r="U21" s="64"/>
-      <c r="V21" s="65"/>
-      <c r="W21" s="52"/>
-      <c r="X21" s="64"/>
-      <c r="Y21" s="64"/>
-      <c r="Z21" s="65"/>
-      <c r="AA21" s="63"/>
-      <c r="AB21" s="64"/>
-      <c r="AC21" s="64"/>
-      <c r="AD21" s="49"/>
-      <c r="AE21" s="65"/>
-      <c r="AF21" s="63"/>
-      <c r="AG21" s="64"/>
-      <c r="AH21" s="64"/>
-      <c r="AI21" s="64"/>
-      <c r="AJ21" s="64"/>
-      <c r="AK21" s="64"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="66"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="67"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="68"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="68"/>
+      <c r="N21" s="69"/>
+      <c r="O21" s="67"/>
+      <c r="P21" s="68"/>
+      <c r="Q21" s="68"/>
+      <c r="R21" s="68"/>
+      <c r="S21" s="68"/>
+      <c r="T21" s="68"/>
+      <c r="U21" s="68"/>
+      <c r="V21" s="69"/>
+      <c r="W21" s="56"/>
+      <c r="X21" s="68"/>
+      <c r="Y21" s="68"/>
+      <c r="Z21" s="69"/>
+      <c r="AA21" s="67"/>
+      <c r="AB21" s="68"/>
+      <c r="AC21" s="68"/>
+      <c r="AD21" s="53"/>
+      <c r="AE21" s="69"/>
+      <c r="AF21" s="67"/>
+      <c r="AG21" s="68"/>
+      <c r="AH21" s="68"/>
+      <c r="AI21" s="68"/>
+      <c r="AJ21" s="68"/>
+      <c r="AK21" s="68"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="61"/>
-      <c r="C22" s="62" t="s">
-        <v>111</v>
-      </c>
-      <c r="D22" s="64"/>
-      <c r="E22" s="64"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="59"/>
-      <c r="J22" s="64"/>
-      <c r="K22" s="64"/>
-      <c r="L22" s="49"/>
-      <c r="M22" s="64"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="63"/>
-      <c r="P22" s="64"/>
-      <c r="Q22" s="64"/>
-      <c r="R22" s="64"/>
-      <c r="S22" s="64"/>
-      <c r="T22" s="64"/>
-      <c r="U22" s="64"/>
-      <c r="V22" s="65"/>
-      <c r="W22" s="52"/>
-      <c r="X22" s="64"/>
-      <c r="Y22" s="64"/>
-      <c r="Z22" s="65"/>
-      <c r="AA22" s="63"/>
-      <c r="AB22" s="64"/>
-      <c r="AC22" s="64"/>
-      <c r="AD22" s="49"/>
-      <c r="AE22" s="65"/>
-      <c r="AF22" s="63"/>
-      <c r="AG22" s="64"/>
-      <c r="AH22" s="64"/>
-      <c r="AI22" s="64"/>
-      <c r="AJ22" s="64"/>
-      <c r="AK22" s="64"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="66" t="s">
+        <v>114</v>
+      </c>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="63"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68"/>
+      <c r="L22" s="53"/>
+      <c r="M22" s="68"/>
+      <c r="N22" s="69"/>
+      <c r="O22" s="67"/>
+      <c r="P22" s="68"/>
+      <c r="Q22" s="68"/>
+      <c r="R22" s="68"/>
+      <c r="S22" s="68"/>
+      <c r="T22" s="68"/>
+      <c r="U22" s="68"/>
+      <c r="V22" s="69"/>
+      <c r="W22" s="56"/>
+      <c r="X22" s="68"/>
+      <c r="Y22" s="68"/>
+      <c r="Z22" s="69"/>
+      <c r="AA22" s="67"/>
+      <c r="AB22" s="68"/>
+      <c r="AC22" s="68"/>
+      <c r="AD22" s="53"/>
+      <c r="AE22" s="69"/>
+      <c r="AF22" s="67"/>
+      <c r="AG22" s="68"/>
+      <c r="AH22" s="68"/>
+      <c r="AI22" s="68"/>
+      <c r="AJ22" s="68"/>
+      <c r="AK22" s="68"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="61"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="64"/>
-      <c r="E23" s="64"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="54"/>
-      <c r="K23" s="64"/>
-      <c r="L23" s="49"/>
-      <c r="M23" s="64"/>
-      <c r="N23" s="65"/>
-      <c r="O23" s="63"/>
-      <c r="P23" s="64"/>
-      <c r="Q23" s="64"/>
-      <c r="R23" s="64"/>
-      <c r="S23" s="64"/>
-      <c r="T23" s="64"/>
-      <c r="U23" s="64"/>
-      <c r="V23" s="65"/>
-      <c r="W23" s="52"/>
-      <c r="X23" s="64"/>
-      <c r="Y23" s="64"/>
-      <c r="Z23" s="65"/>
-      <c r="AA23" s="63"/>
-      <c r="AB23" s="64"/>
-      <c r="AC23" s="64"/>
-      <c r="AD23" s="49"/>
-      <c r="AE23" s="65"/>
-      <c r="AF23" s="63"/>
-      <c r="AG23" s="64"/>
-      <c r="AH23" s="64"/>
-      <c r="AI23" s="64"/>
-      <c r="AJ23" s="64"/>
-      <c r="AK23" s="64"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="69"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="68"/>
+      <c r="L23" s="53"/>
+      <c r="M23" s="68"/>
+      <c r="N23" s="69"/>
+      <c r="O23" s="67"/>
+      <c r="P23" s="68"/>
+      <c r="Q23" s="68"/>
+      <c r="R23" s="68"/>
+      <c r="S23" s="68"/>
+      <c r="T23" s="68"/>
+      <c r="U23" s="68"/>
+      <c r="V23" s="69"/>
+      <c r="W23" s="56"/>
+      <c r="X23" s="68"/>
+      <c r="Y23" s="68"/>
+      <c r="Z23" s="69"/>
+      <c r="AA23" s="67"/>
+      <c r="AB23" s="68"/>
+      <c r="AC23" s="68"/>
+      <c r="AD23" s="53"/>
+      <c r="AE23" s="69"/>
+      <c r="AF23" s="67"/>
+      <c r="AG23" s="68"/>
+      <c r="AH23" s="68"/>
+      <c r="AI23" s="68"/>
+      <c r="AJ23" s="68"/>
+      <c r="AK23" s="68"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="61"/>
-      <c r="C24" s="62" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" s="64"/>
-      <c r="E24" s="64"/>
-      <c r="F24" s="67"/>
-      <c r="G24" s="65"/>
-      <c r="H24" s="63"/>
-      <c r="I24" s="59"/>
-      <c r="J24" s="64"/>
-      <c r="K24" s="64"/>
-      <c r="L24" s="49"/>
-      <c r="M24" s="64"/>
-      <c r="N24" s="65"/>
-      <c r="O24" s="63"/>
-      <c r="P24" s="64"/>
-      <c r="Q24" s="64"/>
-      <c r="R24" s="64"/>
-      <c r="S24" s="64"/>
-      <c r="T24" s="64"/>
-      <c r="U24" s="64"/>
-      <c r="V24" s="65"/>
-      <c r="W24" s="52"/>
-      <c r="X24" s="64"/>
-      <c r="Y24" s="64"/>
-      <c r="Z24" s="65"/>
-      <c r="AA24" s="63"/>
-      <c r="AB24" s="64"/>
-      <c r="AC24" s="64"/>
-      <c r="AD24" s="49"/>
-      <c r="AE24" s="65"/>
-      <c r="AF24" s="63"/>
-      <c r="AG24" s="64"/>
-      <c r="AH24" s="64"/>
-      <c r="AI24" s="64"/>
-      <c r="AJ24" s="64"/>
-      <c r="AK24" s="64"/>
+      <c r="B24" s="65"/>
+      <c r="C24" s="66" t="s">
+        <v>115</v>
+      </c>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="69"/>
+      <c r="H24" s="67"/>
+      <c r="I24" s="63"/>
+      <c r="J24" s="68"/>
+      <c r="K24" s="68"/>
+      <c r="L24" s="53"/>
+      <c r="M24" s="68"/>
+      <c r="N24" s="69"/>
+      <c r="O24" s="67"/>
+      <c r="P24" s="68"/>
+      <c r="Q24" s="68"/>
+      <c r="R24" s="68"/>
+      <c r="S24" s="68"/>
+      <c r="T24" s="68"/>
+      <c r="U24" s="68"/>
+      <c r="V24" s="69"/>
+      <c r="W24" s="56"/>
+      <c r="X24" s="68"/>
+      <c r="Y24" s="68"/>
+      <c r="Z24" s="69"/>
+      <c r="AA24" s="67"/>
+      <c r="AB24" s="68"/>
+      <c r="AC24" s="68"/>
+      <c r="AD24" s="53"/>
+      <c r="AE24" s="69"/>
+      <c r="AF24" s="67"/>
+      <c r="AG24" s="68"/>
+      <c r="AH24" s="68"/>
+      <c r="AI24" s="68"/>
+      <c r="AJ24" s="68"/>
+      <c r="AK24" s="68"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="61"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="64"/>
-      <c r="E25" s="64"/>
-      <c r="F25" s="67"/>
-      <c r="G25" s="65"/>
-      <c r="H25" s="63"/>
-      <c r="I25" s="64"/>
-      <c r="J25" s="54"/>
-      <c r="K25" s="64"/>
-      <c r="L25" s="49"/>
-      <c r="M25" s="64"/>
-      <c r="N25" s="65"/>
-      <c r="O25" s="63"/>
-      <c r="P25" s="64"/>
-      <c r="Q25" s="64"/>
-      <c r="R25" s="64"/>
-      <c r="S25" s="64"/>
-      <c r="T25" s="64"/>
-      <c r="U25" s="64"/>
-      <c r="V25" s="65"/>
-      <c r="W25" s="52"/>
-      <c r="X25" s="64"/>
-      <c r="Y25" s="64"/>
-      <c r="Z25" s="65"/>
-      <c r="AA25" s="63"/>
-      <c r="AB25" s="64"/>
-      <c r="AC25" s="64"/>
-      <c r="AD25" s="49"/>
-      <c r="AE25" s="65"/>
-      <c r="AF25" s="63"/>
-      <c r="AG25" s="64"/>
-      <c r="AH25" s="64"/>
-      <c r="AI25" s="64"/>
-      <c r="AJ25" s="64"/>
-      <c r="AK25" s="64"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="69"/>
+      <c r="H25" s="67"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="58"/>
+      <c r="K25" s="68"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="68"/>
+      <c r="N25" s="69"/>
+      <c r="O25" s="67"/>
+      <c r="P25" s="68"/>
+      <c r="Q25" s="68"/>
+      <c r="R25" s="68"/>
+      <c r="S25" s="68"/>
+      <c r="T25" s="68"/>
+      <c r="U25" s="68"/>
+      <c r="V25" s="69"/>
+      <c r="W25" s="56"/>
+      <c r="X25" s="68"/>
+      <c r="Y25" s="68"/>
+      <c r="Z25" s="69"/>
+      <c r="AA25" s="67"/>
+      <c r="AB25" s="68"/>
+      <c r="AC25" s="68"/>
+      <c r="AD25" s="53"/>
+      <c r="AE25" s="69"/>
+      <c r="AF25" s="67"/>
+      <c r="AG25" s="68"/>
+      <c r="AH25" s="68"/>
+      <c r="AI25" s="68"/>
+      <c r="AJ25" s="68"/>
+      <c r="AK25" s="68"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="43" t="s">
-        <v>113</v>
-      </c>
-      <c r="C26" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="48"/>
-      <c r="I26" s="59"/>
-      <c r="J26" s="45"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="49"/>
-      <c r="M26" s="45"/>
-      <c r="N26" s="50"/>
-      <c r="O26" s="51"/>
-      <c r="P26" s="45"/>
-      <c r="Q26" s="45"/>
-      <c r="R26" s="45"/>
-      <c r="S26" s="45"/>
-      <c r="T26" s="45"/>
-      <c r="U26" s="45"/>
-      <c r="V26" s="50"/>
-      <c r="W26" s="52"/>
-      <c r="X26" s="45"/>
-      <c r="Y26" s="45"/>
-      <c r="Z26" s="50"/>
-      <c r="AA26" s="51"/>
-      <c r="AB26" s="45"/>
-      <c r="AC26" s="45"/>
-      <c r="AD26" s="49"/>
-      <c r="AE26" s="50"/>
-      <c r="AF26" s="51"/>
-      <c r="AG26" s="45"/>
-      <c r="AH26" s="45"/>
-      <c r="AI26" s="45"/>
-      <c r="AJ26" s="45"/>
-      <c r="AK26" s="45"/>
+      <c r="B26" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="C26" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="63"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="53"/>
+      <c r="M26" s="49"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="55"/>
+      <c r="P26" s="49"/>
+      <c r="Q26" s="49"/>
+      <c r="R26" s="49"/>
+      <c r="S26" s="49"/>
+      <c r="T26" s="49"/>
+      <c r="U26" s="49"/>
+      <c r="V26" s="54"/>
+      <c r="W26" s="56"/>
+      <c r="X26" s="49"/>
+      <c r="Y26" s="49"/>
+      <c r="Z26" s="54"/>
+      <c r="AA26" s="55"/>
+      <c r="AB26" s="49"/>
+      <c r="AC26" s="49"/>
+      <c r="AD26" s="53"/>
+      <c r="AE26" s="54"/>
+      <c r="AF26" s="55"/>
+      <c r="AG26" s="49"/>
+      <c r="AH26" s="49"/>
+      <c r="AI26" s="49"/>
+      <c r="AJ26" s="49"/>
+      <c r="AK26" s="49"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="43"/>
-      <c r="C27" s="44"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="45"/>
-      <c r="K27" s="45"/>
-      <c r="L27" s="49"/>
-      <c r="M27" s="45"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="51"/>
-      <c r="P27" s="45"/>
-      <c r="Q27" s="45"/>
-      <c r="R27" s="45"/>
-      <c r="S27" s="45"/>
-      <c r="T27" s="45"/>
-      <c r="U27" s="45"/>
-      <c r="V27" s="50"/>
-      <c r="W27" s="52"/>
-      <c r="X27" s="45"/>
-      <c r="Y27" s="45"/>
-      <c r="Z27" s="50"/>
-      <c r="AA27" s="51"/>
-      <c r="AB27" s="45"/>
-      <c r="AC27" s="45"/>
-      <c r="AD27" s="49"/>
-      <c r="AE27" s="50"/>
-      <c r="AF27" s="51"/>
-      <c r="AG27" s="45"/>
-      <c r="AH27" s="45"/>
-      <c r="AI27" s="45"/>
-      <c r="AJ27" s="45"/>
-      <c r="AK27" s="45"/>
+      <c r="B27" s="47"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="49"/>
+      <c r="J27" s="49"/>
+      <c r="K27" s="49"/>
+      <c r="L27" s="53"/>
+      <c r="M27" s="49"/>
+      <c r="N27" s="54"/>
+      <c r="O27" s="55"/>
+      <c r="P27" s="49"/>
+      <c r="Q27" s="49"/>
+      <c r="R27" s="49"/>
+      <c r="S27" s="49"/>
+      <c r="T27" s="49"/>
+      <c r="U27" s="49"/>
+      <c r="V27" s="54"/>
+      <c r="W27" s="56"/>
+      <c r="X27" s="49"/>
+      <c r="Y27" s="49"/>
+      <c r="Z27" s="54"/>
+      <c r="AA27" s="55"/>
+      <c r="AB27" s="49"/>
+      <c r="AC27" s="49"/>
+      <c r="AD27" s="53"/>
+      <c r="AE27" s="54"/>
+      <c r="AF27" s="55"/>
+      <c r="AG27" s="49"/>
+      <c r="AH27" s="49"/>
+      <c r="AI27" s="49"/>
+      <c r="AJ27" s="49"/>
+      <c r="AK27" s="49"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="43"/>
-      <c r="C28" s="44" t="s">
-        <v>115</v>
-      </c>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="59"/>
-      <c r="J28" s="59"/>
-      <c r="K28" s="59"/>
-      <c r="L28" s="49"/>
-      <c r="M28" s="45"/>
-      <c r="N28" s="50"/>
-      <c r="O28" s="51"/>
-      <c r="P28" s="45"/>
-      <c r="Q28" s="45"/>
-      <c r="R28" s="45"/>
-      <c r="S28" s="45"/>
-      <c r="T28" s="45"/>
-      <c r="U28" s="45"/>
-      <c r="V28" s="50"/>
-      <c r="W28" s="52"/>
-      <c r="X28" s="45"/>
-      <c r="Y28" s="45"/>
-      <c r="Z28" s="50"/>
-      <c r="AA28" s="51"/>
-      <c r="AB28" s="45"/>
-      <c r="AC28" s="45"/>
-      <c r="AD28" s="49"/>
-      <c r="AE28" s="50"/>
-      <c r="AF28" s="51"/>
-      <c r="AG28" s="45"/>
-      <c r="AH28" s="45"/>
-      <c r="AI28" s="45"/>
-      <c r="AJ28" s="45"/>
-      <c r="AK28" s="45"/>
+      <c r="B28" s="47"/>
+      <c r="C28" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="63"/>
+      <c r="K28" s="63"/>
+      <c r="L28" s="53"/>
+      <c r="M28" s="49"/>
+      <c r="N28" s="54"/>
+      <c r="O28" s="55"/>
+      <c r="P28" s="49"/>
+      <c r="Q28" s="49"/>
+      <c r="R28" s="49"/>
+      <c r="S28" s="49"/>
+      <c r="T28" s="49"/>
+      <c r="U28" s="49"/>
+      <c r="V28" s="54"/>
+      <c r="W28" s="56"/>
+      <c r="X28" s="49"/>
+      <c r="Y28" s="49"/>
+      <c r="Z28" s="54"/>
+      <c r="AA28" s="55"/>
+      <c r="AB28" s="49"/>
+      <c r="AC28" s="49"/>
+      <c r="AD28" s="53"/>
+      <c r="AE28" s="54"/>
+      <c r="AF28" s="55"/>
+      <c r="AG28" s="49"/>
+      <c r="AH28" s="49"/>
+      <c r="AI28" s="49"/>
+      <c r="AJ28" s="49"/>
+      <c r="AK28" s="49"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="43"/>
-      <c r="C29" s="44"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="53"/>
-      <c r="G29" s="56"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="60"/>
-      <c r="K29" s="45"/>
-      <c r="L29" s="49"/>
-      <c r="M29" s="45"/>
-      <c r="N29" s="50"/>
-      <c r="O29" s="51"/>
-      <c r="P29" s="45"/>
-      <c r="Q29" s="45"/>
-      <c r="R29" s="45"/>
-      <c r="S29" s="45"/>
-      <c r="T29" s="45"/>
-      <c r="U29" s="45"/>
-      <c r="V29" s="50"/>
-      <c r="W29" s="52"/>
-      <c r="X29" s="45"/>
-      <c r="Y29" s="45"/>
-      <c r="Z29" s="50"/>
-      <c r="AA29" s="51"/>
-      <c r="AB29" s="45"/>
-      <c r="AC29" s="45"/>
-      <c r="AD29" s="49"/>
-      <c r="AE29" s="50"/>
-      <c r="AF29" s="51"/>
-      <c r="AG29" s="45"/>
-      <c r="AH29" s="45"/>
-      <c r="AI29" s="45"/>
-      <c r="AJ29" s="45"/>
-      <c r="AK29" s="45"/>
+      <c r="B29" s="47"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="60"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="49"/>
+      <c r="J29" s="64"/>
+      <c r="K29" s="49"/>
+      <c r="L29" s="53"/>
+      <c r="M29" s="49"/>
+      <c r="N29" s="54"/>
+      <c r="O29" s="55"/>
+      <c r="P29" s="49"/>
+      <c r="Q29" s="49"/>
+      <c r="R29" s="49"/>
+      <c r="S29" s="49"/>
+      <c r="T29" s="49"/>
+      <c r="U29" s="49"/>
+      <c r="V29" s="54"/>
+      <c r="W29" s="56"/>
+      <c r="X29" s="49"/>
+      <c r="Y29" s="49"/>
+      <c r="Z29" s="54"/>
+      <c r="AA29" s="55"/>
+      <c r="AB29" s="49"/>
+      <c r="AC29" s="49"/>
+      <c r="AD29" s="53"/>
+      <c r="AE29" s="54"/>
+      <c r="AF29" s="55"/>
+      <c r="AG29" s="49"/>
+      <c r="AH29" s="49"/>
+      <c r="AI29" s="49"/>
+      <c r="AJ29" s="49"/>
+      <c r="AK29" s="49"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="43"/>
-      <c r="C30" s="44" t="s">
-        <v>116</v>
-      </c>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="53"/>
-      <c r="G30" s="50"/>
-      <c r="H30" s="48"/>
-      <c r="I30" s="59"/>
-      <c r="J30" s="59"/>
-      <c r="K30" s="59"/>
-      <c r="L30" s="49"/>
-      <c r="M30" s="59"/>
-      <c r="N30" s="50"/>
-      <c r="O30" s="51"/>
-      <c r="P30" s="45"/>
-      <c r="Q30" s="45"/>
-      <c r="R30" s="45"/>
-      <c r="S30" s="45"/>
-      <c r="T30" s="45"/>
-      <c r="U30" s="45"/>
-      <c r="V30" s="50"/>
-      <c r="W30" s="52"/>
-      <c r="X30" s="45"/>
-      <c r="Y30" s="45"/>
-      <c r="Z30" s="50"/>
-      <c r="AA30" s="51"/>
-      <c r="AB30" s="45"/>
-      <c r="AC30" s="45"/>
-      <c r="AD30" s="49"/>
-      <c r="AE30" s="50"/>
-      <c r="AF30" s="51"/>
-      <c r="AG30" s="45"/>
-      <c r="AH30" s="45"/>
-      <c r="AI30" s="45"/>
-      <c r="AJ30" s="45"/>
-      <c r="AK30" s="45"/>
+      <c r="B30" s="47"/>
+      <c r="C30" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" s="49"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="63"/>
+      <c r="K30" s="63"/>
+      <c r="L30" s="53"/>
+      <c r="M30" s="63"/>
+      <c r="N30" s="54"/>
+      <c r="O30" s="55"/>
+      <c r="P30" s="49"/>
+      <c r="Q30" s="49"/>
+      <c r="R30" s="49"/>
+      <c r="S30" s="49"/>
+      <c r="T30" s="49"/>
+      <c r="U30" s="49"/>
+      <c r="V30" s="54"/>
+      <c r="W30" s="56"/>
+      <c r="X30" s="49"/>
+      <c r="Y30" s="49"/>
+      <c r="Z30" s="54"/>
+      <c r="AA30" s="55"/>
+      <c r="AB30" s="49"/>
+      <c r="AC30" s="49"/>
+      <c r="AD30" s="53"/>
+      <c r="AE30" s="54"/>
+      <c r="AF30" s="55"/>
+      <c r="AG30" s="49"/>
+      <c r="AH30" s="49"/>
+      <c r="AI30" s="49"/>
+      <c r="AJ30" s="49"/>
+      <c r="AK30" s="49"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="43"/>
-      <c r="C31" s="44"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="56"/>
-      <c r="H31" s="57"/>
-      <c r="I31" s="45"/>
-      <c r="J31" s="60"/>
-      <c r="K31" s="60"/>
-      <c r="L31" s="69"/>
-      <c r="M31" s="45"/>
-      <c r="N31" s="56"/>
-      <c r="O31" s="51"/>
-      <c r="P31" s="45"/>
-      <c r="Q31" s="45"/>
-      <c r="R31" s="45"/>
-      <c r="S31" s="45"/>
-      <c r="T31" s="45"/>
-      <c r="U31" s="45"/>
-      <c r="V31" s="50"/>
-      <c r="W31" s="52"/>
-      <c r="X31" s="45"/>
-      <c r="Y31" s="45"/>
-      <c r="Z31" s="50"/>
-      <c r="AA31" s="51"/>
-      <c r="AB31" s="45"/>
-      <c r="AC31" s="45"/>
-      <c r="AD31" s="49"/>
-      <c r="AE31" s="50"/>
-      <c r="AF31" s="51"/>
-      <c r="AG31" s="45"/>
-      <c r="AH31" s="45"/>
-      <c r="AI31" s="45"/>
-      <c r="AJ31" s="45"/>
-      <c r="AK31" s="45"/>
+      <c r="B31" s="47"/>
+      <c r="C31" s="48"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="60"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="49"/>
+      <c r="J31" s="64"/>
+      <c r="K31" s="64"/>
+      <c r="L31" s="73"/>
+      <c r="M31" s="49"/>
+      <c r="N31" s="60"/>
+      <c r="O31" s="55"/>
+      <c r="P31" s="49"/>
+      <c r="Q31" s="49"/>
+      <c r="R31" s="49"/>
+      <c r="S31" s="49"/>
+      <c r="T31" s="49"/>
+      <c r="U31" s="49"/>
+      <c r="V31" s="54"/>
+      <c r="W31" s="56"/>
+      <c r="X31" s="49"/>
+      <c r="Y31" s="49"/>
+      <c r="Z31" s="54"/>
+      <c r="AA31" s="55"/>
+      <c r="AB31" s="49"/>
+      <c r="AC31" s="49"/>
+      <c r="AD31" s="53"/>
+      <c r="AE31" s="54"/>
+      <c r="AF31" s="55"/>
+      <c r="AG31" s="49"/>
+      <c r="AH31" s="49"/>
+      <c r="AI31" s="49"/>
+      <c r="AJ31" s="49"/>
+      <c r="AK31" s="49"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="43"/>
-      <c r="C32" s="44" t="s">
-        <v>117</v>
-      </c>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="53"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="51"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="49"/>
-      <c r="M32" s="59"/>
-      <c r="N32" s="47"/>
-      <c r="O32" s="51"/>
-      <c r="P32" s="45"/>
-      <c r="Q32" s="45"/>
-      <c r="R32" s="45"/>
-      <c r="S32" s="45"/>
-      <c r="T32" s="45"/>
-      <c r="U32" s="45"/>
-      <c r="V32" s="50"/>
-      <c r="W32" s="52"/>
-      <c r="X32" s="45"/>
-      <c r="Y32" s="45"/>
-      <c r="Z32" s="50"/>
-      <c r="AA32" s="51"/>
-      <c r="AB32" s="45"/>
-      <c r="AC32" s="45"/>
-      <c r="AD32" s="49"/>
-      <c r="AE32" s="50"/>
-      <c r="AF32" s="51"/>
-      <c r="AG32" s="45"/>
-      <c r="AH32" s="45"/>
-      <c r="AI32" s="45"/>
-      <c r="AJ32" s="45"/>
-      <c r="AK32" s="45"/>
+      <c r="B32" s="47"/>
+      <c r="C32" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="D32" s="49"/>
+      <c r="E32" s="49"/>
+      <c r="F32" s="57"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="49"/>
+      <c r="J32" s="49"/>
+      <c r="K32" s="49"/>
+      <c r="L32" s="53"/>
+      <c r="M32" s="63"/>
+      <c r="N32" s="51"/>
+      <c r="O32" s="55"/>
+      <c r="P32" s="49"/>
+      <c r="Q32" s="49"/>
+      <c r="R32" s="49"/>
+      <c r="S32" s="49"/>
+      <c r="T32" s="49"/>
+      <c r="U32" s="49"/>
+      <c r="V32" s="54"/>
+      <c r="W32" s="56"/>
+      <c r="X32" s="49"/>
+      <c r="Y32" s="49"/>
+      <c r="Z32" s="54"/>
+      <c r="AA32" s="55"/>
+      <c r="AB32" s="49"/>
+      <c r="AC32" s="49"/>
+      <c r="AD32" s="53"/>
+      <c r="AE32" s="54"/>
+      <c r="AF32" s="55"/>
+      <c r="AG32" s="49"/>
+      <c r="AH32" s="49"/>
+      <c r="AI32" s="49"/>
+      <c r="AJ32" s="49"/>
+      <c r="AK32" s="49"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="43"/>
-      <c r="C33" s="44"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="53"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="51"/>
-      <c r="I33" s="45"/>
-      <c r="J33" s="45"/>
-      <c r="K33" s="45"/>
-      <c r="L33" s="49"/>
-      <c r="M33" s="45"/>
-      <c r="N33" s="56"/>
-      <c r="O33" s="51"/>
-      <c r="P33" s="45"/>
-      <c r="Q33" s="45"/>
-      <c r="R33" s="45"/>
-      <c r="S33" s="45"/>
-      <c r="T33" s="45"/>
-      <c r="U33" s="45"/>
-      <c r="V33" s="50"/>
-      <c r="W33" s="52"/>
-      <c r="X33" s="45"/>
-      <c r="Y33" s="45"/>
-      <c r="Z33" s="50"/>
-      <c r="AA33" s="51"/>
-      <c r="AB33" s="45"/>
-      <c r="AC33" s="45"/>
-      <c r="AD33" s="49"/>
-      <c r="AE33" s="50"/>
-      <c r="AF33" s="51"/>
-      <c r="AG33" s="45"/>
-      <c r="AH33" s="45"/>
-      <c r="AI33" s="45"/>
-      <c r="AJ33" s="45"/>
-      <c r="AK33" s="45"/>
+      <c r="B33" s="47"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="49"/>
+      <c r="J33" s="49"/>
+      <c r="K33" s="49"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="49"/>
+      <c r="N33" s="60"/>
+      <c r="O33" s="55"/>
+      <c r="P33" s="49"/>
+      <c r="Q33" s="49"/>
+      <c r="R33" s="49"/>
+      <c r="S33" s="49"/>
+      <c r="T33" s="49"/>
+      <c r="U33" s="49"/>
+      <c r="V33" s="54"/>
+      <c r="W33" s="56"/>
+      <c r="X33" s="49"/>
+      <c r="Y33" s="49"/>
+      <c r="Z33" s="54"/>
+      <c r="AA33" s="55"/>
+      <c r="AB33" s="49"/>
+      <c r="AC33" s="49"/>
+      <c r="AD33" s="53"/>
+      <c r="AE33" s="54"/>
+      <c r="AF33" s="55"/>
+      <c r="AG33" s="49"/>
+      <c r="AH33" s="49"/>
+      <c r="AI33" s="49"/>
+      <c r="AJ33" s="49"/>
+      <c r="AK33" s="49"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="61" t="s">
-        <v>118</v>
-      </c>
-      <c r="C34" s="70" t="s">
-        <v>119</v>
-      </c>
-      <c r="D34" s="64"/>
-      <c r="E34" s="64"/>
-      <c r="F34" s="67"/>
-      <c r="G34" s="65"/>
-      <c r="H34" s="63"/>
-      <c r="I34" s="64"/>
-      <c r="J34" s="64"/>
-      <c r="K34" s="64"/>
-      <c r="L34" s="49"/>
-      <c r="M34" s="59"/>
-      <c r="N34" s="47"/>
-      <c r="O34" s="48"/>
-      <c r="P34" s="59"/>
-      <c r="Q34" s="59"/>
-      <c r="R34" s="59"/>
-      <c r="S34" s="64"/>
-      <c r="T34" s="64"/>
-      <c r="U34" s="64"/>
-      <c r="V34" s="65"/>
-      <c r="W34" s="52"/>
-      <c r="X34" s="64"/>
-      <c r="Y34" s="64"/>
-      <c r="Z34" s="65"/>
-      <c r="AA34" s="63"/>
-      <c r="AB34" s="64"/>
-      <c r="AC34" s="64"/>
-      <c r="AD34" s="49"/>
-      <c r="AE34" s="65"/>
-      <c r="AF34" s="63"/>
-      <c r="AG34" s="64"/>
-      <c r="AH34" s="64"/>
-      <c r="AI34" s="64"/>
-      <c r="AJ34" s="64"/>
-      <c r="AK34" s="64"/>
+      <c r="B34" s="65" t="s">
+        <v>121</v>
+      </c>
+      <c r="C34" s="74" t="s">
+        <v>122</v>
+      </c>
+      <c r="D34" s="68"/>
+      <c r="E34" s="68"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="69"/>
+      <c r="H34" s="67"/>
+      <c r="I34" s="68"/>
+      <c r="J34" s="68"/>
+      <c r="K34" s="68"/>
+      <c r="L34" s="53"/>
+      <c r="M34" s="63"/>
+      <c r="N34" s="51"/>
+      <c r="O34" s="52"/>
+      <c r="P34" s="63"/>
+      <c r="Q34" s="63"/>
+      <c r="R34" s="63"/>
+      <c r="S34" s="68"/>
+      <c r="T34" s="68"/>
+      <c r="U34" s="68"/>
+      <c r="V34" s="69"/>
+      <c r="W34" s="56"/>
+      <c r="X34" s="68"/>
+      <c r="Y34" s="68"/>
+      <c r="Z34" s="69"/>
+      <c r="AA34" s="67"/>
+      <c r="AB34" s="68"/>
+      <c r="AC34" s="68"/>
+      <c r="AD34" s="53"/>
+      <c r="AE34" s="69"/>
+      <c r="AF34" s="67"/>
+      <c r="AG34" s="68"/>
+      <c r="AH34" s="68"/>
+      <c r="AI34" s="68"/>
+      <c r="AJ34" s="68"/>
+      <c r="AK34" s="68"/>
     </row>
     <row r="35" ht="12" customHeight="1">
-      <c r="B35" s="61"/>
-      <c r="C35" s="70"/>
-      <c r="D35" s="64"/>
-      <c r="E35" s="64"/>
-      <c r="F35" s="67"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="63"/>
-      <c r="I35" s="64"/>
-      <c r="J35" s="64"/>
-      <c r="K35" s="71"/>
-      <c r="L35" s="49"/>
-      <c r="M35" s="64"/>
-      <c r="N35" s="56"/>
-      <c r="O35" s="63"/>
-      <c r="P35" s="58"/>
-      <c r="Q35" s="64"/>
-      <c r="R35" s="72"/>
-      <c r="S35" s="72"/>
-      <c r="T35" s="64"/>
-      <c r="U35" s="64"/>
-      <c r="V35" s="65"/>
-      <c r="W35" s="52"/>
-      <c r="X35" s="64"/>
-      <c r="Y35" s="64"/>
-      <c r="Z35" s="65"/>
-      <c r="AA35" s="63"/>
-      <c r="AB35" s="64"/>
-      <c r="AC35" s="64"/>
-      <c r="AD35" s="49"/>
-      <c r="AE35" s="65"/>
-      <c r="AF35" s="63"/>
-      <c r="AG35" s="64"/>
-      <c r="AH35" s="64"/>
-      <c r="AI35" s="64"/>
-      <c r="AJ35" s="64"/>
-      <c r="AK35" s="64"/>
+      <c r="B35" s="65"/>
+      <c r="C35" s="74"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="67"/>
+      <c r="I35" s="68"/>
+      <c r="J35" s="68"/>
+      <c r="K35" s="75"/>
+      <c r="L35" s="53"/>
+      <c r="M35" s="68"/>
+      <c r="N35" s="60"/>
+      <c r="O35" s="67"/>
+      <c r="P35" s="62"/>
+      <c r="Q35" s="68"/>
+      <c r="R35" s="76"/>
+      <c r="S35" s="76"/>
+      <c r="T35" s="68"/>
+      <c r="U35" s="68"/>
+      <c r="V35" s="69"/>
+      <c r="W35" s="56"/>
+      <c r="X35" s="68"/>
+      <c r="Y35" s="68"/>
+      <c r="Z35" s="69"/>
+      <c r="AA35" s="67"/>
+      <c r="AB35" s="68"/>
+      <c r="AC35" s="68"/>
+      <c r="AD35" s="53"/>
+      <c r="AE35" s="69"/>
+      <c r="AF35" s="67"/>
+      <c r="AG35" s="68"/>
+      <c r="AH35" s="68"/>
+      <c r="AI35" s="68"/>
+      <c r="AJ35" s="68"/>
+      <c r="AK35" s="68"/>
     </row>
     <row r="36" ht="12" customHeight="1">
-      <c r="B36" s="61"/>
-      <c r="C36" s="70" t="s">
-        <v>120</v>
-      </c>
-      <c r="D36" s="64"/>
-      <c r="E36" s="64"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="65"/>
-      <c r="H36" s="63"/>
-      <c r="I36" s="64"/>
-      <c r="J36" s="64"/>
-      <c r="K36" s="64"/>
-      <c r="L36" s="49"/>
-      <c r="M36" s="59"/>
-      <c r="N36" s="47"/>
-      <c r="O36" s="48"/>
-      <c r="P36" s="59"/>
-      <c r="Q36" s="64"/>
-      <c r="R36" s="64"/>
-      <c r="S36" s="64"/>
-      <c r="T36" s="64"/>
-      <c r="U36" s="64"/>
-      <c r="V36" s="65"/>
-      <c r="W36" s="52"/>
-      <c r="X36" s="64"/>
-      <c r="Y36" s="64"/>
-      <c r="Z36" s="65"/>
-      <c r="AA36" s="63"/>
-      <c r="AB36" s="64"/>
-      <c r="AC36" s="64"/>
-      <c r="AD36" s="49"/>
-      <c r="AE36" s="65"/>
-      <c r="AF36" s="63"/>
-      <c r="AG36" s="64"/>
-      <c r="AH36" s="64"/>
-      <c r="AI36" s="64"/>
-      <c r="AJ36" s="64"/>
-      <c r="AK36" s="64"/>
+      <c r="B36" s="65"/>
+      <c r="C36" s="74" t="s">
+        <v>123</v>
+      </c>
+      <c r="D36" s="68"/>
+      <c r="E36" s="68"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="69"/>
+      <c r="H36" s="67"/>
+      <c r="I36" s="68"/>
+      <c r="J36" s="68"/>
+      <c r="K36" s="68"/>
+      <c r="L36" s="53"/>
+      <c r="M36" s="63"/>
+      <c r="N36" s="51"/>
+      <c r="O36" s="52"/>
+      <c r="P36" s="63"/>
+      <c r="Q36" s="68"/>
+      <c r="R36" s="68"/>
+      <c r="S36" s="68"/>
+      <c r="T36" s="68"/>
+      <c r="U36" s="68"/>
+      <c r="V36" s="69"/>
+      <c r="W36" s="56"/>
+      <c r="X36" s="68"/>
+      <c r="Y36" s="68"/>
+      <c r="Z36" s="69"/>
+      <c r="AA36" s="67"/>
+      <c r="AB36" s="68"/>
+      <c r="AC36" s="68"/>
+      <c r="AD36" s="53"/>
+      <c r="AE36" s="69"/>
+      <c r="AF36" s="67"/>
+      <c r="AG36" s="68"/>
+      <c r="AH36" s="68"/>
+      <c r="AI36" s="68"/>
+      <c r="AJ36" s="68"/>
+      <c r="AK36" s="68"/>
     </row>
     <row r="37" ht="12" customHeight="1">
-      <c r="B37" s="61"/>
-      <c r="C37" s="70"/>
-      <c r="D37" s="64"/>
-      <c r="E37" s="64"/>
-      <c r="F37" s="67"/>
-      <c r="G37" s="65"/>
-      <c r="H37" s="63"/>
-      <c r="I37" s="64"/>
-      <c r="J37" s="64"/>
-      <c r="K37" s="71"/>
-      <c r="L37" s="49"/>
-      <c r="M37" s="64"/>
-      <c r="N37" s="65"/>
-      <c r="O37" s="63"/>
-      <c r="P37" s="58"/>
-      <c r="Q37" s="64"/>
-      <c r="R37" s="72"/>
-      <c r="S37" s="72"/>
-      <c r="T37" s="64"/>
-      <c r="U37" s="64"/>
-      <c r="V37" s="65"/>
-      <c r="W37" s="52"/>
-      <c r="X37" s="64"/>
-      <c r="Y37" s="64"/>
-      <c r="Z37" s="65"/>
-      <c r="AA37" s="63"/>
-      <c r="AB37" s="64"/>
-      <c r="AC37" s="64"/>
-      <c r="AD37" s="49"/>
-      <c r="AE37" s="65"/>
-      <c r="AF37" s="63"/>
-      <c r="AG37" s="64"/>
-      <c r="AH37" s="64"/>
-      <c r="AI37" s="64"/>
-      <c r="AJ37" s="64"/>
-      <c r="AK37" s="64"/>
+      <c r="B37" s="65"/>
+      <c r="C37" s="74"/>
+      <c r="D37" s="68"/>
+      <c r="E37" s="68"/>
+      <c r="F37" s="71"/>
+      <c r="G37" s="69"/>
+      <c r="H37" s="67"/>
+      <c r="I37" s="68"/>
+      <c r="J37" s="68"/>
+      <c r="K37" s="75"/>
+      <c r="L37" s="53"/>
+      <c r="M37" s="68"/>
+      <c r="N37" s="69"/>
+      <c r="O37" s="67"/>
+      <c r="P37" s="62"/>
+      <c r="Q37" s="68"/>
+      <c r="R37" s="76"/>
+      <c r="S37" s="76"/>
+      <c r="T37" s="68"/>
+      <c r="U37" s="68"/>
+      <c r="V37" s="69"/>
+      <c r="W37" s="56"/>
+      <c r="X37" s="68"/>
+      <c r="Y37" s="68"/>
+      <c r="Z37" s="69"/>
+      <c r="AA37" s="67"/>
+      <c r="AB37" s="68"/>
+      <c r="AC37" s="68"/>
+      <c r="AD37" s="53"/>
+      <c r="AE37" s="69"/>
+      <c r="AF37" s="67"/>
+      <c r="AG37" s="68"/>
+      <c r="AH37" s="68"/>
+      <c r="AI37" s="68"/>
+      <c r="AJ37" s="68"/>
+      <c r="AK37" s="68"/>
     </row>
     <row r="38" ht="12" customHeight="1">
-      <c r="B38" s="61"/>
-      <c r="C38" s="70" t="s">
-        <v>121</v>
-      </c>
-      <c r="D38" s="64"/>
-      <c r="E38" s="64"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="65"/>
-      <c r="H38" s="63"/>
-      <c r="I38" s="64"/>
-      <c r="J38" s="64"/>
-      <c r="K38" s="64"/>
-      <c r="L38" s="49"/>
-      <c r="M38" s="64"/>
-      <c r="N38" s="65"/>
-      <c r="O38" s="48"/>
-      <c r="P38" s="59"/>
-      <c r="Q38" s="59"/>
-      <c r="R38" s="59"/>
-      <c r="S38" s="59"/>
-      <c r="T38" s="59"/>
-      <c r="U38" s="59"/>
-      <c r="V38" s="47"/>
-      <c r="W38" s="52"/>
-      <c r="X38" s="59"/>
-      <c r="Y38" s="59"/>
-      <c r="Z38" s="65"/>
-      <c r="AA38" s="63"/>
-      <c r="AB38" s="64"/>
-      <c r="AC38" s="64"/>
-      <c r="AD38" s="49"/>
-      <c r="AE38" s="65"/>
-      <c r="AF38" s="63"/>
-      <c r="AG38" s="64"/>
-      <c r="AH38" s="64"/>
-      <c r="AI38" s="64"/>
-      <c r="AJ38" s="64"/>
-      <c r="AK38" s="64"/>
+      <c r="B38" s="65"/>
+      <c r="C38" s="74" t="s">
+        <v>124</v>
+      </c>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="69"/>
+      <c r="H38" s="67"/>
+      <c r="I38" s="68"/>
+      <c r="J38" s="68"/>
+      <c r="K38" s="68"/>
+      <c r="L38" s="53"/>
+      <c r="M38" s="68"/>
+      <c r="N38" s="69"/>
+      <c r="O38" s="52"/>
+      <c r="P38" s="63"/>
+      <c r="Q38" s="63"/>
+      <c r="R38" s="63"/>
+      <c r="S38" s="63"/>
+      <c r="T38" s="63"/>
+      <c r="U38" s="63"/>
+      <c r="V38" s="51"/>
+      <c r="W38" s="56"/>
+      <c r="X38" s="63"/>
+      <c r="Y38" s="63"/>
+      <c r="Z38" s="69"/>
+      <c r="AA38" s="67"/>
+      <c r="AB38" s="68"/>
+      <c r="AC38" s="68"/>
+      <c r="AD38" s="53"/>
+      <c r="AE38" s="69"/>
+      <c r="AF38" s="67"/>
+      <c r="AG38" s="68"/>
+      <c r="AH38" s="68"/>
+      <c r="AI38" s="68"/>
+      <c r="AJ38" s="68"/>
+      <c r="AK38" s="68"/>
     </row>
     <row r="39" ht="12" customHeight="1">
-      <c r="B39" s="61"/>
-      <c r="C39" s="70"/>
-      <c r="D39" s="64"/>
-      <c r="E39" s="64"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="65"/>
-      <c r="H39" s="63"/>
-      <c r="I39" s="64"/>
-      <c r="J39" s="64"/>
-      <c r="K39" s="64"/>
-      <c r="L39" s="49"/>
-      <c r="M39" s="64"/>
-      <c r="N39" s="65"/>
-      <c r="O39" s="63"/>
-      <c r="P39" s="58"/>
-      <c r="Q39" s="58"/>
-      <c r="R39" s="71"/>
-      <c r="S39" s="71"/>
-      <c r="T39" s="64"/>
-      <c r="U39" s="64"/>
-      <c r="V39" s="65"/>
-      <c r="W39" s="52"/>
-      <c r="X39" s="64"/>
-      <c r="Y39" s="64"/>
-      <c r="Z39" s="65"/>
-      <c r="AA39" s="63"/>
-      <c r="AB39" s="64"/>
-      <c r="AC39" s="64"/>
-      <c r="AD39" s="49"/>
-      <c r="AE39" s="65"/>
-      <c r="AF39" s="63"/>
-      <c r="AG39" s="64"/>
-      <c r="AH39" s="64"/>
-      <c r="AI39" s="64"/>
-      <c r="AJ39" s="64"/>
-      <c r="AK39" s="64"/>
+      <c r="B39" s="65"/>
+      <c r="C39" s="74"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="68"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="69"/>
+      <c r="H39" s="67"/>
+      <c r="I39" s="68"/>
+      <c r="J39" s="68"/>
+      <c r="K39" s="68"/>
+      <c r="L39" s="53"/>
+      <c r="M39" s="68"/>
+      <c r="N39" s="69"/>
+      <c r="O39" s="67"/>
+      <c r="P39" s="62"/>
+      <c r="Q39" s="62"/>
+      <c r="R39" s="75"/>
+      <c r="S39" s="75"/>
+      <c r="T39" s="68"/>
+      <c r="U39" s="68"/>
+      <c r="V39" s="69"/>
+      <c r="W39" s="56"/>
+      <c r="X39" s="68"/>
+      <c r="Y39" s="68"/>
+      <c r="Z39" s="69"/>
+      <c r="AA39" s="67"/>
+      <c r="AB39" s="68"/>
+      <c r="AC39" s="68"/>
+      <c r="AD39" s="53"/>
+      <c r="AE39" s="69"/>
+      <c r="AF39" s="67"/>
+      <c r="AG39" s="68"/>
+      <c r="AH39" s="68"/>
+      <c r="AI39" s="68"/>
+      <c r="AJ39" s="68"/>
+      <c r="AK39" s="68"/>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="B40" s="61"/>
-      <c r="C40" s="70" t="s">
-        <v>122</v>
-      </c>
-      <c r="D40" s="64"/>
-      <c r="E40" s="64"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="65"/>
-      <c r="H40" s="63"/>
-      <c r="I40" s="64"/>
-      <c r="J40" s="64"/>
-      <c r="K40" s="64"/>
-      <c r="L40" s="49"/>
-      <c r="M40" s="64"/>
-      <c r="N40" s="65"/>
-      <c r="O40" s="63"/>
-      <c r="P40" s="64"/>
-      <c r="Q40" s="64"/>
-      <c r="R40" s="59"/>
-      <c r="S40" s="59"/>
-      <c r="T40" s="59"/>
-      <c r="U40" s="59"/>
-      <c r="V40" s="47"/>
-      <c r="W40" s="52"/>
-      <c r="X40" s="59"/>
-      <c r="Y40" s="59"/>
-      <c r="Z40" s="47"/>
-      <c r="AA40" s="48"/>
-      <c r="AB40" s="59"/>
-      <c r="AC40" s="59"/>
-      <c r="AD40" s="49"/>
-      <c r="AE40" s="65"/>
-      <c r="AF40" s="63"/>
-      <c r="AG40" s="64"/>
-      <c r="AH40" s="64"/>
-      <c r="AI40" s="64"/>
-      <c r="AJ40" s="64"/>
-      <c r="AK40" s="64"/>
+      <c r="B40" s="65"/>
+      <c r="C40" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="D40" s="68"/>
+      <c r="E40" s="68"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="69"/>
+      <c r="H40" s="67"/>
+      <c r="I40" s="68"/>
+      <c r="J40" s="68"/>
+      <c r="K40" s="68"/>
+      <c r="L40" s="53"/>
+      <c r="M40" s="68"/>
+      <c r="N40" s="69"/>
+      <c r="O40" s="67"/>
+      <c r="P40" s="68"/>
+      <c r="Q40" s="68"/>
+      <c r="R40" s="63"/>
+      <c r="S40" s="63"/>
+      <c r="T40" s="63"/>
+      <c r="U40" s="63"/>
+      <c r="V40" s="51"/>
+      <c r="W40" s="56"/>
+      <c r="X40" s="63"/>
+      <c r="Y40" s="63"/>
+      <c r="Z40" s="51"/>
+      <c r="AA40" s="52"/>
+      <c r="AB40" s="63"/>
+      <c r="AC40" s="63"/>
+      <c r="AD40" s="53"/>
+      <c r="AE40" s="69"/>
+      <c r="AF40" s="67"/>
+      <c r="AG40" s="68"/>
+      <c r="AH40" s="68"/>
+      <c r="AI40" s="68"/>
+      <c r="AJ40" s="68"/>
+      <c r="AK40" s="68"/>
     </row>
     <row r="41" ht="12" customHeight="1">
-      <c r="B41" s="61"/>
-      <c r="C41" s="70"/>
-      <c r="D41" s="64"/>
-      <c r="E41" s="64"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="65"/>
-      <c r="H41" s="63"/>
-      <c r="I41" s="64"/>
-      <c r="J41" s="64"/>
-      <c r="K41" s="64"/>
-      <c r="L41" s="49"/>
-      <c r="M41" s="64"/>
-      <c r="N41" s="65"/>
-      <c r="O41" s="63"/>
-      <c r="P41" s="64"/>
-      <c r="Q41" s="58"/>
-      <c r="R41" s="71"/>
-      <c r="S41" s="71"/>
-      <c r="T41" s="64"/>
-      <c r="U41" s="64"/>
-      <c r="V41" s="65"/>
-      <c r="W41" s="52"/>
-      <c r="X41" s="64"/>
-      <c r="Y41" s="64"/>
-      <c r="Z41" s="65"/>
-      <c r="AA41" s="63"/>
-      <c r="AB41" s="64"/>
-      <c r="AC41" s="64"/>
-      <c r="AD41" s="49"/>
-      <c r="AE41" s="65"/>
-      <c r="AF41" s="63"/>
-      <c r="AG41" s="64"/>
-      <c r="AH41" s="64"/>
-      <c r="AI41" s="64"/>
-      <c r="AJ41" s="64"/>
-      <c r="AK41" s="64"/>
+      <c r="B41" s="65"/>
+      <c r="C41" s="74"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="71"/>
+      <c r="G41" s="69"/>
+      <c r="H41" s="67"/>
+      <c r="I41" s="68"/>
+      <c r="J41" s="68"/>
+      <c r="K41" s="68"/>
+      <c r="L41" s="53"/>
+      <c r="M41" s="68"/>
+      <c r="N41" s="69"/>
+      <c r="O41" s="67"/>
+      <c r="P41" s="68"/>
+      <c r="Q41" s="62"/>
+      <c r="R41" s="75"/>
+      <c r="S41" s="75"/>
+      <c r="T41" s="68"/>
+      <c r="U41" s="68"/>
+      <c r="V41" s="69"/>
+      <c r="W41" s="56"/>
+      <c r="X41" s="68"/>
+      <c r="Y41" s="68"/>
+      <c r="Z41" s="69"/>
+      <c r="AA41" s="67"/>
+      <c r="AB41" s="68"/>
+      <c r="AC41" s="68"/>
+      <c r="AD41" s="53"/>
+      <c r="AE41" s="69"/>
+      <c r="AF41" s="67"/>
+      <c r="AG41" s="68"/>
+      <c r="AH41" s="68"/>
+      <c r="AI41" s="68"/>
+      <c r="AJ41" s="68"/>
+      <c r="AK41" s="68"/>
     </row>
     <row r="42" ht="12" customHeight="1">
-      <c r="B42" s="43" t="s">
+      <c r="B42" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="73" t="s">
-        <v>123</v>
-      </c>
-      <c r="D42" s="45"/>
-      <c r="E42" s="45"/>
-      <c r="F42" s="53"/>
-      <c r="G42" s="50"/>
-      <c r="H42" s="51"/>
-      <c r="I42" s="45"/>
-      <c r="J42" s="45"/>
-      <c r="K42" s="45"/>
-      <c r="L42" s="49"/>
-      <c r="M42" s="45"/>
-      <c r="N42" s="50"/>
-      <c r="O42" s="51"/>
-      <c r="P42" s="59"/>
-      <c r="Q42" s="59"/>
-      <c r="R42" s="45"/>
-      <c r="S42" s="45"/>
-      <c r="T42" s="45"/>
-      <c r="U42" s="45"/>
-      <c r="V42" s="47"/>
-      <c r="W42" s="52"/>
-      <c r="X42" s="59"/>
-      <c r="Y42" s="59"/>
-      <c r="Z42" s="47"/>
-      <c r="AA42" s="48"/>
-      <c r="AB42" s="59"/>
-      <c r="AC42" s="59"/>
-      <c r="AD42" s="49"/>
-      <c r="AE42" s="50"/>
-      <c r="AF42" s="51"/>
-      <c r="AG42" s="45"/>
-      <c r="AH42" s="45"/>
-      <c r="AI42" s="45"/>
-      <c r="AJ42" s="45"/>
-      <c r="AK42" s="45"/>
+      <c r="C42" s="77" t="s">
+        <v>126</v>
+      </c>
+      <c r="D42" s="49"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="49"/>
+      <c r="J42" s="49"/>
+      <c r="K42" s="49"/>
+      <c r="L42" s="53"/>
+      <c r="M42" s="49"/>
+      <c r="N42" s="54"/>
+      <c r="O42" s="55"/>
+      <c r="P42" s="63"/>
+      <c r="Q42" s="63"/>
+      <c r="R42" s="49"/>
+      <c r="S42" s="49"/>
+      <c r="T42" s="49"/>
+      <c r="U42" s="49"/>
+      <c r="V42" s="51"/>
+      <c r="W42" s="56"/>
+      <c r="X42" s="63"/>
+      <c r="Y42" s="63"/>
+      <c r="Z42" s="51"/>
+      <c r="AA42" s="52"/>
+      <c r="AB42" s="63"/>
+      <c r="AC42" s="63"/>
+      <c r="AD42" s="53"/>
+      <c r="AE42" s="54"/>
+      <c r="AF42" s="55"/>
+      <c r="AG42" s="49"/>
+      <c r="AH42" s="49"/>
+      <c r="AI42" s="49"/>
+      <c r="AJ42" s="49"/>
+      <c r="AK42" s="49"/>
     </row>
     <row r="43" ht="12" customHeight="1">
-      <c r="B43" s="43"/>
-      <c r="C43" s="73"/>
-      <c r="D43" s="45"/>
-      <c r="E43" s="45"/>
-      <c r="F43" s="53"/>
-      <c r="G43" s="50"/>
-      <c r="H43" s="51"/>
-      <c r="I43" s="45"/>
-      <c r="J43" s="45"/>
-      <c r="K43" s="45"/>
-      <c r="L43" s="49"/>
-      <c r="M43" s="45"/>
-      <c r="N43" s="50"/>
-      <c r="O43" s="51"/>
-      <c r="P43" s="45"/>
-      <c r="Q43" s="58"/>
-      <c r="R43" s="45"/>
-      <c r="S43" s="60"/>
-      <c r="T43" s="45"/>
-      <c r="U43" s="45"/>
-      <c r="V43" s="50"/>
-      <c r="W43" s="52"/>
-      <c r="X43" s="45"/>
-      <c r="Y43" s="45"/>
-      <c r="Z43" s="50"/>
-      <c r="AA43" s="51"/>
-      <c r="AB43" s="45"/>
-      <c r="AC43" s="45"/>
-      <c r="AD43" s="49"/>
-      <c r="AE43" s="50"/>
-      <c r="AF43" s="51"/>
-      <c r="AG43" s="45"/>
-      <c r="AH43" s="45"/>
-      <c r="AI43" s="45"/>
-      <c r="AJ43" s="45"/>
-      <c r="AK43" s="45"/>
+      <c r="B43" s="47"/>
+      <c r="C43" s="77"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="57"/>
+      <c r="G43" s="54"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="49"/>
+      <c r="J43" s="49"/>
+      <c r="K43" s="49"/>
+      <c r="L43" s="53"/>
+      <c r="M43" s="49"/>
+      <c r="N43" s="54"/>
+      <c r="O43" s="55"/>
+      <c r="P43" s="49"/>
+      <c r="Q43" s="62"/>
+      <c r="R43" s="49"/>
+      <c r="S43" s="64"/>
+      <c r="T43" s="49"/>
+      <c r="U43" s="49"/>
+      <c r="V43" s="54"/>
+      <c r="W43" s="56"/>
+      <c r="X43" s="49"/>
+      <c r="Y43" s="49"/>
+      <c r="Z43" s="54"/>
+      <c r="AA43" s="55"/>
+      <c r="AB43" s="49"/>
+      <c r="AC43" s="49"/>
+      <c r="AD43" s="53"/>
+      <c r="AE43" s="54"/>
+      <c r="AF43" s="55"/>
+      <c r="AG43" s="49"/>
+      <c r="AH43" s="49"/>
+      <c r="AI43" s="49"/>
+      <c r="AJ43" s="49"/>
+      <c r="AK43" s="49"/>
     </row>
     <row r="44" ht="12" customHeight="1">
-      <c r="B44" s="43"/>
-      <c r="C44" s="73" t="s">
-        <v>124</v>
-      </c>
-      <c r="D44" s="45"/>
-      <c r="E44" s="45"/>
-      <c r="F44" s="53"/>
-      <c r="G44" s="50"/>
-      <c r="H44" s="51"/>
-      <c r="I44" s="45"/>
-      <c r="J44" s="45"/>
-      <c r="K44" s="45"/>
-      <c r="L44" s="49"/>
-      <c r="M44" s="45"/>
-      <c r="N44" s="50"/>
-      <c r="O44" s="51"/>
-      <c r="P44" s="59"/>
-      <c r="Q44" s="59"/>
-      <c r="R44" s="45"/>
-      <c r="S44" s="45"/>
-      <c r="T44" s="45"/>
-      <c r="U44" s="45"/>
-      <c r="V44" s="50"/>
-      <c r="W44" s="52"/>
-      <c r="X44" s="59"/>
-      <c r="Y44" s="59"/>
-      <c r="Z44" s="50"/>
-      <c r="AA44" s="51"/>
-      <c r="AB44" s="45"/>
-      <c r="AC44" s="59"/>
-      <c r="AD44" s="49"/>
-      <c r="AE44" s="47"/>
-      <c r="AF44" s="48"/>
-      <c r="AG44" s="45"/>
-      <c r="AH44" s="45"/>
-      <c r="AI44" s="59"/>
-      <c r="AJ44" s="45"/>
-      <c r="AK44" s="45"/>
+      <c r="B44" s="47"/>
+      <c r="C44" s="77" t="s">
+        <v>127</v>
+      </c>
+      <c r="D44" s="49"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="49"/>
+      <c r="J44" s="49"/>
+      <c r="K44" s="49"/>
+      <c r="L44" s="53"/>
+      <c r="M44" s="49"/>
+      <c r="N44" s="54"/>
+      <c r="O44" s="55"/>
+      <c r="P44" s="63"/>
+      <c r="Q44" s="63"/>
+      <c r="R44" s="49"/>
+      <c r="S44" s="49"/>
+      <c r="T44" s="49"/>
+      <c r="U44" s="49"/>
+      <c r="V44" s="54"/>
+      <c r="W44" s="56"/>
+      <c r="X44" s="63"/>
+      <c r="Y44" s="63"/>
+      <c r="Z44" s="54"/>
+      <c r="AA44" s="55"/>
+      <c r="AB44" s="49"/>
+      <c r="AC44" s="63"/>
+      <c r="AD44" s="53"/>
+      <c r="AE44" s="51"/>
+      <c r="AF44" s="52"/>
+      <c r="AG44" s="49"/>
+      <c r="AH44" s="49"/>
+      <c r="AI44" s="63"/>
+      <c r="AJ44" s="49"/>
+      <c r="AK44" s="49"/>
     </row>
     <row r="45" ht="12" customHeight="1">
-      <c r="B45" s="43"/>
-      <c r="C45" s="73"/>
-      <c r="D45" s="45"/>
-      <c r="E45" s="45"/>
-      <c r="F45" s="53"/>
-      <c r="G45" s="50"/>
-      <c r="H45" s="51"/>
-      <c r="I45" s="45"/>
-      <c r="J45" s="45"/>
-      <c r="K45" s="45"/>
-      <c r="L45" s="49"/>
-      <c r="M45" s="45"/>
-      <c r="N45" s="50"/>
-      <c r="O45" s="51"/>
-      <c r="P45" s="45"/>
-      <c r="Q45" s="45"/>
-      <c r="R45" s="45"/>
-      <c r="S45" s="45"/>
-      <c r="T45" s="45"/>
-      <c r="U45" s="45"/>
-      <c r="V45" s="50"/>
-      <c r="W45" s="52"/>
-      <c r="X45" s="45"/>
-      <c r="Y45" s="45"/>
-      <c r="Z45" s="50"/>
-      <c r="AA45" s="51"/>
-      <c r="AB45" s="45"/>
-      <c r="AC45" s="45"/>
-      <c r="AD45" s="49"/>
-      <c r="AE45" s="50"/>
-      <c r="AF45" s="51"/>
-      <c r="AG45" s="45"/>
-      <c r="AH45" s="45"/>
-      <c r="AI45" s="45"/>
-      <c r="AJ45" s="45"/>
-      <c r="AK45" s="45"/>
+      <c r="B45" s="47"/>
+      <c r="C45" s="77"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="49"/>
+      <c r="J45" s="49"/>
+      <c r="K45" s="49"/>
+      <c r="L45" s="53"/>
+      <c r="M45" s="49"/>
+      <c r="N45" s="54"/>
+      <c r="O45" s="55"/>
+      <c r="P45" s="49"/>
+      <c r="Q45" s="49"/>
+      <c r="R45" s="49"/>
+      <c r="S45" s="49"/>
+      <c r="T45" s="49"/>
+      <c r="U45" s="49"/>
+      <c r="V45" s="54"/>
+      <c r="W45" s="56"/>
+      <c r="X45" s="49"/>
+      <c r="Y45" s="49"/>
+      <c r="Z45" s="54"/>
+      <c r="AA45" s="55"/>
+      <c r="AB45" s="49"/>
+      <c r="AC45" s="49"/>
+      <c r="AD45" s="53"/>
+      <c r="AE45" s="54"/>
+      <c r="AF45" s="55"/>
+      <c r="AG45" s="49"/>
+      <c r="AH45" s="49"/>
+      <c r="AI45" s="49"/>
+      <c r="AJ45" s="49"/>
+      <c r="AK45" s="49"/>
     </row>
     <row r="46" ht="12" customHeight="1">
-      <c r="B46" s="61" t="s">
-        <v>125</v>
-      </c>
-      <c r="C46" s="62" t="s">
+      <c r="B46" s="65" t="s">
+        <v>128</v>
+      </c>
+      <c r="C46" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="D46" s="64"/>
-      <c r="E46" s="64"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="65"/>
-      <c r="H46" s="63"/>
-      <c r="I46" s="64"/>
-      <c r="J46" s="64"/>
-      <c r="K46" s="64"/>
-      <c r="L46" s="49"/>
-      <c r="M46" s="64"/>
-      <c r="N46" s="65"/>
-      <c r="O46" s="63"/>
-      <c r="P46" s="64"/>
-      <c r="Q46" s="64"/>
-      <c r="R46" s="64"/>
-      <c r="S46" s="64"/>
-      <c r="T46" s="64"/>
-      <c r="U46" s="64"/>
-      <c r="V46" s="65"/>
-      <c r="W46" s="52"/>
-      <c r="X46" s="64"/>
-      <c r="Y46" s="64"/>
-      <c r="Z46" s="65"/>
-      <c r="AA46" s="63"/>
-      <c r="AB46" s="64"/>
-      <c r="AC46" s="64"/>
-      <c r="AD46" s="49"/>
-      <c r="AE46" s="65"/>
-      <c r="AF46" s="63"/>
-      <c r="AG46" s="64"/>
-      <c r="AH46" s="64"/>
-      <c r="AI46" s="64"/>
-      <c r="AJ46" s="59"/>
-      <c r="AK46" s="64"/>
+      <c r="D46" s="68"/>
+      <c r="E46" s="68"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="69"/>
+      <c r="H46" s="67"/>
+      <c r="I46" s="68"/>
+      <c r="J46" s="68"/>
+      <c r="K46" s="68"/>
+      <c r="L46" s="53"/>
+      <c r="M46" s="68"/>
+      <c r="N46" s="69"/>
+      <c r="O46" s="67"/>
+      <c r="P46" s="68"/>
+      <c r="Q46" s="68"/>
+      <c r="R46" s="68"/>
+      <c r="S46" s="68"/>
+      <c r="T46" s="68"/>
+      <c r="U46" s="68"/>
+      <c r="V46" s="69"/>
+      <c r="W46" s="56"/>
+      <c r="X46" s="68"/>
+      <c r="Y46" s="68"/>
+      <c r="Z46" s="69"/>
+      <c r="AA46" s="67"/>
+      <c r="AB46" s="68"/>
+      <c r="AC46" s="68"/>
+      <c r="AD46" s="53"/>
+      <c r="AE46" s="69"/>
+      <c r="AF46" s="67"/>
+      <c r="AG46" s="68"/>
+      <c r="AH46" s="68"/>
+      <c r="AI46" s="68"/>
+      <c r="AJ46" s="63"/>
+      <c r="AK46" s="68"/>
     </row>
     <row r="47" ht="12" customHeight="1">
-      <c r="B47" s="61"/>
-      <c r="C47" s="62"/>
-      <c r="D47" s="64"/>
-      <c r="E47" s="64"/>
-      <c r="F47" s="67"/>
-      <c r="G47" s="65"/>
-      <c r="H47" s="63"/>
-      <c r="I47" s="64"/>
-      <c r="J47" s="64"/>
-      <c r="K47" s="64"/>
-      <c r="L47" s="49"/>
-      <c r="M47" s="64"/>
-      <c r="N47" s="65"/>
-      <c r="O47" s="63"/>
-      <c r="P47" s="64"/>
-      <c r="Q47" s="64"/>
-      <c r="R47" s="64"/>
-      <c r="S47" s="64"/>
-      <c r="T47" s="64"/>
-      <c r="U47" s="64"/>
-      <c r="V47" s="65"/>
-      <c r="W47" s="52"/>
-      <c r="X47" s="64"/>
-      <c r="Y47" s="64"/>
-      <c r="Z47" s="65"/>
-      <c r="AA47" s="63"/>
-      <c r="AB47" s="64"/>
-      <c r="AC47" s="64"/>
-      <c r="AD47" s="49"/>
-      <c r="AE47" s="65"/>
-      <c r="AF47" s="63"/>
-      <c r="AG47" s="64"/>
-      <c r="AH47" s="64"/>
-      <c r="AI47" s="64"/>
-      <c r="AJ47" s="64"/>
-      <c r="AK47" s="64"/>
-      <c r="AN47" s="74" t="s">
-        <v>126</v>
-      </c>
-      <c r="AO47" s="59"/>
+      <c r="B47" s="65"/>
+      <c r="C47" s="66"/>
+      <c r="D47" s="68"/>
+      <c r="E47" s="68"/>
+      <c r="F47" s="71"/>
+      <c r="G47" s="69"/>
+      <c r="H47" s="67"/>
+      <c r="I47" s="68"/>
+      <c r="J47" s="68"/>
+      <c r="K47" s="68"/>
+      <c r="L47" s="53"/>
+      <c r="M47" s="68"/>
+      <c r="N47" s="69"/>
+      <c r="O47" s="67"/>
+      <c r="P47" s="68"/>
+      <c r="Q47" s="68"/>
+      <c r="R47" s="68"/>
+      <c r="S47" s="68"/>
+      <c r="T47" s="68"/>
+      <c r="U47" s="68"/>
+      <c r="V47" s="69"/>
+      <c r="W47" s="56"/>
+      <c r="X47" s="68"/>
+      <c r="Y47" s="68"/>
+      <c r="Z47" s="69"/>
+      <c r="AA47" s="67"/>
+      <c r="AB47" s="68"/>
+      <c r="AC47" s="68"/>
+      <c r="AD47" s="53"/>
+      <c r="AE47" s="69"/>
+      <c r="AF47" s="67"/>
+      <c r="AG47" s="68"/>
+      <c r="AH47" s="68"/>
+      <c r="AI47" s="68"/>
+      <c r="AJ47" s="68"/>
+      <c r="AK47" s="68"/>
+      <c r="AN47" s="78" t="s">
+        <v>129</v>
+      </c>
+      <c r="AO47" s="63"/>
     </row>
     <row r="48" ht="12" customHeight="1">
-      <c r="B48" s="61"/>
-      <c r="C48" s="62" t="s">
-        <v>127</v>
-      </c>
-      <c r="D48" s="64"/>
-      <c r="E48" s="64"/>
-      <c r="F48" s="67"/>
-      <c r="G48" s="65"/>
-      <c r="H48" s="63"/>
-      <c r="I48" s="64"/>
-      <c r="J48" s="64"/>
-      <c r="K48" s="64"/>
-      <c r="L48" s="49"/>
-      <c r="M48" s="64"/>
-      <c r="N48" s="65"/>
-      <c r="O48" s="63"/>
-      <c r="P48" s="64"/>
-      <c r="Q48" s="64"/>
-      <c r="R48" s="64"/>
-      <c r="S48" s="64"/>
-      <c r="T48" s="64"/>
-      <c r="U48" s="64"/>
-      <c r="V48" s="65"/>
-      <c r="W48" s="52"/>
-      <c r="X48" s="64"/>
-      <c r="Y48" s="64"/>
-      <c r="Z48" s="65"/>
-      <c r="AA48" s="63"/>
-      <c r="AB48" s="64"/>
-      <c r="AC48" s="64"/>
-      <c r="AD48" s="49"/>
-      <c r="AE48" s="65"/>
-      <c r="AF48" s="63"/>
-      <c r="AG48" s="64"/>
-      <c r="AH48" s="64"/>
-      <c r="AI48" s="64"/>
-      <c r="AJ48" s="64"/>
-      <c r="AK48" s="75"/>
-      <c r="AN48" s="74" t="s">
-        <v>128</v>
-      </c>
-      <c r="AO48" s="58"/>
+      <c r="B48" s="65"/>
+      <c r="C48" s="66" t="s">
+        <v>130</v>
+      </c>
+      <c r="D48" s="68"/>
+      <c r="E48" s="68"/>
+      <c r="F48" s="71"/>
+      <c r="G48" s="69"/>
+      <c r="H48" s="67"/>
+      <c r="I48" s="68"/>
+      <c r="J48" s="68"/>
+      <c r="K48" s="68"/>
+      <c r="L48" s="53"/>
+      <c r="M48" s="68"/>
+      <c r="N48" s="69"/>
+      <c r="O48" s="67"/>
+      <c r="P48" s="68"/>
+      <c r="Q48" s="68"/>
+      <c r="R48" s="68"/>
+      <c r="S48" s="68"/>
+      <c r="T48" s="68"/>
+      <c r="U48" s="68"/>
+      <c r="V48" s="69"/>
+      <c r="W48" s="56"/>
+      <c r="X48" s="68"/>
+      <c r="Y48" s="68"/>
+      <c r="Z48" s="69"/>
+      <c r="AA48" s="67"/>
+      <c r="AB48" s="68"/>
+      <c r="AC48" s="68"/>
+      <c r="AD48" s="53"/>
+      <c r="AE48" s="69"/>
+      <c r="AF48" s="67"/>
+      <c r="AG48" s="68"/>
+      <c r="AH48" s="68"/>
+      <c r="AI48" s="68"/>
+      <c r="AJ48" s="68"/>
+      <c r="AK48" s="79"/>
+      <c r="AN48" s="78" t="s">
+        <v>131</v>
+      </c>
+      <c r="AO48" s="62"/>
     </row>
     <row r="49" ht="12" customHeight="1">
-      <c r="B49" s="61"/>
-      <c r="C49" s="62"/>
-      <c r="D49" s="64"/>
-      <c r="E49" s="64"/>
-      <c r="F49" s="67"/>
-      <c r="G49" s="65"/>
-      <c r="H49" s="63"/>
-      <c r="I49" s="64"/>
-      <c r="J49" s="64"/>
-      <c r="K49" s="64"/>
-      <c r="L49" s="49"/>
-      <c r="M49" s="64"/>
-      <c r="N49" s="65"/>
-      <c r="O49" s="63"/>
-      <c r="P49" s="64"/>
-      <c r="Q49" s="64"/>
-      <c r="R49" s="64"/>
-      <c r="S49" s="64"/>
-      <c r="T49" s="64"/>
-      <c r="U49" s="64"/>
-      <c r="V49" s="65"/>
-      <c r="W49" s="52"/>
-      <c r="X49" s="64"/>
-      <c r="Y49" s="64"/>
-      <c r="Z49" s="65"/>
-      <c r="AA49" s="63"/>
-      <c r="AB49" s="64"/>
-      <c r="AC49" s="64"/>
-      <c r="AD49" s="49"/>
-      <c r="AE49" s="65"/>
-      <c r="AF49" s="63"/>
-      <c r="AG49" s="64"/>
-      <c r="AH49" s="64"/>
-      <c r="AI49" s="64"/>
-      <c r="AJ49" s="64"/>
-      <c r="AK49" s="64"/>
-      <c r="AN49" s="74" t="s">
-        <v>129</v>
-      </c>
-      <c r="AO49" s="54"/>
+      <c r="B49" s="65"/>
+      <c r="C49" s="66"/>
+      <c r="D49" s="68"/>
+      <c r="E49" s="68"/>
+      <c r="F49" s="71"/>
+      <c r="G49" s="69"/>
+      <c r="H49" s="67"/>
+      <c r="I49" s="68"/>
+      <c r="J49" s="68"/>
+      <c r="K49" s="68"/>
+      <c r="L49" s="53"/>
+      <c r="M49" s="68"/>
+      <c r="N49" s="69"/>
+      <c r="O49" s="67"/>
+      <c r="P49" s="68"/>
+      <c r="Q49" s="68"/>
+      <c r="R49" s="68"/>
+      <c r="S49" s="68"/>
+      <c r="T49" s="68"/>
+      <c r="U49" s="68"/>
+      <c r="V49" s="69"/>
+      <c r="W49" s="56"/>
+      <c r="X49" s="68"/>
+      <c r="Y49" s="68"/>
+      <c r="Z49" s="69"/>
+      <c r="AA49" s="67"/>
+      <c r="AB49" s="68"/>
+      <c r="AC49" s="68"/>
+      <c r="AD49" s="53"/>
+      <c r="AE49" s="69"/>
+      <c r="AF49" s="67"/>
+      <c r="AG49" s="68"/>
+      <c r="AH49" s="68"/>
+      <c r="AI49" s="68"/>
+      <c r="AJ49" s="68"/>
+      <c r="AK49" s="68"/>
+      <c r="AN49" s="78" t="s">
+        <v>132</v>
+      </c>
+      <c r="AO49" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -8949,801 +9000,801 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="76"/>
+      <c r="B1" s="80"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="77" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" s="78" t="s">
-        <v>74</v>
-      </c>
-      <c r="D2" s="79" t="s">
-        <v>130</v>
-      </c>
-      <c r="E2" s="80" t="s">
-        <v>131</v>
-      </c>
-      <c r="F2" s="81" t="s">
-        <v>132</v>
-      </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="81" t="s">
+      <c r="B2" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" s="83" t="s">
         <v>133</v>
       </c>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="81" t="s">
+      <c r="E2" s="84" t="s">
         <v>134</v>
       </c>
-      <c r="O2" s="81"/>
-      <c r="P2" s="81"/>
-      <c r="Q2" s="80"/>
-      <c r="R2" s="81" t="s">
+      <c r="F2" s="85" t="s">
         <v>135</v>
       </c>
-      <c r="S2" s="82"/>
-      <c r="AD2" s="25"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="85" t="s">
+        <v>136</v>
+      </c>
+      <c r="K2" s="85"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="85" t="s">
+        <v>137</v>
+      </c>
+      <c r="O2" s="85"/>
+      <c r="P2" s="85"/>
+      <c r="Q2" s="84"/>
+      <c r="R2" s="85" t="s">
+        <v>138</v>
+      </c>
+      <c r="S2" s="86"/>
+      <c r="AD2" s="29"/>
     </row>
     <row r="3">
-      <c r="B3" s="83"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="85" t="s">
-        <v>136</v>
-      </c>
-      <c r="E3" s="86">
+      <c r="B3" s="87"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="89" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3" s="90">
         <v>4</v>
       </c>
-      <c r="F3" s="87">
+      <c r="F3" s="91">
         <v>1</v>
       </c>
-      <c r="G3" s="88">
+      <c r="G3" s="92">
         <v>2</v>
       </c>
-      <c r="H3" s="88">
+      <c r="H3" s="92">
         <v>3</v>
       </c>
-      <c r="I3" s="86">
+      <c r="I3" s="90">
         <v>4</v>
       </c>
-      <c r="J3" s="87">
+      <c r="J3" s="91">
         <v>1</v>
       </c>
-      <c r="K3" s="88">
+      <c r="K3" s="92">
         <v>2</v>
       </c>
-      <c r="L3" s="88">
+      <c r="L3" s="92">
         <v>3</v>
       </c>
-      <c r="M3" s="86">
+      <c r="M3" s="90">
         <v>4</v>
       </c>
-      <c r="N3" s="87">
+      <c r="N3" s="91">
         <v>1</v>
       </c>
-      <c r="O3" s="88">
+      <c r="O3" s="92">
         <v>2</v>
       </c>
-      <c r="P3" s="88">
+      <c r="P3" s="92">
         <v>3</v>
       </c>
-      <c r="Q3" s="86">
+      <c r="Q3" s="90">
         <v>4</v>
       </c>
-      <c r="R3" s="87">
+      <c r="R3" s="91">
         <v>1</v>
       </c>
-      <c r="S3" s="89">
+      <c r="S3" s="93">
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="90" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="78" t="s">
-        <v>139</v>
-      </c>
-      <c r="D4" s="91"/>
-      <c r="E4" s="92"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="94"/>
-      <c r="I4" s="92"/>
-      <c r="J4" s="95"/>
-      <c r="K4" s="94"/>
-      <c r="L4" s="94"/>
-      <c r="M4" s="92"/>
-      <c r="N4" s="95"/>
-      <c r="O4" s="94"/>
-      <c r="P4" s="94"/>
-      <c r="Q4" s="92"/>
-      <c r="R4" s="95"/>
-      <c r="S4" s="96"/>
+      <c r="B4" s="94" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" s="82" t="s">
+        <v>142</v>
+      </c>
+      <c r="D4" s="95"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="99"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="96"/>
+      <c r="N4" s="99"/>
+      <c r="O4" s="98"/>
+      <c r="P4" s="98"/>
+      <c r="Q4" s="96"/>
+      <c r="R4" s="99"/>
+      <c r="S4" s="100"/>
       <c r="U4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="90"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="98"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="101"/>
-      <c r="H5" s="102"/>
-      <c r="I5" s="99"/>
-      <c r="J5" s="103"/>
-      <c r="K5" s="102"/>
-      <c r="L5" s="102"/>
-      <c r="M5" s="99"/>
-      <c r="N5" s="103"/>
-      <c r="O5" s="102"/>
-      <c r="P5" s="102"/>
-      <c r="Q5" s="99"/>
-      <c r="R5" s="103"/>
-      <c r="S5" s="104"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="106"/>
+      <c r="I5" s="103"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="106"/>
+      <c r="L5" s="106"/>
+      <c r="M5" s="103"/>
+      <c r="N5" s="107"/>
+      <c r="O5" s="106"/>
+      <c r="P5" s="106"/>
+      <c r="Q5" s="103"/>
+      <c r="R5" s="107"/>
+      <c r="S5" s="108"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="90"/>
-      <c r="C6" s="105" t="s">
-        <v>141</v>
-      </c>
-      <c r="D6" s="106"/>
-      <c r="E6" s="107"/>
-      <c r="F6" s="108"/>
-      <c r="G6" s="109"/>
-      <c r="H6" s="110"/>
-      <c r="I6" s="107"/>
-      <c r="J6" s="111"/>
-      <c r="K6" s="110"/>
-      <c r="L6" s="110"/>
-      <c r="M6" s="107"/>
-      <c r="N6" s="111"/>
-      <c r="O6" s="110"/>
-      <c r="P6" s="110"/>
-      <c r="Q6" s="107"/>
-      <c r="R6" s="111"/>
-      <c r="S6" s="112"/>
-      <c r="U6" s="113" t="s">
-        <v>142</v>
-      </c>
-      <c r="V6" s="113"/>
+      <c r="B6" s="94"/>
+      <c r="C6" s="109" t="s">
+        <v>144</v>
+      </c>
+      <c r="D6" s="110"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="112"/>
+      <c r="G6" s="113"/>
+      <c r="H6" s="114"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="115"/>
+      <c r="K6" s="114"/>
+      <c r="L6" s="114"/>
+      <c r="M6" s="111"/>
+      <c r="N6" s="115"/>
+      <c r="O6" s="114"/>
+      <c r="P6" s="114"/>
+      <c r="Q6" s="111"/>
+      <c r="R6" s="115"/>
+      <c r="S6" s="116"/>
+      <c r="U6" s="117" t="s">
+        <v>145</v>
+      </c>
+      <c r="V6" s="117"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="90"/>
-      <c r="C7" s="97"/>
-      <c r="D7" s="98"/>
-      <c r="E7" s="99"/>
-      <c r="F7" s="103"/>
-      <c r="G7" s="101"/>
-      <c r="H7" s="101"/>
-      <c r="I7" s="99"/>
-      <c r="J7" s="103"/>
-      <c r="K7" s="102"/>
-      <c r="L7" s="102"/>
-      <c r="M7" s="99"/>
-      <c r="N7" s="103"/>
-      <c r="O7" s="102"/>
-      <c r="P7" s="102"/>
-      <c r="Q7" s="99"/>
-      <c r="R7" s="103"/>
-      <c r="S7" s="104"/>
+      <c r="B7" s="94"/>
+      <c r="C7" s="101"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="107"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="105"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="106"/>
+      <c r="L7" s="106"/>
+      <c r="M7" s="103"/>
+      <c r="N7" s="107"/>
+      <c r="O7" s="106"/>
+      <c r="P7" s="106"/>
+      <c r="Q7" s="103"/>
+      <c r="R7" s="107"/>
+      <c r="S7" s="108"/>
       <c r="U7" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="90"/>
-      <c r="C8" s="105" t="s">
-        <v>144</v>
-      </c>
-      <c r="D8" s="106"/>
-      <c r="E8" s="107"/>
-      <c r="F8" s="108"/>
-      <c r="G8" s="110"/>
-      <c r="H8" s="110"/>
-      <c r="I8" s="107"/>
-      <c r="J8" s="111"/>
-      <c r="K8" s="110"/>
-      <c r="L8" s="110"/>
-      <c r="M8" s="107"/>
-      <c r="N8" s="111"/>
-      <c r="O8" s="110"/>
-      <c r="P8" s="110"/>
-      <c r="Q8" s="107"/>
-      <c r="R8" s="111"/>
-      <c r="S8" s="112"/>
+      <c r="B8" s="94"/>
+      <c r="C8" s="109" t="s">
+        <v>147</v>
+      </c>
+      <c r="D8" s="110"/>
+      <c r="E8" s="111"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="114"/>
+      <c r="H8" s="114"/>
+      <c r="I8" s="111"/>
+      <c r="J8" s="115"/>
+      <c r="K8" s="114"/>
+      <c r="L8" s="114"/>
+      <c r="M8" s="111"/>
+      <c r="N8" s="115"/>
+      <c r="O8" s="114"/>
+      <c r="P8" s="114"/>
+      <c r="Q8" s="111"/>
+      <c r="R8" s="115"/>
+      <c r="S8" s="116"/>
       <c r="U8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="90"/>
-      <c r="C9" s="97"/>
-      <c r="D9" s="98"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="103"/>
-      <c r="G9" s="101"/>
-      <c r="H9" s="102"/>
-      <c r="I9" s="99"/>
-      <c r="J9" s="103"/>
-      <c r="K9" s="102"/>
-      <c r="L9" s="102"/>
-      <c r="M9" s="99"/>
-      <c r="N9" s="103"/>
-      <c r="O9" s="102"/>
-      <c r="P9" s="102"/>
-      <c r="Q9" s="99"/>
-      <c r="R9" s="103"/>
-      <c r="S9" s="104"/>
+      <c r="B9" s="94"/>
+      <c r="C9" s="101"/>
+      <c r="D9" s="102"/>
+      <c r="E9" s="103"/>
+      <c r="F9" s="107"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="106"/>
+      <c r="I9" s="103"/>
+      <c r="J9" s="107"/>
+      <c r="K9" s="106"/>
+      <c r="L9" s="106"/>
+      <c r="M9" s="103"/>
+      <c r="N9" s="107"/>
+      <c r="O9" s="106"/>
+      <c r="P9" s="106"/>
+      <c r="Q9" s="103"/>
+      <c r="R9" s="107"/>
+      <c r="S9" s="108"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="90"/>
-      <c r="C10" s="105" t="s">
-        <v>146</v>
-      </c>
-      <c r="D10" s="106"/>
-      <c r="E10" s="107"/>
-      <c r="F10" s="111"/>
-      <c r="G10" s="109"/>
-      <c r="H10" s="109"/>
-      <c r="I10" s="107"/>
-      <c r="J10" s="111"/>
-      <c r="K10" s="110"/>
-      <c r="L10" s="110"/>
-      <c r="M10" s="107"/>
-      <c r="N10" s="111"/>
-      <c r="O10" s="110"/>
-      <c r="P10" s="110"/>
-      <c r="Q10" s="107"/>
-      <c r="R10" s="111"/>
-      <c r="S10" s="112"/>
+      <c r="B10" s="94"/>
+      <c r="C10" s="109" t="s">
+        <v>149</v>
+      </c>
+      <c r="D10" s="110"/>
+      <c r="E10" s="111"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="113"/>
+      <c r="H10" s="113"/>
+      <c r="I10" s="111"/>
+      <c r="J10" s="115"/>
+      <c r="K10" s="114"/>
+      <c r="L10" s="114"/>
+      <c r="M10" s="111"/>
+      <c r="N10" s="115"/>
+      <c r="O10" s="114"/>
+      <c r="P10" s="114"/>
+      <c r="Q10" s="111"/>
+      <c r="R10" s="115"/>
+      <c r="S10" s="116"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="114"/>
-      <c r="C11" s="115"/>
-      <c r="D11" s="116"/>
-      <c r="E11" s="117"/>
-      <c r="F11" s="118"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="117"/>
-      <c r="J11" s="118"/>
-      <c r="K11" s="120"/>
-      <c r="L11" s="120"/>
-      <c r="M11" s="117"/>
-      <c r="N11" s="118"/>
-      <c r="O11" s="120"/>
-      <c r="P11" s="120"/>
-      <c r="Q11" s="117"/>
-      <c r="R11" s="118"/>
-      <c r="S11" s="121"/>
+      <c r="B11" s="118"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="122"/>
+      <c r="G11" s="123"/>
+      <c r="H11" s="123"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="122"/>
+      <c r="K11" s="124"/>
+      <c r="L11" s="124"/>
+      <c r="M11" s="121"/>
+      <c r="N11" s="122"/>
+      <c r="O11" s="124"/>
+      <c r="P11" s="124"/>
+      <c r="Q11" s="121"/>
+      <c r="R11" s="122"/>
+      <c r="S11" s="125"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="77" t="s">
-        <v>147</v>
-      </c>
-      <c r="C12" s="78" t="s">
-        <v>148</v>
-      </c>
-      <c r="D12" s="91"/>
-      <c r="E12" s="92"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="123"/>
-      <c r="J12" s="95"/>
-      <c r="K12" s="94"/>
-      <c r="L12" s="94"/>
-      <c r="M12" s="92"/>
-      <c r="N12" s="95"/>
-      <c r="O12" s="94"/>
-      <c r="P12" s="94"/>
-      <c r="Q12" s="92"/>
-      <c r="R12" s="95"/>
-      <c r="S12" s="96"/>
+      <c r="B12" s="81" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="82" t="s">
+        <v>151</v>
+      </c>
+      <c r="D12" s="95"/>
+      <c r="E12" s="96"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="126"/>
+      <c r="I12" s="127"/>
+      <c r="J12" s="99"/>
+      <c r="K12" s="98"/>
+      <c r="L12" s="98"/>
+      <c r="M12" s="96"/>
+      <c r="N12" s="99"/>
+      <c r="O12" s="98"/>
+      <c r="P12" s="98"/>
+      <c r="Q12" s="96"/>
+      <c r="R12" s="99"/>
+      <c r="S12" s="100"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="90"/>
-      <c r="C13" s="97"/>
-      <c r="D13" s="98"/>
-      <c r="E13" s="99"/>
-      <c r="F13" s="103"/>
-      <c r="G13" s="102"/>
-      <c r="H13" s="102"/>
-      <c r="I13" s="99"/>
-      <c r="J13" s="100"/>
-      <c r="K13" s="102"/>
-      <c r="L13" s="102"/>
-      <c r="M13" s="99"/>
-      <c r="N13" s="103"/>
-      <c r="O13" s="102"/>
-      <c r="P13" s="102"/>
-      <c r="Q13" s="99"/>
-      <c r="R13" s="103"/>
-      <c r="S13" s="104"/>
+      <c r="B13" s="94"/>
+      <c r="C13" s="101"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="103"/>
+      <c r="F13" s="107"/>
+      <c r="G13" s="106"/>
+      <c r="H13" s="106"/>
+      <c r="I13" s="103"/>
+      <c r="J13" s="104"/>
+      <c r="K13" s="106"/>
+      <c r="L13" s="106"/>
+      <c r="M13" s="103"/>
+      <c r="N13" s="107"/>
+      <c r="O13" s="106"/>
+      <c r="P13" s="106"/>
+      <c r="Q13" s="103"/>
+      <c r="R13" s="107"/>
+      <c r="S13" s="108"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="90"/>
-      <c r="C14" s="105" t="s">
-        <v>149</v>
-      </c>
-      <c r="D14" s="124"/>
-      <c r="E14" s="107"/>
-      <c r="F14" s="111"/>
-      <c r="G14" s="110"/>
-      <c r="H14" s="109"/>
-      <c r="I14" s="107"/>
-      <c r="J14" s="111"/>
-      <c r="K14" s="110"/>
-      <c r="L14" s="110"/>
-      <c r="M14" s="107"/>
-      <c r="N14" s="111"/>
-      <c r="O14" s="110"/>
-      <c r="P14" s="110"/>
-      <c r="Q14" s="107"/>
-      <c r="R14" s="111"/>
-      <c r="S14" s="112"/>
+      <c r="B14" s="94"/>
+      <c r="C14" s="109" t="s">
+        <v>152</v>
+      </c>
+      <c r="D14" s="128"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="115"/>
+      <c r="G14" s="114"/>
+      <c r="H14" s="113"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="115"/>
+      <c r="K14" s="114"/>
+      <c r="L14" s="114"/>
+      <c r="M14" s="111"/>
+      <c r="N14" s="115"/>
+      <c r="O14" s="114"/>
+      <c r="P14" s="114"/>
+      <c r="Q14" s="111"/>
+      <c r="R14" s="115"/>
+      <c r="S14" s="116"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="90"/>
-      <c r="C15" s="97"/>
-      <c r="D15" s="98"/>
-      <c r="E15" s="99"/>
-      <c r="F15" s="103"/>
-      <c r="G15" s="102"/>
-      <c r="H15" s="102"/>
-      <c r="I15" s="125"/>
-      <c r="J15" s="100"/>
-      <c r="K15" s="102"/>
-      <c r="L15" s="102"/>
-      <c r="M15" s="99"/>
-      <c r="N15" s="103"/>
-      <c r="O15" s="102"/>
-      <c r="P15" s="102"/>
-      <c r="Q15" s="99"/>
-      <c r="R15" s="103"/>
-      <c r="S15" s="104"/>
+      <c r="B15" s="94"/>
+      <c r="C15" s="101"/>
+      <c r="D15" s="102"/>
+      <c r="E15" s="103"/>
+      <c r="F15" s="107"/>
+      <c r="G15" s="106"/>
+      <c r="H15" s="106"/>
+      <c r="I15" s="129"/>
+      <c r="J15" s="104"/>
+      <c r="K15" s="106"/>
+      <c r="L15" s="106"/>
+      <c r="M15" s="103"/>
+      <c r="N15" s="107"/>
+      <c r="O15" s="106"/>
+      <c r="P15" s="106"/>
+      <c r="Q15" s="103"/>
+      <c r="R15" s="107"/>
+      <c r="S15" s="108"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="90"/>
-      <c r="C16" s="105" t="s">
-        <v>150</v>
-      </c>
-      <c r="D16" s="106"/>
-      <c r="E16" s="107"/>
-      <c r="F16" s="111"/>
-      <c r="G16" s="110"/>
-      <c r="H16" s="109"/>
-      <c r="I16" s="126"/>
-      <c r="J16" s="111"/>
-      <c r="K16" s="110"/>
-      <c r="L16" s="110"/>
-      <c r="M16" s="107"/>
-      <c r="N16" s="111"/>
-      <c r="O16" s="110"/>
-      <c r="P16" s="110"/>
-      <c r="Q16" s="107"/>
-      <c r="R16" s="111"/>
-      <c r="S16" s="112"/>
+      <c r="B16" s="94"/>
+      <c r="C16" s="109" t="s">
+        <v>153</v>
+      </c>
+      <c r="D16" s="110"/>
+      <c r="E16" s="111"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="114"/>
+      <c r="H16" s="113"/>
+      <c r="I16" s="130"/>
+      <c r="J16" s="115"/>
+      <c r="K16" s="114"/>
+      <c r="L16" s="114"/>
+      <c r="M16" s="111"/>
+      <c r="N16" s="115"/>
+      <c r="O16" s="114"/>
+      <c r="P16" s="114"/>
+      <c r="Q16" s="111"/>
+      <c r="R16" s="115"/>
+      <c r="S16" s="116"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="114"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="116"/>
-      <c r="E17" s="117"/>
-      <c r="F17" s="118"/>
-      <c r="G17" s="120"/>
-      <c r="H17" s="120"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="127"/>
-      <c r="K17" s="119"/>
-      <c r="L17" s="120"/>
-      <c r="M17" s="117"/>
-      <c r="N17" s="118"/>
-      <c r="O17" s="120"/>
-      <c r="P17" s="120"/>
-      <c r="Q17" s="117"/>
-      <c r="R17" s="118"/>
-      <c r="S17" s="121"/>
+      <c r="B17" s="118"/>
+      <c r="C17" s="119"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="122"/>
+      <c r="G17" s="124"/>
+      <c r="H17" s="124"/>
+      <c r="I17" s="121"/>
+      <c r="J17" s="131"/>
+      <c r="K17" s="123"/>
+      <c r="L17" s="124"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="122"/>
+      <c r="O17" s="124"/>
+      <c r="P17" s="124"/>
+      <c r="Q17" s="121"/>
+      <c r="R17" s="122"/>
+      <c r="S17" s="125"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="79" t="s">
-        <v>151</v>
-      </c>
-      <c r="C18" s="78" t="s">
-        <v>152</v>
-      </c>
-      <c r="D18" s="91"/>
-      <c r="E18" s="92"/>
-      <c r="F18" s="95"/>
-      <c r="G18" s="94"/>
-      <c r="H18" s="94"/>
-      <c r="I18" s="123"/>
-      <c r="J18" s="95"/>
-      <c r="K18" s="94"/>
-      <c r="L18" s="94"/>
-      <c r="M18" s="92"/>
-      <c r="N18" s="95"/>
-      <c r="O18" s="94"/>
-      <c r="P18" s="94"/>
-      <c r="Q18" s="92"/>
-      <c r="R18" s="95"/>
-      <c r="S18" s="96"/>
+      <c r="B18" s="83" t="s">
+        <v>154</v>
+      </c>
+      <c r="C18" s="82" t="s">
+        <v>155</v>
+      </c>
+      <c r="D18" s="95"/>
+      <c r="E18" s="96"/>
+      <c r="F18" s="99"/>
+      <c r="G18" s="98"/>
+      <c r="H18" s="98"/>
+      <c r="I18" s="127"/>
+      <c r="J18" s="99"/>
+      <c r="K18" s="98"/>
+      <c r="L18" s="98"/>
+      <c r="M18" s="96"/>
+      <c r="N18" s="99"/>
+      <c r="O18" s="98"/>
+      <c r="P18" s="98"/>
+      <c r="Q18" s="96"/>
+      <c r="R18" s="99"/>
+      <c r="S18" s="100"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="90"/>
-      <c r="C19" s="97"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="99"/>
-      <c r="F19" s="103"/>
-      <c r="G19" s="101"/>
-      <c r="H19" s="102"/>
-      <c r="I19" s="99"/>
-      <c r="J19" s="103"/>
-      <c r="K19" s="102"/>
-      <c r="L19" s="102"/>
-      <c r="M19" s="99"/>
-      <c r="N19" s="103"/>
-      <c r="O19" s="102"/>
-      <c r="P19" s="102"/>
-      <c r="Q19" s="99"/>
-      <c r="R19" s="103"/>
-      <c r="S19" s="104"/>
+      <c r="B19" s="94"/>
+      <c r="C19" s="101"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="103"/>
+      <c r="F19" s="107"/>
+      <c r="G19" s="105"/>
+      <c r="H19" s="106"/>
+      <c r="I19" s="103"/>
+      <c r="J19" s="107"/>
+      <c r="K19" s="106"/>
+      <c r="L19" s="106"/>
+      <c r="M19" s="103"/>
+      <c r="N19" s="107"/>
+      <c r="O19" s="106"/>
+      <c r="P19" s="106"/>
+      <c r="Q19" s="103"/>
+      <c r="R19" s="107"/>
+      <c r="S19" s="108"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="90"/>
-      <c r="C20" s="105" t="s">
-        <v>153</v>
-      </c>
-      <c r="D20" s="106"/>
-      <c r="E20" s="107"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="110"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="126"/>
-      <c r="J20" s="108"/>
-      <c r="K20" s="109"/>
-      <c r="L20" s="109"/>
-      <c r="M20" s="107"/>
-      <c r="N20" s="111"/>
-      <c r="O20" s="110"/>
-      <c r="P20" s="110"/>
-      <c r="Q20" s="107"/>
-      <c r="R20" s="111"/>
-      <c r="S20" s="112"/>
+      <c r="B20" s="94"/>
+      <c r="C20" s="109" t="s">
+        <v>156</v>
+      </c>
+      <c r="D20" s="110"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="115"/>
+      <c r="G20" s="114"/>
+      <c r="H20" s="114"/>
+      <c r="I20" s="130"/>
+      <c r="J20" s="112"/>
+      <c r="K20" s="113"/>
+      <c r="L20" s="113"/>
+      <c r="M20" s="111"/>
+      <c r="N20" s="115"/>
+      <c r="O20" s="114"/>
+      <c r="P20" s="114"/>
+      <c r="Q20" s="111"/>
+      <c r="R20" s="115"/>
+      <c r="S20" s="116"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="90"/>
-      <c r="C21" s="97"/>
-      <c r="D21" s="98"/>
-      <c r="E21" s="99"/>
-      <c r="F21" s="103"/>
-      <c r="G21" s="102"/>
-      <c r="H21" s="102"/>
-      <c r="I21" s="99"/>
-      <c r="J21" s="103"/>
-      <c r="K21" s="102"/>
-      <c r="L21" s="102"/>
-      <c r="M21" s="99"/>
-      <c r="N21" s="128"/>
-      <c r="O21" s="102"/>
-      <c r="P21" s="102"/>
-      <c r="Q21" s="99"/>
-      <c r="R21" s="103"/>
-      <c r="S21" s="104"/>
+      <c r="B21" s="94"/>
+      <c r="C21" s="101"/>
+      <c r="D21" s="102"/>
+      <c r="E21" s="103"/>
+      <c r="F21" s="107"/>
+      <c r="G21" s="106"/>
+      <c r="H21" s="106"/>
+      <c r="I21" s="103"/>
+      <c r="J21" s="107"/>
+      <c r="K21" s="106"/>
+      <c r="L21" s="106"/>
+      <c r="M21" s="103"/>
+      <c r="N21" s="132"/>
+      <c r="O21" s="106"/>
+      <c r="P21" s="106"/>
+      <c r="Q21" s="103"/>
+      <c r="R21" s="107"/>
+      <c r="S21" s="108"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="90"/>
-      <c r="C22" s="105" t="s">
-        <v>154</v>
-      </c>
-      <c r="D22" s="106"/>
-      <c r="E22" s="107"/>
-      <c r="F22" s="111"/>
-      <c r="G22" s="110"/>
-      <c r="H22" s="110"/>
-      <c r="I22" s="107"/>
-      <c r="J22" s="111"/>
-      <c r="K22" s="109"/>
-      <c r="L22" s="109"/>
-      <c r="M22" s="107"/>
-      <c r="N22" s="111"/>
-      <c r="O22" s="110"/>
-      <c r="P22" s="110"/>
-      <c r="Q22" s="107"/>
-      <c r="R22" s="111"/>
-      <c r="S22" s="112"/>
+      <c r="B22" s="94"/>
+      <c r="C22" s="109" t="s">
+        <v>157</v>
+      </c>
+      <c r="D22" s="110"/>
+      <c r="E22" s="111"/>
+      <c r="F22" s="115"/>
+      <c r="G22" s="114"/>
+      <c r="H22" s="114"/>
+      <c r="I22" s="111"/>
+      <c r="J22" s="115"/>
+      <c r="K22" s="113"/>
+      <c r="L22" s="113"/>
+      <c r="M22" s="111"/>
+      <c r="N22" s="115"/>
+      <c r="O22" s="114"/>
+      <c r="P22" s="114"/>
+      <c r="Q22" s="111"/>
+      <c r="R22" s="115"/>
+      <c r="S22" s="116"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="114"/>
-      <c r="C23" s="115"/>
-      <c r="D23" s="116"/>
-      <c r="E23" s="117"/>
-      <c r="F23" s="118"/>
-      <c r="G23" s="120"/>
-      <c r="H23" s="120"/>
-      <c r="I23" s="117"/>
-      <c r="J23" s="118"/>
-      <c r="K23" s="120"/>
-      <c r="L23" s="120"/>
-      <c r="M23" s="117"/>
-      <c r="N23" s="118"/>
-      <c r="O23" s="120"/>
-      <c r="P23" s="120"/>
-      <c r="Q23" s="117"/>
-      <c r="R23" s="118"/>
-      <c r="S23" s="121"/>
+      <c r="B23" s="118"/>
+      <c r="C23" s="119"/>
+      <c r="D23" s="120"/>
+      <c r="E23" s="121"/>
+      <c r="F23" s="122"/>
+      <c r="G23" s="124"/>
+      <c r="H23" s="124"/>
+      <c r="I23" s="121"/>
+      <c r="J23" s="122"/>
+      <c r="K23" s="124"/>
+      <c r="L23" s="124"/>
+      <c r="M23" s="121"/>
+      <c r="N23" s="122"/>
+      <c r="O23" s="124"/>
+      <c r="P23" s="124"/>
+      <c r="Q23" s="121"/>
+      <c r="R23" s="122"/>
+      <c r="S23" s="125"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="79" t="s">
-        <v>155</v>
-      </c>
-      <c r="C24" s="78" t="s">
-        <v>156</v>
-      </c>
-      <c r="D24" s="91"/>
-      <c r="E24" s="92"/>
-      <c r="F24" s="95"/>
-      <c r="G24" s="94"/>
-      <c r="H24" s="94"/>
-      <c r="I24" s="92"/>
-      <c r="J24" s="95"/>
-      <c r="K24" s="94"/>
-      <c r="L24" s="94"/>
-      <c r="M24" s="123"/>
-      <c r="N24" s="93"/>
-      <c r="O24" s="122"/>
-      <c r="P24" s="122"/>
-      <c r="Q24" s="92"/>
-      <c r="R24" s="95"/>
-      <c r="S24" s="96"/>
+      <c r="B24" s="83" t="s">
+        <v>158</v>
+      </c>
+      <c r="C24" s="82" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" s="95"/>
+      <c r="E24" s="96"/>
+      <c r="F24" s="99"/>
+      <c r="G24" s="98"/>
+      <c r="H24" s="98"/>
+      <c r="I24" s="96"/>
+      <c r="J24" s="99"/>
+      <c r="K24" s="98"/>
+      <c r="L24" s="98"/>
+      <c r="M24" s="127"/>
+      <c r="N24" s="97"/>
+      <c r="O24" s="126"/>
+      <c r="P24" s="126"/>
+      <c r="Q24" s="96"/>
+      <c r="R24" s="99"/>
+      <c r="S24" s="100"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="90"/>
-      <c r="C25" s="97"/>
-      <c r="D25" s="98"/>
-      <c r="E25" s="99"/>
-      <c r="F25" s="103"/>
-      <c r="G25" s="102"/>
-      <c r="H25" s="102"/>
-      <c r="I25" s="99"/>
-      <c r="J25" s="103"/>
-      <c r="K25" s="102"/>
-      <c r="L25" s="102"/>
-      <c r="M25" s="99"/>
-      <c r="N25" s="103"/>
-      <c r="O25" s="102"/>
-      <c r="P25" s="102"/>
-      <c r="Q25" s="99"/>
-      <c r="R25" s="103"/>
-      <c r="S25" s="104"/>
+      <c r="B25" s="94"/>
+      <c r="C25" s="101"/>
+      <c r="D25" s="102"/>
+      <c r="E25" s="103"/>
+      <c r="F25" s="107"/>
+      <c r="G25" s="106"/>
+      <c r="H25" s="106"/>
+      <c r="I25" s="103"/>
+      <c r="J25" s="107"/>
+      <c r="K25" s="106"/>
+      <c r="L25" s="106"/>
+      <c r="M25" s="103"/>
+      <c r="N25" s="107"/>
+      <c r="O25" s="106"/>
+      <c r="P25" s="106"/>
+      <c r="Q25" s="103"/>
+      <c r="R25" s="107"/>
+      <c r="S25" s="108"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="90"/>
-      <c r="C26" s="105" t="s">
-        <v>157</v>
-      </c>
-      <c r="D26" s="106"/>
-      <c r="E26" s="107"/>
-      <c r="F26" s="111"/>
-      <c r="G26" s="110"/>
-      <c r="H26" s="110"/>
-      <c r="I26" s="107"/>
-      <c r="J26" s="111"/>
-      <c r="K26" s="110"/>
-      <c r="L26" s="110"/>
-      <c r="M26" s="107"/>
-      <c r="N26" s="111"/>
-      <c r="O26" s="109"/>
-      <c r="P26" s="109"/>
-      <c r="Q26" s="107"/>
-      <c r="R26" s="111"/>
-      <c r="S26" s="112"/>
+      <c r="B26" s="94"/>
+      <c r="C26" s="109" t="s">
+        <v>160</v>
+      </c>
+      <c r="D26" s="110"/>
+      <c r="E26" s="111"/>
+      <c r="F26" s="115"/>
+      <c r="G26" s="114"/>
+      <c r="H26" s="114"/>
+      <c r="I26" s="111"/>
+      <c r="J26" s="115"/>
+      <c r="K26" s="114"/>
+      <c r="L26" s="114"/>
+      <c r="M26" s="111"/>
+      <c r="N26" s="115"/>
+      <c r="O26" s="113"/>
+      <c r="P26" s="113"/>
+      <c r="Q26" s="111"/>
+      <c r="R26" s="115"/>
+      <c r="S26" s="116"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="90"/>
-      <c r="C27" s="97"/>
-      <c r="D27" s="98"/>
-      <c r="E27" s="99"/>
-      <c r="F27" s="103"/>
-      <c r="G27" s="102"/>
-      <c r="H27" s="102"/>
-      <c r="I27" s="99"/>
-      <c r="J27" s="103"/>
-      <c r="K27" s="102"/>
-      <c r="L27" s="102"/>
-      <c r="M27" s="99"/>
-      <c r="N27" s="103"/>
-      <c r="O27" s="102"/>
-      <c r="P27" s="102"/>
-      <c r="Q27" s="99"/>
-      <c r="R27" s="103"/>
-      <c r="S27" s="104"/>
+      <c r="B27" s="94"/>
+      <c r="C27" s="101"/>
+      <c r="D27" s="102"/>
+      <c r="E27" s="103"/>
+      <c r="F27" s="107"/>
+      <c r="G27" s="106"/>
+      <c r="H27" s="106"/>
+      <c r="I27" s="103"/>
+      <c r="J27" s="107"/>
+      <c r="K27" s="106"/>
+      <c r="L27" s="106"/>
+      <c r="M27" s="103"/>
+      <c r="N27" s="107"/>
+      <c r="O27" s="106"/>
+      <c r="P27" s="106"/>
+      <c r="Q27" s="103"/>
+      <c r="R27" s="107"/>
+      <c r="S27" s="108"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="90"/>
-      <c r="C28" s="105" t="s">
-        <v>158</v>
-      </c>
-      <c r="D28" s="106"/>
-      <c r="E28" s="107"/>
-      <c r="F28" s="111"/>
-      <c r="G28" s="110"/>
-      <c r="H28" s="110"/>
-      <c r="I28" s="107"/>
-      <c r="J28" s="111"/>
-      <c r="K28" s="110"/>
-      <c r="L28" s="110"/>
-      <c r="M28" s="107"/>
-      <c r="N28" s="111"/>
-      <c r="O28" s="110"/>
-      <c r="P28" s="109"/>
-      <c r="Q28" s="126"/>
-      <c r="R28" s="111"/>
-      <c r="S28" s="112"/>
+      <c r="B28" s="94"/>
+      <c r="C28" s="109" t="s">
+        <v>161</v>
+      </c>
+      <c r="D28" s="110"/>
+      <c r="E28" s="111"/>
+      <c r="F28" s="115"/>
+      <c r="G28" s="114"/>
+      <c r="H28" s="114"/>
+      <c r="I28" s="111"/>
+      <c r="J28" s="115"/>
+      <c r="K28" s="114"/>
+      <c r="L28" s="114"/>
+      <c r="M28" s="111"/>
+      <c r="N28" s="115"/>
+      <c r="O28" s="114"/>
+      <c r="P28" s="113"/>
+      <c r="Q28" s="130"/>
+      <c r="R28" s="115"/>
+      <c r="S28" s="116"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="90"/>
-      <c r="C29" s="84"/>
-      <c r="D29" s="129"/>
-      <c r="E29" s="130"/>
-      <c r="F29" s="131"/>
-      <c r="G29" s="132"/>
-      <c r="H29" s="133"/>
-      <c r="I29" s="130"/>
-      <c r="J29" s="131"/>
-      <c r="K29" s="132"/>
-      <c r="L29" s="133"/>
-      <c r="M29" s="130"/>
-      <c r="N29" s="134"/>
-      <c r="O29" s="133"/>
-      <c r="P29" s="132"/>
-      <c r="Q29" s="130"/>
-      <c r="R29" s="131"/>
-      <c r="S29" s="135"/>
+      <c r="B29" s="94"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="133"/>
+      <c r="E29" s="134"/>
+      <c r="F29" s="135"/>
+      <c r="G29" s="136"/>
+      <c r="H29" s="137"/>
+      <c r="I29" s="134"/>
+      <c r="J29" s="135"/>
+      <c r="K29" s="136"/>
+      <c r="L29" s="137"/>
+      <c r="M29" s="134"/>
+      <c r="N29" s="138"/>
+      <c r="O29" s="137"/>
+      <c r="P29" s="136"/>
+      <c r="Q29" s="134"/>
+      <c r="R29" s="135"/>
+      <c r="S29" s="139"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="136" t="s">
+      <c r="B30" s="140" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="137" t="s">
-        <v>102</v>
-      </c>
-      <c r="D30" s="91"/>
-      <c r="E30" s="138"/>
-      <c r="F30" s="139"/>
-      <c r="G30" s="139"/>
-      <c r="H30" s="140"/>
-      <c r="I30" s="141"/>
-      <c r="J30" s="139"/>
-      <c r="K30" s="139"/>
-      <c r="L30" s="140"/>
-      <c r="M30" s="141"/>
-      <c r="N30" s="139"/>
-      <c r="O30" s="140"/>
-      <c r="P30" s="139"/>
-      <c r="Q30" s="141"/>
-      <c r="R30" s="139"/>
-      <c r="S30" s="142"/>
+      <c r="C30" s="141" t="s">
+        <v>105</v>
+      </c>
+      <c r="D30" s="95"/>
+      <c r="E30" s="142"/>
+      <c r="F30" s="143"/>
+      <c r="G30" s="143"/>
+      <c r="H30" s="144"/>
+      <c r="I30" s="145"/>
+      <c r="J30" s="143"/>
+      <c r="K30" s="143"/>
+      <c r="L30" s="144"/>
+      <c r="M30" s="145"/>
+      <c r="N30" s="143"/>
+      <c r="O30" s="144"/>
+      <c r="P30" s="143"/>
+      <c r="Q30" s="145"/>
+      <c r="R30" s="143"/>
+      <c r="S30" s="146"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="143"/>
-      <c r="C31" s="144"/>
-      <c r="D31" s="98"/>
-      <c r="E31" s="145"/>
-      <c r="F31" s="146"/>
-      <c r="G31" s="146"/>
-      <c r="H31" s="147"/>
-      <c r="I31" s="148"/>
-      <c r="J31" s="146"/>
-      <c r="K31" s="149"/>
-      <c r="L31" s="147"/>
-      <c r="M31" s="148"/>
-      <c r="N31" s="146"/>
-      <c r="O31" s="147"/>
-      <c r="P31" s="146"/>
-      <c r="Q31" s="148"/>
-      <c r="R31" s="146"/>
-      <c r="S31" s="104"/>
+      <c r="B31" s="147"/>
+      <c r="C31" s="148"/>
+      <c r="D31" s="102"/>
+      <c r="E31" s="149"/>
+      <c r="F31" s="150"/>
+      <c r="G31" s="150"/>
+      <c r="H31" s="151"/>
+      <c r="I31" s="152"/>
+      <c r="J31" s="150"/>
+      <c r="K31" s="153"/>
+      <c r="L31" s="151"/>
+      <c r="M31" s="152"/>
+      <c r="N31" s="150"/>
+      <c r="O31" s="151"/>
+      <c r="P31" s="150"/>
+      <c r="Q31" s="152"/>
+      <c r="R31" s="150"/>
+      <c r="S31" s="108"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="143"/>
-      <c r="C32" s="144" t="s">
+      <c r="B32" s="147"/>
+      <c r="C32" s="148" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="106"/>
-      <c r="E32" s="150"/>
-      <c r="F32" s="151"/>
-      <c r="G32" s="151"/>
-      <c r="H32" s="152"/>
-      <c r="I32" s="153"/>
-      <c r="J32" s="151"/>
-      <c r="K32" s="151"/>
-      <c r="L32" s="152"/>
-      <c r="M32" s="153"/>
-      <c r="N32" s="151"/>
-      <c r="O32" s="152"/>
-      <c r="P32" s="151"/>
-      <c r="Q32" s="153"/>
-      <c r="R32" s="151"/>
-      <c r="S32" s="154"/>
+      <c r="D32" s="110"/>
+      <c r="E32" s="154"/>
+      <c r="F32" s="155"/>
+      <c r="G32" s="155"/>
+      <c r="H32" s="156"/>
+      <c r="I32" s="157"/>
+      <c r="J32" s="155"/>
+      <c r="K32" s="155"/>
+      <c r="L32" s="156"/>
+      <c r="M32" s="157"/>
+      <c r="N32" s="155"/>
+      <c r="O32" s="156"/>
+      <c r="P32" s="155"/>
+      <c r="Q32" s="157"/>
+      <c r="R32" s="155"/>
+      <c r="S32" s="158"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="143"/>
-      <c r="C33" s="144"/>
-      <c r="D33" s="98"/>
-      <c r="E33" s="145"/>
-      <c r="F33" s="149"/>
-      <c r="G33" s="146"/>
-      <c r="H33" s="155"/>
-      <c r="I33" s="156"/>
-      <c r="J33" s="146"/>
-      <c r="K33" s="149"/>
-      <c r="L33" s="147"/>
-      <c r="M33" s="148"/>
-      <c r="N33" s="146"/>
-      <c r="O33" s="147"/>
-      <c r="P33" s="146"/>
-      <c r="Q33" s="148"/>
-      <c r="R33" s="146"/>
-      <c r="S33" s="104"/>
+      <c r="B33" s="147"/>
+      <c r="C33" s="148"/>
+      <c r="D33" s="102"/>
+      <c r="E33" s="149"/>
+      <c r="F33" s="153"/>
+      <c r="G33" s="150"/>
+      <c r="H33" s="159"/>
+      <c r="I33" s="160"/>
+      <c r="J33" s="150"/>
+      <c r="K33" s="153"/>
+      <c r="L33" s="151"/>
+      <c r="M33" s="152"/>
+      <c r="N33" s="150"/>
+      <c r="O33" s="151"/>
+      <c r="P33" s="150"/>
+      <c r="Q33" s="152"/>
+      <c r="R33" s="150"/>
+      <c r="S33" s="108"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="143"/>
-      <c r="C34" s="97" t="s">
-        <v>159</v>
-      </c>
-      <c r="D34" s="129"/>
-      <c r="E34" s="157"/>
-      <c r="F34" s="158"/>
-      <c r="G34" s="158"/>
-      <c r="H34" s="159"/>
-      <c r="I34" s="160"/>
-      <c r="J34" s="158"/>
-      <c r="K34" s="158"/>
-      <c r="L34" s="159"/>
-      <c r="M34" s="160"/>
-      <c r="N34" s="158"/>
-      <c r="O34" s="159"/>
-      <c r="P34" s="158"/>
-      <c r="Q34" s="160"/>
-      <c r="R34" s="158"/>
-      <c r="S34" s="161"/>
-      <c r="U34" s="162"/>
-      <c r="V34" s="163" t="s">
-        <v>160</v>
+      <c r="B34" s="147"/>
+      <c r="C34" s="101" t="s">
+        <v>162</v>
+      </c>
+      <c r="D34" s="133"/>
+      <c r="E34" s="161"/>
+      <c r="F34" s="162"/>
+      <c r="G34" s="162"/>
+      <c r="H34" s="163"/>
+      <c r="I34" s="164"/>
+      <c r="J34" s="162"/>
+      <c r="K34" s="162"/>
+      <c r="L34" s="163"/>
+      <c r="M34" s="164"/>
+      <c r="N34" s="162"/>
+      <c r="O34" s="163"/>
+      <c r="P34" s="162"/>
+      <c r="Q34" s="164"/>
+      <c r="R34" s="162"/>
+      <c r="S34" s="165"/>
+      <c r="U34" s="166"/>
+      <c r="V34" s="167" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="164"/>
-      <c r="C35" s="165"/>
-      <c r="D35" s="116"/>
-      <c r="E35" s="166"/>
-      <c r="F35" s="167"/>
-      <c r="G35" s="167"/>
-      <c r="H35" s="168"/>
-      <c r="I35" s="169"/>
-      <c r="J35" s="167"/>
-      <c r="K35" s="167"/>
-      <c r="L35" s="168"/>
-      <c r="M35" s="169"/>
-      <c r="N35" s="167"/>
-      <c r="O35" s="168"/>
-      <c r="P35" s="167"/>
-      <c r="Q35" s="169"/>
-      <c r="R35" s="167"/>
-      <c r="S35" s="121"/>
-      <c r="U35" s="170"/>
-      <c r="V35" s="171" t="s">
-        <v>161</v>
+      <c r="B35" s="168"/>
+      <c r="C35" s="169"/>
+      <c r="D35" s="120"/>
+      <c r="E35" s="170"/>
+      <c r="F35" s="171"/>
+      <c r="G35" s="171"/>
+      <c r="H35" s="172"/>
+      <c r="I35" s="173"/>
+      <c r="J35" s="171"/>
+      <c r="K35" s="171"/>
+      <c r="L35" s="172"/>
+      <c r="M35" s="173"/>
+      <c r="N35" s="171"/>
+      <c r="O35" s="172"/>
+      <c r="P35" s="171"/>
+      <c r="Q35" s="173"/>
+      <c r="R35" s="171"/>
+      <c r="S35" s="125"/>
+      <c r="U35" s="174"/>
+      <c r="V35" s="175" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/HoferL-JournalPlanif-M5.xlsx
+++ b/Documentation/HoferL-JournalPlanif-M5.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
   <si>
     <t>date</t>
   </si>
@@ -264,25 +264,28 @@
     <t xml:space="preserve">Optimisation des requettes + algorithmes de tris. Optimisation de l'utilisation de la thread d'affichage. Correstion du sens d'animation de transition entre les pages. Optimisation des ressources. Compilation du schéma EF.</t>
   </si>
   <si>
+    <t xml:space="preserve">Recherche de pratique de programmation sur les MVVM.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implémentation correction de la séparation en MVVM.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentation des fichiers MVVM + Documentation du repertoire intérraction avec la BDD et de l'rchitecture globale et modélisation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recherche d'une solution optimal pour stocker des scan d'évaluation dans l'application</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Création d'un PoC du concept. Test de fonctionnement du WorkFlow : PDF -&gt; Compression images -&gt; Archive -&gt; PDF. Fonctionnel 6,8Mo -&gt; 400Ko.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implémentation et séparation des responsabilités dans des classes séparés. WorkFlow en mémoire et Blob pour la souvegarde dans SQLite fonctionnel. (sans test d'injection du blob)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finalisation du PoC. Très concluant, fonctionnel et fluide. Merge de la branche PDF -&gt; Main.</t>
+  </si>
+  <si>
     <t xml:space="preserve">&lt;-- A jour avec la BDD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recherche de pratique de programmation sur les MVVM.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implémentation correction de la séparation en MVVM.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Documentation des fichiers MVVM + Documentation du repertoire intérraction avec la BDD et de l'rchitecture globale et modélisation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recherche d'une solution optimal pour stocker des scan d'évaluation dans l'application</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Création d'un PoC du concept. Test de fonctionnement du WorkFlow : PDF -&gt; Compression images -&gt; Archive -&gt; PDF. Fonctionnel 6,8Mo -&gt; 400Ko.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implémentation et séparation des responsabilités dans des classes séparés. WorkFlow en mémoire et Blob pour la souvegarde dans SQLite fonctionnel. (sans test d'injection du blob)</t>
   </si>
   <si>
     <t>Phases</t>
@@ -1521,7 +1524,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="175">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1564,17 +1567,14 @@
     <xf fontId="0" fillId="0" borderId="2" numFmtId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="20" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2186,16 +2186,16 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>33.5</c:v>
+                  <c:v>37.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>41.5</c:v>
+                  <c:v>53.50000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2405,12 +2405,6 @@
           <c:tx>
             <c:strRef>
               <c:f>SommeParJours!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>somme</c:v>
-                </c:pt>
-              </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr bwMode="auto">
@@ -2428,69 +2422,15 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>SommeParJours!$A$2:$A$18</c:f>
-              <c:strCache>
-                <c:ptCount val="17"/>
-                <c:pt idx="0">
-                  <c:v>20.01.2026</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>27.01.2026</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>30.01.2026</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>03.02.2026</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>04.02.2026</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>06.02.2026</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>08.02.2026</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>09.02.2026</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>10.02.2026</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>12.02.2026</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>13.02.2026</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>24.02.2026</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>03.03.2026</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>05.03.2026</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>3/6/2026</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>3/7/2026</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>3/10/2026</c:v>
-                </c:pt>
-              </c:strCache>
+              <c:f>SommeParJours!$A$2:$A$27</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SommeParJours!$B$2:$B$18</c:f>
+              <c:f>SommeParJours!$B$2:$B$27</c:f>
               <c:numCache>
                 <c:formatCode>h:mm;@</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0.16666666666666666</c:v>
                 </c:pt>
@@ -2541,6 +2481,33 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>0.2916666666666667</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.08333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.1875</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.20833333333333334</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.14583333333333334</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.16666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.20833333333333334</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.3333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.20833333333333331</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3595,8 +3562,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E50">
-  <autoFilter ref="B2:E50"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E51">
+  <autoFilter ref="B2:E51"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -4160,7 +4127,7 @@
       </c>
       <c r="I3" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>2.5210084033613446e-002</v>
+        <v>2.4193548387096774e-002</v>
       </c>
       <c r="J3" s="12" t="str" cm="1">
         <f t="array" ref="J3:J9">_xlfn._xlws.FILTER(G3:G10,H3:H10&gt;0)</f>
@@ -4193,7 +4160,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>2.5210084033613446e-002</v>
+        <v>2.4193548387096774e-002</v>
       </c>
       <c r="J4" s="4" t="str">
         <f/>
@@ -4226,7 +4193,7 @@
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>7.5630252100840331e-002</v>
+        <v>7.2580645161290328e-002</v>
       </c>
       <c r="J5" s="4" t="str">
         <f/>
@@ -4259,7 +4226,7 @@
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.14285714285714285</v>
+        <v>0.13709677419354838</v>
       </c>
       <c r="J6" s="4" t="str">
         <f/>
@@ -4292,7 +4259,7 @@
       </c>
       <c r="I7" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.31512605042016806</v>
+        <v>0.30241935483870969</v>
       </c>
       <c r="J7" s="4" t="str">
         <f/>
@@ -4321,11 +4288,11 @@
       </c>
       <c r="H8" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>48.5</v>
+        <v>53.500000000000007</v>
       </c>
       <c r="I8" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.40756302521008403</v>
+        <v>0.43145161290322587</v>
       </c>
       <c r="J8" s="4" t="str">
         <f/>
@@ -4333,7 +4300,7 @@
       </c>
       <c r="K8" s="13">
         <f/>
-        <v>48.5</v>
+        <v>53.500000000000007</v>
       </c>
     </row>
     <row r="9">
@@ -4358,7 +4325,7 @@
       </c>
       <c r="I9" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>8.4033613445378148e-003</v>
+        <v>8.0645161290322578e-003</v>
       </c>
       <c r="J9" s="4" t="str">
         <f/>
@@ -4414,7 +4381,7 @@
       </c>
       <c r="H11" s="10">
         <f>SUM(H3:H10)</f>
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -4840,7 +4807,7 @@
       <c r="D41" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="E41" s="20" t="s">
         <v>65</v>
       </c>
     </row>
@@ -4854,7 +4821,7 @@
       <c r="D42" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="20" t="s">
         <v>66</v>
       </c>
     </row>
@@ -4868,7 +4835,7 @@
       <c r="D43" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="E43" s="20" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4882,11 +4849,8 @@
       <c r="D44" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E44" s="20" t="s">
         <v>68</v>
-      </c>
-      <c r="G44" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="45">
@@ -4900,7 +4864,7 @@
         <v>8</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46">
@@ -4914,7 +4878,7 @@
         <v>19</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" ht="42.75">
@@ -4927,229 +4891,240 @@
       <c r="D47" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E47" s="20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="48" ht="28.5">
+      <c r="B48" s="21">
+        <v>46102</v>
+      </c>
+      <c r="C48" s="22">
+        <v>8.3333333333333329e-002</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="20" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="48" ht="28.5">
-      <c r="B48" s="20">
+    <row r="49" ht="42.75">
+      <c r="B49" s="21">
         <v>46102</v>
       </c>
-      <c r="C48" s="21">
-        <v>8.3333333333333329e-002</v>
-      </c>
-      <c r="D48" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="E48" s="23" t="s">
+      <c r="C49" s="22">
+        <v>0.125</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="49" ht="42.75">
-      <c r="B49" s="20">
-        <v>46102</v>
-      </c>
-      <c r="C49" s="21">
-        <v>0.125</v>
-      </c>
-      <c r="D49" s="22" t="s">
+    <row r="50" ht="57">
+      <c r="B50" s="21">
+        <v>46103</v>
+      </c>
+      <c r="C50" s="22">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D50" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E49" s="23" t="s">
+      <c r="E50" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="50" ht="57">
-      <c r="B50" s="20">
+    <row r="51" ht="28.5">
+      <c r="B51" s="21">
         <v>46103</v>
       </c>
-      <c r="C50" s="21">
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="D50" s="22" t="s">
+      <c r="C51" s="22">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="D51" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E50" s="23" t="s">
+      <c r="E51" s="20" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="20"/>
-      <c r="C51" s="24"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="8"/>
+      <c r="G51" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="52">
-      <c r="B52" s="20"/>
-      <c r="C52" s="24"/>
+      <c r="B52" s="21"/>
+      <c r="C52" s="23"/>
       <c r="D52" s="7"/>
       <c r="E52" s="8"/>
     </row>
     <row r="53">
-      <c r="B53" s="20"/>
-      <c r="C53" s="24"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="23"/>
       <c r="D53" s="7"/>
       <c r="E53" s="8"/>
     </row>
     <row r="54">
-      <c r="B54" s="20"/>
-      <c r="C54" s="24"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="23"/>
       <c r="D54" s="7"/>
       <c r="E54" s="8"/>
     </row>
     <row r="55">
-      <c r="B55" s="20"/>
-      <c r="C55" s="24"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="23"/>
       <c r="D55" s="7"/>
       <c r="E55" s="8"/>
     </row>
     <row r="56">
-      <c r="B56" s="20"/>
-      <c r="C56" s="24"/>
+      <c r="B56" s="21"/>
+      <c r="C56" s="23"/>
       <c r="D56" s="7"/>
       <c r="E56" s="8"/>
     </row>
     <row r="57">
-      <c r="B57" s="20"/>
-      <c r="C57" s="24"/>
+      <c r="B57" s="21"/>
+      <c r="C57" s="23"/>
       <c r="D57" s="7"/>
       <c r="E57" s="8"/>
     </row>
     <row r="58">
-      <c r="B58" s="20"/>
-      <c r="C58" s="24"/>
+      <c r="B58" s="21"/>
+      <c r="C58" s="23"/>
       <c r="D58" s="7"/>
       <c r="E58" s="8"/>
     </row>
     <row r="59">
-      <c r="B59" s="20"/>
-      <c r="C59" s="24"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="23"/>
       <c r="D59" s="7"/>
       <c r="E59" s="8"/>
     </row>
     <row r="60">
-      <c r="B60" s="20"/>
-      <c r="C60" s="24"/>
+      <c r="B60" s="21"/>
+      <c r="C60" s="23"/>
       <c r="D60" s="7"/>
       <c r="E60" s="8"/>
     </row>
     <row r="61">
-      <c r="B61" s="20"/>
-      <c r="C61" s="24"/>
+      <c r="B61" s="21"/>
+      <c r="C61" s="23"/>
       <c r="D61" s="7"/>
       <c r="E61" s="8"/>
     </row>
     <row r="62">
-      <c r="B62" s="20"/>
-      <c r="C62" s="24"/>
+      <c r="B62" s="21"/>
+      <c r="C62" s="23"/>
       <c r="D62" s="7"/>
       <c r="E62" s="8"/>
     </row>
     <row r="63">
-      <c r="B63" s="20"/>
-      <c r="C63" s="24"/>
+      <c r="B63" s="21"/>
+      <c r="C63" s="23"/>
       <c r="D63" s="7"/>
       <c r="E63" s="8"/>
     </row>
     <row r="64">
-      <c r="B64" s="20"/>
-      <c r="C64" s="24"/>
+      <c r="B64" s="21"/>
+      <c r="C64" s="23"/>
       <c r="D64" s="7"/>
       <c r="E64" s="8"/>
     </row>
     <row r="65">
-      <c r="B65" s="20"/>
-      <c r="C65" s="24"/>
+      <c r="B65" s="21"/>
+      <c r="C65" s="23"/>
       <c r="D65" s="7"/>
       <c r="E65" s="8"/>
     </row>
     <row r="66">
-      <c r="B66" s="20"/>
-      <c r="C66" s="24"/>
+      <c r="B66" s="21"/>
+      <c r="C66" s="23"/>
       <c r="D66" s="7"/>
       <c r="E66" s="8"/>
     </row>
     <row r="67">
-      <c r="B67" s="20"/>
-      <c r="C67" s="24"/>
+      <c r="B67" s="21"/>
+      <c r="C67" s="23"/>
       <c r="D67" s="7"/>
       <c r="E67" s="8"/>
     </row>
     <row r="68">
-      <c r="B68" s="20"/>
-      <c r="C68" s="24"/>
+      <c r="B68" s="21"/>
+      <c r="C68" s="23"/>
       <c r="D68" s="7"/>
       <c r="E68" s="8"/>
     </row>
     <row r="69">
-      <c r="B69" s="20"/>
-      <c r="C69" s="24"/>
+      <c r="B69" s="21"/>
+      <c r="C69" s="23"/>
       <c r="D69" s="7"/>
       <c r="E69" s="8"/>
     </row>
     <row r="70">
-      <c r="B70" s="20"/>
-      <c r="C70" s="24"/>
+      <c r="B70" s="21"/>
+      <c r="C70" s="23"/>
       <c r="D70" s="7"/>
       <c r="E70" s="8"/>
     </row>
     <row r="71">
-      <c r="B71" s="20"/>
-      <c r="C71" s="24"/>
+      <c r="B71" s="21"/>
+      <c r="C71" s="23"/>
       <c r="D71" s="7"/>
       <c r="E71" s="8"/>
     </row>
     <row r="72">
-      <c r="B72" s="20"/>
-      <c r="C72" s="24"/>
+      <c r="B72" s="21"/>
+      <c r="C72" s="23"/>
       <c r="D72" s="7"/>
       <c r="E72" s="8"/>
     </row>
     <row r="73">
-      <c r="B73" s="20"/>
-      <c r="C73" s="24"/>
+      <c r="B73" s="21"/>
+      <c r="C73" s="23"/>
       <c r="D73" s="7"/>
       <c r="E73" s="8"/>
     </row>
     <row r="74">
-      <c r="B74" s="20"/>
-      <c r="C74" s="24"/>
+      <c r="B74" s="21"/>
+      <c r="C74" s="23"/>
       <c r="D74" s="7"/>
       <c r="E74" s="8"/>
     </row>
     <row r="75">
       <c r="B75" s="7"/>
-      <c r="C75" s="24"/>
+      <c r="C75" s="23"/>
       <c r="D75" s="7"/>
       <c r="E75" s="8"/>
     </row>
     <row r="76">
       <c r="B76" s="7"/>
-      <c r="C76" s="24"/>
+      <c r="C76" s="23"/>
       <c r="D76" s="7"/>
       <c r="E76" s="8"/>
     </row>
     <row r="77">
       <c r="B77" s="7"/>
-      <c r="C77" s="24"/>
+      <c r="C77" s="23"/>
       <c r="D77" s="7"/>
       <c r="E77" s="8"/>
     </row>
     <row r="78">
       <c r="B78" s="7"/>
-      <c r="C78" s="24"/>
+      <c r="C78" s="23"/>
       <c r="D78" s="7"/>
       <c r="E78" s="8"/>
     </row>
     <row r="79">
       <c r="B79" s="7"/>
-      <c r="C79" s="24"/>
+      <c r="C79" s="23"/>
       <c r="D79" s="7"/>
       <c r="E79" s="8"/>
     </row>
     <row r="80">
       <c r="B80" s="7"/>
-      <c r="C80" s="24"/>
+      <c r="C80" s="23"/>
       <c r="D80" s="7"/>
       <c r="E80" s="8"/>
     </row>
@@ -5169,7 +5144,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00FC00F8-008A-4DC7-AF34-001F00B8000F}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00D800C9-008E-42D5-940A-00D200B300B4}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -5201,1698 +5176,1734 @@
       <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="str" cm="1">
+      <c r="A2" s="24" t="str" cm="1">
         <f t="array" ref="A2:A27">_xlfn.UNIQUE(Journal[date])</f>
         <v>20.01.2026</v>
       </c>
-      <c r="B2" s="26">
+      <c r="B2" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A2,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C2" s="26"/>
+      <c r="C2" s="25"/>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="str">
+      <c r="A3" s="24" t="str">
         <f/>
         <v>27.01.2026</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="str">
+      <c r="A4" s="24" t="str">
         <f/>
         <v>30.01.2026</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C4"/>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="str">
+      <c r="A5" s="24" t="str">
         <f/>
         <v>03.02.2026</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0.25</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="str">
+      <c r="A6" s="24" t="str">
         <f/>
         <v>04.02.2026</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="str">
+      <c r="A7" s="24" t="str">
         <f/>
         <v>06.02.2026</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C7"/>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="str">
+      <c r="A8" s="24" t="str">
         <f/>
         <v>08.02.2026</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="str">
+      <c r="A9" s="24" t="str">
         <f/>
         <v>09.02.2026</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
         <v>4.1666666666666664e-002</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="str">
+      <c r="A10" s="24" t="str">
         <f/>
         <v>10.02.2026</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="str">
+      <c r="A11" s="24" t="str">
         <f/>
         <v>12.02.2026</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="str">
+      <c r="A12" s="24" t="str">
         <f/>
         <v>13.02.2026</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
         <v>6.25e-002</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="str">
+      <c r="A13" s="24" t="str">
         <f/>
         <v>24.02.2026</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0.125</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="str">
+      <c r="A14" s="24" t="str">
         <f/>
         <v>03.03.2026</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="str">
+      <c r="A15" s="24" t="str">
         <f/>
         <v>05.03.2026</v>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="25">
+      <c r="A16" s="24">
         <f/>
         <v>46087</v>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="25">
+      <c r="A17" s="24">
         <f/>
         <v>46088</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0.25</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="25">
+      <c r="A18" s="24">
         <f/>
         <v>46091</v>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="25">
+      <c r="A19" s="24">
         <f/>
         <v>46093</v>
       </c>
+      <c r="B19" s="25">
+        <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
+        <v>8.3333333333333329e-002</v>
+      </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="25">
+      <c r="A20" s="24">
         <f/>
         <v>46095</v>
       </c>
+      <c r="B20" s="25">
+        <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
+        <v>0.1875</v>
+      </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="25">
+      <c r="A21" s="24">
         <f/>
         <v>46096</v>
       </c>
+      <c r="B21" s="25">
+        <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
+        <v>0.20833333333333334</v>
+      </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="25">
+      <c r="A22" s="24">
         <f/>
         <v>46097</v>
       </c>
+      <c r="B22" s="25">
+        <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
+        <v>0.14583333333333334</v>
+      </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="25">
+      <c r="A23" s="24">
         <f/>
         <v>46098</v>
       </c>
+      <c r="B23" s="25">
+        <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
+        <v>0.16666666666666666</v>
+      </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="25">
+      <c r="A24" s="24">
         <f/>
         <v>46099</v>
       </c>
+      <c r="B24" s="25">
+        <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
+        <v>0.20833333333333334</v>
+      </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="25">
+      <c r="A25" s="24">
         <f/>
         <v>46100</v>
       </c>
+      <c r="B25" s="25">
+        <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
+        <v>0.33333333333333331</v>
+      </c>
       <c r="C25"/>
-      <c r="F25" s="27"/>
+      <c r="F25" s="26"/>
     </row>
     <row r="26">
-      <c r="A26" s="25">
+      <c r="A26" s="24">
         <f/>
         <v>46102</v>
       </c>
-      <c r="C26" s="28">
+      <c r="B26" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
-        <v>0</v>
+        <v>0.20833333333333331</v>
+      </c>
+      <c r="C26" s="27">
+        <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
+        <v>0.20833333333333331</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="25">
+      <c r="A27" s="24">
         <f/>
         <v>46103</v>
       </c>
-      <c r="C27" s="28">
+      <c r="B27" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
-        <v>0.16666666666666666</v>
+        <v>0.375</v>
+      </c>
+      <c r="C27" s="27">
+        <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
+        <v>0.375</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="25"/>
-      <c r="C28" s="28">
+      <c r="A28" s="24"/>
+      <c r="C28" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="25"/>
-      <c r="C29" s="28">
+      <c r="A29" s="24"/>
+      <c r="C29" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="25"/>
-      <c r="C30" s="28">
+      <c r="A30" s="24"/>
+      <c r="C30" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="25"/>
-      <c r="C31" s="28">
+      <c r="A31" s="24"/>
+      <c r="C31" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="25"/>
-      <c r="C32" s="28">
+      <c r="A32" s="24"/>
+      <c r="C32" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="25"/>
-      <c r="C33" s="28">
+      <c r="A33" s="24"/>
+      <c r="C33" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="25"/>
-      <c r="C34" s="28">
+      <c r="A34" s="24"/>
+      <c r="C34" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="25"/>
-      <c r="C35" s="28">
+      <c r="A35" s="24"/>
+      <c r="C35" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="25"/>
-      <c r="C36" s="28">
+      <c r="A36" s="24"/>
+      <c r="C36" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="25"/>
-      <c r="C37" s="28">
+      <c r="A37" s="24"/>
+      <c r="C37" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="25"/>
-      <c r="C38" s="28">
+      <c r="A38" s="24"/>
+      <c r="C38" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="25"/>
-      <c r="C39" s="28">
+      <c r="A39" s="24"/>
+      <c r="C39" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="25"/>
-      <c r="B40" s="26" t="str">
+      <c r="A40" s="24"/>
+      <c r="B40" s="25" t="str">
         <f t="shared" ref="B40:B103" si="0">IF(C40&gt;0,C40,"")</f>
         <v/>
       </c>
-      <c r="C40" s="28">
+      <c r="C40" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="25"/>
-      <c r="B41" s="26" t="str">
+      <c r="A41" s="24"/>
+      <c r="B41" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="28">
+      <c r="C41" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="29"/>
-      <c r="B42" s="26" t="str">
+      <c r="A42" s="28"/>
+      <c r="B42" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="28">
+      <c r="C42" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="29"/>
-      <c r="B43" s="26" t="str">
+      <c r="A43" s="28"/>
+      <c r="B43" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="28">
+      <c r="C43" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="29"/>
-      <c r="B44" s="26" t="str">
+      <c r="A44" s="28"/>
+      <c r="B44" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="28">
+      <c r="C44" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="29"/>
-      <c r="B45" s="26" t="str">
+      <c r="A45" s="28"/>
+      <c r="B45" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="28">
+      <c r="C45" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="29"/>
-      <c r="B46" s="26" t="str">
+      <c r="A46" s="28"/>
+      <c r="B46" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="28">
+      <c r="C46" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="30"/>
-      <c r="B47" s="26" t="str">
+      <c r="A47" s="29"/>
+      <c r="B47" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="28">
+      <c r="C47" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="30"/>
-      <c r="B48" s="26" t="str">
+      <c r="A48" s="29"/>
+      <c r="B48" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="28">
+      <c r="C48" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="30"/>
-      <c r="B49" s="26" t="str">
+      <c r="A49" s="29"/>
+      <c r="B49" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C49" s="28">
+      <c r="C49" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="30"/>
-      <c r="B50" s="26" t="str">
+      <c r="A50" s="29"/>
+      <c r="B50" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C50" s="28">
+      <c r="C50" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="30"/>
-      <c r="B51" s="26" t="str">
+      <c r="A51" s="29"/>
+      <c r="B51" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C51" s="28">
+      <c r="C51" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="30"/>
-      <c r="B52" s="26" t="str">
+      <c r="A52" s="29"/>
+      <c r="B52" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C52" s="28">
+      <c r="C52" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="30"/>
-      <c r="B53" s="26" t="str">
+      <c r="A53" s="29"/>
+      <c r="B53" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C53" s="28">
+      <c r="C53" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="30"/>
-      <c r="B54" s="26" t="str">
+      <c r="A54" s="29"/>
+      <c r="B54" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C54" s="28">
+      <c r="C54" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="30"/>
-      <c r="B55" s="26" t="str">
+      <c r="A55" s="29"/>
+      <c r="B55" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C55" s="28">
+      <c r="C55" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="30"/>
-      <c r="B56" s="26" t="str">
+      <c r="A56" s="29"/>
+      <c r="B56" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C56" s="28">
+      <c r="C56" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="30"/>
-      <c r="B57" s="26" t="str">
+      <c r="A57" s="29"/>
+      <c r="B57" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C57" s="28">
+      <c r="C57" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="30"/>
-      <c r="B58" s="26" t="str">
+      <c r="A58" s="29"/>
+      <c r="B58" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C58" s="28">
+      <c r="C58" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="30"/>
-      <c r="B59" s="26" t="str">
+      <c r="A59" s="29"/>
+      <c r="B59" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C59" s="28">
+      <c r="C59" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="30"/>
-      <c r="B60" s="26" t="str">
+      <c r="A60" s="29"/>
+      <c r="B60" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C60" s="28">
+      <c r="C60" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="30"/>
-      <c r="B61" s="26" t="str">
+      <c r="A61" s="29"/>
+      <c r="B61" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C61" s="28">
+      <c r="C61" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="30"/>
-      <c r="B62" s="26" t="str">
+      <c r="A62" s="29"/>
+      <c r="B62" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C62" s="28">
+      <c r="C62" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="30"/>
-      <c r="B63" s="26" t="str">
+      <c r="A63" s="29"/>
+      <c r="B63" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C63" s="28">
+      <c r="C63" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="30"/>
-      <c r="B64" s="26" t="str">
+      <c r="A64" s="29"/>
+      <c r="B64" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C64" s="28">
+      <c r="C64" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="30"/>
-      <c r="B65" s="26" t="str">
+      <c r="A65" s="29"/>
+      <c r="B65" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C65" s="28">
+      <c r="C65" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="30"/>
-      <c r="B66" s="26" t="str">
+      <c r="A66" s="29"/>
+      <c r="B66" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C66" s="28">
+      <c r="C66" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="30"/>
-      <c r="B67" s="26" t="str">
+      <c r="A67" s="29"/>
+      <c r="B67" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C67" s="28">
+      <c r="C67" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30"/>
-      <c r="B68" s="26" t="str">
+      <c r="A68" s="29"/>
+      <c r="B68" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C68" s="28">
+      <c r="C68" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30"/>
-      <c r="B69" s="26" t="str">
+      <c r="A69" s="29"/>
+      <c r="B69" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C69" s="28">
+      <c r="C69" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30"/>
-      <c r="B70" s="26" t="str">
+      <c r="A70" s="29"/>
+      <c r="B70" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C70" s="28">
+      <c r="C70" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="30"/>
-      <c r="B71" s="26" t="str">
+      <c r="A71" s="29"/>
+      <c r="B71" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C71" s="28">
+      <c r="C71" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="30"/>
-      <c r="B72" s="26" t="str">
+      <c r="A72" s="29"/>
+      <c r="B72" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C72" s="28">
+      <c r="C72" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="30"/>
-      <c r="B73" s="26" t="str">
+      <c r="A73" s="29"/>
+      <c r="B73" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C73" s="28">
+      <c r="C73" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="30"/>
-      <c r="B74" s="26" t="str">
+      <c r="A74" s="29"/>
+      <c r="B74" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C74" s="28">
+      <c r="C74" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="30"/>
-      <c r="B75" s="26" t="str">
+      <c r="A75" s="29"/>
+      <c r="B75" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C75" s="28">
+      <c r="C75" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="30"/>
-      <c r="B76" s="26" t="str">
+      <c r="A76" s="29"/>
+      <c r="B76" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C76" s="28">
+      <c r="C76" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30"/>
-      <c r="B77" s="26" t="str">
+      <c r="A77" s="29"/>
+      <c r="B77" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C77" s="28">
+      <c r="C77" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30"/>
-      <c r="B78" s="26" t="str">
+      <c r="A78" s="29"/>
+      <c r="B78" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C78" s="28">
+      <c r="C78" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="30"/>
-      <c r="B79" s="26" t="str">
+      <c r="A79" s="29"/>
+      <c r="B79" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C79" s="28">
+      <c r="C79" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="30"/>
-      <c r="B80" s="26" t="str">
+      <c r="A80" s="29"/>
+      <c r="B80" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C80" s="28">
+      <c r="C80" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="30"/>
-      <c r="B81" s="26" t="str">
+      <c r="A81" s="29"/>
+      <c r="B81" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C81" s="28">
+      <c r="C81" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="30"/>
-      <c r="B82" s="26" t="str">
+      <c r="A82" s="29"/>
+      <c r="B82" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C82" s="28">
+      <c r="C82" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="30"/>
-      <c r="B83" s="26" t="str">
+      <c r="A83" s="29"/>
+      <c r="B83" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C83" s="28">
+      <c r="C83" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="30"/>
-      <c r="B84" s="26" t="str">
+      <c r="A84" s="29"/>
+      <c r="B84" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C84" s="28">
+      <c r="C84" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="30"/>
-      <c r="B85" s="26" t="str">
+      <c r="A85" s="29"/>
+      <c r="B85" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C85" s="28">
+      <c r="C85" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="30"/>
-      <c r="B86" s="26" t="str">
+      <c r="A86" s="29"/>
+      <c r="B86" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C86" s="28">
+      <c r="C86" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="30"/>
-      <c r="B87" s="26" t="str">
+      <c r="A87" s="29"/>
+      <c r="B87" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C87" s="28">
+      <c r="C87" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="30"/>
-      <c r="B88" s="26" t="str">
+      <c r="A88" s="29"/>
+      <c r="B88" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C88" s="28">
+      <c r="C88" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="30"/>
-      <c r="B89" s="26" t="str">
+      <c r="A89" s="29"/>
+      <c r="B89" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C89" s="28">
+      <c r="C89" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="30"/>
-      <c r="B90" s="26" t="str">
+      <c r="A90" s="29"/>
+      <c r="B90" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C90" s="28">
+      <c r="C90" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="30"/>
-      <c r="B91" s="26" t="str">
+      <c r="A91" s="29"/>
+      <c r="B91" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C91" s="28">
+      <c r="C91" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="30"/>
-      <c r="B92" s="26" t="str">
+      <c r="A92" s="29"/>
+      <c r="B92" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C92" s="28">
+      <c r="C92" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="30"/>
-      <c r="B93" s="26" t="str">
+      <c r="A93" s="29"/>
+      <c r="B93" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C93" s="28">
+      <c r="C93" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="30"/>
-      <c r="B94" s="26" t="str">
+      <c r="A94" s="29"/>
+      <c r="B94" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C94" s="28">
+      <c r="C94" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="30"/>
-      <c r="B95" s="26" t="str">
+      <c r="A95" s="29"/>
+      <c r="B95" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C95" s="28">
+      <c r="C95" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="30"/>
-      <c r="B96" s="26" t="str">
+      <c r="A96" s="29"/>
+      <c r="B96" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C96" s="28">
+      <c r="C96" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="30"/>
-      <c r="B97" s="26" t="str">
+      <c r="A97" s="29"/>
+      <c r="B97" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C97" s="28">
+      <c r="C97" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="30"/>
-      <c r="B98" s="26" t="str">
+      <c r="A98" s="29"/>
+      <c r="B98" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C98" s="28">
+      <c r="C98" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="30"/>
-      <c r="B99" s="26" t="str">
+      <c r="A99" s="29"/>
+      <c r="B99" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C99" s="28">
+      <c r="C99" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="30"/>
-      <c r="B100" s="26" t="str">
+      <c r="A100" s="29"/>
+      <c r="B100" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C100" s="28">
+      <c r="C100" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="30"/>
-      <c r="B101" s="26" t="str">
+      <c r="A101" s="29"/>
+      <c r="B101" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C101" s="28">
+      <c r="C101" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="30"/>
-      <c r="B102" s="26" t="str">
+      <c r="A102" s="29"/>
+      <c r="B102" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C102" s="28">
+      <c r="C102" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="30"/>
-      <c r="B103" s="26" t="str">
+      <c r="A103" s="29"/>
+      <c r="B103" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C103" s="28">
+      <c r="C103" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="30"/>
-      <c r="B104" s="26" t="str">
+      <c r="A104" s="29"/>
+      <c r="B104" s="25" t="str">
         <f t="shared" ref="B104:B114" si="1">IF(C104&gt;0,C104,"")</f>
         <v/>
       </c>
-      <c r="C104" s="28">
+      <c r="C104" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="30"/>
-      <c r="B105" s="26" t="str">
+      <c r="A105" s="29"/>
+      <c r="B105" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C105" s="28">
+      <c r="C105" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="30"/>
-      <c r="B106" s="26" t="str">
+      <c r="A106" s="29"/>
+      <c r="B106" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C106" s="28">
+      <c r="C106" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="30"/>
-      <c r="B107" s="26" t="str">
+      <c r="A107" s="29"/>
+      <c r="B107" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C107" s="28">
+      <c r="C107" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="30"/>
-      <c r="B108" s="26" t="str">
+      <c r="A108" s="29"/>
+      <c r="B108" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C108" s="28">
+      <c r="C108" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="30"/>
-      <c r="B109" s="26" t="str">
+      <c r="A109" s="29"/>
+      <c r="B109" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C109" s="28">
+      <c r="C109" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="30"/>
-      <c r="B110" s="26" t="str">
+      <c r="A110" s="29"/>
+      <c r="B110" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C110" s="28">
+      <c r="C110" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="30"/>
-      <c r="B111" s="26" t="str">
+      <c r="A111" s="29"/>
+      <c r="B111" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C111" s="28">
+      <c r="C111" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="30"/>
-      <c r="B112" s="26" t="str">
+      <c r="A112" s="29"/>
+      <c r="B112" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C112" s="28">
+      <c r="C112" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="30"/>
-      <c r="B113" s="26" t="str">
+      <c r="A113" s="29"/>
+      <c r="B113" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C113" s="28">
+      <c r="C113" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="30"/>
-      <c r="B114" s="26" t="str">
+      <c r="A114" s="29"/>
+      <c r="B114" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C114" s="28">
+      <c r="C114" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="30"/>
-      <c r="B115" s="30"/>
-      <c r="C115" s="28"/>
+      <c r="A115" s="29"/>
+      <c r="B115" s="29"/>
+      <c r="C115" s="27"/>
     </row>
     <row r="116">
-      <c r="A116" s="30"/>
-      <c r="B116" s="30"/>
-      <c r="C116" s="28"/>
+      <c r="A116" s="29"/>
+      <c r="B116" s="29"/>
+      <c r="C116" s="27"/>
     </row>
     <row r="117">
-      <c r="A117" s="30"/>
-      <c r="B117" s="30"/>
-      <c r="C117" s="28"/>
+      <c r="A117" s="29"/>
+      <c r="B117" s="29"/>
+      <c r="C117" s="27"/>
     </row>
     <row r="118">
-      <c r="A118" s="30"/>
-      <c r="B118" s="30"/>
-      <c r="C118" s="28"/>
+      <c r="A118" s="29"/>
+      <c r="B118" s="29"/>
+      <c r="C118" s="27"/>
     </row>
     <row r="119">
-      <c r="A119" s="30"/>
-      <c r="B119" s="30"/>
-      <c r="C119" s="28"/>
+      <c r="A119" s="29"/>
+      <c r="B119" s="29"/>
+      <c r="C119" s="27"/>
     </row>
     <row r="120">
-      <c r="A120" s="30"/>
-      <c r="B120" s="30"/>
-      <c r="C120" s="28"/>
+      <c r="A120" s="29"/>
+      <c r="B120" s="29"/>
+      <c r="C120" s="27"/>
     </row>
     <row r="121">
-      <c r="A121" s="30"/>
-      <c r="B121" s="30"/>
-      <c r="C121" s="28"/>
+      <c r="A121" s="29"/>
+      <c r="B121" s="29"/>
+      <c r="C121" s="27"/>
     </row>
     <row r="122">
-      <c r="A122" s="30"/>
-      <c r="B122" s="30"/>
-      <c r="C122" s="28"/>
+      <c r="A122" s="29"/>
+      <c r="B122" s="29"/>
+      <c r="C122" s="27"/>
     </row>
     <row r="123">
-      <c r="A123" s="30"/>
-      <c r="B123" s="30"/>
-      <c r="C123" s="28"/>
+      <c r="A123" s="29"/>
+      <c r="B123" s="29"/>
+      <c r="C123" s="27"/>
     </row>
     <row r="124">
-      <c r="A124" s="30"/>
-      <c r="B124" s="30"/>
-      <c r="C124" s="28"/>
+      <c r="A124" s="29"/>
+      <c r="B124" s="29"/>
+      <c r="C124" s="27"/>
     </row>
     <row r="125">
-      <c r="A125" s="30"/>
-      <c r="B125" s="30"/>
-      <c r="C125" s="28"/>
+      <c r="A125" s="29"/>
+      <c r="B125" s="29"/>
+      <c r="C125" s="27"/>
     </row>
     <row r="126">
-      <c r="A126" s="30"/>
-      <c r="B126" s="30"/>
-      <c r="C126" s="28"/>
+      <c r="A126" s="29"/>
+      <c r="B126" s="29"/>
+      <c r="C126" s="27"/>
     </row>
     <row r="127">
-      <c r="A127" s="30"/>
-      <c r="B127" s="30"/>
-      <c r="C127" s="28"/>
+      <c r="A127" s="29"/>
+      <c r="B127" s="29"/>
+      <c r="C127" s="27"/>
     </row>
     <row r="128">
-      <c r="A128" s="30"/>
-      <c r="B128" s="30"/>
-      <c r="C128" s="28"/>
+      <c r="A128" s="29"/>
+      <c r="B128" s="29"/>
+      <c r="C128" s="27"/>
     </row>
     <row r="129">
-      <c r="A129" s="30"/>
-      <c r="B129" s="30"/>
-      <c r="C129" s="28"/>
+      <c r="A129" s="29"/>
+      <c r="B129" s="29"/>
+      <c r="C129" s="27"/>
     </row>
     <row r="130">
-      <c r="A130" s="30"/>
-      <c r="B130" s="30"/>
-      <c r="C130" s="28"/>
+      <c r="A130" s="29"/>
+      <c r="B130" s="29"/>
+      <c r="C130" s="27"/>
     </row>
     <row r="131">
-      <c r="A131" s="30"/>
-      <c r="B131" s="30"/>
-      <c r="C131" s="28"/>
+      <c r="A131" s="29"/>
+      <c r="B131" s="29"/>
+      <c r="C131" s="27"/>
     </row>
     <row r="132">
-      <c r="A132" s="30"/>
-      <c r="B132" s="30"/>
-      <c r="C132" s="28"/>
+      <c r="A132" s="29"/>
+      <c r="B132" s="29"/>
+      <c r="C132" s="27"/>
     </row>
     <row r="133">
-      <c r="A133" s="30"/>
-      <c r="B133" s="30"/>
-      <c r="C133" s="28"/>
+      <c r="A133" s="29"/>
+      <c r="B133" s="29"/>
+      <c r="C133" s="27"/>
     </row>
     <row r="134">
-      <c r="A134" s="30"/>
-      <c r="B134" s="30"/>
-      <c r="C134" s="28"/>
+      <c r="A134" s="29"/>
+      <c r="B134" s="29"/>
+      <c r="C134" s="27"/>
     </row>
     <row r="135">
-      <c r="A135" s="30"/>
-      <c r="B135" s="30"/>
-      <c r="C135" s="28"/>
+      <c r="A135" s="29"/>
+      <c r="B135" s="29"/>
+      <c r="C135" s="27"/>
     </row>
     <row r="136">
-      <c r="A136" s="30"/>
-      <c r="B136" s="30"/>
-      <c r="C136" s="28"/>
+      <c r="A136" s="29"/>
+      <c r="B136" s="29"/>
+      <c r="C136" s="27"/>
     </row>
     <row r="137">
-      <c r="A137" s="30"/>
-      <c r="B137" s="30"/>
-      <c r="C137" s="28"/>
+      <c r="A137" s="29"/>
+      <c r="B137" s="29"/>
+      <c r="C137" s="27"/>
     </row>
     <row r="138">
-      <c r="A138" s="30"/>
-      <c r="B138" s="30"/>
-      <c r="C138" s="28"/>
+      <c r="A138" s="29"/>
+      <c r="B138" s="29"/>
+      <c r="C138" s="27"/>
     </row>
     <row r="139">
-      <c r="A139" s="30"/>
-      <c r="B139" s="30"/>
-      <c r="C139" s="28"/>
+      <c r="A139" s="29"/>
+      <c r="B139" s="29"/>
+      <c r="C139" s="27"/>
     </row>
     <row r="140">
-      <c r="A140" s="30"/>
-      <c r="B140" s="30"/>
-      <c r="C140" s="28"/>
+      <c r="A140" s="29"/>
+      <c r="B140" s="29"/>
+      <c r="C140" s="27"/>
     </row>
     <row r="141">
-      <c r="A141" s="30"/>
-      <c r="B141" s="30"/>
-      <c r="C141" s="28"/>
+      <c r="A141" s="29"/>
+      <c r="B141" s="29"/>
+      <c r="C141" s="27"/>
     </row>
     <row r="142">
-      <c r="A142" s="30"/>
-      <c r="B142" s="30"/>
-      <c r="C142" s="28"/>
+      <c r="A142" s="29"/>
+      <c r="B142" s="29"/>
+      <c r="C142" s="27"/>
     </row>
     <row r="143">
-      <c r="A143" s="30"/>
-      <c r="B143" s="30"/>
-      <c r="C143" s="28"/>
+      <c r="A143" s="29"/>
+      <c r="B143" s="29"/>
+      <c r="C143" s="27"/>
     </row>
     <row r="144">
-      <c r="A144" s="30"/>
-      <c r="B144" s="30"/>
-      <c r="C144" s="28"/>
+      <c r="A144" s="29"/>
+      <c r="B144" s="29"/>
+      <c r="C144" s="27"/>
     </row>
     <row r="145">
-      <c r="A145" s="30"/>
-      <c r="B145" s="30"/>
-      <c r="C145" s="28"/>
+      <c r="A145" s="29"/>
+      <c r="B145" s="29"/>
+      <c r="C145" s="27"/>
     </row>
     <row r="146">
-      <c r="A146" s="30"/>
-      <c r="B146" s="30"/>
-      <c r="C146" s="28"/>
+      <c r="A146" s="29"/>
+      <c r="B146" s="29"/>
+      <c r="C146" s="27"/>
     </row>
     <row r="147">
-      <c r="A147" s="30"/>
-      <c r="B147" s="30"/>
-      <c r="C147" s="28"/>
+      <c r="A147" s="29"/>
+      <c r="B147" s="29"/>
+      <c r="C147" s="27"/>
     </row>
     <row r="148">
-      <c r="A148" s="30"/>
-      <c r="B148" s="30"/>
-      <c r="C148" s="28"/>
+      <c r="A148" s="29"/>
+      <c r="B148" s="29"/>
+      <c r="C148" s="27"/>
     </row>
     <row r="149">
-      <c r="A149" s="30"/>
-      <c r="B149" s="30"/>
-      <c r="C149" s="28"/>
+      <c r="A149" s="29"/>
+      <c r="B149" s="29"/>
+      <c r="C149" s="27"/>
     </row>
     <row r="150">
-      <c r="A150" s="30"/>
-      <c r="B150" s="30"/>
-      <c r="C150" s="28"/>
+      <c r="A150" s="29"/>
+      <c r="B150" s="29"/>
+      <c r="C150" s="27"/>
     </row>
     <row r="151">
-      <c r="A151" s="30"/>
-      <c r="B151" s="30"/>
-      <c r="C151" s="28"/>
+      <c r="A151" s="29"/>
+      <c r="B151" s="29"/>
+      <c r="C151" s="27"/>
     </row>
     <row r="152">
-      <c r="A152" s="30"/>
-      <c r="B152" s="30"/>
-      <c r="C152" s="28"/>
+      <c r="A152" s="29"/>
+      <c r="B152" s="29"/>
+      <c r="C152" s="27"/>
     </row>
     <row r="153">
-      <c r="A153" s="30"/>
-      <c r="B153" s="30"/>
-      <c r="C153" s="28"/>
+      <c r="A153" s="29"/>
+      <c r="B153" s="29"/>
+      <c r="C153" s="27"/>
     </row>
     <row r="154">
-      <c r="A154" s="30"/>
-      <c r="B154" s="30"/>
-      <c r="C154" s="28"/>
+      <c r="A154" s="29"/>
+      <c r="B154" s="29"/>
+      <c r="C154" s="27"/>
     </row>
     <row r="155">
-      <c r="A155" s="30"/>
-      <c r="B155" s="30"/>
-      <c r="C155" s="28"/>
+      <c r="A155" s="29"/>
+      <c r="B155" s="29"/>
+      <c r="C155" s="27"/>
     </row>
     <row r="156">
-      <c r="A156" s="30"/>
-      <c r="B156" s="30"/>
-      <c r="C156" s="28"/>
+      <c r="A156" s="29"/>
+      <c r="B156" s="29"/>
+      <c r="C156" s="27"/>
     </row>
     <row r="157">
-      <c r="A157" s="30"/>
-      <c r="B157" s="30"/>
-      <c r="C157" s="28"/>
+      <c r="A157" s="29"/>
+      <c r="B157" s="29"/>
+      <c r="C157" s="27"/>
     </row>
     <row r="158">
-      <c r="A158" s="30"/>
-      <c r="B158" s="30"/>
-      <c r="C158" s="28"/>
+      <c r="A158" s="29"/>
+      <c r="B158" s="29"/>
+      <c r="C158" s="27"/>
     </row>
     <row r="159">
-      <c r="A159" s="30"/>
-      <c r="B159" s="30"/>
+      <c r="A159" s="29"/>
+      <c r="B159" s="29"/>
     </row>
     <row r="160">
-      <c r="A160" s="30"/>
-      <c r="B160" s="30"/>
+      <c r="A160" s="29"/>
+      <c r="B160" s="29"/>
     </row>
     <row r="161">
-      <c r="A161" s="30"/>
-      <c r="B161" s="30"/>
+      <c r="A161" s="29"/>
+      <c r="B161" s="29"/>
     </row>
     <row r="162">
-      <c r="A162" s="30"/>
-      <c r="B162" s="30"/>
+      <c r="A162" s="29"/>
+      <c r="B162" s="29"/>
     </row>
     <row r="163">
-      <c r="A163" s="30"/>
-      <c r="B163" s="30"/>
+      <c r="A163" s="29"/>
+      <c r="B163" s="29"/>
     </row>
     <row r="164">
-      <c r="A164" s="30"/>
-      <c r="B164" s="30"/>
+      <c r="A164" s="29"/>
+      <c r="B164" s="29"/>
     </row>
     <row r="165">
-      <c r="A165" s="30"/>
-      <c r="B165" s="30"/>
+      <c r="A165" s="29"/>
+      <c r="B165" s="29"/>
     </row>
     <row r="166">
-      <c r="A166" s="30"/>
-      <c r="B166" s="30"/>
+      <c r="A166" s="29"/>
+      <c r="B166" s="29"/>
     </row>
     <row r="167">
-      <c r="A167" s="30"/>
-      <c r="B167" s="30"/>
+      <c r="A167" s="29"/>
+      <c r="B167" s="29"/>
     </row>
     <row r="168">
-      <c r="A168" s="30"/>
-      <c r="B168" s="30"/>
+      <c r="A168" s="29"/>
+      <c r="B168" s="29"/>
     </row>
     <row r="169">
-      <c r="A169" s="30"/>
-      <c r="B169" s="30"/>
+      <c r="A169" s="29"/>
+      <c r="B169" s="29"/>
     </row>
     <row r="170">
-      <c r="A170" s="30"/>
-      <c r="B170" s="30"/>
+      <c r="A170" s="29"/>
+      <c r="B170" s="29"/>
     </row>
     <row r="171">
-      <c r="A171" s="30"/>
-      <c r="B171" s="30"/>
+      <c r="A171" s="29"/>
+      <c r="B171" s="29"/>
     </row>
     <row r="172">
-      <c r="A172" s="30"/>
-      <c r="B172" s="30"/>
+      <c r="A172" s="29"/>
+      <c r="B172" s="29"/>
     </row>
     <row r="173">
-      <c r="A173" s="30"/>
-      <c r="B173" s="30"/>
+      <c r="A173" s="29"/>
+      <c r="B173" s="29"/>
     </row>
     <row r="174">
-      <c r="A174" s="30"/>
-      <c r="B174" s="30"/>
+      <c r="A174" s="29"/>
+      <c r="B174" s="29"/>
     </row>
     <row r="175">
-      <c r="A175" s="30"/>
-      <c r="B175" s="30"/>
+      <c r="A175" s="29"/>
+      <c r="B175" s="29"/>
     </row>
     <row r="176">
-      <c r="A176" s="30"/>
-      <c r="B176" s="30"/>
+      <c r="A176" s="29"/>
+      <c r="B176" s="29"/>
     </row>
     <row r="177">
-      <c r="A177" s="30"/>
-      <c r="B177" s="30"/>
+      <c r="A177" s="29"/>
+      <c r="B177" s="29"/>
     </row>
     <row r="178">
-      <c r="A178" s="30"/>
-      <c r="B178" s="30"/>
+      <c r="A178" s="29"/>
+      <c r="B178" s="29"/>
     </row>
     <row r="179">
-      <c r="A179" s="30"/>
-      <c r="B179" s="30"/>
+      <c r="A179" s="29"/>
+      <c r="B179" s="29"/>
     </row>
     <row r="180">
-      <c r="A180" s="30"/>
-      <c r="B180" s="30"/>
+      <c r="A180" s="29"/>
+      <c r="B180" s="29"/>
     </row>
     <row r="181">
-      <c r="A181" s="30"/>
-      <c r="B181" s="30"/>
+      <c r="A181" s="29"/>
+      <c r="B181" s="29"/>
     </row>
     <row r="182">
-      <c r="A182" s="30"/>
-      <c r="B182" s="30"/>
+      <c r="A182" s="29"/>
+      <c r="B182" s="29"/>
     </row>
     <row r="183">
-      <c r="A183" s="30"/>
-      <c r="B183" s="30"/>
+      <c r="A183" s="29"/>
+      <c r="B183" s="29"/>
     </row>
     <row r="184">
-      <c r="A184" s="30"/>
-      <c r="B184" s="30"/>
+      <c r="A184" s="29"/>
+      <c r="B184" s="29"/>
     </row>
     <row r="185">
-      <c r="A185" s="30"/>
-      <c r="B185" s="30"/>
+      <c r="A185" s="29"/>
+      <c r="B185" s="29"/>
     </row>
     <row r="186">
-      <c r="A186" s="30"/>
-      <c r="B186" s="30"/>
+      <c r="A186" s="29"/>
+      <c r="B186" s="29"/>
     </row>
     <row r="187">
-      <c r="A187" s="30"/>
-      <c r="B187" s="30"/>
+      <c r="A187" s="29"/>
+      <c r="B187" s="29"/>
     </row>
     <row r="188">
-      <c r="A188" s="30"/>
-      <c r="B188" s="30"/>
+      <c r="A188" s="29"/>
+      <c r="B188" s="29"/>
     </row>
     <row r="189">
-      <c r="A189" s="30"/>
-      <c r="B189" s="30"/>
+      <c r="A189" s="29"/>
+      <c r="B189" s="29"/>
     </row>
     <row r="190">
-      <c r="A190" s="30"/>
-      <c r="B190" s="30"/>
+      <c r="A190" s="29"/>
+      <c r="B190" s="29"/>
     </row>
     <row r="191">
-      <c r="A191" s="30"/>
-      <c r="B191" s="30"/>
+      <c r="A191" s="29"/>
+      <c r="B191" s="29"/>
     </row>
     <row r="192">
-      <c r="A192" s="30"/>
-      <c r="B192" s="30"/>
+      <c r="A192" s="29"/>
+      <c r="B192" s="29"/>
     </row>
     <row r="193">
-      <c r="A193" s="30"/>
-      <c r="B193" s="30"/>
+      <c r="A193" s="29"/>
+      <c r="B193" s="29"/>
     </row>
     <row r="194">
-      <c r="A194" s="30"/>
-      <c r="B194" s="30"/>
+      <c r="A194" s="29"/>
+      <c r="B194" s="29"/>
     </row>
     <row r="195">
-      <c r="A195" s="30"/>
-      <c r="B195" s="30"/>
+      <c r="A195" s="29"/>
+      <c r="B195" s="29"/>
     </row>
     <row r="196">
-      <c r="A196" s="30"/>
-      <c r="B196" s="30"/>
+      <c r="A196" s="29"/>
+      <c r="B196" s="29"/>
     </row>
     <row r="197">
-      <c r="A197" s="30"/>
-      <c r="B197" s="30"/>
+      <c r="A197" s="29"/>
+      <c r="B197" s="29"/>
     </row>
     <row r="198">
-      <c r="A198" s="30"/>
-      <c r="B198" s="30"/>
+      <c r="A198" s="29"/>
+      <c r="B198" s="29"/>
     </row>
     <row r="199">
-      <c r="A199" s="30"/>
-      <c r="B199" s="30"/>
+      <c r="A199" s="29"/>
+      <c r="B199" s="29"/>
     </row>
     <row r="200">
-      <c r="A200" s="30"/>
-      <c r="B200" s="30"/>
+      <c r="A200" s="29"/>
+      <c r="B200" s="29"/>
     </row>
     <row r="201">
-      <c r="A201" s="30"/>
-      <c r="B201" s="30"/>
+      <c r="A201" s="29"/>
+      <c r="B201" s="29"/>
     </row>
     <row r="202">
-      <c r="A202" s="30"/>
-      <c r="B202" s="30"/>
+      <c r="A202" s="29"/>
+      <c r="B202" s="29"/>
     </row>
     <row r="203">
-      <c r="A203" s="30"/>
-      <c r="B203" s="30"/>
+      <c r="A203" s="29"/>
+      <c r="B203" s="29"/>
     </row>
     <row r="204">
-      <c r="A204" s="30"/>
-      <c r="B204" s="30"/>
+      <c r="A204" s="29"/>
+      <c r="B204" s="29"/>
     </row>
     <row r="205">
-      <c r="A205" s="30"/>
-      <c r="B205" s="30"/>
+      <c r="A205" s="29"/>
+      <c r="B205" s="29"/>
     </row>
     <row r="206">
-      <c r="A206" s="30"/>
-      <c r="B206" s="30"/>
+      <c r="A206" s="29"/>
+      <c r="B206" s="29"/>
     </row>
     <row r="207">
-      <c r="A207" s="30"/>
-      <c r="B207" s="30"/>
+      <c r="A207" s="29"/>
+      <c r="B207" s="29"/>
     </row>
     <row r="208">
-      <c r="A208" s="30"/>
-      <c r="B208" s="30"/>
+      <c r="A208" s="29"/>
+      <c r="B208" s="29"/>
     </row>
     <row r="209">
-      <c r="A209" s="30"/>
-      <c r="B209" s="30"/>
+      <c r="A209" s="29"/>
+      <c r="B209" s="29"/>
     </row>
     <row r="210">
-      <c r="A210" s="30"/>
-      <c r="B210" s="30"/>
+      <c r="A210" s="29"/>
+      <c r="B210" s="29"/>
     </row>
     <row r="211">
-      <c r="A211" s="30"/>
-      <c r="B211" s="30"/>
+      <c r="A211" s="29"/>
+      <c r="B211" s="29"/>
     </row>
     <row r="212">
-      <c r="A212" s="30"/>
-      <c r="B212" s="30"/>
+      <c r="A212" s="29"/>
+      <c r="B212" s="29"/>
     </row>
     <row r="213">
-      <c r="A213" s="30"/>
-      <c r="B213" s="30"/>
+      <c r="A213" s="29"/>
+      <c r="B213" s="29"/>
     </row>
     <row r="214">
-      <c r="A214" s="30"/>
-      <c r="B214" s="30"/>
+      <c r="A214" s="29"/>
+      <c r="B214" s="29"/>
     </row>
     <row r="215">
-      <c r="A215" s="30"/>
-      <c r="B215" s="30"/>
+      <c r="A215" s="29"/>
+      <c r="B215" s="29"/>
     </row>
     <row r="216">
-      <c r="A216" s="30"/>
-      <c r="B216" s="30"/>
+      <c r="A216" s="29"/>
+      <c r="B216" s="29"/>
     </row>
     <row r="217">
-      <c r="A217" s="30"/>
-      <c r="B217" s="30"/>
+      <c r="A217" s="29"/>
+      <c r="B217" s="29"/>
     </row>
     <row r="218">
-      <c r="A218" s="30"/>
-      <c r="B218" s="30"/>
+      <c r="A218" s="29"/>
+      <c r="B218" s="29"/>
     </row>
     <row r="219">
-      <c r="A219" s="30"/>
-      <c r="B219" s="30"/>
+      <c r="A219" s="29"/>
+      <c r="B219" s="29"/>
     </row>
     <row r="220">
-      <c r="A220" s="30"/>
-      <c r="B220" s="30"/>
+      <c r="A220" s="29"/>
+      <c r="B220" s="29"/>
     </row>
     <row r="221">
-      <c r="A221" s="30"/>
-      <c r="B221" s="30"/>
+      <c r="A221" s="29"/>
+      <c r="B221" s="29"/>
     </row>
     <row r="222">
-      <c r="A222" s="30"/>
-      <c r="B222" s="30"/>
+      <c r="A222" s="29"/>
+      <c r="B222" s="29"/>
     </row>
     <row r="223">
-      <c r="A223" s="30"/>
-      <c r="B223" s="30"/>
+      <c r="A223" s="29"/>
+      <c r="B223" s="29"/>
     </row>
     <row r="224">
-      <c r="A224" s="30"/>
-      <c r="B224" s="30"/>
+      <c r="A224" s="29"/>
+      <c r="B224" s="29"/>
     </row>
     <row r="225">
-      <c r="A225" s="30"/>
-      <c r="B225" s="30"/>
+      <c r="A225" s="29"/>
+      <c r="B225" s="29"/>
     </row>
     <row r="226">
-      <c r="A226" s="30"/>
-      <c r="B226" s="30"/>
+      <c r="A226" s="29"/>
+      <c r="B226" s="29"/>
     </row>
     <row r="227">
-      <c r="A227" s="30"/>
-      <c r="B227" s="30"/>
+      <c r="A227" s="29"/>
+      <c r="B227" s="29"/>
     </row>
     <row r="228">
-      <c r="A228" s="30"/>
-      <c r="B228" s="30"/>
+      <c r="A228" s="29"/>
+      <c r="B228" s="29"/>
     </row>
     <row r="229">
-      <c r="A229" s="30"/>
-      <c r="B229" s="30"/>
+      <c r="A229" s="29"/>
+      <c r="B229" s="29"/>
     </row>
     <row r="230">
-      <c r="A230" s="30"/>
-      <c r="B230" s="30"/>
+      <c r="A230" s="29"/>
+      <c r="B230" s="29"/>
     </row>
     <row r="231">
-      <c r="A231" s="30"/>
-      <c r="B231" s="30"/>
+      <c r="A231" s="29"/>
+      <c r="B231" s="29"/>
     </row>
     <row r="232">
-      <c r="A232" s="30"/>
-      <c r="B232" s="30"/>
+      <c r="A232" s="29"/>
+      <c r="B232" s="29"/>
     </row>
     <row r="233">
-      <c r="A233" s="30"/>
-      <c r="B233" s="30"/>
+      <c r="A233" s="29"/>
+      <c r="B233" s="29"/>
     </row>
     <row r="234">
-      <c r="A234" s="30"/>
-      <c r="B234" s="30"/>
+      <c r="A234" s="29"/>
+      <c r="B234" s="29"/>
     </row>
     <row r="235">
-      <c r="A235" s="30"/>
-      <c r="B235" s="30"/>
+      <c r="A235" s="29"/>
+      <c r="B235" s="29"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -6910,2034 +6921,2034 @@
     <col customWidth="1" min="2" max="2" width="4.33203125"/>
     <col bestFit="1" min="3" max="3" width="35.77734375"/>
     <col customWidth="1" min="4" max="11" width="3.44140625"/>
-    <col customWidth="1" min="12" max="12" style="31" width="6"/>
+    <col customWidth="1" min="12" max="12" style="30" width="6"/>
     <col customWidth="1" min="13" max="22" width="3.44140625"/>
-    <col customWidth="1" min="23" max="23" style="31" width="6"/>
+    <col customWidth="1" min="23" max="23" style="30" width="6"/>
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
-    <col customWidth="1" min="30" max="30" style="31" width="6"/>
+    <col customWidth="1" min="30" max="30" style="30" width="6"/>
     <col customWidth="1" min="31" max="39" width="3.44140625"/>
     <col bestFit="1" customWidth="1" min="40" max="40" width="13.88671875"/>
     <col customWidth="1" min="41" max="47" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="32" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="B1" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="34" t="s">
+    <row r="1" s="31" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="B1" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="C1" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" s="36" t="s">
+      <c r="E1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="G1" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="I1" s="35" t="s">
+      <c r="H1" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="35" t="s">
+      <c r="J1" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="L1" s="39" t="s">
+      <c r="K1" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="M1" s="35" t="s">
+      <c r="L1" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="N1" s="37" t="s">
+      <c r="M1" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="N1" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="P1" s="35" t="s">
+      <c r="O1" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="P1" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="S1" s="35" t="s">
+      <c r="Q1" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="R1" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="T1" s="35" t="s">
+      <c r="S1" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="U1" s="35" t="s">
+      <c r="T1" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="V1" s="37" t="s">
+      <c r="U1" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="W1" s="40" t="s">
+      <c r="V1" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="X1" s="35" t="s">
+      <c r="W1" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="Y1" s="35" t="s">
+      <c r="X1" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="Z1" s="37" t="s">
+      <c r="Y1" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="AA1" s="41" t="s">
+      <c r="Z1" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="AB1" s="42" t="s">
+      <c r="AA1" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="AC1" s="42" t="s">
+      <c r="AB1" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="AD1" s="39" t="s">
+      <c r="AC1" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="AE1" s="43" t="s">
+      <c r="AD1" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="AF1" s="44" t="s">
+      <c r="AE1" s="42" t="s">
         <v>98</v>
       </c>
-      <c r="AG1" s="45" t="s">
+      <c r="AF1" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="AH1" s="45" t="s">
+      <c r="AG1" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="AI1" s="45" t="s">
+      <c r="AH1" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="AJ1" s="45" t="s">
+      <c r="AI1" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="AK1" s="42" t="s">
+      <c r="AJ1" s="44" t="s">
         <v>103</v>
       </c>
-      <c r="AL1" s="46"/>
-      <c r="AM1" s="46"/>
-      <c r="AN1" s="46"/>
-      <c r="AO1" s="46"/>
-      <c r="AP1" s="46"/>
-      <c r="AQ1" s="46"/>
-      <c r="AR1" s="46"/>
-      <c r="AS1" s="46"/>
-      <c r="AT1" s="46"/>
-      <c r="AU1" s="46"/>
+      <c r="AK1" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="AL1" s="45"/>
+      <c r="AM1" s="45"/>
+      <c r="AN1" s="45"/>
+      <c r="AO1" s="45"/>
+      <c r="AP1" s="45"/>
+      <c r="AQ1" s="45"/>
+      <c r="AR1" s="45"/>
+      <c r="AS1" s="45"/>
+      <c r="AT1" s="45"/>
+      <c r="AU1" s="45"/>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="49"/>
-      <c r="S2" s="49"/>
-      <c r="T2" s="49"/>
-      <c r="U2" s="49"/>
-      <c r="V2" s="54"/>
-      <c r="W2" s="56"/>
-      <c r="X2" s="49"/>
-      <c r="Y2" s="49"/>
-      <c r="Z2" s="54"/>
-      <c r="AA2" s="55"/>
-      <c r="AB2" s="49"/>
-      <c r="AC2" s="49"/>
-      <c r="AD2" s="53"/>
-      <c r="AE2" s="54"/>
-      <c r="AF2" s="55"/>
-      <c r="AG2" s="49"/>
-      <c r="AH2" s="49"/>
-      <c r="AI2" s="49"/>
-      <c r="AJ2" s="49"/>
-      <c r="AK2" s="49"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="53"/>
+      <c r="W2" s="55"/>
+      <c r="X2" s="48"/>
+      <c r="Y2" s="48"/>
+      <c r="Z2" s="53"/>
+      <c r="AA2" s="54"/>
+      <c r="AB2" s="48"/>
+      <c r="AC2" s="48"/>
+      <c r="AD2" s="52"/>
+      <c r="AE2" s="53"/>
+      <c r="AF2" s="54"/>
+      <c r="AG2" s="48"/>
+      <c r="AH2" s="48"/>
+      <c r="AI2" s="48"/>
+      <c r="AJ2" s="48"/>
+      <c r="AK2" s="48"/>
     </row>
     <row r="3" ht="12" customHeight="1">
-      <c r="B3" s="47"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="49"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="55"/>
-      <c r="P3" s="49"/>
-      <c r="Q3" s="49"/>
-      <c r="R3" s="49"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="49"/>
-      <c r="U3" s="49"/>
-      <c r="V3" s="54"/>
-      <c r="W3" s="56"/>
-      <c r="X3" s="49"/>
-      <c r="Y3" s="49"/>
-      <c r="Z3" s="54"/>
-      <c r="AA3" s="55"/>
-      <c r="AB3" s="49"/>
-      <c r="AC3" s="49"/>
-      <c r="AD3" s="53"/>
-      <c r="AE3" s="54"/>
-      <c r="AF3" s="55"/>
-      <c r="AG3" s="49"/>
-      <c r="AH3" s="49"/>
-      <c r="AI3" s="49"/>
-      <c r="AJ3" s="49"/>
-      <c r="AK3" s="49"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="54"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="53"/>
+      <c r="W3" s="55"/>
+      <c r="X3" s="48"/>
+      <c r="Y3" s="48"/>
+      <c r="Z3" s="53"/>
+      <c r="AA3" s="54"/>
+      <c r="AB3" s="48"/>
+      <c r="AC3" s="48"/>
+      <c r="AD3" s="52"/>
+      <c r="AE3" s="53"/>
+      <c r="AF3" s="54"/>
+      <c r="AG3" s="48"/>
+      <c r="AH3" s="48"/>
+      <c r="AI3" s="48"/>
+      <c r="AJ3" s="48"/>
+      <c r="AK3" s="48"/>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="47"/>
-      <c r="C4" s="48" t="s">
-        <v>104</v>
-      </c>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="49"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="49"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="49"/>
-      <c r="Q4" s="49"/>
-      <c r="R4" s="49"/>
-      <c r="S4" s="49"/>
-      <c r="T4" s="49"/>
-      <c r="U4" s="49"/>
-      <c r="V4" s="54"/>
-      <c r="W4" s="56"/>
-      <c r="X4" s="49"/>
-      <c r="Y4" s="49"/>
-      <c r="Z4" s="54"/>
-      <c r="AA4" s="55"/>
-      <c r="AB4" s="49"/>
-      <c r="AC4" s="49"/>
-      <c r="AD4" s="53"/>
-      <c r="AE4" s="54"/>
-      <c r="AF4" s="55"/>
-      <c r="AG4" s="49"/>
-      <c r="AH4" s="49"/>
-      <c r="AI4" s="49"/>
-      <c r="AJ4" s="49"/>
-      <c r="AK4" s="49"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="48"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="53"/>
+      <c r="W4" s="55"/>
+      <c r="X4" s="48"/>
+      <c r="Y4" s="48"/>
+      <c r="Z4" s="53"/>
+      <c r="AA4" s="54"/>
+      <c r="AB4" s="48"/>
+      <c r="AC4" s="48"/>
+      <c r="AD4" s="52"/>
+      <c r="AE4" s="53"/>
+      <c r="AF4" s="54"/>
+      <c r="AG4" s="48"/>
+      <c r="AH4" s="48"/>
+      <c r="AI4" s="48"/>
+      <c r="AJ4" s="48"/>
+      <c r="AK4" s="48"/>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="47"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="49"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="54"/>
-      <c r="W5" s="56"/>
-      <c r="X5" s="49"/>
-      <c r="Y5" s="49"/>
-      <c r="Z5" s="54"/>
-      <c r="AA5" s="55"/>
-      <c r="AB5" s="49"/>
-      <c r="AC5" s="49"/>
-      <c r="AD5" s="53"/>
-      <c r="AE5" s="54"/>
-      <c r="AF5" s="55"/>
-      <c r="AG5" s="49"/>
-      <c r="AH5" s="49"/>
-      <c r="AI5" s="49"/>
-      <c r="AJ5" s="49"/>
-      <c r="AK5" s="49"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="53"/>
+      <c r="O5" s="54"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="48"/>
+      <c r="R5" s="48"/>
+      <c r="S5" s="48"/>
+      <c r="T5" s="48"/>
+      <c r="U5" s="48"/>
+      <c r="V5" s="53"/>
+      <c r="W5" s="55"/>
+      <c r="X5" s="48"/>
+      <c r="Y5" s="48"/>
+      <c r="Z5" s="53"/>
+      <c r="AA5" s="54"/>
+      <c r="AB5" s="48"/>
+      <c r="AC5" s="48"/>
+      <c r="AD5" s="52"/>
+      <c r="AE5" s="53"/>
+      <c r="AF5" s="54"/>
+      <c r="AG5" s="48"/>
+      <c r="AH5" s="48"/>
+      <c r="AI5" s="48"/>
+      <c r="AJ5" s="48"/>
+      <c r="AK5" s="48"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="47"/>
-      <c r="C6" s="48" t="s">
+      <c r="B6" s="46"/>
+      <c r="C6" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="49"/>
-      <c r="N6" s="54"/>
-      <c r="O6" s="55"/>
-      <c r="P6" s="49"/>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49"/>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
-      <c r="V6" s="54"/>
-      <c r="W6" s="56"/>
-      <c r="X6" s="49"/>
-      <c r="Y6" s="49"/>
-      <c r="Z6" s="54"/>
-      <c r="AA6" s="55"/>
-      <c r="AB6" s="49"/>
-      <c r="AC6" s="49"/>
-      <c r="AD6" s="53"/>
-      <c r="AE6" s="51"/>
-      <c r="AF6" s="52"/>
-      <c r="AG6" s="63"/>
-      <c r="AH6" s="63"/>
-      <c r="AI6" s="63"/>
-      <c r="AJ6" s="63"/>
-      <c r="AK6" s="63"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="53"/>
+      <c r="O6" s="54"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="48"/>
+      <c r="R6" s="48"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="48"/>
+      <c r="U6" s="48"/>
+      <c r="V6" s="53"/>
+      <c r="W6" s="55"/>
+      <c r="X6" s="48"/>
+      <c r="Y6" s="48"/>
+      <c r="Z6" s="53"/>
+      <c r="AA6" s="54"/>
+      <c r="AB6" s="48"/>
+      <c r="AC6" s="48"/>
+      <c r="AD6" s="52"/>
+      <c r="AE6" s="50"/>
+      <c r="AF6" s="51"/>
+      <c r="AG6" s="62"/>
+      <c r="AH6" s="62"/>
+      <c r="AI6" s="62"/>
+      <c r="AJ6" s="62"/>
+      <c r="AK6" s="62"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="47"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="61"/>
-      <c r="I7" s="62"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="49"/>
-      <c r="N7" s="54"/>
-      <c r="O7" s="61"/>
-      <c r="P7" s="49"/>
-      <c r="Q7" s="62"/>
-      <c r="R7" s="49"/>
-      <c r="S7" s="49"/>
-      <c r="T7" s="49"/>
-      <c r="U7" s="49"/>
-      <c r="V7" s="54"/>
-      <c r="W7" s="56"/>
-      <c r="X7" s="49"/>
-      <c r="Y7" s="49"/>
-      <c r="Z7" s="54"/>
-      <c r="AA7" s="55"/>
-      <c r="AB7" s="49"/>
-      <c r="AC7" s="49"/>
-      <c r="AD7" s="53"/>
-      <c r="AE7" s="54"/>
-      <c r="AF7" s="55"/>
-      <c r="AG7" s="49"/>
-      <c r="AH7" s="49"/>
-      <c r="AI7" s="49"/>
-      <c r="AJ7" s="49"/>
-      <c r="AK7" s="49"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="52"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="53"/>
+      <c r="O7" s="60"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="61"/>
+      <c r="R7" s="48"/>
+      <c r="S7" s="48"/>
+      <c r="T7" s="48"/>
+      <c r="U7" s="48"/>
+      <c r="V7" s="53"/>
+      <c r="W7" s="55"/>
+      <c r="X7" s="48"/>
+      <c r="Y7" s="48"/>
+      <c r="Z7" s="53"/>
+      <c r="AA7" s="54"/>
+      <c r="AB7" s="48"/>
+      <c r="AC7" s="48"/>
+      <c r="AD7" s="52"/>
+      <c r="AE7" s="53"/>
+      <c r="AF7" s="54"/>
+      <c r="AG7" s="48"/>
+      <c r="AH7" s="48"/>
+      <c r="AI7" s="48"/>
+      <c r="AJ7" s="48"/>
+      <c r="AK7" s="48"/>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="47"/>
-      <c r="C8" s="48" t="s">
-        <v>105</v>
-      </c>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="63"/>
-      <c r="K8" s="63"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="63"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="52"/>
-      <c r="P8" s="63"/>
-      <c r="Q8" s="63"/>
-      <c r="R8" s="63"/>
-      <c r="S8" s="63"/>
-      <c r="T8" s="63"/>
-      <c r="U8" s="63"/>
-      <c r="V8" s="51"/>
-      <c r="W8" s="56"/>
-      <c r="X8" s="63"/>
-      <c r="Y8" s="63"/>
-      <c r="Z8" s="51"/>
-      <c r="AA8" s="52"/>
-      <c r="AB8" s="63"/>
-      <c r="AC8" s="63"/>
-      <c r="AD8" s="53"/>
-      <c r="AE8" s="51"/>
-      <c r="AF8" s="52"/>
-      <c r="AG8" s="63"/>
-      <c r="AH8" s="63"/>
-      <c r="AI8" s="63"/>
-      <c r="AJ8" s="63"/>
-      <c r="AK8" s="63"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="62"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="62"/>
+      <c r="N8" s="50"/>
+      <c r="O8" s="51"/>
+      <c r="P8" s="62"/>
+      <c r="Q8" s="62"/>
+      <c r="R8" s="62"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="62"/>
+      <c r="U8" s="62"/>
+      <c r="V8" s="50"/>
+      <c r="W8" s="55"/>
+      <c r="X8" s="62"/>
+      <c r="Y8" s="62"/>
+      <c r="Z8" s="50"/>
+      <c r="AA8" s="51"/>
+      <c r="AB8" s="62"/>
+      <c r="AC8" s="62"/>
+      <c r="AD8" s="52"/>
+      <c r="AE8" s="50"/>
+      <c r="AF8" s="51"/>
+      <c r="AG8" s="62"/>
+      <c r="AH8" s="62"/>
+      <c r="AI8" s="62"/>
+      <c r="AJ8" s="62"/>
+      <c r="AK8" s="62"/>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="47"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="62"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="62"/>
-      <c r="J9" s="62"/>
-      <c r="K9" s="49"/>
-      <c r="L9" s="53"/>
-      <c r="M9" s="62"/>
-      <c r="N9" s="54"/>
-      <c r="O9" s="61"/>
-      <c r="P9" s="49"/>
-      <c r="Q9" s="62"/>
-      <c r="R9" s="49"/>
-      <c r="S9" s="64"/>
-      <c r="T9" s="49"/>
-      <c r="U9" s="49"/>
-      <c r="V9" s="54"/>
-      <c r="W9" s="56"/>
-      <c r="X9" s="49"/>
-      <c r="Y9" s="49"/>
-      <c r="Z9" s="54"/>
-      <c r="AA9" s="55"/>
-      <c r="AB9" s="49"/>
-      <c r="AC9" s="49"/>
-      <c r="AD9" s="53"/>
-      <c r="AE9" s="54"/>
-      <c r="AF9" s="55"/>
-      <c r="AG9" s="49"/>
-      <c r="AH9" s="49"/>
-      <c r="AI9" s="49"/>
-      <c r="AJ9" s="49"/>
-      <c r="AK9" s="49"/>
+      <c r="B9" s="46"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="61"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="52"/>
+      <c r="M9" s="61"/>
+      <c r="N9" s="53"/>
+      <c r="O9" s="60"/>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="61"/>
+      <c r="R9" s="48"/>
+      <c r="S9" s="63"/>
+      <c r="T9" s="48"/>
+      <c r="U9" s="48"/>
+      <c r="V9" s="53"/>
+      <c r="W9" s="55"/>
+      <c r="X9" s="48"/>
+      <c r="Y9" s="48"/>
+      <c r="Z9" s="53"/>
+      <c r="AA9" s="54"/>
+      <c r="AB9" s="48"/>
+      <c r="AC9" s="48"/>
+      <c r="AD9" s="52"/>
+      <c r="AE9" s="53"/>
+      <c r="AF9" s="54"/>
+      <c r="AG9" s="48"/>
+      <c r="AH9" s="48"/>
+      <c r="AI9" s="48"/>
+      <c r="AJ9" s="48"/>
+      <c r="AK9" s="48"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="47"/>
-      <c r="C10" s="48" t="s">
-        <v>106</v>
-      </c>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="49"/>
-      <c r="N10" s="54"/>
-      <c r="O10" s="55"/>
-      <c r="P10" s="49"/>
-      <c r="Q10" s="49"/>
-      <c r="R10" s="49"/>
-      <c r="S10" s="49"/>
-      <c r="T10" s="49"/>
-      <c r="U10" s="49"/>
-      <c r="V10" s="51"/>
-      <c r="W10" s="56"/>
-      <c r="X10" s="63"/>
-      <c r="Y10" s="63"/>
-      <c r="Z10" s="51"/>
-      <c r="AA10" s="55"/>
-      <c r="AB10" s="49"/>
-      <c r="AC10" s="49"/>
-      <c r="AD10" s="53"/>
-      <c r="AE10" s="54"/>
-      <c r="AF10" s="55"/>
-      <c r="AG10" s="49"/>
-      <c r="AH10" s="49"/>
-      <c r="AI10" s="49"/>
-      <c r="AJ10" s="49"/>
-      <c r="AK10" s="49"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="47" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="52"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="54"/>
+      <c r="P10" s="48"/>
+      <c r="Q10" s="48"/>
+      <c r="R10" s="48"/>
+      <c r="S10" s="48"/>
+      <c r="T10" s="48"/>
+      <c r="U10" s="48"/>
+      <c r="V10" s="50"/>
+      <c r="W10" s="55"/>
+      <c r="X10" s="62"/>
+      <c r="Y10" s="62"/>
+      <c r="Z10" s="50"/>
+      <c r="AA10" s="54"/>
+      <c r="AB10" s="48"/>
+      <c r="AC10" s="48"/>
+      <c r="AD10" s="52"/>
+      <c r="AE10" s="53"/>
+      <c r="AF10" s="54"/>
+      <c r="AG10" s="48"/>
+      <c r="AH10" s="48"/>
+      <c r="AI10" s="48"/>
+      <c r="AJ10" s="48"/>
+      <c r="AK10" s="48"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="47"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="55"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="49"/>
-      <c r="K11" s="49"/>
-      <c r="L11" s="53"/>
-      <c r="M11" s="49"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="55"/>
-      <c r="P11" s="49"/>
-      <c r="Q11" s="49"/>
-      <c r="R11" s="49"/>
-      <c r="S11" s="49"/>
-      <c r="T11" s="49"/>
-      <c r="U11" s="49"/>
-      <c r="V11" s="54"/>
-      <c r="W11" s="56"/>
-      <c r="X11" s="49"/>
-      <c r="Y11" s="49"/>
-      <c r="Z11" s="54"/>
-      <c r="AA11" s="55"/>
-      <c r="AB11" s="49"/>
-      <c r="AC11" s="49"/>
-      <c r="AD11" s="53"/>
-      <c r="AE11" s="54"/>
-      <c r="AF11" s="55"/>
-      <c r="AG11" s="49"/>
-      <c r="AH11" s="49"/>
-      <c r="AI11" s="49"/>
-      <c r="AJ11" s="49"/>
-      <c r="AK11" s="49"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="52"/>
+      <c r="M11" s="48"/>
+      <c r="N11" s="53"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="48"/>
+      <c r="Q11" s="48"/>
+      <c r="R11" s="48"/>
+      <c r="S11" s="48"/>
+      <c r="T11" s="48"/>
+      <c r="U11" s="48"/>
+      <c r="V11" s="53"/>
+      <c r="W11" s="55"/>
+      <c r="X11" s="48"/>
+      <c r="Y11" s="48"/>
+      <c r="Z11" s="53"/>
+      <c r="AA11" s="54"/>
+      <c r="AB11" s="48"/>
+      <c r="AC11" s="48"/>
+      <c r="AD11" s="52"/>
+      <c r="AE11" s="53"/>
+      <c r="AF11" s="54"/>
+      <c r="AG11" s="48"/>
+      <c r="AH11" s="48"/>
+      <c r="AI11" s="48"/>
+      <c r="AJ11" s="48"/>
+      <c r="AK11" s="48"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="47"/>
-      <c r="C12" s="48" t="s">
-        <v>107</v>
-      </c>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="49"/>
-      <c r="K12" s="49"/>
-      <c r="L12" s="53"/>
-      <c r="M12" s="49"/>
-      <c r="N12" s="54"/>
-      <c r="O12" s="55"/>
-      <c r="P12" s="49"/>
-      <c r="Q12" s="49"/>
-      <c r="R12" s="49"/>
-      <c r="S12" s="49"/>
-      <c r="T12" s="49"/>
-      <c r="U12" s="49"/>
-      <c r="V12" s="54"/>
-      <c r="W12" s="56"/>
-      <c r="X12" s="49"/>
-      <c r="Y12" s="49"/>
-      <c r="Z12" s="54"/>
-      <c r="AA12" s="55"/>
-      <c r="AB12" s="49"/>
-      <c r="AC12" s="49"/>
-      <c r="AD12" s="53"/>
-      <c r="AE12" s="54"/>
-      <c r="AF12" s="52"/>
-      <c r="AG12" s="63"/>
-      <c r="AH12" s="63"/>
-      <c r="AI12" s="63"/>
-      <c r="AJ12" s="63"/>
-      <c r="AK12" s="63"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="48"/>
+      <c r="K12" s="48"/>
+      <c r="L12" s="52"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="54"/>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="48"/>
+      <c r="R12" s="48"/>
+      <c r="S12" s="48"/>
+      <c r="T12" s="48"/>
+      <c r="U12" s="48"/>
+      <c r="V12" s="53"/>
+      <c r="W12" s="55"/>
+      <c r="X12" s="48"/>
+      <c r="Y12" s="48"/>
+      <c r="Z12" s="53"/>
+      <c r="AA12" s="54"/>
+      <c r="AB12" s="48"/>
+      <c r="AC12" s="48"/>
+      <c r="AD12" s="52"/>
+      <c r="AE12" s="53"/>
+      <c r="AF12" s="51"/>
+      <c r="AG12" s="62"/>
+      <c r="AH12" s="62"/>
+      <c r="AI12" s="62"/>
+      <c r="AJ12" s="62"/>
+      <c r="AK12" s="62"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="47"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="49"/>
-      <c r="K13" s="49"/>
-      <c r="L13" s="53"/>
-      <c r="M13" s="49"/>
-      <c r="N13" s="54"/>
-      <c r="O13" s="55"/>
-      <c r="P13" s="49"/>
-      <c r="Q13" s="49"/>
-      <c r="R13" s="49"/>
-      <c r="S13" s="49"/>
-      <c r="T13" s="49"/>
-      <c r="U13" s="49"/>
-      <c r="V13" s="54"/>
-      <c r="W13" s="56"/>
-      <c r="X13" s="49"/>
-      <c r="Y13" s="49"/>
-      <c r="Z13" s="54"/>
-      <c r="AA13" s="55"/>
-      <c r="AB13" s="49"/>
-      <c r="AC13" s="49"/>
-      <c r="AD13" s="53"/>
-      <c r="AE13" s="54"/>
-      <c r="AF13" s="55"/>
-      <c r="AG13" s="49"/>
-      <c r="AH13" s="49"/>
-      <c r="AI13" s="49"/>
-      <c r="AJ13" s="49"/>
-      <c r="AK13" s="49"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="52"/>
+      <c r="M13" s="48"/>
+      <c r="N13" s="53"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="48"/>
+      <c r="Q13" s="48"/>
+      <c r="R13" s="48"/>
+      <c r="S13" s="48"/>
+      <c r="T13" s="48"/>
+      <c r="U13" s="48"/>
+      <c r="V13" s="53"/>
+      <c r="W13" s="55"/>
+      <c r="X13" s="48"/>
+      <c r="Y13" s="48"/>
+      <c r="Z13" s="53"/>
+      <c r="AA13" s="54"/>
+      <c r="AB13" s="48"/>
+      <c r="AC13" s="48"/>
+      <c r="AD13" s="52"/>
+      <c r="AE13" s="53"/>
+      <c r="AF13" s="54"/>
+      <c r="AG13" s="48"/>
+      <c r="AH13" s="48"/>
+      <c r="AI13" s="48"/>
+      <c r="AJ13" s="48"/>
+      <c r="AK13" s="48"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="65" t="s">
-        <v>108</v>
-      </c>
-      <c r="C14" s="66" t="s">
+      <c r="B14" s="64" t="s">
         <v>109</v>
       </c>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="67"/>
-      <c r="I14" s="68"/>
-      <c r="J14" s="68"/>
-      <c r="K14" s="68"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="68"/>
-      <c r="N14" s="69"/>
-      <c r="O14" s="67"/>
-      <c r="P14" s="68"/>
-      <c r="Q14" s="68"/>
-      <c r="R14" s="68"/>
-      <c r="S14" s="68"/>
-      <c r="T14" s="68"/>
-      <c r="U14" s="68"/>
-      <c r="V14" s="69"/>
-      <c r="W14" s="56"/>
-      <c r="X14" s="68"/>
-      <c r="Y14" s="68"/>
-      <c r="Z14" s="69"/>
-      <c r="AA14" s="67"/>
-      <c r="AB14" s="68"/>
-      <c r="AC14" s="68"/>
-      <c r="AD14" s="53"/>
-      <c r="AE14" s="69"/>
-      <c r="AF14" s="67"/>
-      <c r="AG14" s="68"/>
-      <c r="AH14" s="68"/>
-      <c r="AI14" s="68"/>
-      <c r="AJ14" s="68"/>
-      <c r="AK14" s="68"/>
+      <c r="C14" s="65" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="67"/>
+      <c r="J14" s="67"/>
+      <c r="K14" s="67"/>
+      <c r="L14" s="52"/>
+      <c r="M14" s="67"/>
+      <c r="N14" s="68"/>
+      <c r="O14" s="66"/>
+      <c r="P14" s="67"/>
+      <c r="Q14" s="67"/>
+      <c r="R14" s="67"/>
+      <c r="S14" s="67"/>
+      <c r="T14" s="67"/>
+      <c r="U14" s="67"/>
+      <c r="V14" s="68"/>
+      <c r="W14" s="55"/>
+      <c r="X14" s="67"/>
+      <c r="Y14" s="67"/>
+      <c r="Z14" s="68"/>
+      <c r="AA14" s="66"/>
+      <c r="AB14" s="67"/>
+      <c r="AC14" s="67"/>
+      <c r="AD14" s="52"/>
+      <c r="AE14" s="68"/>
+      <c r="AF14" s="66"/>
+      <c r="AG14" s="67"/>
+      <c r="AH14" s="67"/>
+      <c r="AI14" s="67"/>
+      <c r="AJ14" s="67"/>
+      <c r="AK14" s="67"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="65"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="68"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="68"/>
-      <c r="K15" s="68"/>
-      <c r="L15" s="53"/>
-      <c r="M15" s="68"/>
-      <c r="N15" s="69"/>
-      <c r="O15" s="67"/>
-      <c r="P15" s="68"/>
-      <c r="Q15" s="68"/>
-      <c r="R15" s="68"/>
-      <c r="S15" s="68"/>
-      <c r="T15" s="68"/>
-      <c r="U15" s="68"/>
-      <c r="V15" s="69"/>
-      <c r="W15" s="56"/>
-      <c r="X15" s="68"/>
-      <c r="Y15" s="68"/>
-      <c r="Z15" s="69"/>
-      <c r="AA15" s="67"/>
-      <c r="AB15" s="68"/>
-      <c r="AC15" s="68"/>
-      <c r="AD15" s="53"/>
-      <c r="AE15" s="69"/>
-      <c r="AF15" s="67"/>
-      <c r="AG15" s="68"/>
-      <c r="AH15" s="68"/>
-      <c r="AI15" s="68"/>
-      <c r="AJ15" s="68"/>
-      <c r="AK15" s="68"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="67"/>
+      <c r="J15" s="67"/>
+      <c r="K15" s="67"/>
+      <c r="L15" s="52"/>
+      <c r="M15" s="67"/>
+      <c r="N15" s="68"/>
+      <c r="O15" s="66"/>
+      <c r="P15" s="67"/>
+      <c r="Q15" s="67"/>
+      <c r="R15" s="67"/>
+      <c r="S15" s="67"/>
+      <c r="T15" s="67"/>
+      <c r="U15" s="67"/>
+      <c r="V15" s="68"/>
+      <c r="W15" s="55"/>
+      <c r="X15" s="67"/>
+      <c r="Y15" s="67"/>
+      <c r="Z15" s="68"/>
+      <c r="AA15" s="66"/>
+      <c r="AB15" s="67"/>
+      <c r="AC15" s="67"/>
+      <c r="AD15" s="52"/>
+      <c r="AE15" s="68"/>
+      <c r="AF15" s="66"/>
+      <c r="AG15" s="67"/>
+      <c r="AH15" s="67"/>
+      <c r="AI15" s="67"/>
+      <c r="AJ15" s="67"/>
+      <c r="AK15" s="67"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="65"/>
-      <c r="C16" s="66" t="s">
-        <v>110</v>
-      </c>
-      <c r="D16" s="63"/>
-      <c r="E16" s="63"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="67"/>
-      <c r="I16" s="68"/>
-      <c r="J16" s="68"/>
-      <c r="K16" s="68"/>
-      <c r="L16" s="53"/>
-      <c r="M16" s="68"/>
-      <c r="N16" s="69"/>
-      <c r="O16" s="67"/>
-      <c r="P16" s="68"/>
-      <c r="Q16" s="68"/>
-      <c r="R16" s="68"/>
-      <c r="S16" s="68"/>
-      <c r="T16" s="68"/>
-      <c r="U16" s="68"/>
-      <c r="V16" s="69"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="68"/>
-      <c r="Y16" s="68"/>
-      <c r="Z16" s="69"/>
-      <c r="AA16" s="67"/>
-      <c r="AB16" s="68"/>
-      <c r="AC16" s="68"/>
-      <c r="AD16" s="53"/>
-      <c r="AE16" s="69"/>
-      <c r="AF16" s="67"/>
-      <c r="AG16" s="68"/>
-      <c r="AH16" s="68"/>
-      <c r="AI16" s="68"/>
-      <c r="AJ16" s="68"/>
-      <c r="AK16" s="68"/>
+      <c r="B16" s="64"/>
+      <c r="C16" s="65" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="68"/>
+      <c r="H16" s="66"/>
+      <c r="I16" s="67"/>
+      <c r="J16" s="67"/>
+      <c r="K16" s="67"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="67"/>
+      <c r="N16" s="68"/>
+      <c r="O16" s="66"/>
+      <c r="P16" s="67"/>
+      <c r="Q16" s="67"/>
+      <c r="R16" s="67"/>
+      <c r="S16" s="67"/>
+      <c r="T16" s="67"/>
+      <c r="U16" s="67"/>
+      <c r="V16" s="68"/>
+      <c r="W16" s="55"/>
+      <c r="X16" s="67"/>
+      <c r="Y16" s="67"/>
+      <c r="Z16" s="68"/>
+      <c r="AA16" s="66"/>
+      <c r="AB16" s="67"/>
+      <c r="AC16" s="67"/>
+      <c r="AD16" s="52"/>
+      <c r="AE16" s="68"/>
+      <c r="AF16" s="66"/>
+      <c r="AG16" s="67"/>
+      <c r="AH16" s="67"/>
+      <c r="AI16" s="67"/>
+      <c r="AJ16" s="67"/>
+      <c r="AK16" s="67"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="65"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="67"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="68"/>
-      <c r="K17" s="68"/>
-      <c r="L17" s="53"/>
-      <c r="M17" s="68"/>
-      <c r="N17" s="69"/>
-      <c r="O17" s="67"/>
-      <c r="P17" s="68"/>
-      <c r="Q17" s="68"/>
-      <c r="R17" s="68"/>
-      <c r="S17" s="68"/>
-      <c r="T17" s="68"/>
-      <c r="U17" s="68"/>
-      <c r="V17" s="69"/>
-      <c r="W17" s="56"/>
-      <c r="X17" s="68"/>
-      <c r="Y17" s="68"/>
-      <c r="Z17" s="69"/>
-      <c r="AA17" s="67"/>
-      <c r="AB17" s="68"/>
-      <c r="AC17" s="68"/>
-      <c r="AD17" s="53"/>
-      <c r="AE17" s="69"/>
-      <c r="AF17" s="67"/>
-      <c r="AG17" s="68"/>
-      <c r="AH17" s="68"/>
-      <c r="AI17" s="68"/>
-      <c r="AJ17" s="68"/>
-      <c r="AK17" s="68"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="67"/>
+      <c r="J17" s="67"/>
+      <c r="K17" s="67"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="67"/>
+      <c r="N17" s="68"/>
+      <c r="O17" s="66"/>
+      <c r="P17" s="67"/>
+      <c r="Q17" s="67"/>
+      <c r="R17" s="67"/>
+      <c r="S17" s="67"/>
+      <c r="T17" s="67"/>
+      <c r="U17" s="67"/>
+      <c r="V17" s="68"/>
+      <c r="W17" s="55"/>
+      <c r="X17" s="67"/>
+      <c r="Y17" s="67"/>
+      <c r="Z17" s="68"/>
+      <c r="AA17" s="66"/>
+      <c r="AB17" s="67"/>
+      <c r="AC17" s="67"/>
+      <c r="AD17" s="52"/>
+      <c r="AE17" s="68"/>
+      <c r="AF17" s="66"/>
+      <c r="AG17" s="67"/>
+      <c r="AH17" s="67"/>
+      <c r="AI17" s="67"/>
+      <c r="AJ17" s="67"/>
+      <c r="AK17" s="67"/>
       <c r="AN17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="65"/>
-      <c r="C18" s="66" t="s">
-        <v>112</v>
-      </c>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="67"/>
-      <c r="I18" s="68"/>
-      <c r="J18" s="68"/>
-      <c r="K18" s="68"/>
-      <c r="L18" s="53"/>
-      <c r="M18" s="68"/>
-      <c r="N18" s="69"/>
-      <c r="O18" s="67"/>
-      <c r="P18" s="68"/>
-      <c r="Q18" s="68"/>
-      <c r="R18" s="68"/>
-      <c r="S18" s="68"/>
-      <c r="T18" s="68"/>
-      <c r="U18" s="68"/>
-      <c r="V18" s="69"/>
-      <c r="W18" s="56"/>
-      <c r="X18" s="68"/>
-      <c r="Y18" s="68"/>
-      <c r="Z18" s="69"/>
-      <c r="AA18" s="67"/>
-      <c r="AB18" s="68"/>
-      <c r="AC18" s="68"/>
-      <c r="AD18" s="53"/>
-      <c r="AE18" s="69"/>
-      <c r="AF18" s="67"/>
-      <c r="AG18" s="68"/>
-      <c r="AH18" s="68"/>
-      <c r="AI18" s="68"/>
-      <c r="AJ18" s="68"/>
-      <c r="AK18" s="68"/>
+      <c r="B18" s="64"/>
+      <c r="C18" s="65" t="s">
+        <v>113</v>
+      </c>
+      <c r="D18" s="62"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="66"/>
+      <c r="I18" s="67"/>
+      <c r="J18" s="67"/>
+      <c r="K18" s="67"/>
+      <c r="L18" s="52"/>
+      <c r="M18" s="67"/>
+      <c r="N18" s="68"/>
+      <c r="O18" s="66"/>
+      <c r="P18" s="67"/>
+      <c r="Q18" s="67"/>
+      <c r="R18" s="67"/>
+      <c r="S18" s="67"/>
+      <c r="T18" s="67"/>
+      <c r="U18" s="67"/>
+      <c r="V18" s="68"/>
+      <c r="W18" s="55"/>
+      <c r="X18" s="67"/>
+      <c r="Y18" s="67"/>
+      <c r="Z18" s="68"/>
+      <c r="AA18" s="66"/>
+      <c r="AB18" s="67"/>
+      <c r="AC18" s="67"/>
+      <c r="AD18" s="52"/>
+      <c r="AE18" s="68"/>
+      <c r="AF18" s="66"/>
+      <c r="AG18" s="67"/>
+      <c r="AH18" s="67"/>
+      <c r="AI18" s="67"/>
+      <c r="AJ18" s="67"/>
+      <c r="AK18" s="67"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="65"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="69"/>
-      <c r="H19" s="67"/>
-      <c r="I19" s="68"/>
-      <c r="J19" s="68"/>
-      <c r="K19" s="68"/>
-      <c r="L19" s="53"/>
-      <c r="M19" s="68"/>
-      <c r="N19" s="69"/>
-      <c r="O19" s="67"/>
-      <c r="P19" s="68"/>
-      <c r="Q19" s="68"/>
-      <c r="R19" s="68"/>
-      <c r="S19" s="68"/>
-      <c r="T19" s="68"/>
-      <c r="U19" s="68"/>
-      <c r="V19" s="69"/>
-      <c r="W19" s="56"/>
-      <c r="X19" s="68"/>
-      <c r="Y19" s="68"/>
-      <c r="Z19" s="69"/>
-      <c r="AA19" s="67"/>
-      <c r="AB19" s="68"/>
-      <c r="AC19" s="68"/>
-      <c r="AD19" s="53"/>
-      <c r="AE19" s="69"/>
-      <c r="AF19" s="67"/>
-      <c r="AG19" s="68"/>
-      <c r="AH19" s="68"/>
-      <c r="AI19" s="68"/>
-      <c r="AJ19" s="68"/>
-      <c r="AK19" s="68"/>
+      <c r="B19" s="64"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="67"/>
+      <c r="J19" s="67"/>
+      <c r="K19" s="67"/>
+      <c r="L19" s="52"/>
+      <c r="M19" s="67"/>
+      <c r="N19" s="68"/>
+      <c r="O19" s="66"/>
+      <c r="P19" s="67"/>
+      <c r="Q19" s="67"/>
+      <c r="R19" s="67"/>
+      <c r="S19" s="67"/>
+      <c r="T19" s="67"/>
+      <c r="U19" s="67"/>
+      <c r="V19" s="68"/>
+      <c r="W19" s="55"/>
+      <c r="X19" s="67"/>
+      <c r="Y19" s="67"/>
+      <c r="Z19" s="68"/>
+      <c r="AA19" s="66"/>
+      <c r="AB19" s="67"/>
+      <c r="AC19" s="67"/>
+      <c r="AD19" s="52"/>
+      <c r="AE19" s="68"/>
+      <c r="AF19" s="66"/>
+      <c r="AG19" s="67"/>
+      <c r="AH19" s="67"/>
+      <c r="AI19" s="67"/>
+      <c r="AJ19" s="67"/>
+      <c r="AK19" s="67"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="65"/>
-      <c r="C20" s="66" t="s">
-        <v>113</v>
-      </c>
-      <c r="D20" s="68"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="63"/>
-      <c r="J20" s="68"/>
-      <c r="K20" s="68"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="68"/>
-      <c r="N20" s="69"/>
-      <c r="O20" s="67"/>
-      <c r="P20" s="68"/>
-      <c r="Q20" s="68"/>
-      <c r="R20" s="68"/>
-      <c r="S20" s="68"/>
-      <c r="T20" s="68"/>
-      <c r="U20" s="68"/>
-      <c r="V20" s="69"/>
-      <c r="W20" s="56"/>
-      <c r="X20" s="68"/>
-      <c r="Y20" s="68"/>
-      <c r="Z20" s="69"/>
-      <c r="AA20" s="67"/>
-      <c r="AB20" s="68"/>
-      <c r="AC20" s="68"/>
-      <c r="AD20" s="53"/>
-      <c r="AE20" s="69"/>
-      <c r="AF20" s="67"/>
-      <c r="AG20" s="68"/>
-      <c r="AH20" s="68"/>
-      <c r="AI20" s="68"/>
-      <c r="AJ20" s="68"/>
-      <c r="AK20" s="68"/>
+      <c r="B20" s="64"/>
+      <c r="C20" s="65" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" s="67"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="67"/>
+      <c r="K20" s="67"/>
+      <c r="L20" s="52"/>
+      <c r="M20" s="67"/>
+      <c r="N20" s="68"/>
+      <c r="O20" s="66"/>
+      <c r="P20" s="67"/>
+      <c r="Q20" s="67"/>
+      <c r="R20" s="67"/>
+      <c r="S20" s="67"/>
+      <c r="T20" s="67"/>
+      <c r="U20" s="67"/>
+      <c r="V20" s="68"/>
+      <c r="W20" s="55"/>
+      <c r="X20" s="67"/>
+      <c r="Y20" s="67"/>
+      <c r="Z20" s="68"/>
+      <c r="AA20" s="66"/>
+      <c r="AB20" s="67"/>
+      <c r="AC20" s="67"/>
+      <c r="AD20" s="52"/>
+      <c r="AE20" s="68"/>
+      <c r="AF20" s="66"/>
+      <c r="AG20" s="67"/>
+      <c r="AH20" s="67"/>
+      <c r="AI20" s="67"/>
+      <c r="AJ20" s="67"/>
+      <c r="AK20" s="67"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="65"/>
-      <c r="C21" s="66"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="71"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="67"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="68"/>
-      <c r="K21" s="68"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="68"/>
-      <c r="N21" s="69"/>
-      <c r="O21" s="67"/>
-      <c r="P21" s="68"/>
-      <c r="Q21" s="68"/>
-      <c r="R21" s="68"/>
-      <c r="S21" s="68"/>
-      <c r="T21" s="68"/>
-      <c r="U21" s="68"/>
-      <c r="V21" s="69"/>
-      <c r="W21" s="56"/>
-      <c r="X21" s="68"/>
-      <c r="Y21" s="68"/>
-      <c r="Z21" s="69"/>
-      <c r="AA21" s="67"/>
-      <c r="AB21" s="68"/>
-      <c r="AC21" s="68"/>
-      <c r="AD21" s="53"/>
-      <c r="AE21" s="69"/>
-      <c r="AF21" s="67"/>
-      <c r="AG21" s="68"/>
-      <c r="AH21" s="68"/>
-      <c r="AI21" s="68"/>
-      <c r="AJ21" s="68"/>
-      <c r="AK21" s="68"/>
+      <c r="B21" s="64"/>
+      <c r="C21" s="65"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="66"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="67"/>
+      <c r="K21" s="67"/>
+      <c r="L21" s="52"/>
+      <c r="M21" s="67"/>
+      <c r="N21" s="68"/>
+      <c r="O21" s="66"/>
+      <c r="P21" s="67"/>
+      <c r="Q21" s="67"/>
+      <c r="R21" s="67"/>
+      <c r="S21" s="67"/>
+      <c r="T21" s="67"/>
+      <c r="U21" s="67"/>
+      <c r="V21" s="68"/>
+      <c r="W21" s="55"/>
+      <c r="X21" s="67"/>
+      <c r="Y21" s="67"/>
+      <c r="Z21" s="68"/>
+      <c r="AA21" s="66"/>
+      <c r="AB21" s="67"/>
+      <c r="AC21" s="67"/>
+      <c r="AD21" s="52"/>
+      <c r="AE21" s="68"/>
+      <c r="AF21" s="66"/>
+      <c r="AG21" s="67"/>
+      <c r="AH21" s="67"/>
+      <c r="AI21" s="67"/>
+      <c r="AJ21" s="67"/>
+      <c r="AK21" s="67"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="65"/>
-      <c r="C22" s="66" t="s">
-        <v>114</v>
-      </c>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="63"/>
-      <c r="J22" s="68"/>
-      <c r="K22" s="68"/>
-      <c r="L22" s="53"/>
-      <c r="M22" s="68"/>
-      <c r="N22" s="69"/>
-      <c r="O22" s="67"/>
-      <c r="P22" s="68"/>
-      <c r="Q22" s="68"/>
-      <c r="R22" s="68"/>
-      <c r="S22" s="68"/>
-      <c r="T22" s="68"/>
-      <c r="U22" s="68"/>
-      <c r="V22" s="69"/>
-      <c r="W22" s="56"/>
-      <c r="X22" s="68"/>
-      <c r="Y22" s="68"/>
-      <c r="Z22" s="69"/>
-      <c r="AA22" s="67"/>
-      <c r="AB22" s="68"/>
-      <c r="AC22" s="68"/>
-      <c r="AD22" s="53"/>
-      <c r="AE22" s="69"/>
-      <c r="AF22" s="67"/>
-      <c r="AG22" s="68"/>
-      <c r="AH22" s="68"/>
-      <c r="AI22" s="68"/>
-      <c r="AJ22" s="68"/>
-      <c r="AK22" s="68"/>
+      <c r="B22" s="64"/>
+      <c r="C22" s="65" t="s">
+        <v>115</v>
+      </c>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="52"/>
+      <c r="M22" s="67"/>
+      <c r="N22" s="68"/>
+      <c r="O22" s="66"/>
+      <c r="P22" s="67"/>
+      <c r="Q22" s="67"/>
+      <c r="R22" s="67"/>
+      <c r="S22" s="67"/>
+      <c r="T22" s="67"/>
+      <c r="U22" s="67"/>
+      <c r="V22" s="68"/>
+      <c r="W22" s="55"/>
+      <c r="X22" s="67"/>
+      <c r="Y22" s="67"/>
+      <c r="Z22" s="68"/>
+      <c r="AA22" s="66"/>
+      <c r="AB22" s="67"/>
+      <c r="AC22" s="67"/>
+      <c r="AD22" s="52"/>
+      <c r="AE22" s="68"/>
+      <c r="AF22" s="66"/>
+      <c r="AG22" s="67"/>
+      <c r="AH22" s="67"/>
+      <c r="AI22" s="67"/>
+      <c r="AJ22" s="67"/>
+      <c r="AK22" s="67"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="65"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="58"/>
-      <c r="K23" s="68"/>
-      <c r="L23" s="53"/>
-      <c r="M23" s="68"/>
-      <c r="N23" s="69"/>
-      <c r="O23" s="67"/>
-      <c r="P23" s="68"/>
-      <c r="Q23" s="68"/>
-      <c r="R23" s="68"/>
-      <c r="S23" s="68"/>
-      <c r="T23" s="68"/>
-      <c r="U23" s="68"/>
-      <c r="V23" s="69"/>
-      <c r="W23" s="56"/>
-      <c r="X23" s="68"/>
-      <c r="Y23" s="68"/>
-      <c r="Z23" s="69"/>
-      <c r="AA23" s="67"/>
-      <c r="AB23" s="68"/>
-      <c r="AC23" s="68"/>
-      <c r="AD23" s="53"/>
-      <c r="AE23" s="69"/>
-      <c r="AF23" s="67"/>
-      <c r="AG23" s="68"/>
-      <c r="AH23" s="68"/>
-      <c r="AI23" s="68"/>
-      <c r="AJ23" s="68"/>
-      <c r="AK23" s="68"/>
+      <c r="B23" s="64"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="67"/>
+      <c r="L23" s="52"/>
+      <c r="M23" s="67"/>
+      <c r="N23" s="68"/>
+      <c r="O23" s="66"/>
+      <c r="P23" s="67"/>
+      <c r="Q23" s="67"/>
+      <c r="R23" s="67"/>
+      <c r="S23" s="67"/>
+      <c r="T23" s="67"/>
+      <c r="U23" s="67"/>
+      <c r="V23" s="68"/>
+      <c r="W23" s="55"/>
+      <c r="X23" s="67"/>
+      <c r="Y23" s="67"/>
+      <c r="Z23" s="68"/>
+      <c r="AA23" s="66"/>
+      <c r="AB23" s="67"/>
+      <c r="AC23" s="67"/>
+      <c r="AD23" s="52"/>
+      <c r="AE23" s="68"/>
+      <c r="AF23" s="66"/>
+      <c r="AG23" s="67"/>
+      <c r="AH23" s="67"/>
+      <c r="AI23" s="67"/>
+      <c r="AJ23" s="67"/>
+      <c r="AK23" s="67"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="65"/>
-      <c r="C24" s="66" t="s">
-        <v>115</v>
-      </c>
-      <c r="D24" s="68"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="67"/>
-      <c r="I24" s="63"/>
-      <c r="J24" s="68"/>
-      <c r="K24" s="68"/>
-      <c r="L24" s="53"/>
-      <c r="M24" s="68"/>
-      <c r="N24" s="69"/>
-      <c r="O24" s="67"/>
-      <c r="P24" s="68"/>
-      <c r="Q24" s="68"/>
-      <c r="R24" s="68"/>
-      <c r="S24" s="68"/>
-      <c r="T24" s="68"/>
-      <c r="U24" s="68"/>
-      <c r="V24" s="69"/>
-      <c r="W24" s="56"/>
-      <c r="X24" s="68"/>
-      <c r="Y24" s="68"/>
-      <c r="Z24" s="69"/>
-      <c r="AA24" s="67"/>
-      <c r="AB24" s="68"/>
-      <c r="AC24" s="68"/>
-      <c r="AD24" s="53"/>
-      <c r="AE24" s="69"/>
-      <c r="AF24" s="67"/>
-      <c r="AG24" s="68"/>
-      <c r="AH24" s="68"/>
-      <c r="AI24" s="68"/>
-      <c r="AJ24" s="68"/>
-      <c r="AK24" s="68"/>
+      <c r="B24" s="64"/>
+      <c r="C24" s="65" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="67"/>
+      <c r="E24" s="67"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="68"/>
+      <c r="H24" s="66"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="67"/>
+      <c r="K24" s="67"/>
+      <c r="L24" s="52"/>
+      <c r="M24" s="67"/>
+      <c r="N24" s="68"/>
+      <c r="O24" s="66"/>
+      <c r="P24" s="67"/>
+      <c r="Q24" s="67"/>
+      <c r="R24" s="67"/>
+      <c r="S24" s="67"/>
+      <c r="T24" s="67"/>
+      <c r="U24" s="67"/>
+      <c r="V24" s="68"/>
+      <c r="W24" s="55"/>
+      <c r="X24" s="67"/>
+      <c r="Y24" s="67"/>
+      <c r="Z24" s="68"/>
+      <c r="AA24" s="66"/>
+      <c r="AB24" s="67"/>
+      <c r="AC24" s="67"/>
+      <c r="AD24" s="52"/>
+      <c r="AE24" s="68"/>
+      <c r="AF24" s="66"/>
+      <c r="AG24" s="67"/>
+      <c r="AH24" s="67"/>
+      <c r="AI24" s="67"/>
+      <c r="AJ24" s="67"/>
+      <c r="AK24" s="67"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="65"/>
-      <c r="C25" s="66"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="68"/>
-      <c r="L25" s="53"/>
-      <c r="M25" s="68"/>
-      <c r="N25" s="69"/>
-      <c r="O25" s="67"/>
-      <c r="P25" s="68"/>
-      <c r="Q25" s="68"/>
-      <c r="R25" s="68"/>
-      <c r="S25" s="68"/>
-      <c r="T25" s="68"/>
-      <c r="U25" s="68"/>
-      <c r="V25" s="69"/>
-      <c r="W25" s="56"/>
-      <c r="X25" s="68"/>
-      <c r="Y25" s="68"/>
-      <c r="Z25" s="69"/>
-      <c r="AA25" s="67"/>
-      <c r="AB25" s="68"/>
-      <c r="AC25" s="68"/>
-      <c r="AD25" s="53"/>
-      <c r="AE25" s="69"/>
-      <c r="AF25" s="67"/>
-      <c r="AG25" s="68"/>
-      <c r="AH25" s="68"/>
-      <c r="AI25" s="68"/>
-      <c r="AJ25" s="68"/>
-      <c r="AK25" s="68"/>
+      <c r="B25" s="64"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="67"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="67"/>
+      <c r="L25" s="52"/>
+      <c r="M25" s="67"/>
+      <c r="N25" s="68"/>
+      <c r="O25" s="66"/>
+      <c r="P25" s="67"/>
+      <c r="Q25" s="67"/>
+      <c r="R25" s="67"/>
+      <c r="S25" s="67"/>
+      <c r="T25" s="67"/>
+      <c r="U25" s="67"/>
+      <c r="V25" s="68"/>
+      <c r="W25" s="55"/>
+      <c r="X25" s="67"/>
+      <c r="Y25" s="67"/>
+      <c r="Z25" s="68"/>
+      <c r="AA25" s="66"/>
+      <c r="AB25" s="67"/>
+      <c r="AC25" s="67"/>
+      <c r="AD25" s="52"/>
+      <c r="AE25" s="68"/>
+      <c r="AF25" s="66"/>
+      <c r="AG25" s="67"/>
+      <c r="AH25" s="67"/>
+      <c r="AI25" s="67"/>
+      <c r="AJ25" s="67"/>
+      <c r="AK25" s="67"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="C26" s="48" t="s">
+      <c r="B26" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="54"/>
-      <c r="H26" s="52"/>
-      <c r="I26" s="63"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="53"/>
-      <c r="M26" s="49"/>
-      <c r="N26" s="54"/>
-      <c r="O26" s="55"/>
-      <c r="P26" s="49"/>
-      <c r="Q26" s="49"/>
-      <c r="R26" s="49"/>
-      <c r="S26" s="49"/>
-      <c r="T26" s="49"/>
-      <c r="U26" s="49"/>
-      <c r="V26" s="54"/>
-      <c r="W26" s="56"/>
-      <c r="X26" s="49"/>
-      <c r="Y26" s="49"/>
-      <c r="Z26" s="54"/>
-      <c r="AA26" s="55"/>
-      <c r="AB26" s="49"/>
-      <c r="AC26" s="49"/>
-      <c r="AD26" s="53"/>
-      <c r="AE26" s="54"/>
-      <c r="AF26" s="55"/>
-      <c r="AG26" s="49"/>
-      <c r="AH26" s="49"/>
-      <c r="AI26" s="49"/>
-      <c r="AJ26" s="49"/>
-      <c r="AK26" s="49"/>
+      <c r="C26" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="62"/>
+      <c r="J26" s="48"/>
+      <c r="K26" s="48"/>
+      <c r="L26" s="52"/>
+      <c r="M26" s="48"/>
+      <c r="N26" s="53"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="48"/>
+      <c r="Q26" s="48"/>
+      <c r="R26" s="48"/>
+      <c r="S26" s="48"/>
+      <c r="T26" s="48"/>
+      <c r="U26" s="48"/>
+      <c r="V26" s="53"/>
+      <c r="W26" s="55"/>
+      <c r="X26" s="48"/>
+      <c r="Y26" s="48"/>
+      <c r="Z26" s="53"/>
+      <c r="AA26" s="54"/>
+      <c r="AB26" s="48"/>
+      <c r="AC26" s="48"/>
+      <c r="AD26" s="52"/>
+      <c r="AE26" s="53"/>
+      <c r="AF26" s="54"/>
+      <c r="AG26" s="48"/>
+      <c r="AH26" s="48"/>
+      <c r="AI26" s="48"/>
+      <c r="AJ26" s="48"/>
+      <c r="AK26" s="48"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="47"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="60"/>
-      <c r="H27" s="61"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="49"/>
-      <c r="K27" s="49"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="49"/>
-      <c r="N27" s="54"/>
-      <c r="O27" s="55"/>
-      <c r="P27" s="49"/>
-      <c r="Q27" s="49"/>
-      <c r="R27" s="49"/>
-      <c r="S27" s="49"/>
-      <c r="T27" s="49"/>
-      <c r="U27" s="49"/>
-      <c r="V27" s="54"/>
-      <c r="W27" s="56"/>
-      <c r="X27" s="49"/>
-      <c r="Y27" s="49"/>
-      <c r="Z27" s="54"/>
-      <c r="AA27" s="55"/>
-      <c r="AB27" s="49"/>
-      <c r="AC27" s="49"/>
-      <c r="AD27" s="53"/>
-      <c r="AE27" s="54"/>
-      <c r="AF27" s="55"/>
-      <c r="AG27" s="49"/>
-      <c r="AH27" s="49"/>
-      <c r="AI27" s="49"/>
-      <c r="AJ27" s="49"/>
-      <c r="AK27" s="49"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="48"/>
+      <c r="J27" s="48"/>
+      <c r="K27" s="48"/>
+      <c r="L27" s="52"/>
+      <c r="M27" s="48"/>
+      <c r="N27" s="53"/>
+      <c r="O27" s="54"/>
+      <c r="P27" s="48"/>
+      <c r="Q27" s="48"/>
+      <c r="R27" s="48"/>
+      <c r="S27" s="48"/>
+      <c r="T27" s="48"/>
+      <c r="U27" s="48"/>
+      <c r="V27" s="53"/>
+      <c r="W27" s="55"/>
+      <c r="X27" s="48"/>
+      <c r="Y27" s="48"/>
+      <c r="Z27" s="53"/>
+      <c r="AA27" s="54"/>
+      <c r="AB27" s="48"/>
+      <c r="AC27" s="48"/>
+      <c r="AD27" s="52"/>
+      <c r="AE27" s="53"/>
+      <c r="AF27" s="54"/>
+      <c r="AG27" s="48"/>
+      <c r="AH27" s="48"/>
+      <c r="AI27" s="48"/>
+      <c r="AJ27" s="48"/>
+      <c r="AK27" s="48"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="47"/>
-      <c r="C28" s="48" t="s">
-        <v>118</v>
-      </c>
-      <c r="D28" s="49"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="52"/>
-      <c r="I28" s="63"/>
-      <c r="J28" s="63"/>
-      <c r="K28" s="63"/>
-      <c r="L28" s="53"/>
-      <c r="M28" s="49"/>
-      <c r="N28" s="54"/>
-      <c r="O28" s="55"/>
-      <c r="P28" s="49"/>
-      <c r="Q28" s="49"/>
-      <c r="R28" s="49"/>
-      <c r="S28" s="49"/>
-      <c r="T28" s="49"/>
-      <c r="U28" s="49"/>
-      <c r="V28" s="54"/>
-      <c r="W28" s="56"/>
-      <c r="X28" s="49"/>
-      <c r="Y28" s="49"/>
-      <c r="Z28" s="54"/>
-      <c r="AA28" s="55"/>
-      <c r="AB28" s="49"/>
-      <c r="AC28" s="49"/>
-      <c r="AD28" s="53"/>
-      <c r="AE28" s="54"/>
-      <c r="AF28" s="55"/>
-      <c r="AG28" s="49"/>
-      <c r="AH28" s="49"/>
-      <c r="AI28" s="49"/>
-      <c r="AJ28" s="49"/>
-      <c r="AK28" s="49"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" s="48"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="62"/>
+      <c r="K28" s="62"/>
+      <c r="L28" s="52"/>
+      <c r="M28" s="48"/>
+      <c r="N28" s="53"/>
+      <c r="O28" s="54"/>
+      <c r="P28" s="48"/>
+      <c r="Q28" s="48"/>
+      <c r="R28" s="48"/>
+      <c r="S28" s="48"/>
+      <c r="T28" s="48"/>
+      <c r="U28" s="48"/>
+      <c r="V28" s="53"/>
+      <c r="W28" s="55"/>
+      <c r="X28" s="48"/>
+      <c r="Y28" s="48"/>
+      <c r="Z28" s="53"/>
+      <c r="AA28" s="54"/>
+      <c r="AB28" s="48"/>
+      <c r="AC28" s="48"/>
+      <c r="AD28" s="52"/>
+      <c r="AE28" s="53"/>
+      <c r="AF28" s="54"/>
+      <c r="AG28" s="48"/>
+      <c r="AH28" s="48"/>
+      <c r="AI28" s="48"/>
+      <c r="AJ28" s="48"/>
+      <c r="AK28" s="48"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="47"/>
-      <c r="C29" s="48"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="49"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="60"/>
-      <c r="H29" s="61"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="64"/>
-      <c r="K29" s="49"/>
-      <c r="L29" s="53"/>
-      <c r="M29" s="49"/>
-      <c r="N29" s="54"/>
-      <c r="O29" s="55"/>
-      <c r="P29" s="49"/>
-      <c r="Q29" s="49"/>
-      <c r="R29" s="49"/>
-      <c r="S29" s="49"/>
-      <c r="T29" s="49"/>
-      <c r="U29" s="49"/>
-      <c r="V29" s="54"/>
-      <c r="W29" s="56"/>
-      <c r="X29" s="49"/>
-      <c r="Y29" s="49"/>
-      <c r="Z29" s="54"/>
-      <c r="AA29" s="55"/>
-      <c r="AB29" s="49"/>
-      <c r="AC29" s="49"/>
-      <c r="AD29" s="53"/>
-      <c r="AE29" s="54"/>
-      <c r="AF29" s="55"/>
-      <c r="AG29" s="49"/>
-      <c r="AH29" s="49"/>
-      <c r="AI29" s="49"/>
-      <c r="AJ29" s="49"/>
-      <c r="AK29" s="49"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="47"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="60"/>
+      <c r="I29" s="48"/>
+      <c r="J29" s="63"/>
+      <c r="K29" s="48"/>
+      <c r="L29" s="52"/>
+      <c r="M29" s="48"/>
+      <c r="N29" s="53"/>
+      <c r="O29" s="54"/>
+      <c r="P29" s="48"/>
+      <c r="Q29" s="48"/>
+      <c r="R29" s="48"/>
+      <c r="S29" s="48"/>
+      <c r="T29" s="48"/>
+      <c r="U29" s="48"/>
+      <c r="V29" s="53"/>
+      <c r="W29" s="55"/>
+      <c r="X29" s="48"/>
+      <c r="Y29" s="48"/>
+      <c r="Z29" s="53"/>
+      <c r="AA29" s="54"/>
+      <c r="AB29" s="48"/>
+      <c r="AC29" s="48"/>
+      <c r="AD29" s="52"/>
+      <c r="AE29" s="53"/>
+      <c r="AF29" s="54"/>
+      <c r="AG29" s="48"/>
+      <c r="AH29" s="48"/>
+      <c r="AI29" s="48"/>
+      <c r="AJ29" s="48"/>
+      <c r="AK29" s="48"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="47"/>
-      <c r="C30" s="48" t="s">
-        <v>119</v>
-      </c>
-      <c r="D30" s="49"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="54"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="63"/>
-      <c r="J30" s="63"/>
-      <c r="K30" s="63"/>
-      <c r="L30" s="53"/>
-      <c r="M30" s="63"/>
-      <c r="N30" s="54"/>
-      <c r="O30" s="55"/>
-      <c r="P30" s="49"/>
-      <c r="Q30" s="49"/>
-      <c r="R30" s="49"/>
-      <c r="S30" s="49"/>
-      <c r="T30" s="49"/>
-      <c r="U30" s="49"/>
-      <c r="V30" s="54"/>
-      <c r="W30" s="56"/>
-      <c r="X30" s="49"/>
-      <c r="Y30" s="49"/>
-      <c r="Z30" s="54"/>
-      <c r="AA30" s="55"/>
-      <c r="AB30" s="49"/>
-      <c r="AC30" s="49"/>
-      <c r="AD30" s="53"/>
-      <c r="AE30" s="54"/>
-      <c r="AF30" s="55"/>
-      <c r="AG30" s="49"/>
-      <c r="AH30" s="49"/>
-      <c r="AI30" s="49"/>
-      <c r="AJ30" s="49"/>
-      <c r="AK30" s="49"/>
+      <c r="B30" s="46"/>
+      <c r="C30" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" s="48"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="62"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="52"/>
+      <c r="M30" s="62"/>
+      <c r="N30" s="53"/>
+      <c r="O30" s="54"/>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="48"/>
+      <c r="R30" s="48"/>
+      <c r="S30" s="48"/>
+      <c r="T30" s="48"/>
+      <c r="U30" s="48"/>
+      <c r="V30" s="53"/>
+      <c r="W30" s="55"/>
+      <c r="X30" s="48"/>
+      <c r="Y30" s="48"/>
+      <c r="Z30" s="53"/>
+      <c r="AA30" s="54"/>
+      <c r="AB30" s="48"/>
+      <c r="AC30" s="48"/>
+      <c r="AD30" s="52"/>
+      <c r="AE30" s="53"/>
+      <c r="AF30" s="54"/>
+      <c r="AG30" s="48"/>
+      <c r="AH30" s="48"/>
+      <c r="AI30" s="48"/>
+      <c r="AJ30" s="48"/>
+      <c r="AK30" s="48"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="47"/>
-      <c r="C31" s="48"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="60"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="64"/>
-      <c r="K31" s="64"/>
-      <c r="L31" s="73"/>
-      <c r="M31" s="49"/>
-      <c r="N31" s="60"/>
-      <c r="O31" s="55"/>
-      <c r="P31" s="49"/>
-      <c r="Q31" s="49"/>
-      <c r="R31" s="49"/>
-      <c r="S31" s="49"/>
-      <c r="T31" s="49"/>
-      <c r="U31" s="49"/>
-      <c r="V31" s="54"/>
-      <c r="W31" s="56"/>
-      <c r="X31" s="49"/>
-      <c r="Y31" s="49"/>
-      <c r="Z31" s="54"/>
-      <c r="AA31" s="55"/>
-      <c r="AB31" s="49"/>
-      <c r="AC31" s="49"/>
-      <c r="AD31" s="53"/>
-      <c r="AE31" s="54"/>
-      <c r="AF31" s="55"/>
-      <c r="AG31" s="49"/>
-      <c r="AH31" s="49"/>
-      <c r="AI31" s="49"/>
-      <c r="AJ31" s="49"/>
-      <c r="AK31" s="49"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="48"/>
+      <c r="J31" s="63"/>
+      <c r="K31" s="63"/>
+      <c r="L31" s="72"/>
+      <c r="M31" s="48"/>
+      <c r="N31" s="59"/>
+      <c r="O31" s="54"/>
+      <c r="P31" s="48"/>
+      <c r="Q31" s="48"/>
+      <c r="R31" s="48"/>
+      <c r="S31" s="48"/>
+      <c r="T31" s="48"/>
+      <c r="U31" s="48"/>
+      <c r="V31" s="53"/>
+      <c r="W31" s="55"/>
+      <c r="X31" s="48"/>
+      <c r="Y31" s="48"/>
+      <c r="Z31" s="53"/>
+      <c r="AA31" s="54"/>
+      <c r="AB31" s="48"/>
+      <c r="AC31" s="48"/>
+      <c r="AD31" s="52"/>
+      <c r="AE31" s="53"/>
+      <c r="AF31" s="54"/>
+      <c r="AG31" s="48"/>
+      <c r="AH31" s="48"/>
+      <c r="AI31" s="48"/>
+      <c r="AJ31" s="48"/>
+      <c r="AK31" s="48"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="47"/>
-      <c r="C32" s="48" t="s">
-        <v>120</v>
-      </c>
-      <c r="D32" s="49"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="57"/>
-      <c r="G32" s="54"/>
-      <c r="H32" s="55"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="49"/>
-      <c r="K32" s="49"/>
-      <c r="L32" s="53"/>
-      <c r="M32" s="63"/>
-      <c r="N32" s="51"/>
-      <c r="O32" s="55"/>
-      <c r="P32" s="49"/>
-      <c r="Q32" s="49"/>
-      <c r="R32" s="49"/>
-      <c r="S32" s="49"/>
-      <c r="T32" s="49"/>
-      <c r="U32" s="49"/>
-      <c r="V32" s="54"/>
-      <c r="W32" s="56"/>
-      <c r="X32" s="49"/>
-      <c r="Y32" s="49"/>
-      <c r="Z32" s="54"/>
-      <c r="AA32" s="55"/>
-      <c r="AB32" s="49"/>
-      <c r="AC32" s="49"/>
-      <c r="AD32" s="53"/>
-      <c r="AE32" s="54"/>
-      <c r="AF32" s="55"/>
-      <c r="AG32" s="49"/>
-      <c r="AH32" s="49"/>
-      <c r="AI32" s="49"/>
-      <c r="AJ32" s="49"/>
-      <c r="AK32" s="49"/>
+      <c r="B32" s="46"/>
+      <c r="C32" s="47" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" s="48"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="56"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="48"/>
+      <c r="J32" s="48"/>
+      <c r="K32" s="48"/>
+      <c r="L32" s="52"/>
+      <c r="M32" s="62"/>
+      <c r="N32" s="50"/>
+      <c r="O32" s="54"/>
+      <c r="P32" s="48"/>
+      <c r="Q32" s="48"/>
+      <c r="R32" s="48"/>
+      <c r="S32" s="48"/>
+      <c r="T32" s="48"/>
+      <c r="U32" s="48"/>
+      <c r="V32" s="53"/>
+      <c r="W32" s="55"/>
+      <c r="X32" s="48"/>
+      <c r="Y32" s="48"/>
+      <c r="Z32" s="53"/>
+      <c r="AA32" s="54"/>
+      <c r="AB32" s="48"/>
+      <c r="AC32" s="48"/>
+      <c r="AD32" s="52"/>
+      <c r="AE32" s="53"/>
+      <c r="AF32" s="54"/>
+      <c r="AG32" s="48"/>
+      <c r="AH32" s="48"/>
+      <c r="AI32" s="48"/>
+      <c r="AJ32" s="48"/>
+      <c r="AK32" s="48"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="47"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="49"/>
-      <c r="E33" s="49"/>
-      <c r="F33" s="57"/>
-      <c r="G33" s="54"/>
-      <c r="H33" s="55"/>
-      <c r="I33" s="49"/>
-      <c r="J33" s="49"/>
-      <c r="K33" s="49"/>
-      <c r="L33" s="53"/>
-      <c r="M33" s="49"/>
-      <c r="N33" s="60"/>
-      <c r="O33" s="55"/>
-      <c r="P33" s="49"/>
-      <c r="Q33" s="49"/>
-      <c r="R33" s="49"/>
-      <c r="S33" s="49"/>
-      <c r="T33" s="49"/>
-      <c r="U33" s="49"/>
-      <c r="V33" s="54"/>
-      <c r="W33" s="56"/>
-      <c r="X33" s="49"/>
-      <c r="Y33" s="49"/>
-      <c r="Z33" s="54"/>
-      <c r="AA33" s="55"/>
-      <c r="AB33" s="49"/>
-      <c r="AC33" s="49"/>
-      <c r="AD33" s="53"/>
-      <c r="AE33" s="54"/>
-      <c r="AF33" s="55"/>
-      <c r="AG33" s="49"/>
-      <c r="AH33" s="49"/>
-      <c r="AI33" s="49"/>
-      <c r="AJ33" s="49"/>
-      <c r="AK33" s="49"/>
+      <c r="B33" s="46"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="48"/>
+      <c r="J33" s="48"/>
+      <c r="K33" s="48"/>
+      <c r="L33" s="52"/>
+      <c r="M33" s="48"/>
+      <c r="N33" s="59"/>
+      <c r="O33" s="54"/>
+      <c r="P33" s="48"/>
+      <c r="Q33" s="48"/>
+      <c r="R33" s="48"/>
+      <c r="S33" s="48"/>
+      <c r="T33" s="48"/>
+      <c r="U33" s="48"/>
+      <c r="V33" s="53"/>
+      <c r="W33" s="55"/>
+      <c r="X33" s="48"/>
+      <c r="Y33" s="48"/>
+      <c r="Z33" s="53"/>
+      <c r="AA33" s="54"/>
+      <c r="AB33" s="48"/>
+      <c r="AC33" s="48"/>
+      <c r="AD33" s="52"/>
+      <c r="AE33" s="53"/>
+      <c r="AF33" s="54"/>
+      <c r="AG33" s="48"/>
+      <c r="AH33" s="48"/>
+      <c r="AI33" s="48"/>
+      <c r="AJ33" s="48"/>
+      <c r="AK33" s="48"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="65" t="s">
-        <v>121</v>
-      </c>
-      <c r="C34" s="74" t="s">
+      <c r="B34" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="D34" s="68"/>
-      <c r="E34" s="68"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="69"/>
-      <c r="H34" s="67"/>
-      <c r="I34" s="68"/>
-      <c r="J34" s="68"/>
-      <c r="K34" s="68"/>
-      <c r="L34" s="53"/>
-      <c r="M34" s="63"/>
-      <c r="N34" s="51"/>
-      <c r="O34" s="52"/>
-      <c r="P34" s="63"/>
-      <c r="Q34" s="63"/>
-      <c r="R34" s="63"/>
-      <c r="S34" s="68"/>
-      <c r="T34" s="68"/>
-      <c r="U34" s="68"/>
-      <c r="V34" s="69"/>
-      <c r="W34" s="56"/>
-      <c r="X34" s="68"/>
-      <c r="Y34" s="68"/>
-      <c r="Z34" s="69"/>
-      <c r="AA34" s="67"/>
-      <c r="AB34" s="68"/>
-      <c r="AC34" s="68"/>
-      <c r="AD34" s="53"/>
-      <c r="AE34" s="69"/>
-      <c r="AF34" s="67"/>
-      <c r="AG34" s="68"/>
-      <c r="AH34" s="68"/>
-      <c r="AI34" s="68"/>
-      <c r="AJ34" s="68"/>
-      <c r="AK34" s="68"/>
+      <c r="C34" s="73" t="s">
+        <v>123</v>
+      </c>
+      <c r="D34" s="67"/>
+      <c r="E34" s="67"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="68"/>
+      <c r="H34" s="66"/>
+      <c r="I34" s="67"/>
+      <c r="J34" s="67"/>
+      <c r="K34" s="67"/>
+      <c r="L34" s="52"/>
+      <c r="M34" s="62"/>
+      <c r="N34" s="50"/>
+      <c r="O34" s="51"/>
+      <c r="P34" s="62"/>
+      <c r="Q34" s="62"/>
+      <c r="R34" s="62"/>
+      <c r="S34" s="67"/>
+      <c r="T34" s="67"/>
+      <c r="U34" s="67"/>
+      <c r="V34" s="68"/>
+      <c r="W34" s="55"/>
+      <c r="X34" s="67"/>
+      <c r="Y34" s="67"/>
+      <c r="Z34" s="68"/>
+      <c r="AA34" s="66"/>
+      <c r="AB34" s="67"/>
+      <c r="AC34" s="67"/>
+      <c r="AD34" s="52"/>
+      <c r="AE34" s="68"/>
+      <c r="AF34" s="66"/>
+      <c r="AG34" s="67"/>
+      <c r="AH34" s="67"/>
+      <c r="AI34" s="67"/>
+      <c r="AJ34" s="67"/>
+      <c r="AK34" s="67"/>
     </row>
     <row r="35" ht="12" customHeight="1">
-      <c r="B35" s="65"/>
-      <c r="C35" s="74"/>
-      <c r="D35" s="68"/>
-      <c r="E35" s="68"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="69"/>
-      <c r="H35" s="67"/>
-      <c r="I35" s="68"/>
-      <c r="J35" s="68"/>
-      <c r="K35" s="75"/>
-      <c r="L35" s="53"/>
-      <c r="M35" s="68"/>
-      <c r="N35" s="60"/>
-      <c r="O35" s="67"/>
-      <c r="P35" s="62"/>
-      <c r="Q35" s="68"/>
-      <c r="R35" s="76"/>
-      <c r="S35" s="76"/>
-      <c r="T35" s="68"/>
-      <c r="U35" s="68"/>
-      <c r="V35" s="69"/>
-      <c r="W35" s="56"/>
-      <c r="X35" s="68"/>
-      <c r="Y35" s="68"/>
-      <c r="Z35" s="69"/>
-      <c r="AA35" s="67"/>
-      <c r="AB35" s="68"/>
-      <c r="AC35" s="68"/>
-      <c r="AD35" s="53"/>
-      <c r="AE35" s="69"/>
-      <c r="AF35" s="67"/>
-      <c r="AG35" s="68"/>
-      <c r="AH35" s="68"/>
-      <c r="AI35" s="68"/>
-      <c r="AJ35" s="68"/>
-      <c r="AK35" s="68"/>
+      <c r="B35" s="64"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="68"/>
+      <c r="H35" s="66"/>
+      <c r="I35" s="67"/>
+      <c r="J35" s="67"/>
+      <c r="K35" s="74"/>
+      <c r="L35" s="52"/>
+      <c r="M35" s="67"/>
+      <c r="N35" s="59"/>
+      <c r="O35" s="66"/>
+      <c r="P35" s="61"/>
+      <c r="Q35" s="67"/>
+      <c r="R35" s="75"/>
+      <c r="S35" s="75"/>
+      <c r="T35" s="57"/>
+      <c r="U35" s="67"/>
+      <c r="V35" s="68"/>
+      <c r="W35" s="55"/>
+      <c r="X35" s="67"/>
+      <c r="Y35" s="67"/>
+      <c r="Z35" s="68"/>
+      <c r="AA35" s="66"/>
+      <c r="AB35" s="67"/>
+      <c r="AC35" s="67"/>
+      <c r="AD35" s="52"/>
+      <c r="AE35" s="68"/>
+      <c r="AF35" s="66"/>
+      <c r="AG35" s="67"/>
+      <c r="AH35" s="67"/>
+      <c r="AI35" s="67"/>
+      <c r="AJ35" s="67"/>
+      <c r="AK35" s="67"/>
     </row>
     <row r="36" ht="12" customHeight="1">
-      <c r="B36" s="65"/>
-      <c r="C36" s="74" t="s">
-        <v>123</v>
-      </c>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="71"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="67"/>
-      <c r="I36" s="68"/>
-      <c r="J36" s="68"/>
-      <c r="K36" s="68"/>
-      <c r="L36" s="53"/>
-      <c r="M36" s="63"/>
-      <c r="N36" s="51"/>
-      <c r="O36" s="52"/>
-      <c r="P36" s="63"/>
-      <c r="Q36" s="68"/>
-      <c r="R36" s="68"/>
-      <c r="S36" s="68"/>
-      <c r="T36" s="68"/>
-      <c r="U36" s="68"/>
-      <c r="V36" s="69"/>
-      <c r="W36" s="56"/>
-      <c r="X36" s="68"/>
-      <c r="Y36" s="68"/>
-      <c r="Z36" s="69"/>
-      <c r="AA36" s="67"/>
-      <c r="AB36" s="68"/>
-      <c r="AC36" s="68"/>
-      <c r="AD36" s="53"/>
-      <c r="AE36" s="69"/>
-      <c r="AF36" s="67"/>
-      <c r="AG36" s="68"/>
-      <c r="AH36" s="68"/>
-      <c r="AI36" s="68"/>
-      <c r="AJ36" s="68"/>
-      <c r="AK36" s="68"/>
+      <c r="B36" s="64"/>
+      <c r="C36" s="73" t="s">
+        <v>124</v>
+      </c>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="68"/>
+      <c r="H36" s="66"/>
+      <c r="I36" s="67"/>
+      <c r="J36" s="67"/>
+      <c r="K36" s="67"/>
+      <c r="L36" s="52"/>
+      <c r="M36" s="62"/>
+      <c r="N36" s="50"/>
+      <c r="O36" s="51"/>
+      <c r="P36" s="62"/>
+      <c r="Q36" s="67"/>
+      <c r="R36" s="67"/>
+      <c r="S36" s="67"/>
+      <c r="T36" s="67"/>
+      <c r="U36" s="67"/>
+      <c r="V36" s="68"/>
+      <c r="W36" s="55"/>
+      <c r="X36" s="67"/>
+      <c r="Y36" s="67"/>
+      <c r="Z36" s="68"/>
+      <c r="AA36" s="66"/>
+      <c r="AB36" s="67"/>
+      <c r="AC36" s="67"/>
+      <c r="AD36" s="52"/>
+      <c r="AE36" s="68"/>
+      <c r="AF36" s="66"/>
+      <c r="AG36" s="67"/>
+      <c r="AH36" s="67"/>
+      <c r="AI36" s="67"/>
+      <c r="AJ36" s="67"/>
+      <c r="AK36" s="67"/>
     </row>
     <row r="37" ht="12" customHeight="1">
-      <c r="B37" s="65"/>
-      <c r="C37" s="74"/>
-      <c r="D37" s="68"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="71"/>
-      <c r="G37" s="69"/>
-      <c r="H37" s="67"/>
-      <c r="I37" s="68"/>
-      <c r="J37" s="68"/>
-      <c r="K37" s="75"/>
-      <c r="L37" s="53"/>
-      <c r="M37" s="68"/>
-      <c r="N37" s="69"/>
-      <c r="O37" s="67"/>
-      <c r="P37" s="62"/>
-      <c r="Q37" s="68"/>
-      <c r="R37" s="76"/>
-      <c r="S37" s="76"/>
-      <c r="T37" s="68"/>
-      <c r="U37" s="68"/>
-      <c r="V37" s="69"/>
-      <c r="W37" s="56"/>
-      <c r="X37" s="68"/>
-      <c r="Y37" s="68"/>
-      <c r="Z37" s="69"/>
-      <c r="AA37" s="67"/>
-      <c r="AB37" s="68"/>
-      <c r="AC37" s="68"/>
-      <c r="AD37" s="53"/>
-      <c r="AE37" s="69"/>
-      <c r="AF37" s="67"/>
-      <c r="AG37" s="68"/>
-      <c r="AH37" s="68"/>
-      <c r="AI37" s="68"/>
-      <c r="AJ37" s="68"/>
-      <c r="AK37" s="68"/>
+      <c r="B37" s="64"/>
+      <c r="C37" s="73"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="67"/>
+      <c r="F37" s="70"/>
+      <c r="G37" s="68"/>
+      <c r="H37" s="66"/>
+      <c r="I37" s="67"/>
+      <c r="J37" s="67"/>
+      <c r="K37" s="74"/>
+      <c r="L37" s="52"/>
+      <c r="M37" s="67"/>
+      <c r="N37" s="68"/>
+      <c r="O37" s="66"/>
+      <c r="P37" s="61"/>
+      <c r="Q37" s="67"/>
+      <c r="R37" s="75"/>
+      <c r="S37" s="75"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="67"/>
+      <c r="V37" s="68"/>
+      <c r="W37" s="55"/>
+      <c r="X37" s="67"/>
+      <c r="Y37" s="67"/>
+      <c r="Z37" s="68"/>
+      <c r="AA37" s="66"/>
+      <c r="AB37" s="67"/>
+      <c r="AC37" s="67"/>
+      <c r="AD37" s="52"/>
+      <c r="AE37" s="68"/>
+      <c r="AF37" s="66"/>
+      <c r="AG37" s="67"/>
+      <c r="AH37" s="67"/>
+      <c r="AI37" s="67"/>
+      <c r="AJ37" s="67"/>
+      <c r="AK37" s="67"/>
     </row>
     <row r="38" ht="12" customHeight="1">
-      <c r="B38" s="65"/>
-      <c r="C38" s="74" t="s">
-        <v>124</v>
-      </c>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="71"/>
-      <c r="G38" s="69"/>
-      <c r="H38" s="67"/>
-      <c r="I38" s="68"/>
-      <c r="J38" s="68"/>
-      <c r="K38" s="68"/>
-      <c r="L38" s="53"/>
-      <c r="M38" s="68"/>
-      <c r="N38" s="69"/>
-      <c r="O38" s="52"/>
-      <c r="P38" s="63"/>
-      <c r="Q38" s="63"/>
-      <c r="R38" s="63"/>
-      <c r="S38" s="63"/>
-      <c r="T38" s="63"/>
-      <c r="U38" s="63"/>
-      <c r="V38" s="51"/>
-      <c r="W38" s="56"/>
-      <c r="X38" s="63"/>
-      <c r="Y38" s="63"/>
-      <c r="Z38" s="69"/>
-      <c r="AA38" s="67"/>
-      <c r="AB38" s="68"/>
-      <c r="AC38" s="68"/>
-      <c r="AD38" s="53"/>
-      <c r="AE38" s="69"/>
-      <c r="AF38" s="67"/>
-      <c r="AG38" s="68"/>
-      <c r="AH38" s="68"/>
-      <c r="AI38" s="68"/>
-      <c r="AJ38" s="68"/>
-      <c r="AK38" s="68"/>
+      <c r="B38" s="64"/>
+      <c r="C38" s="73" t="s">
+        <v>125</v>
+      </c>
+      <c r="D38" s="67"/>
+      <c r="E38" s="67"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="68"/>
+      <c r="H38" s="66"/>
+      <c r="I38" s="67"/>
+      <c r="J38" s="67"/>
+      <c r="K38" s="67"/>
+      <c r="L38" s="52"/>
+      <c r="M38" s="67"/>
+      <c r="N38" s="68"/>
+      <c r="O38" s="51"/>
+      <c r="P38" s="62"/>
+      <c r="Q38" s="62"/>
+      <c r="R38" s="62"/>
+      <c r="S38" s="62"/>
+      <c r="T38" s="62"/>
+      <c r="U38" s="62"/>
+      <c r="V38" s="50"/>
+      <c r="W38" s="55"/>
+      <c r="X38" s="62"/>
+      <c r="Y38" s="62"/>
+      <c r="Z38" s="68"/>
+      <c r="AA38" s="66"/>
+      <c r="AB38" s="67"/>
+      <c r="AC38" s="67"/>
+      <c r="AD38" s="52"/>
+      <c r="AE38" s="68"/>
+      <c r="AF38" s="66"/>
+      <c r="AG38" s="67"/>
+      <c r="AH38" s="67"/>
+      <c r="AI38" s="67"/>
+      <c r="AJ38" s="67"/>
+      <c r="AK38" s="67"/>
     </row>
     <row r="39" ht="12" customHeight="1">
-      <c r="B39" s="65"/>
-      <c r="C39" s="74"/>
-      <c r="D39" s="68"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="71"/>
-      <c r="G39" s="69"/>
-      <c r="H39" s="67"/>
-      <c r="I39" s="68"/>
-      <c r="J39" s="68"/>
-      <c r="K39" s="68"/>
-      <c r="L39" s="53"/>
-      <c r="M39" s="68"/>
-      <c r="N39" s="69"/>
-      <c r="O39" s="67"/>
-      <c r="P39" s="62"/>
-      <c r="Q39" s="62"/>
-      <c r="R39" s="75"/>
-      <c r="S39" s="75"/>
-      <c r="T39" s="68"/>
-      <c r="U39" s="68"/>
-      <c r="V39" s="69"/>
-      <c r="W39" s="56"/>
-      <c r="X39" s="68"/>
-      <c r="Y39" s="68"/>
-      <c r="Z39" s="69"/>
-      <c r="AA39" s="67"/>
-      <c r="AB39" s="68"/>
-      <c r="AC39" s="68"/>
-      <c r="AD39" s="53"/>
-      <c r="AE39" s="69"/>
-      <c r="AF39" s="67"/>
-      <c r="AG39" s="68"/>
-      <c r="AH39" s="68"/>
-      <c r="AI39" s="68"/>
-      <c r="AJ39" s="68"/>
-      <c r="AK39" s="68"/>
+      <c r="B39" s="64"/>
+      <c r="C39" s="73"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="68"/>
+      <c r="H39" s="66"/>
+      <c r="I39" s="67"/>
+      <c r="J39" s="67"/>
+      <c r="K39" s="67"/>
+      <c r="L39" s="52"/>
+      <c r="M39" s="67"/>
+      <c r="N39" s="68"/>
+      <c r="O39" s="66"/>
+      <c r="P39" s="67"/>
+      <c r="Q39" s="67"/>
+      <c r="R39" s="74"/>
+      <c r="S39" s="74"/>
+      <c r="T39" s="67"/>
+      <c r="U39" s="67"/>
+      <c r="V39" s="68"/>
+      <c r="W39" s="55"/>
+      <c r="X39" s="67"/>
+      <c r="Y39" s="67"/>
+      <c r="Z39" s="68"/>
+      <c r="AA39" s="66"/>
+      <c r="AB39" s="67"/>
+      <c r="AC39" s="67"/>
+      <c r="AD39" s="52"/>
+      <c r="AE39" s="68"/>
+      <c r="AF39" s="66"/>
+      <c r="AG39" s="67"/>
+      <c r="AH39" s="67"/>
+      <c r="AI39" s="67"/>
+      <c r="AJ39" s="67"/>
+      <c r="AK39" s="67"/>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="B40" s="65"/>
-      <c r="C40" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="D40" s="68"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="71"/>
-      <c r="G40" s="69"/>
-      <c r="H40" s="67"/>
-      <c r="I40" s="68"/>
-      <c r="J40" s="68"/>
-      <c r="K40" s="68"/>
-      <c r="L40" s="53"/>
-      <c r="M40" s="68"/>
-      <c r="N40" s="69"/>
-      <c r="O40" s="67"/>
-      <c r="P40" s="68"/>
-      <c r="Q40" s="68"/>
-      <c r="R40" s="63"/>
-      <c r="S40" s="63"/>
-      <c r="T40" s="63"/>
-      <c r="U40" s="63"/>
-      <c r="V40" s="51"/>
-      <c r="W40" s="56"/>
-      <c r="X40" s="63"/>
-      <c r="Y40" s="63"/>
-      <c r="Z40" s="51"/>
-      <c r="AA40" s="52"/>
-      <c r="AB40" s="63"/>
-      <c r="AC40" s="63"/>
-      <c r="AD40" s="53"/>
-      <c r="AE40" s="69"/>
-      <c r="AF40" s="67"/>
-      <c r="AG40" s="68"/>
-      <c r="AH40" s="68"/>
-      <c r="AI40" s="68"/>
-      <c r="AJ40" s="68"/>
-      <c r="AK40" s="68"/>
+      <c r="B40" s="64"/>
+      <c r="C40" s="73" t="s">
+        <v>126</v>
+      </c>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="68"/>
+      <c r="H40" s="66"/>
+      <c r="I40" s="67"/>
+      <c r="J40" s="67"/>
+      <c r="K40" s="67"/>
+      <c r="L40" s="52"/>
+      <c r="M40" s="67"/>
+      <c r="N40" s="68"/>
+      <c r="O40" s="66"/>
+      <c r="P40" s="67"/>
+      <c r="Q40" s="67"/>
+      <c r="R40" s="62"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="62"/>
+      <c r="U40" s="62"/>
+      <c r="V40" s="50"/>
+      <c r="W40" s="55"/>
+      <c r="X40" s="62"/>
+      <c r="Y40" s="62"/>
+      <c r="Z40" s="50"/>
+      <c r="AA40" s="51"/>
+      <c r="AB40" s="62"/>
+      <c r="AC40" s="62"/>
+      <c r="AD40" s="52"/>
+      <c r="AE40" s="68"/>
+      <c r="AF40" s="66"/>
+      <c r="AG40" s="67"/>
+      <c r="AH40" s="67"/>
+      <c r="AI40" s="67"/>
+      <c r="AJ40" s="67"/>
+      <c r="AK40" s="67"/>
     </row>
     <row r="41" ht="12" customHeight="1">
-      <c r="B41" s="65"/>
-      <c r="C41" s="74"/>
-      <c r="D41" s="68"/>
-      <c r="E41" s="68"/>
-      <c r="F41" s="71"/>
-      <c r="G41" s="69"/>
-      <c r="H41" s="67"/>
-      <c r="I41" s="68"/>
-      <c r="J41" s="68"/>
-      <c r="K41" s="68"/>
-      <c r="L41" s="53"/>
-      <c r="M41" s="68"/>
-      <c r="N41" s="69"/>
-      <c r="O41" s="67"/>
-      <c r="P41" s="68"/>
-      <c r="Q41" s="62"/>
-      <c r="R41" s="75"/>
-      <c r="S41" s="75"/>
-      <c r="T41" s="68"/>
-      <c r="U41" s="68"/>
-      <c r="V41" s="69"/>
-      <c r="W41" s="56"/>
-      <c r="X41" s="68"/>
-      <c r="Y41" s="68"/>
-      <c r="Z41" s="69"/>
-      <c r="AA41" s="67"/>
-      <c r="AB41" s="68"/>
-      <c r="AC41" s="68"/>
-      <c r="AD41" s="53"/>
-      <c r="AE41" s="69"/>
-      <c r="AF41" s="67"/>
-      <c r="AG41" s="68"/>
-      <c r="AH41" s="68"/>
-      <c r="AI41" s="68"/>
-      <c r="AJ41" s="68"/>
-      <c r="AK41" s="68"/>
+      <c r="B41" s="64"/>
+      <c r="C41" s="73"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="68"/>
+      <c r="H41" s="66"/>
+      <c r="I41" s="67"/>
+      <c r="J41" s="67"/>
+      <c r="K41" s="67"/>
+      <c r="L41" s="52"/>
+      <c r="M41" s="67"/>
+      <c r="N41" s="68"/>
+      <c r="O41" s="66"/>
+      <c r="P41" s="67"/>
+      <c r="Q41" s="61"/>
+      <c r="R41" s="74"/>
+      <c r="S41" s="74"/>
+      <c r="T41" s="61"/>
+      <c r="U41" s="67"/>
+      <c r="V41" s="68"/>
+      <c r="W41" s="55"/>
+      <c r="X41" s="67"/>
+      <c r="Y41" s="67"/>
+      <c r="Z41" s="68"/>
+      <c r="AA41" s="66"/>
+      <c r="AB41" s="67"/>
+      <c r="AC41" s="67"/>
+      <c r="AD41" s="52"/>
+      <c r="AE41" s="68"/>
+      <c r="AF41" s="66"/>
+      <c r="AG41" s="67"/>
+      <c r="AH41" s="67"/>
+      <c r="AI41" s="67"/>
+      <c r="AJ41" s="67"/>
+      <c r="AK41" s="67"/>
     </row>
     <row r="42" ht="12" customHeight="1">
-      <c r="B42" s="47" t="s">
+      <c r="B42" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="77" t="s">
-        <v>126</v>
-      </c>
-      <c r="D42" s="49"/>
-      <c r="E42" s="49"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="54"/>
-      <c r="H42" s="55"/>
-      <c r="I42" s="49"/>
-      <c r="J42" s="49"/>
-      <c r="K42" s="49"/>
-      <c r="L42" s="53"/>
-      <c r="M42" s="49"/>
-      <c r="N42" s="54"/>
-      <c r="O42" s="55"/>
-      <c r="P42" s="63"/>
-      <c r="Q42" s="63"/>
-      <c r="R42" s="49"/>
-      <c r="S42" s="49"/>
-      <c r="T42" s="49"/>
-      <c r="U42" s="49"/>
-      <c r="V42" s="51"/>
-      <c r="W42" s="56"/>
-      <c r="X42" s="63"/>
-      <c r="Y42" s="63"/>
-      <c r="Z42" s="51"/>
-      <c r="AA42" s="52"/>
-      <c r="AB42" s="63"/>
-      <c r="AC42" s="63"/>
-      <c r="AD42" s="53"/>
-      <c r="AE42" s="54"/>
-      <c r="AF42" s="55"/>
-      <c r="AG42" s="49"/>
-      <c r="AH42" s="49"/>
-      <c r="AI42" s="49"/>
-      <c r="AJ42" s="49"/>
-      <c r="AK42" s="49"/>
+      <c r="C42" s="76" t="s">
+        <v>127</v>
+      </c>
+      <c r="D42" s="48"/>
+      <c r="E42" s="48"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="53"/>
+      <c r="H42" s="54"/>
+      <c r="I42" s="48"/>
+      <c r="J42" s="48"/>
+      <c r="K42" s="48"/>
+      <c r="L42" s="52"/>
+      <c r="M42" s="48"/>
+      <c r="N42" s="53"/>
+      <c r="O42" s="54"/>
+      <c r="P42" s="62"/>
+      <c r="Q42" s="62"/>
+      <c r="R42" s="48"/>
+      <c r="S42" s="48"/>
+      <c r="T42" s="61"/>
+      <c r="U42" s="48"/>
+      <c r="V42" s="50"/>
+      <c r="W42" s="55"/>
+      <c r="X42" s="62"/>
+      <c r="Y42" s="62"/>
+      <c r="Z42" s="50"/>
+      <c r="AA42" s="51"/>
+      <c r="AB42" s="62"/>
+      <c r="AC42" s="62"/>
+      <c r="AD42" s="52"/>
+      <c r="AE42" s="53"/>
+      <c r="AF42" s="54"/>
+      <c r="AG42" s="48"/>
+      <c r="AH42" s="48"/>
+      <c r="AI42" s="48"/>
+      <c r="AJ42" s="48"/>
+      <c r="AK42" s="48"/>
     </row>
     <row r="43" ht="12" customHeight="1">
-      <c r="B43" s="47"/>
-      <c r="C43" s="77"/>
-      <c r="D43" s="49"/>
-      <c r="E43" s="49"/>
-      <c r="F43" s="57"/>
-      <c r="G43" s="54"/>
-      <c r="H43" s="55"/>
-      <c r="I43" s="49"/>
-      <c r="J43" s="49"/>
-      <c r="K43" s="49"/>
-      <c r="L43" s="53"/>
-      <c r="M43" s="49"/>
-      <c r="N43" s="54"/>
-      <c r="O43" s="55"/>
-      <c r="P43" s="49"/>
-      <c r="Q43" s="62"/>
-      <c r="R43" s="49"/>
-      <c r="S43" s="64"/>
-      <c r="T43" s="49"/>
-      <c r="U43" s="49"/>
-      <c r="V43" s="54"/>
-      <c r="W43" s="56"/>
-      <c r="X43" s="49"/>
-      <c r="Y43" s="49"/>
-      <c r="Z43" s="54"/>
-      <c r="AA43" s="55"/>
-      <c r="AB43" s="49"/>
-      <c r="AC43" s="49"/>
-      <c r="AD43" s="53"/>
-      <c r="AE43" s="54"/>
-      <c r="AF43" s="55"/>
-      <c r="AG43" s="49"/>
-      <c r="AH43" s="49"/>
-      <c r="AI43" s="49"/>
-      <c r="AJ43" s="49"/>
-      <c r="AK43" s="49"/>
+      <c r="B43" s="46"/>
+      <c r="C43" s="76"/>
+      <c r="D43" s="48"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="56"/>
+      <c r="G43" s="53"/>
+      <c r="H43" s="54"/>
+      <c r="I43" s="48"/>
+      <c r="J43" s="48"/>
+      <c r="K43" s="48"/>
+      <c r="L43" s="52"/>
+      <c r="M43" s="48"/>
+      <c r="N43" s="53"/>
+      <c r="O43" s="54"/>
+      <c r="P43" s="48"/>
+      <c r="Q43" s="61"/>
+      <c r="R43" s="48"/>
+      <c r="S43" s="63"/>
+      <c r="T43" s="48"/>
+      <c r="U43" s="48"/>
+      <c r="V43" s="53"/>
+      <c r="W43" s="55"/>
+      <c r="X43" s="48"/>
+      <c r="Y43" s="48"/>
+      <c r="Z43" s="53"/>
+      <c r="AA43" s="54"/>
+      <c r="AB43" s="48"/>
+      <c r="AC43" s="48"/>
+      <c r="AD43" s="52"/>
+      <c r="AE43" s="53"/>
+      <c r="AF43" s="54"/>
+      <c r="AG43" s="48"/>
+      <c r="AH43" s="48"/>
+      <c r="AI43" s="48"/>
+      <c r="AJ43" s="48"/>
+      <c r="AK43" s="48"/>
     </row>
     <row r="44" ht="12" customHeight="1">
-      <c r="B44" s="47"/>
-      <c r="C44" s="77" t="s">
-        <v>127</v>
-      </c>
-      <c r="D44" s="49"/>
-      <c r="E44" s="49"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="54"/>
-      <c r="H44" s="55"/>
-      <c r="I44" s="49"/>
-      <c r="J44" s="49"/>
-      <c r="K44" s="49"/>
-      <c r="L44" s="53"/>
-      <c r="M44" s="49"/>
-      <c r="N44" s="54"/>
-      <c r="O44" s="55"/>
-      <c r="P44" s="63"/>
-      <c r="Q44" s="63"/>
-      <c r="R44" s="49"/>
-      <c r="S44" s="49"/>
-      <c r="T44" s="49"/>
-      <c r="U44" s="49"/>
-      <c r="V44" s="54"/>
-      <c r="W44" s="56"/>
-      <c r="X44" s="63"/>
-      <c r="Y44" s="63"/>
-      <c r="Z44" s="54"/>
-      <c r="AA44" s="55"/>
-      <c r="AB44" s="49"/>
-      <c r="AC44" s="63"/>
-      <c r="AD44" s="53"/>
-      <c r="AE44" s="51"/>
-      <c r="AF44" s="52"/>
-      <c r="AG44" s="49"/>
-      <c r="AH44" s="49"/>
-      <c r="AI44" s="63"/>
-      <c r="AJ44" s="49"/>
-      <c r="AK44" s="49"/>
+      <c r="B44" s="46"/>
+      <c r="C44" s="76" t="s">
+        <v>128</v>
+      </c>
+      <c r="D44" s="48"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="56"/>
+      <c r="G44" s="53"/>
+      <c r="H44" s="54"/>
+      <c r="I44" s="48"/>
+      <c r="J44" s="48"/>
+      <c r="K44" s="48"/>
+      <c r="L44" s="52"/>
+      <c r="M44" s="48"/>
+      <c r="N44" s="53"/>
+      <c r="O44" s="54"/>
+      <c r="P44" s="62"/>
+      <c r="Q44" s="62"/>
+      <c r="R44" s="48"/>
+      <c r="S44" s="48"/>
+      <c r="T44" s="48"/>
+      <c r="U44" s="48"/>
+      <c r="V44" s="53"/>
+      <c r="W44" s="55"/>
+      <c r="X44" s="62"/>
+      <c r="Y44" s="62"/>
+      <c r="Z44" s="53"/>
+      <c r="AA44" s="54"/>
+      <c r="AB44" s="48"/>
+      <c r="AC44" s="62"/>
+      <c r="AD44" s="52"/>
+      <c r="AE44" s="50"/>
+      <c r="AF44" s="51"/>
+      <c r="AG44" s="48"/>
+      <c r="AH44" s="48"/>
+      <c r="AI44" s="62"/>
+      <c r="AJ44" s="48"/>
+      <c r="AK44" s="48"/>
     </row>
     <row r="45" ht="12" customHeight="1">
-      <c r="B45" s="47"/>
-      <c r="C45" s="77"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="57"/>
-      <c r="G45" s="54"/>
-      <c r="H45" s="55"/>
-      <c r="I45" s="49"/>
-      <c r="J45" s="49"/>
-      <c r="K45" s="49"/>
-      <c r="L45" s="53"/>
-      <c r="M45" s="49"/>
-      <c r="N45" s="54"/>
-      <c r="O45" s="55"/>
-      <c r="P45" s="49"/>
-      <c r="Q45" s="49"/>
-      <c r="R45" s="49"/>
-      <c r="S45" s="49"/>
-      <c r="T45" s="49"/>
-      <c r="U45" s="49"/>
-      <c r="V45" s="54"/>
-      <c r="W45" s="56"/>
-      <c r="X45" s="49"/>
-      <c r="Y45" s="49"/>
-      <c r="Z45" s="54"/>
-      <c r="AA45" s="55"/>
-      <c r="AB45" s="49"/>
-      <c r="AC45" s="49"/>
-      <c r="AD45" s="53"/>
-      <c r="AE45" s="54"/>
-      <c r="AF45" s="55"/>
-      <c r="AG45" s="49"/>
-      <c r="AH45" s="49"/>
-      <c r="AI45" s="49"/>
-      <c r="AJ45" s="49"/>
-      <c r="AK45" s="49"/>
+      <c r="B45" s="46"/>
+      <c r="C45" s="76"/>
+      <c r="D45" s="48"/>
+      <c r="E45" s="48"/>
+      <c r="F45" s="56"/>
+      <c r="G45" s="53"/>
+      <c r="H45" s="54"/>
+      <c r="I45" s="48"/>
+      <c r="J45" s="48"/>
+      <c r="K45" s="48"/>
+      <c r="L45" s="52"/>
+      <c r="M45" s="48"/>
+      <c r="N45" s="53"/>
+      <c r="O45" s="54"/>
+      <c r="P45" s="48"/>
+      <c r="Q45" s="48"/>
+      <c r="R45" s="48"/>
+      <c r="S45" s="48"/>
+      <c r="T45" s="48"/>
+      <c r="U45" s="48"/>
+      <c r="V45" s="53"/>
+      <c r="W45" s="55"/>
+      <c r="X45" s="48"/>
+      <c r="Y45" s="48"/>
+      <c r="Z45" s="53"/>
+      <c r="AA45" s="54"/>
+      <c r="AB45" s="48"/>
+      <c r="AC45" s="48"/>
+      <c r="AD45" s="52"/>
+      <c r="AE45" s="53"/>
+      <c r="AF45" s="54"/>
+      <c r="AG45" s="48"/>
+      <c r="AH45" s="48"/>
+      <c r="AI45" s="48"/>
+      <c r="AJ45" s="48"/>
+      <c r="AK45" s="48"/>
     </row>
     <row r="46" ht="12" customHeight="1">
-      <c r="B46" s="65" t="s">
-        <v>128</v>
-      </c>
-      <c r="C46" s="66" t="s">
+      <c r="B46" s="64" t="s">
+        <v>129</v>
+      </c>
+      <c r="C46" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="D46" s="68"/>
-      <c r="E46" s="68"/>
-      <c r="F46" s="71"/>
-      <c r="G46" s="69"/>
-      <c r="H46" s="67"/>
-      <c r="I46" s="68"/>
-      <c r="J46" s="68"/>
-      <c r="K46" s="68"/>
-      <c r="L46" s="53"/>
-      <c r="M46" s="68"/>
-      <c r="N46" s="69"/>
-      <c r="O46" s="67"/>
-      <c r="P46" s="68"/>
-      <c r="Q46" s="68"/>
-      <c r="R46" s="68"/>
-      <c r="S46" s="68"/>
-      <c r="T46" s="68"/>
-      <c r="U46" s="68"/>
-      <c r="V46" s="69"/>
-      <c r="W46" s="56"/>
-      <c r="X46" s="68"/>
-      <c r="Y46" s="68"/>
-      <c r="Z46" s="69"/>
-      <c r="AA46" s="67"/>
-      <c r="AB46" s="68"/>
-      <c r="AC46" s="68"/>
-      <c r="AD46" s="53"/>
-      <c r="AE46" s="69"/>
-      <c r="AF46" s="67"/>
-      <c r="AG46" s="68"/>
-      <c r="AH46" s="68"/>
-      <c r="AI46" s="68"/>
-      <c r="AJ46" s="63"/>
-      <c r="AK46" s="68"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="68"/>
+      <c r="H46" s="66"/>
+      <c r="I46" s="67"/>
+      <c r="J46" s="67"/>
+      <c r="K46" s="67"/>
+      <c r="L46" s="52"/>
+      <c r="M46" s="67"/>
+      <c r="N46" s="68"/>
+      <c r="O46" s="66"/>
+      <c r="P46" s="67"/>
+      <c r="Q46" s="67"/>
+      <c r="R46" s="67"/>
+      <c r="S46" s="67"/>
+      <c r="T46" s="67"/>
+      <c r="U46" s="67"/>
+      <c r="V46" s="68"/>
+      <c r="W46" s="55"/>
+      <c r="X46" s="67"/>
+      <c r="Y46" s="67"/>
+      <c r="Z46" s="68"/>
+      <c r="AA46" s="66"/>
+      <c r="AB46" s="67"/>
+      <c r="AC46" s="67"/>
+      <c r="AD46" s="52"/>
+      <c r="AE46" s="68"/>
+      <c r="AF46" s="66"/>
+      <c r="AG46" s="67"/>
+      <c r="AH46" s="67"/>
+      <c r="AI46" s="67"/>
+      <c r="AJ46" s="62"/>
+      <c r="AK46" s="67"/>
     </row>
     <row r="47" ht="12" customHeight="1">
-      <c r="B47" s="65"/>
-      <c r="C47" s="66"/>
-      <c r="D47" s="68"/>
-      <c r="E47" s="68"/>
-      <c r="F47" s="71"/>
-      <c r="G47" s="69"/>
-      <c r="H47" s="67"/>
-      <c r="I47" s="68"/>
-      <c r="J47" s="68"/>
-      <c r="K47" s="68"/>
-      <c r="L47" s="53"/>
-      <c r="M47" s="68"/>
-      <c r="N47" s="69"/>
-      <c r="O47" s="67"/>
-      <c r="P47" s="68"/>
-      <c r="Q47" s="68"/>
-      <c r="R47" s="68"/>
-      <c r="S47" s="68"/>
-      <c r="T47" s="68"/>
-      <c r="U47" s="68"/>
-      <c r="V47" s="69"/>
-      <c r="W47" s="56"/>
-      <c r="X47" s="68"/>
-      <c r="Y47" s="68"/>
-      <c r="Z47" s="69"/>
-      <c r="AA47" s="67"/>
-      <c r="AB47" s="68"/>
-      <c r="AC47" s="68"/>
-      <c r="AD47" s="53"/>
-      <c r="AE47" s="69"/>
-      <c r="AF47" s="67"/>
-      <c r="AG47" s="68"/>
-      <c r="AH47" s="68"/>
-      <c r="AI47" s="68"/>
-      <c r="AJ47" s="68"/>
-      <c r="AK47" s="68"/>
-      <c r="AN47" s="78" t="s">
-        <v>129</v>
-      </c>
-      <c r="AO47" s="63"/>
+      <c r="B47" s="64"/>
+      <c r="C47" s="65"/>
+      <c r="D47" s="67"/>
+      <c r="E47" s="67"/>
+      <c r="F47" s="70"/>
+      <c r="G47" s="68"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="67"/>
+      <c r="J47" s="67"/>
+      <c r="K47" s="67"/>
+      <c r="L47" s="52"/>
+      <c r="M47" s="67"/>
+      <c r="N47" s="68"/>
+      <c r="O47" s="66"/>
+      <c r="P47" s="67"/>
+      <c r="Q47" s="67"/>
+      <c r="R47" s="67"/>
+      <c r="S47" s="67"/>
+      <c r="T47" s="67"/>
+      <c r="U47" s="67"/>
+      <c r="V47" s="68"/>
+      <c r="W47" s="55"/>
+      <c r="X47" s="67"/>
+      <c r="Y47" s="67"/>
+      <c r="Z47" s="68"/>
+      <c r="AA47" s="66"/>
+      <c r="AB47" s="67"/>
+      <c r="AC47" s="67"/>
+      <c r="AD47" s="52"/>
+      <c r="AE47" s="68"/>
+      <c r="AF47" s="66"/>
+      <c r="AG47" s="67"/>
+      <c r="AH47" s="67"/>
+      <c r="AI47" s="67"/>
+      <c r="AJ47" s="67"/>
+      <c r="AK47" s="67"/>
+      <c r="AN47" s="77" t="s">
+        <v>130</v>
+      </c>
+      <c r="AO47" s="62"/>
     </row>
     <row r="48" ht="12" customHeight="1">
-      <c r="B48" s="65"/>
-      <c r="C48" s="66" t="s">
-        <v>130</v>
-      </c>
-      <c r="D48" s="68"/>
-      <c r="E48" s="68"/>
-      <c r="F48" s="71"/>
-      <c r="G48" s="69"/>
-      <c r="H48" s="67"/>
-      <c r="I48" s="68"/>
-      <c r="J48" s="68"/>
-      <c r="K48" s="68"/>
-      <c r="L48" s="53"/>
-      <c r="M48" s="68"/>
-      <c r="N48" s="69"/>
-      <c r="O48" s="67"/>
-      <c r="P48" s="68"/>
-      <c r="Q48" s="68"/>
-      <c r="R48" s="68"/>
-      <c r="S48" s="68"/>
-      <c r="T48" s="68"/>
-      <c r="U48" s="68"/>
-      <c r="V48" s="69"/>
-      <c r="W48" s="56"/>
-      <c r="X48" s="68"/>
-      <c r="Y48" s="68"/>
-      <c r="Z48" s="69"/>
-      <c r="AA48" s="67"/>
-      <c r="AB48" s="68"/>
-      <c r="AC48" s="68"/>
-      <c r="AD48" s="53"/>
-      <c r="AE48" s="69"/>
-      <c r="AF48" s="67"/>
-      <c r="AG48" s="68"/>
-      <c r="AH48" s="68"/>
-      <c r="AI48" s="68"/>
-      <c r="AJ48" s="68"/>
-      <c r="AK48" s="79"/>
-      <c r="AN48" s="78" t="s">
+      <c r="B48" s="64"/>
+      <c r="C48" s="65" t="s">
         <v>131</v>
       </c>
-      <c r="AO48" s="62"/>
+      <c r="D48" s="67"/>
+      <c r="E48" s="67"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="68"/>
+      <c r="H48" s="66"/>
+      <c r="I48" s="67"/>
+      <c r="J48" s="67"/>
+      <c r="K48" s="67"/>
+      <c r="L48" s="52"/>
+      <c r="M48" s="67"/>
+      <c r="N48" s="68"/>
+      <c r="O48" s="66"/>
+      <c r="P48" s="67"/>
+      <c r="Q48" s="67"/>
+      <c r="R48" s="67"/>
+      <c r="S48" s="67"/>
+      <c r="T48" s="67"/>
+      <c r="U48" s="67"/>
+      <c r="V48" s="68"/>
+      <c r="W48" s="55"/>
+      <c r="X48" s="67"/>
+      <c r="Y48" s="67"/>
+      <c r="Z48" s="68"/>
+      <c r="AA48" s="66"/>
+      <c r="AB48" s="67"/>
+      <c r="AC48" s="67"/>
+      <c r="AD48" s="52"/>
+      <c r="AE48" s="68"/>
+      <c r="AF48" s="66"/>
+      <c r="AG48" s="67"/>
+      <c r="AH48" s="67"/>
+      <c r="AI48" s="67"/>
+      <c r="AJ48" s="67"/>
+      <c r="AK48" s="78"/>
+      <c r="AN48" s="77" t="s">
+        <v>132</v>
+      </c>
+      <c r="AO48" s="61"/>
     </row>
     <row r="49" ht="12" customHeight="1">
-      <c r="B49" s="65"/>
-      <c r="C49" s="66"/>
-      <c r="D49" s="68"/>
-      <c r="E49" s="68"/>
-      <c r="F49" s="71"/>
-      <c r="G49" s="69"/>
-      <c r="H49" s="67"/>
-      <c r="I49" s="68"/>
-      <c r="J49" s="68"/>
-      <c r="K49" s="68"/>
-      <c r="L49" s="53"/>
-      <c r="M49" s="68"/>
-      <c r="N49" s="69"/>
-      <c r="O49" s="67"/>
-      <c r="P49" s="68"/>
-      <c r="Q49" s="68"/>
-      <c r="R49" s="68"/>
-      <c r="S49" s="68"/>
-      <c r="T49" s="68"/>
-      <c r="U49" s="68"/>
-      <c r="V49" s="69"/>
-      <c r="W49" s="56"/>
-      <c r="X49" s="68"/>
-      <c r="Y49" s="68"/>
-      <c r="Z49" s="69"/>
-      <c r="AA49" s="67"/>
-      <c r="AB49" s="68"/>
-      <c r="AC49" s="68"/>
-      <c r="AD49" s="53"/>
-      <c r="AE49" s="69"/>
-      <c r="AF49" s="67"/>
-      <c r="AG49" s="68"/>
-      <c r="AH49" s="68"/>
-      <c r="AI49" s="68"/>
-      <c r="AJ49" s="68"/>
-      <c r="AK49" s="68"/>
-      <c r="AN49" s="78" t="s">
-        <v>132</v>
-      </c>
-      <c r="AO49" s="58"/>
+      <c r="B49" s="64"/>
+      <c r="C49" s="65"/>
+      <c r="D49" s="67"/>
+      <c r="E49" s="67"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="68"/>
+      <c r="H49" s="66"/>
+      <c r="I49" s="67"/>
+      <c r="J49" s="67"/>
+      <c r="K49" s="67"/>
+      <c r="L49" s="52"/>
+      <c r="M49" s="67"/>
+      <c r="N49" s="68"/>
+      <c r="O49" s="66"/>
+      <c r="P49" s="67"/>
+      <c r="Q49" s="67"/>
+      <c r="R49" s="67"/>
+      <c r="S49" s="67"/>
+      <c r="T49" s="67"/>
+      <c r="U49" s="67"/>
+      <c r="V49" s="68"/>
+      <c r="W49" s="55"/>
+      <c r="X49" s="67"/>
+      <c r="Y49" s="67"/>
+      <c r="Z49" s="68"/>
+      <c r="AA49" s="66"/>
+      <c r="AB49" s="67"/>
+      <c r="AC49" s="67"/>
+      <c r="AD49" s="52"/>
+      <c r="AE49" s="68"/>
+      <c r="AF49" s="66"/>
+      <c r="AG49" s="67"/>
+      <c r="AH49" s="67"/>
+      <c r="AI49" s="67"/>
+      <c r="AJ49" s="67"/>
+      <c r="AK49" s="67"/>
+      <c r="AN49" s="77" t="s">
+        <v>133</v>
+      </c>
+      <c r="AO49" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -9000,801 +9011,801 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="80"/>
+      <c r="B1" s="79"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="81" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" s="82" t="s">
+      <c r="B2" s="80" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="83" t="s">
-        <v>133</v>
-      </c>
-      <c r="E2" s="84" t="s">
+      <c r="C2" s="81" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="82" t="s">
         <v>134</v>
       </c>
-      <c r="F2" s="85" t="s">
+      <c r="E2" s="83" t="s">
         <v>135</v>
       </c>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="85" t="s">
+      <c r="F2" s="84" t="s">
         <v>136</v>
       </c>
-      <c r="K2" s="85"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="85" t="s">
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="84" t="s">
         <v>137</v>
       </c>
-      <c r="O2" s="85"/>
-      <c r="P2" s="85"/>
-      <c r="Q2" s="84"/>
-      <c r="R2" s="85" t="s">
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="83"/>
+      <c r="N2" s="84" t="s">
         <v>138</v>
       </c>
-      <c r="S2" s="86"/>
-      <c r="AD2" s="29"/>
+      <c r="O2" s="84"/>
+      <c r="P2" s="84"/>
+      <c r="Q2" s="83"/>
+      <c r="R2" s="84" t="s">
+        <v>139</v>
+      </c>
+      <c r="S2" s="85"/>
+      <c r="AD2" s="28"/>
     </row>
     <row r="3">
-      <c r="B3" s="87"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="89" t="s">
-        <v>139</v>
-      </c>
-      <c r="E3" s="90">
+      <c r="B3" s="86"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="88" t="s">
+        <v>140</v>
+      </c>
+      <c r="E3" s="89">
         <v>4</v>
       </c>
-      <c r="F3" s="91">
+      <c r="F3" s="90">
         <v>1</v>
       </c>
-      <c r="G3" s="92">
+      <c r="G3" s="91">
         <v>2</v>
       </c>
-      <c r="H3" s="92">
+      <c r="H3" s="91">
         <v>3</v>
       </c>
-      <c r="I3" s="90">
+      <c r="I3" s="89">
         <v>4</v>
       </c>
-      <c r="J3" s="91">
+      <c r="J3" s="90">
         <v>1</v>
       </c>
-      <c r="K3" s="92">
+      <c r="K3" s="91">
         <v>2</v>
       </c>
-      <c r="L3" s="92">
+      <c r="L3" s="91">
         <v>3</v>
       </c>
-      <c r="M3" s="90">
+      <c r="M3" s="89">
         <v>4</v>
       </c>
-      <c r="N3" s="91">
+      <c r="N3" s="90">
         <v>1</v>
       </c>
-      <c r="O3" s="92">
+      <c r="O3" s="91">
         <v>2</v>
       </c>
-      <c r="P3" s="92">
+      <c r="P3" s="91">
         <v>3</v>
       </c>
-      <c r="Q3" s="90">
+      <c r="Q3" s="89">
         <v>4</v>
       </c>
-      <c r="R3" s="91">
+      <c r="R3" s="90">
         <v>1</v>
       </c>
-      <c r="S3" s="93">
+      <c r="S3" s="92">
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="94" t="s">
-        <v>141</v>
-      </c>
-      <c r="C4" s="82" t="s">
+      <c r="B4" s="93" t="s">
         <v>142</v>
       </c>
-      <c r="D4" s="95"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="99"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="96"/>
-      <c r="N4" s="99"/>
-      <c r="O4" s="98"/>
-      <c r="P4" s="98"/>
-      <c r="Q4" s="96"/>
-      <c r="R4" s="99"/>
-      <c r="S4" s="100"/>
+      <c r="C4" s="81" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" s="94"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="95"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="97"/>
+      <c r="L4" s="97"/>
+      <c r="M4" s="95"/>
+      <c r="N4" s="98"/>
+      <c r="O4" s="97"/>
+      <c r="P4" s="97"/>
+      <c r="Q4" s="95"/>
+      <c r="R4" s="98"/>
+      <c r="S4" s="99"/>
       <c r="U4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="94"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="104"/>
-      <c r="G5" s="105"/>
-      <c r="H5" s="106"/>
-      <c r="I5" s="103"/>
-      <c r="J5" s="107"/>
-      <c r="K5" s="106"/>
-      <c r="L5" s="106"/>
-      <c r="M5" s="103"/>
-      <c r="N5" s="107"/>
-      <c r="O5" s="106"/>
-      <c r="P5" s="106"/>
-      <c r="Q5" s="103"/>
-      <c r="R5" s="107"/>
-      <c r="S5" s="108"/>
+      <c r="B5" s="93"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="102"/>
+      <c r="J5" s="106"/>
+      <c r="K5" s="105"/>
+      <c r="L5" s="105"/>
+      <c r="M5" s="102"/>
+      <c r="N5" s="106"/>
+      <c r="O5" s="105"/>
+      <c r="P5" s="105"/>
+      <c r="Q5" s="102"/>
+      <c r="R5" s="106"/>
+      <c r="S5" s="107"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="94"/>
-      <c r="C6" s="109" t="s">
-        <v>144</v>
-      </c>
-      <c r="D6" s="110"/>
-      <c r="E6" s="111"/>
-      <c r="F6" s="112"/>
-      <c r="G6" s="113"/>
-      <c r="H6" s="114"/>
-      <c r="I6" s="111"/>
-      <c r="J6" s="115"/>
-      <c r="K6" s="114"/>
-      <c r="L6" s="114"/>
-      <c r="M6" s="111"/>
-      <c r="N6" s="115"/>
-      <c r="O6" s="114"/>
-      <c r="P6" s="114"/>
-      <c r="Q6" s="111"/>
-      <c r="R6" s="115"/>
-      <c r="S6" s="116"/>
-      <c r="U6" s="117" t="s">
+      <c r="B6" s="93"/>
+      <c r="C6" s="108" t="s">
         <v>145</v>
       </c>
-      <c r="V6" s="117"/>
+      <c r="D6" s="109"/>
+      <c r="E6" s="110"/>
+      <c r="F6" s="111"/>
+      <c r="G6" s="112"/>
+      <c r="H6" s="113"/>
+      <c r="I6" s="110"/>
+      <c r="J6" s="114"/>
+      <c r="K6" s="113"/>
+      <c r="L6" s="113"/>
+      <c r="M6" s="110"/>
+      <c r="N6" s="114"/>
+      <c r="O6" s="113"/>
+      <c r="P6" s="113"/>
+      <c r="Q6" s="110"/>
+      <c r="R6" s="114"/>
+      <c r="S6" s="115"/>
+      <c r="U6" s="116" t="s">
+        <v>146</v>
+      </c>
+      <c r="V6" s="116"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="94"/>
-      <c r="C7" s="101"/>
-      <c r="D7" s="102"/>
-      <c r="E7" s="103"/>
-      <c r="F7" s="107"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="103"/>
-      <c r="J7" s="107"/>
-      <c r="K7" s="106"/>
-      <c r="L7" s="106"/>
-      <c r="M7" s="103"/>
-      <c r="N7" s="107"/>
-      <c r="O7" s="106"/>
-      <c r="P7" s="106"/>
-      <c r="Q7" s="103"/>
-      <c r="R7" s="107"/>
-      <c r="S7" s="108"/>
+      <c r="B7" s="93"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="101"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="102"/>
+      <c r="J7" s="106"/>
+      <c r="K7" s="105"/>
+      <c r="L7" s="105"/>
+      <c r="M7" s="102"/>
+      <c r="N7" s="106"/>
+      <c r="O7" s="105"/>
+      <c r="P7" s="105"/>
+      <c r="Q7" s="102"/>
+      <c r="R7" s="106"/>
+      <c r="S7" s="107"/>
       <c r="U7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="94"/>
-      <c r="C8" s="109" t="s">
-        <v>147</v>
-      </c>
-      <c r="D8" s="110"/>
-      <c r="E8" s="111"/>
-      <c r="F8" s="112"/>
-      <c r="G8" s="114"/>
-      <c r="H8" s="114"/>
-      <c r="I8" s="111"/>
-      <c r="J8" s="115"/>
-      <c r="K8" s="114"/>
-      <c r="L8" s="114"/>
-      <c r="M8" s="111"/>
-      <c r="N8" s="115"/>
-      <c r="O8" s="114"/>
-      <c r="P8" s="114"/>
-      <c r="Q8" s="111"/>
-      <c r="R8" s="115"/>
-      <c r="S8" s="116"/>
+      <c r="B8" s="93"/>
+      <c r="C8" s="108" t="s">
+        <v>148</v>
+      </c>
+      <c r="D8" s="109"/>
+      <c r="E8" s="110"/>
+      <c r="F8" s="111"/>
+      <c r="G8" s="113"/>
+      <c r="H8" s="113"/>
+      <c r="I8" s="110"/>
+      <c r="J8" s="114"/>
+      <c r="K8" s="113"/>
+      <c r="L8" s="113"/>
+      <c r="M8" s="110"/>
+      <c r="N8" s="114"/>
+      <c r="O8" s="113"/>
+      <c r="P8" s="113"/>
+      <c r="Q8" s="110"/>
+      <c r="R8" s="114"/>
+      <c r="S8" s="115"/>
       <c r="U8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="94"/>
-      <c r="C9" s="101"/>
-      <c r="D9" s="102"/>
-      <c r="E9" s="103"/>
-      <c r="F9" s="107"/>
-      <c r="G9" s="105"/>
-      <c r="H9" s="106"/>
-      <c r="I9" s="103"/>
-      <c r="J9" s="107"/>
-      <c r="K9" s="106"/>
-      <c r="L9" s="106"/>
-      <c r="M9" s="103"/>
-      <c r="N9" s="107"/>
-      <c r="O9" s="106"/>
-      <c r="P9" s="106"/>
-      <c r="Q9" s="103"/>
-      <c r="R9" s="107"/>
-      <c r="S9" s="108"/>
+      <c r="B9" s="93"/>
+      <c r="C9" s="100"/>
+      <c r="D9" s="101"/>
+      <c r="E9" s="102"/>
+      <c r="F9" s="106"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="102"/>
+      <c r="J9" s="106"/>
+      <c r="K9" s="105"/>
+      <c r="L9" s="105"/>
+      <c r="M9" s="102"/>
+      <c r="N9" s="106"/>
+      <c r="O9" s="105"/>
+      <c r="P9" s="105"/>
+      <c r="Q9" s="102"/>
+      <c r="R9" s="106"/>
+      <c r="S9" s="107"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="94"/>
-      <c r="C10" s="109" t="s">
-        <v>149</v>
-      </c>
-      <c r="D10" s="110"/>
-      <c r="E10" s="111"/>
-      <c r="F10" s="115"/>
-      <c r="G10" s="113"/>
-      <c r="H10" s="113"/>
-      <c r="I10" s="111"/>
-      <c r="J10" s="115"/>
-      <c r="K10" s="114"/>
-      <c r="L10" s="114"/>
-      <c r="M10" s="111"/>
-      <c r="N10" s="115"/>
-      <c r="O10" s="114"/>
-      <c r="P10" s="114"/>
-      <c r="Q10" s="111"/>
-      <c r="R10" s="115"/>
-      <c r="S10" s="116"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="108" t="s">
+        <v>150</v>
+      </c>
+      <c r="D10" s="109"/>
+      <c r="E10" s="110"/>
+      <c r="F10" s="114"/>
+      <c r="G10" s="112"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="110"/>
+      <c r="J10" s="114"/>
+      <c r="K10" s="113"/>
+      <c r="L10" s="113"/>
+      <c r="M10" s="110"/>
+      <c r="N10" s="114"/>
+      <c r="O10" s="113"/>
+      <c r="P10" s="113"/>
+      <c r="Q10" s="110"/>
+      <c r="R10" s="114"/>
+      <c r="S10" s="115"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="118"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="120"/>
-      <c r="E11" s="121"/>
-      <c r="F11" s="122"/>
-      <c r="G11" s="123"/>
-      <c r="H11" s="123"/>
-      <c r="I11" s="121"/>
-      <c r="J11" s="122"/>
-      <c r="K11" s="124"/>
-      <c r="L11" s="124"/>
-      <c r="M11" s="121"/>
-      <c r="N11" s="122"/>
-      <c r="O11" s="124"/>
-      <c r="P11" s="124"/>
-      <c r="Q11" s="121"/>
-      <c r="R11" s="122"/>
-      <c r="S11" s="125"/>
+      <c r="B11" s="117"/>
+      <c r="C11" s="118"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="120"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="122"/>
+      <c r="H11" s="122"/>
+      <c r="I11" s="120"/>
+      <c r="J11" s="121"/>
+      <c r="K11" s="123"/>
+      <c r="L11" s="123"/>
+      <c r="M11" s="120"/>
+      <c r="N11" s="121"/>
+      <c r="O11" s="123"/>
+      <c r="P11" s="123"/>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="121"/>
+      <c r="S11" s="124"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="81" t="s">
-        <v>150</v>
-      </c>
-      <c r="C12" s="82" t="s">
+      <c r="B12" s="80" t="s">
         <v>151</v>
       </c>
-      <c r="D12" s="95"/>
-      <c r="E12" s="96"/>
-      <c r="F12" s="99"/>
-      <c r="G12" s="98"/>
-      <c r="H12" s="126"/>
-      <c r="I12" s="127"/>
-      <c r="J12" s="99"/>
-      <c r="K12" s="98"/>
-      <c r="L12" s="98"/>
-      <c r="M12" s="96"/>
-      <c r="N12" s="99"/>
-      <c r="O12" s="98"/>
-      <c r="P12" s="98"/>
-      <c r="Q12" s="96"/>
-      <c r="R12" s="99"/>
-      <c r="S12" s="100"/>
+      <c r="C12" s="81" t="s">
+        <v>152</v>
+      </c>
+      <c r="D12" s="94"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="98"/>
+      <c r="G12" s="97"/>
+      <c r="H12" s="125"/>
+      <c r="I12" s="126"/>
+      <c r="J12" s="98"/>
+      <c r="K12" s="97"/>
+      <c r="L12" s="97"/>
+      <c r="M12" s="95"/>
+      <c r="N12" s="98"/>
+      <c r="O12" s="97"/>
+      <c r="P12" s="97"/>
+      <c r="Q12" s="95"/>
+      <c r="R12" s="98"/>
+      <c r="S12" s="99"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="94"/>
-      <c r="C13" s="101"/>
-      <c r="D13" s="102"/>
-      <c r="E13" s="103"/>
-      <c r="F13" s="107"/>
-      <c r="G13" s="106"/>
-      <c r="H13" s="106"/>
-      <c r="I13" s="103"/>
-      <c r="J13" s="104"/>
-      <c r="K13" s="106"/>
-      <c r="L13" s="106"/>
-      <c r="M13" s="103"/>
-      <c r="N13" s="107"/>
-      <c r="O13" s="106"/>
-      <c r="P13" s="106"/>
-      <c r="Q13" s="103"/>
-      <c r="R13" s="107"/>
-      <c r="S13" s="108"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="100"/>
+      <c r="D13" s="101"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="106"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="102"/>
+      <c r="J13" s="103"/>
+      <c r="K13" s="105"/>
+      <c r="L13" s="105"/>
+      <c r="M13" s="102"/>
+      <c r="N13" s="106"/>
+      <c r="O13" s="105"/>
+      <c r="P13" s="105"/>
+      <c r="Q13" s="102"/>
+      <c r="R13" s="106"/>
+      <c r="S13" s="107"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="94"/>
-      <c r="C14" s="109" t="s">
-        <v>152</v>
-      </c>
-      <c r="D14" s="128"/>
-      <c r="E14" s="111"/>
-      <c r="F14" s="115"/>
-      <c r="G14" s="114"/>
-      <c r="H14" s="113"/>
-      <c r="I14" s="111"/>
-      <c r="J14" s="115"/>
-      <c r="K14" s="114"/>
-      <c r="L14" s="114"/>
-      <c r="M14" s="111"/>
-      <c r="N14" s="115"/>
-      <c r="O14" s="114"/>
-      <c r="P14" s="114"/>
-      <c r="Q14" s="111"/>
-      <c r="R14" s="115"/>
-      <c r="S14" s="116"/>
+      <c r="B14" s="93"/>
+      <c r="C14" s="108" t="s">
+        <v>153</v>
+      </c>
+      <c r="D14" s="127"/>
+      <c r="E14" s="110"/>
+      <c r="F14" s="114"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="112"/>
+      <c r="I14" s="110"/>
+      <c r="J14" s="114"/>
+      <c r="K14" s="113"/>
+      <c r="L14" s="113"/>
+      <c r="M14" s="110"/>
+      <c r="N14" s="114"/>
+      <c r="O14" s="113"/>
+      <c r="P14" s="113"/>
+      <c r="Q14" s="110"/>
+      <c r="R14" s="114"/>
+      <c r="S14" s="115"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="94"/>
-      <c r="C15" s="101"/>
-      <c r="D15" s="102"/>
-      <c r="E15" s="103"/>
-      <c r="F15" s="107"/>
-      <c r="G15" s="106"/>
-      <c r="H15" s="106"/>
-      <c r="I15" s="129"/>
-      <c r="J15" s="104"/>
-      <c r="K15" s="106"/>
-      <c r="L15" s="106"/>
-      <c r="M15" s="103"/>
-      <c r="N15" s="107"/>
-      <c r="O15" s="106"/>
-      <c r="P15" s="106"/>
-      <c r="Q15" s="103"/>
-      <c r="R15" s="107"/>
-      <c r="S15" s="108"/>
+      <c r="B15" s="93"/>
+      <c r="C15" s="100"/>
+      <c r="D15" s="101"/>
+      <c r="E15" s="102"/>
+      <c r="F15" s="106"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="105"/>
+      <c r="I15" s="128"/>
+      <c r="J15" s="103"/>
+      <c r="K15" s="105"/>
+      <c r="L15" s="105"/>
+      <c r="M15" s="102"/>
+      <c r="N15" s="106"/>
+      <c r="O15" s="105"/>
+      <c r="P15" s="105"/>
+      <c r="Q15" s="102"/>
+      <c r="R15" s="106"/>
+      <c r="S15" s="107"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="94"/>
-      <c r="C16" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="D16" s="110"/>
-      <c r="E16" s="111"/>
-      <c r="F16" s="115"/>
-      <c r="G16" s="114"/>
-      <c r="H16" s="113"/>
-      <c r="I16" s="130"/>
-      <c r="J16" s="115"/>
-      <c r="K16" s="114"/>
-      <c r="L16" s="114"/>
-      <c r="M16" s="111"/>
-      <c r="N16" s="115"/>
-      <c r="O16" s="114"/>
-      <c r="P16" s="114"/>
-      <c r="Q16" s="111"/>
-      <c r="R16" s="115"/>
-      <c r="S16" s="116"/>
+      <c r="B16" s="93"/>
+      <c r="C16" s="108" t="s">
+        <v>154</v>
+      </c>
+      <c r="D16" s="109"/>
+      <c r="E16" s="110"/>
+      <c r="F16" s="114"/>
+      <c r="G16" s="113"/>
+      <c r="H16" s="112"/>
+      <c r="I16" s="129"/>
+      <c r="J16" s="114"/>
+      <c r="K16" s="113"/>
+      <c r="L16" s="113"/>
+      <c r="M16" s="110"/>
+      <c r="N16" s="114"/>
+      <c r="O16" s="113"/>
+      <c r="P16" s="113"/>
+      <c r="Q16" s="110"/>
+      <c r="R16" s="114"/>
+      <c r="S16" s="115"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="118"/>
-      <c r="C17" s="119"/>
-      <c r="D17" s="120"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="124"/>
-      <c r="H17" s="124"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="131"/>
-      <c r="K17" s="123"/>
-      <c r="L17" s="124"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="122"/>
-      <c r="O17" s="124"/>
-      <c r="P17" s="124"/>
-      <c r="Q17" s="121"/>
-      <c r="R17" s="122"/>
-      <c r="S17" s="125"/>
+      <c r="B17" s="117"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="120"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="123"/>
+      <c r="H17" s="123"/>
+      <c r="I17" s="120"/>
+      <c r="J17" s="130"/>
+      <c r="K17" s="122"/>
+      <c r="L17" s="123"/>
+      <c r="M17" s="120"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="123"/>
+      <c r="P17" s="123"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="121"/>
+      <c r="S17" s="124"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="83" t="s">
-        <v>154</v>
-      </c>
-      <c r="C18" s="82" t="s">
+      <c r="B18" s="82" t="s">
         <v>155</v>
       </c>
-      <c r="D18" s="95"/>
-      <c r="E18" s="96"/>
-      <c r="F18" s="99"/>
-      <c r="G18" s="98"/>
-      <c r="H18" s="98"/>
-      <c r="I18" s="127"/>
-      <c r="J18" s="99"/>
-      <c r="K18" s="98"/>
-      <c r="L18" s="98"/>
-      <c r="M18" s="96"/>
-      <c r="N18" s="99"/>
-      <c r="O18" s="98"/>
-      <c r="P18" s="98"/>
-      <c r="Q18" s="96"/>
-      <c r="R18" s="99"/>
-      <c r="S18" s="100"/>
+      <c r="C18" s="81" t="s">
+        <v>156</v>
+      </c>
+      <c r="D18" s="94"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="98"/>
+      <c r="G18" s="97"/>
+      <c r="H18" s="97"/>
+      <c r="I18" s="126"/>
+      <c r="J18" s="98"/>
+      <c r="K18" s="97"/>
+      <c r="L18" s="97"/>
+      <c r="M18" s="95"/>
+      <c r="N18" s="98"/>
+      <c r="O18" s="97"/>
+      <c r="P18" s="97"/>
+      <c r="Q18" s="95"/>
+      <c r="R18" s="98"/>
+      <c r="S18" s="99"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="94"/>
-      <c r="C19" s="101"/>
-      <c r="D19" s="102"/>
-      <c r="E19" s="103"/>
-      <c r="F19" s="107"/>
-      <c r="G19" s="105"/>
-      <c r="H19" s="106"/>
-      <c r="I19" s="103"/>
-      <c r="J19" s="107"/>
-      <c r="K19" s="106"/>
-      <c r="L19" s="106"/>
-      <c r="M19" s="103"/>
-      <c r="N19" s="107"/>
-      <c r="O19" s="106"/>
-      <c r="P19" s="106"/>
-      <c r="Q19" s="103"/>
-      <c r="R19" s="107"/>
-      <c r="S19" s="108"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="100"/>
+      <c r="D19" s="101"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="106"/>
+      <c r="G19" s="104"/>
+      <c r="H19" s="105"/>
+      <c r="I19" s="102"/>
+      <c r="J19" s="106"/>
+      <c r="K19" s="105"/>
+      <c r="L19" s="105"/>
+      <c r="M19" s="102"/>
+      <c r="N19" s="106"/>
+      <c r="O19" s="105"/>
+      <c r="P19" s="105"/>
+      <c r="Q19" s="102"/>
+      <c r="R19" s="106"/>
+      <c r="S19" s="107"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="94"/>
-      <c r="C20" s="109" t="s">
-        <v>156</v>
-      </c>
-      <c r="D20" s="110"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="115"/>
-      <c r="G20" s="114"/>
-      <c r="H20" s="114"/>
-      <c r="I20" s="130"/>
-      <c r="J20" s="112"/>
-      <c r="K20" s="113"/>
-      <c r="L20" s="113"/>
-      <c r="M20" s="111"/>
-      <c r="N20" s="115"/>
-      <c r="O20" s="114"/>
-      <c r="P20" s="114"/>
-      <c r="Q20" s="111"/>
-      <c r="R20" s="115"/>
-      <c r="S20" s="116"/>
+      <c r="B20" s="93"/>
+      <c r="C20" s="108" t="s">
+        <v>157</v>
+      </c>
+      <c r="D20" s="109"/>
+      <c r="E20" s="110"/>
+      <c r="F20" s="114"/>
+      <c r="G20" s="113"/>
+      <c r="H20" s="113"/>
+      <c r="I20" s="129"/>
+      <c r="J20" s="111"/>
+      <c r="K20" s="112"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="110"/>
+      <c r="N20" s="114"/>
+      <c r="O20" s="113"/>
+      <c r="P20" s="113"/>
+      <c r="Q20" s="110"/>
+      <c r="R20" s="114"/>
+      <c r="S20" s="115"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="94"/>
-      <c r="C21" s="101"/>
-      <c r="D21" s="102"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="107"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="106"/>
-      <c r="I21" s="103"/>
-      <c r="J21" s="107"/>
-      <c r="K21" s="106"/>
-      <c r="L21" s="106"/>
-      <c r="M21" s="103"/>
-      <c r="N21" s="132"/>
-      <c r="O21" s="106"/>
-      <c r="P21" s="106"/>
-      <c r="Q21" s="103"/>
-      <c r="R21" s="107"/>
-      <c r="S21" s="108"/>
+      <c r="B21" s="93"/>
+      <c r="C21" s="100"/>
+      <c r="D21" s="101"/>
+      <c r="E21" s="102"/>
+      <c r="F21" s="106"/>
+      <c r="G21" s="105"/>
+      <c r="H21" s="105"/>
+      <c r="I21" s="102"/>
+      <c r="J21" s="106"/>
+      <c r="K21" s="105"/>
+      <c r="L21" s="105"/>
+      <c r="M21" s="102"/>
+      <c r="N21" s="131"/>
+      <c r="O21" s="105"/>
+      <c r="P21" s="105"/>
+      <c r="Q21" s="102"/>
+      <c r="R21" s="106"/>
+      <c r="S21" s="107"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="94"/>
-      <c r="C22" s="109" t="s">
-        <v>157</v>
-      </c>
-      <c r="D22" s="110"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="115"/>
-      <c r="G22" s="114"/>
-      <c r="H22" s="114"/>
-      <c r="I22" s="111"/>
-      <c r="J22" s="115"/>
-      <c r="K22" s="113"/>
-      <c r="L22" s="113"/>
-      <c r="M22" s="111"/>
-      <c r="N22" s="115"/>
-      <c r="O22" s="114"/>
-      <c r="P22" s="114"/>
-      <c r="Q22" s="111"/>
-      <c r="R22" s="115"/>
-      <c r="S22" s="116"/>
+      <c r="B22" s="93"/>
+      <c r="C22" s="108" t="s">
+        <v>158</v>
+      </c>
+      <c r="D22" s="109"/>
+      <c r="E22" s="110"/>
+      <c r="F22" s="114"/>
+      <c r="G22" s="113"/>
+      <c r="H22" s="113"/>
+      <c r="I22" s="110"/>
+      <c r="J22" s="114"/>
+      <c r="K22" s="112"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="110"/>
+      <c r="N22" s="114"/>
+      <c r="O22" s="113"/>
+      <c r="P22" s="113"/>
+      <c r="Q22" s="110"/>
+      <c r="R22" s="114"/>
+      <c r="S22" s="115"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="118"/>
-      <c r="C23" s="119"/>
-      <c r="D23" s="120"/>
-      <c r="E23" s="121"/>
-      <c r="F23" s="122"/>
-      <c r="G23" s="124"/>
-      <c r="H23" s="124"/>
-      <c r="I23" s="121"/>
-      <c r="J23" s="122"/>
-      <c r="K23" s="124"/>
-      <c r="L23" s="124"/>
-      <c r="M23" s="121"/>
-      <c r="N23" s="122"/>
-      <c r="O23" s="124"/>
-      <c r="P23" s="124"/>
-      <c r="Q23" s="121"/>
-      <c r="R23" s="122"/>
-      <c r="S23" s="125"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="119"/>
+      <c r="E23" s="120"/>
+      <c r="F23" s="121"/>
+      <c r="G23" s="123"/>
+      <c r="H23" s="123"/>
+      <c r="I23" s="120"/>
+      <c r="J23" s="121"/>
+      <c r="K23" s="123"/>
+      <c r="L23" s="123"/>
+      <c r="M23" s="120"/>
+      <c r="N23" s="121"/>
+      <c r="O23" s="123"/>
+      <c r="P23" s="123"/>
+      <c r="Q23" s="120"/>
+      <c r="R23" s="121"/>
+      <c r="S23" s="124"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="83" t="s">
-        <v>158</v>
-      </c>
-      <c r="C24" s="82" t="s">
+      <c r="B24" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="D24" s="95"/>
-      <c r="E24" s="96"/>
-      <c r="F24" s="99"/>
-      <c r="G24" s="98"/>
-      <c r="H24" s="98"/>
-      <c r="I24" s="96"/>
-      <c r="J24" s="99"/>
-      <c r="K24" s="98"/>
-      <c r="L24" s="98"/>
-      <c r="M24" s="127"/>
-      <c r="N24" s="97"/>
-      <c r="O24" s="126"/>
-      <c r="P24" s="126"/>
-      <c r="Q24" s="96"/>
-      <c r="R24" s="99"/>
-      <c r="S24" s="100"/>
+      <c r="C24" s="81" t="s">
+        <v>160</v>
+      </c>
+      <c r="D24" s="94"/>
+      <c r="E24" s="95"/>
+      <c r="F24" s="98"/>
+      <c r="G24" s="97"/>
+      <c r="H24" s="97"/>
+      <c r="I24" s="95"/>
+      <c r="J24" s="98"/>
+      <c r="K24" s="97"/>
+      <c r="L24" s="97"/>
+      <c r="M24" s="126"/>
+      <c r="N24" s="96"/>
+      <c r="O24" s="125"/>
+      <c r="P24" s="125"/>
+      <c r="Q24" s="95"/>
+      <c r="R24" s="98"/>
+      <c r="S24" s="99"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="94"/>
-      <c r="C25" s="101"/>
-      <c r="D25" s="102"/>
-      <c r="E25" s="103"/>
-      <c r="F25" s="107"/>
-      <c r="G25" s="106"/>
-      <c r="H25" s="106"/>
-      <c r="I25" s="103"/>
-      <c r="J25" s="107"/>
-      <c r="K25" s="106"/>
-      <c r="L25" s="106"/>
-      <c r="M25" s="103"/>
-      <c r="N25" s="107"/>
-      <c r="O25" s="106"/>
-      <c r="P25" s="106"/>
-      <c r="Q25" s="103"/>
-      <c r="R25" s="107"/>
-      <c r="S25" s="108"/>
+      <c r="B25" s="93"/>
+      <c r="C25" s="100"/>
+      <c r="D25" s="101"/>
+      <c r="E25" s="102"/>
+      <c r="F25" s="106"/>
+      <c r="G25" s="105"/>
+      <c r="H25" s="105"/>
+      <c r="I25" s="102"/>
+      <c r="J25" s="106"/>
+      <c r="K25" s="105"/>
+      <c r="L25" s="105"/>
+      <c r="M25" s="102"/>
+      <c r="N25" s="106"/>
+      <c r="O25" s="105"/>
+      <c r="P25" s="105"/>
+      <c r="Q25" s="102"/>
+      <c r="R25" s="106"/>
+      <c r="S25" s="107"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="94"/>
-      <c r="C26" s="109" t="s">
-        <v>160</v>
-      </c>
-      <c r="D26" s="110"/>
-      <c r="E26" s="111"/>
-      <c r="F26" s="115"/>
-      <c r="G26" s="114"/>
-      <c r="H26" s="114"/>
-      <c r="I26" s="111"/>
-      <c r="J26" s="115"/>
-      <c r="K26" s="114"/>
-      <c r="L26" s="114"/>
-      <c r="M26" s="111"/>
-      <c r="N26" s="115"/>
-      <c r="O26" s="113"/>
-      <c r="P26" s="113"/>
-      <c r="Q26" s="111"/>
-      <c r="R26" s="115"/>
-      <c r="S26" s="116"/>
+      <c r="B26" s="93"/>
+      <c r="C26" s="108" t="s">
+        <v>161</v>
+      </c>
+      <c r="D26" s="109"/>
+      <c r="E26" s="110"/>
+      <c r="F26" s="114"/>
+      <c r="G26" s="113"/>
+      <c r="H26" s="113"/>
+      <c r="I26" s="110"/>
+      <c r="J26" s="114"/>
+      <c r="K26" s="113"/>
+      <c r="L26" s="113"/>
+      <c r="M26" s="110"/>
+      <c r="N26" s="114"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="110"/>
+      <c r="R26" s="114"/>
+      <c r="S26" s="115"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="94"/>
-      <c r="C27" s="101"/>
-      <c r="D27" s="102"/>
-      <c r="E27" s="103"/>
-      <c r="F27" s="107"/>
-      <c r="G27" s="106"/>
-      <c r="H27" s="106"/>
-      <c r="I27" s="103"/>
-      <c r="J27" s="107"/>
-      <c r="K27" s="106"/>
-      <c r="L27" s="106"/>
-      <c r="M27" s="103"/>
-      <c r="N27" s="107"/>
-      <c r="O27" s="106"/>
-      <c r="P27" s="106"/>
-      <c r="Q27" s="103"/>
-      <c r="R27" s="107"/>
-      <c r="S27" s="108"/>
+      <c r="B27" s="93"/>
+      <c r="C27" s="100"/>
+      <c r="D27" s="101"/>
+      <c r="E27" s="102"/>
+      <c r="F27" s="106"/>
+      <c r="G27" s="105"/>
+      <c r="H27" s="105"/>
+      <c r="I27" s="102"/>
+      <c r="J27" s="106"/>
+      <c r="K27" s="105"/>
+      <c r="L27" s="105"/>
+      <c r="M27" s="102"/>
+      <c r="N27" s="106"/>
+      <c r="O27" s="105"/>
+      <c r="P27" s="105"/>
+      <c r="Q27" s="102"/>
+      <c r="R27" s="106"/>
+      <c r="S27" s="107"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="94"/>
-      <c r="C28" s="109" t="s">
-        <v>161</v>
-      </c>
-      <c r="D28" s="110"/>
-      <c r="E28" s="111"/>
-      <c r="F28" s="115"/>
-      <c r="G28" s="114"/>
-      <c r="H28" s="114"/>
-      <c r="I28" s="111"/>
-      <c r="J28" s="115"/>
-      <c r="K28" s="114"/>
-      <c r="L28" s="114"/>
-      <c r="M28" s="111"/>
-      <c r="N28" s="115"/>
-      <c r="O28" s="114"/>
-      <c r="P28" s="113"/>
-      <c r="Q28" s="130"/>
-      <c r="R28" s="115"/>
-      <c r="S28" s="116"/>
+      <c r="B28" s="93"/>
+      <c r="C28" s="108" t="s">
+        <v>162</v>
+      </c>
+      <c r="D28" s="109"/>
+      <c r="E28" s="110"/>
+      <c r="F28" s="114"/>
+      <c r="G28" s="113"/>
+      <c r="H28" s="113"/>
+      <c r="I28" s="110"/>
+      <c r="J28" s="114"/>
+      <c r="K28" s="113"/>
+      <c r="L28" s="113"/>
+      <c r="M28" s="110"/>
+      <c r="N28" s="114"/>
+      <c r="O28" s="113"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="129"/>
+      <c r="R28" s="114"/>
+      <c r="S28" s="115"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="94"/>
-      <c r="C29" s="88"/>
-      <c r="D29" s="133"/>
-      <c r="E29" s="134"/>
-      <c r="F29" s="135"/>
-      <c r="G29" s="136"/>
-      <c r="H29" s="137"/>
-      <c r="I29" s="134"/>
-      <c r="J29" s="135"/>
-      <c r="K29" s="136"/>
-      <c r="L29" s="137"/>
-      <c r="M29" s="134"/>
-      <c r="N29" s="138"/>
-      <c r="O29" s="137"/>
-      <c r="P29" s="136"/>
-      <c r="Q29" s="134"/>
-      <c r="R29" s="135"/>
-      <c r="S29" s="139"/>
+      <c r="B29" s="93"/>
+      <c r="C29" s="87"/>
+      <c r="D29" s="132"/>
+      <c r="E29" s="133"/>
+      <c r="F29" s="134"/>
+      <c r="G29" s="135"/>
+      <c r="H29" s="136"/>
+      <c r="I29" s="133"/>
+      <c r="J29" s="134"/>
+      <c r="K29" s="135"/>
+      <c r="L29" s="136"/>
+      <c r="M29" s="133"/>
+      <c r="N29" s="137"/>
+      <c r="O29" s="136"/>
+      <c r="P29" s="135"/>
+      <c r="Q29" s="133"/>
+      <c r="R29" s="134"/>
+      <c r="S29" s="138"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="140" t="s">
+      <c r="B30" s="139" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="141" t="s">
-        <v>105</v>
-      </c>
-      <c r="D30" s="95"/>
-      <c r="E30" s="142"/>
-      <c r="F30" s="143"/>
-      <c r="G30" s="143"/>
-      <c r="H30" s="144"/>
-      <c r="I30" s="145"/>
-      <c r="J30" s="143"/>
-      <c r="K30" s="143"/>
-      <c r="L30" s="144"/>
-      <c r="M30" s="145"/>
-      <c r="N30" s="143"/>
-      <c r="O30" s="144"/>
-      <c r="P30" s="143"/>
-      <c r="Q30" s="145"/>
-      <c r="R30" s="143"/>
-      <c r="S30" s="146"/>
+      <c r="C30" s="140" t="s">
+        <v>106</v>
+      </c>
+      <c r="D30" s="94"/>
+      <c r="E30" s="141"/>
+      <c r="F30" s="142"/>
+      <c r="G30" s="142"/>
+      <c r="H30" s="143"/>
+      <c r="I30" s="144"/>
+      <c r="J30" s="142"/>
+      <c r="K30" s="142"/>
+      <c r="L30" s="143"/>
+      <c r="M30" s="144"/>
+      <c r="N30" s="142"/>
+      <c r="O30" s="143"/>
+      <c r="P30" s="142"/>
+      <c r="Q30" s="144"/>
+      <c r="R30" s="142"/>
+      <c r="S30" s="145"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="147"/>
-      <c r="C31" s="148"/>
-      <c r="D31" s="102"/>
-      <c r="E31" s="149"/>
-      <c r="F31" s="150"/>
-      <c r="G31" s="150"/>
-      <c r="H31" s="151"/>
-      <c r="I31" s="152"/>
-      <c r="J31" s="150"/>
-      <c r="K31" s="153"/>
-      <c r="L31" s="151"/>
-      <c r="M31" s="152"/>
-      <c r="N31" s="150"/>
-      <c r="O31" s="151"/>
-      <c r="P31" s="150"/>
-      <c r="Q31" s="152"/>
-      <c r="R31" s="150"/>
-      <c r="S31" s="108"/>
+      <c r="B31" s="146"/>
+      <c r="C31" s="147"/>
+      <c r="D31" s="101"/>
+      <c r="E31" s="148"/>
+      <c r="F31" s="149"/>
+      <c r="G31" s="149"/>
+      <c r="H31" s="150"/>
+      <c r="I31" s="151"/>
+      <c r="J31" s="149"/>
+      <c r="K31" s="152"/>
+      <c r="L31" s="150"/>
+      <c r="M31" s="151"/>
+      <c r="N31" s="149"/>
+      <c r="O31" s="150"/>
+      <c r="P31" s="149"/>
+      <c r="Q31" s="151"/>
+      <c r="R31" s="149"/>
+      <c r="S31" s="107"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="147"/>
-      <c r="C32" s="148" t="s">
+      <c r="B32" s="146"/>
+      <c r="C32" s="147" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="110"/>
-      <c r="E32" s="154"/>
-      <c r="F32" s="155"/>
-      <c r="G32" s="155"/>
-      <c r="H32" s="156"/>
-      <c r="I32" s="157"/>
-      <c r="J32" s="155"/>
-      <c r="K32" s="155"/>
-      <c r="L32" s="156"/>
-      <c r="M32" s="157"/>
-      <c r="N32" s="155"/>
-      <c r="O32" s="156"/>
-      <c r="P32" s="155"/>
-      <c r="Q32" s="157"/>
-      <c r="R32" s="155"/>
-      <c r="S32" s="158"/>
+      <c r="D32" s="109"/>
+      <c r="E32" s="153"/>
+      <c r="F32" s="154"/>
+      <c r="G32" s="154"/>
+      <c r="H32" s="155"/>
+      <c r="I32" s="156"/>
+      <c r="J32" s="154"/>
+      <c r="K32" s="154"/>
+      <c r="L32" s="155"/>
+      <c r="M32" s="156"/>
+      <c r="N32" s="154"/>
+      <c r="O32" s="155"/>
+      <c r="P32" s="154"/>
+      <c r="Q32" s="156"/>
+      <c r="R32" s="154"/>
+      <c r="S32" s="157"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="147"/>
-      <c r="C33" s="148"/>
-      <c r="D33" s="102"/>
-      <c r="E33" s="149"/>
-      <c r="F33" s="153"/>
-      <c r="G33" s="150"/>
-      <c r="H33" s="159"/>
-      <c r="I33" s="160"/>
-      <c r="J33" s="150"/>
-      <c r="K33" s="153"/>
-      <c r="L33" s="151"/>
-      <c r="M33" s="152"/>
-      <c r="N33" s="150"/>
-      <c r="O33" s="151"/>
-      <c r="P33" s="150"/>
-      <c r="Q33" s="152"/>
-      <c r="R33" s="150"/>
-      <c r="S33" s="108"/>
+      <c r="B33" s="146"/>
+      <c r="C33" s="147"/>
+      <c r="D33" s="101"/>
+      <c r="E33" s="148"/>
+      <c r="F33" s="152"/>
+      <c r="G33" s="149"/>
+      <c r="H33" s="158"/>
+      <c r="I33" s="159"/>
+      <c r="J33" s="149"/>
+      <c r="K33" s="152"/>
+      <c r="L33" s="150"/>
+      <c r="M33" s="151"/>
+      <c r="N33" s="149"/>
+      <c r="O33" s="150"/>
+      <c r="P33" s="149"/>
+      <c r="Q33" s="151"/>
+      <c r="R33" s="149"/>
+      <c r="S33" s="107"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="147"/>
-      <c r="C34" s="101" t="s">
-        <v>162</v>
-      </c>
-      <c r="D34" s="133"/>
-      <c r="E34" s="161"/>
-      <c r="F34" s="162"/>
-      <c r="G34" s="162"/>
-      <c r="H34" s="163"/>
-      <c r="I34" s="164"/>
-      <c r="J34" s="162"/>
-      <c r="K34" s="162"/>
-      <c r="L34" s="163"/>
-      <c r="M34" s="164"/>
-      <c r="N34" s="162"/>
-      <c r="O34" s="163"/>
-      <c r="P34" s="162"/>
-      <c r="Q34" s="164"/>
-      <c r="R34" s="162"/>
-      <c r="S34" s="165"/>
-      <c r="U34" s="166"/>
-      <c r="V34" s="167" t="s">
+      <c r="B34" s="146"/>
+      <c r="C34" s="100" t="s">
         <v>163</v>
       </c>
+      <c r="D34" s="132"/>
+      <c r="E34" s="160"/>
+      <c r="F34" s="161"/>
+      <c r="G34" s="161"/>
+      <c r="H34" s="162"/>
+      <c r="I34" s="163"/>
+      <c r="J34" s="161"/>
+      <c r="K34" s="161"/>
+      <c r="L34" s="162"/>
+      <c r="M34" s="163"/>
+      <c r="N34" s="161"/>
+      <c r="O34" s="162"/>
+      <c r="P34" s="161"/>
+      <c r="Q34" s="163"/>
+      <c r="R34" s="161"/>
+      <c r="S34" s="164"/>
+      <c r="U34" s="165"/>
+      <c r="V34" s="166" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="168"/>
-      <c r="C35" s="169"/>
-      <c r="D35" s="120"/>
-      <c r="E35" s="170"/>
-      <c r="F35" s="171"/>
-      <c r="G35" s="171"/>
-      <c r="H35" s="172"/>
-      <c r="I35" s="173"/>
-      <c r="J35" s="171"/>
-      <c r="K35" s="171"/>
-      <c r="L35" s="172"/>
-      <c r="M35" s="173"/>
-      <c r="N35" s="171"/>
-      <c r="O35" s="172"/>
-      <c r="P35" s="171"/>
-      <c r="Q35" s="173"/>
-      <c r="R35" s="171"/>
-      <c r="S35" s="125"/>
-      <c r="U35" s="174"/>
-      <c r="V35" s="175" t="s">
-        <v>164</v>
+      <c r="B35" s="167"/>
+      <c r="C35" s="168"/>
+      <c r="D35" s="119"/>
+      <c r="E35" s="169"/>
+      <c r="F35" s="170"/>
+      <c r="G35" s="170"/>
+      <c r="H35" s="171"/>
+      <c r="I35" s="172"/>
+      <c r="J35" s="170"/>
+      <c r="K35" s="170"/>
+      <c r="L35" s="171"/>
+      <c r="M35" s="172"/>
+      <c r="N35" s="170"/>
+      <c r="O35" s="171"/>
+      <c r="P35" s="170"/>
+      <c r="Q35" s="172"/>
+      <c r="R35" s="170"/>
+      <c r="S35" s="124"/>
+      <c r="U35" s="173"/>
+      <c r="V35" s="174" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/HoferL-JournalPlanif-M5.xlsx
+++ b/Documentation/HoferL-JournalPlanif-M5.xlsx
@@ -1524,7 +1524,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="176">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1567,14 +1567,17 @@
     <xf fontId="0" fillId="0" borderId="2" numFmtId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="20" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2423,6 +2426,87 @@
           <c:cat>
             <c:strRef>
               <c:f>SommeParJours!$A$2:$A$27</c:f>
+              <c:strCache>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>20.01.2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>27.01.2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30.01.2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>03.02.2026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>04.02.2026</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>06.02.2026</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>08.02.2026</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>09.02.2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10.02.2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12.02.2026</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>13.02.2026</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>24.02.2026</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>03.03.2026</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>05.03.2026</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3/6/2026</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3/7/2026</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3/10/2026</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3/12/2026</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3/14/2026</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3/15/2026</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3/16/2026</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3/17/2026</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3/18/2026</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3/19/2026</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3/21/2026</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3/22/2026</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
@@ -3562,8 +3646,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E51">
-  <autoFilter ref="B2:E51"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E52">
+  <autoFilter ref="B2:E52"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -4127,7 +4211,7 @@
       </c>
       <c r="I3" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>2.4193548387096774e-002</v>
+        <v>0.02412868632707775</v>
       </c>
       <c r="J3" s="12" t="str" cm="1">
         <f t="array" ref="J3:J9">_xlfn._xlws.FILTER(G3:G10,H3:H10&gt;0)</f>
@@ -4143,7 +4227,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
@@ -4160,7 +4244,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>2.4193548387096774e-002</v>
+        <v>0.02412868632707775</v>
       </c>
       <c r="J4" s="4" t="str">
         <f/>
@@ -4193,7 +4277,7 @@
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>7.2580645161290328e-002</v>
+        <v>0.072386058981233251</v>
       </c>
       <c r="J5" s="4" t="str">
         <f/>
@@ -4209,7 +4293,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
@@ -4226,7 +4310,7 @@
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.13709677419354838</v>
+        <v>0.13672922252010725</v>
       </c>
       <c r="J6" s="4" t="str">
         <f/>
@@ -4242,7 +4326,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>8</v>
@@ -4259,7 +4343,7 @@
       </c>
       <c r="I7" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.30241935483870969</v>
+        <v>0.30160857908847188</v>
       </c>
       <c r="J7" s="4" t="str">
         <f/>
@@ -4292,7 +4376,7 @@
       </c>
       <c r="I8" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.43145161290322587</v>
+        <v>0.4302949061662199</v>
       </c>
       <c r="J8" s="4" t="str">
         <f/>
@@ -4321,11 +4405,11 @@
       </c>
       <c r="H9" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>1</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="I9" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>8.0645161290322578e-003</v>
+        <v>0.010723860589812333</v>
       </c>
       <c r="J9" s="4" t="str">
         <f/>
@@ -4333,7 +4417,7 @@
       </c>
       <c r="K9" s="14">
         <f/>
-        <v>1</v>
+        <v>1.3333333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -4341,7 +4425,7 @@
         <v>22</v>
       </c>
       <c r="C10" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>12</v>
@@ -4368,7 +4452,7 @@
         <v>22</v>
       </c>
       <c r="C11" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>12</v>
@@ -4381,7 +4465,7 @@
       </c>
       <c r="H11" s="10">
         <f>SUM(H3:H10)</f>
-        <v>124</v>
+        <v>124.33333333333333</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -4391,7 +4475,7 @@
         <v>22</v>
       </c>
       <c r="C12" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>10</v>
@@ -4406,7 +4490,7 @@
         <v>22</v>
       </c>
       <c r="C13" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>12</v>
@@ -4421,7 +4505,7 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>12</v>
@@ -4477,7 +4561,7 @@
         <v>35</v>
       </c>
       <c r="C18" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>10</v>
@@ -4491,7 +4575,7 @@
         <v>37</v>
       </c>
       <c r="C19" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>12</v>
@@ -4505,7 +4589,7 @@
         <v>39</v>
       </c>
       <c r="C20" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>19</v>
@@ -4519,7 +4603,7 @@
         <v>39</v>
       </c>
       <c r="C21" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>15</v>
@@ -4547,7 +4631,7 @@
         <v>43</v>
       </c>
       <c r="C23" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>15</v>
@@ -4561,7 +4645,7 @@
         <v>45</v>
       </c>
       <c r="C24" s="6">
-        <v>6.25e-002</v>
+        <v>0.0625</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>15</v>
@@ -4603,7 +4687,7 @@
         <v>49</v>
       </c>
       <c r="C27" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>12</v>
@@ -4617,7 +4701,7 @@
         <v>52</v>
       </c>
       <c r="C28" s="6">
-        <v>6.25e-002</v>
+        <v>0.0625</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>15</v>
@@ -4659,7 +4743,7 @@
         <v>46087</v>
       </c>
       <c r="C31" s="6">
-        <v>2.0833333333333332e-002</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>21</v>
@@ -4687,7 +4771,7 @@
         <v>46091</v>
       </c>
       <c r="C33" s="6">
-        <v>2.0833333333333332e-002</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>12</v>
@@ -4715,7 +4799,7 @@
         <v>46091</v>
       </c>
       <c r="C35" s="6">
-        <v>2.0833333333333332e-002</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>19</v>
@@ -4743,7 +4827,7 @@
         <v>46093</v>
       </c>
       <c r="C37" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>19</v>
@@ -4771,7 +4855,7 @@
         <v>46087</v>
       </c>
       <c r="C39" s="6">
-        <v>2.0833333333333332e-002</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>21</v>
@@ -4807,7 +4891,7 @@
       <c r="D41" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E41" s="20" t="s">
+      <c r="E41" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -4821,7 +4905,7 @@
       <c r="D42" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E42" s="20" t="s">
+      <c r="E42" s="8" t="s">
         <v>66</v>
       </c>
     </row>
@@ -4835,7 +4919,7 @@
       <c r="D43" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E43" s="20" t="s">
+      <c r="E43" s="8" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4849,7 +4933,7 @@
       <c r="D44" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E44" s="20" t="s">
+      <c r="E44" s="8" t="s">
         <v>68</v>
       </c>
     </row>
@@ -4858,7 +4942,7 @@
         <v>46100</v>
       </c>
       <c r="C45" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>8</v>
@@ -4872,7 +4956,7 @@
         <v>46100</v>
       </c>
       <c r="C46" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>19</v>
@@ -4891,240 +4975,248 @@
       <c r="D47" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E47" s="20" t="s">
+      <c r="E47" s="8" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="48" ht="28.5">
-      <c r="B48" s="21">
+      <c r="B48" s="20">
         <v>46102</v>
       </c>
-      <c r="C48" s="22">
-        <v>8.3333333333333329e-002</v>
+      <c r="C48" s="21">
+        <v>0.083333333333333329</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E48" s="20" t="s">
+      <c r="E48" s="8" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="49" ht="42.75">
-      <c r="B49" s="21">
+      <c r="B49" s="20">
         <v>46102</v>
       </c>
-      <c r="C49" s="22">
+      <c r="C49" s="21">
         <v>0.125</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E49" s="20" t="s">
+      <c r="E49" s="8" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="50" ht="57">
-      <c r="B50" s="21">
+      <c r="B50" s="20">
         <v>46103</v>
       </c>
-      <c r="C50" s="22">
+      <c r="C50" s="21">
         <v>0.16666666666666666</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E50" s="20" t="s">
+      <c r="E50" s="8" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="51" ht="28.5">
-      <c r="B51" s="21">
+      <c r="B51" s="20">
         <v>46103</v>
       </c>
-      <c r="C51" s="22">
+      <c r="C51" s="21">
         <v>0.20833333333333334</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E51" s="20" t="s">
+      <c r="E51" s="8" t="s">
         <v>75</v>
       </c>
       <c r="G51" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="21"/>
-      <c r="C52" s="23"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="8"/>
+    <row r="52" ht="28.5">
+      <c r="B52" s="20">
+        <v>46104</v>
+      </c>
+      <c r="C52" s="21">
+        <v>0.013888888888888888</v>
+      </c>
+      <c r="D52" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E52" s="23" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="53">
-      <c r="B53" s="21"/>
-      <c r="C53" s="23"/>
+      <c r="B53" s="20"/>
+      <c r="C53" s="24"/>
       <c r="D53" s="7"/>
       <c r="E53" s="8"/>
     </row>
     <row r="54">
-      <c r="B54" s="21"/>
-      <c r="C54" s="23"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="24"/>
       <c r="D54" s="7"/>
       <c r="E54" s="8"/>
     </row>
     <row r="55">
-      <c r="B55" s="21"/>
-      <c r="C55" s="23"/>
+      <c r="B55" s="20"/>
+      <c r="C55" s="24"/>
       <c r="D55" s="7"/>
       <c r="E55" s="8"/>
     </row>
     <row r="56">
-      <c r="B56" s="21"/>
-      <c r="C56" s="23"/>
+      <c r="B56" s="20"/>
+      <c r="C56" s="24"/>
       <c r="D56" s="7"/>
       <c r="E56" s="8"/>
     </row>
     <row r="57">
-      <c r="B57" s="21"/>
-      <c r="C57" s="23"/>
+      <c r="B57" s="20"/>
+      <c r="C57" s="24"/>
       <c r="D57" s="7"/>
       <c r="E57" s="8"/>
     </row>
     <row r="58">
-      <c r="B58" s="21"/>
-      <c r="C58" s="23"/>
+      <c r="B58" s="20"/>
+      <c r="C58" s="24"/>
       <c r="D58" s="7"/>
       <c r="E58" s="8"/>
     </row>
     <row r="59">
-      <c r="B59" s="21"/>
-      <c r="C59" s="23"/>
+      <c r="B59" s="20"/>
+      <c r="C59" s="24"/>
       <c r="D59" s="7"/>
       <c r="E59" s="8"/>
     </row>
     <row r="60">
-      <c r="B60" s="21"/>
-      <c r="C60" s="23"/>
+      <c r="B60" s="20"/>
+      <c r="C60" s="24"/>
       <c r="D60" s="7"/>
       <c r="E60" s="8"/>
     </row>
     <row r="61">
-      <c r="B61" s="21"/>
-      <c r="C61" s="23"/>
+      <c r="B61" s="20"/>
+      <c r="C61" s="24"/>
       <c r="D61" s="7"/>
       <c r="E61" s="8"/>
     </row>
     <row r="62">
-      <c r="B62" s="21"/>
-      <c r="C62" s="23"/>
+      <c r="B62" s="20"/>
+      <c r="C62" s="24"/>
       <c r="D62" s="7"/>
       <c r="E62" s="8"/>
     </row>
     <row r="63">
-      <c r="B63" s="21"/>
-      <c r="C63" s="23"/>
+      <c r="B63" s="20"/>
+      <c r="C63" s="24"/>
       <c r="D63" s="7"/>
       <c r="E63" s="8"/>
     </row>
     <row r="64">
-      <c r="B64" s="21"/>
-      <c r="C64" s="23"/>
+      <c r="B64" s="20"/>
+      <c r="C64" s="24"/>
       <c r="D64" s="7"/>
       <c r="E64" s="8"/>
     </row>
     <row r="65">
-      <c r="B65" s="21"/>
-      <c r="C65" s="23"/>
+      <c r="B65" s="20"/>
+      <c r="C65" s="24"/>
       <c r="D65" s="7"/>
       <c r="E65" s="8"/>
     </row>
     <row r="66">
-      <c r="B66" s="21"/>
-      <c r="C66" s="23"/>
+      <c r="B66" s="20"/>
+      <c r="C66" s="24"/>
       <c r="D66" s="7"/>
       <c r="E66" s="8"/>
     </row>
     <row r="67">
-      <c r="B67" s="21"/>
-      <c r="C67" s="23"/>
+      <c r="B67" s="20"/>
+      <c r="C67" s="24"/>
       <c r="D67" s="7"/>
       <c r="E67" s="8"/>
     </row>
     <row r="68">
-      <c r="B68" s="21"/>
-      <c r="C68" s="23"/>
+      <c r="B68" s="20"/>
+      <c r="C68" s="24"/>
       <c r="D68" s="7"/>
       <c r="E68" s="8"/>
     </row>
     <row r="69">
-      <c r="B69" s="21"/>
-      <c r="C69" s="23"/>
+      <c r="B69" s="20"/>
+      <c r="C69" s="24"/>
       <c r="D69" s="7"/>
       <c r="E69" s="8"/>
     </row>
     <row r="70">
-      <c r="B70" s="21"/>
-      <c r="C70" s="23"/>
+      <c r="B70" s="20"/>
+      <c r="C70" s="24"/>
       <c r="D70" s="7"/>
       <c r="E70" s="8"/>
     </row>
     <row r="71">
-      <c r="B71" s="21"/>
-      <c r="C71" s="23"/>
+      <c r="B71" s="20"/>
+      <c r="C71" s="24"/>
       <c r="D71" s="7"/>
       <c r="E71" s="8"/>
     </row>
     <row r="72">
-      <c r="B72" s="21"/>
-      <c r="C72" s="23"/>
+      <c r="B72" s="20"/>
+      <c r="C72" s="24"/>
       <c r="D72" s="7"/>
       <c r="E72" s="8"/>
     </row>
     <row r="73">
-      <c r="B73" s="21"/>
-      <c r="C73" s="23"/>
+      <c r="B73" s="20"/>
+      <c r="C73" s="24"/>
       <c r="D73" s="7"/>
       <c r="E73" s="8"/>
     </row>
     <row r="74">
-      <c r="B74" s="21"/>
-      <c r="C74" s="23"/>
+      <c r="B74" s="20"/>
+      <c r="C74" s="24"/>
       <c r="D74" s="7"/>
       <c r="E74" s="8"/>
     </row>
     <row r="75">
       <c r="B75" s="7"/>
-      <c r="C75" s="23"/>
+      <c r="C75" s="24"/>
       <c r="D75" s="7"/>
       <c r="E75" s="8"/>
     </row>
     <row r="76">
       <c r="B76" s="7"/>
-      <c r="C76" s="23"/>
+      <c r="C76" s="24"/>
       <c r="D76" s="7"/>
       <c r="E76" s="8"/>
     </row>
     <row r="77">
       <c r="B77" s="7"/>
-      <c r="C77" s="23"/>
+      <c r="C77" s="24"/>
       <c r="D77" s="7"/>
       <c r="E77" s="8"/>
     </row>
     <row r="78">
       <c r="B78" s="7"/>
-      <c r="C78" s="23"/>
+      <c r="C78" s="24"/>
       <c r="D78" s="7"/>
       <c r="E78" s="8"/>
     </row>
     <row r="79">
       <c r="B79" s="7"/>
-      <c r="C79" s="23"/>
+      <c r="C79" s="24"/>
       <c r="D79" s="7"/>
       <c r="E79" s="8"/>
     </row>
     <row r="80">
       <c r="B80" s="7"/>
-      <c r="C80" s="23"/>
+      <c r="C80" s="24"/>
       <c r="D80" s="7"/>
       <c r="E80" s="8"/>
     </row>
@@ -5144,7 +5236,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00D800C9-008E-42D5-940A-00D200B300B4}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00DE0023-00B9-4D4C-941E-0023007B0050}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -5176,1734 +5268,1737 @@
       <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="str" cm="1">
-        <f t="array" ref="A2:A27">_xlfn.UNIQUE(Journal[date])</f>
+      <c r="A2" s="25" t="str" cm="1">
+        <f t="array" ref="A2:A28">_xlfn.UNIQUE(Journal[date])</f>
         <v>20.01.2026</v>
       </c>
-      <c r="B2" s="25">
+      <c r="B2" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A2,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" s="26"/>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="str">
+      <c r="A3" s="25" t="str">
         <f/>
         <v>27.01.2026</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="str">
+      <c r="A4" s="25" t="str">
         <f/>
         <v>30.01.2026</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C4"/>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="str">
+      <c r="A5" s="25" t="str">
         <f/>
         <v>03.02.2026</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0.25</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="str">
+      <c r="A6" s="25" t="str">
         <f/>
         <v>04.02.2026</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="str">
+      <c r="A7" s="25" t="str">
         <f/>
         <v>06.02.2026</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C7"/>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="str">
+      <c r="A8" s="25" t="str">
         <f/>
         <v>08.02.2026</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="str">
+      <c r="A9" s="25" t="str">
         <f/>
         <v>09.02.2026</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="str">
+      <c r="A10" s="25" t="str">
         <f/>
         <v>10.02.2026</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="str">
+      <c r="A11" s="25" t="str">
         <f/>
         <v>12.02.2026</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="str">
+      <c r="A12" s="25" t="str">
         <f/>
         <v>13.02.2026</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
-        <v>6.25e-002</v>
+        <v>0.0625</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="str">
+      <c r="A13" s="25" t="str">
         <f/>
         <v>24.02.2026</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0.125</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="str">
+      <c r="A14" s="25" t="str">
         <f/>
         <v>03.03.2026</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="str">
+      <c r="A15" s="25" t="str">
         <f/>
         <v>05.03.2026</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="24">
+      <c r="A16" s="25">
         <f/>
         <v>46087</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="24">
+      <c r="A17" s="25">
         <f/>
         <v>46088</v>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0.25</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="24">
+      <c r="A18" s="25">
         <f/>
         <v>46091</v>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="24">
+      <c r="A19" s="25">
         <f/>
         <v>46093</v>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="24">
+      <c r="A20" s="25">
         <f/>
         <v>46095</v>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="24">
+      <c r="A21" s="25">
         <f/>
         <v>46096</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="24">
+      <c r="A22" s="25">
         <f/>
         <v>46097</v>
       </c>
-      <c r="B22" s="25">
+      <c r="B22" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0.14583333333333334</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="24">
+      <c r="A23" s="25">
         <f/>
         <v>46098</v>
       </c>
-      <c r="B23" s="25">
+      <c r="B23" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="24">
+      <c r="A24" s="25">
         <f/>
         <v>46099</v>
       </c>
-      <c r="B24" s="25">
+      <c r="B24" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="24">
+      <c r="A25" s="25">
         <f/>
         <v>46100</v>
       </c>
-      <c r="B25" s="25">
+      <c r="B25" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="C25"/>
-      <c r="F25" s="26"/>
+      <c r="F25" s="27"/>
     </row>
     <row r="26">
-      <c r="A26" s="24">
+      <c r="A26" s="25">
         <f/>
         <v>46102</v>
       </c>
-      <c r="B26" s="25">
+      <c r="B26" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="24">
+      <c r="A27" s="25">
         <f/>
         <v>46103</v>
       </c>
-      <c r="B27" s="25">
+      <c r="B27" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0.375</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0.375</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="24"/>
-      <c r="C28" s="27">
+      <c r="A28" s="25">
+        <f/>
+        <v>46104</v>
+      </c>
+      <c r="C28" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
-        <v>0</v>
+        <v>0.013888888888888888</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24"/>
-      <c r="C29" s="27">
+      <c r="A29" s="25"/>
+      <c r="C29" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="24"/>
-      <c r="C30" s="27">
+      <c r="A30" s="25"/>
+      <c r="C30" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="24"/>
-      <c r="C31" s="27">
+      <c r="A31" s="25"/>
+      <c r="C31" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="24"/>
-      <c r="C32" s="27">
+      <c r="A32" s="25"/>
+      <c r="C32" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="24"/>
-      <c r="C33" s="27">
+      <c r="A33" s="25"/>
+      <c r="C33" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24"/>
-      <c r="C34" s="27">
+      <c r="A34" s="25"/>
+      <c r="C34" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="24"/>
-      <c r="C35" s="27">
+      <c r="A35" s="25"/>
+      <c r="C35" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="24"/>
-      <c r="C36" s="27">
+      <c r="A36" s="25"/>
+      <c r="C36" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="24"/>
-      <c r="C37" s="27">
+      <c r="A37" s="25"/>
+      <c r="C37" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="24"/>
-      <c r="C38" s="27">
+      <c r="A38" s="25"/>
+      <c r="C38" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="24"/>
-      <c r="C39" s="27">
+      <c r="A39" s="25"/>
+      <c r="C39" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="24"/>
-      <c r="B40" s="25" t="str">
+      <c r="A40" s="25"/>
+      <c r="B40" s="26" t="str">
         <f t="shared" ref="B40:B103" si="0">IF(C40&gt;0,C40,"")</f>
         <v/>
       </c>
-      <c r="C40" s="27">
+      <c r="C40" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="24"/>
-      <c r="B41" s="25" t="str">
+      <c r="A41" s="25"/>
+      <c r="B41" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="27">
+      <c r="C41" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="28"/>
-      <c r="B42" s="25" t="str">
+      <c r="A42" s="29"/>
+      <c r="B42" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="27">
+      <c r="C42" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="28"/>
-      <c r="B43" s="25" t="str">
+      <c r="A43" s="29"/>
+      <c r="B43" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="27">
+      <c r="C43" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="28"/>
-      <c r="B44" s="25" t="str">
+      <c r="A44" s="29"/>
+      <c r="B44" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="27">
+      <c r="C44" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="28"/>
-      <c r="B45" s="25" t="str">
+      <c r="A45" s="29"/>
+      <c r="B45" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="27">
+      <c r="C45" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="28"/>
-      <c r="B46" s="25" t="str">
+      <c r="A46" s="29"/>
+      <c r="B46" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="27">
+      <c r="C46" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="29"/>
-      <c r="B47" s="25" t="str">
+      <c r="A47" s="30"/>
+      <c r="B47" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="27">
+      <c r="C47" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="29"/>
-      <c r="B48" s="25" t="str">
+      <c r="A48" s="30"/>
+      <c r="B48" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="27">
+      <c r="C48" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="29"/>
-      <c r="B49" s="25" t="str">
+      <c r="A49" s="30"/>
+      <c r="B49" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C49" s="27">
+      <c r="C49" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="29"/>
-      <c r="B50" s="25" t="str">
+      <c r="A50" s="30"/>
+      <c r="B50" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C50" s="27">
+      <c r="C50" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="29"/>
-      <c r="B51" s="25" t="str">
+      <c r="A51" s="30"/>
+      <c r="B51" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C51" s="27">
+      <c r="C51" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="29"/>
-      <c r="B52" s="25" t="str">
+      <c r="A52" s="30"/>
+      <c r="B52" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C52" s="27">
+      <c r="C52" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="29"/>
-      <c r="B53" s="25" t="str">
+      <c r="A53" s="30"/>
+      <c r="B53" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C53" s="27">
+      <c r="C53" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="29"/>
-      <c r="B54" s="25" t="str">
+      <c r="A54" s="30"/>
+      <c r="B54" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C54" s="27">
+      <c r="C54" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="29"/>
-      <c r="B55" s="25" t="str">
+      <c r="A55" s="30"/>
+      <c r="B55" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C55" s="27">
+      <c r="C55" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="29"/>
-      <c r="B56" s="25" t="str">
+      <c r="A56" s="30"/>
+      <c r="B56" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C56" s="27">
+      <c r="C56" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="29"/>
-      <c r="B57" s="25" t="str">
+      <c r="A57" s="30"/>
+      <c r="B57" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C57" s="27">
+      <c r="C57" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="29"/>
-      <c r="B58" s="25" t="str">
+      <c r="A58" s="30"/>
+      <c r="B58" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C58" s="27">
+      <c r="C58" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="29"/>
-      <c r="B59" s="25" t="str">
+      <c r="A59" s="30"/>
+      <c r="B59" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C59" s="27">
+      <c r="C59" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="29"/>
-      <c r="B60" s="25" t="str">
+      <c r="A60" s="30"/>
+      <c r="B60" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C60" s="27">
+      <c r="C60" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="29"/>
-      <c r="B61" s="25" t="str">
+      <c r="A61" s="30"/>
+      <c r="B61" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C61" s="27">
+      <c r="C61" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="29"/>
-      <c r="B62" s="25" t="str">
+      <c r="A62" s="30"/>
+      <c r="B62" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C62" s="27">
+      <c r="C62" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="29"/>
-      <c r="B63" s="25" t="str">
+      <c r="A63" s="30"/>
+      <c r="B63" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C63" s="27">
+      <c r="C63" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="29"/>
-      <c r="B64" s="25" t="str">
+      <c r="A64" s="30"/>
+      <c r="B64" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C64" s="27">
+      <c r="C64" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="29"/>
-      <c r="B65" s="25" t="str">
+      <c r="A65" s="30"/>
+      <c r="B65" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C65" s="27">
+      <c r="C65" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="29"/>
-      <c r="B66" s="25" t="str">
+      <c r="A66" s="30"/>
+      <c r="B66" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C66" s="27">
+      <c r="C66" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="29"/>
-      <c r="B67" s="25" t="str">
+      <c r="A67" s="30"/>
+      <c r="B67" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C67" s="27">
+      <c r="C67" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="29"/>
-      <c r="B68" s="25" t="str">
+      <c r="A68" s="30"/>
+      <c r="B68" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C68" s="27">
+      <c r="C68" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29"/>
-      <c r="B69" s="25" t="str">
+      <c r="A69" s="30"/>
+      <c r="B69" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C69" s="27">
+      <c r="C69" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29"/>
-      <c r="B70" s="25" t="str">
+      <c r="A70" s="30"/>
+      <c r="B70" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C70" s="27">
+      <c r="C70" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="29"/>
-      <c r="B71" s="25" t="str">
+      <c r="A71" s="30"/>
+      <c r="B71" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C71" s="27">
+      <c r="C71" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="29"/>
-      <c r="B72" s="25" t="str">
+      <c r="A72" s="30"/>
+      <c r="B72" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C72" s="27">
+      <c r="C72" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="29"/>
-      <c r="B73" s="25" t="str">
+      <c r="A73" s="30"/>
+      <c r="B73" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C73" s="27">
+      <c r="C73" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="29"/>
-      <c r="B74" s="25" t="str">
+      <c r="A74" s="30"/>
+      <c r="B74" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C74" s="27">
+      <c r="C74" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="29"/>
-      <c r="B75" s="25" t="str">
+      <c r="A75" s="30"/>
+      <c r="B75" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C75" s="27">
+      <c r="C75" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="29"/>
-      <c r="B76" s="25" t="str">
+      <c r="A76" s="30"/>
+      <c r="B76" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C76" s="27">
+      <c r="C76" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29"/>
-      <c r="B77" s="25" t="str">
+      <c r="A77" s="30"/>
+      <c r="B77" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C77" s="27">
+      <c r="C77" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="29"/>
-      <c r="B78" s="25" t="str">
+      <c r="A78" s="30"/>
+      <c r="B78" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C78" s="27">
+      <c r="C78" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="29"/>
-      <c r="B79" s="25" t="str">
+      <c r="A79" s="30"/>
+      <c r="B79" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C79" s="27">
+      <c r="C79" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="29"/>
-      <c r="B80" s="25" t="str">
+      <c r="A80" s="30"/>
+      <c r="B80" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C80" s="27">
+      <c r="C80" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="29"/>
-      <c r="B81" s="25" t="str">
+      <c r="A81" s="30"/>
+      <c r="B81" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C81" s="27">
+      <c r="C81" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="29"/>
-      <c r="B82" s="25" t="str">
+      <c r="A82" s="30"/>
+      <c r="B82" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C82" s="27">
+      <c r="C82" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="29"/>
-      <c r="B83" s="25" t="str">
+      <c r="A83" s="30"/>
+      <c r="B83" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C83" s="27">
+      <c r="C83" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="29"/>
-      <c r="B84" s="25" t="str">
+      <c r="A84" s="30"/>
+      <c r="B84" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C84" s="27">
+      <c r="C84" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="29"/>
-      <c r="B85" s="25" t="str">
+      <c r="A85" s="30"/>
+      <c r="B85" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C85" s="27">
+      <c r="C85" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="29"/>
-      <c r="B86" s="25" t="str">
+      <c r="A86" s="30"/>
+      <c r="B86" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C86" s="27">
+      <c r="C86" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="29"/>
-      <c r="B87" s="25" t="str">
+      <c r="A87" s="30"/>
+      <c r="B87" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C87" s="27">
+      <c r="C87" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="29"/>
-      <c r="B88" s="25" t="str">
+      <c r="A88" s="30"/>
+      <c r="B88" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C88" s="27">
+      <c r="C88" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="29"/>
-      <c r="B89" s="25" t="str">
+      <c r="A89" s="30"/>
+      <c r="B89" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C89" s="27">
+      <c r="C89" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="29"/>
-      <c r="B90" s="25" t="str">
+      <c r="A90" s="30"/>
+      <c r="B90" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C90" s="27">
+      <c r="C90" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="29"/>
-      <c r="B91" s="25" t="str">
+      <c r="A91" s="30"/>
+      <c r="B91" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C91" s="27">
+      <c r="C91" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="29"/>
-      <c r="B92" s="25" t="str">
+      <c r="A92" s="30"/>
+      <c r="B92" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C92" s="27">
+      <c r="C92" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="29"/>
-      <c r="B93" s="25" t="str">
+      <c r="A93" s="30"/>
+      <c r="B93" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C93" s="27">
+      <c r="C93" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="29"/>
-      <c r="B94" s="25" t="str">
+      <c r="A94" s="30"/>
+      <c r="B94" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C94" s="27">
+      <c r="C94" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="29"/>
-      <c r="B95" s="25" t="str">
+      <c r="A95" s="30"/>
+      <c r="B95" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C95" s="27">
+      <c r="C95" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="29"/>
-      <c r="B96" s="25" t="str">
+      <c r="A96" s="30"/>
+      <c r="B96" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C96" s="27">
+      <c r="C96" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="29"/>
-      <c r="B97" s="25" t="str">
+      <c r="A97" s="30"/>
+      <c r="B97" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C97" s="27">
+      <c r="C97" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="29"/>
-      <c r="B98" s="25" t="str">
+      <c r="A98" s="30"/>
+      <c r="B98" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C98" s="27">
+      <c r="C98" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="29"/>
-      <c r="B99" s="25" t="str">
+      <c r="A99" s="30"/>
+      <c r="B99" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C99" s="27">
+      <c r="C99" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="29"/>
-      <c r="B100" s="25" t="str">
+      <c r="A100" s="30"/>
+      <c r="B100" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C100" s="27">
+      <c r="C100" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="29"/>
-      <c r="B101" s="25" t="str">
+      <c r="A101" s="30"/>
+      <c r="B101" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C101" s="27">
+      <c r="C101" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="29"/>
-      <c r="B102" s="25" t="str">
+      <c r="A102" s="30"/>
+      <c r="B102" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C102" s="27">
+      <c r="C102" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="29"/>
-      <c r="B103" s="25" t="str">
+      <c r="A103" s="30"/>
+      <c r="B103" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C103" s="27">
+      <c r="C103" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="29"/>
-      <c r="B104" s="25" t="str">
+      <c r="A104" s="30"/>
+      <c r="B104" s="26" t="str">
         <f t="shared" ref="B104:B114" si="1">IF(C104&gt;0,C104,"")</f>
         <v/>
       </c>
-      <c r="C104" s="27">
+      <c r="C104" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="29"/>
-      <c r="B105" s="25" t="str">
+      <c r="A105" s="30"/>
+      <c r="B105" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C105" s="27">
+      <c r="C105" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="29"/>
-      <c r="B106" s="25" t="str">
+      <c r="A106" s="30"/>
+      <c r="B106" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C106" s="27">
+      <c r="C106" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="29"/>
-      <c r="B107" s="25" t="str">
+      <c r="A107" s="30"/>
+      <c r="B107" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C107" s="27">
+      <c r="C107" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="29"/>
-      <c r="B108" s="25" t="str">
+      <c r="A108" s="30"/>
+      <c r="B108" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C108" s="27">
+      <c r="C108" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="29"/>
-      <c r="B109" s="25" t="str">
+      <c r="A109" s="30"/>
+      <c r="B109" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C109" s="27">
+      <c r="C109" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="29"/>
-      <c r="B110" s="25" t="str">
+      <c r="A110" s="30"/>
+      <c r="B110" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C110" s="27">
+      <c r="C110" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="29"/>
-      <c r="B111" s="25" t="str">
+      <c r="A111" s="30"/>
+      <c r="B111" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C111" s="27">
+      <c r="C111" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="29"/>
-      <c r="B112" s="25" t="str">
+      <c r="A112" s="30"/>
+      <c r="B112" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C112" s="27">
+      <c r="C112" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="29"/>
-      <c r="B113" s="25" t="str">
+      <c r="A113" s="30"/>
+      <c r="B113" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C113" s="27">
+      <c r="C113" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="29"/>
-      <c r="B114" s="25" t="str">
+      <c r="A114" s="30"/>
+      <c r="B114" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C114" s="27">
+      <c r="C114" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="29"/>
-      <c r="B115" s="29"/>
-      <c r="C115" s="27"/>
+      <c r="A115" s="30"/>
+      <c r="B115" s="30"/>
+      <c r="C115" s="28"/>
     </row>
     <row r="116">
-      <c r="A116" s="29"/>
-      <c r="B116" s="29"/>
-      <c r="C116" s="27"/>
+      <c r="A116" s="30"/>
+      <c r="B116" s="30"/>
+      <c r="C116" s="28"/>
     </row>
     <row r="117">
-      <c r="A117" s="29"/>
-      <c r="B117" s="29"/>
-      <c r="C117" s="27"/>
+      <c r="A117" s="30"/>
+      <c r="B117" s="30"/>
+      <c r="C117" s="28"/>
     </row>
     <row r="118">
-      <c r="A118" s="29"/>
-      <c r="B118" s="29"/>
-      <c r="C118" s="27"/>
+      <c r="A118" s="30"/>
+      <c r="B118" s="30"/>
+      <c r="C118" s="28"/>
     </row>
     <row r="119">
-      <c r="A119" s="29"/>
-      <c r="B119" s="29"/>
-      <c r="C119" s="27"/>
+      <c r="A119" s="30"/>
+      <c r="B119" s="30"/>
+      <c r="C119" s="28"/>
     </row>
     <row r="120">
-      <c r="A120" s="29"/>
-      <c r="B120" s="29"/>
-      <c r="C120" s="27"/>
+      <c r="A120" s="30"/>
+      <c r="B120" s="30"/>
+      <c r="C120" s="28"/>
     </row>
     <row r="121">
-      <c r="A121" s="29"/>
-      <c r="B121" s="29"/>
-      <c r="C121" s="27"/>
+      <c r="A121" s="30"/>
+      <c r="B121" s="30"/>
+      <c r="C121" s="28"/>
     </row>
     <row r="122">
-      <c r="A122" s="29"/>
-      <c r="B122" s="29"/>
-      <c r="C122" s="27"/>
+      <c r="A122" s="30"/>
+      <c r="B122" s="30"/>
+      <c r="C122" s="28"/>
     </row>
     <row r="123">
-      <c r="A123" s="29"/>
-      <c r="B123" s="29"/>
-      <c r="C123" s="27"/>
+      <c r="A123" s="30"/>
+      <c r="B123" s="30"/>
+      <c r="C123" s="28"/>
     </row>
     <row r="124">
-      <c r="A124" s="29"/>
-      <c r="B124" s="29"/>
-      <c r="C124" s="27"/>
+      <c r="A124" s="30"/>
+      <c r="B124" s="30"/>
+      <c r="C124" s="28"/>
     </row>
     <row r="125">
-      <c r="A125" s="29"/>
-      <c r="B125" s="29"/>
-      <c r="C125" s="27"/>
+      <c r="A125" s="30"/>
+      <c r="B125" s="30"/>
+      <c r="C125" s="28"/>
     </row>
     <row r="126">
-      <c r="A126" s="29"/>
-      <c r="B126" s="29"/>
-      <c r="C126" s="27"/>
+      <c r="A126" s="30"/>
+      <c r="B126" s="30"/>
+      <c r="C126" s="28"/>
     </row>
     <row r="127">
-      <c r="A127" s="29"/>
-      <c r="B127" s="29"/>
-      <c r="C127" s="27"/>
+      <c r="A127" s="30"/>
+      <c r="B127" s="30"/>
+      <c r="C127" s="28"/>
     </row>
     <row r="128">
-      <c r="A128" s="29"/>
-      <c r="B128" s="29"/>
-      <c r="C128" s="27"/>
+      <c r="A128" s="30"/>
+      <c r="B128" s="30"/>
+      <c r="C128" s="28"/>
     </row>
     <row r="129">
-      <c r="A129" s="29"/>
-      <c r="B129" s="29"/>
-      <c r="C129" s="27"/>
+      <c r="A129" s="30"/>
+      <c r="B129" s="30"/>
+      <c r="C129" s="28"/>
     </row>
     <row r="130">
-      <c r="A130" s="29"/>
-      <c r="B130" s="29"/>
-      <c r="C130" s="27"/>
+      <c r="A130" s="30"/>
+      <c r="B130" s="30"/>
+      <c r="C130" s="28"/>
     </row>
     <row r="131">
-      <c r="A131" s="29"/>
-      <c r="B131" s="29"/>
-      <c r="C131" s="27"/>
+      <c r="A131" s="30"/>
+      <c r="B131" s="30"/>
+      <c r="C131" s="28"/>
     </row>
     <row r="132">
-      <c r="A132" s="29"/>
-      <c r="B132" s="29"/>
-      <c r="C132" s="27"/>
+      <c r="A132" s="30"/>
+      <c r="B132" s="30"/>
+      <c r="C132" s="28"/>
     </row>
     <row r="133">
-      <c r="A133" s="29"/>
-      <c r="B133" s="29"/>
-      <c r="C133" s="27"/>
+      <c r="A133" s="30"/>
+      <c r="B133" s="30"/>
+      <c r="C133" s="28"/>
     </row>
     <row r="134">
-      <c r="A134" s="29"/>
-      <c r="B134" s="29"/>
-      <c r="C134" s="27"/>
+      <c r="A134" s="30"/>
+      <c r="B134" s="30"/>
+      <c r="C134" s="28"/>
     </row>
     <row r="135">
-      <c r="A135" s="29"/>
-      <c r="B135" s="29"/>
-      <c r="C135" s="27"/>
+      <c r="A135" s="30"/>
+      <c r="B135" s="30"/>
+      <c r="C135" s="28"/>
     </row>
     <row r="136">
-      <c r="A136" s="29"/>
-      <c r="B136" s="29"/>
-      <c r="C136" s="27"/>
+      <c r="A136" s="30"/>
+      <c r="B136" s="30"/>
+      <c r="C136" s="28"/>
     </row>
     <row r="137">
-      <c r="A137" s="29"/>
-      <c r="B137" s="29"/>
-      <c r="C137" s="27"/>
+      <c r="A137" s="30"/>
+      <c r="B137" s="30"/>
+      <c r="C137" s="28"/>
     </row>
     <row r="138">
-      <c r="A138" s="29"/>
-      <c r="B138" s="29"/>
-      <c r="C138" s="27"/>
+      <c r="A138" s="30"/>
+      <c r="B138" s="30"/>
+      <c r="C138" s="28"/>
     </row>
     <row r="139">
-      <c r="A139" s="29"/>
-      <c r="B139" s="29"/>
-      <c r="C139" s="27"/>
+      <c r="A139" s="30"/>
+      <c r="B139" s="30"/>
+      <c r="C139" s="28"/>
     </row>
     <row r="140">
-      <c r="A140" s="29"/>
-      <c r="B140" s="29"/>
-      <c r="C140" s="27"/>
+      <c r="A140" s="30"/>
+      <c r="B140" s="30"/>
+      <c r="C140" s="28"/>
     </row>
     <row r="141">
-      <c r="A141" s="29"/>
-      <c r="B141" s="29"/>
-      <c r="C141" s="27"/>
+      <c r="A141" s="30"/>
+      <c r="B141" s="30"/>
+      <c r="C141" s="28"/>
     </row>
     <row r="142">
-      <c r="A142" s="29"/>
-      <c r="B142" s="29"/>
-      <c r="C142" s="27"/>
+      <c r="A142" s="30"/>
+      <c r="B142" s="30"/>
+      <c r="C142" s="28"/>
     </row>
     <row r="143">
-      <c r="A143" s="29"/>
-      <c r="B143" s="29"/>
-      <c r="C143" s="27"/>
+      <c r="A143" s="30"/>
+      <c r="B143" s="30"/>
+      <c r="C143" s="28"/>
     </row>
     <row r="144">
-      <c r="A144" s="29"/>
-      <c r="B144" s="29"/>
-      <c r="C144" s="27"/>
+      <c r="A144" s="30"/>
+      <c r="B144" s="30"/>
+      <c r="C144" s="28"/>
     </row>
     <row r="145">
-      <c r="A145" s="29"/>
-      <c r="B145" s="29"/>
-      <c r="C145" s="27"/>
+      <c r="A145" s="30"/>
+      <c r="B145" s="30"/>
+      <c r="C145" s="28"/>
     </row>
     <row r="146">
-      <c r="A146" s="29"/>
-      <c r="B146" s="29"/>
-      <c r="C146" s="27"/>
+      <c r="A146" s="30"/>
+      <c r="B146" s="30"/>
+      <c r="C146" s="28"/>
     </row>
     <row r="147">
-      <c r="A147" s="29"/>
-      <c r="B147" s="29"/>
-      <c r="C147" s="27"/>
+      <c r="A147" s="30"/>
+      <c r="B147" s="30"/>
+      <c r="C147" s="28"/>
     </row>
     <row r="148">
-      <c r="A148" s="29"/>
-      <c r="B148" s="29"/>
-      <c r="C148" s="27"/>
+      <c r="A148" s="30"/>
+      <c r="B148" s="30"/>
+      <c r="C148" s="28"/>
     </row>
     <row r="149">
-      <c r="A149" s="29"/>
-      <c r="B149" s="29"/>
-      <c r="C149" s="27"/>
+      <c r="A149" s="30"/>
+      <c r="B149" s="30"/>
+      <c r="C149" s="28"/>
     </row>
     <row r="150">
-      <c r="A150" s="29"/>
-      <c r="B150" s="29"/>
-      <c r="C150" s="27"/>
+      <c r="A150" s="30"/>
+      <c r="B150" s="30"/>
+      <c r="C150" s="28"/>
     </row>
     <row r="151">
-      <c r="A151" s="29"/>
-      <c r="B151" s="29"/>
-      <c r="C151" s="27"/>
+      <c r="A151" s="30"/>
+      <c r="B151" s="30"/>
+      <c r="C151" s="28"/>
     </row>
     <row r="152">
-      <c r="A152" s="29"/>
-      <c r="B152" s="29"/>
-      <c r="C152" s="27"/>
+      <c r="A152" s="30"/>
+      <c r="B152" s="30"/>
+      <c r="C152" s="28"/>
     </row>
     <row r="153">
-      <c r="A153" s="29"/>
-      <c r="B153" s="29"/>
-      <c r="C153" s="27"/>
+      <c r="A153" s="30"/>
+      <c r="B153" s="30"/>
+      <c r="C153" s="28"/>
     </row>
     <row r="154">
-      <c r="A154" s="29"/>
-      <c r="B154" s="29"/>
-      <c r="C154" s="27"/>
+      <c r="A154" s="30"/>
+      <c r="B154" s="30"/>
+      <c r="C154" s="28"/>
     </row>
     <row r="155">
-      <c r="A155" s="29"/>
-      <c r="B155" s="29"/>
-      <c r="C155" s="27"/>
+      <c r="A155" s="30"/>
+      <c r="B155" s="30"/>
+      <c r="C155" s="28"/>
     </row>
     <row r="156">
-      <c r="A156" s="29"/>
-      <c r="B156" s="29"/>
-      <c r="C156" s="27"/>
+      <c r="A156" s="30"/>
+      <c r="B156" s="30"/>
+      <c r="C156" s="28"/>
     </row>
     <row r="157">
-      <c r="A157" s="29"/>
-      <c r="B157" s="29"/>
-      <c r="C157" s="27"/>
+      <c r="A157" s="30"/>
+      <c r="B157" s="30"/>
+      <c r="C157" s="28"/>
     </row>
     <row r="158">
-      <c r="A158" s="29"/>
-      <c r="B158" s="29"/>
-      <c r="C158" s="27"/>
+      <c r="A158" s="30"/>
+      <c r="B158" s="30"/>
+      <c r="C158" s="28"/>
     </row>
     <row r="159">
-      <c r="A159" s="29"/>
-      <c r="B159" s="29"/>
+      <c r="A159" s="30"/>
+      <c r="B159" s="30"/>
     </row>
     <row r="160">
-      <c r="A160" s="29"/>
-      <c r="B160" s="29"/>
+      <c r="A160" s="30"/>
+      <c r="B160" s="30"/>
     </row>
     <row r="161">
-      <c r="A161" s="29"/>
-      <c r="B161" s="29"/>
+      <c r="A161" s="30"/>
+      <c r="B161" s="30"/>
     </row>
     <row r="162">
-      <c r="A162" s="29"/>
-      <c r="B162" s="29"/>
+      <c r="A162" s="30"/>
+      <c r="B162" s="30"/>
     </row>
     <row r="163">
-      <c r="A163" s="29"/>
-      <c r="B163" s="29"/>
+      <c r="A163" s="30"/>
+      <c r="B163" s="30"/>
     </row>
     <row r="164">
-      <c r="A164" s="29"/>
-      <c r="B164" s="29"/>
+      <c r="A164" s="30"/>
+      <c r="B164" s="30"/>
     </row>
     <row r="165">
-      <c r="A165" s="29"/>
-      <c r="B165" s="29"/>
+      <c r="A165" s="30"/>
+      <c r="B165" s="30"/>
     </row>
     <row r="166">
-      <c r="A166" s="29"/>
-      <c r="B166" s="29"/>
+      <c r="A166" s="30"/>
+      <c r="B166" s="30"/>
     </row>
     <row r="167">
-      <c r="A167" s="29"/>
-      <c r="B167" s="29"/>
+      <c r="A167" s="30"/>
+      <c r="B167" s="30"/>
     </row>
     <row r="168">
-      <c r="A168" s="29"/>
-      <c r="B168" s="29"/>
+      <c r="A168" s="30"/>
+      <c r="B168" s="30"/>
     </row>
     <row r="169">
-      <c r="A169" s="29"/>
-      <c r="B169" s="29"/>
+      <c r="A169" s="30"/>
+      <c r="B169" s="30"/>
     </row>
     <row r="170">
-      <c r="A170" s="29"/>
-      <c r="B170" s="29"/>
+      <c r="A170" s="30"/>
+      <c r="B170" s="30"/>
     </row>
     <row r="171">
-      <c r="A171" s="29"/>
-      <c r="B171" s="29"/>
+      <c r="A171" s="30"/>
+      <c r="B171" s="30"/>
     </row>
     <row r="172">
-      <c r="A172" s="29"/>
-      <c r="B172" s="29"/>
+      <c r="A172" s="30"/>
+      <c r="B172" s="30"/>
     </row>
     <row r="173">
-      <c r="A173" s="29"/>
-      <c r="B173" s="29"/>
+      <c r="A173" s="30"/>
+      <c r="B173" s="30"/>
     </row>
     <row r="174">
-      <c r="A174" s="29"/>
-      <c r="B174" s="29"/>
+      <c r="A174" s="30"/>
+      <c r="B174" s="30"/>
     </row>
     <row r="175">
-      <c r="A175" s="29"/>
-      <c r="B175" s="29"/>
+      <c r="A175" s="30"/>
+      <c r="B175" s="30"/>
     </row>
     <row r="176">
-      <c r="A176" s="29"/>
-      <c r="B176" s="29"/>
+      <c r="A176" s="30"/>
+      <c r="B176" s="30"/>
     </row>
     <row r="177">
-      <c r="A177" s="29"/>
-      <c r="B177" s="29"/>
+      <c r="A177" s="30"/>
+      <c r="B177" s="30"/>
     </row>
     <row r="178">
-      <c r="A178" s="29"/>
-      <c r="B178" s="29"/>
+      <c r="A178" s="30"/>
+      <c r="B178" s="30"/>
     </row>
     <row r="179">
-      <c r="A179" s="29"/>
-      <c r="B179" s="29"/>
+      <c r="A179" s="30"/>
+      <c r="B179" s="30"/>
     </row>
     <row r="180">
-      <c r="A180" s="29"/>
-      <c r="B180" s="29"/>
+      <c r="A180" s="30"/>
+      <c r="B180" s="30"/>
     </row>
     <row r="181">
-      <c r="A181" s="29"/>
-      <c r="B181" s="29"/>
+      <c r="A181" s="30"/>
+      <c r="B181" s="30"/>
     </row>
     <row r="182">
-      <c r="A182" s="29"/>
-      <c r="B182" s="29"/>
+      <c r="A182" s="30"/>
+      <c r="B182" s="30"/>
     </row>
     <row r="183">
-      <c r="A183" s="29"/>
-      <c r="B183" s="29"/>
+      <c r="A183" s="30"/>
+      <c r="B183" s="30"/>
     </row>
     <row r="184">
-      <c r="A184" s="29"/>
-      <c r="B184" s="29"/>
+      <c r="A184" s="30"/>
+      <c r="B184" s="30"/>
     </row>
     <row r="185">
-      <c r="A185" s="29"/>
-      <c r="B185" s="29"/>
+      <c r="A185" s="30"/>
+      <c r="B185" s="30"/>
     </row>
     <row r="186">
-      <c r="A186" s="29"/>
-      <c r="B186" s="29"/>
+      <c r="A186" s="30"/>
+      <c r="B186" s="30"/>
     </row>
     <row r="187">
-      <c r="A187" s="29"/>
-      <c r="B187" s="29"/>
+      <c r="A187" s="30"/>
+      <c r="B187" s="30"/>
     </row>
     <row r="188">
-      <c r="A188" s="29"/>
-      <c r="B188" s="29"/>
+      <c r="A188" s="30"/>
+      <c r="B188" s="30"/>
     </row>
     <row r="189">
-      <c r="A189" s="29"/>
-      <c r="B189" s="29"/>
+      <c r="A189" s="30"/>
+      <c r="B189" s="30"/>
     </row>
     <row r="190">
-      <c r="A190" s="29"/>
-      <c r="B190" s="29"/>
+      <c r="A190" s="30"/>
+      <c r="B190" s="30"/>
     </row>
     <row r="191">
-      <c r="A191" s="29"/>
-      <c r="B191" s="29"/>
+      <c r="A191" s="30"/>
+      <c r="B191" s="30"/>
     </row>
     <row r="192">
-      <c r="A192" s="29"/>
-      <c r="B192" s="29"/>
+      <c r="A192" s="30"/>
+      <c r="B192" s="30"/>
     </row>
     <row r="193">
-      <c r="A193" s="29"/>
-      <c r="B193" s="29"/>
+      <c r="A193" s="30"/>
+      <c r="B193" s="30"/>
     </row>
     <row r="194">
-      <c r="A194" s="29"/>
-      <c r="B194" s="29"/>
+      <c r="A194" s="30"/>
+      <c r="B194" s="30"/>
     </row>
     <row r="195">
-      <c r="A195" s="29"/>
-      <c r="B195" s="29"/>
+      <c r="A195" s="30"/>
+      <c r="B195" s="30"/>
     </row>
     <row r="196">
-      <c r="A196" s="29"/>
-      <c r="B196" s="29"/>
+      <c r="A196" s="30"/>
+      <c r="B196" s="30"/>
     </row>
     <row r="197">
-      <c r="A197" s="29"/>
-      <c r="B197" s="29"/>
+      <c r="A197" s="30"/>
+      <c r="B197" s="30"/>
     </row>
     <row r="198">
-      <c r="A198" s="29"/>
-      <c r="B198" s="29"/>
+      <c r="A198" s="30"/>
+      <c r="B198" s="30"/>
     </row>
     <row r="199">
-      <c r="A199" s="29"/>
-      <c r="B199" s="29"/>
+      <c r="A199" s="30"/>
+      <c r="B199" s="30"/>
     </row>
     <row r="200">
-      <c r="A200" s="29"/>
-      <c r="B200" s="29"/>
+      <c r="A200" s="30"/>
+      <c r="B200" s="30"/>
     </row>
     <row r="201">
-      <c r="A201" s="29"/>
-      <c r="B201" s="29"/>
+      <c r="A201" s="30"/>
+      <c r="B201" s="30"/>
     </row>
     <row r="202">
-      <c r="A202" s="29"/>
-      <c r="B202" s="29"/>
+      <c r="A202" s="30"/>
+      <c r="B202" s="30"/>
     </row>
     <row r="203">
-      <c r="A203" s="29"/>
-      <c r="B203" s="29"/>
+      <c r="A203" s="30"/>
+      <c r="B203" s="30"/>
     </row>
     <row r="204">
-      <c r="A204" s="29"/>
-      <c r="B204" s="29"/>
+      <c r="A204" s="30"/>
+      <c r="B204" s="30"/>
     </row>
     <row r="205">
-      <c r="A205" s="29"/>
-      <c r="B205" s="29"/>
+      <c r="A205" s="30"/>
+      <c r="B205" s="30"/>
     </row>
     <row r="206">
-      <c r="A206" s="29"/>
-      <c r="B206" s="29"/>
+      <c r="A206" s="30"/>
+      <c r="B206" s="30"/>
     </row>
     <row r="207">
-      <c r="A207" s="29"/>
-      <c r="B207" s="29"/>
+      <c r="A207" s="30"/>
+      <c r="B207" s="30"/>
     </row>
     <row r="208">
-      <c r="A208" s="29"/>
-      <c r="B208" s="29"/>
+      <c r="A208" s="30"/>
+      <c r="B208" s="30"/>
     </row>
     <row r="209">
-      <c r="A209" s="29"/>
-      <c r="B209" s="29"/>
+      <c r="A209" s="30"/>
+      <c r="B209" s="30"/>
     </row>
     <row r="210">
-      <c r="A210" s="29"/>
-      <c r="B210" s="29"/>
+      <c r="A210" s="30"/>
+      <c r="B210" s="30"/>
     </row>
     <row r="211">
-      <c r="A211" s="29"/>
-      <c r="B211" s="29"/>
+      <c r="A211" s="30"/>
+      <c r="B211" s="30"/>
     </row>
     <row r="212">
-      <c r="A212" s="29"/>
-      <c r="B212" s="29"/>
+      <c r="A212" s="30"/>
+      <c r="B212" s="30"/>
     </row>
     <row r="213">
-      <c r="A213" s="29"/>
-      <c r="B213" s="29"/>
+      <c r="A213" s="30"/>
+      <c r="B213" s="30"/>
     </row>
     <row r="214">
-      <c r="A214" s="29"/>
-      <c r="B214" s="29"/>
+      <c r="A214" s="30"/>
+      <c r="B214" s="30"/>
     </row>
     <row r="215">
-      <c r="A215" s="29"/>
-      <c r="B215" s="29"/>
+      <c r="A215" s="30"/>
+      <c r="B215" s="30"/>
     </row>
     <row r="216">
-      <c r="A216" s="29"/>
-      <c r="B216" s="29"/>
+      <c r="A216" s="30"/>
+      <c r="B216" s="30"/>
     </row>
     <row r="217">
-      <c r="A217" s="29"/>
-      <c r="B217" s="29"/>
+      <c r="A217" s="30"/>
+      <c r="B217" s="30"/>
     </row>
     <row r="218">
-      <c r="A218" s="29"/>
-      <c r="B218" s="29"/>
+      <c r="A218" s="30"/>
+      <c r="B218" s="30"/>
     </row>
     <row r="219">
-      <c r="A219" s="29"/>
-      <c r="B219" s="29"/>
+      <c r="A219" s="30"/>
+      <c r="B219" s="30"/>
     </row>
     <row r="220">
-      <c r="A220" s="29"/>
-      <c r="B220" s="29"/>
+      <c r="A220" s="30"/>
+      <c r="B220" s="30"/>
     </row>
     <row r="221">
-      <c r="A221" s="29"/>
-      <c r="B221" s="29"/>
+      <c r="A221" s="30"/>
+      <c r="B221" s="30"/>
     </row>
     <row r="222">
-      <c r="A222" s="29"/>
-      <c r="B222" s="29"/>
+      <c r="A222" s="30"/>
+      <c r="B222" s="30"/>
     </row>
     <row r="223">
-      <c r="A223" s="29"/>
-      <c r="B223" s="29"/>
+      <c r="A223" s="30"/>
+      <c r="B223" s="30"/>
     </row>
     <row r="224">
-      <c r="A224" s="29"/>
-      <c r="B224" s="29"/>
+      <c r="A224" s="30"/>
+      <c r="B224" s="30"/>
     </row>
     <row r="225">
-      <c r="A225" s="29"/>
-      <c r="B225" s="29"/>
+      <c r="A225" s="30"/>
+      <c r="B225" s="30"/>
     </row>
     <row r="226">
-      <c r="A226" s="29"/>
-      <c r="B226" s="29"/>
+      <c r="A226" s="30"/>
+      <c r="B226" s="30"/>
     </row>
     <row r="227">
-      <c r="A227" s="29"/>
-      <c r="B227" s="29"/>
+      <c r="A227" s="30"/>
+      <c r="B227" s="30"/>
     </row>
     <row r="228">
-      <c r="A228" s="29"/>
-      <c r="B228" s="29"/>
+      <c r="A228" s="30"/>
+      <c r="B228" s="30"/>
     </row>
     <row r="229">
-      <c r="A229" s="29"/>
-      <c r="B229" s="29"/>
+      <c r="A229" s="30"/>
+      <c r="B229" s="30"/>
     </row>
     <row r="230">
-      <c r="A230" s="29"/>
-      <c r="B230" s="29"/>
+      <c r="A230" s="30"/>
+      <c r="B230" s="30"/>
     </row>
     <row r="231">
-      <c r="A231" s="29"/>
-      <c r="B231" s="29"/>
+      <c r="A231" s="30"/>
+      <c r="B231" s="30"/>
     </row>
     <row r="232">
-      <c r="A232" s="29"/>
-      <c r="B232" s="29"/>
+      <c r="A232" s="30"/>
+      <c r="B232" s="30"/>
     </row>
     <row r="233">
-      <c r="A233" s="29"/>
-      <c r="B233" s="29"/>
+      <c r="A233" s="30"/>
+      <c r="B233" s="30"/>
     </row>
     <row r="234">
-      <c r="A234" s="29"/>
-      <c r="B234" s="29"/>
+      <c r="A234" s="30"/>
+      <c r="B234" s="30"/>
     </row>
     <row r="235">
-      <c r="A235" s="29"/>
-      <c r="B235" s="29"/>
+      <c r="A235" s="30"/>
+      <c r="B235" s="30"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -6921,2034 +7016,2034 @@
     <col customWidth="1" min="2" max="2" width="4.33203125"/>
     <col bestFit="1" min="3" max="3" width="35.77734375"/>
     <col customWidth="1" min="4" max="11" width="3.44140625"/>
-    <col customWidth="1" min="12" max="12" style="30" width="6"/>
+    <col customWidth="1" min="12" max="12" style="31" width="6"/>
     <col customWidth="1" min="13" max="22" width="3.44140625"/>
-    <col customWidth="1" min="23" max="23" style="30" width="6"/>
+    <col customWidth="1" min="23" max="23" style="31" width="6"/>
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
-    <col customWidth="1" min="30" max="30" style="30" width="6"/>
+    <col customWidth="1" min="30" max="30" style="31" width="6"/>
     <col customWidth="1" min="31" max="39" width="3.44140625"/>
     <col bestFit="1" customWidth="1" min="40" max="40" width="13.88671875"/>
     <col customWidth="1" min="41" max="47" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="31" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="B1" s="32" t="s">
+    <row r="1" s="32" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="B1" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="G1" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="37" t="s">
+      <c r="H1" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="I1" s="34" t="s">
+      <c r="I1" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="34" t="s">
+      <c r="J1" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="L1" s="38" t="s">
+      <c r="L1" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="M1" s="34" t="s">
+      <c r="M1" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="N1" s="36" t="s">
+      <c r="N1" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="37" t="s">
+      <c r="O1" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="P1" s="34" t="s">
+      <c r="P1" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="34" t="s">
+      <c r="Q1" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="T1" s="34" t="s">
+      <c r="T1" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="U1" s="34" t="s">
+      <c r="U1" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="V1" s="36" t="s">
+      <c r="V1" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="W1" s="39" t="s">
+      <c r="W1" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="X1" s="34" t="s">
+      <c r="X1" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="Y1" s="34" t="s">
+      <c r="Y1" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="Z1" s="36" t="s">
+      <c r="Z1" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="AA1" s="40" t="s">
+      <c r="AA1" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="AB1" s="41" t="s">
+      <c r="AB1" s="42" t="s">
         <v>95</v>
       </c>
-      <c r="AC1" s="41" t="s">
+      <c r="AC1" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="AD1" s="38" t="s">
+      <c r="AD1" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="AE1" s="42" t="s">
+      <c r="AE1" s="43" t="s">
         <v>98</v>
       </c>
-      <c r="AF1" s="43" t="s">
+      <c r="AF1" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="AG1" s="44" t="s">
+      <c r="AG1" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="AH1" s="44" t="s">
+      <c r="AH1" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="AI1" s="44" t="s">
+      <c r="AI1" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="AJ1" s="44" t="s">
+      <c r="AJ1" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="AK1" s="41" t="s">
+      <c r="AK1" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="AL1" s="45"/>
-      <c r="AM1" s="45"/>
-      <c r="AN1" s="45"/>
-      <c r="AO1" s="45"/>
-      <c r="AP1" s="45"/>
-      <c r="AQ1" s="45"/>
-      <c r="AR1" s="45"/>
-      <c r="AS1" s="45"/>
-      <c r="AT1" s="45"/>
-      <c r="AU1" s="45"/>
+      <c r="AL1" s="46"/>
+      <c r="AM1" s="46"/>
+      <c r="AN1" s="46"/>
+      <c r="AO1" s="46"/>
+      <c r="AP1" s="46"/>
+      <c r="AQ1" s="46"/>
+      <c r="AR1" s="46"/>
+      <c r="AS1" s="46"/>
+      <c r="AT1" s="46"/>
+      <c r="AU1" s="46"/>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="53"/>
-      <c r="W2" s="55"/>
-      <c r="X2" s="48"/>
-      <c r="Y2" s="48"/>
-      <c r="Z2" s="53"/>
-      <c r="AA2" s="54"/>
-      <c r="AB2" s="48"/>
-      <c r="AC2" s="48"/>
-      <c r="AD2" s="52"/>
-      <c r="AE2" s="53"/>
-      <c r="AF2" s="54"/>
-      <c r="AG2" s="48"/>
-      <c r="AH2" s="48"/>
-      <c r="AI2" s="48"/>
-      <c r="AJ2" s="48"/>
-      <c r="AK2" s="48"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
+      <c r="V2" s="54"/>
+      <c r="W2" s="56"/>
+      <c r="X2" s="49"/>
+      <c r="Y2" s="49"/>
+      <c r="Z2" s="54"/>
+      <c r="AA2" s="55"/>
+      <c r="AB2" s="49"/>
+      <c r="AC2" s="49"/>
+      <c r="AD2" s="53"/>
+      <c r="AE2" s="54"/>
+      <c r="AF2" s="55"/>
+      <c r="AG2" s="49"/>
+      <c r="AH2" s="49"/>
+      <c r="AI2" s="49"/>
+      <c r="AJ2" s="49"/>
+      <c r="AK2" s="49"/>
     </row>
     <row r="3" ht="12" customHeight="1">
-      <c r="B3" s="46"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="48"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="54"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="53"/>
-      <c r="W3" s="55"/>
-      <c r="X3" s="48"/>
-      <c r="Y3" s="48"/>
-      <c r="Z3" s="53"/>
-      <c r="AA3" s="54"/>
-      <c r="AB3" s="48"/>
-      <c r="AC3" s="48"/>
-      <c r="AD3" s="52"/>
-      <c r="AE3" s="53"/>
-      <c r="AF3" s="54"/>
-      <c r="AG3" s="48"/>
-      <c r="AH3" s="48"/>
-      <c r="AI3" s="48"/>
-      <c r="AJ3" s="48"/>
-      <c r="AK3" s="48"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="55"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="49"/>
+      <c r="T3" s="49"/>
+      <c r="U3" s="49"/>
+      <c r="V3" s="54"/>
+      <c r="W3" s="56"/>
+      <c r="X3" s="49"/>
+      <c r="Y3" s="49"/>
+      <c r="Z3" s="54"/>
+      <c r="AA3" s="55"/>
+      <c r="AB3" s="49"/>
+      <c r="AC3" s="49"/>
+      <c r="AD3" s="53"/>
+      <c r="AE3" s="54"/>
+      <c r="AF3" s="55"/>
+      <c r="AG3" s="49"/>
+      <c r="AH3" s="49"/>
+      <c r="AI3" s="49"/>
+      <c r="AJ3" s="49"/>
+      <c r="AK3" s="49"/>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="46"/>
-      <c r="C4" s="47" t="s">
+      <c r="B4" s="47"/>
+      <c r="C4" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="48"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="53"/>
-      <c r="W4" s="55"/>
-      <c r="X4" s="48"/>
-      <c r="Y4" s="48"/>
-      <c r="Z4" s="53"/>
-      <c r="AA4" s="54"/>
-      <c r="AB4" s="48"/>
-      <c r="AC4" s="48"/>
-      <c r="AD4" s="52"/>
-      <c r="AE4" s="53"/>
-      <c r="AF4" s="54"/>
-      <c r="AG4" s="48"/>
-      <c r="AH4" s="48"/>
-      <c r="AI4" s="48"/>
-      <c r="AJ4" s="48"/>
-      <c r="AK4" s="48"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="49"/>
+      <c r="Q4" s="49"/>
+      <c r="R4" s="49"/>
+      <c r="S4" s="49"/>
+      <c r="T4" s="49"/>
+      <c r="U4" s="49"/>
+      <c r="V4" s="54"/>
+      <c r="W4" s="56"/>
+      <c r="X4" s="49"/>
+      <c r="Y4" s="49"/>
+      <c r="Z4" s="54"/>
+      <c r="AA4" s="55"/>
+      <c r="AB4" s="49"/>
+      <c r="AC4" s="49"/>
+      <c r="AD4" s="53"/>
+      <c r="AE4" s="54"/>
+      <c r="AF4" s="55"/>
+      <c r="AG4" s="49"/>
+      <c r="AH4" s="49"/>
+      <c r="AI4" s="49"/>
+      <c r="AJ4" s="49"/>
+      <c r="AK4" s="49"/>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="46"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="48"/>
-      <c r="N5" s="53"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="53"/>
-      <c r="W5" s="55"/>
-      <c r="X5" s="48"/>
-      <c r="Y5" s="48"/>
-      <c r="Z5" s="53"/>
-      <c r="AA5" s="54"/>
-      <c r="AB5" s="48"/>
-      <c r="AC5" s="48"/>
-      <c r="AD5" s="52"/>
-      <c r="AE5" s="53"/>
-      <c r="AF5" s="54"/>
-      <c r="AG5" s="48"/>
-      <c r="AH5" s="48"/>
-      <c r="AI5" s="48"/>
-      <c r="AJ5" s="48"/>
-      <c r="AK5" s="48"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="54"/>
+      <c r="W5" s="56"/>
+      <c r="X5" s="49"/>
+      <c r="Y5" s="49"/>
+      <c r="Z5" s="54"/>
+      <c r="AA5" s="55"/>
+      <c r="AB5" s="49"/>
+      <c r="AC5" s="49"/>
+      <c r="AD5" s="53"/>
+      <c r="AE5" s="54"/>
+      <c r="AF5" s="55"/>
+      <c r="AG5" s="49"/>
+      <c r="AH5" s="49"/>
+      <c r="AI5" s="49"/>
+      <c r="AJ5" s="49"/>
+      <c r="AK5" s="49"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="46"/>
-      <c r="C6" s="47" t="s">
+      <c r="B6" s="47"/>
+      <c r="C6" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="48"/>
-      <c r="N6" s="53"/>
-      <c r="O6" s="54"/>
-      <c r="P6" s="48"/>
-      <c r="Q6" s="48"/>
-      <c r="R6" s="48"/>
-      <c r="S6" s="48"/>
-      <c r="T6" s="48"/>
-      <c r="U6" s="48"/>
-      <c r="V6" s="53"/>
-      <c r="W6" s="55"/>
-      <c r="X6" s="48"/>
-      <c r="Y6" s="48"/>
-      <c r="Z6" s="53"/>
-      <c r="AA6" s="54"/>
-      <c r="AB6" s="48"/>
-      <c r="AC6" s="48"/>
-      <c r="AD6" s="52"/>
-      <c r="AE6" s="50"/>
-      <c r="AF6" s="51"/>
-      <c r="AG6" s="62"/>
-      <c r="AH6" s="62"/>
-      <c r="AI6" s="62"/>
-      <c r="AJ6" s="62"/>
-      <c r="AK6" s="62"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="49"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="54"/>
+      <c r="O6" s="55"/>
+      <c r="P6" s="49"/>
+      <c r="Q6" s="49"/>
+      <c r="R6" s="49"/>
+      <c r="S6" s="49"/>
+      <c r="T6" s="49"/>
+      <c r="U6" s="49"/>
+      <c r="V6" s="54"/>
+      <c r="W6" s="56"/>
+      <c r="X6" s="49"/>
+      <c r="Y6" s="49"/>
+      <c r="Z6" s="54"/>
+      <c r="AA6" s="55"/>
+      <c r="AB6" s="49"/>
+      <c r="AC6" s="49"/>
+      <c r="AD6" s="53"/>
+      <c r="AE6" s="51"/>
+      <c r="AF6" s="52"/>
+      <c r="AG6" s="63"/>
+      <c r="AH6" s="63"/>
+      <c r="AI6" s="63"/>
+      <c r="AJ6" s="63"/>
+      <c r="AK6" s="63"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="46"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="61"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="52"/>
-      <c r="M7" s="48"/>
-      <c r="N7" s="53"/>
-      <c r="O7" s="60"/>
-      <c r="P7" s="48"/>
-      <c r="Q7" s="61"/>
-      <c r="R7" s="48"/>
-      <c r="S7" s="48"/>
-      <c r="T7" s="48"/>
-      <c r="U7" s="48"/>
-      <c r="V7" s="53"/>
-      <c r="W7" s="55"/>
-      <c r="X7" s="48"/>
-      <c r="Y7" s="48"/>
-      <c r="Z7" s="53"/>
-      <c r="AA7" s="54"/>
-      <c r="AB7" s="48"/>
-      <c r="AC7" s="48"/>
-      <c r="AD7" s="52"/>
-      <c r="AE7" s="53"/>
-      <c r="AF7" s="54"/>
-      <c r="AG7" s="48"/>
-      <c r="AH7" s="48"/>
-      <c r="AI7" s="48"/>
-      <c r="AJ7" s="48"/>
-      <c r="AK7" s="48"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="53"/>
+      <c r="M7" s="49"/>
+      <c r="N7" s="54"/>
+      <c r="O7" s="61"/>
+      <c r="P7" s="49"/>
+      <c r="Q7" s="62"/>
+      <c r="R7" s="49"/>
+      <c r="S7" s="49"/>
+      <c r="T7" s="49"/>
+      <c r="U7" s="49"/>
+      <c r="V7" s="54"/>
+      <c r="W7" s="56"/>
+      <c r="X7" s="49"/>
+      <c r="Y7" s="49"/>
+      <c r="Z7" s="54"/>
+      <c r="AA7" s="55"/>
+      <c r="AB7" s="49"/>
+      <c r="AC7" s="49"/>
+      <c r="AD7" s="53"/>
+      <c r="AE7" s="54"/>
+      <c r="AF7" s="55"/>
+      <c r="AG7" s="49"/>
+      <c r="AH7" s="49"/>
+      <c r="AI7" s="49"/>
+      <c r="AJ7" s="49"/>
+      <c r="AK7" s="49"/>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="46"/>
-      <c r="C8" s="47" t="s">
+      <c r="B8" s="47"/>
+      <c r="C8" s="48" t="s">
         <v>106</v>
       </c>
-      <c r="D8" s="62"/>
-      <c r="E8" s="62"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="62"/>
-      <c r="K8" s="62"/>
-      <c r="L8" s="52"/>
-      <c r="M8" s="62"/>
-      <c r="N8" s="50"/>
-      <c r="O8" s="51"/>
-      <c r="P8" s="62"/>
-      <c r="Q8" s="62"/>
-      <c r="R8" s="62"/>
-      <c r="S8" s="62"/>
-      <c r="T8" s="62"/>
-      <c r="U8" s="62"/>
-      <c r="V8" s="50"/>
-      <c r="W8" s="55"/>
-      <c r="X8" s="62"/>
-      <c r="Y8" s="62"/>
-      <c r="Z8" s="50"/>
-      <c r="AA8" s="51"/>
-      <c r="AB8" s="62"/>
-      <c r="AC8" s="62"/>
-      <c r="AD8" s="52"/>
-      <c r="AE8" s="50"/>
-      <c r="AF8" s="51"/>
-      <c r="AG8" s="62"/>
-      <c r="AH8" s="62"/>
-      <c r="AI8" s="62"/>
-      <c r="AJ8" s="62"/>
-      <c r="AK8" s="62"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="63"/>
+      <c r="K8" s="63"/>
+      <c r="L8" s="53"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="51"/>
+      <c r="O8" s="52"/>
+      <c r="P8" s="63"/>
+      <c r="Q8" s="63"/>
+      <c r="R8" s="63"/>
+      <c r="S8" s="63"/>
+      <c r="T8" s="63"/>
+      <c r="U8" s="63"/>
+      <c r="V8" s="51"/>
+      <c r="W8" s="56"/>
+      <c r="X8" s="63"/>
+      <c r="Y8" s="63"/>
+      <c r="Z8" s="51"/>
+      <c r="AA8" s="52"/>
+      <c r="AB8" s="63"/>
+      <c r="AC8" s="63"/>
+      <c r="AD8" s="53"/>
+      <c r="AE8" s="51"/>
+      <c r="AF8" s="52"/>
+      <c r="AG8" s="63"/>
+      <c r="AH8" s="63"/>
+      <c r="AI8" s="63"/>
+      <c r="AJ8" s="63"/>
+      <c r="AK8" s="63"/>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="46"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="61"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="52"/>
-      <c r="M9" s="61"/>
-      <c r="N9" s="53"/>
-      <c r="O9" s="60"/>
-      <c r="P9" s="48"/>
-      <c r="Q9" s="61"/>
-      <c r="R9" s="48"/>
-      <c r="S9" s="63"/>
-      <c r="T9" s="48"/>
-      <c r="U9" s="48"/>
-      <c r="V9" s="53"/>
-      <c r="W9" s="55"/>
-      <c r="X9" s="48"/>
-      <c r="Y9" s="48"/>
-      <c r="Z9" s="53"/>
-      <c r="AA9" s="54"/>
-      <c r="AB9" s="48"/>
-      <c r="AC9" s="48"/>
-      <c r="AD9" s="52"/>
-      <c r="AE9" s="53"/>
-      <c r="AF9" s="54"/>
-      <c r="AG9" s="48"/>
-      <c r="AH9" s="48"/>
-      <c r="AI9" s="48"/>
-      <c r="AJ9" s="48"/>
-      <c r="AK9" s="48"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="62"/>
+      <c r="J9" s="62"/>
+      <c r="K9" s="49"/>
+      <c r="L9" s="53"/>
+      <c r="M9" s="62"/>
+      <c r="N9" s="54"/>
+      <c r="O9" s="61"/>
+      <c r="P9" s="49"/>
+      <c r="Q9" s="62"/>
+      <c r="R9" s="49"/>
+      <c r="S9" s="64"/>
+      <c r="T9" s="49"/>
+      <c r="U9" s="49"/>
+      <c r="V9" s="54"/>
+      <c r="W9" s="56"/>
+      <c r="X9" s="49"/>
+      <c r="Y9" s="49"/>
+      <c r="Z9" s="54"/>
+      <c r="AA9" s="55"/>
+      <c r="AB9" s="49"/>
+      <c r="AC9" s="49"/>
+      <c r="AD9" s="53"/>
+      <c r="AE9" s="54"/>
+      <c r="AF9" s="55"/>
+      <c r="AG9" s="49"/>
+      <c r="AH9" s="49"/>
+      <c r="AI9" s="49"/>
+      <c r="AJ9" s="49"/>
+      <c r="AK9" s="49"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="46"/>
-      <c r="C10" s="47" t="s">
+      <c r="B10" s="47"/>
+      <c r="C10" s="48" t="s">
         <v>107</v>
       </c>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="52"/>
-      <c r="M10" s="48"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="54"/>
-      <c r="P10" s="48"/>
-      <c r="Q10" s="48"/>
-      <c r="R10" s="48"/>
-      <c r="S10" s="48"/>
-      <c r="T10" s="48"/>
-      <c r="U10" s="48"/>
-      <c r="V10" s="50"/>
-      <c r="W10" s="55"/>
-      <c r="X10" s="62"/>
-      <c r="Y10" s="62"/>
-      <c r="Z10" s="50"/>
-      <c r="AA10" s="54"/>
-      <c r="AB10" s="48"/>
-      <c r="AC10" s="48"/>
-      <c r="AD10" s="52"/>
-      <c r="AE10" s="53"/>
-      <c r="AF10" s="54"/>
-      <c r="AG10" s="48"/>
-      <c r="AH10" s="48"/>
-      <c r="AI10" s="48"/>
-      <c r="AJ10" s="48"/>
-      <c r="AK10" s="48"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="49"/>
+      <c r="N10" s="54"/>
+      <c r="O10" s="55"/>
+      <c r="P10" s="49"/>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="49"/>
+      <c r="S10" s="49"/>
+      <c r="T10" s="49"/>
+      <c r="U10" s="49"/>
+      <c r="V10" s="51"/>
+      <c r="W10" s="56"/>
+      <c r="X10" s="63"/>
+      <c r="Y10" s="63"/>
+      <c r="Z10" s="51"/>
+      <c r="AA10" s="55"/>
+      <c r="AB10" s="49"/>
+      <c r="AC10" s="49"/>
+      <c r="AD10" s="53"/>
+      <c r="AE10" s="54"/>
+      <c r="AF10" s="55"/>
+      <c r="AG10" s="49"/>
+      <c r="AH10" s="49"/>
+      <c r="AI10" s="49"/>
+      <c r="AJ10" s="49"/>
+      <c r="AK10" s="49"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="46"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="48"/>
-      <c r="L11" s="52"/>
-      <c r="M11" s="48"/>
-      <c r="N11" s="53"/>
-      <c r="O11" s="54"/>
-      <c r="P11" s="48"/>
-      <c r="Q11" s="48"/>
-      <c r="R11" s="48"/>
-      <c r="S11" s="48"/>
-      <c r="T11" s="48"/>
-      <c r="U11" s="48"/>
-      <c r="V11" s="53"/>
-      <c r="W11" s="55"/>
-      <c r="X11" s="48"/>
-      <c r="Y11" s="48"/>
-      <c r="Z11" s="53"/>
-      <c r="AA11" s="54"/>
-      <c r="AB11" s="48"/>
-      <c r="AC11" s="48"/>
-      <c r="AD11" s="52"/>
-      <c r="AE11" s="53"/>
-      <c r="AF11" s="54"/>
-      <c r="AG11" s="48"/>
-      <c r="AH11" s="48"/>
-      <c r="AI11" s="48"/>
-      <c r="AJ11" s="48"/>
-      <c r="AK11" s="48"/>
+      <c r="B11" s="47"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="49"/>
+      <c r="K11" s="49"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="49"/>
+      <c r="N11" s="54"/>
+      <c r="O11" s="55"/>
+      <c r="P11" s="49"/>
+      <c r="Q11" s="49"/>
+      <c r="R11" s="49"/>
+      <c r="S11" s="49"/>
+      <c r="T11" s="49"/>
+      <c r="U11" s="49"/>
+      <c r="V11" s="54"/>
+      <c r="W11" s="56"/>
+      <c r="X11" s="49"/>
+      <c r="Y11" s="49"/>
+      <c r="Z11" s="54"/>
+      <c r="AA11" s="55"/>
+      <c r="AB11" s="49"/>
+      <c r="AC11" s="49"/>
+      <c r="AD11" s="53"/>
+      <c r="AE11" s="54"/>
+      <c r="AF11" s="55"/>
+      <c r="AG11" s="49"/>
+      <c r="AH11" s="49"/>
+      <c r="AI11" s="49"/>
+      <c r="AJ11" s="49"/>
+      <c r="AK11" s="49"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="46"/>
-      <c r="C12" s="47" t="s">
+      <c r="B12" s="47"/>
+      <c r="C12" s="48" t="s">
         <v>108</v>
       </c>
-      <c r="D12" s="48"/>
-      <c r="E12" s="48"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="48"/>
-      <c r="K12" s="48"/>
-      <c r="L12" s="52"/>
-      <c r="M12" s="48"/>
-      <c r="N12" s="53"/>
-      <c r="O12" s="54"/>
-      <c r="P12" s="48"/>
-      <c r="Q12" s="48"/>
-      <c r="R12" s="48"/>
-      <c r="S12" s="48"/>
-      <c r="T12" s="48"/>
-      <c r="U12" s="48"/>
-      <c r="V12" s="53"/>
-      <c r="W12" s="55"/>
-      <c r="X12" s="48"/>
-      <c r="Y12" s="48"/>
-      <c r="Z12" s="53"/>
-      <c r="AA12" s="54"/>
-      <c r="AB12" s="48"/>
-      <c r="AC12" s="48"/>
-      <c r="AD12" s="52"/>
-      <c r="AE12" s="53"/>
-      <c r="AF12" s="51"/>
-      <c r="AG12" s="62"/>
-      <c r="AH12" s="62"/>
-      <c r="AI12" s="62"/>
-      <c r="AJ12" s="62"/>
-      <c r="AK12" s="62"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="49"/>
+      <c r="L12" s="53"/>
+      <c r="M12" s="49"/>
+      <c r="N12" s="54"/>
+      <c r="O12" s="55"/>
+      <c r="P12" s="49"/>
+      <c r="Q12" s="49"/>
+      <c r="R12" s="49"/>
+      <c r="S12" s="49"/>
+      <c r="T12" s="49"/>
+      <c r="U12" s="49"/>
+      <c r="V12" s="54"/>
+      <c r="W12" s="56"/>
+      <c r="X12" s="49"/>
+      <c r="Y12" s="49"/>
+      <c r="Z12" s="54"/>
+      <c r="AA12" s="55"/>
+      <c r="AB12" s="49"/>
+      <c r="AC12" s="49"/>
+      <c r="AD12" s="53"/>
+      <c r="AE12" s="54"/>
+      <c r="AF12" s="52"/>
+      <c r="AG12" s="63"/>
+      <c r="AH12" s="63"/>
+      <c r="AI12" s="63"/>
+      <c r="AJ12" s="63"/>
+      <c r="AK12" s="63"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="46"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="48"/>
-      <c r="K13" s="48"/>
-      <c r="L13" s="52"/>
-      <c r="M13" s="48"/>
-      <c r="N13" s="53"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="48"/>
-      <c r="Q13" s="48"/>
-      <c r="R13" s="48"/>
-      <c r="S13" s="48"/>
-      <c r="T13" s="48"/>
-      <c r="U13" s="48"/>
-      <c r="V13" s="53"/>
-      <c r="W13" s="55"/>
-      <c r="X13" s="48"/>
-      <c r="Y13" s="48"/>
-      <c r="Z13" s="53"/>
-      <c r="AA13" s="54"/>
-      <c r="AB13" s="48"/>
-      <c r="AC13" s="48"/>
-      <c r="AD13" s="52"/>
-      <c r="AE13" s="53"/>
-      <c r="AF13" s="54"/>
-      <c r="AG13" s="48"/>
-      <c r="AH13" s="48"/>
-      <c r="AI13" s="48"/>
-      <c r="AJ13" s="48"/>
-      <c r="AK13" s="48"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="49"/>
+      <c r="K13" s="49"/>
+      <c r="L13" s="53"/>
+      <c r="M13" s="49"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="55"/>
+      <c r="P13" s="49"/>
+      <c r="Q13" s="49"/>
+      <c r="R13" s="49"/>
+      <c r="S13" s="49"/>
+      <c r="T13" s="49"/>
+      <c r="U13" s="49"/>
+      <c r="V13" s="54"/>
+      <c r="W13" s="56"/>
+      <c r="X13" s="49"/>
+      <c r="Y13" s="49"/>
+      <c r="Z13" s="54"/>
+      <c r="AA13" s="55"/>
+      <c r="AB13" s="49"/>
+      <c r="AC13" s="49"/>
+      <c r="AD13" s="53"/>
+      <c r="AE13" s="54"/>
+      <c r="AF13" s="55"/>
+      <c r="AG13" s="49"/>
+      <c r="AH13" s="49"/>
+      <c r="AI13" s="49"/>
+      <c r="AJ13" s="49"/>
+      <c r="AK13" s="49"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="64" t="s">
+      <c r="B14" s="65" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="65" t="s">
+      <c r="C14" s="66" t="s">
         <v>110</v>
       </c>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="67"/>
-      <c r="J14" s="67"/>
-      <c r="K14" s="67"/>
-      <c r="L14" s="52"/>
-      <c r="M14" s="67"/>
-      <c r="N14" s="68"/>
-      <c r="O14" s="66"/>
-      <c r="P14" s="67"/>
-      <c r="Q14" s="67"/>
-      <c r="R14" s="67"/>
-      <c r="S14" s="67"/>
-      <c r="T14" s="67"/>
-      <c r="U14" s="67"/>
-      <c r="V14" s="68"/>
-      <c r="W14" s="55"/>
-      <c r="X14" s="67"/>
-      <c r="Y14" s="67"/>
-      <c r="Z14" s="68"/>
-      <c r="AA14" s="66"/>
-      <c r="AB14" s="67"/>
-      <c r="AC14" s="67"/>
-      <c r="AD14" s="52"/>
-      <c r="AE14" s="68"/>
-      <c r="AF14" s="66"/>
-      <c r="AG14" s="67"/>
-      <c r="AH14" s="67"/>
-      <c r="AI14" s="67"/>
-      <c r="AJ14" s="67"/>
-      <c r="AK14" s="67"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="68"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="53"/>
+      <c r="M14" s="68"/>
+      <c r="N14" s="69"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="68"/>
+      <c r="Q14" s="68"/>
+      <c r="R14" s="68"/>
+      <c r="S14" s="68"/>
+      <c r="T14" s="68"/>
+      <c r="U14" s="68"/>
+      <c r="V14" s="69"/>
+      <c r="W14" s="56"/>
+      <c r="X14" s="68"/>
+      <c r="Y14" s="68"/>
+      <c r="Z14" s="69"/>
+      <c r="AA14" s="67"/>
+      <c r="AB14" s="68"/>
+      <c r="AC14" s="68"/>
+      <c r="AD14" s="53"/>
+      <c r="AE14" s="69"/>
+      <c r="AF14" s="67"/>
+      <c r="AG14" s="68"/>
+      <c r="AH14" s="68"/>
+      <c r="AI14" s="68"/>
+      <c r="AJ14" s="68"/>
+      <c r="AK14" s="68"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="64"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="67"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="67"/>
-      <c r="J15" s="67"/>
-      <c r="K15" s="67"/>
-      <c r="L15" s="52"/>
-      <c r="M15" s="67"/>
-      <c r="N15" s="68"/>
-      <c r="O15" s="66"/>
-      <c r="P15" s="67"/>
-      <c r="Q15" s="67"/>
-      <c r="R15" s="67"/>
-      <c r="S15" s="67"/>
-      <c r="T15" s="67"/>
-      <c r="U15" s="67"/>
-      <c r="V15" s="68"/>
-      <c r="W15" s="55"/>
-      <c r="X15" s="67"/>
-      <c r="Y15" s="67"/>
-      <c r="Z15" s="68"/>
-      <c r="AA15" s="66"/>
-      <c r="AB15" s="67"/>
-      <c r="AC15" s="67"/>
-      <c r="AD15" s="52"/>
-      <c r="AE15" s="68"/>
-      <c r="AF15" s="66"/>
-      <c r="AG15" s="67"/>
-      <c r="AH15" s="67"/>
-      <c r="AI15" s="67"/>
-      <c r="AJ15" s="67"/>
-      <c r="AK15" s="67"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="68"/>
+      <c r="L15" s="53"/>
+      <c r="M15" s="68"/>
+      <c r="N15" s="69"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="68"/>
+      <c r="Q15" s="68"/>
+      <c r="R15" s="68"/>
+      <c r="S15" s="68"/>
+      <c r="T15" s="68"/>
+      <c r="U15" s="68"/>
+      <c r="V15" s="69"/>
+      <c r="W15" s="56"/>
+      <c r="X15" s="68"/>
+      <c r="Y15" s="68"/>
+      <c r="Z15" s="69"/>
+      <c r="AA15" s="67"/>
+      <c r="AB15" s="68"/>
+      <c r="AC15" s="68"/>
+      <c r="AD15" s="53"/>
+      <c r="AE15" s="69"/>
+      <c r="AF15" s="67"/>
+      <c r="AG15" s="68"/>
+      <c r="AH15" s="68"/>
+      <c r="AI15" s="68"/>
+      <c r="AJ15" s="68"/>
+      <c r="AK15" s="68"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="64"/>
-      <c r="C16" s="65" t="s">
+      <c r="B16" s="65"/>
+      <c r="C16" s="66" t="s">
         <v>111</v>
       </c>
-      <c r="D16" s="62"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="68"/>
-      <c r="H16" s="66"/>
-      <c r="I16" s="67"/>
-      <c r="J16" s="67"/>
-      <c r="K16" s="67"/>
-      <c r="L16" s="52"/>
-      <c r="M16" s="67"/>
-      <c r="N16" s="68"/>
-      <c r="O16" s="66"/>
-      <c r="P16" s="67"/>
-      <c r="Q16" s="67"/>
-      <c r="R16" s="67"/>
-      <c r="S16" s="67"/>
-      <c r="T16" s="67"/>
-      <c r="U16" s="67"/>
-      <c r="V16" s="68"/>
-      <c r="W16" s="55"/>
-      <c r="X16" s="67"/>
-      <c r="Y16" s="67"/>
-      <c r="Z16" s="68"/>
-      <c r="AA16" s="66"/>
-      <c r="AB16" s="67"/>
-      <c r="AC16" s="67"/>
-      <c r="AD16" s="52"/>
-      <c r="AE16" s="68"/>
-      <c r="AF16" s="66"/>
-      <c r="AG16" s="67"/>
-      <c r="AH16" s="67"/>
-      <c r="AI16" s="67"/>
-      <c r="AJ16" s="67"/>
-      <c r="AK16" s="67"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="67"/>
+      <c r="I16" s="68"/>
+      <c r="J16" s="68"/>
+      <c r="K16" s="68"/>
+      <c r="L16" s="53"/>
+      <c r="M16" s="68"/>
+      <c r="N16" s="69"/>
+      <c r="O16" s="67"/>
+      <c r="P16" s="68"/>
+      <c r="Q16" s="68"/>
+      <c r="R16" s="68"/>
+      <c r="S16" s="68"/>
+      <c r="T16" s="68"/>
+      <c r="U16" s="68"/>
+      <c r="V16" s="69"/>
+      <c r="W16" s="56"/>
+      <c r="X16" s="68"/>
+      <c r="Y16" s="68"/>
+      <c r="Z16" s="69"/>
+      <c r="AA16" s="67"/>
+      <c r="AB16" s="68"/>
+      <c r="AC16" s="68"/>
+      <c r="AD16" s="53"/>
+      <c r="AE16" s="69"/>
+      <c r="AF16" s="67"/>
+      <c r="AG16" s="68"/>
+      <c r="AH16" s="68"/>
+      <c r="AI16" s="68"/>
+      <c r="AJ16" s="68"/>
+      <c r="AK16" s="68"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="64"/>
-      <c r="C17" s="65"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="70"/>
-      <c r="G17" s="68"/>
-      <c r="H17" s="66"/>
-      <c r="I17" s="67"/>
-      <c r="J17" s="67"/>
-      <c r="K17" s="67"/>
-      <c r="L17" s="52"/>
-      <c r="M17" s="67"/>
-      <c r="N17" s="68"/>
-      <c r="O17" s="66"/>
-      <c r="P17" s="67"/>
-      <c r="Q17" s="67"/>
-      <c r="R17" s="67"/>
-      <c r="S17" s="67"/>
-      <c r="T17" s="67"/>
-      <c r="U17" s="67"/>
-      <c r="V17" s="68"/>
-      <c r="W17" s="55"/>
-      <c r="X17" s="67"/>
-      <c r="Y17" s="67"/>
-      <c r="Z17" s="68"/>
-      <c r="AA17" s="66"/>
-      <c r="AB17" s="67"/>
-      <c r="AC17" s="67"/>
-      <c r="AD17" s="52"/>
-      <c r="AE17" s="68"/>
-      <c r="AF17" s="66"/>
-      <c r="AG17" s="67"/>
-      <c r="AH17" s="67"/>
-      <c r="AI17" s="67"/>
-      <c r="AJ17" s="67"/>
-      <c r="AK17" s="67"/>
+      <c r="B17" s="65"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="67"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
+      <c r="L17" s="53"/>
+      <c r="M17" s="68"/>
+      <c r="N17" s="69"/>
+      <c r="O17" s="67"/>
+      <c r="P17" s="68"/>
+      <c r="Q17" s="68"/>
+      <c r="R17" s="68"/>
+      <c r="S17" s="68"/>
+      <c r="T17" s="68"/>
+      <c r="U17" s="68"/>
+      <c r="V17" s="69"/>
+      <c r="W17" s="56"/>
+      <c r="X17" s="68"/>
+      <c r="Y17" s="68"/>
+      <c r="Z17" s="69"/>
+      <c r="AA17" s="67"/>
+      <c r="AB17" s="68"/>
+      <c r="AC17" s="68"/>
+      <c r="AD17" s="53"/>
+      <c r="AE17" s="69"/>
+      <c r="AF17" s="67"/>
+      <c r="AG17" s="68"/>
+      <c r="AH17" s="68"/>
+      <c r="AI17" s="68"/>
+      <c r="AJ17" s="68"/>
+      <c r="AK17" s="68"/>
       <c r="AN17" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="64"/>
-      <c r="C18" s="65" t="s">
+      <c r="B18" s="65"/>
+      <c r="C18" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="70"/>
-      <c r="G18" s="68"/>
-      <c r="H18" s="66"/>
-      <c r="I18" s="67"/>
-      <c r="J18" s="67"/>
-      <c r="K18" s="67"/>
-      <c r="L18" s="52"/>
-      <c r="M18" s="67"/>
-      <c r="N18" s="68"/>
-      <c r="O18" s="66"/>
-      <c r="P18" s="67"/>
-      <c r="Q18" s="67"/>
-      <c r="R18" s="67"/>
-      <c r="S18" s="67"/>
-      <c r="T18" s="67"/>
-      <c r="U18" s="67"/>
-      <c r="V18" s="68"/>
-      <c r="W18" s="55"/>
-      <c r="X18" s="67"/>
-      <c r="Y18" s="67"/>
-      <c r="Z18" s="68"/>
-      <c r="AA18" s="66"/>
-      <c r="AB18" s="67"/>
-      <c r="AC18" s="67"/>
-      <c r="AD18" s="52"/>
-      <c r="AE18" s="68"/>
-      <c r="AF18" s="66"/>
-      <c r="AG18" s="67"/>
-      <c r="AH18" s="67"/>
-      <c r="AI18" s="67"/>
-      <c r="AJ18" s="67"/>
-      <c r="AK18" s="67"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="67"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="68"/>
+      <c r="K18" s="68"/>
+      <c r="L18" s="53"/>
+      <c r="M18" s="68"/>
+      <c r="N18" s="69"/>
+      <c r="O18" s="67"/>
+      <c r="P18" s="68"/>
+      <c r="Q18" s="68"/>
+      <c r="R18" s="68"/>
+      <c r="S18" s="68"/>
+      <c r="T18" s="68"/>
+      <c r="U18" s="68"/>
+      <c r="V18" s="69"/>
+      <c r="W18" s="56"/>
+      <c r="X18" s="68"/>
+      <c r="Y18" s="68"/>
+      <c r="Z18" s="69"/>
+      <c r="AA18" s="67"/>
+      <c r="AB18" s="68"/>
+      <c r="AC18" s="68"/>
+      <c r="AD18" s="53"/>
+      <c r="AE18" s="69"/>
+      <c r="AF18" s="67"/>
+      <c r="AG18" s="68"/>
+      <c r="AH18" s="68"/>
+      <c r="AI18" s="68"/>
+      <c r="AJ18" s="68"/>
+      <c r="AK18" s="68"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="64"/>
-      <c r="C19" s="65"/>
-      <c r="D19" s="67"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="68"/>
-      <c r="H19" s="66"/>
-      <c r="I19" s="67"/>
-      <c r="J19" s="67"/>
-      <c r="K19" s="67"/>
-      <c r="L19" s="52"/>
-      <c r="M19" s="67"/>
-      <c r="N19" s="68"/>
-      <c r="O19" s="66"/>
-      <c r="P19" s="67"/>
-      <c r="Q19" s="67"/>
-      <c r="R19" s="67"/>
-      <c r="S19" s="67"/>
-      <c r="T19" s="67"/>
-      <c r="U19" s="67"/>
-      <c r="V19" s="68"/>
-      <c r="W19" s="55"/>
-      <c r="X19" s="67"/>
-      <c r="Y19" s="67"/>
-      <c r="Z19" s="68"/>
-      <c r="AA19" s="66"/>
-      <c r="AB19" s="67"/>
-      <c r="AC19" s="67"/>
-      <c r="AD19" s="52"/>
-      <c r="AE19" s="68"/>
-      <c r="AF19" s="66"/>
-      <c r="AG19" s="67"/>
-      <c r="AH19" s="67"/>
-      <c r="AI19" s="67"/>
-      <c r="AJ19" s="67"/>
-      <c r="AK19" s="67"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="72"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="67"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
+      <c r="L19" s="53"/>
+      <c r="M19" s="68"/>
+      <c r="N19" s="69"/>
+      <c r="O19" s="67"/>
+      <c r="P19" s="68"/>
+      <c r="Q19" s="68"/>
+      <c r="R19" s="68"/>
+      <c r="S19" s="68"/>
+      <c r="T19" s="68"/>
+      <c r="U19" s="68"/>
+      <c r="V19" s="69"/>
+      <c r="W19" s="56"/>
+      <c r="X19" s="68"/>
+      <c r="Y19" s="68"/>
+      <c r="Z19" s="69"/>
+      <c r="AA19" s="67"/>
+      <c r="AB19" s="68"/>
+      <c r="AC19" s="68"/>
+      <c r="AD19" s="53"/>
+      <c r="AE19" s="69"/>
+      <c r="AF19" s="67"/>
+      <c r="AG19" s="68"/>
+      <c r="AH19" s="68"/>
+      <c r="AI19" s="68"/>
+      <c r="AJ19" s="68"/>
+      <c r="AK19" s="68"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="64"/>
-      <c r="C20" s="65" t="s">
+      <c r="B20" s="65"/>
+      <c r="C20" s="66" t="s">
         <v>114</v>
       </c>
-      <c r="D20" s="67"/>
-      <c r="E20" s="67"/>
-      <c r="F20" s="70"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="67"/>
-      <c r="K20" s="67"/>
-      <c r="L20" s="52"/>
-      <c r="M20" s="67"/>
-      <c r="N20" s="68"/>
-      <c r="O20" s="66"/>
-      <c r="P20" s="67"/>
-      <c r="Q20" s="67"/>
-      <c r="R20" s="67"/>
-      <c r="S20" s="67"/>
-      <c r="T20" s="67"/>
-      <c r="U20" s="67"/>
-      <c r="V20" s="68"/>
-      <c r="W20" s="55"/>
-      <c r="X20" s="67"/>
-      <c r="Y20" s="67"/>
-      <c r="Z20" s="68"/>
-      <c r="AA20" s="66"/>
-      <c r="AB20" s="67"/>
-      <c r="AC20" s="67"/>
-      <c r="AD20" s="52"/>
-      <c r="AE20" s="68"/>
-      <c r="AF20" s="66"/>
-      <c r="AG20" s="67"/>
-      <c r="AH20" s="67"/>
-      <c r="AI20" s="67"/>
-      <c r="AJ20" s="67"/>
-      <c r="AK20" s="67"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68"/>
+      <c r="L20" s="53"/>
+      <c r="M20" s="68"/>
+      <c r="N20" s="69"/>
+      <c r="O20" s="67"/>
+      <c r="P20" s="68"/>
+      <c r="Q20" s="68"/>
+      <c r="R20" s="68"/>
+      <c r="S20" s="68"/>
+      <c r="T20" s="68"/>
+      <c r="U20" s="68"/>
+      <c r="V20" s="69"/>
+      <c r="W20" s="56"/>
+      <c r="X20" s="68"/>
+      <c r="Y20" s="68"/>
+      <c r="Z20" s="69"/>
+      <c r="AA20" s="67"/>
+      <c r="AB20" s="68"/>
+      <c r="AC20" s="68"/>
+      <c r="AD20" s="53"/>
+      <c r="AE20" s="69"/>
+      <c r="AF20" s="67"/>
+      <c r="AG20" s="68"/>
+      <c r="AH20" s="68"/>
+      <c r="AI20" s="68"/>
+      <c r="AJ20" s="68"/>
+      <c r="AK20" s="68"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="64"/>
-      <c r="C21" s="65"/>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="70"/>
-      <c r="G21" s="68"/>
-      <c r="H21" s="66"/>
-      <c r="I21" s="61"/>
-      <c r="J21" s="67"/>
-      <c r="K21" s="67"/>
-      <c r="L21" s="52"/>
-      <c r="M21" s="67"/>
-      <c r="N21" s="68"/>
-      <c r="O21" s="66"/>
-      <c r="P21" s="67"/>
-      <c r="Q21" s="67"/>
-      <c r="R21" s="67"/>
-      <c r="S21" s="67"/>
-      <c r="T21" s="67"/>
-      <c r="U21" s="67"/>
-      <c r="V21" s="68"/>
-      <c r="W21" s="55"/>
-      <c r="X21" s="67"/>
-      <c r="Y21" s="67"/>
-      <c r="Z21" s="68"/>
-      <c r="AA21" s="66"/>
-      <c r="AB21" s="67"/>
-      <c r="AC21" s="67"/>
-      <c r="AD21" s="52"/>
-      <c r="AE21" s="68"/>
-      <c r="AF21" s="66"/>
-      <c r="AG21" s="67"/>
-      <c r="AH21" s="67"/>
-      <c r="AI21" s="67"/>
-      <c r="AJ21" s="67"/>
-      <c r="AK21" s="67"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="66"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="67"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="68"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="68"/>
+      <c r="N21" s="69"/>
+      <c r="O21" s="67"/>
+      <c r="P21" s="68"/>
+      <c r="Q21" s="68"/>
+      <c r="R21" s="68"/>
+      <c r="S21" s="68"/>
+      <c r="T21" s="68"/>
+      <c r="U21" s="68"/>
+      <c r="V21" s="69"/>
+      <c r="W21" s="56"/>
+      <c r="X21" s="68"/>
+      <c r="Y21" s="68"/>
+      <c r="Z21" s="69"/>
+      <c r="AA21" s="67"/>
+      <c r="AB21" s="68"/>
+      <c r="AC21" s="68"/>
+      <c r="AD21" s="53"/>
+      <c r="AE21" s="69"/>
+      <c r="AF21" s="67"/>
+      <c r="AG21" s="68"/>
+      <c r="AH21" s="68"/>
+      <c r="AI21" s="68"/>
+      <c r="AJ21" s="68"/>
+      <c r="AK21" s="68"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="64"/>
-      <c r="C22" s="65" t="s">
+      <c r="B22" s="65"/>
+      <c r="C22" s="66" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="70"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="67"/>
-      <c r="K22" s="67"/>
-      <c r="L22" s="52"/>
-      <c r="M22" s="67"/>
-      <c r="N22" s="68"/>
-      <c r="O22" s="66"/>
-      <c r="P22" s="67"/>
-      <c r="Q22" s="67"/>
-      <c r="R22" s="67"/>
-      <c r="S22" s="67"/>
-      <c r="T22" s="67"/>
-      <c r="U22" s="67"/>
-      <c r="V22" s="68"/>
-      <c r="W22" s="55"/>
-      <c r="X22" s="67"/>
-      <c r="Y22" s="67"/>
-      <c r="Z22" s="68"/>
-      <c r="AA22" s="66"/>
-      <c r="AB22" s="67"/>
-      <c r="AC22" s="67"/>
-      <c r="AD22" s="52"/>
-      <c r="AE22" s="68"/>
-      <c r="AF22" s="66"/>
-      <c r="AG22" s="67"/>
-      <c r="AH22" s="67"/>
-      <c r="AI22" s="67"/>
-      <c r="AJ22" s="67"/>
-      <c r="AK22" s="67"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="63"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68"/>
+      <c r="L22" s="53"/>
+      <c r="M22" s="68"/>
+      <c r="N22" s="69"/>
+      <c r="O22" s="67"/>
+      <c r="P22" s="68"/>
+      <c r="Q22" s="68"/>
+      <c r="R22" s="68"/>
+      <c r="S22" s="68"/>
+      <c r="T22" s="68"/>
+      <c r="U22" s="68"/>
+      <c r="V22" s="69"/>
+      <c r="W22" s="56"/>
+      <c r="X22" s="68"/>
+      <c r="Y22" s="68"/>
+      <c r="Z22" s="69"/>
+      <c r="AA22" s="67"/>
+      <c r="AB22" s="68"/>
+      <c r="AC22" s="68"/>
+      <c r="AD22" s="53"/>
+      <c r="AE22" s="69"/>
+      <c r="AF22" s="67"/>
+      <c r="AG22" s="68"/>
+      <c r="AH22" s="68"/>
+      <c r="AI22" s="68"/>
+      <c r="AJ22" s="68"/>
+      <c r="AK22" s="68"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="64"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="70"/>
-      <c r="G23" s="68"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="61"/>
-      <c r="J23" s="57"/>
-      <c r="K23" s="67"/>
-      <c r="L23" s="52"/>
-      <c r="M23" s="67"/>
-      <c r="N23" s="68"/>
-      <c r="O23" s="66"/>
-      <c r="P23" s="67"/>
-      <c r="Q23" s="67"/>
-      <c r="R23" s="67"/>
-      <c r="S23" s="67"/>
-      <c r="T23" s="67"/>
-      <c r="U23" s="67"/>
-      <c r="V23" s="68"/>
-      <c r="W23" s="55"/>
-      <c r="X23" s="67"/>
-      <c r="Y23" s="67"/>
-      <c r="Z23" s="68"/>
-      <c r="AA23" s="66"/>
-      <c r="AB23" s="67"/>
-      <c r="AC23" s="67"/>
-      <c r="AD23" s="52"/>
-      <c r="AE23" s="68"/>
-      <c r="AF23" s="66"/>
-      <c r="AG23" s="67"/>
-      <c r="AH23" s="67"/>
-      <c r="AI23" s="67"/>
-      <c r="AJ23" s="67"/>
-      <c r="AK23" s="67"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="69"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="68"/>
+      <c r="L23" s="53"/>
+      <c r="M23" s="68"/>
+      <c r="N23" s="69"/>
+      <c r="O23" s="67"/>
+      <c r="P23" s="68"/>
+      <c r="Q23" s="68"/>
+      <c r="R23" s="68"/>
+      <c r="S23" s="68"/>
+      <c r="T23" s="68"/>
+      <c r="U23" s="68"/>
+      <c r="V23" s="69"/>
+      <c r="W23" s="56"/>
+      <c r="X23" s="68"/>
+      <c r="Y23" s="68"/>
+      <c r="Z23" s="69"/>
+      <c r="AA23" s="67"/>
+      <c r="AB23" s="68"/>
+      <c r="AC23" s="68"/>
+      <c r="AD23" s="53"/>
+      <c r="AE23" s="69"/>
+      <c r="AF23" s="67"/>
+      <c r="AG23" s="68"/>
+      <c r="AH23" s="68"/>
+      <c r="AI23" s="68"/>
+      <c r="AJ23" s="68"/>
+      <c r="AK23" s="68"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="64"/>
-      <c r="C24" s="65" t="s">
+      <c r="B24" s="65"/>
+      <c r="C24" s="66" t="s">
         <v>116</v>
       </c>
-      <c r="D24" s="67"/>
-      <c r="E24" s="67"/>
-      <c r="F24" s="70"/>
-      <c r="G24" s="68"/>
-      <c r="H24" s="66"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="67"/>
-      <c r="K24" s="67"/>
-      <c r="L24" s="52"/>
-      <c r="M24" s="67"/>
-      <c r="N24" s="68"/>
-      <c r="O24" s="66"/>
-      <c r="P24" s="67"/>
-      <c r="Q24" s="67"/>
-      <c r="R24" s="67"/>
-      <c r="S24" s="67"/>
-      <c r="T24" s="67"/>
-      <c r="U24" s="67"/>
-      <c r="V24" s="68"/>
-      <c r="W24" s="55"/>
-      <c r="X24" s="67"/>
-      <c r="Y24" s="67"/>
-      <c r="Z24" s="68"/>
-      <c r="AA24" s="66"/>
-      <c r="AB24" s="67"/>
-      <c r="AC24" s="67"/>
-      <c r="AD24" s="52"/>
-      <c r="AE24" s="68"/>
-      <c r="AF24" s="66"/>
-      <c r="AG24" s="67"/>
-      <c r="AH24" s="67"/>
-      <c r="AI24" s="67"/>
-      <c r="AJ24" s="67"/>
-      <c r="AK24" s="67"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="69"/>
+      <c r="H24" s="67"/>
+      <c r="I24" s="63"/>
+      <c r="J24" s="68"/>
+      <c r="K24" s="68"/>
+      <c r="L24" s="53"/>
+      <c r="M24" s="68"/>
+      <c r="N24" s="69"/>
+      <c r="O24" s="67"/>
+      <c r="P24" s="68"/>
+      <c r="Q24" s="68"/>
+      <c r="R24" s="68"/>
+      <c r="S24" s="68"/>
+      <c r="T24" s="68"/>
+      <c r="U24" s="68"/>
+      <c r="V24" s="69"/>
+      <c r="W24" s="56"/>
+      <c r="X24" s="68"/>
+      <c r="Y24" s="68"/>
+      <c r="Z24" s="69"/>
+      <c r="AA24" s="67"/>
+      <c r="AB24" s="68"/>
+      <c r="AC24" s="68"/>
+      <c r="AD24" s="53"/>
+      <c r="AE24" s="69"/>
+      <c r="AF24" s="67"/>
+      <c r="AG24" s="68"/>
+      <c r="AH24" s="68"/>
+      <c r="AI24" s="68"/>
+      <c r="AJ24" s="68"/>
+      <c r="AK24" s="68"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="64"/>
-      <c r="C25" s="65"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67"/>
-      <c r="F25" s="70"/>
-      <c r="G25" s="68"/>
-      <c r="H25" s="66"/>
-      <c r="I25" s="67"/>
-      <c r="J25" s="57"/>
-      <c r="K25" s="67"/>
-      <c r="L25" s="52"/>
-      <c r="M25" s="67"/>
-      <c r="N25" s="68"/>
-      <c r="O25" s="66"/>
-      <c r="P25" s="67"/>
-      <c r="Q25" s="67"/>
-      <c r="R25" s="67"/>
-      <c r="S25" s="67"/>
-      <c r="T25" s="67"/>
-      <c r="U25" s="67"/>
-      <c r="V25" s="68"/>
-      <c r="W25" s="55"/>
-      <c r="X25" s="67"/>
-      <c r="Y25" s="67"/>
-      <c r="Z25" s="68"/>
-      <c r="AA25" s="66"/>
-      <c r="AB25" s="67"/>
-      <c r="AC25" s="67"/>
-      <c r="AD25" s="52"/>
-      <c r="AE25" s="68"/>
-      <c r="AF25" s="66"/>
-      <c r="AG25" s="67"/>
-      <c r="AH25" s="67"/>
-      <c r="AI25" s="67"/>
-      <c r="AJ25" s="67"/>
-      <c r="AK25" s="67"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="69"/>
+      <c r="H25" s="67"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="58"/>
+      <c r="K25" s="68"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="68"/>
+      <c r="N25" s="69"/>
+      <c r="O25" s="67"/>
+      <c r="P25" s="68"/>
+      <c r="Q25" s="68"/>
+      <c r="R25" s="68"/>
+      <c r="S25" s="68"/>
+      <c r="T25" s="68"/>
+      <c r="U25" s="68"/>
+      <c r="V25" s="69"/>
+      <c r="W25" s="56"/>
+      <c r="X25" s="68"/>
+      <c r="Y25" s="68"/>
+      <c r="Z25" s="69"/>
+      <c r="AA25" s="67"/>
+      <c r="AB25" s="68"/>
+      <c r="AC25" s="68"/>
+      <c r="AD25" s="53"/>
+      <c r="AE25" s="69"/>
+      <c r="AF25" s="67"/>
+      <c r="AG25" s="68"/>
+      <c r="AH25" s="68"/>
+      <c r="AI25" s="68"/>
+      <c r="AJ25" s="68"/>
+      <c r="AK25" s="68"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="46" t="s">
+      <c r="B26" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="C26" s="47" t="s">
+      <c r="C26" s="48" t="s">
         <v>118</v>
       </c>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="48"/>
-      <c r="K26" s="48"/>
-      <c r="L26" s="52"/>
-      <c r="M26" s="48"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="54"/>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="48"/>
-      <c r="R26" s="48"/>
-      <c r="S26" s="48"/>
-      <c r="T26" s="48"/>
-      <c r="U26" s="48"/>
-      <c r="V26" s="53"/>
-      <c r="W26" s="55"/>
-      <c r="X26" s="48"/>
-      <c r="Y26" s="48"/>
-      <c r="Z26" s="53"/>
-      <c r="AA26" s="54"/>
-      <c r="AB26" s="48"/>
-      <c r="AC26" s="48"/>
-      <c r="AD26" s="52"/>
-      <c r="AE26" s="53"/>
-      <c r="AF26" s="54"/>
-      <c r="AG26" s="48"/>
-      <c r="AH26" s="48"/>
-      <c r="AI26" s="48"/>
-      <c r="AJ26" s="48"/>
-      <c r="AK26" s="48"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="63"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="53"/>
+      <c r="M26" s="49"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="55"/>
+      <c r="P26" s="49"/>
+      <c r="Q26" s="49"/>
+      <c r="R26" s="49"/>
+      <c r="S26" s="49"/>
+      <c r="T26" s="49"/>
+      <c r="U26" s="49"/>
+      <c r="V26" s="54"/>
+      <c r="W26" s="56"/>
+      <c r="X26" s="49"/>
+      <c r="Y26" s="49"/>
+      <c r="Z26" s="54"/>
+      <c r="AA26" s="55"/>
+      <c r="AB26" s="49"/>
+      <c r="AC26" s="49"/>
+      <c r="AD26" s="53"/>
+      <c r="AE26" s="54"/>
+      <c r="AF26" s="55"/>
+      <c r="AG26" s="49"/>
+      <c r="AH26" s="49"/>
+      <c r="AI26" s="49"/>
+      <c r="AJ26" s="49"/>
+      <c r="AK26" s="49"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="46"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="59"/>
-      <c r="H27" s="60"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="48"/>
-      <c r="K27" s="48"/>
-      <c r="L27" s="52"/>
-      <c r="M27" s="48"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="54"/>
-      <c r="P27" s="48"/>
-      <c r="Q27" s="48"/>
-      <c r="R27" s="48"/>
-      <c r="S27" s="48"/>
-      <c r="T27" s="48"/>
-      <c r="U27" s="48"/>
-      <c r="V27" s="53"/>
-      <c r="W27" s="55"/>
-      <c r="X27" s="48"/>
-      <c r="Y27" s="48"/>
-      <c r="Z27" s="53"/>
-      <c r="AA27" s="54"/>
-      <c r="AB27" s="48"/>
-      <c r="AC27" s="48"/>
-      <c r="AD27" s="52"/>
-      <c r="AE27" s="53"/>
-      <c r="AF27" s="54"/>
-      <c r="AG27" s="48"/>
-      <c r="AH27" s="48"/>
-      <c r="AI27" s="48"/>
-      <c r="AJ27" s="48"/>
-      <c r="AK27" s="48"/>
+      <c r="B27" s="47"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="49"/>
+      <c r="J27" s="49"/>
+      <c r="K27" s="49"/>
+      <c r="L27" s="53"/>
+      <c r="M27" s="49"/>
+      <c r="N27" s="54"/>
+      <c r="O27" s="55"/>
+      <c r="P27" s="49"/>
+      <c r="Q27" s="49"/>
+      <c r="R27" s="49"/>
+      <c r="S27" s="49"/>
+      <c r="T27" s="49"/>
+      <c r="U27" s="49"/>
+      <c r="V27" s="54"/>
+      <c r="W27" s="56"/>
+      <c r="X27" s="49"/>
+      <c r="Y27" s="49"/>
+      <c r="Z27" s="54"/>
+      <c r="AA27" s="55"/>
+      <c r="AB27" s="49"/>
+      <c r="AC27" s="49"/>
+      <c r="AD27" s="53"/>
+      <c r="AE27" s="54"/>
+      <c r="AF27" s="55"/>
+      <c r="AG27" s="49"/>
+      <c r="AH27" s="49"/>
+      <c r="AI27" s="49"/>
+      <c r="AJ27" s="49"/>
+      <c r="AK27" s="49"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="46"/>
-      <c r="C28" s="47" t="s">
+      <c r="B28" s="47"/>
+      <c r="C28" s="48" t="s">
         <v>119</v>
       </c>
-      <c r="D28" s="48"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="53"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="62"/>
-      <c r="L28" s="52"/>
-      <c r="M28" s="48"/>
-      <c r="N28" s="53"/>
-      <c r="O28" s="54"/>
-      <c r="P28" s="48"/>
-      <c r="Q28" s="48"/>
-      <c r="R28" s="48"/>
-      <c r="S28" s="48"/>
-      <c r="T28" s="48"/>
-      <c r="U28" s="48"/>
-      <c r="V28" s="53"/>
-      <c r="W28" s="55"/>
-      <c r="X28" s="48"/>
-      <c r="Y28" s="48"/>
-      <c r="Z28" s="53"/>
-      <c r="AA28" s="54"/>
-      <c r="AB28" s="48"/>
-      <c r="AC28" s="48"/>
-      <c r="AD28" s="52"/>
-      <c r="AE28" s="53"/>
-      <c r="AF28" s="54"/>
-      <c r="AG28" s="48"/>
-      <c r="AH28" s="48"/>
-      <c r="AI28" s="48"/>
-      <c r="AJ28" s="48"/>
-      <c r="AK28" s="48"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="63"/>
+      <c r="K28" s="63"/>
+      <c r="L28" s="53"/>
+      <c r="M28" s="49"/>
+      <c r="N28" s="54"/>
+      <c r="O28" s="55"/>
+      <c r="P28" s="49"/>
+      <c r="Q28" s="49"/>
+      <c r="R28" s="49"/>
+      <c r="S28" s="49"/>
+      <c r="T28" s="49"/>
+      <c r="U28" s="49"/>
+      <c r="V28" s="54"/>
+      <c r="W28" s="56"/>
+      <c r="X28" s="49"/>
+      <c r="Y28" s="49"/>
+      <c r="Z28" s="54"/>
+      <c r="AA28" s="55"/>
+      <c r="AB28" s="49"/>
+      <c r="AC28" s="49"/>
+      <c r="AD28" s="53"/>
+      <c r="AE28" s="54"/>
+      <c r="AF28" s="55"/>
+      <c r="AG28" s="49"/>
+      <c r="AH28" s="49"/>
+      <c r="AI28" s="49"/>
+      <c r="AJ28" s="49"/>
+      <c r="AK28" s="49"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="46"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="59"/>
-      <c r="H29" s="60"/>
-      <c r="I29" s="48"/>
-      <c r="J29" s="63"/>
-      <c r="K29" s="48"/>
-      <c r="L29" s="52"/>
-      <c r="M29" s="48"/>
-      <c r="N29" s="53"/>
-      <c r="O29" s="54"/>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="48"/>
-      <c r="R29" s="48"/>
-      <c r="S29" s="48"/>
-      <c r="T29" s="48"/>
-      <c r="U29" s="48"/>
-      <c r="V29" s="53"/>
-      <c r="W29" s="55"/>
-      <c r="X29" s="48"/>
-      <c r="Y29" s="48"/>
-      <c r="Z29" s="53"/>
-      <c r="AA29" s="54"/>
-      <c r="AB29" s="48"/>
-      <c r="AC29" s="48"/>
-      <c r="AD29" s="52"/>
-      <c r="AE29" s="53"/>
-      <c r="AF29" s="54"/>
-      <c r="AG29" s="48"/>
-      <c r="AH29" s="48"/>
-      <c r="AI29" s="48"/>
-      <c r="AJ29" s="48"/>
-      <c r="AK29" s="48"/>
+      <c r="B29" s="47"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="60"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="49"/>
+      <c r="J29" s="64"/>
+      <c r="K29" s="49"/>
+      <c r="L29" s="53"/>
+      <c r="M29" s="49"/>
+      <c r="N29" s="54"/>
+      <c r="O29" s="55"/>
+      <c r="P29" s="49"/>
+      <c r="Q29" s="49"/>
+      <c r="R29" s="49"/>
+      <c r="S29" s="49"/>
+      <c r="T29" s="49"/>
+      <c r="U29" s="49"/>
+      <c r="V29" s="54"/>
+      <c r="W29" s="56"/>
+      <c r="X29" s="49"/>
+      <c r="Y29" s="49"/>
+      <c r="Z29" s="54"/>
+      <c r="AA29" s="55"/>
+      <c r="AB29" s="49"/>
+      <c r="AC29" s="49"/>
+      <c r="AD29" s="53"/>
+      <c r="AE29" s="54"/>
+      <c r="AF29" s="55"/>
+      <c r="AG29" s="49"/>
+      <c r="AH29" s="49"/>
+      <c r="AI29" s="49"/>
+      <c r="AJ29" s="49"/>
+      <c r="AK29" s="49"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="46"/>
-      <c r="C30" s="47" t="s">
+      <c r="B30" s="47"/>
+      <c r="C30" s="48" t="s">
         <v>120</v>
       </c>
-      <c r="D30" s="48"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="53"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="62"/>
-      <c r="J30" s="62"/>
-      <c r="K30" s="62"/>
-      <c r="L30" s="52"/>
-      <c r="M30" s="62"/>
-      <c r="N30" s="53"/>
-      <c r="O30" s="54"/>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="48"/>
-      <c r="R30" s="48"/>
-      <c r="S30" s="48"/>
-      <c r="T30" s="48"/>
-      <c r="U30" s="48"/>
-      <c r="V30" s="53"/>
-      <c r="W30" s="55"/>
-      <c r="X30" s="48"/>
-      <c r="Y30" s="48"/>
-      <c r="Z30" s="53"/>
-      <c r="AA30" s="54"/>
-      <c r="AB30" s="48"/>
-      <c r="AC30" s="48"/>
-      <c r="AD30" s="52"/>
-      <c r="AE30" s="53"/>
-      <c r="AF30" s="54"/>
-      <c r="AG30" s="48"/>
-      <c r="AH30" s="48"/>
-      <c r="AI30" s="48"/>
-      <c r="AJ30" s="48"/>
-      <c r="AK30" s="48"/>
+      <c r="D30" s="49"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="63"/>
+      <c r="K30" s="63"/>
+      <c r="L30" s="53"/>
+      <c r="M30" s="63"/>
+      <c r="N30" s="54"/>
+      <c r="O30" s="55"/>
+      <c r="P30" s="49"/>
+      <c r="Q30" s="49"/>
+      <c r="R30" s="49"/>
+      <c r="S30" s="49"/>
+      <c r="T30" s="49"/>
+      <c r="U30" s="49"/>
+      <c r="V30" s="54"/>
+      <c r="W30" s="56"/>
+      <c r="X30" s="49"/>
+      <c r="Y30" s="49"/>
+      <c r="Z30" s="54"/>
+      <c r="AA30" s="55"/>
+      <c r="AB30" s="49"/>
+      <c r="AC30" s="49"/>
+      <c r="AD30" s="53"/>
+      <c r="AE30" s="54"/>
+      <c r="AF30" s="55"/>
+      <c r="AG30" s="49"/>
+      <c r="AH30" s="49"/>
+      <c r="AI30" s="49"/>
+      <c r="AJ30" s="49"/>
+      <c r="AK30" s="49"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="46"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="59"/>
-      <c r="H31" s="60"/>
-      <c r="I31" s="48"/>
-      <c r="J31" s="63"/>
-      <c r="K31" s="63"/>
-      <c r="L31" s="72"/>
-      <c r="M31" s="48"/>
-      <c r="N31" s="59"/>
-      <c r="O31" s="54"/>
-      <c r="P31" s="48"/>
-      <c r="Q31" s="48"/>
-      <c r="R31" s="48"/>
-      <c r="S31" s="48"/>
-      <c r="T31" s="48"/>
-      <c r="U31" s="48"/>
-      <c r="V31" s="53"/>
-      <c r="W31" s="55"/>
-      <c r="X31" s="48"/>
-      <c r="Y31" s="48"/>
-      <c r="Z31" s="53"/>
-      <c r="AA31" s="54"/>
-      <c r="AB31" s="48"/>
-      <c r="AC31" s="48"/>
-      <c r="AD31" s="52"/>
-      <c r="AE31" s="53"/>
-      <c r="AF31" s="54"/>
-      <c r="AG31" s="48"/>
-      <c r="AH31" s="48"/>
-      <c r="AI31" s="48"/>
-      <c r="AJ31" s="48"/>
-      <c r="AK31" s="48"/>
+      <c r="B31" s="47"/>
+      <c r="C31" s="48"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="60"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="49"/>
+      <c r="J31" s="64"/>
+      <c r="K31" s="64"/>
+      <c r="L31" s="73"/>
+      <c r="M31" s="49"/>
+      <c r="N31" s="60"/>
+      <c r="O31" s="55"/>
+      <c r="P31" s="49"/>
+      <c r="Q31" s="49"/>
+      <c r="R31" s="49"/>
+      <c r="S31" s="49"/>
+      <c r="T31" s="49"/>
+      <c r="U31" s="49"/>
+      <c r="V31" s="54"/>
+      <c r="W31" s="56"/>
+      <c r="X31" s="49"/>
+      <c r="Y31" s="49"/>
+      <c r="Z31" s="54"/>
+      <c r="AA31" s="55"/>
+      <c r="AB31" s="49"/>
+      <c r="AC31" s="49"/>
+      <c r="AD31" s="53"/>
+      <c r="AE31" s="54"/>
+      <c r="AF31" s="55"/>
+      <c r="AG31" s="49"/>
+      <c r="AH31" s="49"/>
+      <c r="AI31" s="49"/>
+      <c r="AJ31" s="49"/>
+      <c r="AK31" s="49"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="46"/>
-      <c r="C32" s="47" t="s">
+      <c r="B32" s="47"/>
+      <c r="C32" s="48" t="s">
         <v>121</v>
       </c>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="56"/>
-      <c r="G32" s="53"/>
-      <c r="H32" s="54"/>
-      <c r="I32" s="48"/>
-      <c r="J32" s="48"/>
-      <c r="K32" s="48"/>
-      <c r="L32" s="52"/>
-      <c r="M32" s="62"/>
-      <c r="N32" s="50"/>
-      <c r="O32" s="54"/>
-      <c r="P32" s="48"/>
-      <c r="Q32" s="48"/>
-      <c r="R32" s="48"/>
-      <c r="S32" s="48"/>
-      <c r="T32" s="48"/>
-      <c r="U32" s="48"/>
-      <c r="V32" s="53"/>
-      <c r="W32" s="55"/>
-      <c r="X32" s="48"/>
-      <c r="Y32" s="48"/>
-      <c r="Z32" s="53"/>
-      <c r="AA32" s="54"/>
-      <c r="AB32" s="48"/>
-      <c r="AC32" s="48"/>
-      <c r="AD32" s="52"/>
-      <c r="AE32" s="53"/>
-      <c r="AF32" s="54"/>
-      <c r="AG32" s="48"/>
-      <c r="AH32" s="48"/>
-      <c r="AI32" s="48"/>
-      <c r="AJ32" s="48"/>
-      <c r="AK32" s="48"/>
+      <c r="D32" s="49"/>
+      <c r="E32" s="49"/>
+      <c r="F32" s="57"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="49"/>
+      <c r="J32" s="49"/>
+      <c r="K32" s="49"/>
+      <c r="L32" s="53"/>
+      <c r="M32" s="63"/>
+      <c r="N32" s="51"/>
+      <c r="O32" s="55"/>
+      <c r="P32" s="49"/>
+      <c r="Q32" s="49"/>
+      <c r="R32" s="49"/>
+      <c r="S32" s="49"/>
+      <c r="T32" s="49"/>
+      <c r="U32" s="49"/>
+      <c r="V32" s="54"/>
+      <c r="W32" s="56"/>
+      <c r="X32" s="49"/>
+      <c r="Y32" s="49"/>
+      <c r="Z32" s="54"/>
+      <c r="AA32" s="55"/>
+      <c r="AB32" s="49"/>
+      <c r="AC32" s="49"/>
+      <c r="AD32" s="53"/>
+      <c r="AE32" s="54"/>
+      <c r="AF32" s="55"/>
+      <c r="AG32" s="49"/>
+      <c r="AH32" s="49"/>
+      <c r="AI32" s="49"/>
+      <c r="AJ32" s="49"/>
+      <c r="AK32" s="49"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="46"/>
-      <c r="C33" s="47"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="56"/>
-      <c r="G33" s="53"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="48"/>
-      <c r="J33" s="48"/>
-      <c r="K33" s="48"/>
-      <c r="L33" s="52"/>
-      <c r="M33" s="48"/>
-      <c r="N33" s="59"/>
-      <c r="O33" s="54"/>
-      <c r="P33" s="48"/>
-      <c r="Q33" s="48"/>
-      <c r="R33" s="48"/>
-      <c r="S33" s="48"/>
-      <c r="T33" s="48"/>
-      <c r="U33" s="48"/>
-      <c r="V33" s="53"/>
-      <c r="W33" s="55"/>
-      <c r="X33" s="48"/>
-      <c r="Y33" s="48"/>
-      <c r="Z33" s="53"/>
-      <c r="AA33" s="54"/>
-      <c r="AB33" s="48"/>
-      <c r="AC33" s="48"/>
-      <c r="AD33" s="52"/>
-      <c r="AE33" s="53"/>
-      <c r="AF33" s="54"/>
-      <c r="AG33" s="48"/>
-      <c r="AH33" s="48"/>
-      <c r="AI33" s="48"/>
-      <c r="AJ33" s="48"/>
-      <c r="AK33" s="48"/>
+      <c r="B33" s="47"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="49"/>
+      <c r="J33" s="49"/>
+      <c r="K33" s="49"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="49"/>
+      <c r="N33" s="60"/>
+      <c r="O33" s="55"/>
+      <c r="P33" s="49"/>
+      <c r="Q33" s="49"/>
+      <c r="R33" s="49"/>
+      <c r="S33" s="49"/>
+      <c r="T33" s="49"/>
+      <c r="U33" s="49"/>
+      <c r="V33" s="54"/>
+      <c r="W33" s="56"/>
+      <c r="X33" s="49"/>
+      <c r="Y33" s="49"/>
+      <c r="Z33" s="54"/>
+      <c r="AA33" s="55"/>
+      <c r="AB33" s="49"/>
+      <c r="AC33" s="49"/>
+      <c r="AD33" s="53"/>
+      <c r="AE33" s="54"/>
+      <c r="AF33" s="55"/>
+      <c r="AG33" s="49"/>
+      <c r="AH33" s="49"/>
+      <c r="AI33" s="49"/>
+      <c r="AJ33" s="49"/>
+      <c r="AK33" s="49"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="64" t="s">
+      <c r="B34" s="65" t="s">
         <v>122</v>
       </c>
-      <c r="C34" s="73" t="s">
+      <c r="C34" s="74" t="s">
         <v>123</v>
       </c>
-      <c r="D34" s="67"/>
-      <c r="E34" s="67"/>
-      <c r="F34" s="70"/>
-      <c r="G34" s="68"/>
-      <c r="H34" s="66"/>
-      <c r="I34" s="67"/>
-      <c r="J34" s="67"/>
-      <c r="K34" s="67"/>
-      <c r="L34" s="52"/>
-      <c r="M34" s="62"/>
-      <c r="N34" s="50"/>
-      <c r="O34" s="51"/>
-      <c r="P34" s="62"/>
-      <c r="Q34" s="62"/>
-      <c r="R34" s="62"/>
-      <c r="S34" s="67"/>
-      <c r="T34" s="67"/>
-      <c r="U34" s="67"/>
-      <c r="V34" s="68"/>
-      <c r="W34" s="55"/>
-      <c r="X34" s="67"/>
-      <c r="Y34" s="67"/>
-      <c r="Z34" s="68"/>
-      <c r="AA34" s="66"/>
-      <c r="AB34" s="67"/>
-      <c r="AC34" s="67"/>
-      <c r="AD34" s="52"/>
-      <c r="AE34" s="68"/>
-      <c r="AF34" s="66"/>
-      <c r="AG34" s="67"/>
-      <c r="AH34" s="67"/>
-      <c r="AI34" s="67"/>
-      <c r="AJ34" s="67"/>
-      <c r="AK34" s="67"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="68"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="69"/>
+      <c r="H34" s="67"/>
+      <c r="I34" s="68"/>
+      <c r="J34" s="68"/>
+      <c r="K34" s="68"/>
+      <c r="L34" s="53"/>
+      <c r="M34" s="63"/>
+      <c r="N34" s="51"/>
+      <c r="O34" s="52"/>
+      <c r="P34" s="63"/>
+      <c r="Q34" s="63"/>
+      <c r="R34" s="63"/>
+      <c r="S34" s="68"/>
+      <c r="T34" s="68"/>
+      <c r="U34" s="68"/>
+      <c r="V34" s="69"/>
+      <c r="W34" s="56"/>
+      <c r="X34" s="68"/>
+      <c r="Y34" s="68"/>
+      <c r="Z34" s="69"/>
+      <c r="AA34" s="67"/>
+      <c r="AB34" s="68"/>
+      <c r="AC34" s="68"/>
+      <c r="AD34" s="53"/>
+      <c r="AE34" s="69"/>
+      <c r="AF34" s="67"/>
+      <c r="AG34" s="68"/>
+      <c r="AH34" s="68"/>
+      <c r="AI34" s="68"/>
+      <c r="AJ34" s="68"/>
+      <c r="AK34" s="68"/>
     </row>
     <row r="35" ht="12" customHeight="1">
-      <c r="B35" s="64"/>
-      <c r="C35" s="73"/>
-      <c r="D35" s="67"/>
-      <c r="E35" s="67"/>
-      <c r="F35" s="70"/>
-      <c r="G35" s="68"/>
-      <c r="H35" s="66"/>
-      <c r="I35" s="67"/>
-      <c r="J35" s="67"/>
-      <c r="K35" s="74"/>
-      <c r="L35" s="52"/>
-      <c r="M35" s="67"/>
-      <c r="N35" s="59"/>
-      <c r="O35" s="66"/>
-      <c r="P35" s="61"/>
-      <c r="Q35" s="67"/>
-      <c r="R35" s="75"/>
-      <c r="S35" s="75"/>
-      <c r="T35" s="57"/>
-      <c r="U35" s="67"/>
-      <c r="V35" s="68"/>
-      <c r="W35" s="55"/>
-      <c r="X35" s="67"/>
-      <c r="Y35" s="67"/>
-      <c r="Z35" s="68"/>
-      <c r="AA35" s="66"/>
-      <c r="AB35" s="67"/>
-      <c r="AC35" s="67"/>
-      <c r="AD35" s="52"/>
-      <c r="AE35" s="68"/>
-      <c r="AF35" s="66"/>
-      <c r="AG35" s="67"/>
-      <c r="AH35" s="67"/>
-      <c r="AI35" s="67"/>
-      <c r="AJ35" s="67"/>
-      <c r="AK35" s="67"/>
+      <c r="B35" s="65"/>
+      <c r="C35" s="74"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="67"/>
+      <c r="I35" s="68"/>
+      <c r="J35" s="68"/>
+      <c r="K35" s="75"/>
+      <c r="L35" s="53"/>
+      <c r="M35" s="68"/>
+      <c r="N35" s="60"/>
+      <c r="O35" s="67"/>
+      <c r="P35" s="62"/>
+      <c r="Q35" s="68"/>
+      <c r="R35" s="76"/>
+      <c r="S35" s="76"/>
+      <c r="T35" s="58"/>
+      <c r="U35" s="68"/>
+      <c r="V35" s="69"/>
+      <c r="W35" s="56"/>
+      <c r="X35" s="68"/>
+      <c r="Y35" s="68"/>
+      <c r="Z35" s="69"/>
+      <c r="AA35" s="67"/>
+      <c r="AB35" s="68"/>
+      <c r="AC35" s="68"/>
+      <c r="AD35" s="53"/>
+      <c r="AE35" s="69"/>
+      <c r="AF35" s="67"/>
+      <c r="AG35" s="68"/>
+      <c r="AH35" s="68"/>
+      <c r="AI35" s="68"/>
+      <c r="AJ35" s="68"/>
+      <c r="AK35" s="68"/>
     </row>
     <row r="36" ht="12" customHeight="1">
-      <c r="B36" s="64"/>
-      <c r="C36" s="73" t="s">
+      <c r="B36" s="65"/>
+      <c r="C36" s="74" t="s">
         <v>124</v>
       </c>
-      <c r="D36" s="67"/>
-      <c r="E36" s="67"/>
-      <c r="F36" s="70"/>
-      <c r="G36" s="68"/>
-      <c r="H36" s="66"/>
-      <c r="I36" s="67"/>
-      <c r="J36" s="67"/>
-      <c r="K36" s="67"/>
-      <c r="L36" s="52"/>
-      <c r="M36" s="62"/>
-      <c r="N36" s="50"/>
-      <c r="O36" s="51"/>
-      <c r="P36" s="62"/>
-      <c r="Q36" s="67"/>
-      <c r="R36" s="67"/>
-      <c r="S36" s="67"/>
-      <c r="T36" s="67"/>
-      <c r="U36" s="67"/>
-      <c r="V36" s="68"/>
-      <c r="W36" s="55"/>
-      <c r="X36" s="67"/>
-      <c r="Y36" s="67"/>
-      <c r="Z36" s="68"/>
-      <c r="AA36" s="66"/>
-      <c r="AB36" s="67"/>
-      <c r="AC36" s="67"/>
-      <c r="AD36" s="52"/>
-      <c r="AE36" s="68"/>
-      <c r="AF36" s="66"/>
-      <c r="AG36" s="67"/>
-      <c r="AH36" s="67"/>
-      <c r="AI36" s="67"/>
-      <c r="AJ36" s="67"/>
-      <c r="AK36" s="67"/>
+      <c r="D36" s="68"/>
+      <c r="E36" s="68"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="69"/>
+      <c r="H36" s="67"/>
+      <c r="I36" s="68"/>
+      <c r="J36" s="68"/>
+      <c r="K36" s="68"/>
+      <c r="L36" s="53"/>
+      <c r="M36" s="63"/>
+      <c r="N36" s="51"/>
+      <c r="O36" s="52"/>
+      <c r="P36" s="63"/>
+      <c r="Q36" s="68"/>
+      <c r="R36" s="68"/>
+      <c r="S36" s="68"/>
+      <c r="T36" s="68"/>
+      <c r="U36" s="68"/>
+      <c r="V36" s="69"/>
+      <c r="W36" s="56"/>
+      <c r="X36" s="68"/>
+      <c r="Y36" s="68"/>
+      <c r="Z36" s="69"/>
+      <c r="AA36" s="67"/>
+      <c r="AB36" s="68"/>
+      <c r="AC36" s="68"/>
+      <c r="AD36" s="53"/>
+      <c r="AE36" s="69"/>
+      <c r="AF36" s="67"/>
+      <c r="AG36" s="68"/>
+      <c r="AH36" s="68"/>
+      <c r="AI36" s="68"/>
+      <c r="AJ36" s="68"/>
+      <c r="AK36" s="68"/>
     </row>
     <row r="37" ht="12" customHeight="1">
-      <c r="B37" s="64"/>
-      <c r="C37" s="73"/>
-      <c r="D37" s="67"/>
-      <c r="E37" s="67"/>
-      <c r="F37" s="70"/>
-      <c r="G37" s="68"/>
-      <c r="H37" s="66"/>
-      <c r="I37" s="67"/>
-      <c r="J37" s="67"/>
-      <c r="K37" s="74"/>
-      <c r="L37" s="52"/>
-      <c r="M37" s="67"/>
-      <c r="N37" s="68"/>
-      <c r="O37" s="66"/>
-      <c r="P37" s="61"/>
-      <c r="Q37" s="67"/>
-      <c r="R37" s="75"/>
-      <c r="S37" s="75"/>
-      <c r="T37" s="57"/>
-      <c r="U37" s="67"/>
-      <c r="V37" s="68"/>
-      <c r="W37" s="55"/>
-      <c r="X37" s="67"/>
-      <c r="Y37" s="67"/>
-      <c r="Z37" s="68"/>
-      <c r="AA37" s="66"/>
-      <c r="AB37" s="67"/>
-      <c r="AC37" s="67"/>
-      <c r="AD37" s="52"/>
-      <c r="AE37" s="68"/>
-      <c r="AF37" s="66"/>
-      <c r="AG37" s="67"/>
-      <c r="AH37" s="67"/>
-      <c r="AI37" s="67"/>
-      <c r="AJ37" s="67"/>
-      <c r="AK37" s="67"/>
+      <c r="B37" s="65"/>
+      <c r="C37" s="74"/>
+      <c r="D37" s="68"/>
+      <c r="E37" s="68"/>
+      <c r="F37" s="71"/>
+      <c r="G37" s="69"/>
+      <c r="H37" s="67"/>
+      <c r="I37" s="68"/>
+      <c r="J37" s="68"/>
+      <c r="K37" s="75"/>
+      <c r="L37" s="53"/>
+      <c r="M37" s="68"/>
+      <c r="N37" s="69"/>
+      <c r="O37" s="67"/>
+      <c r="P37" s="62"/>
+      <c r="Q37" s="68"/>
+      <c r="R37" s="76"/>
+      <c r="S37" s="76"/>
+      <c r="T37" s="58"/>
+      <c r="U37" s="68"/>
+      <c r="V37" s="69"/>
+      <c r="W37" s="56"/>
+      <c r="X37" s="68"/>
+      <c r="Y37" s="68"/>
+      <c r="Z37" s="69"/>
+      <c r="AA37" s="67"/>
+      <c r="AB37" s="68"/>
+      <c r="AC37" s="68"/>
+      <c r="AD37" s="53"/>
+      <c r="AE37" s="69"/>
+      <c r="AF37" s="67"/>
+      <c r="AG37" s="68"/>
+      <c r="AH37" s="68"/>
+      <c r="AI37" s="68"/>
+      <c r="AJ37" s="68"/>
+      <c r="AK37" s="68"/>
     </row>
     <row r="38" ht="12" customHeight="1">
-      <c r="B38" s="64"/>
-      <c r="C38" s="73" t="s">
+      <c r="B38" s="65"/>
+      <c r="C38" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="D38" s="67"/>
-      <c r="E38" s="67"/>
-      <c r="F38" s="70"/>
-      <c r="G38" s="68"/>
-      <c r="H38" s="66"/>
-      <c r="I38" s="67"/>
-      <c r="J38" s="67"/>
-      <c r="K38" s="67"/>
-      <c r="L38" s="52"/>
-      <c r="M38" s="67"/>
-      <c r="N38" s="68"/>
-      <c r="O38" s="51"/>
-      <c r="P38" s="62"/>
-      <c r="Q38" s="62"/>
-      <c r="R38" s="62"/>
-      <c r="S38" s="62"/>
-      <c r="T38" s="62"/>
-      <c r="U38" s="62"/>
-      <c r="V38" s="50"/>
-      <c r="W38" s="55"/>
-      <c r="X38" s="62"/>
-      <c r="Y38" s="62"/>
-      <c r="Z38" s="68"/>
-      <c r="AA38" s="66"/>
-      <c r="AB38" s="67"/>
-      <c r="AC38" s="67"/>
-      <c r="AD38" s="52"/>
-      <c r="AE38" s="68"/>
-      <c r="AF38" s="66"/>
-      <c r="AG38" s="67"/>
-      <c r="AH38" s="67"/>
-      <c r="AI38" s="67"/>
-      <c r="AJ38" s="67"/>
-      <c r="AK38" s="67"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="69"/>
+      <c r="H38" s="67"/>
+      <c r="I38" s="68"/>
+      <c r="J38" s="68"/>
+      <c r="K38" s="68"/>
+      <c r="L38" s="53"/>
+      <c r="M38" s="68"/>
+      <c r="N38" s="69"/>
+      <c r="O38" s="52"/>
+      <c r="P38" s="63"/>
+      <c r="Q38" s="63"/>
+      <c r="R38" s="63"/>
+      <c r="S38" s="63"/>
+      <c r="T38" s="63"/>
+      <c r="U38" s="63"/>
+      <c r="V38" s="51"/>
+      <c r="W38" s="56"/>
+      <c r="X38" s="63"/>
+      <c r="Y38" s="63"/>
+      <c r="Z38" s="69"/>
+      <c r="AA38" s="67"/>
+      <c r="AB38" s="68"/>
+      <c r="AC38" s="68"/>
+      <c r="AD38" s="53"/>
+      <c r="AE38" s="69"/>
+      <c r="AF38" s="67"/>
+      <c r="AG38" s="68"/>
+      <c r="AH38" s="68"/>
+      <c r="AI38" s="68"/>
+      <c r="AJ38" s="68"/>
+      <c r="AK38" s="68"/>
     </row>
     <row r="39" ht="12" customHeight="1">
-      <c r="B39" s="64"/>
-      <c r="C39" s="73"/>
-      <c r="D39" s="67"/>
-      <c r="E39" s="67"/>
-      <c r="F39" s="70"/>
-      <c r="G39" s="68"/>
-      <c r="H39" s="66"/>
-      <c r="I39" s="67"/>
-      <c r="J39" s="67"/>
-      <c r="K39" s="67"/>
-      <c r="L39" s="52"/>
-      <c r="M39" s="67"/>
-      <c r="N39" s="68"/>
-      <c r="O39" s="66"/>
-      <c r="P39" s="67"/>
-      <c r="Q39" s="67"/>
-      <c r="R39" s="74"/>
-      <c r="S39" s="74"/>
-      <c r="T39" s="67"/>
-      <c r="U39" s="67"/>
-      <c r="V39" s="68"/>
-      <c r="W39" s="55"/>
-      <c r="X39" s="67"/>
-      <c r="Y39" s="67"/>
-      <c r="Z39" s="68"/>
-      <c r="AA39" s="66"/>
-      <c r="AB39" s="67"/>
-      <c r="AC39" s="67"/>
-      <c r="AD39" s="52"/>
-      <c r="AE39" s="68"/>
-      <c r="AF39" s="66"/>
-      <c r="AG39" s="67"/>
-      <c r="AH39" s="67"/>
-      <c r="AI39" s="67"/>
-      <c r="AJ39" s="67"/>
-      <c r="AK39" s="67"/>
+      <c r="B39" s="65"/>
+      <c r="C39" s="74"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="68"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="69"/>
+      <c r="H39" s="67"/>
+      <c r="I39" s="68"/>
+      <c r="J39" s="68"/>
+      <c r="K39" s="68"/>
+      <c r="L39" s="53"/>
+      <c r="M39" s="68"/>
+      <c r="N39" s="69"/>
+      <c r="O39" s="67"/>
+      <c r="P39" s="68"/>
+      <c r="Q39" s="68"/>
+      <c r="R39" s="75"/>
+      <c r="S39" s="75"/>
+      <c r="T39" s="68"/>
+      <c r="U39" s="68"/>
+      <c r="V39" s="69"/>
+      <c r="W39" s="56"/>
+      <c r="X39" s="68"/>
+      <c r="Y39" s="68"/>
+      <c r="Z39" s="69"/>
+      <c r="AA39" s="67"/>
+      <c r="AB39" s="68"/>
+      <c r="AC39" s="68"/>
+      <c r="AD39" s="53"/>
+      <c r="AE39" s="69"/>
+      <c r="AF39" s="67"/>
+      <c r="AG39" s="68"/>
+      <c r="AH39" s="68"/>
+      <c r="AI39" s="68"/>
+      <c r="AJ39" s="68"/>
+      <c r="AK39" s="68"/>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="B40" s="64"/>
-      <c r="C40" s="73" t="s">
+      <c r="B40" s="65"/>
+      <c r="C40" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="D40" s="67"/>
-      <c r="E40" s="67"/>
-      <c r="F40" s="70"/>
-      <c r="G40" s="68"/>
-      <c r="H40" s="66"/>
-      <c r="I40" s="67"/>
-      <c r="J40" s="67"/>
-      <c r="K40" s="67"/>
-      <c r="L40" s="52"/>
-      <c r="M40" s="67"/>
-      <c r="N40" s="68"/>
-      <c r="O40" s="66"/>
-      <c r="P40" s="67"/>
-      <c r="Q40" s="67"/>
-      <c r="R40" s="62"/>
-      <c r="S40" s="62"/>
-      <c r="T40" s="62"/>
-      <c r="U40" s="62"/>
-      <c r="V40" s="50"/>
-      <c r="W40" s="55"/>
-      <c r="X40" s="62"/>
-      <c r="Y40" s="62"/>
-      <c r="Z40" s="50"/>
-      <c r="AA40" s="51"/>
-      <c r="AB40" s="62"/>
-      <c r="AC40" s="62"/>
-      <c r="AD40" s="52"/>
-      <c r="AE40" s="68"/>
-      <c r="AF40" s="66"/>
-      <c r="AG40" s="67"/>
-      <c r="AH40" s="67"/>
-      <c r="AI40" s="67"/>
-      <c r="AJ40" s="67"/>
-      <c r="AK40" s="67"/>
+      <c r="D40" s="68"/>
+      <c r="E40" s="68"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="69"/>
+      <c r="H40" s="67"/>
+      <c r="I40" s="68"/>
+      <c r="J40" s="68"/>
+      <c r="K40" s="68"/>
+      <c r="L40" s="53"/>
+      <c r="M40" s="68"/>
+      <c r="N40" s="69"/>
+      <c r="O40" s="67"/>
+      <c r="P40" s="68"/>
+      <c r="Q40" s="68"/>
+      <c r="R40" s="63"/>
+      <c r="S40" s="63"/>
+      <c r="T40" s="63"/>
+      <c r="U40" s="63"/>
+      <c r="V40" s="51"/>
+      <c r="W40" s="56"/>
+      <c r="X40" s="63"/>
+      <c r="Y40" s="63"/>
+      <c r="Z40" s="51"/>
+      <c r="AA40" s="52"/>
+      <c r="AB40" s="63"/>
+      <c r="AC40" s="63"/>
+      <c r="AD40" s="53"/>
+      <c r="AE40" s="69"/>
+      <c r="AF40" s="67"/>
+      <c r="AG40" s="68"/>
+      <c r="AH40" s="68"/>
+      <c r="AI40" s="68"/>
+      <c r="AJ40" s="68"/>
+      <c r="AK40" s="68"/>
     </row>
     <row r="41" ht="12" customHeight="1">
-      <c r="B41" s="64"/>
-      <c r="C41" s="73"/>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="68"/>
-      <c r="H41" s="66"/>
-      <c r="I41" s="67"/>
-      <c r="J41" s="67"/>
-      <c r="K41" s="67"/>
-      <c r="L41" s="52"/>
-      <c r="M41" s="67"/>
-      <c r="N41" s="68"/>
-      <c r="O41" s="66"/>
-      <c r="P41" s="67"/>
-      <c r="Q41" s="61"/>
-      <c r="R41" s="74"/>
-      <c r="S41" s="74"/>
-      <c r="T41" s="61"/>
-      <c r="U41" s="67"/>
-      <c r="V41" s="68"/>
-      <c r="W41" s="55"/>
-      <c r="X41" s="67"/>
-      <c r="Y41" s="67"/>
-      <c r="Z41" s="68"/>
-      <c r="AA41" s="66"/>
-      <c r="AB41" s="67"/>
-      <c r="AC41" s="67"/>
-      <c r="AD41" s="52"/>
-      <c r="AE41" s="68"/>
-      <c r="AF41" s="66"/>
-      <c r="AG41" s="67"/>
-      <c r="AH41" s="67"/>
-      <c r="AI41" s="67"/>
-      <c r="AJ41" s="67"/>
-      <c r="AK41" s="67"/>
+      <c r="B41" s="65"/>
+      <c r="C41" s="74"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="71"/>
+      <c r="G41" s="69"/>
+      <c r="H41" s="67"/>
+      <c r="I41" s="68"/>
+      <c r="J41" s="68"/>
+      <c r="K41" s="68"/>
+      <c r="L41" s="53"/>
+      <c r="M41" s="68"/>
+      <c r="N41" s="69"/>
+      <c r="O41" s="67"/>
+      <c r="P41" s="68"/>
+      <c r="Q41" s="62"/>
+      <c r="R41" s="75"/>
+      <c r="S41" s="75"/>
+      <c r="T41" s="62"/>
+      <c r="U41" s="68"/>
+      <c r="V41" s="69"/>
+      <c r="W41" s="56"/>
+      <c r="X41" s="68"/>
+      <c r="Y41" s="68"/>
+      <c r="Z41" s="69"/>
+      <c r="AA41" s="67"/>
+      <c r="AB41" s="68"/>
+      <c r="AC41" s="68"/>
+      <c r="AD41" s="53"/>
+      <c r="AE41" s="69"/>
+      <c r="AF41" s="67"/>
+      <c r="AG41" s="68"/>
+      <c r="AH41" s="68"/>
+      <c r="AI41" s="68"/>
+      <c r="AJ41" s="68"/>
+      <c r="AK41" s="68"/>
     </row>
     <row r="42" ht="12" customHeight="1">
-      <c r="B42" s="46" t="s">
+      <c r="B42" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="76" t="s">
+      <c r="C42" s="77" t="s">
         <v>127</v>
       </c>
-      <c r="D42" s="48"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="56"/>
-      <c r="G42" s="53"/>
-      <c r="H42" s="54"/>
-      <c r="I42" s="48"/>
-      <c r="J42" s="48"/>
-      <c r="K42" s="48"/>
-      <c r="L42" s="52"/>
-      <c r="M42" s="48"/>
-      <c r="N42" s="53"/>
-      <c r="O42" s="54"/>
-      <c r="P42" s="62"/>
-      <c r="Q42" s="62"/>
-      <c r="R42" s="48"/>
-      <c r="S42" s="48"/>
-      <c r="T42" s="61"/>
-      <c r="U42" s="48"/>
-      <c r="V42" s="50"/>
-      <c r="W42" s="55"/>
-      <c r="X42" s="62"/>
-      <c r="Y42" s="62"/>
-      <c r="Z42" s="50"/>
-      <c r="AA42" s="51"/>
-      <c r="AB42" s="62"/>
-      <c r="AC42" s="62"/>
-      <c r="AD42" s="52"/>
-      <c r="AE42" s="53"/>
-      <c r="AF42" s="54"/>
-      <c r="AG42" s="48"/>
-      <c r="AH42" s="48"/>
-      <c r="AI42" s="48"/>
-      <c r="AJ42" s="48"/>
-      <c r="AK42" s="48"/>
+      <c r="D42" s="49"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="49"/>
+      <c r="J42" s="49"/>
+      <c r="K42" s="49"/>
+      <c r="L42" s="53"/>
+      <c r="M42" s="49"/>
+      <c r="N42" s="54"/>
+      <c r="O42" s="55"/>
+      <c r="P42" s="63"/>
+      <c r="Q42" s="63"/>
+      <c r="R42" s="49"/>
+      <c r="S42" s="49"/>
+      <c r="T42" s="62"/>
+      <c r="U42" s="49"/>
+      <c r="V42" s="51"/>
+      <c r="W42" s="56"/>
+      <c r="X42" s="63"/>
+      <c r="Y42" s="63"/>
+      <c r="Z42" s="51"/>
+      <c r="AA42" s="52"/>
+      <c r="AB42" s="63"/>
+      <c r="AC42" s="63"/>
+      <c r="AD42" s="53"/>
+      <c r="AE42" s="54"/>
+      <c r="AF42" s="55"/>
+      <c r="AG42" s="49"/>
+      <c r="AH42" s="49"/>
+      <c r="AI42" s="49"/>
+      <c r="AJ42" s="49"/>
+      <c r="AK42" s="49"/>
     </row>
     <row r="43" ht="12" customHeight="1">
-      <c r="B43" s="46"/>
-      <c r="C43" s="76"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="56"/>
-      <c r="G43" s="53"/>
-      <c r="H43" s="54"/>
-      <c r="I43" s="48"/>
-      <c r="J43" s="48"/>
-      <c r="K43" s="48"/>
-      <c r="L43" s="52"/>
-      <c r="M43" s="48"/>
-      <c r="N43" s="53"/>
-      <c r="O43" s="54"/>
-      <c r="P43" s="48"/>
-      <c r="Q43" s="61"/>
-      <c r="R43" s="48"/>
-      <c r="S43" s="63"/>
-      <c r="T43" s="48"/>
-      <c r="U43" s="48"/>
-      <c r="V43" s="53"/>
-      <c r="W43" s="55"/>
-      <c r="X43" s="48"/>
-      <c r="Y43" s="48"/>
-      <c r="Z43" s="53"/>
-      <c r="AA43" s="54"/>
-      <c r="AB43" s="48"/>
-      <c r="AC43" s="48"/>
-      <c r="AD43" s="52"/>
-      <c r="AE43" s="53"/>
-      <c r="AF43" s="54"/>
-      <c r="AG43" s="48"/>
-      <c r="AH43" s="48"/>
-      <c r="AI43" s="48"/>
-      <c r="AJ43" s="48"/>
-      <c r="AK43" s="48"/>
+      <c r="B43" s="47"/>
+      <c r="C43" s="77"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="57"/>
+      <c r="G43" s="54"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="49"/>
+      <c r="J43" s="49"/>
+      <c r="K43" s="49"/>
+      <c r="L43" s="53"/>
+      <c r="M43" s="49"/>
+      <c r="N43" s="54"/>
+      <c r="O43" s="55"/>
+      <c r="P43" s="49"/>
+      <c r="Q43" s="62"/>
+      <c r="R43" s="49"/>
+      <c r="S43" s="64"/>
+      <c r="T43" s="49"/>
+      <c r="U43" s="49"/>
+      <c r="V43" s="54"/>
+      <c r="W43" s="56"/>
+      <c r="X43" s="49"/>
+      <c r="Y43" s="49"/>
+      <c r="Z43" s="54"/>
+      <c r="AA43" s="55"/>
+      <c r="AB43" s="49"/>
+      <c r="AC43" s="49"/>
+      <c r="AD43" s="53"/>
+      <c r="AE43" s="54"/>
+      <c r="AF43" s="55"/>
+      <c r="AG43" s="49"/>
+      <c r="AH43" s="49"/>
+      <c r="AI43" s="49"/>
+      <c r="AJ43" s="49"/>
+      <c r="AK43" s="49"/>
     </row>
     <row r="44" ht="12" customHeight="1">
-      <c r="B44" s="46"/>
-      <c r="C44" s="76" t="s">
+      <c r="B44" s="47"/>
+      <c r="C44" s="77" t="s">
         <v>128</v>
       </c>
-      <c r="D44" s="48"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="56"/>
-      <c r="G44" s="53"/>
-      <c r="H44" s="54"/>
-      <c r="I44" s="48"/>
-      <c r="J44" s="48"/>
-      <c r="K44" s="48"/>
-      <c r="L44" s="52"/>
-      <c r="M44" s="48"/>
-      <c r="N44" s="53"/>
-      <c r="O44" s="54"/>
-      <c r="P44" s="62"/>
-      <c r="Q44" s="62"/>
-      <c r="R44" s="48"/>
-      <c r="S44" s="48"/>
-      <c r="T44" s="48"/>
-      <c r="U44" s="48"/>
-      <c r="V44" s="53"/>
-      <c r="W44" s="55"/>
-      <c r="X44" s="62"/>
-      <c r="Y44" s="62"/>
-      <c r="Z44" s="53"/>
-      <c r="AA44" s="54"/>
-      <c r="AB44" s="48"/>
-      <c r="AC44" s="62"/>
-      <c r="AD44" s="52"/>
-      <c r="AE44" s="50"/>
-      <c r="AF44" s="51"/>
-      <c r="AG44" s="48"/>
-      <c r="AH44" s="48"/>
-      <c r="AI44" s="62"/>
-      <c r="AJ44" s="48"/>
-      <c r="AK44" s="48"/>
+      <c r="D44" s="49"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="49"/>
+      <c r="J44" s="49"/>
+      <c r="K44" s="49"/>
+      <c r="L44" s="53"/>
+      <c r="M44" s="49"/>
+      <c r="N44" s="54"/>
+      <c r="O44" s="55"/>
+      <c r="P44" s="63"/>
+      <c r="Q44" s="63"/>
+      <c r="R44" s="49"/>
+      <c r="S44" s="49"/>
+      <c r="T44" s="49"/>
+      <c r="U44" s="49"/>
+      <c r="V44" s="54"/>
+      <c r="W44" s="56"/>
+      <c r="X44" s="63"/>
+      <c r="Y44" s="63"/>
+      <c r="Z44" s="54"/>
+      <c r="AA44" s="55"/>
+      <c r="AB44" s="49"/>
+      <c r="AC44" s="63"/>
+      <c r="AD44" s="53"/>
+      <c r="AE44" s="51"/>
+      <c r="AF44" s="52"/>
+      <c r="AG44" s="49"/>
+      <c r="AH44" s="49"/>
+      <c r="AI44" s="63"/>
+      <c r="AJ44" s="49"/>
+      <c r="AK44" s="49"/>
     </row>
     <row r="45" ht="12" customHeight="1">
-      <c r="B45" s="46"/>
-      <c r="C45" s="76"/>
-      <c r="D45" s="48"/>
-      <c r="E45" s="48"/>
-      <c r="F45" s="56"/>
-      <c r="G45" s="53"/>
-      <c r="H45" s="54"/>
-      <c r="I45" s="48"/>
-      <c r="J45" s="48"/>
-      <c r="K45" s="48"/>
-      <c r="L45" s="52"/>
-      <c r="M45" s="48"/>
-      <c r="N45" s="53"/>
-      <c r="O45" s="54"/>
-      <c r="P45" s="48"/>
-      <c r="Q45" s="48"/>
-      <c r="R45" s="48"/>
-      <c r="S45" s="48"/>
-      <c r="T45" s="48"/>
-      <c r="U45" s="48"/>
-      <c r="V45" s="53"/>
-      <c r="W45" s="55"/>
-      <c r="X45" s="48"/>
-      <c r="Y45" s="48"/>
-      <c r="Z45" s="53"/>
-      <c r="AA45" s="54"/>
-      <c r="AB45" s="48"/>
-      <c r="AC45" s="48"/>
-      <c r="AD45" s="52"/>
-      <c r="AE45" s="53"/>
-      <c r="AF45" s="54"/>
-      <c r="AG45" s="48"/>
-      <c r="AH45" s="48"/>
-      <c r="AI45" s="48"/>
-      <c r="AJ45" s="48"/>
-      <c r="AK45" s="48"/>
+      <c r="B45" s="47"/>
+      <c r="C45" s="77"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="49"/>
+      <c r="J45" s="49"/>
+      <c r="K45" s="49"/>
+      <c r="L45" s="53"/>
+      <c r="M45" s="49"/>
+      <c r="N45" s="54"/>
+      <c r="O45" s="55"/>
+      <c r="P45" s="49"/>
+      <c r="Q45" s="49"/>
+      <c r="R45" s="49"/>
+      <c r="S45" s="49"/>
+      <c r="T45" s="49"/>
+      <c r="U45" s="49"/>
+      <c r="V45" s="54"/>
+      <c r="W45" s="56"/>
+      <c r="X45" s="49"/>
+      <c r="Y45" s="49"/>
+      <c r="Z45" s="54"/>
+      <c r="AA45" s="55"/>
+      <c r="AB45" s="49"/>
+      <c r="AC45" s="49"/>
+      <c r="AD45" s="53"/>
+      <c r="AE45" s="54"/>
+      <c r="AF45" s="55"/>
+      <c r="AG45" s="49"/>
+      <c r="AH45" s="49"/>
+      <c r="AI45" s="49"/>
+      <c r="AJ45" s="49"/>
+      <c r="AK45" s="49"/>
     </row>
     <row r="46" ht="12" customHeight="1">
-      <c r="B46" s="64" t="s">
+      <c r="B46" s="65" t="s">
         <v>129</v>
       </c>
-      <c r="C46" s="65" t="s">
+      <c r="C46" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="D46" s="67"/>
-      <c r="E46" s="67"/>
-      <c r="F46" s="70"/>
-      <c r="G46" s="68"/>
-      <c r="H46" s="66"/>
-      <c r="I46" s="67"/>
-      <c r="J46" s="67"/>
-      <c r="K46" s="67"/>
-      <c r="L46" s="52"/>
-      <c r="M46" s="67"/>
-      <c r="N46" s="68"/>
-      <c r="O46" s="66"/>
-      <c r="P46" s="67"/>
-      <c r="Q46" s="67"/>
-      <c r="R46" s="67"/>
-      <c r="S46" s="67"/>
-      <c r="T46" s="67"/>
-      <c r="U46" s="67"/>
-      <c r="V46" s="68"/>
-      <c r="W46" s="55"/>
-      <c r="X46" s="67"/>
-      <c r="Y46" s="67"/>
-      <c r="Z46" s="68"/>
-      <c r="AA46" s="66"/>
-      <c r="AB46" s="67"/>
-      <c r="AC46" s="67"/>
-      <c r="AD46" s="52"/>
-      <c r="AE46" s="68"/>
-      <c r="AF46" s="66"/>
-      <c r="AG46" s="67"/>
-      <c r="AH46" s="67"/>
-      <c r="AI46" s="67"/>
-      <c r="AJ46" s="62"/>
-      <c r="AK46" s="67"/>
+      <c r="D46" s="68"/>
+      <c r="E46" s="68"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="69"/>
+      <c r="H46" s="67"/>
+      <c r="I46" s="68"/>
+      <c r="J46" s="68"/>
+      <c r="K46" s="68"/>
+      <c r="L46" s="53"/>
+      <c r="M46" s="68"/>
+      <c r="N46" s="69"/>
+      <c r="O46" s="67"/>
+      <c r="P46" s="68"/>
+      <c r="Q46" s="68"/>
+      <c r="R46" s="68"/>
+      <c r="S46" s="68"/>
+      <c r="T46" s="68"/>
+      <c r="U46" s="68"/>
+      <c r="V46" s="69"/>
+      <c r="W46" s="56"/>
+      <c r="X46" s="68"/>
+      <c r="Y46" s="68"/>
+      <c r="Z46" s="69"/>
+      <c r="AA46" s="67"/>
+      <c r="AB46" s="68"/>
+      <c r="AC46" s="68"/>
+      <c r="AD46" s="53"/>
+      <c r="AE46" s="69"/>
+      <c r="AF46" s="67"/>
+      <c r="AG46" s="68"/>
+      <c r="AH46" s="68"/>
+      <c r="AI46" s="68"/>
+      <c r="AJ46" s="63"/>
+      <c r="AK46" s="68"/>
     </row>
     <row r="47" ht="12" customHeight="1">
-      <c r="B47" s="64"/>
-      <c r="C47" s="65"/>
-      <c r="D47" s="67"/>
-      <c r="E47" s="67"/>
-      <c r="F47" s="70"/>
-      <c r="G47" s="68"/>
-      <c r="H47" s="66"/>
-      <c r="I47" s="67"/>
-      <c r="J47" s="67"/>
-      <c r="K47" s="67"/>
-      <c r="L47" s="52"/>
-      <c r="M47" s="67"/>
-      <c r="N47" s="68"/>
-      <c r="O47" s="66"/>
-      <c r="P47" s="67"/>
-      <c r="Q47" s="67"/>
-      <c r="R47" s="67"/>
-      <c r="S47" s="67"/>
-      <c r="T47" s="67"/>
-      <c r="U47" s="67"/>
-      <c r="V47" s="68"/>
-      <c r="W47" s="55"/>
-      <c r="X47" s="67"/>
-      <c r="Y47" s="67"/>
-      <c r="Z47" s="68"/>
-      <c r="AA47" s="66"/>
-      <c r="AB47" s="67"/>
-      <c r="AC47" s="67"/>
-      <c r="AD47" s="52"/>
-      <c r="AE47" s="68"/>
-      <c r="AF47" s="66"/>
-      <c r="AG47" s="67"/>
-      <c r="AH47" s="67"/>
-      <c r="AI47" s="67"/>
-      <c r="AJ47" s="67"/>
-      <c r="AK47" s="67"/>
-      <c r="AN47" s="77" t="s">
+      <c r="B47" s="65"/>
+      <c r="C47" s="66"/>
+      <c r="D47" s="68"/>
+      <c r="E47" s="68"/>
+      <c r="F47" s="71"/>
+      <c r="G47" s="69"/>
+      <c r="H47" s="67"/>
+      <c r="I47" s="68"/>
+      <c r="J47" s="68"/>
+      <c r="K47" s="68"/>
+      <c r="L47" s="53"/>
+      <c r="M47" s="68"/>
+      <c r="N47" s="69"/>
+      <c r="O47" s="67"/>
+      <c r="P47" s="68"/>
+      <c r="Q47" s="68"/>
+      <c r="R47" s="68"/>
+      <c r="S47" s="68"/>
+      <c r="T47" s="68"/>
+      <c r="U47" s="68"/>
+      <c r="V47" s="69"/>
+      <c r="W47" s="56"/>
+      <c r="X47" s="68"/>
+      <c r="Y47" s="68"/>
+      <c r="Z47" s="69"/>
+      <c r="AA47" s="67"/>
+      <c r="AB47" s="68"/>
+      <c r="AC47" s="68"/>
+      <c r="AD47" s="53"/>
+      <c r="AE47" s="69"/>
+      <c r="AF47" s="67"/>
+      <c r="AG47" s="68"/>
+      <c r="AH47" s="68"/>
+      <c r="AI47" s="68"/>
+      <c r="AJ47" s="68"/>
+      <c r="AK47" s="68"/>
+      <c r="AN47" s="78" t="s">
         <v>130</v>
       </c>
-      <c r="AO47" s="62"/>
+      <c r="AO47" s="63"/>
     </row>
     <row r="48" ht="12" customHeight="1">
-      <c r="B48" s="64"/>
-      <c r="C48" s="65" t="s">
+      <c r="B48" s="65"/>
+      <c r="C48" s="66" t="s">
         <v>131</v>
       </c>
-      <c r="D48" s="67"/>
-      <c r="E48" s="67"/>
-      <c r="F48" s="70"/>
-      <c r="G48" s="68"/>
-      <c r="H48" s="66"/>
-      <c r="I48" s="67"/>
-      <c r="J48" s="67"/>
-      <c r="K48" s="67"/>
-      <c r="L48" s="52"/>
-      <c r="M48" s="67"/>
-      <c r="N48" s="68"/>
-      <c r="O48" s="66"/>
-      <c r="P48" s="67"/>
-      <c r="Q48" s="67"/>
-      <c r="R48" s="67"/>
-      <c r="S48" s="67"/>
-      <c r="T48" s="67"/>
-      <c r="U48" s="67"/>
-      <c r="V48" s="68"/>
-      <c r="W48" s="55"/>
-      <c r="X48" s="67"/>
-      <c r="Y48" s="67"/>
-      <c r="Z48" s="68"/>
-      <c r="AA48" s="66"/>
-      <c r="AB48" s="67"/>
-      <c r="AC48" s="67"/>
-      <c r="AD48" s="52"/>
-      <c r="AE48" s="68"/>
-      <c r="AF48" s="66"/>
-      <c r="AG48" s="67"/>
-      <c r="AH48" s="67"/>
-      <c r="AI48" s="67"/>
-      <c r="AJ48" s="67"/>
-      <c r="AK48" s="78"/>
-      <c r="AN48" s="77" t="s">
+      <c r="D48" s="68"/>
+      <c r="E48" s="68"/>
+      <c r="F48" s="71"/>
+      <c r="G48" s="69"/>
+      <c r="H48" s="67"/>
+      <c r="I48" s="68"/>
+      <c r="J48" s="68"/>
+      <c r="K48" s="68"/>
+      <c r="L48" s="53"/>
+      <c r="M48" s="68"/>
+      <c r="N48" s="69"/>
+      <c r="O48" s="67"/>
+      <c r="P48" s="68"/>
+      <c r="Q48" s="68"/>
+      <c r="R48" s="68"/>
+      <c r="S48" s="68"/>
+      <c r="T48" s="68"/>
+      <c r="U48" s="68"/>
+      <c r="V48" s="69"/>
+      <c r="W48" s="56"/>
+      <c r="X48" s="68"/>
+      <c r="Y48" s="68"/>
+      <c r="Z48" s="69"/>
+      <c r="AA48" s="67"/>
+      <c r="AB48" s="68"/>
+      <c r="AC48" s="68"/>
+      <c r="AD48" s="53"/>
+      <c r="AE48" s="69"/>
+      <c r="AF48" s="67"/>
+      <c r="AG48" s="68"/>
+      <c r="AH48" s="68"/>
+      <c r="AI48" s="68"/>
+      <c r="AJ48" s="68"/>
+      <c r="AK48" s="79"/>
+      <c r="AN48" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="AO48" s="61"/>
+      <c r="AO48" s="62"/>
     </row>
     <row r="49" ht="12" customHeight="1">
-      <c r="B49" s="64"/>
-      <c r="C49" s="65"/>
-      <c r="D49" s="67"/>
-      <c r="E49" s="67"/>
-      <c r="F49" s="70"/>
-      <c r="G49" s="68"/>
-      <c r="H49" s="66"/>
-      <c r="I49" s="67"/>
-      <c r="J49" s="67"/>
-      <c r="K49" s="67"/>
-      <c r="L49" s="52"/>
-      <c r="M49" s="67"/>
-      <c r="N49" s="68"/>
-      <c r="O49" s="66"/>
-      <c r="P49" s="67"/>
-      <c r="Q49" s="67"/>
-      <c r="R49" s="67"/>
-      <c r="S49" s="67"/>
-      <c r="T49" s="67"/>
-      <c r="U49" s="67"/>
-      <c r="V49" s="68"/>
-      <c r="W49" s="55"/>
-      <c r="X49" s="67"/>
-      <c r="Y49" s="67"/>
-      <c r="Z49" s="68"/>
-      <c r="AA49" s="66"/>
-      <c r="AB49" s="67"/>
-      <c r="AC49" s="67"/>
-      <c r="AD49" s="52"/>
-      <c r="AE49" s="68"/>
-      <c r="AF49" s="66"/>
-      <c r="AG49" s="67"/>
-      <c r="AH49" s="67"/>
-      <c r="AI49" s="67"/>
-      <c r="AJ49" s="67"/>
-      <c r="AK49" s="67"/>
-      <c r="AN49" s="77" t="s">
+      <c r="B49" s="65"/>
+      <c r="C49" s="66"/>
+      <c r="D49" s="68"/>
+      <c r="E49" s="68"/>
+      <c r="F49" s="71"/>
+      <c r="G49" s="69"/>
+      <c r="H49" s="67"/>
+      <c r="I49" s="68"/>
+      <c r="J49" s="68"/>
+      <c r="K49" s="68"/>
+      <c r="L49" s="53"/>
+      <c r="M49" s="68"/>
+      <c r="N49" s="69"/>
+      <c r="O49" s="67"/>
+      <c r="P49" s="68"/>
+      <c r="Q49" s="68"/>
+      <c r="R49" s="68"/>
+      <c r="S49" s="68"/>
+      <c r="T49" s="68"/>
+      <c r="U49" s="68"/>
+      <c r="V49" s="69"/>
+      <c r="W49" s="56"/>
+      <c r="X49" s="68"/>
+      <c r="Y49" s="68"/>
+      <c r="Z49" s="69"/>
+      <c r="AA49" s="67"/>
+      <c r="AB49" s="68"/>
+      <c r="AC49" s="68"/>
+      <c r="AD49" s="53"/>
+      <c r="AE49" s="69"/>
+      <c r="AF49" s="67"/>
+      <c r="AG49" s="68"/>
+      <c r="AH49" s="68"/>
+      <c r="AI49" s="68"/>
+      <c r="AJ49" s="68"/>
+      <c r="AK49" s="68"/>
+      <c r="AN49" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="AO49" s="57"/>
+      <c r="AO49" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -9011,94 +9106,94 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="79"/>
+      <c r="B1" s="80"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="81" t="s">
+      <c r="C2" s="82" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="82" t="s">
+      <c r="D2" s="83" t="s">
         <v>134</v>
       </c>
-      <c r="E2" s="83" t="s">
+      <c r="E2" s="84" t="s">
         <v>135</v>
       </c>
-      <c r="F2" s="84" t="s">
+      <c r="F2" s="85" t="s">
         <v>136</v>
       </c>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="84" t="s">
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="85" t="s">
         <v>137</v>
       </c>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="83"/>
-      <c r="N2" s="84" t="s">
+      <c r="K2" s="85"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="85" t="s">
         <v>138</v>
       </c>
-      <c r="O2" s="84"/>
-      <c r="P2" s="84"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="84" t="s">
+      <c r="O2" s="85"/>
+      <c r="P2" s="85"/>
+      <c r="Q2" s="84"/>
+      <c r="R2" s="85" t="s">
         <v>139</v>
       </c>
-      <c r="S2" s="85"/>
-      <c r="AD2" s="28"/>
+      <c r="S2" s="86"/>
+      <c r="AD2" s="29"/>
     </row>
     <row r="3">
-      <c r="B3" s="86"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="88" t="s">
+      <c r="B3" s="87"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="89" t="s">
         <v>140</v>
       </c>
-      <c r="E3" s="89">
+      <c r="E3" s="90">
         <v>4</v>
       </c>
-      <c r="F3" s="90">
+      <c r="F3" s="91">
         <v>1</v>
       </c>
-      <c r="G3" s="91">
+      <c r="G3" s="92">
         <v>2</v>
       </c>
-      <c r="H3" s="91">
+      <c r="H3" s="92">
         <v>3</v>
       </c>
-      <c r="I3" s="89">
+      <c r="I3" s="90">
         <v>4</v>
       </c>
-      <c r="J3" s="90">
+      <c r="J3" s="91">
         <v>1</v>
       </c>
-      <c r="K3" s="91">
+      <c r="K3" s="92">
         <v>2</v>
       </c>
-      <c r="L3" s="91">
+      <c r="L3" s="92">
         <v>3</v>
       </c>
-      <c r="M3" s="89">
+      <c r="M3" s="90">
         <v>4</v>
       </c>
-      <c r="N3" s="90">
+      <c r="N3" s="91">
         <v>1</v>
       </c>
-      <c r="O3" s="91">
+      <c r="O3" s="92">
         <v>2</v>
       </c>
-      <c r="P3" s="91">
+      <c r="P3" s="92">
         <v>3</v>
       </c>
-      <c r="Q3" s="89">
+      <c r="Q3" s="90">
         <v>4</v>
       </c>
-      <c r="R3" s="90">
+      <c r="R3" s="91">
         <v>1</v>
       </c>
-      <c r="S3" s="92">
+      <c r="S3" s="93">
         <v>2</v>
       </c>
       <c r="U3" t="s">
@@ -9106,705 +9201,705 @@
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="93" t="s">
+      <c r="B4" s="94" t="s">
         <v>142</v>
       </c>
-      <c r="C4" s="81" t="s">
+      <c r="C4" s="82" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="94"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="95"/>
-      <c r="J4" s="98"/>
-      <c r="K4" s="97"/>
-      <c r="L4" s="97"/>
-      <c r="M4" s="95"/>
-      <c r="N4" s="98"/>
-      <c r="O4" s="97"/>
-      <c r="P4" s="97"/>
-      <c r="Q4" s="95"/>
-      <c r="R4" s="98"/>
-      <c r="S4" s="99"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="99"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="96"/>
+      <c r="N4" s="99"/>
+      <c r="O4" s="98"/>
+      <c r="P4" s="98"/>
+      <c r="Q4" s="96"/>
+      <c r="R4" s="99"/>
+      <c r="S4" s="100"/>
       <c r="U4" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="93"/>
-      <c r="C5" s="100"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="104"/>
-      <c r="H5" s="105"/>
-      <c r="I5" s="102"/>
-      <c r="J5" s="106"/>
-      <c r="K5" s="105"/>
-      <c r="L5" s="105"/>
-      <c r="M5" s="102"/>
-      <c r="N5" s="106"/>
-      <c r="O5" s="105"/>
-      <c r="P5" s="105"/>
-      <c r="Q5" s="102"/>
-      <c r="R5" s="106"/>
-      <c r="S5" s="107"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="106"/>
+      <c r="I5" s="103"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="106"/>
+      <c r="L5" s="106"/>
+      <c r="M5" s="103"/>
+      <c r="N5" s="107"/>
+      <c r="O5" s="106"/>
+      <c r="P5" s="106"/>
+      <c r="Q5" s="103"/>
+      <c r="R5" s="107"/>
+      <c r="S5" s="108"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="93"/>
-      <c r="C6" s="108" t="s">
+      <c r="B6" s="94"/>
+      <c r="C6" s="109" t="s">
         <v>145</v>
       </c>
-      <c r="D6" s="109"/>
-      <c r="E6" s="110"/>
-      <c r="F6" s="111"/>
-      <c r="G6" s="112"/>
-      <c r="H6" s="113"/>
-      <c r="I6" s="110"/>
-      <c r="J6" s="114"/>
-      <c r="K6" s="113"/>
-      <c r="L6" s="113"/>
-      <c r="M6" s="110"/>
-      <c r="N6" s="114"/>
-      <c r="O6" s="113"/>
-      <c r="P6" s="113"/>
-      <c r="Q6" s="110"/>
-      <c r="R6" s="114"/>
-      <c r="S6" s="115"/>
-      <c r="U6" s="116" t="s">
+      <c r="D6" s="110"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="112"/>
+      <c r="G6" s="113"/>
+      <c r="H6" s="114"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="115"/>
+      <c r="K6" s="114"/>
+      <c r="L6" s="114"/>
+      <c r="M6" s="111"/>
+      <c r="N6" s="115"/>
+      <c r="O6" s="114"/>
+      <c r="P6" s="114"/>
+      <c r="Q6" s="111"/>
+      <c r="R6" s="115"/>
+      <c r="S6" s="116"/>
+      <c r="U6" s="117" t="s">
         <v>146</v>
       </c>
-      <c r="V6" s="116"/>
+      <c r="V6" s="117"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="93"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="101"/>
-      <c r="E7" s="102"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="104"/>
-      <c r="H7" s="104"/>
-      <c r="I7" s="102"/>
-      <c r="J7" s="106"/>
-      <c r="K7" s="105"/>
-      <c r="L7" s="105"/>
-      <c r="M7" s="102"/>
-      <c r="N7" s="106"/>
-      <c r="O7" s="105"/>
-      <c r="P7" s="105"/>
-      <c r="Q7" s="102"/>
-      <c r="R7" s="106"/>
-      <c r="S7" s="107"/>
+      <c r="B7" s="94"/>
+      <c r="C7" s="101"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="107"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="105"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="106"/>
+      <c r="L7" s="106"/>
+      <c r="M7" s="103"/>
+      <c r="N7" s="107"/>
+      <c r="O7" s="106"/>
+      <c r="P7" s="106"/>
+      <c r="Q7" s="103"/>
+      <c r="R7" s="107"/>
+      <c r="S7" s="108"/>
       <c r="U7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="93"/>
-      <c r="C8" s="108" t="s">
+      <c r="B8" s="94"/>
+      <c r="C8" s="109" t="s">
         <v>148</v>
       </c>
-      <c r="D8" s="109"/>
-      <c r="E8" s="110"/>
-      <c r="F8" s="111"/>
-      <c r="G8" s="113"/>
-      <c r="H8" s="113"/>
-      <c r="I8" s="110"/>
-      <c r="J8" s="114"/>
-      <c r="K8" s="113"/>
-      <c r="L8" s="113"/>
-      <c r="M8" s="110"/>
-      <c r="N8" s="114"/>
-      <c r="O8" s="113"/>
-      <c r="P8" s="113"/>
-      <c r="Q8" s="110"/>
-      <c r="R8" s="114"/>
-      <c r="S8" s="115"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="111"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="114"/>
+      <c r="H8" s="114"/>
+      <c r="I8" s="111"/>
+      <c r="J8" s="115"/>
+      <c r="K8" s="114"/>
+      <c r="L8" s="114"/>
+      <c r="M8" s="111"/>
+      <c r="N8" s="115"/>
+      <c r="O8" s="114"/>
+      <c r="P8" s="114"/>
+      <c r="Q8" s="111"/>
+      <c r="R8" s="115"/>
+      <c r="S8" s="116"/>
       <c r="U8" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="93"/>
-      <c r="C9" s="100"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="102"/>
-      <c r="F9" s="106"/>
-      <c r="G9" s="104"/>
-      <c r="H9" s="105"/>
-      <c r="I9" s="102"/>
-      <c r="J9" s="106"/>
-      <c r="K9" s="105"/>
-      <c r="L9" s="105"/>
-      <c r="M9" s="102"/>
-      <c r="N9" s="106"/>
-      <c r="O9" s="105"/>
-      <c r="P9" s="105"/>
-      <c r="Q9" s="102"/>
-      <c r="R9" s="106"/>
-      <c r="S9" s="107"/>
+      <c r="B9" s="94"/>
+      <c r="C9" s="101"/>
+      <c r="D9" s="102"/>
+      <c r="E9" s="103"/>
+      <c r="F9" s="107"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="106"/>
+      <c r="I9" s="103"/>
+      <c r="J9" s="107"/>
+      <c r="K9" s="106"/>
+      <c r="L9" s="106"/>
+      <c r="M9" s="103"/>
+      <c r="N9" s="107"/>
+      <c r="O9" s="106"/>
+      <c r="P9" s="106"/>
+      <c r="Q9" s="103"/>
+      <c r="R9" s="107"/>
+      <c r="S9" s="108"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="93"/>
-      <c r="C10" s="108" t="s">
+      <c r="B10" s="94"/>
+      <c r="C10" s="109" t="s">
         <v>150</v>
       </c>
-      <c r="D10" s="109"/>
-      <c r="E10" s="110"/>
-      <c r="F10" s="114"/>
-      <c r="G10" s="112"/>
-      <c r="H10" s="112"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="114"/>
-      <c r="K10" s="113"/>
-      <c r="L10" s="113"/>
-      <c r="M10" s="110"/>
-      <c r="N10" s="114"/>
-      <c r="O10" s="113"/>
-      <c r="P10" s="113"/>
-      <c r="Q10" s="110"/>
-      <c r="R10" s="114"/>
-      <c r="S10" s="115"/>
+      <c r="D10" s="110"/>
+      <c r="E10" s="111"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="113"/>
+      <c r="H10" s="113"/>
+      <c r="I10" s="111"/>
+      <c r="J10" s="115"/>
+      <c r="K10" s="114"/>
+      <c r="L10" s="114"/>
+      <c r="M10" s="111"/>
+      <c r="N10" s="115"/>
+      <c r="O10" s="114"/>
+      <c r="P10" s="114"/>
+      <c r="Q10" s="111"/>
+      <c r="R10" s="115"/>
+      <c r="S10" s="116"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="117"/>
-      <c r="C11" s="118"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="120"/>
-      <c r="F11" s="121"/>
-      <c r="G11" s="122"/>
-      <c r="H11" s="122"/>
-      <c r="I11" s="120"/>
-      <c r="J11" s="121"/>
-      <c r="K11" s="123"/>
-      <c r="L11" s="123"/>
-      <c r="M11" s="120"/>
-      <c r="N11" s="121"/>
-      <c r="O11" s="123"/>
-      <c r="P11" s="123"/>
-      <c r="Q11" s="120"/>
-      <c r="R11" s="121"/>
-      <c r="S11" s="124"/>
+      <c r="B11" s="118"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="122"/>
+      <c r="G11" s="123"/>
+      <c r="H11" s="123"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="122"/>
+      <c r="K11" s="124"/>
+      <c r="L11" s="124"/>
+      <c r="M11" s="121"/>
+      <c r="N11" s="122"/>
+      <c r="O11" s="124"/>
+      <c r="P11" s="124"/>
+      <c r="Q11" s="121"/>
+      <c r="R11" s="122"/>
+      <c r="S11" s="125"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="80" t="s">
+      <c r="B12" s="81" t="s">
         <v>151</v>
       </c>
-      <c r="C12" s="81" t="s">
+      <c r="C12" s="82" t="s">
         <v>152</v>
       </c>
-      <c r="D12" s="94"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="97"/>
-      <c r="H12" s="125"/>
-      <c r="I12" s="126"/>
-      <c r="J12" s="98"/>
-      <c r="K12" s="97"/>
-      <c r="L12" s="97"/>
-      <c r="M12" s="95"/>
-      <c r="N12" s="98"/>
-      <c r="O12" s="97"/>
-      <c r="P12" s="97"/>
-      <c r="Q12" s="95"/>
-      <c r="R12" s="98"/>
-      <c r="S12" s="99"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="96"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="126"/>
+      <c r="I12" s="127"/>
+      <c r="J12" s="99"/>
+      <c r="K12" s="98"/>
+      <c r="L12" s="98"/>
+      <c r="M12" s="96"/>
+      <c r="N12" s="99"/>
+      <c r="O12" s="98"/>
+      <c r="P12" s="98"/>
+      <c r="Q12" s="96"/>
+      <c r="R12" s="99"/>
+      <c r="S12" s="100"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="93"/>
-      <c r="C13" s="100"/>
-      <c r="D13" s="101"/>
-      <c r="E13" s="102"/>
-      <c r="F13" s="106"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="105"/>
-      <c r="I13" s="102"/>
-      <c r="J13" s="103"/>
-      <c r="K13" s="105"/>
-      <c r="L13" s="105"/>
-      <c r="M13" s="102"/>
-      <c r="N13" s="106"/>
-      <c r="O13" s="105"/>
-      <c r="P13" s="105"/>
-      <c r="Q13" s="102"/>
-      <c r="R13" s="106"/>
-      <c r="S13" s="107"/>
+      <c r="B13" s="94"/>
+      <c r="C13" s="101"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="103"/>
+      <c r="F13" s="107"/>
+      <c r="G13" s="106"/>
+      <c r="H13" s="106"/>
+      <c r="I13" s="103"/>
+      <c r="J13" s="104"/>
+      <c r="K13" s="106"/>
+      <c r="L13" s="106"/>
+      <c r="M13" s="103"/>
+      <c r="N13" s="107"/>
+      <c r="O13" s="106"/>
+      <c r="P13" s="106"/>
+      <c r="Q13" s="103"/>
+      <c r="R13" s="107"/>
+      <c r="S13" s="108"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="93"/>
-      <c r="C14" s="108" t="s">
+      <c r="B14" s="94"/>
+      <c r="C14" s="109" t="s">
         <v>153</v>
       </c>
-      <c r="D14" s="127"/>
-      <c r="E14" s="110"/>
-      <c r="F14" s="114"/>
-      <c r="G14" s="113"/>
-      <c r="H14" s="112"/>
-      <c r="I14" s="110"/>
-      <c r="J14" s="114"/>
-      <c r="K14" s="113"/>
-      <c r="L14" s="113"/>
-      <c r="M14" s="110"/>
-      <c r="N14" s="114"/>
-      <c r="O14" s="113"/>
-      <c r="P14" s="113"/>
-      <c r="Q14" s="110"/>
-      <c r="R14" s="114"/>
-      <c r="S14" s="115"/>
+      <c r="D14" s="128"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="115"/>
+      <c r="G14" s="114"/>
+      <c r="H14" s="113"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="115"/>
+      <c r="K14" s="114"/>
+      <c r="L14" s="114"/>
+      <c r="M14" s="111"/>
+      <c r="N14" s="115"/>
+      <c r="O14" s="114"/>
+      <c r="P14" s="114"/>
+      <c r="Q14" s="111"/>
+      <c r="R14" s="115"/>
+      <c r="S14" s="116"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="93"/>
-      <c r="C15" s="100"/>
-      <c r="D15" s="101"/>
-      <c r="E15" s="102"/>
-      <c r="F15" s="106"/>
-      <c r="G15" s="105"/>
-      <c r="H15" s="105"/>
-      <c r="I15" s="128"/>
-      <c r="J15" s="103"/>
-      <c r="K15" s="105"/>
-      <c r="L15" s="105"/>
-      <c r="M15" s="102"/>
-      <c r="N15" s="106"/>
-      <c r="O15" s="105"/>
-      <c r="P15" s="105"/>
-      <c r="Q15" s="102"/>
-      <c r="R15" s="106"/>
-      <c r="S15" s="107"/>
+      <c r="B15" s="94"/>
+      <c r="C15" s="101"/>
+      <c r="D15" s="102"/>
+      <c r="E15" s="103"/>
+      <c r="F15" s="107"/>
+      <c r="G15" s="106"/>
+      <c r="H15" s="106"/>
+      <c r="I15" s="129"/>
+      <c r="J15" s="104"/>
+      <c r="K15" s="106"/>
+      <c r="L15" s="106"/>
+      <c r="M15" s="103"/>
+      <c r="N15" s="107"/>
+      <c r="O15" s="106"/>
+      <c r="P15" s="106"/>
+      <c r="Q15" s="103"/>
+      <c r="R15" s="107"/>
+      <c r="S15" s="108"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="93"/>
-      <c r="C16" s="108" t="s">
+      <c r="B16" s="94"/>
+      <c r="C16" s="109" t="s">
         <v>154</v>
       </c>
-      <c r="D16" s="109"/>
-      <c r="E16" s="110"/>
-      <c r="F16" s="114"/>
-      <c r="G16" s="113"/>
-      <c r="H16" s="112"/>
-      <c r="I16" s="129"/>
-      <c r="J16" s="114"/>
-      <c r="K16" s="113"/>
-      <c r="L16" s="113"/>
-      <c r="M16" s="110"/>
-      <c r="N16" s="114"/>
-      <c r="O16" s="113"/>
-      <c r="P16" s="113"/>
-      <c r="Q16" s="110"/>
-      <c r="R16" s="114"/>
-      <c r="S16" s="115"/>
+      <c r="D16" s="110"/>
+      <c r="E16" s="111"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="114"/>
+      <c r="H16" s="113"/>
+      <c r="I16" s="130"/>
+      <c r="J16" s="115"/>
+      <c r="K16" s="114"/>
+      <c r="L16" s="114"/>
+      <c r="M16" s="111"/>
+      <c r="N16" s="115"/>
+      <c r="O16" s="114"/>
+      <c r="P16" s="114"/>
+      <c r="Q16" s="111"/>
+      <c r="R16" s="115"/>
+      <c r="S16" s="116"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="117"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="119"/>
-      <c r="E17" s="120"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="123"/>
-      <c r="H17" s="123"/>
-      <c r="I17" s="120"/>
-      <c r="J17" s="130"/>
-      <c r="K17" s="122"/>
-      <c r="L17" s="123"/>
-      <c r="M17" s="120"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="123"/>
-      <c r="P17" s="123"/>
-      <c r="Q17" s="120"/>
-      <c r="R17" s="121"/>
-      <c r="S17" s="124"/>
+      <c r="B17" s="118"/>
+      <c r="C17" s="119"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="122"/>
+      <c r="G17" s="124"/>
+      <c r="H17" s="124"/>
+      <c r="I17" s="121"/>
+      <c r="J17" s="131"/>
+      <c r="K17" s="123"/>
+      <c r="L17" s="124"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="122"/>
+      <c r="O17" s="124"/>
+      <c r="P17" s="124"/>
+      <c r="Q17" s="121"/>
+      <c r="R17" s="122"/>
+      <c r="S17" s="125"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="82" t="s">
+      <c r="B18" s="83" t="s">
         <v>155</v>
       </c>
-      <c r="C18" s="81" t="s">
+      <c r="C18" s="82" t="s">
         <v>156</v>
       </c>
-      <c r="D18" s="94"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="98"/>
-      <c r="G18" s="97"/>
-      <c r="H18" s="97"/>
-      <c r="I18" s="126"/>
-      <c r="J18" s="98"/>
-      <c r="K18" s="97"/>
-      <c r="L18" s="97"/>
-      <c r="M18" s="95"/>
-      <c r="N18" s="98"/>
-      <c r="O18" s="97"/>
-      <c r="P18" s="97"/>
-      <c r="Q18" s="95"/>
-      <c r="R18" s="98"/>
-      <c r="S18" s="99"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="96"/>
+      <c r="F18" s="99"/>
+      <c r="G18" s="98"/>
+      <c r="H18" s="98"/>
+      <c r="I18" s="127"/>
+      <c r="J18" s="99"/>
+      <c r="K18" s="98"/>
+      <c r="L18" s="98"/>
+      <c r="M18" s="96"/>
+      <c r="N18" s="99"/>
+      <c r="O18" s="98"/>
+      <c r="P18" s="98"/>
+      <c r="Q18" s="96"/>
+      <c r="R18" s="99"/>
+      <c r="S18" s="100"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="93"/>
-      <c r="C19" s="100"/>
-      <c r="D19" s="101"/>
-      <c r="E19" s="102"/>
-      <c r="F19" s="106"/>
-      <c r="G19" s="104"/>
-      <c r="H19" s="105"/>
-      <c r="I19" s="102"/>
-      <c r="J19" s="106"/>
-      <c r="K19" s="105"/>
-      <c r="L19" s="105"/>
-      <c r="M19" s="102"/>
-      <c r="N19" s="106"/>
-      <c r="O19" s="105"/>
-      <c r="P19" s="105"/>
-      <c r="Q19" s="102"/>
-      <c r="R19" s="106"/>
-      <c r="S19" s="107"/>
+      <c r="B19" s="94"/>
+      <c r="C19" s="101"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="103"/>
+      <c r="F19" s="107"/>
+      <c r="G19" s="105"/>
+      <c r="H19" s="106"/>
+      <c r="I19" s="103"/>
+      <c r="J19" s="107"/>
+      <c r="K19" s="106"/>
+      <c r="L19" s="106"/>
+      <c r="M19" s="103"/>
+      <c r="N19" s="107"/>
+      <c r="O19" s="106"/>
+      <c r="P19" s="106"/>
+      <c r="Q19" s="103"/>
+      <c r="R19" s="107"/>
+      <c r="S19" s="108"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="93"/>
-      <c r="C20" s="108" t="s">
+      <c r="B20" s="94"/>
+      <c r="C20" s="109" t="s">
         <v>157</v>
       </c>
-      <c r="D20" s="109"/>
-      <c r="E20" s="110"/>
-      <c r="F20" s="114"/>
-      <c r="G20" s="113"/>
-      <c r="H20" s="113"/>
-      <c r="I20" s="129"/>
-      <c r="J20" s="111"/>
-      <c r="K20" s="112"/>
-      <c r="L20" s="112"/>
-      <c r="M20" s="110"/>
-      <c r="N20" s="114"/>
-      <c r="O20" s="113"/>
-      <c r="P20" s="113"/>
-      <c r="Q20" s="110"/>
-      <c r="R20" s="114"/>
-      <c r="S20" s="115"/>
+      <c r="D20" s="110"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="115"/>
+      <c r="G20" s="114"/>
+      <c r="H20" s="114"/>
+      <c r="I20" s="130"/>
+      <c r="J20" s="112"/>
+      <c r="K20" s="113"/>
+      <c r="L20" s="113"/>
+      <c r="M20" s="111"/>
+      <c r="N20" s="115"/>
+      <c r="O20" s="114"/>
+      <c r="P20" s="114"/>
+      <c r="Q20" s="111"/>
+      <c r="R20" s="115"/>
+      <c r="S20" s="116"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="93"/>
-      <c r="C21" s="100"/>
-      <c r="D21" s="101"/>
-      <c r="E21" s="102"/>
-      <c r="F21" s="106"/>
-      <c r="G21" s="105"/>
-      <c r="H21" s="105"/>
-      <c r="I21" s="102"/>
-      <c r="J21" s="106"/>
-      <c r="K21" s="105"/>
-      <c r="L21" s="105"/>
-      <c r="M21" s="102"/>
-      <c r="N21" s="131"/>
-      <c r="O21" s="105"/>
-      <c r="P21" s="105"/>
-      <c r="Q21" s="102"/>
-      <c r="R21" s="106"/>
-      <c r="S21" s="107"/>
+      <c r="B21" s="94"/>
+      <c r="C21" s="101"/>
+      <c r="D21" s="102"/>
+      <c r="E21" s="103"/>
+      <c r="F21" s="107"/>
+      <c r="G21" s="106"/>
+      <c r="H21" s="106"/>
+      <c r="I21" s="103"/>
+      <c r="J21" s="107"/>
+      <c r="K21" s="106"/>
+      <c r="L21" s="106"/>
+      <c r="M21" s="103"/>
+      <c r="N21" s="132"/>
+      <c r="O21" s="106"/>
+      <c r="P21" s="106"/>
+      <c r="Q21" s="103"/>
+      <c r="R21" s="107"/>
+      <c r="S21" s="108"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="93"/>
-      <c r="C22" s="108" t="s">
+      <c r="B22" s="94"/>
+      <c r="C22" s="109" t="s">
         <v>158</v>
       </c>
-      <c r="D22" s="109"/>
-      <c r="E22" s="110"/>
-      <c r="F22" s="114"/>
-      <c r="G22" s="113"/>
-      <c r="H22" s="113"/>
-      <c r="I22" s="110"/>
-      <c r="J22" s="114"/>
-      <c r="K22" s="112"/>
-      <c r="L22" s="112"/>
-      <c r="M22" s="110"/>
-      <c r="N22" s="114"/>
-      <c r="O22" s="113"/>
-      <c r="P22" s="113"/>
-      <c r="Q22" s="110"/>
-      <c r="R22" s="114"/>
-      <c r="S22" s="115"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="111"/>
+      <c r="F22" s="115"/>
+      <c r="G22" s="114"/>
+      <c r="H22" s="114"/>
+      <c r="I22" s="111"/>
+      <c r="J22" s="115"/>
+      <c r="K22" s="113"/>
+      <c r="L22" s="113"/>
+      <c r="M22" s="111"/>
+      <c r="N22" s="115"/>
+      <c r="O22" s="114"/>
+      <c r="P22" s="114"/>
+      <c r="Q22" s="111"/>
+      <c r="R22" s="115"/>
+      <c r="S22" s="116"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="117"/>
-      <c r="C23" s="118"/>
-      <c r="D23" s="119"/>
-      <c r="E23" s="120"/>
-      <c r="F23" s="121"/>
-      <c r="G23" s="123"/>
-      <c r="H23" s="123"/>
-      <c r="I23" s="120"/>
-      <c r="J23" s="121"/>
-      <c r="K23" s="123"/>
-      <c r="L23" s="123"/>
-      <c r="M23" s="120"/>
-      <c r="N23" s="121"/>
-      <c r="O23" s="123"/>
-      <c r="P23" s="123"/>
-      <c r="Q23" s="120"/>
-      <c r="R23" s="121"/>
-      <c r="S23" s="124"/>
+      <c r="B23" s="118"/>
+      <c r="C23" s="119"/>
+      <c r="D23" s="120"/>
+      <c r="E23" s="121"/>
+      <c r="F23" s="122"/>
+      <c r="G23" s="124"/>
+      <c r="H23" s="124"/>
+      <c r="I23" s="121"/>
+      <c r="J23" s="122"/>
+      <c r="K23" s="124"/>
+      <c r="L23" s="124"/>
+      <c r="M23" s="121"/>
+      <c r="N23" s="122"/>
+      <c r="O23" s="124"/>
+      <c r="P23" s="124"/>
+      <c r="Q23" s="121"/>
+      <c r="R23" s="122"/>
+      <c r="S23" s="125"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="82" t="s">
+      <c r="B24" s="83" t="s">
         <v>159</v>
       </c>
-      <c r="C24" s="81" t="s">
+      <c r="C24" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="D24" s="94"/>
-      <c r="E24" s="95"/>
-      <c r="F24" s="98"/>
-      <c r="G24" s="97"/>
-      <c r="H24" s="97"/>
-      <c r="I24" s="95"/>
-      <c r="J24" s="98"/>
-      <c r="K24" s="97"/>
-      <c r="L24" s="97"/>
-      <c r="M24" s="126"/>
-      <c r="N24" s="96"/>
-      <c r="O24" s="125"/>
-      <c r="P24" s="125"/>
-      <c r="Q24" s="95"/>
-      <c r="R24" s="98"/>
-      <c r="S24" s="99"/>
+      <c r="D24" s="95"/>
+      <c r="E24" s="96"/>
+      <c r="F24" s="99"/>
+      <c r="G24" s="98"/>
+      <c r="H24" s="98"/>
+      <c r="I24" s="96"/>
+      <c r="J24" s="99"/>
+      <c r="K24" s="98"/>
+      <c r="L24" s="98"/>
+      <c r="M24" s="127"/>
+      <c r="N24" s="97"/>
+      <c r="O24" s="126"/>
+      <c r="P24" s="126"/>
+      <c r="Q24" s="96"/>
+      <c r="R24" s="99"/>
+      <c r="S24" s="100"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="93"/>
-      <c r="C25" s="100"/>
-      <c r="D25" s="101"/>
-      <c r="E25" s="102"/>
-      <c r="F25" s="106"/>
-      <c r="G25" s="105"/>
-      <c r="H25" s="105"/>
-      <c r="I25" s="102"/>
-      <c r="J25" s="106"/>
-      <c r="K25" s="105"/>
-      <c r="L25" s="105"/>
-      <c r="M25" s="102"/>
-      <c r="N25" s="106"/>
-      <c r="O25" s="105"/>
-      <c r="P25" s="105"/>
-      <c r="Q25" s="102"/>
-      <c r="R25" s="106"/>
-      <c r="S25" s="107"/>
+      <c r="B25" s="94"/>
+      <c r="C25" s="101"/>
+      <c r="D25" s="102"/>
+      <c r="E25" s="103"/>
+      <c r="F25" s="107"/>
+      <c r="G25" s="106"/>
+      <c r="H25" s="106"/>
+      <c r="I25" s="103"/>
+      <c r="J25" s="107"/>
+      <c r="K25" s="106"/>
+      <c r="L25" s="106"/>
+      <c r="M25" s="103"/>
+      <c r="N25" s="107"/>
+      <c r="O25" s="106"/>
+      <c r="P25" s="106"/>
+      <c r="Q25" s="103"/>
+      <c r="R25" s="107"/>
+      <c r="S25" s="108"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="93"/>
-      <c r="C26" s="108" t="s">
+      <c r="B26" s="94"/>
+      <c r="C26" s="109" t="s">
         <v>161</v>
       </c>
-      <c r="D26" s="109"/>
-      <c r="E26" s="110"/>
-      <c r="F26" s="114"/>
-      <c r="G26" s="113"/>
-      <c r="H26" s="113"/>
-      <c r="I26" s="110"/>
-      <c r="J26" s="114"/>
-      <c r="K26" s="113"/>
-      <c r="L26" s="113"/>
-      <c r="M26" s="110"/>
-      <c r="N26" s="114"/>
-      <c r="O26" s="112"/>
-      <c r="P26" s="112"/>
-      <c r="Q26" s="110"/>
-      <c r="R26" s="114"/>
-      <c r="S26" s="115"/>
+      <c r="D26" s="110"/>
+      <c r="E26" s="111"/>
+      <c r="F26" s="115"/>
+      <c r="G26" s="114"/>
+      <c r="H26" s="114"/>
+      <c r="I26" s="111"/>
+      <c r="J26" s="115"/>
+      <c r="K26" s="114"/>
+      <c r="L26" s="114"/>
+      <c r="M26" s="111"/>
+      <c r="N26" s="115"/>
+      <c r="O26" s="113"/>
+      <c r="P26" s="113"/>
+      <c r="Q26" s="111"/>
+      <c r="R26" s="115"/>
+      <c r="S26" s="116"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="93"/>
-      <c r="C27" s="100"/>
-      <c r="D27" s="101"/>
-      <c r="E27" s="102"/>
-      <c r="F27" s="106"/>
-      <c r="G27" s="105"/>
-      <c r="H27" s="105"/>
-      <c r="I27" s="102"/>
-      <c r="J27" s="106"/>
-      <c r="K27" s="105"/>
-      <c r="L27" s="105"/>
-      <c r="M27" s="102"/>
-      <c r="N27" s="106"/>
-      <c r="O27" s="105"/>
-      <c r="P27" s="105"/>
-      <c r="Q27" s="102"/>
-      <c r="R27" s="106"/>
-      <c r="S27" s="107"/>
+      <c r="B27" s="94"/>
+      <c r="C27" s="101"/>
+      <c r="D27" s="102"/>
+      <c r="E27" s="103"/>
+      <c r="F27" s="107"/>
+      <c r="G27" s="106"/>
+      <c r="H27" s="106"/>
+      <c r="I27" s="103"/>
+      <c r="J27" s="107"/>
+      <c r="K27" s="106"/>
+      <c r="L27" s="106"/>
+      <c r="M27" s="103"/>
+      <c r="N27" s="107"/>
+      <c r="O27" s="106"/>
+      <c r="P27" s="106"/>
+      <c r="Q27" s="103"/>
+      <c r="R27" s="107"/>
+      <c r="S27" s="108"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="93"/>
-      <c r="C28" s="108" t="s">
+      <c r="B28" s="94"/>
+      <c r="C28" s="109" t="s">
         <v>162</v>
       </c>
-      <c r="D28" s="109"/>
-      <c r="E28" s="110"/>
-      <c r="F28" s="114"/>
-      <c r="G28" s="113"/>
-      <c r="H28" s="113"/>
-      <c r="I28" s="110"/>
-      <c r="J28" s="114"/>
-      <c r="K28" s="113"/>
-      <c r="L28" s="113"/>
-      <c r="M28" s="110"/>
-      <c r="N28" s="114"/>
-      <c r="O28" s="113"/>
-      <c r="P28" s="112"/>
-      <c r="Q28" s="129"/>
-      <c r="R28" s="114"/>
-      <c r="S28" s="115"/>
+      <c r="D28" s="110"/>
+      <c r="E28" s="111"/>
+      <c r="F28" s="115"/>
+      <c r="G28" s="114"/>
+      <c r="H28" s="114"/>
+      <c r="I28" s="111"/>
+      <c r="J28" s="115"/>
+      <c r="K28" s="114"/>
+      <c r="L28" s="114"/>
+      <c r="M28" s="111"/>
+      <c r="N28" s="115"/>
+      <c r="O28" s="114"/>
+      <c r="P28" s="113"/>
+      <c r="Q28" s="130"/>
+      <c r="R28" s="115"/>
+      <c r="S28" s="116"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="93"/>
-      <c r="C29" s="87"/>
-      <c r="D29" s="132"/>
-      <c r="E29" s="133"/>
-      <c r="F29" s="134"/>
-      <c r="G29" s="135"/>
-      <c r="H29" s="136"/>
-      <c r="I29" s="133"/>
-      <c r="J29" s="134"/>
-      <c r="K29" s="135"/>
-      <c r="L29" s="136"/>
-      <c r="M29" s="133"/>
-      <c r="N29" s="137"/>
-      <c r="O29" s="136"/>
-      <c r="P29" s="135"/>
-      <c r="Q29" s="133"/>
-      <c r="R29" s="134"/>
-      <c r="S29" s="138"/>
+      <c r="B29" s="94"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="133"/>
+      <c r="E29" s="134"/>
+      <c r="F29" s="135"/>
+      <c r="G29" s="136"/>
+      <c r="H29" s="137"/>
+      <c r="I29" s="134"/>
+      <c r="J29" s="135"/>
+      <c r="K29" s="136"/>
+      <c r="L29" s="137"/>
+      <c r="M29" s="134"/>
+      <c r="N29" s="138"/>
+      <c r="O29" s="137"/>
+      <c r="P29" s="136"/>
+      <c r="Q29" s="134"/>
+      <c r="R29" s="135"/>
+      <c r="S29" s="139"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="139" t="s">
+      <c r="B30" s="140" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="140" t="s">
+      <c r="C30" s="141" t="s">
         <v>106</v>
       </c>
-      <c r="D30" s="94"/>
-      <c r="E30" s="141"/>
-      <c r="F30" s="142"/>
-      <c r="G30" s="142"/>
-      <c r="H30" s="143"/>
-      <c r="I30" s="144"/>
-      <c r="J30" s="142"/>
-      <c r="K30" s="142"/>
-      <c r="L30" s="143"/>
-      <c r="M30" s="144"/>
-      <c r="N30" s="142"/>
-      <c r="O30" s="143"/>
-      <c r="P30" s="142"/>
-      <c r="Q30" s="144"/>
-      <c r="R30" s="142"/>
-      <c r="S30" s="145"/>
+      <c r="D30" s="95"/>
+      <c r="E30" s="142"/>
+      <c r="F30" s="143"/>
+      <c r="G30" s="143"/>
+      <c r="H30" s="144"/>
+      <c r="I30" s="145"/>
+      <c r="J30" s="143"/>
+      <c r="K30" s="143"/>
+      <c r="L30" s="144"/>
+      <c r="M30" s="145"/>
+      <c r="N30" s="143"/>
+      <c r="O30" s="144"/>
+      <c r="P30" s="143"/>
+      <c r="Q30" s="145"/>
+      <c r="R30" s="143"/>
+      <c r="S30" s="146"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="146"/>
-      <c r="C31" s="147"/>
-      <c r="D31" s="101"/>
-      <c r="E31" s="148"/>
-      <c r="F31" s="149"/>
-      <c r="G31" s="149"/>
-      <c r="H31" s="150"/>
-      <c r="I31" s="151"/>
-      <c r="J31" s="149"/>
-      <c r="K31" s="152"/>
-      <c r="L31" s="150"/>
-      <c r="M31" s="151"/>
-      <c r="N31" s="149"/>
-      <c r="O31" s="150"/>
-      <c r="P31" s="149"/>
-      <c r="Q31" s="151"/>
-      <c r="R31" s="149"/>
-      <c r="S31" s="107"/>
+      <c r="B31" s="147"/>
+      <c r="C31" s="148"/>
+      <c r="D31" s="102"/>
+      <c r="E31" s="149"/>
+      <c r="F31" s="150"/>
+      <c r="G31" s="150"/>
+      <c r="H31" s="151"/>
+      <c r="I31" s="152"/>
+      <c r="J31" s="150"/>
+      <c r="K31" s="153"/>
+      <c r="L31" s="151"/>
+      <c r="M31" s="152"/>
+      <c r="N31" s="150"/>
+      <c r="O31" s="151"/>
+      <c r="P31" s="150"/>
+      <c r="Q31" s="152"/>
+      <c r="R31" s="150"/>
+      <c r="S31" s="108"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="146"/>
-      <c r="C32" s="147" t="s">
+      <c r="B32" s="147"/>
+      <c r="C32" s="148" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="109"/>
-      <c r="E32" s="153"/>
-      <c r="F32" s="154"/>
-      <c r="G32" s="154"/>
-      <c r="H32" s="155"/>
-      <c r="I32" s="156"/>
-      <c r="J32" s="154"/>
-      <c r="K32" s="154"/>
-      <c r="L32" s="155"/>
-      <c r="M32" s="156"/>
-      <c r="N32" s="154"/>
-      <c r="O32" s="155"/>
-      <c r="P32" s="154"/>
-      <c r="Q32" s="156"/>
-      <c r="R32" s="154"/>
-      <c r="S32" s="157"/>
+      <c r="D32" s="110"/>
+      <c r="E32" s="154"/>
+      <c r="F32" s="155"/>
+      <c r="G32" s="155"/>
+      <c r="H32" s="156"/>
+      <c r="I32" s="157"/>
+      <c r="J32" s="155"/>
+      <c r="K32" s="155"/>
+      <c r="L32" s="156"/>
+      <c r="M32" s="157"/>
+      <c r="N32" s="155"/>
+      <c r="O32" s="156"/>
+      <c r="P32" s="155"/>
+      <c r="Q32" s="157"/>
+      <c r="R32" s="155"/>
+      <c r="S32" s="158"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="146"/>
-      <c r="C33" s="147"/>
-      <c r="D33" s="101"/>
-      <c r="E33" s="148"/>
-      <c r="F33" s="152"/>
-      <c r="G33" s="149"/>
-      <c r="H33" s="158"/>
-      <c r="I33" s="159"/>
-      <c r="J33" s="149"/>
-      <c r="K33" s="152"/>
-      <c r="L33" s="150"/>
-      <c r="M33" s="151"/>
-      <c r="N33" s="149"/>
-      <c r="O33" s="150"/>
-      <c r="P33" s="149"/>
-      <c r="Q33" s="151"/>
-      <c r="R33" s="149"/>
-      <c r="S33" s="107"/>
+      <c r="B33" s="147"/>
+      <c r="C33" s="148"/>
+      <c r="D33" s="102"/>
+      <c r="E33" s="149"/>
+      <c r="F33" s="153"/>
+      <c r="G33" s="150"/>
+      <c r="H33" s="159"/>
+      <c r="I33" s="160"/>
+      <c r="J33" s="150"/>
+      <c r="K33" s="153"/>
+      <c r="L33" s="151"/>
+      <c r="M33" s="152"/>
+      <c r="N33" s="150"/>
+      <c r="O33" s="151"/>
+      <c r="P33" s="150"/>
+      <c r="Q33" s="152"/>
+      <c r="R33" s="150"/>
+      <c r="S33" s="108"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="146"/>
-      <c r="C34" s="100" t="s">
+      <c r="B34" s="147"/>
+      <c r="C34" s="101" t="s">
         <v>163</v>
       </c>
-      <c r="D34" s="132"/>
-      <c r="E34" s="160"/>
-      <c r="F34" s="161"/>
-      <c r="G34" s="161"/>
-      <c r="H34" s="162"/>
-      <c r="I34" s="163"/>
-      <c r="J34" s="161"/>
-      <c r="K34" s="161"/>
-      <c r="L34" s="162"/>
-      <c r="M34" s="163"/>
-      <c r="N34" s="161"/>
-      <c r="O34" s="162"/>
-      <c r="P34" s="161"/>
-      <c r="Q34" s="163"/>
-      <c r="R34" s="161"/>
-      <c r="S34" s="164"/>
-      <c r="U34" s="165"/>
-      <c r="V34" s="166" t="s">
+      <c r="D34" s="133"/>
+      <c r="E34" s="161"/>
+      <c r="F34" s="162"/>
+      <c r="G34" s="162"/>
+      <c r="H34" s="163"/>
+      <c r="I34" s="164"/>
+      <c r="J34" s="162"/>
+      <c r="K34" s="162"/>
+      <c r="L34" s="163"/>
+      <c r="M34" s="164"/>
+      <c r="N34" s="162"/>
+      <c r="O34" s="163"/>
+      <c r="P34" s="162"/>
+      <c r="Q34" s="164"/>
+      <c r="R34" s="162"/>
+      <c r="S34" s="165"/>
+      <c r="U34" s="166"/>
+      <c r="V34" s="167" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="167"/>
-      <c r="C35" s="168"/>
-      <c r="D35" s="119"/>
-      <c r="E35" s="169"/>
-      <c r="F35" s="170"/>
-      <c r="G35" s="170"/>
-      <c r="H35" s="171"/>
-      <c r="I35" s="172"/>
-      <c r="J35" s="170"/>
-      <c r="K35" s="170"/>
-      <c r="L35" s="171"/>
-      <c r="M35" s="172"/>
-      <c r="N35" s="170"/>
-      <c r="O35" s="171"/>
-      <c r="P35" s="170"/>
-      <c r="Q35" s="172"/>
-      <c r="R35" s="170"/>
-      <c r="S35" s="124"/>
-      <c r="U35" s="173"/>
-      <c r="V35" s="174" t="s">
+      <c r="B35" s="168"/>
+      <c r="C35" s="169"/>
+      <c r="D35" s="120"/>
+      <c r="E35" s="170"/>
+      <c r="F35" s="171"/>
+      <c r="G35" s="171"/>
+      <c r="H35" s="172"/>
+      <c r="I35" s="173"/>
+      <c r="J35" s="171"/>
+      <c r="K35" s="171"/>
+      <c r="L35" s="172"/>
+      <c r="M35" s="173"/>
+      <c r="N35" s="171"/>
+      <c r="O35" s="172"/>
+      <c r="P35" s="171"/>
+      <c r="Q35" s="173"/>
+      <c r="R35" s="171"/>
+      <c r="S35" s="125"/>
+      <c r="U35" s="174"/>
+      <c r="V35" s="175" t="s">
         <v>165</v>
       </c>
     </row>

--- a/Documentation/HoferL-JournalPlanif-M5.xlsx
+++ b/Documentation/HoferL-JournalPlanif-M5.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="169">
   <si>
     <t>date</t>
   </si>
@@ -286,6 +286,15 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;-- A jour avec la BDD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test de fonctionnement sur Windows, Linux et MacOS. Fonctionnel. Correction d'un dépendance sur Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajout de l'interface pour éditer les modules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implémentation des intéractions avec la BDD pour la gestion de module</t>
   </si>
   <si>
     <t>Phases</t>
@@ -1574,10 +1583,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3646,8 +3655,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E52">
-  <autoFilter ref="B2:E52"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E54">
+  <autoFilter ref="B2:E54"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -4211,7 +4220,7 @@
       </c>
       <c r="I3" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.02412868632707775</v>
+        <v>2.3195876288659791e-002</v>
       </c>
       <c r="J3" s="12" t="str" cm="1">
         <f t="array" ref="J3:J9">_xlfn._xlws.FILTER(G3:G10,H3:H10&gt;0)</f>
@@ -4227,7 +4236,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="6">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
@@ -4244,7 +4253,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.02412868632707775</v>
+        <v>2.3195876288659791e-002</v>
       </c>
       <c r="J4" s="4" t="str">
         <f/>
@@ -4277,7 +4286,7 @@
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.072386058981233251</v>
+        <v>6.958762886597937e-002</v>
       </c>
       <c r="J5" s="4" t="str">
         <f/>
@@ -4293,7 +4302,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="6">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
@@ -4310,7 +4319,7 @@
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.13672922252010725</v>
+        <v>0.13144329896907214</v>
       </c>
       <c r="J6" s="4" t="str">
         <f/>
@@ -4326,7 +4335,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="6">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>8</v>
@@ -4343,7 +4352,7 @@
       </c>
       <c r="I7" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.30160857908847188</v>
+        <v>0.28994845360824739</v>
       </c>
       <c r="J7" s="4" t="str">
         <f/>
@@ -4372,11 +4381,11 @@
       </c>
       <c r="H8" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>53.500000000000007</v>
+        <v>58.500000000000014</v>
       </c>
       <c r="I8" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.4302949061662199</v>
+        <v>0.45231958762886604</v>
       </c>
       <c r="J8" s="4" t="str">
         <f/>
@@ -4384,7 +4393,7 @@
       </c>
       <c r="K8" s="13">
         <f/>
-        <v>53.500000000000007</v>
+        <v>58.500000000000014</v>
       </c>
     </row>
     <row r="9">
@@ -4409,7 +4418,7 @@
       </c>
       <c r="I9" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.010723860589812333</v>
+        <v>1.0309278350515462e-002</v>
       </c>
       <c r="J9" s="4" t="str">
         <f/>
@@ -4425,7 +4434,7 @@
         <v>22</v>
       </c>
       <c r="C10" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>12</v>
@@ -4452,7 +4461,7 @@
         <v>22</v>
       </c>
       <c r="C11" s="6">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>12</v>
@@ -4465,7 +4474,7 @@
       </c>
       <c r="H11" s="10">
         <f>SUM(H3:H10)</f>
-        <v>124.33333333333333</v>
+        <v>129.33333333333334</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -4475,7 +4484,7 @@
         <v>22</v>
       </c>
       <c r="C12" s="6">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>10</v>
@@ -4490,7 +4499,7 @@
         <v>22</v>
       </c>
       <c r="C13" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>12</v>
@@ -4505,7 +4514,7 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>12</v>
@@ -4561,7 +4570,7 @@
         <v>35</v>
       </c>
       <c r="C18" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>10</v>
@@ -4575,7 +4584,7 @@
         <v>37</v>
       </c>
       <c r="C19" s="6">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>12</v>
@@ -4589,7 +4598,7 @@
         <v>39</v>
       </c>
       <c r="C20" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>19</v>
@@ -4603,7 +4612,7 @@
         <v>39</v>
       </c>
       <c r="C21" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>15</v>
@@ -4631,7 +4640,7 @@
         <v>43</v>
       </c>
       <c r="C23" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>15</v>
@@ -4645,7 +4654,7 @@
         <v>45</v>
       </c>
       <c r="C24" s="6">
-        <v>0.0625</v>
+        <v>6.25e-002</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>15</v>
@@ -4687,7 +4696,7 @@
         <v>49</v>
       </c>
       <c r="C27" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>12</v>
@@ -4701,7 +4710,7 @@
         <v>52</v>
       </c>
       <c r="C28" s="6">
-        <v>0.0625</v>
+        <v>6.25e-002</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>15</v>
@@ -4743,7 +4752,7 @@
         <v>46087</v>
       </c>
       <c r="C31" s="6">
-        <v>0.020833333333333332</v>
+        <v>2.0833333333333332e-002</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>21</v>
@@ -4771,7 +4780,7 @@
         <v>46091</v>
       </c>
       <c r="C33" s="6">
-        <v>0.020833333333333332</v>
+        <v>2.0833333333333332e-002</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>12</v>
@@ -4799,7 +4808,7 @@
         <v>46091</v>
       </c>
       <c r="C35" s="6">
-        <v>0.020833333333333332</v>
+        <v>2.0833333333333332e-002</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>19</v>
@@ -4827,7 +4836,7 @@
         <v>46093</v>
       </c>
       <c r="C37" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>19</v>
@@ -4855,7 +4864,7 @@
         <v>46087</v>
       </c>
       <c r="C39" s="6">
-        <v>0.020833333333333332</v>
+        <v>2.0833333333333332e-002</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>21</v>
@@ -4942,7 +4951,7 @@
         <v>46100</v>
       </c>
       <c r="C45" s="6">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>8</v>
@@ -4956,7 +4965,7 @@
         <v>46100</v>
       </c>
       <c r="C46" s="6">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>19</v>
@@ -4984,7 +4993,7 @@
         <v>46102</v>
       </c>
       <c r="C48" s="21">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>8</v>
@@ -5043,26 +5052,42 @@
         <v>46104</v>
       </c>
       <c r="C52" s="21">
-        <v>0.013888888888888888</v>
-      </c>
-      <c r="D52" s="22" t="s">
+        <v>1.3888888888888888e-002</v>
+      </c>
+      <c r="D52" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E52" s="23" t="s">
-        <v>56</v>
+      <c r="E52" s="22" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="20"/>
-      <c r="C53" s="24"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="8"/>
-    </row>
-    <row r="54">
-      <c r="B54" s="20"/>
-      <c r="C54" s="24"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="8"/>
+      <c r="B53" s="20">
+        <v>46117</v>
+      </c>
+      <c r="C53" s="21">
+        <v>0.125</v>
+      </c>
+      <c r="D53" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E53" s="22" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="54" ht="28.5">
+      <c r="B54" s="20">
+        <v>46118</v>
+      </c>
+      <c r="C54" s="21">
+        <v>8.3333333333333329e-002</v>
+      </c>
+      <c r="D54" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E54" s="22" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="55">
       <c r="B55" s="20"/>
@@ -5236,7 +5261,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00DE0023-00B9-4D4C-941E-0023007B0050}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00D0007A-0025-4C9B-8357-00B900E50062}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -5269,7 +5294,7 @@
     </row>
     <row r="2">
       <c r="A2" s="25" t="str" cm="1">
-        <f t="array" ref="A2:A28">_xlfn.UNIQUE(Journal[date])</f>
+        <f t="array" ref="A2:A30">_xlfn.UNIQUE(Journal[date])</f>
         <v>20.01.2026</v>
       </c>
       <c r="B2" s="26">
@@ -5340,7 +5365,7 @@
       </c>
       <c r="B8" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="C8"/>
     </row>
@@ -5351,7 +5376,7 @@
       </c>
       <c r="B9" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="C9"/>
     </row>
@@ -5373,7 +5398,7 @@
       </c>
       <c r="B11" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="C11"/>
     </row>
@@ -5384,7 +5409,7 @@
       </c>
       <c r="B12" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
-        <v>0.0625</v>
+        <v>6.25e-002</v>
       </c>
       <c r="C12"/>
     </row>
@@ -5461,7 +5486,7 @@
       </c>
       <c r="B19" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="C19"/>
     </row>
@@ -5567,21 +5592,27 @@
       </c>
       <c r="C28" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
-        <v>0.013888888888888888</v>
+        <v>1.3888888888888888e-002</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="25"/>
+      <c r="A29" s="25">
+        <f/>
+        <v>46117</v>
+      </c>
       <c r="C29" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="25"/>
+      <c r="A30" s="25">
+        <f/>
+        <v>46118</v>
+      </c>
       <c r="C30" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
-        <v>0</v>
+        <v>8.3333333333333329e-002</v>
       </c>
     </row>
     <row r="31">
@@ -7028,16 +7059,16 @@
   <sheetData>
     <row r="1" s="32" customFormat="1" ht="66.599999999999994" customHeight="1">
       <c r="B1" s="33" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C1" s="34" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D1" s="35" t="s">
         <v>5</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F1" s="36" t="s">
         <v>11</v>
@@ -7046,7 +7077,7 @@
         <v>17</v>
       </c>
       <c r="H1" s="38" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I1" s="35" t="s">
         <v>22</v>
@@ -7055,85 +7086,85 @@
         <v>37</v>
       </c>
       <c r="K1" s="35" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L1" s="39" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M1" s="35" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="N1" s="37" t="s">
         <v>47</v>
       </c>
       <c r="O1" s="38" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="P1" s="35" t="s">
         <v>49</v>
       </c>
       <c r="Q1" s="35" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R1" s="35" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="S1" s="35" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="T1" s="35" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="U1" s="35" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V1" s="37" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="W1" s="40" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="X1" s="35" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="Y1" s="35" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="Z1" s="37" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AA1" s="41" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="AB1" s="42" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AC1" s="42" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AD1" s="39" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AE1" s="43" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AF1" s="44" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AG1" s="45" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AH1" s="45" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="AI1" s="45" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="AJ1" s="45" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="AK1" s="42" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="AL1" s="46"/>
       <c r="AM1" s="46"/>
@@ -7229,7 +7260,7 @@
     <row r="4" ht="12" customHeight="1">
       <c r="B4" s="47"/>
       <c r="C4" s="48" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D4" s="49"/>
       <c r="E4" s="49"/>
@@ -7385,7 +7416,7 @@
     <row r="8" ht="12" customHeight="1">
       <c r="B8" s="47"/>
       <c r="C8" s="48" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D8" s="63"/>
       <c r="E8" s="63"/>
@@ -7463,7 +7494,7 @@
     <row r="10" ht="12" customHeight="1">
       <c r="B10" s="47"/>
       <c r="C10" s="48" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D10" s="49"/>
       <c r="E10" s="49"/>
@@ -7541,7 +7572,7 @@
     <row r="12" ht="12" customHeight="1">
       <c r="B12" s="47"/>
       <c r="C12" s="48" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D12" s="49"/>
       <c r="E12" s="49"/>
@@ -7618,10 +7649,10 @@
     </row>
     <row r="14" ht="12" customHeight="1">
       <c r="B14" s="65" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C14" s="66" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D14" s="63"/>
       <c r="E14" s="63"/>
@@ -7699,7 +7730,7 @@
     <row r="16" ht="12" customHeight="1">
       <c r="B16" s="65"/>
       <c r="C16" s="66" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D16" s="63"/>
       <c r="E16" s="63"/>
@@ -7774,13 +7805,13 @@
       <c r="AJ17" s="68"/>
       <c r="AK17" s="68"/>
       <c r="AN17" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
       <c r="B18" s="65"/>
       <c r="C18" s="66" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D18" s="63"/>
       <c r="E18" s="63"/>
@@ -7858,7 +7889,7 @@
     <row r="20" ht="12" customHeight="1">
       <c r="B20" s="65"/>
       <c r="C20" s="66" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D20" s="68"/>
       <c r="E20" s="68"/>
@@ -7936,7 +7967,7 @@
     <row r="22" ht="12" customHeight="1">
       <c r="B22" s="65"/>
       <c r="C22" s="66" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D22" s="68"/>
       <c r="E22" s="68"/>
@@ -8014,7 +8045,7 @@
     <row r="24" ht="12" customHeight="1">
       <c r="B24" s="65"/>
       <c r="C24" s="66" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D24" s="68"/>
       <c r="E24" s="68"/>
@@ -8091,10 +8122,10 @@
     </row>
     <row r="26" ht="12" customHeight="1">
       <c r="B26" s="47" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C26" s="48" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D26" s="49"/>
       <c r="E26" s="49"/>
@@ -8172,7 +8203,7 @@
     <row r="28" ht="12" customHeight="1">
       <c r="B28" s="47"/>
       <c r="C28" s="48" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D28" s="49"/>
       <c r="E28" s="49"/>
@@ -8250,7 +8281,7 @@
     <row r="30" ht="12" customHeight="1">
       <c r="B30" s="47"/>
       <c r="C30" s="48" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D30" s="49"/>
       <c r="E30" s="49"/>
@@ -8328,7 +8359,7 @@
     <row r="32" ht="12" customHeight="1">
       <c r="B32" s="47"/>
       <c r="C32" s="48" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D32" s="49"/>
       <c r="E32" s="49"/>
@@ -8405,10 +8436,10 @@
     </row>
     <row r="34" ht="12" customHeight="1">
       <c r="B34" s="65" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C34" s="74" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D34" s="68"/>
       <c r="E34" s="68"/>
@@ -8486,7 +8517,7 @@
     <row r="36" ht="12" customHeight="1">
       <c r="B36" s="65"/>
       <c r="C36" s="74" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D36" s="68"/>
       <c r="E36" s="68"/>
@@ -8564,7 +8595,7 @@
     <row r="38" ht="12" customHeight="1">
       <c r="B38" s="65"/>
       <c r="C38" s="74" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D38" s="68"/>
       <c r="E38" s="68"/>
@@ -8642,7 +8673,7 @@
     <row r="40" ht="12" customHeight="1">
       <c r="B40" s="65"/>
       <c r="C40" s="74" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D40" s="68"/>
       <c r="E40" s="68"/>
@@ -8722,7 +8753,7 @@
         <v>21</v>
       </c>
       <c r="C42" s="77" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D42" s="49"/>
       <c r="E42" s="49"/>
@@ -8800,7 +8831,7 @@
     <row r="44" ht="12" customHeight="1">
       <c r="B44" s="47"/>
       <c r="C44" s="77" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D44" s="49"/>
       <c r="E44" s="49"/>
@@ -8877,7 +8908,7 @@
     </row>
     <row r="46" ht="12" customHeight="1">
       <c r="B46" s="65" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C46" s="66" t="s">
         <v>24</v>
@@ -8955,14 +8986,14 @@
       <c r="AJ47" s="68"/>
       <c r="AK47" s="68"/>
       <c r="AN47" s="78" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AO47" s="63"/>
     </row>
     <row r="48" ht="12" customHeight="1">
       <c r="B48" s="65"/>
       <c r="C48" s="66" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D48" s="68"/>
       <c r="E48" s="68"/>
@@ -8999,7 +9030,7 @@
       <c r="AJ48" s="68"/>
       <c r="AK48" s="79"/>
       <c r="AN48" s="78" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="AO48" s="62"/>
     </row>
@@ -9041,7 +9072,7 @@
       <c r="AJ49" s="68"/>
       <c r="AK49" s="68"/>
       <c r="AN49" s="78" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="AO49" s="58"/>
     </row>
@@ -9110,37 +9141,37 @@
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
       <c r="B2" s="81" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C2" s="82" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D2" s="83" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E2" s="84" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F2" s="85" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G2" s="85"/>
       <c r="H2" s="85"/>
       <c r="I2" s="84"/>
       <c r="J2" s="85" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="K2" s="85"/>
       <c r="L2" s="85"/>
       <c r="M2" s="84"/>
       <c r="N2" s="85" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="O2" s="85"/>
       <c r="P2" s="85"/>
       <c r="Q2" s="84"/>
       <c r="R2" s="85" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="S2" s="86"/>
       <c r="AD2" s="29"/>
@@ -9149,7 +9180,7 @@
       <c r="B3" s="87"/>
       <c r="C3" s="88"/>
       <c r="D3" s="89" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E3" s="90">
         <v>4</v>
@@ -9197,15 +9228,15 @@
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
       <c r="B4" s="94" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C4" s="82" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D4" s="95"/>
       <c r="E4" s="96"/>
@@ -9224,7 +9255,7 @@
       <c r="R4" s="99"/>
       <c r="S4" s="100"/>
       <c r="U4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
@@ -9250,7 +9281,7 @@
     <row r="6" ht="12" customHeight="1">
       <c r="B6" s="94"/>
       <c r="C6" s="109" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D6" s="110"/>
       <c r="E6" s="111"/>
@@ -9269,7 +9300,7 @@
       <c r="R6" s="115"/>
       <c r="S6" s="116"/>
       <c r="U6" s="117" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="V6" s="117"/>
     </row>
@@ -9293,13 +9324,13 @@
       <c r="R7" s="107"/>
       <c r="S7" s="108"/>
       <c r="U7" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
       <c r="B8" s="94"/>
       <c r="C8" s="109" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D8" s="110"/>
       <c r="E8" s="111"/>
@@ -9318,7 +9349,7 @@
       <c r="R8" s="115"/>
       <c r="S8" s="116"/>
       <c r="U8" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
@@ -9344,7 +9375,7 @@
     <row r="10" ht="12" customHeight="1">
       <c r="B10" s="94"/>
       <c r="C10" s="109" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D10" s="110"/>
       <c r="E10" s="111"/>
@@ -9385,10 +9416,10 @@
     </row>
     <row r="12" ht="12" customHeight="1">
       <c r="B12" s="81" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C12" s="82" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D12" s="95"/>
       <c r="E12" s="96"/>
@@ -9430,7 +9461,7 @@
     <row r="14" ht="12" customHeight="1">
       <c r="B14" s="94"/>
       <c r="C14" s="109" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D14" s="128"/>
       <c r="E14" s="111"/>
@@ -9472,7 +9503,7 @@
     <row r="16" ht="12" customHeight="1">
       <c r="B16" s="94"/>
       <c r="C16" s="109" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D16" s="110"/>
       <c r="E16" s="111"/>
@@ -9513,10 +9544,10 @@
     </row>
     <row r="18" ht="12" customHeight="1">
       <c r="B18" s="83" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C18" s="82" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D18" s="95"/>
       <c r="E18" s="96"/>
@@ -9558,7 +9589,7 @@
     <row r="20" ht="12" customHeight="1">
       <c r="B20" s="94"/>
       <c r="C20" s="109" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D20" s="110"/>
       <c r="E20" s="111"/>
@@ -9600,7 +9631,7 @@
     <row r="22" ht="12" customHeight="1">
       <c r="B22" s="94"/>
       <c r="C22" s="109" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D22" s="110"/>
       <c r="E22" s="111"/>
@@ -9641,10 +9672,10 @@
     </row>
     <row r="24" ht="12" customHeight="1">
       <c r="B24" s="83" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C24" s="82" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D24" s="95"/>
       <c r="E24" s="96"/>
@@ -9686,7 +9717,7 @@
     <row r="26" ht="12" customHeight="1">
       <c r="B26" s="94"/>
       <c r="C26" s="109" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D26" s="110"/>
       <c r="E26" s="111"/>
@@ -9728,7 +9759,7 @@
     <row r="28" ht="12" customHeight="1">
       <c r="B28" s="94"/>
       <c r="C28" s="109" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D28" s="110"/>
       <c r="E28" s="111"/>
@@ -9772,7 +9803,7 @@
         <v>12</v>
       </c>
       <c r="C30" s="141" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D30" s="95"/>
       <c r="E30" s="142"/>
@@ -9856,7 +9887,7 @@
     <row r="34" ht="12" customHeight="1">
       <c r="B34" s="147"/>
       <c r="C34" s="101" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D34" s="133"/>
       <c r="E34" s="161"/>
@@ -9876,7 +9907,7 @@
       <c r="S34" s="165"/>
       <c r="U34" s="166"/>
       <c r="V34" s="167" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
@@ -9900,7 +9931,7 @@
       <c r="S35" s="125"/>
       <c r="U35" s="174"/>
       <c r="V35" s="175" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/HoferL-JournalPlanif-M5.xlsx
+++ b/Documentation/HoferL-JournalPlanif-M5.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="1" state="visible" r:id="rId4"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="172">
   <si>
     <t>date</t>
   </si>
@@ -285,16 +285,25 @@
     <t xml:space="preserve">Finalisation du PoC. Très concluant, fonctionnel et fluide. Merge de la branche PDF -&gt; Main.</t>
   </si>
   <si>
+    <t xml:space="preserve">Test de fonctionnement sur Windows, Linux et MacOS. Fonctionnel. Correction d'un dépendance sur Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajout de l'interface pour éditer les modules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implémentation des intéractions avec la BDD pour la gestion de module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lecture de la mise a jour d'Avalonia 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migration avalonia 11.3.13 vers 12.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correction de fonctionnement + Optimisation et suppression de mem leak</t>
+  </si>
+  <si>
     <t xml:space="preserve">&lt;-- A jour avec la BDD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test de fonctionnement sur Windows, Linux et MacOS. Fonctionnel. Correction d'un dépendance sur Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ajout de l'interface pour éditer les modules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implémentation des intéractions avec la BDD pour la gestion de module</t>
   </si>
   <si>
     <t>Phases</t>
@@ -2198,7 +2207,7 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9</c:v>
+                  <c:v>9.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>17</c:v>
@@ -2207,7 +2216,7 @@
                   <c:v>37.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>53.50000000000001</c:v>
+                  <c:v>63.000000000000014</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2434,9 +2443,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>SommeParJours!$A$2:$A$27</c:f>
+              <c:f>SommeParJours!$A$2:$A$32</c:f>
               <c:strCache>
-                <c:ptCount val="26"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>20.01.2026</c:v>
                 </c:pt>
@@ -2515,15 +2524,30 @@
                 <c:pt idx="25">
                   <c:v>3/22/2026</c:v>
                 </c:pt>
+                <c:pt idx="26">
+                  <c:v>3/23/2026</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4/5/2026</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>4/6/2026</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>4/7/2026</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>4/10/2026</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SommeParJours!$B$2:$B$27</c:f>
+              <c:f>SommeParJours!$B$2:$B$32</c:f>
               <c:numCache>
                 <c:formatCode>h:mm;@</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>0.16666666666666666</c:v>
                 </c:pt>
@@ -2601,6 +2625,21 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0.375</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.013888888888888888</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.08333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.08333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3655,8 +3694,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E54">
-  <autoFilter ref="B2:E54"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E57">
+  <autoFilter ref="B2:E57"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -4220,7 +4259,7 @@
       </c>
       <c r="I3" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>2.3195876288659791e-002</v>
+        <v>2.2332506203473945e-002</v>
       </c>
       <c r="J3" s="12" t="str" cm="1">
         <f t="array" ref="J3:J9">_xlfn._xlws.FILTER(G3:G10,H3:H10&gt;0)</f>
@@ -4253,7 +4292,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>2.3195876288659791e-002</v>
+        <v>2.2332506203473945e-002</v>
       </c>
       <c r="J4" s="4" t="str">
         <f/>
@@ -4282,11 +4321,11 @@
       </c>
       <c r="H5" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>6.958762886597937e-002</v>
+        <v>7.0719602977667495e-002</v>
       </c>
       <c r="J5" s="4" t="str">
         <f/>
@@ -4294,7 +4333,7 @@
       </c>
       <c r="K5" s="13">
         <f/>
-        <v>9</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="6">
@@ -4319,7 +4358,7 @@
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.13144329896907214</v>
+        <v>0.12655086848635236</v>
       </c>
       <c r="J6" s="4" t="str">
         <f/>
@@ -4352,7 +4391,7 @@
       </c>
       <c r="I7" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.28994845360824739</v>
+        <v>0.27915632754342429</v>
       </c>
       <c r="J7" s="4" t="str">
         <f/>
@@ -4381,11 +4420,11 @@
       </c>
       <c r="H8" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>58.500000000000014</v>
+        <v>63.000000000000014</v>
       </c>
       <c r="I8" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.45231958762886604</v>
+        <v>0.46898263027295295</v>
       </c>
       <c r="J8" s="4" t="str">
         <f/>
@@ -4393,7 +4432,7 @@
       </c>
       <c r="K8" s="13">
         <f/>
-        <v>58.500000000000014</v>
+        <v>63.000000000000014</v>
       </c>
     </row>
     <row r="9">
@@ -4418,7 +4457,7 @@
       </c>
       <c r="I9" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>1.0309278350515462e-002</v>
+        <v>9.9255583126550851e-003</v>
       </c>
       <c r="J9" s="4" t="str">
         <f/>
@@ -4474,7 +4513,7 @@
       </c>
       <c r="H11" s="10">
         <f>SUM(H3:H10)</f>
-        <v>129.33333333333334</v>
+        <v>134.33333333333334</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -5043,9 +5082,6 @@
       <c r="E51" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="G51" t="s">
-        <v>76</v>
-      </c>
     </row>
     <row r="52" ht="28.5">
       <c r="B52" s="20">
@@ -5058,7 +5094,7 @@
         <v>21</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="53">
@@ -5068,11 +5104,11 @@
       <c r="C53" s="21">
         <v>0.125</v>
       </c>
-      <c r="D53" s="23" t="s">
+      <c r="D53" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" ht="28.5">
@@ -5082,30 +5118,57 @@
       <c r="C54" s="21">
         <v>8.3333333333333329e-002</v>
       </c>
-      <c r="D54" s="23" t="s">
+      <c r="D54" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E54" s="22" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="20">
+        <v>46119</v>
+      </c>
+      <c r="C55" s="21">
+        <v>2.0833333333333332e-002</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="22" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="20"/>
-      <c r="C55" s="24"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="8"/>
-    </row>
     <row r="56">
-      <c r="B56" s="20"/>
-      <c r="C56" s="24"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="8"/>
-    </row>
-    <row r="57">
-      <c r="B57" s="20"/>
-      <c r="C57" s="24"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="8"/>
+      <c r="B56" s="20">
+        <v>46119</v>
+      </c>
+      <c r="C56" s="21">
+        <v>6.25e-002</v>
+      </c>
+      <c r="D56" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" s="22" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="57" ht="28.5">
+      <c r="B57" s="20">
+        <v>46122</v>
+      </c>
+      <c r="C57" s="21">
+        <v>0.125</v>
+      </c>
+      <c r="D57" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E57" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="G57" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="58">
       <c r="B58" s="20"/>
@@ -5261,7 +5324,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00D0007A-0025-4C9B-8357-00B900E50062}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{001E0023-0082-40B6-BF21-00E4006D006F}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -5294,7 +5357,7 @@
     </row>
     <row r="2">
       <c r="A2" s="25" t="str" cm="1">
-        <f t="array" ref="A2:A30">_xlfn.UNIQUE(Journal[date])</f>
+        <f t="array" ref="A2:A32">_xlfn.UNIQUE(Journal[date])</f>
         <v>20.01.2026</v>
       </c>
       <c r="B2" s="26">
@@ -5590,6 +5653,10 @@
         <f/>
         <v>46104</v>
       </c>
+      <c r="B28" s="26">
+        <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
+        <v>1.3888888888888888e-002</v>
+      </c>
       <c r="C28" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>1.3888888888888888e-002</v>
@@ -5600,6 +5667,10 @@
         <f/>
         <v>46117</v>
       </c>
+      <c r="B29" s="26">
+        <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
+        <v>0.125</v>
+      </c>
       <c r="C29" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0.125</v>
@@ -5610,23 +5681,41 @@
         <f/>
         <v>46118</v>
       </c>
+      <c r="B30" s="26">
+        <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
+        <v>8.3333333333333329e-002</v>
+      </c>
       <c r="C30" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="25"/>
+      <c r="A31" s="25">
+        <f/>
+        <v>46119</v>
+      </c>
+      <c r="B31" s="26">
+        <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
+        <v>8.3333333333333329e-002</v>
+      </c>
       <c r="C31" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
-        <v>0</v>
+        <v>8.3333333333333329e-002</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="25"/>
+      <c r="A32" s="25">
+        <f/>
+        <v>46122</v>
+      </c>
+      <c r="B32" s="26">
+        <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
+        <v>0.125</v>
+      </c>
       <c r="C32" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="33">
@@ -7059,16 +7148,16 @@
   <sheetData>
     <row r="1" s="32" customFormat="1" ht="66.599999999999994" customHeight="1">
       <c r="B1" s="33" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C1" s="34" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D1" s="35" t="s">
         <v>5</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F1" s="36" t="s">
         <v>11</v>
@@ -7077,7 +7166,7 @@
         <v>17</v>
       </c>
       <c r="H1" s="38" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I1" s="35" t="s">
         <v>22</v>
@@ -7086,85 +7175,85 @@
         <v>37</v>
       </c>
       <c r="K1" s="35" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L1" s="39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="M1" s="35" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N1" s="37" t="s">
         <v>47</v>
       </c>
       <c r="O1" s="38" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="P1" s="35" t="s">
         <v>49</v>
       </c>
       <c r="Q1" s="35" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="R1" s="35" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="S1" s="35" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="T1" s="35" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="U1" s="35" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="V1" s="37" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="W1" s="40" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="X1" s="35" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="Y1" s="35" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Z1" s="37" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AA1" s="41" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AB1" s="42" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AC1" s="42" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AD1" s="39" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AE1" s="43" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="AF1" s="44" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="AG1" s="45" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="AH1" s="45" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="AI1" s="45" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="AJ1" s="45" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="AK1" s="42" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="AL1" s="46"/>
       <c r="AM1" s="46"/>
@@ -7260,7 +7349,7 @@
     <row r="4" ht="12" customHeight="1">
       <c r="B4" s="47"/>
       <c r="C4" s="48" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D4" s="49"/>
       <c r="E4" s="49"/>
@@ -7416,7 +7505,7 @@
     <row r="8" ht="12" customHeight="1">
       <c r="B8" s="47"/>
       <c r="C8" s="48" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D8" s="63"/>
       <c r="E8" s="63"/>
@@ -7494,7 +7583,7 @@
     <row r="10" ht="12" customHeight="1">
       <c r="B10" s="47"/>
       <c r="C10" s="48" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D10" s="49"/>
       <c r="E10" s="49"/>
@@ -7572,7 +7661,7 @@
     <row r="12" ht="12" customHeight="1">
       <c r="B12" s="47"/>
       <c r="C12" s="48" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D12" s="49"/>
       <c r="E12" s="49"/>
@@ -7649,10 +7738,10 @@
     </row>
     <row r="14" ht="12" customHeight="1">
       <c r="B14" s="65" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C14" s="66" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D14" s="63"/>
       <c r="E14" s="63"/>
@@ -7730,7 +7819,7 @@
     <row r="16" ht="12" customHeight="1">
       <c r="B16" s="65"/>
       <c r="C16" s="66" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D16" s="63"/>
       <c r="E16" s="63"/>
@@ -7805,13 +7894,13 @@
       <c r="AJ17" s="68"/>
       <c r="AK17" s="68"/>
       <c r="AN17" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
       <c r="B18" s="65"/>
       <c r="C18" s="66" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D18" s="63"/>
       <c r="E18" s="63"/>
@@ -7889,7 +7978,7 @@
     <row r="20" ht="12" customHeight="1">
       <c r="B20" s="65"/>
       <c r="C20" s="66" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D20" s="68"/>
       <c r="E20" s="68"/>
@@ -7967,7 +8056,7 @@
     <row r="22" ht="12" customHeight="1">
       <c r="B22" s="65"/>
       <c r="C22" s="66" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D22" s="68"/>
       <c r="E22" s="68"/>
@@ -8045,7 +8134,7 @@
     <row r="24" ht="12" customHeight="1">
       <c r="B24" s="65"/>
       <c r="C24" s="66" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D24" s="68"/>
       <c r="E24" s="68"/>
@@ -8122,10 +8211,10 @@
     </row>
     <row r="26" ht="12" customHeight="1">
       <c r="B26" s="47" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C26" s="48" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D26" s="49"/>
       <c r="E26" s="49"/>
@@ -8203,7 +8292,7 @@
     <row r="28" ht="12" customHeight="1">
       <c r="B28" s="47"/>
       <c r="C28" s="48" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D28" s="49"/>
       <c r="E28" s="49"/>
@@ -8281,7 +8370,7 @@
     <row r="30" ht="12" customHeight="1">
       <c r="B30" s="47"/>
       <c r="C30" s="48" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D30" s="49"/>
       <c r="E30" s="49"/>
@@ -8359,7 +8448,7 @@
     <row r="32" ht="12" customHeight="1">
       <c r="B32" s="47"/>
       <c r="C32" s="48" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D32" s="49"/>
       <c r="E32" s="49"/>
@@ -8436,10 +8525,10 @@
     </row>
     <row r="34" ht="12" customHeight="1">
       <c r="B34" s="65" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C34" s="74" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D34" s="68"/>
       <c r="E34" s="68"/>
@@ -8517,7 +8606,7 @@
     <row r="36" ht="12" customHeight="1">
       <c r="B36" s="65"/>
       <c r="C36" s="74" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D36" s="68"/>
       <c r="E36" s="68"/>
@@ -8595,7 +8684,7 @@
     <row r="38" ht="12" customHeight="1">
       <c r="B38" s="65"/>
       <c r="C38" s="74" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D38" s="68"/>
       <c r="E38" s="68"/>
@@ -8673,7 +8762,7 @@
     <row r="40" ht="12" customHeight="1">
       <c r="B40" s="65"/>
       <c r="C40" s="74" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D40" s="68"/>
       <c r="E40" s="68"/>
@@ -8753,7 +8842,7 @@
         <v>21</v>
       </c>
       <c r="C42" s="77" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D42" s="49"/>
       <c r="E42" s="49"/>
@@ -8831,7 +8920,7 @@
     <row r="44" ht="12" customHeight="1">
       <c r="B44" s="47"/>
       <c r="C44" s="77" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D44" s="49"/>
       <c r="E44" s="49"/>
@@ -8908,7 +8997,7 @@
     </row>
     <row r="46" ht="12" customHeight="1">
       <c r="B46" s="65" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C46" s="66" t="s">
         <v>24</v>
@@ -8986,14 +9075,14 @@
       <c r="AJ47" s="68"/>
       <c r="AK47" s="68"/>
       <c r="AN47" s="78" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="AO47" s="63"/>
     </row>
     <row r="48" ht="12" customHeight="1">
       <c r="B48" s="65"/>
       <c r="C48" s="66" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D48" s="68"/>
       <c r="E48" s="68"/>
@@ -9030,7 +9119,7 @@
       <c r="AJ48" s="68"/>
       <c r="AK48" s="79"/>
       <c r="AN48" s="78" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AO48" s="62"/>
     </row>
@@ -9072,7 +9161,7 @@
       <c r="AJ49" s="68"/>
       <c r="AK49" s="68"/>
       <c r="AN49" s="78" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AO49" s="58"/>
     </row>
@@ -9141,37 +9230,37 @@
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
       <c r="B2" s="81" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C2" s="82" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D2" s="83" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E2" s="84" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F2" s="85" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G2" s="85"/>
       <c r="H2" s="85"/>
       <c r="I2" s="84"/>
       <c r="J2" s="85" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K2" s="85"/>
       <c r="L2" s="85"/>
       <c r="M2" s="84"/>
       <c r="N2" s="85" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="O2" s="85"/>
       <c r="P2" s="85"/>
       <c r="Q2" s="84"/>
       <c r="R2" s="85" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="S2" s="86"/>
       <c r="AD2" s="29"/>
@@ -9180,7 +9269,7 @@
       <c r="B3" s="87"/>
       <c r="C3" s="88"/>
       <c r="D3" s="89" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E3" s="90">
         <v>4</v>
@@ -9228,15 +9317,15 @@
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
       <c r="B4" s="94" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C4" s="82" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D4" s="95"/>
       <c r="E4" s="96"/>
@@ -9255,7 +9344,7 @@
       <c r="R4" s="99"/>
       <c r="S4" s="100"/>
       <c r="U4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
@@ -9281,7 +9370,7 @@
     <row r="6" ht="12" customHeight="1">
       <c r="B6" s="94"/>
       <c r="C6" s="109" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D6" s="110"/>
       <c r="E6" s="111"/>
@@ -9300,7 +9389,7 @@
       <c r="R6" s="115"/>
       <c r="S6" s="116"/>
       <c r="U6" s="117" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="V6" s="117"/>
     </row>
@@ -9324,13 +9413,13 @@
       <c r="R7" s="107"/>
       <c r="S7" s="108"/>
       <c r="U7" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
       <c r="B8" s="94"/>
       <c r="C8" s="109" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D8" s="110"/>
       <c r="E8" s="111"/>
@@ -9349,7 +9438,7 @@
       <c r="R8" s="115"/>
       <c r="S8" s="116"/>
       <c r="U8" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
@@ -9375,7 +9464,7 @@
     <row r="10" ht="12" customHeight="1">
       <c r="B10" s="94"/>
       <c r="C10" s="109" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D10" s="110"/>
       <c r="E10" s="111"/>
@@ -9416,10 +9505,10 @@
     </row>
     <row r="12" ht="12" customHeight="1">
       <c r="B12" s="81" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C12" s="82" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D12" s="95"/>
       <c r="E12" s="96"/>
@@ -9461,7 +9550,7 @@
     <row r="14" ht="12" customHeight="1">
       <c r="B14" s="94"/>
       <c r="C14" s="109" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D14" s="128"/>
       <c r="E14" s="111"/>
@@ -9503,7 +9592,7 @@
     <row r="16" ht="12" customHeight="1">
       <c r="B16" s="94"/>
       <c r="C16" s="109" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D16" s="110"/>
       <c r="E16" s="111"/>
@@ -9544,10 +9633,10 @@
     </row>
     <row r="18" ht="12" customHeight="1">
       <c r="B18" s="83" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C18" s="82" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D18" s="95"/>
       <c r="E18" s="96"/>
@@ -9589,7 +9678,7 @@
     <row r="20" ht="12" customHeight="1">
       <c r="B20" s="94"/>
       <c r="C20" s="109" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D20" s="110"/>
       <c r="E20" s="111"/>
@@ -9631,7 +9720,7 @@
     <row r="22" ht="12" customHeight="1">
       <c r="B22" s="94"/>
       <c r="C22" s="109" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D22" s="110"/>
       <c r="E22" s="111"/>
@@ -9672,10 +9761,10 @@
     </row>
     <row r="24" ht="12" customHeight="1">
       <c r="B24" s="83" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C24" s="82" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D24" s="95"/>
       <c r="E24" s="96"/>
@@ -9717,7 +9806,7 @@
     <row r="26" ht="12" customHeight="1">
       <c r="B26" s="94"/>
       <c r="C26" s="109" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D26" s="110"/>
       <c r="E26" s="111"/>
@@ -9759,7 +9848,7 @@
     <row r="28" ht="12" customHeight="1">
       <c r="B28" s="94"/>
       <c r="C28" s="109" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D28" s="110"/>
       <c r="E28" s="111"/>
@@ -9803,7 +9892,7 @@
         <v>12</v>
       </c>
       <c r="C30" s="141" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D30" s="95"/>
       <c r="E30" s="142"/>
@@ -9887,7 +9976,7 @@
     <row r="34" ht="12" customHeight="1">
       <c r="B34" s="147"/>
       <c r="C34" s="101" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D34" s="133"/>
       <c r="E34" s="161"/>
@@ -9907,7 +9996,7 @@
       <c r="S34" s="165"/>
       <c r="U34" s="166"/>
       <c r="V34" s="167" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
@@ -9931,7 +10020,7 @@
       <c r="S35" s="125"/>
       <c r="U35" s="174"/>
       <c r="V35" s="175" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/HoferL-JournalPlanif-M5.xlsx
+++ b/Documentation/HoferL-JournalPlanif-M5.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="1" state="visible" r:id="rId4"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
   <si>
     <t>date</t>
   </si>
@@ -304,6 +304,27 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;-- A jour avec la BDD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentation "Proof Of Concept" du systeme de gestion des scans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correction de l'accès à la BDD. Sécurisation de la connexion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correction d'affichage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Déplacement du modal ExportMD en composant réutilisable et ajout a NotePage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajout de responsivité dans accueil, GridSplitter. Correction d'affichage du graphique donut. Suppression d'une erreur d'héritage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tests et mesures gain PoC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finalisation de la documentation "Proof Of Concept" du systeme de gestion des scans.</t>
   </si>
   <si>
     <t>Phases</t>
@@ -1542,7 +1563,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="177">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1592,10 +1613,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="20" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2213,10 +2237,10 @@
                   <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>37.5</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>63.000000000000014</c:v>
+                  <c:v>71.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3694,8 +3718,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E57">
-  <autoFilter ref="B2:E57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E65">
+  <autoFilter ref="B2:E65"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -4259,7 +4283,7 @@
       </c>
       <c r="I3" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>2.2332506203473945e-002</v>
+        <v>0.019687192387618943</v>
       </c>
       <c r="J3" s="12" t="str" cm="1">
         <f t="array" ref="J3:J9">_xlfn._xlws.FILTER(G3:G10,H3:H10&gt;0)</f>
@@ -4275,7 +4299,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
@@ -4292,7 +4316,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>2.2332506203473945e-002</v>
+        <v>0.019687192387618943</v>
       </c>
       <c r="J4" s="4" t="str">
         <f/>
@@ -4325,7 +4349,7 @@
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>7.0719602977667495e-002</v>
+        <v>0.062342775894126658</v>
       </c>
       <c r="J5" s="4" t="str">
         <f/>
@@ -4341,7 +4365,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
@@ -4358,7 +4382,7 @@
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.12655086848635236</v>
+        <v>0.11156075686317402</v>
       </c>
       <c r="J6" s="4" t="str">
         <f/>
@@ -4374,7 +4398,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>8</v>
@@ -4387,11 +4411,11 @@
       </c>
       <c r="H7" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>37.5</v>
+        <v>46</v>
       </c>
       <c r="I7" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.27915632754342429</v>
+        <v>0.3018702832768238</v>
       </c>
       <c r="J7" s="4" t="str">
         <f/>
@@ -4399,7 +4423,7 @@
       </c>
       <c r="K7" s="13">
         <f/>
-        <v>37.5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" ht="28.5">
@@ -4420,11 +4444,11 @@
       </c>
       <c r="H8" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>63.000000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="I8" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.46898263027295295</v>
+        <v>0.46921141857158483</v>
       </c>
       <c r="J8" s="4" t="str">
         <f/>
@@ -4432,7 +4456,7 @@
       </c>
       <c r="K8" s="13">
         <f/>
-        <v>63.000000000000014</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="9">
@@ -4453,11 +4477,11 @@
       </c>
       <c r="H9" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>1.3333333333333333</v>
+        <v>2.3833333333333333</v>
       </c>
       <c r="I9" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>9.9255583126550851e-003</v>
+        <v>0.015640380619052829</v>
       </c>
       <c r="J9" s="4" t="str">
         <f/>
@@ -4465,7 +4489,7 @@
       </c>
       <c r="K9" s="14">
         <f/>
-        <v>1.3333333333333333</v>
+        <v>2.3833333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -4473,7 +4497,7 @@
         <v>22</v>
       </c>
       <c r="C10" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>12</v>
@@ -4500,7 +4524,7 @@
         <v>22</v>
       </c>
       <c r="C11" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>12</v>
@@ -4513,7 +4537,7 @@
       </c>
       <c r="H11" s="10">
         <f>SUM(H3:H10)</f>
-        <v>134.33333333333334</v>
+        <v>152.38333333333333</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -4523,7 +4547,7 @@
         <v>22</v>
       </c>
       <c r="C12" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>10</v>
@@ -4538,7 +4562,7 @@
         <v>22</v>
       </c>
       <c r="C13" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>12</v>
@@ -4553,7 +4577,7 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>12</v>
@@ -4609,7 +4633,7 @@
         <v>35</v>
       </c>
       <c r="C18" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>10</v>
@@ -4623,7 +4647,7 @@
         <v>37</v>
       </c>
       <c r="C19" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>12</v>
@@ -4637,7 +4661,7 @@
         <v>39</v>
       </c>
       <c r="C20" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>19</v>
@@ -4651,7 +4675,7 @@
         <v>39</v>
       </c>
       <c r="C21" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>15</v>
@@ -4679,7 +4703,7 @@
         <v>43</v>
       </c>
       <c r="C23" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>15</v>
@@ -4693,7 +4717,7 @@
         <v>45</v>
       </c>
       <c r="C24" s="6">
-        <v>6.25e-002</v>
+        <v>0.0625</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>15</v>
@@ -4735,7 +4759,7 @@
         <v>49</v>
       </c>
       <c r="C27" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>12</v>
@@ -4749,7 +4773,7 @@
         <v>52</v>
       </c>
       <c r="C28" s="6">
-        <v>6.25e-002</v>
+        <v>0.0625</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>15</v>
@@ -4791,7 +4815,7 @@
         <v>46087</v>
       </c>
       <c r="C31" s="6">
-        <v>2.0833333333333332e-002</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>21</v>
@@ -4819,7 +4843,7 @@
         <v>46091</v>
       </c>
       <c r="C33" s="6">
-        <v>2.0833333333333332e-002</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>12</v>
@@ -4847,7 +4871,7 @@
         <v>46091</v>
       </c>
       <c r="C35" s="6">
-        <v>2.0833333333333332e-002</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>19</v>
@@ -4875,7 +4899,7 @@
         <v>46093</v>
       </c>
       <c r="C37" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>19</v>
@@ -4903,7 +4927,7 @@
         <v>46087</v>
       </c>
       <c r="C39" s="6">
-        <v>2.0833333333333332e-002</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>21</v>
@@ -4990,7 +5014,7 @@
         <v>46100</v>
       </c>
       <c r="C45" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>8</v>
@@ -5004,7 +5028,7 @@
         <v>46100</v>
       </c>
       <c r="C46" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>19</v>
@@ -5032,7 +5056,7 @@
         <v>46102</v>
       </c>
       <c r="C48" s="21">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>8</v>
@@ -5088,12 +5112,12 @@
         <v>46104</v>
       </c>
       <c r="C52" s="21">
-        <v>1.3888888888888888e-002</v>
+        <v>0.013888888888888888</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E52" s="22" t="s">
+      <c r="E52" s="8" t="s">
         <v>76</v>
       </c>
     </row>
@@ -5107,7 +5131,7 @@
       <c r="D53" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E53" s="22" t="s">
+      <c r="E53" s="8" t="s">
         <v>77</v>
       </c>
     </row>
@@ -5116,12 +5140,12 @@
         <v>46118</v>
       </c>
       <c r="C54" s="21">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E54" s="22" t="s">
+      <c r="E54" s="8" t="s">
         <v>78</v>
       </c>
     </row>
@@ -5130,12 +5154,12 @@
         <v>46119</v>
       </c>
       <c r="C55" s="21">
-        <v>2.0833333333333332e-002</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E55" s="22" t="s">
+      <c r="E55" s="8" t="s">
         <v>79</v>
       </c>
     </row>
@@ -5144,12 +5168,12 @@
         <v>46119</v>
       </c>
       <c r="C56" s="21">
-        <v>6.25e-002</v>
-      </c>
-      <c r="D56" s="23" t="s">
+        <v>0.0625</v>
+      </c>
+      <c r="D56" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E56" s="22" t="s">
+      <c r="E56" s="8" t="s">
         <v>80</v>
       </c>
     </row>
@@ -5160,153 +5184,223 @@
       <c r="C57" s="21">
         <v>0.125</v>
       </c>
-      <c r="D57" s="23" t="s">
+      <c r="D57" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E57" s="22" t="s">
+      <c r="E57" s="8" t="s">
         <v>81</v>
       </c>
       <c r="G57" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="20"/>
-      <c r="C58" s="24"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="8"/>
-    </row>
-    <row r="59">
-      <c r="B59" s="20"/>
-      <c r="C59" s="24"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="8"/>
+    <row r="58" ht="28.5">
+      <c r="B58" s="20">
+        <v>46133</v>
+      </c>
+      <c r="C58" s="21">
+        <v>0.125</v>
+      </c>
+      <c r="D58" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" s="23" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="59" ht="28.5">
+      <c r="B59" s="20">
+        <v>46134</v>
+      </c>
+      <c r="C59" s="21">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="D59" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" s="23" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="60">
-      <c r="B60" s="20"/>
-      <c r="C60" s="24"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="8"/>
+      <c r="B60" s="20">
+        <v>46134</v>
+      </c>
+      <c r="C60" s="21">
+        <v>0.020833333333333332</v>
+      </c>
+      <c r="D60" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="E60" s="23" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="61">
-      <c r="B61" s="20"/>
-      <c r="C61" s="24"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="8"/>
-    </row>
-    <row r="62">
-      <c r="B62" s="20"/>
-      <c r="C62" s="24"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="8"/>
-    </row>
-    <row r="63">
-      <c r="B63" s="20"/>
-      <c r="C63" s="24"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="8"/>
+      <c r="B61" s="20">
+        <v>46135</v>
+      </c>
+      <c r="C61" s="21">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="D61" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" s="23" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="62" ht="28.5">
+      <c r="B62" s="20">
+        <v>46136</v>
+      </c>
+      <c r="C62" s="24">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D62" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="23" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="63" ht="42.75">
+      <c r="B63" s="20">
+        <v>46137</v>
+      </c>
+      <c r="C63" s="21">
+        <v>0.125</v>
+      </c>
+      <c r="D63" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="E63" s="23" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="64">
-      <c r="B64" s="20"/>
-      <c r="C64" s="24"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="8"/>
+      <c r="B64" s="20">
+        <v>46140</v>
+      </c>
+      <c r="C64" s="21">
+        <v>0.043749999999999997</v>
+      </c>
+      <c r="D64" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E64" s="23" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="65">
-      <c r="B65" s="20"/>
-      <c r="C65" s="24"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="8"/>
+      <c r="B65" s="20">
+        <v>46140</v>
+      </c>
+      <c r="C65" s="21">
+        <v>0.14583333333333334</v>
+      </c>
+      <c r="D65" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E65" s="23" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="66">
       <c r="B66" s="20"/>
-      <c r="C66" s="24"/>
+      <c r="C66" s="25"/>
       <c r="D66" s="7"/>
       <c r="E66" s="8"/>
     </row>
     <row r="67">
       <c r="B67" s="20"/>
-      <c r="C67" s="24"/>
+      <c r="C67" s="25"/>
       <c r="D67" s="7"/>
       <c r="E67" s="8"/>
     </row>
     <row r="68">
       <c r="B68" s="20"/>
-      <c r="C68" s="24"/>
+      <c r="C68" s="25"/>
       <c r="D68" s="7"/>
       <c r="E68" s="8"/>
     </row>
     <row r="69">
       <c r="B69" s="20"/>
-      <c r="C69" s="24"/>
+      <c r="C69" s="25"/>
       <c r="D69" s="7"/>
       <c r="E69" s="8"/>
     </row>
     <row r="70">
       <c r="B70" s="20"/>
-      <c r="C70" s="24"/>
+      <c r="C70" s="25"/>
       <c r="D70" s="7"/>
       <c r="E70" s="8"/>
     </row>
     <row r="71">
       <c r="B71" s="20"/>
-      <c r="C71" s="24"/>
+      <c r="C71" s="25"/>
       <c r="D71" s="7"/>
       <c r="E71" s="8"/>
     </row>
     <row r="72">
       <c r="B72" s="20"/>
-      <c r="C72" s="24"/>
+      <c r="C72" s="25"/>
       <c r="D72" s="7"/>
       <c r="E72" s="8"/>
     </row>
     <row r="73">
       <c r="B73" s="20"/>
-      <c r="C73" s="24"/>
+      <c r="C73" s="25"/>
       <c r="D73" s="7"/>
       <c r="E73" s="8"/>
     </row>
     <row r="74">
       <c r="B74" s="20"/>
-      <c r="C74" s="24"/>
+      <c r="C74" s="25"/>
       <c r="D74" s="7"/>
       <c r="E74" s="8"/>
     </row>
     <row r="75">
-      <c r="B75" s="7"/>
-      <c r="C75" s="24"/>
+      <c r="B75" s="20"/>
+      <c r="C75" s="25"/>
       <c r="D75" s="7"/>
       <c r="E75" s="8"/>
     </row>
     <row r="76">
       <c r="B76" s="7"/>
-      <c r="C76" s="24"/>
+      <c r="C76" s="25"/>
       <c r="D76" s="7"/>
       <c r="E76" s="8"/>
     </row>
     <row r="77">
       <c r="B77" s="7"/>
-      <c r="C77" s="24"/>
+      <c r="C77" s="25"/>
       <c r="D77" s="7"/>
       <c r="E77" s="8"/>
     </row>
     <row r="78">
       <c r="B78" s="7"/>
-      <c r="C78" s="24"/>
+      <c r="C78" s="25"/>
       <c r="D78" s="7"/>
       <c r="E78" s="8"/>
     </row>
     <row r="79">
       <c r="B79" s="7"/>
-      <c r="C79" s="24"/>
+      <c r="C79" s="25"/>
       <c r="D79" s="7"/>
       <c r="E79" s="8"/>
     </row>
     <row r="80">
       <c r="B80" s="7"/>
-      <c r="C80" s="24"/>
+      <c r="C80" s="25"/>
       <c r="D80" s="7"/>
       <c r="E80" s="8"/>
+    </row>
+    <row r="81">
+      <c r="B81" s="7"/>
+      <c r="C81" s="25"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -5324,7 +5418,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{001E0023-0082-40B6-BF21-00E4006D006F}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{000A0062-003C-4181-BDC2-0042001A0036}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -5338,7 +5432,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" customWidth="1" min="3" max="3" style="4" width="5.6640625"/>
     <col bestFit="1" customWidth="1" min="4" max="4" width="12.21875"/>
@@ -5356,1769 +5450,1787 @@
       <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="str" cm="1">
-        <f t="array" ref="A2:A32">_xlfn.UNIQUE(Journal[date])</f>
+      <c r="A2" s="26" t="str" cm="1">
+        <f t="array" ref="A2:A38">_xlfn.UNIQUE(Journal[date])</f>
         <v>20.01.2026</v>
       </c>
-      <c r="B2" s="26">
+      <c r="B2" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A2,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C2" s="26"/>
+      <c r="C2" s="27"/>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="str">
+      <c r="A3" s="26" t="str">
         <f/>
         <v>27.01.2026</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="str">
+      <c r="A4" s="26" t="str">
         <f/>
         <v>30.01.2026</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C4"/>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="str">
+      <c r="A5" s="26" t="str">
         <f/>
         <v>03.02.2026</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0.25</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="str">
+      <c r="A6" s="26" t="str">
         <f/>
         <v>04.02.2026</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="str">
+      <c r="A7" s="26" t="str">
         <f/>
         <v>06.02.2026</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C7"/>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="str">
+      <c r="A8" s="26" t="str">
         <f/>
         <v>08.02.2026</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="str">
+      <c r="A9" s="26" t="str">
         <f/>
         <v>09.02.2026</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="str">
+      <c r="A10" s="26" t="str">
         <f/>
         <v>10.02.2026</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="str">
+      <c r="A11" s="26" t="str">
         <f/>
         <v>12.02.2026</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="str">
+      <c r="A12" s="26" t="str">
         <f/>
         <v>13.02.2026</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
-        <v>6.25e-002</v>
+        <v>0.0625</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="str">
+      <c r="A13" s="26" t="str">
         <f/>
         <v>24.02.2026</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0.125</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="str">
+      <c r="A14" s="26" t="str">
         <f/>
         <v>03.03.2026</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="str">
+      <c r="A15" s="26" t="str">
         <f/>
         <v>05.03.2026</v>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="25">
+      <c r="A16" s="26">
         <f/>
         <v>46087</v>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="25">
+      <c r="A17" s="26">
         <f/>
         <v>46088</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0.25</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="25">
+      <c r="A18" s="26">
         <f/>
         <v>46091</v>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="25">
+      <c r="A19" s="26">
         <f/>
         <v>46093</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="25">
+      <c r="A20" s="26">
         <f/>
         <v>46095</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="25">
+      <c r="A21" s="26">
         <f/>
         <v>46096</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="25">
+      <c r="A22" s="26">
         <f/>
         <v>46097</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0.14583333333333334</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="25">
+      <c r="A23" s="26">
         <f/>
         <v>46098</v>
       </c>
-      <c r="B23" s="26">
+      <c r="B23" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="25">
+      <c r="A24" s="26">
         <f/>
         <v>46099</v>
       </c>
-      <c r="B24" s="26">
+      <c r="B24" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="25">
+      <c r="A25" s="26">
         <f/>
         <v>46100</v>
       </c>
-      <c r="B25" s="26">
+      <c r="B25" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="C25"/>
-      <c r="F25" s="27"/>
+      <c r="F25" s="28"/>
     </row>
     <row r="26">
-      <c r="A26" s="25">
+      <c r="A26" s="26">
         <f/>
         <v>46102</v>
       </c>
-      <c r="B26" s="26">
+      <c r="B26" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="25">
+      <c r="A27" s="26">
         <f/>
         <v>46103</v>
       </c>
-      <c r="B27" s="26">
+      <c r="B27" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0.375</v>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0.375</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="25">
+      <c r="A28" s="26">
         <f/>
         <v>46104</v>
       </c>
-      <c r="B28" s="26">
+      <c r="B28" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
-        <v>1.3888888888888888e-002</v>
-      </c>
-      <c r="C28" s="28">
+        <v>0.013888888888888888</v>
+      </c>
+      <c r="C28" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
-        <v>1.3888888888888888e-002</v>
+        <v>0.013888888888888888</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="25">
+      <c r="A29" s="26">
         <f/>
         <v>46117</v>
       </c>
-      <c r="B29" s="26">
+      <c r="B29" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="25">
+      <c r="A30" s="26">
         <f/>
         <v>46118</v>
       </c>
-      <c r="B30" s="26">
+      <c r="B30" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
-        <v>8.3333333333333329e-002</v>
-      </c>
-      <c r="C30" s="28">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="C30" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="25">
+      <c r="A31" s="26">
         <f/>
         <v>46119</v>
       </c>
-      <c r="B31" s="26">
+      <c r="B31" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
-        <v>8.3333333333333329e-002</v>
-      </c>
-      <c r="C31" s="28">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="C31" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="25">
+      <c r="A32" s="26">
         <f/>
         <v>46122</v>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C32" s="28">
+      <c r="C32" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="25"/>
-      <c r="C33" s="28">
+      <c r="A33" s="26">
+        <f/>
+        <v>46133</v>
+      </c>
+      <c r="C33" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="25"/>
-      <c r="C34" s="28">
+      <c r="A34" s="26">
+        <f/>
+        <v>46134</v>
+      </c>
+      <c r="C34" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
-        <v>0</v>
+        <v>0.10416666666666666</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="25"/>
-      <c r="C35" s="28">
+      <c r="A35" s="26">
+        <f/>
+        <v>46135</v>
+      </c>
+      <c r="C35" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
-        <v>0</v>
+        <v>0.041666666666666664</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="25"/>
-      <c r="C36" s="28">
+      <c r="A36" s="26">
+        <f/>
+        <v>46136</v>
+      </c>
+      <c r="C36" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
-        <v>0</v>
+        <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="25"/>
-      <c r="C37" s="28">
+      <c r="A37" s="26">
+        <f/>
+        <v>46137</v>
+      </c>
+      <c r="C37" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="25"/>
-      <c r="C38" s="28">
+      <c r="A38" s="26">
+        <f/>
+        <v>46140</v>
+      </c>
+      <c r="C38" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
-        <v>0</v>
+        <v>0.18958333333333333</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="25"/>
-      <c r="C39" s="28">
+      <c r="A39" s="26"/>
+      <c r="C39" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="25"/>
-      <c r="B40" s="26" t="str">
+      <c r="A40" s="26"/>
+      <c r="B40" s="27" t="str">
         <f t="shared" ref="B40:B103" si="0">IF(C40&gt;0,C40,"")</f>
         <v/>
       </c>
-      <c r="C40" s="28">
+      <c r="C40" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="25"/>
-      <c r="B41" s="26" t="str">
+      <c r="A41" s="26"/>
+      <c r="B41" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="28">
+      <c r="C41" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="29"/>
-      <c r="B42" s="26" t="str">
+      <c r="A42" s="30"/>
+      <c r="B42" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="28">
+      <c r="C42" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="29"/>
-      <c r="B43" s="26" t="str">
+      <c r="A43" s="30"/>
+      <c r="B43" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="28">
+      <c r="C43" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="29"/>
-      <c r="B44" s="26" t="str">
+      <c r="A44" s="30"/>
+      <c r="B44" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="28">
+      <c r="C44" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="29"/>
-      <c r="B45" s="26" t="str">
+      <c r="A45" s="30"/>
+      <c r="B45" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="28">
+      <c r="C45" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="29"/>
-      <c r="B46" s="26" t="str">
+      <c r="A46" s="30"/>
+      <c r="B46" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="28">
+      <c r="C46" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="30"/>
-      <c r="B47" s="26" t="str">
+      <c r="A47" s="31"/>
+      <c r="B47" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="28">
+      <c r="C47" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="30"/>
-      <c r="B48" s="26" t="str">
+      <c r="A48" s="31"/>
+      <c r="B48" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="28">
+      <c r="C48" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="30"/>
-      <c r="B49" s="26" t="str">
+      <c r="A49" s="31"/>
+      <c r="B49" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C49" s="28">
+      <c r="C49" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="30"/>
-      <c r="B50" s="26" t="str">
+      <c r="A50" s="31"/>
+      <c r="B50" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C50" s="28">
+      <c r="C50" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="30"/>
-      <c r="B51" s="26" t="str">
+      <c r="A51" s="31"/>
+      <c r="B51" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C51" s="28">
+      <c r="C51" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="30"/>
-      <c r="B52" s="26" t="str">
+      <c r="A52" s="31"/>
+      <c r="B52" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C52" s="28">
+      <c r="C52" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="30"/>
-      <c r="B53" s="26" t="str">
+      <c r="A53" s="31"/>
+      <c r="B53" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C53" s="28">
+      <c r="C53" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="30"/>
-      <c r="B54" s="26" t="str">
+      <c r="A54" s="31"/>
+      <c r="B54" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C54" s="28">
+      <c r="C54" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="30"/>
-      <c r="B55" s="26" t="str">
+      <c r="A55" s="31"/>
+      <c r="B55" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C55" s="28">
+      <c r="C55" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="30"/>
-      <c r="B56" s="26" t="str">
+      <c r="A56" s="31"/>
+      <c r="B56" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C56" s="28">
+      <c r="C56" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="30"/>
-      <c r="B57" s="26" t="str">
+      <c r="A57" s="31"/>
+      <c r="B57" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C57" s="28">
+      <c r="C57" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="30"/>
-      <c r="B58" s="26" t="str">
+      <c r="A58" s="31"/>
+      <c r="B58" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C58" s="28">
+      <c r="C58" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="30"/>
-      <c r="B59" s="26" t="str">
+      <c r="A59" s="31"/>
+      <c r="B59" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C59" s="28">
+      <c r="C59" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="30"/>
-      <c r="B60" s="26" t="str">
+      <c r="A60" s="31"/>
+      <c r="B60" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C60" s="28">
+      <c r="C60" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="30"/>
-      <c r="B61" s="26" t="str">
+      <c r="A61" s="31"/>
+      <c r="B61" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C61" s="28">
+      <c r="C61" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="30"/>
-      <c r="B62" s="26" t="str">
+      <c r="A62" s="31"/>
+      <c r="B62" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C62" s="28">
+      <c r="C62" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="30"/>
-      <c r="B63" s="26" t="str">
+      <c r="A63" s="31"/>
+      <c r="B63" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C63" s="28">
+      <c r="C63" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="30"/>
-      <c r="B64" s="26" t="str">
+      <c r="A64" s="31"/>
+      <c r="B64" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C64" s="28">
+      <c r="C64" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="30"/>
-      <c r="B65" s="26" t="str">
+      <c r="A65" s="31"/>
+      <c r="B65" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C65" s="28">
+      <c r="C65" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="30"/>
-      <c r="B66" s="26" t="str">
+      <c r="A66" s="31"/>
+      <c r="B66" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C66" s="28">
+      <c r="C66" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="30"/>
-      <c r="B67" s="26" t="str">
+      <c r="A67" s="31"/>
+      <c r="B67" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C67" s="28">
+      <c r="C67" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30"/>
-      <c r="B68" s="26" t="str">
+      <c r="A68" s="31"/>
+      <c r="B68" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C68" s="28">
+      <c r="C68" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30"/>
-      <c r="B69" s="26" t="str">
+      <c r="A69" s="31"/>
+      <c r="B69" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C69" s="28">
+      <c r="C69" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30"/>
-      <c r="B70" s="26" t="str">
+      <c r="A70" s="31"/>
+      <c r="B70" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C70" s="28">
+      <c r="C70" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="30"/>
-      <c r="B71" s="26" t="str">
+      <c r="A71" s="31"/>
+      <c r="B71" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C71" s="28">
+      <c r="C71" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="30"/>
-      <c r="B72" s="26" t="str">
+      <c r="A72" s="31"/>
+      <c r="B72" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C72" s="28">
+      <c r="C72" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="30"/>
-      <c r="B73" s="26" t="str">
+      <c r="A73" s="31"/>
+      <c r="B73" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C73" s="28">
+      <c r="C73" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="30"/>
-      <c r="B74" s="26" t="str">
+      <c r="A74" s="31"/>
+      <c r="B74" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C74" s="28">
+      <c r="C74" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="30"/>
-      <c r="B75" s="26" t="str">
+      <c r="A75" s="31"/>
+      <c r="B75" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C75" s="28">
+      <c r="C75" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="30"/>
-      <c r="B76" s="26" t="str">
+      <c r="A76" s="31"/>
+      <c r="B76" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C76" s="28">
+      <c r="C76" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30"/>
-      <c r="B77" s="26" t="str">
+      <c r="A77" s="31"/>
+      <c r="B77" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C77" s="28">
+      <c r="C77" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30"/>
-      <c r="B78" s="26" t="str">
+      <c r="A78" s="31"/>
+      <c r="B78" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C78" s="28">
+      <c r="C78" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="30"/>
-      <c r="B79" s="26" t="str">
+      <c r="A79" s="31"/>
+      <c r="B79" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C79" s="28">
+      <c r="C79" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="30"/>
-      <c r="B80" s="26" t="str">
+      <c r="A80" s="31"/>
+      <c r="B80" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C80" s="28">
+      <c r="C80" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="30"/>
-      <c r="B81" s="26" t="str">
+      <c r="A81" s="31"/>
+      <c r="B81" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C81" s="28">
+      <c r="C81" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="30"/>
-      <c r="B82" s="26" t="str">
+      <c r="A82" s="31"/>
+      <c r="B82" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C82" s="28">
+      <c r="C82" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="30"/>
-      <c r="B83" s="26" t="str">
+      <c r="A83" s="31"/>
+      <c r="B83" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C83" s="28">
+      <c r="C83" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="30"/>
-      <c r="B84" s="26" t="str">
+      <c r="A84" s="31"/>
+      <c r="B84" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C84" s="28">
+      <c r="C84" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="30"/>
-      <c r="B85" s="26" t="str">
+      <c r="A85" s="31"/>
+      <c r="B85" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C85" s="28">
+      <c r="C85" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="30"/>
-      <c r="B86" s="26" t="str">
+      <c r="A86" s="31"/>
+      <c r="B86" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C86" s="28">
+      <c r="C86" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="30"/>
-      <c r="B87" s="26" t="str">
+      <c r="A87" s="31"/>
+      <c r="B87" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C87" s="28">
+      <c r="C87" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="30"/>
-      <c r="B88" s="26" t="str">
+      <c r="A88" s="31"/>
+      <c r="B88" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C88" s="28">
+      <c r="C88" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="30"/>
-      <c r="B89" s="26" t="str">
+      <c r="A89" s="31"/>
+      <c r="B89" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C89" s="28">
+      <c r="C89" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="30"/>
-      <c r="B90" s="26" t="str">
+      <c r="A90" s="31"/>
+      <c r="B90" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C90" s="28">
+      <c r="C90" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="30"/>
-      <c r="B91" s="26" t="str">
+      <c r="A91" s="31"/>
+      <c r="B91" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C91" s="28">
+      <c r="C91" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="30"/>
-      <c r="B92" s="26" t="str">
+      <c r="A92" s="31"/>
+      <c r="B92" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C92" s="28">
+      <c r="C92" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="30"/>
-      <c r="B93" s="26" t="str">
+      <c r="A93" s="31"/>
+      <c r="B93" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C93" s="28">
+      <c r="C93" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="30"/>
-      <c r="B94" s="26" t="str">
+      <c r="A94" s="31"/>
+      <c r="B94" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C94" s="28">
+      <c r="C94" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="30"/>
-      <c r="B95" s="26" t="str">
+      <c r="A95" s="31"/>
+      <c r="B95" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C95" s="28">
+      <c r="C95" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="30"/>
-      <c r="B96" s="26" t="str">
+      <c r="A96" s="31"/>
+      <c r="B96" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C96" s="28">
+      <c r="C96" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="30"/>
-      <c r="B97" s="26" t="str">
+      <c r="A97" s="31"/>
+      <c r="B97" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C97" s="28">
+      <c r="C97" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="30"/>
-      <c r="B98" s="26" t="str">
+      <c r="A98" s="31"/>
+      <c r="B98" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C98" s="28">
+      <c r="C98" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="30"/>
-      <c r="B99" s="26" t="str">
+      <c r="A99" s="31"/>
+      <c r="B99" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C99" s="28">
+      <c r="C99" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="30"/>
-      <c r="B100" s="26" t="str">
+      <c r="A100" s="31"/>
+      <c r="B100" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C100" s="28">
+      <c r="C100" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="30"/>
-      <c r="B101" s="26" t="str">
+      <c r="A101" s="31"/>
+      <c r="B101" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C101" s="28">
+      <c r="C101" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="30"/>
-      <c r="B102" s="26" t="str">
+      <c r="A102" s="31"/>
+      <c r="B102" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C102" s="28">
+      <c r="C102" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="30"/>
-      <c r="B103" s="26" t="str">
+      <c r="A103" s="31"/>
+      <c r="B103" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C103" s="28">
+      <c r="C103" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="30"/>
-      <c r="B104" s="26" t="str">
+      <c r="A104" s="31"/>
+      <c r="B104" s="27" t="str">
         <f t="shared" ref="B104:B114" si="1">IF(C104&gt;0,C104,"")</f>
         <v/>
       </c>
-      <c r="C104" s="28">
+      <c r="C104" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="30"/>
-      <c r="B105" s="26" t="str">
+      <c r="A105" s="31"/>
+      <c r="B105" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C105" s="28">
+      <c r="C105" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="30"/>
-      <c r="B106" s="26" t="str">
+      <c r="A106" s="31"/>
+      <c r="B106" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C106" s="28">
+      <c r="C106" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="30"/>
-      <c r="B107" s="26" t="str">
+      <c r="A107" s="31"/>
+      <c r="B107" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C107" s="28">
+      <c r="C107" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="30"/>
-      <c r="B108" s="26" t="str">
+      <c r="A108" s="31"/>
+      <c r="B108" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C108" s="28">
+      <c r="C108" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="30"/>
-      <c r="B109" s="26" t="str">
+      <c r="A109" s="31"/>
+      <c r="B109" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C109" s="28">
+      <c r="C109" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="30"/>
-      <c r="B110" s="26" t="str">
+      <c r="A110" s="31"/>
+      <c r="B110" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C110" s="28">
+      <c r="C110" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="30"/>
-      <c r="B111" s="26" t="str">
+      <c r="A111" s="31"/>
+      <c r="B111" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C111" s="28">
+      <c r="C111" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="30"/>
-      <c r="B112" s="26" t="str">
+      <c r="A112" s="31"/>
+      <c r="B112" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C112" s="28">
+      <c r="C112" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="30"/>
-      <c r="B113" s="26" t="str">
+      <c r="A113" s="31"/>
+      <c r="B113" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C113" s="28">
+      <c r="C113" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="30"/>
-      <c r="B114" s="26" t="str">
+      <c r="A114" s="31"/>
+      <c r="B114" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C114" s="28">
+      <c r="C114" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="30"/>
-      <c r="B115" s="30"/>
-      <c r="C115" s="28"/>
+      <c r="A115" s="31"/>
+      <c r="B115" s="31"/>
+      <c r="C115" s="29"/>
     </row>
     <row r="116">
-      <c r="A116" s="30"/>
-      <c r="B116" s="30"/>
-      <c r="C116" s="28"/>
+      <c r="A116" s="31"/>
+      <c r="B116" s="31"/>
+      <c r="C116" s="29"/>
     </row>
     <row r="117">
-      <c r="A117" s="30"/>
-      <c r="B117" s="30"/>
-      <c r="C117" s="28"/>
+      <c r="A117" s="31"/>
+      <c r="B117" s="31"/>
+      <c r="C117" s="29"/>
     </row>
     <row r="118">
-      <c r="A118" s="30"/>
-      <c r="B118" s="30"/>
-      <c r="C118" s="28"/>
+      <c r="A118" s="31"/>
+      <c r="B118" s="31"/>
+      <c r="C118" s="29"/>
     </row>
     <row r="119">
-      <c r="A119" s="30"/>
-      <c r="B119" s="30"/>
-      <c r="C119" s="28"/>
+      <c r="A119" s="31"/>
+      <c r="B119" s="31"/>
+      <c r="C119" s="29"/>
     </row>
     <row r="120">
-      <c r="A120" s="30"/>
-      <c r="B120" s="30"/>
-      <c r="C120" s="28"/>
+      <c r="A120" s="31"/>
+      <c r="B120" s="31"/>
+      <c r="C120" s="29"/>
     </row>
     <row r="121">
-      <c r="A121" s="30"/>
-      <c r="B121" s="30"/>
-      <c r="C121" s="28"/>
+      <c r="A121" s="31"/>
+      <c r="B121" s="31"/>
+      <c r="C121" s="29"/>
     </row>
     <row r="122">
-      <c r="A122" s="30"/>
-      <c r="B122" s="30"/>
-      <c r="C122" s="28"/>
+      <c r="A122" s="31"/>
+      <c r="B122" s="31"/>
+      <c r="C122" s="29"/>
     </row>
     <row r="123">
-      <c r="A123" s="30"/>
-      <c r="B123" s="30"/>
-      <c r="C123" s="28"/>
+      <c r="A123" s="31"/>
+      <c r="B123" s="31"/>
+      <c r="C123" s="29"/>
     </row>
     <row r="124">
-      <c r="A124" s="30"/>
-      <c r="B124" s="30"/>
-      <c r="C124" s="28"/>
+      <c r="A124" s="31"/>
+      <c r="B124" s="31"/>
+      <c r="C124" s="29"/>
     </row>
     <row r="125">
-      <c r="A125" s="30"/>
-      <c r="B125" s="30"/>
-      <c r="C125" s="28"/>
+      <c r="A125" s="31"/>
+      <c r="B125" s="31"/>
+      <c r="C125" s="29"/>
     </row>
     <row r="126">
-      <c r="A126" s="30"/>
-      <c r="B126" s="30"/>
-      <c r="C126" s="28"/>
+      <c r="A126" s="31"/>
+      <c r="B126" s="31"/>
+      <c r="C126" s="29"/>
     </row>
     <row r="127">
-      <c r="A127" s="30"/>
-      <c r="B127" s="30"/>
-      <c r="C127" s="28"/>
+      <c r="A127" s="31"/>
+      <c r="B127" s="31"/>
+      <c r="C127" s="29"/>
     </row>
     <row r="128">
-      <c r="A128" s="30"/>
-      <c r="B128" s="30"/>
-      <c r="C128" s="28"/>
+      <c r="A128" s="31"/>
+      <c r="B128" s="31"/>
+      <c r="C128" s="29"/>
     </row>
     <row r="129">
-      <c r="A129" s="30"/>
-      <c r="B129" s="30"/>
-      <c r="C129" s="28"/>
+      <c r="A129" s="31"/>
+      <c r="B129" s="31"/>
+      <c r="C129" s="29"/>
     </row>
     <row r="130">
-      <c r="A130" s="30"/>
-      <c r="B130" s="30"/>
-      <c r="C130" s="28"/>
+      <c r="A130" s="31"/>
+      <c r="B130" s="31"/>
+      <c r="C130" s="29"/>
     </row>
     <row r="131">
-      <c r="A131" s="30"/>
-      <c r="B131" s="30"/>
-      <c r="C131" s="28"/>
+      <c r="A131" s="31"/>
+      <c r="B131" s="31"/>
+      <c r="C131" s="29"/>
     </row>
     <row r="132">
-      <c r="A132" s="30"/>
-      <c r="B132" s="30"/>
-      <c r="C132" s="28"/>
+      <c r="A132" s="31"/>
+      <c r="B132" s="31"/>
+      <c r="C132" s="29"/>
     </row>
     <row r="133">
-      <c r="A133" s="30"/>
-      <c r="B133" s="30"/>
-      <c r="C133" s="28"/>
+      <c r="A133" s="31"/>
+      <c r="B133" s="31"/>
+      <c r="C133" s="29"/>
     </row>
     <row r="134">
-      <c r="A134" s="30"/>
-      <c r="B134" s="30"/>
-      <c r="C134" s="28"/>
+      <c r="A134" s="31"/>
+      <c r="B134" s="31"/>
+      <c r="C134" s="29"/>
     </row>
     <row r="135">
-      <c r="A135" s="30"/>
-      <c r="B135" s="30"/>
-      <c r="C135" s="28"/>
+      <c r="A135" s="31"/>
+      <c r="B135" s="31"/>
+      <c r="C135" s="29"/>
     </row>
     <row r="136">
-      <c r="A136" s="30"/>
-      <c r="B136" s="30"/>
-      <c r="C136" s="28"/>
+      <c r="A136" s="31"/>
+      <c r="B136" s="31"/>
+      <c r="C136" s="29"/>
     </row>
     <row r="137">
-      <c r="A137" s="30"/>
-      <c r="B137" s="30"/>
-      <c r="C137" s="28"/>
+      <c r="A137" s="31"/>
+      <c r="B137" s="31"/>
+      <c r="C137" s="29"/>
     </row>
     <row r="138">
-      <c r="A138" s="30"/>
-      <c r="B138" s="30"/>
-      <c r="C138" s="28"/>
+      <c r="A138" s="31"/>
+      <c r="B138" s="31"/>
+      <c r="C138" s="29"/>
     </row>
     <row r="139">
-      <c r="A139" s="30"/>
-      <c r="B139" s="30"/>
-      <c r="C139" s="28"/>
+      <c r="A139" s="31"/>
+      <c r="B139" s="31"/>
+      <c r="C139" s="29"/>
     </row>
     <row r="140">
-      <c r="A140" s="30"/>
-      <c r="B140" s="30"/>
-      <c r="C140" s="28"/>
+      <c r="A140" s="31"/>
+      <c r="B140" s="31"/>
+      <c r="C140" s="29"/>
     </row>
     <row r="141">
-      <c r="A141" s="30"/>
-      <c r="B141" s="30"/>
-      <c r="C141" s="28"/>
+      <c r="A141" s="31"/>
+      <c r="B141" s="31"/>
+      <c r="C141" s="29"/>
     </row>
     <row r="142">
-      <c r="A142" s="30"/>
-      <c r="B142" s="30"/>
-      <c r="C142" s="28"/>
+      <c r="A142" s="31"/>
+      <c r="B142" s="31"/>
+      <c r="C142" s="29"/>
     </row>
     <row r="143">
-      <c r="A143" s="30"/>
-      <c r="B143" s="30"/>
-      <c r="C143" s="28"/>
+      <c r="A143" s="31"/>
+      <c r="B143" s="31"/>
+      <c r="C143" s="29"/>
     </row>
     <row r="144">
-      <c r="A144" s="30"/>
-      <c r="B144" s="30"/>
-      <c r="C144" s="28"/>
+      <c r="A144" s="31"/>
+      <c r="B144" s="31"/>
+      <c r="C144" s="29"/>
     </row>
     <row r="145">
-      <c r="A145" s="30"/>
-      <c r="B145" s="30"/>
-      <c r="C145" s="28"/>
+      <c r="A145" s="31"/>
+      <c r="B145" s="31"/>
+      <c r="C145" s="29"/>
     </row>
     <row r="146">
-      <c r="A146" s="30"/>
-      <c r="B146" s="30"/>
-      <c r="C146" s="28"/>
+      <c r="A146" s="31"/>
+      <c r="B146" s="31"/>
+      <c r="C146" s="29"/>
     </row>
     <row r="147">
-      <c r="A147" s="30"/>
-      <c r="B147" s="30"/>
-      <c r="C147" s="28"/>
+      <c r="A147" s="31"/>
+      <c r="B147" s="31"/>
+      <c r="C147" s="29"/>
     </row>
     <row r="148">
-      <c r="A148" s="30"/>
-      <c r="B148" s="30"/>
-      <c r="C148" s="28"/>
+      <c r="A148" s="31"/>
+      <c r="B148" s="31"/>
+      <c r="C148" s="29"/>
     </row>
     <row r="149">
-      <c r="A149" s="30"/>
-      <c r="B149" s="30"/>
-      <c r="C149" s="28"/>
+      <c r="A149" s="31"/>
+      <c r="B149" s="31"/>
+      <c r="C149" s="29"/>
     </row>
     <row r="150">
-      <c r="A150" s="30"/>
-      <c r="B150" s="30"/>
-      <c r="C150" s="28"/>
+      <c r="A150" s="31"/>
+      <c r="B150" s="31"/>
+      <c r="C150" s="29"/>
     </row>
     <row r="151">
-      <c r="A151" s="30"/>
-      <c r="B151" s="30"/>
-      <c r="C151" s="28"/>
+      <c r="A151" s="31"/>
+      <c r="B151" s="31"/>
+      <c r="C151" s="29"/>
     </row>
     <row r="152">
-      <c r="A152" s="30"/>
-      <c r="B152" s="30"/>
-      <c r="C152" s="28"/>
+      <c r="A152" s="31"/>
+      <c r="B152" s="31"/>
+      <c r="C152" s="29"/>
     </row>
     <row r="153">
-      <c r="A153" s="30"/>
-      <c r="B153" s="30"/>
-      <c r="C153" s="28"/>
+      <c r="A153" s="31"/>
+      <c r="B153" s="31"/>
+      <c r="C153" s="29"/>
     </row>
     <row r="154">
-      <c r="A154" s="30"/>
-      <c r="B154" s="30"/>
-      <c r="C154" s="28"/>
+      <c r="A154" s="31"/>
+      <c r="B154" s="31"/>
+      <c r="C154" s="29"/>
     </row>
     <row r="155">
-      <c r="A155" s="30"/>
-      <c r="B155" s="30"/>
-      <c r="C155" s="28"/>
+      <c r="A155" s="31"/>
+      <c r="B155" s="31"/>
+      <c r="C155" s="29"/>
     </row>
     <row r="156">
-      <c r="A156" s="30"/>
-      <c r="B156" s="30"/>
-      <c r="C156" s="28"/>
+      <c r="A156" s="31"/>
+      <c r="B156" s="31"/>
+      <c r="C156" s="29"/>
     </row>
     <row r="157">
-      <c r="A157" s="30"/>
-      <c r="B157" s="30"/>
-      <c r="C157" s="28"/>
+      <c r="A157" s="31"/>
+      <c r="B157" s="31"/>
+      <c r="C157" s="29"/>
     </row>
     <row r="158">
-      <c r="A158" s="30"/>
-      <c r="B158" s="30"/>
-      <c r="C158" s="28"/>
+      <c r="A158" s="31"/>
+      <c r="B158" s="31"/>
+      <c r="C158" s="29"/>
     </row>
     <row r="159">
-      <c r="A159" s="30"/>
-      <c r="B159" s="30"/>
+      <c r="A159" s="31"/>
+      <c r="B159" s="31"/>
     </row>
     <row r="160">
-      <c r="A160" s="30"/>
-      <c r="B160" s="30"/>
+      <c r="A160" s="31"/>
+      <c r="B160" s="31"/>
     </row>
     <row r="161">
-      <c r="A161" s="30"/>
-      <c r="B161" s="30"/>
+      <c r="A161" s="31"/>
+      <c r="B161" s="31"/>
     </row>
     <row r="162">
-      <c r="A162" s="30"/>
-      <c r="B162" s="30"/>
+      <c r="A162" s="31"/>
+      <c r="B162" s="31"/>
     </row>
     <row r="163">
-      <c r="A163" s="30"/>
-      <c r="B163" s="30"/>
+      <c r="A163" s="31"/>
+      <c r="B163" s="31"/>
     </row>
     <row r="164">
-      <c r="A164" s="30"/>
-      <c r="B164" s="30"/>
+      <c r="A164" s="31"/>
+      <c r="B164" s="31"/>
     </row>
     <row r="165">
-      <c r="A165" s="30"/>
-      <c r="B165" s="30"/>
+      <c r="A165" s="31"/>
+      <c r="B165" s="31"/>
     </row>
     <row r="166">
-      <c r="A166" s="30"/>
-      <c r="B166" s="30"/>
+      <c r="A166" s="31"/>
+      <c r="B166" s="31"/>
     </row>
     <row r="167">
-      <c r="A167" s="30"/>
-      <c r="B167" s="30"/>
+      <c r="A167" s="31"/>
+      <c r="B167" s="31"/>
     </row>
     <row r="168">
-      <c r="A168" s="30"/>
-      <c r="B168" s="30"/>
+      <c r="A168" s="31"/>
+      <c r="B168" s="31"/>
     </row>
     <row r="169">
-      <c r="A169" s="30"/>
-      <c r="B169" s="30"/>
+      <c r="A169" s="31"/>
+      <c r="B169" s="31"/>
     </row>
     <row r="170">
-      <c r="A170" s="30"/>
-      <c r="B170" s="30"/>
+      <c r="A170" s="31"/>
+      <c r="B170" s="31"/>
     </row>
     <row r="171">
-      <c r="A171" s="30"/>
-      <c r="B171" s="30"/>
+      <c r="A171" s="31"/>
+      <c r="B171" s="31"/>
     </row>
     <row r="172">
-      <c r="A172" s="30"/>
-      <c r="B172" s="30"/>
+      <c r="A172" s="31"/>
+      <c r="B172" s="31"/>
     </row>
     <row r="173">
-      <c r="A173" s="30"/>
-      <c r="B173" s="30"/>
+      <c r="A173" s="31"/>
+      <c r="B173" s="31"/>
     </row>
     <row r="174">
-      <c r="A174" s="30"/>
-      <c r="B174" s="30"/>
+      <c r="A174" s="31"/>
+      <c r="B174" s="31"/>
     </row>
     <row r="175">
-      <c r="A175" s="30"/>
-      <c r="B175" s="30"/>
+      <c r="A175" s="31"/>
+      <c r="B175" s="31"/>
     </row>
     <row r="176">
-      <c r="A176" s="30"/>
-      <c r="B176" s="30"/>
+      <c r="A176" s="31"/>
+      <c r="B176" s="31"/>
     </row>
     <row r="177">
-      <c r="A177" s="30"/>
-      <c r="B177" s="30"/>
+      <c r="A177" s="31"/>
+      <c r="B177" s="31"/>
     </row>
     <row r="178">
-      <c r="A178" s="30"/>
-      <c r="B178" s="30"/>
+      <c r="A178" s="31"/>
+      <c r="B178" s="31"/>
     </row>
     <row r="179">
-      <c r="A179" s="30"/>
-      <c r="B179" s="30"/>
+      <c r="A179" s="31"/>
+      <c r="B179" s="31"/>
     </row>
     <row r="180">
-      <c r="A180" s="30"/>
-      <c r="B180" s="30"/>
+      <c r="A180" s="31"/>
+      <c r="B180" s="31"/>
     </row>
     <row r="181">
-      <c r="A181" s="30"/>
-      <c r="B181" s="30"/>
+      <c r="A181" s="31"/>
+      <c r="B181" s="31"/>
     </row>
     <row r="182">
-      <c r="A182" s="30"/>
-      <c r="B182" s="30"/>
+      <c r="A182" s="31"/>
+      <c r="B182" s="31"/>
     </row>
     <row r="183">
-      <c r="A183" s="30"/>
-      <c r="B183" s="30"/>
+      <c r="A183" s="31"/>
+      <c r="B183" s="31"/>
     </row>
     <row r="184">
-      <c r="A184" s="30"/>
-      <c r="B184" s="30"/>
+      <c r="A184" s="31"/>
+      <c r="B184" s="31"/>
     </row>
     <row r="185">
-      <c r="A185" s="30"/>
-      <c r="B185" s="30"/>
+      <c r="A185" s="31"/>
+      <c r="B185" s="31"/>
     </row>
     <row r="186">
-      <c r="A186" s="30"/>
-      <c r="B186" s="30"/>
+      <c r="A186" s="31"/>
+      <c r="B186" s="31"/>
     </row>
     <row r="187">
-      <c r="A187" s="30"/>
-      <c r="B187" s="30"/>
+      <c r="A187" s="31"/>
+      <c r="B187" s="31"/>
     </row>
     <row r="188">
-      <c r="A188" s="30"/>
-      <c r="B188" s="30"/>
+      <c r="A188" s="31"/>
+      <c r="B188" s="31"/>
     </row>
     <row r="189">
-      <c r="A189" s="30"/>
-      <c r="B189" s="30"/>
+      <c r="A189" s="31"/>
+      <c r="B189" s="31"/>
     </row>
     <row r="190">
-      <c r="A190" s="30"/>
-      <c r="B190" s="30"/>
+      <c r="A190" s="31"/>
+      <c r="B190" s="31"/>
     </row>
     <row r="191">
-      <c r="A191" s="30"/>
-      <c r="B191" s="30"/>
+      <c r="A191" s="31"/>
+      <c r="B191" s="31"/>
     </row>
     <row r="192">
-      <c r="A192" s="30"/>
-      <c r="B192" s="30"/>
+      <c r="A192" s="31"/>
+      <c r="B192" s="31"/>
     </row>
     <row r="193">
-      <c r="A193" s="30"/>
-      <c r="B193" s="30"/>
+      <c r="A193" s="31"/>
+      <c r="B193" s="31"/>
     </row>
     <row r="194">
-      <c r="A194" s="30"/>
-      <c r="B194" s="30"/>
+      <c r="A194" s="31"/>
+      <c r="B194" s="31"/>
     </row>
     <row r="195">
-      <c r="A195" s="30"/>
-      <c r="B195" s="30"/>
+      <c r="A195" s="31"/>
+      <c r="B195" s="31"/>
     </row>
     <row r="196">
-      <c r="A196" s="30"/>
-      <c r="B196" s="30"/>
+      <c r="A196" s="31"/>
+      <c r="B196" s="31"/>
     </row>
     <row r="197">
-      <c r="A197" s="30"/>
-      <c r="B197" s="30"/>
+      <c r="A197" s="31"/>
+      <c r="B197" s="31"/>
     </row>
     <row r="198">
-      <c r="A198" s="30"/>
-      <c r="B198" s="30"/>
+      <c r="A198" s="31"/>
+      <c r="B198" s="31"/>
     </row>
     <row r="199">
-      <c r="A199" s="30"/>
-      <c r="B199" s="30"/>
+      <c r="A199" s="31"/>
+      <c r="B199" s="31"/>
     </row>
     <row r="200">
-      <c r="A200" s="30"/>
-      <c r="B200" s="30"/>
+      <c r="A200" s="31"/>
+      <c r="B200" s="31"/>
     </row>
     <row r="201">
-      <c r="A201" s="30"/>
-      <c r="B201" s="30"/>
+      <c r="A201" s="31"/>
+      <c r="B201" s="31"/>
     </row>
     <row r="202">
-      <c r="A202" s="30"/>
-      <c r="B202" s="30"/>
+      <c r="A202" s="31"/>
+      <c r="B202" s="31"/>
     </row>
     <row r="203">
-      <c r="A203" s="30"/>
-      <c r="B203" s="30"/>
+      <c r="A203" s="31"/>
+      <c r="B203" s="31"/>
     </row>
     <row r="204">
-      <c r="A204" s="30"/>
-      <c r="B204" s="30"/>
+      <c r="A204" s="31"/>
+      <c r="B204" s="31"/>
     </row>
     <row r="205">
-      <c r="A205" s="30"/>
-      <c r="B205" s="30"/>
+      <c r="A205" s="31"/>
+      <c r="B205" s="31"/>
     </row>
     <row r="206">
-      <c r="A206" s="30"/>
-      <c r="B206" s="30"/>
+      <c r="A206" s="31"/>
+      <c r="B206" s="31"/>
     </row>
     <row r="207">
-      <c r="A207" s="30"/>
-      <c r="B207" s="30"/>
+      <c r="A207" s="31"/>
+      <c r="B207" s="31"/>
     </row>
     <row r="208">
-      <c r="A208" s="30"/>
-      <c r="B208" s="30"/>
+      <c r="A208" s="31"/>
+      <c r="B208" s="31"/>
     </row>
     <row r="209">
-      <c r="A209" s="30"/>
-      <c r="B209" s="30"/>
+      <c r="A209" s="31"/>
+      <c r="B209" s="31"/>
     </row>
     <row r="210">
-      <c r="A210" s="30"/>
-      <c r="B210" s="30"/>
+      <c r="A210" s="31"/>
+      <c r="B210" s="31"/>
     </row>
     <row r="211">
-      <c r="A211" s="30"/>
-      <c r="B211" s="30"/>
+      <c r="A211" s="31"/>
+      <c r="B211" s="31"/>
     </row>
     <row r="212">
-      <c r="A212" s="30"/>
-      <c r="B212" s="30"/>
+      <c r="A212" s="31"/>
+      <c r="B212" s="31"/>
     </row>
     <row r="213">
-      <c r="A213" s="30"/>
-      <c r="B213" s="30"/>
+      <c r="A213" s="31"/>
+      <c r="B213" s="31"/>
     </row>
     <row r="214">
-      <c r="A214" s="30"/>
-      <c r="B214" s="30"/>
+      <c r="A214" s="31"/>
+      <c r="B214" s="31"/>
     </row>
     <row r="215">
-      <c r="A215" s="30"/>
-      <c r="B215" s="30"/>
+      <c r="A215" s="31"/>
+      <c r="B215" s="31"/>
     </row>
     <row r="216">
-      <c r="A216" s="30"/>
-      <c r="B216" s="30"/>
+      <c r="A216" s="31"/>
+      <c r="B216" s="31"/>
     </row>
     <row r="217">
-      <c r="A217" s="30"/>
-      <c r="B217" s="30"/>
+      <c r="A217" s="31"/>
+      <c r="B217" s="31"/>
     </row>
     <row r="218">
-      <c r="A218" s="30"/>
-      <c r="B218" s="30"/>
+      <c r="A218" s="31"/>
+      <c r="B218" s="31"/>
     </row>
     <row r="219">
-      <c r="A219" s="30"/>
-      <c r="B219" s="30"/>
+      <c r="A219" s="31"/>
+      <c r="B219" s="31"/>
     </row>
     <row r="220">
-      <c r="A220" s="30"/>
-      <c r="B220" s="30"/>
+      <c r="A220" s="31"/>
+      <c r="B220" s="31"/>
     </row>
     <row r="221">
-      <c r="A221" s="30"/>
-      <c r="B221" s="30"/>
+      <c r="A221" s="31"/>
+      <c r="B221" s="31"/>
     </row>
     <row r="222">
-      <c r="A222" s="30"/>
-      <c r="B222" s="30"/>
+      <c r="A222" s="31"/>
+      <c r="B222" s="31"/>
     </row>
     <row r="223">
-      <c r="A223" s="30"/>
-      <c r="B223" s="30"/>
+      <c r="A223" s="31"/>
+      <c r="B223" s="31"/>
     </row>
     <row r="224">
-      <c r="A224" s="30"/>
-      <c r="B224" s="30"/>
+      <c r="A224" s="31"/>
+      <c r="B224" s="31"/>
     </row>
     <row r="225">
-      <c r="A225" s="30"/>
-      <c r="B225" s="30"/>
+      <c r="A225" s="31"/>
+      <c r="B225" s="31"/>
     </row>
     <row r="226">
-      <c r="A226" s="30"/>
-      <c r="B226" s="30"/>
+      <c r="A226" s="31"/>
+      <c r="B226" s="31"/>
     </row>
     <row r="227">
-      <c r="A227" s="30"/>
-      <c r="B227" s="30"/>
+      <c r="A227" s="31"/>
+      <c r="B227" s="31"/>
     </row>
     <row r="228">
-      <c r="A228" s="30"/>
-      <c r="B228" s="30"/>
+      <c r="A228" s="31"/>
+      <c r="B228" s="31"/>
     </row>
     <row r="229">
-      <c r="A229" s="30"/>
-      <c r="B229" s="30"/>
+      <c r="A229" s="31"/>
+      <c r="B229" s="31"/>
     </row>
     <row r="230">
-      <c r="A230" s="30"/>
-      <c r="B230" s="30"/>
+      <c r="A230" s="31"/>
+      <c r="B230" s="31"/>
     </row>
     <row r="231">
-      <c r="A231" s="30"/>
-      <c r="B231" s="30"/>
+      <c r="A231" s="31"/>
+      <c r="B231" s="31"/>
     </row>
     <row r="232">
-      <c r="A232" s="30"/>
-      <c r="B232" s="30"/>
+      <c r="A232" s="31"/>
+      <c r="B232" s="31"/>
     </row>
     <row r="233">
-      <c r="A233" s="30"/>
-      <c r="B233" s="30"/>
+      <c r="A233" s="31"/>
+      <c r="B233" s="31"/>
     </row>
     <row r="234">
-      <c r="A234" s="30"/>
-      <c r="B234" s="30"/>
+      <c r="A234" s="31"/>
+      <c r="B234" s="31"/>
     </row>
     <row r="235">
-      <c r="A235" s="30"/>
-      <c r="B235" s="30"/>
+      <c r="A235" s="31"/>
+      <c r="B235" s="31"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -7136,2034 +7248,2034 @@
     <col customWidth="1" min="2" max="2" width="4.33203125"/>
     <col bestFit="1" min="3" max="3" width="35.77734375"/>
     <col customWidth="1" min="4" max="11" width="3.44140625"/>
-    <col customWidth="1" min="12" max="12" style="31" width="6"/>
+    <col customWidth="1" min="12" max="12" style="32" width="6"/>
     <col customWidth="1" min="13" max="22" width="3.44140625"/>
-    <col customWidth="1" min="23" max="23" style="31" width="6"/>
+    <col customWidth="1" min="23" max="23" style="32" width="6"/>
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
-    <col customWidth="1" min="30" max="30" style="31" width="6"/>
+    <col customWidth="1" min="30" max="30" style="32" width="6"/>
     <col customWidth="1" min="31" max="39" width="3.44140625"/>
     <col bestFit="1" customWidth="1" min="40" max="40" width="13.88671875"/>
     <col customWidth="1" min="41" max="47" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="32" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="B1" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="C1" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="D1" s="35" t="s">
+    <row r="1" s="33" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="B1" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="35" t="s">
-        <v>85</v>
-      </c>
-      <c r="F1" s="36" t="s">
+      <c r="E1" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="F1" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="G1" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="I1" s="35" t="s">
+      <c r="H1" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="35" t="s">
+      <c r="J1" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="L1" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="M1" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="N1" s="37" t="s">
+      <c r="K1" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="L1" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="M1" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="N1" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="P1" s="35" t="s">
+      <c r="O1" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="P1" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="R1" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="S1" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="T1" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="U1" s="35" t="s">
+      <c r="Q1" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="V1" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="W1" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="X1" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="Y1" s="35" t="s">
+      <c r="R1" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="Z1" s="37" t="s">
+      <c r="S1" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="AA1" s="41" t="s">
+      <c r="T1" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="AB1" s="42" t="s">
+      <c r="U1" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="AC1" s="42" t="s">
+      <c r="V1" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="AD1" s="39" t="s">
+      <c r="W1" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="AE1" s="43" t="s">
+      <c r="X1" s="36" t="s">
         <v>104</v>
       </c>
-      <c r="AF1" s="44" t="s">
+      <c r="Y1" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="AG1" s="45" t="s">
+      <c r="Z1" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="AH1" s="45" t="s">
+      <c r="AA1" s="42" t="s">
         <v>107</v>
       </c>
-      <c r="AI1" s="45" t="s">
+      <c r="AB1" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="AJ1" s="45" t="s">
+      <c r="AC1" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="AK1" s="42" t="s">
+      <c r="AD1" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="AL1" s="46"/>
-      <c r="AM1" s="46"/>
-      <c r="AN1" s="46"/>
-      <c r="AO1" s="46"/>
-      <c r="AP1" s="46"/>
-      <c r="AQ1" s="46"/>
-      <c r="AR1" s="46"/>
-      <c r="AS1" s="46"/>
-      <c r="AT1" s="46"/>
-      <c r="AU1" s="46"/>
+      <c r="AE1" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="AF1" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG1" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH1" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="AI1" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="AJ1" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="AK1" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="AL1" s="47"/>
+      <c r="AM1" s="47"/>
+      <c r="AN1" s="47"/>
+      <c r="AO1" s="47"/>
+      <c r="AP1" s="47"/>
+      <c r="AQ1" s="47"/>
+      <c r="AR1" s="47"/>
+      <c r="AS1" s="47"/>
+      <c r="AT1" s="47"/>
+      <c r="AU1" s="47"/>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="49"/>
-      <c r="S2" s="49"/>
-      <c r="T2" s="49"/>
-      <c r="U2" s="49"/>
-      <c r="V2" s="54"/>
-      <c r="W2" s="56"/>
-      <c r="X2" s="49"/>
-      <c r="Y2" s="49"/>
-      <c r="Z2" s="54"/>
-      <c r="AA2" s="55"/>
-      <c r="AB2" s="49"/>
-      <c r="AC2" s="49"/>
-      <c r="AD2" s="53"/>
-      <c r="AE2" s="54"/>
-      <c r="AF2" s="55"/>
-      <c r="AG2" s="49"/>
-      <c r="AH2" s="49"/>
-      <c r="AI2" s="49"/>
-      <c r="AJ2" s="49"/>
-      <c r="AK2" s="49"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="50"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="50"/>
+      <c r="V2" s="55"/>
+      <c r="W2" s="57"/>
+      <c r="X2" s="50"/>
+      <c r="Y2" s="50"/>
+      <c r="Z2" s="55"/>
+      <c r="AA2" s="56"/>
+      <c r="AB2" s="50"/>
+      <c r="AC2" s="50"/>
+      <c r="AD2" s="54"/>
+      <c r="AE2" s="55"/>
+      <c r="AF2" s="56"/>
+      <c r="AG2" s="50"/>
+      <c r="AH2" s="50"/>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="50"/>
+      <c r="AK2" s="50"/>
     </row>
     <row r="3" ht="12" customHeight="1">
-      <c r="B3" s="47"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="49"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="55"/>
-      <c r="P3" s="49"/>
-      <c r="Q3" s="49"/>
-      <c r="R3" s="49"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="49"/>
-      <c r="U3" s="49"/>
-      <c r="V3" s="54"/>
-      <c r="W3" s="56"/>
-      <c r="X3" s="49"/>
-      <c r="Y3" s="49"/>
-      <c r="Z3" s="54"/>
-      <c r="AA3" s="55"/>
-      <c r="AB3" s="49"/>
-      <c r="AC3" s="49"/>
-      <c r="AD3" s="53"/>
-      <c r="AE3" s="54"/>
-      <c r="AF3" s="55"/>
-      <c r="AG3" s="49"/>
-      <c r="AH3" s="49"/>
-      <c r="AI3" s="49"/>
-      <c r="AJ3" s="49"/>
-      <c r="AK3" s="49"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="55"/>
+      <c r="O3" s="56"/>
+      <c r="P3" s="50"/>
+      <c r="Q3" s="50"/>
+      <c r="R3" s="50"/>
+      <c r="S3" s="50"/>
+      <c r="T3" s="50"/>
+      <c r="U3" s="50"/>
+      <c r="V3" s="55"/>
+      <c r="W3" s="57"/>
+      <c r="X3" s="50"/>
+      <c r="Y3" s="50"/>
+      <c r="Z3" s="55"/>
+      <c r="AA3" s="56"/>
+      <c r="AB3" s="50"/>
+      <c r="AC3" s="50"/>
+      <c r="AD3" s="54"/>
+      <c r="AE3" s="55"/>
+      <c r="AF3" s="56"/>
+      <c r="AG3" s="50"/>
+      <c r="AH3" s="50"/>
+      <c r="AI3" s="50"/>
+      <c r="AJ3" s="50"/>
+      <c r="AK3" s="50"/>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="47"/>
-      <c r="C4" s="48" t="s">
-        <v>111</v>
-      </c>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="49"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="49"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="49"/>
-      <c r="Q4" s="49"/>
-      <c r="R4" s="49"/>
-      <c r="S4" s="49"/>
-      <c r="T4" s="49"/>
-      <c r="U4" s="49"/>
-      <c r="V4" s="54"/>
-      <c r="W4" s="56"/>
-      <c r="X4" s="49"/>
-      <c r="Y4" s="49"/>
-      <c r="Z4" s="54"/>
-      <c r="AA4" s="55"/>
-      <c r="AB4" s="49"/>
-      <c r="AC4" s="49"/>
-      <c r="AD4" s="53"/>
-      <c r="AE4" s="54"/>
-      <c r="AF4" s="55"/>
-      <c r="AG4" s="49"/>
-      <c r="AH4" s="49"/>
-      <c r="AI4" s="49"/>
-      <c r="AJ4" s="49"/>
-      <c r="AK4" s="49"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="56"/>
+      <c r="P4" s="50"/>
+      <c r="Q4" s="50"/>
+      <c r="R4" s="50"/>
+      <c r="S4" s="50"/>
+      <c r="T4" s="50"/>
+      <c r="U4" s="50"/>
+      <c r="V4" s="55"/>
+      <c r="W4" s="57"/>
+      <c r="X4" s="50"/>
+      <c r="Y4" s="50"/>
+      <c r="Z4" s="55"/>
+      <c r="AA4" s="56"/>
+      <c r="AB4" s="50"/>
+      <c r="AC4" s="50"/>
+      <c r="AD4" s="54"/>
+      <c r="AE4" s="55"/>
+      <c r="AF4" s="56"/>
+      <c r="AG4" s="50"/>
+      <c r="AH4" s="50"/>
+      <c r="AI4" s="50"/>
+      <c r="AJ4" s="50"/>
+      <c r="AK4" s="50"/>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="47"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="49"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="54"/>
-      <c r="W5" s="56"/>
-      <c r="X5" s="49"/>
-      <c r="Y5" s="49"/>
-      <c r="Z5" s="54"/>
-      <c r="AA5" s="55"/>
-      <c r="AB5" s="49"/>
-      <c r="AC5" s="49"/>
-      <c r="AD5" s="53"/>
-      <c r="AE5" s="54"/>
-      <c r="AF5" s="55"/>
-      <c r="AG5" s="49"/>
-      <c r="AH5" s="49"/>
-      <c r="AI5" s="49"/>
-      <c r="AJ5" s="49"/>
-      <c r="AK5" s="49"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="50"/>
+      <c r="N5" s="55"/>
+      <c r="O5" s="56"/>
+      <c r="P5" s="50"/>
+      <c r="Q5" s="50"/>
+      <c r="R5" s="50"/>
+      <c r="S5" s="50"/>
+      <c r="T5" s="50"/>
+      <c r="U5" s="50"/>
+      <c r="V5" s="55"/>
+      <c r="W5" s="57"/>
+      <c r="X5" s="50"/>
+      <c r="Y5" s="50"/>
+      <c r="Z5" s="55"/>
+      <c r="AA5" s="56"/>
+      <c r="AB5" s="50"/>
+      <c r="AC5" s="50"/>
+      <c r="AD5" s="54"/>
+      <c r="AE5" s="55"/>
+      <c r="AF5" s="56"/>
+      <c r="AG5" s="50"/>
+      <c r="AH5" s="50"/>
+      <c r="AI5" s="50"/>
+      <c r="AJ5" s="50"/>
+      <c r="AK5" s="50"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="47"/>
-      <c r="C6" s="48" t="s">
+      <c r="B6" s="48"/>
+      <c r="C6" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="49"/>
-      <c r="N6" s="54"/>
-      <c r="O6" s="55"/>
-      <c r="P6" s="49"/>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49"/>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
-      <c r="V6" s="54"/>
-      <c r="W6" s="56"/>
-      <c r="X6" s="49"/>
-      <c r="Y6" s="49"/>
-      <c r="Z6" s="54"/>
-      <c r="AA6" s="55"/>
-      <c r="AB6" s="49"/>
-      <c r="AC6" s="49"/>
-      <c r="AD6" s="53"/>
-      <c r="AE6" s="51"/>
-      <c r="AF6" s="52"/>
-      <c r="AG6" s="63"/>
-      <c r="AH6" s="63"/>
-      <c r="AI6" s="63"/>
-      <c r="AJ6" s="63"/>
-      <c r="AK6" s="63"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="50"/>
+      <c r="K6" s="50"/>
+      <c r="L6" s="54"/>
+      <c r="M6" s="50"/>
+      <c r="N6" s="55"/>
+      <c r="O6" s="56"/>
+      <c r="P6" s="50"/>
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
+      <c r="V6" s="55"/>
+      <c r="W6" s="57"/>
+      <c r="X6" s="50"/>
+      <c r="Y6" s="50"/>
+      <c r="Z6" s="55"/>
+      <c r="AA6" s="56"/>
+      <c r="AB6" s="50"/>
+      <c r="AC6" s="50"/>
+      <c r="AD6" s="54"/>
+      <c r="AE6" s="52"/>
+      <c r="AF6" s="53"/>
+      <c r="AG6" s="64"/>
+      <c r="AH6" s="64"/>
+      <c r="AI6" s="64"/>
+      <c r="AJ6" s="64"/>
+      <c r="AK6" s="64"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="47"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="61"/>
-      <c r="I7" s="62"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="49"/>
-      <c r="N7" s="54"/>
-      <c r="O7" s="61"/>
-      <c r="P7" s="49"/>
-      <c r="Q7" s="62"/>
-      <c r="R7" s="49"/>
-      <c r="S7" s="49"/>
-      <c r="T7" s="49"/>
-      <c r="U7" s="49"/>
-      <c r="V7" s="54"/>
-      <c r="W7" s="56"/>
-      <c r="X7" s="49"/>
-      <c r="Y7" s="49"/>
-      <c r="Z7" s="54"/>
-      <c r="AA7" s="55"/>
-      <c r="AB7" s="49"/>
-      <c r="AC7" s="49"/>
-      <c r="AD7" s="53"/>
-      <c r="AE7" s="54"/>
-      <c r="AF7" s="55"/>
-      <c r="AG7" s="49"/>
-      <c r="AH7" s="49"/>
-      <c r="AI7" s="49"/>
-      <c r="AJ7" s="49"/>
-      <c r="AK7" s="49"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="50"/>
+      <c r="L7" s="54"/>
+      <c r="M7" s="50"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="62"/>
+      <c r="P7" s="50"/>
+      <c r="Q7" s="63"/>
+      <c r="R7" s="50"/>
+      <c r="S7" s="50"/>
+      <c r="T7" s="50"/>
+      <c r="U7" s="50"/>
+      <c r="V7" s="55"/>
+      <c r="W7" s="57"/>
+      <c r="X7" s="50"/>
+      <c r="Y7" s="50"/>
+      <c r="Z7" s="55"/>
+      <c r="AA7" s="56"/>
+      <c r="AB7" s="50"/>
+      <c r="AC7" s="50"/>
+      <c r="AD7" s="54"/>
+      <c r="AE7" s="55"/>
+      <c r="AF7" s="56"/>
+      <c r="AG7" s="50"/>
+      <c r="AH7" s="50"/>
+      <c r="AI7" s="50"/>
+      <c r="AJ7" s="50"/>
+      <c r="AK7" s="50"/>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="47"/>
-      <c r="C8" s="48" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="63"/>
-      <c r="K8" s="63"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="63"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="52"/>
-      <c r="P8" s="63"/>
-      <c r="Q8" s="63"/>
-      <c r="R8" s="63"/>
-      <c r="S8" s="63"/>
-      <c r="T8" s="63"/>
-      <c r="U8" s="63"/>
-      <c r="V8" s="51"/>
-      <c r="W8" s="56"/>
-      <c r="X8" s="63"/>
-      <c r="Y8" s="63"/>
-      <c r="Z8" s="51"/>
-      <c r="AA8" s="52"/>
-      <c r="AB8" s="63"/>
-      <c r="AC8" s="63"/>
-      <c r="AD8" s="53"/>
-      <c r="AE8" s="51"/>
-      <c r="AF8" s="52"/>
-      <c r="AG8" s="63"/>
-      <c r="AH8" s="63"/>
-      <c r="AI8" s="63"/>
-      <c r="AJ8" s="63"/>
-      <c r="AK8" s="63"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="64"/>
+      <c r="L8" s="54"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="52"/>
+      <c r="O8" s="53"/>
+      <c r="P8" s="64"/>
+      <c r="Q8" s="64"/>
+      <c r="R8" s="64"/>
+      <c r="S8" s="64"/>
+      <c r="T8" s="64"/>
+      <c r="U8" s="64"/>
+      <c r="V8" s="52"/>
+      <c r="W8" s="57"/>
+      <c r="X8" s="64"/>
+      <c r="Y8" s="64"/>
+      <c r="Z8" s="52"/>
+      <c r="AA8" s="53"/>
+      <c r="AB8" s="64"/>
+      <c r="AC8" s="64"/>
+      <c r="AD8" s="54"/>
+      <c r="AE8" s="52"/>
+      <c r="AF8" s="53"/>
+      <c r="AG8" s="64"/>
+      <c r="AH8" s="64"/>
+      <c r="AI8" s="64"/>
+      <c r="AJ8" s="64"/>
+      <c r="AK8" s="64"/>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="47"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="62"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="62"/>
-      <c r="J9" s="62"/>
-      <c r="K9" s="49"/>
-      <c r="L9" s="53"/>
-      <c r="M9" s="62"/>
-      <c r="N9" s="54"/>
-      <c r="O9" s="61"/>
-      <c r="P9" s="49"/>
-      <c r="Q9" s="62"/>
-      <c r="R9" s="49"/>
-      <c r="S9" s="64"/>
-      <c r="T9" s="49"/>
-      <c r="U9" s="49"/>
-      <c r="V9" s="54"/>
-      <c r="W9" s="56"/>
-      <c r="X9" s="49"/>
-      <c r="Y9" s="49"/>
-      <c r="Z9" s="54"/>
-      <c r="AA9" s="55"/>
-      <c r="AB9" s="49"/>
-      <c r="AC9" s="49"/>
-      <c r="AD9" s="53"/>
-      <c r="AE9" s="54"/>
-      <c r="AF9" s="55"/>
-      <c r="AG9" s="49"/>
-      <c r="AH9" s="49"/>
-      <c r="AI9" s="49"/>
-      <c r="AJ9" s="49"/>
-      <c r="AK9" s="49"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="63"/>
+      <c r="K9" s="50"/>
+      <c r="L9" s="54"/>
+      <c r="M9" s="63"/>
+      <c r="N9" s="55"/>
+      <c r="O9" s="62"/>
+      <c r="P9" s="50"/>
+      <c r="Q9" s="63"/>
+      <c r="R9" s="50"/>
+      <c r="S9" s="65"/>
+      <c r="T9" s="50"/>
+      <c r="U9" s="50"/>
+      <c r="V9" s="55"/>
+      <c r="W9" s="57"/>
+      <c r="X9" s="50"/>
+      <c r="Y9" s="50"/>
+      <c r="Z9" s="55"/>
+      <c r="AA9" s="56"/>
+      <c r="AB9" s="50"/>
+      <c r="AC9" s="50"/>
+      <c r="AD9" s="54"/>
+      <c r="AE9" s="55"/>
+      <c r="AF9" s="56"/>
+      <c r="AG9" s="50"/>
+      <c r="AH9" s="50"/>
+      <c r="AI9" s="50"/>
+      <c r="AJ9" s="50"/>
+      <c r="AK9" s="50"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="47"/>
-      <c r="C10" s="48" t="s">
-        <v>113</v>
-      </c>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="49"/>
-      <c r="N10" s="54"/>
-      <c r="O10" s="55"/>
-      <c r="P10" s="49"/>
-      <c r="Q10" s="49"/>
-      <c r="R10" s="49"/>
-      <c r="S10" s="49"/>
-      <c r="T10" s="49"/>
-      <c r="U10" s="49"/>
-      <c r="V10" s="51"/>
-      <c r="W10" s="56"/>
-      <c r="X10" s="63"/>
-      <c r="Y10" s="63"/>
-      <c r="Z10" s="51"/>
-      <c r="AA10" s="55"/>
-      <c r="AB10" s="49"/>
-      <c r="AC10" s="49"/>
-      <c r="AD10" s="53"/>
-      <c r="AE10" s="54"/>
-      <c r="AF10" s="55"/>
-      <c r="AG10" s="49"/>
-      <c r="AH10" s="49"/>
-      <c r="AI10" s="49"/>
-      <c r="AJ10" s="49"/>
-      <c r="AK10" s="49"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="50"/>
+      <c r="J10" s="50"/>
+      <c r="K10" s="50"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="50"/>
+      <c r="N10" s="55"/>
+      <c r="O10" s="56"/>
+      <c r="P10" s="50"/>
+      <c r="Q10" s="50"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="50"/>
+      <c r="T10" s="50"/>
+      <c r="U10" s="50"/>
+      <c r="V10" s="52"/>
+      <c r="W10" s="57"/>
+      <c r="X10" s="64"/>
+      <c r="Y10" s="64"/>
+      <c r="Z10" s="52"/>
+      <c r="AA10" s="56"/>
+      <c r="AB10" s="50"/>
+      <c r="AC10" s="50"/>
+      <c r="AD10" s="54"/>
+      <c r="AE10" s="55"/>
+      <c r="AF10" s="56"/>
+      <c r="AG10" s="50"/>
+      <c r="AH10" s="50"/>
+      <c r="AI10" s="50"/>
+      <c r="AJ10" s="50"/>
+      <c r="AK10" s="50"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="47"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="55"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="49"/>
-      <c r="K11" s="49"/>
-      <c r="L11" s="53"/>
-      <c r="M11" s="49"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="55"/>
-      <c r="P11" s="49"/>
-      <c r="Q11" s="49"/>
-      <c r="R11" s="49"/>
-      <c r="S11" s="49"/>
-      <c r="T11" s="49"/>
-      <c r="U11" s="49"/>
-      <c r="V11" s="54"/>
-      <c r="W11" s="56"/>
-      <c r="X11" s="49"/>
-      <c r="Y11" s="49"/>
-      <c r="Z11" s="54"/>
-      <c r="AA11" s="55"/>
-      <c r="AB11" s="49"/>
-      <c r="AC11" s="49"/>
-      <c r="AD11" s="53"/>
-      <c r="AE11" s="54"/>
-      <c r="AF11" s="55"/>
-      <c r="AG11" s="49"/>
-      <c r="AH11" s="49"/>
-      <c r="AI11" s="49"/>
-      <c r="AJ11" s="49"/>
-      <c r="AK11" s="49"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="50"/>
+      <c r="J11" s="50"/>
+      <c r="K11" s="50"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="50"/>
+      <c r="N11" s="55"/>
+      <c r="O11" s="56"/>
+      <c r="P11" s="50"/>
+      <c r="Q11" s="50"/>
+      <c r="R11" s="50"/>
+      <c r="S11" s="50"/>
+      <c r="T11" s="50"/>
+      <c r="U11" s="50"/>
+      <c r="V11" s="55"/>
+      <c r="W11" s="57"/>
+      <c r="X11" s="50"/>
+      <c r="Y11" s="50"/>
+      <c r="Z11" s="55"/>
+      <c r="AA11" s="56"/>
+      <c r="AB11" s="50"/>
+      <c r="AC11" s="50"/>
+      <c r="AD11" s="54"/>
+      <c r="AE11" s="55"/>
+      <c r="AF11" s="56"/>
+      <c r="AG11" s="50"/>
+      <c r="AH11" s="50"/>
+      <c r="AI11" s="50"/>
+      <c r="AJ11" s="50"/>
+      <c r="AK11" s="50"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="47"/>
-      <c r="C12" s="48" t="s">
-        <v>114</v>
-      </c>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="49"/>
-      <c r="K12" s="49"/>
-      <c r="L12" s="53"/>
-      <c r="M12" s="49"/>
-      <c r="N12" s="54"/>
-      <c r="O12" s="55"/>
-      <c r="P12" s="49"/>
-      <c r="Q12" s="49"/>
-      <c r="R12" s="49"/>
-      <c r="S12" s="49"/>
-      <c r="T12" s="49"/>
-      <c r="U12" s="49"/>
-      <c r="V12" s="54"/>
-      <c r="W12" s="56"/>
-      <c r="X12" s="49"/>
-      <c r="Y12" s="49"/>
-      <c r="Z12" s="54"/>
-      <c r="AA12" s="55"/>
-      <c r="AB12" s="49"/>
-      <c r="AC12" s="49"/>
-      <c r="AD12" s="53"/>
-      <c r="AE12" s="54"/>
-      <c r="AF12" s="52"/>
-      <c r="AG12" s="63"/>
-      <c r="AH12" s="63"/>
-      <c r="AI12" s="63"/>
-      <c r="AJ12" s="63"/>
-      <c r="AK12" s="63"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="49" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="54"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="55"/>
+      <c r="O12" s="56"/>
+      <c r="P12" s="50"/>
+      <c r="Q12" s="50"/>
+      <c r="R12" s="50"/>
+      <c r="S12" s="50"/>
+      <c r="T12" s="50"/>
+      <c r="U12" s="50"/>
+      <c r="V12" s="55"/>
+      <c r="W12" s="57"/>
+      <c r="X12" s="50"/>
+      <c r="Y12" s="50"/>
+      <c r="Z12" s="55"/>
+      <c r="AA12" s="56"/>
+      <c r="AB12" s="50"/>
+      <c r="AC12" s="50"/>
+      <c r="AD12" s="54"/>
+      <c r="AE12" s="55"/>
+      <c r="AF12" s="53"/>
+      <c r="AG12" s="64"/>
+      <c r="AH12" s="64"/>
+      <c r="AI12" s="64"/>
+      <c r="AJ12" s="64"/>
+      <c r="AK12" s="64"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="47"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="49"/>
-      <c r="K13" s="49"/>
-      <c r="L13" s="53"/>
-      <c r="M13" s="49"/>
-      <c r="N13" s="54"/>
-      <c r="O13" s="55"/>
-      <c r="P13" s="49"/>
-      <c r="Q13" s="49"/>
-      <c r="R13" s="49"/>
-      <c r="S13" s="49"/>
-      <c r="T13" s="49"/>
-      <c r="U13" s="49"/>
-      <c r="V13" s="54"/>
-      <c r="W13" s="56"/>
-      <c r="X13" s="49"/>
-      <c r="Y13" s="49"/>
-      <c r="Z13" s="54"/>
-      <c r="AA13" s="55"/>
-      <c r="AB13" s="49"/>
-      <c r="AC13" s="49"/>
-      <c r="AD13" s="53"/>
-      <c r="AE13" s="54"/>
-      <c r="AF13" s="55"/>
-      <c r="AG13" s="49"/>
-      <c r="AH13" s="49"/>
-      <c r="AI13" s="49"/>
-      <c r="AJ13" s="49"/>
-      <c r="AK13" s="49"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="50"/>
+      <c r="K13" s="50"/>
+      <c r="L13" s="54"/>
+      <c r="M13" s="50"/>
+      <c r="N13" s="55"/>
+      <c r="O13" s="56"/>
+      <c r="P13" s="50"/>
+      <c r="Q13" s="50"/>
+      <c r="R13" s="50"/>
+      <c r="S13" s="50"/>
+      <c r="T13" s="50"/>
+      <c r="U13" s="50"/>
+      <c r="V13" s="55"/>
+      <c r="W13" s="57"/>
+      <c r="X13" s="50"/>
+      <c r="Y13" s="50"/>
+      <c r="Z13" s="55"/>
+      <c r="AA13" s="56"/>
+      <c r="AB13" s="50"/>
+      <c r="AC13" s="50"/>
+      <c r="AD13" s="54"/>
+      <c r="AE13" s="55"/>
+      <c r="AF13" s="56"/>
+      <c r="AG13" s="50"/>
+      <c r="AH13" s="50"/>
+      <c r="AI13" s="50"/>
+      <c r="AJ13" s="50"/>
+      <c r="AK13" s="50"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="65" t="s">
-        <v>115</v>
-      </c>
-      <c r="C14" s="66" t="s">
-        <v>116</v>
-      </c>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="67"/>
-      <c r="I14" s="68"/>
-      <c r="J14" s="68"/>
-      <c r="K14" s="68"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="68"/>
-      <c r="N14" s="69"/>
-      <c r="O14" s="67"/>
-      <c r="P14" s="68"/>
-      <c r="Q14" s="68"/>
-      <c r="R14" s="68"/>
-      <c r="S14" s="68"/>
-      <c r="T14" s="68"/>
-      <c r="U14" s="68"/>
-      <c r="V14" s="69"/>
-      <c r="W14" s="56"/>
-      <c r="X14" s="68"/>
-      <c r="Y14" s="68"/>
-      <c r="Z14" s="69"/>
-      <c r="AA14" s="67"/>
-      <c r="AB14" s="68"/>
-      <c r="AC14" s="68"/>
-      <c r="AD14" s="53"/>
-      <c r="AE14" s="69"/>
-      <c r="AF14" s="67"/>
-      <c r="AG14" s="68"/>
-      <c r="AH14" s="68"/>
-      <c r="AI14" s="68"/>
-      <c r="AJ14" s="68"/>
-      <c r="AK14" s="68"/>
+      <c r="B14" s="66" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="67" t="s">
+        <v>123</v>
+      </c>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="69"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="69"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="69"/>
+      <c r="N14" s="70"/>
+      <c r="O14" s="68"/>
+      <c r="P14" s="69"/>
+      <c r="Q14" s="69"/>
+      <c r="R14" s="69"/>
+      <c r="S14" s="69"/>
+      <c r="T14" s="69"/>
+      <c r="U14" s="69"/>
+      <c r="V14" s="70"/>
+      <c r="W14" s="57"/>
+      <c r="X14" s="69"/>
+      <c r="Y14" s="69"/>
+      <c r="Z14" s="70"/>
+      <c r="AA14" s="68"/>
+      <c r="AB14" s="69"/>
+      <c r="AC14" s="69"/>
+      <c r="AD14" s="54"/>
+      <c r="AE14" s="70"/>
+      <c r="AF14" s="68"/>
+      <c r="AG14" s="69"/>
+      <c r="AH14" s="69"/>
+      <c r="AI14" s="69"/>
+      <c r="AJ14" s="69"/>
+      <c r="AK14" s="69"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="65"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="68"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="68"/>
-      <c r="K15" s="68"/>
-      <c r="L15" s="53"/>
-      <c r="M15" s="68"/>
-      <c r="N15" s="69"/>
-      <c r="O15" s="67"/>
-      <c r="P15" s="68"/>
-      <c r="Q15" s="68"/>
-      <c r="R15" s="68"/>
-      <c r="S15" s="68"/>
-      <c r="T15" s="68"/>
-      <c r="U15" s="68"/>
-      <c r="V15" s="69"/>
-      <c r="W15" s="56"/>
-      <c r="X15" s="68"/>
-      <c r="Y15" s="68"/>
-      <c r="Z15" s="69"/>
-      <c r="AA15" s="67"/>
-      <c r="AB15" s="68"/>
-      <c r="AC15" s="68"/>
-      <c r="AD15" s="53"/>
-      <c r="AE15" s="69"/>
-      <c r="AF15" s="67"/>
-      <c r="AG15" s="68"/>
-      <c r="AH15" s="68"/>
-      <c r="AI15" s="68"/>
-      <c r="AJ15" s="68"/>
-      <c r="AK15" s="68"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="67"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="69"/>
+      <c r="J15" s="69"/>
+      <c r="K15" s="69"/>
+      <c r="L15" s="54"/>
+      <c r="M15" s="69"/>
+      <c r="N15" s="70"/>
+      <c r="O15" s="68"/>
+      <c r="P15" s="69"/>
+      <c r="Q15" s="69"/>
+      <c r="R15" s="69"/>
+      <c r="S15" s="69"/>
+      <c r="T15" s="69"/>
+      <c r="U15" s="69"/>
+      <c r="V15" s="70"/>
+      <c r="W15" s="57"/>
+      <c r="X15" s="69"/>
+      <c r="Y15" s="69"/>
+      <c r="Z15" s="70"/>
+      <c r="AA15" s="68"/>
+      <c r="AB15" s="69"/>
+      <c r="AC15" s="69"/>
+      <c r="AD15" s="54"/>
+      <c r="AE15" s="70"/>
+      <c r="AF15" s="68"/>
+      <c r="AG15" s="69"/>
+      <c r="AH15" s="69"/>
+      <c r="AI15" s="69"/>
+      <c r="AJ15" s="69"/>
+      <c r="AK15" s="69"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="65"/>
-      <c r="C16" s="66" t="s">
-        <v>117</v>
-      </c>
-      <c r="D16" s="63"/>
-      <c r="E16" s="63"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="67"/>
-      <c r="I16" s="68"/>
-      <c r="J16" s="68"/>
-      <c r="K16" s="68"/>
-      <c r="L16" s="53"/>
-      <c r="M16" s="68"/>
-      <c r="N16" s="69"/>
-      <c r="O16" s="67"/>
-      <c r="P16" s="68"/>
-      <c r="Q16" s="68"/>
-      <c r="R16" s="68"/>
-      <c r="S16" s="68"/>
-      <c r="T16" s="68"/>
-      <c r="U16" s="68"/>
-      <c r="V16" s="69"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="68"/>
-      <c r="Y16" s="68"/>
-      <c r="Z16" s="69"/>
-      <c r="AA16" s="67"/>
-      <c r="AB16" s="68"/>
-      <c r="AC16" s="68"/>
-      <c r="AD16" s="53"/>
-      <c r="AE16" s="69"/>
-      <c r="AF16" s="67"/>
-      <c r="AG16" s="68"/>
-      <c r="AH16" s="68"/>
-      <c r="AI16" s="68"/>
-      <c r="AJ16" s="68"/>
-      <c r="AK16" s="68"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="67" t="s">
+        <v>124</v>
+      </c>
+      <c r="D16" s="64"/>
+      <c r="E16" s="64"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="68"/>
+      <c r="I16" s="69"/>
+      <c r="J16" s="69"/>
+      <c r="K16" s="69"/>
+      <c r="L16" s="54"/>
+      <c r="M16" s="69"/>
+      <c r="N16" s="70"/>
+      <c r="O16" s="68"/>
+      <c r="P16" s="69"/>
+      <c r="Q16" s="69"/>
+      <c r="R16" s="69"/>
+      <c r="S16" s="69"/>
+      <c r="T16" s="69"/>
+      <c r="U16" s="69"/>
+      <c r="V16" s="70"/>
+      <c r="W16" s="57"/>
+      <c r="X16" s="69"/>
+      <c r="Y16" s="69"/>
+      <c r="Z16" s="70"/>
+      <c r="AA16" s="68"/>
+      <c r="AB16" s="69"/>
+      <c r="AC16" s="69"/>
+      <c r="AD16" s="54"/>
+      <c r="AE16" s="70"/>
+      <c r="AF16" s="68"/>
+      <c r="AG16" s="69"/>
+      <c r="AH16" s="69"/>
+      <c r="AI16" s="69"/>
+      <c r="AJ16" s="69"/>
+      <c r="AK16" s="69"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="65"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="67"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="68"/>
-      <c r="K17" s="68"/>
-      <c r="L17" s="53"/>
-      <c r="M17" s="68"/>
-      <c r="N17" s="69"/>
-      <c r="O17" s="67"/>
-      <c r="P17" s="68"/>
-      <c r="Q17" s="68"/>
-      <c r="R17" s="68"/>
-      <c r="S17" s="68"/>
-      <c r="T17" s="68"/>
-      <c r="U17" s="68"/>
-      <c r="V17" s="69"/>
-      <c r="W17" s="56"/>
-      <c r="X17" s="68"/>
-      <c r="Y17" s="68"/>
-      <c r="Z17" s="69"/>
-      <c r="AA17" s="67"/>
-      <c r="AB17" s="68"/>
-      <c r="AC17" s="68"/>
-      <c r="AD17" s="53"/>
-      <c r="AE17" s="69"/>
-      <c r="AF17" s="67"/>
-      <c r="AG17" s="68"/>
-      <c r="AH17" s="68"/>
-      <c r="AI17" s="68"/>
-      <c r="AJ17" s="68"/>
-      <c r="AK17" s="68"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="72"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="69"/>
+      <c r="K17" s="69"/>
+      <c r="L17" s="54"/>
+      <c r="M17" s="69"/>
+      <c r="N17" s="70"/>
+      <c r="O17" s="68"/>
+      <c r="P17" s="69"/>
+      <c r="Q17" s="69"/>
+      <c r="R17" s="69"/>
+      <c r="S17" s="69"/>
+      <c r="T17" s="69"/>
+      <c r="U17" s="69"/>
+      <c r="V17" s="70"/>
+      <c r="W17" s="57"/>
+      <c r="X17" s="69"/>
+      <c r="Y17" s="69"/>
+      <c r="Z17" s="70"/>
+      <c r="AA17" s="68"/>
+      <c r="AB17" s="69"/>
+      <c r="AC17" s="69"/>
+      <c r="AD17" s="54"/>
+      <c r="AE17" s="70"/>
+      <c r="AF17" s="68"/>
+      <c r="AG17" s="69"/>
+      <c r="AH17" s="69"/>
+      <c r="AI17" s="69"/>
+      <c r="AJ17" s="69"/>
+      <c r="AK17" s="69"/>
       <c r="AN17" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="65"/>
-      <c r="C18" s="66" t="s">
-        <v>119</v>
-      </c>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="67"/>
-      <c r="I18" s="68"/>
-      <c r="J18" s="68"/>
-      <c r="K18" s="68"/>
-      <c r="L18" s="53"/>
-      <c r="M18" s="68"/>
-      <c r="N18" s="69"/>
-      <c r="O18" s="67"/>
-      <c r="P18" s="68"/>
-      <c r="Q18" s="68"/>
-      <c r="R18" s="68"/>
-      <c r="S18" s="68"/>
-      <c r="T18" s="68"/>
-      <c r="U18" s="68"/>
-      <c r="V18" s="69"/>
-      <c r="W18" s="56"/>
-      <c r="X18" s="68"/>
-      <c r="Y18" s="68"/>
-      <c r="Z18" s="69"/>
-      <c r="AA18" s="67"/>
-      <c r="AB18" s="68"/>
-      <c r="AC18" s="68"/>
-      <c r="AD18" s="53"/>
-      <c r="AE18" s="69"/>
-      <c r="AF18" s="67"/>
-      <c r="AG18" s="68"/>
-      <c r="AH18" s="68"/>
-      <c r="AI18" s="68"/>
-      <c r="AJ18" s="68"/>
-      <c r="AK18" s="68"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="67" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" s="64"/>
+      <c r="E18" s="64"/>
+      <c r="F18" s="72"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="69"/>
+      <c r="K18" s="69"/>
+      <c r="L18" s="54"/>
+      <c r="M18" s="69"/>
+      <c r="N18" s="70"/>
+      <c r="O18" s="68"/>
+      <c r="P18" s="69"/>
+      <c r="Q18" s="69"/>
+      <c r="R18" s="69"/>
+      <c r="S18" s="69"/>
+      <c r="T18" s="69"/>
+      <c r="U18" s="69"/>
+      <c r="V18" s="70"/>
+      <c r="W18" s="57"/>
+      <c r="X18" s="69"/>
+      <c r="Y18" s="69"/>
+      <c r="Z18" s="70"/>
+      <c r="AA18" s="68"/>
+      <c r="AB18" s="69"/>
+      <c r="AC18" s="69"/>
+      <c r="AD18" s="54"/>
+      <c r="AE18" s="70"/>
+      <c r="AF18" s="68"/>
+      <c r="AG18" s="69"/>
+      <c r="AH18" s="69"/>
+      <c r="AI18" s="69"/>
+      <c r="AJ18" s="69"/>
+      <c r="AK18" s="69"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="65"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="69"/>
-      <c r="H19" s="67"/>
-      <c r="I19" s="68"/>
-      <c r="J19" s="68"/>
-      <c r="K19" s="68"/>
-      <c r="L19" s="53"/>
-      <c r="M19" s="68"/>
-      <c r="N19" s="69"/>
-      <c r="O19" s="67"/>
-      <c r="P19" s="68"/>
-      <c r="Q19" s="68"/>
-      <c r="R19" s="68"/>
-      <c r="S19" s="68"/>
-      <c r="T19" s="68"/>
-      <c r="U19" s="68"/>
-      <c r="V19" s="69"/>
-      <c r="W19" s="56"/>
-      <c r="X19" s="68"/>
-      <c r="Y19" s="68"/>
-      <c r="Z19" s="69"/>
-      <c r="AA19" s="67"/>
-      <c r="AB19" s="68"/>
-      <c r="AC19" s="68"/>
-      <c r="AD19" s="53"/>
-      <c r="AE19" s="69"/>
-      <c r="AF19" s="67"/>
-      <c r="AG19" s="68"/>
-      <c r="AH19" s="68"/>
-      <c r="AI19" s="68"/>
-      <c r="AJ19" s="68"/>
-      <c r="AK19" s="68"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="73"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="69"/>
+      <c r="J19" s="69"/>
+      <c r="K19" s="69"/>
+      <c r="L19" s="54"/>
+      <c r="M19" s="69"/>
+      <c r="N19" s="70"/>
+      <c r="O19" s="68"/>
+      <c r="P19" s="69"/>
+      <c r="Q19" s="69"/>
+      <c r="R19" s="69"/>
+      <c r="S19" s="69"/>
+      <c r="T19" s="69"/>
+      <c r="U19" s="69"/>
+      <c r="V19" s="70"/>
+      <c r="W19" s="57"/>
+      <c r="X19" s="69"/>
+      <c r="Y19" s="69"/>
+      <c r="Z19" s="70"/>
+      <c r="AA19" s="68"/>
+      <c r="AB19" s="69"/>
+      <c r="AC19" s="69"/>
+      <c r="AD19" s="54"/>
+      <c r="AE19" s="70"/>
+      <c r="AF19" s="68"/>
+      <c r="AG19" s="69"/>
+      <c r="AH19" s="69"/>
+      <c r="AI19" s="69"/>
+      <c r="AJ19" s="69"/>
+      <c r="AK19" s="69"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="65"/>
-      <c r="C20" s="66" t="s">
-        <v>120</v>
-      </c>
-      <c r="D20" s="68"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="63"/>
-      <c r="J20" s="68"/>
-      <c r="K20" s="68"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="68"/>
-      <c r="N20" s="69"/>
-      <c r="O20" s="67"/>
-      <c r="P20" s="68"/>
-      <c r="Q20" s="68"/>
-      <c r="R20" s="68"/>
-      <c r="S20" s="68"/>
-      <c r="T20" s="68"/>
-      <c r="U20" s="68"/>
-      <c r="V20" s="69"/>
-      <c r="W20" s="56"/>
-      <c r="X20" s="68"/>
-      <c r="Y20" s="68"/>
-      <c r="Z20" s="69"/>
-      <c r="AA20" s="67"/>
-      <c r="AB20" s="68"/>
-      <c r="AC20" s="68"/>
-      <c r="AD20" s="53"/>
-      <c r="AE20" s="69"/>
-      <c r="AF20" s="67"/>
-      <c r="AG20" s="68"/>
-      <c r="AH20" s="68"/>
-      <c r="AI20" s="68"/>
-      <c r="AJ20" s="68"/>
-      <c r="AK20" s="68"/>
+      <c r="B20" s="66"/>
+      <c r="C20" s="67" t="s">
+        <v>127</v>
+      </c>
+      <c r="D20" s="69"/>
+      <c r="E20" s="69"/>
+      <c r="F20" s="72"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="69"/>
+      <c r="K20" s="69"/>
+      <c r="L20" s="54"/>
+      <c r="M20" s="69"/>
+      <c r="N20" s="70"/>
+      <c r="O20" s="68"/>
+      <c r="P20" s="69"/>
+      <c r="Q20" s="69"/>
+      <c r="R20" s="69"/>
+      <c r="S20" s="69"/>
+      <c r="T20" s="69"/>
+      <c r="U20" s="69"/>
+      <c r="V20" s="70"/>
+      <c r="W20" s="57"/>
+      <c r="X20" s="69"/>
+      <c r="Y20" s="69"/>
+      <c r="Z20" s="70"/>
+      <c r="AA20" s="68"/>
+      <c r="AB20" s="69"/>
+      <c r="AC20" s="69"/>
+      <c r="AD20" s="54"/>
+      <c r="AE20" s="70"/>
+      <c r="AF20" s="68"/>
+      <c r="AG20" s="69"/>
+      <c r="AH20" s="69"/>
+      <c r="AI20" s="69"/>
+      <c r="AJ20" s="69"/>
+      <c r="AK20" s="69"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="65"/>
-      <c r="C21" s="66"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="71"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="67"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="68"/>
-      <c r="K21" s="68"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="68"/>
-      <c r="N21" s="69"/>
-      <c r="O21" s="67"/>
-      <c r="P21" s="68"/>
-      <c r="Q21" s="68"/>
-      <c r="R21" s="68"/>
-      <c r="S21" s="68"/>
-      <c r="T21" s="68"/>
-      <c r="U21" s="68"/>
-      <c r="V21" s="69"/>
-      <c r="W21" s="56"/>
-      <c r="X21" s="68"/>
-      <c r="Y21" s="68"/>
-      <c r="Z21" s="69"/>
-      <c r="AA21" s="67"/>
-      <c r="AB21" s="68"/>
-      <c r="AC21" s="68"/>
-      <c r="AD21" s="53"/>
-      <c r="AE21" s="69"/>
-      <c r="AF21" s="67"/>
-      <c r="AG21" s="68"/>
-      <c r="AH21" s="68"/>
-      <c r="AI21" s="68"/>
-      <c r="AJ21" s="68"/>
-      <c r="AK21" s="68"/>
+      <c r="B21" s="66"/>
+      <c r="C21" s="67"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="69"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="63"/>
+      <c r="J21" s="69"/>
+      <c r="K21" s="69"/>
+      <c r="L21" s="54"/>
+      <c r="M21" s="69"/>
+      <c r="N21" s="70"/>
+      <c r="O21" s="68"/>
+      <c r="P21" s="69"/>
+      <c r="Q21" s="69"/>
+      <c r="R21" s="69"/>
+      <c r="S21" s="69"/>
+      <c r="T21" s="69"/>
+      <c r="U21" s="69"/>
+      <c r="V21" s="70"/>
+      <c r="W21" s="57"/>
+      <c r="X21" s="69"/>
+      <c r="Y21" s="69"/>
+      <c r="Z21" s="70"/>
+      <c r="AA21" s="68"/>
+      <c r="AB21" s="69"/>
+      <c r="AC21" s="69"/>
+      <c r="AD21" s="54"/>
+      <c r="AE21" s="70"/>
+      <c r="AF21" s="68"/>
+      <c r="AG21" s="69"/>
+      <c r="AH21" s="69"/>
+      <c r="AI21" s="69"/>
+      <c r="AJ21" s="69"/>
+      <c r="AK21" s="69"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="65"/>
-      <c r="C22" s="66" t="s">
-        <v>121</v>
-      </c>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="63"/>
-      <c r="J22" s="68"/>
-      <c r="K22" s="68"/>
-      <c r="L22" s="53"/>
-      <c r="M22" s="68"/>
-      <c r="N22" s="69"/>
-      <c r="O22" s="67"/>
-      <c r="P22" s="68"/>
-      <c r="Q22" s="68"/>
-      <c r="R22" s="68"/>
-      <c r="S22" s="68"/>
-      <c r="T22" s="68"/>
-      <c r="U22" s="68"/>
-      <c r="V22" s="69"/>
-      <c r="W22" s="56"/>
-      <c r="X22" s="68"/>
-      <c r="Y22" s="68"/>
-      <c r="Z22" s="69"/>
-      <c r="AA22" s="67"/>
-      <c r="AB22" s="68"/>
-      <c r="AC22" s="68"/>
-      <c r="AD22" s="53"/>
-      <c r="AE22" s="69"/>
-      <c r="AF22" s="67"/>
-      <c r="AG22" s="68"/>
-      <c r="AH22" s="68"/>
-      <c r="AI22" s="68"/>
-      <c r="AJ22" s="68"/>
-      <c r="AK22" s="68"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="67" t="s">
+        <v>128</v>
+      </c>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="69"/>
+      <c r="K22" s="69"/>
+      <c r="L22" s="54"/>
+      <c r="M22" s="69"/>
+      <c r="N22" s="70"/>
+      <c r="O22" s="68"/>
+      <c r="P22" s="69"/>
+      <c r="Q22" s="69"/>
+      <c r="R22" s="69"/>
+      <c r="S22" s="69"/>
+      <c r="T22" s="69"/>
+      <c r="U22" s="69"/>
+      <c r="V22" s="70"/>
+      <c r="W22" s="57"/>
+      <c r="X22" s="69"/>
+      <c r="Y22" s="69"/>
+      <c r="Z22" s="70"/>
+      <c r="AA22" s="68"/>
+      <c r="AB22" s="69"/>
+      <c r="AC22" s="69"/>
+      <c r="AD22" s="54"/>
+      <c r="AE22" s="70"/>
+      <c r="AF22" s="68"/>
+      <c r="AG22" s="69"/>
+      <c r="AH22" s="69"/>
+      <c r="AI22" s="69"/>
+      <c r="AJ22" s="69"/>
+      <c r="AK22" s="69"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="65"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="58"/>
-      <c r="K23" s="68"/>
-      <c r="L23" s="53"/>
-      <c r="M23" s="68"/>
-      <c r="N23" s="69"/>
-      <c r="O23" s="67"/>
-      <c r="P23" s="68"/>
-      <c r="Q23" s="68"/>
-      <c r="R23" s="68"/>
-      <c r="S23" s="68"/>
-      <c r="T23" s="68"/>
-      <c r="U23" s="68"/>
-      <c r="V23" s="69"/>
-      <c r="W23" s="56"/>
-      <c r="X23" s="68"/>
-      <c r="Y23" s="68"/>
-      <c r="Z23" s="69"/>
-      <c r="AA23" s="67"/>
-      <c r="AB23" s="68"/>
-      <c r="AC23" s="68"/>
-      <c r="AD23" s="53"/>
-      <c r="AE23" s="69"/>
-      <c r="AF23" s="67"/>
-      <c r="AG23" s="68"/>
-      <c r="AH23" s="68"/>
-      <c r="AI23" s="68"/>
-      <c r="AJ23" s="68"/>
-      <c r="AK23" s="68"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="69"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="63"/>
+      <c r="J23" s="59"/>
+      <c r="K23" s="69"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="69"/>
+      <c r="N23" s="70"/>
+      <c r="O23" s="68"/>
+      <c r="P23" s="69"/>
+      <c r="Q23" s="69"/>
+      <c r="R23" s="69"/>
+      <c r="S23" s="69"/>
+      <c r="T23" s="69"/>
+      <c r="U23" s="69"/>
+      <c r="V23" s="70"/>
+      <c r="W23" s="57"/>
+      <c r="X23" s="69"/>
+      <c r="Y23" s="69"/>
+      <c r="Z23" s="70"/>
+      <c r="AA23" s="68"/>
+      <c r="AB23" s="69"/>
+      <c r="AC23" s="69"/>
+      <c r="AD23" s="54"/>
+      <c r="AE23" s="70"/>
+      <c r="AF23" s="68"/>
+      <c r="AG23" s="69"/>
+      <c r="AH23" s="69"/>
+      <c r="AI23" s="69"/>
+      <c r="AJ23" s="69"/>
+      <c r="AK23" s="69"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="65"/>
-      <c r="C24" s="66" t="s">
-        <v>122</v>
-      </c>
-      <c r="D24" s="68"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="67"/>
-      <c r="I24" s="63"/>
-      <c r="J24" s="68"/>
-      <c r="K24" s="68"/>
-      <c r="L24" s="53"/>
-      <c r="M24" s="68"/>
-      <c r="N24" s="69"/>
-      <c r="O24" s="67"/>
-      <c r="P24" s="68"/>
-      <c r="Q24" s="68"/>
-      <c r="R24" s="68"/>
-      <c r="S24" s="68"/>
-      <c r="T24" s="68"/>
-      <c r="U24" s="68"/>
-      <c r="V24" s="69"/>
-      <c r="W24" s="56"/>
-      <c r="X24" s="68"/>
-      <c r="Y24" s="68"/>
-      <c r="Z24" s="69"/>
-      <c r="AA24" s="67"/>
-      <c r="AB24" s="68"/>
-      <c r="AC24" s="68"/>
-      <c r="AD24" s="53"/>
-      <c r="AE24" s="69"/>
-      <c r="AF24" s="67"/>
-      <c r="AG24" s="68"/>
-      <c r="AH24" s="68"/>
-      <c r="AI24" s="68"/>
-      <c r="AJ24" s="68"/>
-      <c r="AK24" s="68"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="67" t="s">
+        <v>129</v>
+      </c>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="69"/>
+      <c r="K24" s="69"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="69"/>
+      <c r="N24" s="70"/>
+      <c r="O24" s="68"/>
+      <c r="P24" s="69"/>
+      <c r="Q24" s="69"/>
+      <c r="R24" s="69"/>
+      <c r="S24" s="69"/>
+      <c r="T24" s="69"/>
+      <c r="U24" s="69"/>
+      <c r="V24" s="70"/>
+      <c r="W24" s="57"/>
+      <c r="X24" s="69"/>
+      <c r="Y24" s="69"/>
+      <c r="Z24" s="70"/>
+      <c r="AA24" s="68"/>
+      <c r="AB24" s="69"/>
+      <c r="AC24" s="69"/>
+      <c r="AD24" s="54"/>
+      <c r="AE24" s="70"/>
+      <c r="AF24" s="68"/>
+      <c r="AG24" s="69"/>
+      <c r="AH24" s="69"/>
+      <c r="AI24" s="69"/>
+      <c r="AJ24" s="69"/>
+      <c r="AK24" s="69"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="65"/>
-      <c r="C25" s="66"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="68"/>
-      <c r="L25" s="53"/>
-      <c r="M25" s="68"/>
-      <c r="N25" s="69"/>
-      <c r="O25" s="67"/>
-      <c r="P25" s="68"/>
-      <c r="Q25" s="68"/>
-      <c r="R25" s="68"/>
-      <c r="S25" s="68"/>
-      <c r="T25" s="68"/>
-      <c r="U25" s="68"/>
-      <c r="V25" s="69"/>
-      <c r="W25" s="56"/>
-      <c r="X25" s="68"/>
-      <c r="Y25" s="68"/>
-      <c r="Z25" s="69"/>
-      <c r="AA25" s="67"/>
-      <c r="AB25" s="68"/>
-      <c r="AC25" s="68"/>
-      <c r="AD25" s="53"/>
-      <c r="AE25" s="69"/>
-      <c r="AF25" s="67"/>
-      <c r="AG25" s="68"/>
-      <c r="AH25" s="68"/>
-      <c r="AI25" s="68"/>
-      <c r="AJ25" s="68"/>
-      <c r="AK25" s="68"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
+      <c r="F25" s="72"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="68"/>
+      <c r="I25" s="69"/>
+      <c r="J25" s="59"/>
+      <c r="K25" s="69"/>
+      <c r="L25" s="54"/>
+      <c r="M25" s="69"/>
+      <c r="N25" s="70"/>
+      <c r="O25" s="68"/>
+      <c r="P25" s="69"/>
+      <c r="Q25" s="69"/>
+      <c r="R25" s="69"/>
+      <c r="S25" s="69"/>
+      <c r="T25" s="69"/>
+      <c r="U25" s="69"/>
+      <c r="V25" s="70"/>
+      <c r="W25" s="57"/>
+      <c r="X25" s="69"/>
+      <c r="Y25" s="69"/>
+      <c r="Z25" s="70"/>
+      <c r="AA25" s="68"/>
+      <c r="AB25" s="69"/>
+      <c r="AC25" s="69"/>
+      <c r="AD25" s="54"/>
+      <c r="AE25" s="70"/>
+      <c r="AF25" s="68"/>
+      <c r="AG25" s="69"/>
+      <c r="AH25" s="69"/>
+      <c r="AI25" s="69"/>
+      <c r="AJ25" s="69"/>
+      <c r="AK25" s="69"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="47" t="s">
-        <v>123</v>
-      </c>
-      <c r="C26" s="48" t="s">
-        <v>124</v>
-      </c>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="54"/>
-      <c r="H26" s="52"/>
-      <c r="I26" s="63"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="53"/>
-      <c r="M26" s="49"/>
-      <c r="N26" s="54"/>
-      <c r="O26" s="55"/>
-      <c r="P26" s="49"/>
-      <c r="Q26" s="49"/>
-      <c r="R26" s="49"/>
-      <c r="S26" s="49"/>
-      <c r="T26" s="49"/>
-      <c r="U26" s="49"/>
-      <c r="V26" s="54"/>
-      <c r="W26" s="56"/>
-      <c r="X26" s="49"/>
-      <c r="Y26" s="49"/>
-      <c r="Z26" s="54"/>
-      <c r="AA26" s="55"/>
-      <c r="AB26" s="49"/>
-      <c r="AC26" s="49"/>
-      <c r="AD26" s="53"/>
-      <c r="AE26" s="54"/>
-      <c r="AF26" s="55"/>
-      <c r="AG26" s="49"/>
-      <c r="AH26" s="49"/>
-      <c r="AI26" s="49"/>
-      <c r="AJ26" s="49"/>
-      <c r="AK26" s="49"/>
+      <c r="B26" s="48" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" s="49" t="s">
+        <v>131</v>
+      </c>
+      <c r="D26" s="50"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="55"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="64"/>
+      <c r="J26" s="50"/>
+      <c r="K26" s="50"/>
+      <c r="L26" s="54"/>
+      <c r="M26" s="50"/>
+      <c r="N26" s="55"/>
+      <c r="O26" s="56"/>
+      <c r="P26" s="50"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50"/>
+      <c r="S26" s="50"/>
+      <c r="T26" s="50"/>
+      <c r="U26" s="50"/>
+      <c r="V26" s="55"/>
+      <c r="W26" s="57"/>
+      <c r="X26" s="50"/>
+      <c r="Y26" s="50"/>
+      <c r="Z26" s="55"/>
+      <c r="AA26" s="56"/>
+      <c r="AB26" s="50"/>
+      <c r="AC26" s="50"/>
+      <c r="AD26" s="54"/>
+      <c r="AE26" s="55"/>
+      <c r="AF26" s="56"/>
+      <c r="AG26" s="50"/>
+      <c r="AH26" s="50"/>
+      <c r="AI26" s="50"/>
+      <c r="AJ26" s="50"/>
+      <c r="AK26" s="50"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="47"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="60"/>
-      <c r="H27" s="61"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="49"/>
-      <c r="K27" s="49"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="49"/>
-      <c r="N27" s="54"/>
-      <c r="O27" s="55"/>
-      <c r="P27" s="49"/>
-      <c r="Q27" s="49"/>
-      <c r="R27" s="49"/>
-      <c r="S27" s="49"/>
-      <c r="T27" s="49"/>
-      <c r="U27" s="49"/>
-      <c r="V27" s="54"/>
-      <c r="W27" s="56"/>
-      <c r="X27" s="49"/>
-      <c r="Y27" s="49"/>
-      <c r="Z27" s="54"/>
-      <c r="AA27" s="55"/>
-      <c r="AB27" s="49"/>
-      <c r="AC27" s="49"/>
-      <c r="AD27" s="53"/>
-      <c r="AE27" s="54"/>
-      <c r="AF27" s="55"/>
-      <c r="AG27" s="49"/>
-      <c r="AH27" s="49"/>
-      <c r="AI27" s="49"/>
-      <c r="AJ27" s="49"/>
-      <c r="AK27" s="49"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="58"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="62"/>
+      <c r="I27" s="50"/>
+      <c r="J27" s="50"/>
+      <c r="K27" s="50"/>
+      <c r="L27" s="54"/>
+      <c r="M27" s="50"/>
+      <c r="N27" s="55"/>
+      <c r="O27" s="56"/>
+      <c r="P27" s="50"/>
+      <c r="Q27" s="50"/>
+      <c r="R27" s="50"/>
+      <c r="S27" s="50"/>
+      <c r="T27" s="50"/>
+      <c r="U27" s="50"/>
+      <c r="V27" s="55"/>
+      <c r="W27" s="57"/>
+      <c r="X27" s="50"/>
+      <c r="Y27" s="50"/>
+      <c r="Z27" s="55"/>
+      <c r="AA27" s="56"/>
+      <c r="AB27" s="50"/>
+      <c r="AC27" s="50"/>
+      <c r="AD27" s="54"/>
+      <c r="AE27" s="55"/>
+      <c r="AF27" s="56"/>
+      <c r="AG27" s="50"/>
+      <c r="AH27" s="50"/>
+      <c r="AI27" s="50"/>
+      <c r="AJ27" s="50"/>
+      <c r="AK27" s="50"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="47"/>
-      <c r="C28" s="48" t="s">
-        <v>125</v>
-      </c>
-      <c r="D28" s="49"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="52"/>
-      <c r="I28" s="63"/>
-      <c r="J28" s="63"/>
-      <c r="K28" s="63"/>
-      <c r="L28" s="53"/>
-      <c r="M28" s="49"/>
-      <c r="N28" s="54"/>
-      <c r="O28" s="55"/>
-      <c r="P28" s="49"/>
-      <c r="Q28" s="49"/>
-      <c r="R28" s="49"/>
-      <c r="S28" s="49"/>
-      <c r="T28" s="49"/>
-      <c r="U28" s="49"/>
-      <c r="V28" s="54"/>
-      <c r="W28" s="56"/>
-      <c r="X28" s="49"/>
-      <c r="Y28" s="49"/>
-      <c r="Z28" s="54"/>
-      <c r="AA28" s="55"/>
-      <c r="AB28" s="49"/>
-      <c r="AC28" s="49"/>
-      <c r="AD28" s="53"/>
-      <c r="AE28" s="54"/>
-      <c r="AF28" s="55"/>
-      <c r="AG28" s="49"/>
-      <c r="AH28" s="49"/>
-      <c r="AI28" s="49"/>
-      <c r="AJ28" s="49"/>
-      <c r="AK28" s="49"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="49" t="s">
+        <v>132</v>
+      </c>
+      <c r="D28" s="50"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="58"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="64"/>
+      <c r="J28" s="64"/>
+      <c r="K28" s="64"/>
+      <c r="L28" s="54"/>
+      <c r="M28" s="50"/>
+      <c r="N28" s="55"/>
+      <c r="O28" s="56"/>
+      <c r="P28" s="50"/>
+      <c r="Q28" s="50"/>
+      <c r="R28" s="50"/>
+      <c r="S28" s="50"/>
+      <c r="T28" s="50"/>
+      <c r="U28" s="50"/>
+      <c r="V28" s="55"/>
+      <c r="W28" s="57"/>
+      <c r="X28" s="50"/>
+      <c r="Y28" s="50"/>
+      <c r="Z28" s="55"/>
+      <c r="AA28" s="56"/>
+      <c r="AB28" s="50"/>
+      <c r="AC28" s="50"/>
+      <c r="AD28" s="54"/>
+      <c r="AE28" s="55"/>
+      <c r="AF28" s="56"/>
+      <c r="AG28" s="50"/>
+      <c r="AH28" s="50"/>
+      <c r="AI28" s="50"/>
+      <c r="AJ28" s="50"/>
+      <c r="AK28" s="50"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="47"/>
-      <c r="C29" s="48"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="49"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="60"/>
-      <c r="H29" s="61"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="64"/>
-      <c r="K29" s="49"/>
-      <c r="L29" s="53"/>
-      <c r="M29" s="49"/>
-      <c r="N29" s="54"/>
-      <c r="O29" s="55"/>
-      <c r="P29" s="49"/>
-      <c r="Q29" s="49"/>
-      <c r="R29" s="49"/>
-      <c r="S29" s="49"/>
-      <c r="T29" s="49"/>
-      <c r="U29" s="49"/>
-      <c r="V29" s="54"/>
-      <c r="W29" s="56"/>
-      <c r="X29" s="49"/>
-      <c r="Y29" s="49"/>
-      <c r="Z29" s="54"/>
-      <c r="AA29" s="55"/>
-      <c r="AB29" s="49"/>
-      <c r="AC29" s="49"/>
-      <c r="AD29" s="53"/>
-      <c r="AE29" s="54"/>
-      <c r="AF29" s="55"/>
-      <c r="AG29" s="49"/>
-      <c r="AH29" s="49"/>
-      <c r="AI29" s="49"/>
-      <c r="AJ29" s="49"/>
-      <c r="AK29" s="49"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="50"/>
+      <c r="J29" s="65"/>
+      <c r="K29" s="50"/>
+      <c r="L29" s="54"/>
+      <c r="M29" s="50"/>
+      <c r="N29" s="55"/>
+      <c r="O29" s="56"/>
+      <c r="P29" s="50"/>
+      <c r="Q29" s="50"/>
+      <c r="R29" s="50"/>
+      <c r="S29" s="50"/>
+      <c r="T29" s="50"/>
+      <c r="U29" s="50"/>
+      <c r="V29" s="55"/>
+      <c r="W29" s="57"/>
+      <c r="X29" s="50"/>
+      <c r="Y29" s="50"/>
+      <c r="Z29" s="55"/>
+      <c r="AA29" s="56"/>
+      <c r="AB29" s="50"/>
+      <c r="AC29" s="50"/>
+      <c r="AD29" s="54"/>
+      <c r="AE29" s="55"/>
+      <c r="AF29" s="56"/>
+      <c r="AG29" s="50"/>
+      <c r="AH29" s="50"/>
+      <c r="AI29" s="50"/>
+      <c r="AJ29" s="50"/>
+      <c r="AK29" s="50"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="47"/>
-      <c r="C30" s="48" t="s">
-        <v>126</v>
-      </c>
-      <c r="D30" s="49"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="54"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="63"/>
-      <c r="J30" s="63"/>
-      <c r="K30" s="63"/>
-      <c r="L30" s="53"/>
-      <c r="M30" s="63"/>
-      <c r="N30" s="54"/>
-      <c r="O30" s="55"/>
-      <c r="P30" s="49"/>
-      <c r="Q30" s="49"/>
-      <c r="R30" s="49"/>
-      <c r="S30" s="49"/>
-      <c r="T30" s="49"/>
-      <c r="U30" s="49"/>
-      <c r="V30" s="54"/>
-      <c r="W30" s="56"/>
-      <c r="X30" s="49"/>
-      <c r="Y30" s="49"/>
-      <c r="Z30" s="54"/>
-      <c r="AA30" s="55"/>
-      <c r="AB30" s="49"/>
-      <c r="AC30" s="49"/>
-      <c r="AD30" s="53"/>
-      <c r="AE30" s="54"/>
-      <c r="AF30" s="55"/>
-      <c r="AG30" s="49"/>
-      <c r="AH30" s="49"/>
-      <c r="AI30" s="49"/>
-      <c r="AJ30" s="49"/>
-      <c r="AK30" s="49"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="58"/>
+      <c r="G30" s="55"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="64"/>
+      <c r="J30" s="64"/>
+      <c r="K30" s="64"/>
+      <c r="L30" s="54"/>
+      <c r="M30" s="64"/>
+      <c r="N30" s="55"/>
+      <c r="O30" s="56"/>
+      <c r="P30" s="50"/>
+      <c r="Q30" s="50"/>
+      <c r="R30" s="50"/>
+      <c r="S30" s="50"/>
+      <c r="T30" s="50"/>
+      <c r="U30" s="50"/>
+      <c r="V30" s="55"/>
+      <c r="W30" s="57"/>
+      <c r="X30" s="50"/>
+      <c r="Y30" s="50"/>
+      <c r="Z30" s="55"/>
+      <c r="AA30" s="56"/>
+      <c r="AB30" s="50"/>
+      <c r="AC30" s="50"/>
+      <c r="AD30" s="54"/>
+      <c r="AE30" s="55"/>
+      <c r="AF30" s="56"/>
+      <c r="AG30" s="50"/>
+      <c r="AH30" s="50"/>
+      <c r="AI30" s="50"/>
+      <c r="AJ30" s="50"/>
+      <c r="AK30" s="50"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="47"/>
-      <c r="C31" s="48"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="60"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="64"/>
-      <c r="K31" s="64"/>
-      <c r="L31" s="73"/>
-      <c r="M31" s="49"/>
-      <c r="N31" s="60"/>
-      <c r="O31" s="55"/>
-      <c r="P31" s="49"/>
-      <c r="Q31" s="49"/>
-      <c r="R31" s="49"/>
-      <c r="S31" s="49"/>
-      <c r="T31" s="49"/>
-      <c r="U31" s="49"/>
-      <c r="V31" s="54"/>
-      <c r="W31" s="56"/>
-      <c r="X31" s="49"/>
-      <c r="Y31" s="49"/>
-      <c r="Z31" s="54"/>
-      <c r="AA31" s="55"/>
-      <c r="AB31" s="49"/>
-      <c r="AC31" s="49"/>
-      <c r="AD31" s="53"/>
-      <c r="AE31" s="54"/>
-      <c r="AF31" s="55"/>
-      <c r="AG31" s="49"/>
-      <c r="AH31" s="49"/>
-      <c r="AI31" s="49"/>
-      <c r="AJ31" s="49"/>
-      <c r="AK31" s="49"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="62"/>
+      <c r="I31" s="50"/>
+      <c r="J31" s="65"/>
+      <c r="K31" s="65"/>
+      <c r="L31" s="74"/>
+      <c r="M31" s="50"/>
+      <c r="N31" s="61"/>
+      <c r="O31" s="56"/>
+      <c r="P31" s="50"/>
+      <c r="Q31" s="50"/>
+      <c r="R31" s="50"/>
+      <c r="S31" s="50"/>
+      <c r="T31" s="50"/>
+      <c r="U31" s="50"/>
+      <c r="V31" s="55"/>
+      <c r="W31" s="57"/>
+      <c r="X31" s="50"/>
+      <c r="Y31" s="50"/>
+      <c r="Z31" s="55"/>
+      <c r="AA31" s="56"/>
+      <c r="AB31" s="50"/>
+      <c r="AC31" s="50"/>
+      <c r="AD31" s="54"/>
+      <c r="AE31" s="55"/>
+      <c r="AF31" s="56"/>
+      <c r="AG31" s="50"/>
+      <c r="AH31" s="50"/>
+      <c r="AI31" s="50"/>
+      <c r="AJ31" s="50"/>
+      <c r="AK31" s="50"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="47"/>
-      <c r="C32" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="D32" s="49"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="57"/>
-      <c r="G32" s="54"/>
-      <c r="H32" s="55"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="49"/>
-      <c r="K32" s="49"/>
-      <c r="L32" s="53"/>
-      <c r="M32" s="63"/>
-      <c r="N32" s="51"/>
-      <c r="O32" s="55"/>
-      <c r="P32" s="49"/>
-      <c r="Q32" s="49"/>
-      <c r="R32" s="49"/>
-      <c r="S32" s="49"/>
-      <c r="T32" s="49"/>
-      <c r="U32" s="49"/>
-      <c r="V32" s="54"/>
-      <c r="W32" s="56"/>
-      <c r="X32" s="49"/>
-      <c r="Y32" s="49"/>
-      <c r="Z32" s="54"/>
-      <c r="AA32" s="55"/>
-      <c r="AB32" s="49"/>
-      <c r="AC32" s="49"/>
-      <c r="AD32" s="53"/>
-      <c r="AE32" s="54"/>
-      <c r="AF32" s="55"/>
-      <c r="AG32" s="49"/>
-      <c r="AH32" s="49"/>
-      <c r="AI32" s="49"/>
-      <c r="AJ32" s="49"/>
-      <c r="AK32" s="49"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="58"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="50"/>
+      <c r="J32" s="50"/>
+      <c r="K32" s="50"/>
+      <c r="L32" s="54"/>
+      <c r="M32" s="64"/>
+      <c r="N32" s="52"/>
+      <c r="O32" s="56"/>
+      <c r="P32" s="50"/>
+      <c r="Q32" s="50"/>
+      <c r="R32" s="50"/>
+      <c r="S32" s="50"/>
+      <c r="T32" s="50"/>
+      <c r="U32" s="50"/>
+      <c r="V32" s="55"/>
+      <c r="W32" s="57"/>
+      <c r="X32" s="50"/>
+      <c r="Y32" s="50"/>
+      <c r="Z32" s="55"/>
+      <c r="AA32" s="56"/>
+      <c r="AB32" s="50"/>
+      <c r="AC32" s="50"/>
+      <c r="AD32" s="54"/>
+      <c r="AE32" s="55"/>
+      <c r="AF32" s="56"/>
+      <c r="AG32" s="50"/>
+      <c r="AH32" s="50"/>
+      <c r="AI32" s="50"/>
+      <c r="AJ32" s="50"/>
+      <c r="AK32" s="50"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="47"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="49"/>
-      <c r="E33" s="49"/>
-      <c r="F33" s="57"/>
-      <c r="G33" s="54"/>
-      <c r="H33" s="55"/>
-      <c r="I33" s="49"/>
-      <c r="J33" s="49"/>
-      <c r="K33" s="49"/>
-      <c r="L33" s="53"/>
-      <c r="M33" s="49"/>
-      <c r="N33" s="60"/>
-      <c r="O33" s="55"/>
-      <c r="P33" s="49"/>
-      <c r="Q33" s="49"/>
-      <c r="R33" s="49"/>
-      <c r="S33" s="49"/>
-      <c r="T33" s="49"/>
-      <c r="U33" s="49"/>
-      <c r="V33" s="54"/>
-      <c r="W33" s="56"/>
-      <c r="X33" s="49"/>
-      <c r="Y33" s="49"/>
-      <c r="Z33" s="54"/>
-      <c r="AA33" s="55"/>
-      <c r="AB33" s="49"/>
-      <c r="AC33" s="49"/>
-      <c r="AD33" s="53"/>
-      <c r="AE33" s="54"/>
-      <c r="AF33" s="55"/>
-      <c r="AG33" s="49"/>
-      <c r="AH33" s="49"/>
-      <c r="AI33" s="49"/>
-      <c r="AJ33" s="49"/>
-      <c r="AK33" s="49"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="49"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="58"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="50"/>
+      <c r="J33" s="50"/>
+      <c r="K33" s="50"/>
+      <c r="L33" s="54"/>
+      <c r="M33" s="50"/>
+      <c r="N33" s="61"/>
+      <c r="O33" s="56"/>
+      <c r="P33" s="50"/>
+      <c r="Q33" s="50"/>
+      <c r="R33" s="50"/>
+      <c r="S33" s="50"/>
+      <c r="T33" s="50"/>
+      <c r="U33" s="50"/>
+      <c r="V33" s="55"/>
+      <c r="W33" s="57"/>
+      <c r="X33" s="50"/>
+      <c r="Y33" s="50"/>
+      <c r="Z33" s="55"/>
+      <c r="AA33" s="56"/>
+      <c r="AB33" s="50"/>
+      <c r="AC33" s="50"/>
+      <c r="AD33" s="54"/>
+      <c r="AE33" s="55"/>
+      <c r="AF33" s="56"/>
+      <c r="AG33" s="50"/>
+      <c r="AH33" s="50"/>
+      <c r="AI33" s="50"/>
+      <c r="AJ33" s="50"/>
+      <c r="AK33" s="50"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="65" t="s">
-        <v>128</v>
-      </c>
-      <c r="C34" s="74" t="s">
-        <v>129</v>
-      </c>
-      <c r="D34" s="68"/>
-      <c r="E34" s="68"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="69"/>
-      <c r="H34" s="67"/>
-      <c r="I34" s="68"/>
-      <c r="J34" s="68"/>
-      <c r="K34" s="68"/>
-      <c r="L34" s="53"/>
-      <c r="M34" s="63"/>
-      <c r="N34" s="51"/>
-      <c r="O34" s="52"/>
-      <c r="P34" s="63"/>
-      <c r="Q34" s="63"/>
-      <c r="R34" s="63"/>
-      <c r="S34" s="68"/>
-      <c r="T34" s="68"/>
-      <c r="U34" s="68"/>
-      <c r="V34" s="69"/>
-      <c r="W34" s="56"/>
-      <c r="X34" s="68"/>
-      <c r="Y34" s="68"/>
-      <c r="Z34" s="69"/>
-      <c r="AA34" s="67"/>
-      <c r="AB34" s="68"/>
-      <c r="AC34" s="68"/>
-      <c r="AD34" s="53"/>
-      <c r="AE34" s="69"/>
-      <c r="AF34" s="67"/>
-      <c r="AG34" s="68"/>
-      <c r="AH34" s="68"/>
-      <c r="AI34" s="68"/>
-      <c r="AJ34" s="68"/>
-      <c r="AK34" s="68"/>
+      <c r="B34" s="66" t="s">
+        <v>135</v>
+      </c>
+      <c r="C34" s="75" t="s">
+        <v>136</v>
+      </c>
+      <c r="D34" s="69"/>
+      <c r="E34" s="69"/>
+      <c r="F34" s="72"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="68"/>
+      <c r="I34" s="69"/>
+      <c r="J34" s="69"/>
+      <c r="K34" s="69"/>
+      <c r="L34" s="54"/>
+      <c r="M34" s="64"/>
+      <c r="N34" s="52"/>
+      <c r="O34" s="53"/>
+      <c r="P34" s="64"/>
+      <c r="Q34" s="64"/>
+      <c r="R34" s="64"/>
+      <c r="S34" s="69"/>
+      <c r="T34" s="69"/>
+      <c r="U34" s="69"/>
+      <c r="V34" s="70"/>
+      <c r="W34" s="57"/>
+      <c r="X34" s="69"/>
+      <c r="Y34" s="69"/>
+      <c r="Z34" s="70"/>
+      <c r="AA34" s="68"/>
+      <c r="AB34" s="69"/>
+      <c r="AC34" s="69"/>
+      <c r="AD34" s="54"/>
+      <c r="AE34" s="70"/>
+      <c r="AF34" s="68"/>
+      <c r="AG34" s="69"/>
+      <c r="AH34" s="69"/>
+      <c r="AI34" s="69"/>
+      <c r="AJ34" s="69"/>
+      <c r="AK34" s="69"/>
     </row>
     <row r="35" ht="12" customHeight="1">
-      <c r="B35" s="65"/>
-      <c r="C35" s="74"/>
-      <c r="D35" s="68"/>
-      <c r="E35" s="68"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="69"/>
-      <c r="H35" s="67"/>
-      <c r="I35" s="68"/>
-      <c r="J35" s="68"/>
-      <c r="K35" s="75"/>
-      <c r="L35" s="53"/>
-      <c r="M35" s="68"/>
-      <c r="N35" s="60"/>
-      <c r="O35" s="67"/>
-      <c r="P35" s="62"/>
-      <c r="Q35" s="68"/>
-      <c r="R35" s="76"/>
-      <c r="S35" s="76"/>
-      <c r="T35" s="58"/>
-      <c r="U35" s="68"/>
-      <c r="V35" s="69"/>
-      <c r="W35" s="56"/>
-      <c r="X35" s="68"/>
-      <c r="Y35" s="68"/>
-      <c r="Z35" s="69"/>
-      <c r="AA35" s="67"/>
-      <c r="AB35" s="68"/>
-      <c r="AC35" s="68"/>
-      <c r="AD35" s="53"/>
-      <c r="AE35" s="69"/>
-      <c r="AF35" s="67"/>
-      <c r="AG35" s="68"/>
-      <c r="AH35" s="68"/>
-      <c r="AI35" s="68"/>
-      <c r="AJ35" s="68"/>
-      <c r="AK35" s="68"/>
+      <c r="B35" s="66"/>
+      <c r="C35" s="75"/>
+      <c r="D35" s="69"/>
+      <c r="E35" s="69"/>
+      <c r="F35" s="72"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="68"/>
+      <c r="I35" s="69"/>
+      <c r="J35" s="69"/>
+      <c r="K35" s="76"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="69"/>
+      <c r="N35" s="61"/>
+      <c r="O35" s="68"/>
+      <c r="P35" s="63"/>
+      <c r="Q35" s="69"/>
+      <c r="R35" s="77"/>
+      <c r="S35" s="77"/>
+      <c r="T35" s="59"/>
+      <c r="U35" s="69"/>
+      <c r="V35" s="70"/>
+      <c r="W35" s="57"/>
+      <c r="X35" s="69"/>
+      <c r="Y35" s="69"/>
+      <c r="Z35" s="70"/>
+      <c r="AA35" s="68"/>
+      <c r="AB35" s="69"/>
+      <c r="AC35" s="69"/>
+      <c r="AD35" s="54"/>
+      <c r="AE35" s="70"/>
+      <c r="AF35" s="68"/>
+      <c r="AG35" s="69"/>
+      <c r="AH35" s="69"/>
+      <c r="AI35" s="69"/>
+      <c r="AJ35" s="69"/>
+      <c r="AK35" s="69"/>
     </row>
     <row r="36" ht="12" customHeight="1">
-      <c r="B36" s="65"/>
-      <c r="C36" s="74" t="s">
-        <v>130</v>
-      </c>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="71"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="67"/>
-      <c r="I36" s="68"/>
-      <c r="J36" s="68"/>
-      <c r="K36" s="68"/>
-      <c r="L36" s="53"/>
-      <c r="M36" s="63"/>
-      <c r="N36" s="51"/>
-      <c r="O36" s="52"/>
-      <c r="P36" s="63"/>
-      <c r="Q36" s="68"/>
-      <c r="R36" s="68"/>
-      <c r="S36" s="68"/>
-      <c r="T36" s="68"/>
-      <c r="U36" s="68"/>
-      <c r="V36" s="69"/>
-      <c r="W36" s="56"/>
-      <c r="X36" s="68"/>
-      <c r="Y36" s="68"/>
-      <c r="Z36" s="69"/>
-      <c r="AA36" s="67"/>
-      <c r="AB36" s="68"/>
-      <c r="AC36" s="68"/>
-      <c r="AD36" s="53"/>
-      <c r="AE36" s="69"/>
-      <c r="AF36" s="67"/>
-      <c r="AG36" s="68"/>
-      <c r="AH36" s="68"/>
-      <c r="AI36" s="68"/>
-      <c r="AJ36" s="68"/>
-      <c r="AK36" s="68"/>
+      <c r="B36" s="66"/>
+      <c r="C36" s="75" t="s">
+        <v>137</v>
+      </c>
+      <c r="D36" s="69"/>
+      <c r="E36" s="69"/>
+      <c r="F36" s="72"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="68"/>
+      <c r="I36" s="69"/>
+      <c r="J36" s="69"/>
+      <c r="K36" s="69"/>
+      <c r="L36" s="54"/>
+      <c r="M36" s="64"/>
+      <c r="N36" s="52"/>
+      <c r="O36" s="53"/>
+      <c r="P36" s="64"/>
+      <c r="Q36" s="69"/>
+      <c r="R36" s="69"/>
+      <c r="S36" s="69"/>
+      <c r="T36" s="69"/>
+      <c r="U36" s="69"/>
+      <c r="V36" s="70"/>
+      <c r="W36" s="57"/>
+      <c r="X36" s="69"/>
+      <c r="Y36" s="69"/>
+      <c r="Z36" s="70"/>
+      <c r="AA36" s="68"/>
+      <c r="AB36" s="69"/>
+      <c r="AC36" s="69"/>
+      <c r="AD36" s="54"/>
+      <c r="AE36" s="70"/>
+      <c r="AF36" s="68"/>
+      <c r="AG36" s="69"/>
+      <c r="AH36" s="69"/>
+      <c r="AI36" s="69"/>
+      <c r="AJ36" s="69"/>
+      <c r="AK36" s="69"/>
     </row>
     <row r="37" ht="12" customHeight="1">
-      <c r="B37" s="65"/>
-      <c r="C37" s="74"/>
-      <c r="D37" s="68"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="71"/>
-      <c r="G37" s="69"/>
-      <c r="H37" s="67"/>
-      <c r="I37" s="68"/>
-      <c r="J37" s="68"/>
-      <c r="K37" s="75"/>
-      <c r="L37" s="53"/>
-      <c r="M37" s="68"/>
-      <c r="N37" s="69"/>
-      <c r="O37" s="67"/>
-      <c r="P37" s="62"/>
-      <c r="Q37" s="68"/>
-      <c r="R37" s="76"/>
-      <c r="S37" s="76"/>
-      <c r="T37" s="58"/>
-      <c r="U37" s="68"/>
-      <c r="V37" s="69"/>
-      <c r="W37" s="56"/>
-      <c r="X37" s="68"/>
-      <c r="Y37" s="68"/>
-      <c r="Z37" s="69"/>
-      <c r="AA37" s="67"/>
-      <c r="AB37" s="68"/>
-      <c r="AC37" s="68"/>
-      <c r="AD37" s="53"/>
-      <c r="AE37" s="69"/>
-      <c r="AF37" s="67"/>
-      <c r="AG37" s="68"/>
-      <c r="AH37" s="68"/>
-      <c r="AI37" s="68"/>
-      <c r="AJ37" s="68"/>
-      <c r="AK37" s="68"/>
+      <c r="B37" s="66"/>
+      <c r="C37" s="75"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="69"/>
+      <c r="F37" s="72"/>
+      <c r="G37" s="70"/>
+      <c r="H37" s="68"/>
+      <c r="I37" s="69"/>
+      <c r="J37" s="69"/>
+      <c r="K37" s="76"/>
+      <c r="L37" s="54"/>
+      <c r="M37" s="69"/>
+      <c r="N37" s="70"/>
+      <c r="O37" s="68"/>
+      <c r="P37" s="63"/>
+      <c r="Q37" s="69"/>
+      <c r="R37" s="77"/>
+      <c r="S37" s="77"/>
+      <c r="T37" s="59"/>
+      <c r="U37" s="69"/>
+      <c r="V37" s="70"/>
+      <c r="W37" s="57"/>
+      <c r="X37" s="69"/>
+      <c r="Y37" s="69"/>
+      <c r="Z37" s="70"/>
+      <c r="AA37" s="68"/>
+      <c r="AB37" s="69"/>
+      <c r="AC37" s="69"/>
+      <c r="AD37" s="54"/>
+      <c r="AE37" s="70"/>
+      <c r="AF37" s="68"/>
+      <c r="AG37" s="69"/>
+      <c r="AH37" s="69"/>
+      <c r="AI37" s="69"/>
+      <c r="AJ37" s="69"/>
+      <c r="AK37" s="69"/>
     </row>
     <row r="38" ht="12" customHeight="1">
-      <c r="B38" s="65"/>
-      <c r="C38" s="74" t="s">
-        <v>131</v>
-      </c>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="71"/>
-      <c r="G38" s="69"/>
-      <c r="H38" s="67"/>
-      <c r="I38" s="68"/>
-      <c r="J38" s="68"/>
-      <c r="K38" s="68"/>
-      <c r="L38" s="53"/>
-      <c r="M38" s="68"/>
-      <c r="N38" s="69"/>
-      <c r="O38" s="52"/>
-      <c r="P38" s="63"/>
-      <c r="Q38" s="63"/>
-      <c r="R38" s="63"/>
-      <c r="S38" s="63"/>
-      <c r="T38" s="63"/>
-      <c r="U38" s="63"/>
-      <c r="V38" s="51"/>
-      <c r="W38" s="56"/>
-      <c r="X38" s="63"/>
-      <c r="Y38" s="63"/>
-      <c r="Z38" s="69"/>
-      <c r="AA38" s="67"/>
-      <c r="AB38" s="68"/>
-      <c r="AC38" s="68"/>
-      <c r="AD38" s="53"/>
-      <c r="AE38" s="69"/>
-      <c r="AF38" s="67"/>
-      <c r="AG38" s="68"/>
-      <c r="AH38" s="68"/>
-      <c r="AI38" s="68"/>
-      <c r="AJ38" s="68"/>
-      <c r="AK38" s="68"/>
+      <c r="B38" s="66"/>
+      <c r="C38" s="75" t="s">
+        <v>138</v>
+      </c>
+      <c r="D38" s="69"/>
+      <c r="E38" s="69"/>
+      <c r="F38" s="72"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="68"/>
+      <c r="I38" s="69"/>
+      <c r="J38" s="69"/>
+      <c r="K38" s="69"/>
+      <c r="L38" s="54"/>
+      <c r="M38" s="69"/>
+      <c r="N38" s="70"/>
+      <c r="O38" s="53"/>
+      <c r="P38" s="64"/>
+      <c r="Q38" s="64"/>
+      <c r="R38" s="64"/>
+      <c r="S38" s="64"/>
+      <c r="T38" s="64"/>
+      <c r="U38" s="64"/>
+      <c r="V38" s="52"/>
+      <c r="W38" s="57"/>
+      <c r="X38" s="64"/>
+      <c r="Y38" s="64"/>
+      <c r="Z38" s="70"/>
+      <c r="AA38" s="68"/>
+      <c r="AB38" s="69"/>
+      <c r="AC38" s="69"/>
+      <c r="AD38" s="54"/>
+      <c r="AE38" s="70"/>
+      <c r="AF38" s="68"/>
+      <c r="AG38" s="69"/>
+      <c r="AH38" s="69"/>
+      <c r="AI38" s="69"/>
+      <c r="AJ38" s="69"/>
+      <c r="AK38" s="69"/>
     </row>
     <row r="39" ht="12" customHeight="1">
-      <c r="B39" s="65"/>
-      <c r="C39" s="74"/>
-      <c r="D39" s="68"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="71"/>
-      <c r="G39" s="69"/>
-      <c r="H39" s="67"/>
-      <c r="I39" s="68"/>
-      <c r="J39" s="68"/>
-      <c r="K39" s="68"/>
-      <c r="L39" s="53"/>
-      <c r="M39" s="68"/>
-      <c r="N39" s="69"/>
-      <c r="O39" s="67"/>
-      <c r="P39" s="68"/>
-      <c r="Q39" s="68"/>
-      <c r="R39" s="75"/>
-      <c r="S39" s="75"/>
-      <c r="T39" s="68"/>
-      <c r="U39" s="68"/>
-      <c r="V39" s="69"/>
-      <c r="W39" s="56"/>
-      <c r="X39" s="68"/>
-      <c r="Y39" s="68"/>
-      <c r="Z39" s="69"/>
-      <c r="AA39" s="67"/>
-      <c r="AB39" s="68"/>
-      <c r="AC39" s="68"/>
-      <c r="AD39" s="53"/>
-      <c r="AE39" s="69"/>
-      <c r="AF39" s="67"/>
-      <c r="AG39" s="68"/>
-      <c r="AH39" s="68"/>
-      <c r="AI39" s="68"/>
-      <c r="AJ39" s="68"/>
-      <c r="AK39" s="68"/>
+      <c r="B39" s="66"/>
+      <c r="C39" s="75"/>
+      <c r="D39" s="69"/>
+      <c r="E39" s="69"/>
+      <c r="F39" s="72"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="68"/>
+      <c r="I39" s="69"/>
+      <c r="J39" s="69"/>
+      <c r="K39" s="69"/>
+      <c r="L39" s="54"/>
+      <c r="M39" s="69"/>
+      <c r="N39" s="70"/>
+      <c r="O39" s="68"/>
+      <c r="P39" s="69"/>
+      <c r="Q39" s="69"/>
+      <c r="R39" s="76"/>
+      <c r="S39" s="76"/>
+      <c r="T39" s="69"/>
+      <c r="U39" s="69"/>
+      <c r="V39" s="70"/>
+      <c r="W39" s="57"/>
+      <c r="X39" s="69"/>
+      <c r="Y39" s="69"/>
+      <c r="Z39" s="70"/>
+      <c r="AA39" s="68"/>
+      <c r="AB39" s="69"/>
+      <c r="AC39" s="69"/>
+      <c r="AD39" s="54"/>
+      <c r="AE39" s="70"/>
+      <c r="AF39" s="68"/>
+      <c r="AG39" s="69"/>
+      <c r="AH39" s="69"/>
+      <c r="AI39" s="69"/>
+      <c r="AJ39" s="69"/>
+      <c r="AK39" s="69"/>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="B40" s="65"/>
-      <c r="C40" s="74" t="s">
-        <v>132</v>
-      </c>
-      <c r="D40" s="68"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="71"/>
-      <c r="G40" s="69"/>
-      <c r="H40" s="67"/>
-      <c r="I40" s="68"/>
-      <c r="J40" s="68"/>
-      <c r="K40" s="68"/>
-      <c r="L40" s="53"/>
-      <c r="M40" s="68"/>
-      <c r="N40" s="69"/>
-      <c r="O40" s="67"/>
-      <c r="P40" s="68"/>
-      <c r="Q40" s="68"/>
-      <c r="R40" s="63"/>
-      <c r="S40" s="63"/>
-      <c r="T40" s="63"/>
-      <c r="U40" s="63"/>
-      <c r="V40" s="51"/>
-      <c r="W40" s="56"/>
-      <c r="X40" s="63"/>
-      <c r="Y40" s="63"/>
-      <c r="Z40" s="51"/>
-      <c r="AA40" s="52"/>
-      <c r="AB40" s="63"/>
-      <c r="AC40" s="63"/>
-      <c r="AD40" s="53"/>
-      <c r="AE40" s="69"/>
-      <c r="AF40" s="67"/>
-      <c r="AG40" s="68"/>
-      <c r="AH40" s="68"/>
-      <c r="AI40" s="68"/>
-      <c r="AJ40" s="68"/>
-      <c r="AK40" s="68"/>
+      <c r="B40" s="66"/>
+      <c r="C40" s="75" t="s">
+        <v>139</v>
+      </c>
+      <c r="D40" s="69"/>
+      <c r="E40" s="69"/>
+      <c r="F40" s="72"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="68"/>
+      <c r="I40" s="69"/>
+      <c r="J40" s="69"/>
+      <c r="K40" s="69"/>
+      <c r="L40" s="54"/>
+      <c r="M40" s="69"/>
+      <c r="N40" s="70"/>
+      <c r="O40" s="68"/>
+      <c r="P40" s="69"/>
+      <c r="Q40" s="69"/>
+      <c r="R40" s="64"/>
+      <c r="S40" s="64"/>
+      <c r="T40" s="64"/>
+      <c r="U40" s="64"/>
+      <c r="V40" s="52"/>
+      <c r="W40" s="57"/>
+      <c r="X40" s="64"/>
+      <c r="Y40" s="64"/>
+      <c r="Z40" s="52"/>
+      <c r="AA40" s="53"/>
+      <c r="AB40" s="64"/>
+      <c r="AC40" s="64"/>
+      <c r="AD40" s="54"/>
+      <c r="AE40" s="70"/>
+      <c r="AF40" s="68"/>
+      <c r="AG40" s="69"/>
+      <c r="AH40" s="69"/>
+      <c r="AI40" s="69"/>
+      <c r="AJ40" s="69"/>
+      <c r="AK40" s="69"/>
     </row>
     <row r="41" ht="12" customHeight="1">
-      <c r="B41" s="65"/>
-      <c r="C41" s="74"/>
-      <c r="D41" s="68"/>
-      <c r="E41" s="68"/>
-      <c r="F41" s="71"/>
-      <c r="G41" s="69"/>
-      <c r="H41" s="67"/>
-      <c r="I41" s="68"/>
-      <c r="J41" s="68"/>
-      <c r="K41" s="68"/>
-      <c r="L41" s="53"/>
-      <c r="M41" s="68"/>
-      <c r="N41" s="69"/>
-      <c r="O41" s="67"/>
-      <c r="P41" s="68"/>
-      <c r="Q41" s="62"/>
-      <c r="R41" s="75"/>
-      <c r="S41" s="75"/>
-      <c r="T41" s="62"/>
-      <c r="U41" s="68"/>
-      <c r="V41" s="69"/>
-      <c r="W41" s="56"/>
-      <c r="X41" s="68"/>
-      <c r="Y41" s="68"/>
-      <c r="Z41" s="69"/>
-      <c r="AA41" s="67"/>
-      <c r="AB41" s="68"/>
-      <c r="AC41" s="68"/>
-      <c r="AD41" s="53"/>
-      <c r="AE41" s="69"/>
-      <c r="AF41" s="67"/>
-      <c r="AG41" s="68"/>
-      <c r="AH41" s="68"/>
-      <c r="AI41" s="68"/>
-      <c r="AJ41" s="68"/>
-      <c r="AK41" s="68"/>
+      <c r="B41" s="66"/>
+      <c r="C41" s="75"/>
+      <c r="D41" s="69"/>
+      <c r="E41" s="69"/>
+      <c r="F41" s="72"/>
+      <c r="G41" s="70"/>
+      <c r="H41" s="68"/>
+      <c r="I41" s="69"/>
+      <c r="J41" s="69"/>
+      <c r="K41" s="69"/>
+      <c r="L41" s="54"/>
+      <c r="M41" s="69"/>
+      <c r="N41" s="70"/>
+      <c r="O41" s="68"/>
+      <c r="P41" s="69"/>
+      <c r="Q41" s="63"/>
+      <c r="R41" s="76"/>
+      <c r="S41" s="76"/>
+      <c r="T41" s="63"/>
+      <c r="U41" s="69"/>
+      <c r="V41" s="70"/>
+      <c r="W41" s="57"/>
+      <c r="X41" s="69"/>
+      <c r="Y41" s="69"/>
+      <c r="Z41" s="70"/>
+      <c r="AA41" s="68"/>
+      <c r="AB41" s="69"/>
+      <c r="AC41" s="69"/>
+      <c r="AD41" s="54"/>
+      <c r="AE41" s="70"/>
+      <c r="AF41" s="68"/>
+      <c r="AG41" s="69"/>
+      <c r="AH41" s="69"/>
+      <c r="AI41" s="69"/>
+      <c r="AJ41" s="69"/>
+      <c r="AK41" s="69"/>
     </row>
     <row r="42" ht="12" customHeight="1">
-      <c r="B42" s="47" t="s">
+      <c r="B42" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="77" t="s">
-        <v>133</v>
-      </c>
-      <c r="D42" s="49"/>
-      <c r="E42" s="49"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="54"/>
-      <c r="H42" s="55"/>
-      <c r="I42" s="49"/>
-      <c r="J42" s="49"/>
-      <c r="K42" s="49"/>
-      <c r="L42" s="53"/>
-      <c r="M42" s="49"/>
-      <c r="N42" s="54"/>
-      <c r="O42" s="55"/>
-      <c r="P42" s="63"/>
-      <c r="Q42" s="63"/>
-      <c r="R42" s="49"/>
-      <c r="S42" s="49"/>
-      <c r="T42" s="62"/>
-      <c r="U42" s="49"/>
-      <c r="V42" s="51"/>
-      <c r="W42" s="56"/>
-      <c r="X42" s="63"/>
-      <c r="Y42" s="63"/>
-      <c r="Z42" s="51"/>
-      <c r="AA42" s="52"/>
-      <c r="AB42" s="63"/>
-      <c r="AC42" s="63"/>
-      <c r="AD42" s="53"/>
-      <c r="AE42" s="54"/>
-      <c r="AF42" s="55"/>
-      <c r="AG42" s="49"/>
-      <c r="AH42" s="49"/>
-      <c r="AI42" s="49"/>
-      <c r="AJ42" s="49"/>
-      <c r="AK42" s="49"/>
+      <c r="C42" s="78" t="s">
+        <v>140</v>
+      </c>
+      <c r="D42" s="50"/>
+      <c r="E42" s="50"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="55"/>
+      <c r="H42" s="56"/>
+      <c r="I42" s="50"/>
+      <c r="J42" s="50"/>
+      <c r="K42" s="50"/>
+      <c r="L42" s="54"/>
+      <c r="M42" s="50"/>
+      <c r="N42" s="55"/>
+      <c r="O42" s="56"/>
+      <c r="P42" s="64"/>
+      <c r="Q42" s="64"/>
+      <c r="R42" s="50"/>
+      <c r="S42" s="50"/>
+      <c r="T42" s="63"/>
+      <c r="U42" s="50"/>
+      <c r="V42" s="52"/>
+      <c r="W42" s="57"/>
+      <c r="X42" s="64"/>
+      <c r="Y42" s="64"/>
+      <c r="Z42" s="52"/>
+      <c r="AA42" s="53"/>
+      <c r="AB42" s="64"/>
+      <c r="AC42" s="64"/>
+      <c r="AD42" s="54"/>
+      <c r="AE42" s="55"/>
+      <c r="AF42" s="56"/>
+      <c r="AG42" s="50"/>
+      <c r="AH42" s="50"/>
+      <c r="AI42" s="50"/>
+      <c r="AJ42" s="50"/>
+      <c r="AK42" s="50"/>
     </row>
     <row r="43" ht="12" customHeight="1">
-      <c r="B43" s="47"/>
-      <c r="C43" s="77"/>
-      <c r="D43" s="49"/>
-      <c r="E43" s="49"/>
-      <c r="F43" s="57"/>
-      <c r="G43" s="54"/>
-      <c r="H43" s="55"/>
-      <c r="I43" s="49"/>
-      <c r="J43" s="49"/>
-      <c r="K43" s="49"/>
-      <c r="L43" s="53"/>
-      <c r="M43" s="49"/>
-      <c r="N43" s="54"/>
-      <c r="O43" s="55"/>
-      <c r="P43" s="49"/>
-      <c r="Q43" s="62"/>
-      <c r="R43" s="49"/>
-      <c r="S43" s="64"/>
-      <c r="T43" s="49"/>
-      <c r="U43" s="49"/>
-      <c r="V43" s="54"/>
-      <c r="W43" s="56"/>
-      <c r="X43" s="49"/>
-      <c r="Y43" s="49"/>
-      <c r="Z43" s="54"/>
-      <c r="AA43" s="55"/>
-      <c r="AB43" s="49"/>
-      <c r="AC43" s="49"/>
-      <c r="AD43" s="53"/>
-      <c r="AE43" s="54"/>
-      <c r="AF43" s="55"/>
-      <c r="AG43" s="49"/>
-      <c r="AH43" s="49"/>
-      <c r="AI43" s="49"/>
-      <c r="AJ43" s="49"/>
-      <c r="AK43" s="49"/>
+      <c r="B43" s="48"/>
+      <c r="C43" s="78"/>
+      <c r="D43" s="50"/>
+      <c r="E43" s="50"/>
+      <c r="F43" s="58"/>
+      <c r="G43" s="55"/>
+      <c r="H43" s="56"/>
+      <c r="I43" s="50"/>
+      <c r="J43" s="50"/>
+      <c r="K43" s="50"/>
+      <c r="L43" s="54"/>
+      <c r="M43" s="50"/>
+      <c r="N43" s="55"/>
+      <c r="O43" s="56"/>
+      <c r="P43" s="50"/>
+      <c r="Q43" s="63"/>
+      <c r="R43" s="50"/>
+      <c r="S43" s="65"/>
+      <c r="T43" s="50"/>
+      <c r="U43" s="50"/>
+      <c r="V43" s="55"/>
+      <c r="W43" s="57"/>
+      <c r="X43" s="50"/>
+      <c r="Y43" s="50"/>
+      <c r="Z43" s="55"/>
+      <c r="AA43" s="56"/>
+      <c r="AB43" s="50"/>
+      <c r="AC43" s="50"/>
+      <c r="AD43" s="54"/>
+      <c r="AE43" s="55"/>
+      <c r="AF43" s="56"/>
+      <c r="AG43" s="50"/>
+      <c r="AH43" s="50"/>
+      <c r="AI43" s="50"/>
+      <c r="AJ43" s="50"/>
+      <c r="AK43" s="50"/>
     </row>
     <row r="44" ht="12" customHeight="1">
-      <c r="B44" s="47"/>
-      <c r="C44" s="77" t="s">
-        <v>134</v>
-      </c>
-      <c r="D44" s="49"/>
-      <c r="E44" s="49"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="54"/>
-      <c r="H44" s="55"/>
-      <c r="I44" s="49"/>
-      <c r="J44" s="49"/>
-      <c r="K44" s="49"/>
-      <c r="L44" s="53"/>
-      <c r="M44" s="49"/>
-      <c r="N44" s="54"/>
-      <c r="O44" s="55"/>
-      <c r="P44" s="63"/>
-      <c r="Q44" s="63"/>
-      <c r="R44" s="49"/>
-      <c r="S44" s="49"/>
-      <c r="T44" s="49"/>
-      <c r="U44" s="49"/>
-      <c r="V44" s="54"/>
-      <c r="W44" s="56"/>
-      <c r="X44" s="63"/>
-      <c r="Y44" s="63"/>
-      <c r="Z44" s="54"/>
-      <c r="AA44" s="55"/>
-      <c r="AB44" s="49"/>
-      <c r="AC44" s="63"/>
-      <c r="AD44" s="53"/>
-      <c r="AE44" s="51"/>
-      <c r="AF44" s="52"/>
-      <c r="AG44" s="49"/>
-      <c r="AH44" s="49"/>
-      <c r="AI44" s="63"/>
-      <c r="AJ44" s="49"/>
-      <c r="AK44" s="49"/>
+      <c r="B44" s="48"/>
+      <c r="C44" s="78" t="s">
+        <v>141</v>
+      </c>
+      <c r="D44" s="50"/>
+      <c r="E44" s="50"/>
+      <c r="F44" s="58"/>
+      <c r="G44" s="55"/>
+      <c r="H44" s="56"/>
+      <c r="I44" s="50"/>
+      <c r="J44" s="50"/>
+      <c r="K44" s="50"/>
+      <c r="L44" s="54"/>
+      <c r="M44" s="50"/>
+      <c r="N44" s="55"/>
+      <c r="O44" s="56"/>
+      <c r="P44" s="64"/>
+      <c r="Q44" s="64"/>
+      <c r="R44" s="50"/>
+      <c r="S44" s="50"/>
+      <c r="T44" s="50"/>
+      <c r="U44" s="50"/>
+      <c r="V44" s="55"/>
+      <c r="W44" s="57"/>
+      <c r="X44" s="64"/>
+      <c r="Y44" s="64"/>
+      <c r="Z44" s="55"/>
+      <c r="AA44" s="56"/>
+      <c r="AB44" s="50"/>
+      <c r="AC44" s="64"/>
+      <c r="AD44" s="54"/>
+      <c r="AE44" s="52"/>
+      <c r="AF44" s="53"/>
+      <c r="AG44" s="50"/>
+      <c r="AH44" s="50"/>
+      <c r="AI44" s="64"/>
+      <c r="AJ44" s="50"/>
+      <c r="AK44" s="50"/>
     </row>
     <row r="45" ht="12" customHeight="1">
-      <c r="B45" s="47"/>
-      <c r="C45" s="77"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="57"/>
-      <c r="G45" s="54"/>
-      <c r="H45" s="55"/>
-      <c r="I45" s="49"/>
-      <c r="J45" s="49"/>
-      <c r="K45" s="49"/>
-      <c r="L45" s="53"/>
-      <c r="M45" s="49"/>
-      <c r="N45" s="54"/>
-      <c r="O45" s="55"/>
-      <c r="P45" s="49"/>
-      <c r="Q45" s="49"/>
-      <c r="R45" s="49"/>
-      <c r="S45" s="49"/>
-      <c r="T45" s="49"/>
-      <c r="U45" s="49"/>
-      <c r="V45" s="54"/>
-      <c r="W45" s="56"/>
-      <c r="X45" s="49"/>
-      <c r="Y45" s="49"/>
-      <c r="Z45" s="54"/>
-      <c r="AA45" s="55"/>
-      <c r="AB45" s="49"/>
-      <c r="AC45" s="49"/>
-      <c r="AD45" s="53"/>
-      <c r="AE45" s="54"/>
-      <c r="AF45" s="55"/>
-      <c r="AG45" s="49"/>
-      <c r="AH45" s="49"/>
-      <c r="AI45" s="49"/>
-      <c r="AJ45" s="49"/>
-      <c r="AK45" s="49"/>
+      <c r="B45" s="48"/>
+      <c r="C45" s="78"/>
+      <c r="D45" s="50"/>
+      <c r="E45" s="50"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="55"/>
+      <c r="H45" s="56"/>
+      <c r="I45" s="50"/>
+      <c r="J45" s="50"/>
+      <c r="K45" s="50"/>
+      <c r="L45" s="54"/>
+      <c r="M45" s="50"/>
+      <c r="N45" s="55"/>
+      <c r="O45" s="56"/>
+      <c r="P45" s="50"/>
+      <c r="Q45" s="50"/>
+      <c r="R45" s="50"/>
+      <c r="S45" s="50"/>
+      <c r="T45" s="50"/>
+      <c r="U45" s="50"/>
+      <c r="V45" s="55"/>
+      <c r="W45" s="57"/>
+      <c r="X45" s="50"/>
+      <c r="Y45" s="50"/>
+      <c r="Z45" s="55"/>
+      <c r="AA45" s="56"/>
+      <c r="AB45" s="50"/>
+      <c r="AC45" s="50"/>
+      <c r="AD45" s="54"/>
+      <c r="AE45" s="55"/>
+      <c r="AF45" s="56"/>
+      <c r="AG45" s="50"/>
+      <c r="AH45" s="50"/>
+      <c r="AI45" s="50"/>
+      <c r="AJ45" s="50"/>
+      <c r="AK45" s="50"/>
     </row>
     <row r="46" ht="12" customHeight="1">
-      <c r="B46" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="C46" s="66" t="s">
+      <c r="B46" s="66" t="s">
+        <v>142</v>
+      </c>
+      <c r="C46" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="D46" s="68"/>
-      <c r="E46" s="68"/>
-      <c r="F46" s="71"/>
-      <c r="G46" s="69"/>
-      <c r="H46" s="67"/>
-      <c r="I46" s="68"/>
-      <c r="J46" s="68"/>
-      <c r="K46" s="68"/>
-      <c r="L46" s="53"/>
-      <c r="M46" s="68"/>
-      <c r="N46" s="69"/>
-      <c r="O46" s="67"/>
-      <c r="P46" s="68"/>
-      <c r="Q46" s="68"/>
-      <c r="R46" s="68"/>
-      <c r="S46" s="68"/>
-      <c r="T46" s="68"/>
-      <c r="U46" s="68"/>
-      <c r="V46" s="69"/>
-      <c r="W46" s="56"/>
-      <c r="X46" s="68"/>
-      <c r="Y46" s="68"/>
-      <c r="Z46" s="69"/>
-      <c r="AA46" s="67"/>
-      <c r="AB46" s="68"/>
-      <c r="AC46" s="68"/>
-      <c r="AD46" s="53"/>
-      <c r="AE46" s="69"/>
-      <c r="AF46" s="67"/>
-      <c r="AG46" s="68"/>
-      <c r="AH46" s="68"/>
-      <c r="AI46" s="68"/>
-      <c r="AJ46" s="63"/>
-      <c r="AK46" s="68"/>
+      <c r="D46" s="69"/>
+      <c r="E46" s="69"/>
+      <c r="F46" s="72"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="68"/>
+      <c r="I46" s="69"/>
+      <c r="J46" s="69"/>
+      <c r="K46" s="69"/>
+      <c r="L46" s="54"/>
+      <c r="M46" s="69"/>
+      <c r="N46" s="70"/>
+      <c r="O46" s="68"/>
+      <c r="P46" s="69"/>
+      <c r="Q46" s="69"/>
+      <c r="R46" s="69"/>
+      <c r="S46" s="69"/>
+      <c r="T46" s="69"/>
+      <c r="U46" s="69"/>
+      <c r="V46" s="70"/>
+      <c r="W46" s="57"/>
+      <c r="X46" s="69"/>
+      <c r="Y46" s="69"/>
+      <c r="Z46" s="70"/>
+      <c r="AA46" s="68"/>
+      <c r="AB46" s="69"/>
+      <c r="AC46" s="69"/>
+      <c r="AD46" s="54"/>
+      <c r="AE46" s="70"/>
+      <c r="AF46" s="68"/>
+      <c r="AG46" s="69"/>
+      <c r="AH46" s="69"/>
+      <c r="AI46" s="69"/>
+      <c r="AJ46" s="64"/>
+      <c r="AK46" s="69"/>
     </row>
     <row r="47" ht="12" customHeight="1">
-      <c r="B47" s="65"/>
-      <c r="C47" s="66"/>
-      <c r="D47" s="68"/>
-      <c r="E47" s="68"/>
-      <c r="F47" s="71"/>
-      <c r="G47" s="69"/>
-      <c r="H47" s="67"/>
-      <c r="I47" s="68"/>
-      <c r="J47" s="68"/>
-      <c r="K47" s="68"/>
-      <c r="L47" s="53"/>
-      <c r="M47" s="68"/>
-      <c r="N47" s="69"/>
-      <c r="O47" s="67"/>
-      <c r="P47" s="68"/>
-      <c r="Q47" s="68"/>
-      <c r="R47" s="68"/>
-      <c r="S47" s="68"/>
-      <c r="T47" s="68"/>
-      <c r="U47" s="68"/>
-      <c r="V47" s="69"/>
-      <c r="W47" s="56"/>
-      <c r="X47" s="68"/>
-      <c r="Y47" s="68"/>
-      <c r="Z47" s="69"/>
-      <c r="AA47" s="67"/>
-      <c r="AB47" s="68"/>
-      <c r="AC47" s="68"/>
-      <c r="AD47" s="53"/>
-      <c r="AE47" s="69"/>
-      <c r="AF47" s="67"/>
-      <c r="AG47" s="68"/>
-      <c r="AH47" s="68"/>
-      <c r="AI47" s="68"/>
-      <c r="AJ47" s="68"/>
-      <c r="AK47" s="68"/>
-      <c r="AN47" s="78" t="s">
-        <v>136</v>
-      </c>
-      <c r="AO47" s="63"/>
+      <c r="B47" s="66"/>
+      <c r="C47" s="67"/>
+      <c r="D47" s="69"/>
+      <c r="E47" s="69"/>
+      <c r="F47" s="72"/>
+      <c r="G47" s="70"/>
+      <c r="H47" s="68"/>
+      <c r="I47" s="69"/>
+      <c r="J47" s="69"/>
+      <c r="K47" s="69"/>
+      <c r="L47" s="54"/>
+      <c r="M47" s="69"/>
+      <c r="N47" s="70"/>
+      <c r="O47" s="68"/>
+      <c r="P47" s="69"/>
+      <c r="Q47" s="69"/>
+      <c r="R47" s="69"/>
+      <c r="S47" s="69"/>
+      <c r="T47" s="69"/>
+      <c r="U47" s="69"/>
+      <c r="V47" s="70"/>
+      <c r="W47" s="57"/>
+      <c r="X47" s="69"/>
+      <c r="Y47" s="69"/>
+      <c r="Z47" s="70"/>
+      <c r="AA47" s="68"/>
+      <c r="AB47" s="69"/>
+      <c r="AC47" s="69"/>
+      <c r="AD47" s="54"/>
+      <c r="AE47" s="70"/>
+      <c r="AF47" s="68"/>
+      <c r="AG47" s="69"/>
+      <c r="AH47" s="69"/>
+      <c r="AI47" s="69"/>
+      <c r="AJ47" s="69"/>
+      <c r="AK47" s="69"/>
+      <c r="AN47" s="79" t="s">
+        <v>143</v>
+      </c>
+      <c r="AO47" s="64"/>
     </row>
     <row r="48" ht="12" customHeight="1">
-      <c r="B48" s="65"/>
-      <c r="C48" s="66" t="s">
-        <v>137</v>
-      </c>
-      <c r="D48" s="68"/>
-      <c r="E48" s="68"/>
-      <c r="F48" s="71"/>
-      <c r="G48" s="69"/>
-      <c r="H48" s="67"/>
-      <c r="I48" s="68"/>
-      <c r="J48" s="68"/>
-      <c r="K48" s="68"/>
-      <c r="L48" s="53"/>
-      <c r="M48" s="68"/>
-      <c r="N48" s="69"/>
-      <c r="O48" s="67"/>
-      <c r="P48" s="68"/>
-      <c r="Q48" s="68"/>
-      <c r="R48" s="68"/>
-      <c r="S48" s="68"/>
-      <c r="T48" s="68"/>
-      <c r="U48" s="68"/>
-      <c r="V48" s="69"/>
-      <c r="W48" s="56"/>
-      <c r="X48" s="68"/>
-      <c r="Y48" s="68"/>
-      <c r="Z48" s="69"/>
-      <c r="AA48" s="67"/>
-      <c r="AB48" s="68"/>
-      <c r="AC48" s="68"/>
-      <c r="AD48" s="53"/>
-      <c r="AE48" s="69"/>
-      <c r="AF48" s="67"/>
-      <c r="AG48" s="68"/>
-      <c r="AH48" s="68"/>
-      <c r="AI48" s="68"/>
-      <c r="AJ48" s="68"/>
-      <c r="AK48" s="79"/>
-      <c r="AN48" s="78" t="s">
-        <v>138</v>
-      </c>
-      <c r="AO48" s="62"/>
+      <c r="B48" s="66"/>
+      <c r="C48" s="67" t="s">
+        <v>144</v>
+      </c>
+      <c r="D48" s="69"/>
+      <c r="E48" s="69"/>
+      <c r="F48" s="72"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="68"/>
+      <c r="I48" s="69"/>
+      <c r="J48" s="69"/>
+      <c r="K48" s="69"/>
+      <c r="L48" s="54"/>
+      <c r="M48" s="69"/>
+      <c r="N48" s="70"/>
+      <c r="O48" s="68"/>
+      <c r="P48" s="69"/>
+      <c r="Q48" s="69"/>
+      <c r="R48" s="69"/>
+      <c r="S48" s="69"/>
+      <c r="T48" s="69"/>
+      <c r="U48" s="69"/>
+      <c r="V48" s="70"/>
+      <c r="W48" s="57"/>
+      <c r="X48" s="69"/>
+      <c r="Y48" s="69"/>
+      <c r="Z48" s="70"/>
+      <c r="AA48" s="68"/>
+      <c r="AB48" s="69"/>
+      <c r="AC48" s="69"/>
+      <c r="AD48" s="54"/>
+      <c r="AE48" s="70"/>
+      <c r="AF48" s="68"/>
+      <c r="AG48" s="69"/>
+      <c r="AH48" s="69"/>
+      <c r="AI48" s="69"/>
+      <c r="AJ48" s="69"/>
+      <c r="AK48" s="80"/>
+      <c r="AN48" s="79" t="s">
+        <v>145</v>
+      </c>
+      <c r="AO48" s="63"/>
     </row>
     <row r="49" ht="12" customHeight="1">
-      <c r="B49" s="65"/>
-      <c r="C49" s="66"/>
-      <c r="D49" s="68"/>
-      <c r="E49" s="68"/>
-      <c r="F49" s="71"/>
-      <c r="G49" s="69"/>
-      <c r="H49" s="67"/>
-      <c r="I49" s="68"/>
-      <c r="J49" s="68"/>
-      <c r="K49" s="68"/>
-      <c r="L49" s="53"/>
-      <c r="M49" s="68"/>
-      <c r="N49" s="69"/>
-      <c r="O49" s="67"/>
-      <c r="P49" s="68"/>
-      <c r="Q49" s="68"/>
-      <c r="R49" s="68"/>
-      <c r="S49" s="68"/>
-      <c r="T49" s="68"/>
-      <c r="U49" s="68"/>
-      <c r="V49" s="69"/>
-      <c r="W49" s="56"/>
-      <c r="X49" s="68"/>
-      <c r="Y49" s="68"/>
-      <c r="Z49" s="69"/>
-      <c r="AA49" s="67"/>
-      <c r="AB49" s="68"/>
-      <c r="AC49" s="68"/>
-      <c r="AD49" s="53"/>
-      <c r="AE49" s="69"/>
-      <c r="AF49" s="67"/>
-      <c r="AG49" s="68"/>
-      <c r="AH49" s="68"/>
-      <c r="AI49" s="68"/>
-      <c r="AJ49" s="68"/>
-      <c r="AK49" s="68"/>
-      <c r="AN49" s="78" t="s">
-        <v>139</v>
-      </c>
-      <c r="AO49" s="58"/>
+      <c r="B49" s="66"/>
+      <c r="C49" s="67"/>
+      <c r="D49" s="69"/>
+      <c r="E49" s="69"/>
+      <c r="F49" s="72"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="68"/>
+      <c r="I49" s="69"/>
+      <c r="J49" s="69"/>
+      <c r="K49" s="69"/>
+      <c r="L49" s="54"/>
+      <c r="M49" s="69"/>
+      <c r="N49" s="70"/>
+      <c r="O49" s="68"/>
+      <c r="P49" s="69"/>
+      <c r="Q49" s="69"/>
+      <c r="R49" s="69"/>
+      <c r="S49" s="69"/>
+      <c r="T49" s="69"/>
+      <c r="U49" s="69"/>
+      <c r="V49" s="70"/>
+      <c r="W49" s="57"/>
+      <c r="X49" s="69"/>
+      <c r="Y49" s="69"/>
+      <c r="Z49" s="70"/>
+      <c r="AA49" s="68"/>
+      <c r="AB49" s="69"/>
+      <c r="AC49" s="69"/>
+      <c r="AD49" s="54"/>
+      <c r="AE49" s="70"/>
+      <c r="AF49" s="68"/>
+      <c r="AG49" s="69"/>
+      <c r="AH49" s="69"/>
+      <c r="AI49" s="69"/>
+      <c r="AJ49" s="69"/>
+      <c r="AK49" s="69"/>
+      <c r="AN49" s="79" t="s">
+        <v>146</v>
+      </c>
+      <c r="AO49" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -9226,801 +9338,801 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="80"/>
+      <c r="B1" s="81"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="81" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="82" t="s">
-        <v>84</v>
-      </c>
-      <c r="D2" s="83" t="s">
-        <v>140</v>
-      </c>
-      <c r="E2" s="84" t="s">
-        <v>141</v>
-      </c>
-      <c r="F2" s="85" t="s">
-        <v>142</v>
-      </c>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="85" t="s">
-        <v>143</v>
-      </c>
-      <c r="K2" s="85"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="85" t="s">
-        <v>144</v>
-      </c>
-      <c r="O2" s="85"/>
-      <c r="P2" s="85"/>
-      <c r="Q2" s="84"/>
-      <c r="R2" s="85" t="s">
-        <v>145</v>
-      </c>
-      <c r="S2" s="86"/>
-      <c r="AD2" s="29"/>
+      <c r="B2" s="82" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="83" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="84" t="s">
+        <v>147</v>
+      </c>
+      <c r="E2" s="85" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2" s="86" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="86" t="s">
+        <v>150</v>
+      </c>
+      <c r="K2" s="86"/>
+      <c r="L2" s="86"/>
+      <c r="M2" s="85"/>
+      <c r="N2" s="86" t="s">
+        <v>151</v>
+      </c>
+      <c r="O2" s="86"/>
+      <c r="P2" s="86"/>
+      <c r="Q2" s="85"/>
+      <c r="R2" s="86" t="s">
+        <v>152</v>
+      </c>
+      <c r="S2" s="87"/>
+      <c r="AD2" s="30"/>
     </row>
     <row r="3">
-      <c r="B3" s="87"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="89" t="s">
-        <v>146</v>
-      </c>
-      <c r="E3" s="90">
+      <c r="B3" s="88"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="90" t="s">
+        <v>153</v>
+      </c>
+      <c r="E3" s="91">
         <v>4</v>
       </c>
-      <c r="F3" s="91">
+      <c r="F3" s="92">
         <v>1</v>
       </c>
-      <c r="G3" s="92">
+      <c r="G3" s="93">
         <v>2</v>
       </c>
-      <c r="H3" s="92">
+      <c r="H3" s="93">
         <v>3</v>
       </c>
-      <c r="I3" s="90">
+      <c r="I3" s="91">
         <v>4</v>
       </c>
-      <c r="J3" s="91">
+      <c r="J3" s="92">
         <v>1</v>
       </c>
-      <c r="K3" s="92">
+      <c r="K3" s="93">
         <v>2</v>
       </c>
-      <c r="L3" s="92">
+      <c r="L3" s="93">
         <v>3</v>
       </c>
-      <c r="M3" s="90">
+      <c r="M3" s="91">
         <v>4</v>
       </c>
-      <c r="N3" s="91">
+      <c r="N3" s="92">
         <v>1</v>
       </c>
-      <c r="O3" s="92">
+      <c r="O3" s="93">
         <v>2</v>
       </c>
-      <c r="P3" s="92">
+      <c r="P3" s="93">
         <v>3</v>
       </c>
-      <c r="Q3" s="90">
+      <c r="Q3" s="91">
         <v>4</v>
       </c>
-      <c r="R3" s="91">
+      <c r="R3" s="92">
         <v>1</v>
       </c>
-      <c r="S3" s="93">
+      <c r="S3" s="94">
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="94" t="s">
-        <v>148</v>
-      </c>
-      <c r="C4" s="82" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" s="95"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="99"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="96"/>
-      <c r="N4" s="99"/>
-      <c r="O4" s="98"/>
-      <c r="P4" s="98"/>
-      <c r="Q4" s="96"/>
-      <c r="R4" s="99"/>
-      <c r="S4" s="100"/>
+      <c r="B4" s="95" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4" s="83" t="s">
+        <v>156</v>
+      </c>
+      <c r="D4" s="96"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="100"/>
+      <c r="K4" s="99"/>
+      <c r="L4" s="99"/>
+      <c r="M4" s="97"/>
+      <c r="N4" s="100"/>
+      <c r="O4" s="99"/>
+      <c r="P4" s="99"/>
+      <c r="Q4" s="97"/>
+      <c r="R4" s="100"/>
+      <c r="S4" s="101"/>
       <c r="U4" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="94"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="104"/>
-      <c r="G5" s="105"/>
-      <c r="H5" s="106"/>
-      <c r="I5" s="103"/>
-      <c r="J5" s="107"/>
-      <c r="K5" s="106"/>
-      <c r="L5" s="106"/>
-      <c r="M5" s="103"/>
-      <c r="N5" s="107"/>
-      <c r="O5" s="106"/>
-      <c r="P5" s="106"/>
-      <c r="Q5" s="103"/>
-      <c r="R5" s="107"/>
-      <c r="S5" s="108"/>
+      <c r="B5" s="95"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="106"/>
+      <c r="H5" s="107"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="108"/>
+      <c r="K5" s="107"/>
+      <c r="L5" s="107"/>
+      <c r="M5" s="104"/>
+      <c r="N5" s="108"/>
+      <c r="O5" s="107"/>
+      <c r="P5" s="107"/>
+      <c r="Q5" s="104"/>
+      <c r="R5" s="108"/>
+      <c r="S5" s="109"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="94"/>
-      <c r="C6" s="109" t="s">
-        <v>151</v>
-      </c>
-      <c r="D6" s="110"/>
-      <c r="E6" s="111"/>
-      <c r="F6" s="112"/>
-      <c r="G6" s="113"/>
-      <c r="H6" s="114"/>
-      <c r="I6" s="111"/>
-      <c r="J6" s="115"/>
-      <c r="K6" s="114"/>
-      <c r="L6" s="114"/>
-      <c r="M6" s="111"/>
-      <c r="N6" s="115"/>
-      <c r="O6" s="114"/>
-      <c r="P6" s="114"/>
-      <c r="Q6" s="111"/>
-      <c r="R6" s="115"/>
-      <c r="S6" s="116"/>
-      <c r="U6" s="117" t="s">
-        <v>152</v>
-      </c>
-      <c r="V6" s="117"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="110" t="s">
+        <v>158</v>
+      </c>
+      <c r="D6" s="111"/>
+      <c r="E6" s="112"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="114"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="112"/>
+      <c r="J6" s="116"/>
+      <c r="K6" s="115"/>
+      <c r="L6" s="115"/>
+      <c r="M6" s="112"/>
+      <c r="N6" s="116"/>
+      <c r="O6" s="115"/>
+      <c r="P6" s="115"/>
+      <c r="Q6" s="112"/>
+      <c r="R6" s="116"/>
+      <c r="S6" s="117"/>
+      <c r="U6" s="118" t="s">
+        <v>159</v>
+      </c>
+      <c r="V6" s="118"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="94"/>
-      <c r="C7" s="101"/>
-      <c r="D7" s="102"/>
-      <c r="E7" s="103"/>
-      <c r="F7" s="107"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="103"/>
-      <c r="J7" s="107"/>
-      <c r="K7" s="106"/>
-      <c r="L7" s="106"/>
-      <c r="M7" s="103"/>
-      <c r="N7" s="107"/>
-      <c r="O7" s="106"/>
-      <c r="P7" s="106"/>
-      <c r="Q7" s="103"/>
-      <c r="R7" s="107"/>
-      <c r="S7" s="108"/>
+      <c r="B7" s="95"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="108"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="106"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="108"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="104"/>
+      <c r="N7" s="108"/>
+      <c r="O7" s="107"/>
+      <c r="P7" s="107"/>
+      <c r="Q7" s="104"/>
+      <c r="R7" s="108"/>
+      <c r="S7" s="109"/>
       <c r="U7" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="94"/>
-      <c r="C8" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="D8" s="110"/>
-      <c r="E8" s="111"/>
-      <c r="F8" s="112"/>
-      <c r="G8" s="114"/>
-      <c r="H8" s="114"/>
-      <c r="I8" s="111"/>
-      <c r="J8" s="115"/>
-      <c r="K8" s="114"/>
-      <c r="L8" s="114"/>
-      <c r="M8" s="111"/>
-      <c r="N8" s="115"/>
-      <c r="O8" s="114"/>
-      <c r="P8" s="114"/>
-      <c r="Q8" s="111"/>
-      <c r="R8" s="115"/>
-      <c r="S8" s="116"/>
+      <c r="B8" s="95"/>
+      <c r="C8" s="110" t="s">
+        <v>161</v>
+      </c>
+      <c r="D8" s="111"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="113"/>
+      <c r="G8" s="115"/>
+      <c r="H8" s="115"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="116"/>
+      <c r="K8" s="115"/>
+      <c r="L8" s="115"/>
+      <c r="M8" s="112"/>
+      <c r="N8" s="116"/>
+      <c r="O8" s="115"/>
+      <c r="P8" s="115"/>
+      <c r="Q8" s="112"/>
+      <c r="R8" s="116"/>
+      <c r="S8" s="117"/>
       <c r="U8" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="94"/>
-      <c r="C9" s="101"/>
-      <c r="D9" s="102"/>
-      <c r="E9" s="103"/>
-      <c r="F9" s="107"/>
-      <c r="G9" s="105"/>
-      <c r="H9" s="106"/>
-      <c r="I9" s="103"/>
-      <c r="J9" s="107"/>
-      <c r="K9" s="106"/>
-      <c r="L9" s="106"/>
-      <c r="M9" s="103"/>
-      <c r="N9" s="107"/>
-      <c r="O9" s="106"/>
-      <c r="P9" s="106"/>
-      <c r="Q9" s="103"/>
-      <c r="R9" s="107"/>
-      <c r="S9" s="108"/>
+      <c r="B9" s="95"/>
+      <c r="C9" s="102"/>
+      <c r="D9" s="103"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="108"/>
+      <c r="G9" s="106"/>
+      <c r="H9" s="107"/>
+      <c r="I9" s="104"/>
+      <c r="J9" s="108"/>
+      <c r="K9" s="107"/>
+      <c r="L9" s="107"/>
+      <c r="M9" s="104"/>
+      <c r="N9" s="108"/>
+      <c r="O9" s="107"/>
+      <c r="P9" s="107"/>
+      <c r="Q9" s="104"/>
+      <c r="R9" s="108"/>
+      <c r="S9" s="109"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="94"/>
-      <c r="C10" s="109" t="s">
-        <v>156</v>
-      </c>
-      <c r="D10" s="110"/>
-      <c r="E10" s="111"/>
-      <c r="F10" s="115"/>
-      <c r="G10" s="113"/>
-      <c r="H10" s="113"/>
-      <c r="I10" s="111"/>
-      <c r="J10" s="115"/>
-      <c r="K10" s="114"/>
-      <c r="L10" s="114"/>
-      <c r="M10" s="111"/>
-      <c r="N10" s="115"/>
-      <c r="O10" s="114"/>
-      <c r="P10" s="114"/>
-      <c r="Q10" s="111"/>
-      <c r="R10" s="115"/>
-      <c r="S10" s="116"/>
+      <c r="B10" s="95"/>
+      <c r="C10" s="110" t="s">
+        <v>163</v>
+      </c>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="116"/>
+      <c r="G10" s="114"/>
+      <c r="H10" s="114"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="116"/>
+      <c r="K10" s="115"/>
+      <c r="L10" s="115"/>
+      <c r="M10" s="112"/>
+      <c r="N10" s="116"/>
+      <c r="O10" s="115"/>
+      <c r="P10" s="115"/>
+      <c r="Q10" s="112"/>
+      <c r="R10" s="116"/>
+      <c r="S10" s="117"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="118"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="120"/>
-      <c r="E11" s="121"/>
-      <c r="F11" s="122"/>
-      <c r="G11" s="123"/>
-      <c r="H11" s="123"/>
-      <c r="I11" s="121"/>
-      <c r="J11" s="122"/>
-      <c r="K11" s="124"/>
-      <c r="L11" s="124"/>
-      <c r="M11" s="121"/>
-      <c r="N11" s="122"/>
-      <c r="O11" s="124"/>
-      <c r="P11" s="124"/>
-      <c r="Q11" s="121"/>
-      <c r="R11" s="122"/>
-      <c r="S11" s="125"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="120"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="122"/>
+      <c r="F11" s="123"/>
+      <c r="G11" s="124"/>
+      <c r="H11" s="124"/>
+      <c r="I11" s="122"/>
+      <c r="J11" s="123"/>
+      <c r="K11" s="125"/>
+      <c r="L11" s="125"/>
+      <c r="M11" s="122"/>
+      <c r="N11" s="123"/>
+      <c r="O11" s="125"/>
+      <c r="P11" s="125"/>
+      <c r="Q11" s="122"/>
+      <c r="R11" s="123"/>
+      <c r="S11" s="126"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="81" t="s">
-        <v>157</v>
-      </c>
-      <c r="C12" s="82" t="s">
-        <v>158</v>
-      </c>
-      <c r="D12" s="95"/>
-      <c r="E12" s="96"/>
-      <c r="F12" s="99"/>
-      <c r="G12" s="98"/>
-      <c r="H12" s="126"/>
-      <c r="I12" s="127"/>
-      <c r="J12" s="99"/>
-      <c r="K12" s="98"/>
-      <c r="L12" s="98"/>
-      <c r="M12" s="96"/>
-      <c r="N12" s="99"/>
-      <c r="O12" s="98"/>
-      <c r="P12" s="98"/>
-      <c r="Q12" s="96"/>
-      <c r="R12" s="99"/>
-      <c r="S12" s="100"/>
+      <c r="B12" s="82" t="s">
+        <v>164</v>
+      </c>
+      <c r="C12" s="83" t="s">
+        <v>165</v>
+      </c>
+      <c r="D12" s="96"/>
+      <c r="E12" s="97"/>
+      <c r="F12" s="100"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="127"/>
+      <c r="I12" s="128"/>
+      <c r="J12" s="100"/>
+      <c r="K12" s="99"/>
+      <c r="L12" s="99"/>
+      <c r="M12" s="97"/>
+      <c r="N12" s="100"/>
+      <c r="O12" s="99"/>
+      <c r="P12" s="99"/>
+      <c r="Q12" s="97"/>
+      <c r="R12" s="100"/>
+      <c r="S12" s="101"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="94"/>
-      <c r="C13" s="101"/>
-      <c r="D13" s="102"/>
-      <c r="E13" s="103"/>
-      <c r="F13" s="107"/>
-      <c r="G13" s="106"/>
-      <c r="H13" s="106"/>
-      <c r="I13" s="103"/>
-      <c r="J13" s="104"/>
-      <c r="K13" s="106"/>
-      <c r="L13" s="106"/>
-      <c r="M13" s="103"/>
-      <c r="N13" s="107"/>
-      <c r="O13" s="106"/>
-      <c r="P13" s="106"/>
-      <c r="Q13" s="103"/>
-      <c r="R13" s="107"/>
-      <c r="S13" s="108"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="102"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="108"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="107"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="105"/>
+      <c r="K13" s="107"/>
+      <c r="L13" s="107"/>
+      <c r="M13" s="104"/>
+      <c r="N13" s="108"/>
+      <c r="O13" s="107"/>
+      <c r="P13" s="107"/>
+      <c r="Q13" s="104"/>
+      <c r="R13" s="108"/>
+      <c r="S13" s="109"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="94"/>
-      <c r="C14" s="109" t="s">
-        <v>159</v>
-      </c>
-      <c r="D14" s="128"/>
-      <c r="E14" s="111"/>
-      <c r="F14" s="115"/>
-      <c r="G14" s="114"/>
-      <c r="H14" s="113"/>
-      <c r="I14" s="111"/>
-      <c r="J14" s="115"/>
-      <c r="K14" s="114"/>
-      <c r="L14" s="114"/>
-      <c r="M14" s="111"/>
-      <c r="N14" s="115"/>
-      <c r="O14" s="114"/>
-      <c r="P14" s="114"/>
-      <c r="Q14" s="111"/>
-      <c r="R14" s="115"/>
-      <c r="S14" s="116"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="110" t="s">
+        <v>166</v>
+      </c>
+      <c r="D14" s="129"/>
+      <c r="E14" s="112"/>
+      <c r="F14" s="116"/>
+      <c r="G14" s="115"/>
+      <c r="H14" s="114"/>
+      <c r="I14" s="112"/>
+      <c r="J14" s="116"/>
+      <c r="K14" s="115"/>
+      <c r="L14" s="115"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="116"/>
+      <c r="O14" s="115"/>
+      <c r="P14" s="115"/>
+      <c r="Q14" s="112"/>
+      <c r="R14" s="116"/>
+      <c r="S14" s="117"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="94"/>
-      <c r="C15" s="101"/>
-      <c r="D15" s="102"/>
-      <c r="E15" s="103"/>
-      <c r="F15" s="107"/>
-      <c r="G15" s="106"/>
-      <c r="H15" s="106"/>
-      <c r="I15" s="129"/>
-      <c r="J15" s="104"/>
-      <c r="K15" s="106"/>
-      <c r="L15" s="106"/>
-      <c r="M15" s="103"/>
-      <c r="N15" s="107"/>
-      <c r="O15" s="106"/>
-      <c r="P15" s="106"/>
-      <c r="Q15" s="103"/>
-      <c r="R15" s="107"/>
-      <c r="S15" s="108"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="102"/>
+      <c r="D15" s="103"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="108"/>
+      <c r="G15" s="107"/>
+      <c r="H15" s="107"/>
+      <c r="I15" s="130"/>
+      <c r="J15" s="105"/>
+      <c r="K15" s="107"/>
+      <c r="L15" s="107"/>
+      <c r="M15" s="104"/>
+      <c r="N15" s="108"/>
+      <c r="O15" s="107"/>
+      <c r="P15" s="107"/>
+      <c r="Q15" s="104"/>
+      <c r="R15" s="108"/>
+      <c r="S15" s="109"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="94"/>
-      <c r="C16" s="109" t="s">
-        <v>160</v>
-      </c>
-      <c r="D16" s="110"/>
-      <c r="E16" s="111"/>
-      <c r="F16" s="115"/>
-      <c r="G16" s="114"/>
-      <c r="H16" s="113"/>
-      <c r="I16" s="130"/>
-      <c r="J16" s="115"/>
-      <c r="K16" s="114"/>
-      <c r="L16" s="114"/>
-      <c r="M16" s="111"/>
-      <c r="N16" s="115"/>
-      <c r="O16" s="114"/>
-      <c r="P16" s="114"/>
-      <c r="Q16" s="111"/>
-      <c r="R16" s="115"/>
-      <c r="S16" s="116"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="110" t="s">
+        <v>167</v>
+      </c>
+      <c r="D16" s="111"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="116"/>
+      <c r="G16" s="115"/>
+      <c r="H16" s="114"/>
+      <c r="I16" s="131"/>
+      <c r="J16" s="116"/>
+      <c r="K16" s="115"/>
+      <c r="L16" s="115"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="116"/>
+      <c r="O16" s="115"/>
+      <c r="P16" s="115"/>
+      <c r="Q16" s="112"/>
+      <c r="R16" s="116"/>
+      <c r="S16" s="117"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="118"/>
-      <c r="C17" s="119"/>
-      <c r="D17" s="120"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="124"/>
-      <c r="H17" s="124"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="131"/>
-      <c r="K17" s="123"/>
-      <c r="L17" s="124"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="122"/>
-      <c r="O17" s="124"/>
-      <c r="P17" s="124"/>
-      <c r="Q17" s="121"/>
-      <c r="R17" s="122"/>
-      <c r="S17" s="125"/>
+      <c r="B17" s="119"/>
+      <c r="C17" s="120"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="122"/>
+      <c r="F17" s="123"/>
+      <c r="G17" s="125"/>
+      <c r="H17" s="125"/>
+      <c r="I17" s="122"/>
+      <c r="J17" s="132"/>
+      <c r="K17" s="124"/>
+      <c r="L17" s="125"/>
+      <c r="M17" s="122"/>
+      <c r="N17" s="123"/>
+      <c r="O17" s="125"/>
+      <c r="P17" s="125"/>
+      <c r="Q17" s="122"/>
+      <c r="R17" s="123"/>
+      <c r="S17" s="126"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="83" t="s">
-        <v>161</v>
-      </c>
-      <c r="C18" s="82" t="s">
-        <v>162</v>
-      </c>
-      <c r="D18" s="95"/>
-      <c r="E18" s="96"/>
-      <c r="F18" s="99"/>
-      <c r="G18" s="98"/>
-      <c r="H18" s="98"/>
-      <c r="I18" s="127"/>
-      <c r="J18" s="99"/>
-      <c r="K18" s="98"/>
-      <c r="L18" s="98"/>
-      <c r="M18" s="96"/>
-      <c r="N18" s="99"/>
-      <c r="O18" s="98"/>
-      <c r="P18" s="98"/>
-      <c r="Q18" s="96"/>
-      <c r="R18" s="99"/>
-      <c r="S18" s="100"/>
+      <c r="B18" s="84" t="s">
+        <v>168</v>
+      </c>
+      <c r="C18" s="83" t="s">
+        <v>169</v>
+      </c>
+      <c r="D18" s="96"/>
+      <c r="E18" s="97"/>
+      <c r="F18" s="100"/>
+      <c r="G18" s="99"/>
+      <c r="H18" s="99"/>
+      <c r="I18" s="128"/>
+      <c r="J18" s="100"/>
+      <c r="K18" s="99"/>
+      <c r="L18" s="99"/>
+      <c r="M18" s="97"/>
+      <c r="N18" s="100"/>
+      <c r="O18" s="99"/>
+      <c r="P18" s="99"/>
+      <c r="Q18" s="97"/>
+      <c r="R18" s="100"/>
+      <c r="S18" s="101"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="94"/>
-      <c r="C19" s="101"/>
-      <c r="D19" s="102"/>
-      <c r="E19" s="103"/>
-      <c r="F19" s="107"/>
-      <c r="G19" s="105"/>
-      <c r="H19" s="106"/>
-      <c r="I19" s="103"/>
-      <c r="J19" s="107"/>
-      <c r="K19" s="106"/>
-      <c r="L19" s="106"/>
-      <c r="M19" s="103"/>
-      <c r="N19" s="107"/>
-      <c r="O19" s="106"/>
-      <c r="P19" s="106"/>
-      <c r="Q19" s="103"/>
-      <c r="R19" s="107"/>
-      <c r="S19" s="108"/>
+      <c r="B19" s="95"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="103"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="108"/>
+      <c r="G19" s="106"/>
+      <c r="H19" s="107"/>
+      <c r="I19" s="104"/>
+      <c r="J19" s="108"/>
+      <c r="K19" s="107"/>
+      <c r="L19" s="107"/>
+      <c r="M19" s="104"/>
+      <c r="N19" s="108"/>
+      <c r="O19" s="107"/>
+      <c r="P19" s="107"/>
+      <c r="Q19" s="104"/>
+      <c r="R19" s="108"/>
+      <c r="S19" s="109"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="94"/>
-      <c r="C20" s="109" t="s">
-        <v>163</v>
-      </c>
-      <c r="D20" s="110"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="115"/>
-      <c r="G20" s="114"/>
-      <c r="H20" s="114"/>
-      <c r="I20" s="130"/>
-      <c r="J20" s="112"/>
-      <c r="K20" s="113"/>
-      <c r="L20" s="113"/>
-      <c r="M20" s="111"/>
-      <c r="N20" s="115"/>
-      <c r="O20" s="114"/>
-      <c r="P20" s="114"/>
-      <c r="Q20" s="111"/>
-      <c r="R20" s="115"/>
-      <c r="S20" s="116"/>
+      <c r="B20" s="95"/>
+      <c r="C20" s="110" t="s">
+        <v>170</v>
+      </c>
+      <c r="D20" s="111"/>
+      <c r="E20" s="112"/>
+      <c r="F20" s="116"/>
+      <c r="G20" s="115"/>
+      <c r="H20" s="115"/>
+      <c r="I20" s="131"/>
+      <c r="J20" s="113"/>
+      <c r="K20" s="114"/>
+      <c r="L20" s="114"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="116"/>
+      <c r="O20" s="115"/>
+      <c r="P20" s="115"/>
+      <c r="Q20" s="112"/>
+      <c r="R20" s="116"/>
+      <c r="S20" s="117"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="94"/>
-      <c r="C21" s="101"/>
-      <c r="D21" s="102"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="107"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="106"/>
-      <c r="I21" s="103"/>
-      <c r="J21" s="107"/>
-      <c r="K21" s="106"/>
-      <c r="L21" s="106"/>
-      <c r="M21" s="103"/>
-      <c r="N21" s="132"/>
-      <c r="O21" s="106"/>
-      <c r="P21" s="106"/>
-      <c r="Q21" s="103"/>
-      <c r="R21" s="107"/>
-      <c r="S21" s="108"/>
+      <c r="B21" s="95"/>
+      <c r="C21" s="102"/>
+      <c r="D21" s="103"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="108"/>
+      <c r="G21" s="107"/>
+      <c r="H21" s="107"/>
+      <c r="I21" s="104"/>
+      <c r="J21" s="108"/>
+      <c r="K21" s="107"/>
+      <c r="L21" s="107"/>
+      <c r="M21" s="104"/>
+      <c r="N21" s="133"/>
+      <c r="O21" s="107"/>
+      <c r="P21" s="107"/>
+      <c r="Q21" s="104"/>
+      <c r="R21" s="108"/>
+      <c r="S21" s="109"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="94"/>
-      <c r="C22" s="109" t="s">
-        <v>164</v>
-      </c>
-      <c r="D22" s="110"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="115"/>
-      <c r="G22" s="114"/>
-      <c r="H22" s="114"/>
-      <c r="I22" s="111"/>
-      <c r="J22" s="115"/>
-      <c r="K22" s="113"/>
-      <c r="L22" s="113"/>
-      <c r="M22" s="111"/>
-      <c r="N22" s="115"/>
-      <c r="O22" s="114"/>
-      <c r="P22" s="114"/>
-      <c r="Q22" s="111"/>
-      <c r="R22" s="115"/>
-      <c r="S22" s="116"/>
+      <c r="B22" s="95"/>
+      <c r="C22" s="110" t="s">
+        <v>171</v>
+      </c>
+      <c r="D22" s="111"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="116"/>
+      <c r="G22" s="115"/>
+      <c r="H22" s="115"/>
+      <c r="I22" s="112"/>
+      <c r="J22" s="116"/>
+      <c r="K22" s="114"/>
+      <c r="L22" s="114"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="116"/>
+      <c r="O22" s="115"/>
+      <c r="P22" s="115"/>
+      <c r="Q22" s="112"/>
+      <c r="R22" s="116"/>
+      <c r="S22" s="117"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="118"/>
-      <c r="C23" s="119"/>
-      <c r="D23" s="120"/>
-      <c r="E23" s="121"/>
-      <c r="F23" s="122"/>
-      <c r="G23" s="124"/>
-      <c r="H23" s="124"/>
-      <c r="I23" s="121"/>
-      <c r="J23" s="122"/>
-      <c r="K23" s="124"/>
-      <c r="L23" s="124"/>
-      <c r="M23" s="121"/>
-      <c r="N23" s="122"/>
-      <c r="O23" s="124"/>
-      <c r="P23" s="124"/>
-      <c r="Q23" s="121"/>
-      <c r="R23" s="122"/>
-      <c r="S23" s="125"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="120"/>
+      <c r="D23" s="121"/>
+      <c r="E23" s="122"/>
+      <c r="F23" s="123"/>
+      <c r="G23" s="125"/>
+      <c r="H23" s="125"/>
+      <c r="I23" s="122"/>
+      <c r="J23" s="123"/>
+      <c r="K23" s="125"/>
+      <c r="L23" s="125"/>
+      <c r="M23" s="122"/>
+      <c r="N23" s="123"/>
+      <c r="O23" s="125"/>
+      <c r="P23" s="125"/>
+      <c r="Q23" s="122"/>
+      <c r="R23" s="123"/>
+      <c r="S23" s="126"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="83" t="s">
-        <v>165</v>
-      </c>
-      <c r="C24" s="82" t="s">
-        <v>166</v>
-      </c>
-      <c r="D24" s="95"/>
-      <c r="E24" s="96"/>
-      <c r="F24" s="99"/>
-      <c r="G24" s="98"/>
-      <c r="H24" s="98"/>
-      <c r="I24" s="96"/>
-      <c r="J24" s="99"/>
-      <c r="K24" s="98"/>
-      <c r="L24" s="98"/>
-      <c r="M24" s="127"/>
-      <c r="N24" s="97"/>
-      <c r="O24" s="126"/>
-      <c r="P24" s="126"/>
-      <c r="Q24" s="96"/>
-      <c r="R24" s="99"/>
-      <c r="S24" s="100"/>
+      <c r="B24" s="84" t="s">
+        <v>172</v>
+      </c>
+      <c r="C24" s="83" t="s">
+        <v>173</v>
+      </c>
+      <c r="D24" s="96"/>
+      <c r="E24" s="97"/>
+      <c r="F24" s="100"/>
+      <c r="G24" s="99"/>
+      <c r="H24" s="99"/>
+      <c r="I24" s="97"/>
+      <c r="J24" s="100"/>
+      <c r="K24" s="99"/>
+      <c r="L24" s="99"/>
+      <c r="M24" s="128"/>
+      <c r="N24" s="98"/>
+      <c r="O24" s="127"/>
+      <c r="P24" s="127"/>
+      <c r="Q24" s="97"/>
+      <c r="R24" s="100"/>
+      <c r="S24" s="101"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="94"/>
-      <c r="C25" s="101"/>
-      <c r="D25" s="102"/>
-      <c r="E25" s="103"/>
-      <c r="F25" s="107"/>
-      <c r="G25" s="106"/>
-      <c r="H25" s="106"/>
-      <c r="I25" s="103"/>
-      <c r="J25" s="107"/>
-      <c r="K25" s="106"/>
-      <c r="L25" s="106"/>
-      <c r="M25" s="103"/>
-      <c r="N25" s="107"/>
-      <c r="O25" s="106"/>
-      <c r="P25" s="106"/>
-      <c r="Q25" s="103"/>
-      <c r="R25" s="107"/>
-      <c r="S25" s="108"/>
+      <c r="B25" s="95"/>
+      <c r="C25" s="102"/>
+      <c r="D25" s="103"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="108"/>
+      <c r="G25" s="107"/>
+      <c r="H25" s="107"/>
+      <c r="I25" s="104"/>
+      <c r="J25" s="108"/>
+      <c r="K25" s="107"/>
+      <c r="L25" s="107"/>
+      <c r="M25" s="104"/>
+      <c r="N25" s="108"/>
+      <c r="O25" s="107"/>
+      <c r="P25" s="107"/>
+      <c r="Q25" s="104"/>
+      <c r="R25" s="108"/>
+      <c r="S25" s="109"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="94"/>
-      <c r="C26" s="109" t="s">
-        <v>167</v>
-      </c>
-      <c r="D26" s="110"/>
-      <c r="E26" s="111"/>
-      <c r="F26" s="115"/>
-      <c r="G26" s="114"/>
-      <c r="H26" s="114"/>
-      <c r="I26" s="111"/>
-      <c r="J26" s="115"/>
-      <c r="K26" s="114"/>
-      <c r="L26" s="114"/>
-      <c r="M26" s="111"/>
-      <c r="N26" s="115"/>
-      <c r="O26" s="113"/>
-      <c r="P26" s="113"/>
-      <c r="Q26" s="111"/>
-      <c r="R26" s="115"/>
-      <c r="S26" s="116"/>
+      <c r="B26" s="95"/>
+      <c r="C26" s="110" t="s">
+        <v>174</v>
+      </c>
+      <c r="D26" s="111"/>
+      <c r="E26" s="112"/>
+      <c r="F26" s="116"/>
+      <c r="G26" s="115"/>
+      <c r="H26" s="115"/>
+      <c r="I26" s="112"/>
+      <c r="J26" s="116"/>
+      <c r="K26" s="115"/>
+      <c r="L26" s="115"/>
+      <c r="M26" s="112"/>
+      <c r="N26" s="116"/>
+      <c r="O26" s="114"/>
+      <c r="P26" s="114"/>
+      <c r="Q26" s="112"/>
+      <c r="R26" s="116"/>
+      <c r="S26" s="117"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="94"/>
-      <c r="C27" s="101"/>
-      <c r="D27" s="102"/>
-      <c r="E27" s="103"/>
-      <c r="F27" s="107"/>
-      <c r="G27" s="106"/>
-      <c r="H27" s="106"/>
-      <c r="I27" s="103"/>
-      <c r="J27" s="107"/>
-      <c r="K27" s="106"/>
-      <c r="L27" s="106"/>
-      <c r="M27" s="103"/>
-      <c r="N27" s="107"/>
-      <c r="O27" s="106"/>
-      <c r="P27" s="106"/>
-      <c r="Q27" s="103"/>
-      <c r="R27" s="107"/>
-      <c r="S27" s="108"/>
+      <c r="B27" s="95"/>
+      <c r="C27" s="102"/>
+      <c r="D27" s="103"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="108"/>
+      <c r="G27" s="107"/>
+      <c r="H27" s="107"/>
+      <c r="I27" s="104"/>
+      <c r="J27" s="108"/>
+      <c r="K27" s="107"/>
+      <c r="L27" s="107"/>
+      <c r="M27" s="104"/>
+      <c r="N27" s="108"/>
+      <c r="O27" s="107"/>
+      <c r="P27" s="107"/>
+      <c r="Q27" s="104"/>
+      <c r="R27" s="108"/>
+      <c r="S27" s="109"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="94"/>
-      <c r="C28" s="109" t="s">
-        <v>168</v>
-      </c>
-      <c r="D28" s="110"/>
-      <c r="E28" s="111"/>
-      <c r="F28" s="115"/>
-      <c r="G28" s="114"/>
-      <c r="H28" s="114"/>
-      <c r="I28" s="111"/>
-      <c r="J28" s="115"/>
-      <c r="K28" s="114"/>
-      <c r="L28" s="114"/>
-      <c r="M28" s="111"/>
-      <c r="N28" s="115"/>
-      <c r="O28" s="114"/>
-      <c r="P28" s="113"/>
-      <c r="Q28" s="130"/>
-      <c r="R28" s="115"/>
-      <c r="S28" s="116"/>
+      <c r="B28" s="95"/>
+      <c r="C28" s="110" t="s">
+        <v>175</v>
+      </c>
+      <c r="D28" s="111"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="116"/>
+      <c r="G28" s="115"/>
+      <c r="H28" s="115"/>
+      <c r="I28" s="112"/>
+      <c r="J28" s="116"/>
+      <c r="K28" s="115"/>
+      <c r="L28" s="115"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="116"/>
+      <c r="O28" s="115"/>
+      <c r="P28" s="114"/>
+      <c r="Q28" s="131"/>
+      <c r="R28" s="116"/>
+      <c r="S28" s="117"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="94"/>
-      <c r="C29" s="88"/>
-      <c r="D29" s="133"/>
-      <c r="E29" s="134"/>
-      <c r="F29" s="135"/>
-      <c r="G29" s="136"/>
-      <c r="H29" s="137"/>
-      <c r="I29" s="134"/>
-      <c r="J29" s="135"/>
-      <c r="K29" s="136"/>
-      <c r="L29" s="137"/>
-      <c r="M29" s="134"/>
-      <c r="N29" s="138"/>
-      <c r="O29" s="137"/>
-      <c r="P29" s="136"/>
-      <c r="Q29" s="134"/>
-      <c r="R29" s="135"/>
-      <c r="S29" s="139"/>
+      <c r="B29" s="95"/>
+      <c r="C29" s="89"/>
+      <c r="D29" s="134"/>
+      <c r="E29" s="135"/>
+      <c r="F29" s="136"/>
+      <c r="G29" s="137"/>
+      <c r="H29" s="138"/>
+      <c r="I29" s="135"/>
+      <c r="J29" s="136"/>
+      <c r="K29" s="137"/>
+      <c r="L29" s="138"/>
+      <c r="M29" s="135"/>
+      <c r="N29" s="139"/>
+      <c r="O29" s="138"/>
+      <c r="P29" s="137"/>
+      <c r="Q29" s="135"/>
+      <c r="R29" s="136"/>
+      <c r="S29" s="140"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="140" t="s">
+      <c r="B30" s="141" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="141" t="s">
-        <v>112</v>
-      </c>
-      <c r="D30" s="95"/>
-      <c r="E30" s="142"/>
-      <c r="F30" s="143"/>
-      <c r="G30" s="143"/>
-      <c r="H30" s="144"/>
-      <c r="I30" s="145"/>
-      <c r="J30" s="143"/>
-      <c r="K30" s="143"/>
-      <c r="L30" s="144"/>
-      <c r="M30" s="145"/>
-      <c r="N30" s="143"/>
-      <c r="O30" s="144"/>
-      <c r="P30" s="143"/>
-      <c r="Q30" s="145"/>
-      <c r="R30" s="143"/>
-      <c r="S30" s="146"/>
+      <c r="C30" s="142" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" s="96"/>
+      <c r="E30" s="143"/>
+      <c r="F30" s="144"/>
+      <c r="G30" s="144"/>
+      <c r="H30" s="145"/>
+      <c r="I30" s="146"/>
+      <c r="J30" s="144"/>
+      <c r="K30" s="144"/>
+      <c r="L30" s="145"/>
+      <c r="M30" s="146"/>
+      <c r="N30" s="144"/>
+      <c r="O30" s="145"/>
+      <c r="P30" s="144"/>
+      <c r="Q30" s="146"/>
+      <c r="R30" s="144"/>
+      <c r="S30" s="147"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="147"/>
-      <c r="C31" s="148"/>
-      <c r="D31" s="102"/>
-      <c r="E31" s="149"/>
-      <c r="F31" s="150"/>
-      <c r="G31" s="150"/>
-      <c r="H31" s="151"/>
-      <c r="I31" s="152"/>
-      <c r="J31" s="150"/>
-      <c r="K31" s="153"/>
-      <c r="L31" s="151"/>
-      <c r="M31" s="152"/>
-      <c r="N31" s="150"/>
-      <c r="O31" s="151"/>
-      <c r="P31" s="150"/>
-      <c r="Q31" s="152"/>
-      <c r="R31" s="150"/>
-      <c r="S31" s="108"/>
+      <c r="B31" s="148"/>
+      <c r="C31" s="149"/>
+      <c r="D31" s="103"/>
+      <c r="E31" s="150"/>
+      <c r="F31" s="151"/>
+      <c r="G31" s="151"/>
+      <c r="H31" s="152"/>
+      <c r="I31" s="153"/>
+      <c r="J31" s="151"/>
+      <c r="K31" s="154"/>
+      <c r="L31" s="152"/>
+      <c r="M31" s="153"/>
+      <c r="N31" s="151"/>
+      <c r="O31" s="152"/>
+      <c r="P31" s="151"/>
+      <c r="Q31" s="153"/>
+      <c r="R31" s="151"/>
+      <c r="S31" s="109"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="147"/>
-      <c r="C32" s="148" t="s">
+      <c r="B32" s="148"/>
+      <c r="C32" s="149" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="110"/>
-      <c r="E32" s="154"/>
-      <c r="F32" s="155"/>
-      <c r="G32" s="155"/>
-      <c r="H32" s="156"/>
-      <c r="I32" s="157"/>
-      <c r="J32" s="155"/>
-      <c r="K32" s="155"/>
-      <c r="L32" s="156"/>
-      <c r="M32" s="157"/>
-      <c r="N32" s="155"/>
-      <c r="O32" s="156"/>
-      <c r="P32" s="155"/>
-      <c r="Q32" s="157"/>
-      <c r="R32" s="155"/>
-      <c r="S32" s="158"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="155"/>
+      <c r="F32" s="156"/>
+      <c r="G32" s="156"/>
+      <c r="H32" s="157"/>
+      <c r="I32" s="158"/>
+      <c r="J32" s="156"/>
+      <c r="K32" s="156"/>
+      <c r="L32" s="157"/>
+      <c r="M32" s="158"/>
+      <c r="N32" s="156"/>
+      <c r="O32" s="157"/>
+      <c r="P32" s="156"/>
+      <c r="Q32" s="158"/>
+      <c r="R32" s="156"/>
+      <c r="S32" s="159"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="147"/>
-      <c r="C33" s="148"/>
-      <c r="D33" s="102"/>
-      <c r="E33" s="149"/>
-      <c r="F33" s="153"/>
-      <c r="G33" s="150"/>
-      <c r="H33" s="159"/>
-      <c r="I33" s="160"/>
-      <c r="J33" s="150"/>
-      <c r="K33" s="153"/>
-      <c r="L33" s="151"/>
-      <c r="M33" s="152"/>
-      <c r="N33" s="150"/>
-      <c r="O33" s="151"/>
-      <c r="P33" s="150"/>
-      <c r="Q33" s="152"/>
-      <c r="R33" s="150"/>
-      <c r="S33" s="108"/>
+      <c r="B33" s="148"/>
+      <c r="C33" s="149"/>
+      <c r="D33" s="103"/>
+      <c r="E33" s="150"/>
+      <c r="F33" s="154"/>
+      <c r="G33" s="151"/>
+      <c r="H33" s="160"/>
+      <c r="I33" s="161"/>
+      <c r="J33" s="151"/>
+      <c r="K33" s="154"/>
+      <c r="L33" s="152"/>
+      <c r="M33" s="153"/>
+      <c r="N33" s="151"/>
+      <c r="O33" s="152"/>
+      <c r="P33" s="151"/>
+      <c r="Q33" s="153"/>
+      <c r="R33" s="151"/>
+      <c r="S33" s="109"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="147"/>
-      <c r="C34" s="101" t="s">
-        <v>169</v>
-      </c>
-      <c r="D34" s="133"/>
-      <c r="E34" s="161"/>
-      <c r="F34" s="162"/>
-      <c r="G34" s="162"/>
-      <c r="H34" s="163"/>
-      <c r="I34" s="164"/>
-      <c r="J34" s="162"/>
-      <c r="K34" s="162"/>
-      <c r="L34" s="163"/>
-      <c r="M34" s="164"/>
-      <c r="N34" s="162"/>
-      <c r="O34" s="163"/>
-      <c r="P34" s="162"/>
-      <c r="Q34" s="164"/>
-      <c r="R34" s="162"/>
-      <c r="S34" s="165"/>
-      <c r="U34" s="166"/>
-      <c r="V34" s="167" t="s">
-        <v>170</v>
+      <c r="B34" s="148"/>
+      <c r="C34" s="102" t="s">
+        <v>176</v>
+      </c>
+      <c r="D34" s="134"/>
+      <c r="E34" s="162"/>
+      <c r="F34" s="163"/>
+      <c r="G34" s="163"/>
+      <c r="H34" s="164"/>
+      <c r="I34" s="165"/>
+      <c r="J34" s="163"/>
+      <c r="K34" s="163"/>
+      <c r="L34" s="164"/>
+      <c r="M34" s="165"/>
+      <c r="N34" s="163"/>
+      <c r="O34" s="164"/>
+      <c r="P34" s="163"/>
+      <c r="Q34" s="165"/>
+      <c r="R34" s="163"/>
+      <c r="S34" s="166"/>
+      <c r="U34" s="167"/>
+      <c r="V34" s="168" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="168"/>
-      <c r="C35" s="169"/>
-      <c r="D35" s="120"/>
-      <c r="E35" s="170"/>
-      <c r="F35" s="171"/>
-      <c r="G35" s="171"/>
-      <c r="H35" s="172"/>
-      <c r="I35" s="173"/>
-      <c r="J35" s="171"/>
-      <c r="K35" s="171"/>
-      <c r="L35" s="172"/>
-      <c r="M35" s="173"/>
-      <c r="N35" s="171"/>
-      <c r="O35" s="172"/>
-      <c r="P35" s="171"/>
-      <c r="Q35" s="173"/>
-      <c r="R35" s="171"/>
-      <c r="S35" s="125"/>
-      <c r="U35" s="174"/>
-      <c r="V35" s="175" t="s">
-        <v>171</v>
+      <c r="B35" s="169"/>
+      <c r="C35" s="170"/>
+      <c r="D35" s="121"/>
+      <c r="E35" s="171"/>
+      <c r="F35" s="172"/>
+      <c r="G35" s="172"/>
+      <c r="H35" s="173"/>
+      <c r="I35" s="174"/>
+      <c r="J35" s="172"/>
+      <c r="K35" s="172"/>
+      <c r="L35" s="173"/>
+      <c r="M35" s="174"/>
+      <c r="N35" s="172"/>
+      <c r="O35" s="173"/>
+      <c r="P35" s="172"/>
+      <c r="Q35" s="174"/>
+      <c r="R35" s="172"/>
+      <c r="S35" s="126"/>
+      <c r="U35" s="175"/>
+      <c r="V35" s="176" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/HoferL-JournalPlanif-M5.xlsx
+++ b/Documentation/HoferL-JournalPlanif-M5.xlsx
@@ -6,10 +6,10 @@
     <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Journal" sheetId="1" state="visible" r:id="rId4"/>
-    <sheet name="SommeParJours" sheetId="2" state="visible" r:id="rId5"/>
-    <sheet name="Plannification" sheetId="3" state="visible" r:id="rId6"/>
-    <sheet name="PlanificationExemple" sheetId="4" state="hidden" r:id="rId7"/>
+    <sheet name="Journal" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="SommeParJours" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Plannification" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="PlanificationExemple" sheetId="4" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$B$2:$H$33</definedName>
@@ -32,30 +32,8 @@
 </connections>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
   <si>
     <t>date</t>
   </si>
@@ -325,6 +303,9 @@
   </si>
   <si>
     <t xml:space="preserve">Finalisation de la documentation "Proof Of Concept" du systeme de gestion des scans.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commencement du manuel utilisateur. Documentation des différents affichages</t>
   </si>
   <si>
     <t>Phases</t>
@@ -1563,7 +1544,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="177">
+  <cellXfs count="175">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1613,13 +1594,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="20" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3718,8 +3693,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E65">
-  <autoFilter ref="B2:E65"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E66">
+  <autoFilter ref="B2:E66"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -4285,11 +4260,11 @@
         <f>types[[#This Row],[somme]]/$H$11</f>
         <v>0.019687192387618943</v>
       </c>
-      <c r="J3" s="12" t="str" cm="1">
+      <c r="J3" s="12" t="str">
         <f t="array" ref="J3:J9">_xlfn._xlws.FILTER(G3:G10,H3:H10&gt;0)</f>
         <v>Cours</v>
       </c>
-      <c r="K3" s="13" cm="1">
+      <c r="K3" s="13">
         <f t="array" ref="K3:K9">_xlfn._xlws.FILTER(H3:H10,H3:H10&gt;0)</f>
         <v>3</v>
       </c>
@@ -5201,10 +5176,10 @@
       <c r="C58" s="21">
         <v>0.125</v>
       </c>
-      <c r="D58" s="22" t="s">
+      <c r="D58" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E58" s="23" t="s">
+      <c r="E58" s="8" t="s">
         <v>83</v>
       </c>
     </row>
@@ -5215,10 +5190,10 @@
       <c r="C59" s="21">
         <v>0.083333333333333329</v>
       </c>
-      <c r="D59" s="22" t="s">
+      <c r="D59" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E59" s="23" t="s">
+      <c r="E59" s="8" t="s">
         <v>83</v>
       </c>
     </row>
@@ -5229,10 +5204,10 @@
       <c r="C60" s="21">
         <v>0.020833333333333332</v>
       </c>
-      <c r="D60" s="22" t="s">
+      <c r="D60" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E60" s="23" t="s">
+      <c r="E60" s="8" t="s">
         <v>84</v>
       </c>
     </row>
@@ -5243,10 +5218,10 @@
       <c r="C61" s="21">
         <v>0.041666666666666664</v>
       </c>
-      <c r="D61" s="22" t="s">
+      <c r="D61" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E61" s="23" t="s">
+      <c r="E61" s="8" t="s">
         <v>85</v>
       </c>
     </row>
@@ -5254,13 +5229,13 @@
       <c r="B62" s="20">
         <v>46136</v>
       </c>
-      <c r="C62" s="24">
+      <c r="C62" s="21">
         <v>0.16666666666666666</v>
       </c>
-      <c r="D62" s="22" t="s">
+      <c r="D62" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E62" s="23" t="s">
+      <c r="E62" s="8" t="s">
         <v>86</v>
       </c>
     </row>
@@ -5271,10 +5246,10 @@
       <c r="C63" s="21">
         <v>0.125</v>
       </c>
-      <c r="D63" s="22" t="s">
+      <c r="D63" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E63" s="23" t="s">
+      <c r="E63" s="8" t="s">
         <v>87</v>
       </c>
     </row>
@@ -5285,10 +5260,10 @@
       <c r="C64" s="21">
         <v>0.043749999999999997</v>
       </c>
-      <c r="D64" s="22" t="s">
+      <c r="D64" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E64" s="23" t="s">
+      <c r="E64" s="8" t="s">
         <v>88</v>
       </c>
     </row>
@@ -5299,106 +5274,114 @@
       <c r="C65" s="21">
         <v>0.14583333333333334</v>
       </c>
-      <c r="D65" s="22" t="s">
+      <c r="D65" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E65" s="23" t="s">
+      <c r="E65" s="8" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="20"/>
-      <c r="C66" s="25"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="8"/>
+      <c r="B66" s="20">
+        <v>46160</v>
+      </c>
+      <c r="C66" s="21">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E66" s="22" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="67">
       <c r="B67" s="20"/>
-      <c r="C67" s="25"/>
+      <c r="C67" s="23"/>
       <c r="D67" s="7"/>
       <c r="E67" s="8"/>
     </row>
     <row r="68">
       <c r="B68" s="20"/>
-      <c r="C68" s="25"/>
+      <c r="C68" s="23"/>
       <c r="D68" s="7"/>
       <c r="E68" s="8"/>
     </row>
     <row r="69">
       <c r="B69" s="20"/>
-      <c r="C69" s="25"/>
+      <c r="C69" s="23"/>
       <c r="D69" s="7"/>
       <c r="E69" s="8"/>
     </row>
     <row r="70">
       <c r="B70" s="20"/>
-      <c r="C70" s="25"/>
+      <c r="C70" s="23"/>
       <c r="D70" s="7"/>
       <c r="E70" s="8"/>
     </row>
     <row r="71">
       <c r="B71" s="20"/>
-      <c r="C71" s="25"/>
+      <c r="C71" s="23"/>
       <c r="D71" s="7"/>
       <c r="E71" s="8"/>
     </row>
     <row r="72">
       <c r="B72" s="20"/>
-      <c r="C72" s="25"/>
+      <c r="C72" s="23"/>
       <c r="D72" s="7"/>
       <c r="E72" s="8"/>
     </row>
     <row r="73">
       <c r="B73" s="20"/>
-      <c r="C73" s="25"/>
+      <c r="C73" s="23"/>
       <c r="D73" s="7"/>
       <c r="E73" s="8"/>
     </row>
     <row r="74">
       <c r="B74" s="20"/>
-      <c r="C74" s="25"/>
+      <c r="C74" s="23"/>
       <c r="D74" s="7"/>
       <c r="E74" s="8"/>
     </row>
     <row r="75">
       <c r="B75" s="20"/>
-      <c r="C75" s="25"/>
+      <c r="C75" s="23"/>
       <c r="D75" s="7"/>
       <c r="E75" s="8"/>
     </row>
     <row r="76">
       <c r="B76" s="7"/>
-      <c r="C76" s="25"/>
+      <c r="C76" s="23"/>
       <c r="D76" s="7"/>
       <c r="E76" s="8"/>
     </row>
     <row r="77">
       <c r="B77" s="7"/>
-      <c r="C77" s="25"/>
+      <c r="C77" s="23"/>
       <c r="D77" s="7"/>
       <c r="E77" s="8"/>
     </row>
     <row r="78">
       <c r="B78" s="7"/>
-      <c r="C78" s="25"/>
+      <c r="C78" s="23"/>
       <c r="D78" s="7"/>
       <c r="E78" s="8"/>
     </row>
     <row r="79">
       <c r="B79" s="7"/>
-      <c r="C79" s="25"/>
+      <c r="C79" s="23"/>
       <c r="D79" s="7"/>
       <c r="E79" s="8"/>
     </row>
     <row r="80">
       <c r="B80" s="7"/>
-      <c r="C80" s="25"/>
+      <c r="C80" s="23"/>
       <c r="D80" s="7"/>
       <c r="E80" s="8"/>
     </row>
     <row r="81">
       <c r="B81" s="7"/>
-      <c r="C81" s="25"/>
+      <c r="C81" s="23"/>
       <c r="D81" s="7"/>
       <c r="E81" s="8"/>
     </row>
@@ -5418,7 +5401,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{000A0062-003C-4181-BDC2-0042001A0036}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00AF00DC-00DB-4AAB-855A-001F00640069}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -5450,1787 +5433,1787 @@
       <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="str" cm="1">
+      <c r="A2" s="24" t="str">
         <f t="array" ref="A2:A38">_xlfn.UNIQUE(Journal[date])</f>
         <v>20.01.2026</v>
       </c>
-      <c r="B2" s="27">
+      <c r="B2" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A2,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C2" s="27"/>
+      <c r="C2" s="25"/>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="str">
+      <c r="A3" s="24" t="str">
         <f/>
         <v>27.01.2026</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="str">
+      <c r="A4" s="24" t="str">
         <f/>
         <v>30.01.2026</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C4"/>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="str">
+      <c r="A5" s="24" t="str">
         <f/>
         <v>03.02.2026</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0.25</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="str">
+      <c r="A6" s="24" t="str">
         <f/>
         <v>04.02.2026</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="str">
+      <c r="A7" s="24" t="str">
         <f/>
         <v>06.02.2026</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C7"/>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="str">
+      <c r="A8" s="24" t="str">
         <f/>
         <v>08.02.2026</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
         <v>0.083333333333333329</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="str">
+      <c r="A9" s="24" t="str">
         <f/>
         <v>09.02.2026</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
         <v>0.041666666666666664</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="str">
+      <c r="A10" s="24" t="str">
         <f/>
         <v>10.02.2026</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="str">
+      <c r="A11" s="24" t="str">
         <f/>
         <v>12.02.2026</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
         <v>0.083333333333333329</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="str">
+      <c r="A12" s="24" t="str">
         <f/>
         <v>13.02.2026</v>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
         <v>0.0625</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="str">
+      <c r="A13" s="24" t="str">
         <f/>
         <v>24.02.2026</v>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0.125</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="str">
+      <c r="A14" s="24" t="str">
         <f/>
         <v>03.03.2026</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="str">
+      <c r="A15" s="24" t="str">
         <f/>
         <v>05.03.2026</v>
       </c>
-      <c r="B15" s="27">
+      <c r="B15" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="26">
+      <c r="A16" s="24">
         <f/>
         <v>46087</v>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="26">
+      <c r="A17" s="24">
         <f/>
         <v>46088</v>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0.25</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="26">
+      <c r="A18" s="24">
         <f/>
         <v>46091</v>
       </c>
-      <c r="B18" s="27">
+      <c r="B18" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="26">
+      <c r="A19" s="24">
         <f/>
         <v>46093</v>
       </c>
-      <c r="B19" s="27">
+      <c r="B19" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
         <v>0.083333333333333329</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="26">
+      <c r="A20" s="24">
         <f/>
         <v>46095</v>
       </c>
-      <c r="B20" s="27">
+      <c r="B20" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="26">
+      <c r="A21" s="24">
         <f/>
         <v>46096</v>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="26">
+      <c r="A22" s="24">
         <f/>
         <v>46097</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0.14583333333333334</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="26">
+      <c r="A23" s="24">
         <f/>
         <v>46098</v>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="26">
+      <c r="A24" s="24">
         <f/>
         <v>46099</v>
       </c>
-      <c r="B24" s="27">
+      <c r="B24" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="26">
+      <c r="A25" s="24">
         <f/>
         <v>46100</v>
       </c>
-      <c r="B25" s="27">
+      <c r="B25" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="C25"/>
-      <c r="F25" s="28"/>
+      <c r="F25" s="26"/>
     </row>
     <row r="26">
-      <c r="A26" s="26">
+      <c r="A26" s="24">
         <f/>
         <v>46102</v>
       </c>
-      <c r="B26" s="27">
+      <c r="B26" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="26">
+      <c r="A27" s="24">
         <f/>
         <v>46103</v>
       </c>
-      <c r="B27" s="27">
+      <c r="B27" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0.375</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0.375</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="26">
+      <c r="A28" s="24">
         <f/>
         <v>46104</v>
       </c>
-      <c r="B28" s="27">
+      <c r="B28" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0.013888888888888888</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0.013888888888888888</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="26">
+      <c r="A29" s="24">
         <f/>
         <v>46117</v>
       </c>
-      <c r="B29" s="27">
+      <c r="B29" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="26">
+      <c r="A30" s="24">
         <f/>
         <v>46118</v>
       </c>
-      <c r="B30" s="27">
+      <c r="B30" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0.083333333333333329</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C30" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0.083333333333333329</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="26">
+      <c r="A31" s="24">
         <f/>
         <v>46119</v>
       </c>
-      <c r="B31" s="27">
+      <c r="B31" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0.083333333333333329</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C31" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0.083333333333333329</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="26">
+      <c r="A32" s="24">
         <f/>
         <v>46122</v>
       </c>
-      <c r="B32" s="27">
+      <c r="B32" s="25">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="26">
+      <c r="A33" s="24">
         <f/>
         <v>46133</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C33" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="26">
+      <c r="A34" s="24">
         <f/>
         <v>46134</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C34" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0.10416666666666666</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="26">
+      <c r="A35" s="24">
         <f/>
         <v>46135</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C35" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0.041666666666666664</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="26">
+      <c r="A36" s="24">
         <f/>
         <v>46136</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C36" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="26">
+      <c r="A37" s="24">
         <f/>
         <v>46137</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C37" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="26">
+      <c r="A38" s="24">
         <f/>
         <v>46140</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C38" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0.18958333333333333</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="26"/>
-      <c r="C39" s="29">
+      <c r="A39" s="24"/>
+      <c r="C39" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="26"/>
-      <c r="B40" s="27" t="str">
+      <c r="A40" s="24"/>
+      <c r="B40" s="25" t="str">
         <f t="shared" ref="B40:B103" si="0">IF(C40&gt;0,C40,"")</f>
         <v/>
       </c>
-      <c r="C40" s="29">
+      <c r="C40" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="26"/>
-      <c r="B41" s="27" t="str">
+      <c r="A41" s="24"/>
+      <c r="B41" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="30"/>
-      <c r="B42" s="27" t="str">
+      <c r="A42" s="28"/>
+      <c r="B42" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="29">
+      <c r="C42" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="30"/>
-      <c r="B43" s="27" t="str">
+      <c r="A43" s="28"/>
+      <c r="B43" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="29">
+      <c r="C43" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="30"/>
-      <c r="B44" s="27" t="str">
+      <c r="A44" s="28"/>
+      <c r="B44" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="29">
+      <c r="C44" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="30"/>
-      <c r="B45" s="27" t="str">
+      <c r="A45" s="28"/>
+      <c r="B45" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="30"/>
-      <c r="B46" s="27" t="str">
+      <c r="A46" s="28"/>
+      <c r="B46" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="29">
+      <c r="C46" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="31"/>
-      <c r="B47" s="27" t="str">
+      <c r="A47" s="29"/>
+      <c r="B47" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="29">
+      <c r="C47" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="31"/>
-      <c r="B48" s="27" t="str">
+      <c r="A48" s="29"/>
+      <c r="B48" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="29">
+      <c r="C48" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="31"/>
-      <c r="B49" s="27" t="str">
+      <c r="A49" s="29"/>
+      <c r="B49" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C49" s="29">
+      <c r="C49" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="31"/>
-      <c r="B50" s="27" t="str">
+      <c r="A50" s="29"/>
+      <c r="B50" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C50" s="29">
+      <c r="C50" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="31"/>
-      <c r="B51" s="27" t="str">
+      <c r="A51" s="29"/>
+      <c r="B51" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C51" s="29">
+      <c r="C51" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="31"/>
-      <c r="B52" s="27" t="str">
+      <c r="A52" s="29"/>
+      <c r="B52" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C52" s="29">
+      <c r="C52" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="31"/>
-      <c r="B53" s="27" t="str">
+      <c r="A53" s="29"/>
+      <c r="B53" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C53" s="29">
+      <c r="C53" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="31"/>
-      <c r="B54" s="27" t="str">
+      <c r="A54" s="29"/>
+      <c r="B54" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C54" s="29">
+      <c r="C54" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="31"/>
-      <c r="B55" s="27" t="str">
+      <c r="A55" s="29"/>
+      <c r="B55" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C55" s="29">
+      <c r="C55" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="31"/>
-      <c r="B56" s="27" t="str">
+      <c r="A56" s="29"/>
+      <c r="B56" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C56" s="29">
+      <c r="C56" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="31"/>
-      <c r="B57" s="27" t="str">
+      <c r="A57" s="29"/>
+      <c r="B57" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C57" s="29">
+      <c r="C57" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="31"/>
-      <c r="B58" s="27" t="str">
+      <c r="A58" s="29"/>
+      <c r="B58" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C58" s="29">
+      <c r="C58" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="31"/>
-      <c r="B59" s="27" t="str">
+      <c r="A59" s="29"/>
+      <c r="B59" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C59" s="29">
+      <c r="C59" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="31"/>
-      <c r="B60" s="27" t="str">
+      <c r="A60" s="29"/>
+      <c r="B60" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C60" s="29">
+      <c r="C60" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="31"/>
-      <c r="B61" s="27" t="str">
+      <c r="A61" s="29"/>
+      <c r="B61" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C61" s="29">
+      <c r="C61" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="31"/>
-      <c r="B62" s="27" t="str">
+      <c r="A62" s="29"/>
+      <c r="B62" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C62" s="29">
+      <c r="C62" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="31"/>
-      <c r="B63" s="27" t="str">
+      <c r="A63" s="29"/>
+      <c r="B63" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C63" s="29">
+      <c r="C63" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="31"/>
-      <c r="B64" s="27" t="str">
+      <c r="A64" s="29"/>
+      <c r="B64" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C64" s="29">
+      <c r="C64" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="31"/>
-      <c r="B65" s="27" t="str">
+      <c r="A65" s="29"/>
+      <c r="B65" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C65" s="29">
+      <c r="C65" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="31"/>
-      <c r="B66" s="27" t="str">
+      <c r="A66" s="29"/>
+      <c r="B66" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C66" s="29">
+      <c r="C66" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="31"/>
-      <c r="B67" s="27" t="str">
+      <c r="A67" s="29"/>
+      <c r="B67" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C67" s="29">
+      <c r="C67" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="31"/>
-      <c r="B68" s="27" t="str">
+      <c r="A68" s="29"/>
+      <c r="B68" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C68" s="29">
+      <c r="C68" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="31"/>
-      <c r="B69" s="27" t="str">
+      <c r="A69" s="29"/>
+      <c r="B69" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C69" s="29">
+      <c r="C69" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="31"/>
-      <c r="B70" s="27" t="str">
+      <c r="A70" s="29"/>
+      <c r="B70" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C70" s="29">
+      <c r="C70" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="31"/>
-      <c r="B71" s="27" t="str">
+      <c r="A71" s="29"/>
+      <c r="B71" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C71" s="29">
+      <c r="C71" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="31"/>
-      <c r="B72" s="27" t="str">
+      <c r="A72" s="29"/>
+      <c r="B72" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C72" s="29">
+      <c r="C72" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="31"/>
-      <c r="B73" s="27" t="str">
+      <c r="A73" s="29"/>
+      <c r="B73" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C73" s="29">
+      <c r="C73" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="31"/>
-      <c r="B74" s="27" t="str">
+      <c r="A74" s="29"/>
+      <c r="B74" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C74" s="29">
+      <c r="C74" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="31"/>
-      <c r="B75" s="27" t="str">
+      <c r="A75" s="29"/>
+      <c r="B75" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C75" s="29">
+      <c r="C75" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="31"/>
-      <c r="B76" s="27" t="str">
+      <c r="A76" s="29"/>
+      <c r="B76" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C76" s="29">
+      <c r="C76" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="31"/>
-      <c r="B77" s="27" t="str">
+      <c r="A77" s="29"/>
+      <c r="B77" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C77" s="29">
+      <c r="C77" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="31"/>
-      <c r="B78" s="27" t="str">
+      <c r="A78" s="29"/>
+      <c r="B78" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C78" s="29">
+      <c r="C78" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="31"/>
-      <c r="B79" s="27" t="str">
+      <c r="A79" s="29"/>
+      <c r="B79" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C79" s="29">
+      <c r="C79" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="31"/>
-      <c r="B80" s="27" t="str">
+      <c r="A80" s="29"/>
+      <c r="B80" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C80" s="29">
+      <c r="C80" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="31"/>
-      <c r="B81" s="27" t="str">
+      <c r="A81" s="29"/>
+      <c r="B81" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C81" s="29">
+      <c r="C81" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="31"/>
-      <c r="B82" s="27" t="str">
+      <c r="A82" s="29"/>
+      <c r="B82" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C82" s="29">
+      <c r="C82" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="31"/>
-      <c r="B83" s="27" t="str">
+      <c r="A83" s="29"/>
+      <c r="B83" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C83" s="29">
+      <c r="C83" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="31"/>
-      <c r="B84" s="27" t="str">
+      <c r="A84" s="29"/>
+      <c r="B84" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C84" s="29">
+      <c r="C84" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="31"/>
-      <c r="B85" s="27" t="str">
+      <c r="A85" s="29"/>
+      <c r="B85" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C85" s="29">
+      <c r="C85" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="31"/>
-      <c r="B86" s="27" t="str">
+      <c r="A86" s="29"/>
+      <c r="B86" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C86" s="29">
+      <c r="C86" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="31"/>
-      <c r="B87" s="27" t="str">
+      <c r="A87" s="29"/>
+      <c r="B87" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C87" s="29">
+      <c r="C87" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="31"/>
-      <c r="B88" s="27" t="str">
+      <c r="A88" s="29"/>
+      <c r="B88" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C88" s="29">
+      <c r="C88" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="31"/>
-      <c r="B89" s="27" t="str">
+      <c r="A89" s="29"/>
+      <c r="B89" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C89" s="29">
+      <c r="C89" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="31"/>
-      <c r="B90" s="27" t="str">
+      <c r="A90" s="29"/>
+      <c r="B90" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C90" s="29">
+      <c r="C90" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="31"/>
-      <c r="B91" s="27" t="str">
+      <c r="A91" s="29"/>
+      <c r="B91" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C91" s="29">
+      <c r="C91" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="31"/>
-      <c r="B92" s="27" t="str">
+      <c r="A92" s="29"/>
+      <c r="B92" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C92" s="29">
+      <c r="C92" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="31"/>
-      <c r="B93" s="27" t="str">
+      <c r="A93" s="29"/>
+      <c r="B93" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C93" s="29">
+      <c r="C93" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="31"/>
-      <c r="B94" s="27" t="str">
+      <c r="A94" s="29"/>
+      <c r="B94" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C94" s="29">
+      <c r="C94" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="31"/>
-      <c r="B95" s="27" t="str">
+      <c r="A95" s="29"/>
+      <c r="B95" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C95" s="29">
+      <c r="C95" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="31"/>
-      <c r="B96" s="27" t="str">
+      <c r="A96" s="29"/>
+      <c r="B96" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C96" s="29">
+      <c r="C96" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="31"/>
-      <c r="B97" s="27" t="str">
+      <c r="A97" s="29"/>
+      <c r="B97" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C97" s="29">
+      <c r="C97" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="31"/>
-      <c r="B98" s="27" t="str">
+      <c r="A98" s="29"/>
+      <c r="B98" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C98" s="29">
+      <c r="C98" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="31"/>
-      <c r="B99" s="27" t="str">
+      <c r="A99" s="29"/>
+      <c r="B99" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C99" s="29">
+      <c r="C99" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="31"/>
-      <c r="B100" s="27" t="str">
+      <c r="A100" s="29"/>
+      <c r="B100" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C100" s="29">
+      <c r="C100" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="31"/>
-      <c r="B101" s="27" t="str">
+      <c r="A101" s="29"/>
+      <c r="B101" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C101" s="29">
+      <c r="C101" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="31"/>
-      <c r="B102" s="27" t="str">
+      <c r="A102" s="29"/>
+      <c r="B102" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C102" s="29">
+      <c r="C102" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="31"/>
-      <c r="B103" s="27" t="str">
+      <c r="A103" s="29"/>
+      <c r="B103" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C103" s="29">
+      <c r="C103" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="31"/>
-      <c r="B104" s="27" t="str">
+      <c r="A104" s="29"/>
+      <c r="B104" s="25" t="str">
         <f t="shared" ref="B104:B114" si="1">IF(C104&gt;0,C104,"")</f>
         <v/>
       </c>
-      <c r="C104" s="29">
+      <c r="C104" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="31"/>
-      <c r="B105" s="27" t="str">
+      <c r="A105" s="29"/>
+      <c r="B105" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C105" s="29">
+      <c r="C105" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="31"/>
-      <c r="B106" s="27" t="str">
+      <c r="A106" s="29"/>
+      <c r="B106" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C106" s="29">
+      <c r="C106" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="31"/>
-      <c r="B107" s="27" t="str">
+      <c r="A107" s="29"/>
+      <c r="B107" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C107" s="29">
+      <c r="C107" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="31"/>
-      <c r="B108" s="27" t="str">
+      <c r="A108" s="29"/>
+      <c r="B108" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C108" s="29">
+      <c r="C108" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="31"/>
-      <c r="B109" s="27" t="str">
+      <c r="A109" s="29"/>
+      <c r="B109" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C109" s="29">
+      <c r="C109" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="31"/>
-      <c r="B110" s="27" t="str">
+      <c r="A110" s="29"/>
+      <c r="B110" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C110" s="29">
+      <c r="C110" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="31"/>
-      <c r="B111" s="27" t="str">
+      <c r="A111" s="29"/>
+      <c r="B111" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C111" s="29">
+      <c r="C111" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="31"/>
-      <c r="B112" s="27" t="str">
+      <c r="A112" s="29"/>
+      <c r="B112" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C112" s="29">
+      <c r="C112" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="31"/>
-      <c r="B113" s="27" t="str">
+      <c r="A113" s="29"/>
+      <c r="B113" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C113" s="29">
+      <c r="C113" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="31"/>
-      <c r="B114" s="27" t="str">
+      <c r="A114" s="29"/>
+      <c r="B114" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C114" s="29">
+      <c r="C114" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="31"/>
-      <c r="B115" s="31"/>
-      <c r="C115" s="29"/>
+      <c r="A115" s="29"/>
+      <c r="B115" s="29"/>
+      <c r="C115" s="27"/>
     </row>
     <row r="116">
-      <c r="A116" s="31"/>
-      <c r="B116" s="31"/>
-      <c r="C116" s="29"/>
+      <c r="A116" s="29"/>
+      <c r="B116" s="29"/>
+      <c r="C116" s="27"/>
     </row>
     <row r="117">
-      <c r="A117" s="31"/>
-      <c r="B117" s="31"/>
-      <c r="C117" s="29"/>
+      <c r="A117" s="29"/>
+      <c r="B117" s="29"/>
+      <c r="C117" s="27"/>
     </row>
     <row r="118">
-      <c r="A118" s="31"/>
-      <c r="B118" s="31"/>
-      <c r="C118" s="29"/>
+      <c r="A118" s="29"/>
+      <c r="B118" s="29"/>
+      <c r="C118" s="27"/>
     </row>
     <row r="119">
-      <c r="A119" s="31"/>
-      <c r="B119" s="31"/>
-      <c r="C119" s="29"/>
+      <c r="A119" s="29"/>
+      <c r="B119" s="29"/>
+      <c r="C119" s="27"/>
     </row>
     <row r="120">
-      <c r="A120" s="31"/>
-      <c r="B120" s="31"/>
-      <c r="C120" s="29"/>
+      <c r="A120" s="29"/>
+      <c r="B120" s="29"/>
+      <c r="C120" s="27"/>
     </row>
     <row r="121">
-      <c r="A121" s="31"/>
-      <c r="B121" s="31"/>
-      <c r="C121" s="29"/>
+      <c r="A121" s="29"/>
+      <c r="B121" s="29"/>
+      <c r="C121" s="27"/>
     </row>
     <row r="122">
-      <c r="A122" s="31"/>
-      <c r="B122" s="31"/>
-      <c r="C122" s="29"/>
+      <c r="A122" s="29"/>
+      <c r="B122" s="29"/>
+      <c r="C122" s="27"/>
     </row>
     <row r="123">
-      <c r="A123" s="31"/>
-      <c r="B123" s="31"/>
-      <c r="C123" s="29"/>
+      <c r="A123" s="29"/>
+      <c r="B123" s="29"/>
+      <c r="C123" s="27"/>
     </row>
     <row r="124">
-      <c r="A124" s="31"/>
-      <c r="B124" s="31"/>
-      <c r="C124" s="29"/>
+      <c r="A124" s="29"/>
+      <c r="B124" s="29"/>
+      <c r="C124" s="27"/>
     </row>
     <row r="125">
-      <c r="A125" s="31"/>
-      <c r="B125" s="31"/>
-      <c r="C125" s="29"/>
+      <c r="A125" s="29"/>
+      <c r="B125" s="29"/>
+      <c r="C125" s="27"/>
     </row>
     <row r="126">
-      <c r="A126" s="31"/>
-      <c r="B126" s="31"/>
-      <c r="C126" s="29"/>
+      <c r="A126" s="29"/>
+      <c r="B126" s="29"/>
+      <c r="C126" s="27"/>
     </row>
     <row r="127">
-      <c r="A127" s="31"/>
-      <c r="B127" s="31"/>
-      <c r="C127" s="29"/>
+      <c r="A127" s="29"/>
+      <c r="B127" s="29"/>
+      <c r="C127" s="27"/>
     </row>
     <row r="128">
-      <c r="A128" s="31"/>
-      <c r="B128" s="31"/>
-      <c r="C128" s="29"/>
+      <c r="A128" s="29"/>
+      <c r="B128" s="29"/>
+      <c r="C128" s="27"/>
     </row>
     <row r="129">
-      <c r="A129" s="31"/>
-      <c r="B129" s="31"/>
-      <c r="C129" s="29"/>
+      <c r="A129" s="29"/>
+      <c r="B129" s="29"/>
+      <c r="C129" s="27"/>
     </row>
     <row r="130">
-      <c r="A130" s="31"/>
-      <c r="B130" s="31"/>
-      <c r="C130" s="29"/>
+      <c r="A130" s="29"/>
+      <c r="B130" s="29"/>
+      <c r="C130" s="27"/>
     </row>
     <row r="131">
-      <c r="A131" s="31"/>
-      <c r="B131" s="31"/>
-      <c r="C131" s="29"/>
+      <c r="A131" s="29"/>
+      <c r="B131" s="29"/>
+      <c r="C131" s="27"/>
     </row>
     <row r="132">
-      <c r="A132" s="31"/>
-      <c r="B132" s="31"/>
-      <c r="C132" s="29"/>
+      <c r="A132" s="29"/>
+      <c r="B132" s="29"/>
+      <c r="C132" s="27"/>
     </row>
     <row r="133">
-      <c r="A133" s="31"/>
-      <c r="B133" s="31"/>
-      <c r="C133" s="29"/>
+      <c r="A133" s="29"/>
+      <c r="B133" s="29"/>
+      <c r="C133" s="27"/>
     </row>
     <row r="134">
-      <c r="A134" s="31"/>
-      <c r="B134" s="31"/>
-      <c r="C134" s="29"/>
+      <c r="A134" s="29"/>
+      <c r="B134" s="29"/>
+      <c r="C134" s="27"/>
     </row>
     <row r="135">
-      <c r="A135" s="31"/>
-      <c r="B135" s="31"/>
-      <c r="C135" s="29"/>
+      <c r="A135" s="29"/>
+      <c r="B135" s="29"/>
+      <c r="C135" s="27"/>
     </row>
     <row r="136">
-      <c r="A136" s="31"/>
-      <c r="B136" s="31"/>
-      <c r="C136" s="29"/>
+      <c r="A136" s="29"/>
+      <c r="B136" s="29"/>
+      <c r="C136" s="27"/>
     </row>
     <row r="137">
-      <c r="A137" s="31"/>
-      <c r="B137" s="31"/>
-      <c r="C137" s="29"/>
+      <c r="A137" s="29"/>
+      <c r="B137" s="29"/>
+      <c r="C137" s="27"/>
     </row>
     <row r="138">
-      <c r="A138" s="31"/>
-      <c r="B138" s="31"/>
-      <c r="C138" s="29"/>
+      <c r="A138" s="29"/>
+      <c r="B138" s="29"/>
+      <c r="C138" s="27"/>
     </row>
     <row r="139">
-      <c r="A139" s="31"/>
-      <c r="B139" s="31"/>
-      <c r="C139" s="29"/>
+      <c r="A139" s="29"/>
+      <c r="B139" s="29"/>
+      <c r="C139" s="27"/>
     </row>
     <row r="140">
-      <c r="A140" s="31"/>
-      <c r="B140" s="31"/>
-      <c r="C140" s="29"/>
+      <c r="A140" s="29"/>
+      <c r="B140" s="29"/>
+      <c r="C140" s="27"/>
     </row>
     <row r="141">
-      <c r="A141" s="31"/>
-      <c r="B141" s="31"/>
-      <c r="C141" s="29"/>
+      <c r="A141" s="29"/>
+      <c r="B141" s="29"/>
+      <c r="C141" s="27"/>
     </row>
     <row r="142">
-      <c r="A142" s="31"/>
-      <c r="B142" s="31"/>
-      <c r="C142" s="29"/>
+      <c r="A142" s="29"/>
+      <c r="B142" s="29"/>
+      <c r="C142" s="27"/>
     </row>
     <row r="143">
-      <c r="A143" s="31"/>
-      <c r="B143" s="31"/>
-      <c r="C143" s="29"/>
+      <c r="A143" s="29"/>
+      <c r="B143" s="29"/>
+      <c r="C143" s="27"/>
     </row>
     <row r="144">
-      <c r="A144" s="31"/>
-      <c r="B144" s="31"/>
-      <c r="C144" s="29"/>
+      <c r="A144" s="29"/>
+      <c r="B144" s="29"/>
+      <c r="C144" s="27"/>
     </row>
     <row r="145">
-      <c r="A145" s="31"/>
-      <c r="B145" s="31"/>
-      <c r="C145" s="29"/>
+      <c r="A145" s="29"/>
+      <c r="B145" s="29"/>
+      <c r="C145" s="27"/>
     </row>
     <row r="146">
-      <c r="A146" s="31"/>
-      <c r="B146" s="31"/>
-      <c r="C146" s="29"/>
+      <c r="A146" s="29"/>
+      <c r="B146" s="29"/>
+      <c r="C146" s="27"/>
     </row>
     <row r="147">
-      <c r="A147" s="31"/>
-      <c r="B147" s="31"/>
-      <c r="C147" s="29"/>
+      <c r="A147" s="29"/>
+      <c r="B147" s="29"/>
+      <c r="C147" s="27"/>
     </row>
     <row r="148">
-      <c r="A148" s="31"/>
-      <c r="B148" s="31"/>
-      <c r="C148" s="29"/>
+      <c r="A148" s="29"/>
+      <c r="B148" s="29"/>
+      <c r="C148" s="27"/>
     </row>
     <row r="149">
-      <c r="A149" s="31"/>
-      <c r="B149" s="31"/>
-      <c r="C149" s="29"/>
+      <c r="A149" s="29"/>
+      <c r="B149" s="29"/>
+      <c r="C149" s="27"/>
     </row>
     <row r="150">
-      <c r="A150" s="31"/>
-      <c r="B150" s="31"/>
-      <c r="C150" s="29"/>
+      <c r="A150" s="29"/>
+      <c r="B150" s="29"/>
+      <c r="C150" s="27"/>
     </row>
     <row r="151">
-      <c r="A151" s="31"/>
-      <c r="B151" s="31"/>
-      <c r="C151" s="29"/>
+      <c r="A151" s="29"/>
+      <c r="B151" s="29"/>
+      <c r="C151" s="27"/>
     </row>
     <row r="152">
-      <c r="A152" s="31"/>
-      <c r="B152" s="31"/>
-      <c r="C152" s="29"/>
+      <c r="A152" s="29"/>
+      <c r="B152" s="29"/>
+      <c r="C152" s="27"/>
     </row>
     <row r="153">
-      <c r="A153" s="31"/>
-      <c r="B153" s="31"/>
-      <c r="C153" s="29"/>
+      <c r="A153" s="29"/>
+      <c r="B153" s="29"/>
+      <c r="C153" s="27"/>
     </row>
     <row r="154">
-      <c r="A154" s="31"/>
-      <c r="B154" s="31"/>
-      <c r="C154" s="29"/>
+      <c r="A154" s="29"/>
+      <c r="B154" s="29"/>
+      <c r="C154" s="27"/>
     </row>
     <row r="155">
-      <c r="A155" s="31"/>
-      <c r="B155" s="31"/>
-      <c r="C155" s="29"/>
+      <c r="A155" s="29"/>
+      <c r="B155" s="29"/>
+      <c r="C155" s="27"/>
     </row>
     <row r="156">
-      <c r="A156" s="31"/>
-      <c r="B156" s="31"/>
-      <c r="C156" s="29"/>
+      <c r="A156" s="29"/>
+      <c r="B156" s="29"/>
+      <c r="C156" s="27"/>
     </row>
     <row r="157">
-      <c r="A157" s="31"/>
-      <c r="B157" s="31"/>
-      <c r="C157" s="29"/>
+      <c r="A157" s="29"/>
+      <c r="B157" s="29"/>
+      <c r="C157" s="27"/>
     </row>
     <row r="158">
-      <c r="A158" s="31"/>
-      <c r="B158" s="31"/>
-      <c r="C158" s="29"/>
+      <c r="A158" s="29"/>
+      <c r="B158" s="29"/>
+      <c r="C158" s="27"/>
     </row>
     <row r="159">
-      <c r="A159" s="31"/>
-      <c r="B159" s="31"/>
+      <c r="A159" s="29"/>
+      <c r="B159" s="29"/>
     </row>
     <row r="160">
-      <c r="A160" s="31"/>
-      <c r="B160" s="31"/>
+      <c r="A160" s="29"/>
+      <c r="B160" s="29"/>
     </row>
     <row r="161">
-      <c r="A161" s="31"/>
-      <c r="B161" s="31"/>
+      <c r="A161" s="29"/>
+      <c r="B161" s="29"/>
     </row>
     <row r="162">
-      <c r="A162" s="31"/>
-      <c r="B162" s="31"/>
+      <c r="A162" s="29"/>
+      <c r="B162" s="29"/>
     </row>
     <row r="163">
-      <c r="A163" s="31"/>
-      <c r="B163" s="31"/>
+      <c r="A163" s="29"/>
+      <c r="B163" s="29"/>
     </row>
     <row r="164">
-      <c r="A164" s="31"/>
-      <c r="B164" s="31"/>
+      <c r="A164" s="29"/>
+      <c r="B164" s="29"/>
     </row>
     <row r="165">
-      <c r="A165" s="31"/>
-      <c r="B165" s="31"/>
+      <c r="A165" s="29"/>
+      <c r="B165" s="29"/>
     </row>
     <row r="166">
-      <c r="A166" s="31"/>
-      <c r="B166" s="31"/>
+      <c r="A166" s="29"/>
+      <c r="B166" s="29"/>
     </row>
     <row r="167">
-      <c r="A167" s="31"/>
-      <c r="B167" s="31"/>
+      <c r="A167" s="29"/>
+      <c r="B167" s="29"/>
     </row>
     <row r="168">
-      <c r="A168" s="31"/>
-      <c r="B168" s="31"/>
+      <c r="A168" s="29"/>
+      <c r="B168" s="29"/>
     </row>
     <row r="169">
-      <c r="A169" s="31"/>
-      <c r="B169" s="31"/>
+      <c r="A169" s="29"/>
+      <c r="B169" s="29"/>
     </row>
     <row r="170">
-      <c r="A170" s="31"/>
-      <c r="B170" s="31"/>
+      <c r="A170" s="29"/>
+      <c r="B170" s="29"/>
     </row>
     <row r="171">
-      <c r="A171" s="31"/>
-      <c r="B171" s="31"/>
+      <c r="A171" s="29"/>
+      <c r="B171" s="29"/>
     </row>
     <row r="172">
-      <c r="A172" s="31"/>
-      <c r="B172" s="31"/>
+      <c r="A172" s="29"/>
+      <c r="B172" s="29"/>
     </row>
     <row r="173">
-      <c r="A173" s="31"/>
-      <c r="B173" s="31"/>
+      <c r="A173" s="29"/>
+      <c r="B173" s="29"/>
     </row>
     <row r="174">
-      <c r="A174" s="31"/>
-      <c r="B174" s="31"/>
+      <c r="A174" s="29"/>
+      <c r="B174" s="29"/>
     </row>
     <row r="175">
-      <c r="A175" s="31"/>
-      <c r="B175" s="31"/>
+      <c r="A175" s="29"/>
+      <c r="B175" s="29"/>
     </row>
     <row r="176">
-      <c r="A176" s="31"/>
-      <c r="B176" s="31"/>
+      <c r="A176" s="29"/>
+      <c r="B176" s="29"/>
     </row>
     <row r="177">
-      <c r="A177" s="31"/>
-      <c r="B177" s="31"/>
+      <c r="A177" s="29"/>
+      <c r="B177" s="29"/>
     </row>
     <row r="178">
-      <c r="A178" s="31"/>
-      <c r="B178" s="31"/>
+      <c r="A178" s="29"/>
+      <c r="B178" s="29"/>
     </row>
     <row r="179">
-      <c r="A179" s="31"/>
-      <c r="B179" s="31"/>
+      <c r="A179" s="29"/>
+      <c r="B179" s="29"/>
     </row>
     <row r="180">
-      <c r="A180" s="31"/>
-      <c r="B180" s="31"/>
+      <c r="A180" s="29"/>
+      <c r="B180" s="29"/>
     </row>
     <row r="181">
-      <c r="A181" s="31"/>
-      <c r="B181" s="31"/>
+      <c r="A181" s="29"/>
+      <c r="B181" s="29"/>
     </row>
     <row r="182">
-      <c r="A182" s="31"/>
-      <c r="B182" s="31"/>
+      <c r="A182" s="29"/>
+      <c r="B182" s="29"/>
     </row>
     <row r="183">
-      <c r="A183" s="31"/>
-      <c r="B183" s="31"/>
+      <c r="A183" s="29"/>
+      <c r="B183" s="29"/>
     </row>
     <row r="184">
-      <c r="A184" s="31"/>
-      <c r="B184" s="31"/>
+      <c r="A184" s="29"/>
+      <c r="B184" s="29"/>
     </row>
     <row r="185">
-      <c r="A185" s="31"/>
-      <c r="B185" s="31"/>
+      <c r="A185" s="29"/>
+      <c r="B185" s="29"/>
     </row>
     <row r="186">
-      <c r="A186" s="31"/>
-      <c r="B186" s="31"/>
+      <c r="A186" s="29"/>
+      <c r="B186" s="29"/>
     </row>
     <row r="187">
-      <c r="A187" s="31"/>
-      <c r="B187" s="31"/>
+      <c r="A187" s="29"/>
+      <c r="B187" s="29"/>
     </row>
     <row r="188">
-      <c r="A188" s="31"/>
-      <c r="B188" s="31"/>
+      <c r="A188" s="29"/>
+      <c r="B188" s="29"/>
     </row>
     <row r="189">
-      <c r="A189" s="31"/>
-      <c r="B189" s="31"/>
+      <c r="A189" s="29"/>
+      <c r="B189" s="29"/>
     </row>
     <row r="190">
-      <c r="A190" s="31"/>
-      <c r="B190" s="31"/>
+      <c r="A190" s="29"/>
+      <c r="B190" s="29"/>
     </row>
     <row r="191">
-      <c r="A191" s="31"/>
-      <c r="B191" s="31"/>
+      <c r="A191" s="29"/>
+      <c r="B191" s="29"/>
     </row>
     <row r="192">
-      <c r="A192" s="31"/>
-      <c r="B192" s="31"/>
+      <c r="A192" s="29"/>
+      <c r="B192" s="29"/>
     </row>
     <row r="193">
-      <c r="A193" s="31"/>
-      <c r="B193" s="31"/>
+      <c r="A193" s="29"/>
+      <c r="B193" s="29"/>
     </row>
     <row r="194">
-      <c r="A194" s="31"/>
-      <c r="B194" s="31"/>
+      <c r="A194" s="29"/>
+      <c r="B194" s="29"/>
     </row>
     <row r="195">
-      <c r="A195" s="31"/>
-      <c r="B195" s="31"/>
+      <c r="A195" s="29"/>
+      <c r="B195" s="29"/>
     </row>
     <row r="196">
-      <c r="A196" s="31"/>
-      <c r="B196" s="31"/>
+      <c r="A196" s="29"/>
+      <c r="B196" s="29"/>
     </row>
     <row r="197">
-      <c r="A197" s="31"/>
-      <c r="B197" s="31"/>
+      <c r="A197" s="29"/>
+      <c r="B197" s="29"/>
     </row>
     <row r="198">
-      <c r="A198" s="31"/>
-      <c r="B198" s="31"/>
+      <c r="A198" s="29"/>
+      <c r="B198" s="29"/>
     </row>
     <row r="199">
-      <c r="A199" s="31"/>
-      <c r="B199" s="31"/>
+      <c r="A199" s="29"/>
+      <c r="B199" s="29"/>
     </row>
     <row r="200">
-      <c r="A200" s="31"/>
-      <c r="B200" s="31"/>
+      <c r="A200" s="29"/>
+      <c r="B200" s="29"/>
     </row>
     <row r="201">
-      <c r="A201" s="31"/>
-      <c r="B201" s="31"/>
+      <c r="A201" s="29"/>
+      <c r="B201" s="29"/>
     </row>
     <row r="202">
-      <c r="A202" s="31"/>
-      <c r="B202" s="31"/>
+      <c r="A202" s="29"/>
+      <c r="B202" s="29"/>
     </row>
     <row r="203">
-      <c r="A203" s="31"/>
-      <c r="B203" s="31"/>
+      <c r="A203" s="29"/>
+      <c r="B203" s="29"/>
     </row>
     <row r="204">
-      <c r="A204" s="31"/>
-      <c r="B204" s="31"/>
+      <c r="A204" s="29"/>
+      <c r="B204" s="29"/>
     </row>
     <row r="205">
-      <c r="A205" s="31"/>
-      <c r="B205" s="31"/>
+      <c r="A205" s="29"/>
+      <c r="B205" s="29"/>
     </row>
     <row r="206">
-      <c r="A206" s="31"/>
-      <c r="B206" s="31"/>
+      <c r="A206" s="29"/>
+      <c r="B206" s="29"/>
     </row>
     <row r="207">
-      <c r="A207" s="31"/>
-      <c r="B207" s="31"/>
+      <c r="A207" s="29"/>
+      <c r="B207" s="29"/>
     </row>
     <row r="208">
-      <c r="A208" s="31"/>
-      <c r="B208" s="31"/>
+      <c r="A208" s="29"/>
+      <c r="B208" s="29"/>
     </row>
     <row r="209">
-      <c r="A209" s="31"/>
-      <c r="B209" s="31"/>
+      <c r="A209" s="29"/>
+      <c r="B209" s="29"/>
     </row>
     <row r="210">
-      <c r="A210" s="31"/>
-      <c r="B210" s="31"/>
+      <c r="A210" s="29"/>
+      <c r="B210" s="29"/>
     </row>
     <row r="211">
-      <c r="A211" s="31"/>
-      <c r="B211" s="31"/>
+      <c r="A211" s="29"/>
+      <c r="B211" s="29"/>
     </row>
     <row r="212">
-      <c r="A212" s="31"/>
-      <c r="B212" s="31"/>
+      <c r="A212" s="29"/>
+      <c r="B212" s="29"/>
     </row>
     <row r="213">
-      <c r="A213" s="31"/>
-      <c r="B213" s="31"/>
+      <c r="A213" s="29"/>
+      <c r="B213" s="29"/>
     </row>
     <row r="214">
-      <c r="A214" s="31"/>
-      <c r="B214" s="31"/>
+      <c r="A214" s="29"/>
+      <c r="B214" s="29"/>
     </row>
     <row r="215">
-      <c r="A215" s="31"/>
-      <c r="B215" s="31"/>
+      <c r="A215" s="29"/>
+      <c r="B215" s="29"/>
     </row>
     <row r="216">
-      <c r="A216" s="31"/>
-      <c r="B216" s="31"/>
+      <c r="A216" s="29"/>
+      <c r="B216" s="29"/>
     </row>
     <row r="217">
-      <c r="A217" s="31"/>
-      <c r="B217" s="31"/>
+      <c r="A217" s="29"/>
+      <c r="B217" s="29"/>
     </row>
     <row r="218">
-      <c r="A218" s="31"/>
-      <c r="B218" s="31"/>
+      <c r="A218" s="29"/>
+      <c r="B218" s="29"/>
     </row>
     <row r="219">
-      <c r="A219" s="31"/>
-      <c r="B219" s="31"/>
+      <c r="A219" s="29"/>
+      <c r="B219" s="29"/>
     </row>
     <row r="220">
-      <c r="A220" s="31"/>
-      <c r="B220" s="31"/>
+      <c r="A220" s="29"/>
+      <c r="B220" s="29"/>
     </row>
     <row r="221">
-      <c r="A221" s="31"/>
-      <c r="B221" s="31"/>
+      <c r="A221" s="29"/>
+      <c r="B221" s="29"/>
     </row>
     <row r="222">
-      <c r="A222" s="31"/>
-      <c r="B222" s="31"/>
+      <c r="A222" s="29"/>
+      <c r="B222" s="29"/>
     </row>
     <row r="223">
-      <c r="A223" s="31"/>
-      <c r="B223" s="31"/>
+      <c r="A223" s="29"/>
+      <c r="B223" s="29"/>
     </row>
     <row r="224">
-      <c r="A224" s="31"/>
-      <c r="B224" s="31"/>
+      <c r="A224" s="29"/>
+      <c r="B224" s="29"/>
     </row>
     <row r="225">
-      <c r="A225" s="31"/>
-      <c r="B225" s="31"/>
+      <c r="A225" s="29"/>
+      <c r="B225" s="29"/>
     </row>
     <row r="226">
-      <c r="A226" s="31"/>
-      <c r="B226" s="31"/>
+      <c r="A226" s="29"/>
+      <c r="B226" s="29"/>
     </row>
     <row r="227">
-      <c r="A227" s="31"/>
-      <c r="B227" s="31"/>
+      <c r="A227" s="29"/>
+      <c r="B227" s="29"/>
     </row>
     <row r="228">
-      <c r="A228" s="31"/>
-      <c r="B228" s="31"/>
+      <c r="A228" s="29"/>
+      <c r="B228" s="29"/>
     </row>
     <row r="229">
-      <c r="A229" s="31"/>
-      <c r="B229" s="31"/>
+      <c r="A229" s="29"/>
+      <c r="B229" s="29"/>
     </row>
     <row r="230">
-      <c r="A230" s="31"/>
-      <c r="B230" s="31"/>
+      <c r="A230" s="29"/>
+      <c r="B230" s="29"/>
     </row>
     <row r="231">
-      <c r="A231" s="31"/>
-      <c r="B231" s="31"/>
+      <c r="A231" s="29"/>
+      <c r="B231" s="29"/>
     </row>
     <row r="232">
-      <c r="A232" s="31"/>
-      <c r="B232" s="31"/>
+      <c r="A232" s="29"/>
+      <c r="B232" s="29"/>
     </row>
     <row r="233">
-      <c r="A233" s="31"/>
-      <c r="B233" s="31"/>
+      <c r="A233" s="29"/>
+      <c r="B233" s="29"/>
     </row>
     <row r="234">
-      <c r="A234" s="31"/>
-      <c r="B234" s="31"/>
+      <c r="A234" s="29"/>
+      <c r="B234" s="29"/>
     </row>
     <row r="235">
-      <c r="A235" s="31"/>
-      <c r="B235" s="31"/>
+      <c r="A235" s="29"/>
+      <c r="B235" s="29"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -7248,2034 +7231,2034 @@
     <col customWidth="1" min="2" max="2" width="4.33203125"/>
     <col bestFit="1" min="3" max="3" width="35.77734375"/>
     <col customWidth="1" min="4" max="11" width="3.44140625"/>
-    <col customWidth="1" min="12" max="12" style="32" width="6"/>
+    <col customWidth="1" min="12" max="12" style="30" width="6"/>
     <col customWidth="1" min="13" max="22" width="3.44140625"/>
-    <col customWidth="1" min="23" max="23" style="32" width="6"/>
+    <col customWidth="1" min="23" max="23" style="30" width="6"/>
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
-    <col customWidth="1" min="30" max="30" style="32" width="6"/>
+    <col customWidth="1" min="30" max="30" style="30" width="6"/>
     <col customWidth="1" min="31" max="39" width="3.44140625"/>
     <col bestFit="1" customWidth="1" min="40" max="40" width="13.88671875"/>
     <col customWidth="1" min="41" max="47" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="33" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="B1" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="C1" s="35" t="s">
+    <row r="1" s="31" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="B1" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="C1" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="F1" s="37" t="s">
+      <c r="E1" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="38" t="s">
+      <c r="G1" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="39" t="s">
-        <v>93</v>
-      </c>
-      <c r="I1" s="36" t="s">
+      <c r="H1" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="I1" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="36" t="s">
+      <c r="J1" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="L1" s="40" t="s">
+      <c r="K1" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="M1" s="36" t="s">
+      <c r="L1" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="N1" s="38" t="s">
+      <c r="M1" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="N1" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="39" t="s">
-        <v>97</v>
-      </c>
-      <c r="P1" s="36" t="s">
+      <c r="O1" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="P1" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="R1" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="S1" s="36" t="s">
+      <c r="Q1" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="R1" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="T1" s="36" t="s">
+      <c r="S1" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="U1" s="36" t="s">
+      <c r="T1" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="V1" s="38" t="s">
+      <c r="U1" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="W1" s="41" t="s">
+      <c r="V1" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="X1" s="36" t="s">
+      <c r="W1" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="Y1" s="36" t="s">
+      <c r="X1" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="Z1" s="38" t="s">
+      <c r="Y1" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="AA1" s="42" t="s">
+      <c r="Z1" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="AB1" s="43" t="s">
+      <c r="AA1" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="AC1" s="43" t="s">
+      <c r="AB1" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="AD1" s="40" t="s">
+      <c r="AC1" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="AE1" s="44" t="s">
+      <c r="AD1" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="AF1" s="45" t="s">
+      <c r="AE1" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="AG1" s="46" t="s">
+      <c r="AF1" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="AH1" s="46" t="s">
+      <c r="AG1" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="AI1" s="46" t="s">
+      <c r="AH1" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="AJ1" s="46" t="s">
+      <c r="AI1" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="AK1" s="43" t="s">
+      <c r="AJ1" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="AL1" s="47"/>
-      <c r="AM1" s="47"/>
-      <c r="AN1" s="47"/>
-      <c r="AO1" s="47"/>
-      <c r="AP1" s="47"/>
-      <c r="AQ1" s="47"/>
-      <c r="AR1" s="47"/>
-      <c r="AS1" s="47"/>
-      <c r="AT1" s="47"/>
-      <c r="AU1" s="47"/>
+      <c r="AK1" s="41" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL1" s="45"/>
+      <c r="AM1" s="45"/>
+      <c r="AN1" s="45"/>
+      <c r="AO1" s="45"/>
+      <c r="AP1" s="45"/>
+      <c r="AQ1" s="45"/>
+      <c r="AR1" s="45"/>
+      <c r="AS1" s="45"/>
+      <c r="AT1" s="45"/>
+      <c r="AU1" s="45"/>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50"/>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="50"/>
-      <c r="V2" s="55"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="50"/>
-      <c r="Y2" s="50"/>
-      <c r="Z2" s="55"/>
-      <c r="AA2" s="56"/>
-      <c r="AB2" s="50"/>
-      <c r="AC2" s="50"/>
-      <c r="AD2" s="54"/>
-      <c r="AE2" s="55"/>
-      <c r="AF2" s="56"/>
-      <c r="AG2" s="50"/>
-      <c r="AH2" s="50"/>
-      <c r="AI2" s="50"/>
-      <c r="AJ2" s="50"/>
-      <c r="AK2" s="50"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="53"/>
+      <c r="W2" s="55"/>
+      <c r="X2" s="48"/>
+      <c r="Y2" s="48"/>
+      <c r="Z2" s="53"/>
+      <c r="AA2" s="54"/>
+      <c r="AB2" s="48"/>
+      <c r="AC2" s="48"/>
+      <c r="AD2" s="52"/>
+      <c r="AE2" s="53"/>
+      <c r="AF2" s="54"/>
+      <c r="AG2" s="48"/>
+      <c r="AH2" s="48"/>
+      <c r="AI2" s="48"/>
+      <c r="AJ2" s="48"/>
+      <c r="AK2" s="48"/>
     </row>
     <row r="3" ht="12" customHeight="1">
-      <c r="B3" s="48"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="55"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="50"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="50"/>
-      <c r="S3" s="50"/>
-      <c r="T3" s="50"/>
-      <c r="U3" s="50"/>
-      <c r="V3" s="55"/>
-      <c r="W3" s="57"/>
-      <c r="X3" s="50"/>
-      <c r="Y3" s="50"/>
-      <c r="Z3" s="55"/>
-      <c r="AA3" s="56"/>
-      <c r="AB3" s="50"/>
-      <c r="AC3" s="50"/>
-      <c r="AD3" s="54"/>
-      <c r="AE3" s="55"/>
-      <c r="AF3" s="56"/>
-      <c r="AG3" s="50"/>
-      <c r="AH3" s="50"/>
-      <c r="AI3" s="50"/>
-      <c r="AJ3" s="50"/>
-      <c r="AK3" s="50"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="54"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="53"/>
+      <c r="W3" s="55"/>
+      <c r="X3" s="48"/>
+      <c r="Y3" s="48"/>
+      <c r="Z3" s="53"/>
+      <c r="AA3" s="54"/>
+      <c r="AB3" s="48"/>
+      <c r="AC3" s="48"/>
+      <c r="AD3" s="52"/>
+      <c r="AE3" s="53"/>
+      <c r="AF3" s="54"/>
+      <c r="AG3" s="48"/>
+      <c r="AH3" s="48"/>
+      <c r="AI3" s="48"/>
+      <c r="AJ3" s="48"/>
+      <c r="AK3" s="48"/>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="48"/>
-      <c r="C4" s="49" t="s">
-        <v>118</v>
-      </c>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="50"/>
-      <c r="Q4" s="50"/>
-      <c r="R4" s="50"/>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="50"/>
-      <c r="V4" s="55"/>
-      <c r="W4" s="57"/>
-      <c r="X4" s="50"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="55"/>
-      <c r="AA4" s="56"/>
-      <c r="AB4" s="50"/>
-      <c r="AC4" s="50"/>
-      <c r="AD4" s="54"/>
-      <c r="AE4" s="55"/>
-      <c r="AF4" s="56"/>
-      <c r="AG4" s="50"/>
-      <c r="AH4" s="50"/>
-      <c r="AI4" s="50"/>
-      <c r="AJ4" s="50"/>
-      <c r="AK4" s="50"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="48"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="53"/>
+      <c r="W4" s="55"/>
+      <c r="X4" s="48"/>
+      <c r="Y4" s="48"/>
+      <c r="Z4" s="53"/>
+      <c r="AA4" s="54"/>
+      <c r="AB4" s="48"/>
+      <c r="AC4" s="48"/>
+      <c r="AD4" s="52"/>
+      <c r="AE4" s="53"/>
+      <c r="AF4" s="54"/>
+      <c r="AG4" s="48"/>
+      <c r="AH4" s="48"/>
+      <c r="AI4" s="48"/>
+      <c r="AJ4" s="48"/>
+      <c r="AK4" s="48"/>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="48"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="55"/>
-      <c r="O5" s="56"/>
-      <c r="P5" s="50"/>
-      <c r="Q5" s="50"/>
-      <c r="R5" s="50"/>
-      <c r="S5" s="50"/>
-      <c r="T5" s="50"/>
-      <c r="U5" s="50"/>
-      <c r="V5" s="55"/>
-      <c r="W5" s="57"/>
-      <c r="X5" s="50"/>
-      <c r="Y5" s="50"/>
-      <c r="Z5" s="55"/>
-      <c r="AA5" s="56"/>
-      <c r="AB5" s="50"/>
-      <c r="AC5" s="50"/>
-      <c r="AD5" s="54"/>
-      <c r="AE5" s="55"/>
-      <c r="AF5" s="56"/>
-      <c r="AG5" s="50"/>
-      <c r="AH5" s="50"/>
-      <c r="AI5" s="50"/>
-      <c r="AJ5" s="50"/>
-      <c r="AK5" s="50"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="53"/>
+      <c r="O5" s="54"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="48"/>
+      <c r="R5" s="48"/>
+      <c r="S5" s="48"/>
+      <c r="T5" s="48"/>
+      <c r="U5" s="48"/>
+      <c r="V5" s="53"/>
+      <c r="W5" s="55"/>
+      <c r="X5" s="48"/>
+      <c r="Y5" s="48"/>
+      <c r="Z5" s="53"/>
+      <c r="AA5" s="54"/>
+      <c r="AB5" s="48"/>
+      <c r="AC5" s="48"/>
+      <c r="AD5" s="52"/>
+      <c r="AE5" s="53"/>
+      <c r="AF5" s="54"/>
+      <c r="AG5" s="48"/>
+      <c r="AH5" s="48"/>
+      <c r="AI5" s="48"/>
+      <c r="AJ5" s="48"/>
+      <c r="AK5" s="48"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="48"/>
-      <c r="C6" s="49" t="s">
+      <c r="B6" s="46"/>
+      <c r="C6" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="54"/>
-      <c r="M6" s="50"/>
-      <c r="N6" s="55"/>
-      <c r="O6" s="56"/>
-      <c r="P6" s="50"/>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50"/>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
-      <c r="V6" s="55"/>
-      <c r="W6" s="57"/>
-      <c r="X6" s="50"/>
-      <c r="Y6" s="50"/>
-      <c r="Z6" s="55"/>
-      <c r="AA6" s="56"/>
-      <c r="AB6" s="50"/>
-      <c r="AC6" s="50"/>
-      <c r="AD6" s="54"/>
-      <c r="AE6" s="52"/>
-      <c r="AF6" s="53"/>
-      <c r="AG6" s="64"/>
-      <c r="AH6" s="64"/>
-      <c r="AI6" s="64"/>
-      <c r="AJ6" s="64"/>
-      <c r="AK6" s="64"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="53"/>
+      <c r="O6" s="54"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="48"/>
+      <c r="R6" s="48"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="48"/>
+      <c r="U6" s="48"/>
+      <c r="V6" s="53"/>
+      <c r="W6" s="55"/>
+      <c r="X6" s="48"/>
+      <c r="Y6" s="48"/>
+      <c r="Z6" s="53"/>
+      <c r="AA6" s="54"/>
+      <c r="AB6" s="48"/>
+      <c r="AC6" s="48"/>
+      <c r="AD6" s="52"/>
+      <c r="AE6" s="50"/>
+      <c r="AF6" s="51"/>
+      <c r="AG6" s="62"/>
+      <c r="AH6" s="62"/>
+      <c r="AI6" s="62"/>
+      <c r="AJ6" s="62"/>
+      <c r="AK6" s="62"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="48"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="62"/>
-      <c r="I7" s="63"/>
-      <c r="J7" s="50"/>
-      <c r="K7" s="50"/>
-      <c r="L7" s="54"/>
-      <c r="M7" s="50"/>
-      <c r="N7" s="55"/>
-      <c r="O7" s="62"/>
-      <c r="P7" s="50"/>
-      <c r="Q7" s="63"/>
-      <c r="R7" s="50"/>
-      <c r="S7" s="50"/>
-      <c r="T7" s="50"/>
-      <c r="U7" s="50"/>
-      <c r="V7" s="55"/>
-      <c r="W7" s="57"/>
-      <c r="X7" s="50"/>
-      <c r="Y7" s="50"/>
-      <c r="Z7" s="55"/>
-      <c r="AA7" s="56"/>
-      <c r="AB7" s="50"/>
-      <c r="AC7" s="50"/>
-      <c r="AD7" s="54"/>
-      <c r="AE7" s="55"/>
-      <c r="AF7" s="56"/>
-      <c r="AG7" s="50"/>
-      <c r="AH7" s="50"/>
-      <c r="AI7" s="50"/>
-      <c r="AJ7" s="50"/>
-      <c r="AK7" s="50"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="52"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="53"/>
+      <c r="O7" s="60"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="61"/>
+      <c r="R7" s="48"/>
+      <c r="S7" s="48"/>
+      <c r="T7" s="48"/>
+      <c r="U7" s="48"/>
+      <c r="V7" s="53"/>
+      <c r="W7" s="55"/>
+      <c r="X7" s="48"/>
+      <c r="Y7" s="48"/>
+      <c r="Z7" s="53"/>
+      <c r="AA7" s="54"/>
+      <c r="AB7" s="48"/>
+      <c r="AC7" s="48"/>
+      <c r="AD7" s="52"/>
+      <c r="AE7" s="53"/>
+      <c r="AF7" s="54"/>
+      <c r="AG7" s="48"/>
+      <c r="AH7" s="48"/>
+      <c r="AI7" s="48"/>
+      <c r="AJ7" s="48"/>
+      <c r="AK7" s="48"/>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="48"/>
-      <c r="C8" s="49" t="s">
-        <v>119</v>
-      </c>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="64"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="54"/>
-      <c r="M8" s="64"/>
-      <c r="N8" s="52"/>
-      <c r="O8" s="53"/>
-      <c r="P8" s="64"/>
-      <c r="Q8" s="64"/>
-      <c r="R8" s="64"/>
-      <c r="S8" s="64"/>
-      <c r="T8" s="64"/>
-      <c r="U8" s="64"/>
-      <c r="V8" s="52"/>
-      <c r="W8" s="57"/>
-      <c r="X8" s="64"/>
-      <c r="Y8" s="64"/>
-      <c r="Z8" s="52"/>
-      <c r="AA8" s="53"/>
-      <c r="AB8" s="64"/>
-      <c r="AC8" s="64"/>
-      <c r="AD8" s="54"/>
-      <c r="AE8" s="52"/>
-      <c r="AF8" s="53"/>
-      <c r="AG8" s="64"/>
-      <c r="AH8" s="64"/>
-      <c r="AI8" s="64"/>
-      <c r="AJ8" s="64"/>
-      <c r="AK8" s="64"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="62"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="62"/>
+      <c r="N8" s="50"/>
+      <c r="O8" s="51"/>
+      <c r="P8" s="62"/>
+      <c r="Q8" s="62"/>
+      <c r="R8" s="62"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="62"/>
+      <c r="U8" s="62"/>
+      <c r="V8" s="50"/>
+      <c r="W8" s="55"/>
+      <c r="X8" s="62"/>
+      <c r="Y8" s="62"/>
+      <c r="Z8" s="50"/>
+      <c r="AA8" s="51"/>
+      <c r="AB8" s="62"/>
+      <c r="AC8" s="62"/>
+      <c r="AD8" s="52"/>
+      <c r="AE8" s="50"/>
+      <c r="AF8" s="51"/>
+      <c r="AG8" s="62"/>
+      <c r="AH8" s="62"/>
+      <c r="AI8" s="62"/>
+      <c r="AJ8" s="62"/>
+      <c r="AK8" s="62"/>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="48"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="63"/>
-      <c r="J9" s="63"/>
-      <c r="K9" s="50"/>
-      <c r="L9" s="54"/>
-      <c r="M9" s="63"/>
-      <c r="N9" s="55"/>
-      <c r="O9" s="62"/>
-      <c r="P9" s="50"/>
-      <c r="Q9" s="63"/>
-      <c r="R9" s="50"/>
-      <c r="S9" s="65"/>
-      <c r="T9" s="50"/>
-      <c r="U9" s="50"/>
-      <c r="V9" s="55"/>
-      <c r="W9" s="57"/>
-      <c r="X9" s="50"/>
-      <c r="Y9" s="50"/>
-      <c r="Z9" s="55"/>
-      <c r="AA9" s="56"/>
-      <c r="AB9" s="50"/>
-      <c r="AC9" s="50"/>
-      <c r="AD9" s="54"/>
-      <c r="AE9" s="55"/>
-      <c r="AF9" s="56"/>
-      <c r="AG9" s="50"/>
-      <c r="AH9" s="50"/>
-      <c r="AI9" s="50"/>
-      <c r="AJ9" s="50"/>
-      <c r="AK9" s="50"/>
+      <c r="B9" s="46"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="61"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="52"/>
+      <c r="M9" s="61"/>
+      <c r="N9" s="53"/>
+      <c r="O9" s="60"/>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="61"/>
+      <c r="R9" s="48"/>
+      <c r="S9" s="63"/>
+      <c r="T9" s="48"/>
+      <c r="U9" s="48"/>
+      <c r="V9" s="53"/>
+      <c r="W9" s="55"/>
+      <c r="X9" s="48"/>
+      <c r="Y9" s="48"/>
+      <c r="Z9" s="53"/>
+      <c r="AA9" s="54"/>
+      <c r="AB9" s="48"/>
+      <c r="AC9" s="48"/>
+      <c r="AD9" s="52"/>
+      <c r="AE9" s="53"/>
+      <c r="AF9" s="54"/>
+      <c r="AG9" s="48"/>
+      <c r="AH9" s="48"/>
+      <c r="AI9" s="48"/>
+      <c r="AJ9" s="48"/>
+      <c r="AK9" s="48"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="48"/>
-      <c r="C10" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="50"/>
-      <c r="K10" s="50"/>
-      <c r="L10" s="54"/>
-      <c r="M10" s="50"/>
-      <c r="N10" s="55"/>
-      <c r="O10" s="56"/>
-      <c r="P10" s="50"/>
-      <c r="Q10" s="50"/>
-      <c r="R10" s="50"/>
-      <c r="S10" s="50"/>
-      <c r="T10" s="50"/>
-      <c r="U10" s="50"/>
-      <c r="V10" s="52"/>
-      <c r="W10" s="57"/>
-      <c r="X10" s="64"/>
-      <c r="Y10" s="64"/>
-      <c r="Z10" s="52"/>
-      <c r="AA10" s="56"/>
-      <c r="AB10" s="50"/>
-      <c r="AC10" s="50"/>
-      <c r="AD10" s="54"/>
-      <c r="AE10" s="55"/>
-      <c r="AF10" s="56"/>
-      <c r="AG10" s="50"/>
-      <c r="AH10" s="50"/>
-      <c r="AI10" s="50"/>
-      <c r="AJ10" s="50"/>
-      <c r="AK10" s="50"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="47" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="52"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="54"/>
+      <c r="P10" s="48"/>
+      <c r="Q10" s="48"/>
+      <c r="R10" s="48"/>
+      <c r="S10" s="48"/>
+      <c r="T10" s="48"/>
+      <c r="U10" s="48"/>
+      <c r="V10" s="50"/>
+      <c r="W10" s="55"/>
+      <c r="X10" s="62"/>
+      <c r="Y10" s="62"/>
+      <c r="Z10" s="50"/>
+      <c r="AA10" s="54"/>
+      <c r="AB10" s="48"/>
+      <c r="AC10" s="48"/>
+      <c r="AD10" s="52"/>
+      <c r="AE10" s="53"/>
+      <c r="AF10" s="54"/>
+      <c r="AG10" s="48"/>
+      <c r="AH10" s="48"/>
+      <c r="AI10" s="48"/>
+      <c r="AJ10" s="48"/>
+      <c r="AK10" s="48"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="48"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="56"/>
-      <c r="I11" s="50"/>
-      <c r="J11" s="50"/>
-      <c r="K11" s="50"/>
-      <c r="L11" s="54"/>
-      <c r="M11" s="50"/>
-      <c r="N11" s="55"/>
-      <c r="O11" s="56"/>
-      <c r="P11" s="50"/>
-      <c r="Q11" s="50"/>
-      <c r="R11" s="50"/>
-      <c r="S11" s="50"/>
-      <c r="T11" s="50"/>
-      <c r="U11" s="50"/>
-      <c r="V11" s="55"/>
-      <c r="W11" s="57"/>
-      <c r="X11" s="50"/>
-      <c r="Y11" s="50"/>
-      <c r="Z11" s="55"/>
-      <c r="AA11" s="56"/>
-      <c r="AB11" s="50"/>
-      <c r="AC11" s="50"/>
-      <c r="AD11" s="54"/>
-      <c r="AE11" s="55"/>
-      <c r="AF11" s="56"/>
-      <c r="AG11" s="50"/>
-      <c r="AH11" s="50"/>
-      <c r="AI11" s="50"/>
-      <c r="AJ11" s="50"/>
-      <c r="AK11" s="50"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="52"/>
+      <c r="M11" s="48"/>
+      <c r="N11" s="53"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="48"/>
+      <c r="Q11" s="48"/>
+      <c r="R11" s="48"/>
+      <c r="S11" s="48"/>
+      <c r="T11" s="48"/>
+      <c r="U11" s="48"/>
+      <c r="V11" s="53"/>
+      <c r="W11" s="55"/>
+      <c r="X11" s="48"/>
+      <c r="Y11" s="48"/>
+      <c r="Z11" s="53"/>
+      <c r="AA11" s="54"/>
+      <c r="AB11" s="48"/>
+      <c r="AC11" s="48"/>
+      <c r="AD11" s="52"/>
+      <c r="AE11" s="53"/>
+      <c r="AF11" s="54"/>
+      <c r="AG11" s="48"/>
+      <c r="AH11" s="48"/>
+      <c r="AI11" s="48"/>
+      <c r="AJ11" s="48"/>
+      <c r="AK11" s="48"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="48"/>
-      <c r="C12" s="49" t="s">
-        <v>121</v>
-      </c>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="54"/>
-      <c r="M12" s="50"/>
-      <c r="N12" s="55"/>
-      <c r="O12" s="56"/>
-      <c r="P12" s="50"/>
-      <c r="Q12" s="50"/>
-      <c r="R12" s="50"/>
-      <c r="S12" s="50"/>
-      <c r="T12" s="50"/>
-      <c r="U12" s="50"/>
-      <c r="V12" s="55"/>
-      <c r="W12" s="57"/>
-      <c r="X12" s="50"/>
-      <c r="Y12" s="50"/>
-      <c r="Z12" s="55"/>
-      <c r="AA12" s="56"/>
-      <c r="AB12" s="50"/>
-      <c r="AC12" s="50"/>
-      <c r="AD12" s="54"/>
-      <c r="AE12" s="55"/>
-      <c r="AF12" s="53"/>
-      <c r="AG12" s="64"/>
-      <c r="AH12" s="64"/>
-      <c r="AI12" s="64"/>
-      <c r="AJ12" s="64"/>
-      <c r="AK12" s="64"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="48"/>
+      <c r="K12" s="48"/>
+      <c r="L12" s="52"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="54"/>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="48"/>
+      <c r="R12" s="48"/>
+      <c r="S12" s="48"/>
+      <c r="T12" s="48"/>
+      <c r="U12" s="48"/>
+      <c r="V12" s="53"/>
+      <c r="W12" s="55"/>
+      <c r="X12" s="48"/>
+      <c r="Y12" s="48"/>
+      <c r="Z12" s="53"/>
+      <c r="AA12" s="54"/>
+      <c r="AB12" s="48"/>
+      <c r="AC12" s="48"/>
+      <c r="AD12" s="52"/>
+      <c r="AE12" s="53"/>
+      <c r="AF12" s="51"/>
+      <c r="AG12" s="62"/>
+      <c r="AH12" s="62"/>
+      <c r="AI12" s="62"/>
+      <c r="AJ12" s="62"/>
+      <c r="AK12" s="62"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="48"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="50"/>
-      <c r="K13" s="50"/>
-      <c r="L13" s="54"/>
-      <c r="M13" s="50"/>
-      <c r="N13" s="55"/>
-      <c r="O13" s="56"/>
-      <c r="P13" s="50"/>
-      <c r="Q13" s="50"/>
-      <c r="R13" s="50"/>
-      <c r="S13" s="50"/>
-      <c r="T13" s="50"/>
-      <c r="U13" s="50"/>
-      <c r="V13" s="55"/>
-      <c r="W13" s="57"/>
-      <c r="X13" s="50"/>
-      <c r="Y13" s="50"/>
-      <c r="Z13" s="55"/>
-      <c r="AA13" s="56"/>
-      <c r="AB13" s="50"/>
-      <c r="AC13" s="50"/>
-      <c r="AD13" s="54"/>
-      <c r="AE13" s="55"/>
-      <c r="AF13" s="56"/>
-      <c r="AG13" s="50"/>
-      <c r="AH13" s="50"/>
-      <c r="AI13" s="50"/>
-      <c r="AJ13" s="50"/>
-      <c r="AK13" s="50"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="52"/>
+      <c r="M13" s="48"/>
+      <c r="N13" s="53"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="48"/>
+      <c r="Q13" s="48"/>
+      <c r="R13" s="48"/>
+      <c r="S13" s="48"/>
+      <c r="T13" s="48"/>
+      <c r="U13" s="48"/>
+      <c r="V13" s="53"/>
+      <c r="W13" s="55"/>
+      <c r="X13" s="48"/>
+      <c r="Y13" s="48"/>
+      <c r="Z13" s="53"/>
+      <c r="AA13" s="54"/>
+      <c r="AB13" s="48"/>
+      <c r="AC13" s="48"/>
+      <c r="AD13" s="52"/>
+      <c r="AE13" s="53"/>
+      <c r="AF13" s="54"/>
+      <c r="AG13" s="48"/>
+      <c r="AH13" s="48"/>
+      <c r="AI13" s="48"/>
+      <c r="AJ13" s="48"/>
+      <c r="AK13" s="48"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="66" t="s">
-        <v>122</v>
-      </c>
-      <c r="C14" s="67" t="s">
+      <c r="B14" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="68"/>
-      <c r="I14" s="69"/>
-      <c r="J14" s="69"/>
-      <c r="K14" s="69"/>
-      <c r="L14" s="54"/>
-      <c r="M14" s="69"/>
-      <c r="N14" s="70"/>
-      <c r="O14" s="68"/>
-      <c r="P14" s="69"/>
-      <c r="Q14" s="69"/>
-      <c r="R14" s="69"/>
-      <c r="S14" s="69"/>
-      <c r="T14" s="69"/>
-      <c r="U14" s="69"/>
-      <c r="V14" s="70"/>
-      <c r="W14" s="57"/>
-      <c r="X14" s="69"/>
-      <c r="Y14" s="69"/>
-      <c r="Z14" s="70"/>
-      <c r="AA14" s="68"/>
-      <c r="AB14" s="69"/>
-      <c r="AC14" s="69"/>
-      <c r="AD14" s="54"/>
-      <c r="AE14" s="70"/>
-      <c r="AF14" s="68"/>
-      <c r="AG14" s="69"/>
-      <c r="AH14" s="69"/>
-      <c r="AI14" s="69"/>
-      <c r="AJ14" s="69"/>
-      <c r="AK14" s="69"/>
+      <c r="C14" s="65" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="67"/>
+      <c r="J14" s="67"/>
+      <c r="K14" s="67"/>
+      <c r="L14" s="52"/>
+      <c r="M14" s="67"/>
+      <c r="N14" s="68"/>
+      <c r="O14" s="66"/>
+      <c r="P14" s="67"/>
+      <c r="Q14" s="67"/>
+      <c r="R14" s="67"/>
+      <c r="S14" s="67"/>
+      <c r="T14" s="67"/>
+      <c r="U14" s="67"/>
+      <c r="V14" s="68"/>
+      <c r="W14" s="55"/>
+      <c r="X14" s="67"/>
+      <c r="Y14" s="67"/>
+      <c r="Z14" s="68"/>
+      <c r="AA14" s="66"/>
+      <c r="AB14" s="67"/>
+      <c r="AC14" s="67"/>
+      <c r="AD14" s="52"/>
+      <c r="AE14" s="68"/>
+      <c r="AF14" s="66"/>
+      <c r="AG14" s="67"/>
+      <c r="AH14" s="67"/>
+      <c r="AI14" s="67"/>
+      <c r="AJ14" s="67"/>
+      <c r="AK14" s="67"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="66"/>
-      <c r="C15" s="67"/>
-      <c r="D15" s="69"/>
-      <c r="E15" s="63"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="69"/>
-      <c r="J15" s="69"/>
-      <c r="K15" s="69"/>
-      <c r="L15" s="54"/>
-      <c r="M15" s="69"/>
-      <c r="N15" s="70"/>
-      <c r="O15" s="68"/>
-      <c r="P15" s="69"/>
-      <c r="Q15" s="69"/>
-      <c r="R15" s="69"/>
-      <c r="S15" s="69"/>
-      <c r="T15" s="69"/>
-      <c r="U15" s="69"/>
-      <c r="V15" s="70"/>
-      <c r="W15" s="57"/>
-      <c r="X15" s="69"/>
-      <c r="Y15" s="69"/>
-      <c r="Z15" s="70"/>
-      <c r="AA15" s="68"/>
-      <c r="AB15" s="69"/>
-      <c r="AC15" s="69"/>
-      <c r="AD15" s="54"/>
-      <c r="AE15" s="70"/>
-      <c r="AF15" s="68"/>
-      <c r="AG15" s="69"/>
-      <c r="AH15" s="69"/>
-      <c r="AI15" s="69"/>
-      <c r="AJ15" s="69"/>
-      <c r="AK15" s="69"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="67"/>
+      <c r="J15" s="67"/>
+      <c r="K15" s="67"/>
+      <c r="L15" s="52"/>
+      <c r="M15" s="67"/>
+      <c r="N15" s="68"/>
+      <c r="O15" s="66"/>
+      <c r="P15" s="67"/>
+      <c r="Q15" s="67"/>
+      <c r="R15" s="67"/>
+      <c r="S15" s="67"/>
+      <c r="T15" s="67"/>
+      <c r="U15" s="67"/>
+      <c r="V15" s="68"/>
+      <c r="W15" s="55"/>
+      <c r="X15" s="67"/>
+      <c r="Y15" s="67"/>
+      <c r="Z15" s="68"/>
+      <c r="AA15" s="66"/>
+      <c r="AB15" s="67"/>
+      <c r="AC15" s="67"/>
+      <c r="AD15" s="52"/>
+      <c r="AE15" s="68"/>
+      <c r="AF15" s="66"/>
+      <c r="AG15" s="67"/>
+      <c r="AH15" s="67"/>
+      <c r="AI15" s="67"/>
+      <c r="AJ15" s="67"/>
+      <c r="AK15" s="67"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="66"/>
-      <c r="C16" s="67" t="s">
-        <v>124</v>
-      </c>
-      <c r="D16" s="64"/>
-      <c r="E16" s="64"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="70"/>
-      <c r="H16" s="68"/>
-      <c r="I16" s="69"/>
-      <c r="J16" s="69"/>
-      <c r="K16" s="69"/>
-      <c r="L16" s="54"/>
-      <c r="M16" s="69"/>
-      <c r="N16" s="70"/>
-      <c r="O16" s="68"/>
-      <c r="P16" s="69"/>
-      <c r="Q16" s="69"/>
-      <c r="R16" s="69"/>
-      <c r="S16" s="69"/>
-      <c r="T16" s="69"/>
-      <c r="U16" s="69"/>
-      <c r="V16" s="70"/>
-      <c r="W16" s="57"/>
-      <c r="X16" s="69"/>
-      <c r="Y16" s="69"/>
-      <c r="Z16" s="70"/>
-      <c r="AA16" s="68"/>
-      <c r="AB16" s="69"/>
-      <c r="AC16" s="69"/>
-      <c r="AD16" s="54"/>
-      <c r="AE16" s="70"/>
-      <c r="AF16" s="68"/>
-      <c r="AG16" s="69"/>
-      <c r="AH16" s="69"/>
-      <c r="AI16" s="69"/>
-      <c r="AJ16" s="69"/>
-      <c r="AK16" s="69"/>
+      <c r="B16" s="64"/>
+      <c r="C16" s="65" t="s">
+        <v>125</v>
+      </c>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="68"/>
+      <c r="H16" s="66"/>
+      <c r="I16" s="67"/>
+      <c r="J16" s="67"/>
+      <c r="K16" s="67"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="67"/>
+      <c r="N16" s="68"/>
+      <c r="O16" s="66"/>
+      <c r="P16" s="67"/>
+      <c r="Q16" s="67"/>
+      <c r="R16" s="67"/>
+      <c r="S16" s="67"/>
+      <c r="T16" s="67"/>
+      <c r="U16" s="67"/>
+      <c r="V16" s="68"/>
+      <c r="W16" s="55"/>
+      <c r="X16" s="67"/>
+      <c r="Y16" s="67"/>
+      <c r="Z16" s="68"/>
+      <c r="AA16" s="66"/>
+      <c r="AB16" s="67"/>
+      <c r="AC16" s="67"/>
+      <c r="AD16" s="52"/>
+      <c r="AE16" s="68"/>
+      <c r="AF16" s="66"/>
+      <c r="AG16" s="67"/>
+      <c r="AH16" s="67"/>
+      <c r="AI16" s="67"/>
+      <c r="AJ16" s="67"/>
+      <c r="AK16" s="67"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="66"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="71"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="72"/>
-      <c r="G17" s="70"/>
-      <c r="H17" s="68"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="69"/>
-      <c r="L17" s="54"/>
-      <c r="M17" s="69"/>
-      <c r="N17" s="70"/>
-      <c r="O17" s="68"/>
-      <c r="P17" s="69"/>
-      <c r="Q17" s="69"/>
-      <c r="R17" s="69"/>
-      <c r="S17" s="69"/>
-      <c r="T17" s="69"/>
-      <c r="U17" s="69"/>
-      <c r="V17" s="70"/>
-      <c r="W17" s="57"/>
-      <c r="X17" s="69"/>
-      <c r="Y17" s="69"/>
-      <c r="Z17" s="70"/>
-      <c r="AA17" s="68"/>
-      <c r="AB17" s="69"/>
-      <c r="AC17" s="69"/>
-      <c r="AD17" s="54"/>
-      <c r="AE17" s="70"/>
-      <c r="AF17" s="68"/>
-      <c r="AG17" s="69"/>
-      <c r="AH17" s="69"/>
-      <c r="AI17" s="69"/>
-      <c r="AJ17" s="69"/>
-      <c r="AK17" s="69"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="67"/>
+      <c r="J17" s="67"/>
+      <c r="K17" s="67"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="67"/>
+      <c r="N17" s="68"/>
+      <c r="O17" s="66"/>
+      <c r="P17" s="67"/>
+      <c r="Q17" s="67"/>
+      <c r="R17" s="67"/>
+      <c r="S17" s="67"/>
+      <c r="T17" s="67"/>
+      <c r="U17" s="67"/>
+      <c r="V17" s="68"/>
+      <c r="W17" s="55"/>
+      <c r="X17" s="67"/>
+      <c r="Y17" s="67"/>
+      <c r="Z17" s="68"/>
+      <c r="AA17" s="66"/>
+      <c r="AB17" s="67"/>
+      <c r="AC17" s="67"/>
+      <c r="AD17" s="52"/>
+      <c r="AE17" s="68"/>
+      <c r="AF17" s="66"/>
+      <c r="AG17" s="67"/>
+      <c r="AH17" s="67"/>
+      <c r="AI17" s="67"/>
+      <c r="AJ17" s="67"/>
+      <c r="AK17" s="67"/>
       <c r="AN17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="66"/>
-      <c r="C18" s="67" t="s">
-        <v>126</v>
-      </c>
-      <c r="D18" s="64"/>
-      <c r="E18" s="64"/>
-      <c r="F18" s="72"/>
-      <c r="G18" s="70"/>
-      <c r="H18" s="68"/>
-      <c r="I18" s="69"/>
-      <c r="J18" s="69"/>
-      <c r="K18" s="69"/>
-      <c r="L18" s="54"/>
-      <c r="M18" s="69"/>
-      <c r="N18" s="70"/>
-      <c r="O18" s="68"/>
-      <c r="P18" s="69"/>
-      <c r="Q18" s="69"/>
-      <c r="R18" s="69"/>
-      <c r="S18" s="69"/>
-      <c r="T18" s="69"/>
-      <c r="U18" s="69"/>
-      <c r="V18" s="70"/>
-      <c r="W18" s="57"/>
-      <c r="X18" s="69"/>
-      <c r="Y18" s="69"/>
-      <c r="Z18" s="70"/>
-      <c r="AA18" s="68"/>
-      <c r="AB18" s="69"/>
-      <c r="AC18" s="69"/>
-      <c r="AD18" s="54"/>
-      <c r="AE18" s="70"/>
-      <c r="AF18" s="68"/>
-      <c r="AG18" s="69"/>
-      <c r="AH18" s="69"/>
-      <c r="AI18" s="69"/>
-      <c r="AJ18" s="69"/>
-      <c r="AK18" s="69"/>
+      <c r="B18" s="64"/>
+      <c r="C18" s="65" t="s">
+        <v>127</v>
+      </c>
+      <c r="D18" s="62"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="66"/>
+      <c r="I18" s="67"/>
+      <c r="J18" s="67"/>
+      <c r="K18" s="67"/>
+      <c r="L18" s="52"/>
+      <c r="M18" s="67"/>
+      <c r="N18" s="68"/>
+      <c r="O18" s="66"/>
+      <c r="P18" s="67"/>
+      <c r="Q18" s="67"/>
+      <c r="R18" s="67"/>
+      <c r="S18" s="67"/>
+      <c r="T18" s="67"/>
+      <c r="U18" s="67"/>
+      <c r="V18" s="68"/>
+      <c r="W18" s="55"/>
+      <c r="X18" s="67"/>
+      <c r="Y18" s="67"/>
+      <c r="Z18" s="68"/>
+      <c r="AA18" s="66"/>
+      <c r="AB18" s="67"/>
+      <c r="AC18" s="67"/>
+      <c r="AD18" s="52"/>
+      <c r="AE18" s="68"/>
+      <c r="AF18" s="66"/>
+      <c r="AG18" s="67"/>
+      <c r="AH18" s="67"/>
+      <c r="AI18" s="67"/>
+      <c r="AJ18" s="67"/>
+      <c r="AK18" s="67"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="66"/>
-      <c r="C19" s="67"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="73"/>
-      <c r="G19" s="70"/>
-      <c r="H19" s="68"/>
-      <c r="I19" s="69"/>
-      <c r="J19" s="69"/>
-      <c r="K19" s="69"/>
-      <c r="L19" s="54"/>
-      <c r="M19" s="69"/>
-      <c r="N19" s="70"/>
-      <c r="O19" s="68"/>
-      <c r="P19" s="69"/>
-      <c r="Q19" s="69"/>
-      <c r="R19" s="69"/>
-      <c r="S19" s="69"/>
-      <c r="T19" s="69"/>
-      <c r="U19" s="69"/>
-      <c r="V19" s="70"/>
-      <c r="W19" s="57"/>
-      <c r="X19" s="69"/>
-      <c r="Y19" s="69"/>
-      <c r="Z19" s="70"/>
-      <c r="AA19" s="68"/>
-      <c r="AB19" s="69"/>
-      <c r="AC19" s="69"/>
-      <c r="AD19" s="54"/>
-      <c r="AE19" s="70"/>
-      <c r="AF19" s="68"/>
-      <c r="AG19" s="69"/>
-      <c r="AH19" s="69"/>
-      <c r="AI19" s="69"/>
-      <c r="AJ19" s="69"/>
-      <c r="AK19" s="69"/>
+      <c r="B19" s="64"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="67"/>
+      <c r="J19" s="67"/>
+      <c r="K19" s="67"/>
+      <c r="L19" s="52"/>
+      <c r="M19" s="67"/>
+      <c r="N19" s="68"/>
+      <c r="O19" s="66"/>
+      <c r="P19" s="67"/>
+      <c r="Q19" s="67"/>
+      <c r="R19" s="67"/>
+      <c r="S19" s="67"/>
+      <c r="T19" s="67"/>
+      <c r="U19" s="67"/>
+      <c r="V19" s="68"/>
+      <c r="W19" s="55"/>
+      <c r="X19" s="67"/>
+      <c r="Y19" s="67"/>
+      <c r="Z19" s="68"/>
+      <c r="AA19" s="66"/>
+      <c r="AB19" s="67"/>
+      <c r="AC19" s="67"/>
+      <c r="AD19" s="52"/>
+      <c r="AE19" s="68"/>
+      <c r="AF19" s="66"/>
+      <c r="AG19" s="67"/>
+      <c r="AH19" s="67"/>
+      <c r="AI19" s="67"/>
+      <c r="AJ19" s="67"/>
+      <c r="AK19" s="67"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="66"/>
-      <c r="C20" s="67" t="s">
-        <v>127</v>
-      </c>
-      <c r="D20" s="69"/>
-      <c r="E20" s="69"/>
-      <c r="F20" s="72"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="69"/>
-      <c r="K20" s="69"/>
-      <c r="L20" s="54"/>
-      <c r="M20" s="69"/>
-      <c r="N20" s="70"/>
-      <c r="O20" s="68"/>
-      <c r="P20" s="69"/>
-      <c r="Q20" s="69"/>
-      <c r="R20" s="69"/>
-      <c r="S20" s="69"/>
-      <c r="T20" s="69"/>
-      <c r="U20" s="69"/>
-      <c r="V20" s="70"/>
-      <c r="W20" s="57"/>
-      <c r="X20" s="69"/>
-      <c r="Y20" s="69"/>
-      <c r="Z20" s="70"/>
-      <c r="AA20" s="68"/>
-      <c r="AB20" s="69"/>
-      <c r="AC20" s="69"/>
-      <c r="AD20" s="54"/>
-      <c r="AE20" s="70"/>
-      <c r="AF20" s="68"/>
-      <c r="AG20" s="69"/>
-      <c r="AH20" s="69"/>
-      <c r="AI20" s="69"/>
-      <c r="AJ20" s="69"/>
-      <c r="AK20" s="69"/>
+      <c r="B20" s="64"/>
+      <c r="C20" s="65" t="s">
+        <v>128</v>
+      </c>
+      <c r="D20" s="67"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="67"/>
+      <c r="K20" s="67"/>
+      <c r="L20" s="52"/>
+      <c r="M20" s="67"/>
+      <c r="N20" s="68"/>
+      <c r="O20" s="66"/>
+      <c r="P20" s="67"/>
+      <c r="Q20" s="67"/>
+      <c r="R20" s="67"/>
+      <c r="S20" s="67"/>
+      <c r="T20" s="67"/>
+      <c r="U20" s="67"/>
+      <c r="V20" s="68"/>
+      <c r="W20" s="55"/>
+      <c r="X20" s="67"/>
+      <c r="Y20" s="67"/>
+      <c r="Z20" s="68"/>
+      <c r="AA20" s="66"/>
+      <c r="AB20" s="67"/>
+      <c r="AC20" s="67"/>
+      <c r="AD20" s="52"/>
+      <c r="AE20" s="68"/>
+      <c r="AF20" s="66"/>
+      <c r="AG20" s="67"/>
+      <c r="AH20" s="67"/>
+      <c r="AI20" s="67"/>
+      <c r="AJ20" s="67"/>
+      <c r="AK20" s="67"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="66"/>
-      <c r="C21" s="67"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="72"/>
-      <c r="G21" s="70"/>
-      <c r="H21" s="68"/>
-      <c r="I21" s="63"/>
-      <c r="J21" s="69"/>
-      <c r="K21" s="69"/>
-      <c r="L21" s="54"/>
-      <c r="M21" s="69"/>
-      <c r="N21" s="70"/>
-      <c r="O21" s="68"/>
-      <c r="P21" s="69"/>
-      <c r="Q21" s="69"/>
-      <c r="R21" s="69"/>
-      <c r="S21" s="69"/>
-      <c r="T21" s="69"/>
-      <c r="U21" s="69"/>
-      <c r="V21" s="70"/>
-      <c r="W21" s="57"/>
-      <c r="X21" s="69"/>
-      <c r="Y21" s="69"/>
-      <c r="Z21" s="70"/>
-      <c r="AA21" s="68"/>
-      <c r="AB21" s="69"/>
-      <c r="AC21" s="69"/>
-      <c r="AD21" s="54"/>
-      <c r="AE21" s="70"/>
-      <c r="AF21" s="68"/>
-      <c r="AG21" s="69"/>
-      <c r="AH21" s="69"/>
-      <c r="AI21" s="69"/>
-      <c r="AJ21" s="69"/>
-      <c r="AK21" s="69"/>
+      <c r="B21" s="64"/>
+      <c r="C21" s="65"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="66"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="67"/>
+      <c r="K21" s="67"/>
+      <c r="L21" s="52"/>
+      <c r="M21" s="67"/>
+      <c r="N21" s="68"/>
+      <c r="O21" s="66"/>
+      <c r="P21" s="67"/>
+      <c r="Q21" s="67"/>
+      <c r="R21" s="67"/>
+      <c r="S21" s="67"/>
+      <c r="T21" s="67"/>
+      <c r="U21" s="67"/>
+      <c r="V21" s="68"/>
+      <c r="W21" s="55"/>
+      <c r="X21" s="67"/>
+      <c r="Y21" s="67"/>
+      <c r="Z21" s="68"/>
+      <c r="AA21" s="66"/>
+      <c r="AB21" s="67"/>
+      <c r="AC21" s="67"/>
+      <c r="AD21" s="52"/>
+      <c r="AE21" s="68"/>
+      <c r="AF21" s="66"/>
+      <c r="AG21" s="67"/>
+      <c r="AH21" s="67"/>
+      <c r="AI21" s="67"/>
+      <c r="AJ21" s="67"/>
+      <c r="AK21" s="67"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="66"/>
-      <c r="C22" s="67" t="s">
-        <v>128</v>
-      </c>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="69"/>
-      <c r="K22" s="69"/>
-      <c r="L22" s="54"/>
-      <c r="M22" s="69"/>
-      <c r="N22" s="70"/>
-      <c r="O22" s="68"/>
-      <c r="P22" s="69"/>
-      <c r="Q22" s="69"/>
-      <c r="R22" s="69"/>
-      <c r="S22" s="69"/>
-      <c r="T22" s="69"/>
-      <c r="U22" s="69"/>
-      <c r="V22" s="70"/>
-      <c r="W22" s="57"/>
-      <c r="X22" s="69"/>
-      <c r="Y22" s="69"/>
-      <c r="Z22" s="70"/>
-      <c r="AA22" s="68"/>
-      <c r="AB22" s="69"/>
-      <c r="AC22" s="69"/>
-      <c r="AD22" s="54"/>
-      <c r="AE22" s="70"/>
-      <c r="AF22" s="68"/>
-      <c r="AG22" s="69"/>
-      <c r="AH22" s="69"/>
-      <c r="AI22" s="69"/>
-      <c r="AJ22" s="69"/>
-      <c r="AK22" s="69"/>
+      <c r="B22" s="64"/>
+      <c r="C22" s="65" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="52"/>
+      <c r="M22" s="67"/>
+      <c r="N22" s="68"/>
+      <c r="O22" s="66"/>
+      <c r="P22" s="67"/>
+      <c r="Q22" s="67"/>
+      <c r="R22" s="67"/>
+      <c r="S22" s="67"/>
+      <c r="T22" s="67"/>
+      <c r="U22" s="67"/>
+      <c r="V22" s="68"/>
+      <c r="W22" s="55"/>
+      <c r="X22" s="67"/>
+      <c r="Y22" s="67"/>
+      <c r="Z22" s="68"/>
+      <c r="AA22" s="66"/>
+      <c r="AB22" s="67"/>
+      <c r="AC22" s="67"/>
+      <c r="AD22" s="52"/>
+      <c r="AE22" s="68"/>
+      <c r="AF22" s="66"/>
+      <c r="AG22" s="67"/>
+      <c r="AH22" s="67"/>
+      <c r="AI22" s="67"/>
+      <c r="AJ22" s="67"/>
+      <c r="AK22" s="67"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="66"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="69"/>
-      <c r="E23" s="69"/>
-      <c r="F23" s="72"/>
-      <c r="G23" s="70"/>
-      <c r="H23" s="68"/>
-      <c r="I23" s="63"/>
-      <c r="J23" s="59"/>
-      <c r="K23" s="69"/>
-      <c r="L23" s="54"/>
-      <c r="M23" s="69"/>
-      <c r="N23" s="70"/>
-      <c r="O23" s="68"/>
-      <c r="P23" s="69"/>
-      <c r="Q23" s="69"/>
-      <c r="R23" s="69"/>
-      <c r="S23" s="69"/>
-      <c r="T23" s="69"/>
-      <c r="U23" s="69"/>
-      <c r="V23" s="70"/>
-      <c r="W23" s="57"/>
-      <c r="X23" s="69"/>
-      <c r="Y23" s="69"/>
-      <c r="Z23" s="70"/>
-      <c r="AA23" s="68"/>
-      <c r="AB23" s="69"/>
-      <c r="AC23" s="69"/>
-      <c r="AD23" s="54"/>
-      <c r="AE23" s="70"/>
-      <c r="AF23" s="68"/>
-      <c r="AG23" s="69"/>
-      <c r="AH23" s="69"/>
-      <c r="AI23" s="69"/>
-      <c r="AJ23" s="69"/>
-      <c r="AK23" s="69"/>
+      <c r="B23" s="64"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="67"/>
+      <c r="L23" s="52"/>
+      <c r="M23" s="67"/>
+      <c r="N23" s="68"/>
+      <c r="O23" s="66"/>
+      <c r="P23" s="67"/>
+      <c r="Q23" s="67"/>
+      <c r="R23" s="67"/>
+      <c r="S23" s="67"/>
+      <c r="T23" s="67"/>
+      <c r="U23" s="67"/>
+      <c r="V23" s="68"/>
+      <c r="W23" s="55"/>
+      <c r="X23" s="67"/>
+      <c r="Y23" s="67"/>
+      <c r="Z23" s="68"/>
+      <c r="AA23" s="66"/>
+      <c r="AB23" s="67"/>
+      <c r="AC23" s="67"/>
+      <c r="AD23" s="52"/>
+      <c r="AE23" s="68"/>
+      <c r="AF23" s="66"/>
+      <c r="AG23" s="67"/>
+      <c r="AH23" s="67"/>
+      <c r="AI23" s="67"/>
+      <c r="AJ23" s="67"/>
+      <c r="AK23" s="67"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="66"/>
-      <c r="C24" s="67" t="s">
-        <v>129</v>
-      </c>
-      <c r="D24" s="69"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="72"/>
-      <c r="G24" s="70"/>
-      <c r="H24" s="68"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="69"/>
-      <c r="K24" s="69"/>
-      <c r="L24" s="54"/>
-      <c r="M24" s="69"/>
-      <c r="N24" s="70"/>
-      <c r="O24" s="68"/>
-      <c r="P24" s="69"/>
-      <c r="Q24" s="69"/>
-      <c r="R24" s="69"/>
-      <c r="S24" s="69"/>
-      <c r="T24" s="69"/>
-      <c r="U24" s="69"/>
-      <c r="V24" s="70"/>
-      <c r="W24" s="57"/>
-      <c r="X24" s="69"/>
-      <c r="Y24" s="69"/>
-      <c r="Z24" s="70"/>
-      <c r="AA24" s="68"/>
-      <c r="AB24" s="69"/>
-      <c r="AC24" s="69"/>
-      <c r="AD24" s="54"/>
-      <c r="AE24" s="70"/>
-      <c r="AF24" s="68"/>
-      <c r="AG24" s="69"/>
-      <c r="AH24" s="69"/>
-      <c r="AI24" s="69"/>
-      <c r="AJ24" s="69"/>
-      <c r="AK24" s="69"/>
+      <c r="B24" s="64"/>
+      <c r="C24" s="65" t="s">
+        <v>130</v>
+      </c>
+      <c r="D24" s="67"/>
+      <c r="E24" s="67"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="68"/>
+      <c r="H24" s="66"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="67"/>
+      <c r="K24" s="67"/>
+      <c r="L24" s="52"/>
+      <c r="M24" s="67"/>
+      <c r="N24" s="68"/>
+      <c r="O24" s="66"/>
+      <c r="P24" s="67"/>
+      <c r="Q24" s="67"/>
+      <c r="R24" s="67"/>
+      <c r="S24" s="67"/>
+      <c r="T24" s="67"/>
+      <c r="U24" s="67"/>
+      <c r="V24" s="68"/>
+      <c r="W24" s="55"/>
+      <c r="X24" s="67"/>
+      <c r="Y24" s="67"/>
+      <c r="Z24" s="68"/>
+      <c r="AA24" s="66"/>
+      <c r="AB24" s="67"/>
+      <c r="AC24" s="67"/>
+      <c r="AD24" s="52"/>
+      <c r="AE24" s="68"/>
+      <c r="AF24" s="66"/>
+      <c r="AG24" s="67"/>
+      <c r="AH24" s="67"/>
+      <c r="AI24" s="67"/>
+      <c r="AJ24" s="67"/>
+      <c r="AK24" s="67"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="66"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="72"/>
-      <c r="G25" s="70"/>
-      <c r="H25" s="68"/>
-      <c r="I25" s="69"/>
-      <c r="J25" s="59"/>
-      <c r="K25" s="69"/>
-      <c r="L25" s="54"/>
-      <c r="M25" s="69"/>
-      <c r="N25" s="70"/>
-      <c r="O25" s="68"/>
-      <c r="P25" s="69"/>
-      <c r="Q25" s="69"/>
-      <c r="R25" s="69"/>
-      <c r="S25" s="69"/>
-      <c r="T25" s="69"/>
-      <c r="U25" s="69"/>
-      <c r="V25" s="70"/>
-      <c r="W25" s="57"/>
-      <c r="X25" s="69"/>
-      <c r="Y25" s="69"/>
-      <c r="Z25" s="70"/>
-      <c r="AA25" s="68"/>
-      <c r="AB25" s="69"/>
-      <c r="AC25" s="69"/>
-      <c r="AD25" s="54"/>
-      <c r="AE25" s="70"/>
-      <c r="AF25" s="68"/>
-      <c r="AG25" s="69"/>
-      <c r="AH25" s="69"/>
-      <c r="AI25" s="69"/>
-      <c r="AJ25" s="69"/>
-      <c r="AK25" s="69"/>
+      <c r="B25" s="64"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="67"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="67"/>
+      <c r="L25" s="52"/>
+      <c r="M25" s="67"/>
+      <c r="N25" s="68"/>
+      <c r="O25" s="66"/>
+      <c r="P25" s="67"/>
+      <c r="Q25" s="67"/>
+      <c r="R25" s="67"/>
+      <c r="S25" s="67"/>
+      <c r="T25" s="67"/>
+      <c r="U25" s="67"/>
+      <c r="V25" s="68"/>
+      <c r="W25" s="55"/>
+      <c r="X25" s="67"/>
+      <c r="Y25" s="67"/>
+      <c r="Z25" s="68"/>
+      <c r="AA25" s="66"/>
+      <c r="AB25" s="67"/>
+      <c r="AC25" s="67"/>
+      <c r="AD25" s="52"/>
+      <c r="AE25" s="68"/>
+      <c r="AF25" s="66"/>
+      <c r="AG25" s="67"/>
+      <c r="AH25" s="67"/>
+      <c r="AI25" s="67"/>
+      <c r="AJ25" s="67"/>
+      <c r="AK25" s="67"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="48" t="s">
-        <v>130</v>
-      </c>
-      <c r="C26" s="49" t="s">
+      <c r="B26" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="55"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="64"/>
-      <c r="J26" s="50"/>
-      <c r="K26" s="50"/>
-      <c r="L26" s="54"/>
-      <c r="M26" s="50"/>
-      <c r="N26" s="55"/>
-      <c r="O26" s="56"/>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50"/>
-      <c r="S26" s="50"/>
-      <c r="T26" s="50"/>
-      <c r="U26" s="50"/>
-      <c r="V26" s="55"/>
-      <c r="W26" s="57"/>
-      <c r="X26" s="50"/>
-      <c r="Y26" s="50"/>
-      <c r="Z26" s="55"/>
-      <c r="AA26" s="56"/>
-      <c r="AB26" s="50"/>
-      <c r="AC26" s="50"/>
-      <c r="AD26" s="54"/>
-      <c r="AE26" s="55"/>
-      <c r="AF26" s="56"/>
-      <c r="AG26" s="50"/>
-      <c r="AH26" s="50"/>
-      <c r="AI26" s="50"/>
-      <c r="AJ26" s="50"/>
-      <c r="AK26" s="50"/>
+      <c r="C26" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="62"/>
+      <c r="J26" s="48"/>
+      <c r="K26" s="48"/>
+      <c r="L26" s="52"/>
+      <c r="M26" s="48"/>
+      <c r="N26" s="53"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="48"/>
+      <c r="Q26" s="48"/>
+      <c r="R26" s="48"/>
+      <c r="S26" s="48"/>
+      <c r="T26" s="48"/>
+      <c r="U26" s="48"/>
+      <c r="V26" s="53"/>
+      <c r="W26" s="55"/>
+      <c r="X26" s="48"/>
+      <c r="Y26" s="48"/>
+      <c r="Z26" s="53"/>
+      <c r="AA26" s="54"/>
+      <c r="AB26" s="48"/>
+      <c r="AC26" s="48"/>
+      <c r="AD26" s="52"/>
+      <c r="AE26" s="53"/>
+      <c r="AF26" s="54"/>
+      <c r="AG26" s="48"/>
+      <c r="AH26" s="48"/>
+      <c r="AI26" s="48"/>
+      <c r="AJ26" s="48"/>
+      <c r="AK26" s="48"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="48"/>
-      <c r="C27" s="49"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="61"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="50"/>
-      <c r="K27" s="50"/>
-      <c r="L27" s="54"/>
-      <c r="M27" s="50"/>
-      <c r="N27" s="55"/>
-      <c r="O27" s="56"/>
-      <c r="P27" s="50"/>
-      <c r="Q27" s="50"/>
-      <c r="R27" s="50"/>
-      <c r="S27" s="50"/>
-      <c r="T27" s="50"/>
-      <c r="U27" s="50"/>
-      <c r="V27" s="55"/>
-      <c r="W27" s="57"/>
-      <c r="X27" s="50"/>
-      <c r="Y27" s="50"/>
-      <c r="Z27" s="55"/>
-      <c r="AA27" s="56"/>
-      <c r="AB27" s="50"/>
-      <c r="AC27" s="50"/>
-      <c r="AD27" s="54"/>
-      <c r="AE27" s="55"/>
-      <c r="AF27" s="56"/>
-      <c r="AG27" s="50"/>
-      <c r="AH27" s="50"/>
-      <c r="AI27" s="50"/>
-      <c r="AJ27" s="50"/>
-      <c r="AK27" s="50"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="48"/>
+      <c r="J27" s="48"/>
+      <c r="K27" s="48"/>
+      <c r="L27" s="52"/>
+      <c r="M27" s="48"/>
+      <c r="N27" s="53"/>
+      <c r="O27" s="54"/>
+      <c r="P27" s="48"/>
+      <c r="Q27" s="48"/>
+      <c r="R27" s="48"/>
+      <c r="S27" s="48"/>
+      <c r="T27" s="48"/>
+      <c r="U27" s="48"/>
+      <c r="V27" s="53"/>
+      <c r="W27" s="55"/>
+      <c r="X27" s="48"/>
+      <c r="Y27" s="48"/>
+      <c r="Z27" s="53"/>
+      <c r="AA27" s="54"/>
+      <c r="AB27" s="48"/>
+      <c r="AC27" s="48"/>
+      <c r="AD27" s="52"/>
+      <c r="AE27" s="53"/>
+      <c r="AF27" s="54"/>
+      <c r="AG27" s="48"/>
+      <c r="AH27" s="48"/>
+      <c r="AI27" s="48"/>
+      <c r="AJ27" s="48"/>
+      <c r="AK27" s="48"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="48"/>
-      <c r="C28" s="49" t="s">
-        <v>132</v>
-      </c>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="53"/>
-      <c r="I28" s="64"/>
-      <c r="J28" s="64"/>
-      <c r="K28" s="64"/>
-      <c r="L28" s="54"/>
-      <c r="M28" s="50"/>
-      <c r="N28" s="55"/>
-      <c r="O28" s="56"/>
-      <c r="P28" s="50"/>
-      <c r="Q28" s="50"/>
-      <c r="R28" s="50"/>
-      <c r="S28" s="50"/>
-      <c r="T28" s="50"/>
-      <c r="U28" s="50"/>
-      <c r="V28" s="55"/>
-      <c r="W28" s="57"/>
-      <c r="X28" s="50"/>
-      <c r="Y28" s="50"/>
-      <c r="Z28" s="55"/>
-      <c r="AA28" s="56"/>
-      <c r="AB28" s="50"/>
-      <c r="AC28" s="50"/>
-      <c r="AD28" s="54"/>
-      <c r="AE28" s="55"/>
-      <c r="AF28" s="56"/>
-      <c r="AG28" s="50"/>
-      <c r="AH28" s="50"/>
-      <c r="AI28" s="50"/>
-      <c r="AJ28" s="50"/>
-      <c r="AK28" s="50"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="D28" s="48"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="62"/>
+      <c r="K28" s="62"/>
+      <c r="L28" s="52"/>
+      <c r="M28" s="48"/>
+      <c r="N28" s="53"/>
+      <c r="O28" s="54"/>
+      <c r="P28" s="48"/>
+      <c r="Q28" s="48"/>
+      <c r="R28" s="48"/>
+      <c r="S28" s="48"/>
+      <c r="T28" s="48"/>
+      <c r="U28" s="48"/>
+      <c r="V28" s="53"/>
+      <c r="W28" s="55"/>
+      <c r="X28" s="48"/>
+      <c r="Y28" s="48"/>
+      <c r="Z28" s="53"/>
+      <c r="AA28" s="54"/>
+      <c r="AB28" s="48"/>
+      <c r="AC28" s="48"/>
+      <c r="AD28" s="52"/>
+      <c r="AE28" s="53"/>
+      <c r="AF28" s="54"/>
+      <c r="AG28" s="48"/>
+      <c r="AH28" s="48"/>
+      <c r="AI28" s="48"/>
+      <c r="AJ28" s="48"/>
+      <c r="AK28" s="48"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="48"/>
-      <c r="C29" s="49"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="61"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="50"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="54"/>
-      <c r="M29" s="50"/>
-      <c r="N29" s="55"/>
-      <c r="O29" s="56"/>
-      <c r="P29" s="50"/>
-      <c r="Q29" s="50"/>
-      <c r="R29" s="50"/>
-      <c r="S29" s="50"/>
-      <c r="T29" s="50"/>
-      <c r="U29" s="50"/>
-      <c r="V29" s="55"/>
-      <c r="W29" s="57"/>
-      <c r="X29" s="50"/>
-      <c r="Y29" s="50"/>
-      <c r="Z29" s="55"/>
-      <c r="AA29" s="56"/>
-      <c r="AB29" s="50"/>
-      <c r="AC29" s="50"/>
-      <c r="AD29" s="54"/>
-      <c r="AE29" s="55"/>
-      <c r="AF29" s="56"/>
-      <c r="AG29" s="50"/>
-      <c r="AH29" s="50"/>
-      <c r="AI29" s="50"/>
-      <c r="AJ29" s="50"/>
-      <c r="AK29" s="50"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="47"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="60"/>
+      <c r="I29" s="48"/>
+      <c r="J29" s="63"/>
+      <c r="K29" s="48"/>
+      <c r="L29" s="52"/>
+      <c r="M29" s="48"/>
+      <c r="N29" s="53"/>
+      <c r="O29" s="54"/>
+      <c r="P29" s="48"/>
+      <c r="Q29" s="48"/>
+      <c r="R29" s="48"/>
+      <c r="S29" s="48"/>
+      <c r="T29" s="48"/>
+      <c r="U29" s="48"/>
+      <c r="V29" s="53"/>
+      <c r="W29" s="55"/>
+      <c r="X29" s="48"/>
+      <c r="Y29" s="48"/>
+      <c r="Z29" s="53"/>
+      <c r="AA29" s="54"/>
+      <c r="AB29" s="48"/>
+      <c r="AC29" s="48"/>
+      <c r="AD29" s="52"/>
+      <c r="AE29" s="53"/>
+      <c r="AF29" s="54"/>
+      <c r="AG29" s="48"/>
+      <c r="AH29" s="48"/>
+      <c r="AI29" s="48"/>
+      <c r="AJ29" s="48"/>
+      <c r="AK29" s="48"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="48"/>
-      <c r="C30" s="49" t="s">
-        <v>133</v>
-      </c>
-      <c r="D30" s="50"/>
-      <c r="E30" s="50"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="55"/>
-      <c r="H30" s="53"/>
-      <c r="I30" s="64"/>
-      <c r="J30" s="64"/>
-      <c r="K30" s="64"/>
-      <c r="L30" s="54"/>
-      <c r="M30" s="64"/>
-      <c r="N30" s="55"/>
-      <c r="O30" s="56"/>
-      <c r="P30" s="50"/>
-      <c r="Q30" s="50"/>
-      <c r="R30" s="50"/>
-      <c r="S30" s="50"/>
-      <c r="T30" s="50"/>
-      <c r="U30" s="50"/>
-      <c r="V30" s="55"/>
-      <c r="W30" s="57"/>
-      <c r="X30" s="50"/>
-      <c r="Y30" s="50"/>
-      <c r="Z30" s="55"/>
-      <c r="AA30" s="56"/>
-      <c r="AB30" s="50"/>
-      <c r="AC30" s="50"/>
-      <c r="AD30" s="54"/>
-      <c r="AE30" s="55"/>
-      <c r="AF30" s="56"/>
-      <c r="AG30" s="50"/>
-      <c r="AH30" s="50"/>
-      <c r="AI30" s="50"/>
-      <c r="AJ30" s="50"/>
-      <c r="AK30" s="50"/>
+      <c r="B30" s="46"/>
+      <c r="C30" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="D30" s="48"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="62"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="52"/>
+      <c r="M30" s="62"/>
+      <c r="N30" s="53"/>
+      <c r="O30" s="54"/>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="48"/>
+      <c r="R30" s="48"/>
+      <c r="S30" s="48"/>
+      <c r="T30" s="48"/>
+      <c r="U30" s="48"/>
+      <c r="V30" s="53"/>
+      <c r="W30" s="55"/>
+      <c r="X30" s="48"/>
+      <c r="Y30" s="48"/>
+      <c r="Z30" s="53"/>
+      <c r="AA30" s="54"/>
+      <c r="AB30" s="48"/>
+      <c r="AC30" s="48"/>
+      <c r="AD30" s="52"/>
+      <c r="AE30" s="53"/>
+      <c r="AF30" s="54"/>
+      <c r="AG30" s="48"/>
+      <c r="AH30" s="48"/>
+      <c r="AI30" s="48"/>
+      <c r="AJ30" s="48"/>
+      <c r="AK30" s="48"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="48"/>
-      <c r="C31" s="49"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="60"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="62"/>
-      <c r="I31" s="50"/>
-      <c r="J31" s="65"/>
-      <c r="K31" s="65"/>
-      <c r="L31" s="74"/>
-      <c r="M31" s="50"/>
-      <c r="N31" s="61"/>
-      <c r="O31" s="56"/>
-      <c r="P31" s="50"/>
-      <c r="Q31" s="50"/>
-      <c r="R31" s="50"/>
-      <c r="S31" s="50"/>
-      <c r="T31" s="50"/>
-      <c r="U31" s="50"/>
-      <c r="V31" s="55"/>
-      <c r="W31" s="57"/>
-      <c r="X31" s="50"/>
-      <c r="Y31" s="50"/>
-      <c r="Z31" s="55"/>
-      <c r="AA31" s="56"/>
-      <c r="AB31" s="50"/>
-      <c r="AC31" s="50"/>
-      <c r="AD31" s="54"/>
-      <c r="AE31" s="55"/>
-      <c r="AF31" s="56"/>
-      <c r="AG31" s="50"/>
-      <c r="AH31" s="50"/>
-      <c r="AI31" s="50"/>
-      <c r="AJ31" s="50"/>
-      <c r="AK31" s="50"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="48"/>
+      <c r="J31" s="63"/>
+      <c r="K31" s="63"/>
+      <c r="L31" s="72"/>
+      <c r="M31" s="48"/>
+      <c r="N31" s="59"/>
+      <c r="O31" s="54"/>
+      <c r="P31" s="48"/>
+      <c r="Q31" s="48"/>
+      <c r="R31" s="48"/>
+      <c r="S31" s="48"/>
+      <c r="T31" s="48"/>
+      <c r="U31" s="48"/>
+      <c r="V31" s="53"/>
+      <c r="W31" s="55"/>
+      <c r="X31" s="48"/>
+      <c r="Y31" s="48"/>
+      <c r="Z31" s="53"/>
+      <c r="AA31" s="54"/>
+      <c r="AB31" s="48"/>
+      <c r="AC31" s="48"/>
+      <c r="AD31" s="52"/>
+      <c r="AE31" s="53"/>
+      <c r="AF31" s="54"/>
+      <c r="AG31" s="48"/>
+      <c r="AH31" s="48"/>
+      <c r="AI31" s="48"/>
+      <c r="AJ31" s="48"/>
+      <c r="AK31" s="48"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="48"/>
-      <c r="C32" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="D32" s="50"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="58"/>
-      <c r="G32" s="55"/>
-      <c r="H32" s="56"/>
-      <c r="I32" s="50"/>
-      <c r="J32" s="50"/>
-      <c r="K32" s="50"/>
-      <c r="L32" s="54"/>
-      <c r="M32" s="64"/>
-      <c r="N32" s="52"/>
-      <c r="O32" s="56"/>
-      <c r="P32" s="50"/>
-      <c r="Q32" s="50"/>
-      <c r="R32" s="50"/>
-      <c r="S32" s="50"/>
-      <c r="T32" s="50"/>
-      <c r="U32" s="50"/>
-      <c r="V32" s="55"/>
-      <c r="W32" s="57"/>
-      <c r="X32" s="50"/>
-      <c r="Y32" s="50"/>
-      <c r="Z32" s="55"/>
-      <c r="AA32" s="56"/>
-      <c r="AB32" s="50"/>
-      <c r="AC32" s="50"/>
-      <c r="AD32" s="54"/>
-      <c r="AE32" s="55"/>
-      <c r="AF32" s="56"/>
-      <c r="AG32" s="50"/>
-      <c r="AH32" s="50"/>
-      <c r="AI32" s="50"/>
-      <c r="AJ32" s="50"/>
-      <c r="AK32" s="50"/>
+      <c r="B32" s="46"/>
+      <c r="C32" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="D32" s="48"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="56"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="48"/>
+      <c r="J32" s="48"/>
+      <c r="K32" s="48"/>
+      <c r="L32" s="52"/>
+      <c r="M32" s="62"/>
+      <c r="N32" s="50"/>
+      <c r="O32" s="54"/>
+      <c r="P32" s="48"/>
+      <c r="Q32" s="48"/>
+      <c r="R32" s="48"/>
+      <c r="S32" s="48"/>
+      <c r="T32" s="48"/>
+      <c r="U32" s="48"/>
+      <c r="V32" s="53"/>
+      <c r="W32" s="55"/>
+      <c r="X32" s="48"/>
+      <c r="Y32" s="48"/>
+      <c r="Z32" s="53"/>
+      <c r="AA32" s="54"/>
+      <c r="AB32" s="48"/>
+      <c r="AC32" s="48"/>
+      <c r="AD32" s="52"/>
+      <c r="AE32" s="53"/>
+      <c r="AF32" s="54"/>
+      <c r="AG32" s="48"/>
+      <c r="AH32" s="48"/>
+      <c r="AI32" s="48"/>
+      <c r="AJ32" s="48"/>
+      <c r="AK32" s="48"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="48"/>
-      <c r="C33" s="49"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="58"/>
-      <c r="G33" s="55"/>
-      <c r="H33" s="56"/>
-      <c r="I33" s="50"/>
-      <c r="J33" s="50"/>
-      <c r="K33" s="50"/>
-      <c r="L33" s="54"/>
-      <c r="M33" s="50"/>
-      <c r="N33" s="61"/>
-      <c r="O33" s="56"/>
-      <c r="P33" s="50"/>
-      <c r="Q33" s="50"/>
-      <c r="R33" s="50"/>
-      <c r="S33" s="50"/>
-      <c r="T33" s="50"/>
-      <c r="U33" s="50"/>
-      <c r="V33" s="55"/>
-      <c r="W33" s="57"/>
-      <c r="X33" s="50"/>
-      <c r="Y33" s="50"/>
-      <c r="Z33" s="55"/>
-      <c r="AA33" s="56"/>
-      <c r="AB33" s="50"/>
-      <c r="AC33" s="50"/>
-      <c r="AD33" s="54"/>
-      <c r="AE33" s="55"/>
-      <c r="AF33" s="56"/>
-      <c r="AG33" s="50"/>
-      <c r="AH33" s="50"/>
-      <c r="AI33" s="50"/>
-      <c r="AJ33" s="50"/>
-      <c r="AK33" s="50"/>
+      <c r="B33" s="46"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="48"/>
+      <c r="J33" s="48"/>
+      <c r="K33" s="48"/>
+      <c r="L33" s="52"/>
+      <c r="M33" s="48"/>
+      <c r="N33" s="59"/>
+      <c r="O33" s="54"/>
+      <c r="P33" s="48"/>
+      <c r="Q33" s="48"/>
+      <c r="R33" s="48"/>
+      <c r="S33" s="48"/>
+      <c r="T33" s="48"/>
+      <c r="U33" s="48"/>
+      <c r="V33" s="53"/>
+      <c r="W33" s="55"/>
+      <c r="X33" s="48"/>
+      <c r="Y33" s="48"/>
+      <c r="Z33" s="53"/>
+      <c r="AA33" s="54"/>
+      <c r="AB33" s="48"/>
+      <c r="AC33" s="48"/>
+      <c r="AD33" s="52"/>
+      <c r="AE33" s="53"/>
+      <c r="AF33" s="54"/>
+      <c r="AG33" s="48"/>
+      <c r="AH33" s="48"/>
+      <c r="AI33" s="48"/>
+      <c r="AJ33" s="48"/>
+      <c r="AK33" s="48"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="66" t="s">
-        <v>135</v>
-      </c>
-      <c r="C34" s="75" t="s">
+      <c r="B34" s="64" t="s">
         <v>136</v>
       </c>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="72"/>
-      <c r="G34" s="70"/>
-      <c r="H34" s="68"/>
-      <c r="I34" s="69"/>
-      <c r="J34" s="69"/>
-      <c r="K34" s="69"/>
-      <c r="L34" s="54"/>
-      <c r="M34" s="64"/>
-      <c r="N34" s="52"/>
-      <c r="O34" s="53"/>
-      <c r="P34" s="64"/>
-      <c r="Q34" s="64"/>
-      <c r="R34" s="64"/>
-      <c r="S34" s="69"/>
-      <c r="T34" s="69"/>
-      <c r="U34" s="69"/>
-      <c r="V34" s="70"/>
-      <c r="W34" s="57"/>
-      <c r="X34" s="69"/>
-      <c r="Y34" s="69"/>
-      <c r="Z34" s="70"/>
-      <c r="AA34" s="68"/>
-      <c r="AB34" s="69"/>
-      <c r="AC34" s="69"/>
-      <c r="AD34" s="54"/>
-      <c r="AE34" s="70"/>
-      <c r="AF34" s="68"/>
-      <c r="AG34" s="69"/>
-      <c r="AH34" s="69"/>
-      <c r="AI34" s="69"/>
-      <c r="AJ34" s="69"/>
-      <c r="AK34" s="69"/>
+      <c r="C34" s="73" t="s">
+        <v>137</v>
+      </c>
+      <c r="D34" s="67"/>
+      <c r="E34" s="67"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="68"/>
+      <c r="H34" s="66"/>
+      <c r="I34" s="67"/>
+      <c r="J34" s="67"/>
+      <c r="K34" s="67"/>
+      <c r="L34" s="52"/>
+      <c r="M34" s="62"/>
+      <c r="N34" s="50"/>
+      <c r="O34" s="51"/>
+      <c r="P34" s="62"/>
+      <c r="Q34" s="62"/>
+      <c r="R34" s="62"/>
+      <c r="S34" s="67"/>
+      <c r="T34" s="67"/>
+      <c r="U34" s="67"/>
+      <c r="V34" s="68"/>
+      <c r="W34" s="55"/>
+      <c r="X34" s="67"/>
+      <c r="Y34" s="67"/>
+      <c r="Z34" s="68"/>
+      <c r="AA34" s="66"/>
+      <c r="AB34" s="67"/>
+      <c r="AC34" s="67"/>
+      <c r="AD34" s="52"/>
+      <c r="AE34" s="68"/>
+      <c r="AF34" s="66"/>
+      <c r="AG34" s="67"/>
+      <c r="AH34" s="67"/>
+      <c r="AI34" s="67"/>
+      <c r="AJ34" s="67"/>
+      <c r="AK34" s="67"/>
     </row>
     <row r="35" ht="12" customHeight="1">
-      <c r="B35" s="66"/>
-      <c r="C35" s="75"/>
-      <c r="D35" s="69"/>
-      <c r="E35" s="69"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="70"/>
-      <c r="H35" s="68"/>
-      <c r="I35" s="69"/>
-      <c r="J35" s="69"/>
-      <c r="K35" s="76"/>
-      <c r="L35" s="54"/>
-      <c r="M35" s="69"/>
-      <c r="N35" s="61"/>
-      <c r="O35" s="68"/>
-      <c r="P35" s="63"/>
-      <c r="Q35" s="69"/>
-      <c r="R35" s="77"/>
-      <c r="S35" s="77"/>
-      <c r="T35" s="59"/>
-      <c r="U35" s="69"/>
-      <c r="V35" s="70"/>
-      <c r="W35" s="57"/>
-      <c r="X35" s="69"/>
-      <c r="Y35" s="69"/>
-      <c r="Z35" s="70"/>
-      <c r="AA35" s="68"/>
-      <c r="AB35" s="69"/>
-      <c r="AC35" s="69"/>
-      <c r="AD35" s="54"/>
-      <c r="AE35" s="70"/>
-      <c r="AF35" s="68"/>
-      <c r="AG35" s="69"/>
-      <c r="AH35" s="69"/>
-      <c r="AI35" s="69"/>
-      <c r="AJ35" s="69"/>
-      <c r="AK35" s="69"/>
+      <c r="B35" s="64"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="68"/>
+      <c r="H35" s="66"/>
+      <c r="I35" s="67"/>
+      <c r="J35" s="67"/>
+      <c r="K35" s="74"/>
+      <c r="L35" s="52"/>
+      <c r="M35" s="67"/>
+      <c r="N35" s="59"/>
+      <c r="O35" s="66"/>
+      <c r="P35" s="61"/>
+      <c r="Q35" s="67"/>
+      <c r="R35" s="75"/>
+      <c r="S35" s="75"/>
+      <c r="T35" s="57"/>
+      <c r="U35" s="67"/>
+      <c r="V35" s="68"/>
+      <c r="W35" s="55"/>
+      <c r="X35" s="67"/>
+      <c r="Y35" s="67"/>
+      <c r="Z35" s="68"/>
+      <c r="AA35" s="66"/>
+      <c r="AB35" s="67"/>
+      <c r="AC35" s="67"/>
+      <c r="AD35" s="52"/>
+      <c r="AE35" s="68"/>
+      <c r="AF35" s="66"/>
+      <c r="AG35" s="67"/>
+      <c r="AH35" s="67"/>
+      <c r="AI35" s="67"/>
+      <c r="AJ35" s="67"/>
+      <c r="AK35" s="67"/>
     </row>
     <row r="36" ht="12" customHeight="1">
-      <c r="B36" s="66"/>
-      <c r="C36" s="75" t="s">
-        <v>137</v>
-      </c>
-      <c r="D36" s="69"/>
-      <c r="E36" s="69"/>
-      <c r="F36" s="72"/>
-      <c r="G36" s="70"/>
-      <c r="H36" s="68"/>
-      <c r="I36" s="69"/>
-      <c r="J36" s="69"/>
-      <c r="K36" s="69"/>
-      <c r="L36" s="54"/>
-      <c r="M36" s="64"/>
-      <c r="N36" s="52"/>
-      <c r="O36" s="53"/>
-      <c r="P36" s="64"/>
-      <c r="Q36" s="69"/>
-      <c r="R36" s="69"/>
-      <c r="S36" s="69"/>
-      <c r="T36" s="69"/>
-      <c r="U36" s="69"/>
-      <c r="V36" s="70"/>
-      <c r="W36" s="57"/>
-      <c r="X36" s="69"/>
-      <c r="Y36" s="69"/>
-      <c r="Z36" s="70"/>
-      <c r="AA36" s="68"/>
-      <c r="AB36" s="69"/>
-      <c r="AC36" s="69"/>
-      <c r="AD36" s="54"/>
-      <c r="AE36" s="70"/>
-      <c r="AF36" s="68"/>
-      <c r="AG36" s="69"/>
-      <c r="AH36" s="69"/>
-      <c r="AI36" s="69"/>
-      <c r="AJ36" s="69"/>
-      <c r="AK36" s="69"/>
+      <c r="B36" s="64"/>
+      <c r="C36" s="73" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="68"/>
+      <c r="H36" s="66"/>
+      <c r="I36" s="67"/>
+      <c r="J36" s="67"/>
+      <c r="K36" s="67"/>
+      <c r="L36" s="52"/>
+      <c r="M36" s="62"/>
+      <c r="N36" s="50"/>
+      <c r="O36" s="51"/>
+      <c r="P36" s="62"/>
+      <c r="Q36" s="67"/>
+      <c r="R36" s="67"/>
+      <c r="S36" s="67"/>
+      <c r="T36" s="67"/>
+      <c r="U36" s="67"/>
+      <c r="V36" s="68"/>
+      <c r="W36" s="55"/>
+      <c r="X36" s="67"/>
+      <c r="Y36" s="67"/>
+      <c r="Z36" s="68"/>
+      <c r="AA36" s="66"/>
+      <c r="AB36" s="67"/>
+      <c r="AC36" s="67"/>
+      <c r="AD36" s="52"/>
+      <c r="AE36" s="68"/>
+      <c r="AF36" s="66"/>
+      <c r="AG36" s="67"/>
+      <c r="AH36" s="67"/>
+      <c r="AI36" s="67"/>
+      <c r="AJ36" s="67"/>
+      <c r="AK36" s="67"/>
     </row>
     <row r="37" ht="12" customHeight="1">
-      <c r="B37" s="66"/>
-      <c r="C37" s="75"/>
-      <c r="D37" s="69"/>
-      <c r="E37" s="69"/>
-      <c r="F37" s="72"/>
-      <c r="G37" s="70"/>
-      <c r="H37" s="68"/>
-      <c r="I37" s="69"/>
-      <c r="J37" s="69"/>
-      <c r="K37" s="76"/>
-      <c r="L37" s="54"/>
-      <c r="M37" s="69"/>
-      <c r="N37" s="70"/>
-      <c r="O37" s="68"/>
-      <c r="P37" s="63"/>
-      <c r="Q37" s="69"/>
-      <c r="R37" s="77"/>
-      <c r="S37" s="77"/>
-      <c r="T37" s="59"/>
-      <c r="U37" s="69"/>
-      <c r="V37" s="70"/>
-      <c r="W37" s="57"/>
-      <c r="X37" s="69"/>
-      <c r="Y37" s="69"/>
-      <c r="Z37" s="70"/>
-      <c r="AA37" s="68"/>
-      <c r="AB37" s="69"/>
-      <c r="AC37" s="69"/>
-      <c r="AD37" s="54"/>
-      <c r="AE37" s="70"/>
-      <c r="AF37" s="68"/>
-      <c r="AG37" s="69"/>
-      <c r="AH37" s="69"/>
-      <c r="AI37" s="69"/>
-      <c r="AJ37" s="69"/>
-      <c r="AK37" s="69"/>
+      <c r="B37" s="64"/>
+      <c r="C37" s="73"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="67"/>
+      <c r="F37" s="70"/>
+      <c r="G37" s="68"/>
+      <c r="H37" s="66"/>
+      <c r="I37" s="67"/>
+      <c r="J37" s="67"/>
+      <c r="K37" s="74"/>
+      <c r="L37" s="52"/>
+      <c r="M37" s="67"/>
+      <c r="N37" s="68"/>
+      <c r="O37" s="66"/>
+      <c r="P37" s="61"/>
+      <c r="Q37" s="67"/>
+      <c r="R37" s="75"/>
+      <c r="S37" s="75"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="67"/>
+      <c r="V37" s="68"/>
+      <c r="W37" s="55"/>
+      <c r="X37" s="67"/>
+      <c r="Y37" s="67"/>
+      <c r="Z37" s="68"/>
+      <c r="AA37" s="66"/>
+      <c r="AB37" s="67"/>
+      <c r="AC37" s="67"/>
+      <c r="AD37" s="52"/>
+      <c r="AE37" s="68"/>
+      <c r="AF37" s="66"/>
+      <c r="AG37" s="67"/>
+      <c r="AH37" s="67"/>
+      <c r="AI37" s="67"/>
+      <c r="AJ37" s="67"/>
+      <c r="AK37" s="67"/>
     </row>
     <row r="38" ht="12" customHeight="1">
-      <c r="B38" s="66"/>
-      <c r="C38" s="75" t="s">
-        <v>138</v>
-      </c>
-      <c r="D38" s="69"/>
-      <c r="E38" s="69"/>
-      <c r="F38" s="72"/>
-      <c r="G38" s="70"/>
-      <c r="H38" s="68"/>
-      <c r="I38" s="69"/>
-      <c r="J38" s="69"/>
-      <c r="K38" s="69"/>
-      <c r="L38" s="54"/>
-      <c r="M38" s="69"/>
-      <c r="N38" s="70"/>
-      <c r="O38" s="53"/>
-      <c r="P38" s="64"/>
-      <c r="Q38" s="64"/>
-      <c r="R38" s="64"/>
-      <c r="S38" s="64"/>
-      <c r="T38" s="64"/>
-      <c r="U38" s="64"/>
-      <c r="V38" s="52"/>
-      <c r="W38" s="57"/>
-      <c r="X38" s="64"/>
-      <c r="Y38" s="64"/>
-      <c r="Z38" s="70"/>
-      <c r="AA38" s="68"/>
-      <c r="AB38" s="69"/>
-      <c r="AC38" s="69"/>
-      <c r="AD38" s="54"/>
-      <c r="AE38" s="70"/>
-      <c r="AF38" s="68"/>
-      <c r="AG38" s="69"/>
-      <c r="AH38" s="69"/>
-      <c r="AI38" s="69"/>
-      <c r="AJ38" s="69"/>
-      <c r="AK38" s="69"/>
+      <c r="B38" s="64"/>
+      <c r="C38" s="73" t="s">
+        <v>139</v>
+      </c>
+      <c r="D38" s="67"/>
+      <c r="E38" s="67"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="68"/>
+      <c r="H38" s="66"/>
+      <c r="I38" s="67"/>
+      <c r="J38" s="67"/>
+      <c r="K38" s="67"/>
+      <c r="L38" s="52"/>
+      <c r="M38" s="67"/>
+      <c r="N38" s="68"/>
+      <c r="O38" s="51"/>
+      <c r="P38" s="62"/>
+      <c r="Q38" s="62"/>
+      <c r="R38" s="62"/>
+      <c r="S38" s="62"/>
+      <c r="T38" s="62"/>
+      <c r="U38" s="62"/>
+      <c r="V38" s="50"/>
+      <c r="W38" s="55"/>
+      <c r="X38" s="62"/>
+      <c r="Y38" s="62"/>
+      <c r="Z38" s="68"/>
+      <c r="AA38" s="66"/>
+      <c r="AB38" s="67"/>
+      <c r="AC38" s="67"/>
+      <c r="AD38" s="52"/>
+      <c r="AE38" s="68"/>
+      <c r="AF38" s="66"/>
+      <c r="AG38" s="67"/>
+      <c r="AH38" s="67"/>
+      <c r="AI38" s="67"/>
+      <c r="AJ38" s="67"/>
+      <c r="AK38" s="67"/>
     </row>
     <row r="39" ht="12" customHeight="1">
-      <c r="B39" s="66"/>
-      <c r="C39" s="75"/>
-      <c r="D39" s="69"/>
-      <c r="E39" s="69"/>
-      <c r="F39" s="72"/>
-      <c r="G39" s="70"/>
-      <c r="H39" s="68"/>
-      <c r="I39" s="69"/>
-      <c r="J39" s="69"/>
-      <c r="K39" s="69"/>
-      <c r="L39" s="54"/>
-      <c r="M39" s="69"/>
-      <c r="N39" s="70"/>
-      <c r="O39" s="68"/>
-      <c r="P39" s="69"/>
-      <c r="Q39" s="69"/>
-      <c r="R39" s="76"/>
-      <c r="S39" s="76"/>
-      <c r="T39" s="69"/>
-      <c r="U39" s="69"/>
-      <c r="V39" s="70"/>
-      <c r="W39" s="57"/>
-      <c r="X39" s="69"/>
-      <c r="Y39" s="69"/>
-      <c r="Z39" s="70"/>
-      <c r="AA39" s="68"/>
-      <c r="AB39" s="69"/>
-      <c r="AC39" s="69"/>
-      <c r="AD39" s="54"/>
-      <c r="AE39" s="70"/>
-      <c r="AF39" s="68"/>
-      <c r="AG39" s="69"/>
-      <c r="AH39" s="69"/>
-      <c r="AI39" s="69"/>
-      <c r="AJ39" s="69"/>
-      <c r="AK39" s="69"/>
+      <c r="B39" s="64"/>
+      <c r="C39" s="73"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="68"/>
+      <c r="H39" s="66"/>
+      <c r="I39" s="67"/>
+      <c r="J39" s="67"/>
+      <c r="K39" s="67"/>
+      <c r="L39" s="52"/>
+      <c r="M39" s="67"/>
+      <c r="N39" s="68"/>
+      <c r="O39" s="66"/>
+      <c r="P39" s="67"/>
+      <c r="Q39" s="67"/>
+      <c r="R39" s="74"/>
+      <c r="S39" s="74"/>
+      <c r="T39" s="67"/>
+      <c r="U39" s="67"/>
+      <c r="V39" s="68"/>
+      <c r="W39" s="55"/>
+      <c r="X39" s="67"/>
+      <c r="Y39" s="67"/>
+      <c r="Z39" s="68"/>
+      <c r="AA39" s="66"/>
+      <c r="AB39" s="67"/>
+      <c r="AC39" s="67"/>
+      <c r="AD39" s="52"/>
+      <c r="AE39" s="68"/>
+      <c r="AF39" s="66"/>
+      <c r="AG39" s="67"/>
+      <c r="AH39" s="67"/>
+      <c r="AI39" s="67"/>
+      <c r="AJ39" s="67"/>
+      <c r="AK39" s="67"/>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="B40" s="66"/>
-      <c r="C40" s="75" t="s">
-        <v>139</v>
-      </c>
-      <c r="D40" s="69"/>
-      <c r="E40" s="69"/>
-      <c r="F40" s="72"/>
-      <c r="G40" s="70"/>
-      <c r="H40" s="68"/>
-      <c r="I40" s="69"/>
-      <c r="J40" s="69"/>
-      <c r="K40" s="69"/>
-      <c r="L40" s="54"/>
-      <c r="M40" s="69"/>
-      <c r="N40" s="70"/>
-      <c r="O40" s="68"/>
-      <c r="P40" s="69"/>
-      <c r="Q40" s="69"/>
-      <c r="R40" s="64"/>
-      <c r="S40" s="64"/>
-      <c r="T40" s="64"/>
-      <c r="U40" s="64"/>
-      <c r="V40" s="52"/>
-      <c r="W40" s="57"/>
-      <c r="X40" s="64"/>
-      <c r="Y40" s="64"/>
-      <c r="Z40" s="52"/>
-      <c r="AA40" s="53"/>
-      <c r="AB40" s="64"/>
-      <c r="AC40" s="64"/>
-      <c r="AD40" s="54"/>
-      <c r="AE40" s="70"/>
-      <c r="AF40" s="68"/>
-      <c r="AG40" s="69"/>
-      <c r="AH40" s="69"/>
-      <c r="AI40" s="69"/>
-      <c r="AJ40" s="69"/>
-      <c r="AK40" s="69"/>
+      <c r="B40" s="64"/>
+      <c r="C40" s="73" t="s">
+        <v>140</v>
+      </c>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="68"/>
+      <c r="H40" s="66"/>
+      <c r="I40" s="67"/>
+      <c r="J40" s="67"/>
+      <c r="K40" s="67"/>
+      <c r="L40" s="52"/>
+      <c r="M40" s="67"/>
+      <c r="N40" s="68"/>
+      <c r="O40" s="66"/>
+      <c r="P40" s="67"/>
+      <c r="Q40" s="67"/>
+      <c r="R40" s="62"/>
+      <c r="S40" s="62"/>
+      <c r="T40" s="62"/>
+      <c r="U40" s="62"/>
+      <c r="V40" s="50"/>
+      <c r="W40" s="55"/>
+      <c r="X40" s="62"/>
+      <c r="Y40" s="62"/>
+      <c r="Z40" s="50"/>
+      <c r="AA40" s="51"/>
+      <c r="AB40" s="62"/>
+      <c r="AC40" s="62"/>
+      <c r="AD40" s="52"/>
+      <c r="AE40" s="68"/>
+      <c r="AF40" s="66"/>
+      <c r="AG40" s="67"/>
+      <c r="AH40" s="67"/>
+      <c r="AI40" s="67"/>
+      <c r="AJ40" s="67"/>
+      <c r="AK40" s="67"/>
     </row>
     <row r="41" ht="12" customHeight="1">
-      <c r="B41" s="66"/>
-      <c r="C41" s="75"/>
-      <c r="D41" s="69"/>
-      <c r="E41" s="69"/>
-      <c r="F41" s="72"/>
-      <c r="G41" s="70"/>
-      <c r="H41" s="68"/>
-      <c r="I41" s="69"/>
-      <c r="J41" s="69"/>
-      <c r="K41" s="69"/>
-      <c r="L41" s="54"/>
-      <c r="M41" s="69"/>
-      <c r="N41" s="70"/>
-      <c r="O41" s="68"/>
-      <c r="P41" s="69"/>
-      <c r="Q41" s="63"/>
-      <c r="R41" s="76"/>
-      <c r="S41" s="76"/>
-      <c r="T41" s="63"/>
-      <c r="U41" s="69"/>
-      <c r="V41" s="70"/>
-      <c r="W41" s="57"/>
-      <c r="X41" s="69"/>
-      <c r="Y41" s="69"/>
-      <c r="Z41" s="70"/>
-      <c r="AA41" s="68"/>
-      <c r="AB41" s="69"/>
-      <c r="AC41" s="69"/>
-      <c r="AD41" s="54"/>
-      <c r="AE41" s="70"/>
-      <c r="AF41" s="68"/>
-      <c r="AG41" s="69"/>
-      <c r="AH41" s="69"/>
-      <c r="AI41" s="69"/>
-      <c r="AJ41" s="69"/>
-      <c r="AK41" s="69"/>
+      <c r="B41" s="64"/>
+      <c r="C41" s="73"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="68"/>
+      <c r="H41" s="66"/>
+      <c r="I41" s="67"/>
+      <c r="J41" s="67"/>
+      <c r="K41" s="67"/>
+      <c r="L41" s="52"/>
+      <c r="M41" s="67"/>
+      <c r="N41" s="68"/>
+      <c r="O41" s="66"/>
+      <c r="P41" s="67"/>
+      <c r="Q41" s="61"/>
+      <c r="R41" s="74"/>
+      <c r="S41" s="74"/>
+      <c r="T41" s="61"/>
+      <c r="U41" s="67"/>
+      <c r="V41" s="68"/>
+      <c r="W41" s="55"/>
+      <c r="X41" s="67"/>
+      <c r="Y41" s="67"/>
+      <c r="Z41" s="68"/>
+      <c r="AA41" s="66"/>
+      <c r="AB41" s="67"/>
+      <c r="AC41" s="67"/>
+      <c r="AD41" s="52"/>
+      <c r="AE41" s="68"/>
+      <c r="AF41" s="66"/>
+      <c r="AG41" s="67"/>
+      <c r="AH41" s="67"/>
+      <c r="AI41" s="67"/>
+      <c r="AJ41" s="67"/>
+      <c r="AK41" s="67"/>
     </row>
     <row r="42" ht="12" customHeight="1">
-      <c r="B42" s="48" t="s">
+      <c r="B42" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="78" t="s">
-        <v>140</v>
-      </c>
-      <c r="D42" s="50"/>
-      <c r="E42" s="50"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="55"/>
-      <c r="H42" s="56"/>
-      <c r="I42" s="50"/>
-      <c r="J42" s="50"/>
-      <c r="K42" s="50"/>
-      <c r="L42" s="54"/>
-      <c r="M42" s="50"/>
-      <c r="N42" s="55"/>
-      <c r="O42" s="56"/>
-      <c r="P42" s="64"/>
-      <c r="Q42" s="64"/>
-      <c r="R42" s="50"/>
-      <c r="S42" s="50"/>
-      <c r="T42" s="63"/>
-      <c r="U42" s="50"/>
-      <c r="V42" s="52"/>
-      <c r="W42" s="57"/>
-      <c r="X42" s="64"/>
-      <c r="Y42" s="64"/>
-      <c r="Z42" s="52"/>
-      <c r="AA42" s="53"/>
-      <c r="AB42" s="64"/>
-      <c r="AC42" s="64"/>
-      <c r="AD42" s="54"/>
-      <c r="AE42" s="55"/>
-      <c r="AF42" s="56"/>
-      <c r="AG42" s="50"/>
-      <c r="AH42" s="50"/>
-      <c r="AI42" s="50"/>
-      <c r="AJ42" s="50"/>
-      <c r="AK42" s="50"/>
+      <c r="C42" s="76" t="s">
+        <v>141</v>
+      </c>
+      <c r="D42" s="48"/>
+      <c r="E42" s="48"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="53"/>
+      <c r="H42" s="54"/>
+      <c r="I42" s="48"/>
+      <c r="J42" s="48"/>
+      <c r="K42" s="48"/>
+      <c r="L42" s="52"/>
+      <c r="M42" s="48"/>
+      <c r="N42" s="53"/>
+      <c r="O42" s="54"/>
+      <c r="P42" s="62"/>
+      <c r="Q42" s="62"/>
+      <c r="R42" s="48"/>
+      <c r="S42" s="48"/>
+      <c r="T42" s="61"/>
+      <c r="U42" s="48"/>
+      <c r="V42" s="50"/>
+      <c r="W42" s="55"/>
+      <c r="X42" s="62"/>
+      <c r="Y42" s="62"/>
+      <c r="Z42" s="50"/>
+      <c r="AA42" s="51"/>
+      <c r="AB42" s="62"/>
+      <c r="AC42" s="62"/>
+      <c r="AD42" s="52"/>
+      <c r="AE42" s="53"/>
+      <c r="AF42" s="54"/>
+      <c r="AG42" s="48"/>
+      <c r="AH42" s="48"/>
+      <c r="AI42" s="48"/>
+      <c r="AJ42" s="48"/>
+      <c r="AK42" s="48"/>
     </row>
     <row r="43" ht="12" customHeight="1">
-      <c r="B43" s="48"/>
-      <c r="C43" s="78"/>
-      <c r="D43" s="50"/>
-      <c r="E43" s="50"/>
-      <c r="F43" s="58"/>
-      <c r="G43" s="55"/>
-      <c r="H43" s="56"/>
-      <c r="I43" s="50"/>
-      <c r="J43" s="50"/>
-      <c r="K43" s="50"/>
-      <c r="L43" s="54"/>
-      <c r="M43" s="50"/>
-      <c r="N43" s="55"/>
-      <c r="O43" s="56"/>
-      <c r="P43" s="50"/>
-      <c r="Q43" s="63"/>
-      <c r="R43" s="50"/>
-      <c r="S43" s="65"/>
-      <c r="T43" s="50"/>
-      <c r="U43" s="50"/>
-      <c r="V43" s="55"/>
-      <c r="W43" s="57"/>
-      <c r="X43" s="50"/>
-      <c r="Y43" s="50"/>
-      <c r="Z43" s="55"/>
-      <c r="AA43" s="56"/>
-      <c r="AB43" s="50"/>
-      <c r="AC43" s="50"/>
-      <c r="AD43" s="54"/>
-      <c r="AE43" s="55"/>
-      <c r="AF43" s="56"/>
-      <c r="AG43" s="50"/>
-      <c r="AH43" s="50"/>
-      <c r="AI43" s="50"/>
-      <c r="AJ43" s="50"/>
-      <c r="AK43" s="50"/>
+      <c r="B43" s="46"/>
+      <c r="C43" s="76"/>
+      <c r="D43" s="48"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="56"/>
+      <c r="G43" s="53"/>
+      <c r="H43" s="54"/>
+      <c r="I43" s="48"/>
+      <c r="J43" s="48"/>
+      <c r="K43" s="48"/>
+      <c r="L43" s="52"/>
+      <c r="M43" s="48"/>
+      <c r="N43" s="53"/>
+      <c r="O43" s="54"/>
+      <c r="P43" s="48"/>
+      <c r="Q43" s="61"/>
+      <c r="R43" s="48"/>
+      <c r="S43" s="63"/>
+      <c r="T43" s="48"/>
+      <c r="U43" s="48"/>
+      <c r="V43" s="53"/>
+      <c r="W43" s="55"/>
+      <c r="X43" s="48"/>
+      <c r="Y43" s="48"/>
+      <c r="Z43" s="53"/>
+      <c r="AA43" s="54"/>
+      <c r="AB43" s="48"/>
+      <c r="AC43" s="48"/>
+      <c r="AD43" s="52"/>
+      <c r="AE43" s="53"/>
+      <c r="AF43" s="54"/>
+      <c r="AG43" s="48"/>
+      <c r="AH43" s="48"/>
+      <c r="AI43" s="48"/>
+      <c r="AJ43" s="48"/>
+      <c r="AK43" s="48"/>
     </row>
     <row r="44" ht="12" customHeight="1">
-      <c r="B44" s="48"/>
-      <c r="C44" s="78" t="s">
-        <v>141</v>
-      </c>
-      <c r="D44" s="50"/>
-      <c r="E44" s="50"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="55"/>
-      <c r="H44" s="56"/>
-      <c r="I44" s="50"/>
-      <c r="J44" s="50"/>
-      <c r="K44" s="50"/>
-      <c r="L44" s="54"/>
-      <c r="M44" s="50"/>
-      <c r="N44" s="55"/>
-      <c r="O44" s="56"/>
-      <c r="P44" s="64"/>
-      <c r="Q44" s="64"/>
-      <c r="R44" s="50"/>
-      <c r="S44" s="50"/>
-      <c r="T44" s="50"/>
-      <c r="U44" s="50"/>
-      <c r="V44" s="55"/>
-      <c r="W44" s="57"/>
-      <c r="X44" s="64"/>
-      <c r="Y44" s="64"/>
-      <c r="Z44" s="55"/>
-      <c r="AA44" s="56"/>
-      <c r="AB44" s="50"/>
-      <c r="AC44" s="64"/>
-      <c r="AD44" s="54"/>
-      <c r="AE44" s="52"/>
-      <c r="AF44" s="53"/>
-      <c r="AG44" s="50"/>
-      <c r="AH44" s="50"/>
-      <c r="AI44" s="64"/>
-      <c r="AJ44" s="50"/>
-      <c r="AK44" s="50"/>
+      <c r="B44" s="46"/>
+      <c r="C44" s="76" t="s">
+        <v>142</v>
+      </c>
+      <c r="D44" s="48"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="56"/>
+      <c r="G44" s="53"/>
+      <c r="H44" s="54"/>
+      <c r="I44" s="48"/>
+      <c r="J44" s="48"/>
+      <c r="K44" s="48"/>
+      <c r="L44" s="52"/>
+      <c r="M44" s="48"/>
+      <c r="N44" s="53"/>
+      <c r="O44" s="54"/>
+      <c r="P44" s="62"/>
+      <c r="Q44" s="62"/>
+      <c r="R44" s="48"/>
+      <c r="S44" s="48"/>
+      <c r="T44" s="48"/>
+      <c r="U44" s="48"/>
+      <c r="V44" s="53"/>
+      <c r="W44" s="55"/>
+      <c r="X44" s="62"/>
+      <c r="Y44" s="62"/>
+      <c r="Z44" s="53"/>
+      <c r="AA44" s="54"/>
+      <c r="AB44" s="48"/>
+      <c r="AC44" s="62"/>
+      <c r="AD44" s="52"/>
+      <c r="AE44" s="50"/>
+      <c r="AF44" s="51"/>
+      <c r="AG44" s="48"/>
+      <c r="AH44" s="48"/>
+      <c r="AI44" s="62"/>
+      <c r="AJ44" s="48"/>
+      <c r="AK44" s="48"/>
     </row>
     <row r="45" ht="12" customHeight="1">
-      <c r="B45" s="48"/>
-      <c r="C45" s="78"/>
-      <c r="D45" s="50"/>
-      <c r="E45" s="50"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="55"/>
-      <c r="H45" s="56"/>
-      <c r="I45" s="50"/>
-      <c r="J45" s="50"/>
-      <c r="K45" s="50"/>
-      <c r="L45" s="54"/>
-      <c r="M45" s="50"/>
-      <c r="N45" s="55"/>
-      <c r="O45" s="56"/>
-      <c r="P45" s="50"/>
-      <c r="Q45" s="50"/>
-      <c r="R45" s="50"/>
-      <c r="S45" s="50"/>
-      <c r="T45" s="50"/>
-      <c r="U45" s="50"/>
-      <c r="V45" s="55"/>
-      <c r="W45" s="57"/>
-      <c r="X45" s="50"/>
-      <c r="Y45" s="50"/>
-      <c r="Z45" s="55"/>
-      <c r="AA45" s="56"/>
-      <c r="AB45" s="50"/>
-      <c r="AC45" s="50"/>
-      <c r="AD45" s="54"/>
-      <c r="AE45" s="55"/>
-      <c r="AF45" s="56"/>
-      <c r="AG45" s="50"/>
-      <c r="AH45" s="50"/>
-      <c r="AI45" s="50"/>
-      <c r="AJ45" s="50"/>
-      <c r="AK45" s="50"/>
+      <c r="B45" s="46"/>
+      <c r="C45" s="76"/>
+      <c r="D45" s="48"/>
+      <c r="E45" s="48"/>
+      <c r="F45" s="56"/>
+      <c r="G45" s="53"/>
+      <c r="H45" s="54"/>
+      <c r="I45" s="48"/>
+      <c r="J45" s="48"/>
+      <c r="K45" s="48"/>
+      <c r="L45" s="52"/>
+      <c r="M45" s="48"/>
+      <c r="N45" s="53"/>
+      <c r="O45" s="54"/>
+      <c r="P45" s="48"/>
+      <c r="Q45" s="48"/>
+      <c r="R45" s="48"/>
+      <c r="S45" s="48"/>
+      <c r="T45" s="48"/>
+      <c r="U45" s="48"/>
+      <c r="V45" s="53"/>
+      <c r="W45" s="55"/>
+      <c r="X45" s="48"/>
+      <c r="Y45" s="48"/>
+      <c r="Z45" s="53"/>
+      <c r="AA45" s="54"/>
+      <c r="AB45" s="48"/>
+      <c r="AC45" s="48"/>
+      <c r="AD45" s="52"/>
+      <c r="AE45" s="53"/>
+      <c r="AF45" s="54"/>
+      <c r="AG45" s="48"/>
+      <c r="AH45" s="48"/>
+      <c r="AI45" s="48"/>
+      <c r="AJ45" s="48"/>
+      <c r="AK45" s="48"/>
     </row>
     <row r="46" ht="12" customHeight="1">
-      <c r="B46" s="66" t="s">
-        <v>142</v>
-      </c>
-      <c r="C46" s="67" t="s">
+      <c r="B46" s="64" t="s">
+        <v>143</v>
+      </c>
+      <c r="C46" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="D46" s="69"/>
-      <c r="E46" s="69"/>
-      <c r="F46" s="72"/>
-      <c r="G46" s="70"/>
-      <c r="H46" s="68"/>
-      <c r="I46" s="69"/>
-      <c r="J46" s="69"/>
-      <c r="K46" s="69"/>
-      <c r="L46" s="54"/>
-      <c r="M46" s="69"/>
-      <c r="N46" s="70"/>
-      <c r="O46" s="68"/>
-      <c r="P46" s="69"/>
-      <c r="Q46" s="69"/>
-      <c r="R46" s="69"/>
-      <c r="S46" s="69"/>
-      <c r="T46" s="69"/>
-      <c r="U46" s="69"/>
-      <c r="V46" s="70"/>
-      <c r="W46" s="57"/>
-      <c r="X46" s="69"/>
-      <c r="Y46" s="69"/>
-      <c r="Z46" s="70"/>
-      <c r="AA46" s="68"/>
-      <c r="AB46" s="69"/>
-      <c r="AC46" s="69"/>
-      <c r="AD46" s="54"/>
-      <c r="AE46" s="70"/>
-      <c r="AF46" s="68"/>
-      <c r="AG46" s="69"/>
-      <c r="AH46" s="69"/>
-      <c r="AI46" s="69"/>
-      <c r="AJ46" s="64"/>
-      <c r="AK46" s="69"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="68"/>
+      <c r="H46" s="66"/>
+      <c r="I46" s="67"/>
+      <c r="J46" s="67"/>
+      <c r="K46" s="67"/>
+      <c r="L46" s="52"/>
+      <c r="M46" s="67"/>
+      <c r="N46" s="68"/>
+      <c r="O46" s="66"/>
+      <c r="P46" s="67"/>
+      <c r="Q46" s="67"/>
+      <c r="R46" s="67"/>
+      <c r="S46" s="67"/>
+      <c r="T46" s="67"/>
+      <c r="U46" s="67"/>
+      <c r="V46" s="68"/>
+      <c r="W46" s="55"/>
+      <c r="X46" s="67"/>
+      <c r="Y46" s="67"/>
+      <c r="Z46" s="68"/>
+      <c r="AA46" s="66"/>
+      <c r="AB46" s="67"/>
+      <c r="AC46" s="67"/>
+      <c r="AD46" s="52"/>
+      <c r="AE46" s="68"/>
+      <c r="AF46" s="66"/>
+      <c r="AG46" s="67"/>
+      <c r="AH46" s="67"/>
+      <c r="AI46" s="67"/>
+      <c r="AJ46" s="62"/>
+      <c r="AK46" s="67"/>
     </row>
     <row r="47" ht="12" customHeight="1">
-      <c r="B47" s="66"/>
-      <c r="C47" s="67"/>
-      <c r="D47" s="69"/>
-      <c r="E47" s="69"/>
-      <c r="F47" s="72"/>
-      <c r="G47" s="70"/>
-      <c r="H47" s="68"/>
-      <c r="I47" s="69"/>
-      <c r="J47" s="69"/>
-      <c r="K47" s="69"/>
-      <c r="L47" s="54"/>
-      <c r="M47" s="69"/>
-      <c r="N47" s="70"/>
-      <c r="O47" s="68"/>
-      <c r="P47" s="69"/>
-      <c r="Q47" s="69"/>
-      <c r="R47" s="69"/>
-      <c r="S47" s="69"/>
-      <c r="T47" s="69"/>
-      <c r="U47" s="69"/>
-      <c r="V47" s="70"/>
-      <c r="W47" s="57"/>
-      <c r="X47" s="69"/>
-      <c r="Y47" s="69"/>
-      <c r="Z47" s="70"/>
-      <c r="AA47" s="68"/>
-      <c r="AB47" s="69"/>
-      <c r="AC47" s="69"/>
-      <c r="AD47" s="54"/>
-      <c r="AE47" s="70"/>
-      <c r="AF47" s="68"/>
-      <c r="AG47" s="69"/>
-      <c r="AH47" s="69"/>
-      <c r="AI47" s="69"/>
-      <c r="AJ47" s="69"/>
-      <c r="AK47" s="69"/>
-      <c r="AN47" s="79" t="s">
-        <v>143</v>
-      </c>
-      <c r="AO47" s="64"/>
+      <c r="B47" s="64"/>
+      <c r="C47" s="65"/>
+      <c r="D47" s="67"/>
+      <c r="E47" s="67"/>
+      <c r="F47" s="70"/>
+      <c r="G47" s="68"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="67"/>
+      <c r="J47" s="67"/>
+      <c r="K47" s="67"/>
+      <c r="L47" s="52"/>
+      <c r="M47" s="67"/>
+      <c r="N47" s="68"/>
+      <c r="O47" s="66"/>
+      <c r="P47" s="67"/>
+      <c r="Q47" s="67"/>
+      <c r="R47" s="67"/>
+      <c r="S47" s="67"/>
+      <c r="T47" s="67"/>
+      <c r="U47" s="67"/>
+      <c r="V47" s="68"/>
+      <c r="W47" s="55"/>
+      <c r="X47" s="67"/>
+      <c r="Y47" s="67"/>
+      <c r="Z47" s="68"/>
+      <c r="AA47" s="66"/>
+      <c r="AB47" s="67"/>
+      <c r="AC47" s="67"/>
+      <c r="AD47" s="52"/>
+      <c r="AE47" s="68"/>
+      <c r="AF47" s="66"/>
+      <c r="AG47" s="67"/>
+      <c r="AH47" s="67"/>
+      <c r="AI47" s="67"/>
+      <c r="AJ47" s="67"/>
+      <c r="AK47" s="67"/>
+      <c r="AN47" s="77" t="s">
+        <v>144</v>
+      </c>
+      <c r="AO47" s="62"/>
     </row>
     <row r="48" ht="12" customHeight="1">
-      <c r="B48" s="66"/>
-      <c r="C48" s="67" t="s">
-        <v>144</v>
-      </c>
-      <c r="D48" s="69"/>
-      <c r="E48" s="69"/>
-      <c r="F48" s="72"/>
-      <c r="G48" s="70"/>
-      <c r="H48" s="68"/>
-      <c r="I48" s="69"/>
-      <c r="J48" s="69"/>
-      <c r="K48" s="69"/>
-      <c r="L48" s="54"/>
-      <c r="M48" s="69"/>
-      <c r="N48" s="70"/>
-      <c r="O48" s="68"/>
-      <c r="P48" s="69"/>
-      <c r="Q48" s="69"/>
-      <c r="R48" s="69"/>
-      <c r="S48" s="69"/>
-      <c r="T48" s="69"/>
-      <c r="U48" s="69"/>
-      <c r="V48" s="70"/>
-      <c r="W48" s="57"/>
-      <c r="X48" s="69"/>
-      <c r="Y48" s="69"/>
-      <c r="Z48" s="70"/>
-      <c r="AA48" s="68"/>
-      <c r="AB48" s="69"/>
-      <c r="AC48" s="69"/>
-      <c r="AD48" s="54"/>
-      <c r="AE48" s="70"/>
-      <c r="AF48" s="68"/>
-      <c r="AG48" s="69"/>
-      <c r="AH48" s="69"/>
-      <c r="AI48" s="69"/>
-      <c r="AJ48" s="69"/>
-      <c r="AK48" s="80"/>
-      <c r="AN48" s="79" t="s">
+      <c r="B48" s="64"/>
+      <c r="C48" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="AO48" s="63"/>
+      <c r="D48" s="67"/>
+      <c r="E48" s="67"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="68"/>
+      <c r="H48" s="66"/>
+      <c r="I48" s="67"/>
+      <c r="J48" s="67"/>
+      <c r="K48" s="67"/>
+      <c r="L48" s="52"/>
+      <c r="M48" s="67"/>
+      <c r="N48" s="68"/>
+      <c r="O48" s="66"/>
+      <c r="P48" s="67"/>
+      <c r="Q48" s="67"/>
+      <c r="R48" s="67"/>
+      <c r="S48" s="67"/>
+      <c r="T48" s="67"/>
+      <c r="U48" s="67"/>
+      <c r="V48" s="68"/>
+      <c r="W48" s="55"/>
+      <c r="X48" s="67"/>
+      <c r="Y48" s="67"/>
+      <c r="Z48" s="68"/>
+      <c r="AA48" s="66"/>
+      <c r="AB48" s="67"/>
+      <c r="AC48" s="67"/>
+      <c r="AD48" s="52"/>
+      <c r="AE48" s="68"/>
+      <c r="AF48" s="66"/>
+      <c r="AG48" s="67"/>
+      <c r="AH48" s="67"/>
+      <c r="AI48" s="67"/>
+      <c r="AJ48" s="67"/>
+      <c r="AK48" s="78"/>
+      <c r="AN48" s="77" t="s">
+        <v>146</v>
+      </c>
+      <c r="AO48" s="61"/>
     </row>
     <row r="49" ht="12" customHeight="1">
-      <c r="B49" s="66"/>
-      <c r="C49" s="67"/>
-      <c r="D49" s="69"/>
-      <c r="E49" s="69"/>
-      <c r="F49" s="72"/>
-      <c r="G49" s="70"/>
-      <c r="H49" s="68"/>
-      <c r="I49" s="69"/>
-      <c r="J49" s="69"/>
-      <c r="K49" s="69"/>
-      <c r="L49" s="54"/>
-      <c r="M49" s="69"/>
-      <c r="N49" s="70"/>
-      <c r="O49" s="68"/>
-      <c r="P49" s="69"/>
-      <c r="Q49" s="69"/>
-      <c r="R49" s="69"/>
-      <c r="S49" s="69"/>
-      <c r="T49" s="69"/>
-      <c r="U49" s="69"/>
-      <c r="V49" s="70"/>
-      <c r="W49" s="57"/>
-      <c r="X49" s="69"/>
-      <c r="Y49" s="69"/>
-      <c r="Z49" s="70"/>
-      <c r="AA49" s="68"/>
-      <c r="AB49" s="69"/>
-      <c r="AC49" s="69"/>
-      <c r="AD49" s="54"/>
-      <c r="AE49" s="70"/>
-      <c r="AF49" s="68"/>
-      <c r="AG49" s="69"/>
-      <c r="AH49" s="69"/>
-      <c r="AI49" s="69"/>
-      <c r="AJ49" s="69"/>
-      <c r="AK49" s="69"/>
-      <c r="AN49" s="79" t="s">
-        <v>146</v>
-      </c>
-      <c r="AO49" s="59"/>
+      <c r="B49" s="64"/>
+      <c r="C49" s="65"/>
+      <c r="D49" s="67"/>
+      <c r="E49" s="67"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="68"/>
+      <c r="H49" s="66"/>
+      <c r="I49" s="67"/>
+      <c r="J49" s="67"/>
+      <c r="K49" s="67"/>
+      <c r="L49" s="52"/>
+      <c r="M49" s="67"/>
+      <c r="N49" s="68"/>
+      <c r="O49" s="66"/>
+      <c r="P49" s="67"/>
+      <c r="Q49" s="67"/>
+      <c r="R49" s="67"/>
+      <c r="S49" s="67"/>
+      <c r="T49" s="67"/>
+      <c r="U49" s="67"/>
+      <c r="V49" s="68"/>
+      <c r="W49" s="55"/>
+      <c r="X49" s="67"/>
+      <c r="Y49" s="67"/>
+      <c r="Z49" s="68"/>
+      <c r="AA49" s="66"/>
+      <c r="AB49" s="67"/>
+      <c r="AC49" s="67"/>
+      <c r="AD49" s="52"/>
+      <c r="AE49" s="68"/>
+      <c r="AF49" s="66"/>
+      <c r="AG49" s="67"/>
+      <c r="AH49" s="67"/>
+      <c r="AI49" s="67"/>
+      <c r="AJ49" s="67"/>
+      <c r="AK49" s="67"/>
+      <c r="AN49" s="77" t="s">
+        <v>147</v>
+      </c>
+      <c r="AO49" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -9338,801 +9321,801 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="81"/>
+      <c r="B1" s="79"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="82" t="s">
-        <v>90</v>
-      </c>
-      <c r="C2" s="83" t="s">
+      <c r="B2" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="D2" s="84" t="s">
-        <v>147</v>
-      </c>
-      <c r="E2" s="85" t="s">
+      <c r="C2" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" s="82" t="s">
         <v>148</v>
       </c>
-      <c r="F2" s="86" t="s">
+      <c r="E2" s="83" t="s">
         <v>149</v>
       </c>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="86" t="s">
+      <c r="F2" s="84" t="s">
         <v>150</v>
       </c>
-      <c r="K2" s="86"/>
-      <c r="L2" s="86"/>
-      <c r="M2" s="85"/>
-      <c r="N2" s="86" t="s">
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="84" t="s">
         <v>151</v>
       </c>
-      <c r="O2" s="86"/>
-      <c r="P2" s="86"/>
-      <c r="Q2" s="85"/>
-      <c r="R2" s="86" t="s">
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="83"/>
+      <c r="N2" s="84" t="s">
         <v>152</v>
       </c>
-      <c r="S2" s="87"/>
-      <c r="AD2" s="30"/>
+      <c r="O2" s="84"/>
+      <c r="P2" s="84"/>
+      <c r="Q2" s="83"/>
+      <c r="R2" s="84" t="s">
+        <v>153</v>
+      </c>
+      <c r="S2" s="85"/>
+      <c r="AD2" s="28"/>
     </row>
     <row r="3">
-      <c r="B3" s="88"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="90" t="s">
-        <v>153</v>
-      </c>
-      <c r="E3" s="91">
+      <c r="B3" s="86"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="88" t="s">
+        <v>154</v>
+      </c>
+      <c r="E3" s="89">
         <v>4</v>
       </c>
-      <c r="F3" s="92">
+      <c r="F3" s="90">
         <v>1</v>
       </c>
-      <c r="G3" s="93">
+      <c r="G3" s="91">
         <v>2</v>
       </c>
-      <c r="H3" s="93">
+      <c r="H3" s="91">
         <v>3</v>
       </c>
-      <c r="I3" s="91">
+      <c r="I3" s="89">
         <v>4</v>
       </c>
-      <c r="J3" s="92">
+      <c r="J3" s="90">
         <v>1</v>
       </c>
-      <c r="K3" s="93">
+      <c r="K3" s="91">
         <v>2</v>
       </c>
-      <c r="L3" s="93">
+      <c r="L3" s="91">
         <v>3</v>
       </c>
-      <c r="M3" s="91">
+      <c r="M3" s="89">
         <v>4</v>
       </c>
-      <c r="N3" s="92">
+      <c r="N3" s="90">
         <v>1</v>
       </c>
-      <c r="O3" s="93">
+      <c r="O3" s="91">
         <v>2</v>
       </c>
-      <c r="P3" s="93">
+      <c r="P3" s="91">
         <v>3</v>
       </c>
-      <c r="Q3" s="91">
+      <c r="Q3" s="89">
         <v>4</v>
       </c>
-      <c r="R3" s="92">
+      <c r="R3" s="90">
         <v>1</v>
       </c>
-      <c r="S3" s="94">
+      <c r="S3" s="92">
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="95" t="s">
-        <v>155</v>
-      </c>
-      <c r="C4" s="83" t="s">
+      <c r="B4" s="93" t="s">
         <v>156</v>
       </c>
-      <c r="D4" s="96"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="100"/>
-      <c r="K4" s="99"/>
-      <c r="L4" s="99"/>
-      <c r="M4" s="97"/>
-      <c r="N4" s="100"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="99"/>
-      <c r="Q4" s="97"/>
-      <c r="R4" s="100"/>
-      <c r="S4" s="101"/>
+      <c r="C4" s="81" t="s">
+        <v>157</v>
+      </c>
+      <c r="D4" s="94"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="95"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="97"/>
+      <c r="L4" s="97"/>
+      <c r="M4" s="95"/>
+      <c r="N4" s="98"/>
+      <c r="O4" s="97"/>
+      <c r="P4" s="97"/>
+      <c r="Q4" s="95"/>
+      <c r="R4" s="98"/>
+      <c r="S4" s="99"/>
       <c r="U4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="95"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="107"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="108"/>
-      <c r="K5" s="107"/>
-      <c r="L5" s="107"/>
-      <c r="M5" s="104"/>
-      <c r="N5" s="108"/>
-      <c r="O5" s="107"/>
-      <c r="P5" s="107"/>
-      <c r="Q5" s="104"/>
-      <c r="R5" s="108"/>
-      <c r="S5" s="109"/>
+      <c r="B5" s="93"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="102"/>
+      <c r="J5" s="106"/>
+      <c r="K5" s="105"/>
+      <c r="L5" s="105"/>
+      <c r="M5" s="102"/>
+      <c r="N5" s="106"/>
+      <c r="O5" s="105"/>
+      <c r="P5" s="105"/>
+      <c r="Q5" s="102"/>
+      <c r="R5" s="106"/>
+      <c r="S5" s="107"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="95"/>
-      <c r="C6" s="110" t="s">
-        <v>158</v>
-      </c>
-      <c r="D6" s="111"/>
-      <c r="E6" s="112"/>
-      <c r="F6" s="113"/>
-      <c r="G6" s="114"/>
-      <c r="H6" s="115"/>
-      <c r="I6" s="112"/>
-      <c r="J6" s="116"/>
-      <c r="K6" s="115"/>
-      <c r="L6" s="115"/>
-      <c r="M6" s="112"/>
-      <c r="N6" s="116"/>
-      <c r="O6" s="115"/>
-      <c r="P6" s="115"/>
-      <c r="Q6" s="112"/>
-      <c r="R6" s="116"/>
-      <c r="S6" s="117"/>
-      <c r="U6" s="118" t="s">
+      <c r="B6" s="93"/>
+      <c r="C6" s="108" t="s">
         <v>159</v>
       </c>
-      <c r="V6" s="118"/>
+      <c r="D6" s="109"/>
+      <c r="E6" s="110"/>
+      <c r="F6" s="111"/>
+      <c r="G6" s="112"/>
+      <c r="H6" s="113"/>
+      <c r="I6" s="110"/>
+      <c r="J6" s="114"/>
+      <c r="K6" s="113"/>
+      <c r="L6" s="113"/>
+      <c r="M6" s="110"/>
+      <c r="N6" s="114"/>
+      <c r="O6" s="113"/>
+      <c r="P6" s="113"/>
+      <c r="Q6" s="110"/>
+      <c r="R6" s="114"/>
+      <c r="S6" s="115"/>
+      <c r="U6" s="116" t="s">
+        <v>160</v>
+      </c>
+      <c r="V6" s="116"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="95"/>
-      <c r="C7" s="102"/>
-      <c r="D7" s="103"/>
-      <c r="E7" s="104"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="106"/>
-      <c r="I7" s="104"/>
-      <c r="J7" s="108"/>
-      <c r="K7" s="107"/>
-      <c r="L7" s="107"/>
-      <c r="M7" s="104"/>
-      <c r="N7" s="108"/>
-      <c r="O7" s="107"/>
-      <c r="P7" s="107"/>
-      <c r="Q7" s="104"/>
-      <c r="R7" s="108"/>
-      <c r="S7" s="109"/>
+      <c r="B7" s="93"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="101"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="102"/>
+      <c r="J7" s="106"/>
+      <c r="K7" s="105"/>
+      <c r="L7" s="105"/>
+      <c r="M7" s="102"/>
+      <c r="N7" s="106"/>
+      <c r="O7" s="105"/>
+      <c r="P7" s="105"/>
+      <c r="Q7" s="102"/>
+      <c r="R7" s="106"/>
+      <c r="S7" s="107"/>
       <c r="U7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="95"/>
-      <c r="C8" s="110" t="s">
-        <v>161</v>
-      </c>
-      <c r="D8" s="111"/>
-      <c r="E8" s="112"/>
-      <c r="F8" s="113"/>
-      <c r="G8" s="115"/>
-      <c r="H8" s="115"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="116"/>
-      <c r="K8" s="115"/>
-      <c r="L8" s="115"/>
-      <c r="M8" s="112"/>
-      <c r="N8" s="116"/>
-      <c r="O8" s="115"/>
-      <c r="P8" s="115"/>
-      <c r="Q8" s="112"/>
-      <c r="R8" s="116"/>
-      <c r="S8" s="117"/>
+      <c r="B8" s="93"/>
+      <c r="C8" s="108" t="s">
+        <v>162</v>
+      </c>
+      <c r="D8" s="109"/>
+      <c r="E8" s="110"/>
+      <c r="F8" s="111"/>
+      <c r="G8" s="113"/>
+      <c r="H8" s="113"/>
+      <c r="I8" s="110"/>
+      <c r="J8" s="114"/>
+      <c r="K8" s="113"/>
+      <c r="L8" s="113"/>
+      <c r="M8" s="110"/>
+      <c r="N8" s="114"/>
+      <c r="O8" s="113"/>
+      <c r="P8" s="113"/>
+      <c r="Q8" s="110"/>
+      <c r="R8" s="114"/>
+      <c r="S8" s="115"/>
       <c r="U8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="95"/>
-      <c r="C9" s="102"/>
-      <c r="D9" s="103"/>
-      <c r="E9" s="104"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="106"/>
-      <c r="H9" s="107"/>
-      <c r="I9" s="104"/>
-      <c r="J9" s="108"/>
-      <c r="K9" s="107"/>
-      <c r="L9" s="107"/>
-      <c r="M9" s="104"/>
-      <c r="N9" s="108"/>
-      <c r="O9" s="107"/>
-      <c r="P9" s="107"/>
-      <c r="Q9" s="104"/>
-      <c r="R9" s="108"/>
-      <c r="S9" s="109"/>
+      <c r="B9" s="93"/>
+      <c r="C9" s="100"/>
+      <c r="D9" s="101"/>
+      <c r="E9" s="102"/>
+      <c r="F9" s="106"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="102"/>
+      <c r="J9" s="106"/>
+      <c r="K9" s="105"/>
+      <c r="L9" s="105"/>
+      <c r="M9" s="102"/>
+      <c r="N9" s="106"/>
+      <c r="O9" s="105"/>
+      <c r="P9" s="105"/>
+      <c r="Q9" s="102"/>
+      <c r="R9" s="106"/>
+      <c r="S9" s="107"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="95"/>
-      <c r="C10" s="110" t="s">
-        <v>163</v>
-      </c>
-      <c r="D10" s="111"/>
-      <c r="E10" s="112"/>
-      <c r="F10" s="116"/>
-      <c r="G10" s="114"/>
-      <c r="H10" s="114"/>
-      <c r="I10" s="112"/>
-      <c r="J10" s="116"/>
-      <c r="K10" s="115"/>
-      <c r="L10" s="115"/>
-      <c r="M10" s="112"/>
-      <c r="N10" s="116"/>
-      <c r="O10" s="115"/>
-      <c r="P10" s="115"/>
-      <c r="Q10" s="112"/>
-      <c r="R10" s="116"/>
-      <c r="S10" s="117"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="108" t="s">
+        <v>164</v>
+      </c>
+      <c r="D10" s="109"/>
+      <c r="E10" s="110"/>
+      <c r="F10" s="114"/>
+      <c r="G10" s="112"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="110"/>
+      <c r="J10" s="114"/>
+      <c r="K10" s="113"/>
+      <c r="L10" s="113"/>
+      <c r="M10" s="110"/>
+      <c r="N10" s="114"/>
+      <c r="O10" s="113"/>
+      <c r="P10" s="113"/>
+      <c r="Q10" s="110"/>
+      <c r="R10" s="114"/>
+      <c r="S10" s="115"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="119"/>
-      <c r="C11" s="120"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="123"/>
-      <c r="G11" s="124"/>
-      <c r="H11" s="124"/>
-      <c r="I11" s="122"/>
-      <c r="J11" s="123"/>
-      <c r="K11" s="125"/>
-      <c r="L11" s="125"/>
-      <c r="M11" s="122"/>
-      <c r="N11" s="123"/>
-      <c r="O11" s="125"/>
-      <c r="P11" s="125"/>
-      <c r="Q11" s="122"/>
-      <c r="R11" s="123"/>
-      <c r="S11" s="126"/>
+      <c r="B11" s="117"/>
+      <c r="C11" s="118"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="120"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="122"/>
+      <c r="H11" s="122"/>
+      <c r="I11" s="120"/>
+      <c r="J11" s="121"/>
+      <c r="K11" s="123"/>
+      <c r="L11" s="123"/>
+      <c r="M11" s="120"/>
+      <c r="N11" s="121"/>
+      <c r="O11" s="123"/>
+      <c r="P11" s="123"/>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="121"/>
+      <c r="S11" s="124"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="82" t="s">
-        <v>164</v>
-      </c>
-      <c r="C12" s="83" t="s">
+      <c r="B12" s="80" t="s">
         <v>165</v>
       </c>
-      <c r="D12" s="96"/>
-      <c r="E12" s="97"/>
-      <c r="F12" s="100"/>
-      <c r="G12" s="99"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="128"/>
-      <c r="J12" s="100"/>
-      <c r="K12" s="99"/>
-      <c r="L12" s="99"/>
-      <c r="M12" s="97"/>
-      <c r="N12" s="100"/>
-      <c r="O12" s="99"/>
-      <c r="P12" s="99"/>
-      <c r="Q12" s="97"/>
-      <c r="R12" s="100"/>
-      <c r="S12" s="101"/>
+      <c r="C12" s="81" t="s">
+        <v>166</v>
+      </c>
+      <c r="D12" s="94"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="98"/>
+      <c r="G12" s="97"/>
+      <c r="H12" s="125"/>
+      <c r="I12" s="126"/>
+      <c r="J12" s="98"/>
+      <c r="K12" s="97"/>
+      <c r="L12" s="97"/>
+      <c r="M12" s="95"/>
+      <c r="N12" s="98"/>
+      <c r="O12" s="97"/>
+      <c r="P12" s="97"/>
+      <c r="Q12" s="95"/>
+      <c r="R12" s="98"/>
+      <c r="S12" s="99"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="95"/>
-      <c r="C13" s="102"/>
-      <c r="D13" s="103"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="107"/>
-      <c r="H13" s="107"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="105"/>
-      <c r="K13" s="107"/>
-      <c r="L13" s="107"/>
-      <c r="M13" s="104"/>
-      <c r="N13" s="108"/>
-      <c r="O13" s="107"/>
-      <c r="P13" s="107"/>
-      <c r="Q13" s="104"/>
-      <c r="R13" s="108"/>
-      <c r="S13" s="109"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="100"/>
+      <c r="D13" s="101"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="106"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="102"/>
+      <c r="J13" s="103"/>
+      <c r="K13" s="105"/>
+      <c r="L13" s="105"/>
+      <c r="M13" s="102"/>
+      <c r="N13" s="106"/>
+      <c r="O13" s="105"/>
+      <c r="P13" s="105"/>
+      <c r="Q13" s="102"/>
+      <c r="R13" s="106"/>
+      <c r="S13" s="107"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="95"/>
-      <c r="C14" s="110" t="s">
-        <v>166</v>
-      </c>
-      <c r="D14" s="129"/>
-      <c r="E14" s="112"/>
-      <c r="F14" s="116"/>
-      <c r="G14" s="115"/>
-      <c r="H14" s="114"/>
-      <c r="I14" s="112"/>
-      <c r="J14" s="116"/>
-      <c r="K14" s="115"/>
-      <c r="L14" s="115"/>
-      <c r="M14" s="112"/>
-      <c r="N14" s="116"/>
-      <c r="O14" s="115"/>
-      <c r="P14" s="115"/>
-      <c r="Q14" s="112"/>
-      <c r="R14" s="116"/>
-      <c r="S14" s="117"/>
+      <c r="B14" s="93"/>
+      <c r="C14" s="108" t="s">
+        <v>167</v>
+      </c>
+      <c r="D14" s="127"/>
+      <c r="E14" s="110"/>
+      <c r="F14" s="114"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="112"/>
+      <c r="I14" s="110"/>
+      <c r="J14" s="114"/>
+      <c r="K14" s="113"/>
+      <c r="L14" s="113"/>
+      <c r="M14" s="110"/>
+      <c r="N14" s="114"/>
+      <c r="O14" s="113"/>
+      <c r="P14" s="113"/>
+      <c r="Q14" s="110"/>
+      <c r="R14" s="114"/>
+      <c r="S14" s="115"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="95"/>
-      <c r="C15" s="102"/>
-      <c r="D15" s="103"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="108"/>
-      <c r="G15" s="107"/>
-      <c r="H15" s="107"/>
-      <c r="I15" s="130"/>
-      <c r="J15" s="105"/>
-      <c r="K15" s="107"/>
-      <c r="L15" s="107"/>
-      <c r="M15" s="104"/>
-      <c r="N15" s="108"/>
-      <c r="O15" s="107"/>
-      <c r="P15" s="107"/>
-      <c r="Q15" s="104"/>
-      <c r="R15" s="108"/>
-      <c r="S15" s="109"/>
+      <c r="B15" s="93"/>
+      <c r="C15" s="100"/>
+      <c r="D15" s="101"/>
+      <c r="E15" s="102"/>
+      <c r="F15" s="106"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="105"/>
+      <c r="I15" s="128"/>
+      <c r="J15" s="103"/>
+      <c r="K15" s="105"/>
+      <c r="L15" s="105"/>
+      <c r="M15" s="102"/>
+      <c r="N15" s="106"/>
+      <c r="O15" s="105"/>
+      <c r="P15" s="105"/>
+      <c r="Q15" s="102"/>
+      <c r="R15" s="106"/>
+      <c r="S15" s="107"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="95"/>
-      <c r="C16" s="110" t="s">
-        <v>167</v>
-      </c>
-      <c r="D16" s="111"/>
-      <c r="E16" s="112"/>
-      <c r="F16" s="116"/>
-      <c r="G16" s="115"/>
-      <c r="H16" s="114"/>
-      <c r="I16" s="131"/>
-      <c r="J16" s="116"/>
-      <c r="K16" s="115"/>
-      <c r="L16" s="115"/>
-      <c r="M16" s="112"/>
-      <c r="N16" s="116"/>
-      <c r="O16" s="115"/>
-      <c r="P16" s="115"/>
-      <c r="Q16" s="112"/>
-      <c r="R16" s="116"/>
-      <c r="S16" s="117"/>
+      <c r="B16" s="93"/>
+      <c r="C16" s="108" t="s">
+        <v>168</v>
+      </c>
+      <c r="D16" s="109"/>
+      <c r="E16" s="110"/>
+      <c r="F16" s="114"/>
+      <c r="G16" s="113"/>
+      <c r="H16" s="112"/>
+      <c r="I16" s="129"/>
+      <c r="J16" s="114"/>
+      <c r="K16" s="113"/>
+      <c r="L16" s="113"/>
+      <c r="M16" s="110"/>
+      <c r="N16" s="114"/>
+      <c r="O16" s="113"/>
+      <c r="P16" s="113"/>
+      <c r="Q16" s="110"/>
+      <c r="R16" s="114"/>
+      <c r="S16" s="115"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="119"/>
-      <c r="C17" s="120"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="123"/>
-      <c r="G17" s="125"/>
-      <c r="H17" s="125"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="132"/>
-      <c r="K17" s="124"/>
-      <c r="L17" s="125"/>
-      <c r="M17" s="122"/>
-      <c r="N17" s="123"/>
-      <c r="O17" s="125"/>
-      <c r="P17" s="125"/>
-      <c r="Q17" s="122"/>
-      <c r="R17" s="123"/>
-      <c r="S17" s="126"/>
+      <c r="B17" s="117"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="120"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="123"/>
+      <c r="H17" s="123"/>
+      <c r="I17" s="120"/>
+      <c r="J17" s="130"/>
+      <c r="K17" s="122"/>
+      <c r="L17" s="123"/>
+      <c r="M17" s="120"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="123"/>
+      <c r="P17" s="123"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="121"/>
+      <c r="S17" s="124"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="84" t="s">
-        <v>168</v>
-      </c>
-      <c r="C18" s="83" t="s">
+      <c r="B18" s="82" t="s">
         <v>169</v>
       </c>
-      <c r="D18" s="96"/>
-      <c r="E18" s="97"/>
-      <c r="F18" s="100"/>
-      <c r="G18" s="99"/>
-      <c r="H18" s="99"/>
-      <c r="I18" s="128"/>
-      <c r="J18" s="100"/>
-      <c r="K18" s="99"/>
-      <c r="L18" s="99"/>
-      <c r="M18" s="97"/>
-      <c r="N18" s="100"/>
-      <c r="O18" s="99"/>
-      <c r="P18" s="99"/>
-      <c r="Q18" s="97"/>
-      <c r="R18" s="100"/>
-      <c r="S18" s="101"/>
+      <c r="C18" s="81" t="s">
+        <v>170</v>
+      </c>
+      <c r="D18" s="94"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="98"/>
+      <c r="G18" s="97"/>
+      <c r="H18" s="97"/>
+      <c r="I18" s="126"/>
+      <c r="J18" s="98"/>
+      <c r="K18" s="97"/>
+      <c r="L18" s="97"/>
+      <c r="M18" s="95"/>
+      <c r="N18" s="98"/>
+      <c r="O18" s="97"/>
+      <c r="P18" s="97"/>
+      <c r="Q18" s="95"/>
+      <c r="R18" s="98"/>
+      <c r="S18" s="99"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="95"/>
-      <c r="C19" s="102"/>
-      <c r="D19" s="103"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="108"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="107"/>
-      <c r="I19" s="104"/>
-      <c r="J19" s="108"/>
-      <c r="K19" s="107"/>
-      <c r="L19" s="107"/>
-      <c r="M19" s="104"/>
-      <c r="N19" s="108"/>
-      <c r="O19" s="107"/>
-      <c r="P19" s="107"/>
-      <c r="Q19" s="104"/>
-      <c r="R19" s="108"/>
-      <c r="S19" s="109"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="100"/>
+      <c r="D19" s="101"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="106"/>
+      <c r="G19" s="104"/>
+      <c r="H19" s="105"/>
+      <c r="I19" s="102"/>
+      <c r="J19" s="106"/>
+      <c r="K19" s="105"/>
+      <c r="L19" s="105"/>
+      <c r="M19" s="102"/>
+      <c r="N19" s="106"/>
+      <c r="O19" s="105"/>
+      <c r="P19" s="105"/>
+      <c r="Q19" s="102"/>
+      <c r="R19" s="106"/>
+      <c r="S19" s="107"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="95"/>
-      <c r="C20" s="110" t="s">
-        <v>170</v>
-      </c>
-      <c r="D20" s="111"/>
-      <c r="E20" s="112"/>
-      <c r="F20" s="116"/>
-      <c r="G20" s="115"/>
-      <c r="H20" s="115"/>
-      <c r="I20" s="131"/>
-      <c r="J20" s="113"/>
-      <c r="K20" s="114"/>
-      <c r="L20" s="114"/>
-      <c r="M20" s="112"/>
-      <c r="N20" s="116"/>
-      <c r="O20" s="115"/>
-      <c r="P20" s="115"/>
-      <c r="Q20" s="112"/>
-      <c r="R20" s="116"/>
-      <c r="S20" s="117"/>
+      <c r="B20" s="93"/>
+      <c r="C20" s="108" t="s">
+        <v>171</v>
+      </c>
+      <c r="D20" s="109"/>
+      <c r="E20" s="110"/>
+      <c r="F20" s="114"/>
+      <c r="G20" s="113"/>
+      <c r="H20" s="113"/>
+      <c r="I20" s="129"/>
+      <c r="J20" s="111"/>
+      <c r="K20" s="112"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="110"/>
+      <c r="N20" s="114"/>
+      <c r="O20" s="113"/>
+      <c r="P20" s="113"/>
+      <c r="Q20" s="110"/>
+      <c r="R20" s="114"/>
+      <c r="S20" s="115"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="95"/>
-      <c r="C21" s="102"/>
-      <c r="D21" s="103"/>
-      <c r="E21" s="104"/>
-      <c r="F21" s="108"/>
-      <c r="G21" s="107"/>
-      <c r="H21" s="107"/>
-      <c r="I21" s="104"/>
-      <c r="J21" s="108"/>
-      <c r="K21" s="107"/>
-      <c r="L21" s="107"/>
-      <c r="M21" s="104"/>
-      <c r="N21" s="133"/>
-      <c r="O21" s="107"/>
-      <c r="P21" s="107"/>
-      <c r="Q21" s="104"/>
-      <c r="R21" s="108"/>
-      <c r="S21" s="109"/>
+      <c r="B21" s="93"/>
+      <c r="C21" s="100"/>
+      <c r="D21" s="101"/>
+      <c r="E21" s="102"/>
+      <c r="F21" s="106"/>
+      <c r="G21" s="105"/>
+      <c r="H21" s="105"/>
+      <c r="I21" s="102"/>
+      <c r="J21" s="106"/>
+      <c r="K21" s="105"/>
+      <c r="L21" s="105"/>
+      <c r="M21" s="102"/>
+      <c r="N21" s="131"/>
+      <c r="O21" s="105"/>
+      <c r="P21" s="105"/>
+      <c r="Q21" s="102"/>
+      <c r="R21" s="106"/>
+      <c r="S21" s="107"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="95"/>
-      <c r="C22" s="110" t="s">
-        <v>171</v>
-      </c>
-      <c r="D22" s="111"/>
-      <c r="E22" s="112"/>
-      <c r="F22" s="116"/>
-      <c r="G22" s="115"/>
-      <c r="H22" s="115"/>
-      <c r="I22" s="112"/>
-      <c r="J22" s="116"/>
-      <c r="K22" s="114"/>
-      <c r="L22" s="114"/>
-      <c r="M22" s="112"/>
-      <c r="N22" s="116"/>
-      <c r="O22" s="115"/>
-      <c r="P22" s="115"/>
-      <c r="Q22" s="112"/>
-      <c r="R22" s="116"/>
-      <c r="S22" s="117"/>
+      <c r="B22" s="93"/>
+      <c r="C22" s="108" t="s">
+        <v>172</v>
+      </c>
+      <c r="D22" s="109"/>
+      <c r="E22" s="110"/>
+      <c r="F22" s="114"/>
+      <c r="G22" s="113"/>
+      <c r="H22" s="113"/>
+      <c r="I22" s="110"/>
+      <c r="J22" s="114"/>
+      <c r="K22" s="112"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="110"/>
+      <c r="N22" s="114"/>
+      <c r="O22" s="113"/>
+      <c r="P22" s="113"/>
+      <c r="Q22" s="110"/>
+      <c r="R22" s="114"/>
+      <c r="S22" s="115"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="119"/>
-      <c r="C23" s="120"/>
-      <c r="D23" s="121"/>
-      <c r="E23" s="122"/>
-      <c r="F23" s="123"/>
-      <c r="G23" s="125"/>
-      <c r="H23" s="125"/>
-      <c r="I23" s="122"/>
-      <c r="J23" s="123"/>
-      <c r="K23" s="125"/>
-      <c r="L23" s="125"/>
-      <c r="M23" s="122"/>
-      <c r="N23" s="123"/>
-      <c r="O23" s="125"/>
-      <c r="P23" s="125"/>
-      <c r="Q23" s="122"/>
-      <c r="R23" s="123"/>
-      <c r="S23" s="126"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="119"/>
+      <c r="E23" s="120"/>
+      <c r="F23" s="121"/>
+      <c r="G23" s="123"/>
+      <c r="H23" s="123"/>
+      <c r="I23" s="120"/>
+      <c r="J23" s="121"/>
+      <c r="K23" s="123"/>
+      <c r="L23" s="123"/>
+      <c r="M23" s="120"/>
+      <c r="N23" s="121"/>
+      <c r="O23" s="123"/>
+      <c r="P23" s="123"/>
+      <c r="Q23" s="120"/>
+      <c r="R23" s="121"/>
+      <c r="S23" s="124"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="84" t="s">
-        <v>172</v>
-      </c>
-      <c r="C24" s="83" t="s">
+      <c r="B24" s="82" t="s">
         <v>173</v>
       </c>
-      <c r="D24" s="96"/>
-      <c r="E24" s="97"/>
-      <c r="F24" s="100"/>
-      <c r="G24" s="99"/>
-      <c r="H24" s="99"/>
-      <c r="I24" s="97"/>
-      <c r="J24" s="100"/>
-      <c r="K24" s="99"/>
-      <c r="L24" s="99"/>
-      <c r="M24" s="128"/>
-      <c r="N24" s="98"/>
-      <c r="O24" s="127"/>
-      <c r="P24" s="127"/>
-      <c r="Q24" s="97"/>
-      <c r="R24" s="100"/>
-      <c r="S24" s="101"/>
+      <c r="C24" s="81" t="s">
+        <v>174</v>
+      </c>
+      <c r="D24" s="94"/>
+      <c r="E24" s="95"/>
+      <c r="F24" s="98"/>
+      <c r="G24" s="97"/>
+      <c r="H24" s="97"/>
+      <c r="I24" s="95"/>
+      <c r="J24" s="98"/>
+      <c r="K24" s="97"/>
+      <c r="L24" s="97"/>
+      <c r="M24" s="126"/>
+      <c r="N24" s="96"/>
+      <c r="O24" s="125"/>
+      <c r="P24" s="125"/>
+      <c r="Q24" s="95"/>
+      <c r="R24" s="98"/>
+      <c r="S24" s="99"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="95"/>
-      <c r="C25" s="102"/>
-      <c r="D25" s="103"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="108"/>
-      <c r="G25" s="107"/>
-      <c r="H25" s="107"/>
-      <c r="I25" s="104"/>
-      <c r="J25" s="108"/>
-      <c r="K25" s="107"/>
-      <c r="L25" s="107"/>
-      <c r="M25" s="104"/>
-      <c r="N25" s="108"/>
-      <c r="O25" s="107"/>
-      <c r="P25" s="107"/>
-      <c r="Q25" s="104"/>
-      <c r="R25" s="108"/>
-      <c r="S25" s="109"/>
+      <c r="B25" s="93"/>
+      <c r="C25" s="100"/>
+      <c r="D25" s="101"/>
+      <c r="E25" s="102"/>
+      <c r="F25" s="106"/>
+      <c r="G25" s="105"/>
+      <c r="H25" s="105"/>
+      <c r="I25" s="102"/>
+      <c r="J25" s="106"/>
+      <c r="K25" s="105"/>
+      <c r="L25" s="105"/>
+      <c r="M25" s="102"/>
+      <c r="N25" s="106"/>
+      <c r="O25" s="105"/>
+      <c r="P25" s="105"/>
+      <c r="Q25" s="102"/>
+      <c r="R25" s="106"/>
+      <c r="S25" s="107"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="95"/>
-      <c r="C26" s="110" t="s">
-        <v>174</v>
-      </c>
-      <c r="D26" s="111"/>
-      <c r="E26" s="112"/>
-      <c r="F26" s="116"/>
-      <c r="G26" s="115"/>
-      <c r="H26" s="115"/>
-      <c r="I26" s="112"/>
-      <c r="J26" s="116"/>
-      <c r="K26" s="115"/>
-      <c r="L26" s="115"/>
-      <c r="M26" s="112"/>
-      <c r="N26" s="116"/>
-      <c r="O26" s="114"/>
-      <c r="P26" s="114"/>
-      <c r="Q26" s="112"/>
-      <c r="R26" s="116"/>
-      <c r="S26" s="117"/>
+      <c r="B26" s="93"/>
+      <c r="C26" s="108" t="s">
+        <v>175</v>
+      </c>
+      <c r="D26" s="109"/>
+      <c r="E26" s="110"/>
+      <c r="F26" s="114"/>
+      <c r="G26" s="113"/>
+      <c r="H26" s="113"/>
+      <c r="I26" s="110"/>
+      <c r="J26" s="114"/>
+      <c r="K26" s="113"/>
+      <c r="L26" s="113"/>
+      <c r="M26" s="110"/>
+      <c r="N26" s="114"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="110"/>
+      <c r="R26" s="114"/>
+      <c r="S26" s="115"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="95"/>
-      <c r="C27" s="102"/>
-      <c r="D27" s="103"/>
-      <c r="E27" s="104"/>
-      <c r="F27" s="108"/>
-      <c r="G27" s="107"/>
-      <c r="H27" s="107"/>
-      <c r="I27" s="104"/>
-      <c r="J27" s="108"/>
-      <c r="K27" s="107"/>
-      <c r="L27" s="107"/>
-      <c r="M27" s="104"/>
-      <c r="N27" s="108"/>
-      <c r="O27" s="107"/>
-      <c r="P27" s="107"/>
-      <c r="Q27" s="104"/>
-      <c r="R27" s="108"/>
-      <c r="S27" s="109"/>
+      <c r="B27" s="93"/>
+      <c r="C27" s="100"/>
+      <c r="D27" s="101"/>
+      <c r="E27" s="102"/>
+      <c r="F27" s="106"/>
+      <c r="G27" s="105"/>
+      <c r="H27" s="105"/>
+      <c r="I27" s="102"/>
+      <c r="J27" s="106"/>
+      <c r="K27" s="105"/>
+      <c r="L27" s="105"/>
+      <c r="M27" s="102"/>
+      <c r="N27" s="106"/>
+      <c r="O27" s="105"/>
+      <c r="P27" s="105"/>
+      <c r="Q27" s="102"/>
+      <c r="R27" s="106"/>
+      <c r="S27" s="107"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="95"/>
-      <c r="C28" s="110" t="s">
-        <v>175</v>
-      </c>
-      <c r="D28" s="111"/>
-      <c r="E28" s="112"/>
-      <c r="F28" s="116"/>
-      <c r="G28" s="115"/>
-      <c r="H28" s="115"/>
-      <c r="I28" s="112"/>
-      <c r="J28" s="116"/>
-      <c r="K28" s="115"/>
-      <c r="L28" s="115"/>
-      <c r="M28" s="112"/>
-      <c r="N28" s="116"/>
-      <c r="O28" s="115"/>
-      <c r="P28" s="114"/>
-      <c r="Q28" s="131"/>
-      <c r="R28" s="116"/>
-      <c r="S28" s="117"/>
+      <c r="B28" s="93"/>
+      <c r="C28" s="108" t="s">
+        <v>176</v>
+      </c>
+      <c r="D28" s="109"/>
+      <c r="E28" s="110"/>
+      <c r="F28" s="114"/>
+      <c r="G28" s="113"/>
+      <c r="H28" s="113"/>
+      <c r="I28" s="110"/>
+      <c r="J28" s="114"/>
+      <c r="K28" s="113"/>
+      <c r="L28" s="113"/>
+      <c r="M28" s="110"/>
+      <c r="N28" s="114"/>
+      <c r="O28" s="113"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="129"/>
+      <c r="R28" s="114"/>
+      <c r="S28" s="115"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="95"/>
-      <c r="C29" s="89"/>
-      <c r="D29" s="134"/>
-      <c r="E29" s="135"/>
-      <c r="F29" s="136"/>
-      <c r="G29" s="137"/>
-      <c r="H29" s="138"/>
-      <c r="I29" s="135"/>
-      <c r="J29" s="136"/>
-      <c r="K29" s="137"/>
-      <c r="L29" s="138"/>
-      <c r="M29" s="135"/>
-      <c r="N29" s="139"/>
-      <c r="O29" s="138"/>
-      <c r="P29" s="137"/>
-      <c r="Q29" s="135"/>
-      <c r="R29" s="136"/>
-      <c r="S29" s="140"/>
+      <c r="B29" s="93"/>
+      <c r="C29" s="87"/>
+      <c r="D29" s="132"/>
+      <c r="E29" s="133"/>
+      <c r="F29" s="134"/>
+      <c r="G29" s="135"/>
+      <c r="H29" s="136"/>
+      <c r="I29" s="133"/>
+      <c r="J29" s="134"/>
+      <c r="K29" s="135"/>
+      <c r="L29" s="136"/>
+      <c r="M29" s="133"/>
+      <c r="N29" s="137"/>
+      <c r="O29" s="136"/>
+      <c r="P29" s="135"/>
+      <c r="Q29" s="133"/>
+      <c r="R29" s="134"/>
+      <c r="S29" s="138"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="141" t="s">
+      <c r="B30" s="139" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="142" t="s">
-        <v>119</v>
-      </c>
-      <c r="D30" s="96"/>
-      <c r="E30" s="143"/>
-      <c r="F30" s="144"/>
-      <c r="G30" s="144"/>
-      <c r="H30" s="145"/>
-      <c r="I30" s="146"/>
-      <c r="J30" s="144"/>
-      <c r="K30" s="144"/>
-      <c r="L30" s="145"/>
-      <c r="M30" s="146"/>
-      <c r="N30" s="144"/>
-      <c r="O30" s="145"/>
-      <c r="P30" s="144"/>
-      <c r="Q30" s="146"/>
-      <c r="R30" s="144"/>
-      <c r="S30" s="147"/>
+      <c r="C30" s="140" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" s="94"/>
+      <c r="E30" s="141"/>
+      <c r="F30" s="142"/>
+      <c r="G30" s="142"/>
+      <c r="H30" s="143"/>
+      <c r="I30" s="144"/>
+      <c r="J30" s="142"/>
+      <c r="K30" s="142"/>
+      <c r="L30" s="143"/>
+      <c r="M30" s="144"/>
+      <c r="N30" s="142"/>
+      <c r="O30" s="143"/>
+      <c r="P30" s="142"/>
+      <c r="Q30" s="144"/>
+      <c r="R30" s="142"/>
+      <c r="S30" s="145"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="148"/>
-      <c r="C31" s="149"/>
-      <c r="D31" s="103"/>
-      <c r="E31" s="150"/>
-      <c r="F31" s="151"/>
-      <c r="G31" s="151"/>
-      <c r="H31" s="152"/>
-      <c r="I31" s="153"/>
-      <c r="J31" s="151"/>
-      <c r="K31" s="154"/>
-      <c r="L31" s="152"/>
-      <c r="M31" s="153"/>
-      <c r="N31" s="151"/>
-      <c r="O31" s="152"/>
-      <c r="P31" s="151"/>
-      <c r="Q31" s="153"/>
-      <c r="R31" s="151"/>
-      <c r="S31" s="109"/>
+      <c r="B31" s="146"/>
+      <c r="C31" s="147"/>
+      <c r="D31" s="101"/>
+      <c r="E31" s="148"/>
+      <c r="F31" s="149"/>
+      <c r="G31" s="149"/>
+      <c r="H31" s="150"/>
+      <c r="I31" s="151"/>
+      <c r="J31" s="149"/>
+      <c r="K31" s="152"/>
+      <c r="L31" s="150"/>
+      <c r="M31" s="151"/>
+      <c r="N31" s="149"/>
+      <c r="O31" s="150"/>
+      <c r="P31" s="149"/>
+      <c r="Q31" s="151"/>
+      <c r="R31" s="149"/>
+      <c r="S31" s="107"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="148"/>
-      <c r="C32" s="149" t="s">
+      <c r="B32" s="146"/>
+      <c r="C32" s="147" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="111"/>
-      <c r="E32" s="155"/>
-      <c r="F32" s="156"/>
-      <c r="G32" s="156"/>
-      <c r="H32" s="157"/>
-      <c r="I32" s="158"/>
-      <c r="J32" s="156"/>
-      <c r="K32" s="156"/>
-      <c r="L32" s="157"/>
-      <c r="M32" s="158"/>
-      <c r="N32" s="156"/>
-      <c r="O32" s="157"/>
-      <c r="P32" s="156"/>
-      <c r="Q32" s="158"/>
-      <c r="R32" s="156"/>
-      <c r="S32" s="159"/>
+      <c r="D32" s="109"/>
+      <c r="E32" s="153"/>
+      <c r="F32" s="154"/>
+      <c r="G32" s="154"/>
+      <c r="H32" s="155"/>
+      <c r="I32" s="156"/>
+      <c r="J32" s="154"/>
+      <c r="K32" s="154"/>
+      <c r="L32" s="155"/>
+      <c r="M32" s="156"/>
+      <c r="N32" s="154"/>
+      <c r="O32" s="155"/>
+      <c r="P32" s="154"/>
+      <c r="Q32" s="156"/>
+      <c r="R32" s="154"/>
+      <c r="S32" s="157"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="148"/>
-      <c r="C33" s="149"/>
-      <c r="D33" s="103"/>
-      <c r="E33" s="150"/>
-      <c r="F33" s="154"/>
-      <c r="G33" s="151"/>
-      <c r="H33" s="160"/>
-      <c r="I33" s="161"/>
-      <c r="J33" s="151"/>
-      <c r="K33" s="154"/>
-      <c r="L33" s="152"/>
-      <c r="M33" s="153"/>
-      <c r="N33" s="151"/>
-      <c r="O33" s="152"/>
-      <c r="P33" s="151"/>
-      <c r="Q33" s="153"/>
-      <c r="R33" s="151"/>
-      <c r="S33" s="109"/>
+      <c r="B33" s="146"/>
+      <c r="C33" s="147"/>
+      <c r="D33" s="101"/>
+      <c r="E33" s="148"/>
+      <c r="F33" s="152"/>
+      <c r="G33" s="149"/>
+      <c r="H33" s="158"/>
+      <c r="I33" s="159"/>
+      <c r="J33" s="149"/>
+      <c r="K33" s="152"/>
+      <c r="L33" s="150"/>
+      <c r="M33" s="151"/>
+      <c r="N33" s="149"/>
+      <c r="O33" s="150"/>
+      <c r="P33" s="149"/>
+      <c r="Q33" s="151"/>
+      <c r="R33" s="149"/>
+      <c r="S33" s="107"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="148"/>
-      <c r="C34" s="102" t="s">
-        <v>176</v>
-      </c>
-      <c r="D34" s="134"/>
-      <c r="E34" s="162"/>
-      <c r="F34" s="163"/>
-      <c r="G34" s="163"/>
-      <c r="H34" s="164"/>
-      <c r="I34" s="165"/>
-      <c r="J34" s="163"/>
-      <c r="K34" s="163"/>
-      <c r="L34" s="164"/>
-      <c r="M34" s="165"/>
-      <c r="N34" s="163"/>
-      <c r="O34" s="164"/>
-      <c r="P34" s="163"/>
-      <c r="Q34" s="165"/>
-      <c r="R34" s="163"/>
-      <c r="S34" s="166"/>
-      <c r="U34" s="167"/>
-      <c r="V34" s="168" t="s">
+      <c r="B34" s="146"/>
+      <c r="C34" s="100" t="s">
         <v>177</v>
       </c>
+      <c r="D34" s="132"/>
+      <c r="E34" s="160"/>
+      <c r="F34" s="161"/>
+      <c r="G34" s="161"/>
+      <c r="H34" s="162"/>
+      <c r="I34" s="163"/>
+      <c r="J34" s="161"/>
+      <c r="K34" s="161"/>
+      <c r="L34" s="162"/>
+      <c r="M34" s="163"/>
+      <c r="N34" s="161"/>
+      <c r="O34" s="162"/>
+      <c r="P34" s="161"/>
+      <c r="Q34" s="163"/>
+      <c r="R34" s="161"/>
+      <c r="S34" s="164"/>
+      <c r="U34" s="165"/>
+      <c r="V34" s="166" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="169"/>
-      <c r="C35" s="170"/>
-      <c r="D35" s="121"/>
-      <c r="E35" s="171"/>
-      <c r="F35" s="172"/>
-      <c r="G35" s="172"/>
-      <c r="H35" s="173"/>
-      <c r="I35" s="174"/>
-      <c r="J35" s="172"/>
-      <c r="K35" s="172"/>
-      <c r="L35" s="173"/>
-      <c r="M35" s="174"/>
-      <c r="N35" s="172"/>
-      <c r="O35" s="173"/>
-      <c r="P35" s="172"/>
-      <c r="Q35" s="174"/>
-      <c r="R35" s="172"/>
-      <c r="S35" s="126"/>
-      <c r="U35" s="175"/>
-      <c r="V35" s="176" t="s">
-        <v>178</v>
+      <c r="B35" s="167"/>
+      <c r="C35" s="168"/>
+      <c r="D35" s="119"/>
+      <c r="E35" s="169"/>
+      <c r="F35" s="170"/>
+      <c r="G35" s="170"/>
+      <c r="H35" s="171"/>
+      <c r="I35" s="172"/>
+      <c r="J35" s="170"/>
+      <c r="K35" s="170"/>
+      <c r="L35" s="171"/>
+      <c r="M35" s="172"/>
+      <c r="N35" s="170"/>
+      <c r="O35" s="171"/>
+      <c r="P35" s="170"/>
+      <c r="Q35" s="172"/>
+      <c r="R35" s="170"/>
+      <c r="S35" s="124"/>
+      <c r="U35" s="173"/>
+      <c r="V35" s="174" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -10177,7 +10160,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="08AA274E-3F80-45FA-9EA1-C00B98F2A092">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00000000-0000-0000-0000-000000000000}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
   </ds:schemaRefs>

--- a/Documentation/HoferL-JournalPlanif-M5.xlsx
+++ b/Documentation/HoferL-JournalPlanif-M5.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="181">
   <si>
     <t>date</t>
   </si>
@@ -306,6 +306,9 @@
   </si>
   <si>
     <t xml:space="preserve">Commencement du manuel utilisateur. Documentation des différents affichages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajout de contenu dans le manuel utilisateur.</t>
   </si>
   <si>
     <t>Phases</t>
@@ -1544,7 +1547,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="176">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1592,6 +1595,9 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="20" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3693,8 +3699,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E66">
-  <autoFilter ref="B2:E66"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E67">
+  <autoFilter ref="B2:E67"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -5291,97 +5297,105 @@
       <c r="D66" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E66" s="22" t="s">
+      <c r="E66" s="8" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="20"/>
-      <c r="C67" s="23"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="8"/>
+      <c r="B67" s="20">
+        <v>46161</v>
+      </c>
+      <c r="C67" s="21">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="D67" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67" s="23" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="68">
       <c r="B68" s="20"/>
-      <c r="C68" s="23"/>
+      <c r="C68" s="24"/>
       <c r="D68" s="7"/>
       <c r="E68" s="8"/>
     </row>
     <row r="69">
       <c r="B69" s="20"/>
-      <c r="C69" s="23"/>
+      <c r="C69" s="24"/>
       <c r="D69" s="7"/>
       <c r="E69" s="8"/>
     </row>
     <row r="70">
       <c r="B70" s="20"/>
-      <c r="C70" s="23"/>
+      <c r="C70" s="24"/>
       <c r="D70" s="7"/>
       <c r="E70" s="8"/>
     </row>
     <row r="71">
       <c r="B71" s="20"/>
-      <c r="C71" s="23"/>
+      <c r="C71" s="24"/>
       <c r="D71" s="7"/>
       <c r="E71" s="8"/>
     </row>
     <row r="72">
       <c r="B72" s="20"/>
-      <c r="C72" s="23"/>
+      <c r="C72" s="24"/>
       <c r="D72" s="7"/>
       <c r="E72" s="8"/>
     </row>
     <row r="73">
       <c r="B73" s="20"/>
-      <c r="C73" s="23"/>
+      <c r="C73" s="24"/>
       <c r="D73" s="7"/>
       <c r="E73" s="8"/>
     </row>
     <row r="74">
       <c r="B74" s="20"/>
-      <c r="C74" s="23"/>
+      <c r="C74" s="24"/>
       <c r="D74" s="7"/>
       <c r="E74" s="8"/>
     </row>
     <row r="75">
       <c r="B75" s="20"/>
-      <c r="C75" s="23"/>
+      <c r="C75" s="24"/>
       <c r="D75" s="7"/>
       <c r="E75" s="8"/>
     </row>
     <row r="76">
       <c r="B76" s="7"/>
-      <c r="C76" s="23"/>
+      <c r="C76" s="24"/>
       <c r="D76" s="7"/>
       <c r="E76" s="8"/>
     </row>
     <row r="77">
       <c r="B77" s="7"/>
-      <c r="C77" s="23"/>
+      <c r="C77" s="24"/>
       <c r="D77" s="7"/>
       <c r="E77" s="8"/>
     </row>
     <row r="78">
       <c r="B78" s="7"/>
-      <c r="C78" s="23"/>
+      <c r="C78" s="24"/>
       <c r="D78" s="7"/>
       <c r="E78" s="8"/>
     </row>
     <row r="79">
       <c r="B79" s="7"/>
-      <c r="C79" s="23"/>
+      <c r="C79" s="24"/>
       <c r="D79" s="7"/>
       <c r="E79" s="8"/>
     </row>
     <row r="80">
       <c r="B80" s="7"/>
-      <c r="C80" s="23"/>
+      <c r="C80" s="24"/>
       <c r="D80" s="7"/>
       <c r="E80" s="8"/>
     </row>
     <row r="81">
       <c r="B81" s="7"/>
-      <c r="C81" s="23"/>
+      <c r="C81" s="24"/>
       <c r="D81" s="7"/>
       <c r="E81" s="8"/>
     </row>
@@ -5401,7 +5415,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00AF00DC-00DB-4AAB-855A-001F00640069}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00A7000F-0089-4EB4-8736-007F004E006B}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -5433,1787 +5447,1787 @@
       <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="str">
+      <c r="A2" s="25" t="str">
         <f t="array" ref="A2:A38">_xlfn.UNIQUE(Journal[date])</f>
         <v>20.01.2026</v>
       </c>
-      <c r="B2" s="25">
+      <c r="B2" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A2,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" s="26"/>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="str">
+      <c r="A3" s="25" t="str">
         <f/>
         <v>27.01.2026</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="str">
+      <c r="A4" s="25" t="str">
         <f/>
         <v>30.01.2026</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C4"/>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="str">
+      <c r="A5" s="25" t="str">
         <f/>
         <v>03.02.2026</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0.25</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="str">
+      <c r="A6" s="25" t="str">
         <f/>
         <v>04.02.2026</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="str">
+      <c r="A7" s="25" t="str">
         <f/>
         <v>06.02.2026</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C7"/>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="str">
+      <c r="A8" s="25" t="str">
         <f/>
         <v>08.02.2026</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
         <v>0.083333333333333329</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="str">
+      <c r="A9" s="25" t="str">
         <f/>
         <v>09.02.2026</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
         <v>0.041666666666666664</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="str">
+      <c r="A10" s="25" t="str">
         <f/>
         <v>10.02.2026</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="str">
+      <c r="A11" s="25" t="str">
         <f/>
         <v>12.02.2026</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
         <v>0.083333333333333329</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="str">
+      <c r="A12" s="25" t="str">
         <f/>
         <v>13.02.2026</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
         <v>0.0625</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="str">
+      <c r="A13" s="25" t="str">
         <f/>
         <v>24.02.2026</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0.125</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="str">
+      <c r="A14" s="25" t="str">
         <f/>
         <v>03.03.2026</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="str">
+      <c r="A15" s="25" t="str">
         <f/>
         <v>05.03.2026</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="24">
+      <c r="A16" s="25">
         <f/>
         <v>46087</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="24">
+      <c r="A17" s="25">
         <f/>
         <v>46088</v>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0.25</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="24">
+      <c r="A18" s="25">
         <f/>
         <v>46091</v>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="24">
+      <c r="A19" s="25">
         <f/>
         <v>46093</v>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
         <v>0.083333333333333329</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="24">
+      <c r="A20" s="25">
         <f/>
         <v>46095</v>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="24">
+      <c r="A21" s="25">
         <f/>
         <v>46096</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="24">
+      <c r="A22" s="25">
         <f/>
         <v>46097</v>
       </c>
-      <c r="B22" s="25">
+      <c r="B22" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0.14583333333333334</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="24">
+      <c r="A23" s="25">
         <f/>
         <v>46098</v>
       </c>
-      <c r="B23" s="25">
+      <c r="B23" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="24">
+      <c r="A24" s="25">
         <f/>
         <v>46099</v>
       </c>
-      <c r="B24" s="25">
+      <c r="B24" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="24">
+      <c r="A25" s="25">
         <f/>
         <v>46100</v>
       </c>
-      <c r="B25" s="25">
+      <c r="B25" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="C25"/>
-      <c r="F25" s="26"/>
+      <c r="F25" s="27"/>
     </row>
     <row r="26">
-      <c r="A26" s="24">
+      <c r="A26" s="25">
         <f/>
         <v>46102</v>
       </c>
-      <c r="B26" s="25">
+      <c r="B26" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="24">
+      <c r="A27" s="25">
         <f/>
         <v>46103</v>
       </c>
-      <c r="B27" s="25">
+      <c r="B27" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0.375</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0.375</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="24">
+      <c r="A28" s="25">
         <f/>
         <v>46104</v>
       </c>
-      <c r="B28" s="25">
+      <c r="B28" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0.013888888888888888</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0.013888888888888888</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24">
+      <c r="A29" s="25">
         <f/>
         <v>46117</v>
       </c>
-      <c r="B29" s="25">
+      <c r="B29" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="24">
+      <c r="A30" s="25">
         <f/>
         <v>46118</v>
       </c>
-      <c r="B30" s="25">
+      <c r="B30" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0.083333333333333329</v>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0.083333333333333329</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="24">
+      <c r="A31" s="25">
         <f/>
         <v>46119</v>
       </c>
-      <c r="B31" s="25">
+      <c r="B31" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0.083333333333333329</v>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0.083333333333333329</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="24">
+      <c r="A32" s="25">
         <f/>
         <v>46122</v>
       </c>
-      <c r="B32" s="25">
+      <c r="B32" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="24">
+      <c r="A33" s="25">
         <f/>
         <v>46133</v>
       </c>
-      <c r="C33" s="27">
+      <c r="C33" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24">
+      <c r="A34" s="25">
         <f/>
         <v>46134</v>
       </c>
-      <c r="C34" s="27">
+      <c r="C34" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0.10416666666666666</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="24">
+      <c r="A35" s="25">
         <f/>
         <v>46135</v>
       </c>
-      <c r="C35" s="27">
+      <c r="C35" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0.041666666666666664</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="24">
+      <c r="A36" s="25">
         <f/>
         <v>46136</v>
       </c>
-      <c r="C36" s="27">
+      <c r="C36" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="24">
+      <c r="A37" s="25">
         <f/>
         <v>46137</v>
       </c>
-      <c r="C37" s="27">
+      <c r="C37" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="24">
+      <c r="A38" s="25">
         <f/>
         <v>46140</v>
       </c>
-      <c r="C38" s="27">
+      <c r="C38" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0.18958333333333333</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="24"/>
-      <c r="C39" s="27">
+      <c r="A39" s="25"/>
+      <c r="C39" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="24"/>
-      <c r="B40" s="25" t="str">
+      <c r="A40" s="25"/>
+      <c r="B40" s="26" t="str">
         <f t="shared" ref="B40:B103" si="0">IF(C40&gt;0,C40,"")</f>
         <v/>
       </c>
-      <c r="C40" s="27">
+      <c r="C40" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="24"/>
-      <c r="B41" s="25" t="str">
+      <c r="A41" s="25"/>
+      <c r="B41" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="27">
+      <c r="C41" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="28"/>
-      <c r="B42" s="25" t="str">
+      <c r="A42" s="29"/>
+      <c r="B42" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="27">
+      <c r="C42" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="28"/>
-      <c r="B43" s="25" t="str">
+      <c r="A43" s="29"/>
+      <c r="B43" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="27">
+      <c r="C43" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="28"/>
-      <c r="B44" s="25" t="str">
+      <c r="A44" s="29"/>
+      <c r="B44" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="27">
+      <c r="C44" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="28"/>
-      <c r="B45" s="25" t="str">
+      <c r="A45" s="29"/>
+      <c r="B45" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="27">
+      <c r="C45" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="28"/>
-      <c r="B46" s="25" t="str">
+      <c r="A46" s="29"/>
+      <c r="B46" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="27">
+      <c r="C46" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="29"/>
-      <c r="B47" s="25" t="str">
+      <c r="A47" s="30"/>
+      <c r="B47" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="27">
+      <c r="C47" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="29"/>
-      <c r="B48" s="25" t="str">
+      <c r="A48" s="30"/>
+      <c r="B48" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="27">
+      <c r="C48" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="29"/>
-      <c r="B49" s="25" t="str">
+      <c r="A49" s="30"/>
+      <c r="B49" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C49" s="27">
+      <c r="C49" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="29"/>
-      <c r="B50" s="25" t="str">
+      <c r="A50" s="30"/>
+      <c r="B50" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C50" s="27">
+      <c r="C50" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="29"/>
-      <c r="B51" s="25" t="str">
+      <c r="A51" s="30"/>
+      <c r="B51" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C51" s="27">
+      <c r="C51" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="29"/>
-      <c r="B52" s="25" t="str">
+      <c r="A52" s="30"/>
+      <c r="B52" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C52" s="27">
+      <c r="C52" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="29"/>
-      <c r="B53" s="25" t="str">
+      <c r="A53" s="30"/>
+      <c r="B53" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C53" s="27">
+      <c r="C53" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="29"/>
-      <c r="B54" s="25" t="str">
+      <c r="A54" s="30"/>
+      <c r="B54" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C54" s="27">
+      <c r="C54" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="29"/>
-      <c r="B55" s="25" t="str">
+      <c r="A55" s="30"/>
+      <c r="B55" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C55" s="27">
+      <c r="C55" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="29"/>
-      <c r="B56" s="25" t="str">
+      <c r="A56" s="30"/>
+      <c r="B56" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C56" s="27">
+      <c r="C56" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="29"/>
-      <c r="B57" s="25" t="str">
+      <c r="A57" s="30"/>
+      <c r="B57" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C57" s="27">
+      <c r="C57" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="29"/>
-      <c r="B58" s="25" t="str">
+      <c r="A58" s="30"/>
+      <c r="B58" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C58" s="27">
+      <c r="C58" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="29"/>
-      <c r="B59" s="25" t="str">
+      <c r="A59" s="30"/>
+      <c r="B59" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C59" s="27">
+      <c r="C59" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="29"/>
-      <c r="B60" s="25" t="str">
+      <c r="A60" s="30"/>
+      <c r="B60" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C60" s="27">
+      <c r="C60" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="29"/>
-      <c r="B61" s="25" t="str">
+      <c r="A61" s="30"/>
+      <c r="B61" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C61" s="27">
+      <c r="C61" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="29"/>
-      <c r="B62" s="25" t="str">
+      <c r="A62" s="30"/>
+      <c r="B62" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C62" s="27">
+      <c r="C62" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="29"/>
-      <c r="B63" s="25" t="str">
+      <c r="A63" s="30"/>
+      <c r="B63" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C63" s="27">
+      <c r="C63" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="29"/>
-      <c r="B64" s="25" t="str">
+      <c r="A64" s="30"/>
+      <c r="B64" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C64" s="27">
+      <c r="C64" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="29"/>
-      <c r="B65" s="25" t="str">
+      <c r="A65" s="30"/>
+      <c r="B65" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C65" s="27">
+      <c r="C65" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="29"/>
-      <c r="B66" s="25" t="str">
+      <c r="A66" s="30"/>
+      <c r="B66" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C66" s="27">
+      <c r="C66" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="29"/>
-      <c r="B67" s="25" t="str">
+      <c r="A67" s="30"/>
+      <c r="B67" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C67" s="27">
+      <c r="C67" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="29"/>
-      <c r="B68" s="25" t="str">
+      <c r="A68" s="30"/>
+      <c r="B68" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C68" s="27">
+      <c r="C68" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29"/>
-      <c r="B69" s="25" t="str">
+      <c r="A69" s="30"/>
+      <c r="B69" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C69" s="27">
+      <c r="C69" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29"/>
-      <c r="B70" s="25" t="str">
+      <c r="A70" s="30"/>
+      <c r="B70" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C70" s="27">
+      <c r="C70" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="29"/>
-      <c r="B71" s="25" t="str">
+      <c r="A71" s="30"/>
+      <c r="B71" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C71" s="27">
+      <c r="C71" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="29"/>
-      <c r="B72" s="25" t="str">
+      <c r="A72" s="30"/>
+      <c r="B72" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C72" s="27">
+      <c r="C72" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="29"/>
-      <c r="B73" s="25" t="str">
+      <c r="A73" s="30"/>
+      <c r="B73" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C73" s="27">
+      <c r="C73" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="29"/>
-      <c r="B74" s="25" t="str">
+      <c r="A74" s="30"/>
+      <c r="B74" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C74" s="27">
+      <c r="C74" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="29"/>
-      <c r="B75" s="25" t="str">
+      <c r="A75" s="30"/>
+      <c r="B75" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C75" s="27">
+      <c r="C75" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="29"/>
-      <c r="B76" s="25" t="str">
+      <c r="A76" s="30"/>
+      <c r="B76" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C76" s="27">
+      <c r="C76" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29"/>
-      <c r="B77" s="25" t="str">
+      <c r="A77" s="30"/>
+      <c r="B77" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C77" s="27">
+      <c r="C77" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="29"/>
-      <c r="B78" s="25" t="str">
+      <c r="A78" s="30"/>
+      <c r="B78" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C78" s="27">
+      <c r="C78" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="29"/>
-      <c r="B79" s="25" t="str">
+      <c r="A79" s="30"/>
+      <c r="B79" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C79" s="27">
+      <c r="C79" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="29"/>
-      <c r="B80" s="25" t="str">
+      <c r="A80" s="30"/>
+      <c r="B80" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C80" s="27">
+      <c r="C80" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="29"/>
-      <c r="B81" s="25" t="str">
+      <c r="A81" s="30"/>
+      <c r="B81" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C81" s="27">
+      <c r="C81" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="29"/>
-      <c r="B82" s="25" t="str">
+      <c r="A82" s="30"/>
+      <c r="B82" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C82" s="27">
+      <c r="C82" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="29"/>
-      <c r="B83" s="25" t="str">
+      <c r="A83" s="30"/>
+      <c r="B83" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C83" s="27">
+      <c r="C83" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="29"/>
-      <c r="B84" s="25" t="str">
+      <c r="A84" s="30"/>
+      <c r="B84" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C84" s="27">
+      <c r="C84" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="29"/>
-      <c r="B85" s="25" t="str">
+      <c r="A85" s="30"/>
+      <c r="B85" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C85" s="27">
+      <c r="C85" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="29"/>
-      <c r="B86" s="25" t="str">
+      <c r="A86" s="30"/>
+      <c r="B86" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C86" s="27">
+      <c r="C86" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="29"/>
-      <c r="B87" s="25" t="str">
+      <c r="A87" s="30"/>
+      <c r="B87" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C87" s="27">
+      <c r="C87" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="29"/>
-      <c r="B88" s="25" t="str">
+      <c r="A88" s="30"/>
+      <c r="B88" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C88" s="27">
+      <c r="C88" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="29"/>
-      <c r="B89" s="25" t="str">
+      <c r="A89" s="30"/>
+      <c r="B89" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C89" s="27">
+      <c r="C89" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="29"/>
-      <c r="B90" s="25" t="str">
+      <c r="A90" s="30"/>
+      <c r="B90" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C90" s="27">
+      <c r="C90" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="29"/>
-      <c r="B91" s="25" t="str">
+      <c r="A91" s="30"/>
+      <c r="B91" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C91" s="27">
+      <c r="C91" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="29"/>
-      <c r="B92" s="25" t="str">
+      <c r="A92" s="30"/>
+      <c r="B92" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C92" s="27">
+      <c r="C92" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="29"/>
-      <c r="B93" s="25" t="str">
+      <c r="A93" s="30"/>
+      <c r="B93" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C93" s="27">
+      <c r="C93" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="29"/>
-      <c r="B94" s="25" t="str">
+      <c r="A94" s="30"/>
+      <c r="B94" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C94" s="27">
+      <c r="C94" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="29"/>
-      <c r="B95" s="25" t="str">
+      <c r="A95" s="30"/>
+      <c r="B95" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C95" s="27">
+      <c r="C95" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="29"/>
-      <c r="B96" s="25" t="str">
+      <c r="A96" s="30"/>
+      <c r="B96" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C96" s="27">
+      <c r="C96" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="29"/>
-      <c r="B97" s="25" t="str">
+      <c r="A97" s="30"/>
+      <c r="B97" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C97" s="27">
+      <c r="C97" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="29"/>
-      <c r="B98" s="25" t="str">
+      <c r="A98" s="30"/>
+      <c r="B98" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C98" s="27">
+      <c r="C98" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="29"/>
-      <c r="B99" s="25" t="str">
+      <c r="A99" s="30"/>
+      <c r="B99" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C99" s="27">
+      <c r="C99" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="29"/>
-      <c r="B100" s="25" t="str">
+      <c r="A100" s="30"/>
+      <c r="B100" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C100" s="27">
+      <c r="C100" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="29"/>
-      <c r="B101" s="25" t="str">
+      <c r="A101" s="30"/>
+      <c r="B101" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C101" s="27">
+      <c r="C101" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="29"/>
-      <c r="B102" s="25" t="str">
+      <c r="A102" s="30"/>
+      <c r="B102" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C102" s="27">
+      <c r="C102" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="29"/>
-      <c r="B103" s="25" t="str">
+      <c r="A103" s="30"/>
+      <c r="B103" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C103" s="27">
+      <c r="C103" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="29"/>
-      <c r="B104" s="25" t="str">
+      <c r="A104" s="30"/>
+      <c r="B104" s="26" t="str">
         <f t="shared" ref="B104:B114" si="1">IF(C104&gt;0,C104,"")</f>
         <v/>
       </c>
-      <c r="C104" s="27">
+      <c r="C104" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="29"/>
-      <c r="B105" s="25" t="str">
+      <c r="A105" s="30"/>
+      <c r="B105" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C105" s="27">
+      <c r="C105" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="29"/>
-      <c r="B106" s="25" t="str">
+      <c r="A106" s="30"/>
+      <c r="B106" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C106" s="27">
+      <c r="C106" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="29"/>
-      <c r="B107" s="25" t="str">
+      <c r="A107" s="30"/>
+      <c r="B107" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C107" s="27">
+      <c r="C107" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="29"/>
-      <c r="B108" s="25" t="str">
+      <c r="A108" s="30"/>
+      <c r="B108" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C108" s="27">
+      <c r="C108" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="29"/>
-      <c r="B109" s="25" t="str">
+      <c r="A109" s="30"/>
+      <c r="B109" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C109" s="27">
+      <c r="C109" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="29"/>
-      <c r="B110" s="25" t="str">
+      <c r="A110" s="30"/>
+      <c r="B110" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C110" s="27">
+      <c r="C110" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="29"/>
-      <c r="B111" s="25" t="str">
+      <c r="A111" s="30"/>
+      <c r="B111" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C111" s="27">
+      <c r="C111" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="29"/>
-      <c r="B112" s="25" t="str">
+      <c r="A112" s="30"/>
+      <c r="B112" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C112" s="27">
+      <c r="C112" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="29"/>
-      <c r="B113" s="25" t="str">
+      <c r="A113" s="30"/>
+      <c r="B113" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C113" s="27">
+      <c r="C113" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="29"/>
-      <c r="B114" s="25" t="str">
+      <c r="A114" s="30"/>
+      <c r="B114" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C114" s="27">
+      <c r="C114" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="29"/>
-      <c r="B115" s="29"/>
-      <c r="C115" s="27"/>
+      <c r="A115" s="30"/>
+      <c r="B115" s="30"/>
+      <c r="C115" s="28"/>
     </row>
     <row r="116">
-      <c r="A116" s="29"/>
-      <c r="B116" s="29"/>
-      <c r="C116" s="27"/>
+      <c r="A116" s="30"/>
+      <c r="B116" s="30"/>
+      <c r="C116" s="28"/>
     </row>
     <row r="117">
-      <c r="A117" s="29"/>
-      <c r="B117" s="29"/>
-      <c r="C117" s="27"/>
+      <c r="A117" s="30"/>
+      <c r="B117" s="30"/>
+      <c r="C117" s="28"/>
     </row>
     <row r="118">
-      <c r="A118" s="29"/>
-      <c r="B118" s="29"/>
-      <c r="C118" s="27"/>
+      <c r="A118" s="30"/>
+      <c r="B118" s="30"/>
+      <c r="C118" s="28"/>
     </row>
     <row r="119">
-      <c r="A119" s="29"/>
-      <c r="B119" s="29"/>
-      <c r="C119" s="27"/>
+      <c r="A119" s="30"/>
+      <c r="B119" s="30"/>
+      <c r="C119" s="28"/>
     </row>
     <row r="120">
-      <c r="A120" s="29"/>
-      <c r="B120" s="29"/>
-      <c r="C120" s="27"/>
+      <c r="A120" s="30"/>
+      <c r="B120" s="30"/>
+      <c r="C120" s="28"/>
     </row>
     <row r="121">
-      <c r="A121" s="29"/>
-      <c r="B121" s="29"/>
-      <c r="C121" s="27"/>
+      <c r="A121" s="30"/>
+      <c r="B121" s="30"/>
+      <c r="C121" s="28"/>
     </row>
     <row r="122">
-      <c r="A122" s="29"/>
-      <c r="B122" s="29"/>
-      <c r="C122" s="27"/>
+      <c r="A122" s="30"/>
+      <c r="B122" s="30"/>
+      <c r="C122" s="28"/>
     </row>
     <row r="123">
-      <c r="A123" s="29"/>
-      <c r="B123" s="29"/>
-      <c r="C123" s="27"/>
+      <c r="A123" s="30"/>
+      <c r="B123" s="30"/>
+      <c r="C123" s="28"/>
     </row>
     <row r="124">
-      <c r="A124" s="29"/>
-      <c r="B124" s="29"/>
-      <c r="C124" s="27"/>
+      <c r="A124" s="30"/>
+      <c r="B124" s="30"/>
+      <c r="C124" s="28"/>
     </row>
     <row r="125">
-      <c r="A125" s="29"/>
-      <c r="B125" s="29"/>
-      <c r="C125" s="27"/>
+      <c r="A125" s="30"/>
+      <c r="B125" s="30"/>
+      <c r="C125" s="28"/>
     </row>
     <row r="126">
-      <c r="A126" s="29"/>
-      <c r="B126" s="29"/>
-      <c r="C126" s="27"/>
+      <c r="A126" s="30"/>
+      <c r="B126" s="30"/>
+      <c r="C126" s="28"/>
     </row>
     <row r="127">
-      <c r="A127" s="29"/>
-      <c r="B127" s="29"/>
-      <c r="C127" s="27"/>
+      <c r="A127" s="30"/>
+      <c r="B127" s="30"/>
+      <c r="C127" s="28"/>
     </row>
     <row r="128">
-      <c r="A128" s="29"/>
-      <c r="B128" s="29"/>
-      <c r="C128" s="27"/>
+      <c r="A128" s="30"/>
+      <c r="B128" s="30"/>
+      <c r="C128" s="28"/>
     </row>
     <row r="129">
-      <c r="A129" s="29"/>
-      <c r="B129" s="29"/>
-      <c r="C129" s="27"/>
+      <c r="A129" s="30"/>
+      <c r="B129" s="30"/>
+      <c r="C129" s="28"/>
     </row>
     <row r="130">
-      <c r="A130" s="29"/>
-      <c r="B130" s="29"/>
-      <c r="C130" s="27"/>
+      <c r="A130" s="30"/>
+      <c r="B130" s="30"/>
+      <c r="C130" s="28"/>
     </row>
     <row r="131">
-      <c r="A131" s="29"/>
-      <c r="B131" s="29"/>
-      <c r="C131" s="27"/>
+      <c r="A131" s="30"/>
+      <c r="B131" s="30"/>
+      <c r="C131" s="28"/>
     </row>
     <row r="132">
-      <c r="A132" s="29"/>
-      <c r="B132" s="29"/>
-      <c r="C132" s="27"/>
+      <c r="A132" s="30"/>
+      <c r="B132" s="30"/>
+      <c r="C132" s="28"/>
     </row>
     <row r="133">
-      <c r="A133" s="29"/>
-      <c r="B133" s="29"/>
-      <c r="C133" s="27"/>
+      <c r="A133" s="30"/>
+      <c r="B133" s="30"/>
+      <c r="C133" s="28"/>
     </row>
     <row r="134">
-      <c r="A134" s="29"/>
-      <c r="B134" s="29"/>
-      <c r="C134" s="27"/>
+      <c r="A134" s="30"/>
+      <c r="B134" s="30"/>
+      <c r="C134" s="28"/>
     </row>
     <row r="135">
-      <c r="A135" s="29"/>
-      <c r="B135" s="29"/>
-      <c r="C135" s="27"/>
+      <c r="A135" s="30"/>
+      <c r="B135" s="30"/>
+      <c r="C135" s="28"/>
     </row>
     <row r="136">
-      <c r="A136" s="29"/>
-      <c r="B136" s="29"/>
-      <c r="C136" s="27"/>
+      <c r="A136" s="30"/>
+      <c r="B136" s="30"/>
+      <c r="C136" s="28"/>
     </row>
     <row r="137">
-      <c r="A137" s="29"/>
-      <c r="B137" s="29"/>
-      <c r="C137" s="27"/>
+      <c r="A137" s="30"/>
+      <c r="B137" s="30"/>
+      <c r="C137" s="28"/>
     </row>
     <row r="138">
-      <c r="A138" s="29"/>
-      <c r="B138" s="29"/>
-      <c r="C138" s="27"/>
+      <c r="A138" s="30"/>
+      <c r="B138" s="30"/>
+      <c r="C138" s="28"/>
     </row>
     <row r="139">
-      <c r="A139" s="29"/>
-      <c r="B139" s="29"/>
-      <c r="C139" s="27"/>
+      <c r="A139" s="30"/>
+      <c r="B139" s="30"/>
+      <c r="C139" s="28"/>
     </row>
     <row r="140">
-      <c r="A140" s="29"/>
-      <c r="B140" s="29"/>
-      <c r="C140" s="27"/>
+      <c r="A140" s="30"/>
+      <c r="B140" s="30"/>
+      <c r="C140" s="28"/>
     </row>
     <row r="141">
-      <c r="A141" s="29"/>
-      <c r="B141" s="29"/>
-      <c r="C141" s="27"/>
+      <c r="A141" s="30"/>
+      <c r="B141" s="30"/>
+      <c r="C141" s="28"/>
     </row>
     <row r="142">
-      <c r="A142" s="29"/>
-      <c r="B142" s="29"/>
-      <c r="C142" s="27"/>
+      <c r="A142" s="30"/>
+      <c r="B142" s="30"/>
+      <c r="C142" s="28"/>
     </row>
     <row r="143">
-      <c r="A143" s="29"/>
-      <c r="B143" s="29"/>
-      <c r="C143" s="27"/>
+      <c r="A143" s="30"/>
+      <c r="B143" s="30"/>
+      <c r="C143" s="28"/>
     </row>
     <row r="144">
-      <c r="A144" s="29"/>
-      <c r="B144" s="29"/>
-      <c r="C144" s="27"/>
+      <c r="A144" s="30"/>
+      <c r="B144" s="30"/>
+      <c r="C144" s="28"/>
     </row>
     <row r="145">
-      <c r="A145" s="29"/>
-      <c r="B145" s="29"/>
-      <c r="C145" s="27"/>
+      <c r="A145" s="30"/>
+      <c r="B145" s="30"/>
+      <c r="C145" s="28"/>
     </row>
     <row r="146">
-      <c r="A146" s="29"/>
-      <c r="B146" s="29"/>
-      <c r="C146" s="27"/>
+      <c r="A146" s="30"/>
+      <c r="B146" s="30"/>
+      <c r="C146" s="28"/>
     </row>
     <row r="147">
-      <c r="A147" s="29"/>
-      <c r="B147" s="29"/>
-      <c r="C147" s="27"/>
+      <c r="A147" s="30"/>
+      <c r="B147" s="30"/>
+      <c r="C147" s="28"/>
     </row>
     <row r="148">
-      <c r="A148" s="29"/>
-      <c r="B148" s="29"/>
-      <c r="C148" s="27"/>
+      <c r="A148" s="30"/>
+      <c r="B148" s="30"/>
+      <c r="C148" s="28"/>
     </row>
     <row r="149">
-      <c r="A149" s="29"/>
-      <c r="B149" s="29"/>
-      <c r="C149" s="27"/>
+      <c r="A149" s="30"/>
+      <c r="B149" s="30"/>
+      <c r="C149" s="28"/>
     </row>
     <row r="150">
-      <c r="A150" s="29"/>
-      <c r="B150" s="29"/>
-      <c r="C150" s="27"/>
+      <c r="A150" s="30"/>
+      <c r="B150" s="30"/>
+      <c r="C150" s="28"/>
     </row>
     <row r="151">
-      <c r="A151" s="29"/>
-      <c r="B151" s="29"/>
-      <c r="C151" s="27"/>
+      <c r="A151" s="30"/>
+      <c r="B151" s="30"/>
+      <c r="C151" s="28"/>
     </row>
     <row r="152">
-      <c r="A152" s="29"/>
-      <c r="B152" s="29"/>
-      <c r="C152" s="27"/>
+      <c r="A152" s="30"/>
+      <c r="B152" s="30"/>
+      <c r="C152" s="28"/>
     </row>
     <row r="153">
-      <c r="A153" s="29"/>
-      <c r="B153" s="29"/>
-      <c r="C153" s="27"/>
+      <c r="A153" s="30"/>
+      <c r="B153" s="30"/>
+      <c r="C153" s="28"/>
     </row>
     <row r="154">
-      <c r="A154" s="29"/>
-      <c r="B154" s="29"/>
-      <c r="C154" s="27"/>
+      <c r="A154" s="30"/>
+      <c r="B154" s="30"/>
+      <c r="C154" s="28"/>
     </row>
     <row r="155">
-      <c r="A155" s="29"/>
-      <c r="B155" s="29"/>
-      <c r="C155" s="27"/>
+      <c r="A155" s="30"/>
+      <c r="B155" s="30"/>
+      <c r="C155" s="28"/>
     </row>
     <row r="156">
-      <c r="A156" s="29"/>
-      <c r="B156" s="29"/>
-      <c r="C156" s="27"/>
+      <c r="A156" s="30"/>
+      <c r="B156" s="30"/>
+      <c r="C156" s="28"/>
     </row>
     <row r="157">
-      <c r="A157" s="29"/>
-      <c r="B157" s="29"/>
-      <c r="C157" s="27"/>
+      <c r="A157" s="30"/>
+      <c r="B157" s="30"/>
+      <c r="C157" s="28"/>
     </row>
     <row r="158">
-      <c r="A158" s="29"/>
-      <c r="B158" s="29"/>
-      <c r="C158" s="27"/>
+      <c r="A158" s="30"/>
+      <c r="B158" s="30"/>
+      <c r="C158" s="28"/>
     </row>
     <row r="159">
-      <c r="A159" s="29"/>
-      <c r="B159" s="29"/>
+      <c r="A159" s="30"/>
+      <c r="B159" s="30"/>
     </row>
     <row r="160">
-      <c r="A160" s="29"/>
-      <c r="B160" s="29"/>
+      <c r="A160" s="30"/>
+      <c r="B160" s="30"/>
     </row>
     <row r="161">
-      <c r="A161" s="29"/>
-      <c r="B161" s="29"/>
+      <c r="A161" s="30"/>
+      <c r="B161" s="30"/>
     </row>
     <row r="162">
-      <c r="A162" s="29"/>
-      <c r="B162" s="29"/>
+      <c r="A162" s="30"/>
+      <c r="B162" s="30"/>
     </row>
     <row r="163">
-      <c r="A163" s="29"/>
-      <c r="B163" s="29"/>
+      <c r="A163" s="30"/>
+      <c r="B163" s="30"/>
     </row>
     <row r="164">
-      <c r="A164" s="29"/>
-      <c r="B164" s="29"/>
+      <c r="A164" s="30"/>
+      <c r="B164" s="30"/>
     </row>
     <row r="165">
-      <c r="A165" s="29"/>
-      <c r="B165" s="29"/>
+      <c r="A165" s="30"/>
+      <c r="B165" s="30"/>
     </row>
     <row r="166">
-      <c r="A166" s="29"/>
-      <c r="B166" s="29"/>
+      <c r="A166" s="30"/>
+      <c r="B166" s="30"/>
     </row>
     <row r="167">
-      <c r="A167" s="29"/>
-      <c r="B167" s="29"/>
+      <c r="A167" s="30"/>
+      <c r="B167" s="30"/>
     </row>
     <row r="168">
-      <c r="A168" s="29"/>
-      <c r="B168" s="29"/>
+      <c r="A168" s="30"/>
+      <c r="B168" s="30"/>
     </row>
     <row r="169">
-      <c r="A169" s="29"/>
-      <c r="B169" s="29"/>
+      <c r="A169" s="30"/>
+      <c r="B169" s="30"/>
     </row>
     <row r="170">
-      <c r="A170" s="29"/>
-      <c r="B170" s="29"/>
+      <c r="A170" s="30"/>
+      <c r="B170" s="30"/>
     </row>
     <row r="171">
-      <c r="A171" s="29"/>
-      <c r="B171" s="29"/>
+      <c r="A171" s="30"/>
+      <c r="B171" s="30"/>
     </row>
     <row r="172">
-      <c r="A172" s="29"/>
-      <c r="B172" s="29"/>
+      <c r="A172" s="30"/>
+      <c r="B172" s="30"/>
     </row>
     <row r="173">
-      <c r="A173" s="29"/>
-      <c r="B173" s="29"/>
+      <c r="A173" s="30"/>
+      <c r="B173" s="30"/>
     </row>
     <row r="174">
-      <c r="A174" s="29"/>
-      <c r="B174" s="29"/>
+      <c r="A174" s="30"/>
+      <c r="B174" s="30"/>
     </row>
     <row r="175">
-      <c r="A175" s="29"/>
-      <c r="B175" s="29"/>
+      <c r="A175" s="30"/>
+      <c r="B175" s="30"/>
     </row>
     <row r="176">
-      <c r="A176" s="29"/>
-      <c r="B176" s="29"/>
+      <c r="A176" s="30"/>
+      <c r="B176" s="30"/>
     </row>
     <row r="177">
-      <c r="A177" s="29"/>
-      <c r="B177" s="29"/>
+      <c r="A177" s="30"/>
+      <c r="B177" s="30"/>
     </row>
     <row r="178">
-      <c r="A178" s="29"/>
-      <c r="B178" s="29"/>
+      <c r="A178" s="30"/>
+      <c r="B178" s="30"/>
     </row>
     <row r="179">
-      <c r="A179" s="29"/>
-      <c r="B179" s="29"/>
+      <c r="A179" s="30"/>
+      <c r="B179" s="30"/>
     </row>
     <row r="180">
-      <c r="A180" s="29"/>
-      <c r="B180" s="29"/>
+      <c r="A180" s="30"/>
+      <c r="B180" s="30"/>
     </row>
     <row r="181">
-      <c r="A181" s="29"/>
-      <c r="B181" s="29"/>
+      <c r="A181" s="30"/>
+      <c r="B181" s="30"/>
     </row>
     <row r="182">
-      <c r="A182" s="29"/>
-      <c r="B182" s="29"/>
+      <c r="A182" s="30"/>
+      <c r="B182" s="30"/>
     </row>
     <row r="183">
-      <c r="A183" s="29"/>
-      <c r="B183" s="29"/>
+      <c r="A183" s="30"/>
+      <c r="B183" s="30"/>
     </row>
     <row r="184">
-      <c r="A184" s="29"/>
-      <c r="B184" s="29"/>
+      <c r="A184" s="30"/>
+      <c r="B184" s="30"/>
     </row>
     <row r="185">
-      <c r="A185" s="29"/>
-      <c r="B185" s="29"/>
+      <c r="A185" s="30"/>
+      <c r="B185" s="30"/>
     </row>
     <row r="186">
-      <c r="A186" s="29"/>
-      <c r="B186" s="29"/>
+      <c r="A186" s="30"/>
+      <c r="B186" s="30"/>
     </row>
     <row r="187">
-      <c r="A187" s="29"/>
-      <c r="B187" s="29"/>
+      <c r="A187" s="30"/>
+      <c r="B187" s="30"/>
     </row>
     <row r="188">
-      <c r="A188" s="29"/>
-      <c r="B188" s="29"/>
+      <c r="A188" s="30"/>
+      <c r="B188" s="30"/>
     </row>
     <row r="189">
-      <c r="A189" s="29"/>
-      <c r="B189" s="29"/>
+      <c r="A189" s="30"/>
+      <c r="B189" s="30"/>
     </row>
     <row r="190">
-      <c r="A190" s="29"/>
-      <c r="B190" s="29"/>
+      <c r="A190" s="30"/>
+      <c r="B190" s="30"/>
     </row>
     <row r="191">
-      <c r="A191" s="29"/>
-      <c r="B191" s="29"/>
+      <c r="A191" s="30"/>
+      <c r="B191" s="30"/>
     </row>
     <row r="192">
-      <c r="A192" s="29"/>
-      <c r="B192" s="29"/>
+      <c r="A192" s="30"/>
+      <c r="B192" s="30"/>
     </row>
     <row r="193">
-      <c r="A193" s="29"/>
-      <c r="B193" s="29"/>
+      <c r="A193" s="30"/>
+      <c r="B193" s="30"/>
     </row>
     <row r="194">
-      <c r="A194" s="29"/>
-      <c r="B194" s="29"/>
+      <c r="A194" s="30"/>
+      <c r="B194" s="30"/>
     </row>
     <row r="195">
-      <c r="A195" s="29"/>
-      <c r="B195" s="29"/>
+      <c r="A195" s="30"/>
+      <c r="B195" s="30"/>
     </row>
     <row r="196">
-      <c r="A196" s="29"/>
-      <c r="B196" s="29"/>
+      <c r="A196" s="30"/>
+      <c r="B196" s="30"/>
     </row>
     <row r="197">
-      <c r="A197" s="29"/>
-      <c r="B197" s="29"/>
+      <c r="A197" s="30"/>
+      <c r="B197" s="30"/>
     </row>
     <row r="198">
-      <c r="A198" s="29"/>
-      <c r="B198" s="29"/>
+      <c r="A198" s="30"/>
+      <c r="B198" s="30"/>
     </row>
     <row r="199">
-      <c r="A199" s="29"/>
-      <c r="B199" s="29"/>
+      <c r="A199" s="30"/>
+      <c r="B199" s="30"/>
     </row>
     <row r="200">
-      <c r="A200" s="29"/>
-      <c r="B200" s="29"/>
+      <c r="A200" s="30"/>
+      <c r="B200" s="30"/>
     </row>
     <row r="201">
-      <c r="A201" s="29"/>
-      <c r="B201" s="29"/>
+      <c r="A201" s="30"/>
+      <c r="B201" s="30"/>
     </row>
     <row r="202">
-      <c r="A202" s="29"/>
-      <c r="B202" s="29"/>
+      <c r="A202" s="30"/>
+      <c r="B202" s="30"/>
     </row>
     <row r="203">
-      <c r="A203" s="29"/>
-      <c r="B203" s="29"/>
+      <c r="A203" s="30"/>
+      <c r="B203" s="30"/>
     </row>
     <row r="204">
-      <c r="A204" s="29"/>
-      <c r="B204" s="29"/>
+      <c r="A204" s="30"/>
+      <c r="B204" s="30"/>
     </row>
     <row r="205">
-      <c r="A205" s="29"/>
-      <c r="B205" s="29"/>
+      <c r="A205" s="30"/>
+      <c r="B205" s="30"/>
     </row>
     <row r="206">
-      <c r="A206" s="29"/>
-      <c r="B206" s="29"/>
+      <c r="A206" s="30"/>
+      <c r="B206" s="30"/>
     </row>
     <row r="207">
-      <c r="A207" s="29"/>
-      <c r="B207" s="29"/>
+      <c r="A207" s="30"/>
+      <c r="B207" s="30"/>
     </row>
     <row r="208">
-      <c r="A208" s="29"/>
-      <c r="B208" s="29"/>
+      <c r="A208" s="30"/>
+      <c r="B208" s="30"/>
     </row>
     <row r="209">
-      <c r="A209" s="29"/>
-      <c r="B209" s="29"/>
+      <c r="A209" s="30"/>
+      <c r="B209" s="30"/>
     </row>
     <row r="210">
-      <c r="A210" s="29"/>
-      <c r="B210" s="29"/>
+      <c r="A210" s="30"/>
+      <c r="B210" s="30"/>
     </row>
     <row r="211">
-      <c r="A211" s="29"/>
-      <c r="B211" s="29"/>
+      <c r="A211" s="30"/>
+      <c r="B211" s="30"/>
     </row>
     <row r="212">
-      <c r="A212" s="29"/>
-      <c r="B212" s="29"/>
+      <c r="A212" s="30"/>
+      <c r="B212" s="30"/>
     </row>
     <row r="213">
-      <c r="A213" s="29"/>
-      <c r="B213" s="29"/>
+      <c r="A213" s="30"/>
+      <c r="B213" s="30"/>
     </row>
     <row r="214">
-      <c r="A214" s="29"/>
-      <c r="B214" s="29"/>
+      <c r="A214" s="30"/>
+      <c r="B214" s="30"/>
     </row>
     <row r="215">
-      <c r="A215" s="29"/>
-      <c r="B215" s="29"/>
+      <c r="A215" s="30"/>
+      <c r="B215" s="30"/>
     </row>
     <row r="216">
-      <c r="A216" s="29"/>
-      <c r="B216" s="29"/>
+      <c r="A216" s="30"/>
+      <c r="B216" s="30"/>
     </row>
     <row r="217">
-      <c r="A217" s="29"/>
-      <c r="B217" s="29"/>
+      <c r="A217" s="30"/>
+      <c r="B217" s="30"/>
     </row>
     <row r="218">
-      <c r="A218" s="29"/>
-      <c r="B218" s="29"/>
+      <c r="A218" s="30"/>
+      <c r="B218" s="30"/>
     </row>
     <row r="219">
-      <c r="A219" s="29"/>
-      <c r="B219" s="29"/>
+      <c r="A219" s="30"/>
+      <c r="B219" s="30"/>
     </row>
     <row r="220">
-      <c r="A220" s="29"/>
-      <c r="B220" s="29"/>
+      <c r="A220" s="30"/>
+      <c r="B220" s="30"/>
     </row>
     <row r="221">
-      <c r="A221" s="29"/>
-      <c r="B221" s="29"/>
+      <c r="A221" s="30"/>
+      <c r="B221" s="30"/>
     </row>
     <row r="222">
-      <c r="A222" s="29"/>
-      <c r="B222" s="29"/>
+      <c r="A222" s="30"/>
+      <c r="B222" s="30"/>
     </row>
     <row r="223">
-      <c r="A223" s="29"/>
-      <c r="B223" s="29"/>
+      <c r="A223" s="30"/>
+      <c r="B223" s="30"/>
     </row>
     <row r="224">
-      <c r="A224" s="29"/>
-      <c r="B224" s="29"/>
+      <c r="A224" s="30"/>
+      <c r="B224" s="30"/>
     </row>
     <row r="225">
-      <c r="A225" s="29"/>
-      <c r="B225" s="29"/>
+      <c r="A225" s="30"/>
+      <c r="B225" s="30"/>
     </row>
     <row r="226">
-      <c r="A226" s="29"/>
-      <c r="B226" s="29"/>
+      <c r="A226" s="30"/>
+      <c r="B226" s="30"/>
     </row>
     <row r="227">
-      <c r="A227" s="29"/>
-      <c r="B227" s="29"/>
+      <c r="A227" s="30"/>
+      <c r="B227" s="30"/>
     </row>
     <row r="228">
-      <c r="A228" s="29"/>
-      <c r="B228" s="29"/>
+      <c r="A228" s="30"/>
+      <c r="B228" s="30"/>
     </row>
     <row r="229">
-      <c r="A229" s="29"/>
-      <c r="B229" s="29"/>
+      <c r="A229" s="30"/>
+      <c r="B229" s="30"/>
     </row>
     <row r="230">
-      <c r="A230" s="29"/>
-      <c r="B230" s="29"/>
+      <c r="A230" s="30"/>
+      <c r="B230" s="30"/>
     </row>
     <row r="231">
-      <c r="A231" s="29"/>
-      <c r="B231" s="29"/>
+      <c r="A231" s="30"/>
+      <c r="B231" s="30"/>
     </row>
     <row r="232">
-      <c r="A232" s="29"/>
-      <c r="B232" s="29"/>
+      <c r="A232" s="30"/>
+      <c r="B232" s="30"/>
     </row>
     <row r="233">
-      <c r="A233" s="29"/>
-      <c r="B233" s="29"/>
+      <c r="A233" s="30"/>
+      <c r="B233" s="30"/>
     </row>
     <row r="234">
-      <c r="A234" s="29"/>
-      <c r="B234" s="29"/>
+      <c r="A234" s="30"/>
+      <c r="B234" s="30"/>
     </row>
     <row r="235">
-      <c r="A235" s="29"/>
-      <c r="B235" s="29"/>
+      <c r="A235" s="30"/>
+      <c r="B235" s="30"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -7231,2034 +7245,2034 @@
     <col customWidth="1" min="2" max="2" width="4.33203125"/>
     <col bestFit="1" min="3" max="3" width="35.77734375"/>
     <col customWidth="1" min="4" max="11" width="3.44140625"/>
-    <col customWidth="1" min="12" max="12" style="30" width="6"/>
+    <col customWidth="1" min="12" max="12" style="31" width="6"/>
     <col customWidth="1" min="13" max="22" width="3.44140625"/>
-    <col customWidth="1" min="23" max="23" style="30" width="6"/>
+    <col customWidth="1" min="23" max="23" style="31" width="6"/>
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
-    <col customWidth="1" min="30" max="30" style="30" width="6"/>
+    <col customWidth="1" min="30" max="30" style="31" width="6"/>
     <col customWidth="1" min="31" max="39" width="3.44140625"/>
     <col bestFit="1" customWidth="1" min="40" max="40" width="13.88671875"/>
     <col customWidth="1" min="41" max="47" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="31" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="B1" s="32" t="s">
-        <v>91</v>
-      </c>
-      <c r="C1" s="33" t="s">
+    <row r="1" s="32" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="B1" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="C1" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="F1" s="35" t="s">
+      <c r="E1" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="G1" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="I1" s="34" t="s">
+      <c r="H1" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="I1" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="34" t="s">
+      <c r="J1" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="L1" s="38" t="s">
+      <c r="K1" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="M1" s="34" t="s">
+      <c r="L1" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="N1" s="36" t="s">
+      <c r="M1" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="N1" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="P1" s="34" t="s">
+      <c r="O1" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="P1" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="R1" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="S1" s="34" t="s">
+      <c r="Q1" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="R1" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="T1" s="34" t="s">
+      <c r="S1" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="U1" s="34" t="s">
+      <c r="T1" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="V1" s="36" t="s">
+      <c r="U1" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="W1" s="39" t="s">
+      <c r="V1" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="X1" s="34" t="s">
+      <c r="W1" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="Y1" s="34" t="s">
+      <c r="X1" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="Z1" s="36" t="s">
+      <c r="Y1" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="AA1" s="40" t="s">
+      <c r="Z1" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="AB1" s="41" t="s">
+      <c r="AA1" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="AC1" s="41" t="s">
+      <c r="AB1" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="AD1" s="38" t="s">
+      <c r="AC1" s="42" t="s">
         <v>111</v>
       </c>
-      <c r="AE1" s="42" t="s">
+      <c r="AD1" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="AF1" s="43" t="s">
+      <c r="AE1" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="AG1" s="44" t="s">
+      <c r="AF1" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="AH1" s="44" t="s">
+      <c r="AG1" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="AI1" s="44" t="s">
+      <c r="AH1" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="AJ1" s="44" t="s">
+      <c r="AI1" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="AK1" s="41" t="s">
+      <c r="AJ1" s="45" t="s">
         <v>118</v>
       </c>
-      <c r="AL1" s="45"/>
-      <c r="AM1" s="45"/>
-      <c r="AN1" s="45"/>
-      <c r="AO1" s="45"/>
-      <c r="AP1" s="45"/>
-      <c r="AQ1" s="45"/>
-      <c r="AR1" s="45"/>
-      <c r="AS1" s="45"/>
-      <c r="AT1" s="45"/>
-      <c r="AU1" s="45"/>
+      <c r="AK1" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="AL1" s="46"/>
+      <c r="AM1" s="46"/>
+      <c r="AN1" s="46"/>
+      <c r="AO1" s="46"/>
+      <c r="AP1" s="46"/>
+      <c r="AQ1" s="46"/>
+      <c r="AR1" s="46"/>
+      <c r="AS1" s="46"/>
+      <c r="AT1" s="46"/>
+      <c r="AU1" s="46"/>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="53"/>
-      <c r="W2" s="55"/>
-      <c r="X2" s="48"/>
-      <c r="Y2" s="48"/>
-      <c r="Z2" s="53"/>
-      <c r="AA2" s="54"/>
-      <c r="AB2" s="48"/>
-      <c r="AC2" s="48"/>
-      <c r="AD2" s="52"/>
-      <c r="AE2" s="53"/>
-      <c r="AF2" s="54"/>
-      <c r="AG2" s="48"/>
-      <c r="AH2" s="48"/>
-      <c r="AI2" s="48"/>
-      <c r="AJ2" s="48"/>
-      <c r="AK2" s="48"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/